--- a/database/BRENT.xlsx
+++ b/database/BRENT.xlsx
@@ -3881,10 +3881,10 @@
         <v>60.96</v>
       </c>
       <c r="E173" t="n">
-        <v>61.65</v>
+        <v>61.74</v>
       </c>
       <c r="F173" t="n">
-        <v>7745</v>
+        <v>7439</v>
       </c>
     </row>
     <row r="174">
@@ -3952,7 +3952,7 @@
         <v>43769</v>
       </c>
       <c r="B177" t="n">
-        <v>60.27</v>
+        <v>60.17</v>
       </c>
       <c r="C177" t="n">
         <v>60.79</v>
@@ -3964,7 +3964,7 @@
         <v>59.46</v>
       </c>
       <c r="F177" t="n">
-        <v>20603</v>
+        <v>20831</v>
       </c>
     </row>
     <row r="178">
@@ -3972,7 +3972,7 @@
         <v>43770</v>
       </c>
       <c r="B178" t="n">
-        <v>59.64</v>
+        <v>59.42</v>
       </c>
       <c r="C178" t="n">
         <v>61.8</v>
@@ -3984,7 +3984,7 @@
         <v>61.65</v>
       </c>
       <c r="F178" t="n">
-        <v>18281</v>
+        <v>18539</v>
       </c>
     </row>
     <row r="179">
@@ -4061,10 +4061,10 @@
         <v>61.63</v>
       </c>
       <c r="E182" t="n">
-        <v>62.29</v>
+        <v>62.14</v>
       </c>
       <c r="F182" t="n">
-        <v>19680</v>
+        <v>19306</v>
       </c>
     </row>
     <row r="183">
@@ -4081,10 +4081,10 @@
         <v>60.65</v>
       </c>
       <c r="E183" t="n">
-        <v>62.64</v>
+        <v>62.61</v>
       </c>
       <c r="F183" t="n">
-        <v>21863</v>
+        <v>21625</v>
       </c>
     </row>
     <row r="184">
@@ -4161,10 +4161,10 @@
         <v>62.14</v>
       </c>
       <c r="E187" t="n">
-        <v>62.33</v>
+        <v>62.38</v>
       </c>
       <c r="F187" t="n">
-        <v>19293</v>
+        <v>19157</v>
       </c>
     </row>
     <row r="188">
@@ -4181,10 +4181,10 @@
         <v>61.69</v>
       </c>
       <c r="E188" t="n">
-        <v>63.41</v>
+        <v>63.32</v>
       </c>
       <c r="F188" t="n">
-        <v>16092</v>
+        <v>15801</v>
       </c>
     </row>
     <row r="189">
@@ -4261,10 +4261,10 @@
         <v>61.91</v>
       </c>
       <c r="E192" t="n">
-        <v>63.64</v>
+        <v>63.74</v>
       </c>
       <c r="F192" t="n">
-        <v>21823</v>
+        <v>21582</v>
       </c>
     </row>
     <row r="193">
@@ -4281,10 +4281,10 @@
         <v>61.92</v>
       </c>
       <c r="E193" t="n">
-        <v>62.52</v>
+        <v>62.58</v>
       </c>
       <c r="F193" t="n">
-        <v>17794</v>
+        <v>17577</v>
       </c>
     </row>
     <row r="194">
@@ -4461,10 +4461,10 @@
         <v>62.73</v>
       </c>
       <c r="E202" t="n">
-        <v>63.26</v>
+        <v>63.33</v>
       </c>
       <c r="F202" t="n">
-        <v>24300</v>
+        <v>24042</v>
       </c>
     </row>
     <row r="203">
@@ -4481,10 +4481,10 @@
         <v>62.82</v>
       </c>
       <c r="E203" t="n">
-        <v>64.34</v>
+        <v>64.22</v>
       </c>
       <c r="F203" t="n">
-        <v>22572</v>
+        <v>22359</v>
       </c>
     </row>
     <row r="204">
@@ -4561,10 +4561,10 @@
         <v>63.86</v>
       </c>
       <c r="E207" t="n">
-        <v>64.28</v>
+        <v>64.31</v>
       </c>
       <c r="F207" t="n">
-        <v>18454</v>
+        <v>18198</v>
       </c>
     </row>
     <row r="208">
@@ -4581,10 +4581,10 @@
         <v>64.48</v>
       </c>
       <c r="E208" t="n">
-        <v>64.90000000000001</v>
+        <v>64.88</v>
       </c>
       <c r="F208" t="n">
-        <v>21671</v>
+        <v>21484</v>
       </c>
     </row>
     <row r="209">
@@ -4661,10 +4661,10 @@
         <v>66.02</v>
       </c>
       <c r="E212" t="n">
-        <v>66.53</v>
+        <v>66.45</v>
       </c>
       <c r="F212" t="n">
-        <v>11180</v>
+        <v>10932</v>
       </c>
     </row>
     <row r="213">
@@ -4681,10 +4681,10 @@
         <v>65.72</v>
       </c>
       <c r="E213" t="n">
-        <v>66.01000000000001</v>
+        <v>65.98</v>
       </c>
       <c r="F213" t="n">
-        <v>14806</v>
+        <v>14693</v>
       </c>
     </row>
     <row r="214">
@@ -4741,10 +4741,10 @@
         <v>66.09</v>
       </c>
       <c r="E216" t="n">
-        <v>66.75</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="F216" t="n">
-        <v>9613</v>
+        <v>9409</v>
       </c>
     </row>
     <row r="217">
@@ -4761,10 +4761,10 @@
         <v>66.34</v>
       </c>
       <c r="E217" t="n">
-        <v>66.84</v>
+        <v>66.81</v>
       </c>
       <c r="F217" t="n">
-        <v>11398</v>
+        <v>11272</v>
       </c>
     </row>
     <row r="218">
@@ -4821,10 +4821,10 @@
         <v>65.7</v>
       </c>
       <c r="E220" t="n">
-        <v>66.23</v>
+        <v>66.19</v>
       </c>
       <c r="F220" t="n">
-        <v>15351</v>
+        <v>15153</v>
       </c>
     </row>
     <row r="221">
@@ -4841,10 +4841,10 @@
         <v>66.19</v>
       </c>
       <c r="E221" t="n">
-        <v>68.59</v>
+        <v>68.55</v>
       </c>
       <c r="F221" t="n">
-        <v>35609</v>
+        <v>35427</v>
       </c>
     </row>
     <row r="222">
@@ -4924,7 +4924,7 @@
         <v>65.38</v>
       </c>
       <c r="F225" t="n">
-        <v>25951</v>
+        <v>25682</v>
       </c>
     </row>
     <row r="226">
@@ -4944,7 +4944,7 @@
         <v>65</v>
       </c>
       <c r="F226" t="n">
-        <v>20436</v>
+        <v>20016</v>
       </c>
     </row>
     <row r="227">
@@ -5021,10 +5021,10 @@
         <v>63.89</v>
       </c>
       <c r="E230" t="n">
-        <v>64.7</v>
+        <v>64.64</v>
       </c>
       <c r="F230" t="n">
-        <v>16472</v>
+        <v>16107</v>
       </c>
     </row>
     <row r="231">
@@ -5041,10 +5041,10 @@
         <v>64.45</v>
       </c>
       <c r="E231" t="n">
-        <v>65.08</v>
+        <v>64.95</v>
       </c>
       <c r="F231" t="n">
-        <v>16251</v>
+        <v>16060</v>
       </c>
     </row>
     <row r="232">
@@ -5121,10 +5121,10 @@
         <v>61.24</v>
       </c>
       <c r="E235" t="n">
-        <v>62.11</v>
+        <v>61.97</v>
       </c>
       <c r="F235" t="n">
-        <v>23208</v>
+        <v>22982</v>
       </c>
     </row>
     <row r="236">
@@ -5141,10 +5141,10 @@
         <v>60.24</v>
       </c>
       <c r="E236" t="n">
-        <v>60.64</v>
+        <v>60.82</v>
       </c>
       <c r="F236" t="n">
-        <v>21687</v>
+        <v>21411</v>
       </c>
     </row>
     <row r="237">
@@ -5221,10 +5221,10 @@
         <v>56.73</v>
       </c>
       <c r="E240" t="n">
-        <v>58.2</v>
+        <v>58.03</v>
       </c>
       <c r="F240" t="n">
-        <v>28894</v>
+        <v>28317</v>
       </c>
     </row>
     <row r="241">
@@ -5244,7 +5244,7 @@
         <v>56.63</v>
       </c>
       <c r="F241" t="n">
-        <v>31264</v>
+        <v>30854</v>
       </c>
     </row>
     <row r="242">
@@ -5321,10 +5321,10 @@
         <v>54.24</v>
       </c>
       <c r="E245" t="n">
-        <v>55.14</v>
+        <v>55.07</v>
       </c>
       <c r="F245" t="n">
-        <v>31917</v>
+        <v>31638</v>
       </c>
     </row>
     <row r="246">
@@ -5341,10 +5341,10 @@
         <v>54.2</v>
       </c>
       <c r="E246" t="n">
-        <v>54.45</v>
+        <v>54.48</v>
       </c>
       <c r="F246" t="n">
-        <v>26144</v>
+        <v>25828</v>
       </c>
     </row>
     <row r="247">
@@ -5421,10 +5421,10 @@
         <v>54.95</v>
       </c>
       <c r="E250" t="n">
-        <v>56.4</v>
+        <v>56.51</v>
       </c>
       <c r="F250" t="n">
-        <v>24914</v>
+        <v>24675</v>
       </c>
     </row>
     <row r="251">
@@ -5441,10 +5441,10 @@
         <v>56.13</v>
       </c>
       <c r="E251" t="n">
-        <v>57.33</v>
+        <v>57.32</v>
       </c>
       <c r="F251" t="n">
-        <v>21778</v>
+        <v>21410</v>
       </c>
     </row>
     <row r="252">
@@ -5521,10 +5521,10 @@
         <v>58.89</v>
       </c>
       <c r="E255" t="n">
-        <v>59.03</v>
+        <v>59.28</v>
       </c>
       <c r="F255" t="n">
-        <v>23391</v>
+        <v>23121</v>
       </c>
     </row>
     <row r="256">
@@ -5541,10 +5541,10 @@
         <v>57.71</v>
       </c>
       <c r="E256" t="n">
-        <v>58.44</v>
+        <v>58.33</v>
       </c>
       <c r="F256" t="n">
-        <v>26971</v>
+        <v>26663</v>
       </c>
     </row>
     <row r="257">
@@ -5621,10 +5621,10 @@
         <v>50.38</v>
       </c>
       <c r="E260" t="n">
-        <v>50.95</v>
+        <v>51.35</v>
       </c>
       <c r="F260" t="n">
-        <v>52807</v>
+        <v>51199</v>
       </c>
     </row>
     <row r="261">
@@ -5641,10 +5641,10 @@
         <v>48.92</v>
       </c>
       <c r="E261" t="n">
-        <v>50.08</v>
+        <v>50.01</v>
       </c>
       <c r="F261" t="n">
-        <v>72794</v>
+        <v>71739</v>
       </c>
     </row>
     <row r="262">
@@ -5721,10 +5721,10 @@
         <v>49.67</v>
       </c>
       <c r="E265" t="n">
-        <v>50</v>
+        <v>49.95</v>
       </c>
       <c r="F265" t="n">
-        <v>42678</v>
+        <v>42080</v>
       </c>
     </row>
     <row r="266">
@@ -5741,10 +5741,10 @@
         <v>45.16</v>
       </c>
       <c r="E266" t="n">
-        <v>45.51</v>
+        <v>45.55</v>
       </c>
       <c r="F266" t="n">
-        <v>65295</v>
+        <v>64437</v>
       </c>
     </row>
     <row r="267">
@@ -5812,7 +5812,7 @@
         <v>43902</v>
       </c>
       <c r="B270" t="n">
-        <v>36.29</v>
+        <v>35.97</v>
       </c>
       <c r="C270" t="n">
         <v>36.45</v>
@@ -5824,7 +5824,7 @@
         <v>33.49</v>
       </c>
       <c r="F270" t="n">
-        <v>64469</v>
+        <v>66181</v>
       </c>
     </row>
     <row r="271">
@@ -6121,10 +6121,10 @@
         <v>26.12</v>
       </c>
       <c r="E285" t="n">
-        <v>29.96</v>
+        <v>30.29</v>
       </c>
       <c r="F285" t="n">
-        <v>214756</v>
+        <v>210087</v>
       </c>
     </row>
     <row r="286">
@@ -6135,16 +6135,16 @@
         <v>29.95</v>
       </c>
       <c r="C286" t="n">
-        <v>35.28</v>
+        <v>35.24</v>
       </c>
       <c r="D286" t="n">
         <v>28.9</v>
       </c>
       <c r="E286" t="n">
-        <v>35.16</v>
+        <v>34.72</v>
       </c>
       <c r="F286" t="n">
-        <v>280402</v>
+        <v>275171</v>
       </c>
     </row>
     <row r="287">
@@ -6221,10 +6221,10 @@
         <v>32.46</v>
       </c>
       <c r="E290" t="n">
-        <v>32.8</v>
+        <v>33.2</v>
       </c>
       <c r="F290" t="n">
-        <v>236196</v>
+        <v>230614</v>
       </c>
     </row>
     <row r="291">
@@ -6321,10 +6321,10 @@
         <v>29.42</v>
       </c>
       <c r="E295" t="n">
-        <v>30.59</v>
+        <v>30.65</v>
       </c>
       <c r="F295" t="n">
-        <v>151526</v>
+        <v>146842</v>
       </c>
     </row>
     <row r="296">
@@ -6341,10 +6341,10 @@
         <v>30.13</v>
       </c>
       <c r="E296" t="n">
-        <v>30.68</v>
+        <v>30.78</v>
       </c>
       <c r="F296" t="n">
-        <v>174982</v>
+        <v>171223</v>
       </c>
     </row>
     <row r="297">
@@ -6421,10 +6421,10 @@
         <v>23.38</v>
       </c>
       <c r="E300" t="n">
-        <v>24.73</v>
+        <v>24.74</v>
       </c>
       <c r="F300" t="n">
-        <v>216653</v>
+        <v>213310</v>
       </c>
     </row>
     <row r="301">
@@ -6441,10 +6441,10 @@
         <v>23.7</v>
       </c>
       <c r="E301" t="n">
-        <v>24.99</v>
+        <v>24.98</v>
       </c>
       <c r="F301" t="n">
-        <v>166443</v>
+        <v>163124</v>
       </c>
     </row>
     <row r="302">
@@ -6521,10 +6521,10 @@
         <v>24.33</v>
       </c>
       <c r="E305" t="n">
-        <v>26.85</v>
+        <v>26.83</v>
       </c>
       <c r="F305" t="n">
-        <v>229615</v>
+        <v>224455</v>
       </c>
     </row>
     <row r="306">
@@ -6541,10 +6541,10 @@
         <v>26.05</v>
       </c>
       <c r="E306" t="n">
-        <v>26.81</v>
+        <v>26.78</v>
       </c>
       <c r="F306" t="n">
-        <v>199609</v>
+        <v>196748</v>
       </c>
     </row>
     <row r="307">
@@ -6621,10 +6621,10 @@
         <v>29.4</v>
       </c>
       <c r="E310" t="n">
-        <v>29.65</v>
+        <v>29.48</v>
       </c>
       <c r="F310" t="n">
-        <v>229585</v>
+        <v>225301</v>
       </c>
     </row>
     <row r="311">
@@ -6641,10 +6641,10 @@
         <v>29.63</v>
       </c>
       <c r="E311" t="n">
-        <v>31.25</v>
+        <v>31.26</v>
       </c>
       <c r="F311" t="n">
-        <v>195288</v>
+        <v>192233</v>
       </c>
     </row>
     <row r="312">
@@ -6715,16 +6715,16 @@
         <v>29.73</v>
       </c>
       <c r="C315" t="n">
-        <v>31.75</v>
+        <v>31.65</v>
       </c>
       <c r="D315" t="n">
         <v>29.32</v>
       </c>
       <c r="E315" t="n">
-        <v>31.58</v>
+        <v>31.44</v>
       </c>
       <c r="F315" t="n">
-        <v>156389</v>
+        <v>152193</v>
       </c>
     </row>
     <row r="316">
@@ -6735,16 +6735,16 @@
         <v>31.58</v>
       </c>
       <c r="C316" t="n">
-        <v>33.06</v>
+        <v>32.96</v>
       </c>
       <c r="D316" t="n">
         <v>31.23</v>
       </c>
       <c r="E316" t="n">
-        <v>32.94</v>
+        <v>32.9</v>
       </c>
       <c r="F316" t="n">
-        <v>163209</v>
+        <v>160121</v>
       </c>
     </row>
     <row r="317">
@@ -6821,10 +6821,10 @@
         <v>35.92</v>
       </c>
       <c r="E320" t="n">
-        <v>36.3</v>
+        <v>36.38</v>
       </c>
       <c r="F320" t="n">
-        <v>160329</v>
+        <v>157279</v>
       </c>
     </row>
     <row r="321">
@@ -6841,10 +6841,10 @@
         <v>33.87</v>
       </c>
       <c r="E321" t="n">
-        <v>35.52</v>
+        <v>35.66</v>
       </c>
       <c r="F321" t="n">
-        <v>198023</v>
+        <v>194062</v>
       </c>
     </row>
     <row r="322">
@@ -6921,10 +6921,10 @@
         <v>34.37</v>
       </c>
       <c r="E325" t="n">
-        <v>35.98</v>
+        <v>35.89</v>
       </c>
       <c r="F325" t="n">
-        <v>213086</v>
+        <v>208524</v>
       </c>
     </row>
     <row r="326">
@@ -6941,10 +6941,10 @@
         <v>34.87</v>
       </c>
       <c r="E326" t="n">
-        <v>37.61</v>
+        <v>37.43</v>
       </c>
       <c r="F326" t="n">
-        <v>198370</v>
+        <v>193664</v>
       </c>
     </row>
     <row r="327">
@@ -7021,10 +7021,10 @@
         <v>39.05</v>
       </c>
       <c r="E330" t="n">
-        <v>39.92</v>
+        <v>39.78</v>
       </c>
       <c r="F330" t="n">
-        <v>161661</v>
+        <v>158433</v>
       </c>
     </row>
     <row r="331">
@@ -7041,10 +7041,10 @@
         <v>39.75</v>
       </c>
       <c r="E331" t="n">
-        <v>41.83</v>
+        <v>42.14</v>
       </c>
       <c r="F331" t="n">
-        <v>167359</v>
+        <v>163467</v>
       </c>
     </row>
     <row r="332">
@@ -7121,10 +7121,10 @@
         <v>37.96</v>
       </c>
       <c r="E335" t="n">
-        <v>38.41</v>
+        <v>38.36</v>
       </c>
       <c r="F335" t="n">
-        <v>227925</v>
+        <v>221502</v>
       </c>
     </row>
     <row r="336">
@@ -7141,10 +7141,10 @@
         <v>37.14</v>
       </c>
       <c r="E336" t="n">
-        <v>38.97</v>
+        <v>38.94</v>
       </c>
       <c r="F336" t="n">
-        <v>263342</v>
+        <v>260674</v>
       </c>
     </row>
     <row r="337">
@@ -7221,10 +7221,10 @@
         <v>40.05</v>
       </c>
       <c r="E340" t="n">
-        <v>41.33</v>
+        <v>41.37</v>
       </c>
       <c r="F340" t="n">
-        <v>163774</v>
+        <v>161532</v>
       </c>
     </row>
     <row r="341">
@@ -7241,10 +7241,10 @@
         <v>40.97</v>
       </c>
       <c r="E341" t="n">
-        <v>41.78</v>
+        <v>41.99</v>
       </c>
       <c r="F341" t="n">
-        <v>156573</v>
+        <v>153177</v>
       </c>
     </row>
     <row r="342">
@@ -7315,16 +7315,16 @@
         <v>40.45</v>
       </c>
       <c r="C345" t="n">
-        <v>41.59</v>
+        <v>41.51</v>
       </c>
       <c r="D345" t="n">
         <v>39.68</v>
       </c>
       <c r="E345" t="n">
-        <v>41.35</v>
+        <v>41.39</v>
       </c>
       <c r="F345" t="n">
-        <v>181021</v>
+        <v>178413</v>
       </c>
     </row>
     <row r="346">
@@ -7341,10 +7341,10 @@
         <v>40.25</v>
       </c>
       <c r="E346" t="n">
-        <v>40.57</v>
+        <v>40.58</v>
       </c>
       <c r="F346" t="n">
-        <v>160433</v>
+        <v>157969</v>
       </c>
     </row>
     <row r="347">
@@ -7421,10 +7421,10 @@
         <v>41.71</v>
       </c>
       <c r="E350" t="n">
-        <v>42.65</v>
+        <v>42.71</v>
       </c>
       <c r="F350" t="n">
-        <v>144329</v>
+        <v>142409</v>
       </c>
     </row>
     <row r="351">
@@ -7521,10 +7521,10 @@
         <v>41.99</v>
       </c>
       <c r="E355" t="n">
-        <v>42.35</v>
+        <v>42.32</v>
       </c>
       <c r="F355" t="n">
-        <v>136451</v>
+        <v>133908</v>
       </c>
     </row>
     <row r="356">
@@ -7541,10 +7541,10 @@
         <v>41.4</v>
       </c>
       <c r="E356" t="n">
-        <v>43.26</v>
+        <v>43.23</v>
       </c>
       <c r="F356" t="n">
-        <v>154800</v>
+        <v>152491</v>
       </c>
     </row>
     <row r="357">
@@ -7621,10 +7621,10 @@
         <v>43.19</v>
       </c>
       <c r="E360" t="n">
-        <v>43.28</v>
+        <v>43.36</v>
       </c>
       <c r="F360" t="n">
-        <v>101544</v>
+        <v>99613</v>
       </c>
     </row>
     <row r="361">
@@ -7641,10 +7641,10 @@
         <v>42.7</v>
       </c>
       <c r="E361" t="n">
-        <v>43.12</v>
+        <v>43.18</v>
       </c>
       <c r="F361" t="n">
-        <v>95049</v>
+        <v>93740</v>
       </c>
     </row>
     <row r="362">
@@ -7721,10 +7721,10 @@
         <v>43.42</v>
       </c>
       <c r="E365" t="n">
-        <v>43.53</v>
+        <v>43.82</v>
       </c>
       <c r="F365" t="n">
-        <v>112495</v>
+        <v>109900</v>
       </c>
     </row>
     <row r="366">
@@ -7741,10 +7741,10 @@
         <v>43.18</v>
       </c>
       <c r="E366" t="n">
-        <v>43.62</v>
+        <v>43.67</v>
       </c>
       <c r="F366" t="n">
-        <v>117377</v>
+        <v>115737</v>
       </c>
     </row>
     <row r="367">
@@ -7821,10 +7821,10 @@
         <v>41.95</v>
       </c>
       <c r="E370" t="n">
-        <v>43.56</v>
+        <v>43.43</v>
       </c>
       <c r="F370" t="n">
-        <v>117072</v>
+        <v>113377</v>
       </c>
     </row>
     <row r="371">
@@ -7841,10 +7841,10 @@
         <v>42.94</v>
       </c>
       <c r="E371" t="n">
-        <v>43.59</v>
+        <v>43.65</v>
       </c>
       <c r="F371" t="n">
-        <v>128800</v>
+        <v>127155</v>
       </c>
     </row>
     <row r="372">
@@ -7921,10 +7921,10 @@
         <v>44.96</v>
       </c>
       <c r="E375" t="n">
-        <v>45.13</v>
+        <v>45.28</v>
       </c>
       <c r="F375" t="n">
-        <v>122044</v>
+        <v>120720</v>
       </c>
     </row>
     <row r="376">
@@ -7941,10 +7941,10 @@
         <v>44.4</v>
       </c>
       <c r="E376" t="n">
-        <v>44.71</v>
+        <v>44.76</v>
       </c>
       <c r="F376" t="n">
-        <v>120731</v>
+        <v>119541</v>
       </c>
     </row>
     <row r="377">
@@ -8021,10 +8021,10 @@
         <v>45.07</v>
       </c>
       <c r="E380" t="n">
-        <v>45.24</v>
+        <v>45.3</v>
       </c>
       <c r="F380" t="n">
-        <v>91702</v>
+        <v>90204</v>
       </c>
     </row>
     <row r="381">
@@ -8041,10 +8041,10 @@
         <v>44.77</v>
       </c>
       <c r="E381" t="n">
-        <v>45.19</v>
+        <v>45.2</v>
       </c>
       <c r="F381" t="n">
-        <v>85013</v>
+        <v>83793</v>
       </c>
     </row>
     <row r="382">
@@ -8121,10 +8121,10 @@
         <v>44.46</v>
       </c>
       <c r="E385" t="n">
-        <v>45.27</v>
+        <v>45.36</v>
       </c>
       <c r="F385" t="n">
-        <v>87294</v>
+        <v>86301</v>
       </c>
     </row>
     <row r="386">
@@ -8141,10 +8141,10 @@
         <v>44.09</v>
       </c>
       <c r="E386" t="n">
-        <v>44.69</v>
+        <v>44.79</v>
       </c>
       <c r="F386" t="n">
-        <v>78965</v>
+        <v>77659</v>
       </c>
     </row>
     <row r="387">
@@ -8224,7 +8224,7 @@
         <v>45.59</v>
       </c>
       <c r="F390" t="n">
-        <v>96916</v>
+        <v>95873</v>
       </c>
     </row>
     <row r="391">
@@ -8241,10 +8241,10 @@
         <v>45.36</v>
       </c>
       <c r="E391" t="n">
-        <v>45.85</v>
+        <v>45.89</v>
       </c>
       <c r="F391" t="n">
-        <v>81841</v>
+        <v>81058</v>
       </c>
     </row>
     <row r="392">
@@ -8321,10 +8321,10 @@
         <v>43.27</v>
       </c>
       <c r="E395" t="n">
-        <v>44.07</v>
+        <v>44.09</v>
       </c>
       <c r="F395" t="n">
-        <v>158723</v>
+        <v>157249</v>
       </c>
     </row>
     <row r="396">
@@ -8338,13 +8338,13 @@
         <v>44.69</v>
       </c>
       <c r="D396" t="n">
-        <v>42.42</v>
+        <v>42.45</v>
       </c>
       <c r="E396" t="n">
-        <v>42.43</v>
+        <v>42.53</v>
       </c>
       <c r="F396" t="n">
-        <v>162787</v>
+        <v>160902</v>
       </c>
     </row>
     <row r="397">
@@ -8418,13 +8418,13 @@
         <v>41.23</v>
       </c>
       <c r="D400" t="n">
-        <v>39.96</v>
+        <v>40.02</v>
       </c>
       <c r="E400" t="n">
-        <v>39.97</v>
+        <v>40.07</v>
       </c>
       <c r="F400" t="n">
-        <v>149451</v>
+        <v>147551</v>
       </c>
     </row>
     <row r="401">
@@ -8441,10 +8441,10 @@
         <v>39.68</v>
       </c>
       <c r="E401" t="n">
-        <v>40.02</v>
+        <v>40.24</v>
       </c>
       <c r="F401" t="n">
-        <v>135456</v>
+        <v>133943</v>
       </c>
     </row>
     <row r="402">
@@ -8521,10 +8521,10 @@
         <v>41.89</v>
       </c>
       <c r="E405" t="n">
-        <v>43.58</v>
+        <v>43.67</v>
       </c>
       <c r="F405" t="n">
-        <v>142611</v>
+        <v>141089</v>
       </c>
     </row>
     <row r="406">
@@ -8541,10 +8541,10 @@
         <v>42.92</v>
       </c>
       <c r="E406" t="n">
-        <v>43.41</v>
+        <v>43.34</v>
       </c>
       <c r="F406" t="n">
-        <v>129546</v>
+        <v>127380</v>
       </c>
     </row>
     <row r="407">
@@ -8621,10 +8621,10 @@
         <v>41.68</v>
       </c>
       <c r="E410" t="n">
-        <v>42.16</v>
+        <v>42.27</v>
       </c>
       <c r="F410" t="n">
-        <v>133961</v>
+        <v>132502</v>
       </c>
     </row>
     <row r="411">
@@ -8641,10 +8641,10 @@
         <v>41.97</v>
       </c>
       <c r="E411" t="n">
-        <v>42.17</v>
+        <v>42.24</v>
       </c>
       <c r="F411" t="n">
-        <v>102107</v>
+        <v>100264</v>
       </c>
     </row>
     <row r="412">
@@ -8721,10 +8721,10 @@
         <v>39.98</v>
       </c>
       <c r="E415" t="n">
-        <v>40.75</v>
+        <v>40.93</v>
       </c>
       <c r="F415" t="n">
-        <v>157712</v>
+        <v>155461</v>
       </c>
     </row>
     <row r="416">
@@ -8741,10 +8741,10 @@
         <v>38.88</v>
       </c>
       <c r="E416" t="n">
-        <v>39.15</v>
+        <v>39.23</v>
       </c>
       <c r="F416" t="n">
-        <v>190634</v>
+        <v>188336</v>
       </c>
     </row>
     <row r="417">
@@ -8821,10 +8821,10 @@
         <v>42.02</v>
       </c>
       <c r="E420" t="n">
-        <v>43.52</v>
+        <v>43.54</v>
       </c>
       <c r="F420" t="n">
-        <v>112342</v>
+        <v>110782</v>
       </c>
     </row>
     <row r="421">
@@ -8841,10 +8841,10 @@
         <v>42.78</v>
       </c>
       <c r="E421" t="n">
-        <v>42.89</v>
+        <v>42.96</v>
       </c>
       <c r="F421" t="n">
-        <v>109695</v>
+        <v>108274</v>
       </c>
     </row>
     <row r="422">
@@ -8921,10 +8921,10 @@
         <v>41.79</v>
       </c>
       <c r="E425" t="n">
-        <v>43.26</v>
+        <v>43.38</v>
       </c>
       <c r="F425" t="n">
-        <v>147757</v>
+        <v>146298</v>
       </c>
     </row>
     <row r="426">
@@ -8941,10 +8941,10 @@
         <v>42.47</v>
       </c>
       <c r="E426" t="n">
-        <v>42.95</v>
+        <v>43.02</v>
       </c>
       <c r="F426" t="n">
-        <v>130839</v>
+        <v>129338</v>
       </c>
     </row>
     <row r="427">
@@ -9021,10 +9021,10 @@
         <v>41.72</v>
       </c>
       <c r="E430" t="n">
-        <v>42.59</v>
+        <v>42.71</v>
       </c>
       <c r="F430" t="n">
-        <v>110171</v>
+        <v>108471</v>
       </c>
     </row>
     <row r="431">
@@ -9041,10 +9041,10 @@
         <v>41.76</v>
       </c>
       <c r="E431" t="n">
-        <v>41.85</v>
+        <v>41.93</v>
       </c>
       <c r="F431" t="n">
-        <v>97195</v>
+        <v>95688</v>
       </c>
     </row>
     <row r="432">
@@ -9112,7 +9112,7 @@
         <v>44133</v>
       </c>
       <c r="B435" t="n">
-        <v>39.76</v>
+        <v>39.52</v>
       </c>
       <c r="C435" t="n">
         <v>39.97</v>
@@ -9124,7 +9124,7 @@
         <v>38.05</v>
       </c>
       <c r="F435" t="n">
-        <v>179602</v>
+        <v>183949</v>
       </c>
     </row>
     <row r="436">
@@ -9132,7 +9132,7 @@
         <v>44134</v>
       </c>
       <c r="B436" t="n">
-        <v>38.25</v>
+        <v>38.05</v>
       </c>
       <c r="C436" t="n">
         <v>38.72</v>
@@ -9144,7 +9144,7 @@
         <v>37.84</v>
       </c>
       <c r="F436" t="n">
-        <v>181739</v>
+        <v>184633</v>
       </c>
     </row>
     <row r="437">
@@ -9221,10 +9221,10 @@
         <v>40.42</v>
       </c>
       <c r="E440" t="n">
-        <v>40.68</v>
+        <v>40.82</v>
       </c>
       <c r="F440" t="n">
-        <v>157779</v>
+        <v>155706</v>
       </c>
     </row>
     <row r="441">
@@ -9241,10 +9241,10 @@
         <v>39.46</v>
       </c>
       <c r="E441" t="n">
-        <v>39.71</v>
+        <v>39.84</v>
       </c>
       <c r="F441" t="n">
-        <v>151438</v>
+        <v>150078</v>
       </c>
     </row>
     <row r="442">
@@ -9318,13 +9318,13 @@
         <v>44.59</v>
       </c>
       <c r="D445" t="n">
-        <v>43.35</v>
+        <v>43.42</v>
       </c>
       <c r="E445" t="n">
-        <v>43.38</v>
+        <v>43.49</v>
       </c>
       <c r="F445" t="n">
-        <v>146964</v>
+        <v>144322</v>
       </c>
     </row>
     <row r="446">
@@ -9338,13 +9338,13 @@
         <v>43.45</v>
       </c>
       <c r="D446" t="n">
-        <v>42.68</v>
+        <v>42.77</v>
       </c>
       <c r="E446" t="n">
-        <v>42.69</v>
+        <v>42.88</v>
       </c>
       <c r="F446" t="n">
-        <v>114191</v>
+        <v>112789</v>
       </c>
     </row>
     <row r="447">
@@ -9421,10 +9421,10 @@
         <v>43.87</v>
       </c>
       <c r="E450" t="n">
-        <v>44.21</v>
+        <v>44.44</v>
       </c>
       <c r="F450" t="n">
-        <v>112468</v>
+        <v>111013</v>
       </c>
     </row>
     <row r="451">
@@ -9441,10 +9441,10 @@
         <v>44.15</v>
       </c>
       <c r="E451" t="n">
-        <v>45.07</v>
+        <v>45.06</v>
       </c>
       <c r="F451" t="n">
-        <v>90427</v>
+        <v>88612</v>
       </c>
     </row>
     <row r="452">
@@ -9624,7 +9624,7 @@
         <v>48.65</v>
       </c>
       <c r="F460" t="n">
-        <v>122403</v>
+        <v>119976</v>
       </c>
     </row>
     <row r="461">
@@ -9641,10 +9641,10 @@
         <v>48.77</v>
       </c>
       <c r="E461" t="n">
-        <v>48.96</v>
+        <v>48.97</v>
       </c>
       <c r="F461" t="n">
-        <v>125701</v>
+        <v>124413</v>
       </c>
     </row>
     <row r="462">
@@ -9721,10 +9721,10 @@
         <v>48.79</v>
       </c>
       <c r="E465" t="n">
-        <v>50.25</v>
+        <v>50.26</v>
       </c>
       <c r="F465" t="n">
-        <v>132386</v>
+        <v>130125</v>
       </c>
     </row>
     <row r="466">
@@ -9741,10 +9741,10 @@
         <v>49.67</v>
       </c>
       <c r="E466" t="n">
-        <v>49.86</v>
+        <v>49.94</v>
       </c>
       <c r="F466" t="n">
-        <v>124721</v>
+        <v>123293</v>
       </c>
     </row>
     <row r="467">
@@ -9821,10 +9821,10 @@
         <v>51.06</v>
       </c>
       <c r="E470" t="n">
-        <v>51.46</v>
+        <v>51.55</v>
       </c>
       <c r="F470" t="n">
-        <v>102867</v>
+        <v>100894</v>
       </c>
     </row>
     <row r="471">
@@ -9841,10 +9841,10 @@
         <v>51.16</v>
       </c>
       <c r="E471" t="n">
-        <v>52.23</v>
+        <v>52.19</v>
       </c>
       <c r="F471" t="n">
-        <v>98705</v>
+        <v>96861</v>
       </c>
     </row>
     <row r="472">
@@ -10081,10 +10081,10 @@
         <v>53.88</v>
       </c>
       <c r="E483" t="n">
-        <v>54.34</v>
+        <v>54.45</v>
       </c>
       <c r="F483" t="n">
-        <v>142258</v>
+        <v>140683</v>
       </c>
     </row>
     <row r="484">
@@ -10095,16 +10095,16 @@
         <v>54.46</v>
       </c>
       <c r="C484" t="n">
-        <v>56.2</v>
+        <v>56.06</v>
       </c>
       <c r="D484" t="n">
         <v>54.3</v>
       </c>
       <c r="E484" t="n">
-        <v>56.11</v>
+        <v>56.02</v>
       </c>
       <c r="F484" t="n">
-        <v>155413</v>
+        <v>151805</v>
       </c>
     </row>
     <row r="485">
@@ -10181,10 +10181,10 @@
         <v>55.21</v>
       </c>
       <c r="E488" t="n">
-        <v>56.37</v>
+        <v>56.3</v>
       </c>
       <c r="F488" t="n">
-        <v>125098</v>
+        <v>123090</v>
       </c>
     </row>
     <row r="489">
@@ -10201,10 +10201,10 @@
         <v>54.63</v>
       </c>
       <c r="E489" t="n">
-        <v>54.75</v>
+        <v>54.94</v>
       </c>
       <c r="F489" t="n">
-        <v>135898</v>
+        <v>133988</v>
       </c>
     </row>
     <row r="490">
@@ -10281,10 +10281,10 @@
         <v>55.38</v>
       </c>
       <c r="E493" t="n">
-        <v>55.84</v>
+        <v>55.86</v>
       </c>
       <c r="F493" t="n">
-        <v>104851</v>
+        <v>103188</v>
       </c>
     </row>
     <row r="494">
@@ -10301,10 +10301,10 @@
         <v>54.38</v>
       </c>
       <c r="E494" t="n">
-        <v>54.88</v>
+        <v>55.08</v>
       </c>
       <c r="F494" t="n">
-        <v>135622</v>
+        <v>133367</v>
       </c>
     </row>
     <row r="495">
@@ -10378,13 +10378,13 @@
         <v>56.16</v>
       </c>
       <c r="D498" t="n">
-        <v>54.84</v>
+        <v>54.93</v>
       </c>
       <c r="E498" t="n">
-        <v>54.84</v>
+        <v>55</v>
       </c>
       <c r="F498" t="n">
-        <v>162289</v>
+        <v>160473</v>
       </c>
     </row>
     <row r="499">
@@ -10401,10 +10401,10 @@
         <v>54.84</v>
       </c>
       <c r="E499" t="n">
-        <v>54.93</v>
+        <v>55</v>
       </c>
       <c r="F499" t="n">
-        <v>163671</v>
+        <v>160923</v>
       </c>
     </row>
     <row r="500">
@@ -10481,10 +10481,10 @@
         <v>57.93</v>
       </c>
       <c r="E503" t="n">
-        <v>58.87</v>
+        <v>58.79</v>
       </c>
       <c r="F503" t="n">
-        <v>125851</v>
+        <v>123567</v>
       </c>
     </row>
     <row r="504">
@@ -10501,10 +10501,10 @@
         <v>58.87</v>
       </c>
       <c r="E504" t="n">
-        <v>59.41</v>
+        <v>59.31</v>
       </c>
       <c r="F504" t="n">
-        <v>120954</v>
+        <v>118436</v>
       </c>
     </row>
     <row r="505">
@@ -10578,13 +10578,13 @@
         <v>61.23</v>
       </c>
       <c r="D508" t="n">
-        <v>60.44</v>
+        <v>60.5</v>
       </c>
       <c r="E508" t="n">
-        <v>60.52</v>
+        <v>60.6</v>
       </c>
       <c r="F508" t="n">
-        <v>107974</v>
+        <v>104511</v>
       </c>
     </row>
     <row r="509">
@@ -10604,7 +10604,7 @@
         <v>62.22</v>
       </c>
       <c r="F509" t="n">
-        <v>126905</v>
+        <v>123306</v>
       </c>
     </row>
     <row r="510">
@@ -10681,10 +10681,10 @@
         <v>62.54</v>
       </c>
       <c r="E513" t="n">
-        <v>62.88</v>
+        <v>62.75</v>
       </c>
       <c r="F513" t="n">
-        <v>173632</v>
+        <v>170306</v>
       </c>
     </row>
     <row r="514">
@@ -10701,10 +10701,10 @@
         <v>61.42</v>
       </c>
       <c r="E514" t="n">
-        <v>61.97</v>
+        <v>61.95</v>
       </c>
       <c r="F514" t="n">
-        <v>184306</v>
+        <v>181146</v>
       </c>
     </row>
     <row r="515">
@@ -10781,10 +10781,10 @@
         <v>65.55</v>
       </c>
       <c r="E518" t="n">
-        <v>65.97</v>
+        <v>65.86</v>
       </c>
       <c r="F518" t="n">
-        <v>215533</v>
+        <v>210726</v>
       </c>
     </row>
     <row r="519">
@@ -10801,10 +10801,10 @@
         <v>64.13</v>
       </c>
       <c r="E519" t="n">
-        <v>64.27</v>
+        <v>64.25</v>
       </c>
       <c r="F519" t="n">
-        <v>239274</v>
+        <v>234931</v>
       </c>
     </row>
     <row r="520">
@@ -10881,10 +10881,10 @@
         <v>63.17</v>
       </c>
       <c r="E523" t="n">
-        <v>66.73999999999999</v>
+        <v>66.94</v>
       </c>
       <c r="F523" t="n">
-        <v>230530</v>
+        <v>225843</v>
       </c>
     </row>
     <row r="524">
@@ -10895,16 +10895,16 @@
         <v>66.86</v>
       </c>
       <c r="C524" t="n">
-        <v>69.41</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="D524" t="n">
         <v>66.43000000000001</v>
       </c>
       <c r="E524" t="n">
-        <v>69.25</v>
+        <v>69.28</v>
       </c>
       <c r="F524" t="n">
-        <v>253026</v>
+        <v>249828</v>
       </c>
     </row>
     <row r="525">
@@ -10981,10 +10981,10 @@
         <v>67.68000000000001</v>
       </c>
       <c r="E528" t="n">
-        <v>69.17</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="F528" t="n">
-        <v>163581</v>
+        <v>160838</v>
       </c>
     </row>
     <row r="529">
@@ -11001,10 +11001,10 @@
         <v>68.66</v>
       </c>
       <c r="E529" t="n">
-        <v>68.81</v>
+        <v>68.88</v>
       </c>
       <c r="F529" t="n">
-        <v>151042</v>
+        <v>148823</v>
       </c>
     </row>
     <row r="530">
@@ -11072,7 +11072,7 @@
         <v>44273</v>
       </c>
       <c r="B533" t="n">
-        <v>67.47</v>
+        <v>67.48</v>
       </c>
       <c r="C533" t="n">
         <v>67.83</v>
@@ -11084,7 +11084,7 @@
         <v>62.5</v>
       </c>
       <c r="F533" t="n">
-        <v>209835</v>
+        <v>212082</v>
       </c>
     </row>
     <row r="534">
@@ -11092,7 +11092,7 @@
         <v>44274</v>
       </c>
       <c r="B534" t="n">
-        <v>63.02</v>
+        <v>62.78</v>
       </c>
       <c r="C534" t="n">
         <v>64.73</v>
@@ -11104,7 +11104,7 @@
         <v>64.31999999999999</v>
       </c>
       <c r="F534" t="n">
-        <v>223529</v>
+        <v>228148</v>
       </c>
     </row>
     <row r="535">
@@ -11172,10 +11172,10 @@
         <v>44280</v>
       </c>
       <c r="B538" t="n">
-        <v>63.89</v>
+        <v>63.95</v>
       </c>
       <c r="C538" t="n">
-        <v>63.9</v>
+        <v>64.01000000000001</v>
       </c>
       <c r="D538" t="n">
         <v>60.82</v>
@@ -11184,7 +11184,7 @@
         <v>61.47</v>
       </c>
       <c r="F538" t="n">
-        <v>203253</v>
+        <v>206155</v>
       </c>
     </row>
     <row r="539">
@@ -11192,19 +11192,19 @@
         <v>44281</v>
       </c>
       <c r="B539" t="n">
-        <v>62.45</v>
+        <v>61.47</v>
       </c>
       <c r="C539" t="n">
         <v>64.73</v>
       </c>
       <c r="D539" t="n">
-        <v>62.07</v>
+        <v>61.47</v>
       </c>
       <c r="E539" t="n">
         <v>64.19</v>
       </c>
       <c r="F539" t="n">
-        <v>167422</v>
+        <v>171041</v>
       </c>
     </row>
     <row r="540">
@@ -11284,7 +11284,7 @@
         <v>64.51000000000001</v>
       </c>
       <c r="F543" t="n">
-        <v>201289</v>
+        <v>197783</v>
       </c>
     </row>
     <row r="544">
@@ -11361,10 +11361,10 @@
         <v>62.18</v>
       </c>
       <c r="E547" t="n">
-        <v>63.04</v>
+        <v>63.07</v>
       </c>
       <c r="F547" t="n">
-        <v>149186</v>
+        <v>146277</v>
       </c>
     </row>
     <row r="548">
@@ -11381,10 +11381,10 @@
         <v>62.33</v>
       </c>
       <c r="E548" t="n">
-        <v>62.76</v>
+        <v>62.81</v>
       </c>
       <c r="F548" t="n">
-        <v>121247</v>
+        <v>119219</v>
       </c>
     </row>
     <row r="549">
@@ -11461,10 +11461,10 @@
         <v>65.65000000000001</v>
       </c>
       <c r="E552" t="n">
-        <v>66.45</v>
+        <v>66.5</v>
       </c>
       <c r="F552" t="n">
-        <v>135521</v>
+        <v>133306</v>
       </c>
     </row>
     <row r="553">
@@ -11481,10 +11481,10 @@
         <v>66.11</v>
       </c>
       <c r="E553" t="n">
-        <v>66.31999999999999</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="F553" t="n">
-        <v>122938</v>
+        <v>120895</v>
       </c>
     </row>
     <row r="554">
@@ -11564,7 +11564,7 @@
         <v>64.95</v>
       </c>
       <c r="F557" t="n">
-        <v>143350</v>
+        <v>140975</v>
       </c>
     </row>
     <row r="558">
@@ -11581,10 +11581,10 @@
         <v>64.52</v>
       </c>
       <c r="E558" t="n">
-        <v>65.31999999999999</v>
+        <v>65.45</v>
       </c>
       <c r="F558" t="n">
-        <v>126302</v>
+        <v>124432</v>
       </c>
     </row>
     <row r="559">
@@ -11661,10 +11661,10 @@
         <v>66.56</v>
       </c>
       <c r="E562" t="n">
-        <v>67.84999999999999</v>
+        <v>67.86</v>
       </c>
       <c r="F562" t="n">
-        <v>160482</v>
+        <v>157092</v>
       </c>
     </row>
     <row r="563">
@@ -11681,10 +11681,10 @@
         <v>66.17</v>
       </c>
       <c r="E563" t="n">
-        <v>66.53</v>
+        <v>66.56</v>
       </c>
       <c r="F563" t="n">
-        <v>148372</v>
+        <v>145779</v>
       </c>
     </row>
     <row r="564">
@@ -11761,10 +11761,10 @@
         <v>67.77</v>
       </c>
       <c r="E567" t="n">
-        <v>68.03</v>
+        <v>68.05</v>
       </c>
       <c r="F567" t="n">
-        <v>155507</v>
+        <v>153533</v>
       </c>
     </row>
     <row r="568">
@@ -11784,7 +11784,7 @@
         <v>68.03</v>
       </c>
       <c r="F568" t="n">
-        <v>139157</v>
+        <v>136012</v>
       </c>
     </row>
     <row r="569">
@@ -11861,10 +11861,10 @@
         <v>66.34</v>
       </c>
       <c r="E572" t="n">
-        <v>66.81999999999999</v>
+        <v>66.83</v>
       </c>
       <c r="F572" t="n">
-        <v>182316</v>
+        <v>180093</v>
       </c>
     </row>
     <row r="573">
@@ -11875,16 +11875,16 @@
         <v>66.81</v>
       </c>
       <c r="C573" t="n">
-        <v>68.63</v>
+        <v>68.52</v>
       </c>
       <c r="D573" t="n">
         <v>66.36</v>
       </c>
       <c r="E573" t="n">
-        <v>68.52</v>
+        <v>68.45</v>
       </c>
       <c r="F573" t="n">
-        <v>142226</v>
+        <v>139950</v>
       </c>
     </row>
     <row r="574">
@@ -11958,13 +11958,13 @@
         <v>67.02</v>
       </c>
       <c r="D577" t="n">
-        <v>64.70999999999999</v>
+        <v>64.73</v>
       </c>
       <c r="E577" t="n">
-        <v>64.73999999999999</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="F577" t="n">
-        <v>168733</v>
+        <v>164782</v>
       </c>
     </row>
     <row r="578">
@@ -11981,10 +11981,10 @@
         <v>64.48</v>
       </c>
       <c r="E578" t="n">
-        <v>66.51000000000001</v>
+        <v>66.58</v>
       </c>
       <c r="F578" t="n">
-        <v>156317</v>
+        <v>153693</v>
       </c>
     </row>
     <row r="579">
@@ -12055,16 +12055,16 @@
         <v>68.58</v>
       </c>
       <c r="C582" t="n">
-        <v>69.2</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="D582" t="n">
         <v>67.89</v>
       </c>
       <c r="E582" t="n">
-        <v>69.12</v>
+        <v>69.05</v>
       </c>
       <c r="F582" t="n">
-        <v>122427</v>
+        <v>119490</v>
       </c>
     </row>
     <row r="583">
@@ -12081,10 +12081,10 @@
         <v>68.48999999999999</v>
       </c>
       <c r="E583" t="n">
-        <v>68.88</v>
+        <v>68.89</v>
       </c>
       <c r="F583" t="n">
-        <v>121324</v>
+        <v>119218</v>
       </c>
     </row>
     <row r="584">
@@ -12161,10 +12161,10 @@
         <v>70.5</v>
       </c>
       <c r="E587" t="n">
-        <v>71.22</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="F587" t="n">
-        <v>128649</v>
+        <v>126247</v>
       </c>
     </row>
     <row r="588">
@@ -12181,10 +12181,10 @@
         <v>70.58</v>
       </c>
       <c r="E588" t="n">
-        <v>71.43000000000001</v>
+        <v>71.47</v>
       </c>
       <c r="F588" t="n">
-        <v>117041</v>
+        <v>113793</v>
       </c>
     </row>
     <row r="589">
@@ -12261,10 +12261,10 @@
         <v>70.66</v>
       </c>
       <c r="E592" t="n">
-        <v>71.95</v>
+        <v>72.09</v>
       </c>
       <c r="F592" t="n">
-        <v>148450</v>
+        <v>146487</v>
       </c>
     </row>
     <row r="593">
@@ -12284,7 +12284,7 @@
         <v>72.23999999999999</v>
       </c>
       <c r="F593" t="n">
-        <v>142367</v>
+        <v>140128</v>
       </c>
     </row>
     <row r="594">
@@ -12361,10 +12361,10 @@
         <v>71.41</v>
       </c>
       <c r="E597" t="n">
-        <v>72.44</v>
+        <v>72.45</v>
       </c>
       <c r="F597" t="n">
-        <v>178094</v>
+        <v>175025</v>
       </c>
     </row>
     <row r="598">
@@ -12381,10 +12381,10 @@
         <v>71.55</v>
       </c>
       <c r="E598" t="n">
-        <v>72.5</v>
+        <v>72.76000000000001</v>
       </c>
       <c r="F598" t="n">
-        <v>151345</v>
+        <v>147859</v>
       </c>
     </row>
     <row r="599">
@@ -12461,10 +12461,10 @@
         <v>73.83</v>
       </c>
       <c r="E602" t="n">
-        <v>74.81</v>
+        <v>74.79000000000001</v>
       </c>
       <c r="F602" t="n">
-        <v>85692</v>
+        <v>84577</v>
       </c>
     </row>
     <row r="603">
@@ -12481,10 +12481,10 @@
         <v>74.14</v>
       </c>
       <c r="E603" t="n">
-        <v>75.28</v>
+        <v>75.27</v>
       </c>
       <c r="F603" t="n">
-        <v>79112</v>
+        <v>77990</v>
       </c>
     </row>
     <row r="604">
@@ -12561,10 +12561,10 @@
         <v>74.36</v>
       </c>
       <c r="E607" t="n">
-        <v>75.34</v>
+        <v>75.33</v>
       </c>
       <c r="F607" t="n">
-        <v>135699</v>
+        <v>134296</v>
       </c>
     </row>
     <row r="608">
@@ -12581,10 +12581,10 @@
         <v>75</v>
       </c>
       <c r="E608" t="n">
-        <v>75.81999999999999</v>
+        <v>76.02</v>
       </c>
       <c r="F608" t="n">
-        <v>104256</v>
+        <v>102316</v>
       </c>
     </row>
     <row r="609">
@@ -12655,16 +12655,16 @@
         <v>72.97</v>
       </c>
       <c r="C612" t="n">
-        <v>74.02</v>
+        <v>73.97</v>
       </c>
       <c r="D612" t="n">
         <v>71.73999999999999</v>
       </c>
       <c r="E612" t="n">
-        <v>73.95999999999999</v>
+        <v>73.92</v>
       </c>
       <c r="F612" t="n">
-        <v>138030</v>
+        <v>136419</v>
       </c>
     </row>
     <row r="613">
@@ -12681,10 +12681,10 @@
         <v>73.38</v>
       </c>
       <c r="E613" t="n">
-        <v>75.14</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="F613" t="n">
-        <v>96988</v>
+        <v>95892</v>
       </c>
     </row>
     <row r="614">
@@ -12761,10 +12761,10 @@
         <v>72.70999999999999</v>
       </c>
       <c r="E617" t="n">
-        <v>72.72</v>
+        <v>72.79000000000001</v>
       </c>
       <c r="F617" t="n">
-        <v>134216</v>
+        <v>132350</v>
       </c>
     </row>
     <row r="618">
@@ -12781,10 +12781,10 @@
         <v>71.88</v>
       </c>
       <c r="E618" t="n">
-        <v>72.64</v>
+        <v>72.81</v>
       </c>
       <c r="F618" t="n">
-        <v>110158</v>
+        <v>108307</v>
       </c>
     </row>
     <row r="619">
@@ -12864,7 +12864,7 @@
         <v>73.01000000000001</v>
       </c>
       <c r="F622" t="n">
-        <v>115159</v>
+        <v>113951</v>
       </c>
     </row>
     <row r="623">
@@ -12875,16 +12875,16 @@
         <v>72.98</v>
       </c>
       <c r="C623" t="n">
-        <v>73.56999999999999</v>
+        <v>73.52</v>
       </c>
       <c r="D623" t="n">
         <v>72.70999999999999</v>
       </c>
       <c r="E623" t="n">
-        <v>73.5</v>
+        <v>73.44</v>
       </c>
       <c r="F623" t="n">
-        <v>84579</v>
+        <v>83411</v>
       </c>
     </row>
     <row r="624">
@@ -12961,10 +12961,10 @@
         <v>73.59999999999999</v>
       </c>
       <c r="E627" t="n">
-        <v>74.75</v>
+        <v>74.97</v>
       </c>
       <c r="F627" t="n">
-        <v>81467</v>
+        <v>79720</v>
       </c>
     </row>
     <row r="628">
@@ -12981,10 +12981,10 @@
         <v>74.26000000000001</v>
       </c>
       <c r="E628" t="n">
-        <v>74.95999999999999</v>
+        <v>74.98999999999999</v>
       </c>
       <c r="F628" t="n">
-        <v>84253</v>
+        <v>83101</v>
       </c>
     </row>
     <row r="629">
@@ -13061,10 +13061,10 @@
         <v>69.56</v>
       </c>
       <c r="E632" t="n">
-        <v>71</v>
+        <v>71.16</v>
       </c>
       <c r="F632" t="n">
-        <v>108267</v>
+        <v>107034</v>
       </c>
     </row>
     <row r="633">
@@ -13078,13 +13078,13 @@
         <v>72.22</v>
       </c>
       <c r="D633" t="n">
-        <v>70.06999999999999</v>
+        <v>70.12</v>
       </c>
       <c r="E633" t="n">
-        <v>70.08</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="F633" t="n">
-        <v>113105</v>
+        <v>111453</v>
       </c>
     </row>
     <row r="634">
@@ -13161,10 +13161,10 @@
         <v>70.41</v>
       </c>
       <c r="E637" t="n">
-        <v>70.86</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="F637" t="n">
-        <v>96203</v>
+        <v>95219</v>
       </c>
     </row>
     <row r="638">
@@ -13181,10 +13181,10 @@
         <v>69.73999999999999</v>
       </c>
       <c r="E638" t="n">
-        <v>69.90000000000001</v>
+        <v>69.92</v>
       </c>
       <c r="F638" t="n">
-        <v>95696</v>
+        <v>93960</v>
       </c>
     </row>
     <row r="639">
@@ -13261,10 +13261,10 @@
         <v>65.2</v>
       </c>
       <c r="E642" t="n">
-        <v>66.23</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="F642" t="n">
-        <v>187712</v>
+        <v>185678</v>
       </c>
     </row>
     <row r="643">
@@ -13278,13 +13278,13 @@
         <v>66.54000000000001</v>
       </c>
       <c r="D643" t="n">
-        <v>64.53</v>
+        <v>64.61</v>
       </c>
       <c r="E643" t="n">
-        <v>64.54000000000001</v>
+        <v>64.62</v>
       </c>
       <c r="F643" t="n">
-        <v>138989</v>
+        <v>137258</v>
       </c>
     </row>
     <row r="644">
@@ -13361,10 +13361,10 @@
         <v>69.73999999999999</v>
       </c>
       <c r="E647" t="n">
-        <v>70.45999999999999</v>
+        <v>70.56</v>
       </c>
       <c r="F647" t="n">
-        <v>115965</v>
+        <v>113839</v>
       </c>
     </row>
     <row r="648">
@@ -13381,10 +13381,10 @@
         <v>70.16</v>
       </c>
       <c r="E648" t="n">
-        <v>71.5</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="F648" t="n">
-        <v>100455</v>
+        <v>99158</v>
       </c>
     </row>
     <row r="649">
@@ -13461,10 +13461,10 @@
         <v>70.75</v>
       </c>
       <c r="E652" t="n">
-        <v>72.61</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="F652" t="n">
-        <v>105073</v>
+        <v>103772</v>
       </c>
     </row>
     <row r="653">
@@ -13481,10 +13481,10 @@
         <v>72.20999999999999</v>
       </c>
       <c r="E653" t="n">
-        <v>72.20999999999999</v>
+        <v>72.36</v>
       </c>
       <c r="F653" t="n">
-        <v>111688</v>
+        <v>110684</v>
       </c>
     </row>
     <row r="654">
@@ -13561,10 +13561,10 @@
         <v>70.54000000000001</v>
       </c>
       <c r="E657" t="n">
-        <v>70.84</v>
+        <v>70.95</v>
       </c>
       <c r="F657" t="n">
-        <v>138553</v>
+        <v>136836</v>
       </c>
     </row>
     <row r="658">
@@ -13581,10 +13581,10 @@
         <v>70.59</v>
       </c>
       <c r="E658" t="n">
-        <v>72.51000000000001</v>
+        <v>72.44</v>
       </c>
       <c r="F658" t="n">
-        <v>107925</v>
+        <v>106315</v>
       </c>
     </row>
     <row r="659">
@@ -13661,10 +13661,10 @@
         <v>74.02</v>
       </c>
       <c r="E662" t="n">
-        <v>75.09</v>
+        <v>75.17</v>
       </c>
       <c r="F662" t="n">
-        <v>136265</v>
+        <v>134873</v>
       </c>
     </row>
     <row r="663">
@@ -13681,10 +13681,10 @@
         <v>74.06999999999999</v>
       </c>
       <c r="E663" t="n">
-        <v>74.67</v>
+        <v>74.79000000000001</v>
       </c>
       <c r="F663" t="n">
-        <v>131243</v>
+        <v>129577</v>
       </c>
     </row>
     <row r="664">
@@ -13764,7 +13764,7 @@
         <v>76.45</v>
       </c>
       <c r="F667" t="n">
-        <v>104066</v>
+        <v>102612</v>
       </c>
     </row>
     <row r="668">
@@ -13781,10 +13781,10 @@
         <v>76.09</v>
       </c>
       <c r="E668" t="n">
-        <v>77.13</v>
+        <v>77.15000000000001</v>
       </c>
       <c r="F668" t="n">
-        <v>94529</v>
+        <v>93448</v>
       </c>
     </row>
     <row r="669">
@@ -13861,10 +13861,10 @@
         <v>76.37</v>
       </c>
       <c r="E672" t="n">
-        <v>78.23999999999999</v>
+        <v>78.13</v>
       </c>
       <c r="F672" t="n">
-        <v>181989</v>
+        <v>180155</v>
       </c>
     </row>
     <row r="673">
@@ -13881,10 +13881,10 @@
         <v>77.38</v>
       </c>
       <c r="E673" t="n">
-        <v>78.93000000000001</v>
+        <v>78.98999999999999</v>
       </c>
       <c r="F673" t="n">
-        <v>151482</v>
+        <v>149729</v>
       </c>
     </row>
     <row r="674">
@@ -13961,10 +13961,10 @@
         <v>78.78</v>
       </c>
       <c r="E677" t="n">
-        <v>82.08</v>
+        <v>82.16</v>
       </c>
       <c r="F677" t="n">
-        <v>153620</v>
+        <v>151677</v>
       </c>
     </row>
     <row r="678">
@@ -13981,10 +13981,10 @@
         <v>81.63</v>
       </c>
       <c r="E678" t="n">
-        <v>82.22</v>
+        <v>82.17</v>
       </c>
       <c r="F678" t="n">
-        <v>149526</v>
+        <v>147722</v>
       </c>
     </row>
     <row r="679">
@@ -14061,10 +14061,10 @@
         <v>82.76000000000001</v>
       </c>
       <c r="E682" t="n">
-        <v>83.67</v>
+        <v>83.69</v>
       </c>
       <c r="F682" t="n">
-        <v>122153</v>
+        <v>120650</v>
       </c>
     </row>
     <row r="683">
@@ -14081,10 +14081,10 @@
         <v>83.68000000000001</v>
       </c>
       <c r="E683" t="n">
-        <v>84.33</v>
+        <v>84.23</v>
       </c>
       <c r="F683" t="n">
-        <v>116437</v>
+        <v>114060</v>
       </c>
     </row>
     <row r="684">
@@ -14161,10 +14161,10 @@
         <v>82.73</v>
       </c>
       <c r="E687" t="n">
-        <v>84.09</v>
+        <v>84.15000000000001</v>
       </c>
       <c r="F687" t="n">
-        <v>122966</v>
+        <v>121250</v>
       </c>
     </row>
     <row r="688">
@@ -14175,16 +14175,16 @@
         <v>83.81999999999999</v>
       </c>
       <c r="C688" t="n">
-        <v>85.08</v>
+        <v>84.97</v>
       </c>
       <c r="D688" t="n">
         <v>83.18000000000001</v>
       </c>
       <c r="E688" t="n">
-        <v>84.83</v>
+        <v>84.97</v>
       </c>
       <c r="F688" t="n">
-        <v>113449</v>
+        <v>111475</v>
       </c>
     </row>
     <row r="689">
@@ -14261,10 +14261,10 @@
         <v>81.48</v>
       </c>
       <c r="E692" t="n">
-        <v>83.78</v>
+        <v>83.83</v>
       </c>
       <c r="F692" t="n">
-        <v>167007</v>
+        <v>164605</v>
       </c>
     </row>
     <row r="693">
@@ -14281,10 +14281,10 @@
         <v>82.39</v>
       </c>
       <c r="E693" t="n">
-        <v>83.41</v>
+        <v>83.55</v>
       </c>
       <c r="F693" t="n">
-        <v>133535</v>
+        <v>132228</v>
       </c>
     </row>
     <row r="694">
@@ -14352,7 +14352,7 @@
         <v>44504</v>
       </c>
       <c r="B697" t="n">
-        <v>80.83</v>
+        <v>81.12</v>
       </c>
       <c r="C697" t="n">
         <v>84.08</v>
@@ -14364,7 +14364,7 @@
         <v>80.54000000000001</v>
       </c>
       <c r="F697" t="n">
-        <v>168783</v>
+        <v>171378</v>
       </c>
     </row>
     <row r="698">
@@ -14372,7 +14372,7 @@
         <v>44505</v>
       </c>
       <c r="B698" t="n">
-        <v>81.04000000000001</v>
+        <v>80.95</v>
       </c>
       <c r="C698" t="n">
         <v>82.72</v>
@@ -14384,7 +14384,7 @@
         <v>81.93000000000001</v>
       </c>
       <c r="F698" t="n">
-        <v>163172</v>
+        <v>166390</v>
       </c>
     </row>
     <row r="699">
@@ -14461,10 +14461,10 @@
         <v>81.06</v>
       </c>
       <c r="E702" t="n">
-        <v>81.92</v>
+        <v>81.91</v>
       </c>
       <c r="F702" t="n">
-        <v>161511</v>
+        <v>159955</v>
       </c>
     </row>
     <row r="703">
@@ -14481,10 +14481,10 @@
         <v>80.63</v>
       </c>
       <c r="E703" t="n">
-        <v>81.29000000000001</v>
+        <v>81.41</v>
       </c>
       <c r="F703" t="n">
-        <v>134507</v>
+        <v>133196</v>
       </c>
     </row>
     <row r="704">
@@ -14561,10 +14561,10 @@
         <v>78.55</v>
       </c>
       <c r="E707" t="n">
-        <v>80.34999999999999</v>
+        <v>80.42</v>
       </c>
       <c r="F707" t="n">
-        <v>132952</v>
+        <v>131123</v>
       </c>
     </row>
     <row r="708">
@@ -14581,10 +14581,10 @@
         <v>77.41</v>
       </c>
       <c r="E708" t="n">
-        <v>77.77</v>
+        <v>77.76000000000001</v>
       </c>
       <c r="F708" t="n">
-        <v>177513</v>
+        <v>175625</v>
       </c>
     </row>
     <row r="709">
@@ -14761,10 +14761,10 @@
         <v>65.67</v>
       </c>
       <c r="E717" t="n">
-        <v>70.36</v>
+        <v>69.94</v>
       </c>
       <c r="F717" t="n">
-        <v>240359</v>
+        <v>237353</v>
       </c>
     </row>
     <row r="718">
@@ -14781,10 +14781,10 @@
         <v>69.09999999999999</v>
       </c>
       <c r="E718" t="n">
-        <v>69.70999999999999</v>
+        <v>69.73</v>
       </c>
       <c r="F718" t="n">
-        <v>208893</v>
+        <v>205214</v>
       </c>
     </row>
     <row r="719">
@@ -14858,13 +14858,13 @@
         <v>76.55</v>
       </c>
       <c r="D722" t="n">
-        <v>73.70999999999999</v>
+        <v>73.78</v>
       </c>
       <c r="E722" t="n">
-        <v>73.84999999999999</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="F722" t="n">
-        <v>142264</v>
+        <v>140659</v>
       </c>
     </row>
     <row r="723">
@@ -14881,10 +14881,10 @@
         <v>73.67</v>
       </c>
       <c r="E723" t="n">
-        <v>75.16</v>
+        <v>75.23</v>
       </c>
       <c r="F723" t="n">
-        <v>153301</v>
+        <v>151698</v>
       </c>
     </row>
     <row r="724">
@@ -14961,10 +14961,10 @@
         <v>73.88</v>
       </c>
       <c r="E727" t="n">
-        <v>74.48999999999999</v>
+        <v>74.63</v>
       </c>
       <c r="F727" t="n">
-        <v>142563</v>
+        <v>140474</v>
       </c>
     </row>
     <row r="728">
@@ -14981,10 +14981,10 @@
         <v>72.63</v>
       </c>
       <c r="E728" t="n">
-        <v>72.88</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="F728" t="n">
-        <v>154875</v>
+        <v>152160</v>
       </c>
     </row>
     <row r="729">
@@ -15061,10 +15061,10 @@
         <v>74.72</v>
       </c>
       <c r="E732" t="n">
-        <v>76.52</v>
+        <v>76.63</v>
       </c>
       <c r="F732" t="n">
-        <v>102802</v>
+        <v>100583</v>
       </c>
     </row>
     <row r="733">
@@ -15161,10 +15161,10 @@
         <v>78.33</v>
       </c>
       <c r="E737" t="n">
-        <v>78.86</v>
+        <v>78.97</v>
       </c>
       <c r="F737" t="n">
-        <v>105405</v>
+        <v>103669</v>
       </c>
     </row>
     <row r="738">
@@ -15261,10 +15261,10 @@
         <v>79.36</v>
       </c>
       <c r="E742" t="n">
-        <v>81.70999999999999</v>
+        <v>81.65000000000001</v>
       </c>
       <c r="F742" t="n">
-        <v>187943</v>
+        <v>185800</v>
       </c>
     </row>
     <row r="743">
@@ -15281,10 +15281,10 @@
         <v>81.12</v>
       </c>
       <c r="E743" t="n">
-        <v>81.48</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="F743" t="n">
-        <v>160491</v>
+        <v>158852</v>
       </c>
     </row>
     <row r="744">
@@ -15361,10 +15361,10 @@
         <v>83.34999999999999</v>
       </c>
       <c r="E747" t="n">
-        <v>83.61</v>
+        <v>83.45</v>
       </c>
       <c r="F747" t="n">
-        <v>147527</v>
+        <v>145171</v>
       </c>
     </row>
     <row r="748">
@@ -15375,16 +15375,16 @@
         <v>83.68000000000001</v>
       </c>
       <c r="C748" t="n">
-        <v>85.98999999999999</v>
+        <v>85.97</v>
       </c>
       <c r="D748" t="n">
         <v>83.53</v>
       </c>
       <c r="E748" t="n">
-        <v>85.77</v>
+        <v>85.91</v>
       </c>
       <c r="F748" t="n">
-        <v>173518</v>
+        <v>171152</v>
       </c>
     </row>
     <row r="749">
@@ -15458,13 +15458,13 @@
         <v>88.8</v>
       </c>
       <c r="D752" t="n">
-        <v>86.38</v>
+        <v>86.56999999999999</v>
       </c>
       <c r="E752" t="n">
-        <v>86.58</v>
+        <v>86.7</v>
       </c>
       <c r="F752" t="n">
-        <v>169439</v>
+        <v>162890</v>
       </c>
     </row>
     <row r="753">
@@ -15481,10 +15481,10 @@
         <v>85.02</v>
       </c>
       <c r="E753" t="n">
-        <v>86.92</v>
+        <v>86.98</v>
       </c>
       <c r="F753" t="n">
-        <v>225683</v>
+        <v>223066</v>
       </c>
     </row>
     <row r="754">
@@ -15561,10 +15561,10 @@
         <v>87.7</v>
       </c>
       <c r="E757" t="n">
-        <v>88.63</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="F757" t="n">
-        <v>275711</v>
+        <v>270152</v>
       </c>
     </row>
     <row r="758">
@@ -15581,10 +15581,10 @@
         <v>88</v>
       </c>
       <c r="E758" t="n">
-        <v>88.81999999999999</v>
+        <v>88.73</v>
       </c>
       <c r="F758" t="n">
-        <v>278896</v>
+        <v>275262</v>
       </c>
     </row>
     <row r="759">
@@ -15655,16 +15655,16 @@
         <v>88.63</v>
       </c>
       <c r="C762" t="n">
-        <v>90.84999999999999</v>
+        <v>90.73999999999999</v>
       </c>
       <c r="D762" t="n">
         <v>87.59999999999999</v>
       </c>
       <c r="E762" t="n">
-        <v>90.51000000000001</v>
+        <v>90.45999999999999</v>
       </c>
       <c r="F762" t="n">
-        <v>168353</v>
+        <v>163057</v>
       </c>
     </row>
     <row r="763">
@@ -15681,10 +15681,10 @@
         <v>90.67</v>
       </c>
       <c r="E763" t="n">
-        <v>92.14</v>
+        <v>92.54000000000001</v>
       </c>
       <c r="F763" t="n">
-        <v>180147</v>
+        <v>177219</v>
       </c>
     </row>
     <row r="764">
@@ -15761,10 +15761,10 @@
         <v>90.09999999999999</v>
       </c>
       <c r="E767" t="n">
-        <v>90.54000000000001</v>
+        <v>90.66</v>
       </c>
       <c r="F767" t="n">
-        <v>186180</v>
+        <v>183590</v>
       </c>
     </row>
     <row r="768">
@@ -15781,10 +15781,10 @@
         <v>89.66</v>
       </c>
       <c r="E768" t="n">
-        <v>93.8</v>
+        <v>93.81</v>
       </c>
       <c r="F768" t="n">
-        <v>194729</v>
+        <v>189880</v>
       </c>
     </row>
     <row r="769">
@@ -15861,10 +15861,10 @@
         <v>90.34999999999999</v>
       </c>
       <c r="E772" t="n">
-        <v>91.16</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="F772" t="n">
-        <v>212213</v>
+        <v>209775</v>
       </c>
     </row>
     <row r="773">
@@ -15875,7 +15875,7 @@
         <v>90.76000000000001</v>
       </c>
       <c r="C773" t="n">
-        <v>92.28</v>
+        <v>92.15000000000001</v>
       </c>
       <c r="D773" t="n">
         <v>88.64</v>
@@ -15884,7 +15884,7 @@
         <v>91.81</v>
       </c>
       <c r="F773" t="n">
-        <v>194995</v>
+        <v>190175</v>
       </c>
     </row>
     <row r="774">
@@ -15961,10 +15961,10 @@
         <v>93.94</v>
       </c>
       <c r="E777" t="n">
-        <v>95.41</v>
+        <v>95.61</v>
       </c>
       <c r="F777" t="n">
-        <v>313423</v>
+        <v>309076</v>
       </c>
     </row>
     <row r="778">
@@ -15981,10 +15981,10 @@
         <v>92.55</v>
       </c>
       <c r="E778" t="n">
-        <v>94.23</v>
+        <v>94.69</v>
       </c>
       <c r="F778" t="n">
-        <v>237786</v>
+        <v>233541</v>
       </c>
     </row>
     <row r="779">
@@ -16061,10 +16061,10 @@
         <v>108.17</v>
       </c>
       <c r="E782" t="n">
-        <v>109.27</v>
+        <v>109.72</v>
       </c>
       <c r="F782" t="n">
-        <v>233799</v>
+        <v>231064</v>
       </c>
     </row>
     <row r="783">
@@ -16081,10 +16081,10 @@
         <v>108.47</v>
       </c>
       <c r="E783" t="n">
-        <v>116.7</v>
+        <v>117.14</v>
       </c>
       <c r="F783" t="n">
-        <v>210974</v>
+        <v>204618</v>
       </c>
     </row>
     <row r="784">
@@ -16161,10 +16161,10 @@
         <v>107.05</v>
       </c>
       <c r="E787" t="n">
-        <v>107.11</v>
+        <v>107.97</v>
       </c>
       <c r="F787" t="n">
-        <v>173653</v>
+        <v>170481</v>
       </c>
     </row>
     <row r="788">
@@ -16181,10 +16181,10 @@
         <v>104.96</v>
       </c>
       <c r="E788" t="n">
-        <v>110.14</v>
+        <v>110.51</v>
       </c>
       <c r="F788" t="n">
-        <v>157669</v>
+        <v>154891</v>
       </c>
     </row>
     <row r="789">
@@ -16252,19 +16252,19 @@
         <v>44637</v>
       </c>
       <c r="B792" t="n">
-        <v>96.70999999999999</v>
+        <v>96.98</v>
       </c>
       <c r="C792" t="n">
         <v>105.3</v>
       </c>
       <c r="D792" t="n">
-        <v>96.70999999999999</v>
+        <v>96.11</v>
       </c>
       <c r="E792" t="n">
         <v>104.46</v>
       </c>
       <c r="F792" t="n">
-        <v>172578</v>
+        <v>176604</v>
       </c>
     </row>
     <row r="793">
@@ -16272,7 +16272,7 @@
         <v>44638</v>
       </c>
       <c r="B793" t="n">
-        <v>105.16</v>
+        <v>104.55</v>
       </c>
       <c r="C793" t="n">
         <v>107.23</v>
@@ -16284,7 +16284,7 @@
         <v>105.63</v>
       </c>
       <c r="F793" t="n">
-        <v>155067</v>
+        <v>158531</v>
       </c>
     </row>
     <row r="794">
@@ -16352,7 +16352,7 @@
         <v>44644</v>
       </c>
       <c r="B797" t="n">
-        <v>119.49</v>
+        <v>118.08</v>
       </c>
       <c r="C797" t="n">
         <v>120.04</v>
@@ -16364,7 +16364,7 @@
         <v>114.47</v>
       </c>
       <c r="F797" t="n">
-        <v>206598</v>
+        <v>215337</v>
       </c>
     </row>
     <row r="798">
@@ -16372,7 +16372,7 @@
         <v>44645</v>
       </c>
       <c r="B798" t="n">
-        <v>114.52</v>
+        <v>115.3</v>
       </c>
       <c r="C798" t="n">
         <v>117.69</v>
@@ -16384,7 +16384,7 @@
         <v>115.94</v>
       </c>
       <c r="F798" t="n">
-        <v>189095</v>
+        <v>195807</v>
       </c>
     </row>
     <row r="799">
@@ -16461,10 +16461,10 @@
         <v>103.71</v>
       </c>
       <c r="E802" t="n">
-        <v>104.99</v>
+        <v>104.6</v>
       </c>
       <c r="F802" t="n">
-        <v>220967</v>
+        <v>217472</v>
       </c>
     </row>
     <row r="803">
@@ -16481,10 +16481,10 @@
         <v>101.94</v>
       </c>
       <c r="E803" t="n">
-        <v>103.88</v>
+        <v>104.13</v>
       </c>
       <c r="F803" t="n">
-        <v>181758</v>
+        <v>179677</v>
       </c>
     </row>
     <row r="804">
@@ -16561,10 +16561,10 @@
         <v>98.2</v>
       </c>
       <c r="E807" t="n">
-        <v>100.96</v>
+        <v>100.94</v>
       </c>
       <c r="F807" t="n">
-        <v>186163</v>
+        <v>183922</v>
       </c>
     </row>
     <row r="808">
@@ -16581,10 +16581,10 @@
         <v>99.28</v>
       </c>
       <c r="E808" t="n">
-        <v>101.81</v>
+        <v>102.16</v>
       </c>
       <c r="F808" t="n">
-        <v>162819</v>
+        <v>159821</v>
       </c>
     </row>
     <row r="809">
@@ -16661,10 +16661,10 @@
         <v>106.14</v>
       </c>
       <c r="E812" t="n">
-        <v>110.62</v>
+        <v>110.56</v>
       </c>
       <c r="F812" t="n">
-        <v>159785</v>
+        <v>156524</v>
       </c>
     </row>
     <row r="813">
@@ -16741,10 +16741,10 @@
         <v>106.38</v>
       </c>
       <c r="E816" t="n">
-        <v>108</v>
+        <v>107.93</v>
       </c>
       <c r="F816" t="n">
-        <v>188001</v>
+        <v>184241</v>
       </c>
     </row>
     <row r="817">
@@ -16758,13 +16758,13 @@
         <v>108.41</v>
       </c>
       <c r="D817" t="n">
-        <v>105.05</v>
+        <v>105.44</v>
       </c>
       <c r="E817" t="n">
-        <v>105.7</v>
+        <v>105.6</v>
       </c>
       <c r="F817" t="n">
-        <v>165632</v>
+        <v>162032</v>
       </c>
     </row>
     <row r="818">
@@ -16841,10 +16841,10 @@
         <v>102.74</v>
       </c>
       <c r="E821" t="n">
-        <v>106.8</v>
+        <v>107.25</v>
       </c>
       <c r="F821" t="n">
-        <v>170514</v>
+        <v>167676</v>
       </c>
     </row>
     <row r="822">
@@ -16861,10 +16861,10 @@
         <v>105.92</v>
       </c>
       <c r="E822" t="n">
-        <v>106.06</v>
+        <v>106.38</v>
       </c>
       <c r="F822" t="n">
-        <v>186051</v>
+        <v>182972</v>
       </c>
     </row>
     <row r="823">
@@ -16941,10 +16941,10 @@
         <v>108.66</v>
       </c>
       <c r="E826" t="n">
-        <v>110.4</v>
+        <v>110.3</v>
       </c>
       <c r="F826" t="n">
-        <v>201234</v>
+        <v>197687</v>
       </c>
     </row>
     <row r="827">
@@ -16961,10 +16961,10 @@
         <v>109.21</v>
       </c>
       <c r="E827" t="n">
-        <v>112.22</v>
+        <v>112.44</v>
       </c>
       <c r="F827" t="n">
-        <v>207851</v>
+        <v>203469</v>
       </c>
     </row>
     <row r="828">
@@ -17041,10 +17041,10 @@
         <v>103.97</v>
       </c>
       <c r="E831" t="n">
-        <v>106.86</v>
+        <v>107.38</v>
       </c>
       <c r="F831" t="n">
-        <v>243371</v>
+        <v>240901</v>
       </c>
     </row>
     <row r="832">
@@ -17061,10 +17061,10 @@
         <v>106.88</v>
       </c>
       <c r="E832" t="n">
-        <v>109.76</v>
+        <v>110.4</v>
       </c>
       <c r="F832" t="n">
-        <v>193013</v>
+        <v>190398</v>
       </c>
     </row>
     <row r="833">
@@ -17141,10 +17141,10 @@
         <v>104.22</v>
       </c>
       <c r="E836" t="n">
-        <v>109.5</v>
+        <v>109.59</v>
       </c>
       <c r="F836" t="n">
-        <v>250583</v>
+        <v>247278</v>
       </c>
     </row>
     <row r="837">
@@ -17161,10 +17161,10 @@
         <v>108.65</v>
       </c>
       <c r="E837" t="n">
-        <v>110.3</v>
+        <v>110.87</v>
       </c>
       <c r="F837" t="n">
-        <v>202895</v>
+        <v>198948</v>
       </c>
     </row>
     <row r="838">
@@ -17241,10 +17241,10 @@
         <v>110.83</v>
       </c>
       <c r="E841" t="n">
-        <v>114.15</v>
+        <v>114</v>
       </c>
       <c r="F841" t="n">
-        <v>175003</v>
+        <v>171535</v>
       </c>
     </row>
     <row r="842">
@@ -17261,10 +17261,10 @@
         <v>113.01</v>
       </c>
       <c r="E842" t="n">
-        <v>115.01</v>
+        <v>115.42</v>
       </c>
       <c r="F842" t="n">
-        <v>213418</v>
+        <v>210750</v>
       </c>
     </row>
     <row r="843">
@@ -17335,16 +17335,16 @@
         <v>113.88</v>
       </c>
       <c r="C846" t="n">
-        <v>117.74</v>
+        <v>117.57</v>
       </c>
       <c r="D846" t="n">
         <v>111.85</v>
       </c>
       <c r="E846" t="n">
-        <v>117.31</v>
+        <v>117.26</v>
       </c>
       <c r="F846" t="n">
-        <v>138282</v>
+        <v>137013</v>
       </c>
     </row>
     <row r="847">
@@ -17355,16 +17355,16 @@
         <v>117.37</v>
       </c>
       <c r="C847" t="n">
-        <v>120.6</v>
+        <v>120.57</v>
       </c>
       <c r="D847" t="n">
         <v>115.28</v>
       </c>
       <c r="E847" t="n">
-        <v>120.23</v>
+        <v>120.41</v>
       </c>
       <c r="F847" t="n">
-        <v>91626</v>
+        <v>90339</v>
       </c>
     </row>
     <row r="848">
@@ -17441,10 +17441,10 @@
         <v>121.23</v>
       </c>
       <c r="E851" t="n">
-        <v>121.41</v>
+        <v>121.71</v>
       </c>
       <c r="F851" t="n">
-        <v>176648</v>
+        <v>174232</v>
       </c>
     </row>
     <row r="852">
@@ -17461,10 +17461,10 @@
         <v>118.31</v>
       </c>
       <c r="E852" t="n">
-        <v>120.02</v>
+        <v>120.29</v>
       </c>
       <c r="F852" t="n">
-        <v>192334</v>
+        <v>190410</v>
       </c>
     </row>
     <row r="853">
@@ -17541,10 +17541,10 @@
         <v>113.72</v>
       </c>
       <c r="E856" t="n">
-        <v>116.92</v>
+        <v>117.15</v>
       </c>
       <c r="F856" t="n">
-        <v>231324</v>
+        <v>228931</v>
       </c>
     </row>
     <row r="857">
@@ -17561,10 +17561,10 @@
         <v>109.77</v>
       </c>
       <c r="E857" t="n">
-        <v>111.27</v>
+        <v>111.29</v>
       </c>
       <c r="F857" t="n">
-        <v>236868</v>
+        <v>233588</v>
       </c>
     </row>
     <row r="858">
@@ -17641,10 +17641,10 @@
         <v>105.25</v>
       </c>
       <c r="E861" t="n">
-        <v>106.13</v>
+        <v>106.29</v>
       </c>
       <c r="F861" t="n">
-        <v>234952</v>
+        <v>233040</v>
       </c>
     </row>
     <row r="862">
@@ -17661,10 +17661,10 @@
         <v>105.78</v>
       </c>
       <c r="E862" t="n">
-        <v>108.33</v>
+        <v>109.13</v>
       </c>
       <c r="F862" t="n">
-        <v>205227</v>
+        <v>202836</v>
       </c>
     </row>
     <row r="863">
@@ -17741,10 +17741,10 @@
         <v>107.7</v>
       </c>
       <c r="E866" t="n">
-        <v>108.43</v>
+        <v>108.69</v>
       </c>
       <c r="F866" t="n">
-        <v>212070</v>
+        <v>208599</v>
       </c>
     </row>
     <row r="867">
@@ -17761,10 +17761,10 @@
         <v>107.32</v>
       </c>
       <c r="E867" t="n">
-        <v>110.43</v>
+        <v>110.56</v>
       </c>
       <c r="F867" t="n">
-        <v>210630</v>
+        <v>209195</v>
       </c>
     </row>
     <row r="868">
@@ -17841,10 +17841,10 @@
         <v>97.11</v>
       </c>
       <c r="E871" t="n">
-        <v>102.32</v>
+        <v>102.75</v>
       </c>
       <c r="F871" t="n">
-        <v>224620</v>
+        <v>221862</v>
       </c>
     </row>
     <row r="872">
@@ -17861,10 +17861,10 @@
         <v>102.16</v>
       </c>
       <c r="E872" t="n">
-        <v>105.2</v>
+        <v>105.32</v>
       </c>
       <c r="F872" t="n">
-        <v>237030</v>
+        <v>235167</v>
       </c>
     </row>
     <row r="873">
@@ -17941,10 +17941,10 @@
         <v>92.42</v>
       </c>
       <c r="E876" t="n">
-        <v>97.12</v>
+        <v>97.17</v>
       </c>
       <c r="F876" t="n">
-        <v>217836</v>
+        <v>215919</v>
       </c>
     </row>
     <row r="877">
@@ -17961,10 +17961,10 @@
         <v>95.59</v>
       </c>
       <c r="E877" t="n">
-        <v>97.98</v>
+        <v>98.34999999999999</v>
       </c>
       <c r="F877" t="n">
-        <v>203134</v>
+        <v>200270</v>
       </c>
     </row>
     <row r="878">
@@ -18041,10 +18041,10 @@
         <v>97.86</v>
       </c>
       <c r="E881" t="n">
-        <v>99.93000000000001</v>
+        <v>100.04</v>
       </c>
       <c r="F881" t="n">
-        <v>229298</v>
+        <v>227231</v>
       </c>
     </row>
     <row r="882">
@@ -18061,10 +18061,10 @@
         <v>97.90000000000001</v>
       </c>
       <c r="E882" t="n">
-        <v>98.98999999999999</v>
+        <v>98.67</v>
       </c>
       <c r="F882" t="n">
-        <v>226135</v>
+        <v>222921</v>
       </c>
     </row>
     <row r="883">
@@ -18141,10 +18141,10 @@
         <v>100.74</v>
       </c>
       <c r="E886" t="n">
-        <v>101.99</v>
+        <v>101.93</v>
       </c>
       <c r="F886" t="n">
-        <v>132446</v>
+        <v>130398</v>
       </c>
     </row>
     <row r="887">
@@ -18161,10 +18161,10 @@
         <v>101.27</v>
       </c>
       <c r="E887" t="n">
-        <v>103.1</v>
+        <v>103.21</v>
       </c>
       <c r="F887" t="n">
-        <v>113461</v>
+        <v>112179</v>
       </c>
     </row>
     <row r="888">
@@ -18238,13 +18238,13 @@
         <v>97.17</v>
       </c>
       <c r="D891" t="n">
-        <v>92.5</v>
+        <v>92.73</v>
       </c>
       <c r="E891" t="n">
-        <v>92.52</v>
+        <v>93.38</v>
       </c>
       <c r="F891" t="n">
-        <v>162676</v>
+        <v>160629</v>
       </c>
     </row>
     <row r="892">
@@ -18261,10 +18261,10 @@
         <v>92.15000000000001</v>
       </c>
       <c r="E892" t="n">
-        <v>93.51000000000001</v>
+        <v>93.69</v>
       </c>
       <c r="F892" t="n">
-        <v>157322</v>
+        <v>155701</v>
       </c>
     </row>
     <row r="893">
@@ -18341,10 +18341,10 @@
         <v>96.08</v>
       </c>
       <c r="E896" t="n">
-        <v>98.31</v>
+        <v>98.66</v>
       </c>
       <c r="F896" t="n">
-        <v>140818</v>
+        <v>139272</v>
       </c>
     </row>
     <row r="897">
@@ -18361,10 +18361,10 @@
         <v>96.26000000000001</v>
       </c>
       <c r="E897" t="n">
-        <v>96.89</v>
+        <v>97.3</v>
       </c>
       <c r="F897" t="n">
-        <v>145858</v>
+        <v>144235</v>
       </c>
     </row>
     <row r="898">
@@ -18441,10 +18441,10 @@
         <v>92.55</v>
       </c>
       <c r="E901" t="n">
-        <v>95.56</v>
+        <v>95.93000000000001</v>
       </c>
       <c r="F901" t="n">
-        <v>123861</v>
+        <v>122235</v>
       </c>
     </row>
     <row r="902">
@@ -18461,10 +18461,10 @@
         <v>93.7</v>
       </c>
       <c r="E902" t="n">
-        <v>95.08</v>
+        <v>95.52</v>
       </c>
       <c r="F902" t="n">
-        <v>126696</v>
+        <v>125387</v>
       </c>
     </row>
     <row r="903">
@@ -18541,10 +18541,10 @@
         <v>98.23</v>
       </c>
       <c r="E906" t="n">
-        <v>98.68000000000001</v>
+        <v>99.05</v>
       </c>
       <c r="F906" t="n">
-        <v>115830</v>
+        <v>114289</v>
       </c>
     </row>
     <row r="907">
@@ -18561,10 +18561,10 @@
         <v>96.92</v>
       </c>
       <c r="E907" t="n">
-        <v>98.56999999999999</v>
+        <v>98.70999999999999</v>
       </c>
       <c r="F907" t="n">
-        <v>128357</v>
+        <v>127109</v>
       </c>
     </row>
     <row r="908">
@@ -18641,10 +18641,10 @@
         <v>91.58</v>
       </c>
       <c r="E911" t="n">
-        <v>91.59</v>
+        <v>91.75</v>
       </c>
       <c r="F911" t="n">
-        <v>172611</v>
+        <v>171383</v>
       </c>
     </row>
     <row r="912">
@@ -18661,10 +18661,10 @@
         <v>92.41</v>
       </c>
       <c r="E912" t="n">
-        <v>92.83</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="F912" t="n">
-        <v>164349</v>
+        <v>162523</v>
       </c>
     </row>
     <row r="913">
@@ -18741,10 +18741,10 @@
         <v>86.86</v>
       </c>
       <c r="E916" t="n">
-        <v>87.73999999999999</v>
+        <v>88.03</v>
       </c>
       <c r="F916" t="n">
-        <v>175783</v>
+        <v>174104</v>
       </c>
     </row>
     <row r="917">
@@ -18761,10 +18761,10 @@
         <v>88.09</v>
       </c>
       <c r="E917" t="n">
-        <v>91.42</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="F917" t="n">
-        <v>139210</v>
+        <v>137562</v>
       </c>
     </row>
     <row r="918">
@@ -18841,10 +18841,10 @@
         <v>89.39</v>
       </c>
       <c r="E921" t="n">
-        <v>89.78</v>
+        <v>90.08</v>
       </c>
       <c r="F921" t="n">
-        <v>179533</v>
+        <v>177670</v>
       </c>
     </row>
     <row r="922">
@@ -18861,10 +18861,10 @@
         <v>89.37</v>
       </c>
       <c r="E922" t="n">
-        <v>90.36</v>
+        <v>90.58</v>
       </c>
       <c r="F922" t="n">
-        <v>177056</v>
+        <v>175462</v>
       </c>
     </row>
     <row r="923">
@@ -18941,10 +18941,10 @@
         <v>88.38</v>
       </c>
       <c r="E926" t="n">
-        <v>89.48999999999999</v>
+        <v>89.53</v>
       </c>
       <c r="F926" t="n">
-        <v>169282</v>
+        <v>167346</v>
       </c>
     </row>
     <row r="927">
@@ -18961,10 +18961,10 @@
         <v>84.61</v>
       </c>
       <c r="E927" t="n">
-        <v>85.65000000000001</v>
+        <v>85.41</v>
       </c>
       <c r="F927" t="n">
-        <v>159709</v>
+        <v>157358</v>
       </c>
     </row>
     <row r="928">
@@ -19041,10 +19041,10 @@
         <v>85.98</v>
       </c>
       <c r="E931" t="n">
-        <v>87.22</v>
+        <v>87.20999999999999</v>
       </c>
       <c r="F931" t="n">
-        <v>184095</v>
+        <v>182346</v>
       </c>
     </row>
     <row r="932">
@@ -19061,10 +19061,10 @@
         <v>84.73999999999999</v>
       </c>
       <c r="E932" t="n">
-        <v>85.04000000000001</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="F932" t="n">
-        <v>174184</v>
+        <v>172540</v>
       </c>
     </row>
     <row r="933">
@@ -19141,10 +19141,10 @@
         <v>92.09</v>
       </c>
       <c r="E936" t="n">
-        <v>94.16</v>
+        <v>94.31999999999999</v>
       </c>
       <c r="F936" t="n">
-        <v>136157</v>
+        <v>134269</v>
       </c>
     </row>
     <row r="937">
@@ -19161,10 +19161,10 @@
         <v>93.25</v>
       </c>
       <c r="E937" t="n">
-        <v>97.59</v>
+        <v>96.95</v>
       </c>
       <c r="F937" t="n">
-        <v>161145</v>
+        <v>158303</v>
       </c>
     </row>
     <row r="938">
@@ -19241,10 +19241,10 @@
         <v>90.18000000000001</v>
       </c>
       <c r="E941" t="n">
-        <v>93.67</v>
+        <v>93.61</v>
       </c>
       <c r="F941" t="n">
-        <v>189909</v>
+        <v>187899</v>
       </c>
     </row>
     <row r="942">
@@ -19261,10 +19261,10 @@
         <v>90.34</v>
       </c>
       <c r="E942" t="n">
-        <v>90.66</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="F942" t="n">
-        <v>186342</v>
+        <v>184164</v>
       </c>
     </row>
     <row r="943">
@@ -19341,10 +19341,10 @@
         <v>90.34</v>
       </c>
       <c r="E946" t="n">
-        <v>91.11</v>
+        <v>91</v>
       </c>
       <c r="F946" t="n">
-        <v>172151</v>
+        <v>169394</v>
       </c>
     </row>
     <row r="947">
@@ -19361,10 +19361,10 @@
         <v>89.40000000000001</v>
       </c>
       <c r="E947" t="n">
-        <v>91.58</v>
+        <v>91.7</v>
       </c>
       <c r="F947" t="n">
-        <v>170499</v>
+        <v>168937</v>
       </c>
     </row>
     <row r="948">
@@ -19441,10 +19441,10 @@
         <v>93.06999999999999</v>
       </c>
       <c r="E951" t="n">
-        <v>94.45999999999999</v>
+        <v>94.91</v>
       </c>
       <c r="F951" t="n">
-        <v>135151</v>
+        <v>130846</v>
       </c>
     </row>
     <row r="952">
@@ -19461,10 +19461,10 @@
         <v>92.81999999999999</v>
       </c>
       <c r="E952" t="n">
-        <v>93.95</v>
+        <v>93.81</v>
       </c>
       <c r="F952" t="n">
-        <v>135363</v>
+        <v>133960</v>
       </c>
     </row>
     <row r="953">
@@ -19532,7 +19532,7 @@
         <v>44868</v>
       </c>
       <c r="B956" t="n">
-        <v>94.84</v>
+        <v>94.81</v>
       </c>
       <c r="C956" t="n">
         <v>95.45</v>
@@ -19544,7 +19544,7 @@
         <v>93.92</v>
       </c>
       <c r="F956" t="n">
-        <v>141621</v>
+        <v>143503</v>
       </c>
     </row>
     <row r="957">
@@ -19552,19 +19552,19 @@
         <v>44869</v>
       </c>
       <c r="B957" t="n">
-        <v>93.94</v>
+        <v>93.98</v>
       </c>
       <c r="C957" t="n">
         <v>98.23999999999999</v>
       </c>
       <c r="D957" t="n">
-        <v>93.94</v>
+        <v>93.76000000000001</v>
       </c>
       <c r="E957" t="n">
         <v>98.01000000000001</v>
       </c>
       <c r="F957" t="n">
-        <v>179958</v>
+        <v>182009</v>
       </c>
     </row>
     <row r="958">
@@ -19641,10 +19641,10 @@
         <v>90.97</v>
       </c>
       <c r="E961" t="n">
-        <v>92.47</v>
+        <v>92.69</v>
       </c>
       <c r="F961" t="n">
-        <v>170823</v>
+        <v>168690</v>
       </c>
     </row>
     <row r="962">
@@ -19661,10 +19661,10 @@
         <v>92.79000000000001</v>
       </c>
       <c r="E962" t="n">
-        <v>94.95999999999999</v>
+        <v>95.04000000000001</v>
       </c>
       <c r="F962" t="n">
-        <v>165782</v>
+        <v>163940</v>
       </c>
     </row>
     <row r="963">
@@ -19741,10 +19741,10 @@
         <v>88.72</v>
       </c>
       <c r="E966" t="n">
-        <v>89.34999999999999</v>
+        <v>89.28</v>
       </c>
       <c r="F966" t="n">
-        <v>159560</v>
+        <v>157265</v>
       </c>
     </row>
     <row r="967">
@@ -19761,10 +19761,10 @@
         <v>85.41</v>
       </c>
       <c r="E967" t="n">
-        <v>87.5</v>
+        <v>87.45</v>
       </c>
       <c r="F967" t="n">
-        <v>162655</v>
+        <v>160818</v>
       </c>
     </row>
     <row r="968">
@@ -19941,10 +19941,10 @@
         <v>86.26000000000001</v>
       </c>
       <c r="E976" t="n">
-        <v>86.98</v>
+        <v>86.84</v>
       </c>
       <c r="F976" t="n">
-        <v>136930</v>
+        <v>135345</v>
       </c>
     </row>
     <row r="977">
@@ -19961,10 +19961,10 @@
         <v>85.17</v>
       </c>
       <c r="E977" t="n">
-        <v>85.90000000000001</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="F977" t="n">
-        <v>137359</v>
+        <v>135815</v>
       </c>
     </row>
     <row r="978">
@@ -20041,10 +20041,10 @@
         <v>75.92</v>
       </c>
       <c r="E981" t="n">
-        <v>76.61</v>
+        <v>76.27</v>
       </c>
       <c r="F981" t="n">
-        <v>167594</v>
+        <v>165742</v>
       </c>
     </row>
     <row r="982">
@@ -20061,10 +20061,10 @@
         <v>75.34999999999999</v>
       </c>
       <c r="E982" t="n">
-        <v>76.79000000000001</v>
+        <v>76.76000000000001</v>
       </c>
       <c r="F982" t="n">
-        <v>153224</v>
+        <v>151706</v>
       </c>
     </row>
     <row r="983">
@@ -20141,10 +20141,10 @@
         <v>80.86</v>
       </c>
       <c r="E986" t="n">
-        <v>81.54000000000001</v>
+        <v>81.39</v>
       </c>
       <c r="F986" t="n">
-        <v>151489</v>
+        <v>149384</v>
       </c>
     </row>
     <row r="987">
@@ -20161,10 +20161,10 @@
         <v>78.61</v>
       </c>
       <c r="E987" t="n">
-        <v>79.44</v>
+        <v>79.36</v>
       </c>
       <c r="F987" t="n">
-        <v>151197</v>
+        <v>149990</v>
       </c>
     </row>
     <row r="988">
@@ -20241,10 +20241,10 @@
         <v>81.28</v>
       </c>
       <c r="E991" t="n">
-        <v>82.20999999999999</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="F991" t="n">
-        <v>95617</v>
+        <v>94348</v>
       </c>
     </row>
     <row r="992">
@@ -20321,10 +20321,10 @@
         <v>81.81999999999999</v>
       </c>
       <c r="E995" t="n">
-        <v>83.63</v>
+        <v>83.68000000000001</v>
       </c>
       <c r="F995" t="n">
-        <v>110699</v>
+        <v>109380</v>
       </c>
     </row>
     <row r="996">
@@ -20401,10 +20401,10 @@
         <v>77.63</v>
       </c>
       <c r="E999" t="n">
-        <v>78.8</v>
+        <v>78.68000000000001</v>
       </c>
       <c r="F999" t="n">
-        <v>150672</v>
+        <v>149266</v>
       </c>
     </row>
     <row r="1000">
@@ -20424,7 +20424,7 @@
         <v>78.51000000000001</v>
       </c>
       <c r="F1000" t="n">
-        <v>148389</v>
+        <v>147017</v>
       </c>
     </row>
     <row r="1001">
@@ -20501,10 +20501,10 @@
         <v>82.43000000000001</v>
       </c>
       <c r="E1004" t="n">
-        <v>83.84999999999999</v>
+        <v>83.91</v>
       </c>
       <c r="F1004" t="n">
-        <v>142735</v>
+        <v>141086</v>
       </c>
     </row>
     <row r="1005">
@@ -20515,16 +20515,16 @@
         <v>83.91</v>
       </c>
       <c r="C1005" t="n">
-        <v>85.61</v>
+        <v>85.55</v>
       </c>
       <c r="D1005" t="n">
         <v>83.55</v>
       </c>
       <c r="E1005" t="n">
-        <v>85.47</v>
+        <v>85.48</v>
       </c>
       <c r="F1005" t="n">
-        <v>131152</v>
+        <v>129757</v>
       </c>
     </row>
     <row r="1006">
@@ -20601,10 +20601,10 @@
         <v>83.95999999999999</v>
       </c>
       <c r="E1009" t="n">
-        <v>86.34</v>
+        <v>86.31999999999999</v>
       </c>
       <c r="F1009" t="n">
-        <v>144410</v>
+        <v>142583</v>
       </c>
     </row>
     <row r="1010">
@@ -20621,10 +20621,10 @@
         <v>85.69</v>
       </c>
       <c r="E1010" t="n">
-        <v>87.59</v>
+        <v>87.75</v>
       </c>
       <c r="F1010" t="n">
-        <v>125225</v>
+        <v>123973</v>
       </c>
     </row>
     <row r="1011">
@@ -20701,10 +20701,10 @@
         <v>85.75</v>
       </c>
       <c r="E1014" t="n">
-        <v>87.29000000000001</v>
+        <v>87.31</v>
       </c>
       <c r="F1014" t="n">
-        <v>96051</v>
+        <v>95077</v>
       </c>
     </row>
     <row r="1015">
@@ -20721,10 +20721,10 @@
         <v>85.48</v>
       </c>
       <c r="E1015" t="n">
-        <v>86.01000000000001</v>
+        <v>86.04000000000001</v>
       </c>
       <c r="F1015" t="n">
-        <v>110922</v>
+        <v>109841</v>
       </c>
     </row>
     <row r="1016">
@@ -20801,10 +20801,10 @@
         <v>81.2</v>
       </c>
       <c r="E1019" t="n">
-        <v>82.12</v>
+        <v>81.98</v>
       </c>
       <c r="F1019" t="n">
-        <v>150704</v>
+        <v>146732</v>
       </c>
     </row>
     <row r="1020">
@@ -20818,13 +20818,13 @@
         <v>84.11</v>
       </c>
       <c r="D1020" t="n">
-        <v>79.53</v>
+        <v>79.62</v>
       </c>
       <c r="E1020" t="n">
-        <v>79.62</v>
+        <v>79.64</v>
       </c>
       <c r="F1020" t="n">
-        <v>163093</v>
+        <v>161681</v>
       </c>
     </row>
     <row r="1021">
@@ -20901,10 +20901,10 @@
         <v>82.86</v>
       </c>
       <c r="E1024" t="n">
-        <v>83.95</v>
+        <v>83.88</v>
       </c>
       <c r="F1024" t="n">
-        <v>144061</v>
+        <v>142722</v>
       </c>
     </row>
     <row r="1025">
@@ -20921,10 +20921,10 @@
         <v>83.66</v>
       </c>
       <c r="E1025" t="n">
-        <v>86.2</v>
+        <v>86.29000000000001</v>
       </c>
       <c r="F1025" t="n">
-        <v>156718</v>
+        <v>155562</v>
       </c>
     </row>
     <row r="1026">
@@ -20998,13 +20998,13 @@
         <v>85.90000000000001</v>
       </c>
       <c r="D1029" t="n">
-        <v>84.28</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="E1029" t="n">
-        <v>84.31</v>
+        <v>84.37</v>
       </c>
       <c r="F1029" t="n">
-        <v>129946</v>
+        <v>128382</v>
       </c>
     </row>
     <row r="1030">
@@ -21021,10 +21021,10 @@
         <v>81.55</v>
       </c>
       <c r="E1030" t="n">
-        <v>82.72</v>
+        <v>82.68000000000001</v>
       </c>
       <c r="F1030" t="n">
-        <v>142763</v>
+        <v>141607</v>
       </c>
     </row>
     <row r="1031">
@@ -21101,10 +21101,10 @@
         <v>80.27</v>
       </c>
       <c r="E1034" t="n">
-        <v>82.18000000000001</v>
+        <v>82.12</v>
       </c>
       <c r="F1034" t="n">
-        <v>108091</v>
+        <v>107083</v>
       </c>
     </row>
     <row r="1035">
@@ -21121,10 +21121,10 @@
         <v>80.7</v>
       </c>
       <c r="E1035" t="n">
-        <v>82.77</v>
+        <v>82.94</v>
       </c>
       <c r="F1035" t="n">
-        <v>130526</v>
+        <v>129354</v>
       </c>
     </row>
     <row r="1036">
@@ -21201,10 +21201,10 @@
         <v>83.66</v>
       </c>
       <c r="E1039" t="n">
-        <v>84.23</v>
+        <v>84.34</v>
       </c>
       <c r="F1039" t="n">
-        <v>115434</v>
+        <v>114302</v>
       </c>
     </row>
     <row r="1040">
@@ -21215,16 +21215,16 @@
         <v>84.37</v>
       </c>
       <c r="C1040" t="n">
-        <v>85.81</v>
+        <v>85.8</v>
       </c>
       <c r="D1040" t="n">
         <v>82.2</v>
       </c>
       <c r="E1040" t="n">
-        <v>85.73999999999999</v>
+        <v>85.72</v>
       </c>
       <c r="F1040" t="n">
-        <v>120888</v>
+        <v>119970</v>
       </c>
     </row>
     <row r="1041">
@@ -21301,10 +21301,10 @@
         <v>81.16</v>
       </c>
       <c r="E1044" t="n">
-        <v>81.23</v>
+        <v>81.26000000000001</v>
       </c>
       <c r="F1044" t="n">
-        <v>121276</v>
+        <v>120126</v>
       </c>
     </row>
     <row r="1045">
@@ -21321,10 +21321,10 @@
         <v>80.47</v>
       </c>
       <c r="E1045" t="n">
-        <v>82.38</v>
+        <v>82.33</v>
       </c>
       <c r="F1045" t="n">
-        <v>172647</v>
+        <v>171433</v>
       </c>
     </row>
     <row r="1046">
@@ -21392,7 +21392,7 @@
         <v>45001</v>
       </c>
       <c r="B1049" t="n">
-        <v>74.59999999999999</v>
+        <v>74.04000000000001</v>
       </c>
       <c r="C1049" t="n">
         <v>75.23</v>
@@ -21404,7 +21404,7 @@
         <v>74.25</v>
       </c>
       <c r="F1049" t="n">
-        <v>206406</v>
+        <v>210322</v>
       </c>
     </row>
     <row r="1050">
@@ -21412,7 +21412,7 @@
         <v>45002</v>
       </c>
       <c r="B1050" t="n">
-        <v>74.41</v>
+        <v>74.45</v>
       </c>
       <c r="C1050" t="n">
         <v>75.65000000000001</v>
@@ -21424,7 +21424,7 @@
         <v>72.3</v>
       </c>
       <c r="F1050" t="n">
-        <v>194486</v>
+        <v>196053</v>
       </c>
     </row>
     <row r="1051">
@@ -21492,7 +21492,7 @@
         <v>45008</v>
       </c>
       <c r="B1054" t="n">
-        <v>75.73</v>
+        <v>75.58</v>
       </c>
       <c r="C1054" t="n">
         <v>77.09</v>
@@ -21504,7 +21504,7 @@
         <v>74.98999999999999</v>
       </c>
       <c r="F1054" t="n">
-        <v>132462</v>
+        <v>134971</v>
       </c>
     </row>
     <row r="1055">
@@ -21512,7 +21512,7 @@
         <v>45009</v>
       </c>
       <c r="B1055" t="n">
-        <v>74.92</v>
+        <v>75.08</v>
       </c>
       <c r="C1055" t="n">
         <v>75.89</v>
@@ -21524,7 +21524,7 @@
         <v>74.52</v>
       </c>
       <c r="F1055" t="n">
-        <v>158419</v>
+        <v>160608</v>
       </c>
     </row>
     <row r="1056">
@@ -21601,10 +21601,10 @@
         <v>77.13</v>
       </c>
       <c r="E1059" t="n">
-        <v>78.43000000000001</v>
+        <v>78.47</v>
       </c>
       <c r="F1059" t="n">
-        <v>102975</v>
+        <v>101875</v>
       </c>
     </row>
     <row r="1060">
@@ -21621,10 +21621,10 @@
         <v>77.79000000000001</v>
       </c>
       <c r="E1060" t="n">
-        <v>79.76000000000001</v>
+        <v>79.73</v>
       </c>
       <c r="F1060" t="n">
-        <v>103341</v>
+        <v>102278</v>
       </c>
     </row>
     <row r="1061">
@@ -21701,10 +21701,10 @@
         <v>83.89</v>
       </c>
       <c r="E1064" t="n">
-        <v>84.62</v>
+        <v>84.73</v>
       </c>
       <c r="F1064" t="n">
-        <v>128978</v>
+        <v>127887</v>
       </c>
     </row>
     <row r="1065">
@@ -21781,10 +21781,10 @@
         <v>85.78</v>
       </c>
       <c r="E1068" t="n">
-        <v>86.03</v>
+        <v>85.98</v>
       </c>
       <c r="F1068" t="n">
-        <v>107747</v>
+        <v>106530</v>
       </c>
     </row>
     <row r="1069">
@@ -21801,10 +21801,10 @@
         <v>85.27</v>
       </c>
       <c r="E1069" t="n">
-        <v>86.12</v>
+        <v>86.13</v>
       </c>
       <c r="F1069" t="n">
-        <v>119789</v>
+        <v>118921</v>
       </c>
     </row>
     <row r="1070">
@@ -21878,13 +21878,13 @@
         <v>82.59999999999999</v>
       </c>
       <c r="D1073" t="n">
-        <v>80.48999999999999</v>
+        <v>80.51000000000001</v>
       </c>
       <c r="E1073" t="n">
-        <v>80.48999999999999</v>
+        <v>80.62</v>
       </c>
       <c r="F1073" t="n">
-        <v>100157</v>
+        <v>99083</v>
       </c>
     </row>
     <row r="1074">
@@ -21901,10 +21901,10 @@
         <v>80.2</v>
       </c>
       <c r="E1074" t="n">
-        <v>81.53</v>
+        <v>81.38</v>
       </c>
       <c r="F1074" t="n">
-        <v>89589</v>
+        <v>88877</v>
       </c>
     </row>
     <row r="1075">
@@ -21981,10 +21981,10 @@
         <v>77.3</v>
       </c>
       <c r="E1078" t="n">
-        <v>78.17</v>
+        <v>78.23</v>
       </c>
       <c r="F1078" t="n">
-        <v>114226</v>
+        <v>112919</v>
       </c>
     </row>
     <row r="1079">
@@ -22001,10 +22001,10 @@
         <v>77.44</v>
       </c>
       <c r="E1079" t="n">
-        <v>80.08</v>
+        <v>80.20999999999999</v>
       </c>
       <c r="F1079" t="n">
-        <v>111593</v>
+        <v>110643</v>
       </c>
     </row>
     <row r="1080">
@@ -22081,10 +22081,10 @@
         <v>71.34</v>
       </c>
       <c r="E1083" t="n">
-        <v>72.38</v>
+        <v>72.34</v>
       </c>
       <c r="F1083" t="n">
-        <v>176458</v>
+        <v>175075</v>
       </c>
     </row>
     <row r="1084">
@@ -22101,10 +22101,10 @@
         <v>72.31999999999999</v>
       </c>
       <c r="E1084" t="n">
-        <v>75.15000000000001</v>
+        <v>75.22</v>
       </c>
       <c r="F1084" t="n">
-        <v>122688</v>
+        <v>121559</v>
       </c>
     </row>
     <row r="1085">
@@ -22181,10 +22181,10 @@
         <v>74.5</v>
       </c>
       <c r="E1088" t="n">
-        <v>75.26000000000001</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="F1088" t="n">
-        <v>142391</v>
+        <v>141443</v>
       </c>
     </row>
     <row r="1089">
@@ -22201,10 +22201,10 @@
         <v>73.84999999999999</v>
       </c>
       <c r="E1089" t="n">
-        <v>73.93000000000001</v>
+        <v>74.02</v>
       </c>
       <c r="F1089" t="n">
-        <v>144762</v>
+        <v>143925</v>
       </c>
     </row>
     <row r="1090">
@@ -22281,10 +22281,10 @@
         <v>75.42</v>
       </c>
       <c r="E1093" t="n">
-        <v>75.84</v>
+        <v>75.89</v>
       </c>
       <c r="F1093" t="n">
-        <v>98116</v>
+        <v>97144</v>
       </c>
     </row>
     <row r="1094">
@@ -22301,10 +22301,10 @@
         <v>75.01000000000001</v>
       </c>
       <c r="E1094" t="n">
-        <v>75.59999999999999</v>
+        <v>75.75</v>
       </c>
       <c r="F1094" t="n">
-        <v>108218</v>
+        <v>107224</v>
       </c>
     </row>
     <row r="1095">
@@ -22381,10 +22381,10 @@
         <v>75.08</v>
       </c>
       <c r="E1098" t="n">
-        <v>75.95999999999999</v>
+        <v>76.13</v>
       </c>
       <c r="F1098" t="n">
-        <v>95663</v>
+        <v>94656</v>
       </c>
     </row>
     <row r="1099">
@@ -22401,10 +22401,10 @@
         <v>75.62</v>
       </c>
       <c r="E1099" t="n">
-        <v>77.14</v>
+        <v>77.03</v>
       </c>
       <c r="F1099" t="n">
-        <v>86227</v>
+        <v>85632</v>
       </c>
     </row>
     <row r="1100">
@@ -22481,10 +22481,10 @@
         <v>72</v>
       </c>
       <c r="E1103" t="n">
-        <v>74.25</v>
+        <v>74.17</v>
       </c>
       <c r="F1103" t="n">
-        <v>124084</v>
+        <v>122959</v>
       </c>
     </row>
     <row r="1104">
@@ -22501,10 +22501,10 @@
         <v>74.13</v>
       </c>
       <c r="E1104" t="n">
-        <v>76.13</v>
+        <v>76.3</v>
       </c>
       <c r="F1104" t="n">
-        <v>111881</v>
+        <v>110715</v>
       </c>
     </row>
     <row r="1105">
@@ -22581,10 +22581,10 @@
         <v>73.52</v>
       </c>
       <c r="E1108" t="n">
-        <v>75.44</v>
+        <v>75.56999999999999</v>
       </c>
       <c r="F1108" t="n">
-        <v>142206</v>
+        <v>141391</v>
       </c>
     </row>
     <row r="1109">
@@ -22601,10 +22601,10 @@
         <v>74.67</v>
       </c>
       <c r="E1109" t="n">
-        <v>74.88</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="F1109" t="n">
-        <v>120995</v>
+        <v>120105</v>
       </c>
     </row>
     <row r="1110">
@@ -22681,10 +22681,10 @@
         <v>72.84999999999999</v>
       </c>
       <c r="E1113" t="n">
-        <v>75.52</v>
+        <v>75.56</v>
       </c>
       <c r="F1113" t="n">
-        <v>105947</v>
+        <v>104970</v>
       </c>
     </row>
     <row r="1114">
@@ -22701,10 +22701,10 @@
         <v>75.09999999999999</v>
       </c>
       <c r="E1114" t="n">
-        <v>76.23</v>
+        <v>76.47</v>
       </c>
       <c r="F1114" t="n">
-        <v>111184</v>
+        <v>109963</v>
       </c>
     </row>
     <row r="1115">
@@ -22781,10 +22781,10 @@
         <v>73.75</v>
       </c>
       <c r="E1118" t="n">
-        <v>74.3</v>
+        <v>74.2</v>
       </c>
       <c r="F1118" t="n">
-        <v>89974</v>
+        <v>89166</v>
       </c>
     </row>
     <row r="1119">
@@ -22795,16 +22795,16 @@
         <v>74.2</v>
       </c>
       <c r="C1119" t="n">
-        <v>74.45999999999999</v>
+        <v>74.36</v>
       </c>
       <c r="D1119" t="n">
         <v>72.25</v>
       </c>
       <c r="E1119" t="n">
-        <v>74.34</v>
+        <v>74.09</v>
       </c>
       <c r="F1119" t="n">
-        <v>101628</v>
+        <v>100773</v>
       </c>
     </row>
     <row r="1120">
@@ -22881,10 +22881,10 @@
         <v>73.56</v>
       </c>
       <c r="E1123" t="n">
-        <v>74.34999999999999</v>
+        <v>74.44</v>
       </c>
       <c r="F1123" t="n">
-        <v>118860</v>
+        <v>118096</v>
       </c>
     </row>
     <row r="1124">
@@ -22901,10 +22901,10 @@
         <v>74.23</v>
       </c>
       <c r="E1124" t="n">
-        <v>75.06999999999999</v>
+        <v>75.26000000000001</v>
       </c>
       <c r="F1124" t="n">
-        <v>108012</v>
+        <v>107062</v>
       </c>
     </row>
     <row r="1125">
@@ -22981,10 +22981,10 @@
         <v>74.94</v>
       </c>
       <c r="E1128" t="n">
-        <v>76.44</v>
+        <v>76.47</v>
       </c>
       <c r="F1128" t="n">
-        <v>121613</v>
+        <v>120498</v>
       </c>
     </row>
     <row r="1129">
@@ -23001,10 +23001,10 @@
         <v>75.91</v>
       </c>
       <c r="E1129" t="n">
-        <v>78.12</v>
+        <v>78.13</v>
       </c>
       <c r="F1129" t="n">
-        <v>101260</v>
+        <v>99946</v>
       </c>
     </row>
     <row r="1130">
@@ -23075,16 +23075,16 @@
         <v>79.95999999999999</v>
       </c>
       <c r="C1133" t="n">
-        <v>81.5</v>
+        <v>81.48999999999999</v>
       </c>
       <c r="D1133" t="n">
         <v>79.69</v>
       </c>
       <c r="E1133" t="n">
-        <v>81.37</v>
+        <v>81.48</v>
       </c>
       <c r="F1133" t="n">
-        <v>97805</v>
+        <v>96443</v>
       </c>
     </row>
     <row r="1134">
@@ -23098,13 +23098,13 @@
         <v>81.42</v>
       </c>
       <c r="D1134" t="n">
-        <v>79.34999999999999</v>
+        <v>79.44</v>
       </c>
       <c r="E1134" t="n">
-        <v>79.45</v>
+        <v>79.54000000000001</v>
       </c>
       <c r="F1134" t="n">
-        <v>99161</v>
+        <v>98000</v>
       </c>
     </row>
     <row r="1135">
@@ -23181,10 +23181,10 @@
         <v>78.56999999999999</v>
       </c>
       <c r="E1138" t="n">
-        <v>79.48</v>
+        <v>79.54000000000001</v>
       </c>
       <c r="F1138" t="n">
-        <v>77506</v>
+        <v>76777</v>
       </c>
     </row>
     <row r="1139">
@@ -23201,10 +23201,10 @@
         <v>79.51000000000001</v>
       </c>
       <c r="E1139" t="n">
-        <v>80.5</v>
+        <v>80.69</v>
       </c>
       <c r="F1139" t="n">
-        <v>70745</v>
+        <v>69907</v>
       </c>
     </row>
     <row r="1140">
@@ -23281,10 +23281,10 @@
         <v>82.54000000000001</v>
       </c>
       <c r="E1143" t="n">
-        <v>83.3</v>
+        <v>83.42</v>
       </c>
       <c r="F1143" t="n">
-        <v>101885</v>
+        <v>100960</v>
       </c>
     </row>
     <row r="1144">
@@ -23301,10 +23301,10 @@
         <v>82.78</v>
       </c>
       <c r="E1144" t="n">
-        <v>84.34999999999999</v>
+        <v>84.26000000000001</v>
       </c>
       <c r="F1144" t="n">
-        <v>96933</v>
+        <v>96080</v>
       </c>
     </row>
     <row r="1145">
@@ -23381,10 +23381,10 @@
         <v>82.23</v>
       </c>
       <c r="E1148" t="n">
-        <v>85.04000000000001</v>
+        <v>85.13</v>
       </c>
       <c r="F1148" t="n">
-        <v>124232</v>
+        <v>122532</v>
       </c>
     </row>
     <row r="1149">
@@ -23401,10 +23401,10 @@
         <v>84.89</v>
       </c>
       <c r="E1149" t="n">
-        <v>85.81</v>
+        <v>85.84</v>
       </c>
       <c r="F1149" t="n">
-        <v>104424</v>
+        <v>103319</v>
       </c>
     </row>
     <row r="1150">
@@ -23481,10 +23481,10 @@
         <v>85.89</v>
       </c>
       <c r="E1153" t="n">
-        <v>86.01000000000001</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="F1153" t="n">
-        <v>120019</v>
+        <v>119054</v>
       </c>
     </row>
     <row r="1154">
@@ -23501,10 +23501,10 @@
         <v>85.53</v>
       </c>
       <c r="E1154" t="n">
-        <v>86.16</v>
+        <v>86.26000000000001</v>
       </c>
       <c r="F1154" t="n">
-        <v>115051</v>
+        <v>114400</v>
       </c>
     </row>
     <row r="1155">
@@ -23581,10 +23581,10 @@
         <v>82.70999999999999</v>
       </c>
       <c r="E1158" t="n">
-        <v>83.42</v>
+        <v>83.45999999999999</v>
       </c>
       <c r="F1158" t="n">
-        <v>88033</v>
+        <v>87119</v>
       </c>
     </row>
     <row r="1159">
@@ -23601,10 +23601,10 @@
         <v>82.98</v>
       </c>
       <c r="E1159" t="n">
-        <v>84.42</v>
+        <v>84.37</v>
       </c>
       <c r="F1159" t="n">
-        <v>98761</v>
+        <v>98085</v>
       </c>
     </row>
     <row r="1160">
@@ -23681,10 +23681,10 @@
         <v>81.61</v>
       </c>
       <c r="E1163" t="n">
-        <v>82.67</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="F1163" t="n">
-        <v>77961</v>
+        <v>77118</v>
       </c>
     </row>
     <row r="1164">
@@ -23701,10 +23701,10 @@
         <v>82.2</v>
       </c>
       <c r="E1164" t="n">
-        <v>84.05</v>
+        <v>84.14</v>
       </c>
       <c r="F1164" t="n">
-        <v>102303</v>
+        <v>101382</v>
       </c>
     </row>
     <row r="1165">
@@ -23781,10 +23781,10 @@
         <v>84.98</v>
       </c>
       <c r="E1168" t="n">
-        <v>86.66</v>
+        <v>86.63</v>
       </c>
       <c r="F1168" t="n">
-        <v>85007</v>
+        <v>83934</v>
       </c>
     </row>
     <row r="1169">
@@ -23795,16 +23795,16 @@
         <v>86.63</v>
       </c>
       <c r="C1169" t="n">
-        <v>88.75</v>
+        <v>88.66</v>
       </c>
       <c r="D1169" t="n">
         <v>86.59</v>
       </c>
       <c r="E1169" t="n">
-        <v>88.68000000000001</v>
+        <v>88.64</v>
       </c>
       <c r="F1169" t="n">
-        <v>98645</v>
+        <v>97671</v>
       </c>
     </row>
     <row r="1170">
@@ -23881,10 +23881,10 @@
         <v>89.17</v>
       </c>
       <c r="E1173" t="n">
-        <v>89.47</v>
+        <v>89.76000000000001</v>
       </c>
       <c r="F1173" t="n">
-        <v>104343</v>
+        <v>103067</v>
       </c>
     </row>
     <row r="1174">
@@ -23901,10 +23901,10 @@
         <v>88.97</v>
       </c>
       <c r="E1174" t="n">
-        <v>90.09999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="F1174" t="n">
-        <v>101197</v>
+        <v>100164</v>
       </c>
     </row>
     <row r="1175">
@@ -23975,16 +23975,16 @@
         <v>91.56999999999999</v>
       </c>
       <c r="C1178" t="n">
-        <v>93.68000000000001</v>
+        <v>93.44</v>
       </c>
       <c r="D1178" t="n">
         <v>91.55</v>
       </c>
       <c r="E1178" t="n">
-        <v>93.56</v>
+        <v>93.36</v>
       </c>
       <c r="F1178" t="n">
-        <v>91727</v>
+        <v>89908</v>
       </c>
     </row>
     <row r="1179">
@@ -24001,10 +24001,10 @@
         <v>92.14</v>
       </c>
       <c r="E1179" t="n">
-        <v>93.56999999999999</v>
+        <v>93.52</v>
       </c>
       <c r="F1179" t="n">
-        <v>101498</v>
+        <v>100530</v>
       </c>
     </row>
     <row r="1180">
@@ -24081,10 +24081,10 @@
         <v>91.23999999999999</v>
       </c>
       <c r="E1183" t="n">
-        <v>92.20999999999999</v>
+        <v>92.27</v>
       </c>
       <c r="F1183" t="n">
-        <v>98137</v>
+        <v>97207</v>
       </c>
     </row>
     <row r="1184">
@@ -24101,10 +24101,10 @@
         <v>91.68000000000001</v>
       </c>
       <c r="E1184" t="n">
-        <v>92.28</v>
+        <v>92.31</v>
       </c>
       <c r="F1184" t="n">
-        <v>99665</v>
+        <v>98960</v>
       </c>
     </row>
     <row r="1185">
@@ -24181,10 +24181,10 @@
         <v>92.56</v>
       </c>
       <c r="E1188" t="n">
-        <v>92.89</v>
+        <v>92.94</v>
       </c>
       <c r="F1188" t="n">
-        <v>128240</v>
+        <v>127194</v>
       </c>
     </row>
     <row r="1189">
@@ -24201,10 +24201,10 @@
         <v>91.68000000000001</v>
       </c>
       <c r="E1189" t="n">
-        <v>91.8</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="F1189" t="n">
-        <v>117877</v>
+        <v>116761</v>
       </c>
     </row>
     <row r="1190">
@@ -24281,10 +24281,10 @@
         <v>83.31999999999999</v>
       </c>
       <c r="E1193" t="n">
-        <v>83.72</v>
+        <v>83.68000000000001</v>
       </c>
       <c r="F1193" t="n">
-        <v>149779</v>
+        <v>148426</v>
       </c>
     </row>
     <row r="1194">
@@ -24301,10 +24301,10 @@
         <v>82.97</v>
       </c>
       <c r="E1194" t="n">
-        <v>83.79000000000001</v>
+        <v>83.88</v>
       </c>
       <c r="F1194" t="n">
-        <v>140020</v>
+        <v>138785</v>
       </c>
     </row>
     <row r="1195">
@@ -24381,10 +24381,10 @@
         <v>84.59</v>
       </c>
       <c r="E1198" t="n">
-        <v>85.59999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="F1198" t="n">
-        <v>124560</v>
+        <v>123421</v>
       </c>
     </row>
     <row r="1199">
@@ -24404,7 +24404,7 @@
         <v>89.93000000000001</v>
       </c>
       <c r="F1199" t="n">
-        <v>120817</v>
+        <v>118765</v>
       </c>
     </row>
     <row r="1200">
@@ -24475,16 +24475,16 @@
         <v>90.26000000000001</v>
       </c>
       <c r="C1203" t="n">
-        <v>92.34999999999999</v>
+        <v>92.22</v>
       </c>
       <c r="D1203" t="n">
         <v>88.69</v>
       </c>
       <c r="E1203" t="n">
-        <v>92.04000000000001</v>
+        <v>92.16</v>
       </c>
       <c r="F1203" t="n">
-        <v>111224</v>
+        <v>109002</v>
       </c>
     </row>
     <row r="1204">
@@ -24501,10 +24501,10 @@
         <v>90.63</v>
       </c>
       <c r="E1204" t="n">
-        <v>91.26000000000001</v>
+        <v>91.13</v>
       </c>
       <c r="F1204" t="n">
-        <v>110661</v>
+        <v>109157</v>
       </c>
     </row>
     <row r="1205">
@@ -24581,10 +24581,10 @@
         <v>86.48</v>
       </c>
       <c r="E1208" t="n">
-        <v>87.23999999999999</v>
+        <v>87.25</v>
       </c>
       <c r="F1208" t="n">
-        <v>114536</v>
+        <v>113368</v>
       </c>
     </row>
     <row r="1209">
@@ -24601,10 +24601,10 @@
         <v>86.76000000000001</v>
       </c>
       <c r="E1209" t="n">
-        <v>88.70999999999999</v>
+        <v>88.76000000000001</v>
       </c>
       <c r="F1209" t="n">
-        <v>123231</v>
+        <v>121600</v>
       </c>
     </row>
     <row r="1210">
@@ -24672,7 +24672,7 @@
         <v>45232</v>
       </c>
       <c r="B1213" t="n">
-        <v>85.03</v>
+        <v>84.83</v>
       </c>
       <c r="C1213" t="n">
         <v>86.88</v>
@@ -24684,7 +24684,7 @@
         <v>86.63</v>
       </c>
       <c r="F1213" t="n">
-        <v>102261</v>
+        <v>103842</v>
       </c>
     </row>
     <row r="1214">
@@ -24692,7 +24692,7 @@
         <v>45233</v>
       </c>
       <c r="B1214" t="n">
-        <v>86.66</v>
+        <v>86.70999999999999</v>
       </c>
       <c r="C1214" t="n">
         <v>87.58</v>
@@ -24704,7 +24704,7 @@
         <v>84.95</v>
       </c>
       <c r="F1214" t="n">
-        <v>117913</v>
+        <v>119097</v>
       </c>
     </row>
     <row r="1215">
@@ -24781,10 +24781,10 @@
         <v>79.33</v>
       </c>
       <c r="E1218" t="n">
-        <v>79.76000000000001</v>
+        <v>79.75</v>
       </c>
       <c r="F1218" t="n">
-        <v>111847</v>
+        <v>110739</v>
       </c>
     </row>
     <row r="1219">
@@ -24801,10 +24801,10 @@
         <v>79.70999999999999</v>
       </c>
       <c r="E1219" t="n">
-        <v>81.43000000000001</v>
+        <v>81.36</v>
       </c>
       <c r="F1219" t="n">
-        <v>92327</v>
+        <v>91256</v>
       </c>
     </row>
     <row r="1220">
@@ -24881,10 +24881,10 @@
         <v>76.64</v>
       </c>
       <c r="E1223" t="n">
-        <v>77.45</v>
+        <v>77.43000000000001</v>
       </c>
       <c r="F1223" t="n">
-        <v>105749</v>
+        <v>104766</v>
       </c>
     </row>
     <row r="1224">
@@ -24901,10 +24901,10 @@
         <v>77.31</v>
       </c>
       <c r="E1224" t="n">
-        <v>80.43000000000001</v>
+        <v>80.37</v>
       </c>
       <c r="F1224" t="n">
-        <v>89648</v>
+        <v>88772</v>
       </c>
     </row>
     <row r="1225">
@@ -25078,13 +25078,13 @@
         <v>84.51000000000001</v>
       </c>
       <c r="D1233" t="n">
-        <v>79.94</v>
+        <v>79.95</v>
       </c>
       <c r="E1233" t="n">
-        <v>80.31</v>
+        <v>80</v>
       </c>
       <c r="F1233" t="n">
-        <v>145419</v>
+        <v>143673</v>
       </c>
     </row>
     <row r="1234">
@@ -25101,10 +25101,10 @@
         <v>78.69</v>
       </c>
       <c r="E1234" t="n">
-        <v>79.02</v>
+        <v>78.93000000000001</v>
       </c>
       <c r="F1234" t="n">
-        <v>126159</v>
+        <v>125186</v>
       </c>
     </row>
     <row r="1235">
@@ -25181,10 +25181,10 @@
         <v>73.68000000000001</v>
       </c>
       <c r="E1238" t="n">
-        <v>74.39</v>
+        <v>74.47</v>
       </c>
       <c r="F1238" t="n">
-        <v>116791</v>
+        <v>115986</v>
       </c>
     </row>
     <row r="1239">
@@ -25201,10 +25201,10 @@
         <v>74.25</v>
       </c>
       <c r="E1239" t="n">
-        <v>75.94</v>
+        <v>75.87</v>
       </c>
       <c r="F1239" t="n">
-        <v>114930</v>
+        <v>114085</v>
       </c>
     </row>
     <row r="1240">
@@ -25281,10 +25281,10 @@
         <v>74.56999999999999</v>
       </c>
       <c r="E1243" t="n">
-        <v>76.75</v>
+        <v>76.86</v>
       </c>
       <c r="F1243" t="n">
-        <v>84712</v>
+        <v>83845</v>
       </c>
     </row>
     <row r="1244">
@@ -25301,10 +25301,10 @@
         <v>75.48</v>
       </c>
       <c r="E1244" t="n">
-        <v>76.98999999999999</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="F1244" t="n">
-        <v>95068</v>
+        <v>94162</v>
       </c>
     </row>
     <row r="1245">
@@ -25381,10 +25381,10 @@
         <v>77.76000000000001</v>
       </c>
       <c r="E1248" t="n">
-        <v>79.12</v>
+        <v>79.19</v>
       </c>
       <c r="F1248" t="n">
-        <v>91755</v>
+        <v>91100</v>
       </c>
     </row>
     <row r="1249">
@@ -25461,10 +25461,10 @@
         <v>77.04000000000001</v>
       </c>
       <c r="E1252" t="n">
-        <v>77.36</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="F1252" t="n">
-        <v>95204</v>
+        <v>94380</v>
       </c>
     </row>
     <row r="1253">
@@ -25544,7 +25544,7 @@
         <v>77.53</v>
       </c>
       <c r="F1256" t="n">
-        <v>119158</v>
+        <v>118273</v>
       </c>
     </row>
     <row r="1257">
@@ -25641,10 +25641,10 @@
         <v>76.45</v>
       </c>
       <c r="E1261" t="n">
-        <v>78.01000000000001</v>
+        <v>77.61</v>
       </c>
       <c r="F1261" t="n">
-        <v>129868</v>
+        <v>128067</v>
       </c>
     </row>
     <row r="1262">
@@ -25741,10 +25741,10 @@
         <v>76.98</v>
       </c>
       <c r="E1266" t="n">
-        <v>78.56</v>
+        <v>78.63</v>
       </c>
       <c r="F1266" t="n">
-        <v>99368</v>
+        <v>98609</v>
       </c>
     </row>
     <row r="1267">
@@ -25841,10 +25841,10 @@
         <v>79.65000000000001</v>
       </c>
       <c r="E1271" t="n">
-        <v>81.69</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="F1271" t="n">
-        <v>76710</v>
+        <v>75889</v>
       </c>
     </row>
     <row r="1272">
@@ -25861,10 +25861,10 @@
         <v>80.75</v>
       </c>
       <c r="E1272" t="n">
-        <v>83.09999999999999</v>
+        <v>83.08</v>
       </c>
       <c r="F1272" t="n">
-        <v>87047</v>
+        <v>85666</v>
       </c>
     </row>
     <row r="1273">
@@ -25941,10 +25941,10 @@
         <v>78.5</v>
       </c>
       <c r="E1276" t="n">
-        <v>78.7</v>
+        <v>78.64</v>
       </c>
       <c r="F1276" t="n">
-        <v>140571</v>
+        <v>138682</v>
       </c>
     </row>
     <row r="1277">
@@ -25961,10 +25961,10 @@
         <v>76.78</v>
       </c>
       <c r="E1277" t="n">
-        <v>77.31999999999999</v>
+        <v>77.11</v>
       </c>
       <c r="F1277" t="n">
-        <v>133396</v>
+        <v>132023</v>
       </c>
     </row>
     <row r="1278">
@@ -26041,10 +26041,10 @@
         <v>78.84999999999999</v>
       </c>
       <c r="E1281" t="n">
-        <v>81.40000000000001</v>
+        <v>81.51000000000001</v>
       </c>
       <c r="F1281" t="n">
-        <v>87658</v>
+        <v>86597</v>
       </c>
     </row>
     <row r="1282">
@@ -26064,7 +26064,7 @@
         <v>81.63</v>
       </c>
       <c r="F1282" t="n">
-        <v>86235</v>
+        <v>85346</v>
       </c>
     </row>
     <row r="1283">
@@ -26141,10 +26141,10 @@
         <v>80.31999999999999</v>
       </c>
       <c r="E1286" t="n">
-        <v>82.22</v>
+        <v>82.37</v>
       </c>
       <c r="F1286" t="n">
-        <v>84560</v>
+        <v>83753</v>
       </c>
     </row>
     <row r="1287">
@@ -26161,10 +26161,10 @@
         <v>81.34</v>
       </c>
       <c r="E1287" t="n">
-        <v>82.68000000000001</v>
+        <v>82.70999999999999</v>
       </c>
       <c r="F1287" t="n">
-        <v>81459</v>
+        <v>80620</v>
       </c>
     </row>
     <row r="1288">
@@ -26241,10 +26241,10 @@
         <v>81.45</v>
       </c>
       <c r="E1291" t="n">
-        <v>82.51000000000001</v>
+        <v>82.63</v>
       </c>
       <c r="F1291" t="n">
-        <v>67848</v>
+        <v>67106</v>
       </c>
     </row>
     <row r="1292">
@@ -26261,10 +26261,10 @@
         <v>80.65000000000001</v>
       </c>
       <c r="E1292" t="n">
-        <v>80.84</v>
+        <v>80.88</v>
       </c>
       <c r="F1292" t="n">
-        <v>73168</v>
+        <v>72495</v>
       </c>
     </row>
     <row r="1293">
@@ -26341,10 +26341,10 @@
         <v>81.37</v>
       </c>
       <c r="E1296" t="n">
-        <v>81.8</v>
+        <v>81.70999999999999</v>
       </c>
       <c r="F1296" t="n">
-        <v>79642</v>
+        <v>78801</v>
       </c>
     </row>
     <row r="1297">
@@ -26361,10 +26361,10 @@
         <v>81.63</v>
       </c>
       <c r="E1297" t="n">
-        <v>83.12</v>
+        <v>83.19</v>
       </c>
       <c r="F1297" t="n">
-        <v>73275</v>
+        <v>72423</v>
       </c>
     </row>
     <row r="1298">
@@ -26441,10 +26441,10 @@
         <v>81.77</v>
       </c>
       <c r="E1301" t="n">
-        <v>82.87</v>
+        <v>82.52</v>
       </c>
       <c r="F1301" t="n">
-        <v>103853</v>
+        <v>102278</v>
       </c>
     </row>
     <row r="1302">
@@ -26461,10 +26461,10 @@
         <v>81.41</v>
       </c>
       <c r="E1302" t="n">
-        <v>81.55</v>
+        <v>81.66</v>
       </c>
       <c r="F1302" t="n">
-        <v>100115</v>
+        <v>99175</v>
       </c>
     </row>
     <row r="1303">
@@ -26532,19 +26532,19 @@
         <v>45365</v>
       </c>
       <c r="B1306" t="n">
-        <v>83.69</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="C1306" t="n">
         <v>85.18000000000001</v>
       </c>
       <c r="D1306" t="n">
-        <v>83.56999999999999</v>
+        <v>83.53</v>
       </c>
       <c r="E1306" t="n">
         <v>84.61</v>
       </c>
       <c r="F1306" t="n">
-        <v>71119</v>
+        <v>71844</v>
       </c>
     </row>
     <row r="1307">
@@ -26552,7 +26552,7 @@
         <v>45366</v>
       </c>
       <c r="B1307" t="n">
-        <v>84.68000000000001</v>
+        <v>84.65000000000001</v>
       </c>
       <c r="C1307" t="n">
         <v>85.09</v>
@@ -26564,7 +26564,7 @@
         <v>84.83</v>
       </c>
       <c r="F1307" t="n">
-        <v>74945</v>
+        <v>75864</v>
       </c>
     </row>
     <row r="1308">
@@ -26632,7 +26632,7 @@
         <v>45372</v>
       </c>
       <c r="B1311" t="n">
-        <v>85.81</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="C1311" t="n">
         <v>86.03</v>
@@ -26644,7 +26644,7 @@
         <v>84.95999999999999</v>
       </c>
       <c r="F1311" t="n">
-        <v>66113</v>
+        <v>67186</v>
       </c>
     </row>
     <row r="1312">
@@ -26652,7 +26652,7 @@
         <v>45373</v>
       </c>
       <c r="B1312" t="n">
-        <v>84.98999999999999</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="C1312" t="n">
         <v>85.58</v>
@@ -26664,7 +26664,7 @@
         <v>84.93000000000001</v>
       </c>
       <c r="F1312" t="n">
-        <v>53666</v>
+        <v>54286</v>
       </c>
     </row>
     <row r="1313">
@@ -26732,7 +26732,7 @@
         <v>45379</v>
       </c>
       <c r="B1316" t="n">
-        <v>85.65000000000001</v>
+        <v>85.56</v>
       </c>
       <c r="C1316" t="n">
         <v>86.89</v>
@@ -26744,7 +26744,7 @@
         <v>86.67</v>
       </c>
       <c r="F1316" t="n">
-        <v>56915</v>
+        <v>57372</v>
       </c>
     </row>
     <row r="1317">
@@ -26821,10 +26821,10 @@
         <v>88.43000000000001</v>
       </c>
       <c r="E1320" t="n">
-        <v>90.56</v>
+        <v>90.38</v>
       </c>
       <c r="F1320" t="n">
-        <v>75666</v>
+        <v>74470</v>
       </c>
     </row>
     <row r="1321">
@@ -26841,10 +26841,10 @@
         <v>90.18000000000001</v>
       </c>
       <c r="E1321" t="n">
-        <v>90.39</v>
+        <v>90.52</v>
       </c>
       <c r="F1321" t="n">
-        <v>80607</v>
+        <v>79937</v>
       </c>
     </row>
     <row r="1322">
@@ -26921,10 +26921,10 @@
         <v>88.87</v>
       </c>
       <c r="E1325" t="n">
-        <v>89.55</v>
+        <v>89.68000000000001</v>
       </c>
       <c r="F1325" t="n">
-        <v>107884</v>
+        <v>107040</v>
       </c>
     </row>
     <row r="1326">
@@ -26941,10 +26941,10 @@
         <v>89.45</v>
       </c>
       <c r="E1326" t="n">
-        <v>89.48999999999999</v>
+        <v>89.73</v>
       </c>
       <c r="F1326" t="n">
-        <v>109120</v>
+        <v>108331</v>
       </c>
     </row>
     <row r="1327">
@@ -27021,10 +27021,10 @@
         <v>85.63</v>
       </c>
       <c r="E1330" t="n">
-        <v>86.19</v>
+        <v>86.47</v>
       </c>
       <c r="F1330" t="n">
-        <v>108132</v>
+        <v>107464</v>
       </c>
     </row>
     <row r="1331">
@@ -27041,10 +27041,10 @@
         <v>85.61</v>
       </c>
       <c r="E1331" t="n">
-        <v>86.38</v>
+        <v>86.51000000000001</v>
       </c>
       <c r="F1331" t="n">
-        <v>144473</v>
+        <v>143518</v>
       </c>
     </row>
     <row r="1332">
@@ -27115,16 +27115,16 @@
         <v>86.88</v>
       </c>
       <c r="C1335" t="n">
-        <v>88</v>
+        <v>87.97</v>
       </c>
       <c r="D1335" t="n">
         <v>86.2</v>
       </c>
       <c r="E1335" t="n">
-        <v>87.83</v>
+        <v>87.95</v>
       </c>
       <c r="F1335" t="n">
-        <v>70059</v>
+        <v>69439</v>
       </c>
     </row>
     <row r="1336">
@@ -27141,10 +27141,10 @@
         <v>87.56999999999999</v>
       </c>
       <c r="E1336" t="n">
-        <v>87.89</v>
+        <v>87.98999999999999</v>
       </c>
       <c r="F1336" t="n">
-        <v>64445</v>
+        <v>63936</v>
       </c>
     </row>
     <row r="1337">
@@ -27221,10 +27221,10 @@
         <v>82.89</v>
       </c>
       <c r="E1340" t="n">
-        <v>83.48</v>
+        <v>83.47</v>
       </c>
       <c r="F1340" t="n">
-        <v>101847</v>
+        <v>100961</v>
       </c>
     </row>
     <row r="1341">
@@ -27238,13 +27238,13 @@
         <v>84.18000000000001</v>
       </c>
       <c r="D1341" t="n">
-        <v>82.53</v>
+        <v>82.65000000000001</v>
       </c>
       <c r="E1341" t="n">
-        <v>82.54000000000001</v>
+        <v>82.77</v>
       </c>
       <c r="F1341" t="n">
-        <v>83584</v>
+        <v>82987</v>
       </c>
     </row>
     <row r="1342">
@@ -27321,10 +27321,10 @@
         <v>83.18000000000001</v>
       </c>
       <c r="E1345" t="n">
-        <v>83.77</v>
+        <v>83.91</v>
       </c>
       <c r="F1345" t="n">
-        <v>67737</v>
+        <v>67201</v>
       </c>
     </row>
     <row r="1346">
@@ -27338,13 +27338,13 @@
         <v>84.23</v>
       </c>
       <c r="D1346" t="n">
-        <v>82.36</v>
+        <v>82.5</v>
       </c>
       <c r="E1346" t="n">
-        <v>82.36</v>
+        <v>82.61</v>
       </c>
       <c r="F1346" t="n">
-        <v>63117</v>
+        <v>62356</v>
       </c>
     </row>
     <row r="1347">
@@ -27421,10 +27421,10 @@
         <v>82.02</v>
       </c>
       <c r="E1350" t="n">
-        <v>82.98999999999999</v>
+        <v>83.04000000000001</v>
       </c>
       <c r="F1350" t="n">
-        <v>65759</v>
+        <v>65306</v>
       </c>
     </row>
     <row r="1351">
@@ -27441,10 +27441,10 @@
         <v>82.81999999999999</v>
       </c>
       <c r="E1351" t="n">
-        <v>83.56</v>
+        <v>83.68000000000001</v>
       </c>
       <c r="F1351" t="n">
-        <v>61133</v>
+        <v>60667</v>
       </c>
     </row>
     <row r="1352">
@@ -27521,10 +27521,10 @@
         <v>80.7</v>
       </c>
       <c r="E1355" t="n">
-        <v>81.06999999999999</v>
+        <v>81.09</v>
       </c>
       <c r="F1355" t="n">
-        <v>69958</v>
+        <v>68901</v>
       </c>
     </row>
     <row r="1356">
@@ -27541,10 +27541,10 @@
         <v>80.42</v>
       </c>
       <c r="E1356" t="n">
-        <v>81.79000000000001</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="F1356" t="n">
-        <v>56381</v>
+        <v>56045</v>
       </c>
     </row>
     <row r="1357">
@@ -27618,13 +27618,13 @@
         <v>83.51000000000001</v>
       </c>
       <c r="D1360" t="n">
-        <v>81.72</v>
+        <v>81.77</v>
       </c>
       <c r="E1360" t="n">
-        <v>81.73</v>
+        <v>81.88</v>
       </c>
       <c r="F1360" t="n">
-        <v>81864</v>
+        <v>81262</v>
       </c>
     </row>
     <row r="1361">
@@ -27641,10 +27641,10 @@
         <v>80.69</v>
       </c>
       <c r="E1361" t="n">
-        <v>81.09</v>
+        <v>81.22</v>
       </c>
       <c r="F1361" t="n">
-        <v>87130</v>
+        <v>86335</v>
       </c>
     </row>
     <row r="1362">
@@ -27721,10 +27721,10 @@
         <v>78.23999999999999</v>
       </c>
       <c r="E1365" t="n">
-        <v>79.69</v>
+        <v>79.73</v>
       </c>
       <c r="F1365" t="n">
-        <v>72677</v>
+        <v>72035</v>
       </c>
     </row>
     <row r="1366">
@@ -27741,10 +27741,10 @@
         <v>79.18000000000001</v>
       </c>
       <c r="E1366" t="n">
-        <v>79.23999999999999</v>
+        <v>79.27</v>
       </c>
       <c r="F1366" t="n">
-        <v>77440</v>
+        <v>76576</v>
       </c>
     </row>
     <row r="1367">
@@ -27821,10 +27821,10 @@
         <v>81.53</v>
       </c>
       <c r="E1370" t="n">
-        <v>81.68000000000001</v>
+        <v>81.98</v>
       </c>
       <c r="F1370" t="n">
-        <v>79567</v>
+        <v>78296</v>
       </c>
     </row>
     <row r="1371">
@@ -27841,10 +27841,10 @@
         <v>81.64</v>
       </c>
       <c r="E1371" t="n">
-        <v>82.06</v>
+        <v>82.2</v>
       </c>
       <c r="F1371" t="n">
-        <v>75768</v>
+        <v>75030</v>
       </c>
     </row>
     <row r="1372">
@@ -27921,10 +27921,10 @@
         <v>84.28</v>
       </c>
       <c r="E1375" t="n">
-        <v>84.7</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="F1375" t="n">
-        <v>59846</v>
+        <v>59448</v>
       </c>
     </row>
     <row r="1376">
@@ -27941,10 +27941,10 @@
         <v>84</v>
       </c>
       <c r="E1376" t="n">
-        <v>84.16</v>
+        <v>84.31</v>
       </c>
       <c r="F1376" t="n">
-        <v>60278</v>
+        <v>59797</v>
       </c>
     </row>
     <row r="1377">
@@ -28021,10 +28021,10 @@
         <v>84.01000000000001</v>
       </c>
       <c r="E1380" t="n">
-        <v>85.04000000000001</v>
+        <v>85.25</v>
       </c>
       <c r="F1380" t="n">
-        <v>64909</v>
+        <v>64362</v>
       </c>
     </row>
     <row r="1381">
@@ -28041,10 +28041,10 @@
         <v>84.39</v>
       </c>
       <c r="E1381" t="n">
-        <v>84.65000000000001</v>
+        <v>84.79000000000001</v>
       </c>
       <c r="F1381" t="n">
-        <v>69862</v>
+        <v>69177</v>
       </c>
     </row>
     <row r="1382">
@@ -28141,10 +28141,10 @@
         <v>86.17</v>
       </c>
       <c r="E1386" t="n">
-        <v>86.43000000000001</v>
+        <v>86.31999999999999</v>
       </c>
       <c r="F1386" t="n">
-        <v>68965</v>
+        <v>67919</v>
       </c>
     </row>
     <row r="1387">
@@ -28221,10 +28221,10 @@
         <v>84.16</v>
       </c>
       <c r="E1390" t="n">
-        <v>84.90000000000001</v>
+        <v>85.19</v>
       </c>
       <c r="F1390" t="n">
-        <v>78990</v>
+        <v>78243</v>
       </c>
     </row>
     <row r="1391">
@@ -28238,13 +28238,13 @@
         <v>85.67</v>
       </c>
       <c r="D1391" t="n">
-        <v>84.31999999999999</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="E1391" t="n">
-        <v>84.31999999999999</v>
+        <v>84.5</v>
       </c>
       <c r="F1391" t="n">
-        <v>74302</v>
+        <v>73607</v>
       </c>
     </row>
     <row r="1392">
@@ -28321,10 +28321,10 @@
         <v>83.41</v>
       </c>
       <c r="E1395" t="n">
-        <v>83.76000000000001</v>
+        <v>83.72</v>
       </c>
       <c r="F1395" t="n">
-        <v>69797</v>
+        <v>68620</v>
       </c>
     </row>
     <row r="1396">
@@ -28338,13 +28338,13 @@
         <v>84.41</v>
       </c>
       <c r="D1396" t="n">
-        <v>81.64</v>
+        <v>81.7</v>
       </c>
       <c r="E1396" t="n">
-        <v>81.64</v>
+        <v>81.89</v>
       </c>
       <c r="F1396" t="n">
-        <v>72736</v>
+        <v>72020</v>
       </c>
     </row>
     <row r="1397">
@@ -28421,10 +28421,10 @@
         <v>79.28</v>
       </c>
       <c r="E1400" t="n">
-        <v>81.37</v>
+        <v>81.33</v>
       </c>
       <c r="F1400" t="n">
-        <v>69789</v>
+        <v>69150</v>
       </c>
     </row>
     <row r="1401">
@@ -28441,10 +28441,10 @@
         <v>79.39</v>
       </c>
       <c r="E1401" t="n">
-        <v>79.48999999999999</v>
+        <v>79.92</v>
       </c>
       <c r="F1401" t="n">
-        <v>65748</v>
+        <v>64725</v>
       </c>
     </row>
     <row r="1402">
@@ -28521,10 +28521,10 @@
         <v>79.3</v>
       </c>
       <c r="E1405" t="n">
-        <v>79.83</v>
+        <v>80</v>
       </c>
       <c r="F1405" t="n">
-        <v>105741</v>
+        <v>104482</v>
       </c>
     </row>
     <row r="1406">
@@ -28541,10 +28541,10 @@
         <v>76.26000000000001</v>
       </c>
       <c r="E1406" t="n">
-        <v>77.14</v>
+        <v>77.08</v>
       </c>
       <c r="F1406" t="n">
-        <v>125792</v>
+        <v>124356</v>
       </c>
     </row>
     <row r="1407">
@@ -28621,10 +28621,10 @@
         <v>77.33</v>
       </c>
       <c r="E1410" t="n">
-        <v>78.59</v>
+        <v>78.73999999999999</v>
       </c>
       <c r="F1410" t="n">
-        <v>113892</v>
+        <v>113028</v>
       </c>
     </row>
     <row r="1411">
@@ -28641,10 +28641,10 @@
         <v>78.43000000000001</v>
       </c>
       <c r="E1411" t="n">
-        <v>79.27</v>
+        <v>79.34</v>
       </c>
       <c r="F1411" t="n">
-        <v>87467</v>
+        <v>86405</v>
       </c>
     </row>
     <row r="1412">
@@ -28721,10 +28721,10 @@
         <v>79.11</v>
       </c>
       <c r="E1415" t="n">
-        <v>80.26000000000001</v>
+        <v>80.31999999999999</v>
       </c>
       <c r="F1415" t="n">
-        <v>79567</v>
+        <v>78757</v>
       </c>
     </row>
     <row r="1416">
@@ -28741,10 +28741,10 @@
         <v>78.09</v>
       </c>
       <c r="E1416" t="n">
-        <v>78.94</v>
+        <v>79.22</v>
       </c>
       <c r="F1416" t="n">
-        <v>82030</v>
+        <v>81009</v>
       </c>
     </row>
     <row r="1417">
@@ -28821,10 +28821,10 @@
         <v>75.25</v>
       </c>
       <c r="E1420" t="n">
-        <v>76.42</v>
+        <v>76.47</v>
       </c>
       <c r="F1420" t="n">
-        <v>79873</v>
+        <v>79280</v>
       </c>
     </row>
     <row r="1421">
@@ -28841,10 +28841,10 @@
         <v>76.40000000000001</v>
       </c>
       <c r="E1421" t="n">
-        <v>78.13</v>
+        <v>78.17</v>
       </c>
       <c r="F1421" t="n">
-        <v>69081</v>
+        <v>68613</v>
       </c>
     </row>
     <row r="1422">
@@ -28921,10 +28921,10 @@
         <v>76.90000000000001</v>
       </c>
       <c r="E1425" t="n">
-        <v>78.72</v>
+        <v>78.81</v>
       </c>
       <c r="F1425" t="n">
-        <v>94397</v>
+        <v>93699</v>
       </c>
     </row>
     <row r="1426">
@@ -28941,10 +28941,10 @@
         <v>76.56</v>
       </c>
       <c r="E1426" t="n">
-        <v>76.77</v>
+        <v>76.81</v>
       </c>
       <c r="F1426" t="n">
-        <v>109124</v>
+        <v>108329</v>
       </c>
     </row>
     <row r="1427">
@@ -29021,10 +29021,10 @@
         <v>72.20999999999999</v>
       </c>
       <c r="E1430" t="n">
-        <v>72.53</v>
+        <v>72.54000000000001</v>
       </c>
       <c r="F1430" t="n">
-        <v>109541</v>
+        <v>108713</v>
       </c>
     </row>
     <row r="1431">
@@ -29041,10 +29041,10 @@
         <v>70.45</v>
       </c>
       <c r="E1431" t="n">
-        <v>71.2</v>
+        <v>71.37</v>
       </c>
       <c r="F1431" t="n">
-        <v>116954</v>
+        <v>115759</v>
       </c>
     </row>
     <row r="1432">
@@ -29121,10 +29121,10 @@
         <v>70.31999999999999</v>
       </c>
       <c r="E1435" t="n">
-        <v>71.67</v>
+        <v>71.89</v>
       </c>
       <c r="F1435" t="n">
-        <v>115156</v>
+        <v>114181</v>
       </c>
     </row>
     <row r="1436">
@@ -29141,10 +29141,10 @@
         <v>71.09</v>
       </c>
       <c r="E1436" t="n">
-        <v>71.59999999999999</v>
+        <v>71.73</v>
       </c>
       <c r="F1436" t="n">
-        <v>99629</v>
+        <v>98569</v>
       </c>
     </row>
     <row r="1437">
@@ -29221,10 +29221,10 @@
         <v>72.26000000000001</v>
       </c>
       <c r="E1440" t="n">
-        <v>73.97</v>
+        <v>74.05</v>
       </c>
       <c r="F1440" t="n">
-        <v>89094</v>
+        <v>88395</v>
       </c>
     </row>
     <row r="1441">
@@ -29241,10 +29241,10 @@
         <v>73.28</v>
       </c>
       <c r="E1441" t="n">
-        <v>73.87</v>
+        <v>73.98</v>
       </c>
       <c r="F1441" t="n">
-        <v>72413</v>
+        <v>71635</v>
       </c>
     </row>
     <row r="1442">
@@ -29321,10 +29321,10 @@
         <v>70.20999999999999</v>
       </c>
       <c r="E1445" t="n">
-        <v>70.68000000000001</v>
+        <v>70.66</v>
       </c>
       <c r="F1445" t="n">
-        <v>155899</v>
+        <v>154979</v>
       </c>
     </row>
     <row r="1446">
@@ -29335,16 +29335,16 @@
         <v>70.68000000000001</v>
       </c>
       <c r="C1446" t="n">
-        <v>71.90000000000001</v>
+        <v>71.89</v>
       </c>
       <c r="D1446" t="n">
         <v>70.39</v>
       </c>
       <c r="E1446" t="n">
-        <v>71.79000000000001</v>
+        <v>71.81999999999999</v>
       </c>
       <c r="F1446" t="n">
-        <v>123787</v>
+        <v>122438</v>
       </c>
     </row>
     <row r="1447">
@@ -29421,10 +29421,10 @@
         <v>74.18000000000001</v>
       </c>
       <c r="E1450" t="n">
-        <v>77.28</v>
+        <v>77.58</v>
       </c>
       <c r="F1450" t="n">
-        <v>125075</v>
+        <v>123449</v>
       </c>
     </row>
     <row r="1451">
@@ -29441,10 +29441,10 @@
         <v>77.19</v>
       </c>
       <c r="E1451" t="n">
-        <v>77.73</v>
+        <v>77.87</v>
       </c>
       <c r="F1451" t="n">
-        <v>121412</v>
+        <v>120535</v>
       </c>
     </row>
     <row r="1452">
@@ -38744,7 +38744,7 @@
         <v>84.87</v>
       </c>
       <c r="F1916" t="n">
-        <v>97676</v>
+        <v>97666</v>
       </c>
     </row>
     <row r="1917">
@@ -38755,16 +38755,16 @@
         <v>85.41</v>
       </c>
       <c r="C1917" t="n">
-        <v>85.43000000000001</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="D1917" t="n">
-        <v>84.95999999999999</v>
+        <v>82.78</v>
       </c>
       <c r="E1917" t="n">
-        <v>85.40000000000001</v>
+        <v>84.41</v>
       </c>
       <c r="F1917" t="n">
-        <v>1200</v>
+        <v>42057</v>
       </c>
     </row>
   </sheetData>

--- a/database/BRENT.xlsx
+++ b/database/BRENT.xlsx
@@ -38744,7 +38744,7 @@
         <v>84.87</v>
       </c>
       <c r="F1916" t="n">
-        <v>97666</v>
+        <v>97676</v>
       </c>
     </row>
     <row r="1917">
@@ -38758,13 +38758,13 @@
         <v>85.59999999999999</v>
       </c>
       <c r="D1917" t="n">
-        <v>82.78</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="E1917" t="n">
-        <v>84.41</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="F1917" t="n">
-        <v>42057</v>
+        <v>69090</v>
       </c>
     </row>
   </sheetData>

--- a/database/BRENT.xlsx
+++ b/database/BRENT.xlsx
@@ -38744,7 +38744,7 @@
         <v>84.87</v>
       </c>
       <c r="F1916" t="n">
-        <v>97676</v>
+        <v>97666</v>
       </c>
     </row>
     <row r="1917">
@@ -38761,10 +38761,10 @@
         <v>80.59999999999999</v>
       </c>
       <c r="E1917" t="n">
-        <v>81.84999999999999</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="F1917" t="n">
-        <v>69090</v>
+        <v>74718</v>
       </c>
     </row>
   </sheetData>

--- a/database/BRENT.xlsx
+++ b/database/BRENT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1917"/>
+  <dimension ref="A1:F1918"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38744,7 +38744,7 @@
         <v>84.87</v>
       </c>
       <c r="F1916" t="n">
-        <v>97666</v>
+        <v>97673</v>
       </c>
     </row>
     <row r="1917">
@@ -38764,7 +38764,27 @@
         <v>81.73999999999999</v>
       </c>
       <c r="F1917" t="n">
-        <v>74718</v>
+        <v>74700</v>
+      </c>
+    </row>
+    <row r="1918">
+      <c r="A1918" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B1918" t="n">
+        <v>82.93000000000001</v>
+      </c>
+      <c r="C1918" t="n">
+        <v>86.90000000000001</v>
+      </c>
+      <c r="D1918" t="n">
+        <v>82.93000000000001</v>
+      </c>
+      <c r="E1918" t="n">
+        <v>85.04000000000001</v>
+      </c>
+      <c r="F1918" t="n">
+        <v>32841</v>
       </c>
     </row>
   </sheetData>

--- a/database/BRENT.xlsx
+++ b/database/BRENT.xlsx
@@ -3881,10 +3881,10 @@
         <v>60.96</v>
       </c>
       <c r="E173" t="n">
-        <v>61.74</v>
+        <v>61.65</v>
       </c>
       <c r="F173" t="n">
-        <v>7439</v>
+        <v>7745</v>
       </c>
     </row>
     <row r="174">
@@ -3952,7 +3952,7 @@
         <v>43769</v>
       </c>
       <c r="B177" t="n">
-        <v>60.17</v>
+        <v>60.27</v>
       </c>
       <c r="C177" t="n">
         <v>60.79</v>
@@ -3964,7 +3964,7 @@
         <v>59.46</v>
       </c>
       <c r="F177" t="n">
-        <v>20831</v>
+        <v>20603</v>
       </c>
     </row>
     <row r="178">
@@ -3972,7 +3972,7 @@
         <v>43770</v>
       </c>
       <c r="B178" t="n">
-        <v>59.42</v>
+        <v>59.64</v>
       </c>
       <c r="C178" t="n">
         <v>61.8</v>
@@ -3984,7 +3984,7 @@
         <v>61.65</v>
       </c>
       <c r="F178" t="n">
-        <v>18539</v>
+        <v>18281</v>
       </c>
     </row>
     <row r="179">
@@ -4061,10 +4061,10 @@
         <v>61.63</v>
       </c>
       <c r="E182" t="n">
-        <v>62.14</v>
+        <v>62.29</v>
       </c>
       <c r="F182" t="n">
-        <v>19306</v>
+        <v>19680</v>
       </c>
     </row>
     <row r="183">
@@ -4081,10 +4081,10 @@
         <v>60.65</v>
       </c>
       <c r="E183" t="n">
-        <v>62.61</v>
+        <v>62.64</v>
       </c>
       <c r="F183" t="n">
-        <v>21625</v>
+        <v>21863</v>
       </c>
     </row>
     <row r="184">
@@ -4161,10 +4161,10 @@
         <v>62.14</v>
       </c>
       <c r="E187" t="n">
-        <v>62.38</v>
+        <v>62.33</v>
       </c>
       <c r="F187" t="n">
-        <v>19157</v>
+        <v>19293</v>
       </c>
     </row>
     <row r="188">
@@ -4181,10 +4181,10 @@
         <v>61.69</v>
       </c>
       <c r="E188" t="n">
-        <v>63.32</v>
+        <v>63.41</v>
       </c>
       <c r="F188" t="n">
-        <v>15801</v>
+        <v>16092</v>
       </c>
     </row>
     <row r="189">
@@ -4261,10 +4261,10 @@
         <v>61.91</v>
       </c>
       <c r="E192" t="n">
-        <v>63.74</v>
+        <v>63.64</v>
       </c>
       <c r="F192" t="n">
-        <v>21582</v>
+        <v>21823</v>
       </c>
     </row>
     <row r="193">
@@ -4281,10 +4281,10 @@
         <v>61.92</v>
       </c>
       <c r="E193" t="n">
-        <v>62.58</v>
+        <v>62.52</v>
       </c>
       <c r="F193" t="n">
-        <v>17577</v>
+        <v>17794</v>
       </c>
     </row>
     <row r="194">
@@ -4461,10 +4461,10 @@
         <v>62.73</v>
       </c>
       <c r="E202" t="n">
-        <v>63.33</v>
+        <v>63.26</v>
       </c>
       <c r="F202" t="n">
-        <v>24042</v>
+        <v>24300</v>
       </c>
     </row>
     <row r="203">
@@ -4481,10 +4481,10 @@
         <v>62.82</v>
       </c>
       <c r="E203" t="n">
-        <v>64.22</v>
+        <v>64.34</v>
       </c>
       <c r="F203" t="n">
-        <v>22359</v>
+        <v>22572</v>
       </c>
     </row>
     <row r="204">
@@ -4561,10 +4561,10 @@
         <v>63.86</v>
       </c>
       <c r="E207" t="n">
-        <v>64.31</v>
+        <v>64.28</v>
       </c>
       <c r="F207" t="n">
-        <v>18198</v>
+        <v>18454</v>
       </c>
     </row>
     <row r="208">
@@ -4581,10 +4581,10 @@
         <v>64.48</v>
       </c>
       <c r="E208" t="n">
-        <v>64.88</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="F208" t="n">
-        <v>21484</v>
+        <v>21671</v>
       </c>
     </row>
     <row r="209">
@@ -4661,10 +4661,10 @@
         <v>66.02</v>
       </c>
       <c r="E212" t="n">
-        <v>66.45</v>
+        <v>66.53</v>
       </c>
       <c r="F212" t="n">
-        <v>10932</v>
+        <v>11180</v>
       </c>
     </row>
     <row r="213">
@@ -4681,10 +4681,10 @@
         <v>65.72</v>
       </c>
       <c r="E213" t="n">
-        <v>65.98</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="F213" t="n">
-        <v>14693</v>
+        <v>14806</v>
       </c>
     </row>
     <row r="214">
@@ -4741,10 +4741,10 @@
         <v>66.09</v>
       </c>
       <c r="E216" t="n">
-        <v>66.65000000000001</v>
+        <v>66.75</v>
       </c>
       <c r="F216" t="n">
-        <v>9409</v>
+        <v>9613</v>
       </c>
     </row>
     <row r="217">
@@ -4761,10 +4761,10 @@
         <v>66.34</v>
       </c>
       <c r="E217" t="n">
-        <v>66.81</v>
+        <v>66.84</v>
       </c>
       <c r="F217" t="n">
-        <v>11272</v>
+        <v>11398</v>
       </c>
     </row>
     <row r="218">
@@ -4821,10 +4821,10 @@
         <v>65.7</v>
       </c>
       <c r="E220" t="n">
-        <v>66.19</v>
+        <v>66.23</v>
       </c>
       <c r="F220" t="n">
-        <v>15153</v>
+        <v>15351</v>
       </c>
     </row>
     <row r="221">
@@ -4841,10 +4841,10 @@
         <v>66.19</v>
       </c>
       <c r="E221" t="n">
-        <v>68.55</v>
+        <v>68.59</v>
       </c>
       <c r="F221" t="n">
-        <v>35427</v>
+        <v>35609</v>
       </c>
     </row>
     <row r="222">
@@ -4924,7 +4924,7 @@
         <v>65.38</v>
       </c>
       <c r="F225" t="n">
-        <v>25682</v>
+        <v>25951</v>
       </c>
     </row>
     <row r="226">
@@ -4944,7 +4944,7 @@
         <v>65</v>
       </c>
       <c r="F226" t="n">
-        <v>20016</v>
+        <v>20436</v>
       </c>
     </row>
     <row r="227">
@@ -5021,10 +5021,10 @@
         <v>63.89</v>
       </c>
       <c r="E230" t="n">
-        <v>64.64</v>
+        <v>64.7</v>
       </c>
       <c r="F230" t="n">
-        <v>16107</v>
+        <v>16472</v>
       </c>
     </row>
     <row r="231">
@@ -5041,10 +5041,10 @@
         <v>64.45</v>
       </c>
       <c r="E231" t="n">
-        <v>64.95</v>
+        <v>65.08</v>
       </c>
       <c r="F231" t="n">
-        <v>16060</v>
+        <v>16251</v>
       </c>
     </row>
     <row r="232">
@@ -5121,10 +5121,10 @@
         <v>61.24</v>
       </c>
       <c r="E235" t="n">
-        <v>61.97</v>
+        <v>62.11</v>
       </c>
       <c r="F235" t="n">
-        <v>22982</v>
+        <v>23208</v>
       </c>
     </row>
     <row r="236">
@@ -5141,10 +5141,10 @@
         <v>60.24</v>
       </c>
       <c r="E236" t="n">
-        <v>60.82</v>
+        <v>60.64</v>
       </c>
       <c r="F236" t="n">
-        <v>21411</v>
+        <v>21687</v>
       </c>
     </row>
     <row r="237">
@@ -5221,10 +5221,10 @@
         <v>56.73</v>
       </c>
       <c r="E240" t="n">
-        <v>58.03</v>
+        <v>58.2</v>
       </c>
       <c r="F240" t="n">
-        <v>28317</v>
+        <v>28894</v>
       </c>
     </row>
     <row r="241">
@@ -5244,7 +5244,7 @@
         <v>56.63</v>
       </c>
       <c r="F241" t="n">
-        <v>30854</v>
+        <v>31264</v>
       </c>
     </row>
     <row r="242">
@@ -5321,10 +5321,10 @@
         <v>54.24</v>
       </c>
       <c r="E245" t="n">
-        <v>55.07</v>
+        <v>55.14</v>
       </c>
       <c r="F245" t="n">
-        <v>31638</v>
+        <v>31917</v>
       </c>
     </row>
     <row r="246">
@@ -5341,10 +5341,10 @@
         <v>54.2</v>
       </c>
       <c r="E246" t="n">
-        <v>54.48</v>
+        <v>54.45</v>
       </c>
       <c r="F246" t="n">
-        <v>25828</v>
+        <v>26144</v>
       </c>
     </row>
     <row r="247">
@@ -5421,10 +5421,10 @@
         <v>54.95</v>
       </c>
       <c r="E250" t="n">
-        <v>56.51</v>
+        <v>56.4</v>
       </c>
       <c r="F250" t="n">
-        <v>24675</v>
+        <v>24914</v>
       </c>
     </row>
     <row r="251">
@@ -5441,10 +5441,10 @@
         <v>56.13</v>
       </c>
       <c r="E251" t="n">
-        <v>57.32</v>
+        <v>57.33</v>
       </c>
       <c r="F251" t="n">
-        <v>21410</v>
+        <v>21778</v>
       </c>
     </row>
     <row r="252">
@@ -5521,10 +5521,10 @@
         <v>58.89</v>
       </c>
       <c r="E255" t="n">
-        <v>59.28</v>
+        <v>59.03</v>
       </c>
       <c r="F255" t="n">
-        <v>23121</v>
+        <v>23391</v>
       </c>
     </row>
     <row r="256">
@@ -5541,10 +5541,10 @@
         <v>57.71</v>
       </c>
       <c r="E256" t="n">
-        <v>58.33</v>
+        <v>58.44</v>
       </c>
       <c r="F256" t="n">
-        <v>26663</v>
+        <v>26971</v>
       </c>
     </row>
     <row r="257">
@@ -5621,10 +5621,10 @@
         <v>50.38</v>
       </c>
       <c r="E260" t="n">
-        <v>51.35</v>
+        <v>50.95</v>
       </c>
       <c r="F260" t="n">
-        <v>51199</v>
+        <v>52807</v>
       </c>
     </row>
     <row r="261">
@@ -5641,10 +5641,10 @@
         <v>48.92</v>
       </c>
       <c r="E261" t="n">
-        <v>50.01</v>
+        <v>50.08</v>
       </c>
       <c r="F261" t="n">
-        <v>71739</v>
+        <v>72794</v>
       </c>
     </row>
     <row r="262">
@@ -5721,10 +5721,10 @@
         <v>49.67</v>
       </c>
       <c r="E265" t="n">
-        <v>49.95</v>
+        <v>50</v>
       </c>
       <c r="F265" t="n">
-        <v>42080</v>
+        <v>42678</v>
       </c>
     </row>
     <row r="266">
@@ -5741,10 +5741,10 @@
         <v>45.16</v>
       </c>
       <c r="E266" t="n">
-        <v>45.55</v>
+        <v>45.51</v>
       </c>
       <c r="F266" t="n">
-        <v>64437</v>
+        <v>65295</v>
       </c>
     </row>
     <row r="267">
@@ -5812,7 +5812,7 @@
         <v>43902</v>
       </c>
       <c r="B270" t="n">
-        <v>35.97</v>
+        <v>36.29</v>
       </c>
       <c r="C270" t="n">
         <v>36.45</v>
@@ -5824,7 +5824,7 @@
         <v>33.49</v>
       </c>
       <c r="F270" t="n">
-        <v>66181</v>
+        <v>64469</v>
       </c>
     </row>
     <row r="271">
@@ -6121,10 +6121,10 @@
         <v>26.12</v>
       </c>
       <c r="E285" t="n">
-        <v>30.29</v>
+        <v>29.96</v>
       </c>
       <c r="F285" t="n">
-        <v>210087</v>
+        <v>214756</v>
       </c>
     </row>
     <row r="286">
@@ -6135,16 +6135,16 @@
         <v>29.95</v>
       </c>
       <c r="C286" t="n">
-        <v>35.24</v>
+        <v>35.28</v>
       </c>
       <c r="D286" t="n">
         <v>28.9</v>
       </c>
       <c r="E286" t="n">
-        <v>34.72</v>
+        <v>35.16</v>
       </c>
       <c r="F286" t="n">
-        <v>275171</v>
+        <v>280402</v>
       </c>
     </row>
     <row r="287">
@@ -6221,10 +6221,10 @@
         <v>32.46</v>
       </c>
       <c r="E290" t="n">
-        <v>33.2</v>
+        <v>32.8</v>
       </c>
       <c r="F290" t="n">
-        <v>230614</v>
+        <v>236196</v>
       </c>
     </row>
     <row r="291">
@@ -6321,10 +6321,10 @@
         <v>29.42</v>
       </c>
       <c r="E295" t="n">
-        <v>30.65</v>
+        <v>30.59</v>
       </c>
       <c r="F295" t="n">
-        <v>146842</v>
+        <v>151526</v>
       </c>
     </row>
     <row r="296">
@@ -6341,10 +6341,10 @@
         <v>30.13</v>
       </c>
       <c r="E296" t="n">
-        <v>30.78</v>
+        <v>30.68</v>
       </c>
       <c r="F296" t="n">
-        <v>171223</v>
+        <v>174982</v>
       </c>
     </row>
     <row r="297">
@@ -6421,10 +6421,10 @@
         <v>23.38</v>
       </c>
       <c r="E300" t="n">
-        <v>24.74</v>
+        <v>24.73</v>
       </c>
       <c r="F300" t="n">
-        <v>213310</v>
+        <v>216653</v>
       </c>
     </row>
     <row r="301">
@@ -6441,10 +6441,10 @@
         <v>23.7</v>
       </c>
       <c r="E301" t="n">
-        <v>24.98</v>
+        <v>24.99</v>
       </c>
       <c r="F301" t="n">
-        <v>163124</v>
+        <v>166443</v>
       </c>
     </row>
     <row r="302">
@@ -6521,10 +6521,10 @@
         <v>24.33</v>
       </c>
       <c r="E305" t="n">
-        <v>26.83</v>
+        <v>26.85</v>
       </c>
       <c r="F305" t="n">
-        <v>224455</v>
+        <v>229615</v>
       </c>
     </row>
     <row r="306">
@@ -6541,10 +6541,10 @@
         <v>26.05</v>
       </c>
       <c r="E306" t="n">
-        <v>26.78</v>
+        <v>26.81</v>
       </c>
       <c r="F306" t="n">
-        <v>196748</v>
+        <v>199609</v>
       </c>
     </row>
     <row r="307">
@@ -6621,10 +6621,10 @@
         <v>29.4</v>
       </c>
       <c r="E310" t="n">
-        <v>29.48</v>
+        <v>29.65</v>
       </c>
       <c r="F310" t="n">
-        <v>225301</v>
+        <v>229585</v>
       </c>
     </row>
     <row r="311">
@@ -6641,10 +6641,10 @@
         <v>29.63</v>
       </c>
       <c r="E311" t="n">
-        <v>31.26</v>
+        <v>31.25</v>
       </c>
       <c r="F311" t="n">
-        <v>192233</v>
+        <v>195288</v>
       </c>
     </row>
     <row r="312">
@@ -6715,16 +6715,16 @@
         <v>29.73</v>
       </c>
       <c r="C315" t="n">
-        <v>31.65</v>
+        <v>31.75</v>
       </c>
       <c r="D315" t="n">
         <v>29.32</v>
       </c>
       <c r="E315" t="n">
-        <v>31.44</v>
+        <v>31.58</v>
       </c>
       <c r="F315" t="n">
-        <v>152193</v>
+        <v>156389</v>
       </c>
     </row>
     <row r="316">
@@ -6735,16 +6735,16 @@
         <v>31.58</v>
       </c>
       <c r="C316" t="n">
-        <v>32.96</v>
+        <v>33.06</v>
       </c>
       <c r="D316" t="n">
         <v>31.23</v>
       </c>
       <c r="E316" t="n">
-        <v>32.9</v>
+        <v>32.94</v>
       </c>
       <c r="F316" t="n">
-        <v>160121</v>
+        <v>163209</v>
       </c>
     </row>
     <row r="317">
@@ -6821,10 +6821,10 @@
         <v>35.92</v>
       </c>
       <c r="E320" t="n">
-        <v>36.38</v>
+        <v>36.3</v>
       </c>
       <c r="F320" t="n">
-        <v>157279</v>
+        <v>160329</v>
       </c>
     </row>
     <row r="321">
@@ -6841,10 +6841,10 @@
         <v>33.87</v>
       </c>
       <c r="E321" t="n">
-        <v>35.66</v>
+        <v>35.52</v>
       </c>
       <c r="F321" t="n">
-        <v>194062</v>
+        <v>198023</v>
       </c>
     </row>
     <row r="322">
@@ -6921,10 +6921,10 @@
         <v>34.37</v>
       </c>
       <c r="E325" t="n">
-        <v>35.89</v>
+        <v>35.98</v>
       </c>
       <c r="F325" t="n">
-        <v>208524</v>
+        <v>213086</v>
       </c>
     </row>
     <row r="326">
@@ -6941,10 +6941,10 @@
         <v>34.87</v>
       </c>
       <c r="E326" t="n">
-        <v>37.43</v>
+        <v>37.61</v>
       </c>
       <c r="F326" t="n">
-        <v>193664</v>
+        <v>198370</v>
       </c>
     </row>
     <row r="327">
@@ -7021,10 +7021,10 @@
         <v>39.05</v>
       </c>
       <c r="E330" t="n">
-        <v>39.78</v>
+        <v>39.92</v>
       </c>
       <c r="F330" t="n">
-        <v>158433</v>
+        <v>161661</v>
       </c>
     </row>
     <row r="331">
@@ -7041,10 +7041,10 @@
         <v>39.75</v>
       </c>
       <c r="E331" t="n">
-        <v>42.14</v>
+        <v>41.83</v>
       </c>
       <c r="F331" t="n">
-        <v>163467</v>
+        <v>167359</v>
       </c>
     </row>
     <row r="332">
@@ -7121,10 +7121,10 @@
         <v>37.96</v>
       </c>
       <c r="E335" t="n">
-        <v>38.36</v>
+        <v>38.41</v>
       </c>
       <c r="F335" t="n">
-        <v>221502</v>
+        <v>227925</v>
       </c>
     </row>
     <row r="336">
@@ -7141,10 +7141,10 @@
         <v>37.14</v>
       </c>
       <c r="E336" t="n">
-        <v>38.94</v>
+        <v>38.97</v>
       </c>
       <c r="F336" t="n">
-        <v>260674</v>
+        <v>263342</v>
       </c>
     </row>
     <row r="337">
@@ -7221,10 +7221,10 @@
         <v>40.05</v>
       </c>
       <c r="E340" t="n">
-        <v>41.37</v>
+        <v>41.33</v>
       </c>
       <c r="F340" t="n">
-        <v>161532</v>
+        <v>163774</v>
       </c>
     </row>
     <row r="341">
@@ -7241,10 +7241,10 @@
         <v>40.97</v>
       </c>
       <c r="E341" t="n">
-        <v>41.99</v>
+        <v>41.78</v>
       </c>
       <c r="F341" t="n">
-        <v>153177</v>
+        <v>156573</v>
       </c>
     </row>
     <row r="342">
@@ -7315,16 +7315,16 @@
         <v>40.45</v>
       </c>
       <c r="C345" t="n">
-        <v>41.51</v>
+        <v>41.59</v>
       </c>
       <c r="D345" t="n">
         <v>39.68</v>
       </c>
       <c r="E345" t="n">
-        <v>41.39</v>
+        <v>41.35</v>
       </c>
       <c r="F345" t="n">
-        <v>178413</v>
+        <v>181021</v>
       </c>
     </row>
     <row r="346">
@@ -7341,10 +7341,10 @@
         <v>40.25</v>
       </c>
       <c r="E346" t="n">
-        <v>40.58</v>
+        <v>40.57</v>
       </c>
       <c r="F346" t="n">
-        <v>157969</v>
+        <v>160433</v>
       </c>
     </row>
     <row r="347">
@@ -7421,10 +7421,10 @@
         <v>41.71</v>
       </c>
       <c r="E350" t="n">
-        <v>42.71</v>
+        <v>42.65</v>
       </c>
       <c r="F350" t="n">
-        <v>142409</v>
+        <v>144329</v>
       </c>
     </row>
     <row r="351">
@@ -7521,10 +7521,10 @@
         <v>41.99</v>
       </c>
       <c r="E355" t="n">
-        <v>42.32</v>
+        <v>42.35</v>
       </c>
       <c r="F355" t="n">
-        <v>133908</v>
+        <v>136451</v>
       </c>
     </row>
     <row r="356">
@@ -7541,10 +7541,10 @@
         <v>41.4</v>
       </c>
       <c r="E356" t="n">
-        <v>43.23</v>
+        <v>43.26</v>
       </c>
       <c r="F356" t="n">
-        <v>152491</v>
+        <v>154800</v>
       </c>
     </row>
     <row r="357">
@@ -7621,10 +7621,10 @@
         <v>43.19</v>
       </c>
       <c r="E360" t="n">
-        <v>43.36</v>
+        <v>43.28</v>
       </c>
       <c r="F360" t="n">
-        <v>99613</v>
+        <v>101544</v>
       </c>
     </row>
     <row r="361">
@@ -7641,10 +7641,10 @@
         <v>42.7</v>
       </c>
       <c r="E361" t="n">
-        <v>43.18</v>
+        <v>43.12</v>
       </c>
       <c r="F361" t="n">
-        <v>93740</v>
+        <v>95049</v>
       </c>
     </row>
     <row r="362">
@@ -7721,10 +7721,10 @@
         <v>43.42</v>
       </c>
       <c r="E365" t="n">
-        <v>43.82</v>
+        <v>43.53</v>
       </c>
       <c r="F365" t="n">
-        <v>109900</v>
+        <v>112495</v>
       </c>
     </row>
     <row r="366">
@@ -7741,10 +7741,10 @@
         <v>43.18</v>
       </c>
       <c r="E366" t="n">
-        <v>43.67</v>
+        <v>43.62</v>
       </c>
       <c r="F366" t="n">
-        <v>115737</v>
+        <v>117377</v>
       </c>
     </row>
     <row r="367">
@@ -7821,10 +7821,10 @@
         <v>41.95</v>
       </c>
       <c r="E370" t="n">
-        <v>43.43</v>
+        <v>43.56</v>
       </c>
       <c r="F370" t="n">
-        <v>113377</v>
+        <v>117072</v>
       </c>
     </row>
     <row r="371">
@@ -7841,10 +7841,10 @@
         <v>42.94</v>
       </c>
       <c r="E371" t="n">
-        <v>43.65</v>
+        <v>43.59</v>
       </c>
       <c r="F371" t="n">
-        <v>127155</v>
+        <v>128800</v>
       </c>
     </row>
     <row r="372">
@@ -7921,10 +7921,10 @@
         <v>44.96</v>
       </c>
       <c r="E375" t="n">
-        <v>45.28</v>
+        <v>45.13</v>
       </c>
       <c r="F375" t="n">
-        <v>120720</v>
+        <v>122044</v>
       </c>
     </row>
     <row r="376">
@@ -7941,10 +7941,10 @@
         <v>44.4</v>
       </c>
       <c r="E376" t="n">
-        <v>44.76</v>
+        <v>44.71</v>
       </c>
       <c r="F376" t="n">
-        <v>119541</v>
+        <v>120731</v>
       </c>
     </row>
     <row r="377">
@@ -8021,10 +8021,10 @@
         <v>45.07</v>
       </c>
       <c r="E380" t="n">
-        <v>45.3</v>
+        <v>45.24</v>
       </c>
       <c r="F380" t="n">
-        <v>90204</v>
+        <v>91702</v>
       </c>
     </row>
     <row r="381">
@@ -8041,10 +8041,10 @@
         <v>44.77</v>
       </c>
       <c r="E381" t="n">
-        <v>45.2</v>
+        <v>45.19</v>
       </c>
       <c r="F381" t="n">
-        <v>83793</v>
+        <v>85013</v>
       </c>
     </row>
     <row r="382">
@@ -8121,10 +8121,10 @@
         <v>44.46</v>
       </c>
       <c r="E385" t="n">
-        <v>45.36</v>
+        <v>45.27</v>
       </c>
       <c r="F385" t="n">
-        <v>86301</v>
+        <v>87294</v>
       </c>
     </row>
     <row r="386">
@@ -8141,10 +8141,10 @@
         <v>44.09</v>
       </c>
       <c r="E386" t="n">
-        <v>44.79</v>
+        <v>44.69</v>
       </c>
       <c r="F386" t="n">
-        <v>77659</v>
+        <v>78965</v>
       </c>
     </row>
     <row r="387">
@@ -8224,7 +8224,7 @@
         <v>45.59</v>
       </c>
       <c r="F390" t="n">
-        <v>95873</v>
+        <v>96916</v>
       </c>
     </row>
     <row r="391">
@@ -8241,10 +8241,10 @@
         <v>45.36</v>
       </c>
       <c r="E391" t="n">
-        <v>45.89</v>
+        <v>45.85</v>
       </c>
       <c r="F391" t="n">
-        <v>81058</v>
+        <v>81841</v>
       </c>
     </row>
     <row r="392">
@@ -8321,10 +8321,10 @@
         <v>43.27</v>
       </c>
       <c r="E395" t="n">
-        <v>44.09</v>
+        <v>44.07</v>
       </c>
       <c r="F395" t="n">
-        <v>157249</v>
+        <v>158723</v>
       </c>
     </row>
     <row r="396">
@@ -8338,13 +8338,13 @@
         <v>44.69</v>
       </c>
       <c r="D396" t="n">
-        <v>42.45</v>
+        <v>42.42</v>
       </c>
       <c r="E396" t="n">
-        <v>42.53</v>
+        <v>42.43</v>
       </c>
       <c r="F396" t="n">
-        <v>160902</v>
+        <v>162787</v>
       </c>
     </row>
     <row r="397">
@@ -8418,13 +8418,13 @@
         <v>41.23</v>
       </c>
       <c r="D400" t="n">
-        <v>40.02</v>
+        <v>39.96</v>
       </c>
       <c r="E400" t="n">
-        <v>40.07</v>
+        <v>39.97</v>
       </c>
       <c r="F400" t="n">
-        <v>147551</v>
+        <v>149451</v>
       </c>
     </row>
     <row r="401">
@@ -8441,10 +8441,10 @@
         <v>39.68</v>
       </c>
       <c r="E401" t="n">
-        <v>40.24</v>
+        <v>40.02</v>
       </c>
       <c r="F401" t="n">
-        <v>133943</v>
+        <v>135456</v>
       </c>
     </row>
     <row r="402">
@@ -8521,10 +8521,10 @@
         <v>41.89</v>
       </c>
       <c r="E405" t="n">
-        <v>43.67</v>
+        <v>43.58</v>
       </c>
       <c r="F405" t="n">
-        <v>141089</v>
+        <v>142611</v>
       </c>
     </row>
     <row r="406">
@@ -8541,10 +8541,10 @@
         <v>42.92</v>
       </c>
       <c r="E406" t="n">
-        <v>43.34</v>
+        <v>43.41</v>
       </c>
       <c r="F406" t="n">
-        <v>127380</v>
+        <v>129546</v>
       </c>
     </row>
     <row r="407">
@@ -8621,10 +8621,10 @@
         <v>41.68</v>
       </c>
       <c r="E410" t="n">
-        <v>42.27</v>
+        <v>42.16</v>
       </c>
       <c r="F410" t="n">
-        <v>132502</v>
+        <v>133961</v>
       </c>
     </row>
     <row r="411">
@@ -8641,10 +8641,10 @@
         <v>41.97</v>
       </c>
       <c r="E411" t="n">
-        <v>42.24</v>
+        <v>42.17</v>
       </c>
       <c r="F411" t="n">
-        <v>100264</v>
+        <v>102107</v>
       </c>
     </row>
     <row r="412">
@@ -8721,10 +8721,10 @@
         <v>39.98</v>
       </c>
       <c r="E415" t="n">
-        <v>40.93</v>
+        <v>40.75</v>
       </c>
       <c r="F415" t="n">
-        <v>155461</v>
+        <v>157712</v>
       </c>
     </row>
     <row r="416">
@@ -8741,10 +8741,10 @@
         <v>38.88</v>
       </c>
       <c r="E416" t="n">
-        <v>39.23</v>
+        <v>39.15</v>
       </c>
       <c r="F416" t="n">
-        <v>188336</v>
+        <v>190634</v>
       </c>
     </row>
     <row r="417">
@@ -8821,10 +8821,10 @@
         <v>42.02</v>
       </c>
       <c r="E420" t="n">
-        <v>43.54</v>
+        <v>43.52</v>
       </c>
       <c r="F420" t="n">
-        <v>110782</v>
+        <v>112342</v>
       </c>
     </row>
     <row r="421">
@@ -8841,10 +8841,10 @@
         <v>42.78</v>
       </c>
       <c r="E421" t="n">
-        <v>42.96</v>
+        <v>42.89</v>
       </c>
       <c r="F421" t="n">
-        <v>108274</v>
+        <v>109695</v>
       </c>
     </row>
     <row r="422">
@@ -8921,10 +8921,10 @@
         <v>41.79</v>
       </c>
       <c r="E425" t="n">
-        <v>43.38</v>
+        <v>43.26</v>
       </c>
       <c r="F425" t="n">
-        <v>146298</v>
+        <v>147757</v>
       </c>
     </row>
     <row r="426">
@@ -8941,10 +8941,10 @@
         <v>42.47</v>
       </c>
       <c r="E426" t="n">
-        <v>43.02</v>
+        <v>42.95</v>
       </c>
       <c r="F426" t="n">
-        <v>129338</v>
+        <v>130839</v>
       </c>
     </row>
     <row r="427">
@@ -9021,10 +9021,10 @@
         <v>41.72</v>
       </c>
       <c r="E430" t="n">
-        <v>42.71</v>
+        <v>42.59</v>
       </c>
       <c r="F430" t="n">
-        <v>108471</v>
+        <v>110171</v>
       </c>
     </row>
     <row r="431">
@@ -9041,10 +9041,10 @@
         <v>41.76</v>
       </c>
       <c r="E431" t="n">
-        <v>41.93</v>
+        <v>41.85</v>
       </c>
       <c r="F431" t="n">
-        <v>95688</v>
+        <v>97195</v>
       </c>
     </row>
     <row r="432">
@@ -9112,7 +9112,7 @@
         <v>44133</v>
       </c>
       <c r="B435" t="n">
-        <v>39.52</v>
+        <v>39.76</v>
       </c>
       <c r="C435" t="n">
         <v>39.97</v>
@@ -9124,7 +9124,7 @@
         <v>38.05</v>
       </c>
       <c r="F435" t="n">
-        <v>183949</v>
+        <v>179602</v>
       </c>
     </row>
     <row r="436">
@@ -9132,7 +9132,7 @@
         <v>44134</v>
       </c>
       <c r="B436" t="n">
-        <v>38.05</v>
+        <v>38.25</v>
       </c>
       <c r="C436" t="n">
         <v>38.72</v>
@@ -9144,7 +9144,7 @@
         <v>37.84</v>
       </c>
       <c r="F436" t="n">
-        <v>184633</v>
+        <v>181739</v>
       </c>
     </row>
     <row r="437">
@@ -9221,10 +9221,10 @@
         <v>40.42</v>
       </c>
       <c r="E440" t="n">
-        <v>40.82</v>
+        <v>40.68</v>
       </c>
       <c r="F440" t="n">
-        <v>155706</v>
+        <v>157779</v>
       </c>
     </row>
     <row r="441">
@@ -9241,10 +9241,10 @@
         <v>39.46</v>
       </c>
       <c r="E441" t="n">
-        <v>39.84</v>
+        <v>39.71</v>
       </c>
       <c r="F441" t="n">
-        <v>150078</v>
+        <v>151438</v>
       </c>
     </row>
     <row r="442">
@@ -9318,13 +9318,13 @@
         <v>44.59</v>
       </c>
       <c r="D445" t="n">
-        <v>43.42</v>
+        <v>43.35</v>
       </c>
       <c r="E445" t="n">
-        <v>43.49</v>
+        <v>43.38</v>
       </c>
       <c r="F445" t="n">
-        <v>144322</v>
+        <v>146964</v>
       </c>
     </row>
     <row r="446">
@@ -9338,13 +9338,13 @@
         <v>43.45</v>
       </c>
       <c r="D446" t="n">
-        <v>42.77</v>
+        <v>42.68</v>
       </c>
       <c r="E446" t="n">
-        <v>42.88</v>
+        <v>42.69</v>
       </c>
       <c r="F446" t="n">
-        <v>112789</v>
+        <v>114191</v>
       </c>
     </row>
     <row r="447">
@@ -9421,10 +9421,10 @@
         <v>43.87</v>
       </c>
       <c r="E450" t="n">
-        <v>44.44</v>
+        <v>44.21</v>
       </c>
       <c r="F450" t="n">
-        <v>111013</v>
+        <v>112468</v>
       </c>
     </row>
     <row r="451">
@@ -9441,10 +9441,10 @@
         <v>44.15</v>
       </c>
       <c r="E451" t="n">
-        <v>45.06</v>
+        <v>45.07</v>
       </c>
       <c r="F451" t="n">
-        <v>88612</v>
+        <v>90427</v>
       </c>
     </row>
     <row r="452">
@@ -9624,7 +9624,7 @@
         <v>48.65</v>
       </c>
       <c r="F460" t="n">
-        <v>119976</v>
+        <v>122403</v>
       </c>
     </row>
     <row r="461">
@@ -9641,10 +9641,10 @@
         <v>48.77</v>
       </c>
       <c r="E461" t="n">
-        <v>48.97</v>
+        <v>48.96</v>
       </c>
       <c r="F461" t="n">
-        <v>124413</v>
+        <v>125701</v>
       </c>
     </row>
     <row r="462">
@@ -9721,10 +9721,10 @@
         <v>48.79</v>
       </c>
       <c r="E465" t="n">
-        <v>50.26</v>
+        <v>50.25</v>
       </c>
       <c r="F465" t="n">
-        <v>130125</v>
+        <v>132386</v>
       </c>
     </row>
     <row r="466">
@@ -9741,10 +9741,10 @@
         <v>49.67</v>
       </c>
       <c r="E466" t="n">
-        <v>49.94</v>
+        <v>49.86</v>
       </c>
       <c r="F466" t="n">
-        <v>123293</v>
+        <v>124721</v>
       </c>
     </row>
     <row r="467">
@@ -9821,10 +9821,10 @@
         <v>51.06</v>
       </c>
       <c r="E470" t="n">
-        <v>51.55</v>
+        <v>51.46</v>
       </c>
       <c r="F470" t="n">
-        <v>100894</v>
+        <v>102867</v>
       </c>
     </row>
     <row r="471">
@@ -9841,10 +9841,10 @@
         <v>51.16</v>
       </c>
       <c r="E471" t="n">
-        <v>52.19</v>
+        <v>52.23</v>
       </c>
       <c r="F471" t="n">
-        <v>96861</v>
+        <v>98705</v>
       </c>
     </row>
     <row r="472">
@@ -10081,10 +10081,10 @@
         <v>53.88</v>
       </c>
       <c r="E483" t="n">
-        <v>54.45</v>
+        <v>54.34</v>
       </c>
       <c r="F483" t="n">
-        <v>140683</v>
+        <v>142258</v>
       </c>
     </row>
     <row r="484">
@@ -10095,16 +10095,16 @@
         <v>54.46</v>
       </c>
       <c r="C484" t="n">
-        <v>56.06</v>
+        <v>56.2</v>
       </c>
       <c r="D484" t="n">
         <v>54.3</v>
       </c>
       <c r="E484" t="n">
-        <v>56.02</v>
+        <v>56.11</v>
       </c>
       <c r="F484" t="n">
-        <v>151805</v>
+        <v>155413</v>
       </c>
     </row>
     <row r="485">
@@ -10181,10 +10181,10 @@
         <v>55.21</v>
       </c>
       <c r="E488" t="n">
-        <v>56.3</v>
+        <v>56.37</v>
       </c>
       <c r="F488" t="n">
-        <v>123090</v>
+        <v>125098</v>
       </c>
     </row>
     <row r="489">
@@ -10201,10 +10201,10 @@
         <v>54.63</v>
       </c>
       <c r="E489" t="n">
-        <v>54.94</v>
+        <v>54.75</v>
       </c>
       <c r="F489" t="n">
-        <v>133988</v>
+        <v>135898</v>
       </c>
     </row>
     <row r="490">
@@ -10281,10 +10281,10 @@
         <v>55.38</v>
       </c>
       <c r="E493" t="n">
-        <v>55.86</v>
+        <v>55.84</v>
       </c>
       <c r="F493" t="n">
-        <v>103188</v>
+        <v>104851</v>
       </c>
     </row>
     <row r="494">
@@ -10301,10 +10301,10 @@
         <v>54.38</v>
       </c>
       <c r="E494" t="n">
-        <v>55.08</v>
+        <v>54.88</v>
       </c>
       <c r="F494" t="n">
-        <v>133367</v>
+        <v>135622</v>
       </c>
     </row>
     <row r="495">
@@ -10378,13 +10378,13 @@
         <v>56.16</v>
       </c>
       <c r="D498" t="n">
-        <v>54.93</v>
+        <v>54.84</v>
       </c>
       <c r="E498" t="n">
-        <v>55</v>
+        <v>54.84</v>
       </c>
       <c r="F498" t="n">
-        <v>160473</v>
+        <v>162289</v>
       </c>
     </row>
     <row r="499">
@@ -10401,10 +10401,10 @@
         <v>54.84</v>
       </c>
       <c r="E499" t="n">
-        <v>55</v>
+        <v>54.93</v>
       </c>
       <c r="F499" t="n">
-        <v>160923</v>
+        <v>163671</v>
       </c>
     </row>
     <row r="500">
@@ -10481,10 +10481,10 @@
         <v>57.93</v>
       </c>
       <c r="E503" t="n">
-        <v>58.79</v>
+        <v>58.87</v>
       </c>
       <c r="F503" t="n">
-        <v>123567</v>
+        <v>125851</v>
       </c>
     </row>
     <row r="504">
@@ -10501,10 +10501,10 @@
         <v>58.87</v>
       </c>
       <c r="E504" t="n">
-        <v>59.31</v>
+        <v>59.41</v>
       </c>
       <c r="F504" t="n">
-        <v>118436</v>
+        <v>120954</v>
       </c>
     </row>
     <row r="505">
@@ -10578,13 +10578,13 @@
         <v>61.23</v>
       </c>
       <c r="D508" t="n">
-        <v>60.5</v>
+        <v>60.44</v>
       </c>
       <c r="E508" t="n">
-        <v>60.6</v>
+        <v>60.52</v>
       </c>
       <c r="F508" t="n">
-        <v>104511</v>
+        <v>107974</v>
       </c>
     </row>
     <row r="509">
@@ -10604,7 +10604,7 @@
         <v>62.22</v>
       </c>
       <c r="F509" t="n">
-        <v>123306</v>
+        <v>126905</v>
       </c>
     </row>
     <row r="510">
@@ -10681,10 +10681,10 @@
         <v>62.54</v>
       </c>
       <c r="E513" t="n">
-        <v>62.75</v>
+        <v>62.88</v>
       </c>
       <c r="F513" t="n">
-        <v>170306</v>
+        <v>173632</v>
       </c>
     </row>
     <row r="514">
@@ -10701,10 +10701,10 @@
         <v>61.42</v>
       </c>
       <c r="E514" t="n">
-        <v>61.95</v>
+        <v>61.97</v>
       </c>
       <c r="F514" t="n">
-        <v>181146</v>
+        <v>184306</v>
       </c>
     </row>
     <row r="515">
@@ -10781,10 +10781,10 @@
         <v>65.55</v>
       </c>
       <c r="E518" t="n">
-        <v>65.86</v>
+        <v>65.97</v>
       </c>
       <c r="F518" t="n">
-        <v>210726</v>
+        <v>215533</v>
       </c>
     </row>
     <row r="519">
@@ -10801,10 +10801,10 @@
         <v>64.13</v>
       </c>
       <c r="E519" t="n">
-        <v>64.25</v>
+        <v>64.27</v>
       </c>
       <c r="F519" t="n">
-        <v>234931</v>
+        <v>239274</v>
       </c>
     </row>
     <row r="520">
@@ -10881,10 +10881,10 @@
         <v>63.17</v>
       </c>
       <c r="E523" t="n">
-        <v>66.94</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="F523" t="n">
-        <v>225843</v>
+        <v>230530</v>
       </c>
     </row>
     <row r="524">
@@ -10895,16 +10895,16 @@
         <v>66.86</v>
       </c>
       <c r="C524" t="n">
-        <v>69.31999999999999</v>
+        <v>69.41</v>
       </c>
       <c r="D524" t="n">
         <v>66.43000000000001</v>
       </c>
       <c r="E524" t="n">
-        <v>69.28</v>
+        <v>69.25</v>
       </c>
       <c r="F524" t="n">
-        <v>249828</v>
+        <v>253026</v>
       </c>
     </row>
     <row r="525">
@@ -10981,10 +10981,10 @@
         <v>67.68000000000001</v>
       </c>
       <c r="E528" t="n">
-        <v>69.40000000000001</v>
+        <v>69.17</v>
       </c>
       <c r="F528" t="n">
-        <v>160838</v>
+        <v>163581</v>
       </c>
     </row>
     <row r="529">
@@ -11001,10 +11001,10 @@
         <v>68.66</v>
       </c>
       <c r="E529" t="n">
-        <v>68.88</v>
+        <v>68.81</v>
       </c>
       <c r="F529" t="n">
-        <v>148823</v>
+        <v>151042</v>
       </c>
     </row>
     <row r="530">
@@ -11072,7 +11072,7 @@
         <v>44273</v>
       </c>
       <c r="B533" t="n">
-        <v>67.48</v>
+        <v>67.47</v>
       </c>
       <c r="C533" t="n">
         <v>67.83</v>
@@ -11084,7 +11084,7 @@
         <v>62.5</v>
       </c>
       <c r="F533" t="n">
-        <v>212082</v>
+        <v>209835</v>
       </c>
     </row>
     <row r="534">
@@ -11092,7 +11092,7 @@
         <v>44274</v>
       </c>
       <c r="B534" t="n">
-        <v>62.78</v>
+        <v>63.02</v>
       </c>
       <c r="C534" t="n">
         <v>64.73</v>
@@ -11104,7 +11104,7 @@
         <v>64.31999999999999</v>
       </c>
       <c r="F534" t="n">
-        <v>228148</v>
+        <v>223529</v>
       </c>
     </row>
     <row r="535">
@@ -11172,10 +11172,10 @@
         <v>44280</v>
       </c>
       <c r="B538" t="n">
-        <v>63.95</v>
+        <v>63.89</v>
       </c>
       <c r="C538" t="n">
-        <v>64.01000000000001</v>
+        <v>63.9</v>
       </c>
       <c r="D538" t="n">
         <v>60.82</v>
@@ -11184,7 +11184,7 @@
         <v>61.47</v>
       </c>
       <c r="F538" t="n">
-        <v>206155</v>
+        <v>203253</v>
       </c>
     </row>
     <row r="539">
@@ -11192,19 +11192,19 @@
         <v>44281</v>
       </c>
       <c r="B539" t="n">
-        <v>61.47</v>
+        <v>62.45</v>
       </c>
       <c r="C539" t="n">
         <v>64.73</v>
       </c>
       <c r="D539" t="n">
-        <v>61.47</v>
+        <v>62.07</v>
       </c>
       <c r="E539" t="n">
         <v>64.19</v>
       </c>
       <c r="F539" t="n">
-        <v>171041</v>
+        <v>167422</v>
       </c>
     </row>
     <row r="540">
@@ -11284,7 +11284,7 @@
         <v>64.51000000000001</v>
       </c>
       <c r="F543" t="n">
-        <v>197783</v>
+        <v>201289</v>
       </c>
     </row>
     <row r="544">
@@ -11361,10 +11361,10 @@
         <v>62.18</v>
       </c>
       <c r="E547" t="n">
-        <v>63.07</v>
+        <v>63.04</v>
       </c>
       <c r="F547" t="n">
-        <v>146277</v>
+        <v>149186</v>
       </c>
     </row>
     <row r="548">
@@ -11381,10 +11381,10 @@
         <v>62.33</v>
       </c>
       <c r="E548" t="n">
-        <v>62.81</v>
+        <v>62.76</v>
       </c>
       <c r="F548" t="n">
-        <v>119219</v>
+        <v>121247</v>
       </c>
     </row>
     <row r="549">
@@ -11461,10 +11461,10 @@
         <v>65.65000000000001</v>
       </c>
       <c r="E552" t="n">
-        <v>66.5</v>
+        <v>66.45</v>
       </c>
       <c r="F552" t="n">
-        <v>133306</v>
+        <v>135521</v>
       </c>
     </row>
     <row r="553">
@@ -11481,10 +11481,10 @@
         <v>66.11</v>
       </c>
       <c r="E553" t="n">
-        <v>66.40000000000001</v>
+        <v>66.31999999999999</v>
       </c>
       <c r="F553" t="n">
-        <v>120895</v>
+        <v>122938</v>
       </c>
     </row>
     <row r="554">
@@ -11564,7 +11564,7 @@
         <v>64.95</v>
       </c>
       <c r="F557" t="n">
-        <v>140975</v>
+        <v>143350</v>
       </c>
     </row>
     <row r="558">
@@ -11581,10 +11581,10 @@
         <v>64.52</v>
       </c>
       <c r="E558" t="n">
-        <v>65.45</v>
+        <v>65.31999999999999</v>
       </c>
       <c r="F558" t="n">
-        <v>124432</v>
+        <v>126302</v>
       </c>
     </row>
     <row r="559">
@@ -11661,10 +11661,10 @@
         <v>66.56</v>
       </c>
       <c r="E562" t="n">
-        <v>67.86</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="F562" t="n">
-        <v>157092</v>
+        <v>160482</v>
       </c>
     </row>
     <row r="563">
@@ -11681,10 +11681,10 @@
         <v>66.17</v>
       </c>
       <c r="E563" t="n">
-        <v>66.56</v>
+        <v>66.53</v>
       </c>
       <c r="F563" t="n">
-        <v>145779</v>
+        <v>148372</v>
       </c>
     </row>
     <row r="564">
@@ -11761,10 +11761,10 @@
         <v>67.77</v>
       </c>
       <c r="E567" t="n">
-        <v>68.05</v>
+        <v>68.03</v>
       </c>
       <c r="F567" t="n">
-        <v>153533</v>
+        <v>155507</v>
       </c>
     </row>
     <row r="568">
@@ -11784,7 +11784,7 @@
         <v>68.03</v>
       </c>
       <c r="F568" t="n">
-        <v>136012</v>
+        <v>139157</v>
       </c>
     </row>
     <row r="569">
@@ -11861,10 +11861,10 @@
         <v>66.34</v>
       </c>
       <c r="E572" t="n">
-        <v>66.83</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="F572" t="n">
-        <v>180093</v>
+        <v>182316</v>
       </c>
     </row>
     <row r="573">
@@ -11875,16 +11875,16 @@
         <v>66.81</v>
       </c>
       <c r="C573" t="n">
-        <v>68.52</v>
+        <v>68.63</v>
       </c>
       <c r="D573" t="n">
         <v>66.36</v>
       </c>
       <c r="E573" t="n">
-        <v>68.45</v>
+        <v>68.52</v>
       </c>
       <c r="F573" t="n">
-        <v>139950</v>
+        <v>142226</v>
       </c>
     </row>
     <row r="574">
@@ -11958,13 +11958,13 @@
         <v>67.02</v>
       </c>
       <c r="D577" t="n">
-        <v>64.73</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="E577" t="n">
-        <v>64.98999999999999</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="F577" t="n">
-        <v>164782</v>
+        <v>168733</v>
       </c>
     </row>
     <row r="578">
@@ -11981,10 +11981,10 @@
         <v>64.48</v>
       </c>
       <c r="E578" t="n">
-        <v>66.58</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="F578" t="n">
-        <v>153693</v>
+        <v>156317</v>
       </c>
     </row>
     <row r="579">
@@ -12055,16 +12055,16 @@
         <v>68.58</v>
       </c>
       <c r="C582" t="n">
-        <v>69.18000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="D582" t="n">
         <v>67.89</v>
       </c>
       <c r="E582" t="n">
-        <v>69.05</v>
+        <v>69.12</v>
       </c>
       <c r="F582" t="n">
-        <v>119490</v>
+        <v>122427</v>
       </c>
     </row>
     <row r="583">
@@ -12081,10 +12081,10 @@
         <v>68.48999999999999</v>
       </c>
       <c r="E583" t="n">
-        <v>68.89</v>
+        <v>68.88</v>
       </c>
       <c r="F583" t="n">
-        <v>119218</v>
+        <v>121324</v>
       </c>
     </row>
     <row r="584">
@@ -12161,10 +12161,10 @@
         <v>70.5</v>
       </c>
       <c r="E587" t="n">
-        <v>71.20999999999999</v>
+        <v>71.22</v>
       </c>
       <c r="F587" t="n">
-        <v>126247</v>
+        <v>128649</v>
       </c>
     </row>
     <row r="588">
@@ -12181,10 +12181,10 @@
         <v>70.58</v>
       </c>
       <c r="E588" t="n">
-        <v>71.47</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="F588" t="n">
-        <v>113793</v>
+        <v>117041</v>
       </c>
     </row>
     <row r="589">
@@ -12261,10 +12261,10 @@
         <v>70.66</v>
       </c>
       <c r="E592" t="n">
-        <v>72.09</v>
+        <v>71.95</v>
       </c>
       <c r="F592" t="n">
-        <v>146487</v>
+        <v>148450</v>
       </c>
     </row>
     <row r="593">
@@ -12284,7 +12284,7 @@
         <v>72.23999999999999</v>
       </c>
       <c r="F593" t="n">
-        <v>140128</v>
+        <v>142367</v>
       </c>
     </row>
     <row r="594">
@@ -12361,10 +12361,10 @@
         <v>71.41</v>
       </c>
       <c r="E597" t="n">
-        <v>72.45</v>
+        <v>72.44</v>
       </c>
       <c r="F597" t="n">
-        <v>175025</v>
+        <v>178094</v>
       </c>
     </row>
     <row r="598">
@@ -12381,10 +12381,10 @@
         <v>71.55</v>
       </c>
       <c r="E598" t="n">
-        <v>72.76000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="F598" t="n">
-        <v>147859</v>
+        <v>151345</v>
       </c>
     </row>
     <row r="599">
@@ -12461,10 +12461,10 @@
         <v>73.83</v>
       </c>
       <c r="E602" t="n">
-        <v>74.79000000000001</v>
+        <v>74.81</v>
       </c>
       <c r="F602" t="n">
-        <v>84577</v>
+        <v>85692</v>
       </c>
     </row>
     <row r="603">
@@ -12481,10 +12481,10 @@
         <v>74.14</v>
       </c>
       <c r="E603" t="n">
-        <v>75.27</v>
+        <v>75.28</v>
       </c>
       <c r="F603" t="n">
-        <v>77990</v>
+        <v>79112</v>
       </c>
     </row>
     <row r="604">
@@ -12561,10 +12561,10 @@
         <v>74.36</v>
       </c>
       <c r="E607" t="n">
-        <v>75.33</v>
+        <v>75.34</v>
       </c>
       <c r="F607" t="n">
-        <v>134296</v>
+        <v>135699</v>
       </c>
     </row>
     <row r="608">
@@ -12581,10 +12581,10 @@
         <v>75</v>
       </c>
       <c r="E608" t="n">
-        <v>76.02</v>
+        <v>75.81999999999999</v>
       </c>
       <c r="F608" t="n">
-        <v>102316</v>
+        <v>104256</v>
       </c>
     </row>
     <row r="609">
@@ -12655,16 +12655,16 @@
         <v>72.97</v>
       </c>
       <c r="C612" t="n">
-        <v>73.97</v>
+        <v>74.02</v>
       </c>
       <c r="D612" t="n">
         <v>71.73999999999999</v>
       </c>
       <c r="E612" t="n">
-        <v>73.92</v>
+        <v>73.95999999999999</v>
       </c>
       <c r="F612" t="n">
-        <v>136419</v>
+        <v>138030</v>
       </c>
     </row>
     <row r="613">
@@ -12681,10 +12681,10 @@
         <v>73.38</v>
       </c>
       <c r="E613" t="n">
-        <v>75.15000000000001</v>
+        <v>75.14</v>
       </c>
       <c r="F613" t="n">
-        <v>95892</v>
+        <v>96988</v>
       </c>
     </row>
     <row r="614">
@@ -12761,10 +12761,10 @@
         <v>72.70999999999999</v>
       </c>
       <c r="E617" t="n">
-        <v>72.79000000000001</v>
+        <v>72.72</v>
       </c>
       <c r="F617" t="n">
-        <v>132350</v>
+        <v>134216</v>
       </c>
     </row>
     <row r="618">
@@ -12781,10 +12781,10 @@
         <v>71.88</v>
       </c>
       <c r="E618" t="n">
-        <v>72.81</v>
+        <v>72.64</v>
       </c>
       <c r="F618" t="n">
-        <v>108307</v>
+        <v>110158</v>
       </c>
     </row>
     <row r="619">
@@ -12864,7 +12864,7 @@
         <v>73.01000000000001</v>
       </c>
       <c r="F622" t="n">
-        <v>113951</v>
+        <v>115159</v>
       </c>
     </row>
     <row r="623">
@@ -12875,16 +12875,16 @@
         <v>72.98</v>
       </c>
       <c r="C623" t="n">
-        <v>73.52</v>
+        <v>73.56999999999999</v>
       </c>
       <c r="D623" t="n">
         <v>72.70999999999999</v>
       </c>
       <c r="E623" t="n">
-        <v>73.44</v>
+        <v>73.5</v>
       </c>
       <c r="F623" t="n">
-        <v>83411</v>
+        <v>84579</v>
       </c>
     </row>
     <row r="624">
@@ -12961,10 +12961,10 @@
         <v>73.59999999999999</v>
       </c>
       <c r="E627" t="n">
-        <v>74.97</v>
+        <v>74.75</v>
       </c>
       <c r="F627" t="n">
-        <v>79720</v>
+        <v>81467</v>
       </c>
     </row>
     <row r="628">
@@ -12981,10 +12981,10 @@
         <v>74.26000000000001</v>
       </c>
       <c r="E628" t="n">
-        <v>74.98999999999999</v>
+        <v>74.95999999999999</v>
       </c>
       <c r="F628" t="n">
-        <v>83101</v>
+        <v>84253</v>
       </c>
     </row>
     <row r="629">
@@ -13061,10 +13061,10 @@
         <v>69.56</v>
       </c>
       <c r="E632" t="n">
-        <v>71.16</v>
+        <v>71</v>
       </c>
       <c r="F632" t="n">
-        <v>107034</v>
+        <v>108267</v>
       </c>
     </row>
     <row r="633">
@@ -13078,13 +13078,13 @@
         <v>72.22</v>
       </c>
       <c r="D633" t="n">
-        <v>70.12</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="E633" t="n">
-        <v>70.34999999999999</v>
+        <v>70.08</v>
       </c>
       <c r="F633" t="n">
-        <v>111453</v>
+        <v>113105</v>
       </c>
     </row>
     <row r="634">
@@ -13161,10 +13161,10 @@
         <v>70.41</v>
       </c>
       <c r="E637" t="n">
-        <v>70.90000000000001</v>
+        <v>70.86</v>
       </c>
       <c r="F637" t="n">
-        <v>95219</v>
+        <v>96203</v>
       </c>
     </row>
     <row r="638">
@@ -13181,10 +13181,10 @@
         <v>69.73999999999999</v>
       </c>
       <c r="E638" t="n">
-        <v>69.92</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="F638" t="n">
-        <v>93960</v>
+        <v>95696</v>
       </c>
     </row>
     <row r="639">
@@ -13261,10 +13261,10 @@
         <v>65.2</v>
       </c>
       <c r="E642" t="n">
-        <v>66.51000000000001</v>
+        <v>66.23</v>
       </c>
       <c r="F642" t="n">
-        <v>185678</v>
+        <v>187712</v>
       </c>
     </row>
     <row r="643">
@@ -13278,13 +13278,13 @@
         <v>66.54000000000001</v>
       </c>
       <c r="D643" t="n">
-        <v>64.61</v>
+        <v>64.53</v>
       </c>
       <c r="E643" t="n">
-        <v>64.62</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="F643" t="n">
-        <v>137258</v>
+        <v>138989</v>
       </c>
     </row>
     <row r="644">
@@ -13361,10 +13361,10 @@
         <v>69.73999999999999</v>
       </c>
       <c r="E647" t="n">
-        <v>70.56</v>
+        <v>70.45999999999999</v>
       </c>
       <c r="F647" t="n">
-        <v>113839</v>
+        <v>115965</v>
       </c>
     </row>
     <row r="648">
@@ -13381,10 +13381,10 @@
         <v>70.16</v>
       </c>
       <c r="E648" t="n">
-        <v>71.59999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="F648" t="n">
-        <v>99158</v>
+        <v>100455</v>
       </c>
     </row>
     <row r="649">
@@ -13461,10 +13461,10 @@
         <v>70.75</v>
       </c>
       <c r="E652" t="n">
-        <v>72.56999999999999</v>
+        <v>72.61</v>
       </c>
       <c r="F652" t="n">
-        <v>103772</v>
+        <v>105073</v>
       </c>
     </row>
     <row r="653">
@@ -13481,10 +13481,10 @@
         <v>72.20999999999999</v>
       </c>
       <c r="E653" t="n">
-        <v>72.36</v>
+        <v>72.20999999999999</v>
       </c>
       <c r="F653" t="n">
-        <v>110684</v>
+        <v>111688</v>
       </c>
     </row>
     <row r="654">
@@ -13561,10 +13561,10 @@
         <v>70.54000000000001</v>
       </c>
       <c r="E657" t="n">
-        <v>70.95</v>
+        <v>70.84</v>
       </c>
       <c r="F657" t="n">
-        <v>136836</v>
+        <v>138553</v>
       </c>
     </row>
     <row r="658">
@@ -13581,10 +13581,10 @@
         <v>70.59</v>
       </c>
       <c r="E658" t="n">
-        <v>72.44</v>
+        <v>72.51000000000001</v>
       </c>
       <c r="F658" t="n">
-        <v>106315</v>
+        <v>107925</v>
       </c>
     </row>
     <row r="659">
@@ -13661,10 +13661,10 @@
         <v>74.02</v>
       </c>
       <c r="E662" t="n">
-        <v>75.17</v>
+        <v>75.09</v>
       </c>
       <c r="F662" t="n">
-        <v>134873</v>
+        <v>136265</v>
       </c>
     </row>
     <row r="663">
@@ -13681,10 +13681,10 @@
         <v>74.06999999999999</v>
       </c>
       <c r="E663" t="n">
-        <v>74.79000000000001</v>
+        <v>74.67</v>
       </c>
       <c r="F663" t="n">
-        <v>129577</v>
+        <v>131243</v>
       </c>
     </row>
     <row r="664">
@@ -13764,7 +13764,7 @@
         <v>76.45</v>
       </c>
       <c r="F667" t="n">
-        <v>102612</v>
+        <v>104066</v>
       </c>
     </row>
     <row r="668">
@@ -13781,10 +13781,10 @@
         <v>76.09</v>
       </c>
       <c r="E668" t="n">
-        <v>77.15000000000001</v>
+        <v>77.13</v>
       </c>
       <c r="F668" t="n">
-        <v>93448</v>
+        <v>94529</v>
       </c>
     </row>
     <row r="669">
@@ -13861,10 +13861,10 @@
         <v>76.37</v>
       </c>
       <c r="E672" t="n">
-        <v>78.13</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="F672" t="n">
-        <v>180155</v>
+        <v>181989</v>
       </c>
     </row>
     <row r="673">
@@ -13881,10 +13881,10 @@
         <v>77.38</v>
       </c>
       <c r="E673" t="n">
-        <v>78.98999999999999</v>
+        <v>78.93000000000001</v>
       </c>
       <c r="F673" t="n">
-        <v>149729</v>
+        <v>151482</v>
       </c>
     </row>
     <row r="674">
@@ -13961,10 +13961,10 @@
         <v>78.78</v>
       </c>
       <c r="E677" t="n">
-        <v>82.16</v>
+        <v>82.08</v>
       </c>
       <c r="F677" t="n">
-        <v>151677</v>
+        <v>153620</v>
       </c>
     </row>
     <row r="678">
@@ -13981,10 +13981,10 @@
         <v>81.63</v>
       </c>
       <c r="E678" t="n">
-        <v>82.17</v>
+        <v>82.22</v>
       </c>
       <c r="F678" t="n">
-        <v>147722</v>
+        <v>149526</v>
       </c>
     </row>
     <row r="679">
@@ -14061,10 +14061,10 @@
         <v>82.76000000000001</v>
       </c>
       <c r="E682" t="n">
-        <v>83.69</v>
+        <v>83.67</v>
       </c>
       <c r="F682" t="n">
-        <v>120650</v>
+        <v>122153</v>
       </c>
     </row>
     <row r="683">
@@ -14081,10 +14081,10 @@
         <v>83.68000000000001</v>
       </c>
       <c r="E683" t="n">
-        <v>84.23</v>
+        <v>84.33</v>
       </c>
       <c r="F683" t="n">
-        <v>114060</v>
+        <v>116437</v>
       </c>
     </row>
     <row r="684">
@@ -14161,10 +14161,10 @@
         <v>82.73</v>
       </c>
       <c r="E687" t="n">
-        <v>84.15000000000001</v>
+        <v>84.09</v>
       </c>
       <c r="F687" t="n">
-        <v>121250</v>
+        <v>122966</v>
       </c>
     </row>
     <row r="688">
@@ -14175,16 +14175,16 @@
         <v>83.81999999999999</v>
       </c>
       <c r="C688" t="n">
-        <v>84.97</v>
+        <v>85.08</v>
       </c>
       <c r="D688" t="n">
         <v>83.18000000000001</v>
       </c>
       <c r="E688" t="n">
-        <v>84.97</v>
+        <v>84.83</v>
       </c>
       <c r="F688" t="n">
-        <v>111475</v>
+        <v>113449</v>
       </c>
     </row>
     <row r="689">
@@ -14261,10 +14261,10 @@
         <v>81.48</v>
       </c>
       <c r="E692" t="n">
-        <v>83.83</v>
+        <v>83.78</v>
       </c>
       <c r="F692" t="n">
-        <v>164605</v>
+        <v>167007</v>
       </c>
     </row>
     <row r="693">
@@ -14281,10 +14281,10 @@
         <v>82.39</v>
       </c>
       <c r="E693" t="n">
-        <v>83.55</v>
+        <v>83.41</v>
       </c>
       <c r="F693" t="n">
-        <v>132228</v>
+        <v>133535</v>
       </c>
     </row>
     <row r="694">
@@ -14352,7 +14352,7 @@
         <v>44504</v>
       </c>
       <c r="B697" t="n">
-        <v>81.12</v>
+        <v>80.83</v>
       </c>
       <c r="C697" t="n">
         <v>84.08</v>
@@ -14364,7 +14364,7 @@
         <v>80.54000000000001</v>
       </c>
       <c r="F697" t="n">
-        <v>171378</v>
+        <v>168783</v>
       </c>
     </row>
     <row r="698">
@@ -14372,7 +14372,7 @@
         <v>44505</v>
       </c>
       <c r="B698" t="n">
-        <v>80.95</v>
+        <v>81.04000000000001</v>
       </c>
       <c r="C698" t="n">
         <v>82.72</v>
@@ -14384,7 +14384,7 @@
         <v>81.93000000000001</v>
       </c>
       <c r="F698" t="n">
-        <v>166390</v>
+        <v>163172</v>
       </c>
     </row>
     <row r="699">
@@ -14461,10 +14461,10 @@
         <v>81.06</v>
       </c>
       <c r="E702" t="n">
-        <v>81.91</v>
+        <v>81.92</v>
       </c>
       <c r="F702" t="n">
-        <v>159955</v>
+        <v>161511</v>
       </c>
     </row>
     <row r="703">
@@ -14481,10 +14481,10 @@
         <v>80.63</v>
       </c>
       <c r="E703" t="n">
-        <v>81.41</v>
+        <v>81.29000000000001</v>
       </c>
       <c r="F703" t="n">
-        <v>133196</v>
+        <v>134507</v>
       </c>
     </row>
     <row r="704">
@@ -14561,10 +14561,10 @@
         <v>78.55</v>
       </c>
       <c r="E707" t="n">
-        <v>80.42</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="F707" t="n">
-        <v>131123</v>
+        <v>132952</v>
       </c>
     </row>
     <row r="708">
@@ -14581,10 +14581,10 @@
         <v>77.41</v>
       </c>
       <c r="E708" t="n">
-        <v>77.76000000000001</v>
+        <v>77.77</v>
       </c>
       <c r="F708" t="n">
-        <v>175625</v>
+        <v>177513</v>
       </c>
     </row>
     <row r="709">
@@ -14761,10 +14761,10 @@
         <v>65.67</v>
       </c>
       <c r="E717" t="n">
-        <v>69.94</v>
+        <v>70.36</v>
       </c>
       <c r="F717" t="n">
-        <v>237353</v>
+        <v>240359</v>
       </c>
     </row>
     <row r="718">
@@ -14781,10 +14781,10 @@
         <v>69.09999999999999</v>
       </c>
       <c r="E718" t="n">
-        <v>69.73</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="F718" t="n">
-        <v>205214</v>
+        <v>208893</v>
       </c>
     </row>
     <row r="719">
@@ -14858,13 +14858,13 @@
         <v>76.55</v>
       </c>
       <c r="D722" t="n">
-        <v>73.78</v>
+        <v>73.70999999999999</v>
       </c>
       <c r="E722" t="n">
-        <v>73.79000000000001</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="F722" t="n">
-        <v>140659</v>
+        <v>142264</v>
       </c>
     </row>
     <row r="723">
@@ -14881,10 +14881,10 @@
         <v>73.67</v>
       </c>
       <c r="E723" t="n">
-        <v>75.23</v>
+        <v>75.16</v>
       </c>
       <c r="F723" t="n">
-        <v>151698</v>
+        <v>153301</v>
       </c>
     </row>
     <row r="724">
@@ -14961,10 +14961,10 @@
         <v>73.88</v>
       </c>
       <c r="E727" t="n">
-        <v>74.63</v>
+        <v>74.48999999999999</v>
       </c>
       <c r="F727" t="n">
-        <v>140474</v>
+        <v>142563</v>
       </c>
     </row>
     <row r="728">
@@ -14981,10 +14981,10 @@
         <v>72.63</v>
       </c>
       <c r="E728" t="n">
-        <v>73.15000000000001</v>
+        <v>72.88</v>
       </c>
       <c r="F728" t="n">
-        <v>152160</v>
+        <v>154875</v>
       </c>
     </row>
     <row r="729">
@@ -15061,10 +15061,10 @@
         <v>74.72</v>
       </c>
       <c r="E732" t="n">
-        <v>76.63</v>
+        <v>76.52</v>
       </c>
       <c r="F732" t="n">
-        <v>100583</v>
+        <v>102802</v>
       </c>
     </row>
     <row r="733">
@@ -15161,10 +15161,10 @@
         <v>78.33</v>
       </c>
       <c r="E737" t="n">
-        <v>78.97</v>
+        <v>78.86</v>
       </c>
       <c r="F737" t="n">
-        <v>103669</v>
+        <v>105405</v>
       </c>
     </row>
     <row r="738">
@@ -15261,10 +15261,10 @@
         <v>79.36</v>
       </c>
       <c r="E742" t="n">
-        <v>81.65000000000001</v>
+        <v>81.70999999999999</v>
       </c>
       <c r="F742" t="n">
-        <v>185800</v>
+        <v>187943</v>
       </c>
     </row>
     <row r="743">
@@ -15281,10 +15281,10 @@
         <v>81.12</v>
       </c>
       <c r="E743" t="n">
-        <v>81.59999999999999</v>
+        <v>81.48</v>
       </c>
       <c r="F743" t="n">
-        <v>158852</v>
+        <v>160491</v>
       </c>
     </row>
     <row r="744">
@@ -15361,10 +15361,10 @@
         <v>83.34999999999999</v>
       </c>
       <c r="E747" t="n">
-        <v>83.45</v>
+        <v>83.61</v>
       </c>
       <c r="F747" t="n">
-        <v>145171</v>
+        <v>147527</v>
       </c>
     </row>
     <row r="748">
@@ -15375,16 +15375,16 @@
         <v>83.68000000000001</v>
       </c>
       <c r="C748" t="n">
-        <v>85.97</v>
+        <v>85.98999999999999</v>
       </c>
       <c r="D748" t="n">
         <v>83.53</v>
       </c>
       <c r="E748" t="n">
-        <v>85.91</v>
+        <v>85.77</v>
       </c>
       <c r="F748" t="n">
-        <v>171152</v>
+        <v>173518</v>
       </c>
     </row>
     <row r="749">
@@ -15458,13 +15458,13 @@
         <v>88.8</v>
       </c>
       <c r="D752" t="n">
-        <v>86.56999999999999</v>
+        <v>86.38</v>
       </c>
       <c r="E752" t="n">
-        <v>86.7</v>
+        <v>86.58</v>
       </c>
       <c r="F752" t="n">
-        <v>162890</v>
+        <v>169439</v>
       </c>
     </row>
     <row r="753">
@@ -15481,10 +15481,10 @@
         <v>85.02</v>
       </c>
       <c r="E753" t="n">
-        <v>86.98</v>
+        <v>86.92</v>
       </c>
       <c r="F753" t="n">
-        <v>223066</v>
+        <v>225683</v>
       </c>
     </row>
     <row r="754">
@@ -15561,10 +15561,10 @@
         <v>87.7</v>
       </c>
       <c r="E757" t="n">
-        <v>88.40000000000001</v>
+        <v>88.63</v>
       </c>
       <c r="F757" t="n">
-        <v>270152</v>
+        <v>275711</v>
       </c>
     </row>
     <row r="758">
@@ -15581,10 +15581,10 @@
         <v>88</v>
       </c>
       <c r="E758" t="n">
-        <v>88.73</v>
+        <v>88.81999999999999</v>
       </c>
       <c r="F758" t="n">
-        <v>275262</v>
+        <v>278896</v>
       </c>
     </row>
     <row r="759">
@@ -15655,16 +15655,16 @@
         <v>88.63</v>
       </c>
       <c r="C762" t="n">
-        <v>90.73999999999999</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="D762" t="n">
         <v>87.59999999999999</v>
       </c>
       <c r="E762" t="n">
-        <v>90.45999999999999</v>
+        <v>90.51000000000001</v>
       </c>
       <c r="F762" t="n">
-        <v>163057</v>
+        <v>168353</v>
       </c>
     </row>
     <row r="763">
@@ -15681,10 +15681,10 @@
         <v>90.67</v>
       </c>
       <c r="E763" t="n">
-        <v>92.54000000000001</v>
+        <v>92.14</v>
       </c>
       <c r="F763" t="n">
-        <v>177219</v>
+        <v>180147</v>
       </c>
     </row>
     <row r="764">
@@ -15761,10 +15761,10 @@
         <v>90.09999999999999</v>
       </c>
       <c r="E767" t="n">
-        <v>90.66</v>
+        <v>90.54000000000001</v>
       </c>
       <c r="F767" t="n">
-        <v>183590</v>
+        <v>186180</v>
       </c>
     </row>
     <row r="768">
@@ -15781,10 +15781,10 @@
         <v>89.66</v>
       </c>
       <c r="E768" t="n">
-        <v>93.81</v>
+        <v>93.8</v>
       </c>
       <c r="F768" t="n">
-        <v>189880</v>
+        <v>194729</v>
       </c>
     </row>
     <row r="769">
@@ -15861,10 +15861,10 @@
         <v>90.34999999999999</v>
       </c>
       <c r="E772" t="n">
-        <v>91.18000000000001</v>
+        <v>91.16</v>
       </c>
       <c r="F772" t="n">
-        <v>209775</v>
+        <v>212213</v>
       </c>
     </row>
     <row r="773">
@@ -15875,7 +15875,7 @@
         <v>90.76000000000001</v>
       </c>
       <c r="C773" t="n">
-        <v>92.15000000000001</v>
+        <v>92.28</v>
       </c>
       <c r="D773" t="n">
         <v>88.64</v>
@@ -15884,7 +15884,7 @@
         <v>91.81</v>
       </c>
       <c r="F773" t="n">
-        <v>190175</v>
+        <v>194995</v>
       </c>
     </row>
     <row r="774">
@@ -15961,10 +15961,10 @@
         <v>93.94</v>
       </c>
       <c r="E777" t="n">
-        <v>95.61</v>
+        <v>95.41</v>
       </c>
       <c r="F777" t="n">
-        <v>309076</v>
+        <v>313423</v>
       </c>
     </row>
     <row r="778">
@@ -15981,10 +15981,10 @@
         <v>92.55</v>
       </c>
       <c r="E778" t="n">
-        <v>94.69</v>
+        <v>94.23</v>
       </c>
       <c r="F778" t="n">
-        <v>233541</v>
+        <v>237786</v>
       </c>
     </row>
     <row r="779">
@@ -16061,10 +16061,10 @@
         <v>108.17</v>
       </c>
       <c r="E782" t="n">
-        <v>109.72</v>
+        <v>109.27</v>
       </c>
       <c r="F782" t="n">
-        <v>231064</v>
+        <v>233799</v>
       </c>
     </row>
     <row r="783">
@@ -16081,10 +16081,10 @@
         <v>108.47</v>
       </c>
       <c r="E783" t="n">
-        <v>117.14</v>
+        <v>116.7</v>
       </c>
       <c r="F783" t="n">
-        <v>204618</v>
+        <v>210974</v>
       </c>
     </row>
     <row r="784">
@@ -16161,10 +16161,10 @@
         <v>107.05</v>
       </c>
       <c r="E787" t="n">
-        <v>107.97</v>
+        <v>107.11</v>
       </c>
       <c r="F787" t="n">
-        <v>170481</v>
+        <v>173653</v>
       </c>
     </row>
     <row r="788">
@@ -16181,10 +16181,10 @@
         <v>104.96</v>
       </c>
       <c r="E788" t="n">
-        <v>110.51</v>
+        <v>110.14</v>
       </c>
       <c r="F788" t="n">
-        <v>154891</v>
+        <v>157669</v>
       </c>
     </row>
     <row r="789">
@@ -16252,19 +16252,19 @@
         <v>44637</v>
       </c>
       <c r="B792" t="n">
-        <v>96.98</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="C792" t="n">
         <v>105.3</v>
       </c>
       <c r="D792" t="n">
-        <v>96.11</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="E792" t="n">
         <v>104.46</v>
       </c>
       <c r="F792" t="n">
-        <v>176604</v>
+        <v>172578</v>
       </c>
     </row>
     <row r="793">
@@ -16272,7 +16272,7 @@
         <v>44638</v>
       </c>
       <c r="B793" t="n">
-        <v>104.55</v>
+        <v>105.16</v>
       </c>
       <c r="C793" t="n">
         <v>107.23</v>
@@ -16284,7 +16284,7 @@
         <v>105.63</v>
       </c>
       <c r="F793" t="n">
-        <v>158531</v>
+        <v>155067</v>
       </c>
     </row>
     <row r="794">
@@ -16352,7 +16352,7 @@
         <v>44644</v>
       </c>
       <c r="B797" t="n">
-        <v>118.08</v>
+        <v>119.49</v>
       </c>
       <c r="C797" t="n">
         <v>120.04</v>
@@ -16364,7 +16364,7 @@
         <v>114.47</v>
       </c>
       <c r="F797" t="n">
-        <v>215337</v>
+        <v>206598</v>
       </c>
     </row>
     <row r="798">
@@ -16372,7 +16372,7 @@
         <v>44645</v>
       </c>
       <c r="B798" t="n">
-        <v>115.3</v>
+        <v>114.52</v>
       </c>
       <c r="C798" t="n">
         <v>117.69</v>
@@ -16384,7 +16384,7 @@
         <v>115.94</v>
       </c>
       <c r="F798" t="n">
-        <v>195807</v>
+        <v>189095</v>
       </c>
     </row>
     <row r="799">
@@ -16461,10 +16461,10 @@
         <v>103.71</v>
       </c>
       <c r="E802" t="n">
-        <v>104.6</v>
+        <v>104.99</v>
       </c>
       <c r="F802" t="n">
-        <v>217472</v>
+        <v>220967</v>
       </c>
     </row>
     <row r="803">
@@ -16481,10 +16481,10 @@
         <v>101.94</v>
       </c>
       <c r="E803" t="n">
-        <v>104.13</v>
+        <v>103.88</v>
       </c>
       <c r="F803" t="n">
-        <v>179677</v>
+        <v>181758</v>
       </c>
     </row>
     <row r="804">
@@ -16561,10 +16561,10 @@
         <v>98.2</v>
       </c>
       <c r="E807" t="n">
-        <v>100.94</v>
+        <v>100.96</v>
       </c>
       <c r="F807" t="n">
-        <v>183922</v>
+        <v>186163</v>
       </c>
     </row>
     <row r="808">
@@ -16581,10 +16581,10 @@
         <v>99.28</v>
       </c>
       <c r="E808" t="n">
-        <v>102.16</v>
+        <v>101.81</v>
       </c>
       <c r="F808" t="n">
-        <v>159821</v>
+        <v>162819</v>
       </c>
     </row>
     <row r="809">
@@ -16661,10 +16661,10 @@
         <v>106.14</v>
       </c>
       <c r="E812" t="n">
-        <v>110.56</v>
+        <v>110.62</v>
       </c>
       <c r="F812" t="n">
-        <v>156524</v>
+        <v>159785</v>
       </c>
     </row>
     <row r="813">
@@ -16741,10 +16741,10 @@
         <v>106.38</v>
       </c>
       <c r="E816" t="n">
-        <v>107.93</v>
+        <v>108</v>
       </c>
       <c r="F816" t="n">
-        <v>184241</v>
+        <v>188001</v>
       </c>
     </row>
     <row r="817">
@@ -16758,13 +16758,13 @@
         <v>108.41</v>
       </c>
       <c r="D817" t="n">
-        <v>105.44</v>
+        <v>105.05</v>
       </c>
       <c r="E817" t="n">
-        <v>105.6</v>
+        <v>105.7</v>
       </c>
       <c r="F817" t="n">
-        <v>162032</v>
+        <v>165632</v>
       </c>
     </row>
     <row r="818">
@@ -16841,10 +16841,10 @@
         <v>102.74</v>
       </c>
       <c r="E821" t="n">
-        <v>107.25</v>
+        <v>106.8</v>
       </c>
       <c r="F821" t="n">
-        <v>167676</v>
+        <v>170514</v>
       </c>
     </row>
     <row r="822">
@@ -16861,10 +16861,10 @@
         <v>105.92</v>
       </c>
       <c r="E822" t="n">
-        <v>106.38</v>
+        <v>106.06</v>
       </c>
       <c r="F822" t="n">
-        <v>182972</v>
+        <v>186051</v>
       </c>
     </row>
     <row r="823">
@@ -16941,10 +16941,10 @@
         <v>108.66</v>
       </c>
       <c r="E826" t="n">
-        <v>110.3</v>
+        <v>110.4</v>
       </c>
       <c r="F826" t="n">
-        <v>197687</v>
+        <v>201234</v>
       </c>
     </row>
     <row r="827">
@@ -16961,10 +16961,10 @@
         <v>109.21</v>
       </c>
       <c r="E827" t="n">
-        <v>112.44</v>
+        <v>112.22</v>
       </c>
       <c r="F827" t="n">
-        <v>203469</v>
+        <v>207851</v>
       </c>
     </row>
     <row r="828">
@@ -17041,10 +17041,10 @@
         <v>103.97</v>
       </c>
       <c r="E831" t="n">
-        <v>107.38</v>
+        <v>106.86</v>
       </c>
       <c r="F831" t="n">
-        <v>240901</v>
+        <v>243371</v>
       </c>
     </row>
     <row r="832">
@@ -17061,10 +17061,10 @@
         <v>106.88</v>
       </c>
       <c r="E832" t="n">
-        <v>110.4</v>
+        <v>109.76</v>
       </c>
       <c r="F832" t="n">
-        <v>190398</v>
+        <v>193013</v>
       </c>
     </row>
     <row r="833">
@@ -17141,10 +17141,10 @@
         <v>104.22</v>
       </c>
       <c r="E836" t="n">
-        <v>109.59</v>
+        <v>109.5</v>
       </c>
       <c r="F836" t="n">
-        <v>247278</v>
+        <v>250583</v>
       </c>
     </row>
     <row r="837">
@@ -17161,10 +17161,10 @@
         <v>108.65</v>
       </c>
       <c r="E837" t="n">
-        <v>110.87</v>
+        <v>110.3</v>
       </c>
       <c r="F837" t="n">
-        <v>198948</v>
+        <v>202895</v>
       </c>
     </row>
     <row r="838">
@@ -17241,10 +17241,10 @@
         <v>110.83</v>
       </c>
       <c r="E841" t="n">
-        <v>114</v>
+        <v>114.15</v>
       </c>
       <c r="F841" t="n">
-        <v>171535</v>
+        <v>175003</v>
       </c>
     </row>
     <row r="842">
@@ -17261,10 +17261,10 @@
         <v>113.01</v>
       </c>
       <c r="E842" t="n">
-        <v>115.42</v>
+        <v>115.01</v>
       </c>
       <c r="F842" t="n">
-        <v>210750</v>
+        <v>213418</v>
       </c>
     </row>
     <row r="843">
@@ -17335,16 +17335,16 @@
         <v>113.88</v>
       </c>
       <c r="C846" t="n">
-        <v>117.57</v>
+        <v>117.74</v>
       </c>
       <c r="D846" t="n">
         <v>111.85</v>
       </c>
       <c r="E846" t="n">
-        <v>117.26</v>
+        <v>117.31</v>
       </c>
       <c r="F846" t="n">
-        <v>137013</v>
+        <v>138282</v>
       </c>
     </row>
     <row r="847">
@@ -17355,16 +17355,16 @@
         <v>117.37</v>
       </c>
       <c r="C847" t="n">
-        <v>120.57</v>
+        <v>120.6</v>
       </c>
       <c r="D847" t="n">
         <v>115.28</v>
       </c>
       <c r="E847" t="n">
-        <v>120.41</v>
+        <v>120.23</v>
       </c>
       <c r="F847" t="n">
-        <v>90339</v>
+        <v>91626</v>
       </c>
     </row>
     <row r="848">
@@ -17441,10 +17441,10 @@
         <v>121.23</v>
       </c>
       <c r="E851" t="n">
-        <v>121.71</v>
+        <v>121.41</v>
       </c>
       <c r="F851" t="n">
-        <v>174232</v>
+        <v>176648</v>
       </c>
     </row>
     <row r="852">
@@ -17461,10 +17461,10 @@
         <v>118.31</v>
       </c>
       <c r="E852" t="n">
-        <v>120.29</v>
+        <v>120.02</v>
       </c>
       <c r="F852" t="n">
-        <v>190410</v>
+        <v>192334</v>
       </c>
     </row>
     <row r="853">
@@ -17541,10 +17541,10 @@
         <v>113.72</v>
       </c>
       <c r="E856" t="n">
-        <v>117.15</v>
+        <v>116.92</v>
       </c>
       <c r="F856" t="n">
-        <v>228931</v>
+        <v>231324</v>
       </c>
     </row>
     <row r="857">
@@ -17561,10 +17561,10 @@
         <v>109.77</v>
       </c>
       <c r="E857" t="n">
-        <v>111.29</v>
+        <v>111.27</v>
       </c>
       <c r="F857" t="n">
-        <v>233588</v>
+        <v>236868</v>
       </c>
     </row>
     <row r="858">
@@ -17641,10 +17641,10 @@
         <v>105.25</v>
       </c>
       <c r="E861" t="n">
-        <v>106.29</v>
+        <v>106.13</v>
       </c>
       <c r="F861" t="n">
-        <v>233040</v>
+        <v>234952</v>
       </c>
     </row>
     <row r="862">
@@ -17661,10 +17661,10 @@
         <v>105.78</v>
       </c>
       <c r="E862" t="n">
-        <v>109.13</v>
+        <v>108.33</v>
       </c>
       <c r="F862" t="n">
-        <v>202836</v>
+        <v>205227</v>
       </c>
     </row>
     <row r="863">
@@ -17741,10 +17741,10 @@
         <v>107.7</v>
       </c>
       <c r="E866" t="n">
-        <v>108.69</v>
+        <v>108.43</v>
       </c>
       <c r="F866" t="n">
-        <v>208599</v>
+        <v>212070</v>
       </c>
     </row>
     <row r="867">
@@ -17761,10 +17761,10 @@
         <v>107.32</v>
       </c>
       <c r="E867" t="n">
-        <v>110.56</v>
+        <v>110.43</v>
       </c>
       <c r="F867" t="n">
-        <v>209195</v>
+        <v>210630</v>
       </c>
     </row>
     <row r="868">
@@ -17841,10 +17841,10 @@
         <v>97.11</v>
       </c>
       <c r="E871" t="n">
-        <v>102.75</v>
+        <v>102.32</v>
       </c>
       <c r="F871" t="n">
-        <v>221862</v>
+        <v>224620</v>
       </c>
     </row>
     <row r="872">
@@ -17861,10 +17861,10 @@
         <v>102.16</v>
       </c>
       <c r="E872" t="n">
-        <v>105.32</v>
+        <v>105.2</v>
       </c>
       <c r="F872" t="n">
-        <v>235167</v>
+        <v>237030</v>
       </c>
     </row>
     <row r="873">
@@ -17941,10 +17941,10 @@
         <v>92.42</v>
       </c>
       <c r="E876" t="n">
-        <v>97.17</v>
+        <v>97.12</v>
       </c>
       <c r="F876" t="n">
-        <v>215919</v>
+        <v>217836</v>
       </c>
     </row>
     <row r="877">
@@ -17961,10 +17961,10 @@
         <v>95.59</v>
       </c>
       <c r="E877" t="n">
-        <v>98.34999999999999</v>
+        <v>97.98</v>
       </c>
       <c r="F877" t="n">
-        <v>200270</v>
+        <v>203134</v>
       </c>
     </row>
     <row r="878">
@@ -18041,10 +18041,10 @@
         <v>97.86</v>
       </c>
       <c r="E881" t="n">
-        <v>100.04</v>
+        <v>99.93000000000001</v>
       </c>
       <c r="F881" t="n">
-        <v>227231</v>
+        <v>229298</v>
       </c>
     </row>
     <row r="882">
@@ -18061,10 +18061,10 @@
         <v>97.90000000000001</v>
       </c>
       <c r="E882" t="n">
-        <v>98.67</v>
+        <v>98.98999999999999</v>
       </c>
       <c r="F882" t="n">
-        <v>222921</v>
+        <v>226135</v>
       </c>
     </row>
     <row r="883">
@@ -18141,10 +18141,10 @@
         <v>100.74</v>
       </c>
       <c r="E886" t="n">
-        <v>101.93</v>
+        <v>101.99</v>
       </c>
       <c r="F886" t="n">
-        <v>130398</v>
+        <v>132446</v>
       </c>
     </row>
     <row r="887">
@@ -18161,10 +18161,10 @@
         <v>101.27</v>
       </c>
       <c r="E887" t="n">
-        <v>103.21</v>
+        <v>103.1</v>
       </c>
       <c r="F887" t="n">
-        <v>112179</v>
+        <v>113461</v>
       </c>
     </row>
     <row r="888">
@@ -18238,13 +18238,13 @@
         <v>97.17</v>
       </c>
       <c r="D891" t="n">
-        <v>92.73</v>
+        <v>92.5</v>
       </c>
       <c r="E891" t="n">
-        <v>93.38</v>
+        <v>92.52</v>
       </c>
       <c r="F891" t="n">
-        <v>160629</v>
+        <v>162676</v>
       </c>
     </row>
     <row r="892">
@@ -18261,10 +18261,10 @@
         <v>92.15000000000001</v>
       </c>
       <c r="E892" t="n">
-        <v>93.69</v>
+        <v>93.51000000000001</v>
       </c>
       <c r="F892" t="n">
-        <v>155701</v>
+        <v>157322</v>
       </c>
     </row>
     <row r="893">
@@ -18341,10 +18341,10 @@
         <v>96.08</v>
       </c>
       <c r="E896" t="n">
-        <v>98.66</v>
+        <v>98.31</v>
       </c>
       <c r="F896" t="n">
-        <v>139272</v>
+        <v>140818</v>
       </c>
     </row>
     <row r="897">
@@ -18361,10 +18361,10 @@
         <v>96.26000000000001</v>
       </c>
       <c r="E897" t="n">
-        <v>97.3</v>
+        <v>96.89</v>
       </c>
       <c r="F897" t="n">
-        <v>144235</v>
+        <v>145858</v>
       </c>
     </row>
     <row r="898">
@@ -18441,10 +18441,10 @@
         <v>92.55</v>
       </c>
       <c r="E901" t="n">
-        <v>95.93000000000001</v>
+        <v>95.56</v>
       </c>
       <c r="F901" t="n">
-        <v>122235</v>
+        <v>123861</v>
       </c>
     </row>
     <row r="902">
@@ -18461,10 +18461,10 @@
         <v>93.7</v>
       </c>
       <c r="E902" t="n">
-        <v>95.52</v>
+        <v>95.08</v>
       </c>
       <c r="F902" t="n">
-        <v>125387</v>
+        <v>126696</v>
       </c>
     </row>
     <row r="903">
@@ -18541,10 +18541,10 @@
         <v>98.23</v>
       </c>
       <c r="E906" t="n">
-        <v>99.05</v>
+        <v>98.68000000000001</v>
       </c>
       <c r="F906" t="n">
-        <v>114289</v>
+        <v>115830</v>
       </c>
     </row>
     <row r="907">
@@ -18561,10 +18561,10 @@
         <v>96.92</v>
       </c>
       <c r="E907" t="n">
-        <v>98.70999999999999</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="F907" t="n">
-        <v>127109</v>
+        <v>128357</v>
       </c>
     </row>
     <row r="908">
@@ -18641,10 +18641,10 @@
         <v>91.58</v>
       </c>
       <c r="E911" t="n">
-        <v>91.75</v>
+        <v>91.59</v>
       </c>
       <c r="F911" t="n">
-        <v>171383</v>
+        <v>172611</v>
       </c>
     </row>
     <row r="912">
@@ -18661,10 +18661,10 @@
         <v>92.41</v>
       </c>
       <c r="E912" t="n">
-        <v>92.68000000000001</v>
+        <v>92.83</v>
       </c>
       <c r="F912" t="n">
-        <v>162523</v>
+        <v>164349</v>
       </c>
     </row>
     <row r="913">
@@ -18741,10 +18741,10 @@
         <v>86.86</v>
       </c>
       <c r="E916" t="n">
-        <v>88.03</v>
+        <v>87.73999999999999</v>
       </c>
       <c r="F916" t="n">
-        <v>174104</v>
+        <v>175783</v>
       </c>
     </row>
     <row r="917">
@@ -18761,10 +18761,10 @@
         <v>88.09</v>
       </c>
       <c r="E917" t="n">
-        <v>91.90000000000001</v>
+        <v>91.42</v>
       </c>
       <c r="F917" t="n">
-        <v>137562</v>
+        <v>139210</v>
       </c>
     </row>
     <row r="918">
@@ -18841,10 +18841,10 @@
         <v>89.39</v>
       </c>
       <c r="E921" t="n">
-        <v>90.08</v>
+        <v>89.78</v>
       </c>
       <c r="F921" t="n">
-        <v>177670</v>
+        <v>179533</v>
       </c>
     </row>
     <row r="922">
@@ -18861,10 +18861,10 @@
         <v>89.37</v>
       </c>
       <c r="E922" t="n">
-        <v>90.58</v>
+        <v>90.36</v>
       </c>
       <c r="F922" t="n">
-        <v>175462</v>
+        <v>177056</v>
       </c>
     </row>
     <row r="923">
@@ -18941,10 +18941,10 @@
         <v>88.38</v>
       </c>
       <c r="E926" t="n">
-        <v>89.53</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="F926" t="n">
-        <v>167346</v>
+        <v>169282</v>
       </c>
     </row>
     <row r="927">
@@ -18961,10 +18961,10 @@
         <v>84.61</v>
       </c>
       <c r="E927" t="n">
-        <v>85.41</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="F927" t="n">
-        <v>157358</v>
+        <v>159709</v>
       </c>
     </row>
     <row r="928">
@@ -19041,10 +19041,10 @@
         <v>85.98</v>
       </c>
       <c r="E931" t="n">
-        <v>87.20999999999999</v>
+        <v>87.22</v>
       </c>
       <c r="F931" t="n">
-        <v>182346</v>
+        <v>184095</v>
       </c>
     </row>
     <row r="932">
@@ -19061,10 +19061,10 @@
         <v>84.73999999999999</v>
       </c>
       <c r="E932" t="n">
-        <v>85.06999999999999</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="F932" t="n">
-        <v>172540</v>
+        <v>174184</v>
       </c>
     </row>
     <row r="933">
@@ -19141,10 +19141,10 @@
         <v>92.09</v>
       </c>
       <c r="E936" t="n">
-        <v>94.31999999999999</v>
+        <v>94.16</v>
       </c>
       <c r="F936" t="n">
-        <v>134269</v>
+        <v>136157</v>
       </c>
     </row>
     <row r="937">
@@ -19161,10 +19161,10 @@
         <v>93.25</v>
       </c>
       <c r="E937" t="n">
-        <v>96.95</v>
+        <v>97.59</v>
       </c>
       <c r="F937" t="n">
-        <v>158303</v>
+        <v>161145</v>
       </c>
     </row>
     <row r="938">
@@ -19241,10 +19241,10 @@
         <v>90.18000000000001</v>
       </c>
       <c r="E941" t="n">
-        <v>93.61</v>
+        <v>93.67</v>
       </c>
       <c r="F941" t="n">
-        <v>187899</v>
+        <v>189909</v>
       </c>
     </row>
     <row r="942">
@@ -19261,10 +19261,10 @@
         <v>90.34</v>
       </c>
       <c r="E942" t="n">
-        <v>90.84999999999999</v>
+        <v>90.66</v>
       </c>
       <c r="F942" t="n">
-        <v>184164</v>
+        <v>186342</v>
       </c>
     </row>
     <row r="943">
@@ -19341,10 +19341,10 @@
         <v>90.34</v>
       </c>
       <c r="E946" t="n">
-        <v>91</v>
+        <v>91.11</v>
       </c>
       <c r="F946" t="n">
-        <v>169394</v>
+        <v>172151</v>
       </c>
     </row>
     <row r="947">
@@ -19361,10 +19361,10 @@
         <v>89.40000000000001</v>
       </c>
       <c r="E947" t="n">
-        <v>91.7</v>
+        <v>91.58</v>
       </c>
       <c r="F947" t="n">
-        <v>168937</v>
+        <v>170499</v>
       </c>
     </row>
     <row r="948">
@@ -19441,10 +19441,10 @@
         <v>93.06999999999999</v>
       </c>
       <c r="E951" t="n">
-        <v>94.91</v>
+        <v>94.45999999999999</v>
       </c>
       <c r="F951" t="n">
-        <v>130846</v>
+        <v>135151</v>
       </c>
     </row>
     <row r="952">
@@ -19461,10 +19461,10 @@
         <v>92.81999999999999</v>
       </c>
       <c r="E952" t="n">
-        <v>93.81</v>
+        <v>93.95</v>
       </c>
       <c r="F952" t="n">
-        <v>133960</v>
+        <v>135363</v>
       </c>
     </row>
     <row r="953">
@@ -19532,7 +19532,7 @@
         <v>44868</v>
       </c>
       <c r="B956" t="n">
-        <v>94.81</v>
+        <v>94.84</v>
       </c>
       <c r="C956" t="n">
         <v>95.45</v>
@@ -19544,7 +19544,7 @@
         <v>93.92</v>
       </c>
       <c r="F956" t="n">
-        <v>143503</v>
+        <v>141621</v>
       </c>
     </row>
     <row r="957">
@@ -19552,19 +19552,19 @@
         <v>44869</v>
       </c>
       <c r="B957" t="n">
-        <v>93.98</v>
+        <v>93.94</v>
       </c>
       <c r="C957" t="n">
         <v>98.23999999999999</v>
       </c>
       <c r="D957" t="n">
-        <v>93.76000000000001</v>
+        <v>93.94</v>
       </c>
       <c r="E957" t="n">
         <v>98.01000000000001</v>
       </c>
       <c r="F957" t="n">
-        <v>182009</v>
+        <v>179958</v>
       </c>
     </row>
     <row r="958">
@@ -19641,10 +19641,10 @@
         <v>90.97</v>
       </c>
       <c r="E961" t="n">
-        <v>92.69</v>
+        <v>92.47</v>
       </c>
       <c r="F961" t="n">
-        <v>168690</v>
+        <v>170823</v>
       </c>
     </row>
     <row r="962">
@@ -19661,10 +19661,10 @@
         <v>92.79000000000001</v>
       </c>
       <c r="E962" t="n">
-        <v>95.04000000000001</v>
+        <v>94.95999999999999</v>
       </c>
       <c r="F962" t="n">
-        <v>163940</v>
+        <v>165782</v>
       </c>
     </row>
     <row r="963">
@@ -19741,10 +19741,10 @@
         <v>88.72</v>
       </c>
       <c r="E966" t="n">
-        <v>89.28</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="F966" t="n">
-        <v>157265</v>
+        <v>159560</v>
       </c>
     </row>
     <row r="967">
@@ -19761,10 +19761,10 @@
         <v>85.41</v>
       </c>
       <c r="E967" t="n">
-        <v>87.45</v>
+        <v>87.5</v>
       </c>
       <c r="F967" t="n">
-        <v>160818</v>
+        <v>162655</v>
       </c>
     </row>
     <row r="968">
@@ -19941,10 +19941,10 @@
         <v>86.26000000000001</v>
       </c>
       <c r="E976" t="n">
-        <v>86.84</v>
+        <v>86.98</v>
       </c>
       <c r="F976" t="n">
-        <v>135345</v>
+        <v>136930</v>
       </c>
     </row>
     <row r="977">
@@ -19961,10 +19961,10 @@
         <v>85.17</v>
       </c>
       <c r="E977" t="n">
-        <v>85.76000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="F977" t="n">
-        <v>135815</v>
+        <v>137359</v>
       </c>
     </row>
     <row r="978">
@@ -20041,10 +20041,10 @@
         <v>75.92</v>
       </c>
       <c r="E981" t="n">
-        <v>76.27</v>
+        <v>76.61</v>
       </c>
       <c r="F981" t="n">
-        <v>165742</v>
+        <v>167594</v>
       </c>
     </row>
     <row r="982">
@@ -20061,10 +20061,10 @@
         <v>75.34999999999999</v>
       </c>
       <c r="E982" t="n">
-        <v>76.76000000000001</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="F982" t="n">
-        <v>151706</v>
+        <v>153224</v>
       </c>
     </row>
     <row r="983">
@@ -20141,10 +20141,10 @@
         <v>80.86</v>
       </c>
       <c r="E986" t="n">
-        <v>81.39</v>
+        <v>81.54000000000001</v>
       </c>
       <c r="F986" t="n">
-        <v>149384</v>
+        <v>151489</v>
       </c>
     </row>
     <row r="987">
@@ -20161,10 +20161,10 @@
         <v>78.61</v>
       </c>
       <c r="E987" t="n">
-        <v>79.36</v>
+        <v>79.44</v>
       </c>
       <c r="F987" t="n">
-        <v>149990</v>
+        <v>151197</v>
       </c>
     </row>
     <row r="988">
@@ -20241,10 +20241,10 @@
         <v>81.28</v>
       </c>
       <c r="E991" t="n">
-        <v>82.18000000000001</v>
+        <v>82.20999999999999</v>
       </c>
       <c r="F991" t="n">
-        <v>94348</v>
+        <v>95617</v>
       </c>
     </row>
     <row r="992">
@@ -20321,10 +20321,10 @@
         <v>81.81999999999999</v>
       </c>
       <c r="E995" t="n">
-        <v>83.68000000000001</v>
+        <v>83.63</v>
       </c>
       <c r="F995" t="n">
-        <v>109380</v>
+        <v>110699</v>
       </c>
     </row>
     <row r="996">
@@ -20401,10 +20401,10 @@
         <v>77.63</v>
       </c>
       <c r="E999" t="n">
-        <v>78.68000000000001</v>
+        <v>78.8</v>
       </c>
       <c r="F999" t="n">
-        <v>149266</v>
+        <v>150672</v>
       </c>
     </row>
     <row r="1000">
@@ -20424,7 +20424,7 @@
         <v>78.51000000000001</v>
       </c>
       <c r="F1000" t="n">
-        <v>147017</v>
+        <v>148389</v>
       </c>
     </row>
     <row r="1001">
@@ -20501,10 +20501,10 @@
         <v>82.43000000000001</v>
       </c>
       <c r="E1004" t="n">
-        <v>83.91</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="F1004" t="n">
-        <v>141086</v>
+        <v>142735</v>
       </c>
     </row>
     <row r="1005">
@@ -20515,16 +20515,16 @@
         <v>83.91</v>
       </c>
       <c r="C1005" t="n">
-        <v>85.55</v>
+        <v>85.61</v>
       </c>
       <c r="D1005" t="n">
         <v>83.55</v>
       </c>
       <c r="E1005" t="n">
-        <v>85.48</v>
+        <v>85.47</v>
       </c>
       <c r="F1005" t="n">
-        <v>129757</v>
+        <v>131152</v>
       </c>
     </row>
     <row r="1006">
@@ -20601,10 +20601,10 @@
         <v>83.95999999999999</v>
       </c>
       <c r="E1009" t="n">
-        <v>86.31999999999999</v>
+        <v>86.34</v>
       </c>
       <c r="F1009" t="n">
-        <v>142583</v>
+        <v>144410</v>
       </c>
     </row>
     <row r="1010">
@@ -20621,10 +20621,10 @@
         <v>85.69</v>
       </c>
       <c r="E1010" t="n">
-        <v>87.75</v>
+        <v>87.59</v>
       </c>
       <c r="F1010" t="n">
-        <v>123973</v>
+        <v>125225</v>
       </c>
     </row>
     <row r="1011">
@@ -20701,10 +20701,10 @@
         <v>85.75</v>
       </c>
       <c r="E1014" t="n">
-        <v>87.31</v>
+        <v>87.29000000000001</v>
       </c>
       <c r="F1014" t="n">
-        <v>95077</v>
+        <v>96051</v>
       </c>
     </row>
     <row r="1015">
@@ -20721,10 +20721,10 @@
         <v>85.48</v>
       </c>
       <c r="E1015" t="n">
-        <v>86.04000000000001</v>
+        <v>86.01000000000001</v>
       </c>
       <c r="F1015" t="n">
-        <v>109841</v>
+        <v>110922</v>
       </c>
     </row>
     <row r="1016">
@@ -20801,10 +20801,10 @@
         <v>81.2</v>
       </c>
       <c r="E1019" t="n">
-        <v>81.98</v>
+        <v>82.12</v>
       </c>
       <c r="F1019" t="n">
-        <v>146732</v>
+        <v>150704</v>
       </c>
     </row>
     <row r="1020">
@@ -20818,13 +20818,13 @@
         <v>84.11</v>
       </c>
       <c r="D1020" t="n">
+        <v>79.53</v>
+      </c>
+      <c r="E1020" t="n">
         <v>79.62</v>
       </c>
-      <c r="E1020" t="n">
-        <v>79.64</v>
-      </c>
       <c r="F1020" t="n">
-        <v>161681</v>
+        <v>163093</v>
       </c>
     </row>
     <row r="1021">
@@ -20901,10 +20901,10 @@
         <v>82.86</v>
       </c>
       <c r="E1024" t="n">
-        <v>83.88</v>
+        <v>83.95</v>
       </c>
       <c r="F1024" t="n">
-        <v>142722</v>
+        <v>144061</v>
       </c>
     </row>
     <row r="1025">
@@ -20921,10 +20921,10 @@
         <v>83.66</v>
       </c>
       <c r="E1025" t="n">
-        <v>86.29000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="F1025" t="n">
-        <v>155562</v>
+        <v>156718</v>
       </c>
     </row>
     <row r="1026">
@@ -20998,13 +20998,13 @@
         <v>85.90000000000001</v>
       </c>
       <c r="D1029" t="n">
-        <v>84.31999999999999</v>
+        <v>84.28</v>
       </c>
       <c r="E1029" t="n">
-        <v>84.37</v>
+        <v>84.31</v>
       </c>
       <c r="F1029" t="n">
-        <v>128382</v>
+        <v>129946</v>
       </c>
     </row>
     <row r="1030">
@@ -21021,10 +21021,10 @@
         <v>81.55</v>
       </c>
       <c r="E1030" t="n">
-        <v>82.68000000000001</v>
+        <v>82.72</v>
       </c>
       <c r="F1030" t="n">
-        <v>141607</v>
+        <v>142763</v>
       </c>
     </row>
     <row r="1031">
@@ -21101,10 +21101,10 @@
         <v>80.27</v>
       </c>
       <c r="E1034" t="n">
-        <v>82.12</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="F1034" t="n">
-        <v>107083</v>
+        <v>108091</v>
       </c>
     </row>
     <row r="1035">
@@ -21121,10 +21121,10 @@
         <v>80.7</v>
       </c>
       <c r="E1035" t="n">
-        <v>82.94</v>
+        <v>82.77</v>
       </c>
       <c r="F1035" t="n">
-        <v>129354</v>
+        <v>130526</v>
       </c>
     </row>
     <row r="1036">
@@ -21201,10 +21201,10 @@
         <v>83.66</v>
       </c>
       <c r="E1039" t="n">
-        <v>84.34</v>
+        <v>84.23</v>
       </c>
       <c r="F1039" t="n">
-        <v>114302</v>
+        <v>115434</v>
       </c>
     </row>
     <row r="1040">
@@ -21215,16 +21215,16 @@
         <v>84.37</v>
       </c>
       <c r="C1040" t="n">
-        <v>85.8</v>
+        <v>85.81</v>
       </c>
       <c r="D1040" t="n">
         <v>82.2</v>
       </c>
       <c r="E1040" t="n">
-        <v>85.72</v>
+        <v>85.73999999999999</v>
       </c>
       <c r="F1040" t="n">
-        <v>119970</v>
+        <v>120888</v>
       </c>
     </row>
     <row r="1041">
@@ -21301,10 +21301,10 @@
         <v>81.16</v>
       </c>
       <c r="E1044" t="n">
-        <v>81.26000000000001</v>
+        <v>81.23</v>
       </c>
       <c r="F1044" t="n">
-        <v>120126</v>
+        <v>121276</v>
       </c>
     </row>
     <row r="1045">
@@ -21321,10 +21321,10 @@
         <v>80.47</v>
       </c>
       <c r="E1045" t="n">
-        <v>82.33</v>
+        <v>82.38</v>
       </c>
       <c r="F1045" t="n">
-        <v>171433</v>
+        <v>172647</v>
       </c>
     </row>
     <row r="1046">
@@ -21392,7 +21392,7 @@
         <v>45001</v>
       </c>
       <c r="B1049" t="n">
-        <v>74.04000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="C1049" t="n">
         <v>75.23</v>
@@ -21404,7 +21404,7 @@
         <v>74.25</v>
       </c>
       <c r="F1049" t="n">
-        <v>210322</v>
+        <v>206406</v>
       </c>
     </row>
     <row r="1050">
@@ -21412,7 +21412,7 @@
         <v>45002</v>
       </c>
       <c r="B1050" t="n">
-        <v>74.45</v>
+        <v>74.41</v>
       </c>
       <c r="C1050" t="n">
         <v>75.65000000000001</v>
@@ -21424,7 +21424,7 @@
         <v>72.3</v>
       </c>
       <c r="F1050" t="n">
-        <v>196053</v>
+        <v>194486</v>
       </c>
     </row>
     <row r="1051">
@@ -21492,7 +21492,7 @@
         <v>45008</v>
       </c>
       <c r="B1054" t="n">
-        <v>75.58</v>
+        <v>75.73</v>
       </c>
       <c r="C1054" t="n">
         <v>77.09</v>
@@ -21504,7 +21504,7 @@
         <v>74.98999999999999</v>
       </c>
       <c r="F1054" t="n">
-        <v>134971</v>
+        <v>132462</v>
       </c>
     </row>
     <row r="1055">
@@ -21512,7 +21512,7 @@
         <v>45009</v>
       </c>
       <c r="B1055" t="n">
-        <v>75.08</v>
+        <v>74.92</v>
       </c>
       <c r="C1055" t="n">
         <v>75.89</v>
@@ -21524,7 +21524,7 @@
         <v>74.52</v>
       </c>
       <c r="F1055" t="n">
-        <v>160608</v>
+        <v>158419</v>
       </c>
     </row>
     <row r="1056">
@@ -21601,10 +21601,10 @@
         <v>77.13</v>
       </c>
       <c r="E1059" t="n">
-        <v>78.47</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="F1059" t="n">
-        <v>101875</v>
+        <v>102975</v>
       </c>
     </row>
     <row r="1060">
@@ -21621,10 +21621,10 @@
         <v>77.79000000000001</v>
       </c>
       <c r="E1060" t="n">
-        <v>79.73</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="F1060" t="n">
-        <v>102278</v>
+        <v>103341</v>
       </c>
     </row>
     <row r="1061">
@@ -21701,10 +21701,10 @@
         <v>83.89</v>
       </c>
       <c r="E1064" t="n">
-        <v>84.73</v>
+        <v>84.62</v>
       </c>
       <c r="F1064" t="n">
-        <v>127887</v>
+        <v>128978</v>
       </c>
     </row>
     <row r="1065">
@@ -21781,10 +21781,10 @@
         <v>85.78</v>
       </c>
       <c r="E1068" t="n">
-        <v>85.98</v>
+        <v>86.03</v>
       </c>
       <c r="F1068" t="n">
-        <v>106530</v>
+        <v>107747</v>
       </c>
     </row>
     <row r="1069">
@@ -21801,10 +21801,10 @@
         <v>85.27</v>
       </c>
       <c r="E1069" t="n">
-        <v>86.13</v>
+        <v>86.12</v>
       </c>
       <c r="F1069" t="n">
-        <v>118921</v>
+        <v>119789</v>
       </c>
     </row>
     <row r="1070">
@@ -21878,13 +21878,13 @@
         <v>82.59999999999999</v>
       </c>
       <c r="D1073" t="n">
-        <v>80.51000000000001</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="E1073" t="n">
-        <v>80.62</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="F1073" t="n">
-        <v>99083</v>
+        <v>100157</v>
       </c>
     </row>
     <row r="1074">
@@ -21901,10 +21901,10 @@
         <v>80.2</v>
       </c>
       <c r="E1074" t="n">
-        <v>81.38</v>
+        <v>81.53</v>
       </c>
       <c r="F1074" t="n">
-        <v>88877</v>
+        <v>89589</v>
       </c>
     </row>
     <row r="1075">
@@ -21981,10 +21981,10 @@
         <v>77.3</v>
       </c>
       <c r="E1078" t="n">
-        <v>78.23</v>
+        <v>78.17</v>
       </c>
       <c r="F1078" t="n">
-        <v>112919</v>
+        <v>114226</v>
       </c>
     </row>
     <row r="1079">
@@ -22001,10 +22001,10 @@
         <v>77.44</v>
       </c>
       <c r="E1079" t="n">
-        <v>80.20999999999999</v>
+        <v>80.08</v>
       </c>
       <c r="F1079" t="n">
-        <v>110643</v>
+        <v>111593</v>
       </c>
     </row>
     <row r="1080">
@@ -22081,10 +22081,10 @@
         <v>71.34</v>
       </c>
       <c r="E1083" t="n">
-        <v>72.34</v>
+        <v>72.38</v>
       </c>
       <c r="F1083" t="n">
-        <v>175075</v>
+        <v>176458</v>
       </c>
     </row>
     <row r="1084">
@@ -22101,10 +22101,10 @@
         <v>72.31999999999999</v>
       </c>
       <c r="E1084" t="n">
-        <v>75.22</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="F1084" t="n">
-        <v>121559</v>
+        <v>122688</v>
       </c>
     </row>
     <row r="1085">
@@ -22181,10 +22181,10 @@
         <v>74.5</v>
       </c>
       <c r="E1088" t="n">
-        <v>75.34999999999999</v>
+        <v>75.26000000000001</v>
       </c>
       <c r="F1088" t="n">
-        <v>141443</v>
+        <v>142391</v>
       </c>
     </row>
     <row r="1089">
@@ -22201,10 +22201,10 @@
         <v>73.84999999999999</v>
       </c>
       <c r="E1089" t="n">
-        <v>74.02</v>
+        <v>73.93000000000001</v>
       </c>
       <c r="F1089" t="n">
-        <v>143925</v>
+        <v>144762</v>
       </c>
     </row>
     <row r="1090">
@@ -22281,10 +22281,10 @@
         <v>75.42</v>
       </c>
       <c r="E1093" t="n">
-        <v>75.89</v>
+        <v>75.84</v>
       </c>
       <c r="F1093" t="n">
-        <v>97144</v>
+        <v>98116</v>
       </c>
     </row>
     <row r="1094">
@@ -22301,10 +22301,10 @@
         <v>75.01000000000001</v>
       </c>
       <c r="E1094" t="n">
-        <v>75.75</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="F1094" t="n">
-        <v>107224</v>
+        <v>108218</v>
       </c>
     </row>
     <row r="1095">
@@ -22381,10 +22381,10 @@
         <v>75.08</v>
       </c>
       <c r="E1098" t="n">
-        <v>76.13</v>
+        <v>75.95999999999999</v>
       </c>
       <c r="F1098" t="n">
-        <v>94656</v>
+        <v>95663</v>
       </c>
     </row>
     <row r="1099">
@@ -22401,10 +22401,10 @@
         <v>75.62</v>
       </c>
       <c r="E1099" t="n">
-        <v>77.03</v>
+        <v>77.14</v>
       </c>
       <c r="F1099" t="n">
-        <v>85632</v>
+        <v>86227</v>
       </c>
     </row>
     <row r="1100">
@@ -22481,10 +22481,10 @@
         <v>72</v>
       </c>
       <c r="E1103" t="n">
-        <v>74.17</v>
+        <v>74.25</v>
       </c>
       <c r="F1103" t="n">
-        <v>122959</v>
+        <v>124084</v>
       </c>
     </row>
     <row r="1104">
@@ -22501,10 +22501,10 @@
         <v>74.13</v>
       </c>
       <c r="E1104" t="n">
-        <v>76.3</v>
+        <v>76.13</v>
       </c>
       <c r="F1104" t="n">
-        <v>110715</v>
+        <v>111881</v>
       </c>
     </row>
     <row r="1105">
@@ -22581,10 +22581,10 @@
         <v>73.52</v>
       </c>
       <c r="E1108" t="n">
-        <v>75.56999999999999</v>
+        <v>75.44</v>
       </c>
       <c r="F1108" t="n">
-        <v>141391</v>
+        <v>142206</v>
       </c>
     </row>
     <row r="1109">
@@ -22601,10 +22601,10 @@
         <v>74.67</v>
       </c>
       <c r="E1109" t="n">
-        <v>74.84999999999999</v>
+        <v>74.88</v>
       </c>
       <c r="F1109" t="n">
-        <v>120105</v>
+        <v>120995</v>
       </c>
     </row>
     <row r="1110">
@@ -22681,10 +22681,10 @@
         <v>72.84999999999999</v>
       </c>
       <c r="E1113" t="n">
-        <v>75.56</v>
+        <v>75.52</v>
       </c>
       <c r="F1113" t="n">
-        <v>104970</v>
+        <v>105947</v>
       </c>
     </row>
     <row r="1114">
@@ -22701,10 +22701,10 @@
         <v>75.09999999999999</v>
       </c>
       <c r="E1114" t="n">
-        <v>76.47</v>
+        <v>76.23</v>
       </c>
       <c r="F1114" t="n">
-        <v>109963</v>
+        <v>111184</v>
       </c>
     </row>
     <row r="1115">
@@ -22781,10 +22781,10 @@
         <v>73.75</v>
       </c>
       <c r="E1118" t="n">
-        <v>74.2</v>
+        <v>74.3</v>
       </c>
       <c r="F1118" t="n">
-        <v>89166</v>
+        <v>89974</v>
       </c>
     </row>
     <row r="1119">
@@ -22795,16 +22795,16 @@
         <v>74.2</v>
       </c>
       <c r="C1119" t="n">
-        <v>74.36</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="D1119" t="n">
         <v>72.25</v>
       </c>
       <c r="E1119" t="n">
-        <v>74.09</v>
+        <v>74.34</v>
       </c>
       <c r="F1119" t="n">
-        <v>100773</v>
+        <v>101628</v>
       </c>
     </row>
     <row r="1120">
@@ -22881,10 +22881,10 @@
         <v>73.56</v>
       </c>
       <c r="E1123" t="n">
-        <v>74.44</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="F1123" t="n">
-        <v>118096</v>
+        <v>118860</v>
       </c>
     </row>
     <row r="1124">
@@ -22901,10 +22901,10 @@
         <v>74.23</v>
       </c>
       <c r="E1124" t="n">
-        <v>75.26000000000001</v>
+        <v>75.06999999999999</v>
       </c>
       <c r="F1124" t="n">
-        <v>107062</v>
+        <v>108012</v>
       </c>
     </row>
     <row r="1125">
@@ -22981,10 +22981,10 @@
         <v>74.94</v>
       </c>
       <c r="E1128" t="n">
-        <v>76.47</v>
+        <v>76.44</v>
       </c>
       <c r="F1128" t="n">
-        <v>120498</v>
+        <v>121613</v>
       </c>
     </row>
     <row r="1129">
@@ -23001,10 +23001,10 @@
         <v>75.91</v>
       </c>
       <c r="E1129" t="n">
-        <v>78.13</v>
+        <v>78.12</v>
       </c>
       <c r="F1129" t="n">
-        <v>99946</v>
+        <v>101260</v>
       </c>
     </row>
     <row r="1130">
@@ -23075,16 +23075,16 @@
         <v>79.95999999999999</v>
       </c>
       <c r="C1133" t="n">
-        <v>81.48999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="D1133" t="n">
         <v>79.69</v>
       </c>
       <c r="E1133" t="n">
-        <v>81.48</v>
+        <v>81.37</v>
       </c>
       <c r="F1133" t="n">
-        <v>96443</v>
+        <v>97805</v>
       </c>
     </row>
     <row r="1134">
@@ -23098,13 +23098,13 @@
         <v>81.42</v>
       </c>
       <c r="D1134" t="n">
-        <v>79.44</v>
+        <v>79.34999999999999</v>
       </c>
       <c r="E1134" t="n">
-        <v>79.54000000000001</v>
+        <v>79.45</v>
       </c>
       <c r="F1134" t="n">
-        <v>98000</v>
+        <v>99161</v>
       </c>
     </row>
     <row r="1135">
@@ -23181,10 +23181,10 @@
         <v>78.56999999999999</v>
       </c>
       <c r="E1138" t="n">
-        <v>79.54000000000001</v>
+        <v>79.48</v>
       </c>
       <c r="F1138" t="n">
-        <v>76777</v>
+        <v>77506</v>
       </c>
     </row>
     <row r="1139">
@@ -23201,10 +23201,10 @@
         <v>79.51000000000001</v>
       </c>
       <c r="E1139" t="n">
-        <v>80.69</v>
+        <v>80.5</v>
       </c>
       <c r="F1139" t="n">
-        <v>69907</v>
+        <v>70745</v>
       </c>
     </row>
     <row r="1140">
@@ -23281,10 +23281,10 @@
         <v>82.54000000000001</v>
       </c>
       <c r="E1143" t="n">
-        <v>83.42</v>
+        <v>83.3</v>
       </c>
       <c r="F1143" t="n">
-        <v>100960</v>
+        <v>101885</v>
       </c>
     </row>
     <row r="1144">
@@ -23301,10 +23301,10 @@
         <v>82.78</v>
       </c>
       <c r="E1144" t="n">
-        <v>84.26000000000001</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="F1144" t="n">
-        <v>96080</v>
+        <v>96933</v>
       </c>
     </row>
     <row r="1145">
@@ -23381,10 +23381,10 @@
         <v>82.23</v>
       </c>
       <c r="E1148" t="n">
-        <v>85.13</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="F1148" t="n">
-        <v>122532</v>
+        <v>124232</v>
       </c>
     </row>
     <row r="1149">
@@ -23401,10 +23401,10 @@
         <v>84.89</v>
       </c>
       <c r="E1149" t="n">
-        <v>85.84</v>
+        <v>85.81</v>
       </c>
       <c r="F1149" t="n">
-        <v>103319</v>
+        <v>104424</v>
       </c>
     </row>
     <row r="1150">
@@ -23481,10 +23481,10 @@
         <v>85.89</v>
       </c>
       <c r="E1153" t="n">
-        <v>86.09999999999999</v>
+        <v>86.01000000000001</v>
       </c>
       <c r="F1153" t="n">
-        <v>119054</v>
+        <v>120019</v>
       </c>
     </row>
     <row r="1154">
@@ -23501,10 +23501,10 @@
         <v>85.53</v>
       </c>
       <c r="E1154" t="n">
-        <v>86.26000000000001</v>
+        <v>86.16</v>
       </c>
       <c r="F1154" t="n">
-        <v>114400</v>
+        <v>115051</v>
       </c>
     </row>
     <row r="1155">
@@ -23581,10 +23581,10 @@
         <v>82.70999999999999</v>
       </c>
       <c r="E1158" t="n">
-        <v>83.45999999999999</v>
+        <v>83.42</v>
       </c>
       <c r="F1158" t="n">
-        <v>87119</v>
+        <v>88033</v>
       </c>
     </row>
     <row r="1159">
@@ -23601,10 +23601,10 @@
         <v>82.98</v>
       </c>
       <c r="E1159" t="n">
-        <v>84.37</v>
+        <v>84.42</v>
       </c>
       <c r="F1159" t="n">
-        <v>98085</v>
+        <v>98761</v>
       </c>
     </row>
     <row r="1160">
@@ -23681,10 +23681,10 @@
         <v>81.61</v>
       </c>
       <c r="E1163" t="n">
-        <v>82.76000000000001</v>
+        <v>82.67</v>
       </c>
       <c r="F1163" t="n">
-        <v>77118</v>
+        <v>77961</v>
       </c>
     </row>
     <row r="1164">
@@ -23701,10 +23701,10 @@
         <v>82.2</v>
       </c>
       <c r="E1164" t="n">
-        <v>84.14</v>
+        <v>84.05</v>
       </c>
       <c r="F1164" t="n">
-        <v>101382</v>
+        <v>102303</v>
       </c>
     </row>
     <row r="1165">
@@ -23781,10 +23781,10 @@
         <v>84.98</v>
       </c>
       <c r="E1168" t="n">
-        <v>86.63</v>
+        <v>86.66</v>
       </c>
       <c r="F1168" t="n">
-        <v>83934</v>
+        <v>85007</v>
       </c>
     </row>
     <row r="1169">
@@ -23795,16 +23795,16 @@
         <v>86.63</v>
       </c>
       <c r="C1169" t="n">
-        <v>88.66</v>
+        <v>88.75</v>
       </c>
       <c r="D1169" t="n">
         <v>86.59</v>
       </c>
       <c r="E1169" t="n">
-        <v>88.64</v>
+        <v>88.68000000000001</v>
       </c>
       <c r="F1169" t="n">
-        <v>97671</v>
+        <v>98645</v>
       </c>
     </row>
     <row r="1170">
@@ -23881,10 +23881,10 @@
         <v>89.17</v>
       </c>
       <c r="E1173" t="n">
-        <v>89.76000000000001</v>
+        <v>89.47</v>
       </c>
       <c r="F1173" t="n">
-        <v>103067</v>
+        <v>104343</v>
       </c>
     </row>
     <row r="1174">
@@ -23901,10 +23901,10 @@
         <v>88.97</v>
       </c>
       <c r="E1174" t="n">
-        <v>90.2</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="F1174" t="n">
-        <v>100164</v>
+        <v>101197</v>
       </c>
     </row>
     <row r="1175">
@@ -23975,16 +23975,16 @@
         <v>91.56999999999999</v>
       </c>
       <c r="C1178" t="n">
-        <v>93.44</v>
+        <v>93.68000000000001</v>
       </c>
       <c r="D1178" t="n">
         <v>91.55</v>
       </c>
       <c r="E1178" t="n">
-        <v>93.36</v>
+        <v>93.56</v>
       </c>
       <c r="F1178" t="n">
-        <v>89908</v>
+        <v>91727</v>
       </c>
     </row>
     <row r="1179">
@@ -24001,10 +24001,10 @@
         <v>92.14</v>
       </c>
       <c r="E1179" t="n">
-        <v>93.52</v>
+        <v>93.56999999999999</v>
       </c>
       <c r="F1179" t="n">
-        <v>100530</v>
+        <v>101498</v>
       </c>
     </row>
     <row r="1180">
@@ -24081,10 +24081,10 @@
         <v>91.23999999999999</v>
       </c>
       <c r="E1183" t="n">
-        <v>92.27</v>
+        <v>92.20999999999999</v>
       </c>
       <c r="F1183" t="n">
-        <v>97207</v>
+        <v>98137</v>
       </c>
     </row>
     <row r="1184">
@@ -24101,10 +24101,10 @@
         <v>91.68000000000001</v>
       </c>
       <c r="E1184" t="n">
-        <v>92.31</v>
+        <v>92.28</v>
       </c>
       <c r="F1184" t="n">
-        <v>98960</v>
+        <v>99665</v>
       </c>
     </row>
     <row r="1185">
@@ -24181,10 +24181,10 @@
         <v>92.56</v>
       </c>
       <c r="E1188" t="n">
-        <v>92.94</v>
+        <v>92.89</v>
       </c>
       <c r="F1188" t="n">
-        <v>127194</v>
+        <v>128240</v>
       </c>
     </row>
     <row r="1189">
@@ -24201,10 +24201,10 @@
         <v>91.68000000000001</v>
       </c>
       <c r="E1189" t="n">
-        <v>91.95999999999999</v>
+        <v>91.8</v>
       </c>
       <c r="F1189" t="n">
-        <v>116761</v>
+        <v>117877</v>
       </c>
     </row>
     <row r="1190">
@@ -24281,10 +24281,10 @@
         <v>83.31999999999999</v>
       </c>
       <c r="E1193" t="n">
-        <v>83.68000000000001</v>
+        <v>83.72</v>
       </c>
       <c r="F1193" t="n">
-        <v>148426</v>
+        <v>149779</v>
       </c>
     </row>
     <row r="1194">
@@ -24301,10 +24301,10 @@
         <v>82.97</v>
       </c>
       <c r="E1194" t="n">
-        <v>83.88</v>
+        <v>83.79000000000001</v>
       </c>
       <c r="F1194" t="n">
-        <v>138785</v>
+        <v>140020</v>
       </c>
     </row>
     <row r="1195">
@@ -24381,10 +24381,10 @@
         <v>84.59</v>
       </c>
       <c r="E1198" t="n">
-        <v>85.7</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="F1198" t="n">
-        <v>123421</v>
+        <v>124560</v>
       </c>
     </row>
     <row r="1199">
@@ -24404,7 +24404,7 @@
         <v>89.93000000000001</v>
       </c>
       <c r="F1199" t="n">
-        <v>118765</v>
+        <v>120817</v>
       </c>
     </row>
     <row r="1200">
@@ -24475,16 +24475,16 @@
         <v>90.26000000000001</v>
       </c>
       <c r="C1203" t="n">
-        <v>92.22</v>
+        <v>92.34999999999999</v>
       </c>
       <c r="D1203" t="n">
         <v>88.69</v>
       </c>
       <c r="E1203" t="n">
-        <v>92.16</v>
+        <v>92.04000000000001</v>
       </c>
       <c r="F1203" t="n">
-        <v>109002</v>
+        <v>111224</v>
       </c>
     </row>
     <row r="1204">
@@ -24501,10 +24501,10 @@
         <v>90.63</v>
       </c>
       <c r="E1204" t="n">
-        <v>91.13</v>
+        <v>91.26000000000001</v>
       </c>
       <c r="F1204" t="n">
-        <v>109157</v>
+        <v>110661</v>
       </c>
     </row>
     <row r="1205">
@@ -24581,10 +24581,10 @@
         <v>86.48</v>
       </c>
       <c r="E1208" t="n">
-        <v>87.25</v>
+        <v>87.23999999999999</v>
       </c>
       <c r="F1208" t="n">
-        <v>113368</v>
+        <v>114536</v>
       </c>
     </row>
     <row r="1209">
@@ -24601,10 +24601,10 @@
         <v>86.76000000000001</v>
       </c>
       <c r="E1209" t="n">
-        <v>88.76000000000001</v>
+        <v>88.70999999999999</v>
       </c>
       <c r="F1209" t="n">
-        <v>121600</v>
+        <v>123231</v>
       </c>
     </row>
     <row r="1210">
@@ -24672,7 +24672,7 @@
         <v>45232</v>
       </c>
       <c r="B1213" t="n">
-        <v>84.83</v>
+        <v>85.03</v>
       </c>
       <c r="C1213" t="n">
         <v>86.88</v>
@@ -24684,7 +24684,7 @@
         <v>86.63</v>
       </c>
       <c r="F1213" t="n">
-        <v>103842</v>
+        <v>102261</v>
       </c>
     </row>
     <row r="1214">
@@ -24692,7 +24692,7 @@
         <v>45233</v>
       </c>
       <c r="B1214" t="n">
-        <v>86.70999999999999</v>
+        <v>86.66</v>
       </c>
       <c r="C1214" t="n">
         <v>87.58</v>
@@ -24704,7 +24704,7 @@
         <v>84.95</v>
       </c>
       <c r="F1214" t="n">
-        <v>119097</v>
+        <v>117913</v>
       </c>
     </row>
     <row r="1215">
@@ -24781,10 +24781,10 @@
         <v>79.33</v>
       </c>
       <c r="E1218" t="n">
-        <v>79.75</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="F1218" t="n">
-        <v>110739</v>
+        <v>111847</v>
       </c>
     </row>
     <row r="1219">
@@ -24801,10 +24801,10 @@
         <v>79.70999999999999</v>
       </c>
       <c r="E1219" t="n">
-        <v>81.36</v>
+        <v>81.43000000000001</v>
       </c>
       <c r="F1219" t="n">
-        <v>91256</v>
+        <v>92327</v>
       </c>
     </row>
     <row r="1220">
@@ -24881,10 +24881,10 @@
         <v>76.64</v>
       </c>
       <c r="E1223" t="n">
-        <v>77.43000000000001</v>
+        <v>77.45</v>
       </c>
       <c r="F1223" t="n">
-        <v>104766</v>
+        <v>105749</v>
       </c>
     </row>
     <row r="1224">
@@ -24901,10 +24901,10 @@
         <v>77.31</v>
       </c>
       <c r="E1224" t="n">
-        <v>80.37</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="F1224" t="n">
-        <v>88772</v>
+        <v>89648</v>
       </c>
     </row>
     <row r="1225">
@@ -25078,13 +25078,13 @@
         <v>84.51000000000001</v>
       </c>
       <c r="D1233" t="n">
-        <v>79.95</v>
+        <v>79.94</v>
       </c>
       <c r="E1233" t="n">
-        <v>80</v>
+        <v>80.31</v>
       </c>
       <c r="F1233" t="n">
-        <v>143673</v>
+        <v>145419</v>
       </c>
     </row>
     <row r="1234">
@@ -25101,10 +25101,10 @@
         <v>78.69</v>
       </c>
       <c r="E1234" t="n">
-        <v>78.93000000000001</v>
+        <v>79.02</v>
       </c>
       <c r="F1234" t="n">
-        <v>125186</v>
+        <v>126159</v>
       </c>
     </row>
     <row r="1235">
@@ -25181,10 +25181,10 @@
         <v>73.68000000000001</v>
       </c>
       <c r="E1238" t="n">
-        <v>74.47</v>
+        <v>74.39</v>
       </c>
       <c r="F1238" t="n">
-        <v>115986</v>
+        <v>116791</v>
       </c>
     </row>
     <row r="1239">
@@ -25201,10 +25201,10 @@
         <v>74.25</v>
       </c>
       <c r="E1239" t="n">
-        <v>75.87</v>
+        <v>75.94</v>
       </c>
       <c r="F1239" t="n">
-        <v>114085</v>
+        <v>114930</v>
       </c>
     </row>
     <row r="1240">
@@ -25281,10 +25281,10 @@
         <v>74.56999999999999</v>
       </c>
       <c r="E1243" t="n">
-        <v>76.86</v>
+        <v>76.75</v>
       </c>
       <c r="F1243" t="n">
-        <v>83845</v>
+        <v>84712</v>
       </c>
     </row>
     <row r="1244">
@@ -25301,10 +25301,10 @@
         <v>75.48</v>
       </c>
       <c r="E1244" t="n">
-        <v>76.90000000000001</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="F1244" t="n">
-        <v>94162</v>
+        <v>95068</v>
       </c>
     </row>
     <row r="1245">
@@ -25381,10 +25381,10 @@
         <v>77.76000000000001</v>
       </c>
       <c r="E1248" t="n">
-        <v>79.19</v>
+        <v>79.12</v>
       </c>
       <c r="F1248" t="n">
-        <v>91100</v>
+        <v>91755</v>
       </c>
     </row>
     <row r="1249">
@@ -25461,10 +25461,10 @@
         <v>77.04000000000001</v>
       </c>
       <c r="E1252" t="n">
-        <v>77.29000000000001</v>
+        <v>77.36</v>
       </c>
       <c r="F1252" t="n">
-        <v>94380</v>
+        <v>95204</v>
       </c>
     </row>
     <row r="1253">
@@ -25544,7 +25544,7 @@
         <v>77.53</v>
       </c>
       <c r="F1256" t="n">
-        <v>118273</v>
+        <v>119158</v>
       </c>
     </row>
     <row r="1257">
@@ -25641,10 +25641,10 @@
         <v>76.45</v>
       </c>
       <c r="E1261" t="n">
-        <v>77.61</v>
+        <v>78.01000000000001</v>
       </c>
       <c r="F1261" t="n">
-        <v>128067</v>
+        <v>129868</v>
       </c>
     </row>
     <row r="1262">
@@ -25741,10 +25741,10 @@
         <v>76.98</v>
       </c>
       <c r="E1266" t="n">
-        <v>78.63</v>
+        <v>78.56</v>
       </c>
       <c r="F1266" t="n">
-        <v>98609</v>
+        <v>99368</v>
       </c>
     </row>
     <row r="1267">
@@ -25841,10 +25841,10 @@
         <v>79.65000000000001</v>
       </c>
       <c r="E1271" t="n">
-        <v>81.84999999999999</v>
+        <v>81.69</v>
       </c>
       <c r="F1271" t="n">
-        <v>75889</v>
+        <v>76710</v>
       </c>
     </row>
     <row r="1272">
@@ -25861,10 +25861,10 @@
         <v>80.75</v>
       </c>
       <c r="E1272" t="n">
-        <v>83.08</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="F1272" t="n">
-        <v>85666</v>
+        <v>87047</v>
       </c>
     </row>
     <row r="1273">
@@ -25941,10 +25941,10 @@
         <v>78.5</v>
       </c>
       <c r="E1276" t="n">
-        <v>78.64</v>
+        <v>78.7</v>
       </c>
       <c r="F1276" t="n">
-        <v>138682</v>
+        <v>140571</v>
       </c>
     </row>
     <row r="1277">
@@ -25961,10 +25961,10 @@
         <v>76.78</v>
       </c>
       <c r="E1277" t="n">
-        <v>77.11</v>
+        <v>77.31999999999999</v>
       </c>
       <c r="F1277" t="n">
-        <v>132023</v>
+        <v>133396</v>
       </c>
     </row>
     <row r="1278">
@@ -26041,10 +26041,10 @@
         <v>78.84999999999999</v>
       </c>
       <c r="E1281" t="n">
-        <v>81.51000000000001</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="F1281" t="n">
-        <v>86597</v>
+        <v>87658</v>
       </c>
     </row>
     <row r="1282">
@@ -26064,7 +26064,7 @@
         <v>81.63</v>
       </c>
       <c r="F1282" t="n">
-        <v>85346</v>
+        <v>86235</v>
       </c>
     </row>
     <row r="1283">
@@ -26141,10 +26141,10 @@
         <v>80.31999999999999</v>
       </c>
       <c r="E1286" t="n">
-        <v>82.37</v>
+        <v>82.22</v>
       </c>
       <c r="F1286" t="n">
-        <v>83753</v>
+        <v>84560</v>
       </c>
     </row>
     <row r="1287">
@@ -26161,10 +26161,10 @@
         <v>81.34</v>
       </c>
       <c r="E1287" t="n">
-        <v>82.70999999999999</v>
+        <v>82.68000000000001</v>
       </c>
       <c r="F1287" t="n">
-        <v>80620</v>
+        <v>81459</v>
       </c>
     </row>
     <row r="1288">
@@ -26241,10 +26241,10 @@
         <v>81.45</v>
       </c>
       <c r="E1291" t="n">
-        <v>82.63</v>
+        <v>82.51000000000001</v>
       </c>
       <c r="F1291" t="n">
-        <v>67106</v>
+        <v>67848</v>
       </c>
     </row>
     <row r="1292">
@@ -26261,10 +26261,10 @@
         <v>80.65000000000001</v>
       </c>
       <c r="E1292" t="n">
-        <v>80.88</v>
+        <v>80.84</v>
       </c>
       <c r="F1292" t="n">
-        <v>72495</v>
+        <v>73168</v>
       </c>
     </row>
     <row r="1293">
@@ -26341,10 +26341,10 @@
         <v>81.37</v>
       </c>
       <c r="E1296" t="n">
-        <v>81.70999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="F1296" t="n">
-        <v>78801</v>
+        <v>79642</v>
       </c>
     </row>
     <row r="1297">
@@ -26361,10 +26361,10 @@
         <v>81.63</v>
       </c>
       <c r="E1297" t="n">
-        <v>83.19</v>
+        <v>83.12</v>
       </c>
       <c r="F1297" t="n">
-        <v>72423</v>
+        <v>73275</v>
       </c>
     </row>
     <row r="1298">
@@ -26441,10 +26441,10 @@
         <v>81.77</v>
       </c>
       <c r="E1301" t="n">
-        <v>82.52</v>
+        <v>82.87</v>
       </c>
       <c r="F1301" t="n">
-        <v>102278</v>
+        <v>103853</v>
       </c>
     </row>
     <row r="1302">
@@ -26461,10 +26461,10 @@
         <v>81.41</v>
       </c>
       <c r="E1302" t="n">
-        <v>81.66</v>
+        <v>81.55</v>
       </c>
       <c r="F1302" t="n">
-        <v>99175</v>
+        <v>100115</v>
       </c>
     </row>
     <row r="1303">
@@ -26532,19 +26532,19 @@
         <v>45365</v>
       </c>
       <c r="B1306" t="n">
-        <v>83.59999999999999</v>
+        <v>83.69</v>
       </c>
       <c r="C1306" t="n">
         <v>85.18000000000001</v>
       </c>
       <c r="D1306" t="n">
-        <v>83.53</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="E1306" t="n">
         <v>84.61</v>
       </c>
       <c r="F1306" t="n">
-        <v>71844</v>
+        <v>71119</v>
       </c>
     </row>
     <row r="1307">
@@ -26552,7 +26552,7 @@
         <v>45366</v>
       </c>
       <c r="B1307" t="n">
-        <v>84.65000000000001</v>
+        <v>84.68000000000001</v>
       </c>
       <c r="C1307" t="n">
         <v>85.09</v>
@@ -26564,7 +26564,7 @@
         <v>84.83</v>
       </c>
       <c r="F1307" t="n">
-        <v>75864</v>
+        <v>74945</v>
       </c>
     </row>
     <row r="1308">
@@ -26632,7 +26632,7 @@
         <v>45372</v>
       </c>
       <c r="B1311" t="n">
-        <v>85.70999999999999</v>
+        <v>85.81</v>
       </c>
       <c r="C1311" t="n">
         <v>86.03</v>
@@ -26644,7 +26644,7 @@
         <v>84.95999999999999</v>
       </c>
       <c r="F1311" t="n">
-        <v>67186</v>
+        <v>66113</v>
       </c>
     </row>
     <row r="1312">
@@ -26652,7 +26652,7 @@
         <v>45373</v>
       </c>
       <c r="B1312" t="n">
-        <v>85.09999999999999</v>
+        <v>84.98999999999999</v>
       </c>
       <c r="C1312" t="n">
         <v>85.58</v>
@@ -26664,7 +26664,7 @@
         <v>84.93000000000001</v>
       </c>
       <c r="F1312" t="n">
-        <v>54286</v>
+        <v>53666</v>
       </c>
     </row>
     <row r="1313">
@@ -26732,7 +26732,7 @@
         <v>45379</v>
       </c>
       <c r="B1316" t="n">
-        <v>85.56</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="C1316" t="n">
         <v>86.89</v>
@@ -26744,7 +26744,7 @@
         <v>86.67</v>
       </c>
       <c r="F1316" t="n">
-        <v>57372</v>
+        <v>56915</v>
       </c>
     </row>
     <row r="1317">
@@ -26821,10 +26821,10 @@
         <v>88.43000000000001</v>
       </c>
       <c r="E1320" t="n">
-        <v>90.38</v>
+        <v>90.56</v>
       </c>
       <c r="F1320" t="n">
-        <v>74470</v>
+        <v>75666</v>
       </c>
     </row>
     <row r="1321">
@@ -26841,10 +26841,10 @@
         <v>90.18000000000001</v>
       </c>
       <c r="E1321" t="n">
-        <v>90.52</v>
+        <v>90.39</v>
       </c>
       <c r="F1321" t="n">
-        <v>79937</v>
+        <v>80607</v>
       </c>
     </row>
     <row r="1322">
@@ -26921,10 +26921,10 @@
         <v>88.87</v>
       </c>
       <c r="E1325" t="n">
-        <v>89.68000000000001</v>
+        <v>89.55</v>
       </c>
       <c r="F1325" t="n">
-        <v>107040</v>
+        <v>107884</v>
       </c>
     </row>
     <row r="1326">
@@ -26941,10 +26941,10 @@
         <v>89.45</v>
       </c>
       <c r="E1326" t="n">
-        <v>89.73</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="F1326" t="n">
-        <v>108331</v>
+        <v>109120</v>
       </c>
     </row>
     <row r="1327">
@@ -27021,10 +27021,10 @@
         <v>85.63</v>
       </c>
       <c r="E1330" t="n">
-        <v>86.47</v>
+        <v>86.19</v>
       </c>
       <c r="F1330" t="n">
-        <v>107464</v>
+        <v>108132</v>
       </c>
     </row>
     <row r="1331">
@@ -27041,10 +27041,10 @@
         <v>85.61</v>
       </c>
       <c r="E1331" t="n">
-        <v>86.51000000000001</v>
+        <v>86.38</v>
       </c>
       <c r="F1331" t="n">
-        <v>143518</v>
+        <v>144473</v>
       </c>
     </row>
     <row r="1332">
@@ -27115,16 +27115,16 @@
         <v>86.88</v>
       </c>
       <c r="C1335" t="n">
-        <v>87.97</v>
+        <v>88</v>
       </c>
       <c r="D1335" t="n">
         <v>86.2</v>
       </c>
       <c r="E1335" t="n">
-        <v>87.95</v>
+        <v>87.83</v>
       </c>
       <c r="F1335" t="n">
-        <v>69439</v>
+        <v>70059</v>
       </c>
     </row>
     <row r="1336">
@@ -27141,10 +27141,10 @@
         <v>87.56999999999999</v>
       </c>
       <c r="E1336" t="n">
-        <v>87.98999999999999</v>
+        <v>87.89</v>
       </c>
       <c r="F1336" t="n">
-        <v>63936</v>
+        <v>64445</v>
       </c>
     </row>
     <row r="1337">
@@ -27221,10 +27221,10 @@
         <v>82.89</v>
       </c>
       <c r="E1340" t="n">
-        <v>83.47</v>
+        <v>83.48</v>
       </c>
       <c r="F1340" t="n">
-        <v>100961</v>
+        <v>101847</v>
       </c>
     </row>
     <row r="1341">
@@ -27238,13 +27238,13 @@
         <v>84.18000000000001</v>
       </c>
       <c r="D1341" t="n">
-        <v>82.65000000000001</v>
+        <v>82.53</v>
       </c>
       <c r="E1341" t="n">
-        <v>82.77</v>
+        <v>82.54000000000001</v>
       </c>
       <c r="F1341" t="n">
-        <v>82987</v>
+        <v>83584</v>
       </c>
     </row>
     <row r="1342">
@@ -27321,10 +27321,10 @@
         <v>83.18000000000001</v>
       </c>
       <c r="E1345" t="n">
-        <v>83.91</v>
+        <v>83.77</v>
       </c>
       <c r="F1345" t="n">
-        <v>67201</v>
+        <v>67737</v>
       </c>
     </row>
     <row r="1346">
@@ -27338,13 +27338,13 @@
         <v>84.23</v>
       </c>
       <c r="D1346" t="n">
-        <v>82.5</v>
+        <v>82.36</v>
       </c>
       <c r="E1346" t="n">
-        <v>82.61</v>
+        <v>82.36</v>
       </c>
       <c r="F1346" t="n">
-        <v>62356</v>
+        <v>63117</v>
       </c>
     </row>
     <row r="1347">
@@ -27421,10 +27421,10 @@
         <v>82.02</v>
       </c>
       <c r="E1350" t="n">
-        <v>83.04000000000001</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="F1350" t="n">
-        <v>65306</v>
+        <v>65759</v>
       </c>
     </row>
     <row r="1351">
@@ -27441,10 +27441,10 @@
         <v>82.81999999999999</v>
       </c>
       <c r="E1351" t="n">
-        <v>83.68000000000001</v>
+        <v>83.56</v>
       </c>
       <c r="F1351" t="n">
-        <v>60667</v>
+        <v>61133</v>
       </c>
     </row>
     <row r="1352">
@@ -27521,10 +27521,10 @@
         <v>80.7</v>
       </c>
       <c r="E1355" t="n">
-        <v>81.09</v>
+        <v>81.06999999999999</v>
       </c>
       <c r="F1355" t="n">
-        <v>68901</v>
+        <v>69958</v>
       </c>
     </row>
     <row r="1356">
@@ -27541,10 +27541,10 @@
         <v>80.42</v>
       </c>
       <c r="E1356" t="n">
-        <v>81.84999999999999</v>
+        <v>81.79000000000001</v>
       </c>
       <c r="F1356" t="n">
-        <v>56045</v>
+        <v>56381</v>
       </c>
     </row>
     <row r="1357">
@@ -27618,13 +27618,13 @@
         <v>83.51000000000001</v>
       </c>
       <c r="D1360" t="n">
-        <v>81.77</v>
+        <v>81.72</v>
       </c>
       <c r="E1360" t="n">
-        <v>81.88</v>
+        <v>81.73</v>
       </c>
       <c r="F1360" t="n">
-        <v>81262</v>
+        <v>81864</v>
       </c>
     </row>
     <row r="1361">
@@ -27641,10 +27641,10 @@
         <v>80.69</v>
       </c>
       <c r="E1361" t="n">
-        <v>81.22</v>
+        <v>81.09</v>
       </c>
       <c r="F1361" t="n">
-        <v>86335</v>
+        <v>87130</v>
       </c>
     </row>
     <row r="1362">
@@ -27721,10 +27721,10 @@
         <v>78.23999999999999</v>
       </c>
       <c r="E1365" t="n">
-        <v>79.73</v>
+        <v>79.69</v>
       </c>
       <c r="F1365" t="n">
-        <v>72035</v>
+        <v>72677</v>
       </c>
     </row>
     <row r="1366">
@@ -27741,10 +27741,10 @@
         <v>79.18000000000001</v>
       </c>
       <c r="E1366" t="n">
-        <v>79.27</v>
+        <v>79.23999999999999</v>
       </c>
       <c r="F1366" t="n">
-        <v>76576</v>
+        <v>77440</v>
       </c>
     </row>
     <row r="1367">
@@ -27821,10 +27821,10 @@
         <v>81.53</v>
       </c>
       <c r="E1370" t="n">
-        <v>81.98</v>
+        <v>81.68000000000001</v>
       </c>
       <c r="F1370" t="n">
-        <v>78296</v>
+        <v>79567</v>
       </c>
     </row>
     <row r="1371">
@@ -27841,10 +27841,10 @@
         <v>81.64</v>
       </c>
       <c r="E1371" t="n">
-        <v>82.2</v>
+        <v>82.06</v>
       </c>
       <c r="F1371" t="n">
-        <v>75030</v>
+        <v>75768</v>
       </c>
     </row>
     <row r="1372">
@@ -27921,10 +27921,10 @@
         <v>84.28</v>
       </c>
       <c r="E1375" t="n">
-        <v>85.01000000000001</v>
+        <v>84.7</v>
       </c>
       <c r="F1375" t="n">
-        <v>59448</v>
+        <v>59846</v>
       </c>
     </row>
     <row r="1376">
@@ -27941,10 +27941,10 @@
         <v>84</v>
       </c>
       <c r="E1376" t="n">
-        <v>84.31</v>
+        <v>84.16</v>
       </c>
       <c r="F1376" t="n">
-        <v>59797</v>
+        <v>60278</v>
       </c>
     </row>
     <row r="1377">
@@ -28021,10 +28021,10 @@
         <v>84.01000000000001</v>
       </c>
       <c r="E1380" t="n">
-        <v>85.25</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="F1380" t="n">
-        <v>64362</v>
+        <v>64909</v>
       </c>
     </row>
     <row r="1381">
@@ -28041,10 +28041,10 @@
         <v>84.39</v>
       </c>
       <c r="E1381" t="n">
-        <v>84.79000000000001</v>
+        <v>84.65000000000001</v>
       </c>
       <c r="F1381" t="n">
-        <v>69177</v>
+        <v>69862</v>
       </c>
     </row>
     <row r="1382">
@@ -28141,10 +28141,10 @@
         <v>86.17</v>
       </c>
       <c r="E1386" t="n">
-        <v>86.31999999999999</v>
+        <v>86.43000000000001</v>
       </c>
       <c r="F1386" t="n">
-        <v>67919</v>
+        <v>68965</v>
       </c>
     </row>
     <row r="1387">
@@ -28221,10 +28221,10 @@
         <v>84.16</v>
       </c>
       <c r="E1390" t="n">
-        <v>85.19</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="F1390" t="n">
-        <v>78243</v>
+        <v>78990</v>
       </c>
     </row>
     <row r="1391">
@@ -28238,13 +28238,13 @@
         <v>85.67</v>
       </c>
       <c r="D1391" t="n">
-        <v>84.40000000000001</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="E1391" t="n">
-        <v>84.5</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="F1391" t="n">
-        <v>73607</v>
+        <v>74302</v>
       </c>
     </row>
     <row r="1392">
@@ -28321,10 +28321,10 @@
         <v>83.41</v>
       </c>
       <c r="E1395" t="n">
-        <v>83.72</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="F1395" t="n">
-        <v>68620</v>
+        <v>69797</v>
       </c>
     </row>
     <row r="1396">
@@ -28338,13 +28338,13 @@
         <v>84.41</v>
       </c>
       <c r="D1396" t="n">
-        <v>81.7</v>
+        <v>81.64</v>
       </c>
       <c r="E1396" t="n">
-        <v>81.89</v>
+        <v>81.64</v>
       </c>
       <c r="F1396" t="n">
-        <v>72020</v>
+        <v>72736</v>
       </c>
     </row>
     <row r="1397">
@@ -28421,10 +28421,10 @@
         <v>79.28</v>
       </c>
       <c r="E1400" t="n">
-        <v>81.33</v>
+        <v>81.37</v>
       </c>
       <c r="F1400" t="n">
-        <v>69150</v>
+        <v>69789</v>
       </c>
     </row>
     <row r="1401">
@@ -28441,10 +28441,10 @@
         <v>79.39</v>
       </c>
       <c r="E1401" t="n">
-        <v>79.92</v>
+        <v>79.48999999999999</v>
       </c>
       <c r="F1401" t="n">
-        <v>64725</v>
+        <v>65748</v>
       </c>
     </row>
     <row r="1402">
@@ -28521,10 +28521,10 @@
         <v>79.3</v>
       </c>
       <c r="E1405" t="n">
-        <v>80</v>
+        <v>79.83</v>
       </c>
       <c r="F1405" t="n">
-        <v>104482</v>
+        <v>105741</v>
       </c>
     </row>
     <row r="1406">
@@ -28541,10 +28541,10 @@
         <v>76.26000000000001</v>
       </c>
       <c r="E1406" t="n">
-        <v>77.08</v>
+        <v>77.14</v>
       </c>
       <c r="F1406" t="n">
-        <v>124356</v>
+        <v>125792</v>
       </c>
     </row>
     <row r="1407">
@@ -28621,10 +28621,10 @@
         <v>77.33</v>
       </c>
       <c r="E1410" t="n">
-        <v>78.73999999999999</v>
+        <v>78.59</v>
       </c>
       <c r="F1410" t="n">
-        <v>113028</v>
+        <v>113892</v>
       </c>
     </row>
     <row r="1411">
@@ -28641,10 +28641,10 @@
         <v>78.43000000000001</v>
       </c>
       <c r="E1411" t="n">
-        <v>79.34</v>
+        <v>79.27</v>
       </c>
       <c r="F1411" t="n">
-        <v>86405</v>
+        <v>87467</v>
       </c>
     </row>
     <row r="1412">
@@ -28721,10 +28721,10 @@
         <v>79.11</v>
       </c>
       <c r="E1415" t="n">
-        <v>80.31999999999999</v>
+        <v>80.26000000000001</v>
       </c>
       <c r="F1415" t="n">
-        <v>78757</v>
+        <v>79567</v>
       </c>
     </row>
     <row r="1416">
@@ -28741,10 +28741,10 @@
         <v>78.09</v>
       </c>
       <c r="E1416" t="n">
-        <v>79.22</v>
+        <v>78.94</v>
       </c>
       <c r="F1416" t="n">
-        <v>81009</v>
+        <v>82030</v>
       </c>
     </row>
     <row r="1417">
@@ -28821,10 +28821,10 @@
         <v>75.25</v>
       </c>
       <c r="E1420" t="n">
-        <v>76.47</v>
+        <v>76.42</v>
       </c>
       <c r="F1420" t="n">
-        <v>79280</v>
+        <v>79873</v>
       </c>
     </row>
     <row r="1421">
@@ -28841,10 +28841,10 @@
         <v>76.40000000000001</v>
       </c>
       <c r="E1421" t="n">
-        <v>78.17</v>
+        <v>78.13</v>
       </c>
       <c r="F1421" t="n">
-        <v>68613</v>
+        <v>69081</v>
       </c>
     </row>
     <row r="1422">
@@ -28921,10 +28921,10 @@
         <v>76.90000000000001</v>
       </c>
       <c r="E1425" t="n">
-        <v>78.81</v>
+        <v>78.72</v>
       </c>
       <c r="F1425" t="n">
-        <v>93699</v>
+        <v>94397</v>
       </c>
     </row>
     <row r="1426">
@@ -28941,10 +28941,10 @@
         <v>76.56</v>
       </c>
       <c r="E1426" t="n">
-        <v>76.81</v>
+        <v>76.77</v>
       </c>
       <c r="F1426" t="n">
-        <v>108329</v>
+        <v>109124</v>
       </c>
     </row>
     <row r="1427">
@@ -29021,10 +29021,10 @@
         <v>72.20999999999999</v>
       </c>
       <c r="E1430" t="n">
-        <v>72.54000000000001</v>
+        <v>72.53</v>
       </c>
       <c r="F1430" t="n">
-        <v>108713</v>
+        <v>109541</v>
       </c>
     </row>
     <row r="1431">
@@ -29041,10 +29041,10 @@
         <v>70.45</v>
       </c>
       <c r="E1431" t="n">
-        <v>71.37</v>
+        <v>71.2</v>
       </c>
       <c r="F1431" t="n">
-        <v>115759</v>
+        <v>116954</v>
       </c>
     </row>
     <row r="1432">
@@ -29121,10 +29121,10 @@
         <v>70.31999999999999</v>
       </c>
       <c r="E1435" t="n">
-        <v>71.89</v>
+        <v>71.67</v>
       </c>
       <c r="F1435" t="n">
-        <v>114181</v>
+        <v>115156</v>
       </c>
     </row>
     <row r="1436">
@@ -29141,10 +29141,10 @@
         <v>71.09</v>
       </c>
       <c r="E1436" t="n">
-        <v>71.73</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="F1436" t="n">
-        <v>98569</v>
+        <v>99629</v>
       </c>
     </row>
     <row r="1437">
@@ -29221,10 +29221,10 @@
         <v>72.26000000000001</v>
       </c>
       <c r="E1440" t="n">
-        <v>74.05</v>
+        <v>73.97</v>
       </c>
       <c r="F1440" t="n">
-        <v>88395</v>
+        <v>89094</v>
       </c>
     </row>
     <row r="1441">
@@ -29241,10 +29241,10 @@
         <v>73.28</v>
       </c>
       <c r="E1441" t="n">
-        <v>73.98</v>
+        <v>73.87</v>
       </c>
       <c r="F1441" t="n">
-        <v>71635</v>
+        <v>72413</v>
       </c>
     </row>
     <row r="1442">
@@ -29321,10 +29321,10 @@
         <v>70.20999999999999</v>
       </c>
       <c r="E1445" t="n">
-        <v>70.66</v>
+        <v>70.68000000000001</v>
       </c>
       <c r="F1445" t="n">
-        <v>154979</v>
+        <v>155899</v>
       </c>
     </row>
     <row r="1446">
@@ -29335,16 +29335,16 @@
         <v>70.68000000000001</v>
       </c>
       <c r="C1446" t="n">
-        <v>71.89</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="D1446" t="n">
         <v>70.39</v>
       </c>
       <c r="E1446" t="n">
-        <v>71.81999999999999</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="F1446" t="n">
-        <v>122438</v>
+        <v>123787</v>
       </c>
     </row>
     <row r="1447">
@@ -29421,10 +29421,10 @@
         <v>74.18000000000001</v>
       </c>
       <c r="E1450" t="n">
-        <v>77.58</v>
+        <v>77.28</v>
       </c>
       <c r="F1450" t="n">
-        <v>123449</v>
+        <v>125075</v>
       </c>
     </row>
     <row r="1451">
@@ -29441,10 +29441,10 @@
         <v>77.19</v>
       </c>
       <c r="E1451" t="n">
-        <v>77.87</v>
+        <v>77.73</v>
       </c>
       <c r="F1451" t="n">
-        <v>120535</v>
+        <v>121412</v>
       </c>
     </row>
     <row r="1452">
@@ -38775,16 +38775,16 @@
         <v>82.93000000000001</v>
       </c>
       <c r="C1918" t="n">
-        <v>86.90000000000001</v>
+        <v>88.22</v>
       </c>
       <c r="D1918" t="n">
         <v>82.93000000000001</v>
       </c>
       <c r="E1918" t="n">
-        <v>85.04000000000001</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="F1918" t="n">
-        <v>32841</v>
+        <v>82895</v>
       </c>
     </row>
   </sheetData>

--- a/database/BRENT.xlsx
+++ b/database/BRENT.xlsx
@@ -3881,10 +3881,10 @@
         <v>60.96</v>
       </c>
       <c r="E173" t="n">
-        <v>61.65</v>
+        <v>61.74</v>
       </c>
       <c r="F173" t="n">
-        <v>7745</v>
+        <v>7439</v>
       </c>
     </row>
     <row r="174">
@@ -3952,7 +3952,7 @@
         <v>43769</v>
       </c>
       <c r="B177" t="n">
-        <v>60.27</v>
+        <v>60.17</v>
       </c>
       <c r="C177" t="n">
         <v>60.79</v>
@@ -3964,7 +3964,7 @@
         <v>59.46</v>
       </c>
       <c r="F177" t="n">
-        <v>20603</v>
+        <v>20831</v>
       </c>
     </row>
     <row r="178">
@@ -3972,7 +3972,7 @@
         <v>43770</v>
       </c>
       <c r="B178" t="n">
-        <v>59.64</v>
+        <v>59.42</v>
       </c>
       <c r="C178" t="n">
         <v>61.8</v>
@@ -3984,7 +3984,7 @@
         <v>61.65</v>
       </c>
       <c r="F178" t="n">
-        <v>18281</v>
+        <v>18539</v>
       </c>
     </row>
     <row r="179">
@@ -4061,10 +4061,10 @@
         <v>61.63</v>
       </c>
       <c r="E182" t="n">
-        <v>62.29</v>
+        <v>62.14</v>
       </c>
       <c r="F182" t="n">
-        <v>19680</v>
+        <v>19306</v>
       </c>
     </row>
     <row r="183">
@@ -4081,10 +4081,10 @@
         <v>60.65</v>
       </c>
       <c r="E183" t="n">
-        <v>62.64</v>
+        <v>62.61</v>
       </c>
       <c r="F183" t="n">
-        <v>21863</v>
+        <v>21625</v>
       </c>
     </row>
     <row r="184">
@@ -4161,10 +4161,10 @@
         <v>62.14</v>
       </c>
       <c r="E187" t="n">
-        <v>62.33</v>
+        <v>62.38</v>
       </c>
       <c r="F187" t="n">
-        <v>19293</v>
+        <v>19157</v>
       </c>
     </row>
     <row r="188">
@@ -4181,10 +4181,10 @@
         <v>61.69</v>
       </c>
       <c r="E188" t="n">
-        <v>63.41</v>
+        <v>63.32</v>
       </c>
       <c r="F188" t="n">
-        <v>16092</v>
+        <v>15801</v>
       </c>
     </row>
     <row r="189">
@@ -4261,10 +4261,10 @@
         <v>61.91</v>
       </c>
       <c r="E192" t="n">
-        <v>63.64</v>
+        <v>63.74</v>
       </c>
       <c r="F192" t="n">
-        <v>21823</v>
+        <v>21582</v>
       </c>
     </row>
     <row r="193">
@@ -4281,10 +4281,10 @@
         <v>61.92</v>
       </c>
       <c r="E193" t="n">
-        <v>62.52</v>
+        <v>62.58</v>
       </c>
       <c r="F193" t="n">
-        <v>17794</v>
+        <v>17577</v>
       </c>
     </row>
     <row r="194">
@@ -4461,10 +4461,10 @@
         <v>62.73</v>
       </c>
       <c r="E202" t="n">
-        <v>63.26</v>
+        <v>63.33</v>
       </c>
       <c r="F202" t="n">
-        <v>24300</v>
+        <v>24042</v>
       </c>
     </row>
     <row r="203">
@@ -4481,10 +4481,10 @@
         <v>62.82</v>
       </c>
       <c r="E203" t="n">
-        <v>64.34</v>
+        <v>64.22</v>
       </c>
       <c r="F203" t="n">
-        <v>22572</v>
+        <v>22359</v>
       </c>
     </row>
     <row r="204">
@@ -4561,10 +4561,10 @@
         <v>63.86</v>
       </c>
       <c r="E207" t="n">
-        <v>64.28</v>
+        <v>64.31</v>
       </c>
       <c r="F207" t="n">
-        <v>18454</v>
+        <v>18198</v>
       </c>
     </row>
     <row r="208">
@@ -4581,10 +4581,10 @@
         <v>64.48</v>
       </c>
       <c r="E208" t="n">
-        <v>64.90000000000001</v>
+        <v>64.88</v>
       </c>
       <c r="F208" t="n">
-        <v>21671</v>
+        <v>21484</v>
       </c>
     </row>
     <row r="209">
@@ -4661,10 +4661,10 @@
         <v>66.02</v>
       </c>
       <c r="E212" t="n">
-        <v>66.53</v>
+        <v>66.45</v>
       </c>
       <c r="F212" t="n">
-        <v>11180</v>
+        <v>10932</v>
       </c>
     </row>
     <row r="213">
@@ -4681,10 +4681,10 @@
         <v>65.72</v>
       </c>
       <c r="E213" t="n">
-        <v>66.01000000000001</v>
+        <v>65.98</v>
       </c>
       <c r="F213" t="n">
-        <v>14806</v>
+        <v>14693</v>
       </c>
     </row>
     <row r="214">
@@ -4741,10 +4741,10 @@
         <v>66.09</v>
       </c>
       <c r="E216" t="n">
-        <v>66.75</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="F216" t="n">
-        <v>9613</v>
+        <v>9409</v>
       </c>
     </row>
     <row r="217">
@@ -4761,10 +4761,10 @@
         <v>66.34</v>
       </c>
       <c r="E217" t="n">
-        <v>66.84</v>
+        <v>66.81</v>
       </c>
       <c r="F217" t="n">
-        <v>11398</v>
+        <v>11272</v>
       </c>
     </row>
     <row r="218">
@@ -4821,10 +4821,10 @@
         <v>65.7</v>
       </c>
       <c r="E220" t="n">
-        <v>66.23</v>
+        <v>66.19</v>
       </c>
       <c r="F220" t="n">
-        <v>15351</v>
+        <v>15153</v>
       </c>
     </row>
     <row r="221">
@@ -4841,10 +4841,10 @@
         <v>66.19</v>
       </c>
       <c r="E221" t="n">
-        <v>68.59</v>
+        <v>68.55</v>
       </c>
       <c r="F221" t="n">
-        <v>35609</v>
+        <v>35427</v>
       </c>
     </row>
     <row r="222">
@@ -4924,7 +4924,7 @@
         <v>65.38</v>
       </c>
       <c r="F225" t="n">
-        <v>25951</v>
+        <v>25682</v>
       </c>
     </row>
     <row r="226">
@@ -4944,7 +4944,7 @@
         <v>65</v>
       </c>
       <c r="F226" t="n">
-        <v>20436</v>
+        <v>20016</v>
       </c>
     </row>
     <row r="227">
@@ -5021,10 +5021,10 @@
         <v>63.89</v>
       </c>
       <c r="E230" t="n">
-        <v>64.7</v>
+        <v>64.64</v>
       </c>
       <c r="F230" t="n">
-        <v>16472</v>
+        <v>16107</v>
       </c>
     </row>
     <row r="231">
@@ -5041,10 +5041,10 @@
         <v>64.45</v>
       </c>
       <c r="E231" t="n">
-        <v>65.08</v>
+        <v>64.95</v>
       </c>
       <c r="F231" t="n">
-        <v>16251</v>
+        <v>16060</v>
       </c>
     </row>
     <row r="232">
@@ -5121,10 +5121,10 @@
         <v>61.24</v>
       </c>
       <c r="E235" t="n">
-        <v>62.11</v>
+        <v>61.97</v>
       </c>
       <c r="F235" t="n">
-        <v>23208</v>
+        <v>22982</v>
       </c>
     </row>
     <row r="236">
@@ -5141,10 +5141,10 @@
         <v>60.24</v>
       </c>
       <c r="E236" t="n">
-        <v>60.64</v>
+        <v>60.82</v>
       </c>
       <c r="F236" t="n">
-        <v>21687</v>
+        <v>21411</v>
       </c>
     </row>
     <row r="237">
@@ -5221,10 +5221,10 @@
         <v>56.73</v>
       </c>
       <c r="E240" t="n">
-        <v>58.2</v>
+        <v>58.03</v>
       </c>
       <c r="F240" t="n">
-        <v>28894</v>
+        <v>28317</v>
       </c>
     </row>
     <row r="241">
@@ -5244,7 +5244,7 @@
         <v>56.63</v>
       </c>
       <c r="F241" t="n">
-        <v>31264</v>
+        <v>30854</v>
       </c>
     </row>
     <row r="242">
@@ -5321,10 +5321,10 @@
         <v>54.24</v>
       </c>
       <c r="E245" t="n">
-        <v>55.14</v>
+        <v>55.07</v>
       </c>
       <c r="F245" t="n">
-        <v>31917</v>
+        <v>31638</v>
       </c>
     </row>
     <row r="246">
@@ -5341,10 +5341,10 @@
         <v>54.2</v>
       </c>
       <c r="E246" t="n">
-        <v>54.45</v>
+        <v>54.48</v>
       </c>
       <c r="F246" t="n">
-        <v>26144</v>
+        <v>25828</v>
       </c>
     </row>
     <row r="247">
@@ -5421,10 +5421,10 @@
         <v>54.95</v>
       </c>
       <c r="E250" t="n">
-        <v>56.4</v>
+        <v>56.51</v>
       </c>
       <c r="F250" t="n">
-        <v>24914</v>
+        <v>24675</v>
       </c>
     </row>
     <row r="251">
@@ -5441,10 +5441,10 @@
         <v>56.13</v>
       </c>
       <c r="E251" t="n">
-        <v>57.33</v>
+        <v>57.32</v>
       </c>
       <c r="F251" t="n">
-        <v>21778</v>
+        <v>21410</v>
       </c>
     </row>
     <row r="252">
@@ -5521,10 +5521,10 @@
         <v>58.89</v>
       </c>
       <c r="E255" t="n">
-        <v>59.03</v>
+        <v>59.28</v>
       </c>
       <c r="F255" t="n">
-        <v>23391</v>
+        <v>23121</v>
       </c>
     </row>
     <row r="256">
@@ -5541,10 +5541,10 @@
         <v>57.71</v>
       </c>
       <c r="E256" t="n">
-        <v>58.44</v>
+        <v>58.33</v>
       </c>
       <c r="F256" t="n">
-        <v>26971</v>
+        <v>26663</v>
       </c>
     </row>
     <row r="257">
@@ -5621,10 +5621,10 @@
         <v>50.38</v>
       </c>
       <c r="E260" t="n">
-        <v>50.95</v>
+        <v>51.35</v>
       </c>
       <c r="F260" t="n">
-        <v>52807</v>
+        <v>51199</v>
       </c>
     </row>
     <row r="261">
@@ -5641,10 +5641,10 @@
         <v>48.92</v>
       </c>
       <c r="E261" t="n">
-        <v>50.08</v>
+        <v>50.01</v>
       </c>
       <c r="F261" t="n">
-        <v>72794</v>
+        <v>71739</v>
       </c>
     </row>
     <row r="262">
@@ -5721,10 +5721,10 @@
         <v>49.67</v>
       </c>
       <c r="E265" t="n">
-        <v>50</v>
+        <v>49.95</v>
       </c>
       <c r="F265" t="n">
-        <v>42678</v>
+        <v>42080</v>
       </c>
     </row>
     <row r="266">
@@ -5741,10 +5741,10 @@
         <v>45.16</v>
       </c>
       <c r="E266" t="n">
-        <v>45.51</v>
+        <v>45.55</v>
       </c>
       <c r="F266" t="n">
-        <v>65295</v>
+        <v>64437</v>
       </c>
     </row>
     <row r="267">
@@ -5812,7 +5812,7 @@
         <v>43902</v>
       </c>
       <c r="B270" t="n">
-        <v>36.29</v>
+        <v>35.97</v>
       </c>
       <c r="C270" t="n">
         <v>36.45</v>
@@ -5824,7 +5824,7 @@
         <v>33.49</v>
       </c>
       <c r="F270" t="n">
-        <v>64469</v>
+        <v>66181</v>
       </c>
     </row>
     <row r="271">
@@ -6121,10 +6121,10 @@
         <v>26.12</v>
       </c>
       <c r="E285" t="n">
-        <v>29.96</v>
+        <v>30.29</v>
       </c>
       <c r="F285" t="n">
-        <v>214756</v>
+        <v>210087</v>
       </c>
     </row>
     <row r="286">
@@ -6135,16 +6135,16 @@
         <v>29.95</v>
       </c>
       <c r="C286" t="n">
-        <v>35.28</v>
+        <v>35.24</v>
       </c>
       <c r="D286" t="n">
         <v>28.9</v>
       </c>
       <c r="E286" t="n">
-        <v>35.16</v>
+        <v>34.72</v>
       </c>
       <c r="F286" t="n">
-        <v>280402</v>
+        <v>275171</v>
       </c>
     </row>
     <row r="287">
@@ -6221,10 +6221,10 @@
         <v>32.46</v>
       </c>
       <c r="E290" t="n">
-        <v>32.8</v>
+        <v>33.2</v>
       </c>
       <c r="F290" t="n">
-        <v>236196</v>
+        <v>230614</v>
       </c>
     </row>
     <row r="291">
@@ -6321,10 +6321,10 @@
         <v>29.42</v>
       </c>
       <c r="E295" t="n">
-        <v>30.59</v>
+        <v>30.65</v>
       </c>
       <c r="F295" t="n">
-        <v>151526</v>
+        <v>146842</v>
       </c>
     </row>
     <row r="296">
@@ -6341,10 +6341,10 @@
         <v>30.13</v>
       </c>
       <c r="E296" t="n">
-        <v>30.68</v>
+        <v>30.78</v>
       </c>
       <c r="F296" t="n">
-        <v>174982</v>
+        <v>171223</v>
       </c>
     </row>
     <row r="297">
@@ -6421,10 +6421,10 @@
         <v>23.38</v>
       </c>
       <c r="E300" t="n">
-        <v>24.73</v>
+        <v>24.74</v>
       </c>
       <c r="F300" t="n">
-        <v>216653</v>
+        <v>213310</v>
       </c>
     </row>
     <row r="301">
@@ -6441,10 +6441,10 @@
         <v>23.7</v>
       </c>
       <c r="E301" t="n">
-        <v>24.99</v>
+        <v>24.98</v>
       </c>
       <c r="F301" t="n">
-        <v>166443</v>
+        <v>163124</v>
       </c>
     </row>
     <row r="302">
@@ -6521,10 +6521,10 @@
         <v>24.33</v>
       </c>
       <c r="E305" t="n">
-        <v>26.85</v>
+        <v>26.83</v>
       </c>
       <c r="F305" t="n">
-        <v>229615</v>
+        <v>224455</v>
       </c>
     </row>
     <row r="306">
@@ -6541,10 +6541,10 @@
         <v>26.05</v>
       </c>
       <c r="E306" t="n">
-        <v>26.81</v>
+        <v>26.78</v>
       </c>
       <c r="F306" t="n">
-        <v>199609</v>
+        <v>196748</v>
       </c>
     </row>
     <row r="307">
@@ -6621,10 +6621,10 @@
         <v>29.4</v>
       </c>
       <c r="E310" t="n">
-        <v>29.65</v>
+        <v>29.48</v>
       </c>
       <c r="F310" t="n">
-        <v>229585</v>
+        <v>225301</v>
       </c>
     </row>
     <row r="311">
@@ -6641,10 +6641,10 @@
         <v>29.63</v>
       </c>
       <c r="E311" t="n">
-        <v>31.25</v>
+        <v>31.26</v>
       </c>
       <c r="F311" t="n">
-        <v>195288</v>
+        <v>192233</v>
       </c>
     </row>
     <row r="312">
@@ -6715,16 +6715,16 @@
         <v>29.73</v>
       </c>
       <c r="C315" t="n">
-        <v>31.75</v>
+        <v>31.65</v>
       </c>
       <c r="D315" t="n">
         <v>29.32</v>
       </c>
       <c r="E315" t="n">
-        <v>31.58</v>
+        <v>31.44</v>
       </c>
       <c r="F315" t="n">
-        <v>156389</v>
+        <v>152193</v>
       </c>
     </row>
     <row r="316">
@@ -6735,16 +6735,16 @@
         <v>31.58</v>
       </c>
       <c r="C316" t="n">
-        <v>33.06</v>
+        <v>32.96</v>
       </c>
       <c r="D316" t="n">
         <v>31.23</v>
       </c>
       <c r="E316" t="n">
-        <v>32.94</v>
+        <v>32.9</v>
       </c>
       <c r="F316" t="n">
-        <v>163209</v>
+        <v>160121</v>
       </c>
     </row>
     <row r="317">
@@ -6821,10 +6821,10 @@
         <v>35.92</v>
       </c>
       <c r="E320" t="n">
-        <v>36.3</v>
+        <v>36.38</v>
       </c>
       <c r="F320" t="n">
-        <v>160329</v>
+        <v>157279</v>
       </c>
     </row>
     <row r="321">
@@ -6841,10 +6841,10 @@
         <v>33.87</v>
       </c>
       <c r="E321" t="n">
-        <v>35.52</v>
+        <v>35.66</v>
       </c>
       <c r="F321" t="n">
-        <v>198023</v>
+        <v>194062</v>
       </c>
     </row>
     <row r="322">
@@ -6921,10 +6921,10 @@
         <v>34.37</v>
       </c>
       <c r="E325" t="n">
-        <v>35.98</v>
+        <v>35.89</v>
       </c>
       <c r="F325" t="n">
-        <v>213086</v>
+        <v>208524</v>
       </c>
     </row>
     <row r="326">
@@ -6941,10 +6941,10 @@
         <v>34.87</v>
       </c>
       <c r="E326" t="n">
-        <v>37.61</v>
+        <v>37.43</v>
       </c>
       <c r="F326" t="n">
-        <v>198370</v>
+        <v>193664</v>
       </c>
     </row>
     <row r="327">
@@ -7021,10 +7021,10 @@
         <v>39.05</v>
       </c>
       <c r="E330" t="n">
-        <v>39.92</v>
+        <v>39.78</v>
       </c>
       <c r="F330" t="n">
-        <v>161661</v>
+        <v>158433</v>
       </c>
     </row>
     <row r="331">
@@ -7041,10 +7041,10 @@
         <v>39.75</v>
       </c>
       <c r="E331" t="n">
-        <v>41.83</v>
+        <v>42.14</v>
       </c>
       <c r="F331" t="n">
-        <v>167359</v>
+        <v>163467</v>
       </c>
     </row>
     <row r="332">
@@ -7121,10 +7121,10 @@
         <v>37.96</v>
       </c>
       <c r="E335" t="n">
-        <v>38.41</v>
+        <v>38.36</v>
       </c>
       <c r="F335" t="n">
-        <v>227925</v>
+        <v>221502</v>
       </c>
     </row>
     <row r="336">
@@ -7141,10 +7141,10 @@
         <v>37.14</v>
       </c>
       <c r="E336" t="n">
-        <v>38.97</v>
+        <v>38.94</v>
       </c>
       <c r="F336" t="n">
-        <v>263342</v>
+        <v>260674</v>
       </c>
     </row>
     <row r="337">
@@ -7221,10 +7221,10 @@
         <v>40.05</v>
       </c>
       <c r="E340" t="n">
-        <v>41.33</v>
+        <v>41.37</v>
       </c>
       <c r="F340" t="n">
-        <v>163774</v>
+        <v>161532</v>
       </c>
     </row>
     <row r="341">
@@ -7241,10 +7241,10 @@
         <v>40.97</v>
       </c>
       <c r="E341" t="n">
-        <v>41.78</v>
+        <v>41.99</v>
       </c>
       <c r="F341" t="n">
-        <v>156573</v>
+        <v>153177</v>
       </c>
     </row>
     <row r="342">
@@ -7315,16 +7315,16 @@
         <v>40.45</v>
       </c>
       <c r="C345" t="n">
-        <v>41.59</v>
+        <v>41.51</v>
       </c>
       <c r="D345" t="n">
         <v>39.68</v>
       </c>
       <c r="E345" t="n">
-        <v>41.35</v>
+        <v>41.39</v>
       </c>
       <c r="F345" t="n">
-        <v>181021</v>
+        <v>178413</v>
       </c>
     </row>
     <row r="346">
@@ -7341,10 +7341,10 @@
         <v>40.25</v>
       </c>
       <c r="E346" t="n">
-        <v>40.57</v>
+        <v>40.58</v>
       </c>
       <c r="F346" t="n">
-        <v>160433</v>
+        <v>157969</v>
       </c>
     </row>
     <row r="347">
@@ -7421,10 +7421,10 @@
         <v>41.71</v>
       </c>
       <c r="E350" t="n">
-        <v>42.65</v>
+        <v>42.71</v>
       </c>
       <c r="F350" t="n">
-        <v>144329</v>
+        <v>142409</v>
       </c>
     </row>
     <row r="351">
@@ -7521,10 +7521,10 @@
         <v>41.99</v>
       </c>
       <c r="E355" t="n">
-        <v>42.35</v>
+        <v>42.32</v>
       </c>
       <c r="F355" t="n">
-        <v>136451</v>
+        <v>133908</v>
       </c>
     </row>
     <row r="356">
@@ -7541,10 +7541,10 @@
         <v>41.4</v>
       </c>
       <c r="E356" t="n">
-        <v>43.26</v>
+        <v>43.23</v>
       </c>
       <c r="F356" t="n">
-        <v>154800</v>
+        <v>152491</v>
       </c>
     </row>
     <row r="357">
@@ -7621,10 +7621,10 @@
         <v>43.19</v>
       </c>
       <c r="E360" t="n">
-        <v>43.28</v>
+        <v>43.36</v>
       </c>
       <c r="F360" t="n">
-        <v>101544</v>
+        <v>99613</v>
       </c>
     </row>
     <row r="361">
@@ -7641,10 +7641,10 @@
         <v>42.7</v>
       </c>
       <c r="E361" t="n">
-        <v>43.12</v>
+        <v>43.18</v>
       </c>
       <c r="F361" t="n">
-        <v>95049</v>
+        <v>93740</v>
       </c>
     </row>
     <row r="362">
@@ -7721,10 +7721,10 @@
         <v>43.42</v>
       </c>
       <c r="E365" t="n">
-        <v>43.53</v>
+        <v>43.82</v>
       </c>
       <c r="F365" t="n">
-        <v>112495</v>
+        <v>109900</v>
       </c>
     </row>
     <row r="366">
@@ -7741,10 +7741,10 @@
         <v>43.18</v>
       </c>
       <c r="E366" t="n">
-        <v>43.62</v>
+        <v>43.67</v>
       </c>
       <c r="F366" t="n">
-        <v>117377</v>
+        <v>115737</v>
       </c>
     </row>
     <row r="367">
@@ -7821,10 +7821,10 @@
         <v>41.95</v>
       </c>
       <c r="E370" t="n">
-        <v>43.56</v>
+        <v>43.43</v>
       </c>
       <c r="F370" t="n">
-        <v>117072</v>
+        <v>113377</v>
       </c>
     </row>
     <row r="371">
@@ -7841,10 +7841,10 @@
         <v>42.94</v>
       </c>
       <c r="E371" t="n">
-        <v>43.59</v>
+        <v>43.65</v>
       </c>
       <c r="F371" t="n">
-        <v>128800</v>
+        <v>127155</v>
       </c>
     </row>
     <row r="372">
@@ -7921,10 +7921,10 @@
         <v>44.96</v>
       </c>
       <c r="E375" t="n">
-        <v>45.13</v>
+        <v>45.28</v>
       </c>
       <c r="F375" t="n">
-        <v>122044</v>
+        <v>120720</v>
       </c>
     </row>
     <row r="376">
@@ -7941,10 +7941,10 @@
         <v>44.4</v>
       </c>
       <c r="E376" t="n">
-        <v>44.71</v>
+        <v>44.76</v>
       </c>
       <c r="F376" t="n">
-        <v>120731</v>
+        <v>119541</v>
       </c>
     </row>
     <row r="377">
@@ -8021,10 +8021,10 @@
         <v>45.07</v>
       </c>
       <c r="E380" t="n">
-        <v>45.24</v>
+        <v>45.3</v>
       </c>
       <c r="F380" t="n">
-        <v>91702</v>
+        <v>90204</v>
       </c>
     </row>
     <row r="381">
@@ -8041,10 +8041,10 @@
         <v>44.77</v>
       </c>
       <c r="E381" t="n">
-        <v>45.19</v>
+        <v>45.2</v>
       </c>
       <c r="F381" t="n">
-        <v>85013</v>
+        <v>83793</v>
       </c>
     </row>
     <row r="382">
@@ -8121,10 +8121,10 @@
         <v>44.46</v>
       </c>
       <c r="E385" t="n">
-        <v>45.27</v>
+        <v>45.36</v>
       </c>
       <c r="F385" t="n">
-        <v>87294</v>
+        <v>86301</v>
       </c>
     </row>
     <row r="386">
@@ -8141,10 +8141,10 @@
         <v>44.09</v>
       </c>
       <c r="E386" t="n">
-        <v>44.69</v>
+        <v>44.79</v>
       </c>
       <c r="F386" t="n">
-        <v>78965</v>
+        <v>77659</v>
       </c>
     </row>
     <row r="387">
@@ -8224,7 +8224,7 @@
         <v>45.59</v>
       </c>
       <c r="F390" t="n">
-        <v>96916</v>
+        <v>95873</v>
       </c>
     </row>
     <row r="391">
@@ -8241,10 +8241,10 @@
         <v>45.36</v>
       </c>
       <c r="E391" t="n">
-        <v>45.85</v>
+        <v>45.89</v>
       </c>
       <c r="F391" t="n">
-        <v>81841</v>
+        <v>81058</v>
       </c>
     </row>
     <row r="392">
@@ -8321,10 +8321,10 @@
         <v>43.27</v>
       </c>
       <c r="E395" t="n">
-        <v>44.07</v>
+        <v>44.09</v>
       </c>
       <c r="F395" t="n">
-        <v>158723</v>
+        <v>157249</v>
       </c>
     </row>
     <row r="396">
@@ -8338,13 +8338,13 @@
         <v>44.69</v>
       </c>
       <c r="D396" t="n">
-        <v>42.42</v>
+        <v>42.45</v>
       </c>
       <c r="E396" t="n">
-        <v>42.43</v>
+        <v>42.53</v>
       </c>
       <c r="F396" t="n">
-        <v>162787</v>
+        <v>160902</v>
       </c>
     </row>
     <row r="397">
@@ -8418,13 +8418,13 @@
         <v>41.23</v>
       </c>
       <c r="D400" t="n">
-        <v>39.96</v>
+        <v>40.02</v>
       </c>
       <c r="E400" t="n">
-        <v>39.97</v>
+        <v>40.07</v>
       </c>
       <c r="F400" t="n">
-        <v>149451</v>
+        <v>147551</v>
       </c>
     </row>
     <row r="401">
@@ -8441,10 +8441,10 @@
         <v>39.68</v>
       </c>
       <c r="E401" t="n">
-        <v>40.02</v>
+        <v>40.24</v>
       </c>
       <c r="F401" t="n">
-        <v>135456</v>
+        <v>133943</v>
       </c>
     </row>
     <row r="402">
@@ -8521,10 +8521,10 @@
         <v>41.89</v>
       </c>
       <c r="E405" t="n">
-        <v>43.58</v>
+        <v>43.67</v>
       </c>
       <c r="F405" t="n">
-        <v>142611</v>
+        <v>141089</v>
       </c>
     </row>
     <row r="406">
@@ -8541,10 +8541,10 @@
         <v>42.92</v>
       </c>
       <c r="E406" t="n">
-        <v>43.41</v>
+        <v>43.34</v>
       </c>
       <c r="F406" t="n">
-        <v>129546</v>
+        <v>127380</v>
       </c>
     </row>
     <row r="407">
@@ -8621,10 +8621,10 @@
         <v>41.68</v>
       </c>
       <c r="E410" t="n">
-        <v>42.16</v>
+        <v>42.27</v>
       </c>
       <c r="F410" t="n">
-        <v>133961</v>
+        <v>132502</v>
       </c>
     </row>
     <row r="411">
@@ -8641,10 +8641,10 @@
         <v>41.97</v>
       </c>
       <c r="E411" t="n">
-        <v>42.17</v>
+        <v>42.24</v>
       </c>
       <c r="F411" t="n">
-        <v>102107</v>
+        <v>100264</v>
       </c>
     </row>
     <row r="412">
@@ -8721,10 +8721,10 @@
         <v>39.98</v>
       </c>
       <c r="E415" t="n">
-        <v>40.75</v>
+        <v>40.93</v>
       </c>
       <c r="F415" t="n">
-        <v>157712</v>
+        <v>155461</v>
       </c>
     </row>
     <row r="416">
@@ -8741,10 +8741,10 @@
         <v>38.88</v>
       </c>
       <c r="E416" t="n">
-        <v>39.15</v>
+        <v>39.23</v>
       </c>
       <c r="F416" t="n">
-        <v>190634</v>
+        <v>188336</v>
       </c>
     </row>
     <row r="417">
@@ -8821,10 +8821,10 @@
         <v>42.02</v>
       </c>
       <c r="E420" t="n">
-        <v>43.52</v>
+        <v>43.54</v>
       </c>
       <c r="F420" t="n">
-        <v>112342</v>
+        <v>110782</v>
       </c>
     </row>
     <row r="421">
@@ -8841,10 +8841,10 @@
         <v>42.78</v>
       </c>
       <c r="E421" t="n">
-        <v>42.89</v>
+        <v>42.96</v>
       </c>
       <c r="F421" t="n">
-        <v>109695</v>
+        <v>108274</v>
       </c>
     </row>
     <row r="422">
@@ -8921,10 +8921,10 @@
         <v>41.79</v>
       </c>
       <c r="E425" t="n">
-        <v>43.26</v>
+        <v>43.38</v>
       </c>
       <c r="F425" t="n">
-        <v>147757</v>
+        <v>146298</v>
       </c>
     </row>
     <row r="426">
@@ -8941,10 +8941,10 @@
         <v>42.47</v>
       </c>
       <c r="E426" t="n">
-        <v>42.95</v>
+        <v>43.02</v>
       </c>
       <c r="F426" t="n">
-        <v>130839</v>
+        <v>129338</v>
       </c>
     </row>
     <row r="427">
@@ -9021,10 +9021,10 @@
         <v>41.72</v>
       </c>
       <c r="E430" t="n">
-        <v>42.59</v>
+        <v>42.71</v>
       </c>
       <c r="F430" t="n">
-        <v>110171</v>
+        <v>108471</v>
       </c>
     </row>
     <row r="431">
@@ -9041,10 +9041,10 @@
         <v>41.76</v>
       </c>
       <c r="E431" t="n">
-        <v>41.85</v>
+        <v>41.93</v>
       </c>
       <c r="F431" t="n">
-        <v>97195</v>
+        <v>95688</v>
       </c>
     </row>
     <row r="432">
@@ -9112,7 +9112,7 @@
         <v>44133</v>
       </c>
       <c r="B435" t="n">
-        <v>39.76</v>
+        <v>39.52</v>
       </c>
       <c r="C435" t="n">
         <v>39.97</v>
@@ -9124,7 +9124,7 @@
         <v>38.05</v>
       </c>
       <c r="F435" t="n">
-        <v>179602</v>
+        <v>183949</v>
       </c>
     </row>
     <row r="436">
@@ -9132,7 +9132,7 @@
         <v>44134</v>
       </c>
       <c r="B436" t="n">
-        <v>38.25</v>
+        <v>38.05</v>
       </c>
       <c r="C436" t="n">
         <v>38.72</v>
@@ -9144,7 +9144,7 @@
         <v>37.84</v>
       </c>
       <c r="F436" t="n">
-        <v>181739</v>
+        <v>184633</v>
       </c>
     </row>
     <row r="437">
@@ -9221,10 +9221,10 @@
         <v>40.42</v>
       </c>
       <c r="E440" t="n">
-        <v>40.68</v>
+        <v>40.82</v>
       </c>
       <c r="F440" t="n">
-        <v>157779</v>
+        <v>155706</v>
       </c>
     </row>
     <row r="441">
@@ -9241,10 +9241,10 @@
         <v>39.46</v>
       </c>
       <c r="E441" t="n">
-        <v>39.71</v>
+        <v>39.84</v>
       </c>
       <c r="F441" t="n">
-        <v>151438</v>
+        <v>150078</v>
       </c>
     </row>
     <row r="442">
@@ -9318,13 +9318,13 @@
         <v>44.59</v>
       </c>
       <c r="D445" t="n">
-        <v>43.35</v>
+        <v>43.42</v>
       </c>
       <c r="E445" t="n">
-        <v>43.38</v>
+        <v>43.49</v>
       </c>
       <c r="F445" t="n">
-        <v>146964</v>
+        <v>144322</v>
       </c>
     </row>
     <row r="446">
@@ -9338,13 +9338,13 @@
         <v>43.45</v>
       </c>
       <c r="D446" t="n">
-        <v>42.68</v>
+        <v>42.77</v>
       </c>
       <c r="E446" t="n">
-        <v>42.69</v>
+        <v>42.88</v>
       </c>
       <c r="F446" t="n">
-        <v>114191</v>
+        <v>112789</v>
       </c>
     </row>
     <row r="447">
@@ -9421,10 +9421,10 @@
         <v>43.87</v>
       </c>
       <c r="E450" t="n">
-        <v>44.21</v>
+        <v>44.44</v>
       </c>
       <c r="F450" t="n">
-        <v>112468</v>
+        <v>111013</v>
       </c>
     </row>
     <row r="451">
@@ -9441,10 +9441,10 @@
         <v>44.15</v>
       </c>
       <c r="E451" t="n">
-        <v>45.07</v>
+        <v>45.06</v>
       </c>
       <c r="F451" t="n">
-        <v>90427</v>
+        <v>88612</v>
       </c>
     </row>
     <row r="452">
@@ -9624,7 +9624,7 @@
         <v>48.65</v>
       </c>
       <c r="F460" t="n">
-        <v>122403</v>
+        <v>119976</v>
       </c>
     </row>
     <row r="461">
@@ -9641,10 +9641,10 @@
         <v>48.77</v>
       </c>
       <c r="E461" t="n">
-        <v>48.96</v>
+        <v>48.97</v>
       </c>
       <c r="F461" t="n">
-        <v>125701</v>
+        <v>124413</v>
       </c>
     </row>
     <row r="462">
@@ -9721,10 +9721,10 @@
         <v>48.79</v>
       </c>
       <c r="E465" t="n">
-        <v>50.25</v>
+        <v>50.26</v>
       </c>
       <c r="F465" t="n">
-        <v>132386</v>
+        <v>130125</v>
       </c>
     </row>
     <row r="466">
@@ -9741,10 +9741,10 @@
         <v>49.67</v>
       </c>
       <c r="E466" t="n">
-        <v>49.86</v>
+        <v>49.94</v>
       </c>
       <c r="F466" t="n">
-        <v>124721</v>
+        <v>123293</v>
       </c>
     </row>
     <row r="467">
@@ -9821,10 +9821,10 @@
         <v>51.06</v>
       </c>
       <c r="E470" t="n">
-        <v>51.46</v>
+        <v>51.55</v>
       </c>
       <c r="F470" t="n">
-        <v>102867</v>
+        <v>100894</v>
       </c>
     </row>
     <row r="471">
@@ -9841,10 +9841,10 @@
         <v>51.16</v>
       </c>
       <c r="E471" t="n">
-        <v>52.23</v>
+        <v>52.19</v>
       </c>
       <c r="F471" t="n">
-        <v>98705</v>
+        <v>96861</v>
       </c>
     </row>
     <row r="472">
@@ -10081,10 +10081,10 @@
         <v>53.88</v>
       </c>
       <c r="E483" t="n">
-        <v>54.34</v>
+        <v>54.45</v>
       </c>
       <c r="F483" t="n">
-        <v>142258</v>
+        <v>140683</v>
       </c>
     </row>
     <row r="484">
@@ -10095,16 +10095,16 @@
         <v>54.46</v>
       </c>
       <c r="C484" t="n">
-        <v>56.2</v>
+        <v>56.06</v>
       </c>
       <c r="D484" t="n">
         <v>54.3</v>
       </c>
       <c r="E484" t="n">
-        <v>56.11</v>
+        <v>56.02</v>
       </c>
       <c r="F484" t="n">
-        <v>155413</v>
+        <v>151805</v>
       </c>
     </row>
     <row r="485">
@@ -10181,10 +10181,10 @@
         <v>55.21</v>
       </c>
       <c r="E488" t="n">
-        <v>56.37</v>
+        <v>56.3</v>
       </c>
       <c r="F488" t="n">
-        <v>125098</v>
+        <v>123090</v>
       </c>
     </row>
     <row r="489">
@@ -10201,10 +10201,10 @@
         <v>54.63</v>
       </c>
       <c r="E489" t="n">
-        <v>54.75</v>
+        <v>54.94</v>
       </c>
       <c r="F489" t="n">
-        <v>135898</v>
+        <v>133988</v>
       </c>
     </row>
     <row r="490">
@@ -10281,10 +10281,10 @@
         <v>55.38</v>
       </c>
       <c r="E493" t="n">
-        <v>55.84</v>
+        <v>55.86</v>
       </c>
       <c r="F493" t="n">
-        <v>104851</v>
+        <v>103188</v>
       </c>
     </row>
     <row r="494">
@@ -10301,10 +10301,10 @@
         <v>54.38</v>
       </c>
       <c r="E494" t="n">
-        <v>54.88</v>
+        <v>55.08</v>
       </c>
       <c r="F494" t="n">
-        <v>135622</v>
+        <v>133367</v>
       </c>
     </row>
     <row r="495">
@@ -10378,13 +10378,13 @@
         <v>56.16</v>
       </c>
       <c r="D498" t="n">
-        <v>54.84</v>
+        <v>54.93</v>
       </c>
       <c r="E498" t="n">
-        <v>54.84</v>
+        <v>55</v>
       </c>
       <c r="F498" t="n">
-        <v>162289</v>
+        <v>160473</v>
       </c>
     </row>
     <row r="499">
@@ -10401,10 +10401,10 @@
         <v>54.84</v>
       </c>
       <c r="E499" t="n">
-        <v>54.93</v>
+        <v>55</v>
       </c>
       <c r="F499" t="n">
-        <v>163671</v>
+        <v>160923</v>
       </c>
     </row>
     <row r="500">
@@ -10481,10 +10481,10 @@
         <v>57.93</v>
       </c>
       <c r="E503" t="n">
-        <v>58.87</v>
+        <v>58.79</v>
       </c>
       <c r="F503" t="n">
-        <v>125851</v>
+        <v>123567</v>
       </c>
     </row>
     <row r="504">
@@ -10501,10 +10501,10 @@
         <v>58.87</v>
       </c>
       <c r="E504" t="n">
-        <v>59.41</v>
+        <v>59.31</v>
       </c>
       <c r="F504" t="n">
-        <v>120954</v>
+        <v>118436</v>
       </c>
     </row>
     <row r="505">
@@ -10578,13 +10578,13 @@
         <v>61.23</v>
       </c>
       <c r="D508" t="n">
-        <v>60.44</v>
+        <v>60.5</v>
       </c>
       <c r="E508" t="n">
-        <v>60.52</v>
+        <v>60.6</v>
       </c>
       <c r="F508" t="n">
-        <v>107974</v>
+        <v>104511</v>
       </c>
     </row>
     <row r="509">
@@ -10604,7 +10604,7 @@
         <v>62.22</v>
       </c>
       <c r="F509" t="n">
-        <v>126905</v>
+        <v>123306</v>
       </c>
     </row>
     <row r="510">
@@ -10681,10 +10681,10 @@
         <v>62.54</v>
       </c>
       <c r="E513" t="n">
-        <v>62.88</v>
+        <v>62.75</v>
       </c>
       <c r="F513" t="n">
-        <v>173632</v>
+        <v>170306</v>
       </c>
     </row>
     <row r="514">
@@ -10701,10 +10701,10 @@
         <v>61.42</v>
       </c>
       <c r="E514" t="n">
-        <v>61.97</v>
+        <v>61.95</v>
       </c>
       <c r="F514" t="n">
-        <v>184306</v>
+        <v>181146</v>
       </c>
     </row>
     <row r="515">
@@ -10781,10 +10781,10 @@
         <v>65.55</v>
       </c>
       <c r="E518" t="n">
-        <v>65.97</v>
+        <v>65.86</v>
       </c>
       <c r="F518" t="n">
-        <v>215533</v>
+        <v>210726</v>
       </c>
     </row>
     <row r="519">
@@ -10801,10 +10801,10 @@
         <v>64.13</v>
       </c>
       <c r="E519" t="n">
-        <v>64.27</v>
+        <v>64.25</v>
       </c>
       <c r="F519" t="n">
-        <v>239274</v>
+        <v>234931</v>
       </c>
     </row>
     <row r="520">
@@ -10881,10 +10881,10 @@
         <v>63.17</v>
       </c>
       <c r="E523" t="n">
-        <v>66.73999999999999</v>
+        <v>66.94</v>
       </c>
       <c r="F523" t="n">
-        <v>230530</v>
+        <v>225843</v>
       </c>
     </row>
     <row r="524">
@@ -10895,16 +10895,16 @@
         <v>66.86</v>
       </c>
       <c r="C524" t="n">
-        <v>69.41</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="D524" t="n">
         <v>66.43000000000001</v>
       </c>
       <c r="E524" t="n">
-        <v>69.25</v>
+        <v>69.28</v>
       </c>
       <c r="F524" t="n">
-        <v>253026</v>
+        <v>249828</v>
       </c>
     </row>
     <row r="525">
@@ -10981,10 +10981,10 @@
         <v>67.68000000000001</v>
       </c>
       <c r="E528" t="n">
-        <v>69.17</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="F528" t="n">
-        <v>163581</v>
+        <v>160838</v>
       </c>
     </row>
     <row r="529">
@@ -11001,10 +11001,10 @@
         <v>68.66</v>
       </c>
       <c r="E529" t="n">
-        <v>68.81</v>
+        <v>68.88</v>
       </c>
       <c r="F529" t="n">
-        <v>151042</v>
+        <v>148823</v>
       </c>
     </row>
     <row r="530">
@@ -11072,7 +11072,7 @@
         <v>44273</v>
       </c>
       <c r="B533" t="n">
-        <v>67.47</v>
+        <v>67.48</v>
       </c>
       <c r="C533" t="n">
         <v>67.83</v>
@@ -11084,7 +11084,7 @@
         <v>62.5</v>
       </c>
       <c r="F533" t="n">
-        <v>209835</v>
+        <v>212082</v>
       </c>
     </row>
     <row r="534">
@@ -11092,7 +11092,7 @@
         <v>44274</v>
       </c>
       <c r="B534" t="n">
-        <v>63.02</v>
+        <v>62.78</v>
       </c>
       <c r="C534" t="n">
         <v>64.73</v>
@@ -11104,7 +11104,7 @@
         <v>64.31999999999999</v>
       </c>
       <c r="F534" t="n">
-        <v>223529</v>
+        <v>228148</v>
       </c>
     </row>
     <row r="535">
@@ -11172,10 +11172,10 @@
         <v>44280</v>
       </c>
       <c r="B538" t="n">
-        <v>63.89</v>
+        <v>63.95</v>
       </c>
       <c r="C538" t="n">
-        <v>63.9</v>
+        <v>64.01000000000001</v>
       </c>
       <c r="D538" t="n">
         <v>60.82</v>
@@ -11184,7 +11184,7 @@
         <v>61.47</v>
       </c>
       <c r="F538" t="n">
-        <v>203253</v>
+        <v>206155</v>
       </c>
     </row>
     <row r="539">
@@ -11192,19 +11192,19 @@
         <v>44281</v>
       </c>
       <c r="B539" t="n">
-        <v>62.45</v>
+        <v>61.47</v>
       </c>
       <c r="C539" t="n">
         <v>64.73</v>
       </c>
       <c r="D539" t="n">
-        <v>62.07</v>
+        <v>61.47</v>
       </c>
       <c r="E539" t="n">
         <v>64.19</v>
       </c>
       <c r="F539" t="n">
-        <v>167422</v>
+        <v>171041</v>
       </c>
     </row>
     <row r="540">
@@ -11284,7 +11284,7 @@
         <v>64.51000000000001</v>
       </c>
       <c r="F543" t="n">
-        <v>201289</v>
+        <v>197783</v>
       </c>
     </row>
     <row r="544">
@@ -11361,10 +11361,10 @@
         <v>62.18</v>
       </c>
       <c r="E547" t="n">
-        <v>63.04</v>
+        <v>63.07</v>
       </c>
       <c r="F547" t="n">
-        <v>149186</v>
+        <v>146277</v>
       </c>
     </row>
     <row r="548">
@@ -11381,10 +11381,10 @@
         <v>62.33</v>
       </c>
       <c r="E548" t="n">
-        <v>62.76</v>
+        <v>62.81</v>
       </c>
       <c r="F548" t="n">
-        <v>121247</v>
+        <v>119219</v>
       </c>
     </row>
     <row r="549">
@@ -11461,10 +11461,10 @@
         <v>65.65000000000001</v>
       </c>
       <c r="E552" t="n">
-        <v>66.45</v>
+        <v>66.5</v>
       </c>
       <c r="F552" t="n">
-        <v>135521</v>
+        <v>133306</v>
       </c>
     </row>
     <row r="553">
@@ -11481,10 +11481,10 @@
         <v>66.11</v>
       </c>
       <c r="E553" t="n">
-        <v>66.31999999999999</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="F553" t="n">
-        <v>122938</v>
+        <v>120895</v>
       </c>
     </row>
     <row r="554">
@@ -11564,7 +11564,7 @@
         <v>64.95</v>
       </c>
       <c r="F557" t="n">
-        <v>143350</v>
+        <v>140975</v>
       </c>
     </row>
     <row r="558">
@@ -11581,10 +11581,10 @@
         <v>64.52</v>
       </c>
       <c r="E558" t="n">
-        <v>65.31999999999999</v>
+        <v>65.45</v>
       </c>
       <c r="F558" t="n">
-        <v>126302</v>
+        <v>124432</v>
       </c>
     </row>
     <row r="559">
@@ -11661,10 +11661,10 @@
         <v>66.56</v>
       </c>
       <c r="E562" t="n">
-        <v>67.84999999999999</v>
+        <v>67.86</v>
       </c>
       <c r="F562" t="n">
-        <v>160482</v>
+        <v>157092</v>
       </c>
     </row>
     <row r="563">
@@ -11681,10 +11681,10 @@
         <v>66.17</v>
       </c>
       <c r="E563" t="n">
-        <v>66.53</v>
+        <v>66.56</v>
       </c>
       <c r="F563" t="n">
-        <v>148372</v>
+        <v>145779</v>
       </c>
     </row>
     <row r="564">
@@ -11761,10 +11761,10 @@
         <v>67.77</v>
       </c>
       <c r="E567" t="n">
-        <v>68.03</v>
+        <v>68.05</v>
       </c>
       <c r="F567" t="n">
-        <v>155507</v>
+        <v>153533</v>
       </c>
     </row>
     <row r="568">
@@ -11784,7 +11784,7 @@
         <v>68.03</v>
       </c>
       <c r="F568" t="n">
-        <v>139157</v>
+        <v>136012</v>
       </c>
     </row>
     <row r="569">
@@ -11861,10 +11861,10 @@
         <v>66.34</v>
       </c>
       <c r="E572" t="n">
-        <v>66.81999999999999</v>
+        <v>66.83</v>
       </c>
       <c r="F572" t="n">
-        <v>182316</v>
+        <v>180093</v>
       </c>
     </row>
     <row r="573">
@@ -11875,16 +11875,16 @@
         <v>66.81</v>
       </c>
       <c r="C573" t="n">
-        <v>68.63</v>
+        <v>68.52</v>
       </c>
       <c r="D573" t="n">
         <v>66.36</v>
       </c>
       <c r="E573" t="n">
-        <v>68.52</v>
+        <v>68.45</v>
       </c>
       <c r="F573" t="n">
-        <v>142226</v>
+        <v>139950</v>
       </c>
     </row>
     <row r="574">
@@ -11958,13 +11958,13 @@
         <v>67.02</v>
       </c>
       <c r="D577" t="n">
-        <v>64.70999999999999</v>
+        <v>64.73</v>
       </c>
       <c r="E577" t="n">
-        <v>64.73999999999999</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="F577" t="n">
-        <v>168733</v>
+        <v>164782</v>
       </c>
     </row>
     <row r="578">
@@ -11981,10 +11981,10 @@
         <v>64.48</v>
       </c>
       <c r="E578" t="n">
-        <v>66.51000000000001</v>
+        <v>66.58</v>
       </c>
       <c r="F578" t="n">
-        <v>156317</v>
+        <v>153693</v>
       </c>
     </row>
     <row r="579">
@@ -12055,16 +12055,16 @@
         <v>68.58</v>
       </c>
       <c r="C582" t="n">
-        <v>69.2</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="D582" t="n">
         <v>67.89</v>
       </c>
       <c r="E582" t="n">
-        <v>69.12</v>
+        <v>69.05</v>
       </c>
       <c r="F582" t="n">
-        <v>122427</v>
+        <v>119490</v>
       </c>
     </row>
     <row r="583">
@@ -12081,10 +12081,10 @@
         <v>68.48999999999999</v>
       </c>
       <c r="E583" t="n">
-        <v>68.88</v>
+        <v>68.89</v>
       </c>
       <c r="F583" t="n">
-        <v>121324</v>
+        <v>119218</v>
       </c>
     </row>
     <row r="584">
@@ -12161,10 +12161,10 @@
         <v>70.5</v>
       </c>
       <c r="E587" t="n">
-        <v>71.22</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="F587" t="n">
-        <v>128649</v>
+        <v>126247</v>
       </c>
     </row>
     <row r="588">
@@ -12181,10 +12181,10 @@
         <v>70.58</v>
       </c>
       <c r="E588" t="n">
-        <v>71.43000000000001</v>
+        <v>71.47</v>
       </c>
       <c r="F588" t="n">
-        <v>117041</v>
+        <v>113793</v>
       </c>
     </row>
     <row r="589">
@@ -12261,10 +12261,10 @@
         <v>70.66</v>
       </c>
       <c r="E592" t="n">
-        <v>71.95</v>
+        <v>72.09</v>
       </c>
       <c r="F592" t="n">
-        <v>148450</v>
+        <v>146487</v>
       </c>
     </row>
     <row r="593">
@@ -12284,7 +12284,7 @@
         <v>72.23999999999999</v>
       </c>
       <c r="F593" t="n">
-        <v>142367</v>
+        <v>140128</v>
       </c>
     </row>
     <row r="594">
@@ -12361,10 +12361,10 @@
         <v>71.41</v>
       </c>
       <c r="E597" t="n">
-        <v>72.44</v>
+        <v>72.45</v>
       </c>
       <c r="F597" t="n">
-        <v>178094</v>
+        <v>175025</v>
       </c>
     </row>
     <row r="598">
@@ -12381,10 +12381,10 @@
         <v>71.55</v>
       </c>
       <c r="E598" t="n">
-        <v>72.5</v>
+        <v>72.76000000000001</v>
       </c>
       <c r="F598" t="n">
-        <v>151345</v>
+        <v>147859</v>
       </c>
     </row>
     <row r="599">
@@ -12461,10 +12461,10 @@
         <v>73.83</v>
       </c>
       <c r="E602" t="n">
-        <v>74.81</v>
+        <v>74.79000000000001</v>
       </c>
       <c r="F602" t="n">
-        <v>85692</v>
+        <v>84577</v>
       </c>
     </row>
     <row r="603">
@@ -12481,10 +12481,10 @@
         <v>74.14</v>
       </c>
       <c r="E603" t="n">
-        <v>75.28</v>
+        <v>75.27</v>
       </c>
       <c r="F603" t="n">
-        <v>79112</v>
+        <v>77990</v>
       </c>
     </row>
     <row r="604">
@@ -12561,10 +12561,10 @@
         <v>74.36</v>
       </c>
       <c r="E607" t="n">
-        <v>75.34</v>
+        <v>75.33</v>
       </c>
       <c r="F607" t="n">
-        <v>135699</v>
+        <v>134296</v>
       </c>
     </row>
     <row r="608">
@@ -12581,10 +12581,10 @@
         <v>75</v>
       </c>
       <c r="E608" t="n">
-        <v>75.81999999999999</v>
+        <v>76.02</v>
       </c>
       <c r="F608" t="n">
-        <v>104256</v>
+        <v>102316</v>
       </c>
     </row>
     <row r="609">
@@ -12655,16 +12655,16 @@
         <v>72.97</v>
       </c>
       <c r="C612" t="n">
-        <v>74.02</v>
+        <v>73.97</v>
       </c>
       <c r="D612" t="n">
         <v>71.73999999999999</v>
       </c>
       <c r="E612" t="n">
-        <v>73.95999999999999</v>
+        <v>73.92</v>
       </c>
       <c r="F612" t="n">
-        <v>138030</v>
+        <v>136419</v>
       </c>
     </row>
     <row r="613">
@@ -12681,10 +12681,10 @@
         <v>73.38</v>
       </c>
       <c r="E613" t="n">
-        <v>75.14</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="F613" t="n">
-        <v>96988</v>
+        <v>95892</v>
       </c>
     </row>
     <row r="614">
@@ -12761,10 +12761,10 @@
         <v>72.70999999999999</v>
       </c>
       <c r="E617" t="n">
-        <v>72.72</v>
+        <v>72.79000000000001</v>
       </c>
       <c r="F617" t="n">
-        <v>134216</v>
+        <v>132350</v>
       </c>
     </row>
     <row r="618">
@@ -12781,10 +12781,10 @@
         <v>71.88</v>
       </c>
       <c r="E618" t="n">
-        <v>72.64</v>
+        <v>72.81</v>
       </c>
       <c r="F618" t="n">
-        <v>110158</v>
+        <v>108307</v>
       </c>
     </row>
     <row r="619">
@@ -12864,7 +12864,7 @@
         <v>73.01000000000001</v>
       </c>
       <c r="F622" t="n">
-        <v>115159</v>
+        <v>113951</v>
       </c>
     </row>
     <row r="623">
@@ -12875,16 +12875,16 @@
         <v>72.98</v>
       </c>
       <c r="C623" t="n">
-        <v>73.56999999999999</v>
+        <v>73.52</v>
       </c>
       <c r="D623" t="n">
         <v>72.70999999999999</v>
       </c>
       <c r="E623" t="n">
-        <v>73.5</v>
+        <v>73.44</v>
       </c>
       <c r="F623" t="n">
-        <v>84579</v>
+        <v>83411</v>
       </c>
     </row>
     <row r="624">
@@ -12961,10 +12961,10 @@
         <v>73.59999999999999</v>
       </c>
       <c r="E627" t="n">
-        <v>74.75</v>
+        <v>74.97</v>
       </c>
       <c r="F627" t="n">
-        <v>81467</v>
+        <v>79720</v>
       </c>
     </row>
     <row r="628">
@@ -12981,10 +12981,10 @@
         <v>74.26000000000001</v>
       </c>
       <c r="E628" t="n">
-        <v>74.95999999999999</v>
+        <v>74.98999999999999</v>
       </c>
       <c r="F628" t="n">
-        <v>84253</v>
+        <v>83101</v>
       </c>
     </row>
     <row r="629">
@@ -13061,10 +13061,10 @@
         <v>69.56</v>
       </c>
       <c r="E632" t="n">
-        <v>71</v>
+        <v>71.16</v>
       </c>
       <c r="F632" t="n">
-        <v>108267</v>
+        <v>107034</v>
       </c>
     </row>
     <row r="633">
@@ -13078,13 +13078,13 @@
         <v>72.22</v>
       </c>
       <c r="D633" t="n">
-        <v>70.06999999999999</v>
+        <v>70.12</v>
       </c>
       <c r="E633" t="n">
-        <v>70.08</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="F633" t="n">
-        <v>113105</v>
+        <v>111453</v>
       </c>
     </row>
     <row r="634">
@@ -13161,10 +13161,10 @@
         <v>70.41</v>
       </c>
       <c r="E637" t="n">
-        <v>70.86</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="F637" t="n">
-        <v>96203</v>
+        <v>95219</v>
       </c>
     </row>
     <row r="638">
@@ -13181,10 +13181,10 @@
         <v>69.73999999999999</v>
       </c>
       <c r="E638" t="n">
-        <v>69.90000000000001</v>
+        <v>69.92</v>
       </c>
       <c r="F638" t="n">
-        <v>95696</v>
+        <v>93960</v>
       </c>
     </row>
     <row r="639">
@@ -13261,10 +13261,10 @@
         <v>65.2</v>
       </c>
       <c r="E642" t="n">
-        <v>66.23</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="F642" t="n">
-        <v>187712</v>
+        <v>185678</v>
       </c>
     </row>
     <row r="643">
@@ -13278,13 +13278,13 @@
         <v>66.54000000000001</v>
       </c>
       <c r="D643" t="n">
-        <v>64.53</v>
+        <v>64.61</v>
       </c>
       <c r="E643" t="n">
-        <v>64.54000000000001</v>
+        <v>64.62</v>
       </c>
       <c r="F643" t="n">
-        <v>138989</v>
+        <v>137258</v>
       </c>
     </row>
     <row r="644">
@@ -13361,10 +13361,10 @@
         <v>69.73999999999999</v>
       </c>
       <c r="E647" t="n">
-        <v>70.45999999999999</v>
+        <v>70.56</v>
       </c>
       <c r="F647" t="n">
-        <v>115965</v>
+        <v>113839</v>
       </c>
     </row>
     <row r="648">
@@ -13381,10 +13381,10 @@
         <v>70.16</v>
       </c>
       <c r="E648" t="n">
-        <v>71.5</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="F648" t="n">
-        <v>100455</v>
+        <v>99158</v>
       </c>
     </row>
     <row r="649">
@@ -13461,10 +13461,10 @@
         <v>70.75</v>
       </c>
       <c r="E652" t="n">
-        <v>72.61</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="F652" t="n">
-        <v>105073</v>
+        <v>103772</v>
       </c>
     </row>
     <row r="653">
@@ -13481,10 +13481,10 @@
         <v>72.20999999999999</v>
       </c>
       <c r="E653" t="n">
-        <v>72.20999999999999</v>
+        <v>72.36</v>
       </c>
       <c r="F653" t="n">
-        <v>111688</v>
+        <v>110684</v>
       </c>
     </row>
     <row r="654">
@@ -13561,10 +13561,10 @@
         <v>70.54000000000001</v>
       </c>
       <c r="E657" t="n">
-        <v>70.84</v>
+        <v>70.95</v>
       </c>
       <c r="F657" t="n">
-        <v>138553</v>
+        <v>136836</v>
       </c>
     </row>
     <row r="658">
@@ -13581,10 +13581,10 @@
         <v>70.59</v>
       </c>
       <c r="E658" t="n">
-        <v>72.51000000000001</v>
+        <v>72.44</v>
       </c>
       <c r="F658" t="n">
-        <v>107925</v>
+        <v>106315</v>
       </c>
     </row>
     <row r="659">
@@ -13661,10 +13661,10 @@
         <v>74.02</v>
       </c>
       <c r="E662" t="n">
-        <v>75.09</v>
+        <v>75.17</v>
       </c>
       <c r="F662" t="n">
-        <v>136265</v>
+        <v>134873</v>
       </c>
     </row>
     <row r="663">
@@ -13681,10 +13681,10 @@
         <v>74.06999999999999</v>
       </c>
       <c r="E663" t="n">
-        <v>74.67</v>
+        <v>74.79000000000001</v>
       </c>
       <c r="F663" t="n">
-        <v>131243</v>
+        <v>129577</v>
       </c>
     </row>
     <row r="664">
@@ -13764,7 +13764,7 @@
         <v>76.45</v>
       </c>
       <c r="F667" t="n">
-        <v>104066</v>
+        <v>102612</v>
       </c>
     </row>
     <row r="668">
@@ -13781,10 +13781,10 @@
         <v>76.09</v>
       </c>
       <c r="E668" t="n">
-        <v>77.13</v>
+        <v>77.15000000000001</v>
       </c>
       <c r="F668" t="n">
-        <v>94529</v>
+        <v>93448</v>
       </c>
     </row>
     <row r="669">
@@ -13861,10 +13861,10 @@
         <v>76.37</v>
       </c>
       <c r="E672" t="n">
-        <v>78.23999999999999</v>
+        <v>78.13</v>
       </c>
       <c r="F672" t="n">
-        <v>181989</v>
+        <v>180155</v>
       </c>
     </row>
     <row r="673">
@@ -13881,10 +13881,10 @@
         <v>77.38</v>
       </c>
       <c r="E673" t="n">
-        <v>78.93000000000001</v>
+        <v>78.98999999999999</v>
       </c>
       <c r="F673" t="n">
-        <v>151482</v>
+        <v>149729</v>
       </c>
     </row>
     <row r="674">
@@ -13961,10 +13961,10 @@
         <v>78.78</v>
       </c>
       <c r="E677" t="n">
-        <v>82.08</v>
+        <v>82.16</v>
       </c>
       <c r="F677" t="n">
-        <v>153620</v>
+        <v>151677</v>
       </c>
     </row>
     <row r="678">
@@ -13981,10 +13981,10 @@
         <v>81.63</v>
       </c>
       <c r="E678" t="n">
-        <v>82.22</v>
+        <v>82.17</v>
       </c>
       <c r="F678" t="n">
-        <v>149526</v>
+        <v>147722</v>
       </c>
     </row>
     <row r="679">
@@ -14061,10 +14061,10 @@
         <v>82.76000000000001</v>
       </c>
       <c r="E682" t="n">
-        <v>83.67</v>
+        <v>83.69</v>
       </c>
       <c r="F682" t="n">
-        <v>122153</v>
+        <v>120650</v>
       </c>
     </row>
     <row r="683">
@@ -14081,10 +14081,10 @@
         <v>83.68000000000001</v>
       </c>
       <c r="E683" t="n">
-        <v>84.33</v>
+        <v>84.23</v>
       </c>
       <c r="F683" t="n">
-        <v>116437</v>
+        <v>114060</v>
       </c>
     </row>
     <row r="684">
@@ -14161,10 +14161,10 @@
         <v>82.73</v>
       </c>
       <c r="E687" t="n">
-        <v>84.09</v>
+        <v>84.15000000000001</v>
       </c>
       <c r="F687" t="n">
-        <v>122966</v>
+        <v>121250</v>
       </c>
     </row>
     <row r="688">
@@ -14175,16 +14175,16 @@
         <v>83.81999999999999</v>
       </c>
       <c r="C688" t="n">
-        <v>85.08</v>
+        <v>84.97</v>
       </c>
       <c r="D688" t="n">
         <v>83.18000000000001</v>
       </c>
       <c r="E688" t="n">
-        <v>84.83</v>
+        <v>84.97</v>
       </c>
       <c r="F688" t="n">
-        <v>113449</v>
+        <v>111475</v>
       </c>
     </row>
     <row r="689">
@@ -14261,10 +14261,10 @@
         <v>81.48</v>
       </c>
       <c r="E692" t="n">
-        <v>83.78</v>
+        <v>83.83</v>
       </c>
       <c r="F692" t="n">
-        <v>167007</v>
+        <v>164605</v>
       </c>
     </row>
     <row r="693">
@@ -14281,10 +14281,10 @@
         <v>82.39</v>
       </c>
       <c r="E693" t="n">
-        <v>83.41</v>
+        <v>83.55</v>
       </c>
       <c r="F693" t="n">
-        <v>133535</v>
+        <v>132228</v>
       </c>
     </row>
     <row r="694">
@@ -14352,7 +14352,7 @@
         <v>44504</v>
       </c>
       <c r="B697" t="n">
-        <v>80.83</v>
+        <v>81.12</v>
       </c>
       <c r="C697" t="n">
         <v>84.08</v>
@@ -14364,7 +14364,7 @@
         <v>80.54000000000001</v>
       </c>
       <c r="F697" t="n">
-        <v>168783</v>
+        <v>171378</v>
       </c>
     </row>
     <row r="698">
@@ -14372,7 +14372,7 @@
         <v>44505</v>
       </c>
       <c r="B698" t="n">
-        <v>81.04000000000001</v>
+        <v>80.95</v>
       </c>
       <c r="C698" t="n">
         <v>82.72</v>
@@ -14384,7 +14384,7 @@
         <v>81.93000000000001</v>
       </c>
       <c r="F698" t="n">
-        <v>163172</v>
+        <v>166390</v>
       </c>
     </row>
     <row r="699">
@@ -14461,10 +14461,10 @@
         <v>81.06</v>
       </c>
       <c r="E702" t="n">
-        <v>81.92</v>
+        <v>81.91</v>
       </c>
       <c r="F702" t="n">
-        <v>161511</v>
+        <v>159955</v>
       </c>
     </row>
     <row r="703">
@@ -14481,10 +14481,10 @@
         <v>80.63</v>
       </c>
       <c r="E703" t="n">
-        <v>81.29000000000001</v>
+        <v>81.41</v>
       </c>
       <c r="F703" t="n">
-        <v>134507</v>
+        <v>133196</v>
       </c>
     </row>
     <row r="704">
@@ -14561,10 +14561,10 @@
         <v>78.55</v>
       </c>
       <c r="E707" t="n">
-        <v>80.34999999999999</v>
+        <v>80.42</v>
       </c>
       <c r="F707" t="n">
-        <v>132952</v>
+        <v>131123</v>
       </c>
     </row>
     <row r="708">
@@ -14581,10 +14581,10 @@
         <v>77.41</v>
       </c>
       <c r="E708" t="n">
-        <v>77.77</v>
+        <v>77.76000000000001</v>
       </c>
       <c r="F708" t="n">
-        <v>177513</v>
+        <v>175625</v>
       </c>
     </row>
     <row r="709">
@@ -14761,10 +14761,10 @@
         <v>65.67</v>
       </c>
       <c r="E717" t="n">
-        <v>70.36</v>
+        <v>69.94</v>
       </c>
       <c r="F717" t="n">
-        <v>240359</v>
+        <v>237353</v>
       </c>
     </row>
     <row r="718">
@@ -14781,10 +14781,10 @@
         <v>69.09999999999999</v>
       </c>
       <c r="E718" t="n">
-        <v>69.70999999999999</v>
+        <v>69.73</v>
       </c>
       <c r="F718" t="n">
-        <v>208893</v>
+        <v>205214</v>
       </c>
     </row>
     <row r="719">
@@ -14858,13 +14858,13 @@
         <v>76.55</v>
       </c>
       <c r="D722" t="n">
-        <v>73.70999999999999</v>
+        <v>73.78</v>
       </c>
       <c r="E722" t="n">
-        <v>73.84999999999999</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="F722" t="n">
-        <v>142264</v>
+        <v>140659</v>
       </c>
     </row>
     <row r="723">
@@ -14881,10 +14881,10 @@
         <v>73.67</v>
       </c>
       <c r="E723" t="n">
-        <v>75.16</v>
+        <v>75.23</v>
       </c>
       <c r="F723" t="n">
-        <v>153301</v>
+        <v>151698</v>
       </c>
     </row>
     <row r="724">
@@ -14961,10 +14961,10 @@
         <v>73.88</v>
       </c>
       <c r="E727" t="n">
-        <v>74.48999999999999</v>
+        <v>74.63</v>
       </c>
       <c r="F727" t="n">
-        <v>142563</v>
+        <v>140474</v>
       </c>
     </row>
     <row r="728">
@@ -14981,10 +14981,10 @@
         <v>72.63</v>
       </c>
       <c r="E728" t="n">
-        <v>72.88</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="F728" t="n">
-        <v>154875</v>
+        <v>152160</v>
       </c>
     </row>
     <row r="729">
@@ -15061,10 +15061,10 @@
         <v>74.72</v>
       </c>
       <c r="E732" t="n">
-        <v>76.52</v>
+        <v>76.63</v>
       </c>
       <c r="F732" t="n">
-        <v>102802</v>
+        <v>100583</v>
       </c>
     </row>
     <row r="733">
@@ -15161,10 +15161,10 @@
         <v>78.33</v>
       </c>
       <c r="E737" t="n">
-        <v>78.86</v>
+        <v>78.97</v>
       </c>
       <c r="F737" t="n">
-        <v>105405</v>
+        <v>103669</v>
       </c>
     </row>
     <row r="738">
@@ -15261,10 +15261,10 @@
         <v>79.36</v>
       </c>
       <c r="E742" t="n">
-        <v>81.70999999999999</v>
+        <v>81.65000000000001</v>
       </c>
       <c r="F742" t="n">
-        <v>187943</v>
+        <v>185800</v>
       </c>
     </row>
     <row r="743">
@@ -15281,10 +15281,10 @@
         <v>81.12</v>
       </c>
       <c r="E743" t="n">
-        <v>81.48</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="F743" t="n">
-        <v>160491</v>
+        <v>158852</v>
       </c>
     </row>
     <row r="744">
@@ -15361,10 +15361,10 @@
         <v>83.34999999999999</v>
       </c>
       <c r="E747" t="n">
-        <v>83.61</v>
+        <v>83.45</v>
       </c>
       <c r="F747" t="n">
-        <v>147527</v>
+        <v>145171</v>
       </c>
     </row>
     <row r="748">
@@ -15375,16 +15375,16 @@
         <v>83.68000000000001</v>
       </c>
       <c r="C748" t="n">
-        <v>85.98999999999999</v>
+        <v>85.97</v>
       </c>
       <c r="D748" t="n">
         <v>83.53</v>
       </c>
       <c r="E748" t="n">
-        <v>85.77</v>
+        <v>85.91</v>
       </c>
       <c r="F748" t="n">
-        <v>173518</v>
+        <v>171152</v>
       </c>
     </row>
     <row r="749">
@@ -15458,13 +15458,13 @@
         <v>88.8</v>
       </c>
       <c r="D752" t="n">
-        <v>86.38</v>
+        <v>86.56999999999999</v>
       </c>
       <c r="E752" t="n">
-        <v>86.58</v>
+        <v>86.7</v>
       </c>
       <c r="F752" t="n">
-        <v>169439</v>
+        <v>162890</v>
       </c>
     </row>
     <row r="753">
@@ -15481,10 +15481,10 @@
         <v>85.02</v>
       </c>
       <c r="E753" t="n">
-        <v>86.92</v>
+        <v>86.98</v>
       </c>
       <c r="F753" t="n">
-        <v>225683</v>
+        <v>223066</v>
       </c>
     </row>
     <row r="754">
@@ -15561,10 +15561,10 @@
         <v>87.7</v>
       </c>
       <c r="E757" t="n">
-        <v>88.63</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="F757" t="n">
-        <v>275711</v>
+        <v>270152</v>
       </c>
     </row>
     <row r="758">
@@ -15581,10 +15581,10 @@
         <v>88</v>
       </c>
       <c r="E758" t="n">
-        <v>88.81999999999999</v>
+        <v>88.73</v>
       </c>
       <c r="F758" t="n">
-        <v>278896</v>
+        <v>275262</v>
       </c>
     </row>
     <row r="759">
@@ -15655,16 +15655,16 @@
         <v>88.63</v>
       </c>
       <c r="C762" t="n">
-        <v>90.84999999999999</v>
+        <v>90.73999999999999</v>
       </c>
       <c r="D762" t="n">
         <v>87.59999999999999</v>
       </c>
       <c r="E762" t="n">
-        <v>90.51000000000001</v>
+        <v>90.45999999999999</v>
       </c>
       <c r="F762" t="n">
-        <v>168353</v>
+        <v>163057</v>
       </c>
     </row>
     <row r="763">
@@ -15681,10 +15681,10 @@
         <v>90.67</v>
       </c>
       <c r="E763" t="n">
-        <v>92.14</v>
+        <v>92.54000000000001</v>
       </c>
       <c r="F763" t="n">
-        <v>180147</v>
+        <v>177219</v>
       </c>
     </row>
     <row r="764">
@@ -15761,10 +15761,10 @@
         <v>90.09999999999999</v>
       </c>
       <c r="E767" t="n">
-        <v>90.54000000000001</v>
+        <v>90.66</v>
       </c>
       <c r="F767" t="n">
-        <v>186180</v>
+        <v>183590</v>
       </c>
     </row>
     <row r="768">
@@ -15781,10 +15781,10 @@
         <v>89.66</v>
       </c>
       <c r="E768" t="n">
-        <v>93.8</v>
+        <v>93.81</v>
       </c>
       <c r="F768" t="n">
-        <v>194729</v>
+        <v>189880</v>
       </c>
     </row>
     <row r="769">
@@ -15861,10 +15861,10 @@
         <v>90.34999999999999</v>
       </c>
       <c r="E772" t="n">
-        <v>91.16</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="F772" t="n">
-        <v>212213</v>
+        <v>209775</v>
       </c>
     </row>
     <row r="773">
@@ -15875,7 +15875,7 @@
         <v>90.76000000000001</v>
       </c>
       <c r="C773" t="n">
-        <v>92.28</v>
+        <v>92.15000000000001</v>
       </c>
       <c r="D773" t="n">
         <v>88.64</v>
@@ -15884,7 +15884,7 @@
         <v>91.81</v>
       </c>
       <c r="F773" t="n">
-        <v>194995</v>
+        <v>190175</v>
       </c>
     </row>
     <row r="774">
@@ -15961,10 +15961,10 @@
         <v>93.94</v>
       </c>
       <c r="E777" t="n">
-        <v>95.41</v>
+        <v>95.61</v>
       </c>
       <c r="F777" t="n">
-        <v>313423</v>
+        <v>309076</v>
       </c>
     </row>
     <row r="778">
@@ -15981,10 +15981,10 @@
         <v>92.55</v>
       </c>
       <c r="E778" t="n">
-        <v>94.23</v>
+        <v>94.69</v>
       </c>
       <c r="F778" t="n">
-        <v>237786</v>
+        <v>233541</v>
       </c>
     </row>
     <row r="779">
@@ -16061,10 +16061,10 @@
         <v>108.17</v>
       </c>
       <c r="E782" t="n">
-        <v>109.27</v>
+        <v>109.72</v>
       </c>
       <c r="F782" t="n">
-        <v>233799</v>
+        <v>231064</v>
       </c>
     </row>
     <row r="783">
@@ -16081,10 +16081,10 @@
         <v>108.47</v>
       </c>
       <c r="E783" t="n">
-        <v>116.7</v>
+        <v>117.14</v>
       </c>
       <c r="F783" t="n">
-        <v>210974</v>
+        <v>204618</v>
       </c>
     </row>
     <row r="784">
@@ -16161,10 +16161,10 @@
         <v>107.05</v>
       </c>
       <c r="E787" t="n">
-        <v>107.11</v>
+        <v>107.97</v>
       </c>
       <c r="F787" t="n">
-        <v>173653</v>
+        <v>170481</v>
       </c>
     </row>
     <row r="788">
@@ -16181,10 +16181,10 @@
         <v>104.96</v>
       </c>
       <c r="E788" t="n">
-        <v>110.14</v>
+        <v>110.51</v>
       </c>
       <c r="F788" t="n">
-        <v>157669</v>
+        <v>154891</v>
       </c>
     </row>
     <row r="789">
@@ -16252,19 +16252,19 @@
         <v>44637</v>
       </c>
       <c r="B792" t="n">
-        <v>96.70999999999999</v>
+        <v>96.98</v>
       </c>
       <c r="C792" t="n">
         <v>105.3</v>
       </c>
       <c r="D792" t="n">
-        <v>96.70999999999999</v>
+        <v>96.11</v>
       </c>
       <c r="E792" t="n">
         <v>104.46</v>
       </c>
       <c r="F792" t="n">
-        <v>172578</v>
+        <v>176604</v>
       </c>
     </row>
     <row r="793">
@@ -16272,7 +16272,7 @@
         <v>44638</v>
       </c>
       <c r="B793" t="n">
-        <v>105.16</v>
+        <v>104.55</v>
       </c>
       <c r="C793" t="n">
         <v>107.23</v>
@@ -16284,7 +16284,7 @@
         <v>105.63</v>
       </c>
       <c r="F793" t="n">
-        <v>155067</v>
+        <v>158531</v>
       </c>
     </row>
     <row r="794">
@@ -16352,7 +16352,7 @@
         <v>44644</v>
       </c>
       <c r="B797" t="n">
-        <v>119.49</v>
+        <v>118.08</v>
       </c>
       <c r="C797" t="n">
         <v>120.04</v>
@@ -16364,7 +16364,7 @@
         <v>114.47</v>
       </c>
       <c r="F797" t="n">
-        <v>206598</v>
+        <v>215337</v>
       </c>
     </row>
     <row r="798">
@@ -16372,7 +16372,7 @@
         <v>44645</v>
       </c>
       <c r="B798" t="n">
-        <v>114.52</v>
+        <v>115.3</v>
       </c>
       <c r="C798" t="n">
         <v>117.69</v>
@@ -16384,7 +16384,7 @@
         <v>115.94</v>
       </c>
       <c r="F798" t="n">
-        <v>189095</v>
+        <v>195807</v>
       </c>
     </row>
     <row r="799">
@@ -16461,10 +16461,10 @@
         <v>103.71</v>
       </c>
       <c r="E802" t="n">
-        <v>104.99</v>
+        <v>104.6</v>
       </c>
       <c r="F802" t="n">
-        <v>220967</v>
+        <v>217472</v>
       </c>
     </row>
     <row r="803">
@@ -16481,10 +16481,10 @@
         <v>101.94</v>
       </c>
       <c r="E803" t="n">
-        <v>103.88</v>
+        <v>104.13</v>
       </c>
       <c r="F803" t="n">
-        <v>181758</v>
+        <v>179677</v>
       </c>
     </row>
     <row r="804">
@@ -16561,10 +16561,10 @@
         <v>98.2</v>
       </c>
       <c r="E807" t="n">
-        <v>100.96</v>
+        <v>100.94</v>
       </c>
       <c r="F807" t="n">
-        <v>186163</v>
+        <v>183922</v>
       </c>
     </row>
     <row r="808">
@@ -16581,10 +16581,10 @@
         <v>99.28</v>
       </c>
       <c r="E808" t="n">
-        <v>101.81</v>
+        <v>102.16</v>
       </c>
       <c r="F808" t="n">
-        <v>162819</v>
+        <v>159821</v>
       </c>
     </row>
     <row r="809">
@@ -16661,10 +16661,10 @@
         <v>106.14</v>
       </c>
       <c r="E812" t="n">
-        <v>110.62</v>
+        <v>110.56</v>
       </c>
       <c r="F812" t="n">
-        <v>159785</v>
+        <v>156524</v>
       </c>
     </row>
     <row r="813">
@@ -16741,10 +16741,10 @@
         <v>106.38</v>
       </c>
       <c r="E816" t="n">
-        <v>108</v>
+        <v>107.93</v>
       </c>
       <c r="F816" t="n">
-        <v>188001</v>
+        <v>184241</v>
       </c>
     </row>
     <row r="817">
@@ -16758,13 +16758,13 @@
         <v>108.41</v>
       </c>
       <c r="D817" t="n">
-        <v>105.05</v>
+        <v>105.44</v>
       </c>
       <c r="E817" t="n">
-        <v>105.7</v>
+        <v>105.6</v>
       </c>
       <c r="F817" t="n">
-        <v>165632</v>
+        <v>162032</v>
       </c>
     </row>
     <row r="818">
@@ -16841,10 +16841,10 @@
         <v>102.74</v>
       </c>
       <c r="E821" t="n">
-        <v>106.8</v>
+        <v>107.25</v>
       </c>
       <c r="F821" t="n">
-        <v>170514</v>
+        <v>167676</v>
       </c>
     </row>
     <row r="822">
@@ -16861,10 +16861,10 @@
         <v>105.92</v>
       </c>
       <c r="E822" t="n">
-        <v>106.06</v>
+        <v>106.38</v>
       </c>
       <c r="F822" t="n">
-        <v>186051</v>
+        <v>182972</v>
       </c>
     </row>
     <row r="823">
@@ -16941,10 +16941,10 @@
         <v>108.66</v>
       </c>
       <c r="E826" t="n">
-        <v>110.4</v>
+        <v>110.3</v>
       </c>
       <c r="F826" t="n">
-        <v>201234</v>
+        <v>197687</v>
       </c>
     </row>
     <row r="827">
@@ -16961,10 +16961,10 @@
         <v>109.21</v>
       </c>
       <c r="E827" t="n">
-        <v>112.22</v>
+        <v>112.44</v>
       </c>
       <c r="F827" t="n">
-        <v>207851</v>
+        <v>203469</v>
       </c>
     </row>
     <row r="828">
@@ -17041,10 +17041,10 @@
         <v>103.97</v>
       </c>
       <c r="E831" t="n">
-        <v>106.86</v>
+        <v>107.38</v>
       </c>
       <c r="F831" t="n">
-        <v>243371</v>
+        <v>240901</v>
       </c>
     </row>
     <row r="832">
@@ -17061,10 +17061,10 @@
         <v>106.88</v>
       </c>
       <c r="E832" t="n">
-        <v>109.76</v>
+        <v>110.4</v>
       </c>
       <c r="F832" t="n">
-        <v>193013</v>
+        <v>190398</v>
       </c>
     </row>
     <row r="833">
@@ -17141,10 +17141,10 @@
         <v>104.22</v>
       </c>
       <c r="E836" t="n">
-        <v>109.5</v>
+        <v>109.59</v>
       </c>
       <c r="F836" t="n">
-        <v>250583</v>
+        <v>247278</v>
       </c>
     </row>
     <row r="837">
@@ -17161,10 +17161,10 @@
         <v>108.65</v>
       </c>
       <c r="E837" t="n">
-        <v>110.3</v>
+        <v>110.87</v>
       </c>
       <c r="F837" t="n">
-        <v>202895</v>
+        <v>198948</v>
       </c>
     </row>
     <row r="838">
@@ -17241,10 +17241,10 @@
         <v>110.83</v>
       </c>
       <c r="E841" t="n">
-        <v>114.15</v>
+        <v>114</v>
       </c>
       <c r="F841" t="n">
-        <v>175003</v>
+        <v>171535</v>
       </c>
     </row>
     <row r="842">
@@ -17261,10 +17261,10 @@
         <v>113.01</v>
       </c>
       <c r="E842" t="n">
-        <v>115.01</v>
+        <v>115.42</v>
       </c>
       <c r="F842" t="n">
-        <v>213418</v>
+        <v>210750</v>
       </c>
     </row>
     <row r="843">
@@ -17335,16 +17335,16 @@
         <v>113.88</v>
       </c>
       <c r="C846" t="n">
-        <v>117.74</v>
+        <v>117.57</v>
       </c>
       <c r="D846" t="n">
         <v>111.85</v>
       </c>
       <c r="E846" t="n">
-        <v>117.31</v>
+        <v>117.26</v>
       </c>
       <c r="F846" t="n">
-        <v>138282</v>
+        <v>137013</v>
       </c>
     </row>
     <row r="847">
@@ -17355,16 +17355,16 @@
         <v>117.37</v>
       </c>
       <c r="C847" t="n">
-        <v>120.6</v>
+        <v>120.57</v>
       </c>
       <c r="D847" t="n">
         <v>115.28</v>
       </c>
       <c r="E847" t="n">
-        <v>120.23</v>
+        <v>120.41</v>
       </c>
       <c r="F847" t="n">
-        <v>91626</v>
+        <v>90339</v>
       </c>
     </row>
     <row r="848">
@@ -17441,10 +17441,10 @@
         <v>121.23</v>
       </c>
       <c r="E851" t="n">
-        <v>121.41</v>
+        <v>121.71</v>
       </c>
       <c r="F851" t="n">
-        <v>176648</v>
+        <v>174232</v>
       </c>
     </row>
     <row r="852">
@@ -17461,10 +17461,10 @@
         <v>118.31</v>
       </c>
       <c r="E852" t="n">
-        <v>120.02</v>
+        <v>120.29</v>
       </c>
       <c r="F852" t="n">
-        <v>192334</v>
+        <v>190410</v>
       </c>
     </row>
     <row r="853">
@@ -17541,10 +17541,10 @@
         <v>113.72</v>
       </c>
       <c r="E856" t="n">
-        <v>116.92</v>
+        <v>117.15</v>
       </c>
       <c r="F856" t="n">
-        <v>231324</v>
+        <v>228931</v>
       </c>
     </row>
     <row r="857">
@@ -17561,10 +17561,10 @@
         <v>109.77</v>
       </c>
       <c r="E857" t="n">
-        <v>111.27</v>
+        <v>111.29</v>
       </c>
       <c r="F857" t="n">
-        <v>236868</v>
+        <v>233588</v>
       </c>
     </row>
     <row r="858">
@@ -17641,10 +17641,10 @@
         <v>105.25</v>
       </c>
       <c r="E861" t="n">
-        <v>106.13</v>
+        <v>106.29</v>
       </c>
       <c r="F861" t="n">
-        <v>234952</v>
+        <v>233040</v>
       </c>
     </row>
     <row r="862">
@@ -17661,10 +17661,10 @@
         <v>105.78</v>
       </c>
       <c r="E862" t="n">
-        <v>108.33</v>
+        <v>109.13</v>
       </c>
       <c r="F862" t="n">
-        <v>205227</v>
+        <v>202836</v>
       </c>
     </row>
     <row r="863">
@@ -17741,10 +17741,10 @@
         <v>107.7</v>
       </c>
       <c r="E866" t="n">
-        <v>108.43</v>
+        <v>108.69</v>
       </c>
       <c r="F866" t="n">
-        <v>212070</v>
+        <v>208599</v>
       </c>
     </row>
     <row r="867">
@@ -17761,10 +17761,10 @@
         <v>107.32</v>
       </c>
       <c r="E867" t="n">
-        <v>110.43</v>
+        <v>110.56</v>
       </c>
       <c r="F867" t="n">
-        <v>210630</v>
+        <v>209195</v>
       </c>
     </row>
     <row r="868">
@@ -17841,10 +17841,10 @@
         <v>97.11</v>
       </c>
       <c r="E871" t="n">
-        <v>102.32</v>
+        <v>102.75</v>
       </c>
       <c r="F871" t="n">
-        <v>224620</v>
+        <v>221862</v>
       </c>
     </row>
     <row r="872">
@@ -17861,10 +17861,10 @@
         <v>102.16</v>
       </c>
       <c r="E872" t="n">
-        <v>105.2</v>
+        <v>105.32</v>
       </c>
       <c r="F872" t="n">
-        <v>237030</v>
+        <v>235167</v>
       </c>
     </row>
     <row r="873">
@@ -17941,10 +17941,10 @@
         <v>92.42</v>
       </c>
       <c r="E876" t="n">
-        <v>97.12</v>
+        <v>97.17</v>
       </c>
       <c r="F876" t="n">
-        <v>217836</v>
+        <v>215919</v>
       </c>
     </row>
     <row r="877">
@@ -17961,10 +17961,10 @@
         <v>95.59</v>
       </c>
       <c r="E877" t="n">
-        <v>97.98</v>
+        <v>98.34999999999999</v>
       </c>
       <c r="F877" t="n">
-        <v>203134</v>
+        <v>200270</v>
       </c>
     </row>
     <row r="878">
@@ -18041,10 +18041,10 @@
         <v>97.86</v>
       </c>
       <c r="E881" t="n">
-        <v>99.93000000000001</v>
+        <v>100.04</v>
       </c>
       <c r="F881" t="n">
-        <v>229298</v>
+        <v>227231</v>
       </c>
     </row>
     <row r="882">
@@ -18061,10 +18061,10 @@
         <v>97.90000000000001</v>
       </c>
       <c r="E882" t="n">
-        <v>98.98999999999999</v>
+        <v>98.67</v>
       </c>
       <c r="F882" t="n">
-        <v>226135</v>
+        <v>222921</v>
       </c>
     </row>
     <row r="883">
@@ -18141,10 +18141,10 @@
         <v>100.74</v>
       </c>
       <c r="E886" t="n">
-        <v>101.99</v>
+        <v>101.93</v>
       </c>
       <c r="F886" t="n">
-        <v>132446</v>
+        <v>130398</v>
       </c>
     </row>
     <row r="887">
@@ -18161,10 +18161,10 @@
         <v>101.27</v>
       </c>
       <c r="E887" t="n">
-        <v>103.1</v>
+        <v>103.21</v>
       </c>
       <c r="F887" t="n">
-        <v>113461</v>
+        <v>112179</v>
       </c>
     </row>
     <row r="888">
@@ -18238,13 +18238,13 @@
         <v>97.17</v>
       </c>
       <c r="D891" t="n">
-        <v>92.5</v>
+        <v>92.73</v>
       </c>
       <c r="E891" t="n">
-        <v>92.52</v>
+        <v>93.38</v>
       </c>
       <c r="F891" t="n">
-        <v>162676</v>
+        <v>160629</v>
       </c>
     </row>
     <row r="892">
@@ -18261,10 +18261,10 @@
         <v>92.15000000000001</v>
       </c>
       <c r="E892" t="n">
-        <v>93.51000000000001</v>
+        <v>93.69</v>
       </c>
       <c r="F892" t="n">
-        <v>157322</v>
+        <v>155701</v>
       </c>
     </row>
     <row r="893">
@@ -18341,10 +18341,10 @@
         <v>96.08</v>
       </c>
       <c r="E896" t="n">
-        <v>98.31</v>
+        <v>98.66</v>
       </c>
       <c r="F896" t="n">
-        <v>140818</v>
+        <v>139272</v>
       </c>
     </row>
     <row r="897">
@@ -18361,10 +18361,10 @@
         <v>96.26000000000001</v>
       </c>
       <c r="E897" t="n">
-        <v>96.89</v>
+        <v>97.3</v>
       </c>
       <c r="F897" t="n">
-        <v>145858</v>
+        <v>144235</v>
       </c>
     </row>
     <row r="898">
@@ -18441,10 +18441,10 @@
         <v>92.55</v>
       </c>
       <c r="E901" t="n">
-        <v>95.56</v>
+        <v>95.93000000000001</v>
       </c>
       <c r="F901" t="n">
-        <v>123861</v>
+        <v>122235</v>
       </c>
     </row>
     <row r="902">
@@ -18461,10 +18461,10 @@
         <v>93.7</v>
       </c>
       <c r="E902" t="n">
-        <v>95.08</v>
+        <v>95.52</v>
       </c>
       <c r="F902" t="n">
-        <v>126696</v>
+        <v>125387</v>
       </c>
     </row>
     <row r="903">
@@ -18541,10 +18541,10 @@
         <v>98.23</v>
       </c>
       <c r="E906" t="n">
-        <v>98.68000000000001</v>
+        <v>99.05</v>
       </c>
       <c r="F906" t="n">
-        <v>115830</v>
+        <v>114289</v>
       </c>
     </row>
     <row r="907">
@@ -18561,10 +18561,10 @@
         <v>96.92</v>
       </c>
       <c r="E907" t="n">
-        <v>98.56999999999999</v>
+        <v>98.70999999999999</v>
       </c>
       <c r="F907" t="n">
-        <v>128357</v>
+        <v>127109</v>
       </c>
     </row>
     <row r="908">
@@ -18641,10 +18641,10 @@
         <v>91.58</v>
       </c>
       <c r="E911" t="n">
-        <v>91.59</v>
+        <v>91.75</v>
       </c>
       <c r="F911" t="n">
-        <v>172611</v>
+        <v>171383</v>
       </c>
     </row>
     <row r="912">
@@ -18661,10 +18661,10 @@
         <v>92.41</v>
       </c>
       <c r="E912" t="n">
-        <v>92.83</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="F912" t="n">
-        <v>164349</v>
+        <v>162523</v>
       </c>
     </row>
     <row r="913">
@@ -18741,10 +18741,10 @@
         <v>86.86</v>
       </c>
       <c r="E916" t="n">
-        <v>87.73999999999999</v>
+        <v>88.03</v>
       </c>
       <c r="F916" t="n">
-        <v>175783</v>
+        <v>174104</v>
       </c>
     </row>
     <row r="917">
@@ -18761,10 +18761,10 @@
         <v>88.09</v>
       </c>
       <c r="E917" t="n">
-        <v>91.42</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="F917" t="n">
-        <v>139210</v>
+        <v>137562</v>
       </c>
     </row>
     <row r="918">
@@ -18841,10 +18841,10 @@
         <v>89.39</v>
       </c>
       <c r="E921" t="n">
-        <v>89.78</v>
+        <v>90.08</v>
       </c>
       <c r="F921" t="n">
-        <v>179533</v>
+        <v>177670</v>
       </c>
     </row>
     <row r="922">
@@ -18861,10 +18861,10 @@
         <v>89.37</v>
       </c>
       <c r="E922" t="n">
-        <v>90.36</v>
+        <v>90.58</v>
       </c>
       <c r="F922" t="n">
-        <v>177056</v>
+        <v>175462</v>
       </c>
     </row>
     <row r="923">
@@ -18941,10 +18941,10 @@
         <v>88.38</v>
       </c>
       <c r="E926" t="n">
-        <v>89.48999999999999</v>
+        <v>89.53</v>
       </c>
       <c r="F926" t="n">
-        <v>169282</v>
+        <v>167346</v>
       </c>
     </row>
     <row r="927">
@@ -18961,10 +18961,10 @@
         <v>84.61</v>
       </c>
       <c r="E927" t="n">
-        <v>85.65000000000001</v>
+        <v>85.41</v>
       </c>
       <c r="F927" t="n">
-        <v>159709</v>
+        <v>157358</v>
       </c>
     </row>
     <row r="928">
@@ -19041,10 +19041,10 @@
         <v>85.98</v>
       </c>
       <c r="E931" t="n">
-        <v>87.22</v>
+        <v>87.20999999999999</v>
       </c>
       <c r="F931" t="n">
-        <v>184095</v>
+        <v>182346</v>
       </c>
     </row>
     <row r="932">
@@ -19061,10 +19061,10 @@
         <v>84.73999999999999</v>
       </c>
       <c r="E932" t="n">
-        <v>85.04000000000001</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="F932" t="n">
-        <v>174184</v>
+        <v>172540</v>
       </c>
     </row>
     <row r="933">
@@ -19141,10 +19141,10 @@
         <v>92.09</v>
       </c>
       <c r="E936" t="n">
-        <v>94.16</v>
+        <v>94.31999999999999</v>
       </c>
       <c r="F936" t="n">
-        <v>136157</v>
+        <v>134269</v>
       </c>
     </row>
     <row r="937">
@@ -19161,10 +19161,10 @@
         <v>93.25</v>
       </c>
       <c r="E937" t="n">
-        <v>97.59</v>
+        <v>96.95</v>
       </c>
       <c r="F937" t="n">
-        <v>161145</v>
+        <v>158303</v>
       </c>
     </row>
     <row r="938">
@@ -19241,10 +19241,10 @@
         <v>90.18000000000001</v>
       </c>
       <c r="E941" t="n">
-        <v>93.67</v>
+        <v>93.61</v>
       </c>
       <c r="F941" t="n">
-        <v>189909</v>
+        <v>187899</v>
       </c>
     </row>
     <row r="942">
@@ -19261,10 +19261,10 @@
         <v>90.34</v>
       </c>
       <c r="E942" t="n">
-        <v>90.66</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="F942" t="n">
-        <v>186342</v>
+        <v>184164</v>
       </c>
     </row>
     <row r="943">
@@ -19341,10 +19341,10 @@
         <v>90.34</v>
       </c>
       <c r="E946" t="n">
-        <v>91.11</v>
+        <v>91</v>
       </c>
       <c r="F946" t="n">
-        <v>172151</v>
+        <v>169394</v>
       </c>
     </row>
     <row r="947">
@@ -19361,10 +19361,10 @@
         <v>89.40000000000001</v>
       </c>
       <c r="E947" t="n">
-        <v>91.58</v>
+        <v>91.7</v>
       </c>
       <c r="F947" t="n">
-        <v>170499</v>
+        <v>168937</v>
       </c>
     </row>
     <row r="948">
@@ -19441,10 +19441,10 @@
         <v>93.06999999999999</v>
       </c>
       <c r="E951" t="n">
-        <v>94.45999999999999</v>
+        <v>94.91</v>
       </c>
       <c r="F951" t="n">
-        <v>135151</v>
+        <v>130846</v>
       </c>
     </row>
     <row r="952">
@@ -19461,10 +19461,10 @@
         <v>92.81999999999999</v>
       </c>
       <c r="E952" t="n">
-        <v>93.95</v>
+        <v>93.81</v>
       </c>
       <c r="F952" t="n">
-        <v>135363</v>
+        <v>133960</v>
       </c>
     </row>
     <row r="953">
@@ -19532,7 +19532,7 @@
         <v>44868</v>
       </c>
       <c r="B956" t="n">
-        <v>94.84</v>
+        <v>94.81</v>
       </c>
       <c r="C956" t="n">
         <v>95.45</v>
@@ -19544,7 +19544,7 @@
         <v>93.92</v>
       </c>
       <c r="F956" t="n">
-        <v>141621</v>
+        <v>143503</v>
       </c>
     </row>
     <row r="957">
@@ -19552,19 +19552,19 @@
         <v>44869</v>
       </c>
       <c r="B957" t="n">
-        <v>93.94</v>
+        <v>93.98</v>
       </c>
       <c r="C957" t="n">
         <v>98.23999999999999</v>
       </c>
       <c r="D957" t="n">
-        <v>93.94</v>
+        <v>93.76000000000001</v>
       </c>
       <c r="E957" t="n">
         <v>98.01000000000001</v>
       </c>
       <c r="F957" t="n">
-        <v>179958</v>
+        <v>182009</v>
       </c>
     </row>
     <row r="958">
@@ -19641,10 +19641,10 @@
         <v>90.97</v>
       </c>
       <c r="E961" t="n">
-        <v>92.47</v>
+        <v>92.69</v>
       </c>
       <c r="F961" t="n">
-        <v>170823</v>
+        <v>168690</v>
       </c>
     </row>
     <row r="962">
@@ -19661,10 +19661,10 @@
         <v>92.79000000000001</v>
       </c>
       <c r="E962" t="n">
-        <v>94.95999999999999</v>
+        <v>95.04000000000001</v>
       </c>
       <c r="F962" t="n">
-        <v>165782</v>
+        <v>163940</v>
       </c>
     </row>
     <row r="963">
@@ -19741,10 +19741,10 @@
         <v>88.72</v>
       </c>
       <c r="E966" t="n">
-        <v>89.34999999999999</v>
+        <v>89.28</v>
       </c>
       <c r="F966" t="n">
-        <v>159560</v>
+        <v>157265</v>
       </c>
     </row>
     <row r="967">
@@ -19761,10 +19761,10 @@
         <v>85.41</v>
       </c>
       <c r="E967" t="n">
-        <v>87.5</v>
+        <v>87.45</v>
       </c>
       <c r="F967" t="n">
-        <v>162655</v>
+        <v>160818</v>
       </c>
     </row>
     <row r="968">
@@ -19941,10 +19941,10 @@
         <v>86.26000000000001</v>
       </c>
       <c r="E976" t="n">
-        <v>86.98</v>
+        <v>86.84</v>
       </c>
       <c r="F976" t="n">
-        <v>136930</v>
+        <v>135345</v>
       </c>
     </row>
     <row r="977">
@@ -19961,10 +19961,10 @@
         <v>85.17</v>
       </c>
       <c r="E977" t="n">
-        <v>85.90000000000001</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="F977" t="n">
-        <v>137359</v>
+        <v>135815</v>
       </c>
     </row>
     <row r="978">
@@ -20041,10 +20041,10 @@
         <v>75.92</v>
       </c>
       <c r="E981" t="n">
-        <v>76.61</v>
+        <v>76.27</v>
       </c>
       <c r="F981" t="n">
-        <v>167594</v>
+        <v>165742</v>
       </c>
     </row>
     <row r="982">
@@ -20061,10 +20061,10 @@
         <v>75.34999999999999</v>
       </c>
       <c r="E982" t="n">
-        <v>76.79000000000001</v>
+        <v>76.76000000000001</v>
       </c>
       <c r="F982" t="n">
-        <v>153224</v>
+        <v>151706</v>
       </c>
     </row>
     <row r="983">
@@ -20141,10 +20141,10 @@
         <v>80.86</v>
       </c>
       <c r="E986" t="n">
-        <v>81.54000000000001</v>
+        <v>81.39</v>
       </c>
       <c r="F986" t="n">
-        <v>151489</v>
+        <v>149384</v>
       </c>
     </row>
     <row r="987">
@@ -20161,10 +20161,10 @@
         <v>78.61</v>
       </c>
       <c r="E987" t="n">
-        <v>79.44</v>
+        <v>79.36</v>
       </c>
       <c r="F987" t="n">
-        <v>151197</v>
+        <v>149990</v>
       </c>
     </row>
     <row r="988">
@@ -20241,10 +20241,10 @@
         <v>81.28</v>
       </c>
       <c r="E991" t="n">
-        <v>82.20999999999999</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="F991" t="n">
-        <v>95617</v>
+        <v>94348</v>
       </c>
     </row>
     <row r="992">
@@ -20321,10 +20321,10 @@
         <v>81.81999999999999</v>
       </c>
       <c r="E995" t="n">
-        <v>83.63</v>
+        <v>83.68000000000001</v>
       </c>
       <c r="F995" t="n">
-        <v>110699</v>
+        <v>109380</v>
       </c>
     </row>
     <row r="996">
@@ -20401,10 +20401,10 @@
         <v>77.63</v>
       </c>
       <c r="E999" t="n">
-        <v>78.8</v>
+        <v>78.68000000000001</v>
       </c>
       <c r="F999" t="n">
-        <v>150672</v>
+        <v>149266</v>
       </c>
     </row>
     <row r="1000">
@@ -20424,7 +20424,7 @@
         <v>78.51000000000001</v>
       </c>
       <c r="F1000" t="n">
-        <v>148389</v>
+        <v>147017</v>
       </c>
     </row>
     <row r="1001">
@@ -20501,10 +20501,10 @@
         <v>82.43000000000001</v>
       </c>
       <c r="E1004" t="n">
-        <v>83.84999999999999</v>
+        <v>83.91</v>
       </c>
       <c r="F1004" t="n">
-        <v>142735</v>
+        <v>141086</v>
       </c>
     </row>
     <row r="1005">
@@ -20515,16 +20515,16 @@
         <v>83.91</v>
       </c>
       <c r="C1005" t="n">
-        <v>85.61</v>
+        <v>85.55</v>
       </c>
       <c r="D1005" t="n">
         <v>83.55</v>
       </c>
       <c r="E1005" t="n">
-        <v>85.47</v>
+        <v>85.48</v>
       </c>
       <c r="F1005" t="n">
-        <v>131152</v>
+        <v>129757</v>
       </c>
     </row>
     <row r="1006">
@@ -20601,10 +20601,10 @@
         <v>83.95999999999999</v>
       </c>
       <c r="E1009" t="n">
-        <v>86.34</v>
+        <v>86.31999999999999</v>
       </c>
       <c r="F1009" t="n">
-        <v>144410</v>
+        <v>142583</v>
       </c>
     </row>
     <row r="1010">
@@ -20621,10 +20621,10 @@
         <v>85.69</v>
       </c>
       <c r="E1010" t="n">
-        <v>87.59</v>
+        <v>87.75</v>
       </c>
       <c r="F1010" t="n">
-        <v>125225</v>
+        <v>123973</v>
       </c>
     </row>
     <row r="1011">
@@ -20701,10 +20701,10 @@
         <v>85.75</v>
       </c>
       <c r="E1014" t="n">
-        <v>87.29000000000001</v>
+        <v>87.31</v>
       </c>
       <c r="F1014" t="n">
-        <v>96051</v>
+        <v>95077</v>
       </c>
     </row>
     <row r="1015">
@@ -20721,10 +20721,10 @@
         <v>85.48</v>
       </c>
       <c r="E1015" t="n">
-        <v>86.01000000000001</v>
+        <v>86.04000000000001</v>
       </c>
       <c r="F1015" t="n">
-        <v>110922</v>
+        <v>109841</v>
       </c>
     </row>
     <row r="1016">
@@ -20801,10 +20801,10 @@
         <v>81.2</v>
       </c>
       <c r="E1019" t="n">
-        <v>82.12</v>
+        <v>81.98</v>
       </c>
       <c r="F1019" t="n">
-        <v>150704</v>
+        <v>146732</v>
       </c>
     </row>
     <row r="1020">
@@ -20818,13 +20818,13 @@
         <v>84.11</v>
       </c>
       <c r="D1020" t="n">
-        <v>79.53</v>
+        <v>79.62</v>
       </c>
       <c r="E1020" t="n">
-        <v>79.62</v>
+        <v>79.64</v>
       </c>
       <c r="F1020" t="n">
-        <v>163093</v>
+        <v>161681</v>
       </c>
     </row>
     <row r="1021">
@@ -20901,10 +20901,10 @@
         <v>82.86</v>
       </c>
       <c r="E1024" t="n">
-        <v>83.95</v>
+        <v>83.88</v>
       </c>
       <c r="F1024" t="n">
-        <v>144061</v>
+        <v>142722</v>
       </c>
     </row>
     <row r="1025">
@@ -20921,10 +20921,10 @@
         <v>83.66</v>
       </c>
       <c r="E1025" t="n">
-        <v>86.2</v>
+        <v>86.29000000000001</v>
       </c>
       <c r="F1025" t="n">
-        <v>156718</v>
+        <v>155562</v>
       </c>
     </row>
     <row r="1026">
@@ -20998,13 +20998,13 @@
         <v>85.90000000000001</v>
       </c>
       <c r="D1029" t="n">
-        <v>84.28</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="E1029" t="n">
-        <v>84.31</v>
+        <v>84.37</v>
       </c>
       <c r="F1029" t="n">
-        <v>129946</v>
+        <v>128382</v>
       </c>
     </row>
     <row r="1030">
@@ -21021,10 +21021,10 @@
         <v>81.55</v>
       </c>
       <c r="E1030" t="n">
-        <v>82.72</v>
+        <v>82.68000000000001</v>
       </c>
       <c r="F1030" t="n">
-        <v>142763</v>
+        <v>141607</v>
       </c>
     </row>
     <row r="1031">
@@ -21101,10 +21101,10 @@
         <v>80.27</v>
       </c>
       <c r="E1034" t="n">
-        <v>82.18000000000001</v>
+        <v>82.12</v>
       </c>
       <c r="F1034" t="n">
-        <v>108091</v>
+        <v>107083</v>
       </c>
     </row>
     <row r="1035">
@@ -21121,10 +21121,10 @@
         <v>80.7</v>
       </c>
       <c r="E1035" t="n">
-        <v>82.77</v>
+        <v>82.94</v>
       </c>
       <c r="F1035" t="n">
-        <v>130526</v>
+        <v>129354</v>
       </c>
     </row>
     <row r="1036">
@@ -21201,10 +21201,10 @@
         <v>83.66</v>
       </c>
       <c r="E1039" t="n">
-        <v>84.23</v>
+        <v>84.34</v>
       </c>
       <c r="F1039" t="n">
-        <v>115434</v>
+        <v>114302</v>
       </c>
     </row>
     <row r="1040">
@@ -21215,16 +21215,16 @@
         <v>84.37</v>
       </c>
       <c r="C1040" t="n">
-        <v>85.81</v>
+        <v>85.8</v>
       </c>
       <c r="D1040" t="n">
         <v>82.2</v>
       </c>
       <c r="E1040" t="n">
-        <v>85.73999999999999</v>
+        <v>85.72</v>
       </c>
       <c r="F1040" t="n">
-        <v>120888</v>
+        <v>119970</v>
       </c>
     </row>
     <row r="1041">
@@ -21301,10 +21301,10 @@
         <v>81.16</v>
       </c>
       <c r="E1044" t="n">
-        <v>81.23</v>
+        <v>81.26000000000001</v>
       </c>
       <c r="F1044" t="n">
-        <v>121276</v>
+        <v>120126</v>
       </c>
     </row>
     <row r="1045">
@@ -21321,10 +21321,10 @@
         <v>80.47</v>
       </c>
       <c r="E1045" t="n">
-        <v>82.38</v>
+        <v>82.33</v>
       </c>
       <c r="F1045" t="n">
-        <v>172647</v>
+        <v>171433</v>
       </c>
     </row>
     <row r="1046">
@@ -21392,7 +21392,7 @@
         <v>45001</v>
       </c>
       <c r="B1049" t="n">
-        <v>74.59999999999999</v>
+        <v>74.04000000000001</v>
       </c>
       <c r="C1049" t="n">
         <v>75.23</v>
@@ -21404,7 +21404,7 @@
         <v>74.25</v>
       </c>
       <c r="F1049" t="n">
-        <v>206406</v>
+        <v>210322</v>
       </c>
     </row>
     <row r="1050">
@@ -21412,7 +21412,7 @@
         <v>45002</v>
       </c>
       <c r="B1050" t="n">
-        <v>74.41</v>
+        <v>74.45</v>
       </c>
       <c r="C1050" t="n">
         <v>75.65000000000001</v>
@@ -21424,7 +21424,7 @@
         <v>72.3</v>
       </c>
       <c r="F1050" t="n">
-        <v>194486</v>
+        <v>196053</v>
       </c>
     </row>
     <row r="1051">
@@ -21492,7 +21492,7 @@
         <v>45008</v>
       </c>
       <c r="B1054" t="n">
-        <v>75.73</v>
+        <v>75.58</v>
       </c>
       <c r="C1054" t="n">
         <v>77.09</v>
@@ -21504,7 +21504,7 @@
         <v>74.98999999999999</v>
       </c>
       <c r="F1054" t="n">
-        <v>132462</v>
+        <v>134971</v>
       </c>
     </row>
     <row r="1055">
@@ -21512,7 +21512,7 @@
         <v>45009</v>
       </c>
       <c r="B1055" t="n">
-        <v>74.92</v>
+        <v>75.08</v>
       </c>
       <c r="C1055" t="n">
         <v>75.89</v>
@@ -21524,7 +21524,7 @@
         <v>74.52</v>
       </c>
       <c r="F1055" t="n">
-        <v>158419</v>
+        <v>160608</v>
       </c>
     </row>
     <row r="1056">
@@ -21601,10 +21601,10 @@
         <v>77.13</v>
       </c>
       <c r="E1059" t="n">
-        <v>78.43000000000001</v>
+        <v>78.47</v>
       </c>
       <c r="F1059" t="n">
-        <v>102975</v>
+        <v>101875</v>
       </c>
     </row>
     <row r="1060">
@@ -21621,10 +21621,10 @@
         <v>77.79000000000001</v>
       </c>
       <c r="E1060" t="n">
-        <v>79.76000000000001</v>
+        <v>79.73</v>
       </c>
       <c r="F1060" t="n">
-        <v>103341</v>
+        <v>102278</v>
       </c>
     </row>
     <row r="1061">
@@ -21701,10 +21701,10 @@
         <v>83.89</v>
       </c>
       <c r="E1064" t="n">
-        <v>84.62</v>
+        <v>84.73</v>
       </c>
       <c r="F1064" t="n">
-        <v>128978</v>
+        <v>127887</v>
       </c>
     </row>
     <row r="1065">
@@ -21781,10 +21781,10 @@
         <v>85.78</v>
       </c>
       <c r="E1068" t="n">
-        <v>86.03</v>
+        <v>85.98</v>
       </c>
       <c r="F1068" t="n">
-        <v>107747</v>
+        <v>106530</v>
       </c>
     </row>
     <row r="1069">
@@ -21801,10 +21801,10 @@
         <v>85.27</v>
       </c>
       <c r="E1069" t="n">
-        <v>86.12</v>
+        <v>86.13</v>
       </c>
       <c r="F1069" t="n">
-        <v>119789</v>
+        <v>118921</v>
       </c>
     </row>
     <row r="1070">
@@ -21878,13 +21878,13 @@
         <v>82.59999999999999</v>
       </c>
       <c r="D1073" t="n">
-        <v>80.48999999999999</v>
+        <v>80.51000000000001</v>
       </c>
       <c r="E1073" t="n">
-        <v>80.48999999999999</v>
+        <v>80.62</v>
       </c>
       <c r="F1073" t="n">
-        <v>100157</v>
+        <v>99083</v>
       </c>
     </row>
     <row r="1074">
@@ -21901,10 +21901,10 @@
         <v>80.2</v>
       </c>
       <c r="E1074" t="n">
-        <v>81.53</v>
+        <v>81.38</v>
       </c>
       <c r="F1074" t="n">
-        <v>89589</v>
+        <v>88877</v>
       </c>
     </row>
     <row r="1075">
@@ -21981,10 +21981,10 @@
         <v>77.3</v>
       </c>
       <c r="E1078" t="n">
-        <v>78.17</v>
+        <v>78.23</v>
       </c>
       <c r="F1078" t="n">
-        <v>114226</v>
+        <v>112919</v>
       </c>
     </row>
     <row r="1079">
@@ -22001,10 +22001,10 @@
         <v>77.44</v>
       </c>
       <c r="E1079" t="n">
-        <v>80.08</v>
+        <v>80.20999999999999</v>
       </c>
       <c r="F1079" t="n">
-        <v>111593</v>
+        <v>110643</v>
       </c>
     </row>
     <row r="1080">
@@ -22081,10 +22081,10 @@
         <v>71.34</v>
       </c>
       <c r="E1083" t="n">
-        <v>72.38</v>
+        <v>72.34</v>
       </c>
       <c r="F1083" t="n">
-        <v>176458</v>
+        <v>175075</v>
       </c>
     </row>
     <row r="1084">
@@ -22101,10 +22101,10 @@
         <v>72.31999999999999</v>
       </c>
       <c r="E1084" t="n">
-        <v>75.15000000000001</v>
+        <v>75.22</v>
       </c>
       <c r="F1084" t="n">
-        <v>122688</v>
+        <v>121559</v>
       </c>
     </row>
     <row r="1085">
@@ -22181,10 +22181,10 @@
         <v>74.5</v>
       </c>
       <c r="E1088" t="n">
-        <v>75.26000000000001</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="F1088" t="n">
-        <v>142391</v>
+        <v>141443</v>
       </c>
     </row>
     <row r="1089">
@@ -22201,10 +22201,10 @@
         <v>73.84999999999999</v>
       </c>
       <c r="E1089" t="n">
-        <v>73.93000000000001</v>
+        <v>74.02</v>
       </c>
       <c r="F1089" t="n">
-        <v>144762</v>
+        <v>143925</v>
       </c>
     </row>
     <row r="1090">
@@ -22281,10 +22281,10 @@
         <v>75.42</v>
       </c>
       <c r="E1093" t="n">
-        <v>75.84</v>
+        <v>75.89</v>
       </c>
       <c r="F1093" t="n">
-        <v>98116</v>
+        <v>97144</v>
       </c>
     </row>
     <row r="1094">
@@ -22301,10 +22301,10 @@
         <v>75.01000000000001</v>
       </c>
       <c r="E1094" t="n">
-        <v>75.59999999999999</v>
+        <v>75.75</v>
       </c>
       <c r="F1094" t="n">
-        <v>108218</v>
+        <v>107224</v>
       </c>
     </row>
     <row r="1095">
@@ -22381,10 +22381,10 @@
         <v>75.08</v>
       </c>
       <c r="E1098" t="n">
-        <v>75.95999999999999</v>
+        <v>76.13</v>
       </c>
       <c r="F1098" t="n">
-        <v>95663</v>
+        <v>94656</v>
       </c>
     </row>
     <row r="1099">
@@ -22401,10 +22401,10 @@
         <v>75.62</v>
       </c>
       <c r="E1099" t="n">
-        <v>77.14</v>
+        <v>77.03</v>
       </c>
       <c r="F1099" t="n">
-        <v>86227</v>
+        <v>85632</v>
       </c>
     </row>
     <row r="1100">
@@ -22481,10 +22481,10 @@
         <v>72</v>
       </c>
       <c r="E1103" t="n">
-        <v>74.25</v>
+        <v>74.17</v>
       </c>
       <c r="F1103" t="n">
-        <v>124084</v>
+        <v>122959</v>
       </c>
     </row>
     <row r="1104">
@@ -22501,10 +22501,10 @@
         <v>74.13</v>
       </c>
       <c r="E1104" t="n">
-        <v>76.13</v>
+        <v>76.3</v>
       </c>
       <c r="F1104" t="n">
-        <v>111881</v>
+        <v>110715</v>
       </c>
     </row>
     <row r="1105">
@@ -22581,10 +22581,10 @@
         <v>73.52</v>
       </c>
       <c r="E1108" t="n">
-        <v>75.44</v>
+        <v>75.56999999999999</v>
       </c>
       <c r="F1108" t="n">
-        <v>142206</v>
+        <v>141391</v>
       </c>
     </row>
     <row r="1109">
@@ -22601,10 +22601,10 @@
         <v>74.67</v>
       </c>
       <c r="E1109" t="n">
-        <v>74.88</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="F1109" t="n">
-        <v>120995</v>
+        <v>120105</v>
       </c>
     </row>
     <row r="1110">
@@ -22681,10 +22681,10 @@
         <v>72.84999999999999</v>
       </c>
       <c r="E1113" t="n">
-        <v>75.52</v>
+        <v>75.56</v>
       </c>
       <c r="F1113" t="n">
-        <v>105947</v>
+        <v>104970</v>
       </c>
     </row>
     <row r="1114">
@@ -22701,10 +22701,10 @@
         <v>75.09999999999999</v>
       </c>
       <c r="E1114" t="n">
-        <v>76.23</v>
+        <v>76.47</v>
       </c>
       <c r="F1114" t="n">
-        <v>111184</v>
+        <v>109963</v>
       </c>
     </row>
     <row r="1115">
@@ -22781,10 +22781,10 @@
         <v>73.75</v>
       </c>
       <c r="E1118" t="n">
-        <v>74.3</v>
+        <v>74.2</v>
       </c>
       <c r="F1118" t="n">
-        <v>89974</v>
+        <v>89166</v>
       </c>
     </row>
     <row r="1119">
@@ -22795,16 +22795,16 @@
         <v>74.2</v>
       </c>
       <c r="C1119" t="n">
-        <v>74.45999999999999</v>
+        <v>74.36</v>
       </c>
       <c r="D1119" t="n">
         <v>72.25</v>
       </c>
       <c r="E1119" t="n">
-        <v>74.34</v>
+        <v>74.09</v>
       </c>
       <c r="F1119" t="n">
-        <v>101628</v>
+        <v>100773</v>
       </c>
     </row>
     <row r="1120">
@@ -22881,10 +22881,10 @@
         <v>73.56</v>
       </c>
       <c r="E1123" t="n">
-        <v>74.34999999999999</v>
+        <v>74.44</v>
       </c>
       <c r="F1123" t="n">
-        <v>118860</v>
+        <v>118096</v>
       </c>
     </row>
     <row r="1124">
@@ -22901,10 +22901,10 @@
         <v>74.23</v>
       </c>
       <c r="E1124" t="n">
-        <v>75.06999999999999</v>
+        <v>75.26000000000001</v>
       </c>
       <c r="F1124" t="n">
-        <v>108012</v>
+        <v>107062</v>
       </c>
     </row>
     <row r="1125">
@@ -22981,10 +22981,10 @@
         <v>74.94</v>
       </c>
       <c r="E1128" t="n">
-        <v>76.44</v>
+        <v>76.47</v>
       </c>
       <c r="F1128" t="n">
-        <v>121613</v>
+        <v>120498</v>
       </c>
     </row>
     <row r="1129">
@@ -23001,10 +23001,10 @@
         <v>75.91</v>
       </c>
       <c r="E1129" t="n">
-        <v>78.12</v>
+        <v>78.13</v>
       </c>
       <c r="F1129" t="n">
-        <v>101260</v>
+        <v>99946</v>
       </c>
     </row>
     <row r="1130">
@@ -23075,16 +23075,16 @@
         <v>79.95999999999999</v>
       </c>
       <c r="C1133" t="n">
-        <v>81.5</v>
+        <v>81.48999999999999</v>
       </c>
       <c r="D1133" t="n">
         <v>79.69</v>
       </c>
       <c r="E1133" t="n">
-        <v>81.37</v>
+        <v>81.48</v>
       </c>
       <c r="F1133" t="n">
-        <v>97805</v>
+        <v>96443</v>
       </c>
     </row>
     <row r="1134">
@@ -23098,13 +23098,13 @@
         <v>81.42</v>
       </c>
       <c r="D1134" t="n">
-        <v>79.34999999999999</v>
+        <v>79.44</v>
       </c>
       <c r="E1134" t="n">
-        <v>79.45</v>
+        <v>79.54000000000001</v>
       </c>
       <c r="F1134" t="n">
-        <v>99161</v>
+        <v>98000</v>
       </c>
     </row>
     <row r="1135">
@@ -23181,10 +23181,10 @@
         <v>78.56999999999999</v>
       </c>
       <c r="E1138" t="n">
-        <v>79.48</v>
+        <v>79.54000000000001</v>
       </c>
       <c r="F1138" t="n">
-        <v>77506</v>
+        <v>76777</v>
       </c>
     </row>
     <row r="1139">
@@ -23201,10 +23201,10 @@
         <v>79.51000000000001</v>
       </c>
       <c r="E1139" t="n">
-        <v>80.5</v>
+        <v>80.69</v>
       </c>
       <c r="F1139" t="n">
-        <v>70745</v>
+        <v>69907</v>
       </c>
     </row>
     <row r="1140">
@@ -23281,10 +23281,10 @@
         <v>82.54000000000001</v>
       </c>
       <c r="E1143" t="n">
-        <v>83.3</v>
+        <v>83.42</v>
       </c>
       <c r="F1143" t="n">
-        <v>101885</v>
+        <v>100960</v>
       </c>
     </row>
     <row r="1144">
@@ -23301,10 +23301,10 @@
         <v>82.78</v>
       </c>
       <c r="E1144" t="n">
-        <v>84.34999999999999</v>
+        <v>84.26000000000001</v>
       </c>
       <c r="F1144" t="n">
-        <v>96933</v>
+        <v>96080</v>
       </c>
     </row>
     <row r="1145">
@@ -23381,10 +23381,10 @@
         <v>82.23</v>
       </c>
       <c r="E1148" t="n">
-        <v>85.04000000000001</v>
+        <v>85.13</v>
       </c>
       <c r="F1148" t="n">
-        <v>124232</v>
+        <v>122532</v>
       </c>
     </row>
     <row r="1149">
@@ -23401,10 +23401,10 @@
         <v>84.89</v>
       </c>
       <c r="E1149" t="n">
-        <v>85.81</v>
+        <v>85.84</v>
       </c>
       <c r="F1149" t="n">
-        <v>104424</v>
+        <v>103319</v>
       </c>
     </row>
     <row r="1150">
@@ -23481,10 +23481,10 @@
         <v>85.89</v>
       </c>
       <c r="E1153" t="n">
-        <v>86.01000000000001</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="F1153" t="n">
-        <v>120019</v>
+        <v>119054</v>
       </c>
     </row>
     <row r="1154">
@@ -23501,10 +23501,10 @@
         <v>85.53</v>
       </c>
       <c r="E1154" t="n">
-        <v>86.16</v>
+        <v>86.26000000000001</v>
       </c>
       <c r="F1154" t="n">
-        <v>115051</v>
+        <v>114400</v>
       </c>
     </row>
     <row r="1155">
@@ -23581,10 +23581,10 @@
         <v>82.70999999999999</v>
       </c>
       <c r="E1158" t="n">
-        <v>83.42</v>
+        <v>83.45999999999999</v>
       </c>
       <c r="F1158" t="n">
-        <v>88033</v>
+        <v>87119</v>
       </c>
     </row>
     <row r="1159">
@@ -23601,10 +23601,10 @@
         <v>82.98</v>
       </c>
       <c r="E1159" t="n">
-        <v>84.42</v>
+        <v>84.37</v>
       </c>
       <c r="F1159" t="n">
-        <v>98761</v>
+        <v>98085</v>
       </c>
     </row>
     <row r="1160">
@@ -23681,10 +23681,10 @@
         <v>81.61</v>
       </c>
       <c r="E1163" t="n">
-        <v>82.67</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="F1163" t="n">
-        <v>77961</v>
+        <v>77118</v>
       </c>
     </row>
     <row r="1164">
@@ -23701,10 +23701,10 @@
         <v>82.2</v>
       </c>
       <c r="E1164" t="n">
-        <v>84.05</v>
+        <v>84.14</v>
       </c>
       <c r="F1164" t="n">
-        <v>102303</v>
+        <v>101382</v>
       </c>
     </row>
     <row r="1165">
@@ -23781,10 +23781,10 @@
         <v>84.98</v>
       </c>
       <c r="E1168" t="n">
-        <v>86.66</v>
+        <v>86.63</v>
       </c>
       <c r="F1168" t="n">
-        <v>85007</v>
+        <v>83934</v>
       </c>
     </row>
     <row r="1169">
@@ -23795,16 +23795,16 @@
         <v>86.63</v>
       </c>
       <c r="C1169" t="n">
-        <v>88.75</v>
+        <v>88.66</v>
       </c>
       <c r="D1169" t="n">
         <v>86.59</v>
       </c>
       <c r="E1169" t="n">
-        <v>88.68000000000001</v>
+        <v>88.64</v>
       </c>
       <c r="F1169" t="n">
-        <v>98645</v>
+        <v>97671</v>
       </c>
     </row>
     <row r="1170">
@@ -23881,10 +23881,10 @@
         <v>89.17</v>
       </c>
       <c r="E1173" t="n">
-        <v>89.47</v>
+        <v>89.76000000000001</v>
       </c>
       <c r="F1173" t="n">
-        <v>104343</v>
+        <v>103067</v>
       </c>
     </row>
     <row r="1174">
@@ -23901,10 +23901,10 @@
         <v>88.97</v>
       </c>
       <c r="E1174" t="n">
-        <v>90.09999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="F1174" t="n">
-        <v>101197</v>
+        <v>100164</v>
       </c>
     </row>
     <row r="1175">
@@ -23975,16 +23975,16 @@
         <v>91.56999999999999</v>
       </c>
       <c r="C1178" t="n">
-        <v>93.68000000000001</v>
+        <v>93.44</v>
       </c>
       <c r="D1178" t="n">
         <v>91.55</v>
       </c>
       <c r="E1178" t="n">
-        <v>93.56</v>
+        <v>93.36</v>
       </c>
       <c r="F1178" t="n">
-        <v>91727</v>
+        <v>89908</v>
       </c>
     </row>
     <row r="1179">
@@ -24001,10 +24001,10 @@
         <v>92.14</v>
       </c>
       <c r="E1179" t="n">
-        <v>93.56999999999999</v>
+        <v>93.52</v>
       </c>
       <c r="F1179" t="n">
-        <v>101498</v>
+        <v>100530</v>
       </c>
     </row>
     <row r="1180">
@@ -24081,10 +24081,10 @@
         <v>91.23999999999999</v>
       </c>
       <c r="E1183" t="n">
-        <v>92.20999999999999</v>
+        <v>92.27</v>
       </c>
       <c r="F1183" t="n">
-        <v>98137</v>
+        <v>97207</v>
       </c>
     </row>
     <row r="1184">
@@ -24101,10 +24101,10 @@
         <v>91.68000000000001</v>
       </c>
       <c r="E1184" t="n">
-        <v>92.28</v>
+        <v>92.31</v>
       </c>
       <c r="F1184" t="n">
-        <v>99665</v>
+        <v>98960</v>
       </c>
     </row>
     <row r="1185">
@@ -24181,10 +24181,10 @@
         <v>92.56</v>
       </c>
       <c r="E1188" t="n">
-        <v>92.89</v>
+        <v>92.94</v>
       </c>
       <c r="F1188" t="n">
-        <v>128240</v>
+        <v>127194</v>
       </c>
     </row>
     <row r="1189">
@@ -24201,10 +24201,10 @@
         <v>91.68000000000001</v>
       </c>
       <c r="E1189" t="n">
-        <v>91.8</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="F1189" t="n">
-        <v>117877</v>
+        <v>116761</v>
       </c>
     </row>
     <row r="1190">
@@ -24281,10 +24281,10 @@
         <v>83.31999999999999</v>
       </c>
       <c r="E1193" t="n">
-        <v>83.72</v>
+        <v>83.68000000000001</v>
       </c>
       <c r="F1193" t="n">
-        <v>149779</v>
+        <v>148426</v>
       </c>
     </row>
     <row r="1194">
@@ -24301,10 +24301,10 @@
         <v>82.97</v>
       </c>
       <c r="E1194" t="n">
-        <v>83.79000000000001</v>
+        <v>83.88</v>
       </c>
       <c r="F1194" t="n">
-        <v>140020</v>
+        <v>138785</v>
       </c>
     </row>
     <row r="1195">
@@ -24381,10 +24381,10 @@
         <v>84.59</v>
       </c>
       <c r="E1198" t="n">
-        <v>85.59999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="F1198" t="n">
-        <v>124560</v>
+        <v>123421</v>
       </c>
     </row>
     <row r="1199">
@@ -24404,7 +24404,7 @@
         <v>89.93000000000001</v>
       </c>
       <c r="F1199" t="n">
-        <v>120817</v>
+        <v>118765</v>
       </c>
     </row>
     <row r="1200">
@@ -24475,16 +24475,16 @@
         <v>90.26000000000001</v>
       </c>
       <c r="C1203" t="n">
-        <v>92.34999999999999</v>
+        <v>92.22</v>
       </c>
       <c r="D1203" t="n">
         <v>88.69</v>
       </c>
       <c r="E1203" t="n">
-        <v>92.04000000000001</v>
+        <v>92.16</v>
       </c>
       <c r="F1203" t="n">
-        <v>111224</v>
+        <v>109002</v>
       </c>
     </row>
     <row r="1204">
@@ -24501,10 +24501,10 @@
         <v>90.63</v>
       </c>
       <c r="E1204" t="n">
-        <v>91.26000000000001</v>
+        <v>91.13</v>
       </c>
       <c r="F1204" t="n">
-        <v>110661</v>
+        <v>109157</v>
       </c>
     </row>
     <row r="1205">
@@ -24581,10 +24581,10 @@
         <v>86.48</v>
       </c>
       <c r="E1208" t="n">
-        <v>87.23999999999999</v>
+        <v>87.25</v>
       </c>
       <c r="F1208" t="n">
-        <v>114536</v>
+        <v>113368</v>
       </c>
     </row>
     <row r="1209">
@@ -24601,10 +24601,10 @@
         <v>86.76000000000001</v>
       </c>
       <c r="E1209" t="n">
-        <v>88.70999999999999</v>
+        <v>88.76000000000001</v>
       </c>
       <c r="F1209" t="n">
-        <v>123231</v>
+        <v>121600</v>
       </c>
     </row>
     <row r="1210">
@@ -24672,7 +24672,7 @@
         <v>45232</v>
       </c>
       <c r="B1213" t="n">
-        <v>85.03</v>
+        <v>84.83</v>
       </c>
       <c r="C1213" t="n">
         <v>86.88</v>
@@ -24684,7 +24684,7 @@
         <v>86.63</v>
       </c>
       <c r="F1213" t="n">
-        <v>102261</v>
+        <v>103842</v>
       </c>
     </row>
     <row r="1214">
@@ -24692,7 +24692,7 @@
         <v>45233</v>
       </c>
       <c r="B1214" t="n">
-        <v>86.66</v>
+        <v>86.70999999999999</v>
       </c>
       <c r="C1214" t="n">
         <v>87.58</v>
@@ -24704,7 +24704,7 @@
         <v>84.95</v>
       </c>
       <c r="F1214" t="n">
-        <v>117913</v>
+        <v>119097</v>
       </c>
     </row>
     <row r="1215">
@@ -24781,10 +24781,10 @@
         <v>79.33</v>
       </c>
       <c r="E1218" t="n">
-        <v>79.76000000000001</v>
+        <v>79.75</v>
       </c>
       <c r="F1218" t="n">
-        <v>111847</v>
+        <v>110739</v>
       </c>
     </row>
     <row r="1219">
@@ -24801,10 +24801,10 @@
         <v>79.70999999999999</v>
       </c>
       <c r="E1219" t="n">
-        <v>81.43000000000001</v>
+        <v>81.36</v>
       </c>
       <c r="F1219" t="n">
-        <v>92327</v>
+        <v>91256</v>
       </c>
     </row>
     <row r="1220">
@@ -24881,10 +24881,10 @@
         <v>76.64</v>
       </c>
       <c r="E1223" t="n">
-        <v>77.45</v>
+        <v>77.43000000000001</v>
       </c>
       <c r="F1223" t="n">
-        <v>105749</v>
+        <v>104766</v>
       </c>
     </row>
     <row r="1224">
@@ -24901,10 +24901,10 @@
         <v>77.31</v>
       </c>
       <c r="E1224" t="n">
-        <v>80.43000000000001</v>
+        <v>80.37</v>
       </c>
       <c r="F1224" t="n">
-        <v>89648</v>
+        <v>88772</v>
       </c>
     </row>
     <row r="1225">
@@ -25078,13 +25078,13 @@
         <v>84.51000000000001</v>
       </c>
       <c r="D1233" t="n">
-        <v>79.94</v>
+        <v>79.95</v>
       </c>
       <c r="E1233" t="n">
-        <v>80.31</v>
+        <v>80</v>
       </c>
       <c r="F1233" t="n">
-        <v>145419</v>
+        <v>143673</v>
       </c>
     </row>
     <row r="1234">
@@ -25101,10 +25101,10 @@
         <v>78.69</v>
       </c>
       <c r="E1234" t="n">
-        <v>79.02</v>
+        <v>78.93000000000001</v>
       </c>
       <c r="F1234" t="n">
-        <v>126159</v>
+        <v>125186</v>
       </c>
     </row>
     <row r="1235">
@@ -25181,10 +25181,10 @@
         <v>73.68000000000001</v>
       </c>
       <c r="E1238" t="n">
-        <v>74.39</v>
+        <v>74.47</v>
       </c>
       <c r="F1238" t="n">
-        <v>116791</v>
+        <v>115986</v>
       </c>
     </row>
     <row r="1239">
@@ -25201,10 +25201,10 @@
         <v>74.25</v>
       </c>
       <c r="E1239" t="n">
-        <v>75.94</v>
+        <v>75.87</v>
       </c>
       <c r="F1239" t="n">
-        <v>114930</v>
+        <v>114085</v>
       </c>
     </row>
     <row r="1240">
@@ -25281,10 +25281,10 @@
         <v>74.56999999999999</v>
       </c>
       <c r="E1243" t="n">
-        <v>76.75</v>
+        <v>76.86</v>
       </c>
       <c r="F1243" t="n">
-        <v>84712</v>
+        <v>83845</v>
       </c>
     </row>
     <row r="1244">
@@ -25301,10 +25301,10 @@
         <v>75.48</v>
       </c>
       <c r="E1244" t="n">
-        <v>76.98999999999999</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="F1244" t="n">
-        <v>95068</v>
+        <v>94162</v>
       </c>
     </row>
     <row r="1245">
@@ -25381,10 +25381,10 @@
         <v>77.76000000000001</v>
       </c>
       <c r="E1248" t="n">
-        <v>79.12</v>
+        <v>79.19</v>
       </c>
       <c r="F1248" t="n">
-        <v>91755</v>
+        <v>91100</v>
       </c>
     </row>
     <row r="1249">
@@ -25461,10 +25461,10 @@
         <v>77.04000000000001</v>
       </c>
       <c r="E1252" t="n">
-        <v>77.36</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="F1252" t="n">
-        <v>95204</v>
+        <v>94380</v>
       </c>
     </row>
     <row r="1253">
@@ -25544,7 +25544,7 @@
         <v>77.53</v>
       </c>
       <c r="F1256" t="n">
-        <v>119158</v>
+        <v>118273</v>
       </c>
     </row>
     <row r="1257">
@@ -25641,10 +25641,10 @@
         <v>76.45</v>
       </c>
       <c r="E1261" t="n">
-        <v>78.01000000000001</v>
+        <v>77.61</v>
       </c>
       <c r="F1261" t="n">
-        <v>129868</v>
+        <v>128067</v>
       </c>
     </row>
     <row r="1262">
@@ -25741,10 +25741,10 @@
         <v>76.98</v>
       </c>
       <c r="E1266" t="n">
-        <v>78.56</v>
+        <v>78.63</v>
       </c>
       <c r="F1266" t="n">
-        <v>99368</v>
+        <v>98609</v>
       </c>
     </row>
     <row r="1267">
@@ -25841,10 +25841,10 @@
         <v>79.65000000000001</v>
       </c>
       <c r="E1271" t="n">
-        <v>81.69</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="F1271" t="n">
-        <v>76710</v>
+        <v>75889</v>
       </c>
     </row>
     <row r="1272">
@@ -25861,10 +25861,10 @@
         <v>80.75</v>
       </c>
       <c r="E1272" t="n">
-        <v>83.09999999999999</v>
+        <v>83.08</v>
       </c>
       <c r="F1272" t="n">
-        <v>87047</v>
+        <v>85666</v>
       </c>
     </row>
     <row r="1273">
@@ -25941,10 +25941,10 @@
         <v>78.5</v>
       </c>
       <c r="E1276" t="n">
-        <v>78.7</v>
+        <v>78.64</v>
       </c>
       <c r="F1276" t="n">
-        <v>140571</v>
+        <v>138682</v>
       </c>
     </row>
     <row r="1277">
@@ -25961,10 +25961,10 @@
         <v>76.78</v>
       </c>
       <c r="E1277" t="n">
-        <v>77.31999999999999</v>
+        <v>77.11</v>
       </c>
       <c r="F1277" t="n">
-        <v>133396</v>
+        <v>132023</v>
       </c>
     </row>
     <row r="1278">
@@ -26041,10 +26041,10 @@
         <v>78.84999999999999</v>
       </c>
       <c r="E1281" t="n">
-        <v>81.40000000000001</v>
+        <v>81.51000000000001</v>
       </c>
       <c r="F1281" t="n">
-        <v>87658</v>
+        <v>86597</v>
       </c>
     </row>
     <row r="1282">
@@ -26064,7 +26064,7 @@
         <v>81.63</v>
       </c>
       <c r="F1282" t="n">
-        <v>86235</v>
+        <v>85346</v>
       </c>
     </row>
     <row r="1283">
@@ -26141,10 +26141,10 @@
         <v>80.31999999999999</v>
       </c>
       <c r="E1286" t="n">
-        <v>82.22</v>
+        <v>82.37</v>
       </c>
       <c r="F1286" t="n">
-        <v>84560</v>
+        <v>83753</v>
       </c>
     </row>
     <row r="1287">
@@ -26161,10 +26161,10 @@
         <v>81.34</v>
       </c>
       <c r="E1287" t="n">
-        <v>82.68000000000001</v>
+        <v>82.70999999999999</v>
       </c>
       <c r="F1287" t="n">
-        <v>81459</v>
+        <v>80620</v>
       </c>
     </row>
     <row r="1288">
@@ -26241,10 +26241,10 @@
         <v>81.45</v>
       </c>
       <c r="E1291" t="n">
-        <v>82.51000000000001</v>
+        <v>82.63</v>
       </c>
       <c r="F1291" t="n">
-        <v>67848</v>
+        <v>67106</v>
       </c>
     </row>
     <row r="1292">
@@ -26261,10 +26261,10 @@
         <v>80.65000000000001</v>
       </c>
       <c r="E1292" t="n">
-        <v>80.84</v>
+        <v>80.88</v>
       </c>
       <c r="F1292" t="n">
-        <v>73168</v>
+        <v>72495</v>
       </c>
     </row>
     <row r="1293">
@@ -26341,10 +26341,10 @@
         <v>81.37</v>
       </c>
       <c r="E1296" t="n">
-        <v>81.8</v>
+        <v>81.70999999999999</v>
       </c>
       <c r="F1296" t="n">
-        <v>79642</v>
+        <v>78801</v>
       </c>
     </row>
     <row r="1297">
@@ -26361,10 +26361,10 @@
         <v>81.63</v>
       </c>
       <c r="E1297" t="n">
-        <v>83.12</v>
+        <v>83.19</v>
       </c>
       <c r="F1297" t="n">
-        <v>73275</v>
+        <v>72423</v>
       </c>
     </row>
     <row r="1298">
@@ -26441,10 +26441,10 @@
         <v>81.77</v>
       </c>
       <c r="E1301" t="n">
-        <v>82.87</v>
+        <v>82.52</v>
       </c>
       <c r="F1301" t="n">
-        <v>103853</v>
+        <v>102278</v>
       </c>
     </row>
     <row r="1302">
@@ -26461,10 +26461,10 @@
         <v>81.41</v>
       </c>
       <c r="E1302" t="n">
-        <v>81.55</v>
+        <v>81.66</v>
       </c>
       <c r="F1302" t="n">
-        <v>100115</v>
+        <v>99175</v>
       </c>
     </row>
     <row r="1303">
@@ -26532,19 +26532,19 @@
         <v>45365</v>
       </c>
       <c r="B1306" t="n">
-        <v>83.69</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="C1306" t="n">
         <v>85.18000000000001</v>
       </c>
       <c r="D1306" t="n">
-        <v>83.56999999999999</v>
+        <v>83.53</v>
       </c>
       <c r="E1306" t="n">
         <v>84.61</v>
       </c>
       <c r="F1306" t="n">
-        <v>71119</v>
+        <v>71844</v>
       </c>
     </row>
     <row r="1307">
@@ -26552,7 +26552,7 @@
         <v>45366</v>
       </c>
       <c r="B1307" t="n">
-        <v>84.68000000000001</v>
+        <v>84.65000000000001</v>
       </c>
       <c r="C1307" t="n">
         <v>85.09</v>
@@ -26564,7 +26564,7 @@
         <v>84.83</v>
       </c>
       <c r="F1307" t="n">
-        <v>74945</v>
+        <v>75864</v>
       </c>
     </row>
     <row r="1308">
@@ -26632,7 +26632,7 @@
         <v>45372</v>
       </c>
       <c r="B1311" t="n">
-        <v>85.81</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="C1311" t="n">
         <v>86.03</v>
@@ -26644,7 +26644,7 @@
         <v>84.95999999999999</v>
       </c>
       <c r="F1311" t="n">
-        <v>66113</v>
+        <v>67186</v>
       </c>
     </row>
     <row r="1312">
@@ -26652,7 +26652,7 @@
         <v>45373</v>
       </c>
       <c r="B1312" t="n">
-        <v>84.98999999999999</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="C1312" t="n">
         <v>85.58</v>
@@ -26664,7 +26664,7 @@
         <v>84.93000000000001</v>
       </c>
       <c r="F1312" t="n">
-        <v>53666</v>
+        <v>54286</v>
       </c>
     </row>
     <row r="1313">
@@ -26732,7 +26732,7 @@
         <v>45379</v>
       </c>
       <c r="B1316" t="n">
-        <v>85.65000000000001</v>
+        <v>85.56</v>
       </c>
       <c r="C1316" t="n">
         <v>86.89</v>
@@ -26744,7 +26744,7 @@
         <v>86.67</v>
       </c>
       <c r="F1316" t="n">
-        <v>56915</v>
+        <v>57372</v>
       </c>
     </row>
     <row r="1317">
@@ -26821,10 +26821,10 @@
         <v>88.43000000000001</v>
       </c>
       <c r="E1320" t="n">
-        <v>90.56</v>
+        <v>90.38</v>
       </c>
       <c r="F1320" t="n">
-        <v>75666</v>
+        <v>74470</v>
       </c>
     </row>
     <row r="1321">
@@ -26841,10 +26841,10 @@
         <v>90.18000000000001</v>
       </c>
       <c r="E1321" t="n">
-        <v>90.39</v>
+        <v>90.52</v>
       </c>
       <c r="F1321" t="n">
-        <v>80607</v>
+        <v>79937</v>
       </c>
     </row>
     <row r="1322">
@@ -26921,10 +26921,10 @@
         <v>88.87</v>
       </c>
       <c r="E1325" t="n">
-        <v>89.55</v>
+        <v>89.68000000000001</v>
       </c>
       <c r="F1325" t="n">
-        <v>107884</v>
+        <v>107040</v>
       </c>
     </row>
     <row r="1326">
@@ -26941,10 +26941,10 @@
         <v>89.45</v>
       </c>
       <c r="E1326" t="n">
-        <v>89.48999999999999</v>
+        <v>89.73</v>
       </c>
       <c r="F1326" t="n">
-        <v>109120</v>
+        <v>108331</v>
       </c>
     </row>
     <row r="1327">
@@ -27021,10 +27021,10 @@
         <v>85.63</v>
       </c>
       <c r="E1330" t="n">
-        <v>86.19</v>
+        <v>86.47</v>
       </c>
       <c r="F1330" t="n">
-        <v>108132</v>
+        <v>107464</v>
       </c>
     </row>
     <row r="1331">
@@ -27041,10 +27041,10 @@
         <v>85.61</v>
       </c>
       <c r="E1331" t="n">
-        <v>86.38</v>
+        <v>86.51000000000001</v>
       </c>
       <c r="F1331" t="n">
-        <v>144473</v>
+        <v>143518</v>
       </c>
     </row>
     <row r="1332">
@@ -27115,16 +27115,16 @@
         <v>86.88</v>
       </c>
       <c r="C1335" t="n">
-        <v>88</v>
+        <v>87.97</v>
       </c>
       <c r="D1335" t="n">
         <v>86.2</v>
       </c>
       <c r="E1335" t="n">
-        <v>87.83</v>
+        <v>87.95</v>
       </c>
       <c r="F1335" t="n">
-        <v>70059</v>
+        <v>69439</v>
       </c>
     </row>
     <row r="1336">
@@ -27141,10 +27141,10 @@
         <v>87.56999999999999</v>
       </c>
       <c r="E1336" t="n">
-        <v>87.89</v>
+        <v>87.98999999999999</v>
       </c>
       <c r="F1336" t="n">
-        <v>64445</v>
+        <v>63936</v>
       </c>
     </row>
     <row r="1337">
@@ -27221,10 +27221,10 @@
         <v>82.89</v>
       </c>
       <c r="E1340" t="n">
-        <v>83.48</v>
+        <v>83.47</v>
       </c>
       <c r="F1340" t="n">
-        <v>101847</v>
+        <v>100961</v>
       </c>
     </row>
     <row r="1341">
@@ -27238,13 +27238,13 @@
         <v>84.18000000000001</v>
       </c>
       <c r="D1341" t="n">
-        <v>82.53</v>
+        <v>82.65000000000001</v>
       </c>
       <c r="E1341" t="n">
-        <v>82.54000000000001</v>
+        <v>82.77</v>
       </c>
       <c r="F1341" t="n">
-        <v>83584</v>
+        <v>82987</v>
       </c>
     </row>
     <row r="1342">
@@ -27321,10 +27321,10 @@
         <v>83.18000000000001</v>
       </c>
       <c r="E1345" t="n">
-        <v>83.77</v>
+        <v>83.91</v>
       </c>
       <c r="F1345" t="n">
-        <v>67737</v>
+        <v>67201</v>
       </c>
     </row>
     <row r="1346">
@@ -27338,13 +27338,13 @@
         <v>84.23</v>
       </c>
       <c r="D1346" t="n">
-        <v>82.36</v>
+        <v>82.5</v>
       </c>
       <c r="E1346" t="n">
-        <v>82.36</v>
+        <v>82.61</v>
       </c>
       <c r="F1346" t="n">
-        <v>63117</v>
+        <v>62356</v>
       </c>
     </row>
     <row r="1347">
@@ -27421,10 +27421,10 @@
         <v>82.02</v>
       </c>
       <c r="E1350" t="n">
-        <v>82.98999999999999</v>
+        <v>83.04000000000001</v>
       </c>
       <c r="F1350" t="n">
-        <v>65759</v>
+        <v>65306</v>
       </c>
     </row>
     <row r="1351">
@@ -27441,10 +27441,10 @@
         <v>82.81999999999999</v>
       </c>
       <c r="E1351" t="n">
-        <v>83.56</v>
+        <v>83.68000000000001</v>
       </c>
       <c r="F1351" t="n">
-        <v>61133</v>
+        <v>60667</v>
       </c>
     </row>
     <row r="1352">
@@ -27521,10 +27521,10 @@
         <v>80.7</v>
       </c>
       <c r="E1355" t="n">
-        <v>81.06999999999999</v>
+        <v>81.09</v>
       </c>
       <c r="F1355" t="n">
-        <v>69958</v>
+        <v>68901</v>
       </c>
     </row>
     <row r="1356">
@@ -27541,10 +27541,10 @@
         <v>80.42</v>
       </c>
       <c r="E1356" t="n">
-        <v>81.79000000000001</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="F1356" t="n">
-        <v>56381</v>
+        <v>56045</v>
       </c>
     </row>
     <row r="1357">
@@ -27618,13 +27618,13 @@
         <v>83.51000000000001</v>
       </c>
       <c r="D1360" t="n">
-        <v>81.72</v>
+        <v>81.77</v>
       </c>
       <c r="E1360" t="n">
-        <v>81.73</v>
+        <v>81.88</v>
       </c>
       <c r="F1360" t="n">
-        <v>81864</v>
+        <v>81262</v>
       </c>
     </row>
     <row r="1361">
@@ -27641,10 +27641,10 @@
         <v>80.69</v>
       </c>
       <c r="E1361" t="n">
-        <v>81.09</v>
+        <v>81.22</v>
       </c>
       <c r="F1361" t="n">
-        <v>87130</v>
+        <v>86335</v>
       </c>
     </row>
     <row r="1362">
@@ -27721,10 +27721,10 @@
         <v>78.23999999999999</v>
       </c>
       <c r="E1365" t="n">
-        <v>79.69</v>
+        <v>79.73</v>
       </c>
       <c r="F1365" t="n">
-        <v>72677</v>
+        <v>72035</v>
       </c>
     </row>
     <row r="1366">
@@ -27741,10 +27741,10 @@
         <v>79.18000000000001</v>
       </c>
       <c r="E1366" t="n">
-        <v>79.23999999999999</v>
+        <v>79.27</v>
       </c>
       <c r="F1366" t="n">
-        <v>77440</v>
+        <v>76576</v>
       </c>
     </row>
     <row r="1367">
@@ -27821,10 +27821,10 @@
         <v>81.53</v>
       </c>
       <c r="E1370" t="n">
-        <v>81.68000000000001</v>
+        <v>81.98</v>
       </c>
       <c r="F1370" t="n">
-        <v>79567</v>
+        <v>78296</v>
       </c>
     </row>
     <row r="1371">
@@ -27841,10 +27841,10 @@
         <v>81.64</v>
       </c>
       <c r="E1371" t="n">
-        <v>82.06</v>
+        <v>82.2</v>
       </c>
       <c r="F1371" t="n">
-        <v>75768</v>
+        <v>75030</v>
       </c>
     </row>
     <row r="1372">
@@ -27921,10 +27921,10 @@
         <v>84.28</v>
       </c>
       <c r="E1375" t="n">
-        <v>84.7</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="F1375" t="n">
-        <v>59846</v>
+        <v>59448</v>
       </c>
     </row>
     <row r="1376">
@@ -27941,10 +27941,10 @@
         <v>84</v>
       </c>
       <c r="E1376" t="n">
-        <v>84.16</v>
+        <v>84.31</v>
       </c>
       <c r="F1376" t="n">
-        <v>60278</v>
+        <v>59797</v>
       </c>
     </row>
     <row r="1377">
@@ -28021,10 +28021,10 @@
         <v>84.01000000000001</v>
       </c>
       <c r="E1380" t="n">
-        <v>85.04000000000001</v>
+        <v>85.25</v>
       </c>
       <c r="F1380" t="n">
-        <v>64909</v>
+        <v>64362</v>
       </c>
     </row>
     <row r="1381">
@@ -28041,10 +28041,10 @@
         <v>84.39</v>
       </c>
       <c r="E1381" t="n">
-        <v>84.65000000000001</v>
+        <v>84.79000000000001</v>
       </c>
       <c r="F1381" t="n">
-        <v>69862</v>
+        <v>69177</v>
       </c>
     </row>
     <row r="1382">
@@ -28141,10 +28141,10 @@
         <v>86.17</v>
       </c>
       <c r="E1386" t="n">
-        <v>86.43000000000001</v>
+        <v>86.31999999999999</v>
       </c>
       <c r="F1386" t="n">
-        <v>68965</v>
+        <v>67919</v>
       </c>
     </row>
     <row r="1387">
@@ -28221,10 +28221,10 @@
         <v>84.16</v>
       </c>
       <c r="E1390" t="n">
-        <v>84.90000000000001</v>
+        <v>85.19</v>
       </c>
       <c r="F1390" t="n">
-        <v>78990</v>
+        <v>78243</v>
       </c>
     </row>
     <row r="1391">
@@ -28238,13 +28238,13 @@
         <v>85.67</v>
       </c>
       <c r="D1391" t="n">
-        <v>84.31999999999999</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="E1391" t="n">
-        <v>84.31999999999999</v>
+        <v>84.5</v>
       </c>
       <c r="F1391" t="n">
-        <v>74302</v>
+        <v>73607</v>
       </c>
     </row>
     <row r="1392">
@@ -28321,10 +28321,10 @@
         <v>83.41</v>
       </c>
       <c r="E1395" t="n">
-        <v>83.76000000000001</v>
+        <v>83.72</v>
       </c>
       <c r="F1395" t="n">
-        <v>69797</v>
+        <v>68620</v>
       </c>
     </row>
     <row r="1396">
@@ -28338,13 +28338,13 @@
         <v>84.41</v>
       </c>
       <c r="D1396" t="n">
-        <v>81.64</v>
+        <v>81.7</v>
       </c>
       <c r="E1396" t="n">
-        <v>81.64</v>
+        <v>81.89</v>
       </c>
       <c r="F1396" t="n">
-        <v>72736</v>
+        <v>72020</v>
       </c>
     </row>
     <row r="1397">
@@ -28421,10 +28421,10 @@
         <v>79.28</v>
       </c>
       <c r="E1400" t="n">
-        <v>81.37</v>
+        <v>81.33</v>
       </c>
       <c r="F1400" t="n">
-        <v>69789</v>
+        <v>69150</v>
       </c>
     </row>
     <row r="1401">
@@ -28441,10 +28441,10 @@
         <v>79.39</v>
       </c>
       <c r="E1401" t="n">
-        <v>79.48999999999999</v>
+        <v>79.92</v>
       </c>
       <c r="F1401" t="n">
-        <v>65748</v>
+        <v>64725</v>
       </c>
     </row>
     <row r="1402">
@@ -28521,10 +28521,10 @@
         <v>79.3</v>
       </c>
       <c r="E1405" t="n">
-        <v>79.83</v>
+        <v>80</v>
       </c>
       <c r="F1405" t="n">
-        <v>105741</v>
+        <v>104482</v>
       </c>
     </row>
     <row r="1406">
@@ -28541,10 +28541,10 @@
         <v>76.26000000000001</v>
       </c>
       <c r="E1406" t="n">
-        <v>77.14</v>
+        <v>77.08</v>
       </c>
       <c r="F1406" t="n">
-        <v>125792</v>
+        <v>124356</v>
       </c>
     </row>
     <row r="1407">
@@ -28621,10 +28621,10 @@
         <v>77.33</v>
       </c>
       <c r="E1410" t="n">
-        <v>78.59</v>
+        <v>78.73999999999999</v>
       </c>
       <c r="F1410" t="n">
-        <v>113892</v>
+        <v>113028</v>
       </c>
     </row>
     <row r="1411">
@@ -28641,10 +28641,10 @@
         <v>78.43000000000001</v>
       </c>
       <c r="E1411" t="n">
-        <v>79.27</v>
+        <v>79.34</v>
       </c>
       <c r="F1411" t="n">
-        <v>87467</v>
+        <v>86405</v>
       </c>
     </row>
     <row r="1412">
@@ -28721,10 +28721,10 @@
         <v>79.11</v>
       </c>
       <c r="E1415" t="n">
-        <v>80.26000000000001</v>
+        <v>80.31999999999999</v>
       </c>
       <c r="F1415" t="n">
-        <v>79567</v>
+        <v>78757</v>
       </c>
     </row>
     <row r="1416">
@@ -28741,10 +28741,10 @@
         <v>78.09</v>
       </c>
       <c r="E1416" t="n">
-        <v>78.94</v>
+        <v>79.22</v>
       </c>
       <c r="F1416" t="n">
-        <v>82030</v>
+        <v>81009</v>
       </c>
     </row>
     <row r="1417">
@@ -28821,10 +28821,10 @@
         <v>75.25</v>
       </c>
       <c r="E1420" t="n">
-        <v>76.42</v>
+        <v>76.47</v>
       </c>
       <c r="F1420" t="n">
-        <v>79873</v>
+        <v>79280</v>
       </c>
     </row>
     <row r="1421">
@@ -28841,10 +28841,10 @@
         <v>76.40000000000001</v>
       </c>
       <c r="E1421" t="n">
-        <v>78.13</v>
+        <v>78.17</v>
       </c>
       <c r="F1421" t="n">
-        <v>69081</v>
+        <v>68613</v>
       </c>
     </row>
     <row r="1422">
@@ -28921,10 +28921,10 @@
         <v>76.90000000000001</v>
       </c>
       <c r="E1425" t="n">
-        <v>78.72</v>
+        <v>78.81</v>
       </c>
       <c r="F1425" t="n">
-        <v>94397</v>
+        <v>93699</v>
       </c>
     </row>
     <row r="1426">
@@ -28941,10 +28941,10 @@
         <v>76.56</v>
       </c>
       <c r="E1426" t="n">
-        <v>76.77</v>
+        <v>76.81</v>
       </c>
       <c r="F1426" t="n">
-        <v>109124</v>
+        <v>108329</v>
       </c>
     </row>
     <row r="1427">
@@ -29021,10 +29021,10 @@
         <v>72.20999999999999</v>
       </c>
       <c r="E1430" t="n">
-        <v>72.53</v>
+        <v>72.54000000000001</v>
       </c>
       <c r="F1430" t="n">
-        <v>109541</v>
+        <v>108713</v>
       </c>
     </row>
     <row r="1431">
@@ -29041,10 +29041,10 @@
         <v>70.45</v>
       </c>
       <c r="E1431" t="n">
-        <v>71.2</v>
+        <v>71.37</v>
       </c>
       <c r="F1431" t="n">
-        <v>116954</v>
+        <v>115759</v>
       </c>
     </row>
     <row r="1432">
@@ -29121,10 +29121,10 @@
         <v>70.31999999999999</v>
       </c>
       <c r="E1435" t="n">
-        <v>71.67</v>
+        <v>71.89</v>
       </c>
       <c r="F1435" t="n">
-        <v>115156</v>
+        <v>114181</v>
       </c>
     </row>
     <row r="1436">
@@ -29141,10 +29141,10 @@
         <v>71.09</v>
       </c>
       <c r="E1436" t="n">
-        <v>71.59999999999999</v>
+        <v>71.73</v>
       </c>
       <c r="F1436" t="n">
-        <v>99629</v>
+        <v>98569</v>
       </c>
     </row>
     <row r="1437">
@@ -29221,10 +29221,10 @@
         <v>72.26000000000001</v>
       </c>
       <c r="E1440" t="n">
-        <v>73.97</v>
+        <v>74.05</v>
       </c>
       <c r="F1440" t="n">
-        <v>89094</v>
+        <v>88395</v>
       </c>
     </row>
     <row r="1441">
@@ -29241,10 +29241,10 @@
         <v>73.28</v>
       </c>
       <c r="E1441" t="n">
-        <v>73.87</v>
+        <v>73.98</v>
       </c>
       <c r="F1441" t="n">
-        <v>72413</v>
+        <v>71635</v>
       </c>
     </row>
     <row r="1442">
@@ -29321,10 +29321,10 @@
         <v>70.20999999999999</v>
       </c>
       <c r="E1445" t="n">
-        <v>70.68000000000001</v>
+        <v>70.66</v>
       </c>
       <c r="F1445" t="n">
-        <v>155899</v>
+        <v>154979</v>
       </c>
     </row>
     <row r="1446">
@@ -29335,16 +29335,16 @@
         <v>70.68000000000001</v>
       </c>
       <c r="C1446" t="n">
-        <v>71.90000000000001</v>
+        <v>71.89</v>
       </c>
       <c r="D1446" t="n">
         <v>70.39</v>
       </c>
       <c r="E1446" t="n">
-        <v>71.79000000000001</v>
+        <v>71.81999999999999</v>
       </c>
       <c r="F1446" t="n">
-        <v>123787</v>
+        <v>122438</v>
       </c>
     </row>
     <row r="1447">
@@ -29421,10 +29421,10 @@
         <v>74.18000000000001</v>
       </c>
       <c r="E1450" t="n">
-        <v>77.28</v>
+        <v>77.58</v>
       </c>
       <c r="F1450" t="n">
-        <v>125075</v>
+        <v>123449</v>
       </c>
     </row>
     <row r="1451">
@@ -29441,10 +29441,10 @@
         <v>77.19</v>
       </c>
       <c r="E1451" t="n">
-        <v>77.73</v>
+        <v>77.87</v>
       </c>
       <c r="F1451" t="n">
-        <v>121412</v>
+        <v>120535</v>
       </c>
     </row>
     <row r="1452">
@@ -38775,16 +38775,16 @@
         <v>82.93000000000001</v>
       </c>
       <c r="C1918" t="n">
-        <v>88.22</v>
+        <v>88.36</v>
       </c>
       <c r="D1918" t="n">
         <v>82.93000000000001</v>
       </c>
       <c r="E1918" t="n">
-        <v>87.68000000000001</v>
+        <v>87.92</v>
       </c>
       <c r="F1918" t="n">
-        <v>82895</v>
+        <v>95428</v>
       </c>
     </row>
   </sheetData>

--- a/database/BRENT.xlsx
+++ b/database/BRENT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1918"/>
+  <dimension ref="A1:F1919"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38784,7 +38784,27 @@
         <v>87.92</v>
       </c>
       <c r="F1918" t="n">
-        <v>95428</v>
+        <v>95407</v>
+      </c>
+    </row>
+    <row r="1919">
+      <c r="A1919" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B1919" t="n">
+        <v>87.53</v>
+      </c>
+      <c r="C1919" t="n">
+        <v>89.17</v>
+      </c>
+      <c r="D1919" t="n">
+        <v>85.95999999999999</v>
+      </c>
+      <c r="E1919" t="n">
+        <v>86.87</v>
+      </c>
+      <c r="F1919" t="n">
+        <v>118721</v>
       </c>
     </row>
   </sheetData>

--- a/database/BRENT.xlsx
+++ b/database/BRENT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1919"/>
+  <dimension ref="A1:F1920"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3881,10 +3881,10 @@
         <v>60.96</v>
       </c>
       <c r="E173" t="n">
-        <v>61.74</v>
+        <v>61.65</v>
       </c>
       <c r="F173" t="n">
-        <v>7439</v>
+        <v>7745</v>
       </c>
     </row>
     <row r="174">
@@ -3952,7 +3952,7 @@
         <v>43769</v>
       </c>
       <c r="B177" t="n">
-        <v>60.17</v>
+        <v>60.27</v>
       </c>
       <c r="C177" t="n">
         <v>60.79</v>
@@ -3964,7 +3964,7 @@
         <v>59.46</v>
       </c>
       <c r="F177" t="n">
-        <v>20831</v>
+        <v>20603</v>
       </c>
     </row>
     <row r="178">
@@ -3972,7 +3972,7 @@
         <v>43770</v>
       </c>
       <c r="B178" t="n">
-        <v>59.42</v>
+        <v>59.64</v>
       </c>
       <c r="C178" t="n">
         <v>61.8</v>
@@ -3984,7 +3984,7 @@
         <v>61.65</v>
       </c>
       <c r="F178" t="n">
-        <v>18539</v>
+        <v>18281</v>
       </c>
     </row>
     <row r="179">
@@ -4061,10 +4061,10 @@
         <v>61.63</v>
       </c>
       <c r="E182" t="n">
-        <v>62.14</v>
+        <v>62.29</v>
       </c>
       <c r="F182" t="n">
-        <v>19306</v>
+        <v>19680</v>
       </c>
     </row>
     <row r="183">
@@ -4081,10 +4081,10 @@
         <v>60.65</v>
       </c>
       <c r="E183" t="n">
-        <v>62.61</v>
+        <v>62.64</v>
       </c>
       <c r="F183" t="n">
-        <v>21625</v>
+        <v>21863</v>
       </c>
     </row>
     <row r="184">
@@ -4161,10 +4161,10 @@
         <v>62.14</v>
       </c>
       <c r="E187" t="n">
-        <v>62.38</v>
+        <v>62.33</v>
       </c>
       <c r="F187" t="n">
-        <v>19157</v>
+        <v>19293</v>
       </c>
     </row>
     <row r="188">
@@ -4181,10 +4181,10 @@
         <v>61.69</v>
       </c>
       <c r="E188" t="n">
-        <v>63.32</v>
+        <v>63.41</v>
       </c>
       <c r="F188" t="n">
-        <v>15801</v>
+        <v>16092</v>
       </c>
     </row>
     <row r="189">
@@ -4261,10 +4261,10 @@
         <v>61.91</v>
       </c>
       <c r="E192" t="n">
-        <v>63.74</v>
+        <v>63.64</v>
       </c>
       <c r="F192" t="n">
-        <v>21582</v>
+        <v>21823</v>
       </c>
     </row>
     <row r="193">
@@ -4281,10 +4281,10 @@
         <v>61.92</v>
       </c>
       <c r="E193" t="n">
-        <v>62.58</v>
+        <v>62.52</v>
       </c>
       <c r="F193" t="n">
-        <v>17577</v>
+        <v>17794</v>
       </c>
     </row>
     <row r="194">
@@ -4461,10 +4461,10 @@
         <v>62.73</v>
       </c>
       <c r="E202" t="n">
-        <v>63.33</v>
+        <v>63.26</v>
       </c>
       <c r="F202" t="n">
-        <v>24042</v>
+        <v>24300</v>
       </c>
     </row>
     <row r="203">
@@ -4481,10 +4481,10 @@
         <v>62.82</v>
       </c>
       <c r="E203" t="n">
-        <v>64.22</v>
+        <v>64.34</v>
       </c>
       <c r="F203" t="n">
-        <v>22359</v>
+        <v>22572</v>
       </c>
     </row>
     <row r="204">
@@ -4561,10 +4561,10 @@
         <v>63.86</v>
       </c>
       <c r="E207" t="n">
-        <v>64.31</v>
+        <v>64.28</v>
       </c>
       <c r="F207" t="n">
-        <v>18198</v>
+        <v>18454</v>
       </c>
     </row>
     <row r="208">
@@ -4581,10 +4581,10 @@
         <v>64.48</v>
       </c>
       <c r="E208" t="n">
-        <v>64.88</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="F208" t="n">
-        <v>21484</v>
+        <v>21671</v>
       </c>
     </row>
     <row r="209">
@@ -4661,10 +4661,10 @@
         <v>66.02</v>
       </c>
       <c r="E212" t="n">
-        <v>66.45</v>
+        <v>66.53</v>
       </c>
       <c r="F212" t="n">
-        <v>10932</v>
+        <v>11180</v>
       </c>
     </row>
     <row r="213">
@@ -4681,10 +4681,10 @@
         <v>65.72</v>
       </c>
       <c r="E213" t="n">
-        <v>65.98</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="F213" t="n">
-        <v>14693</v>
+        <v>14806</v>
       </c>
     </row>
     <row r="214">
@@ -4741,10 +4741,10 @@
         <v>66.09</v>
       </c>
       <c r="E216" t="n">
-        <v>66.65000000000001</v>
+        <v>66.75</v>
       </c>
       <c r="F216" t="n">
-        <v>9409</v>
+        <v>9613</v>
       </c>
     </row>
     <row r="217">
@@ -4761,10 +4761,10 @@
         <v>66.34</v>
       </c>
       <c r="E217" t="n">
-        <v>66.81</v>
+        <v>66.84</v>
       </c>
       <c r="F217" t="n">
-        <v>11272</v>
+        <v>11398</v>
       </c>
     </row>
     <row r="218">
@@ -4821,10 +4821,10 @@
         <v>65.7</v>
       </c>
       <c r="E220" t="n">
-        <v>66.19</v>
+        <v>66.23</v>
       </c>
       <c r="F220" t="n">
-        <v>15153</v>
+        <v>15351</v>
       </c>
     </row>
     <row r="221">
@@ -4841,10 +4841,10 @@
         <v>66.19</v>
       </c>
       <c r="E221" t="n">
-        <v>68.55</v>
+        <v>68.59</v>
       </c>
       <c r="F221" t="n">
-        <v>35427</v>
+        <v>35609</v>
       </c>
     </row>
     <row r="222">
@@ -4924,7 +4924,7 @@
         <v>65.38</v>
       </c>
       <c r="F225" t="n">
-        <v>25682</v>
+        <v>25951</v>
       </c>
     </row>
     <row r="226">
@@ -4944,7 +4944,7 @@
         <v>65</v>
       </c>
       <c r="F226" t="n">
-        <v>20016</v>
+        <v>20436</v>
       </c>
     </row>
     <row r="227">
@@ -5021,10 +5021,10 @@
         <v>63.89</v>
       </c>
       <c r="E230" t="n">
-        <v>64.64</v>
+        <v>64.7</v>
       </c>
       <c r="F230" t="n">
-        <v>16107</v>
+        <v>16472</v>
       </c>
     </row>
     <row r="231">
@@ -5041,10 +5041,10 @@
         <v>64.45</v>
       </c>
       <c r="E231" t="n">
-        <v>64.95</v>
+        <v>65.08</v>
       </c>
       <c r="F231" t="n">
-        <v>16060</v>
+        <v>16251</v>
       </c>
     </row>
     <row r="232">
@@ -5121,10 +5121,10 @@
         <v>61.24</v>
       </c>
       <c r="E235" t="n">
-        <v>61.97</v>
+        <v>62.11</v>
       </c>
       <c r="F235" t="n">
-        <v>22982</v>
+        <v>23208</v>
       </c>
     </row>
     <row r="236">
@@ -5141,10 +5141,10 @@
         <v>60.24</v>
       </c>
       <c r="E236" t="n">
-        <v>60.82</v>
+        <v>60.64</v>
       </c>
       <c r="F236" t="n">
-        <v>21411</v>
+        <v>21687</v>
       </c>
     </row>
     <row r="237">
@@ -5221,10 +5221,10 @@
         <v>56.73</v>
       </c>
       <c r="E240" t="n">
-        <v>58.03</v>
+        <v>58.2</v>
       </c>
       <c r="F240" t="n">
-        <v>28317</v>
+        <v>28894</v>
       </c>
     </row>
     <row r="241">
@@ -5244,7 +5244,7 @@
         <v>56.63</v>
       </c>
       <c r="F241" t="n">
-        <v>30854</v>
+        <v>31264</v>
       </c>
     </row>
     <row r="242">
@@ -5321,10 +5321,10 @@
         <v>54.24</v>
       </c>
       <c r="E245" t="n">
-        <v>55.07</v>
+        <v>55.14</v>
       </c>
       <c r="F245" t="n">
-        <v>31638</v>
+        <v>31917</v>
       </c>
     </row>
     <row r="246">
@@ -5341,10 +5341,10 @@
         <v>54.2</v>
       </c>
       <c r="E246" t="n">
-        <v>54.48</v>
+        <v>54.45</v>
       </c>
       <c r="F246" t="n">
-        <v>25828</v>
+        <v>26144</v>
       </c>
     </row>
     <row r="247">
@@ -5421,10 +5421,10 @@
         <v>54.95</v>
       </c>
       <c r="E250" t="n">
-        <v>56.51</v>
+        <v>56.4</v>
       </c>
       <c r="F250" t="n">
-        <v>24675</v>
+        <v>24914</v>
       </c>
     </row>
     <row r="251">
@@ -5441,10 +5441,10 @@
         <v>56.13</v>
       </c>
       <c r="E251" t="n">
-        <v>57.32</v>
+        <v>57.33</v>
       </c>
       <c r="F251" t="n">
-        <v>21410</v>
+        <v>21778</v>
       </c>
     </row>
     <row r="252">
@@ -5521,10 +5521,10 @@
         <v>58.89</v>
       </c>
       <c r="E255" t="n">
-        <v>59.28</v>
+        <v>59.03</v>
       </c>
       <c r="F255" t="n">
-        <v>23121</v>
+        <v>23391</v>
       </c>
     </row>
     <row r="256">
@@ -5541,10 +5541,10 @@
         <v>57.71</v>
       </c>
       <c r="E256" t="n">
-        <v>58.33</v>
+        <v>58.44</v>
       </c>
       <c r="F256" t="n">
-        <v>26663</v>
+        <v>26971</v>
       </c>
     </row>
     <row r="257">
@@ -5621,10 +5621,10 @@
         <v>50.38</v>
       </c>
       <c r="E260" t="n">
-        <v>51.35</v>
+        <v>50.95</v>
       </c>
       <c r="F260" t="n">
-        <v>51199</v>
+        <v>52807</v>
       </c>
     </row>
     <row r="261">
@@ -5641,10 +5641,10 @@
         <v>48.92</v>
       </c>
       <c r="E261" t="n">
-        <v>50.01</v>
+        <v>50.08</v>
       </c>
       <c r="F261" t="n">
-        <v>71739</v>
+        <v>72794</v>
       </c>
     </row>
     <row r="262">
@@ -5721,10 +5721,10 @@
         <v>49.67</v>
       </c>
       <c r="E265" t="n">
-        <v>49.95</v>
+        <v>50</v>
       </c>
       <c r="F265" t="n">
-        <v>42080</v>
+        <v>42678</v>
       </c>
     </row>
     <row r="266">
@@ -5741,10 +5741,10 @@
         <v>45.16</v>
       </c>
       <c r="E266" t="n">
-        <v>45.55</v>
+        <v>45.51</v>
       </c>
       <c r="F266" t="n">
-        <v>64437</v>
+        <v>65295</v>
       </c>
     </row>
     <row r="267">
@@ -5812,7 +5812,7 @@
         <v>43902</v>
       </c>
       <c r="B270" t="n">
-        <v>35.97</v>
+        <v>36.29</v>
       </c>
       <c r="C270" t="n">
         <v>36.45</v>
@@ -5824,7 +5824,7 @@
         <v>33.49</v>
       </c>
       <c r="F270" t="n">
-        <v>66181</v>
+        <v>64469</v>
       </c>
     </row>
     <row r="271">
@@ -6121,10 +6121,10 @@
         <v>26.12</v>
       </c>
       <c r="E285" t="n">
-        <v>30.29</v>
+        <v>29.96</v>
       </c>
       <c r="F285" t="n">
-        <v>210087</v>
+        <v>214756</v>
       </c>
     </row>
     <row r="286">
@@ -6135,16 +6135,16 @@
         <v>29.95</v>
       </c>
       <c r="C286" t="n">
-        <v>35.24</v>
+        <v>35.28</v>
       </c>
       <c r="D286" t="n">
         <v>28.9</v>
       </c>
       <c r="E286" t="n">
-        <v>34.72</v>
+        <v>35.16</v>
       </c>
       <c r="F286" t="n">
-        <v>275171</v>
+        <v>280402</v>
       </c>
     </row>
     <row r="287">
@@ -6221,10 +6221,10 @@
         <v>32.46</v>
       </c>
       <c r="E290" t="n">
-        <v>33.2</v>
+        <v>32.8</v>
       </c>
       <c r="F290" t="n">
-        <v>230614</v>
+        <v>236196</v>
       </c>
     </row>
     <row r="291">
@@ -6321,10 +6321,10 @@
         <v>29.42</v>
       </c>
       <c r="E295" t="n">
-        <v>30.65</v>
+        <v>30.59</v>
       </c>
       <c r="F295" t="n">
-        <v>146842</v>
+        <v>151526</v>
       </c>
     </row>
     <row r="296">
@@ -6341,10 +6341,10 @@
         <v>30.13</v>
       </c>
       <c r="E296" t="n">
-        <v>30.78</v>
+        <v>30.68</v>
       </c>
       <c r="F296" t="n">
-        <v>171223</v>
+        <v>174982</v>
       </c>
     </row>
     <row r="297">
@@ -6421,10 +6421,10 @@
         <v>23.38</v>
       </c>
       <c r="E300" t="n">
-        <v>24.74</v>
+        <v>24.73</v>
       </c>
       <c r="F300" t="n">
-        <v>213310</v>
+        <v>216653</v>
       </c>
     </row>
     <row r="301">
@@ -6441,10 +6441,10 @@
         <v>23.7</v>
       </c>
       <c r="E301" t="n">
-        <v>24.98</v>
+        <v>24.99</v>
       </c>
       <c r="F301" t="n">
-        <v>163124</v>
+        <v>166443</v>
       </c>
     </row>
     <row r="302">
@@ -6521,10 +6521,10 @@
         <v>24.33</v>
       </c>
       <c r="E305" t="n">
-        <v>26.83</v>
+        <v>26.85</v>
       </c>
       <c r="F305" t="n">
-        <v>224455</v>
+        <v>229615</v>
       </c>
     </row>
     <row r="306">
@@ -6541,10 +6541,10 @@
         <v>26.05</v>
       </c>
       <c r="E306" t="n">
-        <v>26.78</v>
+        <v>26.81</v>
       </c>
       <c r="F306" t="n">
-        <v>196748</v>
+        <v>199609</v>
       </c>
     </row>
     <row r="307">
@@ -6621,10 +6621,10 @@
         <v>29.4</v>
       </c>
       <c r="E310" t="n">
-        <v>29.48</v>
+        <v>29.65</v>
       </c>
       <c r="F310" t="n">
-        <v>225301</v>
+        <v>229585</v>
       </c>
     </row>
     <row r="311">
@@ -6641,10 +6641,10 @@
         <v>29.63</v>
       </c>
       <c r="E311" t="n">
-        <v>31.26</v>
+        <v>31.25</v>
       </c>
       <c r="F311" t="n">
-        <v>192233</v>
+        <v>195288</v>
       </c>
     </row>
     <row r="312">
@@ -6715,16 +6715,16 @@
         <v>29.73</v>
       </c>
       <c r="C315" t="n">
-        <v>31.65</v>
+        <v>31.75</v>
       </c>
       <c r="D315" t="n">
         <v>29.32</v>
       </c>
       <c r="E315" t="n">
-        <v>31.44</v>
+        <v>31.58</v>
       </c>
       <c r="F315" t="n">
-        <v>152193</v>
+        <v>156389</v>
       </c>
     </row>
     <row r="316">
@@ -6735,16 +6735,16 @@
         <v>31.58</v>
       </c>
       <c r="C316" t="n">
-        <v>32.96</v>
+        <v>33.06</v>
       </c>
       <c r="D316" t="n">
         <v>31.23</v>
       </c>
       <c r="E316" t="n">
-        <v>32.9</v>
+        <v>32.94</v>
       </c>
       <c r="F316" t="n">
-        <v>160121</v>
+        <v>163209</v>
       </c>
     </row>
     <row r="317">
@@ -6821,10 +6821,10 @@
         <v>35.92</v>
       </c>
       <c r="E320" t="n">
-        <v>36.38</v>
+        <v>36.3</v>
       </c>
       <c r="F320" t="n">
-        <v>157279</v>
+        <v>160329</v>
       </c>
     </row>
     <row r="321">
@@ -6841,10 +6841,10 @@
         <v>33.87</v>
       </c>
       <c r="E321" t="n">
-        <v>35.66</v>
+        <v>35.52</v>
       </c>
       <c r="F321" t="n">
-        <v>194062</v>
+        <v>198023</v>
       </c>
     </row>
     <row r="322">
@@ -6921,10 +6921,10 @@
         <v>34.37</v>
       </c>
       <c r="E325" t="n">
-        <v>35.89</v>
+        <v>35.98</v>
       </c>
       <c r="F325" t="n">
-        <v>208524</v>
+        <v>213086</v>
       </c>
     </row>
     <row r="326">
@@ -6941,10 +6941,10 @@
         <v>34.87</v>
       </c>
       <c r="E326" t="n">
-        <v>37.43</v>
+        <v>37.61</v>
       </c>
       <c r="F326" t="n">
-        <v>193664</v>
+        <v>198370</v>
       </c>
     </row>
     <row r="327">
@@ -7021,10 +7021,10 @@
         <v>39.05</v>
       </c>
       <c r="E330" t="n">
-        <v>39.78</v>
+        <v>39.92</v>
       </c>
       <c r="F330" t="n">
-        <v>158433</v>
+        <v>161661</v>
       </c>
     </row>
     <row r="331">
@@ -7041,10 +7041,10 @@
         <v>39.75</v>
       </c>
       <c r="E331" t="n">
-        <v>42.14</v>
+        <v>41.83</v>
       </c>
       <c r="F331" t="n">
-        <v>163467</v>
+        <v>167359</v>
       </c>
     </row>
     <row r="332">
@@ -7121,10 +7121,10 @@
         <v>37.96</v>
       </c>
       <c r="E335" t="n">
-        <v>38.36</v>
+        <v>38.41</v>
       </c>
       <c r="F335" t="n">
-        <v>221502</v>
+        <v>227925</v>
       </c>
     </row>
     <row r="336">
@@ -7141,10 +7141,10 @@
         <v>37.14</v>
       </c>
       <c r="E336" t="n">
-        <v>38.94</v>
+        <v>38.97</v>
       </c>
       <c r="F336" t="n">
-        <v>260674</v>
+        <v>263342</v>
       </c>
     </row>
     <row r="337">
@@ -7221,10 +7221,10 @@
         <v>40.05</v>
       </c>
       <c r="E340" t="n">
-        <v>41.37</v>
+        <v>41.33</v>
       </c>
       <c r="F340" t="n">
-        <v>161532</v>
+        <v>163774</v>
       </c>
     </row>
     <row r="341">
@@ -7241,10 +7241,10 @@
         <v>40.97</v>
       </c>
       <c r="E341" t="n">
-        <v>41.99</v>
+        <v>41.78</v>
       </c>
       <c r="F341" t="n">
-        <v>153177</v>
+        <v>156573</v>
       </c>
     </row>
     <row r="342">
@@ -7315,16 +7315,16 @@
         <v>40.45</v>
       </c>
       <c r="C345" t="n">
-        <v>41.51</v>
+        <v>41.59</v>
       </c>
       <c r="D345" t="n">
         <v>39.68</v>
       </c>
       <c r="E345" t="n">
-        <v>41.39</v>
+        <v>41.35</v>
       </c>
       <c r="F345" t="n">
-        <v>178413</v>
+        <v>181021</v>
       </c>
     </row>
     <row r="346">
@@ -7341,10 +7341,10 @@
         <v>40.25</v>
       </c>
       <c r="E346" t="n">
-        <v>40.58</v>
+        <v>40.57</v>
       </c>
       <c r="F346" t="n">
-        <v>157969</v>
+        <v>160433</v>
       </c>
     </row>
     <row r="347">
@@ -7421,10 +7421,10 @@
         <v>41.71</v>
       </c>
       <c r="E350" t="n">
-        <v>42.71</v>
+        <v>42.65</v>
       </c>
       <c r="F350" t="n">
-        <v>142409</v>
+        <v>144329</v>
       </c>
     </row>
     <row r="351">
@@ -7521,10 +7521,10 @@
         <v>41.99</v>
       </c>
       <c r="E355" t="n">
-        <v>42.32</v>
+        <v>42.35</v>
       </c>
       <c r="F355" t="n">
-        <v>133908</v>
+        <v>136451</v>
       </c>
     </row>
     <row r="356">
@@ -7541,10 +7541,10 @@
         <v>41.4</v>
       </c>
       <c r="E356" t="n">
-        <v>43.23</v>
+        <v>43.26</v>
       </c>
       <c r="F356" t="n">
-        <v>152491</v>
+        <v>154800</v>
       </c>
     </row>
     <row r="357">
@@ -7621,10 +7621,10 @@
         <v>43.19</v>
       </c>
       <c r="E360" t="n">
-        <v>43.36</v>
+        <v>43.28</v>
       </c>
       <c r="F360" t="n">
-        <v>99613</v>
+        <v>101544</v>
       </c>
     </row>
     <row r="361">
@@ -7641,10 +7641,10 @@
         <v>42.7</v>
       </c>
       <c r="E361" t="n">
-        <v>43.18</v>
+        <v>43.12</v>
       </c>
       <c r="F361" t="n">
-        <v>93740</v>
+        <v>95049</v>
       </c>
     </row>
     <row r="362">
@@ -7721,10 +7721,10 @@
         <v>43.42</v>
       </c>
       <c r="E365" t="n">
-        <v>43.82</v>
+        <v>43.53</v>
       </c>
       <c r="F365" t="n">
-        <v>109900</v>
+        <v>112495</v>
       </c>
     </row>
     <row r="366">
@@ -7741,10 +7741,10 @@
         <v>43.18</v>
       </c>
       <c r="E366" t="n">
-        <v>43.67</v>
+        <v>43.62</v>
       </c>
       <c r="F366" t="n">
-        <v>115737</v>
+        <v>117377</v>
       </c>
     </row>
     <row r="367">
@@ -7821,10 +7821,10 @@
         <v>41.95</v>
       </c>
       <c r="E370" t="n">
-        <v>43.43</v>
+        <v>43.56</v>
       </c>
       <c r="F370" t="n">
-        <v>113377</v>
+        <v>117072</v>
       </c>
     </row>
     <row r="371">
@@ -7841,10 +7841,10 @@
         <v>42.94</v>
       </c>
       <c r="E371" t="n">
-        <v>43.65</v>
+        <v>43.59</v>
       </c>
       <c r="F371" t="n">
-        <v>127155</v>
+        <v>128800</v>
       </c>
     </row>
     <row r="372">
@@ -7921,10 +7921,10 @@
         <v>44.96</v>
       </c>
       <c r="E375" t="n">
-        <v>45.28</v>
+        <v>45.13</v>
       </c>
       <c r="F375" t="n">
-        <v>120720</v>
+        <v>122044</v>
       </c>
     </row>
     <row r="376">
@@ -7941,10 +7941,10 @@
         <v>44.4</v>
       </c>
       <c r="E376" t="n">
-        <v>44.76</v>
+        <v>44.71</v>
       </c>
       <c r="F376" t="n">
-        <v>119541</v>
+        <v>120731</v>
       </c>
     </row>
     <row r="377">
@@ -8021,10 +8021,10 @@
         <v>45.07</v>
       </c>
       <c r="E380" t="n">
-        <v>45.3</v>
+        <v>45.24</v>
       </c>
       <c r="F380" t="n">
-        <v>90204</v>
+        <v>91702</v>
       </c>
     </row>
     <row r="381">
@@ -8041,10 +8041,10 @@
         <v>44.77</v>
       </c>
       <c r="E381" t="n">
-        <v>45.2</v>
+        <v>45.19</v>
       </c>
       <c r="F381" t="n">
-        <v>83793</v>
+        <v>85013</v>
       </c>
     </row>
     <row r="382">
@@ -8121,10 +8121,10 @@
         <v>44.46</v>
       </c>
       <c r="E385" t="n">
-        <v>45.36</v>
+        <v>45.27</v>
       </c>
       <c r="F385" t="n">
-        <v>86301</v>
+        <v>87294</v>
       </c>
     </row>
     <row r="386">
@@ -8141,10 +8141,10 @@
         <v>44.09</v>
       </c>
       <c r="E386" t="n">
-        <v>44.79</v>
+        <v>44.69</v>
       </c>
       <c r="F386" t="n">
-        <v>77659</v>
+        <v>78965</v>
       </c>
     </row>
     <row r="387">
@@ -8224,7 +8224,7 @@
         <v>45.59</v>
       </c>
       <c r="F390" t="n">
-        <v>95873</v>
+        <v>96916</v>
       </c>
     </row>
     <row r="391">
@@ -8241,10 +8241,10 @@
         <v>45.36</v>
       </c>
       <c r="E391" t="n">
-        <v>45.89</v>
+        <v>45.85</v>
       </c>
       <c r="F391" t="n">
-        <v>81058</v>
+        <v>81841</v>
       </c>
     </row>
     <row r="392">
@@ -8321,10 +8321,10 @@
         <v>43.27</v>
       </c>
       <c r="E395" t="n">
-        <v>44.09</v>
+        <v>44.07</v>
       </c>
       <c r="F395" t="n">
-        <v>157249</v>
+        <v>158723</v>
       </c>
     </row>
     <row r="396">
@@ -8338,13 +8338,13 @@
         <v>44.69</v>
       </c>
       <c r="D396" t="n">
-        <v>42.45</v>
+        <v>42.42</v>
       </c>
       <c r="E396" t="n">
-        <v>42.53</v>
+        <v>42.43</v>
       </c>
       <c r="F396" t="n">
-        <v>160902</v>
+        <v>162787</v>
       </c>
     </row>
     <row r="397">
@@ -8418,13 +8418,13 @@
         <v>41.23</v>
       </c>
       <c r="D400" t="n">
-        <v>40.02</v>
+        <v>39.96</v>
       </c>
       <c r="E400" t="n">
-        <v>40.07</v>
+        <v>39.97</v>
       </c>
       <c r="F400" t="n">
-        <v>147551</v>
+        <v>149451</v>
       </c>
     </row>
     <row r="401">
@@ -8441,10 +8441,10 @@
         <v>39.68</v>
       </c>
       <c r="E401" t="n">
-        <v>40.24</v>
+        <v>40.02</v>
       </c>
       <c r="F401" t="n">
-        <v>133943</v>
+        <v>135456</v>
       </c>
     </row>
     <row r="402">
@@ -8521,10 +8521,10 @@
         <v>41.89</v>
       </c>
       <c r="E405" t="n">
-        <v>43.67</v>
+        <v>43.58</v>
       </c>
       <c r="F405" t="n">
-        <v>141089</v>
+        <v>142611</v>
       </c>
     </row>
     <row r="406">
@@ -8541,10 +8541,10 @@
         <v>42.92</v>
       </c>
       <c r="E406" t="n">
-        <v>43.34</v>
+        <v>43.41</v>
       </c>
       <c r="F406" t="n">
-        <v>127380</v>
+        <v>129546</v>
       </c>
     </row>
     <row r="407">
@@ -8621,10 +8621,10 @@
         <v>41.68</v>
       </c>
       <c r="E410" t="n">
-        <v>42.27</v>
+        <v>42.16</v>
       </c>
       <c r="F410" t="n">
-        <v>132502</v>
+        <v>133961</v>
       </c>
     </row>
     <row r="411">
@@ -8641,10 +8641,10 @@
         <v>41.97</v>
       </c>
       <c r="E411" t="n">
-        <v>42.24</v>
+        <v>42.17</v>
       </c>
       <c r="F411" t="n">
-        <v>100264</v>
+        <v>102107</v>
       </c>
     </row>
     <row r="412">
@@ -8721,10 +8721,10 @@
         <v>39.98</v>
       </c>
       <c r="E415" t="n">
-        <v>40.93</v>
+        <v>40.75</v>
       </c>
       <c r="F415" t="n">
-        <v>155461</v>
+        <v>157712</v>
       </c>
     </row>
     <row r="416">
@@ -8741,10 +8741,10 @@
         <v>38.88</v>
       </c>
       <c r="E416" t="n">
-        <v>39.23</v>
+        <v>39.15</v>
       </c>
       <c r="F416" t="n">
-        <v>188336</v>
+        <v>190634</v>
       </c>
     </row>
     <row r="417">
@@ -8821,10 +8821,10 @@
         <v>42.02</v>
       </c>
       <c r="E420" t="n">
-        <v>43.54</v>
+        <v>43.52</v>
       </c>
       <c r="F420" t="n">
-        <v>110782</v>
+        <v>112342</v>
       </c>
     </row>
     <row r="421">
@@ -8841,10 +8841,10 @@
         <v>42.78</v>
       </c>
       <c r="E421" t="n">
-        <v>42.96</v>
+        <v>42.89</v>
       </c>
       <c r="F421" t="n">
-        <v>108274</v>
+        <v>109695</v>
       </c>
     </row>
     <row r="422">
@@ -8921,10 +8921,10 @@
         <v>41.79</v>
       </c>
       <c r="E425" t="n">
-        <v>43.38</v>
+        <v>43.26</v>
       </c>
       <c r="F425" t="n">
-        <v>146298</v>
+        <v>147757</v>
       </c>
     </row>
     <row r="426">
@@ -8941,10 +8941,10 @@
         <v>42.47</v>
       </c>
       <c r="E426" t="n">
-        <v>43.02</v>
+        <v>42.95</v>
       </c>
       <c r="F426" t="n">
-        <v>129338</v>
+        <v>130839</v>
       </c>
     </row>
     <row r="427">
@@ -9021,10 +9021,10 @@
         <v>41.72</v>
       </c>
       <c r="E430" t="n">
-        <v>42.71</v>
+        <v>42.59</v>
       </c>
       <c r="F430" t="n">
-        <v>108471</v>
+        <v>110171</v>
       </c>
     </row>
     <row r="431">
@@ -9041,10 +9041,10 @@
         <v>41.76</v>
       </c>
       <c r="E431" t="n">
-        <v>41.93</v>
+        <v>41.85</v>
       </c>
       <c r="F431" t="n">
-        <v>95688</v>
+        <v>97195</v>
       </c>
     </row>
     <row r="432">
@@ -9112,7 +9112,7 @@
         <v>44133</v>
       </c>
       <c r="B435" t="n">
-        <v>39.52</v>
+        <v>39.76</v>
       </c>
       <c r="C435" t="n">
         <v>39.97</v>
@@ -9124,7 +9124,7 @@
         <v>38.05</v>
       </c>
       <c r="F435" t="n">
-        <v>183949</v>
+        <v>179602</v>
       </c>
     </row>
     <row r="436">
@@ -9132,7 +9132,7 @@
         <v>44134</v>
       </c>
       <c r="B436" t="n">
-        <v>38.05</v>
+        <v>38.25</v>
       </c>
       <c r="C436" t="n">
         <v>38.72</v>
@@ -9144,7 +9144,7 @@
         <v>37.84</v>
       </c>
       <c r="F436" t="n">
-        <v>184633</v>
+        <v>181739</v>
       </c>
     </row>
     <row r="437">
@@ -9221,10 +9221,10 @@
         <v>40.42</v>
       </c>
       <c r="E440" t="n">
-        <v>40.82</v>
+        <v>40.68</v>
       </c>
       <c r="F440" t="n">
-        <v>155706</v>
+        <v>157779</v>
       </c>
     </row>
     <row r="441">
@@ -9241,10 +9241,10 @@
         <v>39.46</v>
       </c>
       <c r="E441" t="n">
-        <v>39.84</v>
+        <v>39.71</v>
       </c>
       <c r="F441" t="n">
-        <v>150078</v>
+        <v>151438</v>
       </c>
     </row>
     <row r="442">
@@ -9318,13 +9318,13 @@
         <v>44.59</v>
       </c>
       <c r="D445" t="n">
-        <v>43.42</v>
+        <v>43.35</v>
       </c>
       <c r="E445" t="n">
-        <v>43.49</v>
+        <v>43.38</v>
       </c>
       <c r="F445" t="n">
-        <v>144322</v>
+        <v>146964</v>
       </c>
     </row>
     <row r="446">
@@ -9338,13 +9338,13 @@
         <v>43.45</v>
       </c>
       <c r="D446" t="n">
-        <v>42.77</v>
+        <v>42.68</v>
       </c>
       <c r="E446" t="n">
-        <v>42.88</v>
+        <v>42.69</v>
       </c>
       <c r="F446" t="n">
-        <v>112789</v>
+        <v>114191</v>
       </c>
     </row>
     <row r="447">
@@ -9421,10 +9421,10 @@
         <v>43.87</v>
       </c>
       <c r="E450" t="n">
-        <v>44.44</v>
+        <v>44.21</v>
       </c>
       <c r="F450" t="n">
-        <v>111013</v>
+        <v>112468</v>
       </c>
     </row>
     <row r="451">
@@ -9441,10 +9441,10 @@
         <v>44.15</v>
       </c>
       <c r="E451" t="n">
-        <v>45.06</v>
+        <v>45.07</v>
       </c>
       <c r="F451" t="n">
-        <v>88612</v>
+        <v>90427</v>
       </c>
     </row>
     <row r="452">
@@ -9624,7 +9624,7 @@
         <v>48.65</v>
       </c>
       <c r="F460" t="n">
-        <v>119976</v>
+        <v>122403</v>
       </c>
     </row>
     <row r="461">
@@ -9641,10 +9641,10 @@
         <v>48.77</v>
       </c>
       <c r="E461" t="n">
-        <v>48.97</v>
+        <v>48.96</v>
       </c>
       <c r="F461" t="n">
-        <v>124413</v>
+        <v>125701</v>
       </c>
     </row>
     <row r="462">
@@ -9721,10 +9721,10 @@
         <v>48.79</v>
       </c>
       <c r="E465" t="n">
-        <v>50.26</v>
+        <v>50.25</v>
       </c>
       <c r="F465" t="n">
-        <v>130125</v>
+        <v>132386</v>
       </c>
     </row>
     <row r="466">
@@ -9741,10 +9741,10 @@
         <v>49.67</v>
       </c>
       <c r="E466" t="n">
-        <v>49.94</v>
+        <v>49.86</v>
       </c>
       <c r="F466" t="n">
-        <v>123293</v>
+        <v>124721</v>
       </c>
     </row>
     <row r="467">
@@ -9821,10 +9821,10 @@
         <v>51.06</v>
       </c>
       <c r="E470" t="n">
-        <v>51.55</v>
+        <v>51.46</v>
       </c>
       <c r="F470" t="n">
-        <v>100894</v>
+        <v>102867</v>
       </c>
     </row>
     <row r="471">
@@ -9841,10 +9841,10 @@
         <v>51.16</v>
       </c>
       <c r="E471" t="n">
-        <v>52.19</v>
+        <v>52.23</v>
       </c>
       <c r="F471" t="n">
-        <v>96861</v>
+        <v>98705</v>
       </c>
     </row>
     <row r="472">
@@ -10081,10 +10081,10 @@
         <v>53.88</v>
       </c>
       <c r="E483" t="n">
-        <v>54.45</v>
+        <v>54.34</v>
       </c>
       <c r="F483" t="n">
-        <v>140683</v>
+        <v>142258</v>
       </c>
     </row>
     <row r="484">
@@ -10095,16 +10095,16 @@
         <v>54.46</v>
       </c>
       <c r="C484" t="n">
-        <v>56.06</v>
+        <v>56.2</v>
       </c>
       <c r="D484" t="n">
         <v>54.3</v>
       </c>
       <c r="E484" t="n">
-        <v>56.02</v>
+        <v>56.11</v>
       </c>
       <c r="F484" t="n">
-        <v>151805</v>
+        <v>155413</v>
       </c>
     </row>
     <row r="485">
@@ -10181,10 +10181,10 @@
         <v>55.21</v>
       </c>
       <c r="E488" t="n">
-        <v>56.3</v>
+        <v>56.37</v>
       </c>
       <c r="F488" t="n">
-        <v>123090</v>
+        <v>125098</v>
       </c>
     </row>
     <row r="489">
@@ -10201,10 +10201,10 @@
         <v>54.63</v>
       </c>
       <c r="E489" t="n">
-        <v>54.94</v>
+        <v>54.75</v>
       </c>
       <c r="F489" t="n">
-        <v>133988</v>
+        <v>135898</v>
       </c>
     </row>
     <row r="490">
@@ -10281,10 +10281,10 @@
         <v>55.38</v>
       </c>
       <c r="E493" t="n">
-        <v>55.86</v>
+        <v>55.84</v>
       </c>
       <c r="F493" t="n">
-        <v>103188</v>
+        <v>104851</v>
       </c>
     </row>
     <row r="494">
@@ -10301,10 +10301,10 @@
         <v>54.38</v>
       </c>
       <c r="E494" t="n">
-        <v>55.08</v>
+        <v>54.88</v>
       </c>
       <c r="F494" t="n">
-        <v>133367</v>
+        <v>135622</v>
       </c>
     </row>
     <row r="495">
@@ -10378,13 +10378,13 @@
         <v>56.16</v>
       </c>
       <c r="D498" t="n">
-        <v>54.93</v>
+        <v>54.84</v>
       </c>
       <c r="E498" t="n">
-        <v>55</v>
+        <v>54.84</v>
       </c>
       <c r="F498" t="n">
-        <v>160473</v>
+        <v>162289</v>
       </c>
     </row>
     <row r="499">
@@ -10401,10 +10401,10 @@
         <v>54.84</v>
       </c>
       <c r="E499" t="n">
-        <v>55</v>
+        <v>54.93</v>
       </c>
       <c r="F499" t="n">
-        <v>160923</v>
+        <v>163671</v>
       </c>
     </row>
     <row r="500">
@@ -10481,10 +10481,10 @@
         <v>57.93</v>
       </c>
       <c r="E503" t="n">
-        <v>58.79</v>
+        <v>58.87</v>
       </c>
       <c r="F503" t="n">
-        <v>123567</v>
+        <v>125851</v>
       </c>
     </row>
     <row r="504">
@@ -10501,10 +10501,10 @@
         <v>58.87</v>
       </c>
       <c r="E504" t="n">
-        <v>59.31</v>
+        <v>59.41</v>
       </c>
       <c r="F504" t="n">
-        <v>118436</v>
+        <v>120954</v>
       </c>
     </row>
     <row r="505">
@@ -10578,13 +10578,13 @@
         <v>61.23</v>
       </c>
       <c r="D508" t="n">
-        <v>60.5</v>
+        <v>60.44</v>
       </c>
       <c r="E508" t="n">
-        <v>60.6</v>
+        <v>60.52</v>
       </c>
       <c r="F508" t="n">
-        <v>104511</v>
+        <v>107974</v>
       </c>
     </row>
     <row r="509">
@@ -10604,7 +10604,7 @@
         <v>62.22</v>
       </c>
       <c r="F509" t="n">
-        <v>123306</v>
+        <v>126905</v>
       </c>
     </row>
     <row r="510">
@@ -10681,10 +10681,10 @@
         <v>62.54</v>
       </c>
       <c r="E513" t="n">
-        <v>62.75</v>
+        <v>62.88</v>
       </c>
       <c r="F513" t="n">
-        <v>170306</v>
+        <v>173632</v>
       </c>
     </row>
     <row r="514">
@@ -10701,10 +10701,10 @@
         <v>61.42</v>
       </c>
       <c r="E514" t="n">
-        <v>61.95</v>
+        <v>61.97</v>
       </c>
       <c r="F514" t="n">
-        <v>181146</v>
+        <v>184306</v>
       </c>
     </row>
     <row r="515">
@@ -10781,10 +10781,10 @@
         <v>65.55</v>
       </c>
       <c r="E518" t="n">
-        <v>65.86</v>
+        <v>65.97</v>
       </c>
       <c r="F518" t="n">
-        <v>210726</v>
+        <v>215533</v>
       </c>
     </row>
     <row r="519">
@@ -10801,10 +10801,10 @@
         <v>64.13</v>
       </c>
       <c r="E519" t="n">
-        <v>64.25</v>
+        <v>64.27</v>
       </c>
       <c r="F519" t="n">
-        <v>234931</v>
+        <v>239274</v>
       </c>
     </row>
     <row r="520">
@@ -10881,10 +10881,10 @@
         <v>63.17</v>
       </c>
       <c r="E523" t="n">
-        <v>66.94</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="F523" t="n">
-        <v>225843</v>
+        <v>230530</v>
       </c>
     </row>
     <row r="524">
@@ -10895,16 +10895,16 @@
         <v>66.86</v>
       </c>
       <c r="C524" t="n">
-        <v>69.31999999999999</v>
+        <v>69.41</v>
       </c>
       <c r="D524" t="n">
         <v>66.43000000000001</v>
       </c>
       <c r="E524" t="n">
-        <v>69.28</v>
+        <v>69.25</v>
       </c>
       <c r="F524" t="n">
-        <v>249828</v>
+        <v>253026</v>
       </c>
     </row>
     <row r="525">
@@ -10981,10 +10981,10 @@
         <v>67.68000000000001</v>
       </c>
       <c r="E528" t="n">
-        <v>69.40000000000001</v>
+        <v>69.17</v>
       </c>
       <c r="F528" t="n">
-        <v>160838</v>
+        <v>163581</v>
       </c>
     </row>
     <row r="529">
@@ -11001,10 +11001,10 @@
         <v>68.66</v>
       </c>
       <c r="E529" t="n">
-        <v>68.88</v>
+        <v>68.81</v>
       </c>
       <c r="F529" t="n">
-        <v>148823</v>
+        <v>151042</v>
       </c>
     </row>
     <row r="530">
@@ -11072,7 +11072,7 @@
         <v>44273</v>
       </c>
       <c r="B533" t="n">
-        <v>67.48</v>
+        <v>67.47</v>
       </c>
       <c r="C533" t="n">
         <v>67.83</v>
@@ -11084,7 +11084,7 @@
         <v>62.5</v>
       </c>
       <c r="F533" t="n">
-        <v>212082</v>
+        <v>209835</v>
       </c>
     </row>
     <row r="534">
@@ -11092,7 +11092,7 @@
         <v>44274</v>
       </c>
       <c r="B534" t="n">
-        <v>62.78</v>
+        <v>63.02</v>
       </c>
       <c r="C534" t="n">
         <v>64.73</v>
@@ -11104,7 +11104,7 @@
         <v>64.31999999999999</v>
       </c>
       <c r="F534" t="n">
-        <v>228148</v>
+        <v>223529</v>
       </c>
     </row>
     <row r="535">
@@ -11172,10 +11172,10 @@
         <v>44280</v>
       </c>
       <c r="B538" t="n">
-        <v>63.95</v>
+        <v>63.89</v>
       </c>
       <c r="C538" t="n">
-        <v>64.01000000000001</v>
+        <v>63.9</v>
       </c>
       <c r="D538" t="n">
         <v>60.82</v>
@@ -11184,7 +11184,7 @@
         <v>61.47</v>
       </c>
       <c r="F538" t="n">
-        <v>206155</v>
+        <v>203253</v>
       </c>
     </row>
     <row r="539">
@@ -11192,19 +11192,19 @@
         <v>44281</v>
       </c>
       <c r="B539" t="n">
-        <v>61.47</v>
+        <v>62.45</v>
       </c>
       <c r="C539" t="n">
         <v>64.73</v>
       </c>
       <c r="D539" t="n">
-        <v>61.47</v>
+        <v>62.07</v>
       </c>
       <c r="E539" t="n">
         <v>64.19</v>
       </c>
       <c r="F539" t="n">
-        <v>171041</v>
+        <v>167422</v>
       </c>
     </row>
     <row r="540">
@@ -11284,7 +11284,7 @@
         <v>64.51000000000001</v>
       </c>
       <c r="F543" t="n">
-        <v>197783</v>
+        <v>201289</v>
       </c>
     </row>
     <row r="544">
@@ -11361,10 +11361,10 @@
         <v>62.18</v>
       </c>
       <c r="E547" t="n">
-        <v>63.07</v>
+        <v>63.04</v>
       </c>
       <c r="F547" t="n">
-        <v>146277</v>
+        <v>149186</v>
       </c>
     </row>
     <row r="548">
@@ -11381,10 +11381,10 @@
         <v>62.33</v>
       </c>
       <c r="E548" t="n">
-        <v>62.81</v>
+        <v>62.76</v>
       </c>
       <c r="F548" t="n">
-        <v>119219</v>
+        <v>121247</v>
       </c>
     </row>
     <row r="549">
@@ -11461,10 +11461,10 @@
         <v>65.65000000000001</v>
       </c>
       <c r="E552" t="n">
-        <v>66.5</v>
+        <v>66.45</v>
       </c>
       <c r="F552" t="n">
-        <v>133306</v>
+        <v>135521</v>
       </c>
     </row>
     <row r="553">
@@ -11481,10 +11481,10 @@
         <v>66.11</v>
       </c>
       <c r="E553" t="n">
-        <v>66.40000000000001</v>
+        <v>66.31999999999999</v>
       </c>
       <c r="F553" t="n">
-        <v>120895</v>
+        <v>122938</v>
       </c>
     </row>
     <row r="554">
@@ -11564,7 +11564,7 @@
         <v>64.95</v>
       </c>
       <c r="F557" t="n">
-        <v>140975</v>
+        <v>143350</v>
       </c>
     </row>
     <row r="558">
@@ -11581,10 +11581,10 @@
         <v>64.52</v>
       </c>
       <c r="E558" t="n">
-        <v>65.45</v>
+        <v>65.31999999999999</v>
       </c>
       <c r="F558" t="n">
-        <v>124432</v>
+        <v>126302</v>
       </c>
     </row>
     <row r="559">
@@ -11661,10 +11661,10 @@
         <v>66.56</v>
       </c>
       <c r="E562" t="n">
-        <v>67.86</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="F562" t="n">
-        <v>157092</v>
+        <v>160482</v>
       </c>
     </row>
     <row r="563">
@@ -11681,10 +11681,10 @@
         <v>66.17</v>
       </c>
       <c r="E563" t="n">
-        <v>66.56</v>
+        <v>66.53</v>
       </c>
       <c r="F563" t="n">
-        <v>145779</v>
+        <v>148372</v>
       </c>
     </row>
     <row r="564">
@@ -11761,10 +11761,10 @@
         <v>67.77</v>
       </c>
       <c r="E567" t="n">
-        <v>68.05</v>
+        <v>68.03</v>
       </c>
       <c r="F567" t="n">
-        <v>153533</v>
+        <v>155507</v>
       </c>
     </row>
     <row r="568">
@@ -11784,7 +11784,7 @@
         <v>68.03</v>
       </c>
       <c r="F568" t="n">
-        <v>136012</v>
+        <v>139157</v>
       </c>
     </row>
     <row r="569">
@@ -11861,10 +11861,10 @@
         <v>66.34</v>
       </c>
       <c r="E572" t="n">
-        <v>66.83</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="F572" t="n">
-        <v>180093</v>
+        <v>182316</v>
       </c>
     </row>
     <row r="573">
@@ -11875,16 +11875,16 @@
         <v>66.81</v>
       </c>
       <c r="C573" t="n">
-        <v>68.52</v>
+        <v>68.63</v>
       </c>
       <c r="D573" t="n">
         <v>66.36</v>
       </c>
       <c r="E573" t="n">
-        <v>68.45</v>
+        <v>68.52</v>
       </c>
       <c r="F573" t="n">
-        <v>139950</v>
+        <v>142226</v>
       </c>
     </row>
     <row r="574">
@@ -11958,13 +11958,13 @@
         <v>67.02</v>
       </c>
       <c r="D577" t="n">
-        <v>64.73</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="E577" t="n">
-        <v>64.98999999999999</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="F577" t="n">
-        <v>164782</v>
+        <v>168733</v>
       </c>
     </row>
     <row r="578">
@@ -11981,10 +11981,10 @@
         <v>64.48</v>
       </c>
       <c r="E578" t="n">
-        <v>66.58</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="F578" t="n">
-        <v>153693</v>
+        <v>156317</v>
       </c>
     </row>
     <row r="579">
@@ -12055,16 +12055,16 @@
         <v>68.58</v>
       </c>
       <c r="C582" t="n">
-        <v>69.18000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="D582" t="n">
         <v>67.89</v>
       </c>
       <c r="E582" t="n">
-        <v>69.05</v>
+        <v>69.12</v>
       </c>
       <c r="F582" t="n">
-        <v>119490</v>
+        <v>122427</v>
       </c>
     </row>
     <row r="583">
@@ -12081,10 +12081,10 @@
         <v>68.48999999999999</v>
       </c>
       <c r="E583" t="n">
-        <v>68.89</v>
+        <v>68.88</v>
       </c>
       <c r="F583" t="n">
-        <v>119218</v>
+        <v>121324</v>
       </c>
     </row>
     <row r="584">
@@ -12161,10 +12161,10 @@
         <v>70.5</v>
       </c>
       <c r="E587" t="n">
-        <v>71.20999999999999</v>
+        <v>71.22</v>
       </c>
       <c r="F587" t="n">
-        <v>126247</v>
+        <v>128649</v>
       </c>
     </row>
     <row r="588">
@@ -12181,10 +12181,10 @@
         <v>70.58</v>
       </c>
       <c r="E588" t="n">
-        <v>71.47</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="F588" t="n">
-        <v>113793</v>
+        <v>117041</v>
       </c>
     </row>
     <row r="589">
@@ -12261,10 +12261,10 @@
         <v>70.66</v>
       </c>
       <c r="E592" t="n">
-        <v>72.09</v>
+        <v>71.95</v>
       </c>
       <c r="F592" t="n">
-        <v>146487</v>
+        <v>148450</v>
       </c>
     </row>
     <row r="593">
@@ -12284,7 +12284,7 @@
         <v>72.23999999999999</v>
       </c>
       <c r="F593" t="n">
-        <v>140128</v>
+        <v>142367</v>
       </c>
     </row>
     <row r="594">
@@ -12361,10 +12361,10 @@
         <v>71.41</v>
       </c>
       <c r="E597" t="n">
-        <v>72.45</v>
+        <v>72.44</v>
       </c>
       <c r="F597" t="n">
-        <v>175025</v>
+        <v>178094</v>
       </c>
     </row>
     <row r="598">
@@ -12381,10 +12381,10 @@
         <v>71.55</v>
       </c>
       <c r="E598" t="n">
-        <v>72.76000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="F598" t="n">
-        <v>147859</v>
+        <v>151345</v>
       </c>
     </row>
     <row r="599">
@@ -12461,10 +12461,10 @@
         <v>73.83</v>
       </c>
       <c r="E602" t="n">
-        <v>74.79000000000001</v>
+        <v>74.81</v>
       </c>
       <c r="F602" t="n">
-        <v>84577</v>
+        <v>85692</v>
       </c>
     </row>
     <row r="603">
@@ -12481,10 +12481,10 @@
         <v>74.14</v>
       </c>
       <c r="E603" t="n">
-        <v>75.27</v>
+        <v>75.28</v>
       </c>
       <c r="F603" t="n">
-        <v>77990</v>
+        <v>79112</v>
       </c>
     </row>
     <row r="604">
@@ -12561,10 +12561,10 @@
         <v>74.36</v>
       </c>
       <c r="E607" t="n">
-        <v>75.33</v>
+        <v>75.34</v>
       </c>
       <c r="F607" t="n">
-        <v>134296</v>
+        <v>135699</v>
       </c>
     </row>
     <row r="608">
@@ -12581,10 +12581,10 @@
         <v>75</v>
       </c>
       <c r="E608" t="n">
-        <v>76.02</v>
+        <v>75.81999999999999</v>
       </c>
       <c r="F608" t="n">
-        <v>102316</v>
+        <v>104256</v>
       </c>
     </row>
     <row r="609">
@@ -12655,16 +12655,16 @@
         <v>72.97</v>
       </c>
       <c r="C612" t="n">
-        <v>73.97</v>
+        <v>74.02</v>
       </c>
       <c r="D612" t="n">
         <v>71.73999999999999</v>
       </c>
       <c r="E612" t="n">
-        <v>73.92</v>
+        <v>73.95999999999999</v>
       </c>
       <c r="F612" t="n">
-        <v>136419</v>
+        <v>138030</v>
       </c>
     </row>
     <row r="613">
@@ -12681,10 +12681,10 @@
         <v>73.38</v>
       </c>
       <c r="E613" t="n">
-        <v>75.15000000000001</v>
+        <v>75.14</v>
       </c>
       <c r="F613" t="n">
-        <v>95892</v>
+        <v>96988</v>
       </c>
     </row>
     <row r="614">
@@ -12761,10 +12761,10 @@
         <v>72.70999999999999</v>
       </c>
       <c r="E617" t="n">
-        <v>72.79000000000001</v>
+        <v>72.72</v>
       </c>
       <c r="F617" t="n">
-        <v>132350</v>
+        <v>134216</v>
       </c>
     </row>
     <row r="618">
@@ -12781,10 +12781,10 @@
         <v>71.88</v>
       </c>
       <c r="E618" t="n">
-        <v>72.81</v>
+        <v>72.64</v>
       </c>
       <c r="F618" t="n">
-        <v>108307</v>
+        <v>110158</v>
       </c>
     </row>
     <row r="619">
@@ -12864,7 +12864,7 @@
         <v>73.01000000000001</v>
       </c>
       <c r="F622" t="n">
-        <v>113951</v>
+        <v>115159</v>
       </c>
     </row>
     <row r="623">
@@ -12875,16 +12875,16 @@
         <v>72.98</v>
       </c>
       <c r="C623" t="n">
-        <v>73.52</v>
+        <v>73.56999999999999</v>
       </c>
       <c r="D623" t="n">
         <v>72.70999999999999</v>
       </c>
       <c r="E623" t="n">
-        <v>73.44</v>
+        <v>73.5</v>
       </c>
       <c r="F623" t="n">
-        <v>83411</v>
+        <v>84579</v>
       </c>
     </row>
     <row r="624">
@@ -12961,10 +12961,10 @@
         <v>73.59999999999999</v>
       </c>
       <c r="E627" t="n">
-        <v>74.97</v>
+        <v>74.75</v>
       </c>
       <c r="F627" t="n">
-        <v>79720</v>
+        <v>81467</v>
       </c>
     </row>
     <row r="628">
@@ -12981,10 +12981,10 @@
         <v>74.26000000000001</v>
       </c>
       <c r="E628" t="n">
-        <v>74.98999999999999</v>
+        <v>74.95999999999999</v>
       </c>
       <c r="F628" t="n">
-        <v>83101</v>
+        <v>84253</v>
       </c>
     </row>
     <row r="629">
@@ -13061,10 +13061,10 @@
         <v>69.56</v>
       </c>
       <c r="E632" t="n">
-        <v>71.16</v>
+        <v>71</v>
       </c>
       <c r="F632" t="n">
-        <v>107034</v>
+        <v>108267</v>
       </c>
     </row>
     <row r="633">
@@ -13078,13 +13078,13 @@
         <v>72.22</v>
       </c>
       <c r="D633" t="n">
-        <v>70.12</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="E633" t="n">
-        <v>70.34999999999999</v>
+        <v>70.08</v>
       </c>
       <c r="F633" t="n">
-        <v>111453</v>
+        <v>113105</v>
       </c>
     </row>
     <row r="634">
@@ -13161,10 +13161,10 @@
         <v>70.41</v>
       </c>
       <c r="E637" t="n">
-        <v>70.90000000000001</v>
+        <v>70.86</v>
       </c>
       <c r="F637" t="n">
-        <v>95219</v>
+        <v>96203</v>
       </c>
     </row>
     <row r="638">
@@ -13181,10 +13181,10 @@
         <v>69.73999999999999</v>
       </c>
       <c r="E638" t="n">
-        <v>69.92</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="F638" t="n">
-        <v>93960</v>
+        <v>95696</v>
       </c>
     </row>
     <row r="639">
@@ -13261,10 +13261,10 @@
         <v>65.2</v>
       </c>
       <c r="E642" t="n">
-        <v>66.51000000000001</v>
+        <v>66.23</v>
       </c>
       <c r="F642" t="n">
-        <v>185678</v>
+        <v>187712</v>
       </c>
     </row>
     <row r="643">
@@ -13278,13 +13278,13 @@
         <v>66.54000000000001</v>
       </c>
       <c r="D643" t="n">
-        <v>64.61</v>
+        <v>64.53</v>
       </c>
       <c r="E643" t="n">
-        <v>64.62</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="F643" t="n">
-        <v>137258</v>
+        <v>138989</v>
       </c>
     </row>
     <row r="644">
@@ -13361,10 +13361,10 @@
         <v>69.73999999999999</v>
       </c>
       <c r="E647" t="n">
-        <v>70.56</v>
+        <v>70.45999999999999</v>
       </c>
       <c r="F647" t="n">
-        <v>113839</v>
+        <v>115965</v>
       </c>
     </row>
     <row r="648">
@@ -13381,10 +13381,10 @@
         <v>70.16</v>
       </c>
       <c r="E648" t="n">
-        <v>71.59999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="F648" t="n">
-        <v>99158</v>
+        <v>100455</v>
       </c>
     </row>
     <row r="649">
@@ -13461,10 +13461,10 @@
         <v>70.75</v>
       </c>
       <c r="E652" t="n">
-        <v>72.56999999999999</v>
+        <v>72.61</v>
       </c>
       <c r="F652" t="n">
-        <v>103772</v>
+        <v>105073</v>
       </c>
     </row>
     <row r="653">
@@ -13481,10 +13481,10 @@
         <v>72.20999999999999</v>
       </c>
       <c r="E653" t="n">
-        <v>72.36</v>
+        <v>72.20999999999999</v>
       </c>
       <c r="F653" t="n">
-        <v>110684</v>
+        <v>111688</v>
       </c>
     </row>
     <row r="654">
@@ -13561,10 +13561,10 @@
         <v>70.54000000000001</v>
       </c>
       <c r="E657" t="n">
-        <v>70.95</v>
+        <v>70.84</v>
       </c>
       <c r="F657" t="n">
-        <v>136836</v>
+        <v>138553</v>
       </c>
     </row>
     <row r="658">
@@ -13581,10 +13581,10 @@
         <v>70.59</v>
       </c>
       <c r="E658" t="n">
-        <v>72.44</v>
+        <v>72.51000000000001</v>
       </c>
       <c r="F658" t="n">
-        <v>106315</v>
+        <v>107925</v>
       </c>
     </row>
     <row r="659">
@@ -13661,10 +13661,10 @@
         <v>74.02</v>
       </c>
       <c r="E662" t="n">
-        <v>75.17</v>
+        <v>75.09</v>
       </c>
       <c r="F662" t="n">
-        <v>134873</v>
+        <v>136265</v>
       </c>
     </row>
     <row r="663">
@@ -13681,10 +13681,10 @@
         <v>74.06999999999999</v>
       </c>
       <c r="E663" t="n">
-        <v>74.79000000000001</v>
+        <v>74.67</v>
       </c>
       <c r="F663" t="n">
-        <v>129577</v>
+        <v>131243</v>
       </c>
     </row>
     <row r="664">
@@ -13764,7 +13764,7 @@
         <v>76.45</v>
       </c>
       <c r="F667" t="n">
-        <v>102612</v>
+        <v>104066</v>
       </c>
     </row>
     <row r="668">
@@ -13781,10 +13781,10 @@
         <v>76.09</v>
       </c>
       <c r="E668" t="n">
-        <v>77.15000000000001</v>
+        <v>77.13</v>
       </c>
       <c r="F668" t="n">
-        <v>93448</v>
+        <v>94529</v>
       </c>
     </row>
     <row r="669">
@@ -13861,10 +13861,10 @@
         <v>76.37</v>
       </c>
       <c r="E672" t="n">
-        <v>78.13</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="F672" t="n">
-        <v>180155</v>
+        <v>181989</v>
       </c>
     </row>
     <row r="673">
@@ -13881,10 +13881,10 @@
         <v>77.38</v>
       </c>
       <c r="E673" t="n">
-        <v>78.98999999999999</v>
+        <v>78.93000000000001</v>
       </c>
       <c r="F673" t="n">
-        <v>149729</v>
+        <v>151482</v>
       </c>
     </row>
     <row r="674">
@@ -13961,10 +13961,10 @@
         <v>78.78</v>
       </c>
       <c r="E677" t="n">
-        <v>82.16</v>
+        <v>82.08</v>
       </c>
       <c r="F677" t="n">
-        <v>151677</v>
+        <v>153620</v>
       </c>
     </row>
     <row r="678">
@@ -13981,10 +13981,10 @@
         <v>81.63</v>
       </c>
       <c r="E678" t="n">
-        <v>82.17</v>
+        <v>82.22</v>
       </c>
       <c r="F678" t="n">
-        <v>147722</v>
+        <v>149526</v>
       </c>
     </row>
     <row r="679">
@@ -14061,10 +14061,10 @@
         <v>82.76000000000001</v>
       </c>
       <c r="E682" t="n">
-        <v>83.69</v>
+        <v>83.67</v>
       </c>
       <c r="F682" t="n">
-        <v>120650</v>
+        <v>122153</v>
       </c>
     </row>
     <row r="683">
@@ -14081,10 +14081,10 @@
         <v>83.68000000000001</v>
       </c>
       <c r="E683" t="n">
-        <v>84.23</v>
+        <v>84.33</v>
       </c>
       <c r="F683" t="n">
-        <v>114060</v>
+        <v>116437</v>
       </c>
     </row>
     <row r="684">
@@ -14161,10 +14161,10 @@
         <v>82.73</v>
       </c>
       <c r="E687" t="n">
-        <v>84.15000000000001</v>
+        <v>84.09</v>
       </c>
       <c r="F687" t="n">
-        <v>121250</v>
+        <v>122966</v>
       </c>
     </row>
     <row r="688">
@@ -14175,16 +14175,16 @@
         <v>83.81999999999999</v>
       </c>
       <c r="C688" t="n">
-        <v>84.97</v>
+        <v>85.08</v>
       </c>
       <c r="D688" t="n">
         <v>83.18000000000001</v>
       </c>
       <c r="E688" t="n">
-        <v>84.97</v>
+        <v>84.83</v>
       </c>
       <c r="F688" t="n">
-        <v>111475</v>
+        <v>113449</v>
       </c>
     </row>
     <row r="689">
@@ -14261,10 +14261,10 @@
         <v>81.48</v>
       </c>
       <c r="E692" t="n">
-        <v>83.83</v>
+        <v>83.78</v>
       </c>
       <c r="F692" t="n">
-        <v>164605</v>
+        <v>167007</v>
       </c>
     </row>
     <row r="693">
@@ -14281,10 +14281,10 @@
         <v>82.39</v>
       </c>
       <c r="E693" t="n">
-        <v>83.55</v>
+        <v>83.41</v>
       </c>
       <c r="F693" t="n">
-        <v>132228</v>
+        <v>133535</v>
       </c>
     </row>
     <row r="694">
@@ -14352,7 +14352,7 @@
         <v>44504</v>
       </c>
       <c r="B697" t="n">
-        <v>81.12</v>
+        <v>80.83</v>
       </c>
       <c r="C697" t="n">
         <v>84.08</v>
@@ -14364,7 +14364,7 @@
         <v>80.54000000000001</v>
       </c>
       <c r="F697" t="n">
-        <v>171378</v>
+        <v>168783</v>
       </c>
     </row>
     <row r="698">
@@ -14372,7 +14372,7 @@
         <v>44505</v>
       </c>
       <c r="B698" t="n">
-        <v>80.95</v>
+        <v>81.04000000000001</v>
       </c>
       <c r="C698" t="n">
         <v>82.72</v>
@@ -14384,7 +14384,7 @@
         <v>81.93000000000001</v>
       </c>
       <c r="F698" t="n">
-        <v>166390</v>
+        <v>163172</v>
       </c>
     </row>
     <row r="699">
@@ -14461,10 +14461,10 @@
         <v>81.06</v>
       </c>
       <c r="E702" t="n">
-        <v>81.91</v>
+        <v>81.92</v>
       </c>
       <c r="F702" t="n">
-        <v>159955</v>
+        <v>161511</v>
       </c>
     </row>
     <row r="703">
@@ -14481,10 +14481,10 @@
         <v>80.63</v>
       </c>
       <c r="E703" t="n">
-        <v>81.41</v>
+        <v>81.29000000000001</v>
       </c>
       <c r="F703" t="n">
-        <v>133196</v>
+        <v>134507</v>
       </c>
     </row>
     <row r="704">
@@ -14561,10 +14561,10 @@
         <v>78.55</v>
       </c>
       <c r="E707" t="n">
-        <v>80.42</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="F707" t="n">
-        <v>131123</v>
+        <v>132952</v>
       </c>
     </row>
     <row r="708">
@@ -14581,10 +14581,10 @@
         <v>77.41</v>
       </c>
       <c r="E708" t="n">
-        <v>77.76000000000001</v>
+        <v>77.77</v>
       </c>
       <c r="F708" t="n">
-        <v>175625</v>
+        <v>177513</v>
       </c>
     </row>
     <row r="709">
@@ -14761,10 +14761,10 @@
         <v>65.67</v>
       </c>
       <c r="E717" t="n">
-        <v>69.94</v>
+        <v>70.36</v>
       </c>
       <c r="F717" t="n">
-        <v>237353</v>
+        <v>240359</v>
       </c>
     </row>
     <row r="718">
@@ -14781,10 +14781,10 @@
         <v>69.09999999999999</v>
       </c>
       <c r="E718" t="n">
-        <v>69.73</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="F718" t="n">
-        <v>205214</v>
+        <v>208893</v>
       </c>
     </row>
     <row r="719">
@@ -14858,13 +14858,13 @@
         <v>76.55</v>
       </c>
       <c r="D722" t="n">
-        <v>73.78</v>
+        <v>73.70999999999999</v>
       </c>
       <c r="E722" t="n">
-        <v>73.79000000000001</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="F722" t="n">
-        <v>140659</v>
+        <v>142264</v>
       </c>
     </row>
     <row r="723">
@@ -14881,10 +14881,10 @@
         <v>73.67</v>
       </c>
       <c r="E723" t="n">
-        <v>75.23</v>
+        <v>75.16</v>
       </c>
       <c r="F723" t="n">
-        <v>151698</v>
+        <v>153301</v>
       </c>
     </row>
     <row r="724">
@@ -14961,10 +14961,10 @@
         <v>73.88</v>
       </c>
       <c r="E727" t="n">
-        <v>74.63</v>
+        <v>74.48999999999999</v>
       </c>
       <c r="F727" t="n">
-        <v>140474</v>
+        <v>142563</v>
       </c>
     </row>
     <row r="728">
@@ -14981,10 +14981,10 @@
         <v>72.63</v>
       </c>
       <c r="E728" t="n">
-        <v>73.15000000000001</v>
+        <v>72.88</v>
       </c>
       <c r="F728" t="n">
-        <v>152160</v>
+        <v>154875</v>
       </c>
     </row>
     <row r="729">
@@ -15061,10 +15061,10 @@
         <v>74.72</v>
       </c>
       <c r="E732" t="n">
-        <v>76.63</v>
+        <v>76.52</v>
       </c>
       <c r="F732" t="n">
-        <v>100583</v>
+        <v>102802</v>
       </c>
     </row>
     <row r="733">
@@ -15161,10 +15161,10 @@
         <v>78.33</v>
       </c>
       <c r="E737" t="n">
-        <v>78.97</v>
+        <v>78.86</v>
       </c>
       <c r="F737" t="n">
-        <v>103669</v>
+        <v>105405</v>
       </c>
     </row>
     <row r="738">
@@ -15261,10 +15261,10 @@
         <v>79.36</v>
       </c>
       <c r="E742" t="n">
-        <v>81.65000000000001</v>
+        <v>81.70999999999999</v>
       </c>
       <c r="F742" t="n">
-        <v>185800</v>
+        <v>187943</v>
       </c>
     </row>
     <row r="743">
@@ -15281,10 +15281,10 @@
         <v>81.12</v>
       </c>
       <c r="E743" t="n">
-        <v>81.59999999999999</v>
+        <v>81.48</v>
       </c>
       <c r="F743" t="n">
-        <v>158852</v>
+        <v>160491</v>
       </c>
     </row>
     <row r="744">
@@ -15361,10 +15361,10 @@
         <v>83.34999999999999</v>
       </c>
       <c r="E747" t="n">
-        <v>83.45</v>
+        <v>83.61</v>
       </c>
       <c r="F747" t="n">
-        <v>145171</v>
+        <v>147527</v>
       </c>
     </row>
     <row r="748">
@@ -15375,16 +15375,16 @@
         <v>83.68000000000001</v>
       </c>
       <c r="C748" t="n">
-        <v>85.97</v>
+        <v>85.98999999999999</v>
       </c>
       <c r="D748" t="n">
         <v>83.53</v>
       </c>
       <c r="E748" t="n">
-        <v>85.91</v>
+        <v>85.77</v>
       </c>
       <c r="F748" t="n">
-        <v>171152</v>
+        <v>173518</v>
       </c>
     </row>
     <row r="749">
@@ -15458,13 +15458,13 @@
         <v>88.8</v>
       </c>
       <c r="D752" t="n">
-        <v>86.56999999999999</v>
+        <v>86.38</v>
       </c>
       <c r="E752" t="n">
-        <v>86.7</v>
+        <v>86.58</v>
       </c>
       <c r="F752" t="n">
-        <v>162890</v>
+        <v>169439</v>
       </c>
     </row>
     <row r="753">
@@ -15481,10 +15481,10 @@
         <v>85.02</v>
       </c>
       <c r="E753" t="n">
-        <v>86.98</v>
+        <v>86.92</v>
       </c>
       <c r="F753" t="n">
-        <v>223066</v>
+        <v>225683</v>
       </c>
     </row>
     <row r="754">
@@ -15561,10 +15561,10 @@
         <v>87.7</v>
       </c>
       <c r="E757" t="n">
-        <v>88.40000000000001</v>
+        <v>88.63</v>
       </c>
       <c r="F757" t="n">
-        <v>270152</v>
+        <v>275711</v>
       </c>
     </row>
     <row r="758">
@@ -15581,10 +15581,10 @@
         <v>88</v>
       </c>
       <c r="E758" t="n">
-        <v>88.73</v>
+        <v>88.81999999999999</v>
       </c>
       <c r="F758" t="n">
-        <v>275262</v>
+        <v>278896</v>
       </c>
     </row>
     <row r="759">
@@ -15655,16 +15655,16 @@
         <v>88.63</v>
       </c>
       <c r="C762" t="n">
-        <v>90.73999999999999</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="D762" t="n">
         <v>87.59999999999999</v>
       </c>
       <c r="E762" t="n">
-        <v>90.45999999999999</v>
+        <v>90.51000000000001</v>
       </c>
       <c r="F762" t="n">
-        <v>163057</v>
+        <v>168353</v>
       </c>
     </row>
     <row r="763">
@@ -15681,10 +15681,10 @@
         <v>90.67</v>
       </c>
       <c r="E763" t="n">
-        <v>92.54000000000001</v>
+        <v>92.14</v>
       </c>
       <c r="F763" t="n">
-        <v>177219</v>
+        <v>180147</v>
       </c>
     </row>
     <row r="764">
@@ -15761,10 +15761,10 @@
         <v>90.09999999999999</v>
       </c>
       <c r="E767" t="n">
-        <v>90.66</v>
+        <v>90.54000000000001</v>
       </c>
       <c r="F767" t="n">
-        <v>183590</v>
+        <v>186180</v>
       </c>
     </row>
     <row r="768">
@@ -15781,10 +15781,10 @@
         <v>89.66</v>
       </c>
       <c r="E768" t="n">
-        <v>93.81</v>
+        <v>93.8</v>
       </c>
       <c r="F768" t="n">
-        <v>189880</v>
+        <v>194729</v>
       </c>
     </row>
     <row r="769">
@@ -15861,10 +15861,10 @@
         <v>90.34999999999999</v>
       </c>
       <c r="E772" t="n">
-        <v>91.18000000000001</v>
+        <v>91.16</v>
       </c>
       <c r="F772" t="n">
-        <v>209775</v>
+        <v>212213</v>
       </c>
     </row>
     <row r="773">
@@ -15875,7 +15875,7 @@
         <v>90.76000000000001</v>
       </c>
       <c r="C773" t="n">
-        <v>92.15000000000001</v>
+        <v>92.28</v>
       </c>
       <c r="D773" t="n">
         <v>88.64</v>
@@ -15884,7 +15884,7 @@
         <v>91.81</v>
       </c>
       <c r="F773" t="n">
-        <v>190175</v>
+        <v>194995</v>
       </c>
     </row>
     <row r="774">
@@ -15961,10 +15961,10 @@
         <v>93.94</v>
       </c>
       <c r="E777" t="n">
-        <v>95.61</v>
+        <v>95.41</v>
       </c>
       <c r="F777" t="n">
-        <v>309076</v>
+        <v>313423</v>
       </c>
     </row>
     <row r="778">
@@ -15981,10 +15981,10 @@
         <v>92.55</v>
       </c>
       <c r="E778" t="n">
-        <v>94.69</v>
+        <v>94.23</v>
       </c>
       <c r="F778" t="n">
-        <v>233541</v>
+        <v>237786</v>
       </c>
     </row>
     <row r="779">
@@ -16061,10 +16061,10 @@
         <v>108.17</v>
       </c>
       <c r="E782" t="n">
-        <v>109.72</v>
+        <v>109.27</v>
       </c>
       <c r="F782" t="n">
-        <v>231064</v>
+        <v>233799</v>
       </c>
     </row>
     <row r="783">
@@ -16081,10 +16081,10 @@
         <v>108.47</v>
       </c>
       <c r="E783" t="n">
-        <v>117.14</v>
+        <v>116.7</v>
       </c>
       <c r="F783" t="n">
-        <v>204618</v>
+        <v>210974</v>
       </c>
     </row>
     <row r="784">
@@ -16161,10 +16161,10 @@
         <v>107.05</v>
       </c>
       <c r="E787" t="n">
-        <v>107.97</v>
+        <v>107.11</v>
       </c>
       <c r="F787" t="n">
-        <v>170481</v>
+        <v>173653</v>
       </c>
     </row>
     <row r="788">
@@ -16181,10 +16181,10 @@
         <v>104.96</v>
       </c>
       <c r="E788" t="n">
-        <v>110.51</v>
+        <v>110.14</v>
       </c>
       <c r="F788" t="n">
-        <v>154891</v>
+        <v>157669</v>
       </c>
     </row>
     <row r="789">
@@ -16252,19 +16252,19 @@
         <v>44637</v>
       </c>
       <c r="B792" t="n">
-        <v>96.98</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="C792" t="n">
         <v>105.3</v>
       </c>
       <c r="D792" t="n">
-        <v>96.11</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="E792" t="n">
         <v>104.46</v>
       </c>
       <c r="F792" t="n">
-        <v>176604</v>
+        <v>172578</v>
       </c>
     </row>
     <row r="793">
@@ -16272,7 +16272,7 @@
         <v>44638</v>
       </c>
       <c r="B793" t="n">
-        <v>104.55</v>
+        <v>105.16</v>
       </c>
       <c r="C793" t="n">
         <v>107.23</v>
@@ -16284,7 +16284,7 @@
         <v>105.63</v>
       </c>
       <c r="F793" t="n">
-        <v>158531</v>
+        <v>155067</v>
       </c>
     </row>
     <row r="794">
@@ -16352,7 +16352,7 @@
         <v>44644</v>
       </c>
       <c r="B797" t="n">
-        <v>118.08</v>
+        <v>119.49</v>
       </c>
       <c r="C797" t="n">
         <v>120.04</v>
@@ -16364,7 +16364,7 @@
         <v>114.47</v>
       </c>
       <c r="F797" t="n">
-        <v>215337</v>
+        <v>206598</v>
       </c>
     </row>
     <row r="798">
@@ -16372,7 +16372,7 @@
         <v>44645</v>
       </c>
       <c r="B798" t="n">
-        <v>115.3</v>
+        <v>114.52</v>
       </c>
       <c r="C798" t="n">
         <v>117.69</v>
@@ -16384,7 +16384,7 @@
         <v>115.94</v>
       </c>
       <c r="F798" t="n">
-        <v>195807</v>
+        <v>189095</v>
       </c>
     </row>
     <row r="799">
@@ -16461,10 +16461,10 @@
         <v>103.71</v>
       </c>
       <c r="E802" t="n">
-        <v>104.6</v>
+        <v>104.99</v>
       </c>
       <c r="F802" t="n">
-        <v>217472</v>
+        <v>220967</v>
       </c>
     </row>
     <row r="803">
@@ -16481,10 +16481,10 @@
         <v>101.94</v>
       </c>
       <c r="E803" t="n">
-        <v>104.13</v>
+        <v>103.88</v>
       </c>
       <c r="F803" t="n">
-        <v>179677</v>
+        <v>181758</v>
       </c>
     </row>
     <row r="804">
@@ -16561,10 +16561,10 @@
         <v>98.2</v>
       </c>
       <c r="E807" t="n">
-        <v>100.94</v>
+        <v>100.96</v>
       </c>
       <c r="F807" t="n">
-        <v>183922</v>
+        <v>186163</v>
       </c>
     </row>
     <row r="808">
@@ -16581,10 +16581,10 @@
         <v>99.28</v>
       </c>
       <c r="E808" t="n">
-        <v>102.16</v>
+        <v>101.81</v>
       </c>
       <c r="F808" t="n">
-        <v>159821</v>
+        <v>162819</v>
       </c>
     </row>
     <row r="809">
@@ -16661,10 +16661,10 @@
         <v>106.14</v>
       </c>
       <c r="E812" t="n">
-        <v>110.56</v>
+        <v>110.62</v>
       </c>
       <c r="F812" t="n">
-        <v>156524</v>
+        <v>159785</v>
       </c>
     </row>
     <row r="813">
@@ -16741,10 +16741,10 @@
         <v>106.38</v>
       </c>
       <c r="E816" t="n">
-        <v>107.93</v>
+        <v>108</v>
       </c>
       <c r="F816" t="n">
-        <v>184241</v>
+        <v>188001</v>
       </c>
     </row>
     <row r="817">
@@ -16758,13 +16758,13 @@
         <v>108.41</v>
       </c>
       <c r="D817" t="n">
-        <v>105.44</v>
+        <v>105.05</v>
       </c>
       <c r="E817" t="n">
-        <v>105.6</v>
+        <v>105.7</v>
       </c>
       <c r="F817" t="n">
-        <v>162032</v>
+        <v>165632</v>
       </c>
     </row>
     <row r="818">
@@ -16841,10 +16841,10 @@
         <v>102.74</v>
       </c>
       <c r="E821" t="n">
-        <v>107.25</v>
+        <v>106.8</v>
       </c>
       <c r="F821" t="n">
-        <v>167676</v>
+        <v>170514</v>
       </c>
     </row>
     <row r="822">
@@ -16861,10 +16861,10 @@
         <v>105.92</v>
       </c>
       <c r="E822" t="n">
-        <v>106.38</v>
+        <v>106.06</v>
       </c>
       <c r="F822" t="n">
-        <v>182972</v>
+        <v>186051</v>
       </c>
     </row>
     <row r="823">
@@ -16941,10 +16941,10 @@
         <v>108.66</v>
       </c>
       <c r="E826" t="n">
-        <v>110.3</v>
+        <v>110.4</v>
       </c>
       <c r="F826" t="n">
-        <v>197687</v>
+        <v>201234</v>
       </c>
     </row>
     <row r="827">
@@ -16961,10 +16961,10 @@
         <v>109.21</v>
       </c>
       <c r="E827" t="n">
-        <v>112.44</v>
+        <v>112.22</v>
       </c>
       <c r="F827" t="n">
-        <v>203469</v>
+        <v>207851</v>
       </c>
     </row>
     <row r="828">
@@ -17041,10 +17041,10 @@
         <v>103.97</v>
       </c>
       <c r="E831" t="n">
-        <v>107.38</v>
+        <v>106.86</v>
       </c>
       <c r="F831" t="n">
-        <v>240901</v>
+        <v>243371</v>
       </c>
     </row>
     <row r="832">
@@ -17061,10 +17061,10 @@
         <v>106.88</v>
       </c>
       <c r="E832" t="n">
-        <v>110.4</v>
+        <v>109.76</v>
       </c>
       <c r="F832" t="n">
-        <v>190398</v>
+        <v>193013</v>
       </c>
     </row>
     <row r="833">
@@ -17141,10 +17141,10 @@
         <v>104.22</v>
       </c>
       <c r="E836" t="n">
-        <v>109.59</v>
+        <v>109.5</v>
       </c>
       <c r="F836" t="n">
-        <v>247278</v>
+        <v>250583</v>
       </c>
     </row>
     <row r="837">
@@ -17161,10 +17161,10 @@
         <v>108.65</v>
       </c>
       <c r="E837" t="n">
-        <v>110.87</v>
+        <v>110.3</v>
       </c>
       <c r="F837" t="n">
-        <v>198948</v>
+        <v>202895</v>
       </c>
     </row>
     <row r="838">
@@ -17241,10 +17241,10 @@
         <v>110.83</v>
       </c>
       <c r="E841" t="n">
-        <v>114</v>
+        <v>114.15</v>
       </c>
       <c r="F841" t="n">
-        <v>171535</v>
+        <v>175003</v>
       </c>
     </row>
     <row r="842">
@@ -17261,10 +17261,10 @@
         <v>113.01</v>
       </c>
       <c r="E842" t="n">
-        <v>115.42</v>
+        <v>115.01</v>
       </c>
       <c r="F842" t="n">
-        <v>210750</v>
+        <v>213418</v>
       </c>
     </row>
     <row r="843">
@@ -17335,16 +17335,16 @@
         <v>113.88</v>
       </c>
       <c r="C846" t="n">
-        <v>117.57</v>
+        <v>117.74</v>
       </c>
       <c r="D846" t="n">
         <v>111.85</v>
       </c>
       <c r="E846" t="n">
-        <v>117.26</v>
+        <v>117.31</v>
       </c>
       <c r="F846" t="n">
-        <v>137013</v>
+        <v>138282</v>
       </c>
     </row>
     <row r="847">
@@ -17355,16 +17355,16 @@
         <v>117.37</v>
       </c>
       <c r="C847" t="n">
-        <v>120.57</v>
+        <v>120.6</v>
       </c>
       <c r="D847" t="n">
         <v>115.28</v>
       </c>
       <c r="E847" t="n">
-        <v>120.41</v>
+        <v>120.23</v>
       </c>
       <c r="F847" t="n">
-        <v>90339</v>
+        <v>91626</v>
       </c>
     </row>
     <row r="848">
@@ -17441,10 +17441,10 @@
         <v>121.23</v>
       </c>
       <c r="E851" t="n">
-        <v>121.71</v>
+        <v>121.41</v>
       </c>
       <c r="F851" t="n">
-        <v>174232</v>
+        <v>176648</v>
       </c>
     </row>
     <row r="852">
@@ -17461,10 +17461,10 @@
         <v>118.31</v>
       </c>
       <c r="E852" t="n">
-        <v>120.29</v>
+        <v>120.02</v>
       </c>
       <c r="F852" t="n">
-        <v>190410</v>
+        <v>192334</v>
       </c>
     </row>
     <row r="853">
@@ -17541,10 +17541,10 @@
         <v>113.72</v>
       </c>
       <c r="E856" t="n">
-        <v>117.15</v>
+        <v>116.92</v>
       </c>
       <c r="F856" t="n">
-        <v>228931</v>
+        <v>231324</v>
       </c>
     </row>
     <row r="857">
@@ -17561,10 +17561,10 @@
         <v>109.77</v>
       </c>
       <c r="E857" t="n">
-        <v>111.29</v>
+        <v>111.27</v>
       </c>
       <c r="F857" t="n">
-        <v>233588</v>
+        <v>236868</v>
       </c>
     </row>
     <row r="858">
@@ -17641,10 +17641,10 @@
         <v>105.25</v>
       </c>
       <c r="E861" t="n">
-        <v>106.29</v>
+        <v>106.13</v>
       </c>
       <c r="F861" t="n">
-        <v>233040</v>
+        <v>234952</v>
       </c>
     </row>
     <row r="862">
@@ -17661,10 +17661,10 @@
         <v>105.78</v>
       </c>
       <c r="E862" t="n">
-        <v>109.13</v>
+        <v>108.33</v>
       </c>
       <c r="F862" t="n">
-        <v>202836</v>
+        <v>205227</v>
       </c>
     </row>
     <row r="863">
@@ -17741,10 +17741,10 @@
         <v>107.7</v>
       </c>
       <c r="E866" t="n">
-        <v>108.69</v>
+        <v>108.43</v>
       </c>
       <c r="F866" t="n">
-        <v>208599</v>
+        <v>212070</v>
       </c>
     </row>
     <row r="867">
@@ -17761,10 +17761,10 @@
         <v>107.32</v>
       </c>
       <c r="E867" t="n">
-        <v>110.56</v>
+        <v>110.43</v>
       </c>
       <c r="F867" t="n">
-        <v>209195</v>
+        <v>210630</v>
       </c>
     </row>
     <row r="868">
@@ -17841,10 +17841,10 @@
         <v>97.11</v>
       </c>
       <c r="E871" t="n">
-        <v>102.75</v>
+        <v>102.32</v>
       </c>
       <c r="F871" t="n">
-        <v>221862</v>
+        <v>224620</v>
       </c>
     </row>
     <row r="872">
@@ -17861,10 +17861,10 @@
         <v>102.16</v>
       </c>
       <c r="E872" t="n">
-        <v>105.32</v>
+        <v>105.2</v>
       </c>
       <c r="F872" t="n">
-        <v>235167</v>
+        <v>237030</v>
       </c>
     </row>
     <row r="873">
@@ -17941,10 +17941,10 @@
         <v>92.42</v>
       </c>
       <c r="E876" t="n">
-        <v>97.17</v>
+        <v>97.12</v>
       </c>
       <c r="F876" t="n">
-        <v>215919</v>
+        <v>217836</v>
       </c>
     </row>
     <row r="877">
@@ -17961,10 +17961,10 @@
         <v>95.59</v>
       </c>
       <c r="E877" t="n">
-        <v>98.34999999999999</v>
+        <v>97.98</v>
       </c>
       <c r="F877" t="n">
-        <v>200270</v>
+        <v>203134</v>
       </c>
     </row>
     <row r="878">
@@ -18041,10 +18041,10 @@
         <v>97.86</v>
       </c>
       <c r="E881" t="n">
-        <v>100.04</v>
+        <v>99.93000000000001</v>
       </c>
       <c r="F881" t="n">
-        <v>227231</v>
+        <v>229298</v>
       </c>
     </row>
     <row r="882">
@@ -18061,10 +18061,10 @@
         <v>97.90000000000001</v>
       </c>
       <c r="E882" t="n">
-        <v>98.67</v>
+        <v>98.98999999999999</v>
       </c>
       <c r="F882" t="n">
-        <v>222921</v>
+        <v>226135</v>
       </c>
     </row>
     <row r="883">
@@ -18141,10 +18141,10 @@
         <v>100.74</v>
       </c>
       <c r="E886" t="n">
-        <v>101.93</v>
+        <v>101.99</v>
       </c>
       <c r="F886" t="n">
-        <v>130398</v>
+        <v>132446</v>
       </c>
     </row>
     <row r="887">
@@ -18161,10 +18161,10 @@
         <v>101.27</v>
       </c>
       <c r="E887" t="n">
-        <v>103.21</v>
+        <v>103.1</v>
       </c>
       <c r="F887" t="n">
-        <v>112179</v>
+        <v>113461</v>
       </c>
     </row>
     <row r="888">
@@ -18238,13 +18238,13 @@
         <v>97.17</v>
       </c>
       <c r="D891" t="n">
-        <v>92.73</v>
+        <v>92.5</v>
       </c>
       <c r="E891" t="n">
-        <v>93.38</v>
+        <v>92.52</v>
       </c>
       <c r="F891" t="n">
-        <v>160629</v>
+        <v>162676</v>
       </c>
     </row>
     <row r="892">
@@ -18261,10 +18261,10 @@
         <v>92.15000000000001</v>
       </c>
       <c r="E892" t="n">
-        <v>93.69</v>
+        <v>93.51000000000001</v>
       </c>
       <c r="F892" t="n">
-        <v>155701</v>
+        <v>157322</v>
       </c>
     </row>
     <row r="893">
@@ -18341,10 +18341,10 @@
         <v>96.08</v>
       </c>
       <c r="E896" t="n">
-        <v>98.66</v>
+        <v>98.31</v>
       </c>
       <c r="F896" t="n">
-        <v>139272</v>
+        <v>140818</v>
       </c>
     </row>
     <row r="897">
@@ -18361,10 +18361,10 @@
         <v>96.26000000000001</v>
       </c>
       <c r="E897" t="n">
-        <v>97.3</v>
+        <v>96.89</v>
       </c>
       <c r="F897" t="n">
-        <v>144235</v>
+        <v>145858</v>
       </c>
     </row>
     <row r="898">
@@ -18441,10 +18441,10 @@
         <v>92.55</v>
       </c>
       <c r="E901" t="n">
-        <v>95.93000000000001</v>
+        <v>95.56</v>
       </c>
       <c r="F901" t="n">
-        <v>122235</v>
+        <v>123861</v>
       </c>
     </row>
     <row r="902">
@@ -18461,10 +18461,10 @@
         <v>93.7</v>
       </c>
       <c r="E902" t="n">
-        <v>95.52</v>
+        <v>95.08</v>
       </c>
       <c r="F902" t="n">
-        <v>125387</v>
+        <v>126696</v>
       </c>
     </row>
     <row r="903">
@@ -18541,10 +18541,10 @@
         <v>98.23</v>
       </c>
       <c r="E906" t="n">
-        <v>99.05</v>
+        <v>98.68000000000001</v>
       </c>
       <c r="F906" t="n">
-        <v>114289</v>
+        <v>115830</v>
       </c>
     </row>
     <row r="907">
@@ -18561,10 +18561,10 @@
         <v>96.92</v>
       </c>
       <c r="E907" t="n">
-        <v>98.70999999999999</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="F907" t="n">
-        <v>127109</v>
+        <v>128357</v>
       </c>
     </row>
     <row r="908">
@@ -18641,10 +18641,10 @@
         <v>91.58</v>
       </c>
       <c r="E911" t="n">
-        <v>91.75</v>
+        <v>91.59</v>
       </c>
       <c r="F911" t="n">
-        <v>171383</v>
+        <v>172611</v>
       </c>
     </row>
     <row r="912">
@@ -18661,10 +18661,10 @@
         <v>92.41</v>
       </c>
       <c r="E912" t="n">
-        <v>92.68000000000001</v>
+        <v>92.83</v>
       </c>
       <c r="F912" t="n">
-        <v>162523</v>
+        <v>164349</v>
       </c>
     </row>
     <row r="913">
@@ -18741,10 +18741,10 @@
         <v>86.86</v>
       </c>
       <c r="E916" t="n">
-        <v>88.03</v>
+        <v>87.73999999999999</v>
       </c>
       <c r="F916" t="n">
-        <v>174104</v>
+        <v>175783</v>
       </c>
     </row>
     <row r="917">
@@ -18761,10 +18761,10 @@
         <v>88.09</v>
       </c>
       <c r="E917" t="n">
-        <v>91.90000000000001</v>
+        <v>91.42</v>
       </c>
       <c r="F917" t="n">
-        <v>137562</v>
+        <v>139210</v>
       </c>
     </row>
     <row r="918">
@@ -18841,10 +18841,10 @@
         <v>89.39</v>
       </c>
       <c r="E921" t="n">
-        <v>90.08</v>
+        <v>89.78</v>
       </c>
       <c r="F921" t="n">
-        <v>177670</v>
+        <v>179533</v>
       </c>
     </row>
     <row r="922">
@@ -18861,10 +18861,10 @@
         <v>89.37</v>
       </c>
       <c r="E922" t="n">
-        <v>90.58</v>
+        <v>90.36</v>
       </c>
       <c r="F922" t="n">
-        <v>175462</v>
+        <v>177056</v>
       </c>
     </row>
     <row r="923">
@@ -18941,10 +18941,10 @@
         <v>88.38</v>
       </c>
       <c r="E926" t="n">
-        <v>89.53</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="F926" t="n">
-        <v>167346</v>
+        <v>169282</v>
       </c>
     </row>
     <row r="927">
@@ -18961,10 +18961,10 @@
         <v>84.61</v>
       </c>
       <c r="E927" t="n">
-        <v>85.41</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="F927" t="n">
-        <v>157358</v>
+        <v>159709</v>
       </c>
     </row>
     <row r="928">
@@ -19041,10 +19041,10 @@
         <v>85.98</v>
       </c>
       <c r="E931" t="n">
-        <v>87.20999999999999</v>
+        <v>87.22</v>
       </c>
       <c r="F931" t="n">
-        <v>182346</v>
+        <v>184095</v>
       </c>
     </row>
     <row r="932">
@@ -19061,10 +19061,10 @@
         <v>84.73999999999999</v>
       </c>
       <c r="E932" t="n">
-        <v>85.06999999999999</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="F932" t="n">
-        <v>172540</v>
+        <v>174184</v>
       </c>
     </row>
     <row r="933">
@@ -19141,10 +19141,10 @@
         <v>92.09</v>
       </c>
       <c r="E936" t="n">
-        <v>94.31999999999999</v>
+        <v>94.16</v>
       </c>
       <c r="F936" t="n">
-        <v>134269</v>
+        <v>136157</v>
       </c>
     </row>
     <row r="937">
@@ -19161,10 +19161,10 @@
         <v>93.25</v>
       </c>
       <c r="E937" t="n">
-        <v>96.95</v>
+        <v>97.59</v>
       </c>
       <c r="F937" t="n">
-        <v>158303</v>
+        <v>161145</v>
       </c>
     </row>
     <row r="938">
@@ -19241,10 +19241,10 @@
         <v>90.18000000000001</v>
       </c>
       <c r="E941" t="n">
-        <v>93.61</v>
+        <v>93.67</v>
       </c>
       <c r="F941" t="n">
-        <v>187899</v>
+        <v>189909</v>
       </c>
     </row>
     <row r="942">
@@ -19261,10 +19261,10 @@
         <v>90.34</v>
       </c>
       <c r="E942" t="n">
-        <v>90.84999999999999</v>
+        <v>90.66</v>
       </c>
       <c r="F942" t="n">
-        <v>184164</v>
+        <v>186342</v>
       </c>
     </row>
     <row r="943">
@@ -19341,10 +19341,10 @@
         <v>90.34</v>
       </c>
       <c r="E946" t="n">
-        <v>91</v>
+        <v>91.11</v>
       </c>
       <c r="F946" t="n">
-        <v>169394</v>
+        <v>172151</v>
       </c>
     </row>
     <row r="947">
@@ -19361,10 +19361,10 @@
         <v>89.40000000000001</v>
       </c>
       <c r="E947" t="n">
-        <v>91.7</v>
+        <v>91.58</v>
       </c>
       <c r="F947" t="n">
-        <v>168937</v>
+        <v>170499</v>
       </c>
     </row>
     <row r="948">
@@ -19441,10 +19441,10 @@
         <v>93.06999999999999</v>
       </c>
       <c r="E951" t="n">
-        <v>94.91</v>
+        <v>94.45999999999999</v>
       </c>
       <c r="F951" t="n">
-        <v>130846</v>
+        <v>135151</v>
       </c>
     </row>
     <row r="952">
@@ -19461,10 +19461,10 @@
         <v>92.81999999999999</v>
       </c>
       <c r="E952" t="n">
-        <v>93.81</v>
+        <v>93.95</v>
       </c>
       <c r="F952" t="n">
-        <v>133960</v>
+        <v>135363</v>
       </c>
     </row>
     <row r="953">
@@ -19532,7 +19532,7 @@
         <v>44868</v>
       </c>
       <c r="B956" t="n">
-        <v>94.81</v>
+        <v>94.84</v>
       </c>
       <c r="C956" t="n">
         <v>95.45</v>
@@ -19544,7 +19544,7 @@
         <v>93.92</v>
       </c>
       <c r="F956" t="n">
-        <v>143503</v>
+        <v>141621</v>
       </c>
     </row>
     <row r="957">
@@ -19552,19 +19552,19 @@
         <v>44869</v>
       </c>
       <c r="B957" t="n">
-        <v>93.98</v>
+        <v>93.94</v>
       </c>
       <c r="C957" t="n">
         <v>98.23999999999999</v>
       </c>
       <c r="D957" t="n">
-        <v>93.76000000000001</v>
+        <v>93.94</v>
       </c>
       <c r="E957" t="n">
         <v>98.01000000000001</v>
       </c>
       <c r="F957" t="n">
-        <v>182009</v>
+        <v>179958</v>
       </c>
     </row>
     <row r="958">
@@ -19641,10 +19641,10 @@
         <v>90.97</v>
       </c>
       <c r="E961" t="n">
-        <v>92.69</v>
+        <v>92.47</v>
       </c>
       <c r="F961" t="n">
-        <v>168690</v>
+        <v>170823</v>
       </c>
     </row>
     <row r="962">
@@ -19661,10 +19661,10 @@
         <v>92.79000000000001</v>
       </c>
       <c r="E962" t="n">
-        <v>95.04000000000001</v>
+        <v>94.95999999999999</v>
       </c>
       <c r="F962" t="n">
-        <v>163940</v>
+        <v>165782</v>
       </c>
     </row>
     <row r="963">
@@ -19741,10 +19741,10 @@
         <v>88.72</v>
       </c>
       <c r="E966" t="n">
-        <v>89.28</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="F966" t="n">
-        <v>157265</v>
+        <v>159560</v>
       </c>
     </row>
     <row r="967">
@@ -19761,10 +19761,10 @@
         <v>85.41</v>
       </c>
       <c r="E967" t="n">
-        <v>87.45</v>
+        <v>87.5</v>
       </c>
       <c r="F967" t="n">
-        <v>160818</v>
+        <v>162655</v>
       </c>
     </row>
     <row r="968">
@@ -19941,10 +19941,10 @@
         <v>86.26000000000001</v>
       </c>
       <c r="E976" t="n">
-        <v>86.84</v>
+        <v>86.98</v>
       </c>
       <c r="F976" t="n">
-        <v>135345</v>
+        <v>136930</v>
       </c>
     </row>
     <row r="977">
@@ -19961,10 +19961,10 @@
         <v>85.17</v>
       </c>
       <c r="E977" t="n">
-        <v>85.76000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="F977" t="n">
-        <v>135815</v>
+        <v>137359</v>
       </c>
     </row>
     <row r="978">
@@ -20041,10 +20041,10 @@
         <v>75.92</v>
       </c>
       <c r="E981" t="n">
-        <v>76.27</v>
+        <v>76.61</v>
       </c>
       <c r="F981" t="n">
-        <v>165742</v>
+        <v>167594</v>
       </c>
     </row>
     <row r="982">
@@ -20061,10 +20061,10 @@
         <v>75.34999999999999</v>
       </c>
       <c r="E982" t="n">
-        <v>76.76000000000001</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="F982" t="n">
-        <v>151706</v>
+        <v>153224</v>
       </c>
     </row>
     <row r="983">
@@ -20141,10 +20141,10 @@
         <v>80.86</v>
       </c>
       <c r="E986" t="n">
-        <v>81.39</v>
+        <v>81.54000000000001</v>
       </c>
       <c r="F986" t="n">
-        <v>149384</v>
+        <v>151489</v>
       </c>
     </row>
     <row r="987">
@@ -20161,10 +20161,10 @@
         <v>78.61</v>
       </c>
       <c r="E987" t="n">
-        <v>79.36</v>
+        <v>79.44</v>
       </c>
       <c r="F987" t="n">
-        <v>149990</v>
+        <v>151197</v>
       </c>
     </row>
     <row r="988">
@@ -20241,10 +20241,10 @@
         <v>81.28</v>
       </c>
       <c r="E991" t="n">
-        <v>82.18000000000001</v>
+        <v>82.20999999999999</v>
       </c>
       <c r="F991" t="n">
-        <v>94348</v>
+        <v>95617</v>
       </c>
     </row>
     <row r="992">
@@ -20321,10 +20321,10 @@
         <v>81.81999999999999</v>
       </c>
       <c r="E995" t="n">
-        <v>83.68000000000001</v>
+        <v>83.63</v>
       </c>
       <c r="F995" t="n">
-        <v>109380</v>
+        <v>110699</v>
       </c>
     </row>
     <row r="996">
@@ -20401,10 +20401,10 @@
         <v>77.63</v>
       </c>
       <c r="E999" t="n">
-        <v>78.68000000000001</v>
+        <v>78.8</v>
       </c>
       <c r="F999" t="n">
-        <v>149266</v>
+        <v>150672</v>
       </c>
     </row>
     <row r="1000">
@@ -20424,7 +20424,7 @@
         <v>78.51000000000001</v>
       </c>
       <c r="F1000" t="n">
-        <v>147017</v>
+        <v>148389</v>
       </c>
     </row>
     <row r="1001">
@@ -20501,10 +20501,10 @@
         <v>82.43000000000001</v>
       </c>
       <c r="E1004" t="n">
-        <v>83.91</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="F1004" t="n">
-        <v>141086</v>
+        <v>142735</v>
       </c>
     </row>
     <row r="1005">
@@ -20515,16 +20515,16 @@
         <v>83.91</v>
       </c>
       <c r="C1005" t="n">
-        <v>85.55</v>
+        <v>85.61</v>
       </c>
       <c r="D1005" t="n">
         <v>83.55</v>
       </c>
       <c r="E1005" t="n">
-        <v>85.48</v>
+        <v>85.47</v>
       </c>
       <c r="F1005" t="n">
-        <v>129757</v>
+        <v>131152</v>
       </c>
     </row>
     <row r="1006">
@@ -20601,10 +20601,10 @@
         <v>83.95999999999999</v>
       </c>
       <c r="E1009" t="n">
-        <v>86.31999999999999</v>
+        <v>86.34</v>
       </c>
       <c r="F1009" t="n">
-        <v>142583</v>
+        <v>144410</v>
       </c>
     </row>
     <row r="1010">
@@ -20621,10 +20621,10 @@
         <v>85.69</v>
       </c>
       <c r="E1010" t="n">
-        <v>87.75</v>
+        <v>87.59</v>
       </c>
       <c r="F1010" t="n">
-        <v>123973</v>
+        <v>125225</v>
       </c>
     </row>
     <row r="1011">
@@ -20701,10 +20701,10 @@
         <v>85.75</v>
       </c>
       <c r="E1014" t="n">
-        <v>87.31</v>
+        <v>87.29000000000001</v>
       </c>
       <c r="F1014" t="n">
-        <v>95077</v>
+        <v>96051</v>
       </c>
     </row>
     <row r="1015">
@@ -20721,10 +20721,10 @@
         <v>85.48</v>
       </c>
       <c r="E1015" t="n">
-        <v>86.04000000000001</v>
+        <v>86.01000000000001</v>
       </c>
       <c r="F1015" t="n">
-        <v>109841</v>
+        <v>110922</v>
       </c>
     </row>
     <row r="1016">
@@ -20801,10 +20801,10 @@
         <v>81.2</v>
       </c>
       <c r="E1019" t="n">
-        <v>81.98</v>
+        <v>82.12</v>
       </c>
       <c r="F1019" t="n">
-        <v>146732</v>
+        <v>150704</v>
       </c>
     </row>
     <row r="1020">
@@ -20818,13 +20818,13 @@
         <v>84.11</v>
       </c>
       <c r="D1020" t="n">
+        <v>79.53</v>
+      </c>
+      <c r="E1020" t="n">
         <v>79.62</v>
       </c>
-      <c r="E1020" t="n">
-        <v>79.64</v>
-      </c>
       <c r="F1020" t="n">
-        <v>161681</v>
+        <v>163093</v>
       </c>
     </row>
     <row r="1021">
@@ -20901,10 +20901,10 @@
         <v>82.86</v>
       </c>
       <c r="E1024" t="n">
-        <v>83.88</v>
+        <v>83.95</v>
       </c>
       <c r="F1024" t="n">
-        <v>142722</v>
+        <v>144061</v>
       </c>
     </row>
     <row r="1025">
@@ -20921,10 +20921,10 @@
         <v>83.66</v>
       </c>
       <c r="E1025" t="n">
-        <v>86.29000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="F1025" t="n">
-        <v>155562</v>
+        <v>156718</v>
       </c>
     </row>
     <row r="1026">
@@ -20998,13 +20998,13 @@
         <v>85.90000000000001</v>
       </c>
       <c r="D1029" t="n">
-        <v>84.31999999999999</v>
+        <v>84.28</v>
       </c>
       <c r="E1029" t="n">
-        <v>84.37</v>
+        <v>84.31</v>
       </c>
       <c r="F1029" t="n">
-        <v>128382</v>
+        <v>129946</v>
       </c>
     </row>
     <row r="1030">
@@ -21021,10 +21021,10 @@
         <v>81.55</v>
       </c>
       <c r="E1030" t="n">
-        <v>82.68000000000001</v>
+        <v>82.72</v>
       </c>
       <c r="F1030" t="n">
-        <v>141607</v>
+        <v>142763</v>
       </c>
     </row>
     <row r="1031">
@@ -21101,10 +21101,10 @@
         <v>80.27</v>
       </c>
       <c r="E1034" t="n">
-        <v>82.12</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="F1034" t="n">
-        <v>107083</v>
+        <v>108091</v>
       </c>
     </row>
     <row r="1035">
@@ -21121,10 +21121,10 @@
         <v>80.7</v>
       </c>
       <c r="E1035" t="n">
-        <v>82.94</v>
+        <v>82.77</v>
       </c>
       <c r="F1035" t="n">
-        <v>129354</v>
+        <v>130526</v>
       </c>
     </row>
     <row r="1036">
@@ -21201,10 +21201,10 @@
         <v>83.66</v>
       </c>
       <c r="E1039" t="n">
-        <v>84.34</v>
+        <v>84.23</v>
       </c>
       <c r="F1039" t="n">
-        <v>114302</v>
+        <v>115434</v>
       </c>
     </row>
     <row r="1040">
@@ -21215,16 +21215,16 @@
         <v>84.37</v>
       </c>
       <c r="C1040" t="n">
-        <v>85.8</v>
+        <v>85.81</v>
       </c>
       <c r="D1040" t="n">
         <v>82.2</v>
       </c>
       <c r="E1040" t="n">
-        <v>85.72</v>
+        <v>85.73999999999999</v>
       </c>
       <c r="F1040" t="n">
-        <v>119970</v>
+        <v>120888</v>
       </c>
     </row>
     <row r="1041">
@@ -21301,10 +21301,10 @@
         <v>81.16</v>
       </c>
       <c r="E1044" t="n">
-        <v>81.26000000000001</v>
+        <v>81.23</v>
       </c>
       <c r="F1044" t="n">
-        <v>120126</v>
+        <v>121276</v>
       </c>
     </row>
     <row r="1045">
@@ -21321,10 +21321,10 @@
         <v>80.47</v>
       </c>
       <c r="E1045" t="n">
-        <v>82.33</v>
+        <v>82.38</v>
       </c>
       <c r="F1045" t="n">
-        <v>171433</v>
+        <v>172647</v>
       </c>
     </row>
     <row r="1046">
@@ -21392,7 +21392,7 @@
         <v>45001</v>
       </c>
       <c r="B1049" t="n">
-        <v>74.04000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="C1049" t="n">
         <v>75.23</v>
@@ -21404,7 +21404,7 @@
         <v>74.25</v>
       </c>
       <c r="F1049" t="n">
-        <v>210322</v>
+        <v>206406</v>
       </c>
     </row>
     <row r="1050">
@@ -21412,7 +21412,7 @@
         <v>45002</v>
       </c>
       <c r="B1050" t="n">
-        <v>74.45</v>
+        <v>74.41</v>
       </c>
       <c r="C1050" t="n">
         <v>75.65000000000001</v>
@@ -21424,7 +21424,7 @@
         <v>72.3</v>
       </c>
       <c r="F1050" t="n">
-        <v>196053</v>
+        <v>194486</v>
       </c>
     </row>
     <row r="1051">
@@ -21492,7 +21492,7 @@
         <v>45008</v>
       </c>
       <c r="B1054" t="n">
-        <v>75.58</v>
+        <v>75.73</v>
       </c>
       <c r="C1054" t="n">
         <v>77.09</v>
@@ -21504,7 +21504,7 @@
         <v>74.98999999999999</v>
       </c>
       <c r="F1054" t="n">
-        <v>134971</v>
+        <v>132462</v>
       </c>
     </row>
     <row r="1055">
@@ -21512,7 +21512,7 @@
         <v>45009</v>
       </c>
       <c r="B1055" t="n">
-        <v>75.08</v>
+        <v>74.92</v>
       </c>
       <c r="C1055" t="n">
         <v>75.89</v>
@@ -21524,7 +21524,7 @@
         <v>74.52</v>
       </c>
       <c r="F1055" t="n">
-        <v>160608</v>
+        <v>158419</v>
       </c>
     </row>
     <row r="1056">
@@ -21601,10 +21601,10 @@
         <v>77.13</v>
       </c>
       <c r="E1059" t="n">
-        <v>78.47</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="F1059" t="n">
-        <v>101875</v>
+        <v>102975</v>
       </c>
     </row>
     <row r="1060">
@@ -21621,10 +21621,10 @@
         <v>77.79000000000001</v>
       </c>
       <c r="E1060" t="n">
-        <v>79.73</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="F1060" t="n">
-        <v>102278</v>
+        <v>103341</v>
       </c>
     </row>
     <row r="1061">
@@ -21701,10 +21701,10 @@
         <v>83.89</v>
       </c>
       <c r="E1064" t="n">
-        <v>84.73</v>
+        <v>84.62</v>
       </c>
       <c r="F1064" t="n">
-        <v>127887</v>
+        <v>128978</v>
       </c>
     </row>
     <row r="1065">
@@ -21781,10 +21781,10 @@
         <v>85.78</v>
       </c>
       <c r="E1068" t="n">
-        <v>85.98</v>
+        <v>86.03</v>
       </c>
       <c r="F1068" t="n">
-        <v>106530</v>
+        <v>107747</v>
       </c>
     </row>
     <row r="1069">
@@ -21801,10 +21801,10 @@
         <v>85.27</v>
       </c>
       <c r="E1069" t="n">
-        <v>86.13</v>
+        <v>86.12</v>
       </c>
       <c r="F1069" t="n">
-        <v>118921</v>
+        <v>119789</v>
       </c>
     </row>
     <row r="1070">
@@ -21878,13 +21878,13 @@
         <v>82.59999999999999</v>
       </c>
       <c r="D1073" t="n">
-        <v>80.51000000000001</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="E1073" t="n">
-        <v>80.62</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="F1073" t="n">
-        <v>99083</v>
+        <v>100157</v>
       </c>
     </row>
     <row r="1074">
@@ -21901,10 +21901,10 @@
         <v>80.2</v>
       </c>
       <c r="E1074" t="n">
-        <v>81.38</v>
+        <v>81.53</v>
       </c>
       <c r="F1074" t="n">
-        <v>88877</v>
+        <v>89589</v>
       </c>
     </row>
     <row r="1075">
@@ -21981,10 +21981,10 @@
         <v>77.3</v>
       </c>
       <c r="E1078" t="n">
-        <v>78.23</v>
+        <v>78.17</v>
       </c>
       <c r="F1078" t="n">
-        <v>112919</v>
+        <v>114226</v>
       </c>
     </row>
     <row r="1079">
@@ -22001,10 +22001,10 @@
         <v>77.44</v>
       </c>
       <c r="E1079" t="n">
-        <v>80.20999999999999</v>
+        <v>80.08</v>
       </c>
       <c r="F1079" t="n">
-        <v>110643</v>
+        <v>111593</v>
       </c>
     </row>
     <row r="1080">
@@ -22081,10 +22081,10 @@
         <v>71.34</v>
       </c>
       <c r="E1083" t="n">
-        <v>72.34</v>
+        <v>72.38</v>
       </c>
       <c r="F1083" t="n">
-        <v>175075</v>
+        <v>176458</v>
       </c>
     </row>
     <row r="1084">
@@ -22101,10 +22101,10 @@
         <v>72.31999999999999</v>
       </c>
       <c r="E1084" t="n">
-        <v>75.22</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="F1084" t="n">
-        <v>121559</v>
+        <v>122688</v>
       </c>
     </row>
     <row r="1085">
@@ -22181,10 +22181,10 @@
         <v>74.5</v>
       </c>
       <c r="E1088" t="n">
-        <v>75.34999999999999</v>
+        <v>75.26000000000001</v>
       </c>
       <c r="F1088" t="n">
-        <v>141443</v>
+        <v>142391</v>
       </c>
     </row>
     <row r="1089">
@@ -22201,10 +22201,10 @@
         <v>73.84999999999999</v>
       </c>
       <c r="E1089" t="n">
-        <v>74.02</v>
+        <v>73.93000000000001</v>
       </c>
       <c r="F1089" t="n">
-        <v>143925</v>
+        <v>144762</v>
       </c>
     </row>
     <row r="1090">
@@ -22281,10 +22281,10 @@
         <v>75.42</v>
       </c>
       <c r="E1093" t="n">
-        <v>75.89</v>
+        <v>75.84</v>
       </c>
       <c r="F1093" t="n">
-        <v>97144</v>
+        <v>98116</v>
       </c>
     </row>
     <row r="1094">
@@ -22301,10 +22301,10 @@
         <v>75.01000000000001</v>
       </c>
       <c r="E1094" t="n">
-        <v>75.75</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="F1094" t="n">
-        <v>107224</v>
+        <v>108218</v>
       </c>
     </row>
     <row r="1095">
@@ -22381,10 +22381,10 @@
         <v>75.08</v>
       </c>
       <c r="E1098" t="n">
-        <v>76.13</v>
+        <v>75.95999999999999</v>
       </c>
       <c r="F1098" t="n">
-        <v>94656</v>
+        <v>95663</v>
       </c>
     </row>
     <row r="1099">
@@ -22401,10 +22401,10 @@
         <v>75.62</v>
       </c>
       <c r="E1099" t="n">
-        <v>77.03</v>
+        <v>77.14</v>
       </c>
       <c r="F1099" t="n">
-        <v>85632</v>
+        <v>86227</v>
       </c>
     </row>
     <row r="1100">
@@ -22481,10 +22481,10 @@
         <v>72</v>
       </c>
       <c r="E1103" t="n">
-        <v>74.17</v>
+        <v>74.25</v>
       </c>
       <c r="F1103" t="n">
-        <v>122959</v>
+        <v>124084</v>
       </c>
     </row>
     <row r="1104">
@@ -22501,10 +22501,10 @@
         <v>74.13</v>
       </c>
       <c r="E1104" t="n">
-        <v>76.3</v>
+        <v>76.13</v>
       </c>
       <c r="F1104" t="n">
-        <v>110715</v>
+        <v>111881</v>
       </c>
     </row>
     <row r="1105">
@@ -22581,10 +22581,10 @@
         <v>73.52</v>
       </c>
       <c r="E1108" t="n">
-        <v>75.56999999999999</v>
+        <v>75.44</v>
       </c>
       <c r="F1108" t="n">
-        <v>141391</v>
+        <v>142206</v>
       </c>
     </row>
     <row r="1109">
@@ -22601,10 +22601,10 @@
         <v>74.67</v>
       </c>
       <c r="E1109" t="n">
-        <v>74.84999999999999</v>
+        <v>74.88</v>
       </c>
       <c r="F1109" t="n">
-        <v>120105</v>
+        <v>120995</v>
       </c>
     </row>
     <row r="1110">
@@ -22681,10 +22681,10 @@
         <v>72.84999999999999</v>
       </c>
       <c r="E1113" t="n">
-        <v>75.56</v>
+        <v>75.52</v>
       </c>
       <c r="F1113" t="n">
-        <v>104970</v>
+        <v>105947</v>
       </c>
     </row>
     <row r="1114">
@@ -22701,10 +22701,10 @@
         <v>75.09999999999999</v>
       </c>
       <c r="E1114" t="n">
-        <v>76.47</v>
+        <v>76.23</v>
       </c>
       <c r="F1114" t="n">
-        <v>109963</v>
+        <v>111184</v>
       </c>
     </row>
     <row r="1115">
@@ -22781,10 +22781,10 @@
         <v>73.75</v>
       </c>
       <c r="E1118" t="n">
-        <v>74.2</v>
+        <v>74.3</v>
       </c>
       <c r="F1118" t="n">
-        <v>89166</v>
+        <v>89974</v>
       </c>
     </row>
     <row r="1119">
@@ -22795,16 +22795,16 @@
         <v>74.2</v>
       </c>
       <c r="C1119" t="n">
-        <v>74.36</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="D1119" t="n">
         <v>72.25</v>
       </c>
       <c r="E1119" t="n">
-        <v>74.09</v>
+        <v>74.34</v>
       </c>
       <c r="F1119" t="n">
-        <v>100773</v>
+        <v>101628</v>
       </c>
     </row>
     <row r="1120">
@@ -22881,10 +22881,10 @@
         <v>73.56</v>
       </c>
       <c r="E1123" t="n">
-        <v>74.44</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="F1123" t="n">
-        <v>118096</v>
+        <v>118860</v>
       </c>
     </row>
     <row r="1124">
@@ -22901,10 +22901,10 @@
         <v>74.23</v>
       </c>
       <c r="E1124" t="n">
-        <v>75.26000000000001</v>
+        <v>75.06999999999999</v>
       </c>
       <c r="F1124" t="n">
-        <v>107062</v>
+        <v>108012</v>
       </c>
     </row>
     <row r="1125">
@@ -22981,10 +22981,10 @@
         <v>74.94</v>
       </c>
       <c r="E1128" t="n">
-        <v>76.47</v>
+        <v>76.44</v>
       </c>
       <c r="F1128" t="n">
-        <v>120498</v>
+        <v>121613</v>
       </c>
     </row>
     <row r="1129">
@@ -23001,10 +23001,10 @@
         <v>75.91</v>
       </c>
       <c r="E1129" t="n">
-        <v>78.13</v>
+        <v>78.12</v>
       </c>
       <c r="F1129" t="n">
-        <v>99946</v>
+        <v>101260</v>
       </c>
     </row>
     <row r="1130">
@@ -23075,16 +23075,16 @@
         <v>79.95999999999999</v>
       </c>
       <c r="C1133" t="n">
-        <v>81.48999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="D1133" t="n">
         <v>79.69</v>
       </c>
       <c r="E1133" t="n">
-        <v>81.48</v>
+        <v>81.37</v>
       </c>
       <c r="F1133" t="n">
-        <v>96443</v>
+        <v>97805</v>
       </c>
     </row>
     <row r="1134">
@@ -23098,13 +23098,13 @@
         <v>81.42</v>
       </c>
       <c r="D1134" t="n">
-        <v>79.44</v>
+        <v>79.34999999999999</v>
       </c>
       <c r="E1134" t="n">
-        <v>79.54000000000001</v>
+        <v>79.45</v>
       </c>
       <c r="F1134" t="n">
-        <v>98000</v>
+        <v>99161</v>
       </c>
     </row>
     <row r="1135">
@@ -23181,10 +23181,10 @@
         <v>78.56999999999999</v>
       </c>
       <c r="E1138" t="n">
-        <v>79.54000000000001</v>
+        <v>79.48</v>
       </c>
       <c r="F1138" t="n">
-        <v>76777</v>
+        <v>77506</v>
       </c>
     </row>
     <row r="1139">
@@ -23201,10 +23201,10 @@
         <v>79.51000000000001</v>
       </c>
       <c r="E1139" t="n">
-        <v>80.69</v>
+        <v>80.5</v>
       </c>
       <c r="F1139" t="n">
-        <v>69907</v>
+        <v>70745</v>
       </c>
     </row>
     <row r="1140">
@@ -23281,10 +23281,10 @@
         <v>82.54000000000001</v>
       </c>
       <c r="E1143" t="n">
-        <v>83.42</v>
+        <v>83.3</v>
       </c>
       <c r="F1143" t="n">
-        <v>100960</v>
+        <v>101885</v>
       </c>
     </row>
     <row r="1144">
@@ -23301,10 +23301,10 @@
         <v>82.78</v>
       </c>
       <c r="E1144" t="n">
-        <v>84.26000000000001</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="F1144" t="n">
-        <v>96080</v>
+        <v>96933</v>
       </c>
     </row>
     <row r="1145">
@@ -23381,10 +23381,10 @@
         <v>82.23</v>
       </c>
       <c r="E1148" t="n">
-        <v>85.13</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="F1148" t="n">
-        <v>122532</v>
+        <v>124232</v>
       </c>
     </row>
     <row r="1149">
@@ -23401,10 +23401,10 @@
         <v>84.89</v>
       </c>
       <c r="E1149" t="n">
-        <v>85.84</v>
+        <v>85.81</v>
       </c>
       <c r="F1149" t="n">
-        <v>103319</v>
+        <v>104424</v>
       </c>
     </row>
     <row r="1150">
@@ -23481,10 +23481,10 @@
         <v>85.89</v>
       </c>
       <c r="E1153" t="n">
-        <v>86.09999999999999</v>
+        <v>86.01000000000001</v>
       </c>
       <c r="F1153" t="n">
-        <v>119054</v>
+        <v>120019</v>
       </c>
     </row>
     <row r="1154">
@@ -23501,10 +23501,10 @@
         <v>85.53</v>
       </c>
       <c r="E1154" t="n">
-        <v>86.26000000000001</v>
+        <v>86.16</v>
       </c>
       <c r="F1154" t="n">
-        <v>114400</v>
+        <v>115051</v>
       </c>
     </row>
     <row r="1155">
@@ -23581,10 +23581,10 @@
         <v>82.70999999999999</v>
       </c>
       <c r="E1158" t="n">
-        <v>83.45999999999999</v>
+        <v>83.42</v>
       </c>
       <c r="F1158" t="n">
-        <v>87119</v>
+        <v>88033</v>
       </c>
     </row>
     <row r="1159">
@@ -23601,10 +23601,10 @@
         <v>82.98</v>
       </c>
       <c r="E1159" t="n">
-        <v>84.37</v>
+        <v>84.42</v>
       </c>
       <c r="F1159" t="n">
-        <v>98085</v>
+        <v>98761</v>
       </c>
     </row>
     <row r="1160">
@@ -23681,10 +23681,10 @@
         <v>81.61</v>
       </c>
       <c r="E1163" t="n">
-        <v>82.76000000000001</v>
+        <v>82.67</v>
       </c>
       <c r="F1163" t="n">
-        <v>77118</v>
+        <v>77961</v>
       </c>
     </row>
     <row r="1164">
@@ -23701,10 +23701,10 @@
         <v>82.2</v>
       </c>
       <c r="E1164" t="n">
-        <v>84.14</v>
+        <v>84.05</v>
       </c>
       <c r="F1164" t="n">
-        <v>101382</v>
+        <v>102303</v>
       </c>
     </row>
     <row r="1165">
@@ -23781,10 +23781,10 @@
         <v>84.98</v>
       </c>
       <c r="E1168" t="n">
-        <v>86.63</v>
+        <v>86.66</v>
       </c>
       <c r="F1168" t="n">
-        <v>83934</v>
+        <v>85007</v>
       </c>
     </row>
     <row r="1169">
@@ -23795,16 +23795,16 @@
         <v>86.63</v>
       </c>
       <c r="C1169" t="n">
-        <v>88.66</v>
+        <v>88.75</v>
       </c>
       <c r="D1169" t="n">
         <v>86.59</v>
       </c>
       <c r="E1169" t="n">
-        <v>88.64</v>
+        <v>88.68000000000001</v>
       </c>
       <c r="F1169" t="n">
-        <v>97671</v>
+        <v>98645</v>
       </c>
     </row>
     <row r="1170">
@@ -23881,10 +23881,10 @@
         <v>89.17</v>
       </c>
       <c r="E1173" t="n">
-        <v>89.76000000000001</v>
+        <v>89.47</v>
       </c>
       <c r="F1173" t="n">
-        <v>103067</v>
+        <v>104343</v>
       </c>
     </row>
     <row r="1174">
@@ -23901,10 +23901,10 @@
         <v>88.97</v>
       </c>
       <c r="E1174" t="n">
-        <v>90.2</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="F1174" t="n">
-        <v>100164</v>
+        <v>101197</v>
       </c>
     </row>
     <row r="1175">
@@ -23975,16 +23975,16 @@
         <v>91.56999999999999</v>
       </c>
       <c r="C1178" t="n">
-        <v>93.44</v>
+        <v>93.68000000000001</v>
       </c>
       <c r="D1178" t="n">
         <v>91.55</v>
       </c>
       <c r="E1178" t="n">
-        <v>93.36</v>
+        <v>93.56</v>
       </c>
       <c r="F1178" t="n">
-        <v>89908</v>
+        <v>91727</v>
       </c>
     </row>
     <row r="1179">
@@ -24001,10 +24001,10 @@
         <v>92.14</v>
       </c>
       <c r="E1179" t="n">
-        <v>93.52</v>
+        <v>93.56999999999999</v>
       </c>
       <c r="F1179" t="n">
-        <v>100530</v>
+        <v>101498</v>
       </c>
     </row>
     <row r="1180">
@@ -24081,10 +24081,10 @@
         <v>91.23999999999999</v>
       </c>
       <c r="E1183" t="n">
-        <v>92.27</v>
+        <v>92.20999999999999</v>
       </c>
       <c r="F1183" t="n">
-        <v>97207</v>
+        <v>98137</v>
       </c>
     </row>
     <row r="1184">
@@ -24101,10 +24101,10 @@
         <v>91.68000000000001</v>
       </c>
       <c r="E1184" t="n">
-        <v>92.31</v>
+        <v>92.28</v>
       </c>
       <c r="F1184" t="n">
-        <v>98960</v>
+        <v>99665</v>
       </c>
     </row>
     <row r="1185">
@@ -24181,10 +24181,10 @@
         <v>92.56</v>
       </c>
       <c r="E1188" t="n">
-        <v>92.94</v>
+        <v>92.89</v>
       </c>
       <c r="F1188" t="n">
-        <v>127194</v>
+        <v>128240</v>
       </c>
     </row>
     <row r="1189">
@@ -24201,10 +24201,10 @@
         <v>91.68000000000001</v>
       </c>
       <c r="E1189" t="n">
-        <v>91.95999999999999</v>
+        <v>91.8</v>
       </c>
       <c r="F1189" t="n">
-        <v>116761</v>
+        <v>117877</v>
       </c>
     </row>
     <row r="1190">
@@ -24281,10 +24281,10 @@
         <v>83.31999999999999</v>
       </c>
       <c r="E1193" t="n">
-        <v>83.68000000000001</v>
+        <v>83.72</v>
       </c>
       <c r="F1193" t="n">
-        <v>148426</v>
+        <v>149779</v>
       </c>
     </row>
     <row r="1194">
@@ -24301,10 +24301,10 @@
         <v>82.97</v>
       </c>
       <c r="E1194" t="n">
-        <v>83.88</v>
+        <v>83.79000000000001</v>
       </c>
       <c r="F1194" t="n">
-        <v>138785</v>
+        <v>140020</v>
       </c>
     </row>
     <row r="1195">
@@ -24381,10 +24381,10 @@
         <v>84.59</v>
       </c>
       <c r="E1198" t="n">
-        <v>85.7</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="F1198" t="n">
-        <v>123421</v>
+        <v>124560</v>
       </c>
     </row>
     <row r="1199">
@@ -24404,7 +24404,7 @@
         <v>89.93000000000001</v>
       </c>
       <c r="F1199" t="n">
-        <v>118765</v>
+        <v>120817</v>
       </c>
     </row>
     <row r="1200">
@@ -24475,16 +24475,16 @@
         <v>90.26000000000001</v>
       </c>
       <c r="C1203" t="n">
-        <v>92.22</v>
+        <v>92.34999999999999</v>
       </c>
       <c r="D1203" t="n">
         <v>88.69</v>
       </c>
       <c r="E1203" t="n">
-        <v>92.16</v>
+        <v>92.04000000000001</v>
       </c>
       <c r="F1203" t="n">
-        <v>109002</v>
+        <v>111224</v>
       </c>
     </row>
     <row r="1204">
@@ -24501,10 +24501,10 @@
         <v>90.63</v>
       </c>
       <c r="E1204" t="n">
-        <v>91.13</v>
+        <v>91.26000000000001</v>
       </c>
       <c r="F1204" t="n">
-        <v>109157</v>
+        <v>110661</v>
       </c>
     </row>
     <row r="1205">
@@ -24581,10 +24581,10 @@
         <v>86.48</v>
       </c>
       <c r="E1208" t="n">
-        <v>87.25</v>
+        <v>87.23999999999999</v>
       </c>
       <c r="F1208" t="n">
-        <v>113368</v>
+        <v>114536</v>
       </c>
     </row>
     <row r="1209">
@@ -24601,10 +24601,10 @@
         <v>86.76000000000001</v>
       </c>
       <c r="E1209" t="n">
-        <v>88.76000000000001</v>
+        <v>88.70999999999999</v>
       </c>
       <c r="F1209" t="n">
-        <v>121600</v>
+        <v>123231</v>
       </c>
     </row>
     <row r="1210">
@@ -24672,7 +24672,7 @@
         <v>45232</v>
       </c>
       <c r="B1213" t="n">
-        <v>84.83</v>
+        <v>85.03</v>
       </c>
       <c r="C1213" t="n">
         <v>86.88</v>
@@ -24684,7 +24684,7 @@
         <v>86.63</v>
       </c>
       <c r="F1213" t="n">
-        <v>103842</v>
+        <v>102261</v>
       </c>
     </row>
     <row r="1214">
@@ -24692,7 +24692,7 @@
         <v>45233</v>
       </c>
       <c r="B1214" t="n">
-        <v>86.70999999999999</v>
+        <v>86.66</v>
       </c>
       <c r="C1214" t="n">
         <v>87.58</v>
@@ -24704,7 +24704,7 @@
         <v>84.95</v>
       </c>
       <c r="F1214" t="n">
-        <v>119097</v>
+        <v>117913</v>
       </c>
     </row>
     <row r="1215">
@@ -24781,10 +24781,10 @@
         <v>79.33</v>
       </c>
       <c r="E1218" t="n">
-        <v>79.75</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="F1218" t="n">
-        <v>110739</v>
+        <v>111847</v>
       </c>
     </row>
     <row r="1219">
@@ -24801,10 +24801,10 @@
         <v>79.70999999999999</v>
       </c>
       <c r="E1219" t="n">
-        <v>81.36</v>
+        <v>81.43000000000001</v>
       </c>
       <c r="F1219" t="n">
-        <v>91256</v>
+        <v>92327</v>
       </c>
     </row>
     <row r="1220">
@@ -24881,10 +24881,10 @@
         <v>76.64</v>
       </c>
       <c r="E1223" t="n">
-        <v>77.43000000000001</v>
+        <v>77.45</v>
       </c>
       <c r="F1223" t="n">
-        <v>104766</v>
+        <v>105749</v>
       </c>
     </row>
     <row r="1224">
@@ -24901,10 +24901,10 @@
         <v>77.31</v>
       </c>
       <c r="E1224" t="n">
-        <v>80.37</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="F1224" t="n">
-        <v>88772</v>
+        <v>89648</v>
       </c>
     </row>
     <row r="1225">
@@ -25078,13 +25078,13 @@
         <v>84.51000000000001</v>
       </c>
       <c r="D1233" t="n">
-        <v>79.95</v>
+        <v>79.94</v>
       </c>
       <c r="E1233" t="n">
-        <v>80</v>
+        <v>80.31</v>
       </c>
       <c r="F1233" t="n">
-        <v>143673</v>
+        <v>145419</v>
       </c>
     </row>
     <row r="1234">
@@ -25101,10 +25101,10 @@
         <v>78.69</v>
       </c>
       <c r="E1234" t="n">
-        <v>78.93000000000001</v>
+        <v>79.02</v>
       </c>
       <c r="F1234" t="n">
-        <v>125186</v>
+        <v>126159</v>
       </c>
     </row>
     <row r="1235">
@@ -25181,10 +25181,10 @@
         <v>73.68000000000001</v>
       </c>
       <c r="E1238" t="n">
-        <v>74.47</v>
+        <v>74.39</v>
       </c>
       <c r="F1238" t="n">
-        <v>115986</v>
+        <v>116791</v>
       </c>
     </row>
     <row r="1239">
@@ -25201,10 +25201,10 @@
         <v>74.25</v>
       </c>
       <c r="E1239" t="n">
-        <v>75.87</v>
+        <v>75.94</v>
       </c>
       <c r="F1239" t="n">
-        <v>114085</v>
+        <v>114930</v>
       </c>
     </row>
     <row r="1240">
@@ -25281,10 +25281,10 @@
         <v>74.56999999999999</v>
       </c>
       <c r="E1243" t="n">
-        <v>76.86</v>
+        <v>76.75</v>
       </c>
       <c r="F1243" t="n">
-        <v>83845</v>
+        <v>84712</v>
       </c>
     </row>
     <row r="1244">
@@ -25301,10 +25301,10 @@
         <v>75.48</v>
       </c>
       <c r="E1244" t="n">
-        <v>76.90000000000001</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="F1244" t="n">
-        <v>94162</v>
+        <v>95068</v>
       </c>
     </row>
     <row r="1245">
@@ -25381,10 +25381,10 @@
         <v>77.76000000000001</v>
       </c>
       <c r="E1248" t="n">
-        <v>79.19</v>
+        <v>79.12</v>
       </c>
       <c r="F1248" t="n">
-        <v>91100</v>
+        <v>91755</v>
       </c>
     </row>
     <row r="1249">
@@ -25461,10 +25461,10 @@
         <v>77.04000000000001</v>
       </c>
       <c r="E1252" t="n">
-        <v>77.29000000000001</v>
+        <v>77.36</v>
       </c>
       <c r="F1252" t="n">
-        <v>94380</v>
+        <v>95204</v>
       </c>
     </row>
     <row r="1253">
@@ -25544,7 +25544,7 @@
         <v>77.53</v>
       </c>
       <c r="F1256" t="n">
-        <v>118273</v>
+        <v>119158</v>
       </c>
     </row>
     <row r="1257">
@@ -25641,10 +25641,10 @@
         <v>76.45</v>
       </c>
       <c r="E1261" t="n">
-        <v>77.61</v>
+        <v>78.01000000000001</v>
       </c>
       <c r="F1261" t="n">
-        <v>128067</v>
+        <v>129868</v>
       </c>
     </row>
     <row r="1262">
@@ -25741,10 +25741,10 @@
         <v>76.98</v>
       </c>
       <c r="E1266" t="n">
-        <v>78.63</v>
+        <v>78.56</v>
       </c>
       <c r="F1266" t="n">
-        <v>98609</v>
+        <v>99368</v>
       </c>
     </row>
     <row r="1267">
@@ -25841,10 +25841,10 @@
         <v>79.65000000000001</v>
       </c>
       <c r="E1271" t="n">
-        <v>81.84999999999999</v>
+        <v>81.69</v>
       </c>
       <c r="F1271" t="n">
-        <v>75889</v>
+        <v>76710</v>
       </c>
     </row>
     <row r="1272">
@@ -25861,10 +25861,10 @@
         <v>80.75</v>
       </c>
       <c r="E1272" t="n">
-        <v>83.08</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="F1272" t="n">
-        <v>85666</v>
+        <v>87047</v>
       </c>
     </row>
     <row r="1273">
@@ -25941,10 +25941,10 @@
         <v>78.5</v>
       </c>
       <c r="E1276" t="n">
-        <v>78.64</v>
+        <v>78.7</v>
       </c>
       <c r="F1276" t="n">
-        <v>138682</v>
+        <v>140571</v>
       </c>
     </row>
     <row r="1277">
@@ -25961,10 +25961,10 @@
         <v>76.78</v>
       </c>
       <c r="E1277" t="n">
-        <v>77.11</v>
+        <v>77.31999999999999</v>
       </c>
       <c r="F1277" t="n">
-        <v>132023</v>
+        <v>133396</v>
       </c>
     </row>
     <row r="1278">
@@ -26041,10 +26041,10 @@
         <v>78.84999999999999</v>
       </c>
       <c r="E1281" t="n">
-        <v>81.51000000000001</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="F1281" t="n">
-        <v>86597</v>
+        <v>87658</v>
       </c>
     </row>
     <row r="1282">
@@ -26064,7 +26064,7 @@
         <v>81.63</v>
       </c>
       <c r="F1282" t="n">
-        <v>85346</v>
+        <v>86235</v>
       </c>
     </row>
     <row r="1283">
@@ -26141,10 +26141,10 @@
         <v>80.31999999999999</v>
       </c>
       <c r="E1286" t="n">
-        <v>82.37</v>
+        <v>82.22</v>
       </c>
       <c r="F1286" t="n">
-        <v>83753</v>
+        <v>84560</v>
       </c>
     </row>
     <row r="1287">
@@ -26161,10 +26161,10 @@
         <v>81.34</v>
       </c>
       <c r="E1287" t="n">
-        <v>82.70999999999999</v>
+        <v>82.68000000000001</v>
       </c>
       <c r="F1287" t="n">
-        <v>80620</v>
+        <v>81459</v>
       </c>
     </row>
     <row r="1288">
@@ -26241,10 +26241,10 @@
         <v>81.45</v>
       </c>
       <c r="E1291" t="n">
-        <v>82.63</v>
+        <v>82.51000000000001</v>
       </c>
       <c r="F1291" t="n">
-        <v>67106</v>
+        <v>67848</v>
       </c>
     </row>
     <row r="1292">
@@ -26261,10 +26261,10 @@
         <v>80.65000000000001</v>
       </c>
       <c r="E1292" t="n">
-        <v>80.88</v>
+        <v>80.84</v>
       </c>
       <c r="F1292" t="n">
-        <v>72495</v>
+        <v>73168</v>
       </c>
     </row>
     <row r="1293">
@@ -26341,10 +26341,10 @@
         <v>81.37</v>
       </c>
       <c r="E1296" t="n">
-        <v>81.70999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="F1296" t="n">
-        <v>78801</v>
+        <v>79642</v>
       </c>
     </row>
     <row r="1297">
@@ -26361,10 +26361,10 @@
         <v>81.63</v>
       </c>
       <c r="E1297" t="n">
-        <v>83.19</v>
+        <v>83.12</v>
       </c>
       <c r="F1297" t="n">
-        <v>72423</v>
+        <v>73275</v>
       </c>
     </row>
     <row r="1298">
@@ -26441,10 +26441,10 @@
         <v>81.77</v>
       </c>
       <c r="E1301" t="n">
-        <v>82.52</v>
+        <v>82.87</v>
       </c>
       <c r="F1301" t="n">
-        <v>102278</v>
+        <v>103853</v>
       </c>
     </row>
     <row r="1302">
@@ -26461,10 +26461,10 @@
         <v>81.41</v>
       </c>
       <c r="E1302" t="n">
-        <v>81.66</v>
+        <v>81.55</v>
       </c>
       <c r="F1302" t="n">
-        <v>99175</v>
+        <v>100115</v>
       </c>
     </row>
     <row r="1303">
@@ -26532,19 +26532,19 @@
         <v>45365</v>
       </c>
       <c r="B1306" t="n">
-        <v>83.59999999999999</v>
+        <v>83.69</v>
       </c>
       <c r="C1306" t="n">
         <v>85.18000000000001</v>
       </c>
       <c r="D1306" t="n">
-        <v>83.53</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="E1306" t="n">
         <v>84.61</v>
       </c>
       <c r="F1306" t="n">
-        <v>71844</v>
+        <v>71119</v>
       </c>
     </row>
     <row r="1307">
@@ -26552,7 +26552,7 @@
         <v>45366</v>
       </c>
       <c r="B1307" t="n">
-        <v>84.65000000000001</v>
+        <v>84.68000000000001</v>
       </c>
       <c r="C1307" t="n">
         <v>85.09</v>
@@ -26564,7 +26564,7 @@
         <v>84.83</v>
       </c>
       <c r="F1307" t="n">
-        <v>75864</v>
+        <v>74945</v>
       </c>
     </row>
     <row r="1308">
@@ -26632,7 +26632,7 @@
         <v>45372</v>
       </c>
       <c r="B1311" t="n">
-        <v>85.70999999999999</v>
+        <v>85.81</v>
       </c>
       <c r="C1311" t="n">
         <v>86.03</v>
@@ -26644,7 +26644,7 @@
         <v>84.95999999999999</v>
       </c>
       <c r="F1311" t="n">
-        <v>67186</v>
+        <v>66113</v>
       </c>
     </row>
     <row r="1312">
@@ -26652,7 +26652,7 @@
         <v>45373</v>
       </c>
       <c r="B1312" t="n">
-        <v>85.09999999999999</v>
+        <v>84.98999999999999</v>
       </c>
       <c r="C1312" t="n">
         <v>85.58</v>
@@ -26664,7 +26664,7 @@
         <v>84.93000000000001</v>
       </c>
       <c r="F1312" t="n">
-        <v>54286</v>
+        <v>53666</v>
       </c>
     </row>
     <row r="1313">
@@ -26732,7 +26732,7 @@
         <v>45379</v>
       </c>
       <c r="B1316" t="n">
-        <v>85.56</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="C1316" t="n">
         <v>86.89</v>
@@ -26744,7 +26744,7 @@
         <v>86.67</v>
       </c>
       <c r="F1316" t="n">
-        <v>57372</v>
+        <v>56915</v>
       </c>
     </row>
     <row r="1317">
@@ -26821,10 +26821,10 @@
         <v>88.43000000000001</v>
       </c>
       <c r="E1320" t="n">
-        <v>90.38</v>
+        <v>90.56</v>
       </c>
       <c r="F1320" t="n">
-        <v>74470</v>
+        <v>75666</v>
       </c>
     </row>
     <row r="1321">
@@ -26841,10 +26841,10 @@
         <v>90.18000000000001</v>
       </c>
       <c r="E1321" t="n">
-        <v>90.52</v>
+        <v>90.39</v>
       </c>
       <c r="F1321" t="n">
-        <v>79937</v>
+        <v>80607</v>
       </c>
     </row>
     <row r="1322">
@@ -26921,10 +26921,10 @@
         <v>88.87</v>
       </c>
       <c r="E1325" t="n">
-        <v>89.68000000000001</v>
+        <v>89.55</v>
       </c>
       <c r="F1325" t="n">
-        <v>107040</v>
+        <v>107884</v>
       </c>
     </row>
     <row r="1326">
@@ -26941,10 +26941,10 @@
         <v>89.45</v>
       </c>
       <c r="E1326" t="n">
-        <v>89.73</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="F1326" t="n">
-        <v>108331</v>
+        <v>109120</v>
       </c>
     </row>
     <row r="1327">
@@ -27021,10 +27021,10 @@
         <v>85.63</v>
       </c>
       <c r="E1330" t="n">
-        <v>86.47</v>
+        <v>86.19</v>
       </c>
       <c r="F1330" t="n">
-        <v>107464</v>
+        <v>108132</v>
       </c>
     </row>
     <row r="1331">
@@ -27041,10 +27041,10 @@
         <v>85.61</v>
       </c>
       <c r="E1331" t="n">
-        <v>86.51000000000001</v>
+        <v>86.38</v>
       </c>
       <c r="F1331" t="n">
-        <v>143518</v>
+        <v>144473</v>
       </c>
     </row>
     <row r="1332">
@@ -27115,16 +27115,16 @@
         <v>86.88</v>
       </c>
       <c r="C1335" t="n">
-        <v>87.97</v>
+        <v>88</v>
       </c>
       <c r="D1335" t="n">
         <v>86.2</v>
       </c>
       <c r="E1335" t="n">
-        <v>87.95</v>
+        <v>87.83</v>
       </c>
       <c r="F1335" t="n">
-        <v>69439</v>
+        <v>70059</v>
       </c>
     </row>
     <row r="1336">
@@ -27141,10 +27141,10 @@
         <v>87.56999999999999</v>
       </c>
       <c r="E1336" t="n">
-        <v>87.98999999999999</v>
+        <v>87.89</v>
       </c>
       <c r="F1336" t="n">
-        <v>63936</v>
+        <v>64445</v>
       </c>
     </row>
     <row r="1337">
@@ -27221,10 +27221,10 @@
         <v>82.89</v>
       </c>
       <c r="E1340" t="n">
-        <v>83.47</v>
+        <v>83.48</v>
       </c>
       <c r="F1340" t="n">
-        <v>100961</v>
+        <v>101847</v>
       </c>
     </row>
     <row r="1341">
@@ -27238,13 +27238,13 @@
         <v>84.18000000000001</v>
       </c>
       <c r="D1341" t="n">
-        <v>82.65000000000001</v>
+        <v>82.53</v>
       </c>
       <c r="E1341" t="n">
-        <v>82.77</v>
+        <v>82.54000000000001</v>
       </c>
       <c r="F1341" t="n">
-        <v>82987</v>
+        <v>83584</v>
       </c>
     </row>
     <row r="1342">
@@ -27321,10 +27321,10 @@
         <v>83.18000000000001</v>
       </c>
       <c r="E1345" t="n">
-        <v>83.91</v>
+        <v>83.77</v>
       </c>
       <c r="F1345" t="n">
-        <v>67201</v>
+        <v>67737</v>
       </c>
     </row>
     <row r="1346">
@@ -27338,13 +27338,13 @@
         <v>84.23</v>
       </c>
       <c r="D1346" t="n">
-        <v>82.5</v>
+        <v>82.36</v>
       </c>
       <c r="E1346" t="n">
-        <v>82.61</v>
+        <v>82.36</v>
       </c>
       <c r="F1346" t="n">
-        <v>62356</v>
+        <v>63117</v>
       </c>
     </row>
     <row r="1347">
@@ -27421,10 +27421,10 @@
         <v>82.02</v>
       </c>
       <c r="E1350" t="n">
-        <v>83.04000000000001</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="F1350" t="n">
-        <v>65306</v>
+        <v>65759</v>
       </c>
     </row>
     <row r="1351">
@@ -27441,10 +27441,10 @@
         <v>82.81999999999999</v>
       </c>
       <c r="E1351" t="n">
-        <v>83.68000000000001</v>
+        <v>83.56</v>
       </c>
       <c r="F1351" t="n">
-        <v>60667</v>
+        <v>61133</v>
       </c>
     </row>
     <row r="1352">
@@ -27521,10 +27521,10 @@
         <v>80.7</v>
       </c>
       <c r="E1355" t="n">
-        <v>81.09</v>
+        <v>81.06999999999999</v>
       </c>
       <c r="F1355" t="n">
-        <v>68901</v>
+        <v>69958</v>
       </c>
     </row>
     <row r="1356">
@@ -27541,10 +27541,10 @@
         <v>80.42</v>
       </c>
       <c r="E1356" t="n">
-        <v>81.84999999999999</v>
+        <v>81.79000000000001</v>
       </c>
       <c r="F1356" t="n">
-        <v>56045</v>
+        <v>56381</v>
       </c>
     </row>
     <row r="1357">
@@ -27618,13 +27618,13 @@
         <v>83.51000000000001</v>
       </c>
       <c r="D1360" t="n">
-        <v>81.77</v>
+        <v>81.72</v>
       </c>
       <c r="E1360" t="n">
-        <v>81.88</v>
+        <v>81.73</v>
       </c>
       <c r="F1360" t="n">
-        <v>81262</v>
+        <v>81864</v>
       </c>
     </row>
     <row r="1361">
@@ -27641,10 +27641,10 @@
         <v>80.69</v>
       </c>
       <c r="E1361" t="n">
-        <v>81.22</v>
+        <v>81.09</v>
       </c>
       <c r="F1361" t="n">
-        <v>86335</v>
+        <v>87130</v>
       </c>
     </row>
     <row r="1362">
@@ -27721,10 +27721,10 @@
         <v>78.23999999999999</v>
       </c>
       <c r="E1365" t="n">
-        <v>79.73</v>
+        <v>79.69</v>
       </c>
       <c r="F1365" t="n">
-        <v>72035</v>
+        <v>72677</v>
       </c>
     </row>
     <row r="1366">
@@ -27741,10 +27741,10 @@
         <v>79.18000000000001</v>
       </c>
       <c r="E1366" t="n">
-        <v>79.27</v>
+        <v>79.23999999999999</v>
       </c>
       <c r="F1366" t="n">
-        <v>76576</v>
+        <v>77440</v>
       </c>
     </row>
     <row r="1367">
@@ -27821,10 +27821,10 @@
         <v>81.53</v>
       </c>
       <c r="E1370" t="n">
-        <v>81.98</v>
+        <v>81.68000000000001</v>
       </c>
       <c r="F1370" t="n">
-        <v>78296</v>
+        <v>79567</v>
       </c>
     </row>
     <row r="1371">
@@ -27841,10 +27841,10 @@
         <v>81.64</v>
       </c>
       <c r="E1371" t="n">
-        <v>82.2</v>
+        <v>82.06</v>
       </c>
       <c r="F1371" t="n">
-        <v>75030</v>
+        <v>75768</v>
       </c>
     </row>
     <row r="1372">
@@ -27921,10 +27921,10 @@
         <v>84.28</v>
       </c>
       <c r="E1375" t="n">
-        <v>85.01000000000001</v>
+        <v>84.7</v>
       </c>
       <c r="F1375" t="n">
-        <v>59448</v>
+        <v>59846</v>
       </c>
     </row>
     <row r="1376">
@@ -27941,10 +27941,10 @@
         <v>84</v>
       </c>
       <c r="E1376" t="n">
-        <v>84.31</v>
+        <v>84.16</v>
       </c>
       <c r="F1376" t="n">
-        <v>59797</v>
+        <v>60278</v>
       </c>
     </row>
     <row r="1377">
@@ -28021,10 +28021,10 @@
         <v>84.01000000000001</v>
       </c>
       <c r="E1380" t="n">
-        <v>85.25</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="F1380" t="n">
-        <v>64362</v>
+        <v>64909</v>
       </c>
     </row>
     <row r="1381">
@@ -28041,10 +28041,10 @@
         <v>84.39</v>
       </c>
       <c r="E1381" t="n">
-        <v>84.79000000000001</v>
+        <v>84.65000000000001</v>
       </c>
       <c r="F1381" t="n">
-        <v>69177</v>
+        <v>69862</v>
       </c>
     </row>
     <row r="1382">
@@ -28141,10 +28141,10 @@
         <v>86.17</v>
       </c>
       <c r="E1386" t="n">
-        <v>86.31999999999999</v>
+        <v>86.43000000000001</v>
       </c>
       <c r="F1386" t="n">
-        <v>67919</v>
+        <v>68965</v>
       </c>
     </row>
     <row r="1387">
@@ -28221,10 +28221,10 @@
         <v>84.16</v>
       </c>
       <c r="E1390" t="n">
-        <v>85.19</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="F1390" t="n">
-        <v>78243</v>
+        <v>78990</v>
       </c>
     </row>
     <row r="1391">
@@ -28238,13 +28238,13 @@
         <v>85.67</v>
       </c>
       <c r="D1391" t="n">
-        <v>84.40000000000001</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="E1391" t="n">
-        <v>84.5</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="F1391" t="n">
-        <v>73607</v>
+        <v>74302</v>
       </c>
     </row>
     <row r="1392">
@@ -28321,10 +28321,10 @@
         <v>83.41</v>
       </c>
       <c r="E1395" t="n">
-        <v>83.72</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="F1395" t="n">
-        <v>68620</v>
+        <v>69797</v>
       </c>
     </row>
     <row r="1396">
@@ -28338,13 +28338,13 @@
         <v>84.41</v>
       </c>
       <c r="D1396" t="n">
-        <v>81.7</v>
+        <v>81.64</v>
       </c>
       <c r="E1396" t="n">
-        <v>81.89</v>
+        <v>81.64</v>
       </c>
       <c r="F1396" t="n">
-        <v>72020</v>
+        <v>72736</v>
       </c>
     </row>
     <row r="1397">
@@ -28421,10 +28421,10 @@
         <v>79.28</v>
       </c>
       <c r="E1400" t="n">
-        <v>81.33</v>
+        <v>81.37</v>
       </c>
       <c r="F1400" t="n">
-        <v>69150</v>
+        <v>69789</v>
       </c>
     </row>
     <row r="1401">
@@ -28441,10 +28441,10 @@
         <v>79.39</v>
       </c>
       <c r="E1401" t="n">
-        <v>79.92</v>
+        <v>79.48999999999999</v>
       </c>
       <c r="F1401" t="n">
-        <v>64725</v>
+        <v>65748</v>
       </c>
     </row>
     <row r="1402">
@@ -28521,10 +28521,10 @@
         <v>79.3</v>
       </c>
       <c r="E1405" t="n">
-        <v>80</v>
+        <v>79.83</v>
       </c>
       <c r="F1405" t="n">
-        <v>104482</v>
+        <v>105741</v>
       </c>
     </row>
     <row r="1406">
@@ -28541,10 +28541,10 @@
         <v>76.26000000000001</v>
       </c>
       <c r="E1406" t="n">
-        <v>77.08</v>
+        <v>77.14</v>
       </c>
       <c r="F1406" t="n">
-        <v>124356</v>
+        <v>125792</v>
       </c>
     </row>
     <row r="1407">
@@ -28621,10 +28621,10 @@
         <v>77.33</v>
       </c>
       <c r="E1410" t="n">
-        <v>78.73999999999999</v>
+        <v>78.59</v>
       </c>
       <c r="F1410" t="n">
-        <v>113028</v>
+        <v>113892</v>
       </c>
     </row>
     <row r="1411">
@@ -28641,10 +28641,10 @@
         <v>78.43000000000001</v>
       </c>
       <c r="E1411" t="n">
-        <v>79.34</v>
+        <v>79.27</v>
       </c>
       <c r="F1411" t="n">
-        <v>86405</v>
+        <v>87467</v>
       </c>
     </row>
     <row r="1412">
@@ -28721,10 +28721,10 @@
         <v>79.11</v>
       </c>
       <c r="E1415" t="n">
-        <v>80.31999999999999</v>
+        <v>80.26000000000001</v>
       </c>
       <c r="F1415" t="n">
-        <v>78757</v>
+        <v>79567</v>
       </c>
     </row>
     <row r="1416">
@@ -28741,10 +28741,10 @@
         <v>78.09</v>
       </c>
       <c r="E1416" t="n">
-        <v>79.22</v>
+        <v>78.94</v>
       </c>
       <c r="F1416" t="n">
-        <v>81009</v>
+        <v>82030</v>
       </c>
     </row>
     <row r="1417">
@@ -28821,10 +28821,10 @@
         <v>75.25</v>
       </c>
       <c r="E1420" t="n">
-        <v>76.47</v>
+        <v>76.42</v>
       </c>
       <c r="F1420" t="n">
-        <v>79280</v>
+        <v>79873</v>
       </c>
     </row>
     <row r="1421">
@@ -28841,10 +28841,10 @@
         <v>76.40000000000001</v>
       </c>
       <c r="E1421" t="n">
-        <v>78.17</v>
+        <v>78.13</v>
       </c>
       <c r="F1421" t="n">
-        <v>68613</v>
+        <v>69081</v>
       </c>
     </row>
     <row r="1422">
@@ -28921,10 +28921,10 @@
         <v>76.90000000000001</v>
       </c>
       <c r="E1425" t="n">
-        <v>78.81</v>
+        <v>78.72</v>
       </c>
       <c r="F1425" t="n">
-        <v>93699</v>
+        <v>94397</v>
       </c>
     </row>
     <row r="1426">
@@ -28941,10 +28941,10 @@
         <v>76.56</v>
       </c>
       <c r="E1426" t="n">
-        <v>76.81</v>
+        <v>76.77</v>
       </c>
       <c r="F1426" t="n">
-        <v>108329</v>
+        <v>109124</v>
       </c>
     </row>
     <row r="1427">
@@ -29021,10 +29021,10 @@
         <v>72.20999999999999</v>
       </c>
       <c r="E1430" t="n">
-        <v>72.54000000000001</v>
+        <v>72.53</v>
       </c>
       <c r="F1430" t="n">
-        <v>108713</v>
+        <v>109541</v>
       </c>
     </row>
     <row r="1431">
@@ -29041,10 +29041,10 @@
         <v>70.45</v>
       </c>
       <c r="E1431" t="n">
-        <v>71.37</v>
+        <v>71.2</v>
       </c>
       <c r="F1431" t="n">
-        <v>115759</v>
+        <v>116954</v>
       </c>
     </row>
     <row r="1432">
@@ -29121,10 +29121,10 @@
         <v>70.31999999999999</v>
       </c>
       <c r="E1435" t="n">
-        <v>71.89</v>
+        <v>71.67</v>
       </c>
       <c r="F1435" t="n">
-        <v>114181</v>
+        <v>115156</v>
       </c>
     </row>
     <row r="1436">
@@ -29141,10 +29141,10 @@
         <v>71.09</v>
       </c>
       <c r="E1436" t="n">
-        <v>71.73</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="F1436" t="n">
-        <v>98569</v>
+        <v>99629</v>
       </c>
     </row>
     <row r="1437">
@@ -29221,10 +29221,10 @@
         <v>72.26000000000001</v>
       </c>
       <c r="E1440" t="n">
-        <v>74.05</v>
+        <v>73.97</v>
       </c>
       <c r="F1440" t="n">
-        <v>88395</v>
+        <v>89094</v>
       </c>
     </row>
     <row r="1441">
@@ -29241,10 +29241,10 @@
         <v>73.28</v>
       </c>
       <c r="E1441" t="n">
-        <v>73.98</v>
+        <v>73.87</v>
       </c>
       <c r="F1441" t="n">
-        <v>71635</v>
+        <v>72413</v>
       </c>
     </row>
     <row r="1442">
@@ -29321,10 +29321,10 @@
         <v>70.20999999999999</v>
       </c>
       <c r="E1445" t="n">
-        <v>70.66</v>
+        <v>70.68000000000001</v>
       </c>
       <c r="F1445" t="n">
-        <v>154979</v>
+        <v>155899</v>
       </c>
     </row>
     <row r="1446">
@@ -29335,16 +29335,16 @@
         <v>70.68000000000001</v>
       </c>
       <c r="C1446" t="n">
-        <v>71.89</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="D1446" t="n">
         <v>70.39</v>
       </c>
       <c r="E1446" t="n">
-        <v>71.81999999999999</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="F1446" t="n">
-        <v>122438</v>
+        <v>123787</v>
       </c>
     </row>
     <row r="1447">
@@ -29421,10 +29421,10 @@
         <v>74.18000000000001</v>
       </c>
       <c r="E1450" t="n">
-        <v>77.58</v>
+        <v>77.28</v>
       </c>
       <c r="F1450" t="n">
-        <v>123449</v>
+        <v>125075</v>
       </c>
     </row>
     <row r="1451">
@@ -29441,10 +29441,10 @@
         <v>77.19</v>
       </c>
       <c r="E1451" t="n">
-        <v>77.87</v>
+        <v>77.73</v>
       </c>
       <c r="F1451" t="n">
-        <v>120535</v>
+        <v>121412</v>
       </c>
     </row>
     <row r="1452">
@@ -38804,7 +38804,27 @@
         <v>86.87</v>
       </c>
       <c r="F1919" t="n">
-        <v>118721</v>
+        <v>118707</v>
+      </c>
+    </row>
+    <row r="1920">
+      <c r="A1920" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B1920" t="n">
+        <v>86.89</v>
+      </c>
+      <c r="C1920" t="n">
+        <v>89.69</v>
+      </c>
+      <c r="D1920" t="n">
+        <v>84.28</v>
+      </c>
+      <c r="E1920" t="n">
+        <v>89.69</v>
+      </c>
+      <c r="F1920" t="n">
+        <v>118408</v>
       </c>
     </row>
   </sheetData>

--- a/database/BRENT.xlsx
+++ b/database/BRENT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1920"/>
+  <dimension ref="A1:F1921"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38804,7 +38804,7 @@
         <v>86.87</v>
       </c>
       <c r="F1919" t="n">
-        <v>118707</v>
+        <v>118722</v>
       </c>
     </row>
     <row r="1920">
@@ -38825,6 +38825,26 @@
       </c>
       <c r="F1920" t="n">
         <v>118408</v>
+      </c>
+    </row>
+    <row r="1921">
+      <c r="A1921" s="1" t="n">
+        <v>46236</v>
+      </c>
+      <c r="B1921" t="n">
+        <v>82.64</v>
+      </c>
+      <c r="C1921" t="n">
+        <v>84.06999999999999</v>
+      </c>
+      <c r="D1921" t="n">
+        <v>81.48999999999999</v>
+      </c>
+      <c r="E1921" t="n">
+        <v>82.90000000000001</v>
+      </c>
+      <c r="F1921" t="n">
+        <v>120574</v>
       </c>
     </row>
   </sheetData>

--- a/database/BRENT.xlsx
+++ b/database/BRENT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1921"/>
+  <dimension ref="A1:F1922"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3881,10 +3881,10 @@
         <v>60.96</v>
       </c>
       <c r="E173" t="n">
-        <v>61.65</v>
+        <v>61.74</v>
       </c>
       <c r="F173" t="n">
-        <v>7745</v>
+        <v>7439</v>
       </c>
     </row>
     <row r="174">
@@ -3952,7 +3952,7 @@
         <v>43769</v>
       </c>
       <c r="B177" t="n">
-        <v>60.27</v>
+        <v>60.17</v>
       </c>
       <c r="C177" t="n">
         <v>60.79</v>
@@ -3964,7 +3964,7 @@
         <v>59.46</v>
       </c>
       <c r="F177" t="n">
-        <v>20603</v>
+        <v>20831</v>
       </c>
     </row>
     <row r="178">
@@ -3972,7 +3972,7 @@
         <v>43770</v>
       </c>
       <c r="B178" t="n">
-        <v>59.64</v>
+        <v>59.42</v>
       </c>
       <c r="C178" t="n">
         <v>61.8</v>
@@ -3984,7 +3984,7 @@
         <v>61.65</v>
       </c>
       <c r="F178" t="n">
-        <v>18281</v>
+        <v>18539</v>
       </c>
     </row>
     <row r="179">
@@ -4061,10 +4061,10 @@
         <v>61.63</v>
       </c>
       <c r="E182" t="n">
-        <v>62.29</v>
+        <v>62.14</v>
       </c>
       <c r="F182" t="n">
-        <v>19680</v>
+        <v>19306</v>
       </c>
     </row>
     <row r="183">
@@ -4081,10 +4081,10 @@
         <v>60.65</v>
       </c>
       <c r="E183" t="n">
-        <v>62.64</v>
+        <v>62.61</v>
       </c>
       <c r="F183" t="n">
-        <v>21863</v>
+        <v>21625</v>
       </c>
     </row>
     <row r="184">
@@ -4161,10 +4161,10 @@
         <v>62.14</v>
       </c>
       <c r="E187" t="n">
-        <v>62.33</v>
+        <v>62.38</v>
       </c>
       <c r="F187" t="n">
-        <v>19293</v>
+        <v>19157</v>
       </c>
     </row>
     <row r="188">
@@ -4181,10 +4181,10 @@
         <v>61.69</v>
       </c>
       <c r="E188" t="n">
-        <v>63.41</v>
+        <v>63.32</v>
       </c>
       <c r="F188" t="n">
-        <v>16092</v>
+        <v>15801</v>
       </c>
     </row>
     <row r="189">
@@ -4261,10 +4261,10 @@
         <v>61.91</v>
       </c>
       <c r="E192" t="n">
-        <v>63.64</v>
+        <v>63.74</v>
       </c>
       <c r="F192" t="n">
-        <v>21823</v>
+        <v>21582</v>
       </c>
     </row>
     <row r="193">
@@ -4281,10 +4281,10 @@
         <v>61.92</v>
       </c>
       <c r="E193" t="n">
-        <v>62.52</v>
+        <v>62.58</v>
       </c>
       <c r="F193" t="n">
-        <v>17794</v>
+        <v>17577</v>
       </c>
     </row>
     <row r="194">
@@ -4461,10 +4461,10 @@
         <v>62.73</v>
       </c>
       <c r="E202" t="n">
-        <v>63.26</v>
+        <v>63.33</v>
       </c>
       <c r="F202" t="n">
-        <v>24300</v>
+        <v>24042</v>
       </c>
     </row>
     <row r="203">
@@ -4481,10 +4481,10 @@
         <v>62.82</v>
       </c>
       <c r="E203" t="n">
-        <v>64.34</v>
+        <v>64.22</v>
       </c>
       <c r="F203" t="n">
-        <v>22572</v>
+        <v>22359</v>
       </c>
     </row>
     <row r="204">
@@ -4561,10 +4561,10 @@
         <v>63.86</v>
       </c>
       <c r="E207" t="n">
-        <v>64.28</v>
+        <v>64.31</v>
       </c>
       <c r="F207" t="n">
-        <v>18454</v>
+        <v>18198</v>
       </c>
     </row>
     <row r="208">
@@ -4581,10 +4581,10 @@
         <v>64.48</v>
       </c>
       <c r="E208" t="n">
-        <v>64.90000000000001</v>
+        <v>64.88</v>
       </c>
       <c r="F208" t="n">
-        <v>21671</v>
+        <v>21484</v>
       </c>
     </row>
     <row r="209">
@@ -4661,10 +4661,10 @@
         <v>66.02</v>
       </c>
       <c r="E212" t="n">
-        <v>66.53</v>
+        <v>66.45</v>
       </c>
       <c r="F212" t="n">
-        <v>11180</v>
+        <v>10932</v>
       </c>
     </row>
     <row r="213">
@@ -4681,10 +4681,10 @@
         <v>65.72</v>
       </c>
       <c r="E213" t="n">
-        <v>66.01000000000001</v>
+        <v>65.98</v>
       </c>
       <c r="F213" t="n">
-        <v>14806</v>
+        <v>14693</v>
       </c>
     </row>
     <row r="214">
@@ -4741,10 +4741,10 @@
         <v>66.09</v>
       </c>
       <c r="E216" t="n">
-        <v>66.75</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="F216" t="n">
-        <v>9613</v>
+        <v>9409</v>
       </c>
     </row>
     <row r="217">
@@ -4761,10 +4761,10 @@
         <v>66.34</v>
       </c>
       <c r="E217" t="n">
-        <v>66.84</v>
+        <v>66.81</v>
       </c>
       <c r="F217" t="n">
-        <v>11398</v>
+        <v>11272</v>
       </c>
     </row>
     <row r="218">
@@ -4821,10 +4821,10 @@
         <v>65.7</v>
       </c>
       <c r="E220" t="n">
-        <v>66.23</v>
+        <v>66.19</v>
       </c>
       <c r="F220" t="n">
-        <v>15351</v>
+        <v>15153</v>
       </c>
     </row>
     <row r="221">
@@ -4841,10 +4841,10 @@
         <v>66.19</v>
       </c>
       <c r="E221" t="n">
-        <v>68.59</v>
+        <v>68.55</v>
       </c>
       <c r="F221" t="n">
-        <v>35609</v>
+        <v>35427</v>
       </c>
     </row>
     <row r="222">
@@ -4924,7 +4924,7 @@
         <v>65.38</v>
       </c>
       <c r="F225" t="n">
-        <v>25951</v>
+        <v>25682</v>
       </c>
     </row>
     <row r="226">
@@ -4944,7 +4944,7 @@
         <v>65</v>
       </c>
       <c r="F226" t="n">
-        <v>20436</v>
+        <v>20016</v>
       </c>
     </row>
     <row r="227">
@@ -5021,10 +5021,10 @@
         <v>63.89</v>
       </c>
       <c r="E230" t="n">
-        <v>64.7</v>
+        <v>64.64</v>
       </c>
       <c r="F230" t="n">
-        <v>16472</v>
+        <v>16107</v>
       </c>
     </row>
     <row r="231">
@@ -5041,10 +5041,10 @@
         <v>64.45</v>
       </c>
       <c r="E231" t="n">
-        <v>65.08</v>
+        <v>64.95</v>
       </c>
       <c r="F231" t="n">
-        <v>16251</v>
+        <v>16060</v>
       </c>
     </row>
     <row r="232">
@@ -5121,10 +5121,10 @@
         <v>61.24</v>
       </c>
       <c r="E235" t="n">
-        <v>62.11</v>
+        <v>61.97</v>
       </c>
       <c r="F235" t="n">
-        <v>23208</v>
+        <v>22982</v>
       </c>
     </row>
     <row r="236">
@@ -5141,10 +5141,10 @@
         <v>60.24</v>
       </c>
       <c r="E236" t="n">
-        <v>60.64</v>
+        <v>60.82</v>
       </c>
       <c r="F236" t="n">
-        <v>21687</v>
+        <v>21411</v>
       </c>
     </row>
     <row r="237">
@@ -5221,10 +5221,10 @@
         <v>56.73</v>
       </c>
       <c r="E240" t="n">
-        <v>58.2</v>
+        <v>58.03</v>
       </c>
       <c r="F240" t="n">
-        <v>28894</v>
+        <v>28317</v>
       </c>
     </row>
     <row r="241">
@@ -5244,7 +5244,7 @@
         <v>56.63</v>
       </c>
       <c r="F241" t="n">
-        <v>31264</v>
+        <v>30854</v>
       </c>
     </row>
     <row r="242">
@@ -5321,10 +5321,10 @@
         <v>54.24</v>
       </c>
       <c r="E245" t="n">
-        <v>55.14</v>
+        <v>55.07</v>
       </c>
       <c r="F245" t="n">
-        <v>31917</v>
+        <v>31638</v>
       </c>
     </row>
     <row r="246">
@@ -5341,10 +5341,10 @@
         <v>54.2</v>
       </c>
       <c r="E246" t="n">
-        <v>54.45</v>
+        <v>54.48</v>
       </c>
       <c r="F246" t="n">
-        <v>26144</v>
+        <v>25828</v>
       </c>
     </row>
     <row r="247">
@@ -5421,10 +5421,10 @@
         <v>54.95</v>
       </c>
       <c r="E250" t="n">
-        <v>56.4</v>
+        <v>56.51</v>
       </c>
       <c r="F250" t="n">
-        <v>24914</v>
+        <v>24675</v>
       </c>
     </row>
     <row r="251">
@@ -5441,10 +5441,10 @@
         <v>56.13</v>
       </c>
       <c r="E251" t="n">
-        <v>57.33</v>
+        <v>57.32</v>
       </c>
       <c r="F251" t="n">
-        <v>21778</v>
+        <v>21410</v>
       </c>
     </row>
     <row r="252">
@@ -5521,10 +5521,10 @@
         <v>58.89</v>
       </c>
       <c r="E255" t="n">
-        <v>59.03</v>
+        <v>59.28</v>
       </c>
       <c r="F255" t="n">
-        <v>23391</v>
+        <v>23121</v>
       </c>
     </row>
     <row r="256">
@@ -5541,10 +5541,10 @@
         <v>57.71</v>
       </c>
       <c r="E256" t="n">
-        <v>58.44</v>
+        <v>58.33</v>
       </c>
       <c r="F256" t="n">
-        <v>26971</v>
+        <v>26663</v>
       </c>
     </row>
     <row r="257">
@@ -5621,10 +5621,10 @@
         <v>50.38</v>
       </c>
       <c r="E260" t="n">
-        <v>50.95</v>
+        <v>51.35</v>
       </c>
       <c r="F260" t="n">
-        <v>52807</v>
+        <v>51199</v>
       </c>
     </row>
     <row r="261">
@@ -5641,10 +5641,10 @@
         <v>48.92</v>
       </c>
       <c r="E261" t="n">
-        <v>50.08</v>
+        <v>50.01</v>
       </c>
       <c r="F261" t="n">
-        <v>72794</v>
+        <v>71739</v>
       </c>
     </row>
     <row r="262">
@@ -5721,10 +5721,10 @@
         <v>49.67</v>
       </c>
       <c r="E265" t="n">
-        <v>50</v>
+        <v>49.95</v>
       </c>
       <c r="F265" t="n">
-        <v>42678</v>
+        <v>42080</v>
       </c>
     </row>
     <row r="266">
@@ -5741,10 +5741,10 @@
         <v>45.16</v>
       </c>
       <c r="E266" t="n">
-        <v>45.51</v>
+        <v>45.55</v>
       </c>
       <c r="F266" t="n">
-        <v>65295</v>
+        <v>64437</v>
       </c>
     </row>
     <row r="267">
@@ -5812,7 +5812,7 @@
         <v>43902</v>
       </c>
       <c r="B270" t="n">
-        <v>36.29</v>
+        <v>35.97</v>
       </c>
       <c r="C270" t="n">
         <v>36.45</v>
@@ -5824,7 +5824,7 @@
         <v>33.49</v>
       </c>
       <c r="F270" t="n">
-        <v>64469</v>
+        <v>66181</v>
       </c>
     </row>
     <row r="271">
@@ -6121,10 +6121,10 @@
         <v>26.12</v>
       </c>
       <c r="E285" t="n">
-        <v>29.96</v>
+        <v>30.29</v>
       </c>
       <c r="F285" t="n">
-        <v>214756</v>
+        <v>210087</v>
       </c>
     </row>
     <row r="286">
@@ -6135,16 +6135,16 @@
         <v>29.95</v>
       </c>
       <c r="C286" t="n">
-        <v>35.28</v>
+        <v>35.24</v>
       </c>
       <c r="D286" t="n">
         <v>28.9</v>
       </c>
       <c r="E286" t="n">
-        <v>35.16</v>
+        <v>34.72</v>
       </c>
       <c r="F286" t="n">
-        <v>280402</v>
+        <v>275171</v>
       </c>
     </row>
     <row r="287">
@@ -6221,10 +6221,10 @@
         <v>32.46</v>
       </c>
       <c r="E290" t="n">
-        <v>32.8</v>
+        <v>33.2</v>
       </c>
       <c r="F290" t="n">
-        <v>236196</v>
+        <v>230614</v>
       </c>
     </row>
     <row r="291">
@@ -6321,10 +6321,10 @@
         <v>29.42</v>
       </c>
       <c r="E295" t="n">
-        <v>30.59</v>
+        <v>30.65</v>
       </c>
       <c r="F295" t="n">
-        <v>151526</v>
+        <v>146842</v>
       </c>
     </row>
     <row r="296">
@@ -6341,10 +6341,10 @@
         <v>30.13</v>
       </c>
       <c r="E296" t="n">
-        <v>30.68</v>
+        <v>30.78</v>
       </c>
       <c r="F296" t="n">
-        <v>174982</v>
+        <v>171223</v>
       </c>
     </row>
     <row r="297">
@@ -6421,10 +6421,10 @@
         <v>23.38</v>
       </c>
       <c r="E300" t="n">
-        <v>24.73</v>
+        <v>24.74</v>
       </c>
       <c r="F300" t="n">
-        <v>216653</v>
+        <v>213310</v>
       </c>
     </row>
     <row r="301">
@@ -6441,10 +6441,10 @@
         <v>23.7</v>
       </c>
       <c r="E301" t="n">
-        <v>24.99</v>
+        <v>24.98</v>
       </c>
       <c r="F301" t="n">
-        <v>166443</v>
+        <v>163124</v>
       </c>
     </row>
     <row r="302">
@@ -6521,10 +6521,10 @@
         <v>24.33</v>
       </c>
       <c r="E305" t="n">
-        <v>26.85</v>
+        <v>26.83</v>
       </c>
       <c r="F305" t="n">
-        <v>229615</v>
+        <v>224455</v>
       </c>
     </row>
     <row r="306">
@@ -6541,10 +6541,10 @@
         <v>26.05</v>
       </c>
       <c r="E306" t="n">
-        <v>26.81</v>
+        <v>26.78</v>
       </c>
       <c r="F306" t="n">
-        <v>199609</v>
+        <v>196748</v>
       </c>
     </row>
     <row r="307">
@@ -6621,10 +6621,10 @@
         <v>29.4</v>
       </c>
       <c r="E310" t="n">
-        <v>29.65</v>
+        <v>29.48</v>
       </c>
       <c r="F310" t="n">
-        <v>229585</v>
+        <v>225301</v>
       </c>
     </row>
     <row r="311">
@@ -6641,10 +6641,10 @@
         <v>29.63</v>
       </c>
       <c r="E311" t="n">
-        <v>31.25</v>
+        <v>31.26</v>
       </c>
       <c r="F311" t="n">
-        <v>195288</v>
+        <v>192233</v>
       </c>
     </row>
     <row r="312">
@@ -6715,16 +6715,16 @@
         <v>29.73</v>
       </c>
       <c r="C315" t="n">
-        <v>31.75</v>
+        <v>31.65</v>
       </c>
       <c r="D315" t="n">
         <v>29.32</v>
       </c>
       <c r="E315" t="n">
-        <v>31.58</v>
+        <v>31.44</v>
       </c>
       <c r="F315" t="n">
-        <v>156389</v>
+        <v>152193</v>
       </c>
     </row>
     <row r="316">
@@ -6735,16 +6735,16 @@
         <v>31.58</v>
       </c>
       <c r="C316" t="n">
-        <v>33.06</v>
+        <v>32.96</v>
       </c>
       <c r="D316" t="n">
         <v>31.23</v>
       </c>
       <c r="E316" t="n">
-        <v>32.94</v>
+        <v>32.9</v>
       </c>
       <c r="F316" t="n">
-        <v>163209</v>
+        <v>160121</v>
       </c>
     </row>
     <row r="317">
@@ -6821,10 +6821,10 @@
         <v>35.92</v>
       </c>
       <c r="E320" t="n">
-        <v>36.3</v>
+        <v>36.38</v>
       </c>
       <c r="F320" t="n">
-        <v>160329</v>
+        <v>157279</v>
       </c>
     </row>
     <row r="321">
@@ -6841,10 +6841,10 @@
         <v>33.87</v>
       </c>
       <c r="E321" t="n">
-        <v>35.52</v>
+        <v>35.66</v>
       </c>
       <c r="F321" t="n">
-        <v>198023</v>
+        <v>194062</v>
       </c>
     </row>
     <row r="322">
@@ -6921,10 +6921,10 @@
         <v>34.37</v>
       </c>
       <c r="E325" t="n">
-        <v>35.98</v>
+        <v>35.89</v>
       </c>
       <c r="F325" t="n">
-        <v>213086</v>
+        <v>208524</v>
       </c>
     </row>
     <row r="326">
@@ -6941,10 +6941,10 @@
         <v>34.87</v>
       </c>
       <c r="E326" t="n">
-        <v>37.61</v>
+        <v>37.43</v>
       </c>
       <c r="F326" t="n">
-        <v>198370</v>
+        <v>193664</v>
       </c>
     </row>
     <row r="327">
@@ -7021,10 +7021,10 @@
         <v>39.05</v>
       </c>
       <c r="E330" t="n">
-        <v>39.92</v>
+        <v>39.78</v>
       </c>
       <c r="F330" t="n">
-        <v>161661</v>
+        <v>158433</v>
       </c>
     </row>
     <row r="331">
@@ -7041,10 +7041,10 @@
         <v>39.75</v>
       </c>
       <c r="E331" t="n">
-        <v>41.83</v>
+        <v>42.14</v>
       </c>
       <c r="F331" t="n">
-        <v>167359</v>
+        <v>163467</v>
       </c>
     </row>
     <row r="332">
@@ -7121,10 +7121,10 @@
         <v>37.96</v>
       </c>
       <c r="E335" t="n">
-        <v>38.41</v>
+        <v>38.36</v>
       </c>
       <c r="F335" t="n">
-        <v>227925</v>
+        <v>221502</v>
       </c>
     </row>
     <row r="336">
@@ -7141,10 +7141,10 @@
         <v>37.14</v>
       </c>
       <c r="E336" t="n">
-        <v>38.97</v>
+        <v>38.94</v>
       </c>
       <c r="F336" t="n">
-        <v>263342</v>
+        <v>260674</v>
       </c>
     </row>
     <row r="337">
@@ -7221,10 +7221,10 @@
         <v>40.05</v>
       </c>
       <c r="E340" t="n">
-        <v>41.33</v>
+        <v>41.37</v>
       </c>
       <c r="F340" t="n">
-        <v>163774</v>
+        <v>161532</v>
       </c>
     </row>
     <row r="341">
@@ -7241,10 +7241,10 @@
         <v>40.97</v>
       </c>
       <c r="E341" t="n">
-        <v>41.78</v>
+        <v>41.99</v>
       </c>
       <c r="F341" t="n">
-        <v>156573</v>
+        <v>153177</v>
       </c>
     </row>
     <row r="342">
@@ -7315,16 +7315,16 @@
         <v>40.45</v>
       </c>
       <c r="C345" t="n">
-        <v>41.59</v>
+        <v>41.51</v>
       </c>
       <c r="D345" t="n">
         <v>39.68</v>
       </c>
       <c r="E345" t="n">
-        <v>41.35</v>
+        <v>41.39</v>
       </c>
       <c r="F345" t="n">
-        <v>181021</v>
+        <v>178413</v>
       </c>
     </row>
     <row r="346">
@@ -7341,10 +7341,10 @@
         <v>40.25</v>
       </c>
       <c r="E346" t="n">
-        <v>40.57</v>
+        <v>40.58</v>
       </c>
       <c r="F346" t="n">
-        <v>160433</v>
+        <v>157969</v>
       </c>
     </row>
     <row r="347">
@@ -7421,10 +7421,10 @@
         <v>41.71</v>
       </c>
       <c r="E350" t="n">
-        <v>42.65</v>
+        <v>42.71</v>
       </c>
       <c r="F350" t="n">
-        <v>144329</v>
+        <v>142409</v>
       </c>
     </row>
     <row r="351">
@@ -7521,10 +7521,10 @@
         <v>41.99</v>
       </c>
       <c r="E355" t="n">
-        <v>42.35</v>
+        <v>42.32</v>
       </c>
       <c r="F355" t="n">
-        <v>136451</v>
+        <v>133908</v>
       </c>
     </row>
     <row r="356">
@@ -7541,10 +7541,10 @@
         <v>41.4</v>
       </c>
       <c r="E356" t="n">
-        <v>43.26</v>
+        <v>43.23</v>
       </c>
       <c r="F356" t="n">
-        <v>154800</v>
+        <v>152491</v>
       </c>
     </row>
     <row r="357">
@@ -7621,10 +7621,10 @@
         <v>43.19</v>
       </c>
       <c r="E360" t="n">
-        <v>43.28</v>
+        <v>43.36</v>
       </c>
       <c r="F360" t="n">
-        <v>101544</v>
+        <v>99613</v>
       </c>
     </row>
     <row r="361">
@@ -7641,10 +7641,10 @@
         <v>42.7</v>
       </c>
       <c r="E361" t="n">
-        <v>43.12</v>
+        <v>43.18</v>
       </c>
       <c r="F361" t="n">
-        <v>95049</v>
+        <v>93740</v>
       </c>
     </row>
     <row r="362">
@@ -7721,10 +7721,10 @@
         <v>43.42</v>
       </c>
       <c r="E365" t="n">
-        <v>43.53</v>
+        <v>43.82</v>
       </c>
       <c r="F365" t="n">
-        <v>112495</v>
+        <v>109900</v>
       </c>
     </row>
     <row r="366">
@@ -7741,10 +7741,10 @@
         <v>43.18</v>
       </c>
       <c r="E366" t="n">
-        <v>43.62</v>
+        <v>43.67</v>
       </c>
       <c r="F366" t="n">
-        <v>117377</v>
+        <v>115737</v>
       </c>
     </row>
     <row r="367">
@@ -7821,10 +7821,10 @@
         <v>41.95</v>
       </c>
       <c r="E370" t="n">
-        <v>43.56</v>
+        <v>43.43</v>
       </c>
       <c r="F370" t="n">
-        <v>117072</v>
+        <v>113377</v>
       </c>
     </row>
     <row r="371">
@@ -7841,10 +7841,10 @@
         <v>42.94</v>
       </c>
       <c r="E371" t="n">
-        <v>43.59</v>
+        <v>43.65</v>
       </c>
       <c r="F371" t="n">
-        <v>128800</v>
+        <v>127155</v>
       </c>
     </row>
     <row r="372">
@@ -7921,10 +7921,10 @@
         <v>44.96</v>
       </c>
       <c r="E375" t="n">
-        <v>45.13</v>
+        <v>45.28</v>
       </c>
       <c r="F375" t="n">
-        <v>122044</v>
+        <v>120720</v>
       </c>
     </row>
     <row r="376">
@@ -7941,10 +7941,10 @@
         <v>44.4</v>
       </c>
       <c r="E376" t="n">
-        <v>44.71</v>
+        <v>44.76</v>
       </c>
       <c r="F376" t="n">
-        <v>120731</v>
+        <v>119541</v>
       </c>
     </row>
     <row r="377">
@@ -8021,10 +8021,10 @@
         <v>45.07</v>
       </c>
       <c r="E380" t="n">
-        <v>45.24</v>
+        <v>45.3</v>
       </c>
       <c r="F380" t="n">
-        <v>91702</v>
+        <v>90204</v>
       </c>
     </row>
     <row r="381">
@@ -8041,10 +8041,10 @@
         <v>44.77</v>
       </c>
       <c r="E381" t="n">
-        <v>45.19</v>
+        <v>45.2</v>
       </c>
       <c r="F381" t="n">
-        <v>85013</v>
+        <v>83793</v>
       </c>
     </row>
     <row r="382">
@@ -8121,10 +8121,10 @@
         <v>44.46</v>
       </c>
       <c r="E385" t="n">
-        <v>45.27</v>
+        <v>45.36</v>
       </c>
       <c r="F385" t="n">
-        <v>87294</v>
+        <v>86301</v>
       </c>
     </row>
     <row r="386">
@@ -8141,10 +8141,10 @@
         <v>44.09</v>
       </c>
       <c r="E386" t="n">
-        <v>44.69</v>
+        <v>44.79</v>
       </c>
       <c r="F386" t="n">
-        <v>78965</v>
+        <v>77659</v>
       </c>
     </row>
     <row r="387">
@@ -8224,7 +8224,7 @@
         <v>45.59</v>
       </c>
       <c r="F390" t="n">
-        <v>96916</v>
+        <v>95873</v>
       </c>
     </row>
     <row r="391">
@@ -8241,10 +8241,10 @@
         <v>45.36</v>
       </c>
       <c r="E391" t="n">
-        <v>45.85</v>
+        <v>45.89</v>
       </c>
       <c r="F391" t="n">
-        <v>81841</v>
+        <v>81058</v>
       </c>
     </row>
     <row r="392">
@@ -8321,10 +8321,10 @@
         <v>43.27</v>
       </c>
       <c r="E395" t="n">
-        <v>44.07</v>
+        <v>44.09</v>
       </c>
       <c r="F395" t="n">
-        <v>158723</v>
+        <v>157249</v>
       </c>
     </row>
     <row r="396">
@@ -8338,13 +8338,13 @@
         <v>44.69</v>
       </c>
       <c r="D396" t="n">
-        <v>42.42</v>
+        <v>42.45</v>
       </c>
       <c r="E396" t="n">
-        <v>42.43</v>
+        <v>42.53</v>
       </c>
       <c r="F396" t="n">
-        <v>162787</v>
+        <v>160902</v>
       </c>
     </row>
     <row r="397">
@@ -8418,13 +8418,13 @@
         <v>41.23</v>
       </c>
       <c r="D400" t="n">
-        <v>39.96</v>
+        <v>40.02</v>
       </c>
       <c r="E400" t="n">
-        <v>39.97</v>
+        <v>40.07</v>
       </c>
       <c r="F400" t="n">
-        <v>149451</v>
+        <v>147551</v>
       </c>
     </row>
     <row r="401">
@@ -8441,10 +8441,10 @@
         <v>39.68</v>
       </c>
       <c r="E401" t="n">
-        <v>40.02</v>
+        <v>40.24</v>
       </c>
       <c r="F401" t="n">
-        <v>135456</v>
+        <v>133943</v>
       </c>
     </row>
     <row r="402">
@@ -8521,10 +8521,10 @@
         <v>41.89</v>
       </c>
       <c r="E405" t="n">
-        <v>43.58</v>
+        <v>43.67</v>
       </c>
       <c r="F405" t="n">
-        <v>142611</v>
+        <v>141089</v>
       </c>
     </row>
     <row r="406">
@@ -8541,10 +8541,10 @@
         <v>42.92</v>
       </c>
       <c r="E406" t="n">
-        <v>43.41</v>
+        <v>43.34</v>
       </c>
       <c r="F406" t="n">
-        <v>129546</v>
+        <v>127380</v>
       </c>
     </row>
     <row r="407">
@@ -8621,10 +8621,10 @@
         <v>41.68</v>
       </c>
       <c r="E410" t="n">
-        <v>42.16</v>
+        <v>42.27</v>
       </c>
       <c r="F410" t="n">
-        <v>133961</v>
+        <v>132502</v>
       </c>
     </row>
     <row r="411">
@@ -8641,10 +8641,10 @@
         <v>41.97</v>
       </c>
       <c r="E411" t="n">
-        <v>42.17</v>
+        <v>42.24</v>
       </c>
       <c r="F411" t="n">
-        <v>102107</v>
+        <v>100264</v>
       </c>
     </row>
     <row r="412">
@@ -8721,10 +8721,10 @@
         <v>39.98</v>
       </c>
       <c r="E415" t="n">
-        <v>40.75</v>
+        <v>40.93</v>
       </c>
       <c r="F415" t="n">
-        <v>157712</v>
+        <v>155461</v>
       </c>
     </row>
     <row r="416">
@@ -8741,10 +8741,10 @@
         <v>38.88</v>
       </c>
       <c r="E416" t="n">
-        <v>39.15</v>
+        <v>39.23</v>
       </c>
       <c r="F416" t="n">
-        <v>190634</v>
+        <v>188336</v>
       </c>
     </row>
     <row r="417">
@@ -8821,10 +8821,10 @@
         <v>42.02</v>
       </c>
       <c r="E420" t="n">
-        <v>43.52</v>
+        <v>43.54</v>
       </c>
       <c r="F420" t="n">
-        <v>112342</v>
+        <v>110782</v>
       </c>
     </row>
     <row r="421">
@@ -8841,10 +8841,10 @@
         <v>42.78</v>
       </c>
       <c r="E421" t="n">
-        <v>42.89</v>
+        <v>42.96</v>
       </c>
       <c r="F421" t="n">
-        <v>109695</v>
+        <v>108274</v>
       </c>
     </row>
     <row r="422">
@@ -8921,10 +8921,10 @@
         <v>41.79</v>
       </c>
       <c r="E425" t="n">
-        <v>43.26</v>
+        <v>43.38</v>
       </c>
       <c r="F425" t="n">
-        <v>147757</v>
+        <v>146298</v>
       </c>
     </row>
     <row r="426">
@@ -8941,10 +8941,10 @@
         <v>42.47</v>
       </c>
       <c r="E426" t="n">
-        <v>42.95</v>
+        <v>43.02</v>
       </c>
       <c r="F426" t="n">
-        <v>130839</v>
+        <v>129338</v>
       </c>
     </row>
     <row r="427">
@@ -9021,10 +9021,10 @@
         <v>41.72</v>
       </c>
       <c r="E430" t="n">
-        <v>42.59</v>
+        <v>42.71</v>
       </c>
       <c r="F430" t="n">
-        <v>110171</v>
+        <v>108471</v>
       </c>
     </row>
     <row r="431">
@@ -9041,10 +9041,10 @@
         <v>41.76</v>
       </c>
       <c r="E431" t="n">
-        <v>41.85</v>
+        <v>41.93</v>
       </c>
       <c r="F431" t="n">
-        <v>97195</v>
+        <v>95688</v>
       </c>
     </row>
     <row r="432">
@@ -9112,7 +9112,7 @@
         <v>44133</v>
       </c>
       <c r="B435" t="n">
-        <v>39.76</v>
+        <v>39.52</v>
       </c>
       <c r="C435" t="n">
         <v>39.97</v>
@@ -9124,7 +9124,7 @@
         <v>38.05</v>
       </c>
       <c r="F435" t="n">
-        <v>179602</v>
+        <v>183949</v>
       </c>
     </row>
     <row r="436">
@@ -9132,7 +9132,7 @@
         <v>44134</v>
       </c>
       <c r="B436" t="n">
-        <v>38.25</v>
+        <v>38.05</v>
       </c>
       <c r="C436" t="n">
         <v>38.72</v>
@@ -9144,7 +9144,7 @@
         <v>37.84</v>
       </c>
       <c r="F436" t="n">
-        <v>181739</v>
+        <v>184633</v>
       </c>
     </row>
     <row r="437">
@@ -9221,10 +9221,10 @@
         <v>40.42</v>
       </c>
       <c r="E440" t="n">
-        <v>40.68</v>
+        <v>40.82</v>
       </c>
       <c r="F440" t="n">
-        <v>157779</v>
+        <v>155706</v>
       </c>
     </row>
     <row r="441">
@@ -9241,10 +9241,10 @@
         <v>39.46</v>
       </c>
       <c r="E441" t="n">
-        <v>39.71</v>
+        <v>39.84</v>
       </c>
       <c r="F441" t="n">
-        <v>151438</v>
+        <v>150078</v>
       </c>
     </row>
     <row r="442">
@@ -9318,13 +9318,13 @@
         <v>44.59</v>
       </c>
       <c r="D445" t="n">
-        <v>43.35</v>
+        <v>43.42</v>
       </c>
       <c r="E445" t="n">
-        <v>43.38</v>
+        <v>43.49</v>
       </c>
       <c r="F445" t="n">
-        <v>146964</v>
+        <v>144322</v>
       </c>
     </row>
     <row r="446">
@@ -9338,13 +9338,13 @@
         <v>43.45</v>
       </c>
       <c r="D446" t="n">
-        <v>42.68</v>
+        <v>42.77</v>
       </c>
       <c r="E446" t="n">
-        <v>42.69</v>
+        <v>42.88</v>
       </c>
       <c r="F446" t="n">
-        <v>114191</v>
+        <v>112789</v>
       </c>
     </row>
     <row r="447">
@@ -9421,10 +9421,10 @@
         <v>43.87</v>
       </c>
       <c r="E450" t="n">
-        <v>44.21</v>
+        <v>44.44</v>
       </c>
       <c r="F450" t="n">
-        <v>112468</v>
+        <v>111013</v>
       </c>
     </row>
     <row r="451">
@@ -9441,10 +9441,10 @@
         <v>44.15</v>
       </c>
       <c r="E451" t="n">
-        <v>45.07</v>
+        <v>45.06</v>
       </c>
       <c r="F451" t="n">
-        <v>90427</v>
+        <v>88612</v>
       </c>
     </row>
     <row r="452">
@@ -9624,7 +9624,7 @@
         <v>48.65</v>
       </c>
       <c r="F460" t="n">
-        <v>122403</v>
+        <v>119976</v>
       </c>
     </row>
     <row r="461">
@@ -9641,10 +9641,10 @@
         <v>48.77</v>
       </c>
       <c r="E461" t="n">
-        <v>48.96</v>
+        <v>48.97</v>
       </c>
       <c r="F461" t="n">
-        <v>125701</v>
+        <v>124413</v>
       </c>
     </row>
     <row r="462">
@@ -9721,10 +9721,10 @@
         <v>48.79</v>
       </c>
       <c r="E465" t="n">
-        <v>50.25</v>
+        <v>50.26</v>
       </c>
       <c r="F465" t="n">
-        <v>132386</v>
+        <v>130125</v>
       </c>
     </row>
     <row r="466">
@@ -9741,10 +9741,10 @@
         <v>49.67</v>
       </c>
       <c r="E466" t="n">
-        <v>49.86</v>
+        <v>49.94</v>
       </c>
       <c r="F466" t="n">
-        <v>124721</v>
+        <v>123293</v>
       </c>
     </row>
     <row r="467">
@@ -9821,10 +9821,10 @@
         <v>51.06</v>
       </c>
       <c r="E470" t="n">
-        <v>51.46</v>
+        <v>51.55</v>
       </c>
       <c r="F470" t="n">
-        <v>102867</v>
+        <v>100894</v>
       </c>
     </row>
     <row r="471">
@@ -9841,10 +9841,10 @@
         <v>51.16</v>
       </c>
       <c r="E471" t="n">
-        <v>52.23</v>
+        <v>52.19</v>
       </c>
       <c r="F471" t="n">
-        <v>98705</v>
+        <v>96861</v>
       </c>
     </row>
     <row r="472">
@@ -10081,10 +10081,10 @@
         <v>53.88</v>
       </c>
       <c r="E483" t="n">
-        <v>54.34</v>
+        <v>54.45</v>
       </c>
       <c r="F483" t="n">
-        <v>142258</v>
+        <v>140683</v>
       </c>
     </row>
     <row r="484">
@@ -10095,16 +10095,16 @@
         <v>54.46</v>
       </c>
       <c r="C484" t="n">
-        <v>56.2</v>
+        <v>56.06</v>
       </c>
       <c r="D484" t="n">
         <v>54.3</v>
       </c>
       <c r="E484" t="n">
-        <v>56.11</v>
+        <v>56.02</v>
       </c>
       <c r="F484" t="n">
-        <v>155413</v>
+        <v>151805</v>
       </c>
     </row>
     <row r="485">
@@ -10181,10 +10181,10 @@
         <v>55.21</v>
       </c>
       <c r="E488" t="n">
-        <v>56.37</v>
+        <v>56.3</v>
       </c>
       <c r="F488" t="n">
-        <v>125098</v>
+        <v>123090</v>
       </c>
     </row>
     <row r="489">
@@ -10201,10 +10201,10 @@
         <v>54.63</v>
       </c>
       <c r="E489" t="n">
-        <v>54.75</v>
+        <v>54.94</v>
       </c>
       <c r="F489" t="n">
-        <v>135898</v>
+        <v>133988</v>
       </c>
     </row>
     <row r="490">
@@ -10281,10 +10281,10 @@
         <v>55.38</v>
       </c>
       <c r="E493" t="n">
-        <v>55.84</v>
+        <v>55.86</v>
       </c>
       <c r="F493" t="n">
-        <v>104851</v>
+        <v>103188</v>
       </c>
     </row>
     <row r="494">
@@ -10301,10 +10301,10 @@
         <v>54.38</v>
       </c>
       <c r="E494" t="n">
-        <v>54.88</v>
+        <v>55.08</v>
       </c>
       <c r="F494" t="n">
-        <v>135622</v>
+        <v>133367</v>
       </c>
     </row>
     <row r="495">
@@ -10378,13 +10378,13 @@
         <v>56.16</v>
       </c>
       <c r="D498" t="n">
-        <v>54.84</v>
+        <v>54.93</v>
       </c>
       <c r="E498" t="n">
-        <v>54.84</v>
+        <v>55</v>
       </c>
       <c r="F498" t="n">
-        <v>162289</v>
+        <v>160473</v>
       </c>
     </row>
     <row r="499">
@@ -10401,10 +10401,10 @@
         <v>54.84</v>
       </c>
       <c r="E499" t="n">
-        <v>54.93</v>
+        <v>55</v>
       </c>
       <c r="F499" t="n">
-        <v>163671</v>
+        <v>160923</v>
       </c>
     </row>
     <row r="500">
@@ -10481,10 +10481,10 @@
         <v>57.93</v>
       </c>
       <c r="E503" t="n">
-        <v>58.87</v>
+        <v>58.79</v>
       </c>
       <c r="F503" t="n">
-        <v>125851</v>
+        <v>123567</v>
       </c>
     </row>
     <row r="504">
@@ -10501,10 +10501,10 @@
         <v>58.87</v>
       </c>
       <c r="E504" t="n">
-        <v>59.41</v>
+        <v>59.31</v>
       </c>
       <c r="F504" t="n">
-        <v>120954</v>
+        <v>118436</v>
       </c>
     </row>
     <row r="505">
@@ -10578,13 +10578,13 @@
         <v>61.23</v>
       </c>
       <c r="D508" t="n">
-        <v>60.44</v>
+        <v>60.5</v>
       </c>
       <c r="E508" t="n">
-        <v>60.52</v>
+        <v>60.6</v>
       </c>
       <c r="F508" t="n">
-        <v>107974</v>
+        <v>104511</v>
       </c>
     </row>
     <row r="509">
@@ -10604,7 +10604,7 @@
         <v>62.22</v>
       </c>
       <c r="F509" t="n">
-        <v>126905</v>
+        <v>123306</v>
       </c>
     </row>
     <row r="510">
@@ -10681,10 +10681,10 @@
         <v>62.54</v>
       </c>
       <c r="E513" t="n">
-        <v>62.88</v>
+        <v>62.75</v>
       </c>
       <c r="F513" t="n">
-        <v>173632</v>
+        <v>170306</v>
       </c>
     </row>
     <row r="514">
@@ -10701,10 +10701,10 @@
         <v>61.42</v>
       </c>
       <c r="E514" t="n">
-        <v>61.97</v>
+        <v>61.95</v>
       </c>
       <c r="F514" t="n">
-        <v>184306</v>
+        <v>181146</v>
       </c>
     </row>
     <row r="515">
@@ -10781,10 +10781,10 @@
         <v>65.55</v>
       </c>
       <c r="E518" t="n">
-        <v>65.97</v>
+        <v>65.86</v>
       </c>
       <c r="F518" t="n">
-        <v>215533</v>
+        <v>210726</v>
       </c>
     </row>
     <row r="519">
@@ -10801,10 +10801,10 @@
         <v>64.13</v>
       </c>
       <c r="E519" t="n">
-        <v>64.27</v>
+        <v>64.25</v>
       </c>
       <c r="F519" t="n">
-        <v>239274</v>
+        <v>234931</v>
       </c>
     </row>
     <row r="520">
@@ -10881,10 +10881,10 @@
         <v>63.17</v>
       </c>
       <c r="E523" t="n">
-        <v>66.73999999999999</v>
+        <v>66.94</v>
       </c>
       <c r="F523" t="n">
-        <v>230530</v>
+        <v>225843</v>
       </c>
     </row>
     <row r="524">
@@ -10895,16 +10895,16 @@
         <v>66.86</v>
       </c>
       <c r="C524" t="n">
-        <v>69.41</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="D524" t="n">
         <v>66.43000000000001</v>
       </c>
       <c r="E524" t="n">
-        <v>69.25</v>
+        <v>69.28</v>
       </c>
       <c r="F524" t="n">
-        <v>253026</v>
+        <v>249828</v>
       </c>
     </row>
     <row r="525">
@@ -10981,10 +10981,10 @@
         <v>67.68000000000001</v>
       </c>
       <c r="E528" t="n">
-        <v>69.17</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="F528" t="n">
-        <v>163581</v>
+        <v>160838</v>
       </c>
     </row>
     <row r="529">
@@ -11001,10 +11001,10 @@
         <v>68.66</v>
       </c>
       <c r="E529" t="n">
-        <v>68.81</v>
+        <v>68.88</v>
       </c>
       <c r="F529" t="n">
-        <v>151042</v>
+        <v>148823</v>
       </c>
     </row>
     <row r="530">
@@ -11072,7 +11072,7 @@
         <v>44273</v>
       </c>
       <c r="B533" t="n">
-        <v>67.47</v>
+        <v>67.48</v>
       </c>
       <c r="C533" t="n">
         <v>67.83</v>
@@ -11084,7 +11084,7 @@
         <v>62.5</v>
       </c>
       <c r="F533" t="n">
-        <v>209835</v>
+        <v>212082</v>
       </c>
     </row>
     <row r="534">
@@ -11092,7 +11092,7 @@
         <v>44274</v>
       </c>
       <c r="B534" t="n">
-        <v>63.02</v>
+        <v>62.78</v>
       </c>
       <c r="C534" t="n">
         <v>64.73</v>
@@ -11104,7 +11104,7 @@
         <v>64.31999999999999</v>
       </c>
       <c r="F534" t="n">
-        <v>223529</v>
+        <v>228148</v>
       </c>
     </row>
     <row r="535">
@@ -11172,10 +11172,10 @@
         <v>44280</v>
       </c>
       <c r="B538" t="n">
-        <v>63.89</v>
+        <v>63.95</v>
       </c>
       <c r="C538" t="n">
-        <v>63.9</v>
+        <v>64.01000000000001</v>
       </c>
       <c r="D538" t="n">
         <v>60.82</v>
@@ -11184,7 +11184,7 @@
         <v>61.47</v>
       </c>
       <c r="F538" t="n">
-        <v>203253</v>
+        <v>206155</v>
       </c>
     </row>
     <row r="539">
@@ -11192,19 +11192,19 @@
         <v>44281</v>
       </c>
       <c r="B539" t="n">
-        <v>62.45</v>
+        <v>61.47</v>
       </c>
       <c r="C539" t="n">
         <v>64.73</v>
       </c>
       <c r="D539" t="n">
-        <v>62.07</v>
+        <v>61.47</v>
       </c>
       <c r="E539" t="n">
         <v>64.19</v>
       </c>
       <c r="F539" t="n">
-        <v>167422</v>
+        <v>171041</v>
       </c>
     </row>
     <row r="540">
@@ -11284,7 +11284,7 @@
         <v>64.51000000000001</v>
       </c>
       <c r="F543" t="n">
-        <v>201289</v>
+        <v>197783</v>
       </c>
     </row>
     <row r="544">
@@ -11361,10 +11361,10 @@
         <v>62.18</v>
       </c>
       <c r="E547" t="n">
-        <v>63.04</v>
+        <v>63.07</v>
       </c>
       <c r="F547" t="n">
-        <v>149186</v>
+        <v>146277</v>
       </c>
     </row>
     <row r="548">
@@ -11381,10 +11381,10 @@
         <v>62.33</v>
       </c>
       <c r="E548" t="n">
-        <v>62.76</v>
+        <v>62.81</v>
       </c>
       <c r="F548" t="n">
-        <v>121247</v>
+        <v>119219</v>
       </c>
     </row>
     <row r="549">
@@ -11461,10 +11461,10 @@
         <v>65.65000000000001</v>
       </c>
       <c r="E552" t="n">
-        <v>66.45</v>
+        <v>66.5</v>
       </c>
       <c r="F552" t="n">
-        <v>135521</v>
+        <v>133306</v>
       </c>
     </row>
     <row r="553">
@@ -11481,10 +11481,10 @@
         <v>66.11</v>
       </c>
       <c r="E553" t="n">
-        <v>66.31999999999999</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="F553" t="n">
-        <v>122938</v>
+        <v>120895</v>
       </c>
     </row>
     <row r="554">
@@ -11564,7 +11564,7 @@
         <v>64.95</v>
       </c>
       <c r="F557" t="n">
-        <v>143350</v>
+        <v>140975</v>
       </c>
     </row>
     <row r="558">
@@ -11581,10 +11581,10 @@
         <v>64.52</v>
       </c>
       <c r="E558" t="n">
-        <v>65.31999999999999</v>
+        <v>65.45</v>
       </c>
       <c r="F558" t="n">
-        <v>126302</v>
+        <v>124432</v>
       </c>
     </row>
     <row r="559">
@@ -11661,10 +11661,10 @@
         <v>66.56</v>
       </c>
       <c r="E562" t="n">
-        <v>67.84999999999999</v>
+        <v>67.86</v>
       </c>
       <c r="F562" t="n">
-        <v>160482</v>
+        <v>157092</v>
       </c>
     </row>
     <row r="563">
@@ -11681,10 +11681,10 @@
         <v>66.17</v>
       </c>
       <c r="E563" t="n">
-        <v>66.53</v>
+        <v>66.56</v>
       </c>
       <c r="F563" t="n">
-        <v>148372</v>
+        <v>145779</v>
       </c>
     </row>
     <row r="564">
@@ -11761,10 +11761,10 @@
         <v>67.77</v>
       </c>
       <c r="E567" t="n">
-        <v>68.03</v>
+        <v>68.05</v>
       </c>
       <c r="F567" t="n">
-        <v>155507</v>
+        <v>153533</v>
       </c>
     </row>
     <row r="568">
@@ -11784,7 +11784,7 @@
         <v>68.03</v>
       </c>
       <c r="F568" t="n">
-        <v>139157</v>
+        <v>136012</v>
       </c>
     </row>
     <row r="569">
@@ -11861,10 +11861,10 @@
         <v>66.34</v>
       </c>
       <c r="E572" t="n">
-        <v>66.81999999999999</v>
+        <v>66.83</v>
       </c>
       <c r="F572" t="n">
-        <v>182316</v>
+        <v>180093</v>
       </c>
     </row>
     <row r="573">
@@ -11875,16 +11875,16 @@
         <v>66.81</v>
       </c>
       <c r="C573" t="n">
-        <v>68.63</v>
+        <v>68.52</v>
       </c>
       <c r="D573" t="n">
         <v>66.36</v>
       </c>
       <c r="E573" t="n">
-        <v>68.52</v>
+        <v>68.45</v>
       </c>
       <c r="F573" t="n">
-        <v>142226</v>
+        <v>139950</v>
       </c>
     </row>
     <row r="574">
@@ -11958,13 +11958,13 @@
         <v>67.02</v>
       </c>
       <c r="D577" t="n">
-        <v>64.70999999999999</v>
+        <v>64.73</v>
       </c>
       <c r="E577" t="n">
-        <v>64.73999999999999</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="F577" t="n">
-        <v>168733</v>
+        <v>164782</v>
       </c>
     </row>
     <row r="578">
@@ -11981,10 +11981,10 @@
         <v>64.48</v>
       </c>
       <c r="E578" t="n">
-        <v>66.51000000000001</v>
+        <v>66.58</v>
       </c>
       <c r="F578" t="n">
-        <v>156317</v>
+        <v>153693</v>
       </c>
     </row>
     <row r="579">
@@ -12055,16 +12055,16 @@
         <v>68.58</v>
       </c>
       <c r="C582" t="n">
-        <v>69.2</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="D582" t="n">
         <v>67.89</v>
       </c>
       <c r="E582" t="n">
-        <v>69.12</v>
+        <v>69.05</v>
       </c>
       <c r="F582" t="n">
-        <v>122427</v>
+        <v>119490</v>
       </c>
     </row>
     <row r="583">
@@ -12081,10 +12081,10 @@
         <v>68.48999999999999</v>
       </c>
       <c r="E583" t="n">
-        <v>68.88</v>
+        <v>68.89</v>
       </c>
       <c r="F583" t="n">
-        <v>121324</v>
+        <v>119218</v>
       </c>
     </row>
     <row r="584">
@@ -12161,10 +12161,10 @@
         <v>70.5</v>
       </c>
       <c r="E587" t="n">
-        <v>71.22</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="F587" t="n">
-        <v>128649</v>
+        <v>126247</v>
       </c>
     </row>
     <row r="588">
@@ -12181,10 +12181,10 @@
         <v>70.58</v>
       </c>
       <c r="E588" t="n">
-        <v>71.43000000000001</v>
+        <v>71.47</v>
       </c>
       <c r="F588" t="n">
-        <v>117041</v>
+        <v>113793</v>
       </c>
     </row>
     <row r="589">
@@ -12261,10 +12261,10 @@
         <v>70.66</v>
       </c>
       <c r="E592" t="n">
-        <v>71.95</v>
+        <v>72.09</v>
       </c>
       <c r="F592" t="n">
-        <v>148450</v>
+        <v>146487</v>
       </c>
     </row>
     <row r="593">
@@ -12284,7 +12284,7 @@
         <v>72.23999999999999</v>
       </c>
       <c r="F593" t="n">
-        <v>142367</v>
+        <v>140128</v>
       </c>
     </row>
     <row r="594">
@@ -12361,10 +12361,10 @@
         <v>71.41</v>
       </c>
       <c r="E597" t="n">
-        <v>72.44</v>
+        <v>72.45</v>
       </c>
       <c r="F597" t="n">
-        <v>178094</v>
+        <v>175025</v>
       </c>
     </row>
     <row r="598">
@@ -12381,10 +12381,10 @@
         <v>71.55</v>
       </c>
       <c r="E598" t="n">
-        <v>72.5</v>
+        <v>72.76000000000001</v>
       </c>
       <c r="F598" t="n">
-        <v>151345</v>
+        <v>147859</v>
       </c>
     </row>
     <row r="599">
@@ -12461,10 +12461,10 @@
         <v>73.83</v>
       </c>
       <c r="E602" t="n">
-        <v>74.81</v>
+        <v>74.79000000000001</v>
       </c>
       <c r="F602" t="n">
-        <v>85692</v>
+        <v>84577</v>
       </c>
     </row>
     <row r="603">
@@ -12481,10 +12481,10 @@
         <v>74.14</v>
       </c>
       <c r="E603" t="n">
-        <v>75.28</v>
+        <v>75.27</v>
       </c>
       <c r="F603" t="n">
-        <v>79112</v>
+        <v>77990</v>
       </c>
     </row>
     <row r="604">
@@ -12561,10 +12561,10 @@
         <v>74.36</v>
       </c>
       <c r="E607" t="n">
-        <v>75.34</v>
+        <v>75.33</v>
       </c>
       <c r="F607" t="n">
-        <v>135699</v>
+        <v>134296</v>
       </c>
     </row>
     <row r="608">
@@ -12581,10 +12581,10 @@
         <v>75</v>
       </c>
       <c r="E608" t="n">
-        <v>75.81999999999999</v>
+        <v>76.02</v>
       </c>
       <c r="F608" t="n">
-        <v>104256</v>
+        <v>102316</v>
       </c>
     </row>
     <row r="609">
@@ -12655,16 +12655,16 @@
         <v>72.97</v>
       </c>
       <c r="C612" t="n">
-        <v>74.02</v>
+        <v>73.97</v>
       </c>
       <c r="D612" t="n">
         <v>71.73999999999999</v>
       </c>
       <c r="E612" t="n">
-        <v>73.95999999999999</v>
+        <v>73.92</v>
       </c>
       <c r="F612" t="n">
-        <v>138030</v>
+        <v>136419</v>
       </c>
     </row>
     <row r="613">
@@ -12681,10 +12681,10 @@
         <v>73.38</v>
       </c>
       <c r="E613" t="n">
-        <v>75.14</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="F613" t="n">
-        <v>96988</v>
+        <v>95892</v>
       </c>
     </row>
     <row r="614">
@@ -12761,10 +12761,10 @@
         <v>72.70999999999999</v>
       </c>
       <c r="E617" t="n">
-        <v>72.72</v>
+        <v>72.79000000000001</v>
       </c>
       <c r="F617" t="n">
-        <v>134216</v>
+        <v>132350</v>
       </c>
     </row>
     <row r="618">
@@ -12781,10 +12781,10 @@
         <v>71.88</v>
       </c>
       <c r="E618" t="n">
-        <v>72.64</v>
+        <v>72.81</v>
       </c>
       <c r="F618" t="n">
-        <v>110158</v>
+        <v>108307</v>
       </c>
     </row>
     <row r="619">
@@ -12864,7 +12864,7 @@
         <v>73.01000000000001</v>
       </c>
       <c r="F622" t="n">
-        <v>115159</v>
+        <v>113951</v>
       </c>
     </row>
     <row r="623">
@@ -12875,16 +12875,16 @@
         <v>72.98</v>
       </c>
       <c r="C623" t="n">
-        <v>73.56999999999999</v>
+        <v>73.52</v>
       </c>
       <c r="D623" t="n">
         <v>72.70999999999999</v>
       </c>
       <c r="E623" t="n">
-        <v>73.5</v>
+        <v>73.44</v>
       </c>
       <c r="F623" t="n">
-        <v>84579</v>
+        <v>83411</v>
       </c>
     </row>
     <row r="624">
@@ -12961,10 +12961,10 @@
         <v>73.59999999999999</v>
       </c>
       <c r="E627" t="n">
-        <v>74.75</v>
+        <v>74.97</v>
       </c>
       <c r="F627" t="n">
-        <v>81467</v>
+        <v>79720</v>
       </c>
     </row>
     <row r="628">
@@ -12981,10 +12981,10 @@
         <v>74.26000000000001</v>
       </c>
       <c r="E628" t="n">
-        <v>74.95999999999999</v>
+        <v>74.98999999999999</v>
       </c>
       <c r="F628" t="n">
-        <v>84253</v>
+        <v>83101</v>
       </c>
     </row>
     <row r="629">
@@ -13061,10 +13061,10 @@
         <v>69.56</v>
       </c>
       <c r="E632" t="n">
-        <v>71</v>
+        <v>71.16</v>
       </c>
       <c r="F632" t="n">
-        <v>108267</v>
+        <v>107034</v>
       </c>
     </row>
     <row r="633">
@@ -13078,13 +13078,13 @@
         <v>72.22</v>
       </c>
       <c r="D633" t="n">
-        <v>70.06999999999999</v>
+        <v>70.12</v>
       </c>
       <c r="E633" t="n">
-        <v>70.08</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="F633" t="n">
-        <v>113105</v>
+        <v>111453</v>
       </c>
     </row>
     <row r="634">
@@ -13161,10 +13161,10 @@
         <v>70.41</v>
       </c>
       <c r="E637" t="n">
-        <v>70.86</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="F637" t="n">
-        <v>96203</v>
+        <v>95219</v>
       </c>
     </row>
     <row r="638">
@@ -13181,10 +13181,10 @@
         <v>69.73999999999999</v>
       </c>
       <c r="E638" t="n">
-        <v>69.90000000000001</v>
+        <v>69.92</v>
       </c>
       <c r="F638" t="n">
-        <v>95696</v>
+        <v>93960</v>
       </c>
     </row>
     <row r="639">
@@ -13261,10 +13261,10 @@
         <v>65.2</v>
       </c>
       <c r="E642" t="n">
-        <v>66.23</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="F642" t="n">
-        <v>187712</v>
+        <v>185678</v>
       </c>
     </row>
     <row r="643">
@@ -13278,13 +13278,13 @@
         <v>66.54000000000001</v>
       </c>
       <c r="D643" t="n">
-        <v>64.53</v>
+        <v>64.61</v>
       </c>
       <c r="E643" t="n">
-        <v>64.54000000000001</v>
+        <v>64.62</v>
       </c>
       <c r="F643" t="n">
-        <v>138989</v>
+        <v>137258</v>
       </c>
     </row>
     <row r="644">
@@ -13361,10 +13361,10 @@
         <v>69.73999999999999</v>
       </c>
       <c r="E647" t="n">
-        <v>70.45999999999999</v>
+        <v>70.56</v>
       </c>
       <c r="F647" t="n">
-        <v>115965</v>
+        <v>113839</v>
       </c>
     </row>
     <row r="648">
@@ -13381,10 +13381,10 @@
         <v>70.16</v>
       </c>
       <c r="E648" t="n">
-        <v>71.5</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="F648" t="n">
-        <v>100455</v>
+        <v>99158</v>
       </c>
     </row>
     <row r="649">
@@ -13461,10 +13461,10 @@
         <v>70.75</v>
       </c>
       <c r="E652" t="n">
-        <v>72.61</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="F652" t="n">
-        <v>105073</v>
+        <v>103772</v>
       </c>
     </row>
     <row r="653">
@@ -13481,10 +13481,10 @@
         <v>72.20999999999999</v>
       </c>
       <c r="E653" t="n">
-        <v>72.20999999999999</v>
+        <v>72.36</v>
       </c>
       <c r="F653" t="n">
-        <v>111688</v>
+        <v>110684</v>
       </c>
     </row>
     <row r="654">
@@ -13561,10 +13561,10 @@
         <v>70.54000000000001</v>
       </c>
       <c r="E657" t="n">
-        <v>70.84</v>
+        <v>70.95</v>
       </c>
       <c r="F657" t="n">
-        <v>138553</v>
+        <v>136836</v>
       </c>
     </row>
     <row r="658">
@@ -13581,10 +13581,10 @@
         <v>70.59</v>
       </c>
       <c r="E658" t="n">
-        <v>72.51000000000001</v>
+        <v>72.44</v>
       </c>
       <c r="F658" t="n">
-        <v>107925</v>
+        <v>106315</v>
       </c>
     </row>
     <row r="659">
@@ -13661,10 +13661,10 @@
         <v>74.02</v>
       </c>
       <c r="E662" t="n">
-        <v>75.09</v>
+        <v>75.17</v>
       </c>
       <c r="F662" t="n">
-        <v>136265</v>
+        <v>134873</v>
       </c>
     </row>
     <row r="663">
@@ -13681,10 +13681,10 @@
         <v>74.06999999999999</v>
       </c>
       <c r="E663" t="n">
-        <v>74.67</v>
+        <v>74.79000000000001</v>
       </c>
       <c r="F663" t="n">
-        <v>131243</v>
+        <v>129577</v>
       </c>
     </row>
     <row r="664">
@@ -13764,7 +13764,7 @@
         <v>76.45</v>
       </c>
       <c r="F667" t="n">
-        <v>104066</v>
+        <v>102612</v>
       </c>
     </row>
     <row r="668">
@@ -13781,10 +13781,10 @@
         <v>76.09</v>
       </c>
       <c r="E668" t="n">
-        <v>77.13</v>
+        <v>77.15000000000001</v>
       </c>
       <c r="F668" t="n">
-        <v>94529</v>
+        <v>93448</v>
       </c>
     </row>
     <row r="669">
@@ -13861,10 +13861,10 @@
         <v>76.37</v>
       </c>
       <c r="E672" t="n">
-        <v>78.23999999999999</v>
+        <v>78.13</v>
       </c>
       <c r="F672" t="n">
-        <v>181989</v>
+        <v>180155</v>
       </c>
     </row>
     <row r="673">
@@ -13881,10 +13881,10 @@
         <v>77.38</v>
       </c>
       <c r="E673" t="n">
-        <v>78.93000000000001</v>
+        <v>78.98999999999999</v>
       </c>
       <c r="F673" t="n">
-        <v>151482</v>
+        <v>149729</v>
       </c>
     </row>
     <row r="674">
@@ -13961,10 +13961,10 @@
         <v>78.78</v>
       </c>
       <c r="E677" t="n">
-        <v>82.08</v>
+        <v>82.16</v>
       </c>
       <c r="F677" t="n">
-        <v>153620</v>
+        <v>151677</v>
       </c>
     </row>
     <row r="678">
@@ -13981,10 +13981,10 @@
         <v>81.63</v>
       </c>
       <c r="E678" t="n">
-        <v>82.22</v>
+        <v>82.17</v>
       </c>
       <c r="F678" t="n">
-        <v>149526</v>
+        <v>147722</v>
       </c>
     </row>
     <row r="679">
@@ -14061,10 +14061,10 @@
         <v>82.76000000000001</v>
       </c>
       <c r="E682" t="n">
-        <v>83.67</v>
+        <v>83.69</v>
       </c>
       <c r="F682" t="n">
-        <v>122153</v>
+        <v>120650</v>
       </c>
     </row>
     <row r="683">
@@ -14081,10 +14081,10 @@
         <v>83.68000000000001</v>
       </c>
       <c r="E683" t="n">
-        <v>84.33</v>
+        <v>84.23</v>
       </c>
       <c r="F683" t="n">
-        <v>116437</v>
+        <v>114060</v>
       </c>
     </row>
     <row r="684">
@@ -14161,10 +14161,10 @@
         <v>82.73</v>
       </c>
       <c r="E687" t="n">
-        <v>84.09</v>
+        <v>84.15000000000001</v>
       </c>
       <c r="F687" t="n">
-        <v>122966</v>
+        <v>121250</v>
       </c>
     </row>
     <row r="688">
@@ -14175,16 +14175,16 @@
         <v>83.81999999999999</v>
       </c>
       <c r="C688" t="n">
-        <v>85.08</v>
+        <v>84.97</v>
       </c>
       <c r="D688" t="n">
         <v>83.18000000000001</v>
       </c>
       <c r="E688" t="n">
-        <v>84.83</v>
+        <v>84.97</v>
       </c>
       <c r="F688" t="n">
-        <v>113449</v>
+        <v>111475</v>
       </c>
     </row>
     <row r="689">
@@ -14261,10 +14261,10 @@
         <v>81.48</v>
       </c>
       <c r="E692" t="n">
-        <v>83.78</v>
+        <v>83.83</v>
       </c>
       <c r="F692" t="n">
-        <v>167007</v>
+        <v>164605</v>
       </c>
     </row>
     <row r="693">
@@ -14281,10 +14281,10 @@
         <v>82.39</v>
       </c>
       <c r="E693" t="n">
-        <v>83.41</v>
+        <v>83.55</v>
       </c>
       <c r="F693" t="n">
-        <v>133535</v>
+        <v>132228</v>
       </c>
     </row>
     <row r="694">
@@ -14352,7 +14352,7 @@
         <v>44504</v>
       </c>
       <c r="B697" t="n">
-        <v>80.83</v>
+        <v>81.12</v>
       </c>
       <c r="C697" t="n">
         <v>84.08</v>
@@ -14364,7 +14364,7 @@
         <v>80.54000000000001</v>
       </c>
       <c r="F697" t="n">
-        <v>168783</v>
+        <v>171378</v>
       </c>
     </row>
     <row r="698">
@@ -14372,7 +14372,7 @@
         <v>44505</v>
       </c>
       <c r="B698" t="n">
-        <v>81.04000000000001</v>
+        <v>80.95</v>
       </c>
       <c r="C698" t="n">
         <v>82.72</v>
@@ -14384,7 +14384,7 @@
         <v>81.93000000000001</v>
       </c>
       <c r="F698" t="n">
-        <v>163172</v>
+        <v>166390</v>
       </c>
     </row>
     <row r="699">
@@ -14461,10 +14461,10 @@
         <v>81.06</v>
       </c>
       <c r="E702" t="n">
-        <v>81.92</v>
+        <v>81.91</v>
       </c>
       <c r="F702" t="n">
-        <v>161511</v>
+        <v>159955</v>
       </c>
     </row>
     <row r="703">
@@ -14481,10 +14481,10 @@
         <v>80.63</v>
       </c>
       <c r="E703" t="n">
-        <v>81.29000000000001</v>
+        <v>81.41</v>
       </c>
       <c r="F703" t="n">
-        <v>134507</v>
+        <v>133196</v>
       </c>
     </row>
     <row r="704">
@@ -14561,10 +14561,10 @@
         <v>78.55</v>
       </c>
       <c r="E707" t="n">
-        <v>80.34999999999999</v>
+        <v>80.42</v>
       </c>
       <c r="F707" t="n">
-        <v>132952</v>
+        <v>131123</v>
       </c>
     </row>
     <row r="708">
@@ -14581,10 +14581,10 @@
         <v>77.41</v>
       </c>
       <c r="E708" t="n">
-        <v>77.77</v>
+        <v>77.76000000000001</v>
       </c>
       <c r="F708" t="n">
-        <v>177513</v>
+        <v>175625</v>
       </c>
     </row>
     <row r="709">
@@ -14761,10 +14761,10 @@
         <v>65.67</v>
       </c>
       <c r="E717" t="n">
-        <v>70.36</v>
+        <v>69.94</v>
       </c>
       <c r="F717" t="n">
-        <v>240359</v>
+        <v>237353</v>
       </c>
     </row>
     <row r="718">
@@ -14781,10 +14781,10 @@
         <v>69.09999999999999</v>
       </c>
       <c r="E718" t="n">
-        <v>69.70999999999999</v>
+        <v>69.73</v>
       </c>
       <c r="F718" t="n">
-        <v>208893</v>
+        <v>205214</v>
       </c>
     </row>
     <row r="719">
@@ -14858,13 +14858,13 @@
         <v>76.55</v>
       </c>
       <c r="D722" t="n">
-        <v>73.70999999999999</v>
+        <v>73.78</v>
       </c>
       <c r="E722" t="n">
-        <v>73.84999999999999</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="F722" t="n">
-        <v>142264</v>
+        <v>140659</v>
       </c>
     </row>
     <row r="723">
@@ -14881,10 +14881,10 @@
         <v>73.67</v>
       </c>
       <c r="E723" t="n">
-        <v>75.16</v>
+        <v>75.23</v>
       </c>
       <c r="F723" t="n">
-        <v>153301</v>
+        <v>151698</v>
       </c>
     </row>
     <row r="724">
@@ -14961,10 +14961,10 @@
         <v>73.88</v>
       </c>
       <c r="E727" t="n">
-        <v>74.48999999999999</v>
+        <v>74.63</v>
       </c>
       <c r="F727" t="n">
-        <v>142563</v>
+        <v>140474</v>
       </c>
     </row>
     <row r="728">
@@ -14981,10 +14981,10 @@
         <v>72.63</v>
       </c>
       <c r="E728" t="n">
-        <v>72.88</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="F728" t="n">
-        <v>154875</v>
+        <v>152160</v>
       </c>
     </row>
     <row r="729">
@@ -15061,10 +15061,10 @@
         <v>74.72</v>
       </c>
       <c r="E732" t="n">
-        <v>76.52</v>
+        <v>76.63</v>
       </c>
       <c r="F732" t="n">
-        <v>102802</v>
+        <v>100583</v>
       </c>
     </row>
     <row r="733">
@@ -15161,10 +15161,10 @@
         <v>78.33</v>
       </c>
       <c r="E737" t="n">
-        <v>78.86</v>
+        <v>78.97</v>
       </c>
       <c r="F737" t="n">
-        <v>105405</v>
+        <v>103669</v>
       </c>
     </row>
     <row r="738">
@@ -15261,10 +15261,10 @@
         <v>79.36</v>
       </c>
       <c r="E742" t="n">
-        <v>81.70999999999999</v>
+        <v>81.65000000000001</v>
       </c>
       <c r="F742" t="n">
-        <v>187943</v>
+        <v>185800</v>
       </c>
     </row>
     <row r="743">
@@ -15281,10 +15281,10 @@
         <v>81.12</v>
       </c>
       <c r="E743" t="n">
-        <v>81.48</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="F743" t="n">
-        <v>160491</v>
+        <v>158852</v>
       </c>
     </row>
     <row r="744">
@@ -15361,10 +15361,10 @@
         <v>83.34999999999999</v>
       </c>
       <c r="E747" t="n">
-        <v>83.61</v>
+        <v>83.45</v>
       </c>
       <c r="F747" t="n">
-        <v>147527</v>
+        <v>145171</v>
       </c>
     </row>
     <row r="748">
@@ -15375,16 +15375,16 @@
         <v>83.68000000000001</v>
       </c>
       <c r="C748" t="n">
-        <v>85.98999999999999</v>
+        <v>85.97</v>
       </c>
       <c r="D748" t="n">
         <v>83.53</v>
       </c>
       <c r="E748" t="n">
-        <v>85.77</v>
+        <v>85.91</v>
       </c>
       <c r="F748" t="n">
-        <v>173518</v>
+        <v>171152</v>
       </c>
     </row>
     <row r="749">
@@ -15458,13 +15458,13 @@
         <v>88.8</v>
       </c>
       <c r="D752" t="n">
-        <v>86.38</v>
+        <v>86.56999999999999</v>
       </c>
       <c r="E752" t="n">
-        <v>86.58</v>
+        <v>86.7</v>
       </c>
       <c r="F752" t="n">
-        <v>169439</v>
+        <v>162890</v>
       </c>
     </row>
     <row r="753">
@@ -15481,10 +15481,10 @@
         <v>85.02</v>
       </c>
       <c r="E753" t="n">
-        <v>86.92</v>
+        <v>86.98</v>
       </c>
       <c r="F753" t="n">
-        <v>225683</v>
+        <v>223066</v>
       </c>
     </row>
     <row r="754">
@@ -15561,10 +15561,10 @@
         <v>87.7</v>
       </c>
       <c r="E757" t="n">
-        <v>88.63</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="F757" t="n">
-        <v>275711</v>
+        <v>270152</v>
       </c>
     </row>
     <row r="758">
@@ -15581,10 +15581,10 @@
         <v>88</v>
       </c>
       <c r="E758" t="n">
-        <v>88.81999999999999</v>
+        <v>88.73</v>
       </c>
       <c r="F758" t="n">
-        <v>278896</v>
+        <v>275262</v>
       </c>
     </row>
     <row r="759">
@@ -15655,16 +15655,16 @@
         <v>88.63</v>
       </c>
       <c r="C762" t="n">
-        <v>90.84999999999999</v>
+        <v>90.73999999999999</v>
       </c>
       <c r="D762" t="n">
         <v>87.59999999999999</v>
       </c>
       <c r="E762" t="n">
-        <v>90.51000000000001</v>
+        <v>90.45999999999999</v>
       </c>
       <c r="F762" t="n">
-        <v>168353</v>
+        <v>163057</v>
       </c>
     </row>
     <row r="763">
@@ -15681,10 +15681,10 @@
         <v>90.67</v>
       </c>
       <c r="E763" t="n">
-        <v>92.14</v>
+        <v>92.54000000000001</v>
       </c>
       <c r="F763" t="n">
-        <v>180147</v>
+        <v>177219</v>
       </c>
     </row>
     <row r="764">
@@ -15761,10 +15761,10 @@
         <v>90.09999999999999</v>
       </c>
       <c r="E767" t="n">
-        <v>90.54000000000001</v>
+        <v>90.66</v>
       </c>
       <c r="F767" t="n">
-        <v>186180</v>
+        <v>183590</v>
       </c>
     </row>
     <row r="768">
@@ -15781,10 +15781,10 @@
         <v>89.66</v>
       </c>
       <c r="E768" t="n">
-        <v>93.8</v>
+        <v>93.81</v>
       </c>
       <c r="F768" t="n">
-        <v>194729</v>
+        <v>189880</v>
       </c>
     </row>
     <row r="769">
@@ -15861,10 +15861,10 @@
         <v>90.34999999999999</v>
       </c>
       <c r="E772" t="n">
-        <v>91.16</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="F772" t="n">
-        <v>212213</v>
+        <v>209775</v>
       </c>
     </row>
     <row r="773">
@@ -15875,7 +15875,7 @@
         <v>90.76000000000001</v>
       </c>
       <c r="C773" t="n">
-        <v>92.28</v>
+        <v>92.15000000000001</v>
       </c>
       <c r="D773" t="n">
         <v>88.64</v>
@@ -15884,7 +15884,7 @@
         <v>91.81</v>
       </c>
       <c r="F773" t="n">
-        <v>194995</v>
+        <v>190175</v>
       </c>
     </row>
     <row r="774">
@@ -15961,10 +15961,10 @@
         <v>93.94</v>
       </c>
       <c r="E777" t="n">
-        <v>95.41</v>
+        <v>95.61</v>
       </c>
       <c r="F777" t="n">
-        <v>313423</v>
+        <v>309076</v>
       </c>
     </row>
     <row r="778">
@@ -15981,10 +15981,10 @@
         <v>92.55</v>
       </c>
       <c r="E778" t="n">
-        <v>94.23</v>
+        <v>94.69</v>
       </c>
       <c r="F778" t="n">
-        <v>237786</v>
+        <v>233541</v>
       </c>
     </row>
     <row r="779">
@@ -16061,10 +16061,10 @@
         <v>108.17</v>
       </c>
       <c r="E782" t="n">
-        <v>109.27</v>
+        <v>109.72</v>
       </c>
       <c r="F782" t="n">
-        <v>233799</v>
+        <v>231064</v>
       </c>
     </row>
     <row r="783">
@@ -16081,10 +16081,10 @@
         <v>108.47</v>
       </c>
       <c r="E783" t="n">
-        <v>116.7</v>
+        <v>117.14</v>
       </c>
       <c r="F783" t="n">
-        <v>210974</v>
+        <v>204618</v>
       </c>
     </row>
     <row r="784">
@@ -16161,10 +16161,10 @@
         <v>107.05</v>
       </c>
       <c r="E787" t="n">
-        <v>107.11</v>
+        <v>107.97</v>
       </c>
       <c r="F787" t="n">
-        <v>173653</v>
+        <v>170481</v>
       </c>
     </row>
     <row r="788">
@@ -16181,10 +16181,10 @@
         <v>104.96</v>
       </c>
       <c r="E788" t="n">
-        <v>110.14</v>
+        <v>110.51</v>
       </c>
       <c r="F788" t="n">
-        <v>157669</v>
+        <v>154891</v>
       </c>
     </row>
     <row r="789">
@@ -16252,19 +16252,19 @@
         <v>44637</v>
       </c>
       <c r="B792" t="n">
-        <v>96.70999999999999</v>
+        <v>96.98</v>
       </c>
       <c r="C792" t="n">
         <v>105.3</v>
       </c>
       <c r="D792" t="n">
-        <v>96.70999999999999</v>
+        <v>96.11</v>
       </c>
       <c r="E792" t="n">
         <v>104.46</v>
       </c>
       <c r="F792" t="n">
-        <v>172578</v>
+        <v>176604</v>
       </c>
     </row>
     <row r="793">
@@ -16272,7 +16272,7 @@
         <v>44638</v>
       </c>
       <c r="B793" t="n">
-        <v>105.16</v>
+        <v>104.55</v>
       </c>
       <c r="C793" t="n">
         <v>107.23</v>
@@ -16284,7 +16284,7 @@
         <v>105.63</v>
       </c>
       <c r="F793" t="n">
-        <v>155067</v>
+        <v>158531</v>
       </c>
     </row>
     <row r="794">
@@ -16352,7 +16352,7 @@
         <v>44644</v>
       </c>
       <c r="B797" t="n">
-        <v>119.49</v>
+        <v>118.08</v>
       </c>
       <c r="C797" t="n">
         <v>120.04</v>
@@ -16364,7 +16364,7 @@
         <v>114.47</v>
       </c>
       <c r="F797" t="n">
-        <v>206598</v>
+        <v>215337</v>
       </c>
     </row>
     <row r="798">
@@ -16372,7 +16372,7 @@
         <v>44645</v>
       </c>
       <c r="B798" t="n">
-        <v>114.52</v>
+        <v>115.3</v>
       </c>
       <c r="C798" t="n">
         <v>117.69</v>
@@ -16384,7 +16384,7 @@
         <v>115.94</v>
       </c>
       <c r="F798" t="n">
-        <v>189095</v>
+        <v>195807</v>
       </c>
     </row>
     <row r="799">
@@ -16461,10 +16461,10 @@
         <v>103.71</v>
       </c>
       <c r="E802" t="n">
-        <v>104.99</v>
+        <v>104.6</v>
       </c>
       <c r="F802" t="n">
-        <v>220967</v>
+        <v>217472</v>
       </c>
     </row>
     <row r="803">
@@ -16481,10 +16481,10 @@
         <v>101.94</v>
       </c>
       <c r="E803" t="n">
-        <v>103.88</v>
+        <v>104.13</v>
       </c>
       <c r="F803" t="n">
-        <v>181758</v>
+        <v>179677</v>
       </c>
     </row>
     <row r="804">
@@ -16561,10 +16561,10 @@
         <v>98.2</v>
       </c>
       <c r="E807" t="n">
-        <v>100.96</v>
+        <v>100.94</v>
       </c>
       <c r="F807" t="n">
-        <v>186163</v>
+        <v>183922</v>
       </c>
     </row>
     <row r="808">
@@ -16581,10 +16581,10 @@
         <v>99.28</v>
       </c>
       <c r="E808" t="n">
-        <v>101.81</v>
+        <v>102.16</v>
       </c>
       <c r="F808" t="n">
-        <v>162819</v>
+        <v>159821</v>
       </c>
     </row>
     <row r="809">
@@ -16661,10 +16661,10 @@
         <v>106.14</v>
       </c>
       <c r="E812" t="n">
-        <v>110.62</v>
+        <v>110.56</v>
       </c>
       <c r="F812" t="n">
-        <v>159785</v>
+        <v>156524</v>
       </c>
     </row>
     <row r="813">
@@ -16741,10 +16741,10 @@
         <v>106.38</v>
       </c>
       <c r="E816" t="n">
-        <v>108</v>
+        <v>107.93</v>
       </c>
       <c r="F816" t="n">
-        <v>188001</v>
+        <v>184241</v>
       </c>
     </row>
     <row r="817">
@@ -16758,13 +16758,13 @@
         <v>108.41</v>
       </c>
       <c r="D817" t="n">
-        <v>105.05</v>
+        <v>105.44</v>
       </c>
       <c r="E817" t="n">
-        <v>105.7</v>
+        <v>105.6</v>
       </c>
       <c r="F817" t="n">
-        <v>165632</v>
+        <v>162032</v>
       </c>
     </row>
     <row r="818">
@@ -16841,10 +16841,10 @@
         <v>102.74</v>
       </c>
       <c r="E821" t="n">
-        <v>106.8</v>
+        <v>107.25</v>
       </c>
       <c r="F821" t="n">
-        <v>170514</v>
+        <v>167676</v>
       </c>
     </row>
     <row r="822">
@@ -16861,10 +16861,10 @@
         <v>105.92</v>
       </c>
       <c r="E822" t="n">
-        <v>106.06</v>
+        <v>106.38</v>
       </c>
       <c r="F822" t="n">
-        <v>186051</v>
+        <v>182972</v>
       </c>
     </row>
     <row r="823">
@@ -16941,10 +16941,10 @@
         <v>108.66</v>
       </c>
       <c r="E826" t="n">
-        <v>110.4</v>
+        <v>110.3</v>
       </c>
       <c r="F826" t="n">
-        <v>201234</v>
+        <v>197687</v>
       </c>
     </row>
     <row r="827">
@@ -16961,10 +16961,10 @@
         <v>109.21</v>
       </c>
       <c r="E827" t="n">
-        <v>112.22</v>
+        <v>112.44</v>
       </c>
       <c r="F827" t="n">
-        <v>207851</v>
+        <v>203469</v>
       </c>
     </row>
     <row r="828">
@@ -17041,10 +17041,10 @@
         <v>103.97</v>
       </c>
       <c r="E831" t="n">
-        <v>106.86</v>
+        <v>107.38</v>
       </c>
       <c r="F831" t="n">
-        <v>243371</v>
+        <v>240901</v>
       </c>
     </row>
     <row r="832">
@@ -17061,10 +17061,10 @@
         <v>106.88</v>
       </c>
       <c r="E832" t="n">
-        <v>109.76</v>
+        <v>110.4</v>
       </c>
       <c r="F832" t="n">
-        <v>193013</v>
+        <v>190398</v>
       </c>
     </row>
     <row r="833">
@@ -17141,10 +17141,10 @@
         <v>104.22</v>
       </c>
       <c r="E836" t="n">
-        <v>109.5</v>
+        <v>109.59</v>
       </c>
       <c r="F836" t="n">
-        <v>250583</v>
+        <v>247278</v>
       </c>
     </row>
     <row r="837">
@@ -17161,10 +17161,10 @@
         <v>108.65</v>
       </c>
       <c r="E837" t="n">
-        <v>110.3</v>
+        <v>110.87</v>
       </c>
       <c r="F837" t="n">
-        <v>202895</v>
+        <v>198948</v>
       </c>
     </row>
     <row r="838">
@@ -17241,10 +17241,10 @@
         <v>110.83</v>
       </c>
       <c r="E841" t="n">
-        <v>114.15</v>
+        <v>114</v>
       </c>
       <c r="F841" t="n">
-        <v>175003</v>
+        <v>171535</v>
       </c>
     </row>
     <row r="842">
@@ -17261,10 +17261,10 @@
         <v>113.01</v>
       </c>
       <c r="E842" t="n">
-        <v>115.01</v>
+        <v>115.42</v>
       </c>
       <c r="F842" t="n">
-        <v>213418</v>
+        <v>210750</v>
       </c>
     </row>
     <row r="843">
@@ -17335,16 +17335,16 @@
         <v>113.88</v>
       </c>
       <c r="C846" t="n">
-        <v>117.74</v>
+        <v>117.57</v>
       </c>
       <c r="D846" t="n">
         <v>111.85</v>
       </c>
       <c r="E846" t="n">
-        <v>117.31</v>
+        <v>117.26</v>
       </c>
       <c r="F846" t="n">
-        <v>138282</v>
+        <v>137013</v>
       </c>
     </row>
     <row r="847">
@@ -17355,16 +17355,16 @@
         <v>117.37</v>
       </c>
       <c r="C847" t="n">
-        <v>120.6</v>
+        <v>120.57</v>
       </c>
       <c r="D847" t="n">
         <v>115.28</v>
       </c>
       <c r="E847" t="n">
-        <v>120.23</v>
+        <v>120.41</v>
       </c>
       <c r="F847" t="n">
-        <v>91626</v>
+        <v>90339</v>
       </c>
     </row>
     <row r="848">
@@ -17441,10 +17441,10 @@
         <v>121.23</v>
       </c>
       <c r="E851" t="n">
-        <v>121.41</v>
+        <v>121.71</v>
       </c>
       <c r="F851" t="n">
-        <v>176648</v>
+        <v>174232</v>
       </c>
     </row>
     <row r="852">
@@ -17461,10 +17461,10 @@
         <v>118.31</v>
       </c>
       <c r="E852" t="n">
-        <v>120.02</v>
+        <v>120.29</v>
       </c>
       <c r="F852" t="n">
-        <v>192334</v>
+        <v>190410</v>
       </c>
     </row>
     <row r="853">
@@ -17541,10 +17541,10 @@
         <v>113.72</v>
       </c>
       <c r="E856" t="n">
-        <v>116.92</v>
+        <v>117.15</v>
       </c>
       <c r="F856" t="n">
-        <v>231324</v>
+        <v>228931</v>
       </c>
     </row>
     <row r="857">
@@ -17561,10 +17561,10 @@
         <v>109.77</v>
       </c>
       <c r="E857" t="n">
-        <v>111.27</v>
+        <v>111.29</v>
       </c>
       <c r="F857" t="n">
-        <v>236868</v>
+        <v>233588</v>
       </c>
     </row>
     <row r="858">
@@ -17641,10 +17641,10 @@
         <v>105.25</v>
       </c>
       <c r="E861" t="n">
-        <v>106.13</v>
+        <v>106.29</v>
       </c>
       <c r="F861" t="n">
-        <v>234952</v>
+        <v>233040</v>
       </c>
     </row>
     <row r="862">
@@ -17661,10 +17661,10 @@
         <v>105.78</v>
       </c>
       <c r="E862" t="n">
-        <v>108.33</v>
+        <v>109.13</v>
       </c>
       <c r="F862" t="n">
-        <v>205227</v>
+        <v>202836</v>
       </c>
     </row>
     <row r="863">
@@ -17741,10 +17741,10 @@
         <v>107.7</v>
       </c>
       <c r="E866" t="n">
-        <v>108.43</v>
+        <v>108.69</v>
       </c>
       <c r="F866" t="n">
-        <v>212070</v>
+        <v>208599</v>
       </c>
     </row>
     <row r="867">
@@ -17761,10 +17761,10 @@
         <v>107.32</v>
       </c>
       <c r="E867" t="n">
-        <v>110.43</v>
+        <v>110.56</v>
       </c>
       <c r="F867" t="n">
-        <v>210630</v>
+        <v>209195</v>
       </c>
     </row>
     <row r="868">
@@ -17841,10 +17841,10 @@
         <v>97.11</v>
       </c>
       <c r="E871" t="n">
-        <v>102.32</v>
+        <v>102.75</v>
       </c>
       <c r="F871" t="n">
-        <v>224620</v>
+        <v>221862</v>
       </c>
     </row>
     <row r="872">
@@ -17861,10 +17861,10 @@
         <v>102.16</v>
       </c>
       <c r="E872" t="n">
-        <v>105.2</v>
+        <v>105.32</v>
       </c>
       <c r="F872" t="n">
-        <v>237030</v>
+        <v>235167</v>
       </c>
     </row>
     <row r="873">
@@ -17941,10 +17941,10 @@
         <v>92.42</v>
       </c>
       <c r="E876" t="n">
-        <v>97.12</v>
+        <v>97.17</v>
       </c>
       <c r="F876" t="n">
-        <v>217836</v>
+        <v>215919</v>
       </c>
     </row>
     <row r="877">
@@ -17961,10 +17961,10 @@
         <v>95.59</v>
       </c>
       <c r="E877" t="n">
-        <v>97.98</v>
+        <v>98.34999999999999</v>
       </c>
       <c r="F877" t="n">
-        <v>203134</v>
+        <v>200270</v>
       </c>
     </row>
     <row r="878">
@@ -18041,10 +18041,10 @@
         <v>97.86</v>
       </c>
       <c r="E881" t="n">
-        <v>99.93000000000001</v>
+        <v>100.04</v>
       </c>
       <c r="F881" t="n">
-        <v>229298</v>
+        <v>227231</v>
       </c>
     </row>
     <row r="882">
@@ -18061,10 +18061,10 @@
         <v>97.90000000000001</v>
       </c>
       <c r="E882" t="n">
-        <v>98.98999999999999</v>
+        <v>98.67</v>
       </c>
       <c r="F882" t="n">
-        <v>226135</v>
+        <v>222921</v>
       </c>
     </row>
     <row r="883">
@@ -18141,10 +18141,10 @@
         <v>100.74</v>
       </c>
       <c r="E886" t="n">
-        <v>101.99</v>
+        <v>101.93</v>
       </c>
       <c r="F886" t="n">
-        <v>132446</v>
+        <v>130398</v>
       </c>
     </row>
     <row r="887">
@@ -18161,10 +18161,10 @@
         <v>101.27</v>
       </c>
       <c r="E887" t="n">
-        <v>103.1</v>
+        <v>103.21</v>
       </c>
       <c r="F887" t="n">
-        <v>113461</v>
+        <v>112179</v>
       </c>
     </row>
     <row r="888">
@@ -18238,13 +18238,13 @@
         <v>97.17</v>
       </c>
       <c r="D891" t="n">
-        <v>92.5</v>
+        <v>92.73</v>
       </c>
       <c r="E891" t="n">
-        <v>92.52</v>
+        <v>93.38</v>
       </c>
       <c r="F891" t="n">
-        <v>162676</v>
+        <v>160629</v>
       </c>
     </row>
     <row r="892">
@@ -18261,10 +18261,10 @@
         <v>92.15000000000001</v>
       </c>
       <c r="E892" t="n">
-        <v>93.51000000000001</v>
+        <v>93.69</v>
       </c>
       <c r="F892" t="n">
-        <v>157322</v>
+        <v>155701</v>
       </c>
     </row>
     <row r="893">
@@ -18341,10 +18341,10 @@
         <v>96.08</v>
       </c>
       <c r="E896" t="n">
-        <v>98.31</v>
+        <v>98.66</v>
       </c>
       <c r="F896" t="n">
-        <v>140818</v>
+        <v>139272</v>
       </c>
     </row>
     <row r="897">
@@ -18361,10 +18361,10 @@
         <v>96.26000000000001</v>
       </c>
       <c r="E897" t="n">
-        <v>96.89</v>
+        <v>97.3</v>
       </c>
       <c r="F897" t="n">
-        <v>145858</v>
+        <v>144235</v>
       </c>
     </row>
     <row r="898">
@@ -18441,10 +18441,10 @@
         <v>92.55</v>
       </c>
       <c r="E901" t="n">
-        <v>95.56</v>
+        <v>95.93000000000001</v>
       </c>
       <c r="F901" t="n">
-        <v>123861</v>
+        <v>122235</v>
       </c>
     </row>
     <row r="902">
@@ -18461,10 +18461,10 @@
         <v>93.7</v>
       </c>
       <c r="E902" t="n">
-        <v>95.08</v>
+        <v>95.52</v>
       </c>
       <c r="F902" t="n">
-        <v>126696</v>
+        <v>125387</v>
       </c>
     </row>
     <row r="903">
@@ -18541,10 +18541,10 @@
         <v>98.23</v>
       </c>
       <c r="E906" t="n">
-        <v>98.68000000000001</v>
+        <v>99.05</v>
       </c>
       <c r="F906" t="n">
-        <v>115830</v>
+        <v>114289</v>
       </c>
     </row>
     <row r="907">
@@ -18561,10 +18561,10 @@
         <v>96.92</v>
       </c>
       <c r="E907" t="n">
-        <v>98.56999999999999</v>
+        <v>98.70999999999999</v>
       </c>
       <c r="F907" t="n">
-        <v>128357</v>
+        <v>127109</v>
       </c>
     </row>
     <row r="908">
@@ -18641,10 +18641,10 @@
         <v>91.58</v>
       </c>
       <c r="E911" t="n">
-        <v>91.59</v>
+        <v>91.75</v>
       </c>
       <c r="F911" t="n">
-        <v>172611</v>
+        <v>171383</v>
       </c>
     </row>
     <row r="912">
@@ -18661,10 +18661,10 @@
         <v>92.41</v>
       </c>
       <c r="E912" t="n">
-        <v>92.83</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="F912" t="n">
-        <v>164349</v>
+        <v>162523</v>
       </c>
     </row>
     <row r="913">
@@ -18741,10 +18741,10 @@
         <v>86.86</v>
       </c>
       <c r="E916" t="n">
-        <v>87.73999999999999</v>
+        <v>88.03</v>
       </c>
       <c r="F916" t="n">
-        <v>175783</v>
+        <v>174104</v>
       </c>
     </row>
     <row r="917">
@@ -18761,10 +18761,10 @@
         <v>88.09</v>
       </c>
       <c r="E917" t="n">
-        <v>91.42</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="F917" t="n">
-        <v>139210</v>
+        <v>137562</v>
       </c>
     </row>
     <row r="918">
@@ -18841,10 +18841,10 @@
         <v>89.39</v>
       </c>
       <c r="E921" t="n">
-        <v>89.78</v>
+        <v>90.08</v>
       </c>
       <c r="F921" t="n">
-        <v>179533</v>
+        <v>177670</v>
       </c>
     </row>
     <row r="922">
@@ -18861,10 +18861,10 @@
         <v>89.37</v>
       </c>
       <c r="E922" t="n">
-        <v>90.36</v>
+        <v>90.58</v>
       </c>
       <c r="F922" t="n">
-        <v>177056</v>
+        <v>175462</v>
       </c>
     </row>
     <row r="923">
@@ -18941,10 +18941,10 @@
         <v>88.38</v>
       </c>
       <c r="E926" t="n">
-        <v>89.48999999999999</v>
+        <v>89.53</v>
       </c>
       <c r="F926" t="n">
-        <v>169282</v>
+        <v>167346</v>
       </c>
     </row>
     <row r="927">
@@ -18961,10 +18961,10 @@
         <v>84.61</v>
       </c>
       <c r="E927" t="n">
-        <v>85.65000000000001</v>
+        <v>85.41</v>
       </c>
       <c r="F927" t="n">
-        <v>159709</v>
+        <v>157358</v>
       </c>
     </row>
     <row r="928">
@@ -19041,10 +19041,10 @@
         <v>85.98</v>
       </c>
       <c r="E931" t="n">
-        <v>87.22</v>
+        <v>87.20999999999999</v>
       </c>
       <c r="F931" t="n">
-        <v>184095</v>
+        <v>182346</v>
       </c>
     </row>
     <row r="932">
@@ -19061,10 +19061,10 @@
         <v>84.73999999999999</v>
       </c>
       <c r="E932" t="n">
-        <v>85.04000000000001</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="F932" t="n">
-        <v>174184</v>
+        <v>172540</v>
       </c>
     </row>
     <row r="933">
@@ -19141,10 +19141,10 @@
         <v>92.09</v>
       </c>
       <c r="E936" t="n">
-        <v>94.16</v>
+        <v>94.31999999999999</v>
       </c>
       <c r="F936" t="n">
-        <v>136157</v>
+        <v>134269</v>
       </c>
     </row>
     <row r="937">
@@ -19161,10 +19161,10 @@
         <v>93.25</v>
       </c>
       <c r="E937" t="n">
-        <v>97.59</v>
+        <v>96.95</v>
       </c>
       <c r="F937" t="n">
-        <v>161145</v>
+        <v>158303</v>
       </c>
     </row>
     <row r="938">
@@ -19241,10 +19241,10 @@
         <v>90.18000000000001</v>
       </c>
       <c r="E941" t="n">
-        <v>93.67</v>
+        <v>93.61</v>
       </c>
       <c r="F941" t="n">
-        <v>189909</v>
+        <v>187899</v>
       </c>
     </row>
     <row r="942">
@@ -19261,10 +19261,10 @@
         <v>90.34</v>
       </c>
       <c r="E942" t="n">
-        <v>90.66</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="F942" t="n">
-        <v>186342</v>
+        <v>184164</v>
       </c>
     </row>
     <row r="943">
@@ -19341,10 +19341,10 @@
         <v>90.34</v>
       </c>
       <c r="E946" t="n">
-        <v>91.11</v>
+        <v>91</v>
       </c>
       <c r="F946" t="n">
-        <v>172151</v>
+        <v>169394</v>
       </c>
     </row>
     <row r="947">
@@ -19361,10 +19361,10 @@
         <v>89.40000000000001</v>
       </c>
       <c r="E947" t="n">
-        <v>91.58</v>
+        <v>91.7</v>
       </c>
       <c r="F947" t="n">
-        <v>170499</v>
+        <v>168937</v>
       </c>
     </row>
     <row r="948">
@@ -19441,10 +19441,10 @@
         <v>93.06999999999999</v>
       </c>
       <c r="E951" t="n">
-        <v>94.45999999999999</v>
+        <v>94.91</v>
       </c>
       <c r="F951" t="n">
-        <v>135151</v>
+        <v>130846</v>
       </c>
     </row>
     <row r="952">
@@ -19461,10 +19461,10 @@
         <v>92.81999999999999</v>
       </c>
       <c r="E952" t="n">
-        <v>93.95</v>
+        <v>93.81</v>
       </c>
       <c r="F952" t="n">
-        <v>135363</v>
+        <v>133960</v>
       </c>
     </row>
     <row r="953">
@@ -19532,7 +19532,7 @@
         <v>44868</v>
       </c>
       <c r="B956" t="n">
-        <v>94.84</v>
+        <v>94.81</v>
       </c>
       <c r="C956" t="n">
         <v>95.45</v>
@@ -19544,7 +19544,7 @@
         <v>93.92</v>
       </c>
       <c r="F956" t="n">
-        <v>141621</v>
+        <v>143503</v>
       </c>
     </row>
     <row r="957">
@@ -19552,19 +19552,19 @@
         <v>44869</v>
       </c>
       <c r="B957" t="n">
-        <v>93.94</v>
+        <v>93.98</v>
       </c>
       <c r="C957" t="n">
         <v>98.23999999999999</v>
       </c>
       <c r="D957" t="n">
-        <v>93.94</v>
+        <v>93.76000000000001</v>
       </c>
       <c r="E957" t="n">
         <v>98.01000000000001</v>
       </c>
       <c r="F957" t="n">
-        <v>179958</v>
+        <v>182009</v>
       </c>
     </row>
     <row r="958">
@@ -19641,10 +19641,10 @@
         <v>90.97</v>
       </c>
       <c r="E961" t="n">
-        <v>92.47</v>
+        <v>92.69</v>
       </c>
       <c r="F961" t="n">
-        <v>170823</v>
+        <v>168690</v>
       </c>
     </row>
     <row r="962">
@@ -19661,10 +19661,10 @@
         <v>92.79000000000001</v>
       </c>
       <c r="E962" t="n">
-        <v>94.95999999999999</v>
+        <v>95.04000000000001</v>
       </c>
       <c r="F962" t="n">
-        <v>165782</v>
+        <v>163940</v>
       </c>
     </row>
     <row r="963">
@@ -19741,10 +19741,10 @@
         <v>88.72</v>
       </c>
       <c r="E966" t="n">
-        <v>89.34999999999999</v>
+        <v>89.28</v>
       </c>
       <c r="F966" t="n">
-        <v>159560</v>
+        <v>157265</v>
       </c>
     </row>
     <row r="967">
@@ -19761,10 +19761,10 @@
         <v>85.41</v>
       </c>
       <c r="E967" t="n">
-        <v>87.5</v>
+        <v>87.45</v>
       </c>
       <c r="F967" t="n">
-        <v>162655</v>
+        <v>160818</v>
       </c>
     </row>
     <row r="968">
@@ -19941,10 +19941,10 @@
         <v>86.26000000000001</v>
       </c>
       <c r="E976" t="n">
-        <v>86.98</v>
+        <v>86.84</v>
       </c>
       <c r="F976" t="n">
-        <v>136930</v>
+        <v>135345</v>
       </c>
     </row>
     <row r="977">
@@ -19961,10 +19961,10 @@
         <v>85.17</v>
       </c>
       <c r="E977" t="n">
-        <v>85.90000000000001</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="F977" t="n">
-        <v>137359</v>
+        <v>135815</v>
       </c>
     </row>
     <row r="978">
@@ -20041,10 +20041,10 @@
         <v>75.92</v>
       </c>
       <c r="E981" t="n">
-        <v>76.61</v>
+        <v>76.27</v>
       </c>
       <c r="F981" t="n">
-        <v>167594</v>
+        <v>165742</v>
       </c>
     </row>
     <row r="982">
@@ -20061,10 +20061,10 @@
         <v>75.34999999999999</v>
       </c>
       <c r="E982" t="n">
-        <v>76.79000000000001</v>
+        <v>76.76000000000001</v>
       </c>
       <c r="F982" t="n">
-        <v>153224</v>
+        <v>151706</v>
       </c>
     </row>
     <row r="983">
@@ -20141,10 +20141,10 @@
         <v>80.86</v>
       </c>
       <c r="E986" t="n">
-        <v>81.54000000000001</v>
+        <v>81.39</v>
       </c>
       <c r="F986" t="n">
-        <v>151489</v>
+        <v>149384</v>
       </c>
     </row>
     <row r="987">
@@ -20161,10 +20161,10 @@
         <v>78.61</v>
       </c>
       <c r="E987" t="n">
-        <v>79.44</v>
+        <v>79.36</v>
       </c>
       <c r="F987" t="n">
-        <v>151197</v>
+        <v>149990</v>
       </c>
     </row>
     <row r="988">
@@ -20241,10 +20241,10 @@
         <v>81.28</v>
       </c>
       <c r="E991" t="n">
-        <v>82.20999999999999</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="F991" t="n">
-        <v>95617</v>
+        <v>94348</v>
       </c>
     </row>
     <row r="992">
@@ -20321,10 +20321,10 @@
         <v>81.81999999999999</v>
       </c>
       <c r="E995" t="n">
-        <v>83.63</v>
+        <v>83.68000000000001</v>
       </c>
       <c r="F995" t="n">
-        <v>110699</v>
+        <v>109380</v>
       </c>
     </row>
     <row r="996">
@@ -20401,10 +20401,10 @@
         <v>77.63</v>
       </c>
       <c r="E999" t="n">
-        <v>78.8</v>
+        <v>78.68000000000001</v>
       </c>
       <c r="F999" t="n">
-        <v>150672</v>
+        <v>149266</v>
       </c>
     </row>
     <row r="1000">
@@ -20424,7 +20424,7 @@
         <v>78.51000000000001</v>
       </c>
       <c r="F1000" t="n">
-        <v>148389</v>
+        <v>147017</v>
       </c>
     </row>
     <row r="1001">
@@ -20501,10 +20501,10 @@
         <v>82.43000000000001</v>
       </c>
       <c r="E1004" t="n">
-        <v>83.84999999999999</v>
+        <v>83.91</v>
       </c>
       <c r="F1004" t="n">
-        <v>142735</v>
+        <v>141086</v>
       </c>
     </row>
     <row r="1005">
@@ -20515,16 +20515,16 @@
         <v>83.91</v>
       </c>
       <c r="C1005" t="n">
-        <v>85.61</v>
+        <v>85.55</v>
       </c>
       <c r="D1005" t="n">
         <v>83.55</v>
       </c>
       <c r="E1005" t="n">
-        <v>85.47</v>
+        <v>85.48</v>
       </c>
       <c r="F1005" t="n">
-        <v>131152</v>
+        <v>129757</v>
       </c>
     </row>
     <row r="1006">
@@ -20601,10 +20601,10 @@
         <v>83.95999999999999</v>
       </c>
       <c r="E1009" t="n">
-        <v>86.34</v>
+        <v>86.31999999999999</v>
       </c>
       <c r="F1009" t="n">
-        <v>144410</v>
+        <v>142583</v>
       </c>
     </row>
     <row r="1010">
@@ -20621,10 +20621,10 @@
         <v>85.69</v>
       </c>
       <c r="E1010" t="n">
-        <v>87.59</v>
+        <v>87.75</v>
       </c>
       <c r="F1010" t="n">
-        <v>125225</v>
+        <v>123973</v>
       </c>
     </row>
     <row r="1011">
@@ -20701,10 +20701,10 @@
         <v>85.75</v>
       </c>
       <c r="E1014" t="n">
-        <v>87.29000000000001</v>
+        <v>87.31</v>
       </c>
       <c r="F1014" t="n">
-        <v>96051</v>
+        <v>95077</v>
       </c>
     </row>
     <row r="1015">
@@ -20721,10 +20721,10 @@
         <v>85.48</v>
       </c>
       <c r="E1015" t="n">
-        <v>86.01000000000001</v>
+        <v>86.04000000000001</v>
       </c>
       <c r="F1015" t="n">
-        <v>110922</v>
+        <v>109841</v>
       </c>
     </row>
     <row r="1016">
@@ -20801,10 +20801,10 @@
         <v>81.2</v>
       </c>
       <c r="E1019" t="n">
-        <v>82.12</v>
+        <v>81.98</v>
       </c>
       <c r="F1019" t="n">
-        <v>150704</v>
+        <v>146732</v>
       </c>
     </row>
     <row r="1020">
@@ -20818,13 +20818,13 @@
         <v>84.11</v>
       </c>
       <c r="D1020" t="n">
-        <v>79.53</v>
+        <v>79.62</v>
       </c>
       <c r="E1020" t="n">
-        <v>79.62</v>
+        <v>79.64</v>
       </c>
       <c r="F1020" t="n">
-        <v>163093</v>
+        <v>161681</v>
       </c>
     </row>
     <row r="1021">
@@ -20901,10 +20901,10 @@
         <v>82.86</v>
       </c>
       <c r="E1024" t="n">
-        <v>83.95</v>
+        <v>83.88</v>
       </c>
       <c r="F1024" t="n">
-        <v>144061</v>
+        <v>142722</v>
       </c>
     </row>
     <row r="1025">
@@ -20921,10 +20921,10 @@
         <v>83.66</v>
       </c>
       <c r="E1025" t="n">
-        <v>86.2</v>
+        <v>86.29000000000001</v>
       </c>
       <c r="F1025" t="n">
-        <v>156718</v>
+        <v>155562</v>
       </c>
     </row>
     <row r="1026">
@@ -20998,13 +20998,13 @@
         <v>85.90000000000001</v>
       </c>
       <c r="D1029" t="n">
-        <v>84.28</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="E1029" t="n">
-        <v>84.31</v>
+        <v>84.37</v>
       </c>
       <c r="F1029" t="n">
-        <v>129946</v>
+        <v>128382</v>
       </c>
     </row>
     <row r="1030">
@@ -21021,10 +21021,10 @@
         <v>81.55</v>
       </c>
       <c r="E1030" t="n">
-        <v>82.72</v>
+        <v>82.68000000000001</v>
       </c>
       <c r="F1030" t="n">
-        <v>142763</v>
+        <v>141607</v>
       </c>
     </row>
     <row r="1031">
@@ -21101,10 +21101,10 @@
         <v>80.27</v>
       </c>
       <c r="E1034" t="n">
-        <v>82.18000000000001</v>
+        <v>82.12</v>
       </c>
       <c r="F1034" t="n">
-        <v>108091</v>
+        <v>107083</v>
       </c>
     </row>
     <row r="1035">
@@ -21121,10 +21121,10 @@
         <v>80.7</v>
       </c>
       <c r="E1035" t="n">
-        <v>82.77</v>
+        <v>82.94</v>
       </c>
       <c r="F1035" t="n">
-        <v>130526</v>
+        <v>129354</v>
       </c>
     </row>
     <row r="1036">
@@ -21201,10 +21201,10 @@
         <v>83.66</v>
       </c>
       <c r="E1039" t="n">
-        <v>84.23</v>
+        <v>84.34</v>
       </c>
       <c r="F1039" t="n">
-        <v>115434</v>
+        <v>114302</v>
       </c>
     </row>
     <row r="1040">
@@ -21215,16 +21215,16 @@
         <v>84.37</v>
       </c>
       <c r="C1040" t="n">
-        <v>85.81</v>
+        <v>85.8</v>
       </c>
       <c r="D1040" t="n">
         <v>82.2</v>
       </c>
       <c r="E1040" t="n">
-        <v>85.73999999999999</v>
+        <v>85.72</v>
       </c>
       <c r="F1040" t="n">
-        <v>120888</v>
+        <v>119970</v>
       </c>
     </row>
     <row r="1041">
@@ -21301,10 +21301,10 @@
         <v>81.16</v>
       </c>
       <c r="E1044" t="n">
-        <v>81.23</v>
+        <v>81.26000000000001</v>
       </c>
       <c r="F1044" t="n">
-        <v>121276</v>
+        <v>120126</v>
       </c>
     </row>
     <row r="1045">
@@ -21321,10 +21321,10 @@
         <v>80.47</v>
       </c>
       <c r="E1045" t="n">
-        <v>82.38</v>
+        <v>82.33</v>
       </c>
       <c r="F1045" t="n">
-        <v>172647</v>
+        <v>171433</v>
       </c>
     </row>
     <row r="1046">
@@ -21392,7 +21392,7 @@
         <v>45001</v>
       </c>
       <c r="B1049" t="n">
-        <v>74.59999999999999</v>
+        <v>74.04000000000001</v>
       </c>
       <c r="C1049" t="n">
         <v>75.23</v>
@@ -21404,7 +21404,7 @@
         <v>74.25</v>
       </c>
       <c r="F1049" t="n">
-        <v>206406</v>
+        <v>210322</v>
       </c>
     </row>
     <row r="1050">
@@ -21412,7 +21412,7 @@
         <v>45002</v>
       </c>
       <c r="B1050" t="n">
-        <v>74.41</v>
+        <v>74.45</v>
       </c>
       <c r="C1050" t="n">
         <v>75.65000000000001</v>
@@ -21424,7 +21424,7 @@
         <v>72.3</v>
       </c>
       <c r="F1050" t="n">
-        <v>194486</v>
+        <v>196053</v>
       </c>
     </row>
     <row r="1051">
@@ -21492,7 +21492,7 @@
         <v>45008</v>
       </c>
       <c r="B1054" t="n">
-        <v>75.73</v>
+        <v>75.58</v>
       </c>
       <c r="C1054" t="n">
         <v>77.09</v>
@@ -21504,7 +21504,7 @@
         <v>74.98999999999999</v>
       </c>
       <c r="F1054" t="n">
-        <v>132462</v>
+        <v>134971</v>
       </c>
     </row>
     <row r="1055">
@@ -21512,7 +21512,7 @@
         <v>45009</v>
       </c>
       <c r="B1055" t="n">
-        <v>74.92</v>
+        <v>75.08</v>
       </c>
       <c r="C1055" t="n">
         <v>75.89</v>
@@ -21524,7 +21524,7 @@
         <v>74.52</v>
       </c>
       <c r="F1055" t="n">
-        <v>158419</v>
+        <v>160608</v>
       </c>
     </row>
     <row r="1056">
@@ -21601,10 +21601,10 @@
         <v>77.13</v>
       </c>
       <c r="E1059" t="n">
-        <v>78.43000000000001</v>
+        <v>78.47</v>
       </c>
       <c r="F1059" t="n">
-        <v>102975</v>
+        <v>101875</v>
       </c>
     </row>
     <row r="1060">
@@ -21621,10 +21621,10 @@
         <v>77.79000000000001</v>
       </c>
       <c r="E1060" t="n">
-        <v>79.76000000000001</v>
+        <v>79.73</v>
       </c>
       <c r="F1060" t="n">
-        <v>103341</v>
+        <v>102278</v>
       </c>
     </row>
     <row r="1061">
@@ -21701,10 +21701,10 @@
         <v>83.89</v>
       </c>
       <c r="E1064" t="n">
-        <v>84.62</v>
+        <v>84.73</v>
       </c>
       <c r="F1064" t="n">
-        <v>128978</v>
+        <v>127887</v>
       </c>
     </row>
     <row r="1065">
@@ -21781,10 +21781,10 @@
         <v>85.78</v>
       </c>
       <c r="E1068" t="n">
-        <v>86.03</v>
+        <v>85.98</v>
       </c>
       <c r="F1068" t="n">
-        <v>107747</v>
+        <v>106530</v>
       </c>
     </row>
     <row r="1069">
@@ -21801,10 +21801,10 @@
         <v>85.27</v>
       </c>
       <c r="E1069" t="n">
-        <v>86.12</v>
+        <v>86.13</v>
       </c>
       <c r="F1069" t="n">
-        <v>119789</v>
+        <v>118921</v>
       </c>
     </row>
     <row r="1070">
@@ -21878,13 +21878,13 @@
         <v>82.59999999999999</v>
       </c>
       <c r="D1073" t="n">
-        <v>80.48999999999999</v>
+        <v>80.51000000000001</v>
       </c>
       <c r="E1073" t="n">
-        <v>80.48999999999999</v>
+        <v>80.62</v>
       </c>
       <c r="F1073" t="n">
-        <v>100157</v>
+        <v>99083</v>
       </c>
     </row>
     <row r="1074">
@@ -21901,10 +21901,10 @@
         <v>80.2</v>
       </c>
       <c r="E1074" t="n">
-        <v>81.53</v>
+        <v>81.38</v>
       </c>
       <c r="F1074" t="n">
-        <v>89589</v>
+        <v>88877</v>
       </c>
     </row>
     <row r="1075">
@@ -21981,10 +21981,10 @@
         <v>77.3</v>
       </c>
       <c r="E1078" t="n">
-        <v>78.17</v>
+        <v>78.23</v>
       </c>
       <c r="F1078" t="n">
-        <v>114226</v>
+        <v>112919</v>
       </c>
     </row>
     <row r="1079">
@@ -22001,10 +22001,10 @@
         <v>77.44</v>
       </c>
       <c r="E1079" t="n">
-        <v>80.08</v>
+        <v>80.20999999999999</v>
       </c>
       <c r="F1079" t="n">
-        <v>111593</v>
+        <v>110643</v>
       </c>
     </row>
     <row r="1080">
@@ -22081,10 +22081,10 @@
         <v>71.34</v>
       </c>
       <c r="E1083" t="n">
-        <v>72.38</v>
+        <v>72.34</v>
       </c>
       <c r="F1083" t="n">
-        <v>176458</v>
+        <v>175075</v>
       </c>
     </row>
     <row r="1084">
@@ -22101,10 +22101,10 @@
         <v>72.31999999999999</v>
       </c>
       <c r="E1084" t="n">
-        <v>75.15000000000001</v>
+        <v>75.22</v>
       </c>
       <c r="F1084" t="n">
-        <v>122688</v>
+        <v>121559</v>
       </c>
     </row>
     <row r="1085">
@@ -22181,10 +22181,10 @@
         <v>74.5</v>
       </c>
       <c r="E1088" t="n">
-        <v>75.26000000000001</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="F1088" t="n">
-        <v>142391</v>
+        <v>141443</v>
       </c>
     </row>
     <row r="1089">
@@ -22201,10 +22201,10 @@
         <v>73.84999999999999</v>
       </c>
       <c r="E1089" t="n">
-        <v>73.93000000000001</v>
+        <v>74.02</v>
       </c>
       <c r="F1089" t="n">
-        <v>144762</v>
+        <v>143925</v>
       </c>
     </row>
     <row r="1090">
@@ -22281,10 +22281,10 @@
         <v>75.42</v>
       </c>
       <c r="E1093" t="n">
-        <v>75.84</v>
+        <v>75.89</v>
       </c>
       <c r="F1093" t="n">
-        <v>98116</v>
+        <v>97144</v>
       </c>
     </row>
     <row r="1094">
@@ -22301,10 +22301,10 @@
         <v>75.01000000000001</v>
       </c>
       <c r="E1094" t="n">
-        <v>75.59999999999999</v>
+        <v>75.75</v>
       </c>
       <c r="F1094" t="n">
-        <v>108218</v>
+        <v>107224</v>
       </c>
     </row>
     <row r="1095">
@@ -22381,10 +22381,10 @@
         <v>75.08</v>
       </c>
       <c r="E1098" t="n">
-        <v>75.95999999999999</v>
+        <v>76.13</v>
       </c>
       <c r="F1098" t="n">
-        <v>95663</v>
+        <v>94656</v>
       </c>
     </row>
     <row r="1099">
@@ -22401,10 +22401,10 @@
         <v>75.62</v>
       </c>
       <c r="E1099" t="n">
-        <v>77.14</v>
+        <v>77.03</v>
       </c>
       <c r="F1099" t="n">
-        <v>86227</v>
+        <v>85632</v>
       </c>
     </row>
     <row r="1100">
@@ -22481,10 +22481,10 @@
         <v>72</v>
       </c>
       <c r="E1103" t="n">
-        <v>74.25</v>
+        <v>74.17</v>
       </c>
       <c r="F1103" t="n">
-        <v>124084</v>
+        <v>122959</v>
       </c>
     </row>
     <row r="1104">
@@ -22501,10 +22501,10 @@
         <v>74.13</v>
       </c>
       <c r="E1104" t="n">
-        <v>76.13</v>
+        <v>76.3</v>
       </c>
       <c r="F1104" t="n">
-        <v>111881</v>
+        <v>110715</v>
       </c>
     </row>
     <row r="1105">
@@ -22581,10 +22581,10 @@
         <v>73.52</v>
       </c>
       <c r="E1108" t="n">
-        <v>75.44</v>
+        <v>75.56999999999999</v>
       </c>
       <c r="F1108" t="n">
-        <v>142206</v>
+        <v>141391</v>
       </c>
     </row>
     <row r="1109">
@@ -22601,10 +22601,10 @@
         <v>74.67</v>
       </c>
       <c r="E1109" t="n">
-        <v>74.88</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="F1109" t="n">
-        <v>120995</v>
+        <v>120105</v>
       </c>
     </row>
     <row r="1110">
@@ -22681,10 +22681,10 @@
         <v>72.84999999999999</v>
       </c>
       <c r="E1113" t="n">
-        <v>75.52</v>
+        <v>75.56</v>
       </c>
       <c r="F1113" t="n">
-        <v>105947</v>
+        <v>104970</v>
       </c>
     </row>
     <row r="1114">
@@ -22701,10 +22701,10 @@
         <v>75.09999999999999</v>
       </c>
       <c r="E1114" t="n">
-        <v>76.23</v>
+        <v>76.47</v>
       </c>
       <c r="F1114" t="n">
-        <v>111184</v>
+        <v>109963</v>
       </c>
     </row>
     <row r="1115">
@@ -22781,10 +22781,10 @@
         <v>73.75</v>
       </c>
       <c r="E1118" t="n">
-        <v>74.3</v>
+        <v>74.2</v>
       </c>
       <c r="F1118" t="n">
-        <v>89974</v>
+        <v>89166</v>
       </c>
     </row>
     <row r="1119">
@@ -22795,16 +22795,16 @@
         <v>74.2</v>
       </c>
       <c r="C1119" t="n">
-        <v>74.45999999999999</v>
+        <v>74.36</v>
       </c>
       <c r="D1119" t="n">
         <v>72.25</v>
       </c>
       <c r="E1119" t="n">
-        <v>74.34</v>
+        <v>74.09</v>
       </c>
       <c r="F1119" t="n">
-        <v>101628</v>
+        <v>100773</v>
       </c>
     </row>
     <row r="1120">
@@ -22881,10 +22881,10 @@
         <v>73.56</v>
       </c>
       <c r="E1123" t="n">
-        <v>74.34999999999999</v>
+        <v>74.44</v>
       </c>
       <c r="F1123" t="n">
-        <v>118860</v>
+        <v>118096</v>
       </c>
     </row>
     <row r="1124">
@@ -22901,10 +22901,10 @@
         <v>74.23</v>
       </c>
       <c r="E1124" t="n">
-        <v>75.06999999999999</v>
+        <v>75.26000000000001</v>
       </c>
       <c r="F1124" t="n">
-        <v>108012</v>
+        <v>107062</v>
       </c>
     </row>
     <row r="1125">
@@ -22981,10 +22981,10 @@
         <v>74.94</v>
       </c>
       <c r="E1128" t="n">
-        <v>76.44</v>
+        <v>76.47</v>
       </c>
       <c r="F1128" t="n">
-        <v>121613</v>
+        <v>120498</v>
       </c>
     </row>
     <row r="1129">
@@ -23001,10 +23001,10 @@
         <v>75.91</v>
       </c>
       <c r="E1129" t="n">
-        <v>78.12</v>
+        <v>78.13</v>
       </c>
       <c r="F1129" t="n">
-        <v>101260</v>
+        <v>99946</v>
       </c>
     </row>
     <row r="1130">
@@ -23075,16 +23075,16 @@
         <v>79.95999999999999</v>
       </c>
       <c r="C1133" t="n">
-        <v>81.5</v>
+        <v>81.48999999999999</v>
       </c>
       <c r="D1133" t="n">
         <v>79.69</v>
       </c>
       <c r="E1133" t="n">
-        <v>81.37</v>
+        <v>81.48</v>
       </c>
       <c r="F1133" t="n">
-        <v>97805</v>
+        <v>96443</v>
       </c>
     </row>
     <row r="1134">
@@ -23098,13 +23098,13 @@
         <v>81.42</v>
       </c>
       <c r="D1134" t="n">
-        <v>79.34999999999999</v>
+        <v>79.44</v>
       </c>
       <c r="E1134" t="n">
-        <v>79.45</v>
+        <v>79.54000000000001</v>
       </c>
       <c r="F1134" t="n">
-        <v>99161</v>
+        <v>98000</v>
       </c>
     </row>
     <row r="1135">
@@ -23181,10 +23181,10 @@
         <v>78.56999999999999</v>
       </c>
       <c r="E1138" t="n">
-        <v>79.48</v>
+        <v>79.54000000000001</v>
       </c>
       <c r="F1138" t="n">
-        <v>77506</v>
+        <v>76777</v>
       </c>
     </row>
     <row r="1139">
@@ -23201,10 +23201,10 @@
         <v>79.51000000000001</v>
       </c>
       <c r="E1139" t="n">
-        <v>80.5</v>
+        <v>80.69</v>
       </c>
       <c r="F1139" t="n">
-        <v>70745</v>
+        <v>69907</v>
       </c>
     </row>
     <row r="1140">
@@ -23281,10 +23281,10 @@
         <v>82.54000000000001</v>
       </c>
       <c r="E1143" t="n">
-        <v>83.3</v>
+        <v>83.42</v>
       </c>
       <c r="F1143" t="n">
-        <v>101885</v>
+        <v>100960</v>
       </c>
     </row>
     <row r="1144">
@@ -23301,10 +23301,10 @@
         <v>82.78</v>
       </c>
       <c r="E1144" t="n">
-        <v>84.34999999999999</v>
+        <v>84.26000000000001</v>
       </c>
       <c r="F1144" t="n">
-        <v>96933</v>
+        <v>96080</v>
       </c>
     </row>
     <row r="1145">
@@ -23381,10 +23381,10 @@
         <v>82.23</v>
       </c>
       <c r="E1148" t="n">
-        <v>85.04000000000001</v>
+        <v>85.13</v>
       </c>
       <c r="F1148" t="n">
-        <v>124232</v>
+        <v>122532</v>
       </c>
     </row>
     <row r="1149">
@@ -23401,10 +23401,10 @@
         <v>84.89</v>
       </c>
       <c r="E1149" t="n">
-        <v>85.81</v>
+        <v>85.84</v>
       </c>
       <c r="F1149" t="n">
-        <v>104424</v>
+        <v>103319</v>
       </c>
     </row>
     <row r="1150">
@@ -23481,10 +23481,10 @@
         <v>85.89</v>
       </c>
       <c r="E1153" t="n">
-        <v>86.01000000000001</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="F1153" t="n">
-        <v>120019</v>
+        <v>119054</v>
       </c>
     </row>
     <row r="1154">
@@ -23501,10 +23501,10 @@
         <v>85.53</v>
       </c>
       <c r="E1154" t="n">
-        <v>86.16</v>
+        <v>86.26000000000001</v>
       </c>
       <c r="F1154" t="n">
-        <v>115051</v>
+        <v>114400</v>
       </c>
     </row>
     <row r="1155">
@@ -23581,10 +23581,10 @@
         <v>82.70999999999999</v>
       </c>
       <c r="E1158" t="n">
-        <v>83.42</v>
+        <v>83.45999999999999</v>
       </c>
       <c r="F1158" t="n">
-        <v>88033</v>
+        <v>87119</v>
       </c>
     </row>
     <row r="1159">
@@ -23601,10 +23601,10 @@
         <v>82.98</v>
       </c>
       <c r="E1159" t="n">
-        <v>84.42</v>
+        <v>84.37</v>
       </c>
       <c r="F1159" t="n">
-        <v>98761</v>
+        <v>98085</v>
       </c>
     </row>
     <row r="1160">
@@ -23681,10 +23681,10 @@
         <v>81.61</v>
       </c>
       <c r="E1163" t="n">
-        <v>82.67</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="F1163" t="n">
-        <v>77961</v>
+        <v>77118</v>
       </c>
     </row>
     <row r="1164">
@@ -23701,10 +23701,10 @@
         <v>82.2</v>
       </c>
       <c r="E1164" t="n">
-        <v>84.05</v>
+        <v>84.14</v>
       </c>
       <c r="F1164" t="n">
-        <v>102303</v>
+        <v>101382</v>
       </c>
     </row>
     <row r="1165">
@@ -23781,10 +23781,10 @@
         <v>84.98</v>
       </c>
       <c r="E1168" t="n">
-        <v>86.66</v>
+        <v>86.63</v>
       </c>
       <c r="F1168" t="n">
-        <v>85007</v>
+        <v>83934</v>
       </c>
     </row>
     <row r="1169">
@@ -23795,16 +23795,16 @@
         <v>86.63</v>
       </c>
       <c r="C1169" t="n">
-        <v>88.75</v>
+        <v>88.66</v>
       </c>
       <c r="D1169" t="n">
         <v>86.59</v>
       </c>
       <c r="E1169" t="n">
-        <v>88.68000000000001</v>
+        <v>88.64</v>
       </c>
       <c r="F1169" t="n">
-        <v>98645</v>
+        <v>97671</v>
       </c>
     </row>
     <row r="1170">
@@ -23881,10 +23881,10 @@
         <v>89.17</v>
       </c>
       <c r="E1173" t="n">
-        <v>89.47</v>
+        <v>89.76000000000001</v>
       </c>
       <c r="F1173" t="n">
-        <v>104343</v>
+        <v>103067</v>
       </c>
     </row>
     <row r="1174">
@@ -23901,10 +23901,10 @@
         <v>88.97</v>
       </c>
       <c r="E1174" t="n">
-        <v>90.09999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="F1174" t="n">
-        <v>101197</v>
+        <v>100164</v>
       </c>
     </row>
     <row r="1175">
@@ -23975,16 +23975,16 @@
         <v>91.56999999999999</v>
       </c>
       <c r="C1178" t="n">
-        <v>93.68000000000001</v>
+        <v>93.44</v>
       </c>
       <c r="D1178" t="n">
         <v>91.55</v>
       </c>
       <c r="E1178" t="n">
-        <v>93.56</v>
+        <v>93.36</v>
       </c>
       <c r="F1178" t="n">
-        <v>91727</v>
+        <v>89908</v>
       </c>
     </row>
     <row r="1179">
@@ -24001,10 +24001,10 @@
         <v>92.14</v>
       </c>
       <c r="E1179" t="n">
-        <v>93.56999999999999</v>
+        <v>93.52</v>
       </c>
       <c r="F1179" t="n">
-        <v>101498</v>
+        <v>100530</v>
       </c>
     </row>
     <row r="1180">
@@ -24081,10 +24081,10 @@
         <v>91.23999999999999</v>
       </c>
       <c r="E1183" t="n">
-        <v>92.20999999999999</v>
+        <v>92.27</v>
       </c>
       <c r="F1183" t="n">
-        <v>98137</v>
+        <v>97207</v>
       </c>
     </row>
     <row r="1184">
@@ -24101,10 +24101,10 @@
         <v>91.68000000000001</v>
       </c>
       <c r="E1184" t="n">
-        <v>92.28</v>
+        <v>92.31</v>
       </c>
       <c r="F1184" t="n">
-        <v>99665</v>
+        <v>98960</v>
       </c>
     </row>
     <row r="1185">
@@ -24181,10 +24181,10 @@
         <v>92.56</v>
       </c>
       <c r="E1188" t="n">
-        <v>92.89</v>
+        <v>92.94</v>
       </c>
       <c r="F1188" t="n">
-        <v>128240</v>
+        <v>127194</v>
       </c>
     </row>
     <row r="1189">
@@ -24201,10 +24201,10 @@
         <v>91.68000000000001</v>
       </c>
       <c r="E1189" t="n">
-        <v>91.8</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="F1189" t="n">
-        <v>117877</v>
+        <v>116761</v>
       </c>
     </row>
     <row r="1190">
@@ -24281,10 +24281,10 @@
         <v>83.31999999999999</v>
       </c>
       <c r="E1193" t="n">
-        <v>83.72</v>
+        <v>83.68000000000001</v>
       </c>
       <c r="F1193" t="n">
-        <v>149779</v>
+        <v>148426</v>
       </c>
     </row>
     <row r="1194">
@@ -24301,10 +24301,10 @@
         <v>82.97</v>
       </c>
       <c r="E1194" t="n">
-        <v>83.79000000000001</v>
+        <v>83.88</v>
       </c>
       <c r="F1194" t="n">
-        <v>140020</v>
+        <v>138785</v>
       </c>
     </row>
     <row r="1195">
@@ -24381,10 +24381,10 @@
         <v>84.59</v>
       </c>
       <c r="E1198" t="n">
-        <v>85.59999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="F1198" t="n">
-        <v>124560</v>
+        <v>123421</v>
       </c>
     </row>
     <row r="1199">
@@ -24404,7 +24404,7 @@
         <v>89.93000000000001</v>
       </c>
       <c r="F1199" t="n">
-        <v>120817</v>
+        <v>118765</v>
       </c>
     </row>
     <row r="1200">
@@ -24475,16 +24475,16 @@
         <v>90.26000000000001</v>
       </c>
       <c r="C1203" t="n">
-        <v>92.34999999999999</v>
+        <v>92.22</v>
       </c>
       <c r="D1203" t="n">
         <v>88.69</v>
       </c>
       <c r="E1203" t="n">
-        <v>92.04000000000001</v>
+        <v>92.16</v>
       </c>
       <c r="F1203" t="n">
-        <v>111224</v>
+        <v>109002</v>
       </c>
     </row>
     <row r="1204">
@@ -24501,10 +24501,10 @@
         <v>90.63</v>
       </c>
       <c r="E1204" t="n">
-        <v>91.26000000000001</v>
+        <v>91.13</v>
       </c>
       <c r="F1204" t="n">
-        <v>110661</v>
+        <v>109157</v>
       </c>
     </row>
     <row r="1205">
@@ -24581,10 +24581,10 @@
         <v>86.48</v>
       </c>
       <c r="E1208" t="n">
-        <v>87.23999999999999</v>
+        <v>87.25</v>
       </c>
       <c r="F1208" t="n">
-        <v>114536</v>
+        <v>113368</v>
       </c>
     </row>
     <row r="1209">
@@ -24601,10 +24601,10 @@
         <v>86.76000000000001</v>
       </c>
       <c r="E1209" t="n">
-        <v>88.70999999999999</v>
+        <v>88.76000000000001</v>
       </c>
       <c r="F1209" t="n">
-        <v>123231</v>
+        <v>121600</v>
       </c>
     </row>
     <row r="1210">
@@ -24672,7 +24672,7 @@
         <v>45232</v>
       </c>
       <c r="B1213" t="n">
-        <v>85.03</v>
+        <v>84.83</v>
       </c>
       <c r="C1213" t="n">
         <v>86.88</v>
@@ -24684,7 +24684,7 @@
         <v>86.63</v>
       </c>
       <c r="F1213" t="n">
-        <v>102261</v>
+        <v>103842</v>
       </c>
     </row>
     <row r="1214">
@@ -24692,7 +24692,7 @@
         <v>45233</v>
       </c>
       <c r="B1214" t="n">
-        <v>86.66</v>
+        <v>86.70999999999999</v>
       </c>
       <c r="C1214" t="n">
         <v>87.58</v>
@@ -24704,7 +24704,7 @@
         <v>84.95</v>
       </c>
       <c r="F1214" t="n">
-        <v>117913</v>
+        <v>119097</v>
       </c>
     </row>
     <row r="1215">
@@ -24781,10 +24781,10 @@
         <v>79.33</v>
       </c>
       <c r="E1218" t="n">
-        <v>79.76000000000001</v>
+        <v>79.75</v>
       </c>
       <c r="F1218" t="n">
-        <v>111847</v>
+        <v>110739</v>
       </c>
     </row>
     <row r="1219">
@@ -24801,10 +24801,10 @@
         <v>79.70999999999999</v>
       </c>
       <c r="E1219" t="n">
-        <v>81.43000000000001</v>
+        <v>81.36</v>
       </c>
       <c r="F1219" t="n">
-        <v>92327</v>
+        <v>91256</v>
       </c>
     </row>
     <row r="1220">
@@ -24881,10 +24881,10 @@
         <v>76.64</v>
       </c>
       <c r="E1223" t="n">
-        <v>77.45</v>
+        <v>77.43000000000001</v>
       </c>
       <c r="F1223" t="n">
-        <v>105749</v>
+        <v>104766</v>
       </c>
     </row>
     <row r="1224">
@@ -24901,10 +24901,10 @@
         <v>77.31</v>
       </c>
       <c r="E1224" t="n">
-        <v>80.43000000000001</v>
+        <v>80.37</v>
       </c>
       <c r="F1224" t="n">
-        <v>89648</v>
+        <v>88772</v>
       </c>
     </row>
     <row r="1225">
@@ -25078,13 +25078,13 @@
         <v>84.51000000000001</v>
       </c>
       <c r="D1233" t="n">
-        <v>79.94</v>
+        <v>79.95</v>
       </c>
       <c r="E1233" t="n">
-        <v>80.31</v>
+        <v>80</v>
       </c>
       <c r="F1233" t="n">
-        <v>145419</v>
+        <v>143673</v>
       </c>
     </row>
     <row r="1234">
@@ -25101,10 +25101,10 @@
         <v>78.69</v>
       </c>
       <c r="E1234" t="n">
-        <v>79.02</v>
+        <v>78.93000000000001</v>
       </c>
       <c r="F1234" t="n">
-        <v>126159</v>
+        <v>125186</v>
       </c>
     </row>
     <row r="1235">
@@ -25181,10 +25181,10 @@
         <v>73.68000000000001</v>
       </c>
       <c r="E1238" t="n">
-        <v>74.39</v>
+        <v>74.47</v>
       </c>
       <c r="F1238" t="n">
-        <v>116791</v>
+        <v>115986</v>
       </c>
     </row>
     <row r="1239">
@@ -25201,10 +25201,10 @@
         <v>74.25</v>
       </c>
       <c r="E1239" t="n">
-        <v>75.94</v>
+        <v>75.87</v>
       </c>
       <c r="F1239" t="n">
-        <v>114930</v>
+        <v>114085</v>
       </c>
     </row>
     <row r="1240">
@@ -25281,10 +25281,10 @@
         <v>74.56999999999999</v>
       </c>
       <c r="E1243" t="n">
-        <v>76.75</v>
+        <v>76.86</v>
       </c>
       <c r="F1243" t="n">
-        <v>84712</v>
+        <v>83845</v>
       </c>
     </row>
     <row r="1244">
@@ -25301,10 +25301,10 @@
         <v>75.48</v>
       </c>
       <c r="E1244" t="n">
-        <v>76.98999999999999</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="F1244" t="n">
-        <v>95068</v>
+        <v>94162</v>
       </c>
     </row>
     <row r="1245">
@@ -25381,10 +25381,10 @@
         <v>77.76000000000001</v>
       </c>
       <c r="E1248" t="n">
-        <v>79.12</v>
+        <v>79.19</v>
       </c>
       <c r="F1248" t="n">
-        <v>91755</v>
+        <v>91100</v>
       </c>
     </row>
     <row r="1249">
@@ -25461,10 +25461,10 @@
         <v>77.04000000000001</v>
       </c>
       <c r="E1252" t="n">
-        <v>77.36</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="F1252" t="n">
-        <v>95204</v>
+        <v>94380</v>
       </c>
     </row>
     <row r="1253">
@@ -25544,7 +25544,7 @@
         <v>77.53</v>
       </c>
       <c r="F1256" t="n">
-        <v>119158</v>
+        <v>118273</v>
       </c>
     </row>
     <row r="1257">
@@ -25641,10 +25641,10 @@
         <v>76.45</v>
       </c>
       <c r="E1261" t="n">
-        <v>78.01000000000001</v>
+        <v>77.61</v>
       </c>
       <c r="F1261" t="n">
-        <v>129868</v>
+        <v>128067</v>
       </c>
     </row>
     <row r="1262">
@@ -25741,10 +25741,10 @@
         <v>76.98</v>
       </c>
       <c r="E1266" t="n">
-        <v>78.56</v>
+        <v>78.63</v>
       </c>
       <c r="F1266" t="n">
-        <v>99368</v>
+        <v>98609</v>
       </c>
     </row>
     <row r="1267">
@@ -25841,10 +25841,10 @@
         <v>79.65000000000001</v>
       </c>
       <c r="E1271" t="n">
-        <v>81.69</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="F1271" t="n">
-        <v>76710</v>
+        <v>75889</v>
       </c>
     </row>
     <row r="1272">
@@ -25861,10 +25861,10 @@
         <v>80.75</v>
       </c>
       <c r="E1272" t="n">
-        <v>83.09999999999999</v>
+        <v>83.08</v>
       </c>
       <c r="F1272" t="n">
-        <v>87047</v>
+        <v>85666</v>
       </c>
     </row>
     <row r="1273">
@@ -25941,10 +25941,10 @@
         <v>78.5</v>
       </c>
       <c r="E1276" t="n">
-        <v>78.7</v>
+        <v>78.64</v>
       </c>
       <c r="F1276" t="n">
-        <v>140571</v>
+        <v>138682</v>
       </c>
     </row>
     <row r="1277">
@@ -25961,10 +25961,10 @@
         <v>76.78</v>
       </c>
       <c r="E1277" t="n">
-        <v>77.31999999999999</v>
+        <v>77.11</v>
       </c>
       <c r="F1277" t="n">
-        <v>133396</v>
+        <v>132023</v>
       </c>
     </row>
     <row r="1278">
@@ -26041,10 +26041,10 @@
         <v>78.84999999999999</v>
       </c>
       <c r="E1281" t="n">
-        <v>81.40000000000001</v>
+        <v>81.51000000000001</v>
       </c>
       <c r="F1281" t="n">
-        <v>87658</v>
+        <v>86597</v>
       </c>
     </row>
     <row r="1282">
@@ -26064,7 +26064,7 @@
         <v>81.63</v>
       </c>
       <c r="F1282" t="n">
-        <v>86235</v>
+        <v>85346</v>
       </c>
     </row>
     <row r="1283">
@@ -26141,10 +26141,10 @@
         <v>80.31999999999999</v>
       </c>
       <c r="E1286" t="n">
-        <v>82.22</v>
+        <v>82.37</v>
       </c>
       <c r="F1286" t="n">
-        <v>84560</v>
+        <v>83753</v>
       </c>
     </row>
     <row r="1287">
@@ -26161,10 +26161,10 @@
         <v>81.34</v>
       </c>
       <c r="E1287" t="n">
-        <v>82.68000000000001</v>
+        <v>82.70999999999999</v>
       </c>
       <c r="F1287" t="n">
-        <v>81459</v>
+        <v>80620</v>
       </c>
     </row>
     <row r="1288">
@@ -26241,10 +26241,10 @@
         <v>81.45</v>
       </c>
       <c r="E1291" t="n">
-        <v>82.51000000000001</v>
+        <v>82.63</v>
       </c>
       <c r="F1291" t="n">
-        <v>67848</v>
+        <v>67106</v>
       </c>
     </row>
     <row r="1292">
@@ -26261,10 +26261,10 @@
         <v>80.65000000000001</v>
       </c>
       <c r="E1292" t="n">
-        <v>80.84</v>
+        <v>80.88</v>
       </c>
       <c r="F1292" t="n">
-        <v>73168</v>
+        <v>72495</v>
       </c>
     </row>
     <row r="1293">
@@ -26341,10 +26341,10 @@
         <v>81.37</v>
       </c>
       <c r="E1296" t="n">
-        <v>81.8</v>
+        <v>81.70999999999999</v>
       </c>
       <c r="F1296" t="n">
-        <v>79642</v>
+        <v>78801</v>
       </c>
     </row>
     <row r="1297">
@@ -26361,10 +26361,10 @@
         <v>81.63</v>
       </c>
       <c r="E1297" t="n">
-        <v>83.12</v>
+        <v>83.19</v>
       </c>
       <c r="F1297" t="n">
-        <v>73275</v>
+        <v>72423</v>
       </c>
     </row>
     <row r="1298">
@@ -26441,10 +26441,10 @@
         <v>81.77</v>
       </c>
       <c r="E1301" t="n">
-        <v>82.87</v>
+        <v>82.52</v>
       </c>
       <c r="F1301" t="n">
-        <v>103853</v>
+        <v>102278</v>
       </c>
     </row>
     <row r="1302">
@@ -26461,10 +26461,10 @@
         <v>81.41</v>
       </c>
       <c r="E1302" t="n">
-        <v>81.55</v>
+        <v>81.66</v>
       </c>
       <c r="F1302" t="n">
-        <v>100115</v>
+        <v>99175</v>
       </c>
     </row>
     <row r="1303">
@@ -26532,19 +26532,19 @@
         <v>45365</v>
       </c>
       <c r="B1306" t="n">
-        <v>83.69</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="C1306" t="n">
         <v>85.18000000000001</v>
       </c>
       <c r="D1306" t="n">
-        <v>83.56999999999999</v>
+        <v>83.53</v>
       </c>
       <c r="E1306" t="n">
         <v>84.61</v>
       </c>
       <c r="F1306" t="n">
-        <v>71119</v>
+        <v>71844</v>
       </c>
     </row>
     <row r="1307">
@@ -26552,7 +26552,7 @@
         <v>45366</v>
       </c>
       <c r="B1307" t="n">
-        <v>84.68000000000001</v>
+        <v>84.65000000000001</v>
       </c>
       <c r="C1307" t="n">
         <v>85.09</v>
@@ -26564,7 +26564,7 @@
         <v>84.83</v>
       </c>
       <c r="F1307" t="n">
-        <v>74945</v>
+        <v>75864</v>
       </c>
     </row>
     <row r="1308">
@@ -26632,7 +26632,7 @@
         <v>45372</v>
       </c>
       <c r="B1311" t="n">
-        <v>85.81</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="C1311" t="n">
         <v>86.03</v>
@@ -26644,7 +26644,7 @@
         <v>84.95999999999999</v>
       </c>
       <c r="F1311" t="n">
-        <v>66113</v>
+        <v>67186</v>
       </c>
     </row>
     <row r="1312">
@@ -26652,7 +26652,7 @@
         <v>45373</v>
       </c>
       <c r="B1312" t="n">
-        <v>84.98999999999999</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="C1312" t="n">
         <v>85.58</v>
@@ -26664,7 +26664,7 @@
         <v>84.93000000000001</v>
       </c>
       <c r="F1312" t="n">
-        <v>53666</v>
+        <v>54286</v>
       </c>
     </row>
     <row r="1313">
@@ -26732,7 +26732,7 @@
         <v>45379</v>
       </c>
       <c r="B1316" t="n">
-        <v>85.65000000000001</v>
+        <v>85.56</v>
       </c>
       <c r="C1316" t="n">
         <v>86.89</v>
@@ -26744,7 +26744,7 @@
         <v>86.67</v>
       </c>
       <c r="F1316" t="n">
-        <v>56915</v>
+        <v>57372</v>
       </c>
     </row>
     <row r="1317">
@@ -26821,10 +26821,10 @@
         <v>88.43000000000001</v>
       </c>
       <c r="E1320" t="n">
-        <v>90.56</v>
+        <v>90.38</v>
       </c>
       <c r="F1320" t="n">
-        <v>75666</v>
+        <v>74470</v>
       </c>
     </row>
     <row r="1321">
@@ -26841,10 +26841,10 @@
         <v>90.18000000000001</v>
       </c>
       <c r="E1321" t="n">
-        <v>90.39</v>
+        <v>90.52</v>
       </c>
       <c r="F1321" t="n">
-        <v>80607</v>
+        <v>79937</v>
       </c>
     </row>
     <row r="1322">
@@ -26921,10 +26921,10 @@
         <v>88.87</v>
       </c>
       <c r="E1325" t="n">
-        <v>89.55</v>
+        <v>89.68000000000001</v>
       </c>
       <c r="F1325" t="n">
-        <v>107884</v>
+        <v>107040</v>
       </c>
     </row>
     <row r="1326">
@@ -26941,10 +26941,10 @@
         <v>89.45</v>
       </c>
       <c r="E1326" t="n">
-        <v>89.48999999999999</v>
+        <v>89.73</v>
       </c>
       <c r="F1326" t="n">
-        <v>109120</v>
+        <v>108331</v>
       </c>
     </row>
     <row r="1327">
@@ -27021,10 +27021,10 @@
         <v>85.63</v>
       </c>
       <c r="E1330" t="n">
-        <v>86.19</v>
+        <v>86.47</v>
       </c>
       <c r="F1330" t="n">
-        <v>108132</v>
+        <v>107464</v>
       </c>
     </row>
     <row r="1331">
@@ -27041,10 +27041,10 @@
         <v>85.61</v>
       </c>
       <c r="E1331" t="n">
-        <v>86.38</v>
+        <v>86.51000000000001</v>
       </c>
       <c r="F1331" t="n">
-        <v>144473</v>
+        <v>143518</v>
       </c>
     </row>
     <row r="1332">
@@ -27115,16 +27115,16 @@
         <v>86.88</v>
       </c>
       <c r="C1335" t="n">
-        <v>88</v>
+        <v>87.97</v>
       </c>
       <c r="D1335" t="n">
         <v>86.2</v>
       </c>
       <c r="E1335" t="n">
-        <v>87.83</v>
+        <v>87.95</v>
       </c>
       <c r="F1335" t="n">
-        <v>70059</v>
+        <v>69439</v>
       </c>
     </row>
     <row r="1336">
@@ -27141,10 +27141,10 @@
         <v>87.56999999999999</v>
       </c>
       <c r="E1336" t="n">
-        <v>87.89</v>
+        <v>87.98999999999999</v>
       </c>
       <c r="F1336" t="n">
-        <v>64445</v>
+        <v>63936</v>
       </c>
     </row>
     <row r="1337">
@@ -27221,10 +27221,10 @@
         <v>82.89</v>
       </c>
       <c r="E1340" t="n">
-        <v>83.48</v>
+        <v>83.47</v>
       </c>
       <c r="F1340" t="n">
-        <v>101847</v>
+        <v>100961</v>
       </c>
     </row>
     <row r="1341">
@@ -27238,13 +27238,13 @@
         <v>84.18000000000001</v>
       </c>
       <c r="D1341" t="n">
-        <v>82.53</v>
+        <v>82.65000000000001</v>
       </c>
       <c r="E1341" t="n">
-        <v>82.54000000000001</v>
+        <v>82.77</v>
       </c>
       <c r="F1341" t="n">
-        <v>83584</v>
+        <v>82987</v>
       </c>
     </row>
     <row r="1342">
@@ -27321,10 +27321,10 @@
         <v>83.18000000000001</v>
       </c>
       <c r="E1345" t="n">
-        <v>83.77</v>
+        <v>83.91</v>
       </c>
       <c r="F1345" t="n">
-        <v>67737</v>
+        <v>67201</v>
       </c>
     </row>
     <row r="1346">
@@ -27338,13 +27338,13 @@
         <v>84.23</v>
       </c>
       <c r="D1346" t="n">
-        <v>82.36</v>
+        <v>82.5</v>
       </c>
       <c r="E1346" t="n">
-        <v>82.36</v>
+        <v>82.61</v>
       </c>
       <c r="F1346" t="n">
-        <v>63117</v>
+        <v>62356</v>
       </c>
     </row>
     <row r="1347">
@@ -27421,10 +27421,10 @@
         <v>82.02</v>
       </c>
       <c r="E1350" t="n">
-        <v>82.98999999999999</v>
+        <v>83.04000000000001</v>
       </c>
       <c r="F1350" t="n">
-        <v>65759</v>
+        <v>65306</v>
       </c>
     </row>
     <row r="1351">
@@ -27441,10 +27441,10 @@
         <v>82.81999999999999</v>
       </c>
       <c r="E1351" t="n">
-        <v>83.56</v>
+        <v>83.68000000000001</v>
       </c>
       <c r="F1351" t="n">
-        <v>61133</v>
+        <v>60667</v>
       </c>
     </row>
     <row r="1352">
@@ -27521,10 +27521,10 @@
         <v>80.7</v>
       </c>
       <c r="E1355" t="n">
-        <v>81.06999999999999</v>
+        <v>81.09</v>
       </c>
       <c r="F1355" t="n">
-        <v>69958</v>
+        <v>68901</v>
       </c>
     </row>
     <row r="1356">
@@ -27541,10 +27541,10 @@
         <v>80.42</v>
       </c>
       <c r="E1356" t="n">
-        <v>81.79000000000001</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="F1356" t="n">
-        <v>56381</v>
+        <v>56045</v>
       </c>
     </row>
     <row r="1357">
@@ -27618,13 +27618,13 @@
         <v>83.51000000000001</v>
       </c>
       <c r="D1360" t="n">
-        <v>81.72</v>
+        <v>81.77</v>
       </c>
       <c r="E1360" t="n">
-        <v>81.73</v>
+        <v>81.88</v>
       </c>
       <c r="F1360" t="n">
-        <v>81864</v>
+        <v>81262</v>
       </c>
     </row>
     <row r="1361">
@@ -27641,10 +27641,10 @@
         <v>80.69</v>
       </c>
       <c r="E1361" t="n">
-        <v>81.09</v>
+        <v>81.22</v>
       </c>
       <c r="F1361" t="n">
-        <v>87130</v>
+        <v>86335</v>
       </c>
     </row>
     <row r="1362">
@@ -27721,10 +27721,10 @@
         <v>78.23999999999999</v>
       </c>
       <c r="E1365" t="n">
-        <v>79.69</v>
+        <v>79.73</v>
       </c>
       <c r="F1365" t="n">
-        <v>72677</v>
+        <v>72035</v>
       </c>
     </row>
     <row r="1366">
@@ -27741,10 +27741,10 @@
         <v>79.18000000000001</v>
       </c>
       <c r="E1366" t="n">
-        <v>79.23999999999999</v>
+        <v>79.27</v>
       </c>
       <c r="F1366" t="n">
-        <v>77440</v>
+        <v>76576</v>
       </c>
     </row>
     <row r="1367">
@@ -27821,10 +27821,10 @@
         <v>81.53</v>
       </c>
       <c r="E1370" t="n">
-        <v>81.68000000000001</v>
+        <v>81.98</v>
       </c>
       <c r="F1370" t="n">
-        <v>79567</v>
+        <v>78296</v>
       </c>
     </row>
     <row r="1371">
@@ -27841,10 +27841,10 @@
         <v>81.64</v>
       </c>
       <c r="E1371" t="n">
-        <v>82.06</v>
+        <v>82.2</v>
       </c>
       <c r="F1371" t="n">
-        <v>75768</v>
+        <v>75030</v>
       </c>
     </row>
     <row r="1372">
@@ -27921,10 +27921,10 @@
         <v>84.28</v>
       </c>
       <c r="E1375" t="n">
-        <v>84.7</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="F1375" t="n">
-        <v>59846</v>
+        <v>59448</v>
       </c>
     </row>
     <row r="1376">
@@ -27941,10 +27941,10 @@
         <v>84</v>
       </c>
       <c r="E1376" t="n">
-        <v>84.16</v>
+        <v>84.31</v>
       </c>
       <c r="F1376" t="n">
-        <v>60278</v>
+        <v>59797</v>
       </c>
     </row>
     <row r="1377">
@@ -28021,10 +28021,10 @@
         <v>84.01000000000001</v>
       </c>
       <c r="E1380" t="n">
-        <v>85.04000000000001</v>
+        <v>85.25</v>
       </c>
       <c r="F1380" t="n">
-        <v>64909</v>
+        <v>64362</v>
       </c>
     </row>
     <row r="1381">
@@ -28041,10 +28041,10 @@
         <v>84.39</v>
       </c>
       <c r="E1381" t="n">
-        <v>84.65000000000001</v>
+        <v>84.79000000000001</v>
       </c>
       <c r="F1381" t="n">
-        <v>69862</v>
+        <v>69177</v>
       </c>
     </row>
     <row r="1382">
@@ -28141,10 +28141,10 @@
         <v>86.17</v>
       </c>
       <c r="E1386" t="n">
-        <v>86.43000000000001</v>
+        <v>86.31999999999999</v>
       </c>
       <c r="F1386" t="n">
-        <v>68965</v>
+        <v>67919</v>
       </c>
     </row>
     <row r="1387">
@@ -28221,10 +28221,10 @@
         <v>84.16</v>
       </c>
       <c r="E1390" t="n">
-        <v>84.90000000000001</v>
+        <v>85.19</v>
       </c>
       <c r="F1390" t="n">
-        <v>78990</v>
+        <v>78243</v>
       </c>
     </row>
     <row r="1391">
@@ -28238,13 +28238,13 @@
         <v>85.67</v>
       </c>
       <c r="D1391" t="n">
-        <v>84.31999999999999</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="E1391" t="n">
-        <v>84.31999999999999</v>
+        <v>84.5</v>
       </c>
       <c r="F1391" t="n">
-        <v>74302</v>
+        <v>73607</v>
       </c>
     </row>
     <row r="1392">
@@ -28321,10 +28321,10 @@
         <v>83.41</v>
       </c>
       <c r="E1395" t="n">
-        <v>83.76000000000001</v>
+        <v>83.72</v>
       </c>
       <c r="F1395" t="n">
-        <v>69797</v>
+        <v>68620</v>
       </c>
     </row>
     <row r="1396">
@@ -28338,13 +28338,13 @@
         <v>84.41</v>
       </c>
       <c r="D1396" t="n">
-        <v>81.64</v>
+        <v>81.7</v>
       </c>
       <c r="E1396" t="n">
-        <v>81.64</v>
+        <v>81.89</v>
       </c>
       <c r="F1396" t="n">
-        <v>72736</v>
+        <v>72020</v>
       </c>
     </row>
     <row r="1397">
@@ -28421,10 +28421,10 @@
         <v>79.28</v>
       </c>
       <c r="E1400" t="n">
-        <v>81.37</v>
+        <v>81.33</v>
       </c>
       <c r="F1400" t="n">
-        <v>69789</v>
+        <v>69150</v>
       </c>
     </row>
     <row r="1401">
@@ -28441,10 +28441,10 @@
         <v>79.39</v>
       </c>
       <c r="E1401" t="n">
-        <v>79.48999999999999</v>
+        <v>79.92</v>
       </c>
       <c r="F1401" t="n">
-        <v>65748</v>
+        <v>64725</v>
       </c>
     </row>
     <row r="1402">
@@ -28521,10 +28521,10 @@
         <v>79.3</v>
       </c>
       <c r="E1405" t="n">
-        <v>79.83</v>
+        <v>80</v>
       </c>
       <c r="F1405" t="n">
-        <v>105741</v>
+        <v>104482</v>
       </c>
     </row>
     <row r="1406">
@@ -28541,10 +28541,10 @@
         <v>76.26000000000001</v>
       </c>
       <c r="E1406" t="n">
-        <v>77.14</v>
+        <v>77.08</v>
       </c>
       <c r="F1406" t="n">
-        <v>125792</v>
+        <v>124356</v>
       </c>
     </row>
     <row r="1407">
@@ -28621,10 +28621,10 @@
         <v>77.33</v>
       </c>
       <c r="E1410" t="n">
-        <v>78.59</v>
+        <v>78.73999999999999</v>
       </c>
       <c r="F1410" t="n">
-        <v>113892</v>
+        <v>113028</v>
       </c>
     </row>
     <row r="1411">
@@ -28641,10 +28641,10 @@
         <v>78.43000000000001</v>
       </c>
       <c r="E1411" t="n">
-        <v>79.27</v>
+        <v>79.34</v>
       </c>
       <c r="F1411" t="n">
-        <v>87467</v>
+        <v>86405</v>
       </c>
     </row>
     <row r="1412">
@@ -28721,10 +28721,10 @@
         <v>79.11</v>
       </c>
       <c r="E1415" t="n">
-        <v>80.26000000000001</v>
+        <v>80.31999999999999</v>
       </c>
       <c r="F1415" t="n">
-        <v>79567</v>
+        <v>78757</v>
       </c>
     </row>
     <row r="1416">
@@ -28741,10 +28741,10 @@
         <v>78.09</v>
       </c>
       <c r="E1416" t="n">
-        <v>78.94</v>
+        <v>79.22</v>
       </c>
       <c r="F1416" t="n">
-        <v>82030</v>
+        <v>81009</v>
       </c>
     </row>
     <row r="1417">
@@ -28821,10 +28821,10 @@
         <v>75.25</v>
       </c>
       <c r="E1420" t="n">
-        <v>76.42</v>
+        <v>76.47</v>
       </c>
       <c r="F1420" t="n">
-        <v>79873</v>
+        <v>79280</v>
       </c>
     </row>
     <row r="1421">
@@ -28841,10 +28841,10 @@
         <v>76.40000000000001</v>
       </c>
       <c r="E1421" t="n">
-        <v>78.13</v>
+        <v>78.17</v>
       </c>
       <c r="F1421" t="n">
-        <v>69081</v>
+        <v>68613</v>
       </c>
     </row>
     <row r="1422">
@@ -28921,10 +28921,10 @@
         <v>76.90000000000001</v>
       </c>
       <c r="E1425" t="n">
-        <v>78.72</v>
+        <v>78.81</v>
       </c>
       <c r="F1425" t="n">
-        <v>94397</v>
+        <v>93699</v>
       </c>
     </row>
     <row r="1426">
@@ -28941,10 +28941,10 @@
         <v>76.56</v>
       </c>
       <c r="E1426" t="n">
-        <v>76.77</v>
+        <v>76.81</v>
       </c>
       <c r="F1426" t="n">
-        <v>109124</v>
+        <v>108329</v>
       </c>
     </row>
     <row r="1427">
@@ -29021,10 +29021,10 @@
         <v>72.20999999999999</v>
       </c>
       <c r="E1430" t="n">
-        <v>72.53</v>
+        <v>72.54000000000001</v>
       </c>
       <c r="F1430" t="n">
-        <v>109541</v>
+        <v>108713</v>
       </c>
     </row>
     <row r="1431">
@@ -29041,10 +29041,10 @@
         <v>70.45</v>
       </c>
       <c r="E1431" t="n">
-        <v>71.2</v>
+        <v>71.37</v>
       </c>
       <c r="F1431" t="n">
-        <v>116954</v>
+        <v>115759</v>
       </c>
     </row>
     <row r="1432">
@@ -29121,10 +29121,10 @@
         <v>70.31999999999999</v>
       </c>
       <c r="E1435" t="n">
-        <v>71.67</v>
+        <v>71.89</v>
       </c>
       <c r="F1435" t="n">
-        <v>115156</v>
+        <v>114181</v>
       </c>
     </row>
     <row r="1436">
@@ -29141,10 +29141,10 @@
         <v>71.09</v>
       </c>
       <c r="E1436" t="n">
-        <v>71.59999999999999</v>
+        <v>71.73</v>
       </c>
       <c r="F1436" t="n">
-        <v>99629</v>
+        <v>98569</v>
       </c>
     </row>
     <row r="1437">
@@ -29221,10 +29221,10 @@
         <v>72.26000000000001</v>
       </c>
       <c r="E1440" t="n">
-        <v>73.97</v>
+        <v>74.05</v>
       </c>
       <c r="F1440" t="n">
-        <v>89094</v>
+        <v>88395</v>
       </c>
     </row>
     <row r="1441">
@@ -29241,10 +29241,10 @@
         <v>73.28</v>
       </c>
       <c r="E1441" t="n">
-        <v>73.87</v>
+        <v>73.98</v>
       </c>
       <c r="F1441" t="n">
-        <v>72413</v>
+        <v>71635</v>
       </c>
     </row>
     <row r="1442">
@@ -29321,10 +29321,10 @@
         <v>70.20999999999999</v>
       </c>
       <c r="E1445" t="n">
-        <v>70.68000000000001</v>
+        <v>70.66</v>
       </c>
       <c r="F1445" t="n">
-        <v>155899</v>
+        <v>154979</v>
       </c>
     </row>
     <row r="1446">
@@ -29335,16 +29335,16 @@
         <v>70.68000000000001</v>
       </c>
       <c r="C1446" t="n">
-        <v>71.90000000000001</v>
+        <v>71.89</v>
       </c>
       <c r="D1446" t="n">
         <v>70.39</v>
       </c>
       <c r="E1446" t="n">
-        <v>71.79000000000001</v>
+        <v>71.81999999999999</v>
       </c>
       <c r="F1446" t="n">
-        <v>123787</v>
+        <v>122438</v>
       </c>
     </row>
     <row r="1447">
@@ -29421,10 +29421,10 @@
         <v>74.18000000000001</v>
       </c>
       <c r="E1450" t="n">
-        <v>77.28</v>
+        <v>77.58</v>
       </c>
       <c r="F1450" t="n">
-        <v>125075</v>
+        <v>123449</v>
       </c>
     </row>
     <row r="1451">
@@ -29441,10 +29441,10 @@
         <v>77.19</v>
       </c>
       <c r="E1451" t="n">
-        <v>77.73</v>
+        <v>77.87</v>
       </c>
       <c r="F1451" t="n">
-        <v>121412</v>
+        <v>120535</v>
       </c>
     </row>
     <row r="1452">
@@ -38764,7 +38764,7 @@
         <v>81.73999999999999</v>
       </c>
       <c r="F1917" t="n">
-        <v>74700</v>
+        <v>74712</v>
       </c>
     </row>
     <row r="1918">
@@ -38772,19 +38772,19 @@
         <v>46232</v>
       </c>
       <c r="B1918" t="n">
-        <v>82.93000000000001</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="C1918" t="n">
         <v>88.36</v>
       </c>
       <c r="D1918" t="n">
-        <v>82.93000000000001</v>
+        <v>83.97</v>
       </c>
       <c r="E1918" t="n">
         <v>87.92</v>
       </c>
       <c r="F1918" t="n">
-        <v>95407</v>
+        <v>95426</v>
       </c>
     </row>
     <row r="1919">
@@ -38824,7 +38824,7 @@
         <v>89.69</v>
       </c>
       <c r="F1920" t="n">
-        <v>118408</v>
+        <v>118405</v>
       </c>
     </row>
     <row r="1921">
@@ -38844,7 +38844,27 @@
         <v>82.90000000000001</v>
       </c>
       <c r="F1921" t="n">
-        <v>120574</v>
+        <v>120569</v>
+      </c>
+    </row>
+    <row r="1922">
+      <c r="A1922" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B1922" t="n">
+        <v>83.09</v>
+      </c>
+      <c r="C1922" t="n">
+        <v>85.54000000000001</v>
+      </c>
+      <c r="D1922" t="n">
+        <v>78.27</v>
+      </c>
+      <c r="E1922" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="F1922" t="n">
+        <v>132810</v>
       </c>
     </row>
   </sheetData>

--- a/database/BRENT.xlsx
+++ b/database/BRENT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1922"/>
+  <dimension ref="A1:F1923"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3881,10 +3881,10 @@
         <v>60.96</v>
       </c>
       <c r="E173" t="n">
-        <v>61.74</v>
+        <v>61.65</v>
       </c>
       <c r="F173" t="n">
-        <v>7439</v>
+        <v>7745</v>
       </c>
     </row>
     <row r="174">
@@ -3952,7 +3952,7 @@
         <v>43769</v>
       </c>
       <c r="B177" t="n">
-        <v>60.17</v>
+        <v>60.27</v>
       </c>
       <c r="C177" t="n">
         <v>60.79</v>
@@ -3964,7 +3964,7 @@
         <v>59.46</v>
       </c>
       <c r="F177" t="n">
-        <v>20831</v>
+        <v>20603</v>
       </c>
     </row>
     <row r="178">
@@ -3972,7 +3972,7 @@
         <v>43770</v>
       </c>
       <c r="B178" t="n">
-        <v>59.42</v>
+        <v>59.64</v>
       </c>
       <c r="C178" t="n">
         <v>61.8</v>
@@ -3984,7 +3984,7 @@
         <v>61.65</v>
       </c>
       <c r="F178" t="n">
-        <v>18539</v>
+        <v>18281</v>
       </c>
     </row>
     <row r="179">
@@ -4061,10 +4061,10 @@
         <v>61.63</v>
       </c>
       <c r="E182" t="n">
-        <v>62.14</v>
+        <v>62.29</v>
       </c>
       <c r="F182" t="n">
-        <v>19306</v>
+        <v>19680</v>
       </c>
     </row>
     <row r="183">
@@ -4081,10 +4081,10 @@
         <v>60.65</v>
       </c>
       <c r="E183" t="n">
-        <v>62.61</v>
+        <v>62.64</v>
       </c>
       <c r="F183" t="n">
-        <v>21625</v>
+        <v>21863</v>
       </c>
     </row>
     <row r="184">
@@ -4161,10 +4161,10 @@
         <v>62.14</v>
       </c>
       <c r="E187" t="n">
-        <v>62.38</v>
+        <v>62.33</v>
       </c>
       <c r="F187" t="n">
-        <v>19157</v>
+        <v>19293</v>
       </c>
     </row>
     <row r="188">
@@ -4181,10 +4181,10 @@
         <v>61.69</v>
       </c>
       <c r="E188" t="n">
-        <v>63.32</v>
+        <v>63.41</v>
       </c>
       <c r="F188" t="n">
-        <v>15801</v>
+        <v>16092</v>
       </c>
     </row>
     <row r="189">
@@ -4261,10 +4261,10 @@
         <v>61.91</v>
       </c>
       <c r="E192" t="n">
-        <v>63.74</v>
+        <v>63.64</v>
       </c>
       <c r="F192" t="n">
-        <v>21582</v>
+        <v>21823</v>
       </c>
     </row>
     <row r="193">
@@ -4281,10 +4281,10 @@
         <v>61.92</v>
       </c>
       <c r="E193" t="n">
-        <v>62.58</v>
+        <v>62.52</v>
       </c>
       <c r="F193" t="n">
-        <v>17577</v>
+        <v>17794</v>
       </c>
     </row>
     <row r="194">
@@ -4461,10 +4461,10 @@
         <v>62.73</v>
       </c>
       <c r="E202" t="n">
-        <v>63.33</v>
+        <v>63.26</v>
       </c>
       <c r="F202" t="n">
-        <v>24042</v>
+        <v>24300</v>
       </c>
     </row>
     <row r="203">
@@ -4481,10 +4481,10 @@
         <v>62.82</v>
       </c>
       <c r="E203" t="n">
-        <v>64.22</v>
+        <v>64.34</v>
       </c>
       <c r="F203" t="n">
-        <v>22359</v>
+        <v>22572</v>
       </c>
     </row>
     <row r="204">
@@ -4561,10 +4561,10 @@
         <v>63.86</v>
       </c>
       <c r="E207" t="n">
-        <v>64.31</v>
+        <v>64.28</v>
       </c>
       <c r="F207" t="n">
-        <v>18198</v>
+        <v>18454</v>
       </c>
     </row>
     <row r="208">
@@ -4581,10 +4581,10 @@
         <v>64.48</v>
       </c>
       <c r="E208" t="n">
-        <v>64.88</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="F208" t="n">
-        <v>21484</v>
+        <v>21671</v>
       </c>
     </row>
     <row r="209">
@@ -4661,10 +4661,10 @@
         <v>66.02</v>
       </c>
       <c r="E212" t="n">
-        <v>66.45</v>
+        <v>66.53</v>
       </c>
       <c r="F212" t="n">
-        <v>10932</v>
+        <v>11180</v>
       </c>
     </row>
     <row r="213">
@@ -4681,10 +4681,10 @@
         <v>65.72</v>
       </c>
       <c r="E213" t="n">
-        <v>65.98</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="F213" t="n">
-        <v>14693</v>
+        <v>14806</v>
       </c>
     </row>
     <row r="214">
@@ -4741,10 +4741,10 @@
         <v>66.09</v>
       </c>
       <c r="E216" t="n">
-        <v>66.65000000000001</v>
+        <v>66.75</v>
       </c>
       <c r="F216" t="n">
-        <v>9409</v>
+        <v>9613</v>
       </c>
     </row>
     <row r="217">
@@ -4761,10 +4761,10 @@
         <v>66.34</v>
       </c>
       <c r="E217" t="n">
-        <v>66.81</v>
+        <v>66.84</v>
       </c>
       <c r="F217" t="n">
-        <v>11272</v>
+        <v>11398</v>
       </c>
     </row>
     <row r="218">
@@ -4821,10 +4821,10 @@
         <v>65.7</v>
       </c>
       <c r="E220" t="n">
-        <v>66.19</v>
+        <v>66.23</v>
       </c>
       <c r="F220" t="n">
-        <v>15153</v>
+        <v>15351</v>
       </c>
     </row>
     <row r="221">
@@ -4841,10 +4841,10 @@
         <v>66.19</v>
       </c>
       <c r="E221" t="n">
-        <v>68.55</v>
+        <v>68.59</v>
       </c>
       <c r="F221" t="n">
-        <v>35427</v>
+        <v>35609</v>
       </c>
     </row>
     <row r="222">
@@ -4924,7 +4924,7 @@
         <v>65.38</v>
       </c>
       <c r="F225" t="n">
-        <v>25682</v>
+        <v>25951</v>
       </c>
     </row>
     <row r="226">
@@ -4944,7 +4944,7 @@
         <v>65</v>
       </c>
       <c r="F226" t="n">
-        <v>20016</v>
+        <v>20436</v>
       </c>
     </row>
     <row r="227">
@@ -5021,10 +5021,10 @@
         <v>63.89</v>
       </c>
       <c r="E230" t="n">
-        <v>64.64</v>
+        <v>64.7</v>
       </c>
       <c r="F230" t="n">
-        <v>16107</v>
+        <v>16472</v>
       </c>
     </row>
     <row r="231">
@@ -5041,10 +5041,10 @@
         <v>64.45</v>
       </c>
       <c r="E231" t="n">
-        <v>64.95</v>
+        <v>65.08</v>
       </c>
       <c r="F231" t="n">
-        <v>16060</v>
+        <v>16251</v>
       </c>
     </row>
     <row r="232">
@@ -5121,10 +5121,10 @@
         <v>61.24</v>
       </c>
       <c r="E235" t="n">
-        <v>61.97</v>
+        <v>62.11</v>
       </c>
       <c r="F235" t="n">
-        <v>22982</v>
+        <v>23208</v>
       </c>
     </row>
     <row r="236">
@@ -5141,10 +5141,10 @@
         <v>60.24</v>
       </c>
       <c r="E236" t="n">
-        <v>60.82</v>
+        <v>60.64</v>
       </c>
       <c r="F236" t="n">
-        <v>21411</v>
+        <v>21687</v>
       </c>
     </row>
     <row r="237">
@@ -5221,10 +5221,10 @@
         <v>56.73</v>
       </c>
       <c r="E240" t="n">
-        <v>58.03</v>
+        <v>58.2</v>
       </c>
       <c r="F240" t="n">
-        <v>28317</v>
+        <v>28894</v>
       </c>
     </row>
     <row r="241">
@@ -5244,7 +5244,7 @@
         <v>56.63</v>
       </c>
       <c r="F241" t="n">
-        <v>30854</v>
+        <v>31264</v>
       </c>
     </row>
     <row r="242">
@@ -5321,10 +5321,10 @@
         <v>54.24</v>
       </c>
       <c r="E245" t="n">
-        <v>55.07</v>
+        <v>55.14</v>
       </c>
       <c r="F245" t="n">
-        <v>31638</v>
+        <v>31917</v>
       </c>
     </row>
     <row r="246">
@@ -5341,10 +5341,10 @@
         <v>54.2</v>
       </c>
       <c r="E246" t="n">
-        <v>54.48</v>
+        <v>54.45</v>
       </c>
       <c r="F246" t="n">
-        <v>25828</v>
+        <v>26144</v>
       </c>
     </row>
     <row r="247">
@@ -5421,10 +5421,10 @@
         <v>54.95</v>
       </c>
       <c r="E250" t="n">
-        <v>56.51</v>
+        <v>56.4</v>
       </c>
       <c r="F250" t="n">
-        <v>24675</v>
+        <v>24914</v>
       </c>
     </row>
     <row r="251">
@@ -5441,10 +5441,10 @@
         <v>56.13</v>
       </c>
       <c r="E251" t="n">
-        <v>57.32</v>
+        <v>57.33</v>
       </c>
       <c r="F251" t="n">
-        <v>21410</v>
+        <v>21778</v>
       </c>
     </row>
     <row r="252">
@@ -5521,10 +5521,10 @@
         <v>58.89</v>
       </c>
       <c r="E255" t="n">
-        <v>59.28</v>
+        <v>59.03</v>
       </c>
       <c r="F255" t="n">
-        <v>23121</v>
+        <v>23391</v>
       </c>
     </row>
     <row r="256">
@@ -5541,10 +5541,10 @@
         <v>57.71</v>
       </c>
       <c r="E256" t="n">
-        <v>58.33</v>
+        <v>58.44</v>
       </c>
       <c r="F256" t="n">
-        <v>26663</v>
+        <v>26971</v>
       </c>
     </row>
     <row r="257">
@@ -5621,10 +5621,10 @@
         <v>50.38</v>
       </c>
       <c r="E260" t="n">
-        <v>51.35</v>
+        <v>50.95</v>
       </c>
       <c r="F260" t="n">
-        <v>51199</v>
+        <v>52807</v>
       </c>
     </row>
     <row r="261">
@@ -5641,10 +5641,10 @@
         <v>48.92</v>
       </c>
       <c r="E261" t="n">
-        <v>50.01</v>
+        <v>50.08</v>
       </c>
       <c r="F261" t="n">
-        <v>71739</v>
+        <v>72794</v>
       </c>
     </row>
     <row r="262">
@@ -5721,10 +5721,10 @@
         <v>49.67</v>
       </c>
       <c r="E265" t="n">
-        <v>49.95</v>
+        <v>50</v>
       </c>
       <c r="F265" t="n">
-        <v>42080</v>
+        <v>42678</v>
       </c>
     </row>
     <row r="266">
@@ -5741,10 +5741,10 @@
         <v>45.16</v>
       </c>
       <c r="E266" t="n">
-        <v>45.55</v>
+        <v>45.51</v>
       </c>
       <c r="F266" t="n">
-        <v>64437</v>
+        <v>65295</v>
       </c>
     </row>
     <row r="267">
@@ -5812,7 +5812,7 @@
         <v>43902</v>
       </c>
       <c r="B270" t="n">
-        <v>35.97</v>
+        <v>36.29</v>
       </c>
       <c r="C270" t="n">
         <v>36.45</v>
@@ -5824,7 +5824,7 @@
         <v>33.49</v>
       </c>
       <c r="F270" t="n">
-        <v>66181</v>
+        <v>64469</v>
       </c>
     </row>
     <row r="271">
@@ -6121,10 +6121,10 @@
         <v>26.12</v>
       </c>
       <c r="E285" t="n">
-        <v>30.29</v>
+        <v>29.96</v>
       </c>
       <c r="F285" t="n">
-        <v>210087</v>
+        <v>214756</v>
       </c>
     </row>
     <row r="286">
@@ -6135,16 +6135,16 @@
         <v>29.95</v>
       </c>
       <c r="C286" t="n">
-        <v>35.24</v>
+        <v>35.28</v>
       </c>
       <c r="D286" t="n">
         <v>28.9</v>
       </c>
       <c r="E286" t="n">
-        <v>34.72</v>
+        <v>35.16</v>
       </c>
       <c r="F286" t="n">
-        <v>275171</v>
+        <v>280402</v>
       </c>
     </row>
     <row r="287">
@@ -6221,10 +6221,10 @@
         <v>32.46</v>
       </c>
       <c r="E290" t="n">
-        <v>33.2</v>
+        <v>32.8</v>
       </c>
       <c r="F290" t="n">
-        <v>230614</v>
+        <v>236196</v>
       </c>
     </row>
     <row r="291">
@@ -6321,10 +6321,10 @@
         <v>29.42</v>
       </c>
       <c r="E295" t="n">
-        <v>30.65</v>
+        <v>30.59</v>
       </c>
       <c r="F295" t="n">
-        <v>146842</v>
+        <v>151526</v>
       </c>
     </row>
     <row r="296">
@@ -6341,10 +6341,10 @@
         <v>30.13</v>
       </c>
       <c r="E296" t="n">
-        <v>30.78</v>
+        <v>30.68</v>
       </c>
       <c r="F296" t="n">
-        <v>171223</v>
+        <v>174982</v>
       </c>
     </row>
     <row r="297">
@@ -6421,10 +6421,10 @@
         <v>23.38</v>
       </c>
       <c r="E300" t="n">
-        <v>24.74</v>
+        <v>24.73</v>
       </c>
       <c r="F300" t="n">
-        <v>213310</v>
+        <v>216653</v>
       </c>
     </row>
     <row r="301">
@@ -6441,10 +6441,10 @@
         <v>23.7</v>
       </c>
       <c r="E301" t="n">
-        <v>24.98</v>
+        <v>24.99</v>
       </c>
       <c r="F301" t="n">
-        <v>163124</v>
+        <v>166443</v>
       </c>
     </row>
     <row r="302">
@@ -6521,10 +6521,10 @@
         <v>24.33</v>
       </c>
       <c r="E305" t="n">
-        <v>26.83</v>
+        <v>26.85</v>
       </c>
       <c r="F305" t="n">
-        <v>224455</v>
+        <v>229615</v>
       </c>
     </row>
     <row r="306">
@@ -6541,10 +6541,10 @@
         <v>26.05</v>
       </c>
       <c r="E306" t="n">
-        <v>26.78</v>
+        <v>26.81</v>
       </c>
       <c r="F306" t="n">
-        <v>196748</v>
+        <v>199609</v>
       </c>
     </row>
     <row r="307">
@@ -6621,10 +6621,10 @@
         <v>29.4</v>
       </c>
       <c r="E310" t="n">
-        <v>29.48</v>
+        <v>29.65</v>
       </c>
       <c r="F310" t="n">
-        <v>225301</v>
+        <v>229585</v>
       </c>
     </row>
     <row r="311">
@@ -6641,10 +6641,10 @@
         <v>29.63</v>
       </c>
       <c r="E311" t="n">
-        <v>31.26</v>
+        <v>31.25</v>
       </c>
       <c r="F311" t="n">
-        <v>192233</v>
+        <v>195288</v>
       </c>
     </row>
     <row r="312">
@@ -6715,16 +6715,16 @@
         <v>29.73</v>
       </c>
       <c r="C315" t="n">
-        <v>31.65</v>
+        <v>31.75</v>
       </c>
       <c r="D315" t="n">
         <v>29.32</v>
       </c>
       <c r="E315" t="n">
-        <v>31.44</v>
+        <v>31.58</v>
       </c>
       <c r="F315" t="n">
-        <v>152193</v>
+        <v>156389</v>
       </c>
     </row>
     <row r="316">
@@ -6735,16 +6735,16 @@
         <v>31.58</v>
       </c>
       <c r="C316" t="n">
-        <v>32.96</v>
+        <v>33.06</v>
       </c>
       <c r="D316" t="n">
         <v>31.23</v>
       </c>
       <c r="E316" t="n">
-        <v>32.9</v>
+        <v>32.94</v>
       </c>
       <c r="F316" t="n">
-        <v>160121</v>
+        <v>163209</v>
       </c>
     </row>
     <row r="317">
@@ -6821,10 +6821,10 @@
         <v>35.92</v>
       </c>
       <c r="E320" t="n">
-        <v>36.38</v>
+        <v>36.3</v>
       </c>
       <c r="F320" t="n">
-        <v>157279</v>
+        <v>160329</v>
       </c>
     </row>
     <row r="321">
@@ -6841,10 +6841,10 @@
         <v>33.87</v>
       </c>
       <c r="E321" t="n">
-        <v>35.66</v>
+        <v>35.52</v>
       </c>
       <c r="F321" t="n">
-        <v>194062</v>
+        <v>198023</v>
       </c>
     </row>
     <row r="322">
@@ -6921,10 +6921,10 @@
         <v>34.37</v>
       </c>
       <c r="E325" t="n">
-        <v>35.89</v>
+        <v>35.98</v>
       </c>
       <c r="F325" t="n">
-        <v>208524</v>
+        <v>213086</v>
       </c>
     </row>
     <row r="326">
@@ -6941,10 +6941,10 @@
         <v>34.87</v>
       </c>
       <c r="E326" t="n">
-        <v>37.43</v>
+        <v>37.61</v>
       </c>
       <c r="F326" t="n">
-        <v>193664</v>
+        <v>198370</v>
       </c>
     </row>
     <row r="327">
@@ -7021,10 +7021,10 @@
         <v>39.05</v>
       </c>
       <c r="E330" t="n">
-        <v>39.78</v>
+        <v>39.92</v>
       </c>
       <c r="F330" t="n">
-        <v>158433</v>
+        <v>161661</v>
       </c>
     </row>
     <row r="331">
@@ -7041,10 +7041,10 @@
         <v>39.75</v>
       </c>
       <c r="E331" t="n">
-        <v>42.14</v>
+        <v>41.83</v>
       </c>
       <c r="F331" t="n">
-        <v>163467</v>
+        <v>167359</v>
       </c>
     </row>
     <row r="332">
@@ -7121,10 +7121,10 @@
         <v>37.96</v>
       </c>
       <c r="E335" t="n">
-        <v>38.36</v>
+        <v>38.41</v>
       </c>
       <c r="F335" t="n">
-        <v>221502</v>
+        <v>227925</v>
       </c>
     </row>
     <row r="336">
@@ -7141,10 +7141,10 @@
         <v>37.14</v>
       </c>
       <c r="E336" t="n">
-        <v>38.94</v>
+        <v>38.97</v>
       </c>
       <c r="F336" t="n">
-        <v>260674</v>
+        <v>263342</v>
       </c>
     </row>
     <row r="337">
@@ -7221,10 +7221,10 @@
         <v>40.05</v>
       </c>
       <c r="E340" t="n">
-        <v>41.37</v>
+        <v>41.33</v>
       </c>
       <c r="F340" t="n">
-        <v>161532</v>
+        <v>163774</v>
       </c>
     </row>
     <row r="341">
@@ -7241,10 +7241,10 @@
         <v>40.97</v>
       </c>
       <c r="E341" t="n">
-        <v>41.99</v>
+        <v>41.78</v>
       </c>
       <c r="F341" t="n">
-        <v>153177</v>
+        <v>156573</v>
       </c>
     </row>
     <row r="342">
@@ -7315,16 +7315,16 @@
         <v>40.45</v>
       </c>
       <c r="C345" t="n">
-        <v>41.51</v>
+        <v>41.59</v>
       </c>
       <c r="D345" t="n">
         <v>39.68</v>
       </c>
       <c r="E345" t="n">
-        <v>41.39</v>
+        <v>41.35</v>
       </c>
       <c r="F345" t="n">
-        <v>178413</v>
+        <v>181021</v>
       </c>
     </row>
     <row r="346">
@@ -7341,10 +7341,10 @@
         <v>40.25</v>
       </c>
       <c r="E346" t="n">
-        <v>40.58</v>
+        <v>40.57</v>
       </c>
       <c r="F346" t="n">
-        <v>157969</v>
+        <v>160433</v>
       </c>
     </row>
     <row r="347">
@@ -7421,10 +7421,10 @@
         <v>41.71</v>
       </c>
       <c r="E350" t="n">
-        <v>42.71</v>
+        <v>42.65</v>
       </c>
       <c r="F350" t="n">
-        <v>142409</v>
+        <v>144329</v>
       </c>
     </row>
     <row r="351">
@@ -7521,10 +7521,10 @@
         <v>41.99</v>
       </c>
       <c r="E355" t="n">
-        <v>42.32</v>
+        <v>42.35</v>
       </c>
       <c r="F355" t="n">
-        <v>133908</v>
+        <v>136451</v>
       </c>
     </row>
     <row r="356">
@@ -7541,10 +7541,10 @@
         <v>41.4</v>
       </c>
       <c r="E356" t="n">
-        <v>43.23</v>
+        <v>43.26</v>
       </c>
       <c r="F356" t="n">
-        <v>152491</v>
+        <v>154800</v>
       </c>
     </row>
     <row r="357">
@@ -7621,10 +7621,10 @@
         <v>43.19</v>
       </c>
       <c r="E360" t="n">
-        <v>43.36</v>
+        <v>43.28</v>
       </c>
       <c r="F360" t="n">
-        <v>99613</v>
+        <v>101544</v>
       </c>
     </row>
     <row r="361">
@@ -7641,10 +7641,10 @@
         <v>42.7</v>
       </c>
       <c r="E361" t="n">
-        <v>43.18</v>
+        <v>43.12</v>
       </c>
       <c r="F361" t="n">
-        <v>93740</v>
+        <v>95049</v>
       </c>
     </row>
     <row r="362">
@@ -7721,10 +7721,10 @@
         <v>43.42</v>
       </c>
       <c r="E365" t="n">
-        <v>43.82</v>
+        <v>43.53</v>
       </c>
       <c r="F365" t="n">
-        <v>109900</v>
+        <v>112495</v>
       </c>
     </row>
     <row r="366">
@@ -7741,10 +7741,10 @@
         <v>43.18</v>
       </c>
       <c r="E366" t="n">
-        <v>43.67</v>
+        <v>43.62</v>
       </c>
       <c r="F366" t="n">
-        <v>115737</v>
+        <v>117377</v>
       </c>
     </row>
     <row r="367">
@@ -7821,10 +7821,10 @@
         <v>41.95</v>
       </c>
       <c r="E370" t="n">
-        <v>43.43</v>
+        <v>43.56</v>
       </c>
       <c r="F370" t="n">
-        <v>113377</v>
+        <v>117072</v>
       </c>
     </row>
     <row r="371">
@@ -7841,10 +7841,10 @@
         <v>42.94</v>
       </c>
       <c r="E371" t="n">
-        <v>43.65</v>
+        <v>43.59</v>
       </c>
       <c r="F371" t="n">
-        <v>127155</v>
+        <v>128800</v>
       </c>
     </row>
     <row r="372">
@@ -7921,10 +7921,10 @@
         <v>44.96</v>
       </c>
       <c r="E375" t="n">
-        <v>45.28</v>
+        <v>45.13</v>
       </c>
       <c r="F375" t="n">
-        <v>120720</v>
+        <v>122044</v>
       </c>
     </row>
     <row r="376">
@@ -7941,10 +7941,10 @@
         <v>44.4</v>
       </c>
       <c r="E376" t="n">
-        <v>44.76</v>
+        <v>44.71</v>
       </c>
       <c r="F376" t="n">
-        <v>119541</v>
+        <v>120731</v>
       </c>
     </row>
     <row r="377">
@@ -8021,10 +8021,10 @@
         <v>45.07</v>
       </c>
       <c r="E380" t="n">
-        <v>45.3</v>
+        <v>45.24</v>
       </c>
       <c r="F380" t="n">
-        <v>90204</v>
+        <v>91702</v>
       </c>
     </row>
     <row r="381">
@@ -8041,10 +8041,10 @@
         <v>44.77</v>
       </c>
       <c r="E381" t="n">
-        <v>45.2</v>
+        <v>45.19</v>
       </c>
       <c r="F381" t="n">
-        <v>83793</v>
+        <v>85013</v>
       </c>
     </row>
     <row r="382">
@@ -8121,10 +8121,10 @@
         <v>44.46</v>
       </c>
       <c r="E385" t="n">
-        <v>45.36</v>
+        <v>45.27</v>
       </c>
       <c r="F385" t="n">
-        <v>86301</v>
+        <v>87294</v>
       </c>
     </row>
     <row r="386">
@@ -8141,10 +8141,10 @@
         <v>44.09</v>
       </c>
       <c r="E386" t="n">
-        <v>44.79</v>
+        <v>44.69</v>
       </c>
       <c r="F386" t="n">
-        <v>77659</v>
+        <v>78965</v>
       </c>
     </row>
     <row r="387">
@@ -8224,7 +8224,7 @@
         <v>45.59</v>
       </c>
       <c r="F390" t="n">
-        <v>95873</v>
+        <v>96916</v>
       </c>
     </row>
     <row r="391">
@@ -8241,10 +8241,10 @@
         <v>45.36</v>
       </c>
       <c r="E391" t="n">
-        <v>45.89</v>
+        <v>45.85</v>
       </c>
       <c r="F391" t="n">
-        <v>81058</v>
+        <v>81841</v>
       </c>
     </row>
     <row r="392">
@@ -8321,10 +8321,10 @@
         <v>43.27</v>
       </c>
       <c r="E395" t="n">
-        <v>44.09</v>
+        <v>44.07</v>
       </c>
       <c r="F395" t="n">
-        <v>157249</v>
+        <v>158723</v>
       </c>
     </row>
     <row r="396">
@@ -8338,13 +8338,13 @@
         <v>44.69</v>
       </c>
       <c r="D396" t="n">
-        <v>42.45</v>
+        <v>42.42</v>
       </c>
       <c r="E396" t="n">
-        <v>42.53</v>
+        <v>42.43</v>
       </c>
       <c r="F396" t="n">
-        <v>160902</v>
+        <v>162787</v>
       </c>
     </row>
     <row r="397">
@@ -8418,13 +8418,13 @@
         <v>41.23</v>
       </c>
       <c r="D400" t="n">
-        <v>40.02</v>
+        <v>39.96</v>
       </c>
       <c r="E400" t="n">
-        <v>40.07</v>
+        <v>39.97</v>
       </c>
       <c r="F400" t="n">
-        <v>147551</v>
+        <v>149451</v>
       </c>
     </row>
     <row r="401">
@@ -8441,10 +8441,10 @@
         <v>39.68</v>
       </c>
       <c r="E401" t="n">
-        <v>40.24</v>
+        <v>40.02</v>
       </c>
       <c r="F401" t="n">
-        <v>133943</v>
+        <v>135456</v>
       </c>
     </row>
     <row r="402">
@@ -8521,10 +8521,10 @@
         <v>41.89</v>
       </c>
       <c r="E405" t="n">
-        <v>43.67</v>
+        <v>43.58</v>
       </c>
       <c r="F405" t="n">
-        <v>141089</v>
+        <v>142611</v>
       </c>
     </row>
     <row r="406">
@@ -8541,10 +8541,10 @@
         <v>42.92</v>
       </c>
       <c r="E406" t="n">
-        <v>43.34</v>
+        <v>43.41</v>
       </c>
       <c r="F406" t="n">
-        <v>127380</v>
+        <v>129546</v>
       </c>
     </row>
     <row r="407">
@@ -8621,10 +8621,10 @@
         <v>41.68</v>
       </c>
       <c r="E410" t="n">
-        <v>42.27</v>
+        <v>42.16</v>
       </c>
       <c r="F410" t="n">
-        <v>132502</v>
+        <v>133961</v>
       </c>
     </row>
     <row r="411">
@@ -8641,10 +8641,10 @@
         <v>41.97</v>
       </c>
       <c r="E411" t="n">
-        <v>42.24</v>
+        <v>42.17</v>
       </c>
       <c r="F411" t="n">
-        <v>100264</v>
+        <v>102107</v>
       </c>
     </row>
     <row r="412">
@@ -8721,10 +8721,10 @@
         <v>39.98</v>
       </c>
       <c r="E415" t="n">
-        <v>40.93</v>
+        <v>40.75</v>
       </c>
       <c r="F415" t="n">
-        <v>155461</v>
+        <v>157712</v>
       </c>
     </row>
     <row r="416">
@@ -8741,10 +8741,10 @@
         <v>38.88</v>
       </c>
       <c r="E416" t="n">
-        <v>39.23</v>
+        <v>39.15</v>
       </c>
       <c r="F416" t="n">
-        <v>188336</v>
+        <v>190634</v>
       </c>
     </row>
     <row r="417">
@@ -8821,10 +8821,10 @@
         <v>42.02</v>
       </c>
       <c r="E420" t="n">
-        <v>43.54</v>
+        <v>43.52</v>
       </c>
       <c r="F420" t="n">
-        <v>110782</v>
+        <v>112342</v>
       </c>
     </row>
     <row r="421">
@@ -8841,10 +8841,10 @@
         <v>42.78</v>
       </c>
       <c r="E421" t="n">
-        <v>42.96</v>
+        <v>42.89</v>
       </c>
       <c r="F421" t="n">
-        <v>108274</v>
+        <v>109695</v>
       </c>
     </row>
     <row r="422">
@@ -8921,10 +8921,10 @@
         <v>41.79</v>
       </c>
       <c r="E425" t="n">
-        <v>43.38</v>
+        <v>43.26</v>
       </c>
       <c r="F425" t="n">
-        <v>146298</v>
+        <v>147757</v>
       </c>
     </row>
     <row r="426">
@@ -8941,10 +8941,10 @@
         <v>42.47</v>
       </c>
       <c r="E426" t="n">
-        <v>43.02</v>
+        <v>42.95</v>
       </c>
       <c r="F426" t="n">
-        <v>129338</v>
+        <v>130839</v>
       </c>
     </row>
     <row r="427">
@@ -9021,10 +9021,10 @@
         <v>41.72</v>
       </c>
       <c r="E430" t="n">
-        <v>42.71</v>
+        <v>42.59</v>
       </c>
       <c r="F430" t="n">
-        <v>108471</v>
+        <v>110171</v>
       </c>
     </row>
     <row r="431">
@@ -9041,10 +9041,10 @@
         <v>41.76</v>
       </c>
       <c r="E431" t="n">
-        <v>41.93</v>
+        <v>41.85</v>
       </c>
       <c r="F431" t="n">
-        <v>95688</v>
+        <v>97195</v>
       </c>
     </row>
     <row r="432">
@@ -9112,7 +9112,7 @@
         <v>44133</v>
       </c>
       <c r="B435" t="n">
-        <v>39.52</v>
+        <v>39.76</v>
       </c>
       <c r="C435" t="n">
         <v>39.97</v>
@@ -9124,7 +9124,7 @@
         <v>38.05</v>
       </c>
       <c r="F435" t="n">
-        <v>183949</v>
+        <v>179602</v>
       </c>
     </row>
     <row r="436">
@@ -9132,7 +9132,7 @@
         <v>44134</v>
       </c>
       <c r="B436" t="n">
-        <v>38.05</v>
+        <v>38.25</v>
       </c>
       <c r="C436" t="n">
         <v>38.72</v>
@@ -9144,7 +9144,7 @@
         <v>37.84</v>
       </c>
       <c r="F436" t="n">
-        <v>184633</v>
+        <v>181739</v>
       </c>
     </row>
     <row r="437">
@@ -9221,10 +9221,10 @@
         <v>40.42</v>
       </c>
       <c r="E440" t="n">
-        <v>40.82</v>
+        <v>40.68</v>
       </c>
       <c r="F440" t="n">
-        <v>155706</v>
+        <v>157779</v>
       </c>
     </row>
     <row r="441">
@@ -9241,10 +9241,10 @@
         <v>39.46</v>
       </c>
       <c r="E441" t="n">
-        <v>39.84</v>
+        <v>39.71</v>
       </c>
       <c r="F441" t="n">
-        <v>150078</v>
+        <v>151438</v>
       </c>
     </row>
     <row r="442">
@@ -9318,13 +9318,13 @@
         <v>44.59</v>
       </c>
       <c r="D445" t="n">
-        <v>43.42</v>
+        <v>43.35</v>
       </c>
       <c r="E445" t="n">
-        <v>43.49</v>
+        <v>43.38</v>
       </c>
       <c r="F445" t="n">
-        <v>144322</v>
+        <v>146964</v>
       </c>
     </row>
     <row r="446">
@@ -9338,13 +9338,13 @@
         <v>43.45</v>
       </c>
       <c r="D446" t="n">
-        <v>42.77</v>
+        <v>42.68</v>
       </c>
       <c r="E446" t="n">
-        <v>42.88</v>
+        <v>42.69</v>
       </c>
       <c r="F446" t="n">
-        <v>112789</v>
+        <v>114191</v>
       </c>
     </row>
     <row r="447">
@@ -9421,10 +9421,10 @@
         <v>43.87</v>
       </c>
       <c r="E450" t="n">
-        <v>44.44</v>
+        <v>44.21</v>
       </c>
       <c r="F450" t="n">
-        <v>111013</v>
+        <v>112468</v>
       </c>
     </row>
     <row r="451">
@@ -9441,10 +9441,10 @@
         <v>44.15</v>
       </c>
       <c r="E451" t="n">
-        <v>45.06</v>
+        <v>45.07</v>
       </c>
       <c r="F451" t="n">
-        <v>88612</v>
+        <v>90427</v>
       </c>
     </row>
     <row r="452">
@@ -9624,7 +9624,7 @@
         <v>48.65</v>
       </c>
       <c r="F460" t="n">
-        <v>119976</v>
+        <v>122403</v>
       </c>
     </row>
     <row r="461">
@@ -9641,10 +9641,10 @@
         <v>48.77</v>
       </c>
       <c r="E461" t="n">
-        <v>48.97</v>
+        <v>48.96</v>
       </c>
       <c r="F461" t="n">
-        <v>124413</v>
+        <v>125701</v>
       </c>
     </row>
     <row r="462">
@@ -9721,10 +9721,10 @@
         <v>48.79</v>
       </c>
       <c r="E465" t="n">
-        <v>50.26</v>
+        <v>50.25</v>
       </c>
       <c r="F465" t="n">
-        <v>130125</v>
+        <v>132386</v>
       </c>
     </row>
     <row r="466">
@@ -9741,10 +9741,10 @@
         <v>49.67</v>
       </c>
       <c r="E466" t="n">
-        <v>49.94</v>
+        <v>49.86</v>
       </c>
       <c r="F466" t="n">
-        <v>123293</v>
+        <v>124721</v>
       </c>
     </row>
     <row r="467">
@@ -9821,10 +9821,10 @@
         <v>51.06</v>
       </c>
       <c r="E470" t="n">
-        <v>51.55</v>
+        <v>51.46</v>
       </c>
       <c r="F470" t="n">
-        <v>100894</v>
+        <v>102867</v>
       </c>
     </row>
     <row r="471">
@@ -9841,10 +9841,10 @@
         <v>51.16</v>
       </c>
       <c r="E471" t="n">
-        <v>52.19</v>
+        <v>52.23</v>
       </c>
       <c r="F471" t="n">
-        <v>96861</v>
+        <v>98705</v>
       </c>
     </row>
     <row r="472">
@@ -10081,10 +10081,10 @@
         <v>53.88</v>
       </c>
       <c r="E483" t="n">
-        <v>54.45</v>
+        <v>54.34</v>
       </c>
       <c r="F483" t="n">
-        <v>140683</v>
+        <v>142258</v>
       </c>
     </row>
     <row r="484">
@@ -10095,16 +10095,16 @@
         <v>54.46</v>
       </c>
       <c r="C484" t="n">
-        <v>56.06</v>
+        <v>56.2</v>
       </c>
       <c r="D484" t="n">
         <v>54.3</v>
       </c>
       <c r="E484" t="n">
-        <v>56.02</v>
+        <v>56.11</v>
       </c>
       <c r="F484" t="n">
-        <v>151805</v>
+        <v>155413</v>
       </c>
     </row>
     <row r="485">
@@ -10181,10 +10181,10 @@
         <v>55.21</v>
       </c>
       <c r="E488" t="n">
-        <v>56.3</v>
+        <v>56.37</v>
       </c>
       <c r="F488" t="n">
-        <v>123090</v>
+        <v>125098</v>
       </c>
     </row>
     <row r="489">
@@ -10201,10 +10201,10 @@
         <v>54.63</v>
       </c>
       <c r="E489" t="n">
-        <v>54.94</v>
+        <v>54.75</v>
       </c>
       <c r="F489" t="n">
-        <v>133988</v>
+        <v>135898</v>
       </c>
     </row>
     <row r="490">
@@ -10281,10 +10281,10 @@
         <v>55.38</v>
       </c>
       <c r="E493" t="n">
-        <v>55.86</v>
+        <v>55.84</v>
       </c>
       <c r="F493" t="n">
-        <v>103188</v>
+        <v>104851</v>
       </c>
     </row>
     <row r="494">
@@ -10301,10 +10301,10 @@
         <v>54.38</v>
       </c>
       <c r="E494" t="n">
-        <v>55.08</v>
+        <v>54.88</v>
       </c>
       <c r="F494" t="n">
-        <v>133367</v>
+        <v>135622</v>
       </c>
     </row>
     <row r="495">
@@ -10378,13 +10378,13 @@
         <v>56.16</v>
       </c>
       <c r="D498" t="n">
-        <v>54.93</v>
+        <v>54.84</v>
       </c>
       <c r="E498" t="n">
-        <v>55</v>
+        <v>54.84</v>
       </c>
       <c r="F498" t="n">
-        <v>160473</v>
+        <v>162289</v>
       </c>
     </row>
     <row r="499">
@@ -10401,10 +10401,10 @@
         <v>54.84</v>
       </c>
       <c r="E499" t="n">
-        <v>55</v>
+        <v>54.93</v>
       </c>
       <c r="F499" t="n">
-        <v>160923</v>
+        <v>163671</v>
       </c>
     </row>
     <row r="500">
@@ -10481,10 +10481,10 @@
         <v>57.93</v>
       </c>
       <c r="E503" t="n">
-        <v>58.79</v>
+        <v>58.87</v>
       </c>
       <c r="F503" t="n">
-        <v>123567</v>
+        <v>125851</v>
       </c>
     </row>
     <row r="504">
@@ -10501,10 +10501,10 @@
         <v>58.87</v>
       </c>
       <c r="E504" t="n">
-        <v>59.31</v>
+        <v>59.41</v>
       </c>
       <c r="F504" t="n">
-        <v>118436</v>
+        <v>120954</v>
       </c>
     </row>
     <row r="505">
@@ -10578,13 +10578,13 @@
         <v>61.23</v>
       </c>
       <c r="D508" t="n">
-        <v>60.5</v>
+        <v>60.44</v>
       </c>
       <c r="E508" t="n">
-        <v>60.6</v>
+        <v>60.52</v>
       </c>
       <c r="F508" t="n">
-        <v>104511</v>
+        <v>107974</v>
       </c>
     </row>
     <row r="509">
@@ -10604,7 +10604,7 @@
         <v>62.22</v>
       </c>
       <c r="F509" t="n">
-        <v>123306</v>
+        <v>126905</v>
       </c>
     </row>
     <row r="510">
@@ -10681,10 +10681,10 @@
         <v>62.54</v>
       </c>
       <c r="E513" t="n">
-        <v>62.75</v>
+        <v>62.88</v>
       </c>
       <c r="F513" t="n">
-        <v>170306</v>
+        <v>173632</v>
       </c>
     </row>
     <row r="514">
@@ -10701,10 +10701,10 @@
         <v>61.42</v>
       </c>
       <c r="E514" t="n">
-        <v>61.95</v>
+        <v>61.97</v>
       </c>
       <c r="F514" t="n">
-        <v>181146</v>
+        <v>184306</v>
       </c>
     </row>
     <row r="515">
@@ -10781,10 +10781,10 @@
         <v>65.55</v>
       </c>
       <c r="E518" t="n">
-        <v>65.86</v>
+        <v>65.97</v>
       </c>
       <c r="F518" t="n">
-        <v>210726</v>
+        <v>215533</v>
       </c>
     </row>
     <row r="519">
@@ -10801,10 +10801,10 @@
         <v>64.13</v>
       </c>
       <c r="E519" t="n">
-        <v>64.25</v>
+        <v>64.27</v>
       </c>
       <c r="F519" t="n">
-        <v>234931</v>
+        <v>239274</v>
       </c>
     </row>
     <row r="520">
@@ -10881,10 +10881,10 @@
         <v>63.17</v>
       </c>
       <c r="E523" t="n">
-        <v>66.94</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="F523" t="n">
-        <v>225843</v>
+        <v>230530</v>
       </c>
     </row>
     <row r="524">
@@ -10895,16 +10895,16 @@
         <v>66.86</v>
       </c>
       <c r="C524" t="n">
-        <v>69.31999999999999</v>
+        <v>69.41</v>
       </c>
       <c r="D524" t="n">
         <v>66.43000000000001</v>
       </c>
       <c r="E524" t="n">
-        <v>69.28</v>
+        <v>69.25</v>
       </c>
       <c r="F524" t="n">
-        <v>249828</v>
+        <v>253026</v>
       </c>
     </row>
     <row r="525">
@@ -10981,10 +10981,10 @@
         <v>67.68000000000001</v>
       </c>
       <c r="E528" t="n">
-        <v>69.40000000000001</v>
+        <v>69.17</v>
       </c>
       <c r="F528" t="n">
-        <v>160838</v>
+        <v>163581</v>
       </c>
     </row>
     <row r="529">
@@ -11001,10 +11001,10 @@
         <v>68.66</v>
       </c>
       <c r="E529" t="n">
-        <v>68.88</v>
+        <v>68.81</v>
       </c>
       <c r="F529" t="n">
-        <v>148823</v>
+        <v>151042</v>
       </c>
     </row>
     <row r="530">
@@ -11072,7 +11072,7 @@
         <v>44273</v>
       </c>
       <c r="B533" t="n">
-        <v>67.48</v>
+        <v>67.47</v>
       </c>
       <c r="C533" t="n">
         <v>67.83</v>
@@ -11084,7 +11084,7 @@
         <v>62.5</v>
       </c>
       <c r="F533" t="n">
-        <v>212082</v>
+        <v>209835</v>
       </c>
     </row>
     <row r="534">
@@ -11092,7 +11092,7 @@
         <v>44274</v>
       </c>
       <c r="B534" t="n">
-        <v>62.78</v>
+        <v>63.02</v>
       </c>
       <c r="C534" t="n">
         <v>64.73</v>
@@ -11104,7 +11104,7 @@
         <v>64.31999999999999</v>
       </c>
       <c r="F534" t="n">
-        <v>228148</v>
+        <v>223529</v>
       </c>
     </row>
     <row r="535">
@@ -11172,10 +11172,10 @@
         <v>44280</v>
       </c>
       <c r="B538" t="n">
-        <v>63.95</v>
+        <v>63.89</v>
       </c>
       <c r="C538" t="n">
-        <v>64.01000000000001</v>
+        <v>63.9</v>
       </c>
       <c r="D538" t="n">
         <v>60.82</v>
@@ -11184,7 +11184,7 @@
         <v>61.47</v>
       </c>
       <c r="F538" t="n">
-        <v>206155</v>
+        <v>203253</v>
       </c>
     </row>
     <row r="539">
@@ -11192,19 +11192,19 @@
         <v>44281</v>
       </c>
       <c r="B539" t="n">
-        <v>61.47</v>
+        <v>62.45</v>
       </c>
       <c r="C539" t="n">
         <v>64.73</v>
       </c>
       <c r="D539" t="n">
-        <v>61.47</v>
+        <v>62.07</v>
       </c>
       <c r="E539" t="n">
         <v>64.19</v>
       </c>
       <c r="F539" t="n">
-        <v>171041</v>
+        <v>167422</v>
       </c>
     </row>
     <row r="540">
@@ -11284,7 +11284,7 @@
         <v>64.51000000000001</v>
       </c>
       <c r="F543" t="n">
-        <v>197783</v>
+        <v>201289</v>
       </c>
     </row>
     <row r="544">
@@ -11361,10 +11361,10 @@
         <v>62.18</v>
       </c>
       <c r="E547" t="n">
-        <v>63.07</v>
+        <v>63.04</v>
       </c>
       <c r="F547" t="n">
-        <v>146277</v>
+        <v>149186</v>
       </c>
     </row>
     <row r="548">
@@ -11381,10 +11381,10 @@
         <v>62.33</v>
       </c>
       <c r="E548" t="n">
-        <v>62.81</v>
+        <v>62.76</v>
       </c>
       <c r="F548" t="n">
-        <v>119219</v>
+        <v>121247</v>
       </c>
     </row>
     <row r="549">
@@ -11461,10 +11461,10 @@
         <v>65.65000000000001</v>
       </c>
       <c r="E552" t="n">
-        <v>66.5</v>
+        <v>66.45</v>
       </c>
       <c r="F552" t="n">
-        <v>133306</v>
+        <v>135521</v>
       </c>
     </row>
     <row r="553">
@@ -11481,10 +11481,10 @@
         <v>66.11</v>
       </c>
       <c r="E553" t="n">
-        <v>66.40000000000001</v>
+        <v>66.31999999999999</v>
       </c>
       <c r="F553" t="n">
-        <v>120895</v>
+        <v>122938</v>
       </c>
     </row>
     <row r="554">
@@ -11564,7 +11564,7 @@
         <v>64.95</v>
       </c>
       <c r="F557" t="n">
-        <v>140975</v>
+        <v>143350</v>
       </c>
     </row>
     <row r="558">
@@ -11581,10 +11581,10 @@
         <v>64.52</v>
       </c>
       <c r="E558" t="n">
-        <v>65.45</v>
+        <v>65.31999999999999</v>
       </c>
       <c r="F558" t="n">
-        <v>124432</v>
+        <v>126302</v>
       </c>
     </row>
     <row r="559">
@@ -11661,10 +11661,10 @@
         <v>66.56</v>
       </c>
       <c r="E562" t="n">
-        <v>67.86</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="F562" t="n">
-        <v>157092</v>
+        <v>160482</v>
       </c>
     </row>
     <row r="563">
@@ -11681,10 +11681,10 @@
         <v>66.17</v>
       </c>
       <c r="E563" t="n">
-        <v>66.56</v>
+        <v>66.53</v>
       </c>
       <c r="F563" t="n">
-        <v>145779</v>
+        <v>148372</v>
       </c>
     </row>
     <row r="564">
@@ -11761,10 +11761,10 @@
         <v>67.77</v>
       </c>
       <c r="E567" t="n">
-        <v>68.05</v>
+        <v>68.03</v>
       </c>
       <c r="F567" t="n">
-        <v>153533</v>
+        <v>155507</v>
       </c>
     </row>
     <row r="568">
@@ -11784,7 +11784,7 @@
         <v>68.03</v>
       </c>
       <c r="F568" t="n">
-        <v>136012</v>
+        <v>139157</v>
       </c>
     </row>
     <row r="569">
@@ -11861,10 +11861,10 @@
         <v>66.34</v>
       </c>
       <c r="E572" t="n">
-        <v>66.83</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="F572" t="n">
-        <v>180093</v>
+        <v>182316</v>
       </c>
     </row>
     <row r="573">
@@ -11875,16 +11875,16 @@
         <v>66.81</v>
       </c>
       <c r="C573" t="n">
-        <v>68.52</v>
+        <v>68.63</v>
       </c>
       <c r="D573" t="n">
         <v>66.36</v>
       </c>
       <c r="E573" t="n">
-        <v>68.45</v>
+        <v>68.52</v>
       </c>
       <c r="F573" t="n">
-        <v>139950</v>
+        <v>142226</v>
       </c>
     </row>
     <row r="574">
@@ -11958,13 +11958,13 @@
         <v>67.02</v>
       </c>
       <c r="D577" t="n">
-        <v>64.73</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="E577" t="n">
-        <v>64.98999999999999</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="F577" t="n">
-        <v>164782</v>
+        <v>168733</v>
       </c>
     </row>
     <row r="578">
@@ -11981,10 +11981,10 @@
         <v>64.48</v>
       </c>
       <c r="E578" t="n">
-        <v>66.58</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="F578" t="n">
-        <v>153693</v>
+        <v>156317</v>
       </c>
     </row>
     <row r="579">
@@ -12055,16 +12055,16 @@
         <v>68.58</v>
       </c>
       <c r="C582" t="n">
-        <v>69.18000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="D582" t="n">
         <v>67.89</v>
       </c>
       <c r="E582" t="n">
-        <v>69.05</v>
+        <v>69.12</v>
       </c>
       <c r="F582" t="n">
-        <v>119490</v>
+        <v>122427</v>
       </c>
     </row>
     <row r="583">
@@ -12081,10 +12081,10 @@
         <v>68.48999999999999</v>
       </c>
       <c r="E583" t="n">
-        <v>68.89</v>
+        <v>68.88</v>
       </c>
       <c r="F583" t="n">
-        <v>119218</v>
+        <v>121324</v>
       </c>
     </row>
     <row r="584">
@@ -12161,10 +12161,10 @@
         <v>70.5</v>
       </c>
       <c r="E587" t="n">
-        <v>71.20999999999999</v>
+        <v>71.22</v>
       </c>
       <c r="F587" t="n">
-        <v>126247</v>
+        <v>128649</v>
       </c>
     </row>
     <row r="588">
@@ -12181,10 +12181,10 @@
         <v>70.58</v>
       </c>
       <c r="E588" t="n">
-        <v>71.47</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="F588" t="n">
-        <v>113793</v>
+        <v>117041</v>
       </c>
     </row>
     <row r="589">
@@ -12261,10 +12261,10 @@
         <v>70.66</v>
       </c>
       <c r="E592" t="n">
-        <v>72.09</v>
+        <v>71.95</v>
       </c>
       <c r="F592" t="n">
-        <v>146487</v>
+        <v>148450</v>
       </c>
     </row>
     <row r="593">
@@ -12284,7 +12284,7 @@
         <v>72.23999999999999</v>
       </c>
       <c r="F593" t="n">
-        <v>140128</v>
+        <v>142367</v>
       </c>
     </row>
     <row r="594">
@@ -12361,10 +12361,10 @@
         <v>71.41</v>
       </c>
       <c r="E597" t="n">
-        <v>72.45</v>
+        <v>72.44</v>
       </c>
       <c r="F597" t="n">
-        <v>175025</v>
+        <v>178094</v>
       </c>
     </row>
     <row r="598">
@@ -12381,10 +12381,10 @@
         <v>71.55</v>
       </c>
       <c r="E598" t="n">
-        <v>72.76000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="F598" t="n">
-        <v>147859</v>
+        <v>151345</v>
       </c>
     </row>
     <row r="599">
@@ -12461,10 +12461,10 @@
         <v>73.83</v>
       </c>
       <c r="E602" t="n">
-        <v>74.79000000000001</v>
+        <v>74.81</v>
       </c>
       <c r="F602" t="n">
-        <v>84577</v>
+        <v>85692</v>
       </c>
     </row>
     <row r="603">
@@ -12481,10 +12481,10 @@
         <v>74.14</v>
       </c>
       <c r="E603" t="n">
-        <v>75.27</v>
+        <v>75.28</v>
       </c>
       <c r="F603" t="n">
-        <v>77990</v>
+        <v>79112</v>
       </c>
     </row>
     <row r="604">
@@ -12561,10 +12561,10 @@
         <v>74.36</v>
       </c>
       <c r="E607" t="n">
-        <v>75.33</v>
+        <v>75.34</v>
       </c>
       <c r="F607" t="n">
-        <v>134296</v>
+        <v>135699</v>
       </c>
     </row>
     <row r="608">
@@ -12581,10 +12581,10 @@
         <v>75</v>
       </c>
       <c r="E608" t="n">
-        <v>76.02</v>
+        <v>75.81999999999999</v>
       </c>
       <c r="F608" t="n">
-        <v>102316</v>
+        <v>104256</v>
       </c>
     </row>
     <row r="609">
@@ -12655,16 +12655,16 @@
         <v>72.97</v>
       </c>
       <c r="C612" t="n">
-        <v>73.97</v>
+        <v>74.02</v>
       </c>
       <c r="D612" t="n">
         <v>71.73999999999999</v>
       </c>
       <c r="E612" t="n">
-        <v>73.92</v>
+        <v>73.95999999999999</v>
       </c>
       <c r="F612" t="n">
-        <v>136419</v>
+        <v>138030</v>
       </c>
     </row>
     <row r="613">
@@ -12681,10 +12681,10 @@
         <v>73.38</v>
       </c>
       <c r="E613" t="n">
-        <v>75.15000000000001</v>
+        <v>75.14</v>
       </c>
       <c r="F613" t="n">
-        <v>95892</v>
+        <v>96988</v>
       </c>
     </row>
     <row r="614">
@@ -12761,10 +12761,10 @@
         <v>72.70999999999999</v>
       </c>
       <c r="E617" t="n">
-        <v>72.79000000000001</v>
+        <v>72.72</v>
       </c>
       <c r="F617" t="n">
-        <v>132350</v>
+        <v>134216</v>
       </c>
     </row>
     <row r="618">
@@ -12781,10 +12781,10 @@
         <v>71.88</v>
       </c>
       <c r="E618" t="n">
-        <v>72.81</v>
+        <v>72.64</v>
       </c>
       <c r="F618" t="n">
-        <v>108307</v>
+        <v>110158</v>
       </c>
     </row>
     <row r="619">
@@ -12864,7 +12864,7 @@
         <v>73.01000000000001</v>
       </c>
       <c r="F622" t="n">
-        <v>113951</v>
+        <v>115159</v>
       </c>
     </row>
     <row r="623">
@@ -12875,16 +12875,16 @@
         <v>72.98</v>
       </c>
       <c r="C623" t="n">
-        <v>73.52</v>
+        <v>73.56999999999999</v>
       </c>
       <c r="D623" t="n">
         <v>72.70999999999999</v>
       </c>
       <c r="E623" t="n">
-        <v>73.44</v>
+        <v>73.5</v>
       </c>
       <c r="F623" t="n">
-        <v>83411</v>
+        <v>84579</v>
       </c>
     </row>
     <row r="624">
@@ -12961,10 +12961,10 @@
         <v>73.59999999999999</v>
       </c>
       <c r="E627" t="n">
-        <v>74.97</v>
+        <v>74.75</v>
       </c>
       <c r="F627" t="n">
-        <v>79720</v>
+        <v>81467</v>
       </c>
     </row>
     <row r="628">
@@ -12981,10 +12981,10 @@
         <v>74.26000000000001</v>
       </c>
       <c r="E628" t="n">
-        <v>74.98999999999999</v>
+        <v>74.95999999999999</v>
       </c>
       <c r="F628" t="n">
-        <v>83101</v>
+        <v>84253</v>
       </c>
     </row>
     <row r="629">
@@ -13061,10 +13061,10 @@
         <v>69.56</v>
       </c>
       <c r="E632" t="n">
-        <v>71.16</v>
+        <v>71</v>
       </c>
       <c r="F632" t="n">
-        <v>107034</v>
+        <v>108267</v>
       </c>
     </row>
     <row r="633">
@@ -13078,13 +13078,13 @@
         <v>72.22</v>
       </c>
       <c r="D633" t="n">
-        <v>70.12</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="E633" t="n">
-        <v>70.34999999999999</v>
+        <v>70.08</v>
       </c>
       <c r="F633" t="n">
-        <v>111453</v>
+        <v>113105</v>
       </c>
     </row>
     <row r="634">
@@ -13161,10 +13161,10 @@
         <v>70.41</v>
       </c>
       <c r="E637" t="n">
-        <v>70.90000000000001</v>
+        <v>70.86</v>
       </c>
       <c r="F637" t="n">
-        <v>95219</v>
+        <v>96203</v>
       </c>
     </row>
     <row r="638">
@@ -13181,10 +13181,10 @@
         <v>69.73999999999999</v>
       </c>
       <c r="E638" t="n">
-        <v>69.92</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="F638" t="n">
-        <v>93960</v>
+        <v>95696</v>
       </c>
     </row>
     <row r="639">
@@ -13261,10 +13261,10 @@
         <v>65.2</v>
       </c>
       <c r="E642" t="n">
-        <v>66.51000000000001</v>
+        <v>66.23</v>
       </c>
       <c r="F642" t="n">
-        <v>185678</v>
+        <v>187712</v>
       </c>
     </row>
     <row r="643">
@@ -13278,13 +13278,13 @@
         <v>66.54000000000001</v>
       </c>
       <c r="D643" t="n">
-        <v>64.61</v>
+        <v>64.53</v>
       </c>
       <c r="E643" t="n">
-        <v>64.62</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="F643" t="n">
-        <v>137258</v>
+        <v>138989</v>
       </c>
     </row>
     <row r="644">
@@ -13361,10 +13361,10 @@
         <v>69.73999999999999</v>
       </c>
       <c r="E647" t="n">
-        <v>70.56</v>
+        <v>70.45999999999999</v>
       </c>
       <c r="F647" t="n">
-        <v>113839</v>
+        <v>115965</v>
       </c>
     </row>
     <row r="648">
@@ -13381,10 +13381,10 @@
         <v>70.16</v>
       </c>
       <c r="E648" t="n">
-        <v>71.59999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="F648" t="n">
-        <v>99158</v>
+        <v>100455</v>
       </c>
     </row>
     <row r="649">
@@ -13461,10 +13461,10 @@
         <v>70.75</v>
       </c>
       <c r="E652" t="n">
-        <v>72.56999999999999</v>
+        <v>72.61</v>
       </c>
       <c r="F652" t="n">
-        <v>103772</v>
+        <v>105073</v>
       </c>
     </row>
     <row r="653">
@@ -13481,10 +13481,10 @@
         <v>72.20999999999999</v>
       </c>
       <c r="E653" t="n">
-        <v>72.36</v>
+        <v>72.20999999999999</v>
       </c>
       <c r="F653" t="n">
-        <v>110684</v>
+        <v>111688</v>
       </c>
     </row>
     <row r="654">
@@ -13561,10 +13561,10 @@
         <v>70.54000000000001</v>
       </c>
       <c r="E657" t="n">
-        <v>70.95</v>
+        <v>70.84</v>
       </c>
       <c r="F657" t="n">
-        <v>136836</v>
+        <v>138553</v>
       </c>
     </row>
     <row r="658">
@@ -13581,10 +13581,10 @@
         <v>70.59</v>
       </c>
       <c r="E658" t="n">
-        <v>72.44</v>
+        <v>72.51000000000001</v>
       </c>
       <c r="F658" t="n">
-        <v>106315</v>
+        <v>107925</v>
       </c>
     </row>
     <row r="659">
@@ -13661,10 +13661,10 @@
         <v>74.02</v>
       </c>
       <c r="E662" t="n">
-        <v>75.17</v>
+        <v>75.09</v>
       </c>
       <c r="F662" t="n">
-        <v>134873</v>
+        <v>136265</v>
       </c>
     </row>
     <row r="663">
@@ -13681,10 +13681,10 @@
         <v>74.06999999999999</v>
       </c>
       <c r="E663" t="n">
-        <v>74.79000000000001</v>
+        <v>74.67</v>
       </c>
       <c r="F663" t="n">
-        <v>129577</v>
+        <v>131243</v>
       </c>
     </row>
     <row r="664">
@@ -13764,7 +13764,7 @@
         <v>76.45</v>
       </c>
       <c r="F667" t="n">
-        <v>102612</v>
+        <v>104066</v>
       </c>
     </row>
     <row r="668">
@@ -13781,10 +13781,10 @@
         <v>76.09</v>
       </c>
       <c r="E668" t="n">
-        <v>77.15000000000001</v>
+        <v>77.13</v>
       </c>
       <c r="F668" t="n">
-        <v>93448</v>
+        <v>94529</v>
       </c>
     </row>
     <row r="669">
@@ -13861,10 +13861,10 @@
         <v>76.37</v>
       </c>
       <c r="E672" t="n">
-        <v>78.13</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="F672" t="n">
-        <v>180155</v>
+        <v>181989</v>
       </c>
     </row>
     <row r="673">
@@ -13881,10 +13881,10 @@
         <v>77.38</v>
       </c>
       <c r="E673" t="n">
-        <v>78.98999999999999</v>
+        <v>78.93000000000001</v>
       </c>
       <c r="F673" t="n">
-        <v>149729</v>
+        <v>151482</v>
       </c>
     </row>
     <row r="674">
@@ -13961,10 +13961,10 @@
         <v>78.78</v>
       </c>
       <c r="E677" t="n">
-        <v>82.16</v>
+        <v>82.08</v>
       </c>
       <c r="F677" t="n">
-        <v>151677</v>
+        <v>153620</v>
       </c>
     </row>
     <row r="678">
@@ -13981,10 +13981,10 @@
         <v>81.63</v>
       </c>
       <c r="E678" t="n">
-        <v>82.17</v>
+        <v>82.22</v>
       </c>
       <c r="F678" t="n">
-        <v>147722</v>
+        <v>149526</v>
       </c>
     </row>
     <row r="679">
@@ -14061,10 +14061,10 @@
         <v>82.76000000000001</v>
       </c>
       <c r="E682" t="n">
-        <v>83.69</v>
+        <v>83.67</v>
       </c>
       <c r="F682" t="n">
-        <v>120650</v>
+        <v>122153</v>
       </c>
     </row>
     <row r="683">
@@ -14081,10 +14081,10 @@
         <v>83.68000000000001</v>
       </c>
       <c r="E683" t="n">
-        <v>84.23</v>
+        <v>84.33</v>
       </c>
       <c r="F683" t="n">
-        <v>114060</v>
+        <v>116437</v>
       </c>
     </row>
     <row r="684">
@@ -14161,10 +14161,10 @@
         <v>82.73</v>
       </c>
       <c r="E687" t="n">
-        <v>84.15000000000001</v>
+        <v>84.09</v>
       </c>
       <c r="F687" t="n">
-        <v>121250</v>
+        <v>122966</v>
       </c>
     </row>
     <row r="688">
@@ -14175,16 +14175,16 @@
         <v>83.81999999999999</v>
       </c>
       <c r="C688" t="n">
-        <v>84.97</v>
+        <v>85.08</v>
       </c>
       <c r="D688" t="n">
         <v>83.18000000000001</v>
       </c>
       <c r="E688" t="n">
-        <v>84.97</v>
+        <v>84.83</v>
       </c>
       <c r="F688" t="n">
-        <v>111475</v>
+        <v>113449</v>
       </c>
     </row>
     <row r="689">
@@ -14261,10 +14261,10 @@
         <v>81.48</v>
       </c>
       <c r="E692" t="n">
-        <v>83.83</v>
+        <v>83.78</v>
       </c>
       <c r="F692" t="n">
-        <v>164605</v>
+        <v>167007</v>
       </c>
     </row>
     <row r="693">
@@ -14281,10 +14281,10 @@
         <v>82.39</v>
       </c>
       <c r="E693" t="n">
-        <v>83.55</v>
+        <v>83.41</v>
       </c>
       <c r="F693" t="n">
-        <v>132228</v>
+        <v>133535</v>
       </c>
     </row>
     <row r="694">
@@ -14352,7 +14352,7 @@
         <v>44504</v>
       </c>
       <c r="B697" t="n">
-        <v>81.12</v>
+        <v>80.83</v>
       </c>
       <c r="C697" t="n">
         <v>84.08</v>
@@ -14364,7 +14364,7 @@
         <v>80.54000000000001</v>
       </c>
       <c r="F697" t="n">
-        <v>171378</v>
+        <v>168783</v>
       </c>
     </row>
     <row r="698">
@@ -14372,7 +14372,7 @@
         <v>44505</v>
       </c>
       <c r="B698" t="n">
-        <v>80.95</v>
+        <v>81.04000000000001</v>
       </c>
       <c r="C698" t="n">
         <v>82.72</v>
@@ -14384,7 +14384,7 @@
         <v>81.93000000000001</v>
       </c>
       <c r="F698" t="n">
-        <v>166390</v>
+        <v>163172</v>
       </c>
     </row>
     <row r="699">
@@ -14461,10 +14461,10 @@
         <v>81.06</v>
       </c>
       <c r="E702" t="n">
-        <v>81.91</v>
+        <v>81.92</v>
       </c>
       <c r="F702" t="n">
-        <v>159955</v>
+        <v>161511</v>
       </c>
     </row>
     <row r="703">
@@ -14481,10 +14481,10 @@
         <v>80.63</v>
       </c>
       <c r="E703" t="n">
-        <v>81.41</v>
+        <v>81.29000000000001</v>
       </c>
       <c r="F703" t="n">
-        <v>133196</v>
+        <v>134507</v>
       </c>
     </row>
     <row r="704">
@@ -14561,10 +14561,10 @@
         <v>78.55</v>
       </c>
       <c r="E707" t="n">
-        <v>80.42</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="F707" t="n">
-        <v>131123</v>
+        <v>132952</v>
       </c>
     </row>
     <row r="708">
@@ -14581,10 +14581,10 @@
         <v>77.41</v>
       </c>
       <c r="E708" t="n">
-        <v>77.76000000000001</v>
+        <v>77.77</v>
       </c>
       <c r="F708" t="n">
-        <v>175625</v>
+        <v>177513</v>
       </c>
     </row>
     <row r="709">
@@ -14761,10 +14761,10 @@
         <v>65.67</v>
       </c>
       <c r="E717" t="n">
-        <v>69.94</v>
+        <v>70.36</v>
       </c>
       <c r="F717" t="n">
-        <v>237353</v>
+        <v>240359</v>
       </c>
     </row>
     <row r="718">
@@ -14781,10 +14781,10 @@
         <v>69.09999999999999</v>
       </c>
       <c r="E718" t="n">
-        <v>69.73</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="F718" t="n">
-        <v>205214</v>
+        <v>208893</v>
       </c>
     </row>
     <row r="719">
@@ -14858,13 +14858,13 @@
         <v>76.55</v>
       </c>
       <c r="D722" t="n">
-        <v>73.78</v>
+        <v>73.70999999999999</v>
       </c>
       <c r="E722" t="n">
-        <v>73.79000000000001</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="F722" t="n">
-        <v>140659</v>
+        <v>142264</v>
       </c>
     </row>
     <row r="723">
@@ -14881,10 +14881,10 @@
         <v>73.67</v>
       </c>
       <c r="E723" t="n">
-        <v>75.23</v>
+        <v>75.16</v>
       </c>
       <c r="F723" t="n">
-        <v>151698</v>
+        <v>153301</v>
       </c>
     </row>
     <row r="724">
@@ -14961,10 +14961,10 @@
         <v>73.88</v>
       </c>
       <c r="E727" t="n">
-        <v>74.63</v>
+        <v>74.48999999999999</v>
       </c>
       <c r="F727" t="n">
-        <v>140474</v>
+        <v>142563</v>
       </c>
     </row>
     <row r="728">
@@ -14981,10 +14981,10 @@
         <v>72.63</v>
       </c>
       <c r="E728" t="n">
-        <v>73.15000000000001</v>
+        <v>72.88</v>
       </c>
       <c r="F728" t="n">
-        <v>152160</v>
+        <v>154875</v>
       </c>
     </row>
     <row r="729">
@@ -15061,10 +15061,10 @@
         <v>74.72</v>
       </c>
       <c r="E732" t="n">
-        <v>76.63</v>
+        <v>76.52</v>
       </c>
       <c r="F732" t="n">
-        <v>100583</v>
+        <v>102802</v>
       </c>
     </row>
     <row r="733">
@@ -15161,10 +15161,10 @@
         <v>78.33</v>
       </c>
       <c r="E737" t="n">
-        <v>78.97</v>
+        <v>78.86</v>
       </c>
       <c r="F737" t="n">
-        <v>103669</v>
+        <v>105405</v>
       </c>
     </row>
     <row r="738">
@@ -15261,10 +15261,10 @@
         <v>79.36</v>
       </c>
       <c r="E742" t="n">
-        <v>81.65000000000001</v>
+        <v>81.70999999999999</v>
       </c>
       <c r="F742" t="n">
-        <v>185800</v>
+        <v>187943</v>
       </c>
     </row>
     <row r="743">
@@ -15281,10 +15281,10 @@
         <v>81.12</v>
       </c>
       <c r="E743" t="n">
-        <v>81.59999999999999</v>
+        <v>81.48</v>
       </c>
       <c r="F743" t="n">
-        <v>158852</v>
+        <v>160491</v>
       </c>
     </row>
     <row r="744">
@@ -15361,10 +15361,10 @@
         <v>83.34999999999999</v>
       </c>
       <c r="E747" t="n">
-        <v>83.45</v>
+        <v>83.61</v>
       </c>
       <c r="F747" t="n">
-        <v>145171</v>
+        <v>147527</v>
       </c>
     </row>
     <row r="748">
@@ -15375,16 +15375,16 @@
         <v>83.68000000000001</v>
       </c>
       <c r="C748" t="n">
-        <v>85.97</v>
+        <v>85.98999999999999</v>
       </c>
       <c r="D748" t="n">
         <v>83.53</v>
       </c>
       <c r="E748" t="n">
-        <v>85.91</v>
+        <v>85.77</v>
       </c>
       <c r="F748" t="n">
-        <v>171152</v>
+        <v>173518</v>
       </c>
     </row>
     <row r="749">
@@ -15458,13 +15458,13 @@
         <v>88.8</v>
       </c>
       <c r="D752" t="n">
-        <v>86.56999999999999</v>
+        <v>86.38</v>
       </c>
       <c r="E752" t="n">
-        <v>86.7</v>
+        <v>86.58</v>
       </c>
       <c r="F752" t="n">
-        <v>162890</v>
+        <v>169439</v>
       </c>
     </row>
     <row r="753">
@@ -15481,10 +15481,10 @@
         <v>85.02</v>
       </c>
       <c r="E753" t="n">
-        <v>86.98</v>
+        <v>86.92</v>
       </c>
       <c r="F753" t="n">
-        <v>223066</v>
+        <v>225683</v>
       </c>
     </row>
     <row r="754">
@@ -15561,10 +15561,10 @@
         <v>87.7</v>
       </c>
       <c r="E757" t="n">
-        <v>88.40000000000001</v>
+        <v>88.63</v>
       </c>
       <c r="F757" t="n">
-        <v>270152</v>
+        <v>275711</v>
       </c>
     </row>
     <row r="758">
@@ -15581,10 +15581,10 @@
         <v>88</v>
       </c>
       <c r="E758" t="n">
-        <v>88.73</v>
+        <v>88.81999999999999</v>
       </c>
       <c r="F758" t="n">
-        <v>275262</v>
+        <v>278896</v>
       </c>
     </row>
     <row r="759">
@@ -15655,16 +15655,16 @@
         <v>88.63</v>
       </c>
       <c r="C762" t="n">
-        <v>90.73999999999999</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="D762" t="n">
         <v>87.59999999999999</v>
       </c>
       <c r="E762" t="n">
-        <v>90.45999999999999</v>
+        <v>90.51000000000001</v>
       </c>
       <c r="F762" t="n">
-        <v>163057</v>
+        <v>168353</v>
       </c>
     </row>
     <row r="763">
@@ -15681,10 +15681,10 @@
         <v>90.67</v>
       </c>
       <c r="E763" t="n">
-        <v>92.54000000000001</v>
+        <v>92.14</v>
       </c>
       <c r="F763" t="n">
-        <v>177219</v>
+        <v>180147</v>
       </c>
     </row>
     <row r="764">
@@ -15761,10 +15761,10 @@
         <v>90.09999999999999</v>
       </c>
       <c r="E767" t="n">
-        <v>90.66</v>
+        <v>90.54000000000001</v>
       </c>
       <c r="F767" t="n">
-        <v>183590</v>
+        <v>186180</v>
       </c>
     </row>
     <row r="768">
@@ -15781,10 +15781,10 @@
         <v>89.66</v>
       </c>
       <c r="E768" t="n">
-        <v>93.81</v>
+        <v>93.8</v>
       </c>
       <c r="F768" t="n">
-        <v>189880</v>
+        <v>194729</v>
       </c>
     </row>
     <row r="769">
@@ -15861,10 +15861,10 @@
         <v>90.34999999999999</v>
       </c>
       <c r="E772" t="n">
-        <v>91.18000000000001</v>
+        <v>91.16</v>
       </c>
       <c r="F772" t="n">
-        <v>209775</v>
+        <v>212213</v>
       </c>
     </row>
     <row r="773">
@@ -15875,7 +15875,7 @@
         <v>90.76000000000001</v>
       </c>
       <c r="C773" t="n">
-        <v>92.15000000000001</v>
+        <v>92.28</v>
       </c>
       <c r="D773" t="n">
         <v>88.64</v>
@@ -15884,7 +15884,7 @@
         <v>91.81</v>
       </c>
       <c r="F773" t="n">
-        <v>190175</v>
+        <v>194995</v>
       </c>
     </row>
     <row r="774">
@@ -15961,10 +15961,10 @@
         <v>93.94</v>
       </c>
       <c r="E777" t="n">
-        <v>95.61</v>
+        <v>95.41</v>
       </c>
       <c r="F777" t="n">
-        <v>309076</v>
+        <v>313423</v>
       </c>
     </row>
     <row r="778">
@@ -15981,10 +15981,10 @@
         <v>92.55</v>
       </c>
       <c r="E778" t="n">
-        <v>94.69</v>
+        <v>94.23</v>
       </c>
       <c r="F778" t="n">
-        <v>233541</v>
+        <v>237786</v>
       </c>
     </row>
     <row r="779">
@@ -16061,10 +16061,10 @@
         <v>108.17</v>
       </c>
       <c r="E782" t="n">
-        <v>109.72</v>
+        <v>109.27</v>
       </c>
       <c r="F782" t="n">
-        <v>231064</v>
+        <v>233799</v>
       </c>
     </row>
     <row r="783">
@@ -16081,10 +16081,10 @@
         <v>108.47</v>
       </c>
       <c r="E783" t="n">
-        <v>117.14</v>
+        <v>116.7</v>
       </c>
       <c r="F783" t="n">
-        <v>204618</v>
+        <v>210974</v>
       </c>
     </row>
     <row r="784">
@@ -16161,10 +16161,10 @@
         <v>107.05</v>
       </c>
       <c r="E787" t="n">
-        <v>107.97</v>
+        <v>107.11</v>
       </c>
       <c r="F787" t="n">
-        <v>170481</v>
+        <v>173653</v>
       </c>
     </row>
     <row r="788">
@@ -16181,10 +16181,10 @@
         <v>104.96</v>
       </c>
       <c r="E788" t="n">
-        <v>110.51</v>
+        <v>110.14</v>
       </c>
       <c r="F788" t="n">
-        <v>154891</v>
+        <v>157669</v>
       </c>
     </row>
     <row r="789">
@@ -16252,19 +16252,19 @@
         <v>44637</v>
       </c>
       <c r="B792" t="n">
-        <v>96.98</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="C792" t="n">
         <v>105.3</v>
       </c>
       <c r="D792" t="n">
-        <v>96.11</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="E792" t="n">
         <v>104.46</v>
       </c>
       <c r="F792" t="n">
-        <v>176604</v>
+        <v>172578</v>
       </c>
     </row>
     <row r="793">
@@ -16272,7 +16272,7 @@
         <v>44638</v>
       </c>
       <c r="B793" t="n">
-        <v>104.55</v>
+        <v>105.16</v>
       </c>
       <c r="C793" t="n">
         <v>107.23</v>
@@ -16284,7 +16284,7 @@
         <v>105.63</v>
       </c>
       <c r="F793" t="n">
-        <v>158531</v>
+        <v>155067</v>
       </c>
     </row>
     <row r="794">
@@ -16352,7 +16352,7 @@
         <v>44644</v>
       </c>
       <c r="B797" t="n">
-        <v>118.08</v>
+        <v>119.49</v>
       </c>
       <c r="C797" t="n">
         <v>120.04</v>
@@ -16364,7 +16364,7 @@
         <v>114.47</v>
       </c>
       <c r="F797" t="n">
-        <v>215337</v>
+        <v>206598</v>
       </c>
     </row>
     <row r="798">
@@ -16372,7 +16372,7 @@
         <v>44645</v>
       </c>
       <c r="B798" t="n">
-        <v>115.3</v>
+        <v>114.52</v>
       </c>
       <c r="C798" t="n">
         <v>117.69</v>
@@ -16384,7 +16384,7 @@
         <v>115.94</v>
       </c>
       <c r="F798" t="n">
-        <v>195807</v>
+        <v>189095</v>
       </c>
     </row>
     <row r="799">
@@ -16461,10 +16461,10 @@
         <v>103.71</v>
       </c>
       <c r="E802" t="n">
-        <v>104.6</v>
+        <v>104.99</v>
       </c>
       <c r="F802" t="n">
-        <v>217472</v>
+        <v>220967</v>
       </c>
     </row>
     <row r="803">
@@ -16481,10 +16481,10 @@
         <v>101.94</v>
       </c>
       <c r="E803" t="n">
-        <v>104.13</v>
+        <v>103.88</v>
       </c>
       <c r="F803" t="n">
-        <v>179677</v>
+        <v>181758</v>
       </c>
     </row>
     <row r="804">
@@ -16561,10 +16561,10 @@
         <v>98.2</v>
       </c>
       <c r="E807" t="n">
-        <v>100.94</v>
+        <v>100.96</v>
       </c>
       <c r="F807" t="n">
-        <v>183922</v>
+        <v>186163</v>
       </c>
     </row>
     <row r="808">
@@ -16581,10 +16581,10 @@
         <v>99.28</v>
       </c>
       <c r="E808" t="n">
-        <v>102.16</v>
+        <v>101.81</v>
       </c>
       <c r="F808" t="n">
-        <v>159821</v>
+        <v>162819</v>
       </c>
     </row>
     <row r="809">
@@ -16661,10 +16661,10 @@
         <v>106.14</v>
       </c>
       <c r="E812" t="n">
-        <v>110.56</v>
+        <v>110.62</v>
       </c>
       <c r="F812" t="n">
-        <v>156524</v>
+        <v>159785</v>
       </c>
     </row>
     <row r="813">
@@ -16741,10 +16741,10 @@
         <v>106.38</v>
       </c>
       <c r="E816" t="n">
-        <v>107.93</v>
+        <v>108</v>
       </c>
       <c r="F816" t="n">
-        <v>184241</v>
+        <v>188001</v>
       </c>
     </row>
     <row r="817">
@@ -16758,13 +16758,13 @@
         <v>108.41</v>
       </c>
       <c r="D817" t="n">
-        <v>105.44</v>
+        <v>105.05</v>
       </c>
       <c r="E817" t="n">
-        <v>105.6</v>
+        <v>105.7</v>
       </c>
       <c r="F817" t="n">
-        <v>162032</v>
+        <v>165632</v>
       </c>
     </row>
     <row r="818">
@@ -16841,10 +16841,10 @@
         <v>102.74</v>
       </c>
       <c r="E821" t="n">
-        <v>107.25</v>
+        <v>106.8</v>
       </c>
       <c r="F821" t="n">
-        <v>167676</v>
+        <v>170514</v>
       </c>
     </row>
     <row r="822">
@@ -16861,10 +16861,10 @@
         <v>105.92</v>
       </c>
       <c r="E822" t="n">
-        <v>106.38</v>
+        <v>106.06</v>
       </c>
       <c r="F822" t="n">
-        <v>182972</v>
+        <v>186051</v>
       </c>
     </row>
     <row r="823">
@@ -16941,10 +16941,10 @@
         <v>108.66</v>
       </c>
       <c r="E826" t="n">
-        <v>110.3</v>
+        <v>110.4</v>
       </c>
       <c r="F826" t="n">
-        <v>197687</v>
+        <v>201234</v>
       </c>
     </row>
     <row r="827">
@@ -16961,10 +16961,10 @@
         <v>109.21</v>
       </c>
       <c r="E827" t="n">
-        <v>112.44</v>
+        <v>112.22</v>
       </c>
       <c r="F827" t="n">
-        <v>203469</v>
+        <v>207851</v>
       </c>
     </row>
     <row r="828">
@@ -17041,10 +17041,10 @@
         <v>103.97</v>
       </c>
       <c r="E831" t="n">
-        <v>107.38</v>
+        <v>106.86</v>
       </c>
       <c r="F831" t="n">
-        <v>240901</v>
+        <v>243371</v>
       </c>
     </row>
     <row r="832">
@@ -17061,10 +17061,10 @@
         <v>106.88</v>
       </c>
       <c r="E832" t="n">
-        <v>110.4</v>
+        <v>109.76</v>
       </c>
       <c r="F832" t="n">
-        <v>190398</v>
+        <v>193013</v>
       </c>
     </row>
     <row r="833">
@@ -17141,10 +17141,10 @@
         <v>104.22</v>
       </c>
       <c r="E836" t="n">
-        <v>109.59</v>
+        <v>109.5</v>
       </c>
       <c r="F836" t="n">
-        <v>247278</v>
+        <v>250583</v>
       </c>
     </row>
     <row r="837">
@@ -17161,10 +17161,10 @@
         <v>108.65</v>
       </c>
       <c r="E837" t="n">
-        <v>110.87</v>
+        <v>110.3</v>
       </c>
       <c r="F837" t="n">
-        <v>198948</v>
+        <v>202895</v>
       </c>
     </row>
     <row r="838">
@@ -17241,10 +17241,10 @@
         <v>110.83</v>
       </c>
       <c r="E841" t="n">
-        <v>114</v>
+        <v>114.15</v>
       </c>
       <c r="F841" t="n">
-        <v>171535</v>
+        <v>175003</v>
       </c>
     </row>
     <row r="842">
@@ -17261,10 +17261,10 @@
         <v>113.01</v>
       </c>
       <c r="E842" t="n">
-        <v>115.42</v>
+        <v>115.01</v>
       </c>
       <c r="F842" t="n">
-        <v>210750</v>
+        <v>213418</v>
       </c>
     </row>
     <row r="843">
@@ -17335,16 +17335,16 @@
         <v>113.88</v>
       </c>
       <c r="C846" t="n">
-        <v>117.57</v>
+        <v>117.74</v>
       </c>
       <c r="D846" t="n">
         <v>111.85</v>
       </c>
       <c r="E846" t="n">
-        <v>117.26</v>
+        <v>117.31</v>
       </c>
       <c r="F846" t="n">
-        <v>137013</v>
+        <v>138282</v>
       </c>
     </row>
     <row r="847">
@@ -17355,16 +17355,16 @@
         <v>117.37</v>
       </c>
       <c r="C847" t="n">
-        <v>120.57</v>
+        <v>120.6</v>
       </c>
       <c r="D847" t="n">
         <v>115.28</v>
       </c>
       <c r="E847" t="n">
-        <v>120.41</v>
+        <v>120.23</v>
       </c>
       <c r="F847" t="n">
-        <v>90339</v>
+        <v>91626</v>
       </c>
     </row>
     <row r="848">
@@ -17441,10 +17441,10 @@
         <v>121.23</v>
       </c>
       <c r="E851" t="n">
-        <v>121.71</v>
+        <v>121.41</v>
       </c>
       <c r="F851" t="n">
-        <v>174232</v>
+        <v>176648</v>
       </c>
     </row>
     <row r="852">
@@ -17461,10 +17461,10 @@
         <v>118.31</v>
       </c>
       <c r="E852" t="n">
-        <v>120.29</v>
+        <v>120.02</v>
       </c>
       <c r="F852" t="n">
-        <v>190410</v>
+        <v>192334</v>
       </c>
     </row>
     <row r="853">
@@ -17541,10 +17541,10 @@
         <v>113.72</v>
       </c>
       <c r="E856" t="n">
-        <v>117.15</v>
+        <v>116.92</v>
       </c>
       <c r="F856" t="n">
-        <v>228931</v>
+        <v>231324</v>
       </c>
     </row>
     <row r="857">
@@ -17561,10 +17561,10 @@
         <v>109.77</v>
       </c>
       <c r="E857" t="n">
-        <v>111.29</v>
+        <v>111.27</v>
       </c>
       <c r="F857" t="n">
-        <v>233588</v>
+        <v>236868</v>
       </c>
     </row>
     <row r="858">
@@ -17641,10 +17641,10 @@
         <v>105.25</v>
       </c>
       <c r="E861" t="n">
-        <v>106.29</v>
+        <v>106.13</v>
       </c>
       <c r="F861" t="n">
-        <v>233040</v>
+        <v>234952</v>
       </c>
     </row>
     <row r="862">
@@ -17661,10 +17661,10 @@
         <v>105.78</v>
       </c>
       <c r="E862" t="n">
-        <v>109.13</v>
+        <v>108.33</v>
       </c>
       <c r="F862" t="n">
-        <v>202836</v>
+        <v>205227</v>
       </c>
     </row>
     <row r="863">
@@ -17741,10 +17741,10 @@
         <v>107.7</v>
       </c>
       <c r="E866" t="n">
-        <v>108.69</v>
+        <v>108.43</v>
       </c>
       <c r="F866" t="n">
-        <v>208599</v>
+        <v>212070</v>
       </c>
     </row>
     <row r="867">
@@ -17761,10 +17761,10 @@
         <v>107.32</v>
       </c>
       <c r="E867" t="n">
-        <v>110.56</v>
+        <v>110.43</v>
       </c>
       <c r="F867" t="n">
-        <v>209195</v>
+        <v>210630</v>
       </c>
     </row>
     <row r="868">
@@ -17841,10 +17841,10 @@
         <v>97.11</v>
       </c>
       <c r="E871" t="n">
-        <v>102.75</v>
+        <v>102.32</v>
       </c>
       <c r="F871" t="n">
-        <v>221862</v>
+        <v>224620</v>
       </c>
     </row>
     <row r="872">
@@ -17861,10 +17861,10 @@
         <v>102.16</v>
       </c>
       <c r="E872" t="n">
-        <v>105.32</v>
+        <v>105.2</v>
       </c>
       <c r="F872" t="n">
-        <v>235167</v>
+        <v>237030</v>
       </c>
     </row>
     <row r="873">
@@ -17941,10 +17941,10 @@
         <v>92.42</v>
       </c>
       <c r="E876" t="n">
-        <v>97.17</v>
+        <v>97.12</v>
       </c>
       <c r="F876" t="n">
-        <v>215919</v>
+        <v>217836</v>
       </c>
     </row>
     <row r="877">
@@ -17961,10 +17961,10 @@
         <v>95.59</v>
       </c>
       <c r="E877" t="n">
-        <v>98.34999999999999</v>
+        <v>97.98</v>
       </c>
       <c r="F877" t="n">
-        <v>200270</v>
+        <v>203134</v>
       </c>
     </row>
     <row r="878">
@@ -18041,10 +18041,10 @@
         <v>97.86</v>
       </c>
       <c r="E881" t="n">
-        <v>100.04</v>
+        <v>99.93000000000001</v>
       </c>
       <c r="F881" t="n">
-        <v>227231</v>
+        <v>229298</v>
       </c>
     </row>
     <row r="882">
@@ -18061,10 +18061,10 @@
         <v>97.90000000000001</v>
       </c>
       <c r="E882" t="n">
-        <v>98.67</v>
+        <v>98.98999999999999</v>
       </c>
       <c r="F882" t="n">
-        <v>222921</v>
+        <v>226135</v>
       </c>
     </row>
     <row r="883">
@@ -18141,10 +18141,10 @@
         <v>100.74</v>
       </c>
       <c r="E886" t="n">
-        <v>101.93</v>
+        <v>101.99</v>
       </c>
       <c r="F886" t="n">
-        <v>130398</v>
+        <v>132446</v>
       </c>
     </row>
     <row r="887">
@@ -18161,10 +18161,10 @@
         <v>101.27</v>
       </c>
       <c r="E887" t="n">
-        <v>103.21</v>
+        <v>103.1</v>
       </c>
       <c r="F887" t="n">
-        <v>112179</v>
+        <v>113461</v>
       </c>
     </row>
     <row r="888">
@@ -18238,13 +18238,13 @@
         <v>97.17</v>
       </c>
       <c r="D891" t="n">
-        <v>92.73</v>
+        <v>92.5</v>
       </c>
       <c r="E891" t="n">
-        <v>93.38</v>
+        <v>92.52</v>
       </c>
       <c r="F891" t="n">
-        <v>160629</v>
+        <v>162676</v>
       </c>
     </row>
     <row r="892">
@@ -18261,10 +18261,10 @@
         <v>92.15000000000001</v>
       </c>
       <c r="E892" t="n">
-        <v>93.69</v>
+        <v>93.51000000000001</v>
       </c>
       <c r="F892" t="n">
-        <v>155701</v>
+        <v>157322</v>
       </c>
     </row>
     <row r="893">
@@ -18341,10 +18341,10 @@
         <v>96.08</v>
       </c>
       <c r="E896" t="n">
-        <v>98.66</v>
+        <v>98.31</v>
       </c>
       <c r="F896" t="n">
-        <v>139272</v>
+        <v>140818</v>
       </c>
     </row>
     <row r="897">
@@ -18361,10 +18361,10 @@
         <v>96.26000000000001</v>
       </c>
       <c r="E897" t="n">
-        <v>97.3</v>
+        <v>96.89</v>
       </c>
       <c r="F897" t="n">
-        <v>144235</v>
+        <v>145858</v>
       </c>
     </row>
     <row r="898">
@@ -18441,10 +18441,10 @@
         <v>92.55</v>
       </c>
       <c r="E901" t="n">
-        <v>95.93000000000001</v>
+        <v>95.56</v>
       </c>
       <c r="F901" t="n">
-        <v>122235</v>
+        <v>123861</v>
       </c>
     </row>
     <row r="902">
@@ -18461,10 +18461,10 @@
         <v>93.7</v>
       </c>
       <c r="E902" t="n">
-        <v>95.52</v>
+        <v>95.08</v>
       </c>
       <c r="F902" t="n">
-        <v>125387</v>
+        <v>126696</v>
       </c>
     </row>
     <row r="903">
@@ -18541,10 +18541,10 @@
         <v>98.23</v>
       </c>
       <c r="E906" t="n">
-        <v>99.05</v>
+        <v>98.68000000000001</v>
       </c>
       <c r="F906" t="n">
-        <v>114289</v>
+        <v>115830</v>
       </c>
     </row>
     <row r="907">
@@ -18561,10 +18561,10 @@
         <v>96.92</v>
       </c>
       <c r="E907" t="n">
-        <v>98.70999999999999</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="F907" t="n">
-        <v>127109</v>
+        <v>128357</v>
       </c>
     </row>
     <row r="908">
@@ -18641,10 +18641,10 @@
         <v>91.58</v>
       </c>
       <c r="E911" t="n">
-        <v>91.75</v>
+        <v>91.59</v>
       </c>
       <c r="F911" t="n">
-        <v>171383</v>
+        <v>172611</v>
       </c>
     </row>
     <row r="912">
@@ -18661,10 +18661,10 @@
         <v>92.41</v>
       </c>
       <c r="E912" t="n">
-        <v>92.68000000000001</v>
+        <v>92.83</v>
       </c>
       <c r="F912" t="n">
-        <v>162523</v>
+        <v>164349</v>
       </c>
     </row>
     <row r="913">
@@ -18741,10 +18741,10 @@
         <v>86.86</v>
       </c>
       <c r="E916" t="n">
-        <v>88.03</v>
+        <v>87.73999999999999</v>
       </c>
       <c r="F916" t="n">
-        <v>174104</v>
+        <v>175783</v>
       </c>
     </row>
     <row r="917">
@@ -18761,10 +18761,10 @@
         <v>88.09</v>
       </c>
       <c r="E917" t="n">
-        <v>91.90000000000001</v>
+        <v>91.42</v>
       </c>
       <c r="F917" t="n">
-        <v>137562</v>
+        <v>139210</v>
       </c>
     </row>
     <row r="918">
@@ -18841,10 +18841,10 @@
         <v>89.39</v>
       </c>
       <c r="E921" t="n">
-        <v>90.08</v>
+        <v>89.78</v>
       </c>
       <c r="F921" t="n">
-        <v>177670</v>
+        <v>179533</v>
       </c>
     </row>
     <row r="922">
@@ -18861,10 +18861,10 @@
         <v>89.37</v>
       </c>
       <c r="E922" t="n">
-        <v>90.58</v>
+        <v>90.36</v>
       </c>
       <c r="F922" t="n">
-        <v>175462</v>
+        <v>177056</v>
       </c>
     </row>
     <row r="923">
@@ -18941,10 +18941,10 @@
         <v>88.38</v>
       </c>
       <c r="E926" t="n">
-        <v>89.53</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="F926" t="n">
-        <v>167346</v>
+        <v>169282</v>
       </c>
     </row>
     <row r="927">
@@ -18961,10 +18961,10 @@
         <v>84.61</v>
       </c>
       <c r="E927" t="n">
-        <v>85.41</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="F927" t="n">
-        <v>157358</v>
+        <v>159709</v>
       </c>
     </row>
     <row r="928">
@@ -19041,10 +19041,10 @@
         <v>85.98</v>
       </c>
       <c r="E931" t="n">
-        <v>87.20999999999999</v>
+        <v>87.22</v>
       </c>
       <c r="F931" t="n">
-        <v>182346</v>
+        <v>184095</v>
       </c>
     </row>
     <row r="932">
@@ -19061,10 +19061,10 @@
         <v>84.73999999999999</v>
       </c>
       <c r="E932" t="n">
-        <v>85.06999999999999</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="F932" t="n">
-        <v>172540</v>
+        <v>174184</v>
       </c>
     </row>
     <row r="933">
@@ -19141,10 +19141,10 @@
         <v>92.09</v>
       </c>
       <c r="E936" t="n">
-        <v>94.31999999999999</v>
+        <v>94.16</v>
       </c>
       <c r="F936" t="n">
-        <v>134269</v>
+        <v>136157</v>
       </c>
     </row>
     <row r="937">
@@ -19161,10 +19161,10 @@
         <v>93.25</v>
       </c>
       <c r="E937" t="n">
-        <v>96.95</v>
+        <v>97.59</v>
       </c>
       <c r="F937" t="n">
-        <v>158303</v>
+        <v>161145</v>
       </c>
     </row>
     <row r="938">
@@ -19241,10 +19241,10 @@
         <v>90.18000000000001</v>
       </c>
       <c r="E941" t="n">
-        <v>93.61</v>
+        <v>93.67</v>
       </c>
       <c r="F941" t="n">
-        <v>187899</v>
+        <v>189909</v>
       </c>
     </row>
     <row r="942">
@@ -19261,10 +19261,10 @@
         <v>90.34</v>
       </c>
       <c r="E942" t="n">
-        <v>90.84999999999999</v>
+        <v>90.66</v>
       </c>
       <c r="F942" t="n">
-        <v>184164</v>
+        <v>186342</v>
       </c>
     </row>
     <row r="943">
@@ -19341,10 +19341,10 @@
         <v>90.34</v>
       </c>
       <c r="E946" t="n">
-        <v>91</v>
+        <v>91.11</v>
       </c>
       <c r="F946" t="n">
-        <v>169394</v>
+        <v>172151</v>
       </c>
     </row>
     <row r="947">
@@ -19361,10 +19361,10 @@
         <v>89.40000000000001</v>
       </c>
       <c r="E947" t="n">
-        <v>91.7</v>
+        <v>91.58</v>
       </c>
       <c r="F947" t="n">
-        <v>168937</v>
+        <v>170499</v>
       </c>
     </row>
     <row r="948">
@@ -19441,10 +19441,10 @@
         <v>93.06999999999999</v>
       </c>
       <c r="E951" t="n">
-        <v>94.91</v>
+        <v>94.45999999999999</v>
       </c>
       <c r="F951" t="n">
-        <v>130846</v>
+        <v>135151</v>
       </c>
     </row>
     <row r="952">
@@ -19461,10 +19461,10 @@
         <v>92.81999999999999</v>
       </c>
       <c r="E952" t="n">
-        <v>93.81</v>
+        <v>93.95</v>
       </c>
       <c r="F952" t="n">
-        <v>133960</v>
+        <v>135363</v>
       </c>
     </row>
     <row r="953">
@@ -19532,7 +19532,7 @@
         <v>44868</v>
       </c>
       <c r="B956" t="n">
-        <v>94.81</v>
+        <v>94.84</v>
       </c>
       <c r="C956" t="n">
         <v>95.45</v>
@@ -19544,7 +19544,7 @@
         <v>93.92</v>
       </c>
       <c r="F956" t="n">
-        <v>143503</v>
+        <v>141621</v>
       </c>
     </row>
     <row r="957">
@@ -19552,19 +19552,19 @@
         <v>44869</v>
       </c>
       <c r="B957" t="n">
-        <v>93.98</v>
+        <v>93.94</v>
       </c>
       <c r="C957" t="n">
         <v>98.23999999999999</v>
       </c>
       <c r="D957" t="n">
-        <v>93.76000000000001</v>
+        <v>93.94</v>
       </c>
       <c r="E957" t="n">
         <v>98.01000000000001</v>
       </c>
       <c r="F957" t="n">
-        <v>182009</v>
+        <v>179958</v>
       </c>
     </row>
     <row r="958">
@@ -19641,10 +19641,10 @@
         <v>90.97</v>
       </c>
       <c r="E961" t="n">
-        <v>92.69</v>
+        <v>92.47</v>
       </c>
       <c r="F961" t="n">
-        <v>168690</v>
+        <v>170823</v>
       </c>
     </row>
     <row r="962">
@@ -19661,10 +19661,10 @@
         <v>92.79000000000001</v>
       </c>
       <c r="E962" t="n">
-        <v>95.04000000000001</v>
+        <v>94.95999999999999</v>
       </c>
       <c r="F962" t="n">
-        <v>163940</v>
+        <v>165782</v>
       </c>
     </row>
     <row r="963">
@@ -19741,10 +19741,10 @@
         <v>88.72</v>
       </c>
       <c r="E966" t="n">
-        <v>89.28</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="F966" t="n">
-        <v>157265</v>
+        <v>159560</v>
       </c>
     </row>
     <row r="967">
@@ -19761,10 +19761,10 @@
         <v>85.41</v>
       </c>
       <c r="E967" t="n">
-        <v>87.45</v>
+        <v>87.5</v>
       </c>
       <c r="F967" t="n">
-        <v>160818</v>
+        <v>162655</v>
       </c>
     </row>
     <row r="968">
@@ -19941,10 +19941,10 @@
         <v>86.26000000000001</v>
       </c>
       <c r="E976" t="n">
-        <v>86.84</v>
+        <v>86.98</v>
       </c>
       <c r="F976" t="n">
-        <v>135345</v>
+        <v>136930</v>
       </c>
     </row>
     <row r="977">
@@ -19961,10 +19961,10 @@
         <v>85.17</v>
       </c>
       <c r="E977" t="n">
-        <v>85.76000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="F977" t="n">
-        <v>135815</v>
+        <v>137359</v>
       </c>
     </row>
     <row r="978">
@@ -20041,10 +20041,10 @@
         <v>75.92</v>
       </c>
       <c r="E981" t="n">
-        <v>76.27</v>
+        <v>76.61</v>
       </c>
       <c r="F981" t="n">
-        <v>165742</v>
+        <v>167594</v>
       </c>
     </row>
     <row r="982">
@@ -20061,10 +20061,10 @@
         <v>75.34999999999999</v>
       </c>
       <c r="E982" t="n">
-        <v>76.76000000000001</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="F982" t="n">
-        <v>151706</v>
+        <v>153224</v>
       </c>
     </row>
     <row r="983">
@@ -20141,10 +20141,10 @@
         <v>80.86</v>
       </c>
       <c r="E986" t="n">
-        <v>81.39</v>
+        <v>81.54000000000001</v>
       </c>
       <c r="F986" t="n">
-        <v>149384</v>
+        <v>151489</v>
       </c>
     </row>
     <row r="987">
@@ -20161,10 +20161,10 @@
         <v>78.61</v>
       </c>
       <c r="E987" t="n">
-        <v>79.36</v>
+        <v>79.44</v>
       </c>
       <c r="F987" t="n">
-        <v>149990</v>
+        <v>151197</v>
       </c>
     </row>
     <row r="988">
@@ -20241,10 +20241,10 @@
         <v>81.28</v>
       </c>
       <c r="E991" t="n">
-        <v>82.18000000000001</v>
+        <v>82.20999999999999</v>
       </c>
       <c r="F991" t="n">
-        <v>94348</v>
+        <v>95617</v>
       </c>
     </row>
     <row r="992">
@@ -20321,10 +20321,10 @@
         <v>81.81999999999999</v>
       </c>
       <c r="E995" t="n">
-        <v>83.68000000000001</v>
+        <v>83.63</v>
       </c>
       <c r="F995" t="n">
-        <v>109380</v>
+        <v>110699</v>
       </c>
     </row>
     <row r="996">
@@ -20401,10 +20401,10 @@
         <v>77.63</v>
       </c>
       <c r="E999" t="n">
-        <v>78.68000000000001</v>
+        <v>78.8</v>
       </c>
       <c r="F999" t="n">
-        <v>149266</v>
+        <v>150672</v>
       </c>
     </row>
     <row r="1000">
@@ -20424,7 +20424,7 @@
         <v>78.51000000000001</v>
       </c>
       <c r="F1000" t="n">
-        <v>147017</v>
+        <v>148389</v>
       </c>
     </row>
     <row r="1001">
@@ -20501,10 +20501,10 @@
         <v>82.43000000000001</v>
       </c>
       <c r="E1004" t="n">
-        <v>83.91</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="F1004" t="n">
-        <v>141086</v>
+        <v>142735</v>
       </c>
     </row>
     <row r="1005">
@@ -20515,16 +20515,16 @@
         <v>83.91</v>
       </c>
       <c r="C1005" t="n">
-        <v>85.55</v>
+        <v>85.61</v>
       </c>
       <c r="D1005" t="n">
         <v>83.55</v>
       </c>
       <c r="E1005" t="n">
-        <v>85.48</v>
+        <v>85.47</v>
       </c>
       <c r="F1005" t="n">
-        <v>129757</v>
+        <v>131152</v>
       </c>
     </row>
     <row r="1006">
@@ -20601,10 +20601,10 @@
         <v>83.95999999999999</v>
       </c>
       <c r="E1009" t="n">
-        <v>86.31999999999999</v>
+        <v>86.34</v>
       </c>
       <c r="F1009" t="n">
-        <v>142583</v>
+        <v>144410</v>
       </c>
     </row>
     <row r="1010">
@@ -20621,10 +20621,10 @@
         <v>85.69</v>
       </c>
       <c r="E1010" t="n">
-        <v>87.75</v>
+        <v>87.59</v>
       </c>
       <c r="F1010" t="n">
-        <v>123973</v>
+        <v>125225</v>
       </c>
     </row>
     <row r="1011">
@@ -20701,10 +20701,10 @@
         <v>85.75</v>
       </c>
       <c r="E1014" t="n">
-        <v>87.31</v>
+        <v>87.29000000000001</v>
       </c>
       <c r="F1014" t="n">
-        <v>95077</v>
+        <v>96051</v>
       </c>
     </row>
     <row r="1015">
@@ -20721,10 +20721,10 @@
         <v>85.48</v>
       </c>
       <c r="E1015" t="n">
-        <v>86.04000000000001</v>
+        <v>86.01000000000001</v>
       </c>
       <c r="F1015" t="n">
-        <v>109841</v>
+        <v>110922</v>
       </c>
     </row>
     <row r="1016">
@@ -20801,10 +20801,10 @@
         <v>81.2</v>
       </c>
       <c r="E1019" t="n">
-        <v>81.98</v>
+        <v>82.12</v>
       </c>
       <c r="F1019" t="n">
-        <v>146732</v>
+        <v>150704</v>
       </c>
     </row>
     <row r="1020">
@@ -20818,13 +20818,13 @@
         <v>84.11</v>
       </c>
       <c r="D1020" t="n">
+        <v>79.53</v>
+      </c>
+      <c r="E1020" t="n">
         <v>79.62</v>
       </c>
-      <c r="E1020" t="n">
-        <v>79.64</v>
-      </c>
       <c r="F1020" t="n">
-        <v>161681</v>
+        <v>163093</v>
       </c>
     </row>
     <row r="1021">
@@ -20901,10 +20901,10 @@
         <v>82.86</v>
       </c>
       <c r="E1024" t="n">
-        <v>83.88</v>
+        <v>83.95</v>
       </c>
       <c r="F1024" t="n">
-        <v>142722</v>
+        <v>144061</v>
       </c>
     </row>
     <row r="1025">
@@ -20921,10 +20921,10 @@
         <v>83.66</v>
       </c>
       <c r="E1025" t="n">
-        <v>86.29000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="F1025" t="n">
-        <v>155562</v>
+        <v>156718</v>
       </c>
     </row>
     <row r="1026">
@@ -20998,13 +20998,13 @@
         <v>85.90000000000001</v>
       </c>
       <c r="D1029" t="n">
-        <v>84.31999999999999</v>
+        <v>84.28</v>
       </c>
       <c r="E1029" t="n">
-        <v>84.37</v>
+        <v>84.31</v>
       </c>
       <c r="F1029" t="n">
-        <v>128382</v>
+        <v>129946</v>
       </c>
     </row>
     <row r="1030">
@@ -21021,10 +21021,10 @@
         <v>81.55</v>
       </c>
       <c r="E1030" t="n">
-        <v>82.68000000000001</v>
+        <v>82.72</v>
       </c>
       <c r="F1030" t="n">
-        <v>141607</v>
+        <v>142763</v>
       </c>
     </row>
     <row r="1031">
@@ -21101,10 +21101,10 @@
         <v>80.27</v>
       </c>
       <c r="E1034" t="n">
-        <v>82.12</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="F1034" t="n">
-        <v>107083</v>
+        <v>108091</v>
       </c>
     </row>
     <row r="1035">
@@ -21121,10 +21121,10 @@
         <v>80.7</v>
       </c>
       <c r="E1035" t="n">
-        <v>82.94</v>
+        <v>82.77</v>
       </c>
       <c r="F1035" t="n">
-        <v>129354</v>
+        <v>130526</v>
       </c>
     </row>
     <row r="1036">
@@ -21201,10 +21201,10 @@
         <v>83.66</v>
       </c>
       <c r="E1039" t="n">
-        <v>84.34</v>
+        <v>84.23</v>
       </c>
       <c r="F1039" t="n">
-        <v>114302</v>
+        <v>115434</v>
       </c>
     </row>
     <row r="1040">
@@ -21215,16 +21215,16 @@
         <v>84.37</v>
       </c>
       <c r="C1040" t="n">
-        <v>85.8</v>
+        <v>85.81</v>
       </c>
       <c r="D1040" t="n">
         <v>82.2</v>
       </c>
       <c r="E1040" t="n">
-        <v>85.72</v>
+        <v>85.73999999999999</v>
       </c>
       <c r="F1040" t="n">
-        <v>119970</v>
+        <v>120888</v>
       </c>
     </row>
     <row r="1041">
@@ -21301,10 +21301,10 @@
         <v>81.16</v>
       </c>
       <c r="E1044" t="n">
-        <v>81.26000000000001</v>
+        <v>81.23</v>
       </c>
       <c r="F1044" t="n">
-        <v>120126</v>
+        <v>121276</v>
       </c>
     </row>
     <row r="1045">
@@ -21321,10 +21321,10 @@
         <v>80.47</v>
       </c>
       <c r="E1045" t="n">
-        <v>82.33</v>
+        <v>82.38</v>
       </c>
       <c r="F1045" t="n">
-        <v>171433</v>
+        <v>172647</v>
       </c>
     </row>
     <row r="1046">
@@ -21392,7 +21392,7 @@
         <v>45001</v>
       </c>
       <c r="B1049" t="n">
-        <v>74.04000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="C1049" t="n">
         <v>75.23</v>
@@ -21404,7 +21404,7 @@
         <v>74.25</v>
       </c>
       <c r="F1049" t="n">
-        <v>210322</v>
+        <v>206406</v>
       </c>
     </row>
     <row r="1050">
@@ -21412,7 +21412,7 @@
         <v>45002</v>
       </c>
       <c r="B1050" t="n">
-        <v>74.45</v>
+        <v>74.41</v>
       </c>
       <c r="C1050" t="n">
         <v>75.65000000000001</v>
@@ -21424,7 +21424,7 @@
         <v>72.3</v>
       </c>
       <c r="F1050" t="n">
-        <v>196053</v>
+        <v>194486</v>
       </c>
     </row>
     <row r="1051">
@@ -21492,7 +21492,7 @@
         <v>45008</v>
       </c>
       <c r="B1054" t="n">
-        <v>75.58</v>
+        <v>75.73</v>
       </c>
       <c r="C1054" t="n">
         <v>77.09</v>
@@ -21504,7 +21504,7 @@
         <v>74.98999999999999</v>
       </c>
       <c r="F1054" t="n">
-        <v>134971</v>
+        <v>132462</v>
       </c>
     </row>
     <row r="1055">
@@ -21512,7 +21512,7 @@
         <v>45009</v>
       </c>
       <c r="B1055" t="n">
-        <v>75.08</v>
+        <v>74.92</v>
       </c>
       <c r="C1055" t="n">
         <v>75.89</v>
@@ -21524,7 +21524,7 @@
         <v>74.52</v>
       </c>
       <c r="F1055" t="n">
-        <v>160608</v>
+        <v>158419</v>
       </c>
     </row>
     <row r="1056">
@@ -21601,10 +21601,10 @@
         <v>77.13</v>
       </c>
       <c r="E1059" t="n">
-        <v>78.47</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="F1059" t="n">
-        <v>101875</v>
+        <v>102975</v>
       </c>
     </row>
     <row r="1060">
@@ -21621,10 +21621,10 @@
         <v>77.79000000000001</v>
       </c>
       <c r="E1060" t="n">
-        <v>79.73</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="F1060" t="n">
-        <v>102278</v>
+        <v>103341</v>
       </c>
     </row>
     <row r="1061">
@@ -21701,10 +21701,10 @@
         <v>83.89</v>
       </c>
       <c r="E1064" t="n">
-        <v>84.73</v>
+        <v>84.62</v>
       </c>
       <c r="F1064" t="n">
-        <v>127887</v>
+        <v>128978</v>
       </c>
     </row>
     <row r="1065">
@@ -21781,10 +21781,10 @@
         <v>85.78</v>
       </c>
       <c r="E1068" t="n">
-        <v>85.98</v>
+        <v>86.03</v>
       </c>
       <c r="F1068" t="n">
-        <v>106530</v>
+        <v>107747</v>
       </c>
     </row>
     <row r="1069">
@@ -21801,10 +21801,10 @@
         <v>85.27</v>
       </c>
       <c r="E1069" t="n">
-        <v>86.13</v>
+        <v>86.12</v>
       </c>
       <c r="F1069" t="n">
-        <v>118921</v>
+        <v>119789</v>
       </c>
     </row>
     <row r="1070">
@@ -21878,13 +21878,13 @@
         <v>82.59999999999999</v>
       </c>
       <c r="D1073" t="n">
-        <v>80.51000000000001</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="E1073" t="n">
-        <v>80.62</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="F1073" t="n">
-        <v>99083</v>
+        <v>100157</v>
       </c>
     </row>
     <row r="1074">
@@ -21901,10 +21901,10 @@
         <v>80.2</v>
       </c>
       <c r="E1074" t="n">
-        <v>81.38</v>
+        <v>81.53</v>
       </c>
       <c r="F1074" t="n">
-        <v>88877</v>
+        <v>89589</v>
       </c>
     </row>
     <row r="1075">
@@ -21981,10 +21981,10 @@
         <v>77.3</v>
       </c>
       <c r="E1078" t="n">
-        <v>78.23</v>
+        <v>78.17</v>
       </c>
       <c r="F1078" t="n">
-        <v>112919</v>
+        <v>114226</v>
       </c>
     </row>
     <row r="1079">
@@ -22001,10 +22001,10 @@
         <v>77.44</v>
       </c>
       <c r="E1079" t="n">
-        <v>80.20999999999999</v>
+        <v>80.08</v>
       </c>
       <c r="F1079" t="n">
-        <v>110643</v>
+        <v>111593</v>
       </c>
     </row>
     <row r="1080">
@@ -22081,10 +22081,10 @@
         <v>71.34</v>
       </c>
       <c r="E1083" t="n">
-        <v>72.34</v>
+        <v>72.38</v>
       </c>
       <c r="F1083" t="n">
-        <v>175075</v>
+        <v>176458</v>
       </c>
     </row>
     <row r="1084">
@@ -22101,10 +22101,10 @@
         <v>72.31999999999999</v>
       </c>
       <c r="E1084" t="n">
-        <v>75.22</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="F1084" t="n">
-        <v>121559</v>
+        <v>122688</v>
       </c>
     </row>
     <row r="1085">
@@ -22181,10 +22181,10 @@
         <v>74.5</v>
       </c>
       <c r="E1088" t="n">
-        <v>75.34999999999999</v>
+        <v>75.26000000000001</v>
       </c>
       <c r="F1088" t="n">
-        <v>141443</v>
+        <v>142391</v>
       </c>
     </row>
     <row r="1089">
@@ -22201,10 +22201,10 @@
         <v>73.84999999999999</v>
       </c>
       <c r="E1089" t="n">
-        <v>74.02</v>
+        <v>73.93000000000001</v>
       </c>
       <c r="F1089" t="n">
-        <v>143925</v>
+        <v>144762</v>
       </c>
     </row>
     <row r="1090">
@@ -22281,10 +22281,10 @@
         <v>75.42</v>
       </c>
       <c r="E1093" t="n">
-        <v>75.89</v>
+        <v>75.84</v>
       </c>
       <c r="F1093" t="n">
-        <v>97144</v>
+        <v>98116</v>
       </c>
     </row>
     <row r="1094">
@@ -22301,10 +22301,10 @@
         <v>75.01000000000001</v>
       </c>
       <c r="E1094" t="n">
-        <v>75.75</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="F1094" t="n">
-        <v>107224</v>
+        <v>108218</v>
       </c>
     </row>
     <row r="1095">
@@ -22381,10 +22381,10 @@
         <v>75.08</v>
       </c>
       <c r="E1098" t="n">
-        <v>76.13</v>
+        <v>75.95999999999999</v>
       </c>
       <c r="F1098" t="n">
-        <v>94656</v>
+        <v>95663</v>
       </c>
     </row>
     <row r="1099">
@@ -22401,10 +22401,10 @@
         <v>75.62</v>
       </c>
       <c r="E1099" t="n">
-        <v>77.03</v>
+        <v>77.14</v>
       </c>
       <c r="F1099" t="n">
-        <v>85632</v>
+        <v>86227</v>
       </c>
     </row>
     <row r="1100">
@@ -22481,10 +22481,10 @@
         <v>72</v>
       </c>
       <c r="E1103" t="n">
-        <v>74.17</v>
+        <v>74.25</v>
       </c>
       <c r="F1103" t="n">
-        <v>122959</v>
+        <v>124084</v>
       </c>
     </row>
     <row r="1104">
@@ -22501,10 +22501,10 @@
         <v>74.13</v>
       </c>
       <c r="E1104" t="n">
-        <v>76.3</v>
+        <v>76.13</v>
       </c>
       <c r="F1104" t="n">
-        <v>110715</v>
+        <v>111881</v>
       </c>
     </row>
     <row r="1105">
@@ -22581,10 +22581,10 @@
         <v>73.52</v>
       </c>
       <c r="E1108" t="n">
-        <v>75.56999999999999</v>
+        <v>75.44</v>
       </c>
       <c r="F1108" t="n">
-        <v>141391</v>
+        <v>142206</v>
       </c>
     </row>
     <row r="1109">
@@ -22601,10 +22601,10 @@
         <v>74.67</v>
       </c>
       <c r="E1109" t="n">
-        <v>74.84999999999999</v>
+        <v>74.88</v>
       </c>
       <c r="F1109" t="n">
-        <v>120105</v>
+        <v>120995</v>
       </c>
     </row>
     <row r="1110">
@@ -22681,10 +22681,10 @@
         <v>72.84999999999999</v>
       </c>
       <c r="E1113" t="n">
-        <v>75.56</v>
+        <v>75.52</v>
       </c>
       <c r="F1113" t="n">
-        <v>104970</v>
+        <v>105947</v>
       </c>
     </row>
     <row r="1114">
@@ -22701,10 +22701,10 @@
         <v>75.09999999999999</v>
       </c>
       <c r="E1114" t="n">
-        <v>76.47</v>
+        <v>76.23</v>
       </c>
       <c r="F1114" t="n">
-        <v>109963</v>
+        <v>111184</v>
       </c>
     </row>
     <row r="1115">
@@ -22781,10 +22781,10 @@
         <v>73.75</v>
       </c>
       <c r="E1118" t="n">
-        <v>74.2</v>
+        <v>74.3</v>
       </c>
       <c r="F1118" t="n">
-        <v>89166</v>
+        <v>89974</v>
       </c>
     </row>
     <row r="1119">
@@ -22795,16 +22795,16 @@
         <v>74.2</v>
       </c>
       <c r="C1119" t="n">
-        <v>74.36</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="D1119" t="n">
         <v>72.25</v>
       </c>
       <c r="E1119" t="n">
-        <v>74.09</v>
+        <v>74.34</v>
       </c>
       <c r="F1119" t="n">
-        <v>100773</v>
+        <v>101628</v>
       </c>
     </row>
     <row r="1120">
@@ -22881,10 +22881,10 @@
         <v>73.56</v>
       </c>
       <c r="E1123" t="n">
-        <v>74.44</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="F1123" t="n">
-        <v>118096</v>
+        <v>118860</v>
       </c>
     </row>
     <row r="1124">
@@ -22901,10 +22901,10 @@
         <v>74.23</v>
       </c>
       <c r="E1124" t="n">
-        <v>75.26000000000001</v>
+        <v>75.06999999999999</v>
       </c>
       <c r="F1124" t="n">
-        <v>107062</v>
+        <v>108012</v>
       </c>
     </row>
     <row r="1125">
@@ -22981,10 +22981,10 @@
         <v>74.94</v>
       </c>
       <c r="E1128" t="n">
-        <v>76.47</v>
+        <v>76.44</v>
       </c>
       <c r="F1128" t="n">
-        <v>120498</v>
+        <v>121613</v>
       </c>
     </row>
     <row r="1129">
@@ -23001,10 +23001,10 @@
         <v>75.91</v>
       </c>
       <c r="E1129" t="n">
-        <v>78.13</v>
+        <v>78.12</v>
       </c>
       <c r="F1129" t="n">
-        <v>99946</v>
+        <v>101260</v>
       </c>
     </row>
     <row r="1130">
@@ -23075,16 +23075,16 @@
         <v>79.95999999999999</v>
       </c>
       <c r="C1133" t="n">
-        <v>81.48999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="D1133" t="n">
         <v>79.69</v>
       </c>
       <c r="E1133" t="n">
-        <v>81.48</v>
+        <v>81.37</v>
       </c>
       <c r="F1133" t="n">
-        <v>96443</v>
+        <v>97805</v>
       </c>
     </row>
     <row r="1134">
@@ -23098,13 +23098,13 @@
         <v>81.42</v>
       </c>
       <c r="D1134" t="n">
-        <v>79.44</v>
+        <v>79.34999999999999</v>
       </c>
       <c r="E1134" t="n">
-        <v>79.54000000000001</v>
+        <v>79.45</v>
       </c>
       <c r="F1134" t="n">
-        <v>98000</v>
+        <v>99161</v>
       </c>
     </row>
     <row r="1135">
@@ -23181,10 +23181,10 @@
         <v>78.56999999999999</v>
       </c>
       <c r="E1138" t="n">
-        <v>79.54000000000001</v>
+        <v>79.48</v>
       </c>
       <c r="F1138" t="n">
-        <v>76777</v>
+        <v>77506</v>
       </c>
     </row>
     <row r="1139">
@@ -23201,10 +23201,10 @@
         <v>79.51000000000001</v>
       </c>
       <c r="E1139" t="n">
-        <v>80.69</v>
+        <v>80.5</v>
       </c>
       <c r="F1139" t="n">
-        <v>69907</v>
+        <v>70745</v>
       </c>
     </row>
     <row r="1140">
@@ -23281,10 +23281,10 @@
         <v>82.54000000000001</v>
       </c>
       <c r="E1143" t="n">
-        <v>83.42</v>
+        <v>83.3</v>
       </c>
       <c r="F1143" t="n">
-        <v>100960</v>
+        <v>101885</v>
       </c>
     </row>
     <row r="1144">
@@ -23301,10 +23301,10 @@
         <v>82.78</v>
       </c>
       <c r="E1144" t="n">
-        <v>84.26000000000001</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="F1144" t="n">
-        <v>96080</v>
+        <v>96933</v>
       </c>
     </row>
     <row r="1145">
@@ -23381,10 +23381,10 @@
         <v>82.23</v>
       </c>
       <c r="E1148" t="n">
-        <v>85.13</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="F1148" t="n">
-        <v>122532</v>
+        <v>124232</v>
       </c>
     </row>
     <row r="1149">
@@ -23401,10 +23401,10 @@
         <v>84.89</v>
       </c>
       <c r="E1149" t="n">
-        <v>85.84</v>
+        <v>85.81</v>
       </c>
       <c r="F1149" t="n">
-        <v>103319</v>
+        <v>104424</v>
       </c>
     </row>
     <row r="1150">
@@ -23481,10 +23481,10 @@
         <v>85.89</v>
       </c>
       <c r="E1153" t="n">
-        <v>86.09999999999999</v>
+        <v>86.01000000000001</v>
       </c>
       <c r="F1153" t="n">
-        <v>119054</v>
+        <v>120019</v>
       </c>
     </row>
     <row r="1154">
@@ -23501,10 +23501,10 @@
         <v>85.53</v>
       </c>
       <c r="E1154" t="n">
-        <v>86.26000000000001</v>
+        <v>86.16</v>
       </c>
       <c r="F1154" t="n">
-        <v>114400</v>
+        <v>115051</v>
       </c>
     </row>
     <row r="1155">
@@ -23581,10 +23581,10 @@
         <v>82.70999999999999</v>
       </c>
       <c r="E1158" t="n">
-        <v>83.45999999999999</v>
+        <v>83.42</v>
       </c>
       <c r="F1158" t="n">
-        <v>87119</v>
+        <v>88033</v>
       </c>
     </row>
     <row r="1159">
@@ -23601,10 +23601,10 @@
         <v>82.98</v>
       </c>
       <c r="E1159" t="n">
-        <v>84.37</v>
+        <v>84.42</v>
       </c>
       <c r="F1159" t="n">
-        <v>98085</v>
+        <v>98761</v>
       </c>
     </row>
     <row r="1160">
@@ -23681,10 +23681,10 @@
         <v>81.61</v>
       </c>
       <c r="E1163" t="n">
-        <v>82.76000000000001</v>
+        <v>82.67</v>
       </c>
       <c r="F1163" t="n">
-        <v>77118</v>
+        <v>77961</v>
       </c>
     </row>
     <row r="1164">
@@ -23701,10 +23701,10 @@
         <v>82.2</v>
       </c>
       <c r="E1164" t="n">
-        <v>84.14</v>
+        <v>84.05</v>
       </c>
       <c r="F1164" t="n">
-        <v>101382</v>
+        <v>102303</v>
       </c>
     </row>
     <row r="1165">
@@ -23781,10 +23781,10 @@
         <v>84.98</v>
       </c>
       <c r="E1168" t="n">
-        <v>86.63</v>
+        <v>86.66</v>
       </c>
       <c r="F1168" t="n">
-        <v>83934</v>
+        <v>85007</v>
       </c>
     </row>
     <row r="1169">
@@ -23795,16 +23795,16 @@
         <v>86.63</v>
       </c>
       <c r="C1169" t="n">
-        <v>88.66</v>
+        <v>88.75</v>
       </c>
       <c r="D1169" t="n">
         <v>86.59</v>
       </c>
       <c r="E1169" t="n">
-        <v>88.64</v>
+        <v>88.68000000000001</v>
       </c>
       <c r="F1169" t="n">
-        <v>97671</v>
+        <v>98645</v>
       </c>
     </row>
     <row r="1170">
@@ -23881,10 +23881,10 @@
         <v>89.17</v>
       </c>
       <c r="E1173" t="n">
-        <v>89.76000000000001</v>
+        <v>89.47</v>
       </c>
       <c r="F1173" t="n">
-        <v>103067</v>
+        <v>104343</v>
       </c>
     </row>
     <row r="1174">
@@ -23901,10 +23901,10 @@
         <v>88.97</v>
       </c>
       <c r="E1174" t="n">
-        <v>90.2</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="F1174" t="n">
-        <v>100164</v>
+        <v>101197</v>
       </c>
     </row>
     <row r="1175">
@@ -23975,16 +23975,16 @@
         <v>91.56999999999999</v>
       </c>
       <c r="C1178" t="n">
-        <v>93.44</v>
+        <v>93.68000000000001</v>
       </c>
       <c r="D1178" t="n">
         <v>91.55</v>
       </c>
       <c r="E1178" t="n">
-        <v>93.36</v>
+        <v>93.56</v>
       </c>
       <c r="F1178" t="n">
-        <v>89908</v>
+        <v>91727</v>
       </c>
     </row>
     <row r="1179">
@@ -24001,10 +24001,10 @@
         <v>92.14</v>
       </c>
       <c r="E1179" t="n">
-        <v>93.52</v>
+        <v>93.56999999999999</v>
       </c>
       <c r="F1179" t="n">
-        <v>100530</v>
+        <v>101498</v>
       </c>
     </row>
     <row r="1180">
@@ -24081,10 +24081,10 @@
         <v>91.23999999999999</v>
       </c>
       <c r="E1183" t="n">
-        <v>92.27</v>
+        <v>92.20999999999999</v>
       </c>
       <c r="F1183" t="n">
-        <v>97207</v>
+        <v>98137</v>
       </c>
     </row>
     <row r="1184">
@@ -24101,10 +24101,10 @@
         <v>91.68000000000001</v>
       </c>
       <c r="E1184" t="n">
-        <v>92.31</v>
+        <v>92.28</v>
       </c>
       <c r="F1184" t="n">
-        <v>98960</v>
+        <v>99665</v>
       </c>
     </row>
     <row r="1185">
@@ -24181,10 +24181,10 @@
         <v>92.56</v>
       </c>
       <c r="E1188" t="n">
-        <v>92.94</v>
+        <v>92.89</v>
       </c>
       <c r="F1188" t="n">
-        <v>127194</v>
+        <v>128240</v>
       </c>
     </row>
     <row r="1189">
@@ -24201,10 +24201,10 @@
         <v>91.68000000000001</v>
       </c>
       <c r="E1189" t="n">
-        <v>91.95999999999999</v>
+        <v>91.8</v>
       </c>
       <c r="F1189" t="n">
-        <v>116761</v>
+        <v>117877</v>
       </c>
     </row>
     <row r="1190">
@@ -24281,10 +24281,10 @@
         <v>83.31999999999999</v>
       </c>
       <c r="E1193" t="n">
-        <v>83.68000000000001</v>
+        <v>83.72</v>
       </c>
       <c r="F1193" t="n">
-        <v>148426</v>
+        <v>149779</v>
       </c>
     </row>
     <row r="1194">
@@ -24301,10 +24301,10 @@
         <v>82.97</v>
       </c>
       <c r="E1194" t="n">
-        <v>83.88</v>
+        <v>83.79000000000001</v>
       </c>
       <c r="F1194" t="n">
-        <v>138785</v>
+        <v>140020</v>
       </c>
     </row>
     <row r="1195">
@@ -24381,10 +24381,10 @@
         <v>84.59</v>
       </c>
       <c r="E1198" t="n">
-        <v>85.7</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="F1198" t="n">
-        <v>123421</v>
+        <v>124560</v>
       </c>
     </row>
     <row r="1199">
@@ -24404,7 +24404,7 @@
         <v>89.93000000000001</v>
       </c>
       <c r="F1199" t="n">
-        <v>118765</v>
+        <v>120817</v>
       </c>
     </row>
     <row r="1200">
@@ -24475,16 +24475,16 @@
         <v>90.26000000000001</v>
       </c>
       <c r="C1203" t="n">
-        <v>92.22</v>
+        <v>92.34999999999999</v>
       </c>
       <c r="D1203" t="n">
         <v>88.69</v>
       </c>
       <c r="E1203" t="n">
-        <v>92.16</v>
+        <v>92.04000000000001</v>
       </c>
       <c r="F1203" t="n">
-        <v>109002</v>
+        <v>111224</v>
       </c>
     </row>
     <row r="1204">
@@ -24501,10 +24501,10 @@
         <v>90.63</v>
       </c>
       <c r="E1204" t="n">
-        <v>91.13</v>
+        <v>91.26000000000001</v>
       </c>
       <c r="F1204" t="n">
-        <v>109157</v>
+        <v>110661</v>
       </c>
     </row>
     <row r="1205">
@@ -24581,10 +24581,10 @@
         <v>86.48</v>
       </c>
       <c r="E1208" t="n">
-        <v>87.25</v>
+        <v>87.23999999999999</v>
       </c>
       <c r="F1208" t="n">
-        <v>113368</v>
+        <v>114536</v>
       </c>
     </row>
     <row r="1209">
@@ -24601,10 +24601,10 @@
         <v>86.76000000000001</v>
       </c>
       <c r="E1209" t="n">
-        <v>88.76000000000001</v>
+        <v>88.70999999999999</v>
       </c>
       <c r="F1209" t="n">
-        <v>121600</v>
+        <v>123231</v>
       </c>
     </row>
     <row r="1210">
@@ -24672,7 +24672,7 @@
         <v>45232</v>
       </c>
       <c r="B1213" t="n">
-        <v>84.83</v>
+        <v>85.03</v>
       </c>
       <c r="C1213" t="n">
         <v>86.88</v>
@@ -24684,7 +24684,7 @@
         <v>86.63</v>
       </c>
       <c r="F1213" t="n">
-        <v>103842</v>
+        <v>102261</v>
       </c>
     </row>
     <row r="1214">
@@ -24692,7 +24692,7 @@
         <v>45233</v>
       </c>
       <c r="B1214" t="n">
-        <v>86.70999999999999</v>
+        <v>86.66</v>
       </c>
       <c r="C1214" t="n">
         <v>87.58</v>
@@ -24704,7 +24704,7 @@
         <v>84.95</v>
       </c>
       <c r="F1214" t="n">
-        <v>119097</v>
+        <v>117913</v>
       </c>
     </row>
     <row r="1215">
@@ -24781,10 +24781,10 @@
         <v>79.33</v>
       </c>
       <c r="E1218" t="n">
-        <v>79.75</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="F1218" t="n">
-        <v>110739</v>
+        <v>111847</v>
       </c>
     </row>
     <row r="1219">
@@ -24801,10 +24801,10 @@
         <v>79.70999999999999</v>
       </c>
       <c r="E1219" t="n">
-        <v>81.36</v>
+        <v>81.43000000000001</v>
       </c>
       <c r="F1219" t="n">
-        <v>91256</v>
+        <v>92327</v>
       </c>
     </row>
     <row r="1220">
@@ -24881,10 +24881,10 @@
         <v>76.64</v>
       </c>
       <c r="E1223" t="n">
-        <v>77.43000000000001</v>
+        <v>77.45</v>
       </c>
       <c r="F1223" t="n">
-        <v>104766</v>
+        <v>105749</v>
       </c>
     </row>
     <row r="1224">
@@ -24901,10 +24901,10 @@
         <v>77.31</v>
       </c>
       <c r="E1224" t="n">
-        <v>80.37</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="F1224" t="n">
-        <v>88772</v>
+        <v>89648</v>
       </c>
     </row>
     <row r="1225">
@@ -25078,13 +25078,13 @@
         <v>84.51000000000001</v>
       </c>
       <c r="D1233" t="n">
-        <v>79.95</v>
+        <v>79.94</v>
       </c>
       <c r="E1233" t="n">
-        <v>80</v>
+        <v>80.31</v>
       </c>
       <c r="F1233" t="n">
-        <v>143673</v>
+        <v>145419</v>
       </c>
     </row>
     <row r="1234">
@@ -25101,10 +25101,10 @@
         <v>78.69</v>
       </c>
       <c r="E1234" t="n">
-        <v>78.93000000000001</v>
+        <v>79.02</v>
       </c>
       <c r="F1234" t="n">
-        <v>125186</v>
+        <v>126159</v>
       </c>
     </row>
     <row r="1235">
@@ -25181,10 +25181,10 @@
         <v>73.68000000000001</v>
       </c>
       <c r="E1238" t="n">
-        <v>74.47</v>
+        <v>74.39</v>
       </c>
       <c r="F1238" t="n">
-        <v>115986</v>
+        <v>116791</v>
       </c>
     </row>
     <row r="1239">
@@ -25201,10 +25201,10 @@
         <v>74.25</v>
       </c>
       <c r="E1239" t="n">
-        <v>75.87</v>
+        <v>75.94</v>
       </c>
       <c r="F1239" t="n">
-        <v>114085</v>
+        <v>114930</v>
       </c>
     </row>
     <row r="1240">
@@ -25281,10 +25281,10 @@
         <v>74.56999999999999</v>
       </c>
       <c r="E1243" t="n">
-        <v>76.86</v>
+        <v>76.75</v>
       </c>
       <c r="F1243" t="n">
-        <v>83845</v>
+        <v>84712</v>
       </c>
     </row>
     <row r="1244">
@@ -25301,10 +25301,10 @@
         <v>75.48</v>
       </c>
       <c r="E1244" t="n">
-        <v>76.90000000000001</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="F1244" t="n">
-        <v>94162</v>
+        <v>95068</v>
       </c>
     </row>
     <row r="1245">
@@ -25381,10 +25381,10 @@
         <v>77.76000000000001</v>
       </c>
       <c r="E1248" t="n">
-        <v>79.19</v>
+        <v>79.12</v>
       </c>
       <c r="F1248" t="n">
-        <v>91100</v>
+        <v>91755</v>
       </c>
     </row>
     <row r="1249">
@@ -25461,10 +25461,10 @@
         <v>77.04000000000001</v>
       </c>
       <c r="E1252" t="n">
-        <v>77.29000000000001</v>
+        <v>77.36</v>
       </c>
       <c r="F1252" t="n">
-        <v>94380</v>
+        <v>95204</v>
       </c>
     </row>
     <row r="1253">
@@ -25544,7 +25544,7 @@
         <v>77.53</v>
       </c>
       <c r="F1256" t="n">
-        <v>118273</v>
+        <v>119158</v>
       </c>
     </row>
     <row r="1257">
@@ -25641,10 +25641,10 @@
         <v>76.45</v>
       </c>
       <c r="E1261" t="n">
-        <v>77.61</v>
+        <v>78.01000000000001</v>
       </c>
       <c r="F1261" t="n">
-        <v>128067</v>
+        <v>129868</v>
       </c>
     </row>
     <row r="1262">
@@ -25741,10 +25741,10 @@
         <v>76.98</v>
       </c>
       <c r="E1266" t="n">
-        <v>78.63</v>
+        <v>78.56</v>
       </c>
       <c r="F1266" t="n">
-        <v>98609</v>
+        <v>99368</v>
       </c>
     </row>
     <row r="1267">
@@ -25841,10 +25841,10 @@
         <v>79.65000000000001</v>
       </c>
       <c r="E1271" t="n">
-        <v>81.84999999999999</v>
+        <v>81.69</v>
       </c>
       <c r="F1271" t="n">
-        <v>75889</v>
+        <v>76710</v>
       </c>
     </row>
     <row r="1272">
@@ -25861,10 +25861,10 @@
         <v>80.75</v>
       </c>
       <c r="E1272" t="n">
-        <v>83.08</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="F1272" t="n">
-        <v>85666</v>
+        <v>87047</v>
       </c>
     </row>
     <row r="1273">
@@ -25941,10 +25941,10 @@
         <v>78.5</v>
       </c>
       <c r="E1276" t="n">
-        <v>78.64</v>
+        <v>78.7</v>
       </c>
       <c r="F1276" t="n">
-        <v>138682</v>
+        <v>140571</v>
       </c>
     </row>
     <row r="1277">
@@ -25961,10 +25961,10 @@
         <v>76.78</v>
       </c>
       <c r="E1277" t="n">
-        <v>77.11</v>
+        <v>77.31999999999999</v>
       </c>
       <c r="F1277" t="n">
-        <v>132023</v>
+        <v>133396</v>
       </c>
     </row>
     <row r="1278">
@@ -26041,10 +26041,10 @@
         <v>78.84999999999999</v>
       </c>
       <c r="E1281" t="n">
-        <v>81.51000000000001</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="F1281" t="n">
-        <v>86597</v>
+        <v>87658</v>
       </c>
     </row>
     <row r="1282">
@@ -26064,7 +26064,7 @@
         <v>81.63</v>
       </c>
       <c r="F1282" t="n">
-        <v>85346</v>
+        <v>86235</v>
       </c>
     </row>
     <row r="1283">
@@ -26141,10 +26141,10 @@
         <v>80.31999999999999</v>
       </c>
       <c r="E1286" t="n">
-        <v>82.37</v>
+        <v>82.22</v>
       </c>
       <c r="F1286" t="n">
-        <v>83753</v>
+        <v>84560</v>
       </c>
     </row>
     <row r="1287">
@@ -26161,10 +26161,10 @@
         <v>81.34</v>
       </c>
       <c r="E1287" t="n">
-        <v>82.70999999999999</v>
+        <v>82.68000000000001</v>
       </c>
       <c r="F1287" t="n">
-        <v>80620</v>
+        <v>81459</v>
       </c>
     </row>
     <row r="1288">
@@ -26241,10 +26241,10 @@
         <v>81.45</v>
       </c>
       <c r="E1291" t="n">
-        <v>82.63</v>
+        <v>82.51000000000001</v>
       </c>
       <c r="F1291" t="n">
-        <v>67106</v>
+        <v>67848</v>
       </c>
     </row>
     <row r="1292">
@@ -26261,10 +26261,10 @@
         <v>80.65000000000001</v>
       </c>
       <c r="E1292" t="n">
-        <v>80.88</v>
+        <v>80.84</v>
       </c>
       <c r="F1292" t="n">
-        <v>72495</v>
+        <v>73168</v>
       </c>
     </row>
     <row r="1293">
@@ -26341,10 +26341,10 @@
         <v>81.37</v>
       </c>
       <c r="E1296" t="n">
-        <v>81.70999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="F1296" t="n">
-        <v>78801</v>
+        <v>79642</v>
       </c>
     </row>
     <row r="1297">
@@ -26361,10 +26361,10 @@
         <v>81.63</v>
       </c>
       <c r="E1297" t="n">
-        <v>83.19</v>
+        <v>83.12</v>
       </c>
       <c r="F1297" t="n">
-        <v>72423</v>
+        <v>73275</v>
       </c>
     </row>
     <row r="1298">
@@ -26441,10 +26441,10 @@
         <v>81.77</v>
       </c>
       <c r="E1301" t="n">
-        <v>82.52</v>
+        <v>82.87</v>
       </c>
       <c r="F1301" t="n">
-        <v>102278</v>
+        <v>103853</v>
       </c>
     </row>
     <row r="1302">
@@ -26461,10 +26461,10 @@
         <v>81.41</v>
       </c>
       <c r="E1302" t="n">
-        <v>81.66</v>
+        <v>81.55</v>
       </c>
       <c r="F1302" t="n">
-        <v>99175</v>
+        <v>100115</v>
       </c>
     </row>
     <row r="1303">
@@ -26532,19 +26532,19 @@
         <v>45365</v>
       </c>
       <c r="B1306" t="n">
-        <v>83.59999999999999</v>
+        <v>83.69</v>
       </c>
       <c r="C1306" t="n">
         <v>85.18000000000001</v>
       </c>
       <c r="D1306" t="n">
-        <v>83.53</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="E1306" t="n">
         <v>84.61</v>
       </c>
       <c r="F1306" t="n">
-        <v>71844</v>
+        <v>71119</v>
       </c>
     </row>
     <row r="1307">
@@ -26552,7 +26552,7 @@
         <v>45366</v>
       </c>
       <c r="B1307" t="n">
-        <v>84.65000000000001</v>
+        <v>84.68000000000001</v>
       </c>
       <c r="C1307" t="n">
         <v>85.09</v>
@@ -26564,7 +26564,7 @@
         <v>84.83</v>
       </c>
       <c r="F1307" t="n">
-        <v>75864</v>
+        <v>74945</v>
       </c>
     </row>
     <row r="1308">
@@ -26632,7 +26632,7 @@
         <v>45372</v>
       </c>
       <c r="B1311" t="n">
-        <v>85.70999999999999</v>
+        <v>85.81</v>
       </c>
       <c r="C1311" t="n">
         <v>86.03</v>
@@ -26644,7 +26644,7 @@
         <v>84.95999999999999</v>
       </c>
       <c r="F1311" t="n">
-        <v>67186</v>
+        <v>66113</v>
       </c>
     </row>
     <row r="1312">
@@ -26652,7 +26652,7 @@
         <v>45373</v>
       </c>
       <c r="B1312" t="n">
-        <v>85.09999999999999</v>
+        <v>84.98999999999999</v>
       </c>
       <c r="C1312" t="n">
         <v>85.58</v>
@@ -26664,7 +26664,7 @@
         <v>84.93000000000001</v>
       </c>
       <c r="F1312" t="n">
-        <v>54286</v>
+        <v>53666</v>
       </c>
     </row>
     <row r="1313">
@@ -26732,7 +26732,7 @@
         <v>45379</v>
       </c>
       <c r="B1316" t="n">
-        <v>85.56</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="C1316" t="n">
         <v>86.89</v>
@@ -26744,7 +26744,7 @@
         <v>86.67</v>
       </c>
       <c r="F1316" t="n">
-        <v>57372</v>
+        <v>56915</v>
       </c>
     </row>
     <row r="1317">
@@ -26821,10 +26821,10 @@
         <v>88.43000000000001</v>
       </c>
       <c r="E1320" t="n">
-        <v>90.38</v>
+        <v>90.56</v>
       </c>
       <c r="F1320" t="n">
-        <v>74470</v>
+        <v>75666</v>
       </c>
     </row>
     <row r="1321">
@@ -26841,10 +26841,10 @@
         <v>90.18000000000001</v>
       </c>
       <c r="E1321" t="n">
-        <v>90.52</v>
+        <v>90.39</v>
       </c>
       <c r="F1321" t="n">
-        <v>79937</v>
+        <v>80607</v>
       </c>
     </row>
     <row r="1322">
@@ -26921,10 +26921,10 @@
         <v>88.87</v>
       </c>
       <c r="E1325" t="n">
-        <v>89.68000000000001</v>
+        <v>89.55</v>
       </c>
       <c r="F1325" t="n">
-        <v>107040</v>
+        <v>107884</v>
       </c>
     </row>
     <row r="1326">
@@ -26941,10 +26941,10 @@
         <v>89.45</v>
       </c>
       <c r="E1326" t="n">
-        <v>89.73</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="F1326" t="n">
-        <v>108331</v>
+        <v>109120</v>
       </c>
     </row>
     <row r="1327">
@@ -27021,10 +27021,10 @@
         <v>85.63</v>
       </c>
       <c r="E1330" t="n">
-        <v>86.47</v>
+        <v>86.19</v>
       </c>
       <c r="F1330" t="n">
-        <v>107464</v>
+        <v>108132</v>
       </c>
     </row>
     <row r="1331">
@@ -27041,10 +27041,10 @@
         <v>85.61</v>
       </c>
       <c r="E1331" t="n">
-        <v>86.51000000000001</v>
+        <v>86.38</v>
       </c>
       <c r="F1331" t="n">
-        <v>143518</v>
+        <v>144473</v>
       </c>
     </row>
     <row r="1332">
@@ -27115,16 +27115,16 @@
         <v>86.88</v>
       </c>
       <c r="C1335" t="n">
-        <v>87.97</v>
+        <v>88</v>
       </c>
       <c r="D1335" t="n">
         <v>86.2</v>
       </c>
       <c r="E1335" t="n">
-        <v>87.95</v>
+        <v>87.83</v>
       </c>
       <c r="F1335" t="n">
-        <v>69439</v>
+        <v>70059</v>
       </c>
     </row>
     <row r="1336">
@@ -27141,10 +27141,10 @@
         <v>87.56999999999999</v>
       </c>
       <c r="E1336" t="n">
-        <v>87.98999999999999</v>
+        <v>87.89</v>
       </c>
       <c r="F1336" t="n">
-        <v>63936</v>
+        <v>64445</v>
       </c>
     </row>
     <row r="1337">
@@ -27221,10 +27221,10 @@
         <v>82.89</v>
       </c>
       <c r="E1340" t="n">
-        <v>83.47</v>
+        <v>83.48</v>
       </c>
       <c r="F1340" t="n">
-        <v>100961</v>
+        <v>101847</v>
       </c>
     </row>
     <row r="1341">
@@ -27238,13 +27238,13 @@
         <v>84.18000000000001</v>
       </c>
       <c r="D1341" t="n">
-        <v>82.65000000000001</v>
+        <v>82.53</v>
       </c>
       <c r="E1341" t="n">
-        <v>82.77</v>
+        <v>82.54000000000001</v>
       </c>
       <c r="F1341" t="n">
-        <v>82987</v>
+        <v>83584</v>
       </c>
     </row>
     <row r="1342">
@@ -27321,10 +27321,10 @@
         <v>83.18000000000001</v>
       </c>
       <c r="E1345" t="n">
-        <v>83.91</v>
+        <v>83.77</v>
       </c>
       <c r="F1345" t="n">
-        <v>67201</v>
+        <v>67737</v>
       </c>
     </row>
     <row r="1346">
@@ -27338,13 +27338,13 @@
         <v>84.23</v>
       </c>
       <c r="D1346" t="n">
-        <v>82.5</v>
+        <v>82.36</v>
       </c>
       <c r="E1346" t="n">
-        <v>82.61</v>
+        <v>82.36</v>
       </c>
       <c r="F1346" t="n">
-        <v>62356</v>
+        <v>63117</v>
       </c>
     </row>
     <row r="1347">
@@ -27421,10 +27421,10 @@
         <v>82.02</v>
       </c>
       <c r="E1350" t="n">
-        <v>83.04000000000001</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="F1350" t="n">
-        <v>65306</v>
+        <v>65759</v>
       </c>
     </row>
     <row r="1351">
@@ -27441,10 +27441,10 @@
         <v>82.81999999999999</v>
       </c>
       <c r="E1351" t="n">
-        <v>83.68000000000001</v>
+        <v>83.56</v>
       </c>
       <c r="F1351" t="n">
-        <v>60667</v>
+        <v>61133</v>
       </c>
     </row>
     <row r="1352">
@@ -27521,10 +27521,10 @@
         <v>80.7</v>
       </c>
       <c r="E1355" t="n">
-        <v>81.09</v>
+        <v>81.06999999999999</v>
       </c>
       <c r="F1355" t="n">
-        <v>68901</v>
+        <v>69958</v>
       </c>
     </row>
     <row r="1356">
@@ -27541,10 +27541,10 @@
         <v>80.42</v>
       </c>
       <c r="E1356" t="n">
-        <v>81.84999999999999</v>
+        <v>81.79000000000001</v>
       </c>
       <c r="F1356" t="n">
-        <v>56045</v>
+        <v>56381</v>
       </c>
     </row>
     <row r="1357">
@@ -27618,13 +27618,13 @@
         <v>83.51000000000001</v>
       </c>
       <c r="D1360" t="n">
-        <v>81.77</v>
+        <v>81.72</v>
       </c>
       <c r="E1360" t="n">
-        <v>81.88</v>
+        <v>81.73</v>
       </c>
       <c r="F1360" t="n">
-        <v>81262</v>
+        <v>81864</v>
       </c>
     </row>
     <row r="1361">
@@ -27641,10 +27641,10 @@
         <v>80.69</v>
       </c>
       <c r="E1361" t="n">
-        <v>81.22</v>
+        <v>81.09</v>
       </c>
       <c r="F1361" t="n">
-        <v>86335</v>
+        <v>87130</v>
       </c>
     </row>
     <row r="1362">
@@ -27721,10 +27721,10 @@
         <v>78.23999999999999</v>
       </c>
       <c r="E1365" t="n">
-        <v>79.73</v>
+        <v>79.69</v>
       </c>
       <c r="F1365" t="n">
-        <v>72035</v>
+        <v>72677</v>
       </c>
     </row>
     <row r="1366">
@@ -27741,10 +27741,10 @@
         <v>79.18000000000001</v>
       </c>
       <c r="E1366" t="n">
-        <v>79.27</v>
+        <v>79.23999999999999</v>
       </c>
       <c r="F1366" t="n">
-        <v>76576</v>
+        <v>77440</v>
       </c>
     </row>
     <row r="1367">
@@ -27821,10 +27821,10 @@
         <v>81.53</v>
       </c>
       <c r="E1370" t="n">
-        <v>81.98</v>
+        <v>81.68000000000001</v>
       </c>
       <c r="F1370" t="n">
-        <v>78296</v>
+        <v>79567</v>
       </c>
     </row>
     <row r="1371">
@@ -27841,10 +27841,10 @@
         <v>81.64</v>
       </c>
       <c r="E1371" t="n">
-        <v>82.2</v>
+        <v>82.06</v>
       </c>
       <c r="F1371" t="n">
-        <v>75030</v>
+        <v>75768</v>
       </c>
     </row>
     <row r="1372">
@@ -27921,10 +27921,10 @@
         <v>84.28</v>
       </c>
       <c r="E1375" t="n">
-        <v>85.01000000000001</v>
+        <v>84.7</v>
       </c>
       <c r="F1375" t="n">
-        <v>59448</v>
+        <v>59846</v>
       </c>
     </row>
     <row r="1376">
@@ -27941,10 +27941,10 @@
         <v>84</v>
       </c>
       <c r="E1376" t="n">
-        <v>84.31</v>
+        <v>84.16</v>
       </c>
       <c r="F1376" t="n">
-        <v>59797</v>
+        <v>60278</v>
       </c>
     </row>
     <row r="1377">
@@ -28021,10 +28021,10 @@
         <v>84.01000000000001</v>
       </c>
       <c r="E1380" t="n">
-        <v>85.25</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="F1380" t="n">
-        <v>64362</v>
+        <v>64909</v>
       </c>
     </row>
     <row r="1381">
@@ -28041,10 +28041,10 @@
         <v>84.39</v>
       </c>
       <c r="E1381" t="n">
-        <v>84.79000000000001</v>
+        <v>84.65000000000001</v>
       </c>
       <c r="F1381" t="n">
-        <v>69177</v>
+        <v>69862</v>
       </c>
     </row>
     <row r="1382">
@@ -28141,10 +28141,10 @@
         <v>86.17</v>
       </c>
       <c r="E1386" t="n">
-        <v>86.31999999999999</v>
+        <v>86.43000000000001</v>
       </c>
       <c r="F1386" t="n">
-        <v>67919</v>
+        <v>68965</v>
       </c>
     </row>
     <row r="1387">
@@ -28221,10 +28221,10 @@
         <v>84.16</v>
       </c>
       <c r="E1390" t="n">
-        <v>85.19</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="F1390" t="n">
-        <v>78243</v>
+        <v>78990</v>
       </c>
     </row>
     <row r="1391">
@@ -28238,13 +28238,13 @@
         <v>85.67</v>
       </c>
       <c r="D1391" t="n">
-        <v>84.40000000000001</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="E1391" t="n">
-        <v>84.5</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="F1391" t="n">
-        <v>73607</v>
+        <v>74302</v>
       </c>
     </row>
     <row r="1392">
@@ -28321,10 +28321,10 @@
         <v>83.41</v>
       </c>
       <c r="E1395" t="n">
-        <v>83.72</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="F1395" t="n">
-        <v>68620</v>
+        <v>69797</v>
       </c>
     </row>
     <row r="1396">
@@ -28338,13 +28338,13 @@
         <v>84.41</v>
       </c>
       <c r="D1396" t="n">
-        <v>81.7</v>
+        <v>81.64</v>
       </c>
       <c r="E1396" t="n">
-        <v>81.89</v>
+        <v>81.64</v>
       </c>
       <c r="F1396" t="n">
-        <v>72020</v>
+        <v>72736</v>
       </c>
     </row>
     <row r="1397">
@@ -28421,10 +28421,10 @@
         <v>79.28</v>
       </c>
       <c r="E1400" t="n">
-        <v>81.33</v>
+        <v>81.37</v>
       </c>
       <c r="F1400" t="n">
-        <v>69150</v>
+        <v>69789</v>
       </c>
     </row>
     <row r="1401">
@@ -28441,10 +28441,10 @@
         <v>79.39</v>
       </c>
       <c r="E1401" t="n">
-        <v>79.92</v>
+        <v>79.48999999999999</v>
       </c>
       <c r="F1401" t="n">
-        <v>64725</v>
+        <v>65748</v>
       </c>
     </row>
     <row r="1402">
@@ -28521,10 +28521,10 @@
         <v>79.3</v>
       </c>
       <c r="E1405" t="n">
-        <v>80</v>
+        <v>79.83</v>
       </c>
       <c r="F1405" t="n">
-        <v>104482</v>
+        <v>105741</v>
       </c>
     </row>
     <row r="1406">
@@ -28541,10 +28541,10 @@
         <v>76.26000000000001</v>
       </c>
       <c r="E1406" t="n">
-        <v>77.08</v>
+        <v>77.14</v>
       </c>
       <c r="F1406" t="n">
-        <v>124356</v>
+        <v>125792</v>
       </c>
     </row>
     <row r="1407">
@@ -28621,10 +28621,10 @@
         <v>77.33</v>
       </c>
       <c r="E1410" t="n">
-        <v>78.73999999999999</v>
+        <v>78.59</v>
       </c>
       <c r="F1410" t="n">
-        <v>113028</v>
+        <v>113892</v>
       </c>
     </row>
     <row r="1411">
@@ -28641,10 +28641,10 @@
         <v>78.43000000000001</v>
       </c>
       <c r="E1411" t="n">
-        <v>79.34</v>
+        <v>79.27</v>
       </c>
       <c r="F1411" t="n">
-        <v>86405</v>
+        <v>87467</v>
       </c>
     </row>
     <row r="1412">
@@ -28721,10 +28721,10 @@
         <v>79.11</v>
       </c>
       <c r="E1415" t="n">
-        <v>80.31999999999999</v>
+        <v>80.26000000000001</v>
       </c>
       <c r="F1415" t="n">
-        <v>78757</v>
+        <v>79567</v>
       </c>
     </row>
     <row r="1416">
@@ -28741,10 +28741,10 @@
         <v>78.09</v>
       </c>
       <c r="E1416" t="n">
-        <v>79.22</v>
+        <v>78.94</v>
       </c>
       <c r="F1416" t="n">
-        <v>81009</v>
+        <v>82030</v>
       </c>
     </row>
     <row r="1417">
@@ -28821,10 +28821,10 @@
         <v>75.25</v>
       </c>
       <c r="E1420" t="n">
-        <v>76.47</v>
+        <v>76.42</v>
       </c>
       <c r="F1420" t="n">
-        <v>79280</v>
+        <v>79873</v>
       </c>
     </row>
     <row r="1421">
@@ -28841,10 +28841,10 @@
         <v>76.40000000000001</v>
       </c>
       <c r="E1421" t="n">
-        <v>78.17</v>
+        <v>78.13</v>
       </c>
       <c r="F1421" t="n">
-        <v>68613</v>
+        <v>69081</v>
       </c>
     </row>
     <row r="1422">
@@ -28921,10 +28921,10 @@
         <v>76.90000000000001</v>
       </c>
       <c r="E1425" t="n">
-        <v>78.81</v>
+        <v>78.72</v>
       </c>
       <c r="F1425" t="n">
-        <v>93699</v>
+        <v>94397</v>
       </c>
     </row>
     <row r="1426">
@@ -28941,10 +28941,10 @@
         <v>76.56</v>
       </c>
       <c r="E1426" t="n">
-        <v>76.81</v>
+        <v>76.77</v>
       </c>
       <c r="F1426" t="n">
-        <v>108329</v>
+        <v>109124</v>
       </c>
     </row>
     <row r="1427">
@@ -29021,10 +29021,10 @@
         <v>72.20999999999999</v>
       </c>
       <c r="E1430" t="n">
-        <v>72.54000000000001</v>
+        <v>72.53</v>
       </c>
       <c r="F1430" t="n">
-        <v>108713</v>
+        <v>109541</v>
       </c>
     </row>
     <row r="1431">
@@ -29041,10 +29041,10 @@
         <v>70.45</v>
       </c>
       <c r="E1431" t="n">
-        <v>71.37</v>
+        <v>71.2</v>
       </c>
       <c r="F1431" t="n">
-        <v>115759</v>
+        <v>116954</v>
       </c>
     </row>
     <row r="1432">
@@ -29121,10 +29121,10 @@
         <v>70.31999999999999</v>
       </c>
       <c r="E1435" t="n">
-        <v>71.89</v>
+        <v>71.67</v>
       </c>
       <c r="F1435" t="n">
-        <v>114181</v>
+        <v>115156</v>
       </c>
     </row>
     <row r="1436">
@@ -29141,10 +29141,10 @@
         <v>71.09</v>
       </c>
       <c r="E1436" t="n">
-        <v>71.73</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="F1436" t="n">
-        <v>98569</v>
+        <v>99629</v>
       </c>
     </row>
     <row r="1437">
@@ -29221,10 +29221,10 @@
         <v>72.26000000000001</v>
       </c>
       <c r="E1440" t="n">
-        <v>74.05</v>
+        <v>73.97</v>
       </c>
       <c r="F1440" t="n">
-        <v>88395</v>
+        <v>89094</v>
       </c>
     </row>
     <row r="1441">
@@ -29241,10 +29241,10 @@
         <v>73.28</v>
       </c>
       <c r="E1441" t="n">
-        <v>73.98</v>
+        <v>73.87</v>
       </c>
       <c r="F1441" t="n">
-        <v>71635</v>
+        <v>72413</v>
       </c>
     </row>
     <row r="1442">
@@ -29321,10 +29321,10 @@
         <v>70.20999999999999</v>
       </c>
       <c r="E1445" t="n">
-        <v>70.66</v>
+        <v>70.68000000000001</v>
       </c>
       <c r="F1445" t="n">
-        <v>154979</v>
+        <v>155899</v>
       </c>
     </row>
     <row r="1446">
@@ -29335,16 +29335,16 @@
         <v>70.68000000000001</v>
       </c>
       <c r="C1446" t="n">
-        <v>71.89</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="D1446" t="n">
         <v>70.39</v>
       </c>
       <c r="E1446" t="n">
-        <v>71.81999999999999</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="F1446" t="n">
-        <v>122438</v>
+        <v>123787</v>
       </c>
     </row>
     <row r="1447">
@@ -29421,10 +29421,10 @@
         <v>74.18000000000001</v>
       </c>
       <c r="E1450" t="n">
-        <v>77.58</v>
+        <v>77.28</v>
       </c>
       <c r="F1450" t="n">
-        <v>123449</v>
+        <v>125075</v>
       </c>
     </row>
     <row r="1451">
@@ -29441,10 +29441,10 @@
         <v>77.19</v>
       </c>
       <c r="E1451" t="n">
-        <v>77.87</v>
+        <v>77.73</v>
       </c>
       <c r="F1451" t="n">
-        <v>120535</v>
+        <v>121412</v>
       </c>
     </row>
     <row r="1452">
@@ -38764,7 +38764,7 @@
         <v>81.73999999999999</v>
       </c>
       <c r="F1917" t="n">
-        <v>74712</v>
+        <v>74700</v>
       </c>
     </row>
     <row r="1918">
@@ -38772,19 +38772,19 @@
         <v>46232</v>
       </c>
       <c r="B1918" t="n">
-        <v>84.20999999999999</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="C1918" t="n">
         <v>88.36</v>
       </c>
       <c r="D1918" t="n">
-        <v>83.97</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="E1918" t="n">
         <v>87.92</v>
       </c>
       <c r="F1918" t="n">
-        <v>95426</v>
+        <v>95407</v>
       </c>
     </row>
     <row r="1919">
@@ -38804,7 +38804,7 @@
         <v>86.87</v>
       </c>
       <c r="F1919" t="n">
-        <v>118722</v>
+        <v>118707</v>
       </c>
     </row>
     <row r="1920">
@@ -38824,7 +38824,7 @@
         <v>89.69</v>
       </c>
       <c r="F1920" t="n">
-        <v>118405</v>
+        <v>118408</v>
       </c>
     </row>
     <row r="1921">
@@ -38844,7 +38844,7 @@
         <v>82.90000000000001</v>
       </c>
       <c r="F1921" t="n">
-        <v>120569</v>
+        <v>120658</v>
       </c>
     </row>
     <row r="1922">
@@ -38864,7 +38864,27 @@
         <v>78.3</v>
       </c>
       <c r="F1922" t="n">
-        <v>132810</v>
+        <v>132834</v>
+      </c>
+    </row>
+    <row r="1923">
+      <c r="A1923" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B1923" t="n">
+        <v>78.37</v>
+      </c>
+      <c r="C1923" t="n">
+        <v>80.41</v>
+      </c>
+      <c r="D1923" t="n">
+        <v>77.7</v>
+      </c>
+      <c r="E1923" t="n">
+        <v>78.86</v>
+      </c>
+      <c r="F1923" t="n">
+        <v>121224</v>
       </c>
     </row>
   </sheetData>

--- a/database/BRENT.xlsx
+++ b/database/BRENT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1923"/>
+  <dimension ref="A1:F1924"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3881,10 +3881,10 @@
         <v>60.96</v>
       </c>
       <c r="E173" t="n">
-        <v>61.65</v>
+        <v>61.74</v>
       </c>
       <c r="F173" t="n">
-        <v>7745</v>
+        <v>7439</v>
       </c>
     </row>
     <row r="174">
@@ -3952,7 +3952,7 @@
         <v>43769</v>
       </c>
       <c r="B177" t="n">
-        <v>60.27</v>
+        <v>60.17</v>
       </c>
       <c r="C177" t="n">
         <v>60.79</v>
@@ -3964,7 +3964,7 @@
         <v>59.46</v>
       </c>
       <c r="F177" t="n">
-        <v>20603</v>
+        <v>20831</v>
       </c>
     </row>
     <row r="178">
@@ -3972,7 +3972,7 @@
         <v>43770</v>
       </c>
       <c r="B178" t="n">
-        <v>59.64</v>
+        <v>59.42</v>
       </c>
       <c r="C178" t="n">
         <v>61.8</v>
@@ -3984,7 +3984,7 @@
         <v>61.65</v>
       </c>
       <c r="F178" t="n">
-        <v>18281</v>
+        <v>18539</v>
       </c>
     </row>
     <row r="179">
@@ -4061,10 +4061,10 @@
         <v>61.63</v>
       </c>
       <c r="E182" t="n">
-        <v>62.29</v>
+        <v>62.14</v>
       </c>
       <c r="F182" t="n">
-        <v>19680</v>
+        <v>19306</v>
       </c>
     </row>
     <row r="183">
@@ -4081,10 +4081,10 @@
         <v>60.65</v>
       </c>
       <c r="E183" t="n">
-        <v>62.64</v>
+        <v>62.61</v>
       </c>
       <c r="F183" t="n">
-        <v>21863</v>
+        <v>21625</v>
       </c>
     </row>
     <row r="184">
@@ -4161,10 +4161,10 @@
         <v>62.14</v>
       </c>
       <c r="E187" t="n">
-        <v>62.33</v>
+        <v>62.38</v>
       </c>
       <c r="F187" t="n">
-        <v>19293</v>
+        <v>19157</v>
       </c>
     </row>
     <row r="188">
@@ -4181,10 +4181,10 @@
         <v>61.69</v>
       </c>
       <c r="E188" t="n">
-        <v>63.41</v>
+        <v>63.32</v>
       </c>
       <c r="F188" t="n">
-        <v>16092</v>
+        <v>15801</v>
       </c>
     </row>
     <row r="189">
@@ -4261,10 +4261,10 @@
         <v>61.91</v>
       </c>
       <c r="E192" t="n">
-        <v>63.64</v>
+        <v>63.74</v>
       </c>
       <c r="F192" t="n">
-        <v>21823</v>
+        <v>21582</v>
       </c>
     </row>
     <row r="193">
@@ -4281,10 +4281,10 @@
         <v>61.92</v>
       </c>
       <c r="E193" t="n">
-        <v>62.52</v>
+        <v>62.58</v>
       </c>
       <c r="F193" t="n">
-        <v>17794</v>
+        <v>17577</v>
       </c>
     </row>
     <row r="194">
@@ -4461,10 +4461,10 @@
         <v>62.73</v>
       </c>
       <c r="E202" t="n">
-        <v>63.26</v>
+        <v>63.33</v>
       </c>
       <c r="F202" t="n">
-        <v>24300</v>
+        <v>24042</v>
       </c>
     </row>
     <row r="203">
@@ -4481,10 +4481,10 @@
         <v>62.82</v>
       </c>
       <c r="E203" t="n">
-        <v>64.34</v>
+        <v>64.22</v>
       </c>
       <c r="F203" t="n">
-        <v>22572</v>
+        <v>22359</v>
       </c>
     </row>
     <row r="204">
@@ -4561,10 +4561,10 @@
         <v>63.86</v>
       </c>
       <c r="E207" t="n">
-        <v>64.28</v>
+        <v>64.31</v>
       </c>
       <c r="F207" t="n">
-        <v>18454</v>
+        <v>18198</v>
       </c>
     </row>
     <row r="208">
@@ -4581,10 +4581,10 @@
         <v>64.48</v>
       </c>
       <c r="E208" t="n">
-        <v>64.90000000000001</v>
+        <v>64.88</v>
       </c>
       <c r="F208" t="n">
-        <v>21671</v>
+        <v>21484</v>
       </c>
     </row>
     <row r="209">
@@ -4661,10 +4661,10 @@
         <v>66.02</v>
       </c>
       <c r="E212" t="n">
-        <v>66.53</v>
+        <v>66.45</v>
       </c>
       <c r="F212" t="n">
-        <v>11180</v>
+        <v>10932</v>
       </c>
     </row>
     <row r="213">
@@ -4681,10 +4681,10 @@
         <v>65.72</v>
       </c>
       <c r="E213" t="n">
-        <v>66.01000000000001</v>
+        <v>65.98</v>
       </c>
       <c r="F213" t="n">
-        <v>14806</v>
+        <v>14693</v>
       </c>
     </row>
     <row r="214">
@@ -4741,10 +4741,10 @@
         <v>66.09</v>
       </c>
       <c r="E216" t="n">
-        <v>66.75</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="F216" t="n">
-        <v>9613</v>
+        <v>9409</v>
       </c>
     </row>
     <row r="217">
@@ -4761,10 +4761,10 @@
         <v>66.34</v>
       </c>
       <c r="E217" t="n">
-        <v>66.84</v>
+        <v>66.81</v>
       </c>
       <c r="F217" t="n">
-        <v>11398</v>
+        <v>11272</v>
       </c>
     </row>
     <row r="218">
@@ -4821,10 +4821,10 @@
         <v>65.7</v>
       </c>
       <c r="E220" t="n">
-        <v>66.23</v>
+        <v>66.19</v>
       </c>
       <c r="F220" t="n">
-        <v>15351</v>
+        <v>15153</v>
       </c>
     </row>
     <row r="221">
@@ -4841,10 +4841,10 @@
         <v>66.19</v>
       </c>
       <c r="E221" t="n">
-        <v>68.59</v>
+        <v>68.55</v>
       </c>
       <c r="F221" t="n">
-        <v>35609</v>
+        <v>35427</v>
       </c>
     </row>
     <row r="222">
@@ -4924,7 +4924,7 @@
         <v>65.38</v>
       </c>
       <c r="F225" t="n">
-        <v>25951</v>
+        <v>25682</v>
       </c>
     </row>
     <row r="226">
@@ -4944,7 +4944,7 @@
         <v>65</v>
       </c>
       <c r="F226" t="n">
-        <v>20436</v>
+        <v>20016</v>
       </c>
     </row>
     <row r="227">
@@ -5021,10 +5021,10 @@
         <v>63.89</v>
       </c>
       <c r="E230" t="n">
-        <v>64.7</v>
+        <v>64.64</v>
       </c>
       <c r="F230" t="n">
-        <v>16472</v>
+        <v>16107</v>
       </c>
     </row>
     <row r="231">
@@ -5041,10 +5041,10 @@
         <v>64.45</v>
       </c>
       <c r="E231" t="n">
-        <v>65.08</v>
+        <v>64.95</v>
       </c>
       <c r="F231" t="n">
-        <v>16251</v>
+        <v>16060</v>
       </c>
     </row>
     <row r="232">
@@ -5121,10 +5121,10 @@
         <v>61.24</v>
       </c>
       <c r="E235" t="n">
-        <v>62.11</v>
+        <v>61.97</v>
       </c>
       <c r="F235" t="n">
-        <v>23208</v>
+        <v>22982</v>
       </c>
     </row>
     <row r="236">
@@ -5141,10 +5141,10 @@
         <v>60.24</v>
       </c>
       <c r="E236" t="n">
-        <v>60.64</v>
+        <v>60.82</v>
       </c>
       <c r="F236" t="n">
-        <v>21687</v>
+        <v>21411</v>
       </c>
     </row>
     <row r="237">
@@ -5221,10 +5221,10 @@
         <v>56.73</v>
       </c>
       <c r="E240" t="n">
-        <v>58.2</v>
+        <v>58.03</v>
       </c>
       <c r="F240" t="n">
-        <v>28894</v>
+        <v>28317</v>
       </c>
     </row>
     <row r="241">
@@ -5244,7 +5244,7 @@
         <v>56.63</v>
       </c>
       <c r="F241" t="n">
-        <v>31264</v>
+        <v>30854</v>
       </c>
     </row>
     <row r="242">
@@ -5321,10 +5321,10 @@
         <v>54.24</v>
       </c>
       <c r="E245" t="n">
-        <v>55.14</v>
+        <v>55.07</v>
       </c>
       <c r="F245" t="n">
-        <v>31917</v>
+        <v>31638</v>
       </c>
     </row>
     <row r="246">
@@ -5341,10 +5341,10 @@
         <v>54.2</v>
       </c>
       <c r="E246" t="n">
-        <v>54.45</v>
+        <v>54.48</v>
       </c>
       <c r="F246" t="n">
-        <v>26144</v>
+        <v>25828</v>
       </c>
     </row>
     <row r="247">
@@ -5421,10 +5421,10 @@
         <v>54.95</v>
       </c>
       <c r="E250" t="n">
-        <v>56.4</v>
+        <v>56.51</v>
       </c>
       <c r="F250" t="n">
-        <v>24914</v>
+        <v>24675</v>
       </c>
     </row>
     <row r="251">
@@ -5441,10 +5441,10 @@
         <v>56.13</v>
       </c>
       <c r="E251" t="n">
-        <v>57.33</v>
+        <v>57.32</v>
       </c>
       <c r="F251" t="n">
-        <v>21778</v>
+        <v>21410</v>
       </c>
     </row>
     <row r="252">
@@ -5521,10 +5521,10 @@
         <v>58.89</v>
       </c>
       <c r="E255" t="n">
-        <v>59.03</v>
+        <v>59.28</v>
       </c>
       <c r="F255" t="n">
-        <v>23391</v>
+        <v>23121</v>
       </c>
     </row>
     <row r="256">
@@ -5541,10 +5541,10 @@
         <v>57.71</v>
       </c>
       <c r="E256" t="n">
-        <v>58.44</v>
+        <v>58.33</v>
       </c>
       <c r="F256" t="n">
-        <v>26971</v>
+        <v>26663</v>
       </c>
     </row>
     <row r="257">
@@ -5621,10 +5621,10 @@
         <v>50.38</v>
       </c>
       <c r="E260" t="n">
-        <v>50.95</v>
+        <v>51.35</v>
       </c>
       <c r="F260" t="n">
-        <v>52807</v>
+        <v>51199</v>
       </c>
     </row>
     <row r="261">
@@ -5641,10 +5641,10 @@
         <v>48.92</v>
       </c>
       <c r="E261" t="n">
-        <v>50.08</v>
+        <v>50.01</v>
       </c>
       <c r="F261" t="n">
-        <v>72794</v>
+        <v>71739</v>
       </c>
     </row>
     <row r="262">
@@ -5721,10 +5721,10 @@
         <v>49.67</v>
       </c>
       <c r="E265" t="n">
-        <v>50</v>
+        <v>49.95</v>
       </c>
       <c r="F265" t="n">
-        <v>42678</v>
+        <v>42080</v>
       </c>
     </row>
     <row r="266">
@@ -5741,10 +5741,10 @@
         <v>45.16</v>
       </c>
       <c r="E266" t="n">
-        <v>45.51</v>
+        <v>45.55</v>
       </c>
       <c r="F266" t="n">
-        <v>65295</v>
+        <v>64437</v>
       </c>
     </row>
     <row r="267">
@@ -5812,7 +5812,7 @@
         <v>43902</v>
       </c>
       <c r="B270" t="n">
-        <v>36.29</v>
+        <v>35.97</v>
       </c>
       <c r="C270" t="n">
         <v>36.45</v>
@@ -5824,7 +5824,7 @@
         <v>33.49</v>
       </c>
       <c r="F270" t="n">
-        <v>64469</v>
+        <v>66181</v>
       </c>
     </row>
     <row r="271">
@@ -6121,10 +6121,10 @@
         <v>26.12</v>
       </c>
       <c r="E285" t="n">
-        <v>29.96</v>
+        <v>30.29</v>
       </c>
       <c r="F285" t="n">
-        <v>214756</v>
+        <v>210087</v>
       </c>
     </row>
     <row r="286">
@@ -6135,16 +6135,16 @@
         <v>29.95</v>
       </c>
       <c r="C286" t="n">
-        <v>35.28</v>
+        <v>35.24</v>
       </c>
       <c r="D286" t="n">
         <v>28.9</v>
       </c>
       <c r="E286" t="n">
-        <v>35.16</v>
+        <v>34.72</v>
       </c>
       <c r="F286" t="n">
-        <v>280402</v>
+        <v>275171</v>
       </c>
     </row>
     <row r="287">
@@ -6221,10 +6221,10 @@
         <v>32.46</v>
       </c>
       <c r="E290" t="n">
-        <v>32.8</v>
+        <v>33.2</v>
       </c>
       <c r="F290" t="n">
-        <v>236196</v>
+        <v>230614</v>
       </c>
     </row>
     <row r="291">
@@ -6321,10 +6321,10 @@
         <v>29.42</v>
       </c>
       <c r="E295" t="n">
-        <v>30.59</v>
+        <v>30.65</v>
       </c>
       <c r="F295" t="n">
-        <v>151526</v>
+        <v>146842</v>
       </c>
     </row>
     <row r="296">
@@ -6341,10 +6341,10 @@
         <v>30.13</v>
       </c>
       <c r="E296" t="n">
-        <v>30.68</v>
+        <v>30.78</v>
       </c>
       <c r="F296" t="n">
-        <v>174982</v>
+        <v>171223</v>
       </c>
     </row>
     <row r="297">
@@ -6421,10 +6421,10 @@
         <v>23.38</v>
       </c>
       <c r="E300" t="n">
-        <v>24.73</v>
+        <v>24.74</v>
       </c>
       <c r="F300" t="n">
-        <v>216653</v>
+        <v>213310</v>
       </c>
     </row>
     <row r="301">
@@ -6441,10 +6441,10 @@
         <v>23.7</v>
       </c>
       <c r="E301" t="n">
-        <v>24.99</v>
+        <v>24.98</v>
       </c>
       <c r="F301" t="n">
-        <v>166443</v>
+        <v>163124</v>
       </c>
     </row>
     <row r="302">
@@ -6521,10 +6521,10 @@
         <v>24.33</v>
       </c>
       <c r="E305" t="n">
-        <v>26.85</v>
+        <v>26.83</v>
       </c>
       <c r="F305" t="n">
-        <v>229615</v>
+        <v>224455</v>
       </c>
     </row>
     <row r="306">
@@ -6541,10 +6541,10 @@
         <v>26.05</v>
       </c>
       <c r="E306" t="n">
-        <v>26.81</v>
+        <v>26.78</v>
       </c>
       <c r="F306" t="n">
-        <v>199609</v>
+        <v>196748</v>
       </c>
     </row>
     <row r="307">
@@ -6621,10 +6621,10 @@
         <v>29.4</v>
       </c>
       <c r="E310" t="n">
-        <v>29.65</v>
+        <v>29.48</v>
       </c>
       <c r="F310" t="n">
-        <v>229585</v>
+        <v>225301</v>
       </c>
     </row>
     <row r="311">
@@ -6641,10 +6641,10 @@
         <v>29.63</v>
       </c>
       <c r="E311" t="n">
-        <v>31.25</v>
+        <v>31.26</v>
       </c>
       <c r="F311" t="n">
-        <v>195288</v>
+        <v>192233</v>
       </c>
     </row>
     <row r="312">
@@ -6715,16 +6715,16 @@
         <v>29.73</v>
       </c>
       <c r="C315" t="n">
-        <v>31.75</v>
+        <v>31.65</v>
       </c>
       <c r="D315" t="n">
         <v>29.32</v>
       </c>
       <c r="E315" t="n">
-        <v>31.58</v>
+        <v>31.44</v>
       </c>
       <c r="F315" t="n">
-        <v>156389</v>
+        <v>152193</v>
       </c>
     </row>
     <row r="316">
@@ -6735,16 +6735,16 @@
         <v>31.58</v>
       </c>
       <c r="C316" t="n">
-        <v>33.06</v>
+        <v>32.96</v>
       </c>
       <c r="D316" t="n">
         <v>31.23</v>
       </c>
       <c r="E316" t="n">
-        <v>32.94</v>
+        <v>32.9</v>
       </c>
       <c r="F316" t="n">
-        <v>163209</v>
+        <v>160121</v>
       </c>
     </row>
     <row r="317">
@@ -6821,10 +6821,10 @@
         <v>35.92</v>
       </c>
       <c r="E320" t="n">
-        <v>36.3</v>
+        <v>36.38</v>
       </c>
       <c r="F320" t="n">
-        <v>160329</v>
+        <v>157279</v>
       </c>
     </row>
     <row r="321">
@@ -6841,10 +6841,10 @@
         <v>33.87</v>
       </c>
       <c r="E321" t="n">
-        <v>35.52</v>
+        <v>35.66</v>
       </c>
       <c r="F321" t="n">
-        <v>198023</v>
+        <v>194062</v>
       </c>
     </row>
     <row r="322">
@@ -6921,10 +6921,10 @@
         <v>34.37</v>
       </c>
       <c r="E325" t="n">
-        <v>35.98</v>
+        <v>35.89</v>
       </c>
       <c r="F325" t="n">
-        <v>213086</v>
+        <v>208524</v>
       </c>
     </row>
     <row r="326">
@@ -6941,10 +6941,10 @@
         <v>34.87</v>
       </c>
       <c r="E326" t="n">
-        <v>37.61</v>
+        <v>37.43</v>
       </c>
       <c r="F326" t="n">
-        <v>198370</v>
+        <v>193664</v>
       </c>
     </row>
     <row r="327">
@@ -7021,10 +7021,10 @@
         <v>39.05</v>
       </c>
       <c r="E330" t="n">
-        <v>39.92</v>
+        <v>39.78</v>
       </c>
       <c r="F330" t="n">
-        <v>161661</v>
+        <v>158433</v>
       </c>
     </row>
     <row r="331">
@@ -7041,10 +7041,10 @@
         <v>39.75</v>
       </c>
       <c r="E331" t="n">
-        <v>41.83</v>
+        <v>42.14</v>
       </c>
       <c r="F331" t="n">
-        <v>167359</v>
+        <v>163467</v>
       </c>
     </row>
     <row r="332">
@@ -7121,10 +7121,10 @@
         <v>37.96</v>
       </c>
       <c r="E335" t="n">
-        <v>38.41</v>
+        <v>38.36</v>
       </c>
       <c r="F335" t="n">
-        <v>227925</v>
+        <v>221502</v>
       </c>
     </row>
     <row r="336">
@@ -7141,10 +7141,10 @@
         <v>37.14</v>
       </c>
       <c r="E336" t="n">
-        <v>38.97</v>
+        <v>38.94</v>
       </c>
       <c r="F336" t="n">
-        <v>263342</v>
+        <v>260674</v>
       </c>
     </row>
     <row r="337">
@@ -7221,10 +7221,10 @@
         <v>40.05</v>
       </c>
       <c r="E340" t="n">
-        <v>41.33</v>
+        <v>41.37</v>
       </c>
       <c r="F340" t="n">
-        <v>163774</v>
+        <v>161532</v>
       </c>
     </row>
     <row r="341">
@@ -7241,10 +7241,10 @@
         <v>40.97</v>
       </c>
       <c r="E341" t="n">
-        <v>41.78</v>
+        <v>41.99</v>
       </c>
       <c r="F341" t="n">
-        <v>156573</v>
+        <v>153177</v>
       </c>
     </row>
     <row r="342">
@@ -7315,16 +7315,16 @@
         <v>40.45</v>
       </c>
       <c r="C345" t="n">
-        <v>41.59</v>
+        <v>41.51</v>
       </c>
       <c r="D345" t="n">
         <v>39.68</v>
       </c>
       <c r="E345" t="n">
-        <v>41.35</v>
+        <v>41.39</v>
       </c>
       <c r="F345" t="n">
-        <v>181021</v>
+        <v>178413</v>
       </c>
     </row>
     <row r="346">
@@ -7341,10 +7341,10 @@
         <v>40.25</v>
       </c>
       <c r="E346" t="n">
-        <v>40.57</v>
+        <v>40.58</v>
       </c>
       <c r="F346" t="n">
-        <v>160433</v>
+        <v>157969</v>
       </c>
     </row>
     <row r="347">
@@ -7421,10 +7421,10 @@
         <v>41.71</v>
       </c>
       <c r="E350" t="n">
-        <v>42.65</v>
+        <v>42.71</v>
       </c>
       <c r="F350" t="n">
-        <v>144329</v>
+        <v>142409</v>
       </c>
     </row>
     <row r="351">
@@ -7521,10 +7521,10 @@
         <v>41.99</v>
       </c>
       <c r="E355" t="n">
-        <v>42.35</v>
+        <v>42.32</v>
       </c>
       <c r="F355" t="n">
-        <v>136451</v>
+        <v>133908</v>
       </c>
     </row>
     <row r="356">
@@ -7541,10 +7541,10 @@
         <v>41.4</v>
       </c>
       <c r="E356" t="n">
-        <v>43.26</v>
+        <v>43.23</v>
       </c>
       <c r="F356" t="n">
-        <v>154800</v>
+        <v>152491</v>
       </c>
     </row>
     <row r="357">
@@ -7621,10 +7621,10 @@
         <v>43.19</v>
       </c>
       <c r="E360" t="n">
-        <v>43.28</v>
+        <v>43.36</v>
       </c>
       <c r="F360" t="n">
-        <v>101544</v>
+        <v>99613</v>
       </c>
     </row>
     <row r="361">
@@ -7641,10 +7641,10 @@
         <v>42.7</v>
       </c>
       <c r="E361" t="n">
-        <v>43.12</v>
+        <v>43.18</v>
       </c>
       <c r="F361" t="n">
-        <v>95049</v>
+        <v>93740</v>
       </c>
     </row>
     <row r="362">
@@ -7721,10 +7721,10 @@
         <v>43.42</v>
       </c>
       <c r="E365" t="n">
-        <v>43.53</v>
+        <v>43.82</v>
       </c>
       <c r="F365" t="n">
-        <v>112495</v>
+        <v>109900</v>
       </c>
     </row>
     <row r="366">
@@ -7741,10 +7741,10 @@
         <v>43.18</v>
       </c>
       <c r="E366" t="n">
-        <v>43.62</v>
+        <v>43.67</v>
       </c>
       <c r="F366" t="n">
-        <v>117377</v>
+        <v>115737</v>
       </c>
     </row>
     <row r="367">
@@ -7821,10 +7821,10 @@
         <v>41.95</v>
       </c>
       <c r="E370" t="n">
-        <v>43.56</v>
+        <v>43.43</v>
       </c>
       <c r="F370" t="n">
-        <v>117072</v>
+        <v>113377</v>
       </c>
     </row>
     <row r="371">
@@ -7841,10 +7841,10 @@
         <v>42.94</v>
       </c>
       <c r="E371" t="n">
-        <v>43.59</v>
+        <v>43.65</v>
       </c>
       <c r="F371" t="n">
-        <v>128800</v>
+        <v>127155</v>
       </c>
     </row>
     <row r="372">
@@ -7921,10 +7921,10 @@
         <v>44.96</v>
       </c>
       <c r="E375" t="n">
-        <v>45.13</v>
+        <v>45.28</v>
       </c>
       <c r="F375" t="n">
-        <v>122044</v>
+        <v>120720</v>
       </c>
     </row>
     <row r="376">
@@ -7941,10 +7941,10 @@
         <v>44.4</v>
       </c>
       <c r="E376" t="n">
-        <v>44.71</v>
+        <v>44.76</v>
       </c>
       <c r="F376" t="n">
-        <v>120731</v>
+        <v>119541</v>
       </c>
     </row>
     <row r="377">
@@ -8021,10 +8021,10 @@
         <v>45.07</v>
       </c>
       <c r="E380" t="n">
-        <v>45.24</v>
+        <v>45.3</v>
       </c>
       <c r="F380" t="n">
-        <v>91702</v>
+        <v>90204</v>
       </c>
     </row>
     <row r="381">
@@ -8041,10 +8041,10 @@
         <v>44.77</v>
       </c>
       <c r="E381" t="n">
-        <v>45.19</v>
+        <v>45.2</v>
       </c>
       <c r="F381" t="n">
-        <v>85013</v>
+        <v>83793</v>
       </c>
     </row>
     <row r="382">
@@ -8121,10 +8121,10 @@
         <v>44.46</v>
       </c>
       <c r="E385" t="n">
-        <v>45.27</v>
+        <v>45.36</v>
       </c>
       <c r="F385" t="n">
-        <v>87294</v>
+        <v>86301</v>
       </c>
     </row>
     <row r="386">
@@ -8141,10 +8141,10 @@
         <v>44.09</v>
       </c>
       <c r="E386" t="n">
-        <v>44.69</v>
+        <v>44.79</v>
       </c>
       <c r="F386" t="n">
-        <v>78965</v>
+        <v>77659</v>
       </c>
     </row>
     <row r="387">
@@ -8224,7 +8224,7 @@
         <v>45.59</v>
       </c>
       <c r="F390" t="n">
-        <v>96916</v>
+        <v>95873</v>
       </c>
     </row>
     <row r="391">
@@ -8241,10 +8241,10 @@
         <v>45.36</v>
       </c>
       <c r="E391" t="n">
-        <v>45.85</v>
+        <v>45.89</v>
       </c>
       <c r="F391" t="n">
-        <v>81841</v>
+        <v>81058</v>
       </c>
     </row>
     <row r="392">
@@ -8321,10 +8321,10 @@
         <v>43.27</v>
       </c>
       <c r="E395" t="n">
-        <v>44.07</v>
+        <v>44.09</v>
       </c>
       <c r="F395" t="n">
-        <v>158723</v>
+        <v>157249</v>
       </c>
     </row>
     <row r="396">
@@ -8338,13 +8338,13 @@
         <v>44.69</v>
       </c>
       <c r="D396" t="n">
-        <v>42.42</v>
+        <v>42.45</v>
       </c>
       <c r="E396" t="n">
-        <v>42.43</v>
+        <v>42.53</v>
       </c>
       <c r="F396" t="n">
-        <v>162787</v>
+        <v>160902</v>
       </c>
     </row>
     <row r="397">
@@ -8418,13 +8418,13 @@
         <v>41.23</v>
       </c>
       <c r="D400" t="n">
-        <v>39.96</v>
+        <v>40.02</v>
       </c>
       <c r="E400" t="n">
-        <v>39.97</v>
+        <v>40.07</v>
       </c>
       <c r="F400" t="n">
-        <v>149451</v>
+        <v>147551</v>
       </c>
     </row>
     <row r="401">
@@ -8441,10 +8441,10 @@
         <v>39.68</v>
       </c>
       <c r="E401" t="n">
-        <v>40.02</v>
+        <v>40.24</v>
       </c>
       <c r="F401" t="n">
-        <v>135456</v>
+        <v>133943</v>
       </c>
     </row>
     <row r="402">
@@ -8521,10 +8521,10 @@
         <v>41.89</v>
       </c>
       <c r="E405" t="n">
-        <v>43.58</v>
+        <v>43.67</v>
       </c>
       <c r="F405" t="n">
-        <v>142611</v>
+        <v>141089</v>
       </c>
     </row>
     <row r="406">
@@ -8541,10 +8541,10 @@
         <v>42.92</v>
       </c>
       <c r="E406" t="n">
-        <v>43.41</v>
+        <v>43.34</v>
       </c>
       <c r="F406" t="n">
-        <v>129546</v>
+        <v>127380</v>
       </c>
     </row>
     <row r="407">
@@ -8621,10 +8621,10 @@
         <v>41.68</v>
       </c>
       <c r="E410" t="n">
-        <v>42.16</v>
+        <v>42.27</v>
       </c>
       <c r="F410" t="n">
-        <v>133961</v>
+        <v>132502</v>
       </c>
     </row>
     <row r="411">
@@ -8641,10 +8641,10 @@
         <v>41.97</v>
       </c>
       <c r="E411" t="n">
-        <v>42.17</v>
+        <v>42.24</v>
       </c>
       <c r="F411" t="n">
-        <v>102107</v>
+        <v>100264</v>
       </c>
     </row>
     <row r="412">
@@ -8721,10 +8721,10 @@
         <v>39.98</v>
       </c>
       <c r="E415" t="n">
-        <v>40.75</v>
+        <v>40.93</v>
       </c>
       <c r="F415" t="n">
-        <v>157712</v>
+        <v>155461</v>
       </c>
     </row>
     <row r="416">
@@ -8741,10 +8741,10 @@
         <v>38.88</v>
       </c>
       <c r="E416" t="n">
-        <v>39.15</v>
+        <v>39.23</v>
       </c>
       <c r="F416" t="n">
-        <v>190634</v>
+        <v>188336</v>
       </c>
     </row>
     <row r="417">
@@ -8821,10 +8821,10 @@
         <v>42.02</v>
       </c>
       <c r="E420" t="n">
-        <v>43.52</v>
+        <v>43.54</v>
       </c>
       <c r="F420" t="n">
-        <v>112342</v>
+        <v>110782</v>
       </c>
     </row>
     <row r="421">
@@ -8841,10 +8841,10 @@
         <v>42.78</v>
       </c>
       <c r="E421" t="n">
-        <v>42.89</v>
+        <v>42.96</v>
       </c>
       <c r="F421" t="n">
-        <v>109695</v>
+        <v>108274</v>
       </c>
     </row>
     <row r="422">
@@ -8921,10 +8921,10 @@
         <v>41.79</v>
       </c>
       <c r="E425" t="n">
-        <v>43.26</v>
+        <v>43.38</v>
       </c>
       <c r="F425" t="n">
-        <v>147757</v>
+        <v>146298</v>
       </c>
     </row>
     <row r="426">
@@ -8941,10 +8941,10 @@
         <v>42.47</v>
       </c>
       <c r="E426" t="n">
-        <v>42.95</v>
+        <v>43.02</v>
       </c>
       <c r="F426" t="n">
-        <v>130839</v>
+        <v>129338</v>
       </c>
     </row>
     <row r="427">
@@ -9021,10 +9021,10 @@
         <v>41.72</v>
       </c>
       <c r="E430" t="n">
-        <v>42.59</v>
+        <v>42.71</v>
       </c>
       <c r="F430" t="n">
-        <v>110171</v>
+        <v>108471</v>
       </c>
     </row>
     <row r="431">
@@ -9041,10 +9041,10 @@
         <v>41.76</v>
       </c>
       <c r="E431" t="n">
-        <v>41.85</v>
+        <v>41.93</v>
       </c>
       <c r="F431" t="n">
-        <v>97195</v>
+        <v>95688</v>
       </c>
     </row>
     <row r="432">
@@ -9112,7 +9112,7 @@
         <v>44133</v>
       </c>
       <c r="B435" t="n">
-        <v>39.76</v>
+        <v>39.52</v>
       </c>
       <c r="C435" t="n">
         <v>39.97</v>
@@ -9124,7 +9124,7 @@
         <v>38.05</v>
       </c>
       <c r="F435" t="n">
-        <v>179602</v>
+        <v>183949</v>
       </c>
     </row>
     <row r="436">
@@ -9132,7 +9132,7 @@
         <v>44134</v>
       </c>
       <c r="B436" t="n">
-        <v>38.25</v>
+        <v>38.05</v>
       </c>
       <c r="C436" t="n">
         <v>38.72</v>
@@ -9144,7 +9144,7 @@
         <v>37.84</v>
       </c>
       <c r="F436" t="n">
-        <v>181739</v>
+        <v>184633</v>
       </c>
     </row>
     <row r="437">
@@ -9221,10 +9221,10 @@
         <v>40.42</v>
       </c>
       <c r="E440" t="n">
-        <v>40.68</v>
+        <v>40.82</v>
       </c>
       <c r="F440" t="n">
-        <v>157779</v>
+        <v>155706</v>
       </c>
     </row>
     <row r="441">
@@ -9241,10 +9241,10 @@
         <v>39.46</v>
       </c>
       <c r="E441" t="n">
-        <v>39.71</v>
+        <v>39.84</v>
       </c>
       <c r="F441" t="n">
-        <v>151438</v>
+        <v>150078</v>
       </c>
     </row>
     <row r="442">
@@ -9318,13 +9318,13 @@
         <v>44.59</v>
       </c>
       <c r="D445" t="n">
-        <v>43.35</v>
+        <v>43.42</v>
       </c>
       <c r="E445" t="n">
-        <v>43.38</v>
+        <v>43.49</v>
       </c>
       <c r="F445" t="n">
-        <v>146964</v>
+        <v>144322</v>
       </c>
     </row>
     <row r="446">
@@ -9338,13 +9338,13 @@
         <v>43.45</v>
       </c>
       <c r="D446" t="n">
-        <v>42.68</v>
+        <v>42.77</v>
       </c>
       <c r="E446" t="n">
-        <v>42.69</v>
+        <v>42.88</v>
       </c>
       <c r="F446" t="n">
-        <v>114191</v>
+        <v>112789</v>
       </c>
     </row>
     <row r="447">
@@ -9421,10 +9421,10 @@
         <v>43.87</v>
       </c>
       <c r="E450" t="n">
-        <v>44.21</v>
+        <v>44.44</v>
       </c>
       <c r="F450" t="n">
-        <v>112468</v>
+        <v>111013</v>
       </c>
     </row>
     <row r="451">
@@ -9441,10 +9441,10 @@
         <v>44.15</v>
       </c>
       <c r="E451" t="n">
-        <v>45.07</v>
+        <v>45.06</v>
       </c>
       <c r="F451" t="n">
-        <v>90427</v>
+        <v>88612</v>
       </c>
     </row>
     <row r="452">
@@ -9624,7 +9624,7 @@
         <v>48.65</v>
       </c>
       <c r="F460" t="n">
-        <v>122403</v>
+        <v>119976</v>
       </c>
     </row>
     <row r="461">
@@ -9641,10 +9641,10 @@
         <v>48.77</v>
       </c>
       <c r="E461" t="n">
-        <v>48.96</v>
+        <v>48.97</v>
       </c>
       <c r="F461" t="n">
-        <v>125701</v>
+        <v>124413</v>
       </c>
     </row>
     <row r="462">
@@ -9721,10 +9721,10 @@
         <v>48.79</v>
       </c>
       <c r="E465" t="n">
-        <v>50.25</v>
+        <v>50.26</v>
       </c>
       <c r="F465" t="n">
-        <v>132386</v>
+        <v>130125</v>
       </c>
     </row>
     <row r="466">
@@ -9741,10 +9741,10 @@
         <v>49.67</v>
       </c>
       <c r="E466" t="n">
-        <v>49.86</v>
+        <v>49.94</v>
       </c>
       <c r="F466" t="n">
-        <v>124721</v>
+        <v>123293</v>
       </c>
     </row>
     <row r="467">
@@ -9821,10 +9821,10 @@
         <v>51.06</v>
       </c>
       <c r="E470" t="n">
-        <v>51.46</v>
+        <v>51.55</v>
       </c>
       <c r="F470" t="n">
-        <v>102867</v>
+        <v>100894</v>
       </c>
     </row>
     <row r="471">
@@ -9841,10 +9841,10 @@
         <v>51.16</v>
       </c>
       <c r="E471" t="n">
-        <v>52.23</v>
+        <v>52.19</v>
       </c>
       <c r="F471" t="n">
-        <v>98705</v>
+        <v>96861</v>
       </c>
     </row>
     <row r="472">
@@ -10081,10 +10081,10 @@
         <v>53.88</v>
       </c>
       <c r="E483" t="n">
-        <v>54.34</v>
+        <v>54.45</v>
       </c>
       <c r="F483" t="n">
-        <v>142258</v>
+        <v>140683</v>
       </c>
     </row>
     <row r="484">
@@ -10095,16 +10095,16 @@
         <v>54.46</v>
       </c>
       <c r="C484" t="n">
-        <v>56.2</v>
+        <v>56.06</v>
       </c>
       <c r="D484" t="n">
         <v>54.3</v>
       </c>
       <c r="E484" t="n">
-        <v>56.11</v>
+        <v>56.02</v>
       </c>
       <c r="F484" t="n">
-        <v>155413</v>
+        <v>151805</v>
       </c>
     </row>
     <row r="485">
@@ -10181,10 +10181,10 @@
         <v>55.21</v>
       </c>
       <c r="E488" t="n">
-        <v>56.37</v>
+        <v>56.3</v>
       </c>
       <c r="F488" t="n">
-        <v>125098</v>
+        <v>123090</v>
       </c>
     </row>
     <row r="489">
@@ -10201,10 +10201,10 @@
         <v>54.63</v>
       </c>
       <c r="E489" t="n">
-        <v>54.75</v>
+        <v>54.94</v>
       </c>
       <c r="F489" t="n">
-        <v>135898</v>
+        <v>133988</v>
       </c>
     </row>
     <row r="490">
@@ -10281,10 +10281,10 @@
         <v>55.38</v>
       </c>
       <c r="E493" t="n">
-        <v>55.84</v>
+        <v>55.86</v>
       </c>
       <c r="F493" t="n">
-        <v>104851</v>
+        <v>103188</v>
       </c>
     </row>
     <row r="494">
@@ -10301,10 +10301,10 @@
         <v>54.38</v>
       </c>
       <c r="E494" t="n">
-        <v>54.88</v>
+        <v>55.08</v>
       </c>
       <c r="F494" t="n">
-        <v>135622</v>
+        <v>133367</v>
       </c>
     </row>
     <row r="495">
@@ -10378,13 +10378,13 @@
         <v>56.16</v>
       </c>
       <c r="D498" t="n">
-        <v>54.84</v>
+        <v>54.93</v>
       </c>
       <c r="E498" t="n">
-        <v>54.84</v>
+        <v>55</v>
       </c>
       <c r="F498" t="n">
-        <v>162289</v>
+        <v>160473</v>
       </c>
     </row>
     <row r="499">
@@ -10401,10 +10401,10 @@
         <v>54.84</v>
       </c>
       <c r="E499" t="n">
-        <v>54.93</v>
+        <v>55</v>
       </c>
       <c r="F499" t="n">
-        <v>163671</v>
+        <v>160923</v>
       </c>
     </row>
     <row r="500">
@@ -10481,10 +10481,10 @@
         <v>57.93</v>
       </c>
       <c r="E503" t="n">
-        <v>58.87</v>
+        <v>58.79</v>
       </c>
       <c r="F503" t="n">
-        <v>125851</v>
+        <v>123567</v>
       </c>
     </row>
     <row r="504">
@@ -10501,10 +10501,10 @@
         <v>58.87</v>
       </c>
       <c r="E504" t="n">
-        <v>59.41</v>
+        <v>59.31</v>
       </c>
       <c r="F504" t="n">
-        <v>120954</v>
+        <v>118436</v>
       </c>
     </row>
     <row r="505">
@@ -10578,13 +10578,13 @@
         <v>61.23</v>
       </c>
       <c r="D508" t="n">
-        <v>60.44</v>
+        <v>60.5</v>
       </c>
       <c r="E508" t="n">
-        <v>60.52</v>
+        <v>60.6</v>
       </c>
       <c r="F508" t="n">
-        <v>107974</v>
+        <v>104511</v>
       </c>
     </row>
     <row r="509">
@@ -10604,7 +10604,7 @@
         <v>62.22</v>
       </c>
       <c r="F509" t="n">
-        <v>126905</v>
+        <v>123306</v>
       </c>
     </row>
     <row r="510">
@@ -10681,10 +10681,10 @@
         <v>62.54</v>
       </c>
       <c r="E513" t="n">
-        <v>62.88</v>
+        <v>62.75</v>
       </c>
       <c r="F513" t="n">
-        <v>173632</v>
+        <v>170306</v>
       </c>
     </row>
     <row r="514">
@@ -10701,10 +10701,10 @@
         <v>61.42</v>
       </c>
       <c r="E514" t="n">
-        <v>61.97</v>
+        <v>61.95</v>
       </c>
       <c r="F514" t="n">
-        <v>184306</v>
+        <v>181146</v>
       </c>
     </row>
     <row r="515">
@@ -10781,10 +10781,10 @@
         <v>65.55</v>
       </c>
       <c r="E518" t="n">
-        <v>65.97</v>
+        <v>65.86</v>
       </c>
       <c r="F518" t="n">
-        <v>215533</v>
+        <v>210726</v>
       </c>
     </row>
     <row r="519">
@@ -10801,10 +10801,10 @@
         <v>64.13</v>
       </c>
       <c r="E519" t="n">
-        <v>64.27</v>
+        <v>64.25</v>
       </c>
       <c r="F519" t="n">
-        <v>239274</v>
+        <v>234931</v>
       </c>
     </row>
     <row r="520">
@@ -10881,10 +10881,10 @@
         <v>63.17</v>
       </c>
       <c r="E523" t="n">
-        <v>66.73999999999999</v>
+        <v>66.94</v>
       </c>
       <c r="F523" t="n">
-        <v>230530</v>
+        <v>225843</v>
       </c>
     </row>
     <row r="524">
@@ -10895,16 +10895,16 @@
         <v>66.86</v>
       </c>
       <c r="C524" t="n">
-        <v>69.41</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="D524" t="n">
         <v>66.43000000000001</v>
       </c>
       <c r="E524" t="n">
-        <v>69.25</v>
+        <v>69.28</v>
       </c>
       <c r="F524" t="n">
-        <v>253026</v>
+        <v>249828</v>
       </c>
     </row>
     <row r="525">
@@ -10981,10 +10981,10 @@
         <v>67.68000000000001</v>
       </c>
       <c r="E528" t="n">
-        <v>69.17</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="F528" t="n">
-        <v>163581</v>
+        <v>160838</v>
       </c>
     </row>
     <row r="529">
@@ -11001,10 +11001,10 @@
         <v>68.66</v>
       </c>
       <c r="E529" t="n">
-        <v>68.81</v>
+        <v>68.88</v>
       </c>
       <c r="F529" t="n">
-        <v>151042</v>
+        <v>148823</v>
       </c>
     </row>
     <row r="530">
@@ -11072,7 +11072,7 @@
         <v>44273</v>
       </c>
       <c r="B533" t="n">
-        <v>67.47</v>
+        <v>67.48</v>
       </c>
       <c r="C533" t="n">
         <v>67.83</v>
@@ -11084,7 +11084,7 @@
         <v>62.5</v>
       </c>
       <c r="F533" t="n">
-        <v>209835</v>
+        <v>212082</v>
       </c>
     </row>
     <row r="534">
@@ -11092,7 +11092,7 @@
         <v>44274</v>
       </c>
       <c r="B534" t="n">
-        <v>63.02</v>
+        <v>62.78</v>
       </c>
       <c r="C534" t="n">
         <v>64.73</v>
@@ -11104,7 +11104,7 @@
         <v>64.31999999999999</v>
       </c>
       <c r="F534" t="n">
-        <v>223529</v>
+        <v>228148</v>
       </c>
     </row>
     <row r="535">
@@ -11172,10 +11172,10 @@
         <v>44280</v>
       </c>
       <c r="B538" t="n">
-        <v>63.89</v>
+        <v>63.95</v>
       </c>
       <c r="C538" t="n">
-        <v>63.9</v>
+        <v>64.01000000000001</v>
       </c>
       <c r="D538" t="n">
         <v>60.82</v>
@@ -11184,7 +11184,7 @@
         <v>61.47</v>
       </c>
       <c r="F538" t="n">
-        <v>203253</v>
+        <v>206155</v>
       </c>
     </row>
     <row r="539">
@@ -11192,19 +11192,19 @@
         <v>44281</v>
       </c>
       <c r="B539" t="n">
-        <v>62.45</v>
+        <v>61.47</v>
       </c>
       <c r="C539" t="n">
         <v>64.73</v>
       </c>
       <c r="D539" t="n">
-        <v>62.07</v>
+        <v>61.47</v>
       </c>
       <c r="E539" t="n">
         <v>64.19</v>
       </c>
       <c r="F539" t="n">
-        <v>167422</v>
+        <v>171041</v>
       </c>
     </row>
     <row r="540">
@@ -11284,7 +11284,7 @@
         <v>64.51000000000001</v>
       </c>
       <c r="F543" t="n">
-        <v>201289</v>
+        <v>197783</v>
       </c>
     </row>
     <row r="544">
@@ -11361,10 +11361,10 @@
         <v>62.18</v>
       </c>
       <c r="E547" t="n">
-        <v>63.04</v>
+        <v>63.07</v>
       </c>
       <c r="F547" t="n">
-        <v>149186</v>
+        <v>146277</v>
       </c>
     </row>
     <row r="548">
@@ -11381,10 +11381,10 @@
         <v>62.33</v>
       </c>
       <c r="E548" t="n">
-        <v>62.76</v>
+        <v>62.81</v>
       </c>
       <c r="F548" t="n">
-        <v>121247</v>
+        <v>119219</v>
       </c>
     </row>
     <row r="549">
@@ -11461,10 +11461,10 @@
         <v>65.65000000000001</v>
       </c>
       <c r="E552" t="n">
-        <v>66.45</v>
+        <v>66.5</v>
       </c>
       <c r="F552" t="n">
-        <v>135521</v>
+        <v>133306</v>
       </c>
     </row>
     <row r="553">
@@ -11481,10 +11481,10 @@
         <v>66.11</v>
       </c>
       <c r="E553" t="n">
-        <v>66.31999999999999</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="F553" t="n">
-        <v>122938</v>
+        <v>120895</v>
       </c>
     </row>
     <row r="554">
@@ -11564,7 +11564,7 @@
         <v>64.95</v>
       </c>
       <c r="F557" t="n">
-        <v>143350</v>
+        <v>140975</v>
       </c>
     </row>
     <row r="558">
@@ -11581,10 +11581,10 @@
         <v>64.52</v>
       </c>
       <c r="E558" t="n">
-        <v>65.31999999999999</v>
+        <v>65.45</v>
       </c>
       <c r="F558" t="n">
-        <v>126302</v>
+        <v>124432</v>
       </c>
     </row>
     <row r="559">
@@ -11661,10 +11661,10 @@
         <v>66.56</v>
       </c>
       <c r="E562" t="n">
-        <v>67.84999999999999</v>
+        <v>67.86</v>
       </c>
       <c r="F562" t="n">
-        <v>160482</v>
+        <v>157092</v>
       </c>
     </row>
     <row r="563">
@@ -11681,10 +11681,10 @@
         <v>66.17</v>
       </c>
       <c r="E563" t="n">
-        <v>66.53</v>
+        <v>66.56</v>
       </c>
       <c r="F563" t="n">
-        <v>148372</v>
+        <v>145779</v>
       </c>
     </row>
     <row r="564">
@@ -11761,10 +11761,10 @@
         <v>67.77</v>
       </c>
       <c r="E567" t="n">
-        <v>68.03</v>
+        <v>68.05</v>
       </c>
       <c r="F567" t="n">
-        <v>155507</v>
+        <v>153533</v>
       </c>
     </row>
     <row r="568">
@@ -11784,7 +11784,7 @@
         <v>68.03</v>
       </c>
       <c r="F568" t="n">
-        <v>139157</v>
+        <v>136012</v>
       </c>
     </row>
     <row r="569">
@@ -11861,10 +11861,10 @@
         <v>66.34</v>
       </c>
       <c r="E572" t="n">
-        <v>66.81999999999999</v>
+        <v>66.83</v>
       </c>
       <c r="F572" t="n">
-        <v>182316</v>
+        <v>180093</v>
       </c>
     </row>
     <row r="573">
@@ -11875,16 +11875,16 @@
         <v>66.81</v>
       </c>
       <c r="C573" t="n">
-        <v>68.63</v>
+        <v>68.52</v>
       </c>
       <c r="D573" t="n">
         <v>66.36</v>
       </c>
       <c r="E573" t="n">
-        <v>68.52</v>
+        <v>68.45</v>
       </c>
       <c r="F573" t="n">
-        <v>142226</v>
+        <v>139950</v>
       </c>
     </row>
     <row r="574">
@@ -11958,13 +11958,13 @@
         <v>67.02</v>
       </c>
       <c r="D577" t="n">
-        <v>64.70999999999999</v>
+        <v>64.73</v>
       </c>
       <c r="E577" t="n">
-        <v>64.73999999999999</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="F577" t="n">
-        <v>168733</v>
+        <v>164782</v>
       </c>
     </row>
     <row r="578">
@@ -11981,10 +11981,10 @@
         <v>64.48</v>
       </c>
       <c r="E578" t="n">
-        <v>66.51000000000001</v>
+        <v>66.58</v>
       </c>
       <c r="F578" t="n">
-        <v>156317</v>
+        <v>153693</v>
       </c>
     </row>
     <row r="579">
@@ -12055,16 +12055,16 @@
         <v>68.58</v>
       </c>
       <c r="C582" t="n">
-        <v>69.2</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="D582" t="n">
         <v>67.89</v>
       </c>
       <c r="E582" t="n">
-        <v>69.12</v>
+        <v>69.05</v>
       </c>
       <c r="F582" t="n">
-        <v>122427</v>
+        <v>119490</v>
       </c>
     </row>
     <row r="583">
@@ -12081,10 +12081,10 @@
         <v>68.48999999999999</v>
       </c>
       <c r="E583" t="n">
-        <v>68.88</v>
+        <v>68.89</v>
       </c>
       <c r="F583" t="n">
-        <v>121324</v>
+        <v>119218</v>
       </c>
     </row>
     <row r="584">
@@ -12161,10 +12161,10 @@
         <v>70.5</v>
       </c>
       <c r="E587" t="n">
-        <v>71.22</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="F587" t="n">
-        <v>128649</v>
+        <v>126247</v>
       </c>
     </row>
     <row r="588">
@@ -12181,10 +12181,10 @@
         <v>70.58</v>
       </c>
       <c r="E588" t="n">
-        <v>71.43000000000001</v>
+        <v>71.47</v>
       </c>
       <c r="F588" t="n">
-        <v>117041</v>
+        <v>113793</v>
       </c>
     </row>
     <row r="589">
@@ -12261,10 +12261,10 @@
         <v>70.66</v>
       </c>
       <c r="E592" t="n">
-        <v>71.95</v>
+        <v>72.09</v>
       </c>
       <c r="F592" t="n">
-        <v>148450</v>
+        <v>146487</v>
       </c>
     </row>
     <row r="593">
@@ -12284,7 +12284,7 @@
         <v>72.23999999999999</v>
       </c>
       <c r="F593" t="n">
-        <v>142367</v>
+        <v>140128</v>
       </c>
     </row>
     <row r="594">
@@ -12361,10 +12361,10 @@
         <v>71.41</v>
       </c>
       <c r="E597" t="n">
-        <v>72.44</v>
+        <v>72.45</v>
       </c>
       <c r="F597" t="n">
-        <v>178094</v>
+        <v>175025</v>
       </c>
     </row>
     <row r="598">
@@ -12381,10 +12381,10 @@
         <v>71.55</v>
       </c>
       <c r="E598" t="n">
-        <v>72.5</v>
+        <v>72.76000000000001</v>
       </c>
       <c r="F598" t="n">
-        <v>151345</v>
+        <v>147859</v>
       </c>
     </row>
     <row r="599">
@@ -12461,10 +12461,10 @@
         <v>73.83</v>
       </c>
       <c r="E602" t="n">
-        <v>74.81</v>
+        <v>74.79000000000001</v>
       </c>
       <c r="F602" t="n">
-        <v>85692</v>
+        <v>84577</v>
       </c>
     </row>
     <row r="603">
@@ -12481,10 +12481,10 @@
         <v>74.14</v>
       </c>
       <c r="E603" t="n">
-        <v>75.28</v>
+        <v>75.27</v>
       </c>
       <c r="F603" t="n">
-        <v>79112</v>
+        <v>77990</v>
       </c>
     </row>
     <row r="604">
@@ -12561,10 +12561,10 @@
         <v>74.36</v>
       </c>
       <c r="E607" t="n">
-        <v>75.34</v>
+        <v>75.33</v>
       </c>
       <c r="F607" t="n">
-        <v>135699</v>
+        <v>134296</v>
       </c>
     </row>
     <row r="608">
@@ -12581,10 +12581,10 @@
         <v>75</v>
       </c>
       <c r="E608" t="n">
-        <v>75.81999999999999</v>
+        <v>76.02</v>
       </c>
       <c r="F608" t="n">
-        <v>104256</v>
+        <v>102316</v>
       </c>
     </row>
     <row r="609">
@@ -12655,16 +12655,16 @@
         <v>72.97</v>
       </c>
       <c r="C612" t="n">
-        <v>74.02</v>
+        <v>73.97</v>
       </c>
       <c r="D612" t="n">
         <v>71.73999999999999</v>
       </c>
       <c r="E612" t="n">
-        <v>73.95999999999999</v>
+        <v>73.92</v>
       </c>
       <c r="F612" t="n">
-        <v>138030</v>
+        <v>136419</v>
       </c>
     </row>
     <row r="613">
@@ -12681,10 +12681,10 @@
         <v>73.38</v>
       </c>
       <c r="E613" t="n">
-        <v>75.14</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="F613" t="n">
-        <v>96988</v>
+        <v>95892</v>
       </c>
     </row>
     <row r="614">
@@ -12761,10 +12761,10 @@
         <v>72.70999999999999</v>
       </c>
       <c r="E617" t="n">
-        <v>72.72</v>
+        <v>72.79000000000001</v>
       </c>
       <c r="F617" t="n">
-        <v>134216</v>
+        <v>132350</v>
       </c>
     </row>
     <row r="618">
@@ -12781,10 +12781,10 @@
         <v>71.88</v>
       </c>
       <c r="E618" t="n">
-        <v>72.64</v>
+        <v>72.81</v>
       </c>
       <c r="F618" t="n">
-        <v>110158</v>
+        <v>108307</v>
       </c>
     </row>
     <row r="619">
@@ -12864,7 +12864,7 @@
         <v>73.01000000000001</v>
       </c>
       <c r="F622" t="n">
-        <v>115159</v>
+        <v>113951</v>
       </c>
     </row>
     <row r="623">
@@ -12875,16 +12875,16 @@
         <v>72.98</v>
       </c>
       <c r="C623" t="n">
-        <v>73.56999999999999</v>
+        <v>73.52</v>
       </c>
       <c r="D623" t="n">
         <v>72.70999999999999</v>
       </c>
       <c r="E623" t="n">
-        <v>73.5</v>
+        <v>73.44</v>
       </c>
       <c r="F623" t="n">
-        <v>84579</v>
+        <v>83411</v>
       </c>
     </row>
     <row r="624">
@@ -12961,10 +12961,10 @@
         <v>73.59999999999999</v>
       </c>
       <c r="E627" t="n">
-        <v>74.75</v>
+        <v>74.97</v>
       </c>
       <c r="F627" t="n">
-        <v>81467</v>
+        <v>79720</v>
       </c>
     </row>
     <row r="628">
@@ -12981,10 +12981,10 @@
         <v>74.26000000000001</v>
       </c>
       <c r="E628" t="n">
-        <v>74.95999999999999</v>
+        <v>74.98999999999999</v>
       </c>
       <c r="F628" t="n">
-        <v>84253</v>
+        <v>83101</v>
       </c>
     </row>
     <row r="629">
@@ -13061,10 +13061,10 @@
         <v>69.56</v>
       </c>
       <c r="E632" t="n">
-        <v>71</v>
+        <v>71.16</v>
       </c>
       <c r="F632" t="n">
-        <v>108267</v>
+        <v>107034</v>
       </c>
     </row>
     <row r="633">
@@ -13078,13 +13078,13 @@
         <v>72.22</v>
       </c>
       <c r="D633" t="n">
-        <v>70.06999999999999</v>
+        <v>70.12</v>
       </c>
       <c r="E633" t="n">
-        <v>70.08</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="F633" t="n">
-        <v>113105</v>
+        <v>111453</v>
       </c>
     </row>
     <row r="634">
@@ -13161,10 +13161,10 @@
         <v>70.41</v>
       </c>
       <c r="E637" t="n">
-        <v>70.86</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="F637" t="n">
-        <v>96203</v>
+        <v>95219</v>
       </c>
     </row>
     <row r="638">
@@ -13181,10 +13181,10 @@
         <v>69.73999999999999</v>
       </c>
       <c r="E638" t="n">
-        <v>69.90000000000001</v>
+        <v>69.92</v>
       </c>
       <c r="F638" t="n">
-        <v>95696</v>
+        <v>93960</v>
       </c>
     </row>
     <row r="639">
@@ -13261,10 +13261,10 @@
         <v>65.2</v>
       </c>
       <c r="E642" t="n">
-        <v>66.23</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="F642" t="n">
-        <v>187712</v>
+        <v>185678</v>
       </c>
     </row>
     <row r="643">
@@ -13278,13 +13278,13 @@
         <v>66.54000000000001</v>
       </c>
       <c r="D643" t="n">
-        <v>64.53</v>
+        <v>64.61</v>
       </c>
       <c r="E643" t="n">
-        <v>64.54000000000001</v>
+        <v>64.62</v>
       </c>
       <c r="F643" t="n">
-        <v>138989</v>
+        <v>137258</v>
       </c>
     </row>
     <row r="644">
@@ -13361,10 +13361,10 @@
         <v>69.73999999999999</v>
       </c>
       <c r="E647" t="n">
-        <v>70.45999999999999</v>
+        <v>70.56</v>
       </c>
       <c r="F647" t="n">
-        <v>115965</v>
+        <v>113839</v>
       </c>
     </row>
     <row r="648">
@@ -13381,10 +13381,10 @@
         <v>70.16</v>
       </c>
       <c r="E648" t="n">
-        <v>71.5</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="F648" t="n">
-        <v>100455</v>
+        <v>99158</v>
       </c>
     </row>
     <row r="649">
@@ -13461,10 +13461,10 @@
         <v>70.75</v>
       </c>
       <c r="E652" t="n">
-        <v>72.61</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="F652" t="n">
-        <v>105073</v>
+        <v>103772</v>
       </c>
     </row>
     <row r="653">
@@ -13481,10 +13481,10 @@
         <v>72.20999999999999</v>
       </c>
       <c r="E653" t="n">
-        <v>72.20999999999999</v>
+        <v>72.36</v>
       </c>
       <c r="F653" t="n">
-        <v>111688</v>
+        <v>110684</v>
       </c>
     </row>
     <row r="654">
@@ -13561,10 +13561,10 @@
         <v>70.54000000000001</v>
       </c>
       <c r="E657" t="n">
-        <v>70.84</v>
+        <v>70.95</v>
       </c>
       <c r="F657" t="n">
-        <v>138553</v>
+        <v>136836</v>
       </c>
     </row>
     <row r="658">
@@ -13581,10 +13581,10 @@
         <v>70.59</v>
       </c>
       <c r="E658" t="n">
-        <v>72.51000000000001</v>
+        <v>72.44</v>
       </c>
       <c r="F658" t="n">
-        <v>107925</v>
+        <v>106315</v>
       </c>
     </row>
     <row r="659">
@@ -13661,10 +13661,10 @@
         <v>74.02</v>
       </c>
       <c r="E662" t="n">
-        <v>75.09</v>
+        <v>75.17</v>
       </c>
       <c r="F662" t="n">
-        <v>136265</v>
+        <v>134873</v>
       </c>
     </row>
     <row r="663">
@@ -13681,10 +13681,10 @@
         <v>74.06999999999999</v>
       </c>
       <c r="E663" t="n">
-        <v>74.67</v>
+        <v>74.79000000000001</v>
       </c>
       <c r="F663" t="n">
-        <v>131243</v>
+        <v>129577</v>
       </c>
     </row>
     <row r="664">
@@ -13764,7 +13764,7 @@
         <v>76.45</v>
       </c>
       <c r="F667" t="n">
-        <v>104066</v>
+        <v>102612</v>
       </c>
     </row>
     <row r="668">
@@ -13781,10 +13781,10 @@
         <v>76.09</v>
       </c>
       <c r="E668" t="n">
-        <v>77.13</v>
+        <v>77.15000000000001</v>
       </c>
       <c r="F668" t="n">
-        <v>94529</v>
+        <v>93448</v>
       </c>
     </row>
     <row r="669">
@@ -13861,10 +13861,10 @@
         <v>76.37</v>
       </c>
       <c r="E672" t="n">
-        <v>78.23999999999999</v>
+        <v>78.13</v>
       </c>
       <c r="F672" t="n">
-        <v>181989</v>
+        <v>180155</v>
       </c>
     </row>
     <row r="673">
@@ -13881,10 +13881,10 @@
         <v>77.38</v>
       </c>
       <c r="E673" t="n">
-        <v>78.93000000000001</v>
+        <v>78.98999999999999</v>
       </c>
       <c r="F673" t="n">
-        <v>151482</v>
+        <v>149729</v>
       </c>
     </row>
     <row r="674">
@@ -13961,10 +13961,10 @@
         <v>78.78</v>
       </c>
       <c r="E677" t="n">
-        <v>82.08</v>
+        <v>82.16</v>
       </c>
       <c r="F677" t="n">
-        <v>153620</v>
+        <v>151677</v>
       </c>
     </row>
     <row r="678">
@@ -13981,10 +13981,10 @@
         <v>81.63</v>
       </c>
       <c r="E678" t="n">
-        <v>82.22</v>
+        <v>82.17</v>
       </c>
       <c r="F678" t="n">
-        <v>149526</v>
+        <v>147722</v>
       </c>
     </row>
     <row r="679">
@@ -14061,10 +14061,10 @@
         <v>82.76000000000001</v>
       </c>
       <c r="E682" t="n">
-        <v>83.67</v>
+        <v>83.69</v>
       </c>
       <c r="F682" t="n">
-        <v>122153</v>
+        <v>120650</v>
       </c>
     </row>
     <row r="683">
@@ -14081,10 +14081,10 @@
         <v>83.68000000000001</v>
       </c>
       <c r="E683" t="n">
-        <v>84.33</v>
+        <v>84.23</v>
       </c>
       <c r="F683" t="n">
-        <v>116437</v>
+        <v>114060</v>
       </c>
     </row>
     <row r="684">
@@ -14161,10 +14161,10 @@
         <v>82.73</v>
       </c>
       <c r="E687" t="n">
-        <v>84.09</v>
+        <v>84.15000000000001</v>
       </c>
       <c r="F687" t="n">
-        <v>122966</v>
+        <v>121250</v>
       </c>
     </row>
     <row r="688">
@@ -14175,16 +14175,16 @@
         <v>83.81999999999999</v>
       </c>
       <c r="C688" t="n">
-        <v>85.08</v>
+        <v>84.97</v>
       </c>
       <c r="D688" t="n">
         <v>83.18000000000001</v>
       </c>
       <c r="E688" t="n">
-        <v>84.83</v>
+        <v>84.97</v>
       </c>
       <c r="F688" t="n">
-        <v>113449</v>
+        <v>111475</v>
       </c>
     </row>
     <row r="689">
@@ -14261,10 +14261,10 @@
         <v>81.48</v>
       </c>
       <c r="E692" t="n">
-        <v>83.78</v>
+        <v>83.83</v>
       </c>
       <c r="F692" t="n">
-        <v>167007</v>
+        <v>164605</v>
       </c>
     </row>
     <row r="693">
@@ -14281,10 +14281,10 @@
         <v>82.39</v>
       </c>
       <c r="E693" t="n">
-        <v>83.41</v>
+        <v>83.55</v>
       </c>
       <c r="F693" t="n">
-        <v>133535</v>
+        <v>132228</v>
       </c>
     </row>
     <row r="694">
@@ -14352,7 +14352,7 @@
         <v>44504</v>
       </c>
       <c r="B697" t="n">
-        <v>80.83</v>
+        <v>81.12</v>
       </c>
       <c r="C697" t="n">
         <v>84.08</v>
@@ -14364,7 +14364,7 @@
         <v>80.54000000000001</v>
       </c>
       <c r="F697" t="n">
-        <v>168783</v>
+        <v>171378</v>
       </c>
     </row>
     <row r="698">
@@ -14372,7 +14372,7 @@
         <v>44505</v>
       </c>
       <c r="B698" t="n">
-        <v>81.04000000000001</v>
+        <v>80.95</v>
       </c>
       <c r="C698" t="n">
         <v>82.72</v>
@@ -14384,7 +14384,7 @@
         <v>81.93000000000001</v>
       </c>
       <c r="F698" t="n">
-        <v>163172</v>
+        <v>166390</v>
       </c>
     </row>
     <row r="699">
@@ -14461,10 +14461,10 @@
         <v>81.06</v>
       </c>
       <c r="E702" t="n">
-        <v>81.92</v>
+        <v>81.91</v>
       </c>
       <c r="F702" t="n">
-        <v>161511</v>
+        <v>159955</v>
       </c>
     </row>
     <row r="703">
@@ -14481,10 +14481,10 @@
         <v>80.63</v>
       </c>
       <c r="E703" t="n">
-        <v>81.29000000000001</v>
+        <v>81.41</v>
       </c>
       <c r="F703" t="n">
-        <v>134507</v>
+        <v>133196</v>
       </c>
     </row>
     <row r="704">
@@ -14561,10 +14561,10 @@
         <v>78.55</v>
       </c>
       <c r="E707" t="n">
-        <v>80.34999999999999</v>
+        <v>80.42</v>
       </c>
       <c r="F707" t="n">
-        <v>132952</v>
+        <v>131123</v>
       </c>
     </row>
     <row r="708">
@@ -14581,10 +14581,10 @@
         <v>77.41</v>
       </c>
       <c r="E708" t="n">
-        <v>77.77</v>
+        <v>77.76000000000001</v>
       </c>
       <c r="F708" t="n">
-        <v>177513</v>
+        <v>175625</v>
       </c>
     </row>
     <row r="709">
@@ -14761,10 +14761,10 @@
         <v>65.67</v>
       </c>
       <c r="E717" t="n">
-        <v>70.36</v>
+        <v>69.94</v>
       </c>
       <c r="F717" t="n">
-        <v>240359</v>
+        <v>237353</v>
       </c>
     </row>
     <row r="718">
@@ -14781,10 +14781,10 @@
         <v>69.09999999999999</v>
       </c>
       <c r="E718" t="n">
-        <v>69.70999999999999</v>
+        <v>69.73</v>
       </c>
       <c r="F718" t="n">
-        <v>208893</v>
+        <v>205214</v>
       </c>
     </row>
     <row r="719">
@@ -14858,13 +14858,13 @@
         <v>76.55</v>
       </c>
       <c r="D722" t="n">
-        <v>73.70999999999999</v>
+        <v>73.78</v>
       </c>
       <c r="E722" t="n">
-        <v>73.84999999999999</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="F722" t="n">
-        <v>142264</v>
+        <v>140659</v>
       </c>
     </row>
     <row r="723">
@@ -14881,10 +14881,10 @@
         <v>73.67</v>
       </c>
       <c r="E723" t="n">
-        <v>75.16</v>
+        <v>75.23</v>
       </c>
       <c r="F723" t="n">
-        <v>153301</v>
+        <v>151698</v>
       </c>
     </row>
     <row r="724">
@@ -14961,10 +14961,10 @@
         <v>73.88</v>
       </c>
       <c r="E727" t="n">
-        <v>74.48999999999999</v>
+        <v>74.63</v>
       </c>
       <c r="F727" t="n">
-        <v>142563</v>
+        <v>140474</v>
       </c>
     </row>
     <row r="728">
@@ -14981,10 +14981,10 @@
         <v>72.63</v>
       </c>
       <c r="E728" t="n">
-        <v>72.88</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="F728" t="n">
-        <v>154875</v>
+        <v>152160</v>
       </c>
     </row>
     <row r="729">
@@ -15061,10 +15061,10 @@
         <v>74.72</v>
       </c>
       <c r="E732" t="n">
-        <v>76.52</v>
+        <v>76.63</v>
       </c>
       <c r="F732" t="n">
-        <v>102802</v>
+        <v>100583</v>
       </c>
     </row>
     <row r="733">
@@ -15161,10 +15161,10 @@
         <v>78.33</v>
       </c>
       <c r="E737" t="n">
-        <v>78.86</v>
+        <v>78.97</v>
       </c>
       <c r="F737" t="n">
-        <v>105405</v>
+        <v>103669</v>
       </c>
     </row>
     <row r="738">
@@ -15261,10 +15261,10 @@
         <v>79.36</v>
       </c>
       <c r="E742" t="n">
-        <v>81.70999999999999</v>
+        <v>81.65000000000001</v>
       </c>
       <c r="F742" t="n">
-        <v>187943</v>
+        <v>185800</v>
       </c>
     </row>
     <row r="743">
@@ -15281,10 +15281,10 @@
         <v>81.12</v>
       </c>
       <c r="E743" t="n">
-        <v>81.48</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="F743" t="n">
-        <v>160491</v>
+        <v>158852</v>
       </c>
     </row>
     <row r="744">
@@ -15361,10 +15361,10 @@
         <v>83.34999999999999</v>
       </c>
       <c r="E747" t="n">
-        <v>83.61</v>
+        <v>83.45</v>
       </c>
       <c r="F747" t="n">
-        <v>147527</v>
+        <v>145171</v>
       </c>
     </row>
     <row r="748">
@@ -15375,16 +15375,16 @@
         <v>83.68000000000001</v>
       </c>
       <c r="C748" t="n">
-        <v>85.98999999999999</v>
+        <v>85.97</v>
       </c>
       <c r="D748" t="n">
         <v>83.53</v>
       </c>
       <c r="E748" t="n">
-        <v>85.77</v>
+        <v>85.91</v>
       </c>
       <c r="F748" t="n">
-        <v>173518</v>
+        <v>171152</v>
       </c>
     </row>
     <row r="749">
@@ -15458,13 +15458,13 @@
         <v>88.8</v>
       </c>
       <c r="D752" t="n">
-        <v>86.38</v>
+        <v>86.56999999999999</v>
       </c>
       <c r="E752" t="n">
-        <v>86.58</v>
+        <v>86.7</v>
       </c>
       <c r="F752" t="n">
-        <v>169439</v>
+        <v>162890</v>
       </c>
     </row>
     <row r="753">
@@ -15481,10 +15481,10 @@
         <v>85.02</v>
       </c>
       <c r="E753" t="n">
-        <v>86.92</v>
+        <v>86.98</v>
       </c>
       <c r="F753" t="n">
-        <v>225683</v>
+        <v>223066</v>
       </c>
     </row>
     <row r="754">
@@ -15561,10 +15561,10 @@
         <v>87.7</v>
       </c>
       <c r="E757" t="n">
-        <v>88.63</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="F757" t="n">
-        <v>275711</v>
+        <v>270152</v>
       </c>
     </row>
     <row r="758">
@@ -15581,10 +15581,10 @@
         <v>88</v>
       </c>
       <c r="E758" t="n">
-        <v>88.81999999999999</v>
+        <v>88.73</v>
       </c>
       <c r="F758" t="n">
-        <v>278896</v>
+        <v>275262</v>
       </c>
     </row>
     <row r="759">
@@ -15655,16 +15655,16 @@
         <v>88.63</v>
       </c>
       <c r="C762" t="n">
-        <v>90.84999999999999</v>
+        <v>90.73999999999999</v>
       </c>
       <c r="D762" t="n">
         <v>87.59999999999999</v>
       </c>
       <c r="E762" t="n">
-        <v>90.51000000000001</v>
+        <v>90.45999999999999</v>
       </c>
       <c r="F762" t="n">
-        <v>168353</v>
+        <v>163057</v>
       </c>
     </row>
     <row r="763">
@@ -15681,10 +15681,10 @@
         <v>90.67</v>
       </c>
       <c r="E763" t="n">
-        <v>92.14</v>
+        <v>92.54000000000001</v>
       </c>
       <c r="F763" t="n">
-        <v>180147</v>
+        <v>177219</v>
       </c>
     </row>
     <row r="764">
@@ -15761,10 +15761,10 @@
         <v>90.09999999999999</v>
       </c>
       <c r="E767" t="n">
-        <v>90.54000000000001</v>
+        <v>90.66</v>
       </c>
       <c r="F767" t="n">
-        <v>186180</v>
+        <v>183590</v>
       </c>
     </row>
     <row r="768">
@@ -15781,10 +15781,10 @@
         <v>89.66</v>
       </c>
       <c r="E768" t="n">
-        <v>93.8</v>
+        <v>93.81</v>
       </c>
       <c r="F768" t="n">
-        <v>194729</v>
+        <v>189880</v>
       </c>
     </row>
     <row r="769">
@@ -15861,10 +15861,10 @@
         <v>90.34999999999999</v>
       </c>
       <c r="E772" t="n">
-        <v>91.16</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="F772" t="n">
-        <v>212213</v>
+        <v>209775</v>
       </c>
     </row>
     <row r="773">
@@ -15875,7 +15875,7 @@
         <v>90.76000000000001</v>
       </c>
       <c r="C773" t="n">
-        <v>92.28</v>
+        <v>92.15000000000001</v>
       </c>
       <c r="D773" t="n">
         <v>88.64</v>
@@ -15884,7 +15884,7 @@
         <v>91.81</v>
       </c>
       <c r="F773" t="n">
-        <v>194995</v>
+        <v>190175</v>
       </c>
     </row>
     <row r="774">
@@ -15961,10 +15961,10 @@
         <v>93.94</v>
       </c>
       <c r="E777" t="n">
-        <v>95.41</v>
+        <v>95.61</v>
       </c>
       <c r="F777" t="n">
-        <v>313423</v>
+        <v>309076</v>
       </c>
     </row>
     <row r="778">
@@ -15981,10 +15981,10 @@
         <v>92.55</v>
       </c>
       <c r="E778" t="n">
-        <v>94.23</v>
+        <v>94.69</v>
       </c>
       <c r="F778" t="n">
-        <v>237786</v>
+        <v>233541</v>
       </c>
     </row>
     <row r="779">
@@ -16061,10 +16061,10 @@
         <v>108.17</v>
       </c>
       <c r="E782" t="n">
-        <v>109.27</v>
+        <v>109.72</v>
       </c>
       <c r="F782" t="n">
-        <v>233799</v>
+        <v>231064</v>
       </c>
     </row>
     <row r="783">
@@ -16081,10 +16081,10 @@
         <v>108.47</v>
       </c>
       <c r="E783" t="n">
-        <v>116.7</v>
+        <v>117.14</v>
       </c>
       <c r="F783" t="n">
-        <v>210974</v>
+        <v>204618</v>
       </c>
     </row>
     <row r="784">
@@ -16161,10 +16161,10 @@
         <v>107.05</v>
       </c>
       <c r="E787" t="n">
-        <v>107.11</v>
+        <v>107.97</v>
       </c>
       <c r="F787" t="n">
-        <v>173653</v>
+        <v>170481</v>
       </c>
     </row>
     <row r="788">
@@ -16181,10 +16181,10 @@
         <v>104.96</v>
       </c>
       <c r="E788" t="n">
-        <v>110.14</v>
+        <v>110.51</v>
       </c>
       <c r="F788" t="n">
-        <v>157669</v>
+        <v>154891</v>
       </c>
     </row>
     <row r="789">
@@ -16252,19 +16252,19 @@
         <v>44637</v>
       </c>
       <c r="B792" t="n">
-        <v>96.70999999999999</v>
+        <v>96.98</v>
       </c>
       <c r="C792" t="n">
         <v>105.3</v>
       </c>
       <c r="D792" t="n">
-        <v>96.70999999999999</v>
+        <v>96.11</v>
       </c>
       <c r="E792" t="n">
         <v>104.46</v>
       </c>
       <c r="F792" t="n">
-        <v>172578</v>
+        <v>176604</v>
       </c>
     </row>
     <row r="793">
@@ -16272,7 +16272,7 @@
         <v>44638</v>
       </c>
       <c r="B793" t="n">
-        <v>105.16</v>
+        <v>104.55</v>
       </c>
       <c r="C793" t="n">
         <v>107.23</v>
@@ -16284,7 +16284,7 @@
         <v>105.63</v>
       </c>
       <c r="F793" t="n">
-        <v>155067</v>
+        <v>158531</v>
       </c>
     </row>
     <row r="794">
@@ -16352,7 +16352,7 @@
         <v>44644</v>
       </c>
       <c r="B797" t="n">
-        <v>119.49</v>
+        <v>118.08</v>
       </c>
       <c r="C797" t="n">
         <v>120.04</v>
@@ -16364,7 +16364,7 @@
         <v>114.47</v>
       </c>
       <c r="F797" t="n">
-        <v>206598</v>
+        <v>215337</v>
       </c>
     </row>
     <row r="798">
@@ -16372,7 +16372,7 @@
         <v>44645</v>
       </c>
       <c r="B798" t="n">
-        <v>114.52</v>
+        <v>115.3</v>
       </c>
       <c r="C798" t="n">
         <v>117.69</v>
@@ -16384,7 +16384,7 @@
         <v>115.94</v>
       </c>
       <c r="F798" t="n">
-        <v>189095</v>
+        <v>195807</v>
       </c>
     </row>
     <row r="799">
@@ -16461,10 +16461,10 @@
         <v>103.71</v>
       </c>
       <c r="E802" t="n">
-        <v>104.99</v>
+        <v>104.6</v>
       </c>
       <c r="F802" t="n">
-        <v>220967</v>
+        <v>217472</v>
       </c>
     </row>
     <row r="803">
@@ -16481,10 +16481,10 @@
         <v>101.94</v>
       </c>
       <c r="E803" t="n">
-        <v>103.88</v>
+        <v>104.13</v>
       </c>
       <c r="F803" t="n">
-        <v>181758</v>
+        <v>179677</v>
       </c>
     </row>
     <row r="804">
@@ -16561,10 +16561,10 @@
         <v>98.2</v>
       </c>
       <c r="E807" t="n">
-        <v>100.96</v>
+        <v>100.94</v>
       </c>
       <c r="F807" t="n">
-        <v>186163</v>
+        <v>183922</v>
       </c>
     </row>
     <row r="808">
@@ -16581,10 +16581,10 @@
         <v>99.28</v>
       </c>
       <c r="E808" t="n">
-        <v>101.81</v>
+        <v>102.16</v>
       </c>
       <c r="F808" t="n">
-        <v>162819</v>
+        <v>159821</v>
       </c>
     </row>
     <row r="809">
@@ -16661,10 +16661,10 @@
         <v>106.14</v>
       </c>
       <c r="E812" t="n">
-        <v>110.62</v>
+        <v>110.56</v>
       </c>
       <c r="F812" t="n">
-        <v>159785</v>
+        <v>156524</v>
       </c>
     </row>
     <row r="813">
@@ -16741,10 +16741,10 @@
         <v>106.38</v>
       </c>
       <c r="E816" t="n">
-        <v>108</v>
+        <v>107.93</v>
       </c>
       <c r="F816" t="n">
-        <v>188001</v>
+        <v>184241</v>
       </c>
     </row>
     <row r="817">
@@ -16758,13 +16758,13 @@
         <v>108.41</v>
       </c>
       <c r="D817" t="n">
-        <v>105.05</v>
+        <v>105.44</v>
       </c>
       <c r="E817" t="n">
-        <v>105.7</v>
+        <v>105.6</v>
       </c>
       <c r="F817" t="n">
-        <v>165632</v>
+        <v>162032</v>
       </c>
     </row>
     <row r="818">
@@ -16841,10 +16841,10 @@
         <v>102.74</v>
       </c>
       <c r="E821" t="n">
-        <v>106.8</v>
+        <v>107.25</v>
       </c>
       <c r="F821" t="n">
-        <v>170514</v>
+        <v>167676</v>
       </c>
     </row>
     <row r="822">
@@ -16861,10 +16861,10 @@
         <v>105.92</v>
       </c>
       <c r="E822" t="n">
-        <v>106.06</v>
+        <v>106.38</v>
       </c>
       <c r="F822" t="n">
-        <v>186051</v>
+        <v>182972</v>
       </c>
     </row>
     <row r="823">
@@ -16941,10 +16941,10 @@
         <v>108.66</v>
       </c>
       <c r="E826" t="n">
-        <v>110.4</v>
+        <v>110.3</v>
       </c>
       <c r="F826" t="n">
-        <v>201234</v>
+        <v>197687</v>
       </c>
     </row>
     <row r="827">
@@ -16961,10 +16961,10 @@
         <v>109.21</v>
       </c>
       <c r="E827" t="n">
-        <v>112.22</v>
+        <v>112.44</v>
       </c>
       <c r="F827" t="n">
-        <v>207851</v>
+        <v>203469</v>
       </c>
     </row>
     <row r="828">
@@ -17041,10 +17041,10 @@
         <v>103.97</v>
       </c>
       <c r="E831" t="n">
-        <v>106.86</v>
+        <v>107.38</v>
       </c>
       <c r="F831" t="n">
-        <v>243371</v>
+        <v>240901</v>
       </c>
     </row>
     <row r="832">
@@ -17061,10 +17061,10 @@
         <v>106.88</v>
       </c>
       <c r="E832" t="n">
-        <v>109.76</v>
+        <v>110.4</v>
       </c>
       <c r="F832" t="n">
-        <v>193013</v>
+        <v>190398</v>
       </c>
     </row>
     <row r="833">
@@ -17141,10 +17141,10 @@
         <v>104.22</v>
       </c>
       <c r="E836" t="n">
-        <v>109.5</v>
+        <v>109.59</v>
       </c>
       <c r="F836" t="n">
-        <v>250583</v>
+        <v>247278</v>
       </c>
     </row>
     <row r="837">
@@ -17161,10 +17161,10 @@
         <v>108.65</v>
       </c>
       <c r="E837" t="n">
-        <v>110.3</v>
+        <v>110.87</v>
       </c>
       <c r="F837" t="n">
-        <v>202895</v>
+        <v>198948</v>
       </c>
     </row>
     <row r="838">
@@ -17241,10 +17241,10 @@
         <v>110.83</v>
       </c>
       <c r="E841" t="n">
-        <v>114.15</v>
+        <v>114</v>
       </c>
       <c r="F841" t="n">
-        <v>175003</v>
+        <v>171535</v>
       </c>
     </row>
     <row r="842">
@@ -17261,10 +17261,10 @@
         <v>113.01</v>
       </c>
       <c r="E842" t="n">
-        <v>115.01</v>
+        <v>115.42</v>
       </c>
       <c r="F842" t="n">
-        <v>213418</v>
+        <v>210750</v>
       </c>
     </row>
     <row r="843">
@@ -17335,16 +17335,16 @@
         <v>113.88</v>
       </c>
       <c r="C846" t="n">
-        <v>117.74</v>
+        <v>117.57</v>
       </c>
       <c r="D846" t="n">
         <v>111.85</v>
       </c>
       <c r="E846" t="n">
-        <v>117.31</v>
+        <v>117.26</v>
       </c>
       <c r="F846" t="n">
-        <v>138282</v>
+        <v>137013</v>
       </c>
     </row>
     <row r="847">
@@ -17355,16 +17355,16 @@
         <v>117.37</v>
       </c>
       <c r="C847" t="n">
-        <v>120.6</v>
+        <v>120.57</v>
       </c>
       <c r="D847" t="n">
         <v>115.28</v>
       </c>
       <c r="E847" t="n">
-        <v>120.23</v>
+        <v>120.41</v>
       </c>
       <c r="F847" t="n">
-        <v>91626</v>
+        <v>90339</v>
       </c>
     </row>
     <row r="848">
@@ -17441,10 +17441,10 @@
         <v>121.23</v>
       </c>
       <c r="E851" t="n">
-        <v>121.41</v>
+        <v>121.71</v>
       </c>
       <c r="F851" t="n">
-        <v>176648</v>
+        <v>174232</v>
       </c>
     </row>
     <row r="852">
@@ -17461,10 +17461,10 @@
         <v>118.31</v>
       </c>
       <c r="E852" t="n">
-        <v>120.02</v>
+        <v>120.29</v>
       </c>
       <c r="F852" t="n">
-        <v>192334</v>
+        <v>190410</v>
       </c>
     </row>
     <row r="853">
@@ -17541,10 +17541,10 @@
         <v>113.72</v>
       </c>
       <c r="E856" t="n">
-        <v>116.92</v>
+        <v>117.15</v>
       </c>
       <c r="F856" t="n">
-        <v>231324</v>
+        <v>228931</v>
       </c>
     </row>
     <row r="857">
@@ -17561,10 +17561,10 @@
         <v>109.77</v>
       </c>
       <c r="E857" t="n">
-        <v>111.27</v>
+        <v>111.29</v>
       </c>
       <c r="F857" t="n">
-        <v>236868</v>
+        <v>233588</v>
       </c>
     </row>
     <row r="858">
@@ -17641,10 +17641,10 @@
         <v>105.25</v>
       </c>
       <c r="E861" t="n">
-        <v>106.13</v>
+        <v>106.29</v>
       </c>
       <c r="F861" t="n">
-        <v>234952</v>
+        <v>233040</v>
       </c>
     </row>
     <row r="862">
@@ -17661,10 +17661,10 @@
         <v>105.78</v>
       </c>
       <c r="E862" t="n">
-        <v>108.33</v>
+        <v>109.13</v>
       </c>
       <c r="F862" t="n">
-        <v>205227</v>
+        <v>202836</v>
       </c>
     </row>
     <row r="863">
@@ -17741,10 +17741,10 @@
         <v>107.7</v>
       </c>
       <c r="E866" t="n">
-        <v>108.43</v>
+        <v>108.69</v>
       </c>
       <c r="F866" t="n">
-        <v>212070</v>
+        <v>208599</v>
       </c>
     </row>
     <row r="867">
@@ -17761,10 +17761,10 @@
         <v>107.32</v>
       </c>
       <c r="E867" t="n">
-        <v>110.43</v>
+        <v>110.56</v>
       </c>
       <c r="F867" t="n">
-        <v>210630</v>
+        <v>209195</v>
       </c>
     </row>
     <row r="868">
@@ -17841,10 +17841,10 @@
         <v>97.11</v>
       </c>
       <c r="E871" t="n">
-        <v>102.32</v>
+        <v>102.75</v>
       </c>
       <c r="F871" t="n">
-        <v>224620</v>
+        <v>221862</v>
       </c>
     </row>
     <row r="872">
@@ -17861,10 +17861,10 @@
         <v>102.16</v>
       </c>
       <c r="E872" t="n">
-        <v>105.2</v>
+        <v>105.32</v>
       </c>
       <c r="F872" t="n">
-        <v>237030</v>
+        <v>235167</v>
       </c>
     </row>
     <row r="873">
@@ -17941,10 +17941,10 @@
         <v>92.42</v>
       </c>
       <c r="E876" t="n">
-        <v>97.12</v>
+        <v>97.17</v>
       </c>
       <c r="F876" t="n">
-        <v>217836</v>
+        <v>215919</v>
       </c>
     </row>
     <row r="877">
@@ -17961,10 +17961,10 @@
         <v>95.59</v>
       </c>
       <c r="E877" t="n">
-        <v>97.98</v>
+        <v>98.34999999999999</v>
       </c>
       <c r="F877" t="n">
-        <v>203134</v>
+        <v>200270</v>
       </c>
     </row>
     <row r="878">
@@ -18041,10 +18041,10 @@
         <v>97.86</v>
       </c>
       <c r="E881" t="n">
-        <v>99.93000000000001</v>
+        <v>100.04</v>
       </c>
       <c r="F881" t="n">
-        <v>229298</v>
+        <v>227231</v>
       </c>
     </row>
     <row r="882">
@@ -18061,10 +18061,10 @@
         <v>97.90000000000001</v>
       </c>
       <c r="E882" t="n">
-        <v>98.98999999999999</v>
+        <v>98.67</v>
       </c>
       <c r="F882" t="n">
-        <v>226135</v>
+        <v>222921</v>
       </c>
     </row>
     <row r="883">
@@ -18141,10 +18141,10 @@
         <v>100.74</v>
       </c>
       <c r="E886" t="n">
-        <v>101.99</v>
+        <v>101.93</v>
       </c>
       <c r="F886" t="n">
-        <v>132446</v>
+        <v>130398</v>
       </c>
     </row>
     <row r="887">
@@ -18161,10 +18161,10 @@
         <v>101.27</v>
       </c>
       <c r="E887" t="n">
-        <v>103.1</v>
+        <v>103.21</v>
       </c>
       <c r="F887" t="n">
-        <v>113461</v>
+        <v>112179</v>
       </c>
     </row>
     <row r="888">
@@ -18238,13 +18238,13 @@
         <v>97.17</v>
       </c>
       <c r="D891" t="n">
-        <v>92.5</v>
+        <v>92.73</v>
       </c>
       <c r="E891" t="n">
-        <v>92.52</v>
+        <v>93.38</v>
       </c>
       <c r="F891" t="n">
-        <v>162676</v>
+        <v>160629</v>
       </c>
     </row>
     <row r="892">
@@ -18261,10 +18261,10 @@
         <v>92.15000000000001</v>
       </c>
       <c r="E892" t="n">
-        <v>93.51000000000001</v>
+        <v>93.69</v>
       </c>
       <c r="F892" t="n">
-        <v>157322</v>
+        <v>155701</v>
       </c>
     </row>
     <row r="893">
@@ -18341,10 +18341,10 @@
         <v>96.08</v>
       </c>
       <c r="E896" t="n">
-        <v>98.31</v>
+        <v>98.66</v>
       </c>
       <c r="F896" t="n">
-        <v>140818</v>
+        <v>139272</v>
       </c>
     </row>
     <row r="897">
@@ -18361,10 +18361,10 @@
         <v>96.26000000000001</v>
       </c>
       <c r="E897" t="n">
-        <v>96.89</v>
+        <v>97.3</v>
       </c>
       <c r="F897" t="n">
-        <v>145858</v>
+        <v>144235</v>
       </c>
     </row>
     <row r="898">
@@ -18441,10 +18441,10 @@
         <v>92.55</v>
       </c>
       <c r="E901" t="n">
-        <v>95.56</v>
+        <v>95.93000000000001</v>
       </c>
       <c r="F901" t="n">
-        <v>123861</v>
+        <v>122235</v>
       </c>
     </row>
     <row r="902">
@@ -18461,10 +18461,10 @@
         <v>93.7</v>
       </c>
       <c r="E902" t="n">
-        <v>95.08</v>
+        <v>95.52</v>
       </c>
       <c r="F902" t="n">
-        <v>126696</v>
+        <v>125387</v>
       </c>
     </row>
     <row r="903">
@@ -18541,10 +18541,10 @@
         <v>98.23</v>
       </c>
       <c r="E906" t="n">
-        <v>98.68000000000001</v>
+        <v>99.05</v>
       </c>
       <c r="F906" t="n">
-        <v>115830</v>
+        <v>114289</v>
       </c>
     </row>
     <row r="907">
@@ -18561,10 +18561,10 @@
         <v>96.92</v>
       </c>
       <c r="E907" t="n">
-        <v>98.56999999999999</v>
+        <v>98.70999999999999</v>
       </c>
       <c r="F907" t="n">
-        <v>128357</v>
+        <v>127109</v>
       </c>
     </row>
     <row r="908">
@@ -18641,10 +18641,10 @@
         <v>91.58</v>
       </c>
       <c r="E911" t="n">
-        <v>91.59</v>
+        <v>91.75</v>
       </c>
       <c r="F911" t="n">
-        <v>172611</v>
+        <v>171383</v>
       </c>
     </row>
     <row r="912">
@@ -18661,10 +18661,10 @@
         <v>92.41</v>
       </c>
       <c r="E912" t="n">
-        <v>92.83</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="F912" t="n">
-        <v>164349</v>
+        <v>162523</v>
       </c>
     </row>
     <row r="913">
@@ -18741,10 +18741,10 @@
         <v>86.86</v>
       </c>
       <c r="E916" t="n">
-        <v>87.73999999999999</v>
+        <v>88.03</v>
       </c>
       <c r="F916" t="n">
-        <v>175783</v>
+        <v>174104</v>
       </c>
     </row>
     <row r="917">
@@ -18761,10 +18761,10 @@
         <v>88.09</v>
       </c>
       <c r="E917" t="n">
-        <v>91.42</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="F917" t="n">
-        <v>139210</v>
+        <v>137562</v>
       </c>
     </row>
     <row r="918">
@@ -18841,10 +18841,10 @@
         <v>89.39</v>
       </c>
       <c r="E921" t="n">
-        <v>89.78</v>
+        <v>90.08</v>
       </c>
       <c r="F921" t="n">
-        <v>179533</v>
+        <v>177670</v>
       </c>
     </row>
     <row r="922">
@@ -18861,10 +18861,10 @@
         <v>89.37</v>
       </c>
       <c r="E922" t="n">
-        <v>90.36</v>
+        <v>90.58</v>
       </c>
       <c r="F922" t="n">
-        <v>177056</v>
+        <v>175462</v>
       </c>
     </row>
     <row r="923">
@@ -18941,10 +18941,10 @@
         <v>88.38</v>
       </c>
       <c r="E926" t="n">
-        <v>89.48999999999999</v>
+        <v>89.53</v>
       </c>
       <c r="F926" t="n">
-        <v>169282</v>
+        <v>167346</v>
       </c>
     </row>
     <row r="927">
@@ -18961,10 +18961,10 @@
         <v>84.61</v>
       </c>
       <c r="E927" t="n">
-        <v>85.65000000000001</v>
+        <v>85.41</v>
       </c>
       <c r="F927" t="n">
-        <v>159709</v>
+        <v>157358</v>
       </c>
     </row>
     <row r="928">
@@ -19041,10 +19041,10 @@
         <v>85.98</v>
       </c>
       <c r="E931" t="n">
-        <v>87.22</v>
+        <v>87.20999999999999</v>
       </c>
       <c r="F931" t="n">
-        <v>184095</v>
+        <v>182346</v>
       </c>
     </row>
     <row r="932">
@@ -19061,10 +19061,10 @@
         <v>84.73999999999999</v>
       </c>
       <c r="E932" t="n">
-        <v>85.04000000000001</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="F932" t="n">
-        <v>174184</v>
+        <v>172540</v>
       </c>
     </row>
     <row r="933">
@@ -19141,10 +19141,10 @@
         <v>92.09</v>
       </c>
       <c r="E936" t="n">
-        <v>94.16</v>
+        <v>94.31999999999999</v>
       </c>
       <c r="F936" t="n">
-        <v>136157</v>
+        <v>134269</v>
       </c>
     </row>
     <row r="937">
@@ -19161,10 +19161,10 @@
         <v>93.25</v>
       </c>
       <c r="E937" t="n">
-        <v>97.59</v>
+        <v>96.95</v>
       </c>
       <c r="F937" t="n">
-        <v>161145</v>
+        <v>158303</v>
       </c>
     </row>
     <row r="938">
@@ -19241,10 +19241,10 @@
         <v>90.18000000000001</v>
       </c>
       <c r="E941" t="n">
-        <v>93.67</v>
+        <v>93.61</v>
       </c>
       <c r="F941" t="n">
-        <v>189909</v>
+        <v>187899</v>
       </c>
     </row>
     <row r="942">
@@ -19261,10 +19261,10 @@
         <v>90.34</v>
       </c>
       <c r="E942" t="n">
-        <v>90.66</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="F942" t="n">
-        <v>186342</v>
+        <v>184164</v>
       </c>
     </row>
     <row r="943">
@@ -19341,10 +19341,10 @@
         <v>90.34</v>
       </c>
       <c r="E946" t="n">
-        <v>91.11</v>
+        <v>91</v>
       </c>
       <c r="F946" t="n">
-        <v>172151</v>
+        <v>169394</v>
       </c>
     </row>
     <row r="947">
@@ -19361,10 +19361,10 @@
         <v>89.40000000000001</v>
       </c>
       <c r="E947" t="n">
-        <v>91.58</v>
+        <v>91.7</v>
       </c>
       <c r="F947" t="n">
-        <v>170499</v>
+        <v>168937</v>
       </c>
     </row>
     <row r="948">
@@ -19441,10 +19441,10 @@
         <v>93.06999999999999</v>
       </c>
       <c r="E951" t="n">
-        <v>94.45999999999999</v>
+        <v>94.91</v>
       </c>
       <c r="F951" t="n">
-        <v>135151</v>
+        <v>130846</v>
       </c>
     </row>
     <row r="952">
@@ -19461,10 +19461,10 @@
         <v>92.81999999999999</v>
       </c>
       <c r="E952" t="n">
-        <v>93.95</v>
+        <v>93.81</v>
       </c>
       <c r="F952" t="n">
-        <v>135363</v>
+        <v>133960</v>
       </c>
     </row>
     <row r="953">
@@ -19532,7 +19532,7 @@
         <v>44868</v>
       </c>
       <c r="B956" t="n">
-        <v>94.84</v>
+        <v>94.81</v>
       </c>
       <c r="C956" t="n">
         <v>95.45</v>
@@ -19544,7 +19544,7 @@
         <v>93.92</v>
       </c>
       <c r="F956" t="n">
-        <v>141621</v>
+        <v>143503</v>
       </c>
     </row>
     <row r="957">
@@ -19552,19 +19552,19 @@
         <v>44869</v>
       </c>
       <c r="B957" t="n">
-        <v>93.94</v>
+        <v>93.98</v>
       </c>
       <c r="C957" t="n">
         <v>98.23999999999999</v>
       </c>
       <c r="D957" t="n">
-        <v>93.94</v>
+        <v>93.76000000000001</v>
       </c>
       <c r="E957" t="n">
         <v>98.01000000000001</v>
       </c>
       <c r="F957" t="n">
-        <v>179958</v>
+        <v>182009</v>
       </c>
     </row>
     <row r="958">
@@ -19641,10 +19641,10 @@
         <v>90.97</v>
       </c>
       <c r="E961" t="n">
-        <v>92.47</v>
+        <v>92.69</v>
       </c>
       <c r="F961" t="n">
-        <v>170823</v>
+        <v>168690</v>
       </c>
     </row>
     <row r="962">
@@ -19661,10 +19661,10 @@
         <v>92.79000000000001</v>
       </c>
       <c r="E962" t="n">
-        <v>94.95999999999999</v>
+        <v>95.04000000000001</v>
       </c>
       <c r="F962" t="n">
-        <v>165782</v>
+        <v>163940</v>
       </c>
     </row>
     <row r="963">
@@ -19741,10 +19741,10 @@
         <v>88.72</v>
       </c>
       <c r="E966" t="n">
-        <v>89.34999999999999</v>
+        <v>89.28</v>
       </c>
       <c r="F966" t="n">
-        <v>159560</v>
+        <v>157265</v>
       </c>
     </row>
     <row r="967">
@@ -19761,10 +19761,10 @@
         <v>85.41</v>
       </c>
       <c r="E967" t="n">
-        <v>87.5</v>
+        <v>87.45</v>
       </c>
       <c r="F967" t="n">
-        <v>162655</v>
+        <v>160818</v>
       </c>
     </row>
     <row r="968">
@@ -19941,10 +19941,10 @@
         <v>86.26000000000001</v>
       </c>
       <c r="E976" t="n">
-        <v>86.98</v>
+        <v>86.84</v>
       </c>
       <c r="F976" t="n">
-        <v>136930</v>
+        <v>135345</v>
       </c>
     </row>
     <row r="977">
@@ -19961,10 +19961,10 @@
         <v>85.17</v>
       </c>
       <c r="E977" t="n">
-        <v>85.90000000000001</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="F977" t="n">
-        <v>137359</v>
+        <v>135815</v>
       </c>
     </row>
     <row r="978">
@@ -20041,10 +20041,10 @@
         <v>75.92</v>
       </c>
       <c r="E981" t="n">
-        <v>76.61</v>
+        <v>76.27</v>
       </c>
       <c r="F981" t="n">
-        <v>167594</v>
+        <v>165742</v>
       </c>
     </row>
     <row r="982">
@@ -20061,10 +20061,10 @@
         <v>75.34999999999999</v>
       </c>
       <c r="E982" t="n">
-        <v>76.79000000000001</v>
+        <v>76.76000000000001</v>
       </c>
       <c r="F982" t="n">
-        <v>153224</v>
+        <v>151706</v>
       </c>
     </row>
     <row r="983">
@@ -20141,10 +20141,10 @@
         <v>80.86</v>
       </c>
       <c r="E986" t="n">
-        <v>81.54000000000001</v>
+        <v>81.39</v>
       </c>
       <c r="F986" t="n">
-        <v>151489</v>
+        <v>149384</v>
       </c>
     </row>
     <row r="987">
@@ -20161,10 +20161,10 @@
         <v>78.61</v>
       </c>
       <c r="E987" t="n">
-        <v>79.44</v>
+        <v>79.36</v>
       </c>
       <c r="F987" t="n">
-        <v>151197</v>
+        <v>149990</v>
       </c>
     </row>
     <row r="988">
@@ -20241,10 +20241,10 @@
         <v>81.28</v>
       </c>
       <c r="E991" t="n">
-        <v>82.20999999999999</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="F991" t="n">
-        <v>95617</v>
+        <v>94348</v>
       </c>
     </row>
     <row r="992">
@@ -20321,10 +20321,10 @@
         <v>81.81999999999999</v>
       </c>
       <c r="E995" t="n">
-        <v>83.63</v>
+        <v>83.68000000000001</v>
       </c>
       <c r="F995" t="n">
-        <v>110699</v>
+        <v>109380</v>
       </c>
     </row>
     <row r="996">
@@ -20401,10 +20401,10 @@
         <v>77.63</v>
       </c>
       <c r="E999" t="n">
-        <v>78.8</v>
+        <v>78.68000000000001</v>
       </c>
       <c r="F999" t="n">
-        <v>150672</v>
+        <v>149266</v>
       </c>
     </row>
     <row r="1000">
@@ -20424,7 +20424,7 @@
         <v>78.51000000000001</v>
       </c>
       <c r="F1000" t="n">
-        <v>148389</v>
+        <v>147017</v>
       </c>
     </row>
     <row r="1001">
@@ -20501,10 +20501,10 @@
         <v>82.43000000000001</v>
       </c>
       <c r="E1004" t="n">
-        <v>83.84999999999999</v>
+        <v>83.91</v>
       </c>
       <c r="F1004" t="n">
-        <v>142735</v>
+        <v>141086</v>
       </c>
     </row>
     <row r="1005">
@@ -20515,16 +20515,16 @@
         <v>83.91</v>
       </c>
       <c r="C1005" t="n">
-        <v>85.61</v>
+        <v>85.55</v>
       </c>
       <c r="D1005" t="n">
         <v>83.55</v>
       </c>
       <c r="E1005" t="n">
-        <v>85.47</v>
+        <v>85.48</v>
       </c>
       <c r="F1005" t="n">
-        <v>131152</v>
+        <v>129757</v>
       </c>
     </row>
     <row r="1006">
@@ -20601,10 +20601,10 @@
         <v>83.95999999999999</v>
       </c>
       <c r="E1009" t="n">
-        <v>86.34</v>
+        <v>86.31999999999999</v>
       </c>
       <c r="F1009" t="n">
-        <v>144410</v>
+        <v>142583</v>
       </c>
     </row>
     <row r="1010">
@@ -20621,10 +20621,10 @@
         <v>85.69</v>
       </c>
       <c r="E1010" t="n">
-        <v>87.59</v>
+        <v>87.75</v>
       </c>
       <c r="F1010" t="n">
-        <v>125225</v>
+        <v>123973</v>
       </c>
     </row>
     <row r="1011">
@@ -20701,10 +20701,10 @@
         <v>85.75</v>
       </c>
       <c r="E1014" t="n">
-        <v>87.29000000000001</v>
+        <v>87.31</v>
       </c>
       <c r="F1014" t="n">
-        <v>96051</v>
+        <v>95077</v>
       </c>
     </row>
     <row r="1015">
@@ -20721,10 +20721,10 @@
         <v>85.48</v>
       </c>
       <c r="E1015" t="n">
-        <v>86.01000000000001</v>
+        <v>86.04000000000001</v>
       </c>
       <c r="F1015" t="n">
-        <v>110922</v>
+        <v>109841</v>
       </c>
     </row>
     <row r="1016">
@@ -20801,10 +20801,10 @@
         <v>81.2</v>
       </c>
       <c r="E1019" t="n">
-        <v>82.12</v>
+        <v>81.98</v>
       </c>
       <c r="F1019" t="n">
-        <v>150704</v>
+        <v>146732</v>
       </c>
     </row>
     <row r="1020">
@@ -20818,13 +20818,13 @@
         <v>84.11</v>
       </c>
       <c r="D1020" t="n">
-        <v>79.53</v>
+        <v>79.62</v>
       </c>
       <c r="E1020" t="n">
-        <v>79.62</v>
+        <v>79.64</v>
       </c>
       <c r="F1020" t="n">
-        <v>163093</v>
+        <v>161681</v>
       </c>
     </row>
     <row r="1021">
@@ -20901,10 +20901,10 @@
         <v>82.86</v>
       </c>
       <c r="E1024" t="n">
-        <v>83.95</v>
+        <v>83.88</v>
       </c>
       <c r="F1024" t="n">
-        <v>144061</v>
+        <v>142722</v>
       </c>
     </row>
     <row r="1025">
@@ -20921,10 +20921,10 @@
         <v>83.66</v>
       </c>
       <c r="E1025" t="n">
-        <v>86.2</v>
+        <v>86.29000000000001</v>
       </c>
       <c r="F1025" t="n">
-        <v>156718</v>
+        <v>155562</v>
       </c>
     </row>
     <row r="1026">
@@ -20998,13 +20998,13 @@
         <v>85.90000000000001</v>
       </c>
       <c r="D1029" t="n">
-        <v>84.28</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="E1029" t="n">
-        <v>84.31</v>
+        <v>84.37</v>
       </c>
       <c r="F1029" t="n">
-        <v>129946</v>
+        <v>128382</v>
       </c>
     </row>
     <row r="1030">
@@ -21021,10 +21021,10 @@
         <v>81.55</v>
       </c>
       <c r="E1030" t="n">
-        <v>82.72</v>
+        <v>82.68000000000001</v>
       </c>
       <c r="F1030" t="n">
-        <v>142763</v>
+        <v>141607</v>
       </c>
     </row>
     <row r="1031">
@@ -21101,10 +21101,10 @@
         <v>80.27</v>
       </c>
       <c r="E1034" t="n">
-        <v>82.18000000000001</v>
+        <v>82.12</v>
       </c>
       <c r="F1034" t="n">
-        <v>108091</v>
+        <v>107083</v>
       </c>
     </row>
     <row r="1035">
@@ -21121,10 +21121,10 @@
         <v>80.7</v>
       </c>
       <c r="E1035" t="n">
-        <v>82.77</v>
+        <v>82.94</v>
       </c>
       <c r="F1035" t="n">
-        <v>130526</v>
+        <v>129354</v>
       </c>
     </row>
     <row r="1036">
@@ -21201,10 +21201,10 @@
         <v>83.66</v>
       </c>
       <c r="E1039" t="n">
-        <v>84.23</v>
+        <v>84.34</v>
       </c>
       <c r="F1039" t="n">
-        <v>115434</v>
+        <v>114302</v>
       </c>
     </row>
     <row r="1040">
@@ -21215,16 +21215,16 @@
         <v>84.37</v>
       </c>
       <c r="C1040" t="n">
-        <v>85.81</v>
+        <v>85.8</v>
       </c>
       <c r="D1040" t="n">
         <v>82.2</v>
       </c>
       <c r="E1040" t="n">
-        <v>85.73999999999999</v>
+        <v>85.72</v>
       </c>
       <c r="F1040" t="n">
-        <v>120888</v>
+        <v>119970</v>
       </c>
     </row>
     <row r="1041">
@@ -21301,10 +21301,10 @@
         <v>81.16</v>
       </c>
       <c r="E1044" t="n">
-        <v>81.23</v>
+        <v>81.26000000000001</v>
       </c>
       <c r="F1044" t="n">
-        <v>121276</v>
+        <v>120126</v>
       </c>
     </row>
     <row r="1045">
@@ -21321,10 +21321,10 @@
         <v>80.47</v>
       </c>
       <c r="E1045" t="n">
-        <v>82.38</v>
+        <v>82.33</v>
       </c>
       <c r="F1045" t="n">
-        <v>172647</v>
+        <v>171433</v>
       </c>
     </row>
     <row r="1046">
@@ -21392,7 +21392,7 @@
         <v>45001</v>
       </c>
       <c r="B1049" t="n">
-        <v>74.59999999999999</v>
+        <v>74.04000000000001</v>
       </c>
       <c r="C1049" t="n">
         <v>75.23</v>
@@ -21404,7 +21404,7 @@
         <v>74.25</v>
       </c>
       <c r="F1049" t="n">
-        <v>206406</v>
+        <v>210322</v>
       </c>
     </row>
     <row r="1050">
@@ -21412,7 +21412,7 @@
         <v>45002</v>
       </c>
       <c r="B1050" t="n">
-        <v>74.41</v>
+        <v>74.45</v>
       </c>
       <c r="C1050" t="n">
         <v>75.65000000000001</v>
@@ -21424,7 +21424,7 @@
         <v>72.3</v>
       </c>
       <c r="F1050" t="n">
-        <v>194486</v>
+        <v>196053</v>
       </c>
     </row>
     <row r="1051">
@@ -21492,7 +21492,7 @@
         <v>45008</v>
       </c>
       <c r="B1054" t="n">
-        <v>75.73</v>
+        <v>75.58</v>
       </c>
       <c r="C1054" t="n">
         <v>77.09</v>
@@ -21504,7 +21504,7 @@
         <v>74.98999999999999</v>
       </c>
       <c r="F1054" t="n">
-        <v>132462</v>
+        <v>134971</v>
       </c>
     </row>
     <row r="1055">
@@ -21512,7 +21512,7 @@
         <v>45009</v>
       </c>
       <c r="B1055" t="n">
-        <v>74.92</v>
+        <v>75.08</v>
       </c>
       <c r="C1055" t="n">
         <v>75.89</v>
@@ -21524,7 +21524,7 @@
         <v>74.52</v>
       </c>
       <c r="F1055" t="n">
-        <v>158419</v>
+        <v>160608</v>
       </c>
     </row>
     <row r="1056">
@@ -21601,10 +21601,10 @@
         <v>77.13</v>
       </c>
       <c r="E1059" t="n">
-        <v>78.43000000000001</v>
+        <v>78.47</v>
       </c>
       <c r="F1059" t="n">
-        <v>102975</v>
+        <v>101875</v>
       </c>
     </row>
     <row r="1060">
@@ -21621,10 +21621,10 @@
         <v>77.79000000000001</v>
       </c>
       <c r="E1060" t="n">
-        <v>79.76000000000001</v>
+        <v>79.73</v>
       </c>
       <c r="F1060" t="n">
-        <v>103341</v>
+        <v>102278</v>
       </c>
     </row>
     <row r="1061">
@@ -21701,10 +21701,10 @@
         <v>83.89</v>
       </c>
       <c r="E1064" t="n">
-        <v>84.62</v>
+        <v>84.73</v>
       </c>
       <c r="F1064" t="n">
-        <v>128978</v>
+        <v>127887</v>
       </c>
     </row>
     <row r="1065">
@@ -21781,10 +21781,10 @@
         <v>85.78</v>
       </c>
       <c r="E1068" t="n">
-        <v>86.03</v>
+        <v>85.98</v>
       </c>
       <c r="F1068" t="n">
-        <v>107747</v>
+        <v>106530</v>
       </c>
     </row>
     <row r="1069">
@@ -21801,10 +21801,10 @@
         <v>85.27</v>
       </c>
       <c r="E1069" t="n">
-        <v>86.12</v>
+        <v>86.13</v>
       </c>
       <c r="F1069" t="n">
-        <v>119789</v>
+        <v>118921</v>
       </c>
     </row>
     <row r="1070">
@@ -21878,13 +21878,13 @@
         <v>82.59999999999999</v>
       </c>
       <c r="D1073" t="n">
-        <v>80.48999999999999</v>
+        <v>80.51000000000001</v>
       </c>
       <c r="E1073" t="n">
-        <v>80.48999999999999</v>
+        <v>80.62</v>
       </c>
       <c r="F1073" t="n">
-        <v>100157</v>
+        <v>99083</v>
       </c>
     </row>
     <row r="1074">
@@ -21901,10 +21901,10 @@
         <v>80.2</v>
       </c>
       <c r="E1074" t="n">
-        <v>81.53</v>
+        <v>81.38</v>
       </c>
       <c r="F1074" t="n">
-        <v>89589</v>
+        <v>88877</v>
       </c>
     </row>
     <row r="1075">
@@ -21981,10 +21981,10 @@
         <v>77.3</v>
       </c>
       <c r="E1078" t="n">
-        <v>78.17</v>
+        <v>78.23</v>
       </c>
       <c r="F1078" t="n">
-        <v>114226</v>
+        <v>112919</v>
       </c>
     </row>
     <row r="1079">
@@ -22001,10 +22001,10 @@
         <v>77.44</v>
       </c>
       <c r="E1079" t="n">
-        <v>80.08</v>
+        <v>80.20999999999999</v>
       </c>
       <c r="F1079" t="n">
-        <v>111593</v>
+        <v>110643</v>
       </c>
     </row>
     <row r="1080">
@@ -22081,10 +22081,10 @@
         <v>71.34</v>
       </c>
       <c r="E1083" t="n">
-        <v>72.38</v>
+        <v>72.34</v>
       </c>
       <c r="F1083" t="n">
-        <v>176458</v>
+        <v>175075</v>
       </c>
     </row>
     <row r="1084">
@@ -22101,10 +22101,10 @@
         <v>72.31999999999999</v>
       </c>
       <c r="E1084" t="n">
-        <v>75.15000000000001</v>
+        <v>75.22</v>
       </c>
       <c r="F1084" t="n">
-        <v>122688</v>
+        <v>121559</v>
       </c>
     </row>
     <row r="1085">
@@ -22181,10 +22181,10 @@
         <v>74.5</v>
       </c>
       <c r="E1088" t="n">
-        <v>75.26000000000001</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="F1088" t="n">
-        <v>142391</v>
+        <v>141443</v>
       </c>
     </row>
     <row r="1089">
@@ -22201,10 +22201,10 @@
         <v>73.84999999999999</v>
       </c>
       <c r="E1089" t="n">
-        <v>73.93000000000001</v>
+        <v>74.02</v>
       </c>
       <c r="F1089" t="n">
-        <v>144762</v>
+        <v>143925</v>
       </c>
     </row>
     <row r="1090">
@@ -22281,10 +22281,10 @@
         <v>75.42</v>
       </c>
       <c r="E1093" t="n">
-        <v>75.84</v>
+        <v>75.89</v>
       </c>
       <c r="F1093" t="n">
-        <v>98116</v>
+        <v>97144</v>
       </c>
     </row>
     <row r="1094">
@@ -22301,10 +22301,10 @@
         <v>75.01000000000001</v>
       </c>
       <c r="E1094" t="n">
-        <v>75.59999999999999</v>
+        <v>75.75</v>
       </c>
       <c r="F1094" t="n">
-        <v>108218</v>
+        <v>107224</v>
       </c>
     </row>
     <row r="1095">
@@ -22381,10 +22381,10 @@
         <v>75.08</v>
       </c>
       <c r="E1098" t="n">
-        <v>75.95999999999999</v>
+        <v>76.13</v>
       </c>
       <c r="F1098" t="n">
-        <v>95663</v>
+        <v>94656</v>
       </c>
     </row>
     <row r="1099">
@@ -22401,10 +22401,10 @@
         <v>75.62</v>
       </c>
       <c r="E1099" t="n">
-        <v>77.14</v>
+        <v>77.03</v>
       </c>
       <c r="F1099" t="n">
-        <v>86227</v>
+        <v>85632</v>
       </c>
     </row>
     <row r="1100">
@@ -22481,10 +22481,10 @@
         <v>72</v>
       </c>
       <c r="E1103" t="n">
-        <v>74.25</v>
+        <v>74.17</v>
       </c>
       <c r="F1103" t="n">
-        <v>124084</v>
+        <v>122959</v>
       </c>
     </row>
     <row r="1104">
@@ -22501,10 +22501,10 @@
         <v>74.13</v>
       </c>
       <c r="E1104" t="n">
-        <v>76.13</v>
+        <v>76.3</v>
       </c>
       <c r="F1104" t="n">
-        <v>111881</v>
+        <v>110715</v>
       </c>
     </row>
     <row r="1105">
@@ -22581,10 +22581,10 @@
         <v>73.52</v>
       </c>
       <c r="E1108" t="n">
-        <v>75.44</v>
+        <v>75.56999999999999</v>
       </c>
       <c r="F1108" t="n">
-        <v>142206</v>
+        <v>141391</v>
       </c>
     </row>
     <row r="1109">
@@ -22601,10 +22601,10 @@
         <v>74.67</v>
       </c>
       <c r="E1109" t="n">
-        <v>74.88</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="F1109" t="n">
-        <v>120995</v>
+        <v>120105</v>
       </c>
     </row>
     <row r="1110">
@@ -22681,10 +22681,10 @@
         <v>72.84999999999999</v>
       </c>
       <c r="E1113" t="n">
-        <v>75.52</v>
+        <v>75.56</v>
       </c>
       <c r="F1113" t="n">
-        <v>105947</v>
+        <v>104970</v>
       </c>
     </row>
     <row r="1114">
@@ -22701,10 +22701,10 @@
         <v>75.09999999999999</v>
       </c>
       <c r="E1114" t="n">
-        <v>76.23</v>
+        <v>76.47</v>
       </c>
       <c r="F1114" t="n">
-        <v>111184</v>
+        <v>109963</v>
       </c>
     </row>
     <row r="1115">
@@ -22781,10 +22781,10 @@
         <v>73.75</v>
       </c>
       <c r="E1118" t="n">
-        <v>74.3</v>
+        <v>74.2</v>
       </c>
       <c r="F1118" t="n">
-        <v>89974</v>
+        <v>89166</v>
       </c>
     </row>
     <row r="1119">
@@ -22795,16 +22795,16 @@
         <v>74.2</v>
       </c>
       <c r="C1119" t="n">
-        <v>74.45999999999999</v>
+        <v>74.36</v>
       </c>
       <c r="D1119" t="n">
         <v>72.25</v>
       </c>
       <c r="E1119" t="n">
-        <v>74.34</v>
+        <v>74.09</v>
       </c>
       <c r="F1119" t="n">
-        <v>101628</v>
+        <v>100773</v>
       </c>
     </row>
     <row r="1120">
@@ -22881,10 +22881,10 @@
         <v>73.56</v>
       </c>
       <c r="E1123" t="n">
-        <v>74.34999999999999</v>
+        <v>74.44</v>
       </c>
       <c r="F1123" t="n">
-        <v>118860</v>
+        <v>118096</v>
       </c>
     </row>
     <row r="1124">
@@ -22901,10 +22901,10 @@
         <v>74.23</v>
       </c>
       <c r="E1124" t="n">
-        <v>75.06999999999999</v>
+        <v>75.26000000000001</v>
       </c>
       <c r="F1124" t="n">
-        <v>108012</v>
+        <v>107062</v>
       </c>
     </row>
     <row r="1125">
@@ -22981,10 +22981,10 @@
         <v>74.94</v>
       </c>
       <c r="E1128" t="n">
-        <v>76.44</v>
+        <v>76.47</v>
       </c>
       <c r="F1128" t="n">
-        <v>121613</v>
+        <v>120498</v>
       </c>
     </row>
     <row r="1129">
@@ -23001,10 +23001,10 @@
         <v>75.91</v>
       </c>
       <c r="E1129" t="n">
-        <v>78.12</v>
+        <v>78.13</v>
       </c>
       <c r="F1129" t="n">
-        <v>101260</v>
+        <v>99946</v>
       </c>
     </row>
     <row r="1130">
@@ -23075,16 +23075,16 @@
         <v>79.95999999999999</v>
       </c>
       <c r="C1133" t="n">
-        <v>81.5</v>
+        <v>81.48999999999999</v>
       </c>
       <c r="D1133" t="n">
         <v>79.69</v>
       </c>
       <c r="E1133" t="n">
-        <v>81.37</v>
+        <v>81.48</v>
       </c>
       <c r="F1133" t="n">
-        <v>97805</v>
+        <v>96443</v>
       </c>
     </row>
     <row r="1134">
@@ -23098,13 +23098,13 @@
         <v>81.42</v>
       </c>
       <c r="D1134" t="n">
-        <v>79.34999999999999</v>
+        <v>79.44</v>
       </c>
       <c r="E1134" t="n">
-        <v>79.45</v>
+        <v>79.54000000000001</v>
       </c>
       <c r="F1134" t="n">
-        <v>99161</v>
+        <v>98000</v>
       </c>
     </row>
     <row r="1135">
@@ -23181,10 +23181,10 @@
         <v>78.56999999999999</v>
       </c>
       <c r="E1138" t="n">
-        <v>79.48</v>
+        <v>79.54000000000001</v>
       </c>
       <c r="F1138" t="n">
-        <v>77506</v>
+        <v>76777</v>
       </c>
     </row>
     <row r="1139">
@@ -23201,10 +23201,10 @@
         <v>79.51000000000001</v>
       </c>
       <c r="E1139" t="n">
-        <v>80.5</v>
+        <v>80.69</v>
       </c>
       <c r="F1139" t="n">
-        <v>70745</v>
+        <v>69907</v>
       </c>
     </row>
     <row r="1140">
@@ -23281,10 +23281,10 @@
         <v>82.54000000000001</v>
       </c>
       <c r="E1143" t="n">
-        <v>83.3</v>
+        <v>83.42</v>
       </c>
       <c r="F1143" t="n">
-        <v>101885</v>
+        <v>100960</v>
       </c>
     </row>
     <row r="1144">
@@ -23301,10 +23301,10 @@
         <v>82.78</v>
       </c>
       <c r="E1144" t="n">
-        <v>84.34999999999999</v>
+        <v>84.26000000000001</v>
       </c>
       <c r="F1144" t="n">
-        <v>96933</v>
+        <v>96080</v>
       </c>
     </row>
     <row r="1145">
@@ -23381,10 +23381,10 @@
         <v>82.23</v>
       </c>
       <c r="E1148" t="n">
-        <v>85.04000000000001</v>
+        <v>85.13</v>
       </c>
       <c r="F1148" t="n">
-        <v>124232</v>
+        <v>122532</v>
       </c>
     </row>
     <row r="1149">
@@ -23401,10 +23401,10 @@
         <v>84.89</v>
       </c>
       <c r="E1149" t="n">
-        <v>85.81</v>
+        <v>85.84</v>
       </c>
       <c r="F1149" t="n">
-        <v>104424</v>
+        <v>103319</v>
       </c>
     </row>
     <row r="1150">
@@ -23481,10 +23481,10 @@
         <v>85.89</v>
       </c>
       <c r="E1153" t="n">
-        <v>86.01000000000001</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="F1153" t="n">
-        <v>120019</v>
+        <v>119054</v>
       </c>
     </row>
     <row r="1154">
@@ -23501,10 +23501,10 @@
         <v>85.53</v>
       </c>
       <c r="E1154" t="n">
-        <v>86.16</v>
+        <v>86.26000000000001</v>
       </c>
       <c r="F1154" t="n">
-        <v>115051</v>
+        <v>114400</v>
       </c>
     </row>
     <row r="1155">
@@ -23581,10 +23581,10 @@
         <v>82.70999999999999</v>
       </c>
       <c r="E1158" t="n">
-        <v>83.42</v>
+        <v>83.45999999999999</v>
       </c>
       <c r="F1158" t="n">
-        <v>88033</v>
+        <v>87119</v>
       </c>
     </row>
     <row r="1159">
@@ -23601,10 +23601,10 @@
         <v>82.98</v>
       </c>
       <c r="E1159" t="n">
-        <v>84.42</v>
+        <v>84.37</v>
       </c>
       <c r="F1159" t="n">
-        <v>98761</v>
+        <v>98085</v>
       </c>
     </row>
     <row r="1160">
@@ -23681,10 +23681,10 @@
         <v>81.61</v>
       </c>
       <c r="E1163" t="n">
-        <v>82.67</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="F1163" t="n">
-        <v>77961</v>
+        <v>77118</v>
       </c>
     </row>
     <row r="1164">
@@ -23701,10 +23701,10 @@
         <v>82.2</v>
       </c>
       <c r="E1164" t="n">
-        <v>84.05</v>
+        <v>84.14</v>
       </c>
       <c r="F1164" t="n">
-        <v>102303</v>
+        <v>101382</v>
       </c>
     </row>
     <row r="1165">
@@ -23781,10 +23781,10 @@
         <v>84.98</v>
       </c>
       <c r="E1168" t="n">
-        <v>86.66</v>
+        <v>86.63</v>
       </c>
       <c r="F1168" t="n">
-        <v>85007</v>
+        <v>83934</v>
       </c>
     </row>
     <row r="1169">
@@ -23795,16 +23795,16 @@
         <v>86.63</v>
       </c>
       <c r="C1169" t="n">
-        <v>88.75</v>
+        <v>88.66</v>
       </c>
       <c r="D1169" t="n">
         <v>86.59</v>
       </c>
       <c r="E1169" t="n">
-        <v>88.68000000000001</v>
+        <v>88.64</v>
       </c>
       <c r="F1169" t="n">
-        <v>98645</v>
+        <v>97671</v>
       </c>
     </row>
     <row r="1170">
@@ -23881,10 +23881,10 @@
         <v>89.17</v>
       </c>
       <c r="E1173" t="n">
-        <v>89.47</v>
+        <v>89.76000000000001</v>
       </c>
       <c r="F1173" t="n">
-        <v>104343</v>
+        <v>103067</v>
       </c>
     </row>
     <row r="1174">
@@ -23901,10 +23901,10 @@
         <v>88.97</v>
       </c>
       <c r="E1174" t="n">
-        <v>90.09999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="F1174" t="n">
-        <v>101197</v>
+        <v>100164</v>
       </c>
     </row>
     <row r="1175">
@@ -23975,16 +23975,16 @@
         <v>91.56999999999999</v>
       </c>
       <c r="C1178" t="n">
-        <v>93.68000000000001</v>
+        <v>93.44</v>
       </c>
       <c r="D1178" t="n">
         <v>91.55</v>
       </c>
       <c r="E1178" t="n">
-        <v>93.56</v>
+        <v>93.36</v>
       </c>
       <c r="F1178" t="n">
-        <v>91727</v>
+        <v>89908</v>
       </c>
     </row>
     <row r="1179">
@@ -24001,10 +24001,10 @@
         <v>92.14</v>
       </c>
       <c r="E1179" t="n">
-        <v>93.56999999999999</v>
+        <v>93.52</v>
       </c>
       <c r="F1179" t="n">
-        <v>101498</v>
+        <v>100530</v>
       </c>
     </row>
     <row r="1180">
@@ -24081,10 +24081,10 @@
         <v>91.23999999999999</v>
       </c>
       <c r="E1183" t="n">
-        <v>92.20999999999999</v>
+        <v>92.27</v>
       </c>
       <c r="F1183" t="n">
-        <v>98137</v>
+        <v>97207</v>
       </c>
     </row>
     <row r="1184">
@@ -24101,10 +24101,10 @@
         <v>91.68000000000001</v>
       </c>
       <c r="E1184" t="n">
-        <v>92.28</v>
+        <v>92.31</v>
       </c>
       <c r="F1184" t="n">
-        <v>99665</v>
+        <v>98960</v>
       </c>
     </row>
     <row r="1185">
@@ -24181,10 +24181,10 @@
         <v>92.56</v>
       </c>
       <c r="E1188" t="n">
-        <v>92.89</v>
+        <v>92.94</v>
       </c>
       <c r="F1188" t="n">
-        <v>128240</v>
+        <v>127194</v>
       </c>
     </row>
     <row r="1189">
@@ -24201,10 +24201,10 @@
         <v>91.68000000000001</v>
       </c>
       <c r="E1189" t="n">
-        <v>91.8</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="F1189" t="n">
-        <v>117877</v>
+        <v>116761</v>
       </c>
     </row>
     <row r="1190">
@@ -24281,10 +24281,10 @@
         <v>83.31999999999999</v>
       </c>
       <c r="E1193" t="n">
-        <v>83.72</v>
+        <v>83.68000000000001</v>
       </c>
       <c r="F1193" t="n">
-        <v>149779</v>
+        <v>148426</v>
       </c>
     </row>
     <row r="1194">
@@ -24301,10 +24301,10 @@
         <v>82.97</v>
       </c>
       <c r="E1194" t="n">
-        <v>83.79000000000001</v>
+        <v>83.88</v>
       </c>
       <c r="F1194" t="n">
-        <v>140020</v>
+        <v>138785</v>
       </c>
     </row>
     <row r="1195">
@@ -24381,10 +24381,10 @@
         <v>84.59</v>
       </c>
       <c r="E1198" t="n">
-        <v>85.59999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="F1198" t="n">
-        <v>124560</v>
+        <v>123421</v>
       </c>
     </row>
     <row r="1199">
@@ -24404,7 +24404,7 @@
         <v>89.93000000000001</v>
       </c>
       <c r="F1199" t="n">
-        <v>120817</v>
+        <v>118765</v>
       </c>
     </row>
     <row r="1200">
@@ -24475,16 +24475,16 @@
         <v>90.26000000000001</v>
       </c>
       <c r="C1203" t="n">
-        <v>92.34999999999999</v>
+        <v>92.22</v>
       </c>
       <c r="D1203" t="n">
         <v>88.69</v>
       </c>
       <c r="E1203" t="n">
-        <v>92.04000000000001</v>
+        <v>92.16</v>
       </c>
       <c r="F1203" t="n">
-        <v>111224</v>
+        <v>109002</v>
       </c>
     </row>
     <row r="1204">
@@ -24501,10 +24501,10 @@
         <v>90.63</v>
       </c>
       <c r="E1204" t="n">
-        <v>91.26000000000001</v>
+        <v>91.13</v>
       </c>
       <c r="F1204" t="n">
-        <v>110661</v>
+        <v>109157</v>
       </c>
     </row>
     <row r="1205">
@@ -24581,10 +24581,10 @@
         <v>86.48</v>
       </c>
       <c r="E1208" t="n">
-        <v>87.23999999999999</v>
+        <v>87.25</v>
       </c>
       <c r="F1208" t="n">
-        <v>114536</v>
+        <v>113368</v>
       </c>
     </row>
     <row r="1209">
@@ -24601,10 +24601,10 @@
         <v>86.76000000000001</v>
       </c>
       <c r="E1209" t="n">
-        <v>88.70999999999999</v>
+        <v>88.76000000000001</v>
       </c>
       <c r="F1209" t="n">
-        <v>123231</v>
+        <v>121600</v>
       </c>
     </row>
     <row r="1210">
@@ -24672,7 +24672,7 @@
         <v>45232</v>
       </c>
       <c r="B1213" t="n">
-        <v>85.03</v>
+        <v>84.83</v>
       </c>
       <c r="C1213" t="n">
         <v>86.88</v>
@@ -24684,7 +24684,7 @@
         <v>86.63</v>
       </c>
       <c r="F1213" t="n">
-        <v>102261</v>
+        <v>103842</v>
       </c>
     </row>
     <row r="1214">
@@ -24692,7 +24692,7 @@
         <v>45233</v>
       </c>
       <c r="B1214" t="n">
-        <v>86.66</v>
+        <v>86.70999999999999</v>
       </c>
       <c r="C1214" t="n">
         <v>87.58</v>
@@ -24704,7 +24704,7 @@
         <v>84.95</v>
       </c>
       <c r="F1214" t="n">
-        <v>117913</v>
+        <v>119097</v>
       </c>
     </row>
     <row r="1215">
@@ -24781,10 +24781,10 @@
         <v>79.33</v>
       </c>
       <c r="E1218" t="n">
-        <v>79.76000000000001</v>
+        <v>79.75</v>
       </c>
       <c r="F1218" t="n">
-        <v>111847</v>
+        <v>110739</v>
       </c>
     </row>
     <row r="1219">
@@ -24801,10 +24801,10 @@
         <v>79.70999999999999</v>
       </c>
       <c r="E1219" t="n">
-        <v>81.43000000000001</v>
+        <v>81.36</v>
       </c>
       <c r="F1219" t="n">
-        <v>92327</v>
+        <v>91256</v>
       </c>
     </row>
     <row r="1220">
@@ -24881,10 +24881,10 @@
         <v>76.64</v>
       </c>
       <c r="E1223" t="n">
-        <v>77.45</v>
+        <v>77.43000000000001</v>
       </c>
       <c r="F1223" t="n">
-        <v>105749</v>
+        <v>104766</v>
       </c>
     </row>
     <row r="1224">
@@ -24901,10 +24901,10 @@
         <v>77.31</v>
       </c>
       <c r="E1224" t="n">
-        <v>80.43000000000001</v>
+        <v>80.37</v>
       </c>
       <c r="F1224" t="n">
-        <v>89648</v>
+        <v>88772</v>
       </c>
     </row>
     <row r="1225">
@@ -25078,13 +25078,13 @@
         <v>84.51000000000001</v>
       </c>
       <c r="D1233" t="n">
-        <v>79.94</v>
+        <v>79.95</v>
       </c>
       <c r="E1233" t="n">
-        <v>80.31</v>
+        <v>80</v>
       </c>
       <c r="F1233" t="n">
-        <v>145419</v>
+        <v>143673</v>
       </c>
     </row>
     <row r="1234">
@@ -25101,10 +25101,10 @@
         <v>78.69</v>
       </c>
       <c r="E1234" t="n">
-        <v>79.02</v>
+        <v>78.93000000000001</v>
       </c>
       <c r="F1234" t="n">
-        <v>126159</v>
+        <v>125186</v>
       </c>
     </row>
     <row r="1235">
@@ -25181,10 +25181,10 @@
         <v>73.68000000000001</v>
       </c>
       <c r="E1238" t="n">
-        <v>74.39</v>
+        <v>74.47</v>
       </c>
       <c r="F1238" t="n">
-        <v>116791</v>
+        <v>115986</v>
       </c>
     </row>
     <row r="1239">
@@ -25201,10 +25201,10 @@
         <v>74.25</v>
       </c>
       <c r="E1239" t="n">
-        <v>75.94</v>
+        <v>75.87</v>
       </c>
       <c r="F1239" t="n">
-        <v>114930</v>
+        <v>114085</v>
       </c>
     </row>
     <row r="1240">
@@ -25281,10 +25281,10 @@
         <v>74.56999999999999</v>
       </c>
       <c r="E1243" t="n">
-        <v>76.75</v>
+        <v>76.86</v>
       </c>
       <c r="F1243" t="n">
-        <v>84712</v>
+        <v>83845</v>
       </c>
     </row>
     <row r="1244">
@@ -25301,10 +25301,10 @@
         <v>75.48</v>
       </c>
       <c r="E1244" t="n">
-        <v>76.98999999999999</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="F1244" t="n">
-        <v>95068</v>
+        <v>94162</v>
       </c>
     </row>
     <row r="1245">
@@ -25381,10 +25381,10 @@
         <v>77.76000000000001</v>
       </c>
       <c r="E1248" t="n">
-        <v>79.12</v>
+        <v>79.19</v>
       </c>
       <c r="F1248" t="n">
-        <v>91755</v>
+        <v>91100</v>
       </c>
     </row>
     <row r="1249">
@@ -25461,10 +25461,10 @@
         <v>77.04000000000001</v>
       </c>
       <c r="E1252" t="n">
-        <v>77.36</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="F1252" t="n">
-        <v>95204</v>
+        <v>94380</v>
       </c>
     </row>
     <row r="1253">
@@ -25544,7 +25544,7 @@
         <v>77.53</v>
       </c>
       <c r="F1256" t="n">
-        <v>119158</v>
+        <v>118273</v>
       </c>
     </row>
     <row r="1257">
@@ -25641,10 +25641,10 @@
         <v>76.45</v>
       </c>
       <c r="E1261" t="n">
-        <v>78.01000000000001</v>
+        <v>77.61</v>
       </c>
       <c r="F1261" t="n">
-        <v>129868</v>
+        <v>128067</v>
       </c>
     </row>
     <row r="1262">
@@ -25741,10 +25741,10 @@
         <v>76.98</v>
       </c>
       <c r="E1266" t="n">
-        <v>78.56</v>
+        <v>78.63</v>
       </c>
       <c r="F1266" t="n">
-        <v>99368</v>
+        <v>98609</v>
       </c>
     </row>
     <row r="1267">
@@ -25841,10 +25841,10 @@
         <v>79.65000000000001</v>
       </c>
       <c r="E1271" t="n">
-        <v>81.69</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="F1271" t="n">
-        <v>76710</v>
+        <v>75889</v>
       </c>
     </row>
     <row r="1272">
@@ -25861,10 +25861,10 @@
         <v>80.75</v>
       </c>
       <c r="E1272" t="n">
-        <v>83.09999999999999</v>
+        <v>83.08</v>
       </c>
       <c r="F1272" t="n">
-        <v>87047</v>
+        <v>85666</v>
       </c>
     </row>
     <row r="1273">
@@ -25941,10 +25941,10 @@
         <v>78.5</v>
       </c>
       <c r="E1276" t="n">
-        <v>78.7</v>
+        <v>78.64</v>
       </c>
       <c r="F1276" t="n">
-        <v>140571</v>
+        <v>138682</v>
       </c>
     </row>
     <row r="1277">
@@ -25961,10 +25961,10 @@
         <v>76.78</v>
       </c>
       <c r="E1277" t="n">
-        <v>77.31999999999999</v>
+        <v>77.11</v>
       </c>
       <c r="F1277" t="n">
-        <v>133396</v>
+        <v>132023</v>
       </c>
     </row>
     <row r="1278">
@@ -26041,10 +26041,10 @@
         <v>78.84999999999999</v>
       </c>
       <c r="E1281" t="n">
-        <v>81.40000000000001</v>
+        <v>81.51000000000001</v>
       </c>
       <c r="F1281" t="n">
-        <v>87658</v>
+        <v>86597</v>
       </c>
     </row>
     <row r="1282">
@@ -26064,7 +26064,7 @@
         <v>81.63</v>
       </c>
       <c r="F1282" t="n">
-        <v>86235</v>
+        <v>85346</v>
       </c>
     </row>
     <row r="1283">
@@ -26141,10 +26141,10 @@
         <v>80.31999999999999</v>
       </c>
       <c r="E1286" t="n">
-        <v>82.22</v>
+        <v>82.37</v>
       </c>
       <c r="F1286" t="n">
-        <v>84560</v>
+        <v>83753</v>
       </c>
     </row>
     <row r="1287">
@@ -26161,10 +26161,10 @@
         <v>81.34</v>
       </c>
       <c r="E1287" t="n">
-        <v>82.68000000000001</v>
+        <v>82.70999999999999</v>
       </c>
       <c r="F1287" t="n">
-        <v>81459</v>
+        <v>80620</v>
       </c>
     </row>
     <row r="1288">
@@ -26241,10 +26241,10 @@
         <v>81.45</v>
       </c>
       <c r="E1291" t="n">
-        <v>82.51000000000001</v>
+        <v>82.63</v>
       </c>
       <c r="F1291" t="n">
-        <v>67848</v>
+        <v>67106</v>
       </c>
     </row>
     <row r="1292">
@@ -26261,10 +26261,10 @@
         <v>80.65000000000001</v>
       </c>
       <c r="E1292" t="n">
-        <v>80.84</v>
+        <v>80.88</v>
       </c>
       <c r="F1292" t="n">
-        <v>73168</v>
+        <v>72495</v>
       </c>
     </row>
     <row r="1293">
@@ -26341,10 +26341,10 @@
         <v>81.37</v>
       </c>
       <c r="E1296" t="n">
-        <v>81.8</v>
+        <v>81.70999999999999</v>
       </c>
       <c r="F1296" t="n">
-        <v>79642</v>
+        <v>78801</v>
       </c>
     </row>
     <row r="1297">
@@ -26361,10 +26361,10 @@
         <v>81.63</v>
       </c>
       <c r="E1297" t="n">
-        <v>83.12</v>
+        <v>83.19</v>
       </c>
       <c r="F1297" t="n">
-        <v>73275</v>
+        <v>72423</v>
       </c>
     </row>
     <row r="1298">
@@ -26441,10 +26441,10 @@
         <v>81.77</v>
       </c>
       <c r="E1301" t="n">
-        <v>82.87</v>
+        <v>82.52</v>
       </c>
       <c r="F1301" t="n">
-        <v>103853</v>
+        <v>102278</v>
       </c>
     </row>
     <row r="1302">
@@ -26461,10 +26461,10 @@
         <v>81.41</v>
       </c>
       <c r="E1302" t="n">
-        <v>81.55</v>
+        <v>81.66</v>
       </c>
       <c r="F1302" t="n">
-        <v>100115</v>
+        <v>99175</v>
       </c>
     </row>
     <row r="1303">
@@ -26532,19 +26532,19 @@
         <v>45365</v>
       </c>
       <c r="B1306" t="n">
-        <v>83.69</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="C1306" t="n">
         <v>85.18000000000001</v>
       </c>
       <c r="D1306" t="n">
-        <v>83.56999999999999</v>
+        <v>83.53</v>
       </c>
       <c r="E1306" t="n">
         <v>84.61</v>
       </c>
       <c r="F1306" t="n">
-        <v>71119</v>
+        <v>71844</v>
       </c>
     </row>
     <row r="1307">
@@ -26552,7 +26552,7 @@
         <v>45366</v>
       </c>
       <c r="B1307" t="n">
-        <v>84.68000000000001</v>
+        <v>84.65000000000001</v>
       </c>
       <c r="C1307" t="n">
         <v>85.09</v>
@@ -26564,7 +26564,7 @@
         <v>84.83</v>
       </c>
       <c r="F1307" t="n">
-        <v>74945</v>
+        <v>75864</v>
       </c>
     </row>
     <row r="1308">
@@ -26632,7 +26632,7 @@
         <v>45372</v>
       </c>
       <c r="B1311" t="n">
-        <v>85.81</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="C1311" t="n">
         <v>86.03</v>
@@ -26644,7 +26644,7 @@
         <v>84.95999999999999</v>
       </c>
       <c r="F1311" t="n">
-        <v>66113</v>
+        <v>67186</v>
       </c>
     </row>
     <row r="1312">
@@ -26652,7 +26652,7 @@
         <v>45373</v>
       </c>
       <c r="B1312" t="n">
-        <v>84.98999999999999</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="C1312" t="n">
         <v>85.58</v>
@@ -26664,7 +26664,7 @@
         <v>84.93000000000001</v>
       </c>
       <c r="F1312" t="n">
-        <v>53666</v>
+        <v>54286</v>
       </c>
     </row>
     <row r="1313">
@@ -26732,7 +26732,7 @@
         <v>45379</v>
       </c>
       <c r="B1316" t="n">
-        <v>85.65000000000001</v>
+        <v>85.56</v>
       </c>
       <c r="C1316" t="n">
         <v>86.89</v>
@@ -26744,7 +26744,7 @@
         <v>86.67</v>
       </c>
       <c r="F1316" t="n">
-        <v>56915</v>
+        <v>57372</v>
       </c>
     </row>
     <row r="1317">
@@ -26821,10 +26821,10 @@
         <v>88.43000000000001</v>
       </c>
       <c r="E1320" t="n">
-        <v>90.56</v>
+        <v>90.38</v>
       </c>
       <c r="F1320" t="n">
-        <v>75666</v>
+        <v>74470</v>
       </c>
     </row>
     <row r="1321">
@@ -26841,10 +26841,10 @@
         <v>90.18000000000001</v>
       </c>
       <c r="E1321" t="n">
-        <v>90.39</v>
+        <v>90.52</v>
       </c>
       <c r="F1321" t="n">
-        <v>80607</v>
+        <v>79937</v>
       </c>
     </row>
     <row r="1322">
@@ -26921,10 +26921,10 @@
         <v>88.87</v>
       </c>
       <c r="E1325" t="n">
-        <v>89.55</v>
+        <v>89.68000000000001</v>
       </c>
       <c r="F1325" t="n">
-        <v>107884</v>
+        <v>107040</v>
       </c>
     </row>
     <row r="1326">
@@ -26941,10 +26941,10 @@
         <v>89.45</v>
       </c>
       <c r="E1326" t="n">
-        <v>89.48999999999999</v>
+        <v>89.73</v>
       </c>
       <c r="F1326" t="n">
-        <v>109120</v>
+        <v>108331</v>
       </c>
     </row>
     <row r="1327">
@@ -27021,10 +27021,10 @@
         <v>85.63</v>
       </c>
       <c r="E1330" t="n">
-        <v>86.19</v>
+        <v>86.47</v>
       </c>
       <c r="F1330" t="n">
-        <v>108132</v>
+        <v>107464</v>
       </c>
     </row>
     <row r="1331">
@@ -27041,10 +27041,10 @@
         <v>85.61</v>
       </c>
       <c r="E1331" t="n">
-        <v>86.38</v>
+        <v>86.51000000000001</v>
       </c>
       <c r="F1331" t="n">
-        <v>144473</v>
+        <v>143518</v>
       </c>
     </row>
     <row r="1332">
@@ -27115,16 +27115,16 @@
         <v>86.88</v>
       </c>
       <c r="C1335" t="n">
-        <v>88</v>
+        <v>87.97</v>
       </c>
       <c r="D1335" t="n">
         <v>86.2</v>
       </c>
       <c r="E1335" t="n">
-        <v>87.83</v>
+        <v>87.95</v>
       </c>
       <c r="F1335" t="n">
-        <v>70059</v>
+        <v>69439</v>
       </c>
     </row>
     <row r="1336">
@@ -27141,10 +27141,10 @@
         <v>87.56999999999999</v>
       </c>
       <c r="E1336" t="n">
-        <v>87.89</v>
+        <v>87.98999999999999</v>
       </c>
       <c r="F1336" t="n">
-        <v>64445</v>
+        <v>63936</v>
       </c>
     </row>
     <row r="1337">
@@ -27221,10 +27221,10 @@
         <v>82.89</v>
       </c>
       <c r="E1340" t="n">
-        <v>83.48</v>
+        <v>83.47</v>
       </c>
       <c r="F1340" t="n">
-        <v>101847</v>
+        <v>100961</v>
       </c>
     </row>
     <row r="1341">
@@ -27238,13 +27238,13 @@
         <v>84.18000000000001</v>
       </c>
       <c r="D1341" t="n">
-        <v>82.53</v>
+        <v>82.65000000000001</v>
       </c>
       <c r="E1341" t="n">
-        <v>82.54000000000001</v>
+        <v>82.77</v>
       </c>
       <c r="F1341" t="n">
-        <v>83584</v>
+        <v>82987</v>
       </c>
     </row>
     <row r="1342">
@@ -27321,10 +27321,10 @@
         <v>83.18000000000001</v>
       </c>
       <c r="E1345" t="n">
-        <v>83.77</v>
+        <v>83.91</v>
       </c>
       <c r="F1345" t="n">
-        <v>67737</v>
+        <v>67201</v>
       </c>
     </row>
     <row r="1346">
@@ -27338,13 +27338,13 @@
         <v>84.23</v>
       </c>
       <c r="D1346" t="n">
-        <v>82.36</v>
+        <v>82.5</v>
       </c>
       <c r="E1346" t="n">
-        <v>82.36</v>
+        <v>82.61</v>
       </c>
       <c r="F1346" t="n">
-        <v>63117</v>
+        <v>62356</v>
       </c>
     </row>
     <row r="1347">
@@ -27421,10 +27421,10 @@
         <v>82.02</v>
       </c>
       <c r="E1350" t="n">
-        <v>82.98999999999999</v>
+        <v>83.04000000000001</v>
       </c>
       <c r="F1350" t="n">
-        <v>65759</v>
+        <v>65306</v>
       </c>
     </row>
     <row r="1351">
@@ -27441,10 +27441,10 @@
         <v>82.81999999999999</v>
       </c>
       <c r="E1351" t="n">
-        <v>83.56</v>
+        <v>83.68000000000001</v>
       </c>
       <c r="F1351" t="n">
-        <v>61133</v>
+        <v>60667</v>
       </c>
     </row>
     <row r="1352">
@@ -27521,10 +27521,10 @@
         <v>80.7</v>
       </c>
       <c r="E1355" t="n">
-        <v>81.06999999999999</v>
+        <v>81.09</v>
       </c>
       <c r="F1355" t="n">
-        <v>69958</v>
+        <v>68901</v>
       </c>
     </row>
     <row r="1356">
@@ -27541,10 +27541,10 @@
         <v>80.42</v>
       </c>
       <c r="E1356" t="n">
-        <v>81.79000000000001</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="F1356" t="n">
-        <v>56381</v>
+        <v>56045</v>
       </c>
     </row>
     <row r="1357">
@@ -27618,13 +27618,13 @@
         <v>83.51000000000001</v>
       </c>
       <c r="D1360" t="n">
-        <v>81.72</v>
+        <v>81.77</v>
       </c>
       <c r="E1360" t="n">
-        <v>81.73</v>
+        <v>81.88</v>
       </c>
       <c r="F1360" t="n">
-        <v>81864</v>
+        <v>81262</v>
       </c>
     </row>
     <row r="1361">
@@ -27641,10 +27641,10 @@
         <v>80.69</v>
       </c>
       <c r="E1361" t="n">
-        <v>81.09</v>
+        <v>81.22</v>
       </c>
       <c r="F1361" t="n">
-        <v>87130</v>
+        <v>86335</v>
       </c>
     </row>
     <row r="1362">
@@ -27721,10 +27721,10 @@
         <v>78.23999999999999</v>
       </c>
       <c r="E1365" t="n">
-        <v>79.69</v>
+        <v>79.73</v>
       </c>
       <c r="F1365" t="n">
-        <v>72677</v>
+        <v>72035</v>
       </c>
     </row>
     <row r="1366">
@@ -27741,10 +27741,10 @@
         <v>79.18000000000001</v>
       </c>
       <c r="E1366" t="n">
-        <v>79.23999999999999</v>
+        <v>79.27</v>
       </c>
       <c r="F1366" t="n">
-        <v>77440</v>
+        <v>76576</v>
       </c>
     </row>
     <row r="1367">
@@ -27821,10 +27821,10 @@
         <v>81.53</v>
       </c>
       <c r="E1370" t="n">
-        <v>81.68000000000001</v>
+        <v>81.98</v>
       </c>
       <c r="F1370" t="n">
-        <v>79567</v>
+        <v>78296</v>
       </c>
     </row>
     <row r="1371">
@@ -27841,10 +27841,10 @@
         <v>81.64</v>
       </c>
       <c r="E1371" t="n">
-        <v>82.06</v>
+        <v>82.2</v>
       </c>
       <c r="F1371" t="n">
-        <v>75768</v>
+        <v>75030</v>
       </c>
     </row>
     <row r="1372">
@@ -27921,10 +27921,10 @@
         <v>84.28</v>
       </c>
       <c r="E1375" t="n">
-        <v>84.7</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="F1375" t="n">
-        <v>59846</v>
+        <v>59448</v>
       </c>
     </row>
     <row r="1376">
@@ -27941,10 +27941,10 @@
         <v>84</v>
       </c>
       <c r="E1376" t="n">
-        <v>84.16</v>
+        <v>84.31</v>
       </c>
       <c r="F1376" t="n">
-        <v>60278</v>
+        <v>59797</v>
       </c>
     </row>
     <row r="1377">
@@ -28021,10 +28021,10 @@
         <v>84.01000000000001</v>
       </c>
       <c r="E1380" t="n">
-        <v>85.04000000000001</v>
+        <v>85.25</v>
       </c>
       <c r="F1380" t="n">
-        <v>64909</v>
+        <v>64362</v>
       </c>
     </row>
     <row r="1381">
@@ -28041,10 +28041,10 @@
         <v>84.39</v>
       </c>
       <c r="E1381" t="n">
-        <v>84.65000000000001</v>
+        <v>84.79000000000001</v>
       </c>
       <c r="F1381" t="n">
-        <v>69862</v>
+        <v>69177</v>
       </c>
     </row>
     <row r="1382">
@@ -28141,10 +28141,10 @@
         <v>86.17</v>
       </c>
       <c r="E1386" t="n">
-        <v>86.43000000000001</v>
+        <v>86.31999999999999</v>
       </c>
       <c r="F1386" t="n">
-        <v>68965</v>
+        <v>67919</v>
       </c>
     </row>
     <row r="1387">
@@ -28221,10 +28221,10 @@
         <v>84.16</v>
       </c>
       <c r="E1390" t="n">
-        <v>84.90000000000001</v>
+        <v>85.19</v>
       </c>
       <c r="F1390" t="n">
-        <v>78990</v>
+        <v>78243</v>
       </c>
     </row>
     <row r="1391">
@@ -28238,13 +28238,13 @@
         <v>85.67</v>
       </c>
       <c r="D1391" t="n">
-        <v>84.31999999999999</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="E1391" t="n">
-        <v>84.31999999999999</v>
+        <v>84.5</v>
       </c>
       <c r="F1391" t="n">
-        <v>74302</v>
+        <v>73607</v>
       </c>
     </row>
     <row r="1392">
@@ -28321,10 +28321,10 @@
         <v>83.41</v>
       </c>
       <c r="E1395" t="n">
-        <v>83.76000000000001</v>
+        <v>83.72</v>
       </c>
       <c r="F1395" t="n">
-        <v>69797</v>
+        <v>68620</v>
       </c>
     </row>
     <row r="1396">
@@ -28338,13 +28338,13 @@
         <v>84.41</v>
       </c>
       <c r="D1396" t="n">
-        <v>81.64</v>
+        <v>81.7</v>
       </c>
       <c r="E1396" t="n">
-        <v>81.64</v>
+        <v>81.89</v>
       </c>
       <c r="F1396" t="n">
-        <v>72736</v>
+        <v>72020</v>
       </c>
     </row>
     <row r="1397">
@@ -28421,10 +28421,10 @@
         <v>79.28</v>
       </c>
       <c r="E1400" t="n">
-        <v>81.37</v>
+        <v>81.33</v>
       </c>
       <c r="F1400" t="n">
-        <v>69789</v>
+        <v>69150</v>
       </c>
     </row>
     <row r="1401">
@@ -28441,10 +28441,10 @@
         <v>79.39</v>
       </c>
       <c r="E1401" t="n">
-        <v>79.48999999999999</v>
+        <v>79.92</v>
       </c>
       <c r="F1401" t="n">
-        <v>65748</v>
+        <v>64725</v>
       </c>
     </row>
     <row r="1402">
@@ -28521,10 +28521,10 @@
         <v>79.3</v>
       </c>
       <c r="E1405" t="n">
-        <v>79.83</v>
+        <v>80</v>
       </c>
       <c r="F1405" t="n">
-        <v>105741</v>
+        <v>104482</v>
       </c>
     </row>
     <row r="1406">
@@ -28541,10 +28541,10 @@
         <v>76.26000000000001</v>
       </c>
       <c r="E1406" t="n">
-        <v>77.14</v>
+        <v>77.08</v>
       </c>
       <c r="F1406" t="n">
-        <v>125792</v>
+        <v>124356</v>
       </c>
     </row>
     <row r="1407">
@@ -28621,10 +28621,10 @@
         <v>77.33</v>
       </c>
       <c r="E1410" t="n">
-        <v>78.59</v>
+        <v>78.73999999999999</v>
       </c>
       <c r="F1410" t="n">
-        <v>113892</v>
+        <v>113028</v>
       </c>
     </row>
     <row r="1411">
@@ -28641,10 +28641,10 @@
         <v>78.43000000000001</v>
       </c>
       <c r="E1411" t="n">
-        <v>79.27</v>
+        <v>79.34</v>
       </c>
       <c r="F1411" t="n">
-        <v>87467</v>
+        <v>86405</v>
       </c>
     </row>
     <row r="1412">
@@ -28721,10 +28721,10 @@
         <v>79.11</v>
       </c>
       <c r="E1415" t="n">
-        <v>80.26000000000001</v>
+        <v>80.31999999999999</v>
       </c>
       <c r="F1415" t="n">
-        <v>79567</v>
+        <v>78757</v>
       </c>
     </row>
     <row r="1416">
@@ -28741,10 +28741,10 @@
         <v>78.09</v>
       </c>
       <c r="E1416" t="n">
-        <v>78.94</v>
+        <v>79.22</v>
       </c>
       <c r="F1416" t="n">
-        <v>82030</v>
+        <v>81009</v>
       </c>
     </row>
     <row r="1417">
@@ -28821,10 +28821,10 @@
         <v>75.25</v>
       </c>
       <c r="E1420" t="n">
-        <v>76.42</v>
+        <v>76.47</v>
       </c>
       <c r="F1420" t="n">
-        <v>79873</v>
+        <v>79280</v>
       </c>
     </row>
     <row r="1421">
@@ -28841,10 +28841,10 @@
         <v>76.40000000000001</v>
       </c>
       <c r="E1421" t="n">
-        <v>78.13</v>
+        <v>78.17</v>
       </c>
       <c r="F1421" t="n">
-        <v>69081</v>
+        <v>68613</v>
       </c>
     </row>
     <row r="1422">
@@ -28921,10 +28921,10 @@
         <v>76.90000000000001</v>
       </c>
       <c r="E1425" t="n">
-        <v>78.72</v>
+        <v>78.81</v>
       </c>
       <c r="F1425" t="n">
-        <v>94397</v>
+        <v>93699</v>
       </c>
     </row>
     <row r="1426">
@@ -28941,10 +28941,10 @@
         <v>76.56</v>
       </c>
       <c r="E1426" t="n">
-        <v>76.77</v>
+        <v>76.81</v>
       </c>
       <c r="F1426" t="n">
-        <v>109124</v>
+        <v>108329</v>
       </c>
     </row>
     <row r="1427">
@@ -29021,10 +29021,10 @@
         <v>72.20999999999999</v>
       </c>
       <c r="E1430" t="n">
-        <v>72.53</v>
+        <v>72.54000000000001</v>
       </c>
       <c r="F1430" t="n">
-        <v>109541</v>
+        <v>108713</v>
       </c>
     </row>
     <row r="1431">
@@ -29041,10 +29041,10 @@
         <v>70.45</v>
       </c>
       <c r="E1431" t="n">
-        <v>71.2</v>
+        <v>71.37</v>
       </c>
       <c r="F1431" t="n">
-        <v>116954</v>
+        <v>115759</v>
       </c>
     </row>
     <row r="1432">
@@ -29121,10 +29121,10 @@
         <v>70.31999999999999</v>
       </c>
       <c r="E1435" t="n">
-        <v>71.67</v>
+        <v>71.89</v>
       </c>
       <c r="F1435" t="n">
-        <v>115156</v>
+        <v>114181</v>
       </c>
     </row>
     <row r="1436">
@@ -29141,10 +29141,10 @@
         <v>71.09</v>
       </c>
       <c r="E1436" t="n">
-        <v>71.59999999999999</v>
+        <v>71.73</v>
       </c>
       <c r="F1436" t="n">
-        <v>99629</v>
+        <v>98569</v>
       </c>
     </row>
     <row r="1437">
@@ -29221,10 +29221,10 @@
         <v>72.26000000000001</v>
       </c>
       <c r="E1440" t="n">
-        <v>73.97</v>
+        <v>74.05</v>
       </c>
       <c r="F1440" t="n">
-        <v>89094</v>
+        <v>88395</v>
       </c>
     </row>
     <row r="1441">
@@ -29241,10 +29241,10 @@
         <v>73.28</v>
       </c>
       <c r="E1441" t="n">
-        <v>73.87</v>
+        <v>73.98</v>
       </c>
       <c r="F1441" t="n">
-        <v>72413</v>
+        <v>71635</v>
       </c>
     </row>
     <row r="1442">
@@ -29321,10 +29321,10 @@
         <v>70.20999999999999</v>
       </c>
       <c r="E1445" t="n">
-        <v>70.68000000000001</v>
+        <v>70.66</v>
       </c>
       <c r="F1445" t="n">
-        <v>155899</v>
+        <v>154979</v>
       </c>
     </row>
     <row r="1446">
@@ -29335,16 +29335,16 @@
         <v>70.68000000000001</v>
       </c>
       <c r="C1446" t="n">
-        <v>71.90000000000001</v>
+        <v>71.89</v>
       </c>
       <c r="D1446" t="n">
         <v>70.39</v>
       </c>
       <c r="E1446" t="n">
-        <v>71.79000000000001</v>
+        <v>71.81999999999999</v>
       </c>
       <c r="F1446" t="n">
-        <v>123787</v>
+        <v>122438</v>
       </c>
     </row>
     <row r="1447">
@@ -29421,10 +29421,10 @@
         <v>74.18000000000001</v>
       </c>
       <c r="E1450" t="n">
-        <v>77.28</v>
+        <v>77.58</v>
       </c>
       <c r="F1450" t="n">
-        <v>125075</v>
+        <v>123449</v>
       </c>
     </row>
     <row r="1451">
@@ -29441,10 +29441,10 @@
         <v>77.19</v>
       </c>
       <c r="E1451" t="n">
-        <v>77.73</v>
+        <v>77.87</v>
       </c>
       <c r="F1451" t="n">
-        <v>121412</v>
+        <v>120535</v>
       </c>
     </row>
     <row r="1452">
@@ -38764,7 +38764,7 @@
         <v>81.73999999999999</v>
       </c>
       <c r="F1917" t="n">
-        <v>74700</v>
+        <v>74712</v>
       </c>
     </row>
     <row r="1918">
@@ -38772,19 +38772,19 @@
         <v>46232</v>
       </c>
       <c r="B1918" t="n">
-        <v>82.93000000000001</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="C1918" t="n">
         <v>88.36</v>
       </c>
       <c r="D1918" t="n">
-        <v>82.93000000000001</v>
+        <v>83.97</v>
       </c>
       <c r="E1918" t="n">
         <v>87.92</v>
       </c>
       <c r="F1918" t="n">
-        <v>95407</v>
+        <v>95426</v>
       </c>
     </row>
     <row r="1919">
@@ -38804,7 +38804,7 @@
         <v>86.87</v>
       </c>
       <c r="F1919" t="n">
-        <v>118707</v>
+        <v>118722</v>
       </c>
     </row>
     <row r="1920">
@@ -38824,7 +38824,7 @@
         <v>89.69</v>
       </c>
       <c r="F1920" t="n">
-        <v>118408</v>
+        <v>118405</v>
       </c>
     </row>
     <row r="1921">
@@ -38844,7 +38844,7 @@
         <v>82.90000000000001</v>
       </c>
       <c r="F1921" t="n">
-        <v>120658</v>
+        <v>120569</v>
       </c>
     </row>
     <row r="1922">
@@ -38864,7 +38864,7 @@
         <v>78.3</v>
       </c>
       <c r="F1922" t="n">
-        <v>132834</v>
+        <v>132836</v>
       </c>
     </row>
     <row r="1923">
@@ -38884,7 +38884,27 @@
         <v>78.86</v>
       </c>
       <c r="F1923" t="n">
-        <v>121224</v>
+        <v>121230</v>
+      </c>
+    </row>
+    <row r="1924">
+      <c r="A1924" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B1924" t="n">
+        <v>78.58</v>
+      </c>
+      <c r="C1924" t="n">
+        <v>82.98</v>
+      </c>
+      <c r="D1924" t="n">
+        <v>78.41</v>
+      </c>
+      <c r="E1924" t="n">
+        <v>82.76000000000001</v>
+      </c>
+      <c r="F1924" t="n">
+        <v>102987</v>
       </c>
     </row>
   </sheetData>

--- a/database/BRENT.xlsx
+++ b/database/BRENT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1924"/>
+  <dimension ref="A1:F1925"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38907,6 +38907,26 @@
         <v>102987</v>
       </c>
     </row>
+    <row r="1925">
+      <c r="A1925" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B1925" t="n">
+        <v>82.43000000000001</v>
+      </c>
+      <c r="C1925" t="n">
+        <v>83.02</v>
+      </c>
+      <c r="D1925" t="n">
+        <v>82.29000000000001</v>
+      </c>
+      <c r="E1925" t="n">
+        <v>82.55</v>
+      </c>
+      <c r="F1925" t="n">
+        <v>3269</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/BRENT.xlsx
+++ b/database/BRENT.xlsx
@@ -3881,10 +3881,10 @@
         <v>60.96</v>
       </c>
       <c r="E173" t="n">
-        <v>61.74</v>
+        <v>61.65</v>
       </c>
       <c r="F173" t="n">
-        <v>7439</v>
+        <v>7745</v>
       </c>
     </row>
     <row r="174">
@@ -3952,7 +3952,7 @@
         <v>43769</v>
       </c>
       <c r="B177" t="n">
-        <v>60.17</v>
+        <v>60.27</v>
       </c>
       <c r="C177" t="n">
         <v>60.79</v>
@@ -3964,7 +3964,7 @@
         <v>59.46</v>
       </c>
       <c r="F177" t="n">
-        <v>20831</v>
+        <v>20603</v>
       </c>
     </row>
     <row r="178">
@@ -3972,7 +3972,7 @@
         <v>43770</v>
       </c>
       <c r="B178" t="n">
-        <v>59.42</v>
+        <v>59.64</v>
       </c>
       <c r="C178" t="n">
         <v>61.8</v>
@@ -3984,7 +3984,7 @@
         <v>61.65</v>
       </c>
       <c r="F178" t="n">
-        <v>18539</v>
+        <v>18281</v>
       </c>
     </row>
     <row r="179">
@@ -4061,10 +4061,10 @@
         <v>61.63</v>
       </c>
       <c r="E182" t="n">
-        <v>62.14</v>
+        <v>62.29</v>
       </c>
       <c r="F182" t="n">
-        <v>19306</v>
+        <v>19680</v>
       </c>
     </row>
     <row r="183">
@@ -4081,10 +4081,10 @@
         <v>60.65</v>
       </c>
       <c r="E183" t="n">
-        <v>62.61</v>
+        <v>62.64</v>
       </c>
       <c r="F183" t="n">
-        <v>21625</v>
+        <v>21863</v>
       </c>
     </row>
     <row r="184">
@@ -4161,10 +4161,10 @@
         <v>62.14</v>
       </c>
       <c r="E187" t="n">
-        <v>62.38</v>
+        <v>62.33</v>
       </c>
       <c r="F187" t="n">
-        <v>19157</v>
+        <v>19293</v>
       </c>
     </row>
     <row r="188">
@@ -4181,10 +4181,10 @@
         <v>61.69</v>
       </c>
       <c r="E188" t="n">
-        <v>63.32</v>
+        <v>63.41</v>
       </c>
       <c r="F188" t="n">
-        <v>15801</v>
+        <v>16092</v>
       </c>
     </row>
     <row r="189">
@@ -4261,10 +4261,10 @@
         <v>61.91</v>
       </c>
       <c r="E192" t="n">
-        <v>63.74</v>
+        <v>63.64</v>
       </c>
       <c r="F192" t="n">
-        <v>21582</v>
+        <v>21823</v>
       </c>
     </row>
     <row r="193">
@@ -4281,10 +4281,10 @@
         <v>61.92</v>
       </c>
       <c r="E193" t="n">
-        <v>62.58</v>
+        <v>62.52</v>
       </c>
       <c r="F193" t="n">
-        <v>17577</v>
+        <v>17794</v>
       </c>
     </row>
     <row r="194">
@@ -4461,10 +4461,10 @@
         <v>62.73</v>
       </c>
       <c r="E202" t="n">
-        <v>63.33</v>
+        <v>63.26</v>
       </c>
       <c r="F202" t="n">
-        <v>24042</v>
+        <v>24300</v>
       </c>
     </row>
     <row r="203">
@@ -4481,10 +4481,10 @@
         <v>62.82</v>
       </c>
       <c r="E203" t="n">
-        <v>64.22</v>
+        <v>64.34</v>
       </c>
       <c r="F203" t="n">
-        <v>22359</v>
+        <v>22572</v>
       </c>
     </row>
     <row r="204">
@@ -4561,10 +4561,10 @@
         <v>63.86</v>
       </c>
       <c r="E207" t="n">
-        <v>64.31</v>
+        <v>64.28</v>
       </c>
       <c r="F207" t="n">
-        <v>18198</v>
+        <v>18454</v>
       </c>
     </row>
     <row r="208">
@@ -4581,10 +4581,10 @@
         <v>64.48</v>
       </c>
       <c r="E208" t="n">
-        <v>64.88</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="F208" t="n">
-        <v>21484</v>
+        <v>21671</v>
       </c>
     </row>
     <row r="209">
@@ -4661,10 +4661,10 @@
         <v>66.02</v>
       </c>
       <c r="E212" t="n">
-        <v>66.45</v>
+        <v>66.53</v>
       </c>
       <c r="F212" t="n">
-        <v>10932</v>
+        <v>11180</v>
       </c>
     </row>
     <row r="213">
@@ -4681,10 +4681,10 @@
         <v>65.72</v>
       </c>
       <c r="E213" t="n">
-        <v>65.98</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="F213" t="n">
-        <v>14693</v>
+        <v>14806</v>
       </c>
     </row>
     <row r="214">
@@ -4741,10 +4741,10 @@
         <v>66.09</v>
       </c>
       <c r="E216" t="n">
-        <v>66.65000000000001</v>
+        <v>66.75</v>
       </c>
       <c r="F216" t="n">
-        <v>9409</v>
+        <v>9613</v>
       </c>
     </row>
     <row r="217">
@@ -4761,10 +4761,10 @@
         <v>66.34</v>
       </c>
       <c r="E217" t="n">
-        <v>66.81</v>
+        <v>66.84</v>
       </c>
       <c r="F217" t="n">
-        <v>11272</v>
+        <v>11398</v>
       </c>
     </row>
     <row r="218">
@@ -4821,10 +4821,10 @@
         <v>65.7</v>
       </c>
       <c r="E220" t="n">
-        <v>66.19</v>
+        <v>66.23</v>
       </c>
       <c r="F220" t="n">
-        <v>15153</v>
+        <v>15351</v>
       </c>
     </row>
     <row r="221">
@@ -4841,10 +4841,10 @@
         <v>66.19</v>
       </c>
       <c r="E221" t="n">
-        <v>68.55</v>
+        <v>68.59</v>
       </c>
       <c r="F221" t="n">
-        <v>35427</v>
+        <v>35609</v>
       </c>
     </row>
     <row r="222">
@@ -4924,7 +4924,7 @@
         <v>65.38</v>
       </c>
       <c r="F225" t="n">
-        <v>25682</v>
+        <v>25951</v>
       </c>
     </row>
     <row r="226">
@@ -4944,7 +4944,7 @@
         <v>65</v>
       </c>
       <c r="F226" t="n">
-        <v>20016</v>
+        <v>20436</v>
       </c>
     </row>
     <row r="227">
@@ -5021,10 +5021,10 @@
         <v>63.89</v>
       </c>
       <c r="E230" t="n">
-        <v>64.64</v>
+        <v>64.7</v>
       </c>
       <c r="F230" t="n">
-        <v>16107</v>
+        <v>16472</v>
       </c>
     </row>
     <row r="231">
@@ -5041,10 +5041,10 @@
         <v>64.45</v>
       </c>
       <c r="E231" t="n">
-        <v>64.95</v>
+        <v>65.08</v>
       </c>
       <c r="F231" t="n">
-        <v>16060</v>
+        <v>16251</v>
       </c>
     </row>
     <row r="232">
@@ -5121,10 +5121,10 @@
         <v>61.24</v>
       </c>
       <c r="E235" t="n">
-        <v>61.97</v>
+        <v>62.11</v>
       </c>
       <c r="F235" t="n">
-        <v>22982</v>
+        <v>23208</v>
       </c>
     </row>
     <row r="236">
@@ -5141,10 +5141,10 @@
         <v>60.24</v>
       </c>
       <c r="E236" t="n">
-        <v>60.82</v>
+        <v>60.64</v>
       </c>
       <c r="F236" t="n">
-        <v>21411</v>
+        <v>21687</v>
       </c>
     </row>
     <row r="237">
@@ -5221,10 +5221,10 @@
         <v>56.73</v>
       </c>
       <c r="E240" t="n">
-        <v>58.03</v>
+        <v>58.2</v>
       </c>
       <c r="F240" t="n">
-        <v>28317</v>
+        <v>28894</v>
       </c>
     </row>
     <row r="241">
@@ -5244,7 +5244,7 @@
         <v>56.63</v>
       </c>
       <c r="F241" t="n">
-        <v>30854</v>
+        <v>31264</v>
       </c>
     </row>
     <row r="242">
@@ -5321,10 +5321,10 @@
         <v>54.24</v>
       </c>
       <c r="E245" t="n">
-        <v>55.07</v>
+        <v>55.14</v>
       </c>
       <c r="F245" t="n">
-        <v>31638</v>
+        <v>31917</v>
       </c>
     </row>
     <row r="246">
@@ -5341,10 +5341,10 @@
         <v>54.2</v>
       </c>
       <c r="E246" t="n">
-        <v>54.48</v>
+        <v>54.45</v>
       </c>
       <c r="F246" t="n">
-        <v>25828</v>
+        <v>26144</v>
       </c>
     </row>
     <row r="247">
@@ -5421,10 +5421,10 @@
         <v>54.95</v>
       </c>
       <c r="E250" t="n">
-        <v>56.51</v>
+        <v>56.4</v>
       </c>
       <c r="F250" t="n">
-        <v>24675</v>
+        <v>24914</v>
       </c>
     </row>
     <row r="251">
@@ -5441,10 +5441,10 @@
         <v>56.13</v>
       </c>
       <c r="E251" t="n">
-        <v>57.32</v>
+        <v>57.33</v>
       </c>
       <c r="F251" t="n">
-        <v>21410</v>
+        <v>21778</v>
       </c>
     </row>
     <row r="252">
@@ -5521,10 +5521,10 @@
         <v>58.89</v>
       </c>
       <c r="E255" t="n">
-        <v>59.28</v>
+        <v>59.03</v>
       </c>
       <c r="F255" t="n">
-        <v>23121</v>
+        <v>23391</v>
       </c>
     </row>
     <row r="256">
@@ -5541,10 +5541,10 @@
         <v>57.71</v>
       </c>
       <c r="E256" t="n">
-        <v>58.33</v>
+        <v>58.44</v>
       </c>
       <c r="F256" t="n">
-        <v>26663</v>
+        <v>26971</v>
       </c>
     </row>
     <row r="257">
@@ -5621,10 +5621,10 @@
         <v>50.38</v>
       </c>
       <c r="E260" t="n">
-        <v>51.35</v>
+        <v>50.95</v>
       </c>
       <c r="F260" t="n">
-        <v>51199</v>
+        <v>52807</v>
       </c>
     </row>
     <row r="261">
@@ -5641,10 +5641,10 @@
         <v>48.92</v>
       </c>
       <c r="E261" t="n">
-        <v>50.01</v>
+        <v>50.08</v>
       </c>
       <c r="F261" t="n">
-        <v>71739</v>
+        <v>72794</v>
       </c>
     </row>
     <row r="262">
@@ -5721,10 +5721,10 @@
         <v>49.67</v>
       </c>
       <c r="E265" t="n">
-        <v>49.95</v>
+        <v>50</v>
       </c>
       <c r="F265" t="n">
-        <v>42080</v>
+        <v>42678</v>
       </c>
     </row>
     <row r="266">
@@ -5741,10 +5741,10 @@
         <v>45.16</v>
       </c>
       <c r="E266" t="n">
-        <v>45.55</v>
+        <v>45.51</v>
       </c>
       <c r="F266" t="n">
-        <v>64437</v>
+        <v>65295</v>
       </c>
     </row>
     <row r="267">
@@ -5812,7 +5812,7 @@
         <v>43902</v>
       </c>
       <c r="B270" t="n">
-        <v>35.97</v>
+        <v>36.29</v>
       </c>
       <c r="C270" t="n">
         <v>36.45</v>
@@ -5824,7 +5824,7 @@
         <v>33.49</v>
       </c>
       <c r="F270" t="n">
-        <v>66181</v>
+        <v>64469</v>
       </c>
     </row>
     <row r="271">
@@ -6121,10 +6121,10 @@
         <v>26.12</v>
       </c>
       <c r="E285" t="n">
-        <v>30.29</v>
+        <v>29.96</v>
       </c>
       <c r="F285" t="n">
-        <v>210087</v>
+        <v>214756</v>
       </c>
     </row>
     <row r="286">
@@ -6135,16 +6135,16 @@
         <v>29.95</v>
       </c>
       <c r="C286" t="n">
-        <v>35.24</v>
+        <v>35.28</v>
       </c>
       <c r="D286" t="n">
         <v>28.9</v>
       </c>
       <c r="E286" t="n">
-        <v>34.72</v>
+        <v>35.16</v>
       </c>
       <c r="F286" t="n">
-        <v>275171</v>
+        <v>280402</v>
       </c>
     </row>
     <row r="287">
@@ -6221,10 +6221,10 @@
         <v>32.46</v>
       </c>
       <c r="E290" t="n">
-        <v>33.2</v>
+        <v>32.8</v>
       </c>
       <c r="F290" t="n">
-        <v>230614</v>
+        <v>236196</v>
       </c>
     </row>
     <row r="291">
@@ -6321,10 +6321,10 @@
         <v>29.42</v>
       </c>
       <c r="E295" t="n">
-        <v>30.65</v>
+        <v>30.59</v>
       </c>
       <c r="F295" t="n">
-        <v>146842</v>
+        <v>151526</v>
       </c>
     </row>
     <row r="296">
@@ -6341,10 +6341,10 @@
         <v>30.13</v>
       </c>
       <c r="E296" t="n">
-        <v>30.78</v>
+        <v>30.68</v>
       </c>
       <c r="F296" t="n">
-        <v>171223</v>
+        <v>174982</v>
       </c>
     </row>
     <row r="297">
@@ -6421,10 +6421,10 @@
         <v>23.38</v>
       </c>
       <c r="E300" t="n">
-        <v>24.74</v>
+        <v>24.73</v>
       </c>
       <c r="F300" t="n">
-        <v>213310</v>
+        <v>216653</v>
       </c>
     </row>
     <row r="301">
@@ -6441,10 +6441,10 @@
         <v>23.7</v>
       </c>
       <c r="E301" t="n">
-        <v>24.98</v>
+        <v>24.99</v>
       </c>
       <c r="F301" t="n">
-        <v>163124</v>
+        <v>166443</v>
       </c>
     </row>
     <row r="302">
@@ -6521,10 +6521,10 @@
         <v>24.33</v>
       </c>
       <c r="E305" t="n">
-        <v>26.83</v>
+        <v>26.85</v>
       </c>
       <c r="F305" t="n">
-        <v>224455</v>
+        <v>229615</v>
       </c>
     </row>
     <row r="306">
@@ -6541,10 +6541,10 @@
         <v>26.05</v>
       </c>
       <c r="E306" t="n">
-        <v>26.78</v>
+        <v>26.81</v>
       </c>
       <c r="F306" t="n">
-        <v>196748</v>
+        <v>199609</v>
       </c>
     </row>
     <row r="307">
@@ -6621,10 +6621,10 @@
         <v>29.4</v>
       </c>
       <c r="E310" t="n">
-        <v>29.48</v>
+        <v>29.65</v>
       </c>
       <c r="F310" t="n">
-        <v>225301</v>
+        <v>229585</v>
       </c>
     </row>
     <row r="311">
@@ -6641,10 +6641,10 @@
         <v>29.63</v>
       </c>
       <c r="E311" t="n">
-        <v>31.26</v>
+        <v>31.25</v>
       </c>
       <c r="F311" t="n">
-        <v>192233</v>
+        <v>195288</v>
       </c>
     </row>
     <row r="312">
@@ -6715,16 +6715,16 @@
         <v>29.73</v>
       </c>
       <c r="C315" t="n">
-        <v>31.65</v>
+        <v>31.75</v>
       </c>
       <c r="D315" t="n">
         <v>29.32</v>
       </c>
       <c r="E315" t="n">
-        <v>31.44</v>
+        <v>31.58</v>
       </c>
       <c r="F315" t="n">
-        <v>152193</v>
+        <v>156389</v>
       </c>
     </row>
     <row r="316">
@@ -6735,16 +6735,16 @@
         <v>31.58</v>
       </c>
       <c r="C316" t="n">
-        <v>32.96</v>
+        <v>33.06</v>
       </c>
       <c r="D316" t="n">
         <v>31.23</v>
       </c>
       <c r="E316" t="n">
-        <v>32.9</v>
+        <v>32.94</v>
       </c>
       <c r="F316" t="n">
-        <v>160121</v>
+        <v>163209</v>
       </c>
     </row>
     <row r="317">
@@ -6821,10 +6821,10 @@
         <v>35.92</v>
       </c>
       <c r="E320" t="n">
-        <v>36.38</v>
+        <v>36.3</v>
       </c>
       <c r="F320" t="n">
-        <v>157279</v>
+        <v>160329</v>
       </c>
     </row>
     <row r="321">
@@ -6841,10 +6841,10 @@
         <v>33.87</v>
       </c>
       <c r="E321" t="n">
-        <v>35.66</v>
+        <v>35.52</v>
       </c>
       <c r="F321" t="n">
-        <v>194062</v>
+        <v>198023</v>
       </c>
     </row>
     <row r="322">
@@ -6921,10 +6921,10 @@
         <v>34.37</v>
       </c>
       <c r="E325" t="n">
-        <v>35.89</v>
+        <v>35.98</v>
       </c>
       <c r="F325" t="n">
-        <v>208524</v>
+        <v>213086</v>
       </c>
     </row>
     <row r="326">
@@ -6941,10 +6941,10 @@
         <v>34.87</v>
       </c>
       <c r="E326" t="n">
-        <v>37.43</v>
+        <v>37.61</v>
       </c>
       <c r="F326" t="n">
-        <v>193664</v>
+        <v>198370</v>
       </c>
     </row>
     <row r="327">
@@ -7021,10 +7021,10 @@
         <v>39.05</v>
       </c>
       <c r="E330" t="n">
-        <v>39.78</v>
+        <v>39.92</v>
       </c>
       <c r="F330" t="n">
-        <v>158433</v>
+        <v>161661</v>
       </c>
     </row>
     <row r="331">
@@ -7041,10 +7041,10 @@
         <v>39.75</v>
       </c>
       <c r="E331" t="n">
-        <v>42.14</v>
+        <v>41.83</v>
       </c>
       <c r="F331" t="n">
-        <v>163467</v>
+        <v>167359</v>
       </c>
     </row>
     <row r="332">
@@ -7121,10 +7121,10 @@
         <v>37.96</v>
       </c>
       <c r="E335" t="n">
-        <v>38.36</v>
+        <v>38.41</v>
       </c>
       <c r="F335" t="n">
-        <v>221502</v>
+        <v>227925</v>
       </c>
     </row>
     <row r="336">
@@ -7141,10 +7141,10 @@
         <v>37.14</v>
       </c>
       <c r="E336" t="n">
-        <v>38.94</v>
+        <v>38.97</v>
       </c>
       <c r="F336" t="n">
-        <v>260674</v>
+        <v>263342</v>
       </c>
     </row>
     <row r="337">
@@ -7221,10 +7221,10 @@
         <v>40.05</v>
       </c>
       <c r="E340" t="n">
-        <v>41.37</v>
+        <v>41.33</v>
       </c>
       <c r="F340" t="n">
-        <v>161532</v>
+        <v>163774</v>
       </c>
     </row>
     <row r="341">
@@ -7241,10 +7241,10 @@
         <v>40.97</v>
       </c>
       <c r="E341" t="n">
-        <v>41.99</v>
+        <v>41.78</v>
       </c>
       <c r="F341" t="n">
-        <v>153177</v>
+        <v>156573</v>
       </c>
     </row>
     <row r="342">
@@ -7315,16 +7315,16 @@
         <v>40.45</v>
       </c>
       <c r="C345" t="n">
-        <v>41.51</v>
+        <v>41.59</v>
       </c>
       <c r="D345" t="n">
         <v>39.68</v>
       </c>
       <c r="E345" t="n">
-        <v>41.39</v>
+        <v>41.35</v>
       </c>
       <c r="F345" t="n">
-        <v>178413</v>
+        <v>181021</v>
       </c>
     </row>
     <row r="346">
@@ -7341,10 +7341,10 @@
         <v>40.25</v>
       </c>
       <c r="E346" t="n">
-        <v>40.58</v>
+        <v>40.57</v>
       </c>
       <c r="F346" t="n">
-        <v>157969</v>
+        <v>160433</v>
       </c>
     </row>
     <row r="347">
@@ -7421,10 +7421,10 @@
         <v>41.71</v>
       </c>
       <c r="E350" t="n">
-        <v>42.71</v>
+        <v>42.65</v>
       </c>
       <c r="F350" t="n">
-        <v>142409</v>
+        <v>144329</v>
       </c>
     </row>
     <row r="351">
@@ -7521,10 +7521,10 @@
         <v>41.99</v>
       </c>
       <c r="E355" t="n">
-        <v>42.32</v>
+        <v>42.35</v>
       </c>
       <c r="F355" t="n">
-        <v>133908</v>
+        <v>136451</v>
       </c>
     </row>
     <row r="356">
@@ -7541,10 +7541,10 @@
         <v>41.4</v>
       </c>
       <c r="E356" t="n">
-        <v>43.23</v>
+        <v>43.26</v>
       </c>
       <c r="F356" t="n">
-        <v>152491</v>
+        <v>154800</v>
       </c>
     </row>
     <row r="357">
@@ -7621,10 +7621,10 @@
         <v>43.19</v>
       </c>
       <c r="E360" t="n">
-        <v>43.36</v>
+        <v>43.28</v>
       </c>
       <c r="F360" t="n">
-        <v>99613</v>
+        <v>101544</v>
       </c>
     </row>
     <row r="361">
@@ -7641,10 +7641,10 @@
         <v>42.7</v>
       </c>
       <c r="E361" t="n">
-        <v>43.18</v>
+        <v>43.12</v>
       </c>
       <c r="F361" t="n">
-        <v>93740</v>
+        <v>95049</v>
       </c>
     </row>
     <row r="362">
@@ -7721,10 +7721,10 @@
         <v>43.42</v>
       </c>
       <c r="E365" t="n">
-        <v>43.82</v>
+        <v>43.53</v>
       </c>
       <c r="F365" t="n">
-        <v>109900</v>
+        <v>112495</v>
       </c>
     </row>
     <row r="366">
@@ -7741,10 +7741,10 @@
         <v>43.18</v>
       </c>
       <c r="E366" t="n">
-        <v>43.67</v>
+        <v>43.62</v>
       </c>
       <c r="F366" t="n">
-        <v>115737</v>
+        <v>117377</v>
       </c>
     </row>
     <row r="367">
@@ -7821,10 +7821,10 @@
         <v>41.95</v>
       </c>
       <c r="E370" t="n">
-        <v>43.43</v>
+        <v>43.56</v>
       </c>
       <c r="F370" t="n">
-        <v>113377</v>
+        <v>117072</v>
       </c>
     </row>
     <row r="371">
@@ -7841,10 +7841,10 @@
         <v>42.94</v>
       </c>
       <c r="E371" t="n">
-        <v>43.65</v>
+        <v>43.59</v>
       </c>
       <c r="F371" t="n">
-        <v>127155</v>
+        <v>128800</v>
       </c>
     </row>
     <row r="372">
@@ -7921,10 +7921,10 @@
         <v>44.96</v>
       </c>
       <c r="E375" t="n">
-        <v>45.28</v>
+        <v>45.13</v>
       </c>
       <c r="F375" t="n">
-        <v>120720</v>
+        <v>122044</v>
       </c>
     </row>
     <row r="376">
@@ -7941,10 +7941,10 @@
         <v>44.4</v>
       </c>
       <c r="E376" t="n">
-        <v>44.76</v>
+        <v>44.71</v>
       </c>
       <c r="F376" t="n">
-        <v>119541</v>
+        <v>120731</v>
       </c>
     </row>
     <row r="377">
@@ -8021,10 +8021,10 @@
         <v>45.07</v>
       </c>
       <c r="E380" t="n">
-        <v>45.3</v>
+        <v>45.24</v>
       </c>
       <c r="F380" t="n">
-        <v>90204</v>
+        <v>91702</v>
       </c>
     </row>
     <row r="381">
@@ -8041,10 +8041,10 @@
         <v>44.77</v>
       </c>
       <c r="E381" t="n">
-        <v>45.2</v>
+        <v>45.19</v>
       </c>
       <c r="F381" t="n">
-        <v>83793</v>
+        <v>85013</v>
       </c>
     </row>
     <row r="382">
@@ -8121,10 +8121,10 @@
         <v>44.46</v>
       </c>
       <c r="E385" t="n">
-        <v>45.36</v>
+        <v>45.27</v>
       </c>
       <c r="F385" t="n">
-        <v>86301</v>
+        <v>87294</v>
       </c>
     </row>
     <row r="386">
@@ -8141,10 +8141,10 @@
         <v>44.09</v>
       </c>
       <c r="E386" t="n">
-        <v>44.79</v>
+        <v>44.69</v>
       </c>
       <c r="F386" t="n">
-        <v>77659</v>
+        <v>78965</v>
       </c>
     </row>
     <row r="387">
@@ -8224,7 +8224,7 @@
         <v>45.59</v>
       </c>
       <c r="F390" t="n">
-        <v>95873</v>
+        <v>96916</v>
       </c>
     </row>
     <row r="391">
@@ -8241,10 +8241,10 @@
         <v>45.36</v>
       </c>
       <c r="E391" t="n">
-        <v>45.89</v>
+        <v>45.85</v>
       </c>
       <c r="F391" t="n">
-        <v>81058</v>
+        <v>81841</v>
       </c>
     </row>
     <row r="392">
@@ -8321,10 +8321,10 @@
         <v>43.27</v>
       </c>
       <c r="E395" t="n">
-        <v>44.09</v>
+        <v>44.07</v>
       </c>
       <c r="F395" t="n">
-        <v>157249</v>
+        <v>158723</v>
       </c>
     </row>
     <row r="396">
@@ -8338,13 +8338,13 @@
         <v>44.69</v>
       </c>
       <c r="D396" t="n">
-        <v>42.45</v>
+        <v>42.42</v>
       </c>
       <c r="E396" t="n">
-        <v>42.53</v>
+        <v>42.43</v>
       </c>
       <c r="F396" t="n">
-        <v>160902</v>
+        <v>162787</v>
       </c>
     </row>
     <row r="397">
@@ -8418,13 +8418,13 @@
         <v>41.23</v>
       </c>
       <c r="D400" t="n">
-        <v>40.02</v>
+        <v>39.96</v>
       </c>
       <c r="E400" t="n">
-        <v>40.07</v>
+        <v>39.97</v>
       </c>
       <c r="F400" t="n">
-        <v>147551</v>
+        <v>149451</v>
       </c>
     </row>
     <row r="401">
@@ -8441,10 +8441,10 @@
         <v>39.68</v>
       </c>
       <c r="E401" t="n">
-        <v>40.24</v>
+        <v>40.02</v>
       </c>
       <c r="F401" t="n">
-        <v>133943</v>
+        <v>135456</v>
       </c>
     </row>
     <row r="402">
@@ -8521,10 +8521,10 @@
         <v>41.89</v>
       </c>
       <c r="E405" t="n">
-        <v>43.67</v>
+        <v>43.58</v>
       </c>
       <c r="F405" t="n">
-        <v>141089</v>
+        <v>142611</v>
       </c>
     </row>
     <row r="406">
@@ -8541,10 +8541,10 @@
         <v>42.92</v>
       </c>
       <c r="E406" t="n">
-        <v>43.34</v>
+        <v>43.41</v>
       </c>
       <c r="F406" t="n">
-        <v>127380</v>
+        <v>129546</v>
       </c>
     </row>
     <row r="407">
@@ -8621,10 +8621,10 @@
         <v>41.68</v>
       </c>
       <c r="E410" t="n">
-        <v>42.27</v>
+        <v>42.16</v>
       </c>
       <c r="F410" t="n">
-        <v>132502</v>
+        <v>133961</v>
       </c>
     </row>
     <row r="411">
@@ -8641,10 +8641,10 @@
         <v>41.97</v>
       </c>
       <c r="E411" t="n">
-        <v>42.24</v>
+        <v>42.17</v>
       </c>
       <c r="F411" t="n">
-        <v>100264</v>
+        <v>102107</v>
       </c>
     </row>
     <row r="412">
@@ -8721,10 +8721,10 @@
         <v>39.98</v>
       </c>
       <c r="E415" t="n">
-        <v>40.93</v>
+        <v>40.75</v>
       </c>
       <c r="F415" t="n">
-        <v>155461</v>
+        <v>157712</v>
       </c>
     </row>
     <row r="416">
@@ -8741,10 +8741,10 @@
         <v>38.88</v>
       </c>
       <c r="E416" t="n">
-        <v>39.23</v>
+        <v>39.15</v>
       </c>
       <c r="F416" t="n">
-        <v>188336</v>
+        <v>190634</v>
       </c>
     </row>
     <row r="417">
@@ -8821,10 +8821,10 @@
         <v>42.02</v>
       </c>
       <c r="E420" t="n">
-        <v>43.54</v>
+        <v>43.52</v>
       </c>
       <c r="F420" t="n">
-        <v>110782</v>
+        <v>112342</v>
       </c>
     </row>
     <row r="421">
@@ -8841,10 +8841,10 @@
         <v>42.78</v>
       </c>
       <c r="E421" t="n">
-        <v>42.96</v>
+        <v>42.89</v>
       </c>
       <c r="F421" t="n">
-        <v>108274</v>
+        <v>109695</v>
       </c>
     </row>
     <row r="422">
@@ -8921,10 +8921,10 @@
         <v>41.79</v>
       </c>
       <c r="E425" t="n">
-        <v>43.38</v>
+        <v>43.26</v>
       </c>
       <c r="F425" t="n">
-        <v>146298</v>
+        <v>147757</v>
       </c>
     </row>
     <row r="426">
@@ -8941,10 +8941,10 @@
         <v>42.47</v>
       </c>
       <c r="E426" t="n">
-        <v>43.02</v>
+        <v>42.95</v>
       </c>
       <c r="F426" t="n">
-        <v>129338</v>
+        <v>130839</v>
       </c>
     </row>
     <row r="427">
@@ -9021,10 +9021,10 @@
         <v>41.72</v>
       </c>
       <c r="E430" t="n">
-        <v>42.71</v>
+        <v>42.59</v>
       </c>
       <c r="F430" t="n">
-        <v>108471</v>
+        <v>110171</v>
       </c>
     </row>
     <row r="431">
@@ -9041,10 +9041,10 @@
         <v>41.76</v>
       </c>
       <c r="E431" t="n">
-        <v>41.93</v>
+        <v>41.85</v>
       </c>
       <c r="F431" t="n">
-        <v>95688</v>
+        <v>97195</v>
       </c>
     </row>
     <row r="432">
@@ -9112,7 +9112,7 @@
         <v>44133</v>
       </c>
       <c r="B435" t="n">
-        <v>39.52</v>
+        <v>39.76</v>
       </c>
       <c r="C435" t="n">
         <v>39.97</v>
@@ -9124,7 +9124,7 @@
         <v>38.05</v>
       </c>
       <c r="F435" t="n">
-        <v>183949</v>
+        <v>179602</v>
       </c>
     </row>
     <row r="436">
@@ -9132,7 +9132,7 @@
         <v>44134</v>
       </c>
       <c r="B436" t="n">
-        <v>38.05</v>
+        <v>38.25</v>
       </c>
       <c r="C436" t="n">
         <v>38.72</v>
@@ -9144,7 +9144,7 @@
         <v>37.84</v>
       </c>
       <c r="F436" t="n">
-        <v>184633</v>
+        <v>181739</v>
       </c>
     </row>
     <row r="437">
@@ -9221,10 +9221,10 @@
         <v>40.42</v>
       </c>
       <c r="E440" t="n">
-        <v>40.82</v>
+        <v>40.68</v>
       </c>
       <c r="F440" t="n">
-        <v>155706</v>
+        <v>157779</v>
       </c>
     </row>
     <row r="441">
@@ -9241,10 +9241,10 @@
         <v>39.46</v>
       </c>
       <c r="E441" t="n">
-        <v>39.84</v>
+        <v>39.71</v>
       </c>
       <c r="F441" t="n">
-        <v>150078</v>
+        <v>151438</v>
       </c>
     </row>
     <row r="442">
@@ -9318,13 +9318,13 @@
         <v>44.59</v>
       </c>
       <c r="D445" t="n">
-        <v>43.42</v>
+        <v>43.35</v>
       </c>
       <c r="E445" t="n">
-        <v>43.49</v>
+        <v>43.38</v>
       </c>
       <c r="F445" t="n">
-        <v>144322</v>
+        <v>146964</v>
       </c>
     </row>
     <row r="446">
@@ -9338,13 +9338,13 @@
         <v>43.45</v>
       </c>
       <c r="D446" t="n">
-        <v>42.77</v>
+        <v>42.68</v>
       </c>
       <c r="E446" t="n">
-        <v>42.88</v>
+        <v>42.69</v>
       </c>
       <c r="F446" t="n">
-        <v>112789</v>
+        <v>114191</v>
       </c>
     </row>
     <row r="447">
@@ -9421,10 +9421,10 @@
         <v>43.87</v>
       </c>
       <c r="E450" t="n">
-        <v>44.44</v>
+        <v>44.21</v>
       </c>
       <c r="F450" t="n">
-        <v>111013</v>
+        <v>112468</v>
       </c>
     </row>
     <row r="451">
@@ -9441,10 +9441,10 @@
         <v>44.15</v>
       </c>
       <c r="E451" t="n">
-        <v>45.06</v>
+        <v>45.07</v>
       </c>
       <c r="F451" t="n">
-        <v>88612</v>
+        <v>90427</v>
       </c>
     </row>
     <row r="452">
@@ -9624,7 +9624,7 @@
         <v>48.65</v>
       </c>
       <c r="F460" t="n">
-        <v>119976</v>
+        <v>122403</v>
       </c>
     </row>
     <row r="461">
@@ -9641,10 +9641,10 @@
         <v>48.77</v>
       </c>
       <c r="E461" t="n">
-        <v>48.97</v>
+        <v>48.96</v>
       </c>
       <c r="F461" t="n">
-        <v>124413</v>
+        <v>125701</v>
       </c>
     </row>
     <row r="462">
@@ -9721,10 +9721,10 @@
         <v>48.79</v>
       </c>
       <c r="E465" t="n">
-        <v>50.26</v>
+        <v>50.25</v>
       </c>
       <c r="F465" t="n">
-        <v>130125</v>
+        <v>132386</v>
       </c>
     </row>
     <row r="466">
@@ -9741,10 +9741,10 @@
         <v>49.67</v>
       </c>
       <c r="E466" t="n">
-        <v>49.94</v>
+        <v>49.86</v>
       </c>
       <c r="F466" t="n">
-        <v>123293</v>
+        <v>124721</v>
       </c>
     </row>
     <row r="467">
@@ -9821,10 +9821,10 @@
         <v>51.06</v>
       </c>
       <c r="E470" t="n">
-        <v>51.55</v>
+        <v>51.46</v>
       </c>
       <c r="F470" t="n">
-        <v>100894</v>
+        <v>102867</v>
       </c>
     </row>
     <row r="471">
@@ -9841,10 +9841,10 @@
         <v>51.16</v>
       </c>
       <c r="E471" t="n">
-        <v>52.19</v>
+        <v>52.23</v>
       </c>
       <c r="F471" t="n">
-        <v>96861</v>
+        <v>98705</v>
       </c>
     </row>
     <row r="472">
@@ -10081,10 +10081,10 @@
         <v>53.88</v>
       </c>
       <c r="E483" t="n">
-        <v>54.45</v>
+        <v>54.34</v>
       </c>
       <c r="F483" t="n">
-        <v>140683</v>
+        <v>142258</v>
       </c>
     </row>
     <row r="484">
@@ -10095,16 +10095,16 @@
         <v>54.46</v>
       </c>
       <c r="C484" t="n">
-        <v>56.06</v>
+        <v>56.2</v>
       </c>
       <c r="D484" t="n">
         <v>54.3</v>
       </c>
       <c r="E484" t="n">
-        <v>56.02</v>
+        <v>56.11</v>
       </c>
       <c r="F484" t="n">
-        <v>151805</v>
+        <v>155413</v>
       </c>
     </row>
     <row r="485">
@@ -10181,10 +10181,10 @@
         <v>55.21</v>
       </c>
       <c r="E488" t="n">
-        <v>56.3</v>
+        <v>56.37</v>
       </c>
       <c r="F488" t="n">
-        <v>123090</v>
+        <v>125098</v>
       </c>
     </row>
     <row r="489">
@@ -10201,10 +10201,10 @@
         <v>54.63</v>
       </c>
       <c r="E489" t="n">
-        <v>54.94</v>
+        <v>54.75</v>
       </c>
       <c r="F489" t="n">
-        <v>133988</v>
+        <v>135898</v>
       </c>
     </row>
     <row r="490">
@@ -10281,10 +10281,10 @@
         <v>55.38</v>
       </c>
       <c r="E493" t="n">
-        <v>55.86</v>
+        <v>55.84</v>
       </c>
       <c r="F493" t="n">
-        <v>103188</v>
+        <v>104851</v>
       </c>
     </row>
     <row r="494">
@@ -10301,10 +10301,10 @@
         <v>54.38</v>
       </c>
       <c r="E494" t="n">
-        <v>55.08</v>
+        <v>54.88</v>
       </c>
       <c r="F494" t="n">
-        <v>133367</v>
+        <v>135622</v>
       </c>
     </row>
     <row r="495">
@@ -10378,13 +10378,13 @@
         <v>56.16</v>
       </c>
       <c r="D498" t="n">
-        <v>54.93</v>
+        <v>54.84</v>
       </c>
       <c r="E498" t="n">
-        <v>55</v>
+        <v>54.84</v>
       </c>
       <c r="F498" t="n">
-        <v>160473</v>
+        <v>162289</v>
       </c>
     </row>
     <row r="499">
@@ -10401,10 +10401,10 @@
         <v>54.84</v>
       </c>
       <c r="E499" t="n">
-        <v>55</v>
+        <v>54.93</v>
       </c>
       <c r="F499" t="n">
-        <v>160923</v>
+        <v>163671</v>
       </c>
     </row>
     <row r="500">
@@ -10481,10 +10481,10 @@
         <v>57.93</v>
       </c>
       <c r="E503" t="n">
-        <v>58.79</v>
+        <v>58.87</v>
       </c>
       <c r="F503" t="n">
-        <v>123567</v>
+        <v>125851</v>
       </c>
     </row>
     <row r="504">
@@ -10501,10 +10501,10 @@
         <v>58.87</v>
       </c>
       <c r="E504" t="n">
-        <v>59.31</v>
+        <v>59.41</v>
       </c>
       <c r="F504" t="n">
-        <v>118436</v>
+        <v>120954</v>
       </c>
     </row>
     <row r="505">
@@ -10578,13 +10578,13 @@
         <v>61.23</v>
       </c>
       <c r="D508" t="n">
-        <v>60.5</v>
+        <v>60.44</v>
       </c>
       <c r="E508" t="n">
-        <v>60.6</v>
+        <v>60.52</v>
       </c>
       <c r="F508" t="n">
-        <v>104511</v>
+        <v>107974</v>
       </c>
     </row>
     <row r="509">
@@ -10604,7 +10604,7 @@
         <v>62.22</v>
       </c>
       <c r="F509" t="n">
-        <v>123306</v>
+        <v>126905</v>
       </c>
     </row>
     <row r="510">
@@ -10681,10 +10681,10 @@
         <v>62.54</v>
       </c>
       <c r="E513" t="n">
-        <v>62.75</v>
+        <v>62.88</v>
       </c>
       <c r="F513" t="n">
-        <v>170306</v>
+        <v>173632</v>
       </c>
     </row>
     <row r="514">
@@ -10701,10 +10701,10 @@
         <v>61.42</v>
       </c>
       <c r="E514" t="n">
-        <v>61.95</v>
+        <v>61.97</v>
       </c>
       <c r="F514" t="n">
-        <v>181146</v>
+        <v>184306</v>
       </c>
     </row>
     <row r="515">
@@ -10781,10 +10781,10 @@
         <v>65.55</v>
       </c>
       <c r="E518" t="n">
-        <v>65.86</v>
+        <v>65.97</v>
       </c>
       <c r="F518" t="n">
-        <v>210726</v>
+        <v>215533</v>
       </c>
     </row>
     <row r="519">
@@ -10801,10 +10801,10 @@
         <v>64.13</v>
       </c>
       <c r="E519" t="n">
-        <v>64.25</v>
+        <v>64.27</v>
       </c>
       <c r="F519" t="n">
-        <v>234931</v>
+        <v>239274</v>
       </c>
     </row>
     <row r="520">
@@ -10881,10 +10881,10 @@
         <v>63.17</v>
       </c>
       <c r="E523" t="n">
-        <v>66.94</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="F523" t="n">
-        <v>225843</v>
+        <v>230530</v>
       </c>
     </row>
     <row r="524">
@@ -10895,16 +10895,16 @@
         <v>66.86</v>
       </c>
       <c r="C524" t="n">
-        <v>69.31999999999999</v>
+        <v>69.41</v>
       </c>
       <c r="D524" t="n">
         <v>66.43000000000001</v>
       </c>
       <c r="E524" t="n">
-        <v>69.28</v>
+        <v>69.25</v>
       </c>
       <c r="F524" t="n">
-        <v>249828</v>
+        <v>253026</v>
       </c>
     </row>
     <row r="525">
@@ -10981,10 +10981,10 @@
         <v>67.68000000000001</v>
       </c>
       <c r="E528" t="n">
-        <v>69.40000000000001</v>
+        <v>69.17</v>
       </c>
       <c r="F528" t="n">
-        <v>160838</v>
+        <v>163581</v>
       </c>
     </row>
     <row r="529">
@@ -11001,10 +11001,10 @@
         <v>68.66</v>
       </c>
       <c r="E529" t="n">
-        <v>68.88</v>
+        <v>68.81</v>
       </c>
       <c r="F529" t="n">
-        <v>148823</v>
+        <v>151042</v>
       </c>
     </row>
     <row r="530">
@@ -11072,7 +11072,7 @@
         <v>44273</v>
       </c>
       <c r="B533" t="n">
-        <v>67.48</v>
+        <v>67.47</v>
       </c>
       <c r="C533" t="n">
         <v>67.83</v>
@@ -11084,7 +11084,7 @@
         <v>62.5</v>
       </c>
       <c r="F533" t="n">
-        <v>212082</v>
+        <v>209835</v>
       </c>
     </row>
     <row r="534">
@@ -11092,7 +11092,7 @@
         <v>44274</v>
       </c>
       <c r="B534" t="n">
-        <v>62.78</v>
+        <v>63.02</v>
       </c>
       <c r="C534" t="n">
         <v>64.73</v>
@@ -11104,7 +11104,7 @@
         <v>64.31999999999999</v>
       </c>
       <c r="F534" t="n">
-        <v>228148</v>
+        <v>223529</v>
       </c>
     </row>
     <row r="535">
@@ -11172,10 +11172,10 @@
         <v>44280</v>
       </c>
       <c r="B538" t="n">
-        <v>63.95</v>
+        <v>63.89</v>
       </c>
       <c r="C538" t="n">
-        <v>64.01000000000001</v>
+        <v>63.9</v>
       </c>
       <c r="D538" t="n">
         <v>60.82</v>
@@ -11184,7 +11184,7 @@
         <v>61.47</v>
       </c>
       <c r="F538" t="n">
-        <v>206155</v>
+        <v>203253</v>
       </c>
     </row>
     <row r="539">
@@ -11192,19 +11192,19 @@
         <v>44281</v>
       </c>
       <c r="B539" t="n">
-        <v>61.47</v>
+        <v>62.45</v>
       </c>
       <c r="C539" t="n">
         <v>64.73</v>
       </c>
       <c r="D539" t="n">
-        <v>61.47</v>
+        <v>62.07</v>
       </c>
       <c r="E539" t="n">
         <v>64.19</v>
       </c>
       <c r="F539" t="n">
-        <v>171041</v>
+        <v>167422</v>
       </c>
     </row>
     <row r="540">
@@ -11284,7 +11284,7 @@
         <v>64.51000000000001</v>
       </c>
       <c r="F543" t="n">
-        <v>197783</v>
+        <v>201289</v>
       </c>
     </row>
     <row r="544">
@@ -11361,10 +11361,10 @@
         <v>62.18</v>
       </c>
       <c r="E547" t="n">
-        <v>63.07</v>
+        <v>63.04</v>
       </c>
       <c r="F547" t="n">
-        <v>146277</v>
+        <v>149186</v>
       </c>
     </row>
     <row r="548">
@@ -11381,10 +11381,10 @@
         <v>62.33</v>
       </c>
       <c r="E548" t="n">
-        <v>62.81</v>
+        <v>62.76</v>
       </c>
       <c r="F548" t="n">
-        <v>119219</v>
+        <v>121247</v>
       </c>
     </row>
     <row r="549">
@@ -11461,10 +11461,10 @@
         <v>65.65000000000001</v>
       </c>
       <c r="E552" t="n">
-        <v>66.5</v>
+        <v>66.45</v>
       </c>
       <c r="F552" t="n">
-        <v>133306</v>
+        <v>135521</v>
       </c>
     </row>
     <row r="553">
@@ -11481,10 +11481,10 @@
         <v>66.11</v>
       </c>
       <c r="E553" t="n">
-        <v>66.40000000000001</v>
+        <v>66.31999999999999</v>
       </c>
       <c r="F553" t="n">
-        <v>120895</v>
+        <v>122938</v>
       </c>
     </row>
     <row r="554">
@@ -11564,7 +11564,7 @@
         <v>64.95</v>
       </c>
       <c r="F557" t="n">
-        <v>140975</v>
+        <v>143350</v>
       </c>
     </row>
     <row r="558">
@@ -11581,10 +11581,10 @@
         <v>64.52</v>
       </c>
       <c r="E558" t="n">
-        <v>65.45</v>
+        <v>65.31999999999999</v>
       </c>
       <c r="F558" t="n">
-        <v>124432</v>
+        <v>126302</v>
       </c>
     </row>
     <row r="559">
@@ -11661,10 +11661,10 @@
         <v>66.56</v>
       </c>
       <c r="E562" t="n">
-        <v>67.86</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="F562" t="n">
-        <v>157092</v>
+        <v>160482</v>
       </c>
     </row>
     <row r="563">
@@ -11681,10 +11681,10 @@
         <v>66.17</v>
       </c>
       <c r="E563" t="n">
-        <v>66.56</v>
+        <v>66.53</v>
       </c>
       <c r="F563" t="n">
-        <v>145779</v>
+        <v>148372</v>
       </c>
     </row>
     <row r="564">
@@ -11761,10 +11761,10 @@
         <v>67.77</v>
       </c>
       <c r="E567" t="n">
-        <v>68.05</v>
+        <v>68.03</v>
       </c>
       <c r="F567" t="n">
-        <v>153533</v>
+        <v>155507</v>
       </c>
     </row>
     <row r="568">
@@ -11784,7 +11784,7 @@
         <v>68.03</v>
       </c>
       <c r="F568" t="n">
-        <v>136012</v>
+        <v>139157</v>
       </c>
     </row>
     <row r="569">
@@ -11861,10 +11861,10 @@
         <v>66.34</v>
       </c>
       <c r="E572" t="n">
-        <v>66.83</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="F572" t="n">
-        <v>180093</v>
+        <v>182316</v>
       </c>
     </row>
     <row r="573">
@@ -11875,16 +11875,16 @@
         <v>66.81</v>
       </c>
       <c r="C573" t="n">
-        <v>68.52</v>
+        <v>68.63</v>
       </c>
       <c r="D573" t="n">
         <v>66.36</v>
       </c>
       <c r="E573" t="n">
-        <v>68.45</v>
+        <v>68.52</v>
       </c>
       <c r="F573" t="n">
-        <v>139950</v>
+        <v>142226</v>
       </c>
     </row>
     <row r="574">
@@ -11958,13 +11958,13 @@
         <v>67.02</v>
       </c>
       <c r="D577" t="n">
-        <v>64.73</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="E577" t="n">
-        <v>64.98999999999999</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="F577" t="n">
-        <v>164782</v>
+        <v>168733</v>
       </c>
     </row>
     <row r="578">
@@ -11981,10 +11981,10 @@
         <v>64.48</v>
       </c>
       <c r="E578" t="n">
-        <v>66.58</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="F578" t="n">
-        <v>153693</v>
+        <v>156317</v>
       </c>
     </row>
     <row r="579">
@@ -12055,16 +12055,16 @@
         <v>68.58</v>
       </c>
       <c r="C582" t="n">
-        <v>69.18000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="D582" t="n">
         <v>67.89</v>
       </c>
       <c r="E582" t="n">
-        <v>69.05</v>
+        <v>69.12</v>
       </c>
       <c r="F582" t="n">
-        <v>119490</v>
+        <v>122427</v>
       </c>
     </row>
     <row r="583">
@@ -12081,10 +12081,10 @@
         <v>68.48999999999999</v>
       </c>
       <c r="E583" t="n">
-        <v>68.89</v>
+        <v>68.88</v>
       </c>
       <c r="F583" t="n">
-        <v>119218</v>
+        <v>121324</v>
       </c>
     </row>
     <row r="584">
@@ -12161,10 +12161,10 @@
         <v>70.5</v>
       </c>
       <c r="E587" t="n">
-        <v>71.20999999999999</v>
+        <v>71.22</v>
       </c>
       <c r="F587" t="n">
-        <v>126247</v>
+        <v>128649</v>
       </c>
     </row>
     <row r="588">
@@ -12181,10 +12181,10 @@
         <v>70.58</v>
       </c>
       <c r="E588" t="n">
-        <v>71.47</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="F588" t="n">
-        <v>113793</v>
+        <v>117041</v>
       </c>
     </row>
     <row r="589">
@@ -12261,10 +12261,10 @@
         <v>70.66</v>
       </c>
       <c r="E592" t="n">
-        <v>72.09</v>
+        <v>71.95</v>
       </c>
       <c r="F592" t="n">
-        <v>146487</v>
+        <v>148450</v>
       </c>
     </row>
     <row r="593">
@@ -12284,7 +12284,7 @@
         <v>72.23999999999999</v>
       </c>
       <c r="F593" t="n">
-        <v>140128</v>
+        <v>142367</v>
       </c>
     </row>
     <row r="594">
@@ -12361,10 +12361,10 @@
         <v>71.41</v>
       </c>
       <c r="E597" t="n">
-        <v>72.45</v>
+        <v>72.44</v>
       </c>
       <c r="F597" t="n">
-        <v>175025</v>
+        <v>178094</v>
       </c>
     </row>
     <row r="598">
@@ -12381,10 +12381,10 @@
         <v>71.55</v>
       </c>
       <c r="E598" t="n">
-        <v>72.76000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="F598" t="n">
-        <v>147859</v>
+        <v>151345</v>
       </c>
     </row>
     <row r="599">
@@ -12461,10 +12461,10 @@
         <v>73.83</v>
       </c>
       <c r="E602" t="n">
-        <v>74.79000000000001</v>
+        <v>74.81</v>
       </c>
       <c r="F602" t="n">
-        <v>84577</v>
+        <v>85692</v>
       </c>
     </row>
     <row r="603">
@@ -12481,10 +12481,10 @@
         <v>74.14</v>
       </c>
       <c r="E603" t="n">
-        <v>75.27</v>
+        <v>75.28</v>
       </c>
       <c r="F603" t="n">
-        <v>77990</v>
+        <v>79112</v>
       </c>
     </row>
     <row r="604">
@@ -12561,10 +12561,10 @@
         <v>74.36</v>
       </c>
       <c r="E607" t="n">
-        <v>75.33</v>
+        <v>75.34</v>
       </c>
       <c r="F607" t="n">
-        <v>134296</v>
+        <v>135699</v>
       </c>
     </row>
     <row r="608">
@@ -12581,10 +12581,10 @@
         <v>75</v>
       </c>
       <c r="E608" t="n">
-        <v>76.02</v>
+        <v>75.81999999999999</v>
       </c>
       <c r="F608" t="n">
-        <v>102316</v>
+        <v>104256</v>
       </c>
     </row>
     <row r="609">
@@ -12655,16 +12655,16 @@
         <v>72.97</v>
       </c>
       <c r="C612" t="n">
-        <v>73.97</v>
+        <v>74.02</v>
       </c>
       <c r="D612" t="n">
         <v>71.73999999999999</v>
       </c>
       <c r="E612" t="n">
-        <v>73.92</v>
+        <v>73.95999999999999</v>
       </c>
       <c r="F612" t="n">
-        <v>136419</v>
+        <v>138030</v>
       </c>
     </row>
     <row r="613">
@@ -12681,10 +12681,10 @@
         <v>73.38</v>
       </c>
       <c r="E613" t="n">
-        <v>75.15000000000001</v>
+        <v>75.14</v>
       </c>
       <c r="F613" t="n">
-        <v>95892</v>
+        <v>96988</v>
       </c>
     </row>
     <row r="614">
@@ -12761,10 +12761,10 @@
         <v>72.70999999999999</v>
       </c>
       <c r="E617" t="n">
-        <v>72.79000000000001</v>
+        <v>72.72</v>
       </c>
       <c r="F617" t="n">
-        <v>132350</v>
+        <v>134216</v>
       </c>
     </row>
     <row r="618">
@@ -12781,10 +12781,10 @@
         <v>71.88</v>
       </c>
       <c r="E618" t="n">
-        <v>72.81</v>
+        <v>72.64</v>
       </c>
       <c r="F618" t="n">
-        <v>108307</v>
+        <v>110158</v>
       </c>
     </row>
     <row r="619">
@@ -12864,7 +12864,7 @@
         <v>73.01000000000001</v>
       </c>
       <c r="F622" t="n">
-        <v>113951</v>
+        <v>115159</v>
       </c>
     </row>
     <row r="623">
@@ -12875,16 +12875,16 @@
         <v>72.98</v>
       </c>
       <c r="C623" t="n">
-        <v>73.52</v>
+        <v>73.56999999999999</v>
       </c>
       <c r="D623" t="n">
         <v>72.70999999999999</v>
       </c>
       <c r="E623" t="n">
-        <v>73.44</v>
+        <v>73.5</v>
       </c>
       <c r="F623" t="n">
-        <v>83411</v>
+        <v>84579</v>
       </c>
     </row>
     <row r="624">
@@ -12961,10 +12961,10 @@
         <v>73.59999999999999</v>
       </c>
       <c r="E627" t="n">
-        <v>74.97</v>
+        <v>74.75</v>
       </c>
       <c r="F627" t="n">
-        <v>79720</v>
+        <v>81467</v>
       </c>
     </row>
     <row r="628">
@@ -12981,10 +12981,10 @@
         <v>74.26000000000001</v>
       </c>
       <c r="E628" t="n">
-        <v>74.98999999999999</v>
+        <v>74.95999999999999</v>
       </c>
       <c r="F628" t="n">
-        <v>83101</v>
+        <v>84253</v>
       </c>
     </row>
     <row r="629">
@@ -13061,10 +13061,10 @@
         <v>69.56</v>
       </c>
       <c r="E632" t="n">
-        <v>71.16</v>
+        <v>71</v>
       </c>
       <c r="F632" t="n">
-        <v>107034</v>
+        <v>108267</v>
       </c>
     </row>
     <row r="633">
@@ -13078,13 +13078,13 @@
         <v>72.22</v>
       </c>
       <c r="D633" t="n">
-        <v>70.12</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="E633" t="n">
-        <v>70.34999999999999</v>
+        <v>70.08</v>
       </c>
       <c r="F633" t="n">
-        <v>111453</v>
+        <v>113105</v>
       </c>
     </row>
     <row r="634">
@@ -13161,10 +13161,10 @@
         <v>70.41</v>
       </c>
       <c r="E637" t="n">
-        <v>70.90000000000001</v>
+        <v>70.86</v>
       </c>
       <c r="F637" t="n">
-        <v>95219</v>
+        <v>96203</v>
       </c>
     </row>
     <row r="638">
@@ -13181,10 +13181,10 @@
         <v>69.73999999999999</v>
       </c>
       <c r="E638" t="n">
-        <v>69.92</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="F638" t="n">
-        <v>93960</v>
+        <v>95696</v>
       </c>
     </row>
     <row r="639">
@@ -13261,10 +13261,10 @@
         <v>65.2</v>
       </c>
       <c r="E642" t="n">
-        <v>66.51000000000001</v>
+        <v>66.23</v>
       </c>
       <c r="F642" t="n">
-        <v>185678</v>
+        <v>187712</v>
       </c>
     </row>
     <row r="643">
@@ -13278,13 +13278,13 @@
         <v>66.54000000000001</v>
       </c>
       <c r="D643" t="n">
-        <v>64.61</v>
+        <v>64.53</v>
       </c>
       <c r="E643" t="n">
-        <v>64.62</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="F643" t="n">
-        <v>137258</v>
+        <v>138989</v>
       </c>
     </row>
     <row r="644">
@@ -13361,10 +13361,10 @@
         <v>69.73999999999999</v>
       </c>
       <c r="E647" t="n">
-        <v>70.56</v>
+        <v>70.45999999999999</v>
       </c>
       <c r="F647" t="n">
-        <v>113839</v>
+        <v>115965</v>
       </c>
     </row>
     <row r="648">
@@ -13381,10 +13381,10 @@
         <v>70.16</v>
       </c>
       <c r="E648" t="n">
-        <v>71.59999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="F648" t="n">
-        <v>99158</v>
+        <v>100455</v>
       </c>
     </row>
     <row r="649">
@@ -13461,10 +13461,10 @@
         <v>70.75</v>
       </c>
       <c r="E652" t="n">
-        <v>72.56999999999999</v>
+        <v>72.61</v>
       </c>
       <c r="F652" t="n">
-        <v>103772</v>
+        <v>105073</v>
       </c>
     </row>
     <row r="653">
@@ -13481,10 +13481,10 @@
         <v>72.20999999999999</v>
       </c>
       <c r="E653" t="n">
-        <v>72.36</v>
+        <v>72.20999999999999</v>
       </c>
       <c r="F653" t="n">
-        <v>110684</v>
+        <v>111688</v>
       </c>
     </row>
     <row r="654">
@@ -13561,10 +13561,10 @@
         <v>70.54000000000001</v>
       </c>
       <c r="E657" t="n">
-        <v>70.95</v>
+        <v>70.84</v>
       </c>
       <c r="F657" t="n">
-        <v>136836</v>
+        <v>138553</v>
       </c>
     </row>
     <row r="658">
@@ -13581,10 +13581,10 @@
         <v>70.59</v>
       </c>
       <c r="E658" t="n">
-        <v>72.44</v>
+        <v>72.51000000000001</v>
       </c>
       <c r="F658" t="n">
-        <v>106315</v>
+        <v>107925</v>
       </c>
     </row>
     <row r="659">
@@ -13661,10 +13661,10 @@
         <v>74.02</v>
       </c>
       <c r="E662" t="n">
-        <v>75.17</v>
+        <v>75.09</v>
       </c>
       <c r="F662" t="n">
-        <v>134873</v>
+        <v>136265</v>
       </c>
     </row>
     <row r="663">
@@ -13681,10 +13681,10 @@
         <v>74.06999999999999</v>
       </c>
       <c r="E663" t="n">
-        <v>74.79000000000001</v>
+        <v>74.67</v>
       </c>
       <c r="F663" t="n">
-        <v>129577</v>
+        <v>131243</v>
       </c>
     </row>
     <row r="664">
@@ -13764,7 +13764,7 @@
         <v>76.45</v>
       </c>
       <c r="F667" t="n">
-        <v>102612</v>
+        <v>104066</v>
       </c>
     </row>
     <row r="668">
@@ -13781,10 +13781,10 @@
         <v>76.09</v>
       </c>
       <c r="E668" t="n">
-        <v>77.15000000000001</v>
+        <v>77.13</v>
       </c>
       <c r="F668" t="n">
-        <v>93448</v>
+        <v>94529</v>
       </c>
     </row>
     <row r="669">
@@ -13861,10 +13861,10 @@
         <v>76.37</v>
       </c>
       <c r="E672" t="n">
-        <v>78.13</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="F672" t="n">
-        <v>180155</v>
+        <v>181989</v>
       </c>
     </row>
     <row r="673">
@@ -13881,10 +13881,10 @@
         <v>77.38</v>
       </c>
       <c r="E673" t="n">
-        <v>78.98999999999999</v>
+        <v>78.93000000000001</v>
       </c>
       <c r="F673" t="n">
-        <v>149729</v>
+        <v>151482</v>
       </c>
     </row>
     <row r="674">
@@ -13961,10 +13961,10 @@
         <v>78.78</v>
       </c>
       <c r="E677" t="n">
-        <v>82.16</v>
+        <v>82.08</v>
       </c>
       <c r="F677" t="n">
-        <v>151677</v>
+        <v>153620</v>
       </c>
     </row>
     <row r="678">
@@ -13981,10 +13981,10 @@
         <v>81.63</v>
       </c>
       <c r="E678" t="n">
-        <v>82.17</v>
+        <v>82.22</v>
       </c>
       <c r="F678" t="n">
-        <v>147722</v>
+        <v>149526</v>
       </c>
     </row>
     <row r="679">
@@ -14061,10 +14061,10 @@
         <v>82.76000000000001</v>
       </c>
       <c r="E682" t="n">
-        <v>83.69</v>
+        <v>83.67</v>
       </c>
       <c r="F682" t="n">
-        <v>120650</v>
+        <v>122153</v>
       </c>
     </row>
     <row r="683">
@@ -14081,10 +14081,10 @@
         <v>83.68000000000001</v>
       </c>
       <c r="E683" t="n">
-        <v>84.23</v>
+        <v>84.33</v>
       </c>
       <c r="F683" t="n">
-        <v>114060</v>
+        <v>116437</v>
       </c>
     </row>
     <row r="684">
@@ -14161,10 +14161,10 @@
         <v>82.73</v>
       </c>
       <c r="E687" t="n">
-        <v>84.15000000000001</v>
+        <v>84.09</v>
       </c>
       <c r="F687" t="n">
-        <v>121250</v>
+        <v>122966</v>
       </c>
     </row>
     <row r="688">
@@ -14175,16 +14175,16 @@
         <v>83.81999999999999</v>
       </c>
       <c r="C688" t="n">
-        <v>84.97</v>
+        <v>85.08</v>
       </c>
       <c r="D688" t="n">
         <v>83.18000000000001</v>
       </c>
       <c r="E688" t="n">
-        <v>84.97</v>
+        <v>84.83</v>
       </c>
       <c r="F688" t="n">
-        <v>111475</v>
+        <v>113449</v>
       </c>
     </row>
     <row r="689">
@@ -14261,10 +14261,10 @@
         <v>81.48</v>
       </c>
       <c r="E692" t="n">
-        <v>83.83</v>
+        <v>83.78</v>
       </c>
       <c r="F692" t="n">
-        <v>164605</v>
+        <v>167007</v>
       </c>
     </row>
     <row r="693">
@@ -14281,10 +14281,10 @@
         <v>82.39</v>
       </c>
       <c r="E693" t="n">
-        <v>83.55</v>
+        <v>83.41</v>
       </c>
       <c r="F693" t="n">
-        <v>132228</v>
+        <v>133535</v>
       </c>
     </row>
     <row r="694">
@@ -14352,7 +14352,7 @@
         <v>44504</v>
       </c>
       <c r="B697" t="n">
-        <v>81.12</v>
+        <v>80.83</v>
       </c>
       <c r="C697" t="n">
         <v>84.08</v>
@@ -14364,7 +14364,7 @@
         <v>80.54000000000001</v>
       </c>
       <c r="F697" t="n">
-        <v>171378</v>
+        <v>168783</v>
       </c>
     </row>
     <row r="698">
@@ -14372,7 +14372,7 @@
         <v>44505</v>
       </c>
       <c r="B698" t="n">
-        <v>80.95</v>
+        <v>81.04000000000001</v>
       </c>
       <c r="C698" t="n">
         <v>82.72</v>
@@ -14384,7 +14384,7 @@
         <v>81.93000000000001</v>
       </c>
       <c r="F698" t="n">
-        <v>166390</v>
+        <v>163172</v>
       </c>
     </row>
     <row r="699">
@@ -14461,10 +14461,10 @@
         <v>81.06</v>
       </c>
       <c r="E702" t="n">
-        <v>81.91</v>
+        <v>81.92</v>
       </c>
       <c r="F702" t="n">
-        <v>159955</v>
+        <v>161511</v>
       </c>
     </row>
     <row r="703">
@@ -14481,10 +14481,10 @@
         <v>80.63</v>
       </c>
       <c r="E703" t="n">
-        <v>81.41</v>
+        <v>81.29000000000001</v>
       </c>
       <c r="F703" t="n">
-        <v>133196</v>
+        <v>134507</v>
       </c>
     </row>
     <row r="704">
@@ -14561,10 +14561,10 @@
         <v>78.55</v>
       </c>
       <c r="E707" t="n">
-        <v>80.42</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="F707" t="n">
-        <v>131123</v>
+        <v>132952</v>
       </c>
     </row>
     <row r="708">
@@ -14581,10 +14581,10 @@
         <v>77.41</v>
       </c>
       <c r="E708" t="n">
-        <v>77.76000000000001</v>
+        <v>77.77</v>
       </c>
       <c r="F708" t="n">
-        <v>175625</v>
+        <v>177513</v>
       </c>
     </row>
     <row r="709">
@@ -14761,10 +14761,10 @@
         <v>65.67</v>
       </c>
       <c r="E717" t="n">
-        <v>69.94</v>
+        <v>70.36</v>
       </c>
       <c r="F717" t="n">
-        <v>237353</v>
+        <v>240359</v>
       </c>
     </row>
     <row r="718">
@@ -14781,10 +14781,10 @@
         <v>69.09999999999999</v>
       </c>
       <c r="E718" t="n">
-        <v>69.73</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="F718" t="n">
-        <v>205214</v>
+        <v>208893</v>
       </c>
     </row>
     <row r="719">
@@ -14858,13 +14858,13 @@
         <v>76.55</v>
       </c>
       <c r="D722" t="n">
-        <v>73.78</v>
+        <v>73.70999999999999</v>
       </c>
       <c r="E722" t="n">
-        <v>73.79000000000001</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="F722" t="n">
-        <v>140659</v>
+        <v>142264</v>
       </c>
     </row>
     <row r="723">
@@ -14881,10 +14881,10 @@
         <v>73.67</v>
       </c>
       <c r="E723" t="n">
-        <v>75.23</v>
+        <v>75.16</v>
       </c>
       <c r="F723" t="n">
-        <v>151698</v>
+        <v>153301</v>
       </c>
     </row>
     <row r="724">
@@ -14961,10 +14961,10 @@
         <v>73.88</v>
       </c>
       <c r="E727" t="n">
-        <v>74.63</v>
+        <v>74.48999999999999</v>
       </c>
       <c r="F727" t="n">
-        <v>140474</v>
+        <v>142563</v>
       </c>
     </row>
     <row r="728">
@@ -14981,10 +14981,10 @@
         <v>72.63</v>
       </c>
       <c r="E728" t="n">
-        <v>73.15000000000001</v>
+        <v>72.88</v>
       </c>
       <c r="F728" t="n">
-        <v>152160</v>
+        <v>154875</v>
       </c>
     </row>
     <row r="729">
@@ -15061,10 +15061,10 @@
         <v>74.72</v>
       </c>
       <c r="E732" t="n">
-        <v>76.63</v>
+        <v>76.52</v>
       </c>
       <c r="F732" t="n">
-        <v>100583</v>
+        <v>102802</v>
       </c>
     </row>
     <row r="733">
@@ -15161,10 +15161,10 @@
         <v>78.33</v>
       </c>
       <c r="E737" t="n">
-        <v>78.97</v>
+        <v>78.86</v>
       </c>
       <c r="F737" t="n">
-        <v>103669</v>
+        <v>105405</v>
       </c>
     </row>
     <row r="738">
@@ -15261,10 +15261,10 @@
         <v>79.36</v>
       </c>
       <c r="E742" t="n">
-        <v>81.65000000000001</v>
+        <v>81.70999999999999</v>
       </c>
       <c r="F742" t="n">
-        <v>185800</v>
+        <v>187943</v>
       </c>
     </row>
     <row r="743">
@@ -15281,10 +15281,10 @@
         <v>81.12</v>
       </c>
       <c r="E743" t="n">
-        <v>81.59999999999999</v>
+        <v>81.48</v>
       </c>
       <c r="F743" t="n">
-        <v>158852</v>
+        <v>160491</v>
       </c>
     </row>
     <row r="744">
@@ -15361,10 +15361,10 @@
         <v>83.34999999999999</v>
       </c>
       <c r="E747" t="n">
-        <v>83.45</v>
+        <v>83.61</v>
       </c>
       <c r="F747" t="n">
-        <v>145171</v>
+        <v>147527</v>
       </c>
     </row>
     <row r="748">
@@ -15375,16 +15375,16 @@
         <v>83.68000000000001</v>
       </c>
       <c r="C748" t="n">
-        <v>85.97</v>
+        <v>85.98999999999999</v>
       </c>
       <c r="D748" t="n">
         <v>83.53</v>
       </c>
       <c r="E748" t="n">
-        <v>85.91</v>
+        <v>85.77</v>
       </c>
       <c r="F748" t="n">
-        <v>171152</v>
+        <v>173518</v>
       </c>
     </row>
     <row r="749">
@@ -15458,13 +15458,13 @@
         <v>88.8</v>
       </c>
       <c r="D752" t="n">
-        <v>86.56999999999999</v>
+        <v>86.38</v>
       </c>
       <c r="E752" t="n">
-        <v>86.7</v>
+        <v>86.58</v>
       </c>
       <c r="F752" t="n">
-        <v>162890</v>
+        <v>169439</v>
       </c>
     </row>
     <row r="753">
@@ -15481,10 +15481,10 @@
         <v>85.02</v>
       </c>
       <c r="E753" t="n">
-        <v>86.98</v>
+        <v>86.92</v>
       </c>
       <c r="F753" t="n">
-        <v>223066</v>
+        <v>225683</v>
       </c>
     </row>
     <row r="754">
@@ -15561,10 +15561,10 @@
         <v>87.7</v>
       </c>
       <c r="E757" t="n">
-        <v>88.40000000000001</v>
+        <v>88.63</v>
       </c>
       <c r="F757" t="n">
-        <v>270152</v>
+        <v>275711</v>
       </c>
     </row>
     <row r="758">
@@ -15581,10 +15581,10 @@
         <v>88</v>
       </c>
       <c r="E758" t="n">
-        <v>88.73</v>
+        <v>88.81999999999999</v>
       </c>
       <c r="F758" t="n">
-        <v>275262</v>
+        <v>278896</v>
       </c>
     </row>
     <row r="759">
@@ -15655,16 +15655,16 @@
         <v>88.63</v>
       </c>
       <c r="C762" t="n">
-        <v>90.73999999999999</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="D762" t="n">
         <v>87.59999999999999</v>
       </c>
       <c r="E762" t="n">
-        <v>90.45999999999999</v>
+        <v>90.51000000000001</v>
       </c>
       <c r="F762" t="n">
-        <v>163057</v>
+        <v>168353</v>
       </c>
     </row>
     <row r="763">
@@ -15681,10 +15681,10 @@
         <v>90.67</v>
       </c>
       <c r="E763" t="n">
-        <v>92.54000000000001</v>
+        <v>92.14</v>
       </c>
       <c r="F763" t="n">
-        <v>177219</v>
+        <v>180147</v>
       </c>
     </row>
     <row r="764">
@@ -15761,10 +15761,10 @@
         <v>90.09999999999999</v>
       </c>
       <c r="E767" t="n">
-        <v>90.66</v>
+        <v>90.54000000000001</v>
       </c>
       <c r="F767" t="n">
-        <v>183590</v>
+        <v>186180</v>
       </c>
     </row>
     <row r="768">
@@ -15781,10 +15781,10 @@
         <v>89.66</v>
       </c>
       <c r="E768" t="n">
-        <v>93.81</v>
+        <v>93.8</v>
       </c>
       <c r="F768" t="n">
-        <v>189880</v>
+        <v>194729</v>
       </c>
     </row>
     <row r="769">
@@ -15861,10 +15861,10 @@
         <v>90.34999999999999</v>
       </c>
       <c r="E772" t="n">
-        <v>91.18000000000001</v>
+        <v>91.16</v>
       </c>
       <c r="F772" t="n">
-        <v>209775</v>
+        <v>212213</v>
       </c>
     </row>
     <row r="773">
@@ -15875,7 +15875,7 @@
         <v>90.76000000000001</v>
       </c>
       <c r="C773" t="n">
-        <v>92.15000000000001</v>
+        <v>92.28</v>
       </c>
       <c r="D773" t="n">
         <v>88.64</v>
@@ -15884,7 +15884,7 @@
         <v>91.81</v>
       </c>
       <c r="F773" t="n">
-        <v>190175</v>
+        <v>194995</v>
       </c>
     </row>
     <row r="774">
@@ -15961,10 +15961,10 @@
         <v>93.94</v>
       </c>
       <c r="E777" t="n">
-        <v>95.61</v>
+        <v>95.41</v>
       </c>
       <c r="F777" t="n">
-        <v>309076</v>
+        <v>313423</v>
       </c>
     </row>
     <row r="778">
@@ -15981,10 +15981,10 @@
         <v>92.55</v>
       </c>
       <c r="E778" t="n">
-        <v>94.69</v>
+        <v>94.23</v>
       </c>
       <c r="F778" t="n">
-        <v>233541</v>
+        <v>237786</v>
       </c>
     </row>
     <row r="779">
@@ -16061,10 +16061,10 @@
         <v>108.17</v>
       </c>
       <c r="E782" t="n">
-        <v>109.72</v>
+        <v>109.27</v>
       </c>
       <c r="F782" t="n">
-        <v>231064</v>
+        <v>233799</v>
       </c>
     </row>
     <row r="783">
@@ -16081,10 +16081,10 @@
         <v>108.47</v>
       </c>
       <c r="E783" t="n">
-        <v>117.14</v>
+        <v>116.7</v>
       </c>
       <c r="F783" t="n">
-        <v>204618</v>
+        <v>210974</v>
       </c>
     </row>
     <row r="784">
@@ -16161,10 +16161,10 @@
         <v>107.05</v>
       </c>
       <c r="E787" t="n">
-        <v>107.97</v>
+        <v>107.11</v>
       </c>
       <c r="F787" t="n">
-        <v>170481</v>
+        <v>173653</v>
       </c>
     </row>
     <row r="788">
@@ -16181,10 +16181,10 @@
         <v>104.96</v>
       </c>
       <c r="E788" t="n">
-        <v>110.51</v>
+        <v>110.14</v>
       </c>
       <c r="F788" t="n">
-        <v>154891</v>
+        <v>157669</v>
       </c>
     </row>
     <row r="789">
@@ -16252,19 +16252,19 @@
         <v>44637</v>
       </c>
       <c r="B792" t="n">
-        <v>96.98</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="C792" t="n">
         <v>105.3</v>
       </c>
       <c r="D792" t="n">
-        <v>96.11</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="E792" t="n">
         <v>104.46</v>
       </c>
       <c r="F792" t="n">
-        <v>176604</v>
+        <v>172578</v>
       </c>
     </row>
     <row r="793">
@@ -16272,7 +16272,7 @@
         <v>44638</v>
       </c>
       <c r="B793" t="n">
-        <v>104.55</v>
+        <v>105.16</v>
       </c>
       <c r="C793" t="n">
         <v>107.23</v>
@@ -16284,7 +16284,7 @@
         <v>105.63</v>
       </c>
       <c r="F793" t="n">
-        <v>158531</v>
+        <v>155067</v>
       </c>
     </row>
     <row r="794">
@@ -16352,7 +16352,7 @@
         <v>44644</v>
       </c>
       <c r="B797" t="n">
-        <v>118.08</v>
+        <v>119.49</v>
       </c>
       <c r="C797" t="n">
         <v>120.04</v>
@@ -16364,7 +16364,7 @@
         <v>114.47</v>
       </c>
       <c r="F797" t="n">
-        <v>215337</v>
+        <v>206598</v>
       </c>
     </row>
     <row r="798">
@@ -16372,7 +16372,7 @@
         <v>44645</v>
       </c>
       <c r="B798" t="n">
-        <v>115.3</v>
+        <v>114.52</v>
       </c>
       <c r="C798" t="n">
         <v>117.69</v>
@@ -16384,7 +16384,7 @@
         <v>115.94</v>
       </c>
       <c r="F798" t="n">
-        <v>195807</v>
+        <v>189095</v>
       </c>
     </row>
     <row r="799">
@@ -16461,10 +16461,10 @@
         <v>103.71</v>
       </c>
       <c r="E802" t="n">
-        <v>104.6</v>
+        <v>104.99</v>
       </c>
       <c r="F802" t="n">
-        <v>217472</v>
+        <v>220967</v>
       </c>
     </row>
     <row r="803">
@@ -16481,10 +16481,10 @@
         <v>101.94</v>
       </c>
       <c r="E803" t="n">
-        <v>104.13</v>
+        <v>103.88</v>
       </c>
       <c r="F803" t="n">
-        <v>179677</v>
+        <v>181758</v>
       </c>
     </row>
     <row r="804">
@@ -16561,10 +16561,10 @@
         <v>98.2</v>
       </c>
       <c r="E807" t="n">
-        <v>100.94</v>
+        <v>100.96</v>
       </c>
       <c r="F807" t="n">
-        <v>183922</v>
+        <v>186163</v>
       </c>
     </row>
     <row r="808">
@@ -16581,10 +16581,10 @@
         <v>99.28</v>
       </c>
       <c r="E808" t="n">
-        <v>102.16</v>
+        <v>101.81</v>
       </c>
       <c r="F808" t="n">
-        <v>159821</v>
+        <v>162819</v>
       </c>
     </row>
     <row r="809">
@@ -16661,10 +16661,10 @@
         <v>106.14</v>
       </c>
       <c r="E812" t="n">
-        <v>110.56</v>
+        <v>110.62</v>
       </c>
       <c r="F812" t="n">
-        <v>156524</v>
+        <v>159785</v>
       </c>
     </row>
     <row r="813">
@@ -16741,10 +16741,10 @@
         <v>106.38</v>
       </c>
       <c r="E816" t="n">
-        <v>107.93</v>
+        <v>108</v>
       </c>
       <c r="F816" t="n">
-        <v>184241</v>
+        <v>188001</v>
       </c>
     </row>
     <row r="817">
@@ -16758,13 +16758,13 @@
         <v>108.41</v>
       </c>
       <c r="D817" t="n">
-        <v>105.44</v>
+        <v>105.05</v>
       </c>
       <c r="E817" t="n">
-        <v>105.6</v>
+        <v>105.7</v>
       </c>
       <c r="F817" t="n">
-        <v>162032</v>
+        <v>165632</v>
       </c>
     </row>
     <row r="818">
@@ -16841,10 +16841,10 @@
         <v>102.74</v>
       </c>
       <c r="E821" t="n">
-        <v>107.25</v>
+        <v>106.8</v>
       </c>
       <c r="F821" t="n">
-        <v>167676</v>
+        <v>170514</v>
       </c>
     </row>
     <row r="822">
@@ -16861,10 +16861,10 @@
         <v>105.92</v>
       </c>
       <c r="E822" t="n">
-        <v>106.38</v>
+        <v>106.06</v>
       </c>
       <c r="F822" t="n">
-        <v>182972</v>
+        <v>186051</v>
       </c>
     </row>
     <row r="823">
@@ -16941,10 +16941,10 @@
         <v>108.66</v>
       </c>
       <c r="E826" t="n">
-        <v>110.3</v>
+        <v>110.4</v>
       </c>
       <c r="F826" t="n">
-        <v>197687</v>
+        <v>201234</v>
       </c>
     </row>
     <row r="827">
@@ -16961,10 +16961,10 @@
         <v>109.21</v>
       </c>
       <c r="E827" t="n">
-        <v>112.44</v>
+        <v>112.22</v>
       </c>
       <c r="F827" t="n">
-        <v>203469</v>
+        <v>207851</v>
       </c>
     </row>
     <row r="828">
@@ -17041,10 +17041,10 @@
         <v>103.97</v>
       </c>
       <c r="E831" t="n">
-        <v>107.38</v>
+        <v>106.86</v>
       </c>
       <c r="F831" t="n">
-        <v>240901</v>
+        <v>243371</v>
       </c>
     </row>
     <row r="832">
@@ -17061,10 +17061,10 @@
         <v>106.88</v>
       </c>
       <c r="E832" t="n">
-        <v>110.4</v>
+        <v>109.76</v>
       </c>
       <c r="F832" t="n">
-        <v>190398</v>
+        <v>193013</v>
       </c>
     </row>
     <row r="833">
@@ -17141,10 +17141,10 @@
         <v>104.22</v>
       </c>
       <c r="E836" t="n">
-        <v>109.59</v>
+        <v>109.5</v>
       </c>
       <c r="F836" t="n">
-        <v>247278</v>
+        <v>250583</v>
       </c>
     </row>
     <row r="837">
@@ -17161,10 +17161,10 @@
         <v>108.65</v>
       </c>
       <c r="E837" t="n">
-        <v>110.87</v>
+        <v>110.3</v>
       </c>
       <c r="F837" t="n">
-        <v>198948</v>
+        <v>202895</v>
       </c>
     </row>
     <row r="838">
@@ -17241,10 +17241,10 @@
         <v>110.83</v>
       </c>
       <c r="E841" t="n">
-        <v>114</v>
+        <v>114.15</v>
       </c>
       <c r="F841" t="n">
-        <v>171535</v>
+        <v>175003</v>
       </c>
     </row>
     <row r="842">
@@ -17261,10 +17261,10 @@
         <v>113.01</v>
       </c>
       <c r="E842" t="n">
-        <v>115.42</v>
+        <v>115.01</v>
       </c>
       <c r="F842" t="n">
-        <v>210750</v>
+        <v>213418</v>
       </c>
     </row>
     <row r="843">
@@ -17335,16 +17335,16 @@
         <v>113.88</v>
       </c>
       <c r="C846" t="n">
-        <v>117.57</v>
+        <v>117.74</v>
       </c>
       <c r="D846" t="n">
         <v>111.85</v>
       </c>
       <c r="E846" t="n">
-        <v>117.26</v>
+        <v>117.31</v>
       </c>
       <c r="F846" t="n">
-        <v>137013</v>
+        <v>138282</v>
       </c>
     </row>
     <row r="847">
@@ -17355,16 +17355,16 @@
         <v>117.37</v>
       </c>
       <c r="C847" t="n">
-        <v>120.57</v>
+        <v>120.6</v>
       </c>
       <c r="D847" t="n">
         <v>115.28</v>
       </c>
       <c r="E847" t="n">
-        <v>120.41</v>
+        <v>120.23</v>
       </c>
       <c r="F847" t="n">
-        <v>90339</v>
+        <v>91626</v>
       </c>
     </row>
     <row r="848">
@@ -17441,10 +17441,10 @@
         <v>121.23</v>
       </c>
       <c r="E851" t="n">
-        <v>121.71</v>
+        <v>121.41</v>
       </c>
       <c r="F851" t="n">
-        <v>174232</v>
+        <v>176648</v>
       </c>
     </row>
     <row r="852">
@@ -17461,10 +17461,10 @@
         <v>118.31</v>
       </c>
       <c r="E852" t="n">
-        <v>120.29</v>
+        <v>120.02</v>
       </c>
       <c r="F852" t="n">
-        <v>190410</v>
+        <v>192334</v>
       </c>
     </row>
     <row r="853">
@@ -17541,10 +17541,10 @@
         <v>113.72</v>
       </c>
       <c r="E856" t="n">
-        <v>117.15</v>
+        <v>116.92</v>
       </c>
       <c r="F856" t="n">
-        <v>228931</v>
+        <v>231324</v>
       </c>
     </row>
     <row r="857">
@@ -17561,10 +17561,10 @@
         <v>109.77</v>
       </c>
       <c r="E857" t="n">
-        <v>111.29</v>
+        <v>111.27</v>
       </c>
       <c r="F857" t="n">
-        <v>233588</v>
+        <v>236868</v>
       </c>
     </row>
     <row r="858">
@@ -17641,10 +17641,10 @@
         <v>105.25</v>
       </c>
       <c r="E861" t="n">
-        <v>106.29</v>
+        <v>106.13</v>
       </c>
       <c r="F861" t="n">
-        <v>233040</v>
+        <v>234952</v>
       </c>
     </row>
     <row r="862">
@@ -17661,10 +17661,10 @@
         <v>105.78</v>
       </c>
       <c r="E862" t="n">
-        <v>109.13</v>
+        <v>108.33</v>
       </c>
       <c r="F862" t="n">
-        <v>202836</v>
+        <v>205227</v>
       </c>
     </row>
     <row r="863">
@@ -17741,10 +17741,10 @@
         <v>107.7</v>
       </c>
       <c r="E866" t="n">
-        <v>108.69</v>
+        <v>108.43</v>
       </c>
       <c r="F866" t="n">
-        <v>208599</v>
+        <v>212070</v>
       </c>
     </row>
     <row r="867">
@@ -17761,10 +17761,10 @@
         <v>107.32</v>
       </c>
       <c r="E867" t="n">
-        <v>110.56</v>
+        <v>110.43</v>
       </c>
       <c r="F867" t="n">
-        <v>209195</v>
+        <v>210630</v>
       </c>
     </row>
     <row r="868">
@@ -17841,10 +17841,10 @@
         <v>97.11</v>
       </c>
       <c r="E871" t="n">
-        <v>102.75</v>
+        <v>102.32</v>
       </c>
       <c r="F871" t="n">
-        <v>221862</v>
+        <v>224620</v>
       </c>
     </row>
     <row r="872">
@@ -17861,10 +17861,10 @@
         <v>102.16</v>
       </c>
       <c r="E872" t="n">
-        <v>105.32</v>
+        <v>105.2</v>
       </c>
       <c r="F872" t="n">
-        <v>235167</v>
+        <v>237030</v>
       </c>
     </row>
     <row r="873">
@@ -17941,10 +17941,10 @@
         <v>92.42</v>
       </c>
       <c r="E876" t="n">
-        <v>97.17</v>
+        <v>97.12</v>
       </c>
       <c r="F876" t="n">
-        <v>215919</v>
+        <v>217836</v>
       </c>
     </row>
     <row r="877">
@@ -17961,10 +17961,10 @@
         <v>95.59</v>
       </c>
       <c r="E877" t="n">
-        <v>98.34999999999999</v>
+        <v>97.98</v>
       </c>
       <c r="F877" t="n">
-        <v>200270</v>
+        <v>203134</v>
       </c>
     </row>
     <row r="878">
@@ -18041,10 +18041,10 @@
         <v>97.86</v>
       </c>
       <c r="E881" t="n">
-        <v>100.04</v>
+        <v>99.93000000000001</v>
       </c>
       <c r="F881" t="n">
-        <v>227231</v>
+        <v>229298</v>
       </c>
     </row>
     <row r="882">
@@ -18061,10 +18061,10 @@
         <v>97.90000000000001</v>
       </c>
       <c r="E882" t="n">
-        <v>98.67</v>
+        <v>98.98999999999999</v>
       </c>
       <c r="F882" t="n">
-        <v>222921</v>
+        <v>226135</v>
       </c>
     </row>
     <row r="883">
@@ -18141,10 +18141,10 @@
         <v>100.74</v>
       </c>
       <c r="E886" t="n">
-        <v>101.93</v>
+        <v>101.99</v>
       </c>
       <c r="F886" t="n">
-        <v>130398</v>
+        <v>132446</v>
       </c>
     </row>
     <row r="887">
@@ -18161,10 +18161,10 @@
         <v>101.27</v>
       </c>
       <c r="E887" t="n">
-        <v>103.21</v>
+        <v>103.1</v>
       </c>
       <c r="F887" t="n">
-        <v>112179</v>
+        <v>113461</v>
       </c>
     </row>
     <row r="888">
@@ -18238,13 +18238,13 @@
         <v>97.17</v>
       </c>
       <c r="D891" t="n">
-        <v>92.73</v>
+        <v>92.5</v>
       </c>
       <c r="E891" t="n">
-        <v>93.38</v>
+        <v>92.52</v>
       </c>
       <c r="F891" t="n">
-        <v>160629</v>
+        <v>162676</v>
       </c>
     </row>
     <row r="892">
@@ -18261,10 +18261,10 @@
         <v>92.15000000000001</v>
       </c>
       <c r="E892" t="n">
-        <v>93.69</v>
+        <v>93.51000000000001</v>
       </c>
       <c r="F892" t="n">
-        <v>155701</v>
+        <v>157322</v>
       </c>
     </row>
     <row r="893">
@@ -18341,10 +18341,10 @@
         <v>96.08</v>
       </c>
       <c r="E896" t="n">
-        <v>98.66</v>
+        <v>98.31</v>
       </c>
       <c r="F896" t="n">
-        <v>139272</v>
+        <v>140818</v>
       </c>
     </row>
     <row r="897">
@@ -18361,10 +18361,10 @@
         <v>96.26000000000001</v>
       </c>
       <c r="E897" t="n">
-        <v>97.3</v>
+        <v>96.89</v>
       </c>
       <c r="F897" t="n">
-        <v>144235</v>
+        <v>145858</v>
       </c>
     </row>
     <row r="898">
@@ -18441,10 +18441,10 @@
         <v>92.55</v>
       </c>
       <c r="E901" t="n">
-        <v>95.93000000000001</v>
+        <v>95.56</v>
       </c>
       <c r="F901" t="n">
-        <v>122235</v>
+        <v>123861</v>
       </c>
     </row>
     <row r="902">
@@ -18461,10 +18461,10 @@
         <v>93.7</v>
       </c>
       <c r="E902" t="n">
-        <v>95.52</v>
+        <v>95.08</v>
       </c>
       <c r="F902" t="n">
-        <v>125387</v>
+        <v>126696</v>
       </c>
     </row>
     <row r="903">
@@ -18541,10 +18541,10 @@
         <v>98.23</v>
       </c>
       <c r="E906" t="n">
-        <v>99.05</v>
+        <v>98.68000000000001</v>
       </c>
       <c r="F906" t="n">
-        <v>114289</v>
+        <v>115830</v>
       </c>
     </row>
     <row r="907">
@@ -18561,10 +18561,10 @@
         <v>96.92</v>
       </c>
       <c r="E907" t="n">
-        <v>98.70999999999999</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="F907" t="n">
-        <v>127109</v>
+        <v>128357</v>
       </c>
     </row>
     <row r="908">
@@ -18641,10 +18641,10 @@
         <v>91.58</v>
       </c>
       <c r="E911" t="n">
-        <v>91.75</v>
+        <v>91.59</v>
       </c>
       <c r="F911" t="n">
-        <v>171383</v>
+        <v>172611</v>
       </c>
     </row>
     <row r="912">
@@ -18661,10 +18661,10 @@
         <v>92.41</v>
       </c>
       <c r="E912" t="n">
-        <v>92.68000000000001</v>
+        <v>92.83</v>
       </c>
       <c r="F912" t="n">
-        <v>162523</v>
+        <v>164349</v>
       </c>
     </row>
     <row r="913">
@@ -18741,10 +18741,10 @@
         <v>86.86</v>
       </c>
       <c r="E916" t="n">
-        <v>88.03</v>
+        <v>87.73999999999999</v>
       </c>
       <c r="F916" t="n">
-        <v>174104</v>
+        <v>175783</v>
       </c>
     </row>
     <row r="917">
@@ -18761,10 +18761,10 @@
         <v>88.09</v>
       </c>
       <c r="E917" t="n">
-        <v>91.90000000000001</v>
+        <v>91.42</v>
       </c>
       <c r="F917" t="n">
-        <v>137562</v>
+        <v>139210</v>
       </c>
     </row>
     <row r="918">
@@ -18841,10 +18841,10 @@
         <v>89.39</v>
       </c>
       <c r="E921" t="n">
-        <v>90.08</v>
+        <v>89.78</v>
       </c>
       <c r="F921" t="n">
-        <v>177670</v>
+        <v>179533</v>
       </c>
     </row>
     <row r="922">
@@ -18861,10 +18861,10 @@
         <v>89.37</v>
       </c>
       <c r="E922" t="n">
-        <v>90.58</v>
+        <v>90.36</v>
       </c>
       <c r="F922" t="n">
-        <v>175462</v>
+        <v>177056</v>
       </c>
     </row>
     <row r="923">
@@ -18941,10 +18941,10 @@
         <v>88.38</v>
       </c>
       <c r="E926" t="n">
-        <v>89.53</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="F926" t="n">
-        <v>167346</v>
+        <v>169282</v>
       </c>
     </row>
     <row r="927">
@@ -18961,10 +18961,10 @@
         <v>84.61</v>
       </c>
       <c r="E927" t="n">
-        <v>85.41</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="F927" t="n">
-        <v>157358</v>
+        <v>159709</v>
       </c>
     </row>
     <row r="928">
@@ -19041,10 +19041,10 @@
         <v>85.98</v>
       </c>
       <c r="E931" t="n">
-        <v>87.20999999999999</v>
+        <v>87.22</v>
       </c>
       <c r="F931" t="n">
-        <v>182346</v>
+        <v>184095</v>
       </c>
     </row>
     <row r="932">
@@ -19061,10 +19061,10 @@
         <v>84.73999999999999</v>
       </c>
       <c r="E932" t="n">
-        <v>85.06999999999999</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="F932" t="n">
-        <v>172540</v>
+        <v>174184</v>
       </c>
     </row>
     <row r="933">
@@ -19141,10 +19141,10 @@
         <v>92.09</v>
       </c>
       <c r="E936" t="n">
-        <v>94.31999999999999</v>
+        <v>94.16</v>
       </c>
       <c r="F936" t="n">
-        <v>134269</v>
+        <v>136157</v>
       </c>
     </row>
     <row r="937">
@@ -19161,10 +19161,10 @@
         <v>93.25</v>
       </c>
       <c r="E937" t="n">
-        <v>96.95</v>
+        <v>97.59</v>
       </c>
       <c r="F937" t="n">
-        <v>158303</v>
+        <v>161145</v>
       </c>
     </row>
     <row r="938">
@@ -19241,10 +19241,10 @@
         <v>90.18000000000001</v>
       </c>
       <c r="E941" t="n">
-        <v>93.61</v>
+        <v>93.67</v>
       </c>
       <c r="F941" t="n">
-        <v>187899</v>
+        <v>189909</v>
       </c>
     </row>
     <row r="942">
@@ -19261,10 +19261,10 @@
         <v>90.34</v>
       </c>
       <c r="E942" t="n">
-        <v>90.84999999999999</v>
+        <v>90.66</v>
       </c>
       <c r="F942" t="n">
-        <v>184164</v>
+        <v>186342</v>
       </c>
     </row>
     <row r="943">
@@ -19341,10 +19341,10 @@
         <v>90.34</v>
       </c>
       <c r="E946" t="n">
-        <v>91</v>
+        <v>91.11</v>
       </c>
       <c r="F946" t="n">
-        <v>169394</v>
+        <v>172151</v>
       </c>
     </row>
     <row r="947">
@@ -19361,10 +19361,10 @@
         <v>89.40000000000001</v>
       </c>
       <c r="E947" t="n">
-        <v>91.7</v>
+        <v>91.58</v>
       </c>
       <c r="F947" t="n">
-        <v>168937</v>
+        <v>170499</v>
       </c>
     </row>
     <row r="948">
@@ -19441,10 +19441,10 @@
         <v>93.06999999999999</v>
       </c>
       <c r="E951" t="n">
-        <v>94.91</v>
+        <v>94.45999999999999</v>
       </c>
       <c r="F951" t="n">
-        <v>130846</v>
+        <v>135151</v>
       </c>
     </row>
     <row r="952">
@@ -19461,10 +19461,10 @@
         <v>92.81999999999999</v>
       </c>
       <c r="E952" t="n">
-        <v>93.81</v>
+        <v>93.95</v>
       </c>
       <c r="F952" t="n">
-        <v>133960</v>
+        <v>135363</v>
       </c>
     </row>
     <row r="953">
@@ -19532,7 +19532,7 @@
         <v>44868</v>
       </c>
       <c r="B956" t="n">
-        <v>94.81</v>
+        <v>94.84</v>
       </c>
       <c r="C956" t="n">
         <v>95.45</v>
@@ -19544,7 +19544,7 @@
         <v>93.92</v>
       </c>
       <c r="F956" t="n">
-        <v>143503</v>
+        <v>141621</v>
       </c>
     </row>
     <row r="957">
@@ -19552,19 +19552,19 @@
         <v>44869</v>
       </c>
       <c r="B957" t="n">
-        <v>93.98</v>
+        <v>93.94</v>
       </c>
       <c r="C957" t="n">
         <v>98.23999999999999</v>
       </c>
       <c r="D957" t="n">
-        <v>93.76000000000001</v>
+        <v>93.94</v>
       </c>
       <c r="E957" t="n">
         <v>98.01000000000001</v>
       </c>
       <c r="F957" t="n">
-        <v>182009</v>
+        <v>179958</v>
       </c>
     </row>
     <row r="958">
@@ -19641,10 +19641,10 @@
         <v>90.97</v>
       </c>
       <c r="E961" t="n">
-        <v>92.69</v>
+        <v>92.47</v>
       </c>
       <c r="F961" t="n">
-        <v>168690</v>
+        <v>170823</v>
       </c>
     </row>
     <row r="962">
@@ -19661,10 +19661,10 @@
         <v>92.79000000000001</v>
       </c>
       <c r="E962" t="n">
-        <v>95.04000000000001</v>
+        <v>94.95999999999999</v>
       </c>
       <c r="F962" t="n">
-        <v>163940</v>
+        <v>165782</v>
       </c>
     </row>
     <row r="963">
@@ -19741,10 +19741,10 @@
         <v>88.72</v>
       </c>
       <c r="E966" t="n">
-        <v>89.28</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="F966" t="n">
-        <v>157265</v>
+        <v>159560</v>
       </c>
     </row>
     <row r="967">
@@ -19761,10 +19761,10 @@
         <v>85.41</v>
       </c>
       <c r="E967" t="n">
-        <v>87.45</v>
+        <v>87.5</v>
       </c>
       <c r="F967" t="n">
-        <v>160818</v>
+        <v>162655</v>
       </c>
     </row>
     <row r="968">
@@ -19941,10 +19941,10 @@
         <v>86.26000000000001</v>
       </c>
       <c r="E976" t="n">
-        <v>86.84</v>
+        <v>86.98</v>
       </c>
       <c r="F976" t="n">
-        <v>135345</v>
+        <v>136930</v>
       </c>
     </row>
     <row r="977">
@@ -19961,10 +19961,10 @@
         <v>85.17</v>
       </c>
       <c r="E977" t="n">
-        <v>85.76000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="F977" t="n">
-        <v>135815</v>
+        <v>137359</v>
       </c>
     </row>
     <row r="978">
@@ -20041,10 +20041,10 @@
         <v>75.92</v>
       </c>
       <c r="E981" t="n">
-        <v>76.27</v>
+        <v>76.61</v>
       </c>
       <c r="F981" t="n">
-        <v>165742</v>
+        <v>167594</v>
       </c>
     </row>
     <row r="982">
@@ -20061,10 +20061,10 @@
         <v>75.34999999999999</v>
       </c>
       <c r="E982" t="n">
-        <v>76.76000000000001</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="F982" t="n">
-        <v>151706</v>
+        <v>153224</v>
       </c>
     </row>
     <row r="983">
@@ -20141,10 +20141,10 @@
         <v>80.86</v>
       </c>
       <c r="E986" t="n">
-        <v>81.39</v>
+        <v>81.54000000000001</v>
       </c>
       <c r="F986" t="n">
-        <v>149384</v>
+        <v>151489</v>
       </c>
     </row>
     <row r="987">
@@ -20161,10 +20161,10 @@
         <v>78.61</v>
       </c>
       <c r="E987" t="n">
-        <v>79.36</v>
+        <v>79.44</v>
       </c>
       <c r="F987" t="n">
-        <v>149990</v>
+        <v>151197</v>
       </c>
     </row>
     <row r="988">
@@ -20241,10 +20241,10 @@
         <v>81.28</v>
       </c>
       <c r="E991" t="n">
-        <v>82.18000000000001</v>
+        <v>82.20999999999999</v>
       </c>
       <c r="F991" t="n">
-        <v>94348</v>
+        <v>95617</v>
       </c>
     </row>
     <row r="992">
@@ -20321,10 +20321,10 @@
         <v>81.81999999999999</v>
       </c>
       <c r="E995" t="n">
-        <v>83.68000000000001</v>
+        <v>83.63</v>
       </c>
       <c r="F995" t="n">
-        <v>109380</v>
+        <v>110699</v>
       </c>
     </row>
     <row r="996">
@@ -20401,10 +20401,10 @@
         <v>77.63</v>
       </c>
       <c r="E999" t="n">
-        <v>78.68000000000001</v>
+        <v>78.8</v>
       </c>
       <c r="F999" t="n">
-        <v>149266</v>
+        <v>150672</v>
       </c>
     </row>
     <row r="1000">
@@ -20424,7 +20424,7 @@
         <v>78.51000000000001</v>
       </c>
       <c r="F1000" t="n">
-        <v>147017</v>
+        <v>148389</v>
       </c>
     </row>
     <row r="1001">
@@ -20501,10 +20501,10 @@
         <v>82.43000000000001</v>
       </c>
       <c r="E1004" t="n">
-        <v>83.91</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="F1004" t="n">
-        <v>141086</v>
+        <v>142735</v>
       </c>
     </row>
     <row r="1005">
@@ -20515,16 +20515,16 @@
         <v>83.91</v>
       </c>
       <c r="C1005" t="n">
-        <v>85.55</v>
+        <v>85.61</v>
       </c>
       <c r="D1005" t="n">
         <v>83.55</v>
       </c>
       <c r="E1005" t="n">
-        <v>85.48</v>
+        <v>85.47</v>
       </c>
       <c r="F1005" t="n">
-        <v>129757</v>
+        <v>131152</v>
       </c>
     </row>
     <row r="1006">
@@ -20601,10 +20601,10 @@
         <v>83.95999999999999</v>
       </c>
       <c r="E1009" t="n">
-        <v>86.31999999999999</v>
+        <v>86.34</v>
       </c>
       <c r="F1009" t="n">
-        <v>142583</v>
+        <v>144410</v>
       </c>
     </row>
     <row r="1010">
@@ -20621,10 +20621,10 @@
         <v>85.69</v>
       </c>
       <c r="E1010" t="n">
-        <v>87.75</v>
+        <v>87.59</v>
       </c>
       <c r="F1010" t="n">
-        <v>123973</v>
+        <v>125225</v>
       </c>
     </row>
     <row r="1011">
@@ -20701,10 +20701,10 @@
         <v>85.75</v>
       </c>
       <c r="E1014" t="n">
-        <v>87.31</v>
+        <v>87.29000000000001</v>
       </c>
       <c r="F1014" t="n">
-        <v>95077</v>
+        <v>96051</v>
       </c>
     </row>
     <row r="1015">
@@ -20721,10 +20721,10 @@
         <v>85.48</v>
       </c>
       <c r="E1015" t="n">
-        <v>86.04000000000001</v>
+        <v>86.01000000000001</v>
       </c>
       <c r="F1015" t="n">
-        <v>109841</v>
+        <v>110922</v>
       </c>
     </row>
     <row r="1016">
@@ -20801,10 +20801,10 @@
         <v>81.2</v>
       </c>
       <c r="E1019" t="n">
-        <v>81.98</v>
+        <v>82.12</v>
       </c>
       <c r="F1019" t="n">
-        <v>146732</v>
+        <v>150704</v>
       </c>
     </row>
     <row r="1020">
@@ -20818,13 +20818,13 @@
         <v>84.11</v>
       </c>
       <c r="D1020" t="n">
+        <v>79.53</v>
+      </c>
+      <c r="E1020" t="n">
         <v>79.62</v>
       </c>
-      <c r="E1020" t="n">
-        <v>79.64</v>
-      </c>
       <c r="F1020" t="n">
-        <v>161681</v>
+        <v>163093</v>
       </c>
     </row>
     <row r="1021">
@@ -20901,10 +20901,10 @@
         <v>82.86</v>
       </c>
       <c r="E1024" t="n">
-        <v>83.88</v>
+        <v>83.95</v>
       </c>
       <c r="F1024" t="n">
-        <v>142722</v>
+        <v>144061</v>
       </c>
     </row>
     <row r="1025">
@@ -20921,10 +20921,10 @@
         <v>83.66</v>
       </c>
       <c r="E1025" t="n">
-        <v>86.29000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="F1025" t="n">
-        <v>155562</v>
+        <v>156718</v>
       </c>
     </row>
     <row r="1026">
@@ -20998,13 +20998,13 @@
         <v>85.90000000000001</v>
       </c>
       <c r="D1029" t="n">
-        <v>84.31999999999999</v>
+        <v>84.28</v>
       </c>
       <c r="E1029" t="n">
-        <v>84.37</v>
+        <v>84.31</v>
       </c>
       <c r="F1029" t="n">
-        <v>128382</v>
+        <v>129946</v>
       </c>
     </row>
     <row r="1030">
@@ -21021,10 +21021,10 @@
         <v>81.55</v>
       </c>
       <c r="E1030" t="n">
-        <v>82.68000000000001</v>
+        <v>82.72</v>
       </c>
       <c r="F1030" t="n">
-        <v>141607</v>
+        <v>142763</v>
       </c>
     </row>
     <row r="1031">
@@ -21101,10 +21101,10 @@
         <v>80.27</v>
       </c>
       <c r="E1034" t="n">
-        <v>82.12</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="F1034" t="n">
-        <v>107083</v>
+        <v>108091</v>
       </c>
     </row>
     <row r="1035">
@@ -21121,10 +21121,10 @@
         <v>80.7</v>
       </c>
       <c r="E1035" t="n">
-        <v>82.94</v>
+        <v>82.77</v>
       </c>
       <c r="F1035" t="n">
-        <v>129354</v>
+        <v>130526</v>
       </c>
     </row>
     <row r="1036">
@@ -21201,10 +21201,10 @@
         <v>83.66</v>
       </c>
       <c r="E1039" t="n">
-        <v>84.34</v>
+        <v>84.23</v>
       </c>
       <c r="F1039" t="n">
-        <v>114302</v>
+        <v>115434</v>
       </c>
     </row>
     <row r="1040">
@@ -21215,16 +21215,16 @@
         <v>84.37</v>
       </c>
       <c r="C1040" t="n">
-        <v>85.8</v>
+        <v>85.81</v>
       </c>
       <c r="D1040" t="n">
         <v>82.2</v>
       </c>
       <c r="E1040" t="n">
-        <v>85.72</v>
+        <v>85.73999999999999</v>
       </c>
       <c r="F1040" t="n">
-        <v>119970</v>
+        <v>120888</v>
       </c>
     </row>
     <row r="1041">
@@ -21301,10 +21301,10 @@
         <v>81.16</v>
       </c>
       <c r="E1044" t="n">
-        <v>81.26000000000001</v>
+        <v>81.23</v>
       </c>
       <c r="F1044" t="n">
-        <v>120126</v>
+        <v>121276</v>
       </c>
     </row>
     <row r="1045">
@@ -21321,10 +21321,10 @@
         <v>80.47</v>
       </c>
       <c r="E1045" t="n">
-        <v>82.33</v>
+        <v>82.38</v>
       </c>
       <c r="F1045" t="n">
-        <v>171433</v>
+        <v>172647</v>
       </c>
     </row>
     <row r="1046">
@@ -21392,7 +21392,7 @@
         <v>45001</v>
       </c>
       <c r="B1049" t="n">
-        <v>74.04000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="C1049" t="n">
         <v>75.23</v>
@@ -21404,7 +21404,7 @@
         <v>74.25</v>
       </c>
       <c r="F1049" t="n">
-        <v>210322</v>
+        <v>206406</v>
       </c>
     </row>
     <row r="1050">
@@ -21412,7 +21412,7 @@
         <v>45002</v>
       </c>
       <c r="B1050" t="n">
-        <v>74.45</v>
+        <v>74.41</v>
       </c>
       <c r="C1050" t="n">
         <v>75.65000000000001</v>
@@ -21424,7 +21424,7 @@
         <v>72.3</v>
       </c>
       <c r="F1050" t="n">
-        <v>196053</v>
+        <v>194486</v>
       </c>
     </row>
     <row r="1051">
@@ -21492,7 +21492,7 @@
         <v>45008</v>
       </c>
       <c r="B1054" t="n">
-        <v>75.58</v>
+        <v>75.73</v>
       </c>
       <c r="C1054" t="n">
         <v>77.09</v>
@@ -21504,7 +21504,7 @@
         <v>74.98999999999999</v>
       </c>
       <c r="F1054" t="n">
-        <v>134971</v>
+        <v>132462</v>
       </c>
     </row>
     <row r="1055">
@@ -21512,7 +21512,7 @@
         <v>45009</v>
       </c>
       <c r="B1055" t="n">
-        <v>75.08</v>
+        <v>74.92</v>
       </c>
       <c r="C1055" t="n">
         <v>75.89</v>
@@ -21524,7 +21524,7 @@
         <v>74.52</v>
       </c>
       <c r="F1055" t="n">
-        <v>160608</v>
+        <v>158419</v>
       </c>
     </row>
     <row r="1056">
@@ -21601,10 +21601,10 @@
         <v>77.13</v>
       </c>
       <c r="E1059" t="n">
-        <v>78.47</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="F1059" t="n">
-        <v>101875</v>
+        <v>102975</v>
       </c>
     </row>
     <row r="1060">
@@ -21621,10 +21621,10 @@
         <v>77.79000000000001</v>
       </c>
       <c r="E1060" t="n">
-        <v>79.73</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="F1060" t="n">
-        <v>102278</v>
+        <v>103341</v>
       </c>
     </row>
     <row r="1061">
@@ -21701,10 +21701,10 @@
         <v>83.89</v>
       </c>
       <c r="E1064" t="n">
-        <v>84.73</v>
+        <v>84.62</v>
       </c>
       <c r="F1064" t="n">
-        <v>127887</v>
+        <v>128978</v>
       </c>
     </row>
     <row r="1065">
@@ -21781,10 +21781,10 @@
         <v>85.78</v>
       </c>
       <c r="E1068" t="n">
-        <v>85.98</v>
+        <v>86.03</v>
       </c>
       <c r="F1068" t="n">
-        <v>106530</v>
+        <v>107747</v>
       </c>
     </row>
     <row r="1069">
@@ -21801,10 +21801,10 @@
         <v>85.27</v>
       </c>
       <c r="E1069" t="n">
-        <v>86.13</v>
+        <v>86.12</v>
       </c>
       <c r="F1069" t="n">
-        <v>118921</v>
+        <v>119789</v>
       </c>
     </row>
     <row r="1070">
@@ -21878,13 +21878,13 @@
         <v>82.59999999999999</v>
       </c>
       <c r="D1073" t="n">
-        <v>80.51000000000001</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="E1073" t="n">
-        <v>80.62</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="F1073" t="n">
-        <v>99083</v>
+        <v>100157</v>
       </c>
     </row>
     <row r="1074">
@@ -21901,10 +21901,10 @@
         <v>80.2</v>
       </c>
       <c r="E1074" t="n">
-        <v>81.38</v>
+        <v>81.53</v>
       </c>
       <c r="F1074" t="n">
-        <v>88877</v>
+        <v>89589</v>
       </c>
     </row>
     <row r="1075">
@@ -21981,10 +21981,10 @@
         <v>77.3</v>
       </c>
       <c r="E1078" t="n">
-        <v>78.23</v>
+        <v>78.17</v>
       </c>
       <c r="F1078" t="n">
-        <v>112919</v>
+        <v>114226</v>
       </c>
     </row>
     <row r="1079">
@@ -22001,10 +22001,10 @@
         <v>77.44</v>
       </c>
       <c r="E1079" t="n">
-        <v>80.20999999999999</v>
+        <v>80.08</v>
       </c>
       <c r="F1079" t="n">
-        <v>110643</v>
+        <v>111593</v>
       </c>
     </row>
     <row r="1080">
@@ -22081,10 +22081,10 @@
         <v>71.34</v>
       </c>
       <c r="E1083" t="n">
-        <v>72.34</v>
+        <v>72.38</v>
       </c>
       <c r="F1083" t="n">
-        <v>175075</v>
+        <v>176458</v>
       </c>
     </row>
     <row r="1084">
@@ -22101,10 +22101,10 @@
         <v>72.31999999999999</v>
       </c>
       <c r="E1084" t="n">
-        <v>75.22</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="F1084" t="n">
-        <v>121559</v>
+        <v>122688</v>
       </c>
     </row>
     <row r="1085">
@@ -22181,10 +22181,10 @@
         <v>74.5</v>
       </c>
       <c r="E1088" t="n">
-        <v>75.34999999999999</v>
+        <v>75.26000000000001</v>
       </c>
       <c r="F1088" t="n">
-        <v>141443</v>
+        <v>142391</v>
       </c>
     </row>
     <row r="1089">
@@ -22201,10 +22201,10 @@
         <v>73.84999999999999</v>
       </c>
       <c r="E1089" t="n">
-        <v>74.02</v>
+        <v>73.93000000000001</v>
       </c>
       <c r="F1089" t="n">
-        <v>143925</v>
+        <v>144762</v>
       </c>
     </row>
     <row r="1090">
@@ -22281,10 +22281,10 @@
         <v>75.42</v>
       </c>
       <c r="E1093" t="n">
-        <v>75.89</v>
+        <v>75.84</v>
       </c>
       <c r="F1093" t="n">
-        <v>97144</v>
+        <v>98116</v>
       </c>
     </row>
     <row r="1094">
@@ -22301,10 +22301,10 @@
         <v>75.01000000000001</v>
       </c>
       <c r="E1094" t="n">
-        <v>75.75</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="F1094" t="n">
-        <v>107224</v>
+        <v>108218</v>
       </c>
     </row>
     <row r="1095">
@@ -22381,10 +22381,10 @@
         <v>75.08</v>
       </c>
       <c r="E1098" t="n">
-        <v>76.13</v>
+        <v>75.95999999999999</v>
       </c>
       <c r="F1098" t="n">
-        <v>94656</v>
+        <v>95663</v>
       </c>
     </row>
     <row r="1099">
@@ -22401,10 +22401,10 @@
         <v>75.62</v>
       </c>
       <c r="E1099" t="n">
-        <v>77.03</v>
+        <v>77.14</v>
       </c>
       <c r="F1099" t="n">
-        <v>85632</v>
+        <v>86227</v>
       </c>
     </row>
     <row r="1100">
@@ -22481,10 +22481,10 @@
         <v>72</v>
       </c>
       <c r="E1103" t="n">
-        <v>74.17</v>
+        <v>74.25</v>
       </c>
       <c r="F1103" t="n">
-        <v>122959</v>
+        <v>124084</v>
       </c>
     </row>
     <row r="1104">
@@ -22501,10 +22501,10 @@
         <v>74.13</v>
       </c>
       <c r="E1104" t="n">
-        <v>76.3</v>
+        <v>76.13</v>
       </c>
       <c r="F1104" t="n">
-        <v>110715</v>
+        <v>111881</v>
       </c>
     </row>
     <row r="1105">
@@ -22581,10 +22581,10 @@
         <v>73.52</v>
       </c>
       <c r="E1108" t="n">
-        <v>75.56999999999999</v>
+        <v>75.44</v>
       </c>
       <c r="F1108" t="n">
-        <v>141391</v>
+        <v>142206</v>
       </c>
     </row>
     <row r="1109">
@@ -22601,10 +22601,10 @@
         <v>74.67</v>
       </c>
       <c r="E1109" t="n">
-        <v>74.84999999999999</v>
+        <v>74.88</v>
       </c>
       <c r="F1109" t="n">
-        <v>120105</v>
+        <v>120995</v>
       </c>
     </row>
     <row r="1110">
@@ -22681,10 +22681,10 @@
         <v>72.84999999999999</v>
       </c>
       <c r="E1113" t="n">
-        <v>75.56</v>
+        <v>75.52</v>
       </c>
       <c r="F1113" t="n">
-        <v>104970</v>
+        <v>105947</v>
       </c>
     </row>
     <row r="1114">
@@ -22701,10 +22701,10 @@
         <v>75.09999999999999</v>
       </c>
       <c r="E1114" t="n">
-        <v>76.47</v>
+        <v>76.23</v>
       </c>
       <c r="F1114" t="n">
-        <v>109963</v>
+        <v>111184</v>
       </c>
     </row>
     <row r="1115">
@@ -22781,10 +22781,10 @@
         <v>73.75</v>
       </c>
       <c r="E1118" t="n">
-        <v>74.2</v>
+        <v>74.3</v>
       </c>
       <c r="F1118" t="n">
-        <v>89166</v>
+        <v>89974</v>
       </c>
     </row>
     <row r="1119">
@@ -22795,16 +22795,16 @@
         <v>74.2</v>
       </c>
       <c r="C1119" t="n">
-        <v>74.36</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="D1119" t="n">
         <v>72.25</v>
       </c>
       <c r="E1119" t="n">
-        <v>74.09</v>
+        <v>74.34</v>
       </c>
       <c r="F1119" t="n">
-        <v>100773</v>
+        <v>101628</v>
       </c>
     </row>
     <row r="1120">
@@ -22881,10 +22881,10 @@
         <v>73.56</v>
       </c>
       <c r="E1123" t="n">
-        <v>74.44</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="F1123" t="n">
-        <v>118096</v>
+        <v>118860</v>
       </c>
     </row>
     <row r="1124">
@@ -22901,10 +22901,10 @@
         <v>74.23</v>
       </c>
       <c r="E1124" t="n">
-        <v>75.26000000000001</v>
+        <v>75.06999999999999</v>
       </c>
       <c r="F1124" t="n">
-        <v>107062</v>
+        <v>108012</v>
       </c>
     </row>
     <row r="1125">
@@ -22981,10 +22981,10 @@
         <v>74.94</v>
       </c>
       <c r="E1128" t="n">
-        <v>76.47</v>
+        <v>76.44</v>
       </c>
       <c r="F1128" t="n">
-        <v>120498</v>
+        <v>121613</v>
       </c>
     </row>
     <row r="1129">
@@ -23001,10 +23001,10 @@
         <v>75.91</v>
       </c>
       <c r="E1129" t="n">
-        <v>78.13</v>
+        <v>78.12</v>
       </c>
       <c r="F1129" t="n">
-        <v>99946</v>
+        <v>101260</v>
       </c>
     </row>
     <row r="1130">
@@ -23075,16 +23075,16 @@
         <v>79.95999999999999</v>
       </c>
       <c r="C1133" t="n">
-        <v>81.48999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="D1133" t="n">
         <v>79.69</v>
       </c>
       <c r="E1133" t="n">
-        <v>81.48</v>
+        <v>81.37</v>
       </c>
       <c r="F1133" t="n">
-        <v>96443</v>
+        <v>97805</v>
       </c>
     </row>
     <row r="1134">
@@ -23098,13 +23098,13 @@
         <v>81.42</v>
       </c>
       <c r="D1134" t="n">
-        <v>79.44</v>
+        <v>79.34999999999999</v>
       </c>
       <c r="E1134" t="n">
-        <v>79.54000000000001</v>
+        <v>79.45</v>
       </c>
       <c r="F1134" t="n">
-        <v>98000</v>
+        <v>99161</v>
       </c>
     </row>
     <row r="1135">
@@ -23181,10 +23181,10 @@
         <v>78.56999999999999</v>
       </c>
       <c r="E1138" t="n">
-        <v>79.54000000000001</v>
+        <v>79.48</v>
       </c>
       <c r="F1138" t="n">
-        <v>76777</v>
+        <v>77506</v>
       </c>
     </row>
     <row r="1139">
@@ -23201,10 +23201,10 @@
         <v>79.51000000000001</v>
       </c>
       <c r="E1139" t="n">
-        <v>80.69</v>
+        <v>80.5</v>
       </c>
       <c r="F1139" t="n">
-        <v>69907</v>
+        <v>70745</v>
       </c>
     </row>
     <row r="1140">
@@ -23281,10 +23281,10 @@
         <v>82.54000000000001</v>
       </c>
       <c r="E1143" t="n">
-        <v>83.42</v>
+        <v>83.3</v>
       </c>
       <c r="F1143" t="n">
-        <v>100960</v>
+        <v>101885</v>
       </c>
     </row>
     <row r="1144">
@@ -23301,10 +23301,10 @@
         <v>82.78</v>
       </c>
       <c r="E1144" t="n">
-        <v>84.26000000000001</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="F1144" t="n">
-        <v>96080</v>
+        <v>96933</v>
       </c>
     </row>
     <row r="1145">
@@ -23381,10 +23381,10 @@
         <v>82.23</v>
       </c>
       <c r="E1148" t="n">
-        <v>85.13</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="F1148" t="n">
-        <v>122532</v>
+        <v>124232</v>
       </c>
     </row>
     <row r="1149">
@@ -23401,10 +23401,10 @@
         <v>84.89</v>
       </c>
       <c r="E1149" t="n">
-        <v>85.84</v>
+        <v>85.81</v>
       </c>
       <c r="F1149" t="n">
-        <v>103319</v>
+        <v>104424</v>
       </c>
     </row>
     <row r="1150">
@@ -23481,10 +23481,10 @@
         <v>85.89</v>
       </c>
       <c r="E1153" t="n">
-        <v>86.09999999999999</v>
+        <v>86.01000000000001</v>
       </c>
       <c r="F1153" t="n">
-        <v>119054</v>
+        <v>120019</v>
       </c>
     </row>
     <row r="1154">
@@ -23501,10 +23501,10 @@
         <v>85.53</v>
       </c>
       <c r="E1154" t="n">
-        <v>86.26000000000001</v>
+        <v>86.16</v>
       </c>
       <c r="F1154" t="n">
-        <v>114400</v>
+        <v>115051</v>
       </c>
     </row>
     <row r="1155">
@@ -23581,10 +23581,10 @@
         <v>82.70999999999999</v>
       </c>
       <c r="E1158" t="n">
-        <v>83.45999999999999</v>
+        <v>83.42</v>
       </c>
       <c r="F1158" t="n">
-        <v>87119</v>
+        <v>88033</v>
       </c>
     </row>
     <row r="1159">
@@ -23601,10 +23601,10 @@
         <v>82.98</v>
       </c>
       <c r="E1159" t="n">
-        <v>84.37</v>
+        <v>84.42</v>
       </c>
       <c r="F1159" t="n">
-        <v>98085</v>
+        <v>98761</v>
       </c>
     </row>
     <row r="1160">
@@ -23681,10 +23681,10 @@
         <v>81.61</v>
       </c>
       <c r="E1163" t="n">
-        <v>82.76000000000001</v>
+        <v>82.67</v>
       </c>
       <c r="F1163" t="n">
-        <v>77118</v>
+        <v>77961</v>
       </c>
     </row>
     <row r="1164">
@@ -23701,10 +23701,10 @@
         <v>82.2</v>
       </c>
       <c r="E1164" t="n">
-        <v>84.14</v>
+        <v>84.05</v>
       </c>
       <c r="F1164" t="n">
-        <v>101382</v>
+        <v>102303</v>
       </c>
     </row>
     <row r="1165">
@@ -23781,10 +23781,10 @@
         <v>84.98</v>
       </c>
       <c r="E1168" t="n">
-        <v>86.63</v>
+        <v>86.66</v>
       </c>
       <c r="F1168" t="n">
-        <v>83934</v>
+        <v>85007</v>
       </c>
     </row>
     <row r="1169">
@@ -23795,16 +23795,16 @@
         <v>86.63</v>
       </c>
       <c r="C1169" t="n">
-        <v>88.66</v>
+        <v>88.75</v>
       </c>
       <c r="D1169" t="n">
         <v>86.59</v>
       </c>
       <c r="E1169" t="n">
-        <v>88.64</v>
+        <v>88.68000000000001</v>
       </c>
       <c r="F1169" t="n">
-        <v>97671</v>
+        <v>98645</v>
       </c>
     </row>
     <row r="1170">
@@ -23881,10 +23881,10 @@
         <v>89.17</v>
       </c>
       <c r="E1173" t="n">
-        <v>89.76000000000001</v>
+        <v>89.47</v>
       </c>
       <c r="F1173" t="n">
-        <v>103067</v>
+        <v>104343</v>
       </c>
     </row>
     <row r="1174">
@@ -23901,10 +23901,10 @@
         <v>88.97</v>
       </c>
       <c r="E1174" t="n">
-        <v>90.2</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="F1174" t="n">
-        <v>100164</v>
+        <v>101197</v>
       </c>
     </row>
     <row r="1175">
@@ -23975,16 +23975,16 @@
         <v>91.56999999999999</v>
       </c>
       <c r="C1178" t="n">
-        <v>93.44</v>
+        <v>93.68000000000001</v>
       </c>
       <c r="D1178" t="n">
         <v>91.55</v>
       </c>
       <c r="E1178" t="n">
-        <v>93.36</v>
+        <v>93.56</v>
       </c>
       <c r="F1178" t="n">
-        <v>89908</v>
+        <v>91727</v>
       </c>
     </row>
     <row r="1179">
@@ -24001,10 +24001,10 @@
         <v>92.14</v>
       </c>
       <c r="E1179" t="n">
-        <v>93.52</v>
+        <v>93.56999999999999</v>
       </c>
       <c r="F1179" t="n">
-        <v>100530</v>
+        <v>101498</v>
       </c>
     </row>
     <row r="1180">
@@ -24081,10 +24081,10 @@
         <v>91.23999999999999</v>
       </c>
       <c r="E1183" t="n">
-        <v>92.27</v>
+        <v>92.20999999999999</v>
       </c>
       <c r="F1183" t="n">
-        <v>97207</v>
+        <v>98137</v>
       </c>
     </row>
     <row r="1184">
@@ -24101,10 +24101,10 @@
         <v>91.68000000000001</v>
       </c>
       <c r="E1184" t="n">
-        <v>92.31</v>
+        <v>92.28</v>
       </c>
       <c r="F1184" t="n">
-        <v>98960</v>
+        <v>99665</v>
       </c>
     </row>
     <row r="1185">
@@ -24181,10 +24181,10 @@
         <v>92.56</v>
       </c>
       <c r="E1188" t="n">
-        <v>92.94</v>
+        <v>92.89</v>
       </c>
       <c r="F1188" t="n">
-        <v>127194</v>
+        <v>128240</v>
       </c>
     </row>
     <row r="1189">
@@ -24201,10 +24201,10 @@
         <v>91.68000000000001</v>
       </c>
       <c r="E1189" t="n">
-        <v>91.95999999999999</v>
+        <v>91.8</v>
       </c>
       <c r="F1189" t="n">
-        <v>116761</v>
+        <v>117877</v>
       </c>
     </row>
     <row r="1190">
@@ -24281,10 +24281,10 @@
         <v>83.31999999999999</v>
       </c>
       <c r="E1193" t="n">
-        <v>83.68000000000001</v>
+        <v>83.72</v>
       </c>
       <c r="F1193" t="n">
-        <v>148426</v>
+        <v>149779</v>
       </c>
     </row>
     <row r="1194">
@@ -24301,10 +24301,10 @@
         <v>82.97</v>
       </c>
       <c r="E1194" t="n">
-        <v>83.88</v>
+        <v>83.79000000000001</v>
       </c>
       <c r="F1194" t="n">
-        <v>138785</v>
+        <v>140020</v>
       </c>
     </row>
     <row r="1195">
@@ -24381,10 +24381,10 @@
         <v>84.59</v>
       </c>
       <c r="E1198" t="n">
-        <v>85.7</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="F1198" t="n">
-        <v>123421</v>
+        <v>124560</v>
       </c>
     </row>
     <row r="1199">
@@ -24404,7 +24404,7 @@
         <v>89.93000000000001</v>
       </c>
       <c r="F1199" t="n">
-        <v>118765</v>
+        <v>120817</v>
       </c>
     </row>
     <row r="1200">
@@ -24475,16 +24475,16 @@
         <v>90.26000000000001</v>
       </c>
       <c r="C1203" t="n">
-        <v>92.22</v>
+        <v>92.34999999999999</v>
       </c>
       <c r="D1203" t="n">
         <v>88.69</v>
       </c>
       <c r="E1203" t="n">
-        <v>92.16</v>
+        <v>92.04000000000001</v>
       </c>
       <c r="F1203" t="n">
-        <v>109002</v>
+        <v>111224</v>
       </c>
     </row>
     <row r="1204">
@@ -24501,10 +24501,10 @@
         <v>90.63</v>
       </c>
       <c r="E1204" t="n">
-        <v>91.13</v>
+        <v>91.26000000000001</v>
       </c>
       <c r="F1204" t="n">
-        <v>109157</v>
+        <v>110661</v>
       </c>
     </row>
     <row r="1205">
@@ -24581,10 +24581,10 @@
         <v>86.48</v>
       </c>
       <c r="E1208" t="n">
-        <v>87.25</v>
+        <v>87.23999999999999</v>
       </c>
       <c r="F1208" t="n">
-        <v>113368</v>
+        <v>114536</v>
       </c>
     </row>
     <row r="1209">
@@ -24601,10 +24601,10 @@
         <v>86.76000000000001</v>
       </c>
       <c r="E1209" t="n">
-        <v>88.76000000000001</v>
+        <v>88.70999999999999</v>
       </c>
       <c r="F1209" t="n">
-        <v>121600</v>
+        <v>123231</v>
       </c>
     </row>
     <row r="1210">
@@ -24672,7 +24672,7 @@
         <v>45232</v>
       </c>
       <c r="B1213" t="n">
-        <v>84.83</v>
+        <v>85.03</v>
       </c>
       <c r="C1213" t="n">
         <v>86.88</v>
@@ -24684,7 +24684,7 @@
         <v>86.63</v>
       </c>
       <c r="F1213" t="n">
-        <v>103842</v>
+        <v>102261</v>
       </c>
     </row>
     <row r="1214">
@@ -24692,7 +24692,7 @@
         <v>45233</v>
       </c>
       <c r="B1214" t="n">
-        <v>86.70999999999999</v>
+        <v>86.66</v>
       </c>
       <c r="C1214" t="n">
         <v>87.58</v>
@@ -24704,7 +24704,7 @@
         <v>84.95</v>
       </c>
       <c r="F1214" t="n">
-        <v>119097</v>
+        <v>117913</v>
       </c>
     </row>
     <row r="1215">
@@ -24781,10 +24781,10 @@
         <v>79.33</v>
       </c>
       <c r="E1218" t="n">
-        <v>79.75</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="F1218" t="n">
-        <v>110739</v>
+        <v>111847</v>
       </c>
     </row>
     <row r="1219">
@@ -24801,10 +24801,10 @@
         <v>79.70999999999999</v>
       </c>
       <c r="E1219" t="n">
-        <v>81.36</v>
+        <v>81.43000000000001</v>
       </c>
       <c r="F1219" t="n">
-        <v>91256</v>
+        <v>92327</v>
       </c>
     </row>
     <row r="1220">
@@ -24881,10 +24881,10 @@
         <v>76.64</v>
       </c>
       <c r="E1223" t="n">
-        <v>77.43000000000001</v>
+        <v>77.45</v>
       </c>
       <c r="F1223" t="n">
-        <v>104766</v>
+        <v>105749</v>
       </c>
     </row>
     <row r="1224">
@@ -24901,10 +24901,10 @@
         <v>77.31</v>
       </c>
       <c r="E1224" t="n">
-        <v>80.37</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="F1224" t="n">
-        <v>88772</v>
+        <v>89648</v>
       </c>
     </row>
     <row r="1225">
@@ -25078,13 +25078,13 @@
         <v>84.51000000000001</v>
       </c>
       <c r="D1233" t="n">
-        <v>79.95</v>
+        <v>79.94</v>
       </c>
       <c r="E1233" t="n">
-        <v>80</v>
+        <v>80.31</v>
       </c>
       <c r="F1233" t="n">
-        <v>143673</v>
+        <v>145419</v>
       </c>
     </row>
     <row r="1234">
@@ -25101,10 +25101,10 @@
         <v>78.69</v>
       </c>
       <c r="E1234" t="n">
-        <v>78.93000000000001</v>
+        <v>79.02</v>
       </c>
       <c r="F1234" t="n">
-        <v>125186</v>
+        <v>126159</v>
       </c>
     </row>
     <row r="1235">
@@ -25181,10 +25181,10 @@
         <v>73.68000000000001</v>
       </c>
       <c r="E1238" t="n">
-        <v>74.47</v>
+        <v>74.39</v>
       </c>
       <c r="F1238" t="n">
-        <v>115986</v>
+        <v>116791</v>
       </c>
     </row>
     <row r="1239">
@@ -25201,10 +25201,10 @@
         <v>74.25</v>
       </c>
       <c r="E1239" t="n">
-        <v>75.87</v>
+        <v>75.94</v>
       </c>
       <c r="F1239" t="n">
-        <v>114085</v>
+        <v>114930</v>
       </c>
     </row>
     <row r="1240">
@@ -25281,10 +25281,10 @@
         <v>74.56999999999999</v>
       </c>
       <c r="E1243" t="n">
-        <v>76.86</v>
+        <v>76.75</v>
       </c>
       <c r="F1243" t="n">
-        <v>83845</v>
+        <v>84712</v>
       </c>
     </row>
     <row r="1244">
@@ -25301,10 +25301,10 @@
         <v>75.48</v>
       </c>
       <c r="E1244" t="n">
-        <v>76.90000000000001</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="F1244" t="n">
-        <v>94162</v>
+        <v>95068</v>
       </c>
     </row>
     <row r="1245">
@@ -25381,10 +25381,10 @@
         <v>77.76000000000001</v>
       </c>
       <c r="E1248" t="n">
-        <v>79.19</v>
+        <v>79.12</v>
       </c>
       <c r="F1248" t="n">
-        <v>91100</v>
+        <v>91755</v>
       </c>
     </row>
     <row r="1249">
@@ -25461,10 +25461,10 @@
         <v>77.04000000000001</v>
       </c>
       <c r="E1252" t="n">
-        <v>77.29000000000001</v>
+        <v>77.36</v>
       </c>
       <c r="F1252" t="n">
-        <v>94380</v>
+        <v>95204</v>
       </c>
     </row>
     <row r="1253">
@@ -25544,7 +25544,7 @@
         <v>77.53</v>
       </c>
       <c r="F1256" t="n">
-        <v>118273</v>
+        <v>119158</v>
       </c>
     </row>
     <row r="1257">
@@ -25641,10 +25641,10 @@
         <v>76.45</v>
       </c>
       <c r="E1261" t="n">
-        <v>77.61</v>
+        <v>78.01000000000001</v>
       </c>
       <c r="F1261" t="n">
-        <v>128067</v>
+        <v>129868</v>
       </c>
     </row>
     <row r="1262">
@@ -25741,10 +25741,10 @@
         <v>76.98</v>
       </c>
       <c r="E1266" t="n">
-        <v>78.63</v>
+        <v>78.56</v>
       </c>
       <c r="F1266" t="n">
-        <v>98609</v>
+        <v>99368</v>
       </c>
     </row>
     <row r="1267">
@@ -25841,10 +25841,10 @@
         <v>79.65000000000001</v>
       </c>
       <c r="E1271" t="n">
-        <v>81.84999999999999</v>
+        <v>81.69</v>
       </c>
       <c r="F1271" t="n">
-        <v>75889</v>
+        <v>76710</v>
       </c>
     </row>
     <row r="1272">
@@ -25861,10 +25861,10 @@
         <v>80.75</v>
       </c>
       <c r="E1272" t="n">
-        <v>83.08</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="F1272" t="n">
-        <v>85666</v>
+        <v>87047</v>
       </c>
     </row>
     <row r="1273">
@@ -25941,10 +25941,10 @@
         <v>78.5</v>
       </c>
       <c r="E1276" t="n">
-        <v>78.64</v>
+        <v>78.7</v>
       </c>
       <c r="F1276" t="n">
-        <v>138682</v>
+        <v>140571</v>
       </c>
     </row>
     <row r="1277">
@@ -25961,10 +25961,10 @@
         <v>76.78</v>
       </c>
       <c r="E1277" t="n">
-        <v>77.11</v>
+        <v>77.31999999999999</v>
       </c>
       <c r="F1277" t="n">
-        <v>132023</v>
+        <v>133396</v>
       </c>
     </row>
     <row r="1278">
@@ -26041,10 +26041,10 @@
         <v>78.84999999999999</v>
       </c>
       <c r="E1281" t="n">
-        <v>81.51000000000001</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="F1281" t="n">
-        <v>86597</v>
+        <v>87658</v>
       </c>
     </row>
     <row r="1282">
@@ -26064,7 +26064,7 @@
         <v>81.63</v>
       </c>
       <c r="F1282" t="n">
-        <v>85346</v>
+        <v>86235</v>
       </c>
     </row>
     <row r="1283">
@@ -26141,10 +26141,10 @@
         <v>80.31999999999999</v>
       </c>
       <c r="E1286" t="n">
-        <v>82.37</v>
+        <v>82.22</v>
       </c>
       <c r="F1286" t="n">
-        <v>83753</v>
+        <v>84560</v>
       </c>
     </row>
     <row r="1287">
@@ -26161,10 +26161,10 @@
         <v>81.34</v>
       </c>
       <c r="E1287" t="n">
-        <v>82.70999999999999</v>
+        <v>82.68000000000001</v>
       </c>
       <c r="F1287" t="n">
-        <v>80620</v>
+        <v>81459</v>
       </c>
     </row>
     <row r="1288">
@@ -26241,10 +26241,10 @@
         <v>81.45</v>
       </c>
       <c r="E1291" t="n">
-        <v>82.63</v>
+        <v>82.51000000000001</v>
       </c>
       <c r="F1291" t="n">
-        <v>67106</v>
+        <v>67848</v>
       </c>
     </row>
     <row r="1292">
@@ -26261,10 +26261,10 @@
         <v>80.65000000000001</v>
       </c>
       <c r="E1292" t="n">
-        <v>80.88</v>
+        <v>80.84</v>
       </c>
       <c r="F1292" t="n">
-        <v>72495</v>
+        <v>73168</v>
       </c>
     </row>
     <row r="1293">
@@ -26341,10 +26341,10 @@
         <v>81.37</v>
       </c>
       <c r="E1296" t="n">
-        <v>81.70999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="F1296" t="n">
-        <v>78801</v>
+        <v>79642</v>
       </c>
     </row>
     <row r="1297">
@@ -26361,10 +26361,10 @@
         <v>81.63</v>
       </c>
       <c r="E1297" t="n">
-        <v>83.19</v>
+        <v>83.12</v>
       </c>
       <c r="F1297" t="n">
-        <v>72423</v>
+        <v>73275</v>
       </c>
     </row>
     <row r="1298">
@@ -26441,10 +26441,10 @@
         <v>81.77</v>
       </c>
       <c r="E1301" t="n">
-        <v>82.52</v>
+        <v>82.87</v>
       </c>
       <c r="F1301" t="n">
-        <v>102278</v>
+        <v>103853</v>
       </c>
     </row>
     <row r="1302">
@@ -26461,10 +26461,10 @@
         <v>81.41</v>
       </c>
       <c r="E1302" t="n">
-        <v>81.66</v>
+        <v>81.55</v>
       </c>
       <c r="F1302" t="n">
-        <v>99175</v>
+        <v>100115</v>
       </c>
     </row>
     <row r="1303">
@@ -26532,19 +26532,19 @@
         <v>45365</v>
       </c>
       <c r="B1306" t="n">
-        <v>83.59999999999999</v>
+        <v>83.69</v>
       </c>
       <c r="C1306" t="n">
         <v>85.18000000000001</v>
       </c>
       <c r="D1306" t="n">
-        <v>83.53</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="E1306" t="n">
         <v>84.61</v>
       </c>
       <c r="F1306" t="n">
-        <v>71844</v>
+        <v>71119</v>
       </c>
     </row>
     <row r="1307">
@@ -26552,7 +26552,7 @@
         <v>45366</v>
       </c>
       <c r="B1307" t="n">
-        <v>84.65000000000001</v>
+        <v>84.68000000000001</v>
       </c>
       <c r="C1307" t="n">
         <v>85.09</v>
@@ -26564,7 +26564,7 @@
         <v>84.83</v>
       </c>
       <c r="F1307" t="n">
-        <v>75864</v>
+        <v>74945</v>
       </c>
     </row>
     <row r="1308">
@@ -26632,7 +26632,7 @@
         <v>45372</v>
       </c>
       <c r="B1311" t="n">
-        <v>85.70999999999999</v>
+        <v>85.81</v>
       </c>
       <c r="C1311" t="n">
         <v>86.03</v>
@@ -26644,7 +26644,7 @@
         <v>84.95999999999999</v>
       </c>
       <c r="F1311" t="n">
-        <v>67186</v>
+        <v>66113</v>
       </c>
     </row>
     <row r="1312">
@@ -26652,7 +26652,7 @@
         <v>45373</v>
       </c>
       <c r="B1312" t="n">
-        <v>85.09999999999999</v>
+        <v>84.98999999999999</v>
       </c>
       <c r="C1312" t="n">
         <v>85.58</v>
@@ -26664,7 +26664,7 @@
         <v>84.93000000000001</v>
       </c>
       <c r="F1312" t="n">
-        <v>54286</v>
+        <v>53666</v>
       </c>
     </row>
     <row r="1313">
@@ -26732,7 +26732,7 @@
         <v>45379</v>
       </c>
       <c r="B1316" t="n">
-        <v>85.56</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="C1316" t="n">
         <v>86.89</v>
@@ -26744,7 +26744,7 @@
         <v>86.67</v>
       </c>
       <c r="F1316" t="n">
-        <v>57372</v>
+        <v>56915</v>
       </c>
     </row>
     <row r="1317">
@@ -26821,10 +26821,10 @@
         <v>88.43000000000001</v>
       </c>
       <c r="E1320" t="n">
-        <v>90.38</v>
+        <v>90.56</v>
       </c>
       <c r="F1320" t="n">
-        <v>74470</v>
+        <v>75666</v>
       </c>
     </row>
     <row r="1321">
@@ -26841,10 +26841,10 @@
         <v>90.18000000000001</v>
       </c>
       <c r="E1321" t="n">
-        <v>90.52</v>
+        <v>90.39</v>
       </c>
       <c r="F1321" t="n">
-        <v>79937</v>
+        <v>80607</v>
       </c>
     </row>
     <row r="1322">
@@ -26921,10 +26921,10 @@
         <v>88.87</v>
       </c>
       <c r="E1325" t="n">
-        <v>89.68000000000001</v>
+        <v>89.55</v>
       </c>
       <c r="F1325" t="n">
-        <v>107040</v>
+        <v>107884</v>
       </c>
     </row>
     <row r="1326">
@@ -26941,10 +26941,10 @@
         <v>89.45</v>
       </c>
       <c r="E1326" t="n">
-        <v>89.73</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="F1326" t="n">
-        <v>108331</v>
+        <v>109120</v>
       </c>
     </row>
     <row r="1327">
@@ -27021,10 +27021,10 @@
         <v>85.63</v>
       </c>
       <c r="E1330" t="n">
-        <v>86.47</v>
+        <v>86.19</v>
       </c>
       <c r="F1330" t="n">
-        <v>107464</v>
+        <v>108132</v>
       </c>
     </row>
     <row r="1331">
@@ -27041,10 +27041,10 @@
         <v>85.61</v>
       </c>
       <c r="E1331" t="n">
-        <v>86.51000000000001</v>
+        <v>86.38</v>
       </c>
       <c r="F1331" t="n">
-        <v>143518</v>
+        <v>144473</v>
       </c>
     </row>
     <row r="1332">
@@ -27115,16 +27115,16 @@
         <v>86.88</v>
       </c>
       <c r="C1335" t="n">
-        <v>87.97</v>
+        <v>88</v>
       </c>
       <c r="D1335" t="n">
         <v>86.2</v>
       </c>
       <c r="E1335" t="n">
-        <v>87.95</v>
+        <v>87.83</v>
       </c>
       <c r="F1335" t="n">
-        <v>69439</v>
+        <v>70059</v>
       </c>
     </row>
     <row r="1336">
@@ -27141,10 +27141,10 @@
         <v>87.56999999999999</v>
       </c>
       <c r="E1336" t="n">
-        <v>87.98999999999999</v>
+        <v>87.89</v>
       </c>
       <c r="F1336" t="n">
-        <v>63936</v>
+        <v>64445</v>
       </c>
     </row>
     <row r="1337">
@@ -27221,10 +27221,10 @@
         <v>82.89</v>
       </c>
       <c r="E1340" t="n">
-        <v>83.47</v>
+        <v>83.48</v>
       </c>
       <c r="F1340" t="n">
-        <v>100961</v>
+        <v>101847</v>
       </c>
     </row>
     <row r="1341">
@@ -27238,13 +27238,13 @@
         <v>84.18000000000001</v>
       </c>
       <c r="D1341" t="n">
-        <v>82.65000000000001</v>
+        <v>82.53</v>
       </c>
       <c r="E1341" t="n">
-        <v>82.77</v>
+        <v>82.54000000000001</v>
       </c>
       <c r="F1341" t="n">
-        <v>82987</v>
+        <v>83584</v>
       </c>
     </row>
     <row r="1342">
@@ -27321,10 +27321,10 @@
         <v>83.18000000000001</v>
       </c>
       <c r="E1345" t="n">
-        <v>83.91</v>
+        <v>83.77</v>
       </c>
       <c r="F1345" t="n">
-        <v>67201</v>
+        <v>67737</v>
       </c>
     </row>
     <row r="1346">
@@ -27338,13 +27338,13 @@
         <v>84.23</v>
       </c>
       <c r="D1346" t="n">
-        <v>82.5</v>
+        <v>82.36</v>
       </c>
       <c r="E1346" t="n">
-        <v>82.61</v>
+        <v>82.36</v>
       </c>
       <c r="F1346" t="n">
-        <v>62356</v>
+        <v>63117</v>
       </c>
     </row>
     <row r="1347">
@@ -27421,10 +27421,10 @@
         <v>82.02</v>
       </c>
       <c r="E1350" t="n">
-        <v>83.04000000000001</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="F1350" t="n">
-        <v>65306</v>
+        <v>65759</v>
       </c>
     </row>
     <row r="1351">
@@ -27441,10 +27441,10 @@
         <v>82.81999999999999</v>
       </c>
       <c r="E1351" t="n">
-        <v>83.68000000000001</v>
+        <v>83.56</v>
       </c>
       <c r="F1351" t="n">
-        <v>60667</v>
+        <v>61133</v>
       </c>
     </row>
     <row r="1352">
@@ -27521,10 +27521,10 @@
         <v>80.7</v>
       </c>
       <c r="E1355" t="n">
-        <v>81.09</v>
+        <v>81.06999999999999</v>
       </c>
       <c r="F1355" t="n">
-        <v>68901</v>
+        <v>69958</v>
       </c>
     </row>
     <row r="1356">
@@ -27541,10 +27541,10 @@
         <v>80.42</v>
       </c>
       <c r="E1356" t="n">
-        <v>81.84999999999999</v>
+        <v>81.79000000000001</v>
       </c>
       <c r="F1356" t="n">
-        <v>56045</v>
+        <v>56381</v>
       </c>
     </row>
     <row r="1357">
@@ -27618,13 +27618,13 @@
         <v>83.51000000000001</v>
       </c>
       <c r="D1360" t="n">
-        <v>81.77</v>
+        <v>81.72</v>
       </c>
       <c r="E1360" t="n">
-        <v>81.88</v>
+        <v>81.73</v>
       </c>
       <c r="F1360" t="n">
-        <v>81262</v>
+        <v>81864</v>
       </c>
     </row>
     <row r="1361">
@@ -27641,10 +27641,10 @@
         <v>80.69</v>
       </c>
       <c r="E1361" t="n">
-        <v>81.22</v>
+        <v>81.09</v>
       </c>
       <c r="F1361" t="n">
-        <v>86335</v>
+        <v>87130</v>
       </c>
     </row>
     <row r="1362">
@@ -27721,10 +27721,10 @@
         <v>78.23999999999999</v>
       </c>
       <c r="E1365" t="n">
-        <v>79.73</v>
+        <v>79.69</v>
       </c>
       <c r="F1365" t="n">
-        <v>72035</v>
+        <v>72677</v>
       </c>
     </row>
     <row r="1366">
@@ -27741,10 +27741,10 @@
         <v>79.18000000000001</v>
       </c>
       <c r="E1366" t="n">
-        <v>79.27</v>
+        <v>79.23999999999999</v>
       </c>
       <c r="F1366" t="n">
-        <v>76576</v>
+        <v>77440</v>
       </c>
     </row>
     <row r="1367">
@@ -27821,10 +27821,10 @@
         <v>81.53</v>
       </c>
       <c r="E1370" t="n">
-        <v>81.98</v>
+        <v>81.68000000000001</v>
       </c>
       <c r="F1370" t="n">
-        <v>78296</v>
+        <v>79567</v>
       </c>
     </row>
     <row r="1371">
@@ -27841,10 +27841,10 @@
         <v>81.64</v>
       </c>
       <c r="E1371" t="n">
-        <v>82.2</v>
+        <v>82.06</v>
       </c>
       <c r="F1371" t="n">
-        <v>75030</v>
+        <v>75768</v>
       </c>
     </row>
     <row r="1372">
@@ -27921,10 +27921,10 @@
         <v>84.28</v>
       </c>
       <c r="E1375" t="n">
-        <v>85.01000000000001</v>
+        <v>84.7</v>
       </c>
       <c r="F1375" t="n">
-        <v>59448</v>
+        <v>59846</v>
       </c>
     </row>
     <row r="1376">
@@ -27941,10 +27941,10 @@
         <v>84</v>
       </c>
       <c r="E1376" t="n">
-        <v>84.31</v>
+        <v>84.16</v>
       </c>
       <c r="F1376" t="n">
-        <v>59797</v>
+        <v>60278</v>
       </c>
     </row>
     <row r="1377">
@@ -28021,10 +28021,10 @@
         <v>84.01000000000001</v>
       </c>
       <c r="E1380" t="n">
-        <v>85.25</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="F1380" t="n">
-        <v>64362</v>
+        <v>64909</v>
       </c>
     </row>
     <row r="1381">
@@ -28041,10 +28041,10 @@
         <v>84.39</v>
       </c>
       <c r="E1381" t="n">
-        <v>84.79000000000001</v>
+        <v>84.65000000000001</v>
       </c>
       <c r="F1381" t="n">
-        <v>69177</v>
+        <v>69862</v>
       </c>
     </row>
     <row r="1382">
@@ -28141,10 +28141,10 @@
         <v>86.17</v>
       </c>
       <c r="E1386" t="n">
-        <v>86.31999999999999</v>
+        <v>86.43000000000001</v>
       </c>
       <c r="F1386" t="n">
-        <v>67919</v>
+        <v>68965</v>
       </c>
     </row>
     <row r="1387">
@@ -28221,10 +28221,10 @@
         <v>84.16</v>
       </c>
       <c r="E1390" t="n">
-        <v>85.19</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="F1390" t="n">
-        <v>78243</v>
+        <v>78990</v>
       </c>
     </row>
     <row r="1391">
@@ -28238,13 +28238,13 @@
         <v>85.67</v>
       </c>
       <c r="D1391" t="n">
-        <v>84.40000000000001</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="E1391" t="n">
-        <v>84.5</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="F1391" t="n">
-        <v>73607</v>
+        <v>74302</v>
       </c>
     </row>
     <row r="1392">
@@ -28321,10 +28321,10 @@
         <v>83.41</v>
       </c>
       <c r="E1395" t="n">
-        <v>83.72</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="F1395" t="n">
-        <v>68620</v>
+        <v>69797</v>
       </c>
     </row>
     <row r="1396">
@@ -28338,13 +28338,13 @@
         <v>84.41</v>
       </c>
       <c r="D1396" t="n">
-        <v>81.7</v>
+        <v>81.64</v>
       </c>
       <c r="E1396" t="n">
-        <v>81.89</v>
+        <v>81.64</v>
       </c>
       <c r="F1396" t="n">
-        <v>72020</v>
+        <v>72736</v>
       </c>
     </row>
     <row r="1397">
@@ -28421,10 +28421,10 @@
         <v>79.28</v>
       </c>
       <c r="E1400" t="n">
-        <v>81.33</v>
+        <v>81.37</v>
       </c>
       <c r="F1400" t="n">
-        <v>69150</v>
+        <v>69789</v>
       </c>
     </row>
     <row r="1401">
@@ -28441,10 +28441,10 @@
         <v>79.39</v>
       </c>
       <c r="E1401" t="n">
-        <v>79.92</v>
+        <v>79.48999999999999</v>
       </c>
       <c r="F1401" t="n">
-        <v>64725</v>
+        <v>65748</v>
       </c>
     </row>
     <row r="1402">
@@ -28521,10 +28521,10 @@
         <v>79.3</v>
       </c>
       <c r="E1405" t="n">
-        <v>80</v>
+        <v>79.83</v>
       </c>
       <c r="F1405" t="n">
-        <v>104482</v>
+        <v>105741</v>
       </c>
     </row>
     <row r="1406">
@@ -28541,10 +28541,10 @@
         <v>76.26000000000001</v>
       </c>
       <c r="E1406" t="n">
-        <v>77.08</v>
+        <v>77.14</v>
       </c>
       <c r="F1406" t="n">
-        <v>124356</v>
+        <v>125792</v>
       </c>
     </row>
     <row r="1407">
@@ -28621,10 +28621,10 @@
         <v>77.33</v>
       </c>
       <c r="E1410" t="n">
-        <v>78.73999999999999</v>
+        <v>78.59</v>
       </c>
       <c r="F1410" t="n">
-        <v>113028</v>
+        <v>113892</v>
       </c>
     </row>
     <row r="1411">
@@ -28641,10 +28641,10 @@
         <v>78.43000000000001</v>
       </c>
       <c r="E1411" t="n">
-        <v>79.34</v>
+        <v>79.27</v>
       </c>
       <c r="F1411" t="n">
-        <v>86405</v>
+        <v>87467</v>
       </c>
     </row>
     <row r="1412">
@@ -28721,10 +28721,10 @@
         <v>79.11</v>
       </c>
       <c r="E1415" t="n">
-        <v>80.31999999999999</v>
+        <v>80.26000000000001</v>
       </c>
       <c r="F1415" t="n">
-        <v>78757</v>
+        <v>79567</v>
       </c>
     </row>
     <row r="1416">
@@ -28741,10 +28741,10 @@
         <v>78.09</v>
       </c>
       <c r="E1416" t="n">
-        <v>79.22</v>
+        <v>78.94</v>
       </c>
       <c r="F1416" t="n">
-        <v>81009</v>
+        <v>82030</v>
       </c>
     </row>
     <row r="1417">
@@ -28821,10 +28821,10 @@
         <v>75.25</v>
       </c>
       <c r="E1420" t="n">
-        <v>76.47</v>
+        <v>76.42</v>
       </c>
       <c r="F1420" t="n">
-        <v>79280</v>
+        <v>79873</v>
       </c>
     </row>
     <row r="1421">
@@ -28841,10 +28841,10 @@
         <v>76.40000000000001</v>
       </c>
       <c r="E1421" t="n">
-        <v>78.17</v>
+        <v>78.13</v>
       </c>
       <c r="F1421" t="n">
-        <v>68613</v>
+        <v>69081</v>
       </c>
     </row>
     <row r="1422">
@@ -28921,10 +28921,10 @@
         <v>76.90000000000001</v>
       </c>
       <c r="E1425" t="n">
-        <v>78.81</v>
+        <v>78.72</v>
       </c>
       <c r="F1425" t="n">
-        <v>93699</v>
+        <v>94397</v>
       </c>
     </row>
     <row r="1426">
@@ -28941,10 +28941,10 @@
         <v>76.56</v>
       </c>
       <c r="E1426" t="n">
-        <v>76.81</v>
+        <v>76.77</v>
       </c>
       <c r="F1426" t="n">
-        <v>108329</v>
+        <v>109124</v>
       </c>
     </row>
     <row r="1427">
@@ -29021,10 +29021,10 @@
         <v>72.20999999999999</v>
       </c>
       <c r="E1430" t="n">
-        <v>72.54000000000001</v>
+        <v>72.53</v>
       </c>
       <c r="F1430" t="n">
-        <v>108713</v>
+        <v>109541</v>
       </c>
     </row>
     <row r="1431">
@@ -29041,10 +29041,10 @@
         <v>70.45</v>
       </c>
       <c r="E1431" t="n">
-        <v>71.37</v>
+        <v>71.2</v>
       </c>
       <c r="F1431" t="n">
-        <v>115759</v>
+        <v>116954</v>
       </c>
     </row>
     <row r="1432">
@@ -29121,10 +29121,10 @@
         <v>70.31999999999999</v>
       </c>
       <c r="E1435" t="n">
-        <v>71.89</v>
+        <v>71.67</v>
       </c>
       <c r="F1435" t="n">
-        <v>114181</v>
+        <v>115156</v>
       </c>
     </row>
     <row r="1436">
@@ -29141,10 +29141,10 @@
         <v>71.09</v>
       </c>
       <c r="E1436" t="n">
-        <v>71.73</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="F1436" t="n">
-        <v>98569</v>
+        <v>99629</v>
       </c>
     </row>
     <row r="1437">
@@ -29221,10 +29221,10 @@
         <v>72.26000000000001</v>
       </c>
       <c r="E1440" t="n">
-        <v>74.05</v>
+        <v>73.97</v>
       </c>
       <c r="F1440" t="n">
-        <v>88395</v>
+        <v>89094</v>
       </c>
     </row>
     <row r="1441">
@@ -29241,10 +29241,10 @@
         <v>73.28</v>
       </c>
       <c r="E1441" t="n">
-        <v>73.98</v>
+        <v>73.87</v>
       </c>
       <c r="F1441" t="n">
-        <v>71635</v>
+        <v>72413</v>
       </c>
     </row>
     <row r="1442">
@@ -29321,10 +29321,10 @@
         <v>70.20999999999999</v>
       </c>
       <c r="E1445" t="n">
-        <v>70.66</v>
+        <v>70.68000000000001</v>
       </c>
       <c r="F1445" t="n">
-        <v>154979</v>
+        <v>155899</v>
       </c>
     </row>
     <row r="1446">
@@ -29335,16 +29335,16 @@
         <v>70.68000000000001</v>
       </c>
       <c r="C1446" t="n">
-        <v>71.89</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="D1446" t="n">
         <v>70.39</v>
       </c>
       <c r="E1446" t="n">
-        <v>71.81999999999999</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="F1446" t="n">
-        <v>122438</v>
+        <v>123787</v>
       </c>
     </row>
     <row r="1447">
@@ -29421,10 +29421,10 @@
         <v>74.18000000000001</v>
       </c>
       <c r="E1450" t="n">
-        <v>77.58</v>
+        <v>77.28</v>
       </c>
       <c r="F1450" t="n">
-        <v>123449</v>
+        <v>125075</v>
       </c>
     </row>
     <row r="1451">
@@ -29441,10 +29441,10 @@
         <v>77.19</v>
       </c>
       <c r="E1451" t="n">
-        <v>77.87</v>
+        <v>77.73</v>
       </c>
       <c r="F1451" t="n">
-        <v>120535</v>
+        <v>121412</v>
       </c>
     </row>
     <row r="1452">
@@ -38904,7 +38904,7 @@
         <v>82.76000000000001</v>
       </c>
       <c r="F1924" t="n">
-        <v>102987</v>
+        <v>103015</v>
       </c>
     </row>
     <row r="1925">
@@ -38915,16 +38915,16 @@
         <v>82.43000000000001</v>
       </c>
       <c r="C1925" t="n">
-        <v>83.02</v>
+        <v>83.55</v>
       </c>
       <c r="D1925" t="n">
-        <v>82.29000000000001</v>
+        <v>80.81999999999999</v>
       </c>
       <c r="E1925" t="n">
-        <v>82.55</v>
+        <v>81.53</v>
       </c>
       <c r="F1925" t="n">
-        <v>3269</v>
+        <v>90710</v>
       </c>
     </row>
   </sheetData>

--- a/database/BRENT.xlsx
+++ b/database/BRENT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1925"/>
+  <dimension ref="A1:F1926"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38904,7 +38904,7 @@
         <v>82.76000000000001</v>
       </c>
       <c r="F1924" t="n">
-        <v>103015</v>
+        <v>103018</v>
       </c>
     </row>
     <row r="1925">
@@ -38924,7 +38924,27 @@
         <v>81.53</v>
       </c>
       <c r="F1925" t="n">
-        <v>90710</v>
+        <v>90754</v>
+      </c>
+    </row>
+    <row r="1926">
+      <c r="A1926" s="1" t="n">
+        <v>46243</v>
+      </c>
+      <c r="B1926" t="n">
+        <v>82.34</v>
+      </c>
+      <c r="C1926" t="n">
+        <v>87.03</v>
+      </c>
+      <c r="D1926" t="n">
+        <v>82.34</v>
+      </c>
+      <c r="E1926" t="n">
+        <v>86.88</v>
+      </c>
+      <c r="F1926" t="n">
+        <v>101192</v>
       </c>
     </row>
   </sheetData>

--- a/database/BRENT.xlsx
+++ b/database/BRENT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1926"/>
+  <dimension ref="A1:F1927"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3881,10 +3881,10 @@
         <v>60.96</v>
       </c>
       <c r="E173" t="n">
-        <v>61.65</v>
+        <v>61.74</v>
       </c>
       <c r="F173" t="n">
-        <v>7745</v>
+        <v>7439</v>
       </c>
     </row>
     <row r="174">
@@ -3952,7 +3952,7 @@
         <v>43769</v>
       </c>
       <c r="B177" t="n">
-        <v>60.27</v>
+        <v>60.17</v>
       </c>
       <c r="C177" t="n">
         <v>60.79</v>
@@ -3964,7 +3964,7 @@
         <v>59.46</v>
       </c>
       <c r="F177" t="n">
-        <v>20603</v>
+        <v>20831</v>
       </c>
     </row>
     <row r="178">
@@ -3972,7 +3972,7 @@
         <v>43770</v>
       </c>
       <c r="B178" t="n">
-        <v>59.64</v>
+        <v>59.42</v>
       </c>
       <c r="C178" t="n">
         <v>61.8</v>
@@ -3984,7 +3984,7 @@
         <v>61.65</v>
       </c>
       <c r="F178" t="n">
-        <v>18281</v>
+        <v>18539</v>
       </c>
     </row>
     <row r="179">
@@ -4061,10 +4061,10 @@
         <v>61.63</v>
       </c>
       <c r="E182" t="n">
-        <v>62.29</v>
+        <v>62.14</v>
       </c>
       <c r="F182" t="n">
-        <v>19680</v>
+        <v>19306</v>
       </c>
     </row>
     <row r="183">
@@ -4081,10 +4081,10 @@
         <v>60.65</v>
       </c>
       <c r="E183" t="n">
-        <v>62.64</v>
+        <v>62.61</v>
       </c>
       <c r="F183" t="n">
-        <v>21863</v>
+        <v>21625</v>
       </c>
     </row>
     <row r="184">
@@ -4161,10 +4161,10 @@
         <v>62.14</v>
       </c>
       <c r="E187" t="n">
-        <v>62.33</v>
+        <v>62.38</v>
       </c>
       <c r="F187" t="n">
-        <v>19293</v>
+        <v>19157</v>
       </c>
     </row>
     <row r="188">
@@ -4181,10 +4181,10 @@
         <v>61.69</v>
       </c>
       <c r="E188" t="n">
-        <v>63.41</v>
+        <v>63.32</v>
       </c>
       <c r="F188" t="n">
-        <v>16092</v>
+        <v>15801</v>
       </c>
     </row>
     <row r="189">
@@ -4261,10 +4261,10 @@
         <v>61.91</v>
       </c>
       <c r="E192" t="n">
-        <v>63.64</v>
+        <v>63.74</v>
       </c>
       <c r="F192" t="n">
-        <v>21823</v>
+        <v>21582</v>
       </c>
     </row>
     <row r="193">
@@ -4281,10 +4281,10 @@
         <v>61.92</v>
       </c>
       <c r="E193" t="n">
-        <v>62.52</v>
+        <v>62.58</v>
       </c>
       <c r="F193" t="n">
-        <v>17794</v>
+        <v>17577</v>
       </c>
     </row>
     <row r="194">
@@ -4461,10 +4461,10 @@
         <v>62.73</v>
       </c>
       <c r="E202" t="n">
-        <v>63.26</v>
+        <v>63.33</v>
       </c>
       <c r="F202" t="n">
-        <v>24300</v>
+        <v>24042</v>
       </c>
     </row>
     <row r="203">
@@ -4481,10 +4481,10 @@
         <v>62.82</v>
       </c>
       <c r="E203" t="n">
-        <v>64.34</v>
+        <v>64.22</v>
       </c>
       <c r="F203" t="n">
-        <v>22572</v>
+        <v>22359</v>
       </c>
     </row>
     <row r="204">
@@ -4561,10 +4561,10 @@
         <v>63.86</v>
       </c>
       <c r="E207" t="n">
-        <v>64.28</v>
+        <v>64.31</v>
       </c>
       <c r="F207" t="n">
-        <v>18454</v>
+        <v>18198</v>
       </c>
     </row>
     <row r="208">
@@ -4581,10 +4581,10 @@
         <v>64.48</v>
       </c>
       <c r="E208" t="n">
-        <v>64.90000000000001</v>
+        <v>64.88</v>
       </c>
       <c r="F208" t="n">
-        <v>21671</v>
+        <v>21484</v>
       </c>
     </row>
     <row r="209">
@@ -4661,10 +4661,10 @@
         <v>66.02</v>
       </c>
       <c r="E212" t="n">
-        <v>66.53</v>
+        <v>66.45</v>
       </c>
       <c r="F212" t="n">
-        <v>11180</v>
+        <v>10932</v>
       </c>
     </row>
     <row r="213">
@@ -4681,10 +4681,10 @@
         <v>65.72</v>
       </c>
       <c r="E213" t="n">
-        <v>66.01000000000001</v>
+        <v>65.98</v>
       </c>
       <c r="F213" t="n">
-        <v>14806</v>
+        <v>14693</v>
       </c>
     </row>
     <row r="214">
@@ -4741,10 +4741,10 @@
         <v>66.09</v>
       </c>
       <c r="E216" t="n">
-        <v>66.75</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="F216" t="n">
-        <v>9613</v>
+        <v>9409</v>
       </c>
     </row>
     <row r="217">
@@ -4761,10 +4761,10 @@
         <v>66.34</v>
       </c>
       <c r="E217" t="n">
-        <v>66.84</v>
+        <v>66.81</v>
       </c>
       <c r="F217" t="n">
-        <v>11398</v>
+        <v>11272</v>
       </c>
     </row>
     <row r="218">
@@ -4821,10 +4821,10 @@
         <v>65.7</v>
       </c>
       <c r="E220" t="n">
-        <v>66.23</v>
+        <v>66.19</v>
       </c>
       <c r="F220" t="n">
-        <v>15351</v>
+        <v>15153</v>
       </c>
     </row>
     <row r="221">
@@ -4841,10 +4841,10 @@
         <v>66.19</v>
       </c>
       <c r="E221" t="n">
-        <v>68.59</v>
+        <v>68.55</v>
       </c>
       <c r="F221" t="n">
-        <v>35609</v>
+        <v>35427</v>
       </c>
     </row>
     <row r="222">
@@ -4924,7 +4924,7 @@
         <v>65.38</v>
       </c>
       <c r="F225" t="n">
-        <v>25951</v>
+        <v>25682</v>
       </c>
     </row>
     <row r="226">
@@ -4944,7 +4944,7 @@
         <v>65</v>
       </c>
       <c r="F226" t="n">
-        <v>20436</v>
+        <v>20016</v>
       </c>
     </row>
     <row r="227">
@@ -5021,10 +5021,10 @@
         <v>63.89</v>
       </c>
       <c r="E230" t="n">
-        <v>64.7</v>
+        <v>64.64</v>
       </c>
       <c r="F230" t="n">
-        <v>16472</v>
+        <v>16107</v>
       </c>
     </row>
     <row r="231">
@@ -5041,10 +5041,10 @@
         <v>64.45</v>
       </c>
       <c r="E231" t="n">
-        <v>65.08</v>
+        <v>64.95</v>
       </c>
       <c r="F231" t="n">
-        <v>16251</v>
+        <v>16060</v>
       </c>
     </row>
     <row r="232">
@@ -5121,10 +5121,10 @@
         <v>61.24</v>
       </c>
       <c r="E235" t="n">
-        <v>62.11</v>
+        <v>61.97</v>
       </c>
       <c r="F235" t="n">
-        <v>23208</v>
+        <v>22982</v>
       </c>
     </row>
     <row r="236">
@@ -5141,10 +5141,10 @@
         <v>60.24</v>
       </c>
       <c r="E236" t="n">
-        <v>60.64</v>
+        <v>60.82</v>
       </c>
       <c r="F236" t="n">
-        <v>21687</v>
+        <v>21411</v>
       </c>
     </row>
     <row r="237">
@@ -5221,10 +5221,10 @@
         <v>56.73</v>
       </c>
       <c r="E240" t="n">
-        <v>58.2</v>
+        <v>58.03</v>
       </c>
       <c r="F240" t="n">
-        <v>28894</v>
+        <v>28317</v>
       </c>
     </row>
     <row r="241">
@@ -5244,7 +5244,7 @@
         <v>56.63</v>
       </c>
       <c r="F241" t="n">
-        <v>31264</v>
+        <v>30854</v>
       </c>
     </row>
     <row r="242">
@@ -5321,10 +5321,10 @@
         <v>54.24</v>
       </c>
       <c r="E245" t="n">
-        <v>55.14</v>
+        <v>55.07</v>
       </c>
       <c r="F245" t="n">
-        <v>31917</v>
+        <v>31638</v>
       </c>
     </row>
     <row r="246">
@@ -5341,10 +5341,10 @@
         <v>54.2</v>
       </c>
       <c r="E246" t="n">
-        <v>54.45</v>
+        <v>54.48</v>
       </c>
       <c r="F246" t="n">
-        <v>26144</v>
+        <v>25828</v>
       </c>
     </row>
     <row r="247">
@@ -5421,10 +5421,10 @@
         <v>54.95</v>
       </c>
       <c r="E250" t="n">
-        <v>56.4</v>
+        <v>56.51</v>
       </c>
       <c r="F250" t="n">
-        <v>24914</v>
+        <v>24675</v>
       </c>
     </row>
     <row r="251">
@@ -5441,10 +5441,10 @@
         <v>56.13</v>
       </c>
       <c r="E251" t="n">
-        <v>57.33</v>
+        <v>57.32</v>
       </c>
       <c r="F251" t="n">
-        <v>21778</v>
+        <v>21410</v>
       </c>
     </row>
     <row r="252">
@@ -5521,10 +5521,10 @@
         <v>58.89</v>
       </c>
       <c r="E255" t="n">
-        <v>59.03</v>
+        <v>59.28</v>
       </c>
       <c r="F255" t="n">
-        <v>23391</v>
+        <v>23121</v>
       </c>
     </row>
     <row r="256">
@@ -5541,10 +5541,10 @@
         <v>57.71</v>
       </c>
       <c r="E256" t="n">
-        <v>58.44</v>
+        <v>58.33</v>
       </c>
       <c r="F256" t="n">
-        <v>26971</v>
+        <v>26663</v>
       </c>
     </row>
     <row r="257">
@@ -5621,10 +5621,10 @@
         <v>50.38</v>
       </c>
       <c r="E260" t="n">
-        <v>50.95</v>
+        <v>51.35</v>
       </c>
       <c r="F260" t="n">
-        <v>52807</v>
+        <v>51199</v>
       </c>
     </row>
     <row r="261">
@@ -5641,10 +5641,10 @@
         <v>48.92</v>
       </c>
       <c r="E261" t="n">
-        <v>50.08</v>
+        <v>50.01</v>
       </c>
       <c r="F261" t="n">
-        <v>72794</v>
+        <v>71739</v>
       </c>
     </row>
     <row r="262">
@@ -5721,10 +5721,10 @@
         <v>49.67</v>
       </c>
       <c r="E265" t="n">
-        <v>50</v>
+        <v>49.95</v>
       </c>
       <c r="F265" t="n">
-        <v>42678</v>
+        <v>42080</v>
       </c>
     </row>
     <row r="266">
@@ -5741,10 +5741,10 @@
         <v>45.16</v>
       </c>
       <c r="E266" t="n">
-        <v>45.51</v>
+        <v>45.55</v>
       </c>
       <c r="F266" t="n">
-        <v>65295</v>
+        <v>64437</v>
       </c>
     </row>
     <row r="267">
@@ -5812,7 +5812,7 @@
         <v>43902</v>
       </c>
       <c r="B270" t="n">
-        <v>36.29</v>
+        <v>35.97</v>
       </c>
       <c r="C270" t="n">
         <v>36.45</v>
@@ -5824,7 +5824,7 @@
         <v>33.49</v>
       </c>
       <c r="F270" t="n">
-        <v>64469</v>
+        <v>66181</v>
       </c>
     </row>
     <row r="271">
@@ -6121,10 +6121,10 @@
         <v>26.12</v>
       </c>
       <c r="E285" t="n">
-        <v>29.96</v>
+        <v>30.29</v>
       </c>
       <c r="F285" t="n">
-        <v>214756</v>
+        <v>210087</v>
       </c>
     </row>
     <row r="286">
@@ -6135,16 +6135,16 @@
         <v>29.95</v>
       </c>
       <c r="C286" t="n">
-        <v>35.28</v>
+        <v>35.24</v>
       </c>
       <c r="D286" t="n">
         <v>28.9</v>
       </c>
       <c r="E286" t="n">
-        <v>35.16</v>
+        <v>34.72</v>
       </c>
       <c r="F286" t="n">
-        <v>280402</v>
+        <v>275171</v>
       </c>
     </row>
     <row r="287">
@@ -6221,10 +6221,10 @@
         <v>32.46</v>
       </c>
       <c r="E290" t="n">
-        <v>32.8</v>
+        <v>33.2</v>
       </c>
       <c r="F290" t="n">
-        <v>236196</v>
+        <v>230614</v>
       </c>
     </row>
     <row r="291">
@@ -6321,10 +6321,10 @@
         <v>29.42</v>
       </c>
       <c r="E295" t="n">
-        <v>30.59</v>
+        <v>30.65</v>
       </c>
       <c r="F295" t="n">
-        <v>151526</v>
+        <v>146842</v>
       </c>
     </row>
     <row r="296">
@@ -6341,10 +6341,10 @@
         <v>30.13</v>
       </c>
       <c r="E296" t="n">
-        <v>30.68</v>
+        <v>30.78</v>
       </c>
       <c r="F296" t="n">
-        <v>174982</v>
+        <v>171223</v>
       </c>
     </row>
     <row r="297">
@@ -6421,10 +6421,10 @@
         <v>23.38</v>
       </c>
       <c r="E300" t="n">
-        <v>24.73</v>
+        <v>24.74</v>
       </c>
       <c r="F300" t="n">
-        <v>216653</v>
+        <v>213310</v>
       </c>
     </row>
     <row r="301">
@@ -6441,10 +6441,10 @@
         <v>23.7</v>
       </c>
       <c r="E301" t="n">
-        <v>24.99</v>
+        <v>24.98</v>
       </c>
       <c r="F301" t="n">
-        <v>166443</v>
+        <v>163124</v>
       </c>
     </row>
     <row r="302">
@@ -6521,10 +6521,10 @@
         <v>24.33</v>
       </c>
       <c r="E305" t="n">
-        <v>26.85</v>
+        <v>26.83</v>
       </c>
       <c r="F305" t="n">
-        <v>229615</v>
+        <v>224455</v>
       </c>
     </row>
     <row r="306">
@@ -6541,10 +6541,10 @@
         <v>26.05</v>
       </c>
       <c r="E306" t="n">
-        <v>26.81</v>
+        <v>26.78</v>
       </c>
       <c r="F306" t="n">
-        <v>199609</v>
+        <v>196748</v>
       </c>
     </row>
     <row r="307">
@@ -6621,10 +6621,10 @@
         <v>29.4</v>
       </c>
       <c r="E310" t="n">
-        <v>29.65</v>
+        <v>29.48</v>
       </c>
       <c r="F310" t="n">
-        <v>229585</v>
+        <v>225301</v>
       </c>
     </row>
     <row r="311">
@@ -6641,10 +6641,10 @@
         <v>29.63</v>
       </c>
       <c r="E311" t="n">
-        <v>31.25</v>
+        <v>31.26</v>
       </c>
       <c r="F311" t="n">
-        <v>195288</v>
+        <v>192233</v>
       </c>
     </row>
     <row r="312">
@@ -6715,16 +6715,16 @@
         <v>29.73</v>
       </c>
       <c r="C315" t="n">
-        <v>31.75</v>
+        <v>31.65</v>
       </c>
       <c r="D315" t="n">
         <v>29.32</v>
       </c>
       <c r="E315" t="n">
-        <v>31.58</v>
+        <v>31.44</v>
       </c>
       <c r="F315" t="n">
-        <v>156389</v>
+        <v>152193</v>
       </c>
     </row>
     <row r="316">
@@ -6735,16 +6735,16 @@
         <v>31.58</v>
       </c>
       <c r="C316" t="n">
-        <v>33.06</v>
+        <v>32.96</v>
       </c>
       <c r="D316" t="n">
         <v>31.23</v>
       </c>
       <c r="E316" t="n">
-        <v>32.94</v>
+        <v>32.9</v>
       </c>
       <c r="F316" t="n">
-        <v>163209</v>
+        <v>160121</v>
       </c>
     </row>
     <row r="317">
@@ -6821,10 +6821,10 @@
         <v>35.92</v>
       </c>
       <c r="E320" t="n">
-        <v>36.3</v>
+        <v>36.38</v>
       </c>
       <c r="F320" t="n">
-        <v>160329</v>
+        <v>157279</v>
       </c>
     </row>
     <row r="321">
@@ -6841,10 +6841,10 @@
         <v>33.87</v>
       </c>
       <c r="E321" t="n">
-        <v>35.52</v>
+        <v>35.66</v>
       </c>
       <c r="F321" t="n">
-        <v>198023</v>
+        <v>194062</v>
       </c>
     </row>
     <row r="322">
@@ -6921,10 +6921,10 @@
         <v>34.37</v>
       </c>
       <c r="E325" t="n">
-        <v>35.98</v>
+        <v>35.89</v>
       </c>
       <c r="F325" t="n">
-        <v>213086</v>
+        <v>208524</v>
       </c>
     </row>
     <row r="326">
@@ -6941,10 +6941,10 @@
         <v>34.87</v>
       </c>
       <c r="E326" t="n">
-        <v>37.61</v>
+        <v>37.43</v>
       </c>
       <c r="F326" t="n">
-        <v>198370</v>
+        <v>193664</v>
       </c>
     </row>
     <row r="327">
@@ -7021,10 +7021,10 @@
         <v>39.05</v>
       </c>
       <c r="E330" t="n">
-        <v>39.92</v>
+        <v>39.78</v>
       </c>
       <c r="F330" t="n">
-        <v>161661</v>
+        <v>158433</v>
       </c>
     </row>
     <row r="331">
@@ -7041,10 +7041,10 @@
         <v>39.75</v>
       </c>
       <c r="E331" t="n">
-        <v>41.83</v>
+        <v>42.14</v>
       </c>
       <c r="F331" t="n">
-        <v>167359</v>
+        <v>163467</v>
       </c>
     </row>
     <row r="332">
@@ -7121,10 +7121,10 @@
         <v>37.96</v>
       </c>
       <c r="E335" t="n">
-        <v>38.41</v>
+        <v>38.36</v>
       </c>
       <c r="F335" t="n">
-        <v>227925</v>
+        <v>221502</v>
       </c>
     </row>
     <row r="336">
@@ -7141,10 +7141,10 @@
         <v>37.14</v>
       </c>
       <c r="E336" t="n">
-        <v>38.97</v>
+        <v>38.94</v>
       </c>
       <c r="F336" t="n">
-        <v>263342</v>
+        <v>260674</v>
       </c>
     </row>
     <row r="337">
@@ -7221,10 +7221,10 @@
         <v>40.05</v>
       </c>
       <c r="E340" t="n">
-        <v>41.33</v>
+        <v>41.37</v>
       </c>
       <c r="F340" t="n">
-        <v>163774</v>
+        <v>161532</v>
       </c>
     </row>
     <row r="341">
@@ -7241,10 +7241,10 @@
         <v>40.97</v>
       </c>
       <c r="E341" t="n">
-        <v>41.78</v>
+        <v>41.99</v>
       </c>
       <c r="F341" t="n">
-        <v>156573</v>
+        <v>153177</v>
       </c>
     </row>
     <row r="342">
@@ -7315,16 +7315,16 @@
         <v>40.45</v>
       </c>
       <c r="C345" t="n">
-        <v>41.59</v>
+        <v>41.51</v>
       </c>
       <c r="D345" t="n">
         <v>39.68</v>
       </c>
       <c r="E345" t="n">
-        <v>41.35</v>
+        <v>41.39</v>
       </c>
       <c r="F345" t="n">
-        <v>181021</v>
+        <v>178413</v>
       </c>
     </row>
     <row r="346">
@@ -7341,10 +7341,10 @@
         <v>40.25</v>
       </c>
       <c r="E346" t="n">
-        <v>40.57</v>
+        <v>40.58</v>
       </c>
       <c r="F346" t="n">
-        <v>160433</v>
+        <v>157969</v>
       </c>
     </row>
     <row r="347">
@@ -7421,10 +7421,10 @@
         <v>41.71</v>
       </c>
       <c r="E350" t="n">
-        <v>42.65</v>
+        <v>42.71</v>
       </c>
       <c r="F350" t="n">
-        <v>144329</v>
+        <v>142409</v>
       </c>
     </row>
     <row r="351">
@@ -7521,10 +7521,10 @@
         <v>41.99</v>
       </c>
       <c r="E355" t="n">
-        <v>42.35</v>
+        <v>42.32</v>
       </c>
       <c r="F355" t="n">
-        <v>136451</v>
+        <v>133908</v>
       </c>
     </row>
     <row r="356">
@@ -7541,10 +7541,10 @@
         <v>41.4</v>
       </c>
       <c r="E356" t="n">
-        <v>43.26</v>
+        <v>43.23</v>
       </c>
       <c r="F356" t="n">
-        <v>154800</v>
+        <v>152491</v>
       </c>
     </row>
     <row r="357">
@@ -7621,10 +7621,10 @@
         <v>43.19</v>
       </c>
       <c r="E360" t="n">
-        <v>43.28</v>
+        <v>43.36</v>
       </c>
       <c r="F360" t="n">
-        <v>101544</v>
+        <v>99613</v>
       </c>
     </row>
     <row r="361">
@@ -7641,10 +7641,10 @@
         <v>42.7</v>
       </c>
       <c r="E361" t="n">
-        <v>43.12</v>
+        <v>43.18</v>
       </c>
       <c r="F361" t="n">
-        <v>95049</v>
+        <v>93740</v>
       </c>
     </row>
     <row r="362">
@@ -7721,10 +7721,10 @@
         <v>43.42</v>
       </c>
       <c r="E365" t="n">
-        <v>43.53</v>
+        <v>43.82</v>
       </c>
       <c r="F365" t="n">
-        <v>112495</v>
+        <v>109900</v>
       </c>
     </row>
     <row r="366">
@@ -7741,10 +7741,10 @@
         <v>43.18</v>
       </c>
       <c r="E366" t="n">
-        <v>43.62</v>
+        <v>43.67</v>
       </c>
       <c r="F366" t="n">
-        <v>117377</v>
+        <v>115737</v>
       </c>
     </row>
     <row r="367">
@@ -7821,10 +7821,10 @@
         <v>41.95</v>
       </c>
       <c r="E370" t="n">
-        <v>43.56</v>
+        <v>43.43</v>
       </c>
       <c r="F370" t="n">
-        <v>117072</v>
+        <v>113377</v>
       </c>
     </row>
     <row r="371">
@@ -7841,10 +7841,10 @@
         <v>42.94</v>
       </c>
       <c r="E371" t="n">
-        <v>43.59</v>
+        <v>43.65</v>
       </c>
       <c r="F371" t="n">
-        <v>128800</v>
+        <v>127155</v>
       </c>
     </row>
     <row r="372">
@@ -7921,10 +7921,10 @@
         <v>44.96</v>
       </c>
       <c r="E375" t="n">
-        <v>45.13</v>
+        <v>45.28</v>
       </c>
       <c r="F375" t="n">
-        <v>122044</v>
+        <v>120720</v>
       </c>
     </row>
     <row r="376">
@@ -7941,10 +7941,10 @@
         <v>44.4</v>
       </c>
       <c r="E376" t="n">
-        <v>44.71</v>
+        <v>44.76</v>
       </c>
       <c r="F376" t="n">
-        <v>120731</v>
+        <v>119541</v>
       </c>
     </row>
     <row r="377">
@@ -8021,10 +8021,10 @@
         <v>45.07</v>
       </c>
       <c r="E380" t="n">
-        <v>45.24</v>
+        <v>45.3</v>
       </c>
       <c r="F380" t="n">
-        <v>91702</v>
+        <v>90204</v>
       </c>
     </row>
     <row r="381">
@@ -8041,10 +8041,10 @@
         <v>44.77</v>
       </c>
       <c r="E381" t="n">
-        <v>45.19</v>
+        <v>45.2</v>
       </c>
       <c r="F381" t="n">
-        <v>85013</v>
+        <v>83793</v>
       </c>
     </row>
     <row r="382">
@@ -8121,10 +8121,10 @@
         <v>44.46</v>
       </c>
       <c r="E385" t="n">
-        <v>45.27</v>
+        <v>45.36</v>
       </c>
       <c r="F385" t="n">
-        <v>87294</v>
+        <v>86301</v>
       </c>
     </row>
     <row r="386">
@@ -8141,10 +8141,10 @@
         <v>44.09</v>
       </c>
       <c r="E386" t="n">
-        <v>44.69</v>
+        <v>44.79</v>
       </c>
       <c r="F386" t="n">
-        <v>78965</v>
+        <v>77659</v>
       </c>
     </row>
     <row r="387">
@@ -8224,7 +8224,7 @@
         <v>45.59</v>
       </c>
       <c r="F390" t="n">
-        <v>96916</v>
+        <v>95873</v>
       </c>
     </row>
     <row r="391">
@@ -8241,10 +8241,10 @@
         <v>45.36</v>
       </c>
       <c r="E391" t="n">
-        <v>45.85</v>
+        <v>45.89</v>
       </c>
       <c r="F391" t="n">
-        <v>81841</v>
+        <v>81058</v>
       </c>
     </row>
     <row r="392">
@@ -8321,10 +8321,10 @@
         <v>43.27</v>
       </c>
       <c r="E395" t="n">
-        <v>44.07</v>
+        <v>44.09</v>
       </c>
       <c r="F395" t="n">
-        <v>158723</v>
+        <v>157249</v>
       </c>
     </row>
     <row r="396">
@@ -8338,13 +8338,13 @@
         <v>44.69</v>
       </c>
       <c r="D396" t="n">
-        <v>42.42</v>
+        <v>42.45</v>
       </c>
       <c r="E396" t="n">
-        <v>42.43</v>
+        <v>42.53</v>
       </c>
       <c r="F396" t="n">
-        <v>162787</v>
+        <v>160902</v>
       </c>
     </row>
     <row r="397">
@@ -8418,13 +8418,13 @@
         <v>41.23</v>
       </c>
       <c r="D400" t="n">
-        <v>39.96</v>
+        <v>40.02</v>
       </c>
       <c r="E400" t="n">
-        <v>39.97</v>
+        <v>40.07</v>
       </c>
       <c r="F400" t="n">
-        <v>149451</v>
+        <v>147551</v>
       </c>
     </row>
     <row r="401">
@@ -8441,10 +8441,10 @@
         <v>39.68</v>
       </c>
       <c r="E401" t="n">
-        <v>40.02</v>
+        <v>40.24</v>
       </c>
       <c r="F401" t="n">
-        <v>135456</v>
+        <v>133943</v>
       </c>
     </row>
     <row r="402">
@@ -8521,10 +8521,10 @@
         <v>41.89</v>
       </c>
       <c r="E405" t="n">
-        <v>43.58</v>
+        <v>43.67</v>
       </c>
       <c r="F405" t="n">
-        <v>142611</v>
+        <v>141089</v>
       </c>
     </row>
     <row r="406">
@@ -8541,10 +8541,10 @@
         <v>42.92</v>
       </c>
       <c r="E406" t="n">
-        <v>43.41</v>
+        <v>43.34</v>
       </c>
       <c r="F406" t="n">
-        <v>129546</v>
+        <v>127380</v>
       </c>
     </row>
     <row r="407">
@@ -8621,10 +8621,10 @@
         <v>41.68</v>
       </c>
       <c r="E410" t="n">
-        <v>42.16</v>
+        <v>42.27</v>
       </c>
       <c r="F410" t="n">
-        <v>133961</v>
+        <v>132502</v>
       </c>
     </row>
     <row r="411">
@@ -8641,10 +8641,10 @@
         <v>41.97</v>
       </c>
       <c r="E411" t="n">
-        <v>42.17</v>
+        <v>42.24</v>
       </c>
       <c r="F411" t="n">
-        <v>102107</v>
+        <v>100264</v>
       </c>
     </row>
     <row r="412">
@@ -8721,10 +8721,10 @@
         <v>39.98</v>
       </c>
       <c r="E415" t="n">
-        <v>40.75</v>
+        <v>40.93</v>
       </c>
       <c r="F415" t="n">
-        <v>157712</v>
+        <v>155461</v>
       </c>
     </row>
     <row r="416">
@@ -8741,10 +8741,10 @@
         <v>38.88</v>
       </c>
       <c r="E416" t="n">
-        <v>39.15</v>
+        <v>39.23</v>
       </c>
       <c r="F416" t="n">
-        <v>190634</v>
+        <v>188336</v>
       </c>
     </row>
     <row r="417">
@@ -8821,10 +8821,10 @@
         <v>42.02</v>
       </c>
       <c r="E420" t="n">
-        <v>43.52</v>
+        <v>43.54</v>
       </c>
       <c r="F420" t="n">
-        <v>112342</v>
+        <v>110782</v>
       </c>
     </row>
     <row r="421">
@@ -8841,10 +8841,10 @@
         <v>42.78</v>
       </c>
       <c r="E421" t="n">
-        <v>42.89</v>
+        <v>42.96</v>
       </c>
       <c r="F421" t="n">
-        <v>109695</v>
+        <v>108274</v>
       </c>
     </row>
     <row r="422">
@@ -8921,10 +8921,10 @@
         <v>41.79</v>
       </c>
       <c r="E425" t="n">
-        <v>43.26</v>
+        <v>43.38</v>
       </c>
       <c r="F425" t="n">
-        <v>147757</v>
+        <v>146298</v>
       </c>
     </row>
     <row r="426">
@@ -8941,10 +8941,10 @@
         <v>42.47</v>
       </c>
       <c r="E426" t="n">
-        <v>42.95</v>
+        <v>43.02</v>
       </c>
       <c r="F426" t="n">
-        <v>130839</v>
+        <v>129338</v>
       </c>
     </row>
     <row r="427">
@@ -9021,10 +9021,10 @@
         <v>41.72</v>
       </c>
       <c r="E430" t="n">
-        <v>42.59</v>
+        <v>42.71</v>
       </c>
       <c r="F430" t="n">
-        <v>110171</v>
+        <v>108471</v>
       </c>
     </row>
     <row r="431">
@@ -9041,10 +9041,10 @@
         <v>41.76</v>
       </c>
       <c r="E431" t="n">
-        <v>41.85</v>
+        <v>41.93</v>
       </c>
       <c r="F431" t="n">
-        <v>97195</v>
+        <v>95688</v>
       </c>
     </row>
     <row r="432">
@@ -9112,7 +9112,7 @@
         <v>44133</v>
       </c>
       <c r="B435" t="n">
-        <v>39.76</v>
+        <v>39.52</v>
       </c>
       <c r="C435" t="n">
         <v>39.97</v>
@@ -9124,7 +9124,7 @@
         <v>38.05</v>
       </c>
       <c r="F435" t="n">
-        <v>179602</v>
+        <v>183949</v>
       </c>
     </row>
     <row r="436">
@@ -9132,7 +9132,7 @@
         <v>44134</v>
       </c>
       <c r="B436" t="n">
-        <v>38.25</v>
+        <v>38.05</v>
       </c>
       <c r="C436" t="n">
         <v>38.72</v>
@@ -9144,7 +9144,7 @@
         <v>37.84</v>
       </c>
       <c r="F436" t="n">
-        <v>181739</v>
+        <v>184633</v>
       </c>
     </row>
     <row r="437">
@@ -9221,10 +9221,10 @@
         <v>40.42</v>
       </c>
       <c r="E440" t="n">
-        <v>40.68</v>
+        <v>40.82</v>
       </c>
       <c r="F440" t="n">
-        <v>157779</v>
+        <v>155706</v>
       </c>
     </row>
     <row r="441">
@@ -9241,10 +9241,10 @@
         <v>39.46</v>
       </c>
       <c r="E441" t="n">
-        <v>39.71</v>
+        <v>39.84</v>
       </c>
       <c r="F441" t="n">
-        <v>151438</v>
+        <v>150078</v>
       </c>
     </row>
     <row r="442">
@@ -9318,13 +9318,13 @@
         <v>44.59</v>
       </c>
       <c r="D445" t="n">
-        <v>43.35</v>
+        <v>43.42</v>
       </c>
       <c r="E445" t="n">
-        <v>43.38</v>
+        <v>43.49</v>
       </c>
       <c r="F445" t="n">
-        <v>146964</v>
+        <v>144322</v>
       </c>
     </row>
     <row r="446">
@@ -9338,13 +9338,13 @@
         <v>43.45</v>
       </c>
       <c r="D446" t="n">
-        <v>42.68</v>
+        <v>42.77</v>
       </c>
       <c r="E446" t="n">
-        <v>42.69</v>
+        <v>42.88</v>
       </c>
       <c r="F446" t="n">
-        <v>114191</v>
+        <v>112789</v>
       </c>
     </row>
     <row r="447">
@@ -9421,10 +9421,10 @@
         <v>43.87</v>
       </c>
       <c r="E450" t="n">
-        <v>44.21</v>
+        <v>44.44</v>
       </c>
       <c r="F450" t="n">
-        <v>112468</v>
+        <v>111013</v>
       </c>
     </row>
     <row r="451">
@@ -9441,10 +9441,10 @@
         <v>44.15</v>
       </c>
       <c r="E451" t="n">
-        <v>45.07</v>
+        <v>45.06</v>
       </c>
       <c r="F451" t="n">
-        <v>90427</v>
+        <v>88612</v>
       </c>
     </row>
     <row r="452">
@@ -9624,7 +9624,7 @@
         <v>48.65</v>
       </c>
       <c r="F460" t="n">
-        <v>122403</v>
+        <v>119976</v>
       </c>
     </row>
     <row r="461">
@@ -9641,10 +9641,10 @@
         <v>48.77</v>
       </c>
       <c r="E461" t="n">
-        <v>48.96</v>
+        <v>48.97</v>
       </c>
       <c r="F461" t="n">
-        <v>125701</v>
+        <v>124413</v>
       </c>
     </row>
     <row r="462">
@@ -9721,10 +9721,10 @@
         <v>48.79</v>
       </c>
       <c r="E465" t="n">
-        <v>50.25</v>
+        <v>50.26</v>
       </c>
       <c r="F465" t="n">
-        <v>132386</v>
+        <v>130125</v>
       </c>
     </row>
     <row r="466">
@@ -9741,10 +9741,10 @@
         <v>49.67</v>
       </c>
       <c r="E466" t="n">
-        <v>49.86</v>
+        <v>49.94</v>
       </c>
       <c r="F466" t="n">
-        <v>124721</v>
+        <v>123293</v>
       </c>
     </row>
     <row r="467">
@@ -9821,10 +9821,10 @@
         <v>51.06</v>
       </c>
       <c r="E470" t="n">
-        <v>51.46</v>
+        <v>51.55</v>
       </c>
       <c r="F470" t="n">
-        <v>102867</v>
+        <v>100894</v>
       </c>
     </row>
     <row r="471">
@@ -9841,10 +9841,10 @@
         <v>51.16</v>
       </c>
       <c r="E471" t="n">
-        <v>52.23</v>
+        <v>52.19</v>
       </c>
       <c r="F471" t="n">
-        <v>98705</v>
+        <v>96861</v>
       </c>
     </row>
     <row r="472">
@@ -10081,10 +10081,10 @@
         <v>53.88</v>
       </c>
       <c r="E483" t="n">
-        <v>54.34</v>
+        <v>54.45</v>
       </c>
       <c r="F483" t="n">
-        <v>142258</v>
+        <v>140683</v>
       </c>
     </row>
     <row r="484">
@@ -10095,16 +10095,16 @@
         <v>54.46</v>
       </c>
       <c r="C484" t="n">
-        <v>56.2</v>
+        <v>56.06</v>
       </c>
       <c r="D484" t="n">
         <v>54.3</v>
       </c>
       <c r="E484" t="n">
-        <v>56.11</v>
+        <v>56.02</v>
       </c>
       <c r="F484" t="n">
-        <v>155413</v>
+        <v>151805</v>
       </c>
     </row>
     <row r="485">
@@ -10181,10 +10181,10 @@
         <v>55.21</v>
       </c>
       <c r="E488" t="n">
-        <v>56.37</v>
+        <v>56.3</v>
       </c>
       <c r="F488" t="n">
-        <v>125098</v>
+        <v>123090</v>
       </c>
     </row>
     <row r="489">
@@ -10201,10 +10201,10 @@
         <v>54.63</v>
       </c>
       <c r="E489" t="n">
-        <v>54.75</v>
+        <v>54.94</v>
       </c>
       <c r="F489" t="n">
-        <v>135898</v>
+        <v>133988</v>
       </c>
     </row>
     <row r="490">
@@ -10281,10 +10281,10 @@
         <v>55.38</v>
       </c>
       <c r="E493" t="n">
-        <v>55.84</v>
+        <v>55.86</v>
       </c>
       <c r="F493" t="n">
-        <v>104851</v>
+        <v>103188</v>
       </c>
     </row>
     <row r="494">
@@ -10301,10 +10301,10 @@
         <v>54.38</v>
       </c>
       <c r="E494" t="n">
-        <v>54.88</v>
+        <v>55.08</v>
       </c>
       <c r="F494" t="n">
-        <v>135622</v>
+        <v>133367</v>
       </c>
     </row>
     <row r="495">
@@ -10378,13 +10378,13 @@
         <v>56.16</v>
       </c>
       <c r="D498" t="n">
-        <v>54.84</v>
+        <v>54.93</v>
       </c>
       <c r="E498" t="n">
-        <v>54.84</v>
+        <v>55</v>
       </c>
       <c r="F498" t="n">
-        <v>162289</v>
+        <v>160473</v>
       </c>
     </row>
     <row r="499">
@@ -10401,10 +10401,10 @@
         <v>54.84</v>
       </c>
       <c r="E499" t="n">
-        <v>54.93</v>
+        <v>55</v>
       </c>
       <c r="F499" t="n">
-        <v>163671</v>
+        <v>160923</v>
       </c>
     </row>
     <row r="500">
@@ -10481,10 +10481,10 @@
         <v>57.93</v>
       </c>
       <c r="E503" t="n">
-        <v>58.87</v>
+        <v>58.79</v>
       </c>
       <c r="F503" t="n">
-        <v>125851</v>
+        <v>123567</v>
       </c>
     </row>
     <row r="504">
@@ -10501,10 +10501,10 @@
         <v>58.87</v>
       </c>
       <c r="E504" t="n">
-        <v>59.41</v>
+        <v>59.31</v>
       </c>
       <c r="F504" t="n">
-        <v>120954</v>
+        <v>118436</v>
       </c>
     </row>
     <row r="505">
@@ -10578,13 +10578,13 @@
         <v>61.23</v>
       </c>
       <c r="D508" t="n">
-        <v>60.44</v>
+        <v>60.5</v>
       </c>
       <c r="E508" t="n">
-        <v>60.52</v>
+        <v>60.6</v>
       </c>
       <c r="F508" t="n">
-        <v>107974</v>
+        <v>104511</v>
       </c>
     </row>
     <row r="509">
@@ -10604,7 +10604,7 @@
         <v>62.22</v>
       </c>
       <c r="F509" t="n">
-        <v>126905</v>
+        <v>123306</v>
       </c>
     </row>
     <row r="510">
@@ -10681,10 +10681,10 @@
         <v>62.54</v>
       </c>
       <c r="E513" t="n">
-        <v>62.88</v>
+        <v>62.75</v>
       </c>
       <c r="F513" t="n">
-        <v>173632</v>
+        <v>170306</v>
       </c>
     </row>
     <row r="514">
@@ -10701,10 +10701,10 @@
         <v>61.42</v>
       </c>
       <c r="E514" t="n">
-        <v>61.97</v>
+        <v>61.95</v>
       </c>
       <c r="F514" t="n">
-        <v>184306</v>
+        <v>181146</v>
       </c>
     </row>
     <row r="515">
@@ -10781,10 +10781,10 @@
         <v>65.55</v>
       </c>
       <c r="E518" t="n">
-        <v>65.97</v>
+        <v>65.86</v>
       </c>
       <c r="F518" t="n">
-        <v>215533</v>
+        <v>210726</v>
       </c>
     </row>
     <row r="519">
@@ -10801,10 +10801,10 @@
         <v>64.13</v>
       </c>
       <c r="E519" t="n">
-        <v>64.27</v>
+        <v>64.25</v>
       </c>
       <c r="F519" t="n">
-        <v>239274</v>
+        <v>234931</v>
       </c>
     </row>
     <row r="520">
@@ -10881,10 +10881,10 @@
         <v>63.17</v>
       </c>
       <c r="E523" t="n">
-        <v>66.73999999999999</v>
+        <v>66.94</v>
       </c>
       <c r="F523" t="n">
-        <v>230530</v>
+        <v>225843</v>
       </c>
     </row>
     <row r="524">
@@ -10895,16 +10895,16 @@
         <v>66.86</v>
       </c>
       <c r="C524" t="n">
-        <v>69.41</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="D524" t="n">
         <v>66.43000000000001</v>
       </c>
       <c r="E524" t="n">
-        <v>69.25</v>
+        <v>69.28</v>
       </c>
       <c r="F524" t="n">
-        <v>253026</v>
+        <v>249828</v>
       </c>
     </row>
     <row r="525">
@@ -10981,10 +10981,10 @@
         <v>67.68000000000001</v>
       </c>
       <c r="E528" t="n">
-        <v>69.17</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="F528" t="n">
-        <v>163581</v>
+        <v>160838</v>
       </c>
     </row>
     <row r="529">
@@ -11001,10 +11001,10 @@
         <v>68.66</v>
       </c>
       <c r="E529" t="n">
-        <v>68.81</v>
+        <v>68.88</v>
       </c>
       <c r="F529" t="n">
-        <v>151042</v>
+        <v>148823</v>
       </c>
     </row>
     <row r="530">
@@ -11072,7 +11072,7 @@
         <v>44273</v>
       </c>
       <c r="B533" t="n">
-        <v>67.47</v>
+        <v>67.48</v>
       </c>
       <c r="C533" t="n">
         <v>67.83</v>
@@ -11084,7 +11084,7 @@
         <v>62.5</v>
       </c>
       <c r="F533" t="n">
-        <v>209835</v>
+        <v>212082</v>
       </c>
     </row>
     <row r="534">
@@ -11092,7 +11092,7 @@
         <v>44274</v>
       </c>
       <c r="B534" t="n">
-        <v>63.02</v>
+        <v>62.78</v>
       </c>
       <c r="C534" t="n">
         <v>64.73</v>
@@ -11104,7 +11104,7 @@
         <v>64.31999999999999</v>
       </c>
       <c r="F534" t="n">
-        <v>223529</v>
+        <v>228148</v>
       </c>
     </row>
     <row r="535">
@@ -11172,10 +11172,10 @@
         <v>44280</v>
       </c>
       <c r="B538" t="n">
-        <v>63.89</v>
+        <v>63.95</v>
       </c>
       <c r="C538" t="n">
-        <v>63.9</v>
+        <v>64.01000000000001</v>
       </c>
       <c r="D538" t="n">
         <v>60.82</v>
@@ -11184,7 +11184,7 @@
         <v>61.47</v>
       </c>
       <c r="F538" t="n">
-        <v>203253</v>
+        <v>206155</v>
       </c>
     </row>
     <row r="539">
@@ -11192,19 +11192,19 @@
         <v>44281</v>
       </c>
       <c r="B539" t="n">
-        <v>62.45</v>
+        <v>61.47</v>
       </c>
       <c r="C539" t="n">
         <v>64.73</v>
       </c>
       <c r="D539" t="n">
-        <v>62.07</v>
+        <v>61.47</v>
       </c>
       <c r="E539" t="n">
         <v>64.19</v>
       </c>
       <c r="F539" t="n">
-        <v>167422</v>
+        <v>171041</v>
       </c>
     </row>
     <row r="540">
@@ -11284,7 +11284,7 @@
         <v>64.51000000000001</v>
       </c>
       <c r="F543" t="n">
-        <v>201289</v>
+        <v>197783</v>
       </c>
     </row>
     <row r="544">
@@ -11361,10 +11361,10 @@
         <v>62.18</v>
       </c>
       <c r="E547" t="n">
-        <v>63.04</v>
+        <v>63.07</v>
       </c>
       <c r="F547" t="n">
-        <v>149186</v>
+        <v>146277</v>
       </c>
     </row>
     <row r="548">
@@ -11381,10 +11381,10 @@
         <v>62.33</v>
       </c>
       <c r="E548" t="n">
-        <v>62.76</v>
+        <v>62.81</v>
       </c>
       <c r="F548" t="n">
-        <v>121247</v>
+        <v>119219</v>
       </c>
     </row>
     <row r="549">
@@ -11461,10 +11461,10 @@
         <v>65.65000000000001</v>
       </c>
       <c r="E552" t="n">
-        <v>66.45</v>
+        <v>66.5</v>
       </c>
       <c r="F552" t="n">
-        <v>135521</v>
+        <v>133306</v>
       </c>
     </row>
     <row r="553">
@@ -11481,10 +11481,10 @@
         <v>66.11</v>
       </c>
       <c r="E553" t="n">
-        <v>66.31999999999999</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="F553" t="n">
-        <v>122938</v>
+        <v>120895</v>
       </c>
     </row>
     <row r="554">
@@ -11564,7 +11564,7 @@
         <v>64.95</v>
       </c>
       <c r="F557" t="n">
-        <v>143350</v>
+        <v>140975</v>
       </c>
     </row>
     <row r="558">
@@ -11581,10 +11581,10 @@
         <v>64.52</v>
       </c>
       <c r="E558" t="n">
-        <v>65.31999999999999</v>
+        <v>65.45</v>
       </c>
       <c r="F558" t="n">
-        <v>126302</v>
+        <v>124432</v>
       </c>
     </row>
     <row r="559">
@@ -11661,10 +11661,10 @@
         <v>66.56</v>
       </c>
       <c r="E562" t="n">
-        <v>67.84999999999999</v>
+        <v>67.86</v>
       </c>
       <c r="F562" t="n">
-        <v>160482</v>
+        <v>157092</v>
       </c>
     </row>
     <row r="563">
@@ -11681,10 +11681,10 @@
         <v>66.17</v>
       </c>
       <c r="E563" t="n">
-        <v>66.53</v>
+        <v>66.56</v>
       </c>
       <c r="F563" t="n">
-        <v>148372</v>
+        <v>145779</v>
       </c>
     </row>
     <row r="564">
@@ -11761,10 +11761,10 @@
         <v>67.77</v>
       </c>
       <c r="E567" t="n">
-        <v>68.03</v>
+        <v>68.05</v>
       </c>
       <c r="F567" t="n">
-        <v>155507</v>
+        <v>153533</v>
       </c>
     </row>
     <row r="568">
@@ -11784,7 +11784,7 @@
         <v>68.03</v>
       </c>
       <c r="F568" t="n">
-        <v>139157</v>
+        <v>136012</v>
       </c>
     </row>
     <row r="569">
@@ -11861,10 +11861,10 @@
         <v>66.34</v>
       </c>
       <c r="E572" t="n">
-        <v>66.81999999999999</v>
+        <v>66.83</v>
       </c>
       <c r="F572" t="n">
-        <v>182316</v>
+        <v>180093</v>
       </c>
     </row>
     <row r="573">
@@ -11875,16 +11875,16 @@
         <v>66.81</v>
       </c>
       <c r="C573" t="n">
-        <v>68.63</v>
+        <v>68.52</v>
       </c>
       <c r="D573" t="n">
         <v>66.36</v>
       </c>
       <c r="E573" t="n">
-        <v>68.52</v>
+        <v>68.45</v>
       </c>
       <c r="F573" t="n">
-        <v>142226</v>
+        <v>139950</v>
       </c>
     </row>
     <row r="574">
@@ -11958,13 +11958,13 @@
         <v>67.02</v>
       </c>
       <c r="D577" t="n">
-        <v>64.70999999999999</v>
+        <v>64.73</v>
       </c>
       <c r="E577" t="n">
-        <v>64.73999999999999</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="F577" t="n">
-        <v>168733</v>
+        <v>164782</v>
       </c>
     </row>
     <row r="578">
@@ -11981,10 +11981,10 @@
         <v>64.48</v>
       </c>
       <c r="E578" t="n">
-        <v>66.51000000000001</v>
+        <v>66.58</v>
       </c>
       <c r="F578" t="n">
-        <v>156317</v>
+        <v>153693</v>
       </c>
     </row>
     <row r="579">
@@ -12055,16 +12055,16 @@
         <v>68.58</v>
       </c>
       <c r="C582" t="n">
-        <v>69.2</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="D582" t="n">
         <v>67.89</v>
       </c>
       <c r="E582" t="n">
-        <v>69.12</v>
+        <v>69.05</v>
       </c>
       <c r="F582" t="n">
-        <v>122427</v>
+        <v>119490</v>
       </c>
     </row>
     <row r="583">
@@ -12081,10 +12081,10 @@
         <v>68.48999999999999</v>
       </c>
       <c r="E583" t="n">
-        <v>68.88</v>
+        <v>68.89</v>
       </c>
       <c r="F583" t="n">
-        <v>121324</v>
+        <v>119218</v>
       </c>
     </row>
     <row r="584">
@@ -12161,10 +12161,10 @@
         <v>70.5</v>
       </c>
       <c r="E587" t="n">
-        <v>71.22</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="F587" t="n">
-        <v>128649</v>
+        <v>126247</v>
       </c>
     </row>
     <row r="588">
@@ -12181,10 +12181,10 @@
         <v>70.58</v>
       </c>
       <c r="E588" t="n">
-        <v>71.43000000000001</v>
+        <v>71.47</v>
       </c>
       <c r="F588" t="n">
-        <v>117041</v>
+        <v>113793</v>
       </c>
     </row>
     <row r="589">
@@ -12261,10 +12261,10 @@
         <v>70.66</v>
       </c>
       <c r="E592" t="n">
-        <v>71.95</v>
+        <v>72.09</v>
       </c>
       <c r="F592" t="n">
-        <v>148450</v>
+        <v>146487</v>
       </c>
     </row>
     <row r="593">
@@ -12284,7 +12284,7 @@
         <v>72.23999999999999</v>
       </c>
       <c r="F593" t="n">
-        <v>142367</v>
+        <v>140128</v>
       </c>
     </row>
     <row r="594">
@@ -12361,10 +12361,10 @@
         <v>71.41</v>
       </c>
       <c r="E597" t="n">
-        <v>72.44</v>
+        <v>72.45</v>
       </c>
       <c r="F597" t="n">
-        <v>178094</v>
+        <v>175025</v>
       </c>
     </row>
     <row r="598">
@@ -12381,10 +12381,10 @@
         <v>71.55</v>
       </c>
       <c r="E598" t="n">
-        <v>72.5</v>
+        <v>72.76000000000001</v>
       </c>
       <c r="F598" t="n">
-        <v>151345</v>
+        <v>147859</v>
       </c>
     </row>
     <row r="599">
@@ -12461,10 +12461,10 @@
         <v>73.83</v>
       </c>
       <c r="E602" t="n">
-        <v>74.81</v>
+        <v>74.79000000000001</v>
       </c>
       <c r="F602" t="n">
-        <v>85692</v>
+        <v>84577</v>
       </c>
     </row>
     <row r="603">
@@ -12481,10 +12481,10 @@
         <v>74.14</v>
       </c>
       <c r="E603" t="n">
-        <v>75.28</v>
+        <v>75.27</v>
       </c>
       <c r="F603" t="n">
-        <v>79112</v>
+        <v>77990</v>
       </c>
     </row>
     <row r="604">
@@ -12561,10 +12561,10 @@
         <v>74.36</v>
       </c>
       <c r="E607" t="n">
-        <v>75.34</v>
+        <v>75.33</v>
       </c>
       <c r="F607" t="n">
-        <v>135699</v>
+        <v>134296</v>
       </c>
     </row>
     <row r="608">
@@ -12581,10 +12581,10 @@
         <v>75</v>
       </c>
       <c r="E608" t="n">
-        <v>75.81999999999999</v>
+        <v>76.02</v>
       </c>
       <c r="F608" t="n">
-        <v>104256</v>
+        <v>102316</v>
       </c>
     </row>
     <row r="609">
@@ -12655,16 +12655,16 @@
         <v>72.97</v>
       </c>
       <c r="C612" t="n">
-        <v>74.02</v>
+        <v>73.97</v>
       </c>
       <c r="D612" t="n">
         <v>71.73999999999999</v>
       </c>
       <c r="E612" t="n">
-        <v>73.95999999999999</v>
+        <v>73.92</v>
       </c>
       <c r="F612" t="n">
-        <v>138030</v>
+        <v>136419</v>
       </c>
     </row>
     <row r="613">
@@ -12681,10 +12681,10 @@
         <v>73.38</v>
       </c>
       <c r="E613" t="n">
-        <v>75.14</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="F613" t="n">
-        <v>96988</v>
+        <v>95892</v>
       </c>
     </row>
     <row r="614">
@@ -12761,10 +12761,10 @@
         <v>72.70999999999999</v>
       </c>
       <c r="E617" t="n">
-        <v>72.72</v>
+        <v>72.79000000000001</v>
       </c>
       <c r="F617" t="n">
-        <v>134216</v>
+        <v>132350</v>
       </c>
     </row>
     <row r="618">
@@ -12781,10 +12781,10 @@
         <v>71.88</v>
       </c>
       <c r="E618" t="n">
-        <v>72.64</v>
+        <v>72.81</v>
       </c>
       <c r="F618" t="n">
-        <v>110158</v>
+        <v>108307</v>
       </c>
     </row>
     <row r="619">
@@ -12864,7 +12864,7 @@
         <v>73.01000000000001</v>
       </c>
       <c r="F622" t="n">
-        <v>115159</v>
+        <v>113951</v>
       </c>
     </row>
     <row r="623">
@@ -12875,16 +12875,16 @@
         <v>72.98</v>
       </c>
       <c r="C623" t="n">
-        <v>73.56999999999999</v>
+        <v>73.52</v>
       </c>
       <c r="D623" t="n">
         <v>72.70999999999999</v>
       </c>
       <c r="E623" t="n">
-        <v>73.5</v>
+        <v>73.44</v>
       </c>
       <c r="F623" t="n">
-        <v>84579</v>
+        <v>83411</v>
       </c>
     </row>
     <row r="624">
@@ -12961,10 +12961,10 @@
         <v>73.59999999999999</v>
       </c>
       <c r="E627" t="n">
-        <v>74.75</v>
+        <v>74.97</v>
       </c>
       <c r="F627" t="n">
-        <v>81467</v>
+        <v>79720</v>
       </c>
     </row>
     <row r="628">
@@ -12981,10 +12981,10 @@
         <v>74.26000000000001</v>
       </c>
       <c r="E628" t="n">
-        <v>74.95999999999999</v>
+        <v>74.98999999999999</v>
       </c>
       <c r="F628" t="n">
-        <v>84253</v>
+        <v>83101</v>
       </c>
     </row>
     <row r="629">
@@ -13061,10 +13061,10 @@
         <v>69.56</v>
       </c>
       <c r="E632" t="n">
-        <v>71</v>
+        <v>71.16</v>
       </c>
       <c r="F632" t="n">
-        <v>108267</v>
+        <v>107034</v>
       </c>
     </row>
     <row r="633">
@@ -13078,13 +13078,13 @@
         <v>72.22</v>
       </c>
       <c r="D633" t="n">
-        <v>70.06999999999999</v>
+        <v>70.12</v>
       </c>
       <c r="E633" t="n">
-        <v>70.08</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="F633" t="n">
-        <v>113105</v>
+        <v>111453</v>
       </c>
     </row>
     <row r="634">
@@ -13161,10 +13161,10 @@
         <v>70.41</v>
       </c>
       <c r="E637" t="n">
-        <v>70.86</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="F637" t="n">
-        <v>96203</v>
+        <v>95219</v>
       </c>
     </row>
     <row r="638">
@@ -13181,10 +13181,10 @@
         <v>69.73999999999999</v>
       </c>
       <c r="E638" t="n">
-        <v>69.90000000000001</v>
+        <v>69.92</v>
       </c>
       <c r="F638" t="n">
-        <v>95696</v>
+        <v>93960</v>
       </c>
     </row>
     <row r="639">
@@ -13261,10 +13261,10 @@
         <v>65.2</v>
       </c>
       <c r="E642" t="n">
-        <v>66.23</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="F642" t="n">
-        <v>187712</v>
+        <v>185678</v>
       </c>
     </row>
     <row r="643">
@@ -13278,13 +13278,13 @@
         <v>66.54000000000001</v>
       </c>
       <c r="D643" t="n">
-        <v>64.53</v>
+        <v>64.61</v>
       </c>
       <c r="E643" t="n">
-        <v>64.54000000000001</v>
+        <v>64.62</v>
       </c>
       <c r="F643" t="n">
-        <v>138989</v>
+        <v>137258</v>
       </c>
     </row>
     <row r="644">
@@ -13361,10 +13361,10 @@
         <v>69.73999999999999</v>
       </c>
       <c r="E647" t="n">
-        <v>70.45999999999999</v>
+        <v>70.56</v>
       </c>
       <c r="F647" t="n">
-        <v>115965</v>
+        <v>113839</v>
       </c>
     </row>
     <row r="648">
@@ -13381,10 +13381,10 @@
         <v>70.16</v>
       </c>
       <c r="E648" t="n">
-        <v>71.5</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="F648" t="n">
-        <v>100455</v>
+        <v>99158</v>
       </c>
     </row>
     <row r="649">
@@ -13461,10 +13461,10 @@
         <v>70.75</v>
       </c>
       <c r="E652" t="n">
-        <v>72.61</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="F652" t="n">
-        <v>105073</v>
+        <v>103772</v>
       </c>
     </row>
     <row r="653">
@@ -13481,10 +13481,10 @@
         <v>72.20999999999999</v>
       </c>
       <c r="E653" t="n">
-        <v>72.20999999999999</v>
+        <v>72.36</v>
       </c>
       <c r="F653" t="n">
-        <v>111688</v>
+        <v>110684</v>
       </c>
     </row>
     <row r="654">
@@ -13561,10 +13561,10 @@
         <v>70.54000000000001</v>
       </c>
       <c r="E657" t="n">
-        <v>70.84</v>
+        <v>70.95</v>
       </c>
       <c r="F657" t="n">
-        <v>138553</v>
+        <v>136836</v>
       </c>
     </row>
     <row r="658">
@@ -13581,10 +13581,10 @@
         <v>70.59</v>
       </c>
       <c r="E658" t="n">
-        <v>72.51000000000001</v>
+        <v>72.44</v>
       </c>
       <c r="F658" t="n">
-        <v>107925</v>
+        <v>106315</v>
       </c>
     </row>
     <row r="659">
@@ -13661,10 +13661,10 @@
         <v>74.02</v>
       </c>
       <c r="E662" t="n">
-        <v>75.09</v>
+        <v>75.17</v>
       </c>
       <c r="F662" t="n">
-        <v>136265</v>
+        <v>134873</v>
       </c>
     </row>
     <row r="663">
@@ -13681,10 +13681,10 @@
         <v>74.06999999999999</v>
       </c>
       <c r="E663" t="n">
-        <v>74.67</v>
+        <v>74.79000000000001</v>
       </c>
       <c r="F663" t="n">
-        <v>131243</v>
+        <v>129577</v>
       </c>
     </row>
     <row r="664">
@@ -13764,7 +13764,7 @@
         <v>76.45</v>
       </c>
       <c r="F667" t="n">
-        <v>104066</v>
+        <v>102612</v>
       </c>
     </row>
     <row r="668">
@@ -13781,10 +13781,10 @@
         <v>76.09</v>
       </c>
       <c r="E668" t="n">
-        <v>77.13</v>
+        <v>77.15000000000001</v>
       </c>
       <c r="F668" t="n">
-        <v>94529</v>
+        <v>93448</v>
       </c>
     </row>
     <row r="669">
@@ -13861,10 +13861,10 @@
         <v>76.37</v>
       </c>
       <c r="E672" t="n">
-        <v>78.23999999999999</v>
+        <v>78.13</v>
       </c>
       <c r="F672" t="n">
-        <v>181989</v>
+        <v>180155</v>
       </c>
     </row>
     <row r="673">
@@ -13881,10 +13881,10 @@
         <v>77.38</v>
       </c>
       <c r="E673" t="n">
-        <v>78.93000000000001</v>
+        <v>78.98999999999999</v>
       </c>
       <c r="F673" t="n">
-        <v>151482</v>
+        <v>149729</v>
       </c>
     </row>
     <row r="674">
@@ -13961,10 +13961,10 @@
         <v>78.78</v>
       </c>
       <c r="E677" t="n">
-        <v>82.08</v>
+        <v>82.16</v>
       </c>
       <c r="F677" t="n">
-        <v>153620</v>
+        <v>151677</v>
       </c>
     </row>
     <row r="678">
@@ -13981,10 +13981,10 @@
         <v>81.63</v>
       </c>
       <c r="E678" t="n">
-        <v>82.22</v>
+        <v>82.17</v>
       </c>
       <c r="F678" t="n">
-        <v>149526</v>
+        <v>147722</v>
       </c>
     </row>
     <row r="679">
@@ -14061,10 +14061,10 @@
         <v>82.76000000000001</v>
       </c>
       <c r="E682" t="n">
-        <v>83.67</v>
+        <v>83.69</v>
       </c>
       <c r="F682" t="n">
-        <v>122153</v>
+        <v>120650</v>
       </c>
     </row>
     <row r="683">
@@ -14081,10 +14081,10 @@
         <v>83.68000000000001</v>
       </c>
       <c r="E683" t="n">
-        <v>84.33</v>
+        <v>84.23</v>
       </c>
       <c r="F683" t="n">
-        <v>116437</v>
+        <v>114060</v>
       </c>
     </row>
     <row r="684">
@@ -14161,10 +14161,10 @@
         <v>82.73</v>
       </c>
       <c r="E687" t="n">
-        <v>84.09</v>
+        <v>84.15000000000001</v>
       </c>
       <c r="F687" t="n">
-        <v>122966</v>
+        <v>121250</v>
       </c>
     </row>
     <row r="688">
@@ -14175,16 +14175,16 @@
         <v>83.81999999999999</v>
       </c>
       <c r="C688" t="n">
-        <v>85.08</v>
+        <v>84.97</v>
       </c>
       <c r="D688" t="n">
         <v>83.18000000000001</v>
       </c>
       <c r="E688" t="n">
-        <v>84.83</v>
+        <v>84.97</v>
       </c>
       <c r="F688" t="n">
-        <v>113449</v>
+        <v>111475</v>
       </c>
     </row>
     <row r="689">
@@ -14261,10 +14261,10 @@
         <v>81.48</v>
       </c>
       <c r="E692" t="n">
-        <v>83.78</v>
+        <v>83.83</v>
       </c>
       <c r="F692" t="n">
-        <v>167007</v>
+        <v>164605</v>
       </c>
     </row>
     <row r="693">
@@ -14281,10 +14281,10 @@
         <v>82.39</v>
       </c>
       <c r="E693" t="n">
-        <v>83.41</v>
+        <v>83.55</v>
       </c>
       <c r="F693" t="n">
-        <v>133535</v>
+        <v>132228</v>
       </c>
     </row>
     <row r="694">
@@ -14352,7 +14352,7 @@
         <v>44504</v>
       </c>
       <c r="B697" t="n">
-        <v>80.83</v>
+        <v>81.12</v>
       </c>
       <c r="C697" t="n">
         <v>84.08</v>
@@ -14364,7 +14364,7 @@
         <v>80.54000000000001</v>
       </c>
       <c r="F697" t="n">
-        <v>168783</v>
+        <v>171378</v>
       </c>
     </row>
     <row r="698">
@@ -14372,7 +14372,7 @@
         <v>44505</v>
       </c>
       <c r="B698" t="n">
-        <v>81.04000000000001</v>
+        <v>80.95</v>
       </c>
       <c r="C698" t="n">
         <v>82.72</v>
@@ -14384,7 +14384,7 @@
         <v>81.93000000000001</v>
       </c>
       <c r="F698" t="n">
-        <v>163172</v>
+        <v>166390</v>
       </c>
     </row>
     <row r="699">
@@ -14461,10 +14461,10 @@
         <v>81.06</v>
       </c>
       <c r="E702" t="n">
-        <v>81.92</v>
+        <v>81.91</v>
       </c>
       <c r="F702" t="n">
-        <v>161511</v>
+        <v>159955</v>
       </c>
     </row>
     <row r="703">
@@ -14481,10 +14481,10 @@
         <v>80.63</v>
       </c>
       <c r="E703" t="n">
-        <v>81.29000000000001</v>
+        <v>81.41</v>
       </c>
       <c r="F703" t="n">
-        <v>134507</v>
+        <v>133196</v>
       </c>
     </row>
     <row r="704">
@@ -14561,10 +14561,10 @@
         <v>78.55</v>
       </c>
       <c r="E707" t="n">
-        <v>80.34999999999999</v>
+        <v>80.42</v>
       </c>
       <c r="F707" t="n">
-        <v>132952</v>
+        <v>131123</v>
       </c>
     </row>
     <row r="708">
@@ -14581,10 +14581,10 @@
         <v>77.41</v>
       </c>
       <c r="E708" t="n">
-        <v>77.77</v>
+        <v>77.76000000000001</v>
       </c>
       <c r="F708" t="n">
-        <v>177513</v>
+        <v>175625</v>
       </c>
     </row>
     <row r="709">
@@ -14761,10 +14761,10 @@
         <v>65.67</v>
       </c>
       <c r="E717" t="n">
-        <v>70.36</v>
+        <v>69.94</v>
       </c>
       <c r="F717" t="n">
-        <v>240359</v>
+        <v>237353</v>
       </c>
     </row>
     <row r="718">
@@ -14781,10 +14781,10 @@
         <v>69.09999999999999</v>
       </c>
       <c r="E718" t="n">
-        <v>69.70999999999999</v>
+        <v>69.73</v>
       </c>
       <c r="F718" t="n">
-        <v>208893</v>
+        <v>205214</v>
       </c>
     </row>
     <row r="719">
@@ -14858,13 +14858,13 @@
         <v>76.55</v>
       </c>
       <c r="D722" t="n">
-        <v>73.70999999999999</v>
+        <v>73.78</v>
       </c>
       <c r="E722" t="n">
-        <v>73.84999999999999</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="F722" t="n">
-        <v>142264</v>
+        <v>140659</v>
       </c>
     </row>
     <row r="723">
@@ -14881,10 +14881,10 @@
         <v>73.67</v>
       </c>
       <c r="E723" t="n">
-        <v>75.16</v>
+        <v>75.23</v>
       </c>
       <c r="F723" t="n">
-        <v>153301</v>
+        <v>151698</v>
       </c>
     </row>
     <row r="724">
@@ -14961,10 +14961,10 @@
         <v>73.88</v>
       </c>
       <c r="E727" t="n">
-        <v>74.48999999999999</v>
+        <v>74.63</v>
       </c>
       <c r="F727" t="n">
-        <v>142563</v>
+        <v>140474</v>
       </c>
     </row>
     <row r="728">
@@ -14981,10 +14981,10 @@
         <v>72.63</v>
       </c>
       <c r="E728" t="n">
-        <v>72.88</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="F728" t="n">
-        <v>154875</v>
+        <v>152160</v>
       </c>
     </row>
     <row r="729">
@@ -15061,10 +15061,10 @@
         <v>74.72</v>
       </c>
       <c r="E732" t="n">
-        <v>76.52</v>
+        <v>76.63</v>
       </c>
       <c r="F732" t="n">
-        <v>102802</v>
+        <v>100583</v>
       </c>
     </row>
     <row r="733">
@@ -15161,10 +15161,10 @@
         <v>78.33</v>
       </c>
       <c r="E737" t="n">
-        <v>78.86</v>
+        <v>78.97</v>
       </c>
       <c r="F737" t="n">
-        <v>105405</v>
+        <v>103669</v>
       </c>
     </row>
     <row r="738">
@@ -15261,10 +15261,10 @@
         <v>79.36</v>
       </c>
       <c r="E742" t="n">
-        <v>81.70999999999999</v>
+        <v>81.65000000000001</v>
       </c>
       <c r="F742" t="n">
-        <v>187943</v>
+        <v>185800</v>
       </c>
     </row>
     <row r="743">
@@ -15281,10 +15281,10 @@
         <v>81.12</v>
       </c>
       <c r="E743" t="n">
-        <v>81.48</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="F743" t="n">
-        <v>160491</v>
+        <v>158852</v>
       </c>
     </row>
     <row r="744">
@@ -15361,10 +15361,10 @@
         <v>83.34999999999999</v>
       </c>
       <c r="E747" t="n">
-        <v>83.61</v>
+        <v>83.45</v>
       </c>
       <c r="F747" t="n">
-        <v>147527</v>
+        <v>145171</v>
       </c>
     </row>
     <row r="748">
@@ -15375,16 +15375,16 @@
         <v>83.68000000000001</v>
       </c>
       <c r="C748" t="n">
-        <v>85.98999999999999</v>
+        <v>85.97</v>
       </c>
       <c r="D748" t="n">
         <v>83.53</v>
       </c>
       <c r="E748" t="n">
-        <v>85.77</v>
+        <v>85.91</v>
       </c>
       <c r="F748" t="n">
-        <v>173518</v>
+        <v>171152</v>
       </c>
     </row>
     <row r="749">
@@ -15458,13 +15458,13 @@
         <v>88.8</v>
       </c>
       <c r="D752" t="n">
-        <v>86.38</v>
+        <v>86.56999999999999</v>
       </c>
       <c r="E752" t="n">
-        <v>86.58</v>
+        <v>86.7</v>
       </c>
       <c r="F752" t="n">
-        <v>169439</v>
+        <v>162890</v>
       </c>
     </row>
     <row r="753">
@@ -15481,10 +15481,10 @@
         <v>85.02</v>
       </c>
       <c r="E753" t="n">
-        <v>86.92</v>
+        <v>86.98</v>
       </c>
       <c r="F753" t="n">
-        <v>225683</v>
+        <v>223066</v>
       </c>
     </row>
     <row r="754">
@@ -15561,10 +15561,10 @@
         <v>87.7</v>
       </c>
       <c r="E757" t="n">
-        <v>88.63</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="F757" t="n">
-        <v>275711</v>
+        <v>270152</v>
       </c>
     </row>
     <row r="758">
@@ -15581,10 +15581,10 @@
         <v>88</v>
       </c>
       <c r="E758" t="n">
-        <v>88.81999999999999</v>
+        <v>88.73</v>
       </c>
       <c r="F758" t="n">
-        <v>278896</v>
+        <v>275262</v>
       </c>
     </row>
     <row r="759">
@@ -15655,16 +15655,16 @@
         <v>88.63</v>
       </c>
       <c r="C762" t="n">
-        <v>90.84999999999999</v>
+        <v>90.73999999999999</v>
       </c>
       <c r="D762" t="n">
         <v>87.59999999999999</v>
       </c>
       <c r="E762" t="n">
-        <v>90.51000000000001</v>
+        <v>90.45999999999999</v>
       </c>
       <c r="F762" t="n">
-        <v>168353</v>
+        <v>163057</v>
       </c>
     </row>
     <row r="763">
@@ -15681,10 +15681,10 @@
         <v>90.67</v>
       </c>
       <c r="E763" t="n">
-        <v>92.14</v>
+        <v>92.54000000000001</v>
       </c>
       <c r="F763" t="n">
-        <v>180147</v>
+        <v>177219</v>
       </c>
     </row>
     <row r="764">
@@ -15761,10 +15761,10 @@
         <v>90.09999999999999</v>
       </c>
       <c r="E767" t="n">
-        <v>90.54000000000001</v>
+        <v>90.66</v>
       </c>
       <c r="F767" t="n">
-        <v>186180</v>
+        <v>183590</v>
       </c>
     </row>
     <row r="768">
@@ -15781,10 +15781,10 @@
         <v>89.66</v>
       </c>
       <c r="E768" t="n">
-        <v>93.8</v>
+        <v>93.81</v>
       </c>
       <c r="F768" t="n">
-        <v>194729</v>
+        <v>189880</v>
       </c>
     </row>
     <row r="769">
@@ -15861,10 +15861,10 @@
         <v>90.34999999999999</v>
       </c>
       <c r="E772" t="n">
-        <v>91.16</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="F772" t="n">
-        <v>212213</v>
+        <v>209775</v>
       </c>
     </row>
     <row r="773">
@@ -15875,7 +15875,7 @@
         <v>90.76000000000001</v>
       </c>
       <c r="C773" t="n">
-        <v>92.28</v>
+        <v>92.15000000000001</v>
       </c>
       <c r="D773" t="n">
         <v>88.64</v>
@@ -15884,7 +15884,7 @@
         <v>91.81</v>
       </c>
       <c r="F773" t="n">
-        <v>194995</v>
+        <v>190175</v>
       </c>
     </row>
     <row r="774">
@@ -15961,10 +15961,10 @@
         <v>93.94</v>
       </c>
       <c r="E777" t="n">
-        <v>95.41</v>
+        <v>95.61</v>
       </c>
       <c r="F777" t="n">
-        <v>313423</v>
+        <v>309076</v>
       </c>
     </row>
     <row r="778">
@@ -15981,10 +15981,10 @@
         <v>92.55</v>
       </c>
       <c r="E778" t="n">
-        <v>94.23</v>
+        <v>94.69</v>
       </c>
       <c r="F778" t="n">
-        <v>237786</v>
+        <v>233541</v>
       </c>
     </row>
     <row r="779">
@@ -16061,10 +16061,10 @@
         <v>108.17</v>
       </c>
       <c r="E782" t="n">
-        <v>109.27</v>
+        <v>109.72</v>
       </c>
       <c r="F782" t="n">
-        <v>233799</v>
+        <v>231064</v>
       </c>
     </row>
     <row r="783">
@@ -16081,10 +16081,10 @@
         <v>108.47</v>
       </c>
       <c r="E783" t="n">
-        <v>116.7</v>
+        <v>117.14</v>
       </c>
       <c r="F783" t="n">
-        <v>210974</v>
+        <v>204618</v>
       </c>
     </row>
     <row r="784">
@@ -16161,10 +16161,10 @@
         <v>107.05</v>
       </c>
       <c r="E787" t="n">
-        <v>107.11</v>
+        <v>107.97</v>
       </c>
       <c r="F787" t="n">
-        <v>173653</v>
+        <v>170481</v>
       </c>
     </row>
     <row r="788">
@@ -16181,10 +16181,10 @@
         <v>104.96</v>
       </c>
       <c r="E788" t="n">
-        <v>110.14</v>
+        <v>110.51</v>
       </c>
       <c r="F788" t="n">
-        <v>157669</v>
+        <v>154891</v>
       </c>
     </row>
     <row r="789">
@@ -16252,19 +16252,19 @@
         <v>44637</v>
       </c>
       <c r="B792" t="n">
-        <v>96.70999999999999</v>
+        <v>96.98</v>
       </c>
       <c r="C792" t="n">
         <v>105.3</v>
       </c>
       <c r="D792" t="n">
-        <v>96.70999999999999</v>
+        <v>96.11</v>
       </c>
       <c r="E792" t="n">
         <v>104.46</v>
       </c>
       <c r="F792" t="n">
-        <v>172578</v>
+        <v>176604</v>
       </c>
     </row>
     <row r="793">
@@ -16272,7 +16272,7 @@
         <v>44638</v>
       </c>
       <c r="B793" t="n">
-        <v>105.16</v>
+        <v>104.55</v>
       </c>
       <c r="C793" t="n">
         <v>107.23</v>
@@ -16284,7 +16284,7 @@
         <v>105.63</v>
       </c>
       <c r="F793" t="n">
-        <v>155067</v>
+        <v>158531</v>
       </c>
     </row>
     <row r="794">
@@ -16352,7 +16352,7 @@
         <v>44644</v>
       </c>
       <c r="B797" t="n">
-        <v>119.49</v>
+        <v>118.08</v>
       </c>
       <c r="C797" t="n">
         <v>120.04</v>
@@ -16364,7 +16364,7 @@
         <v>114.47</v>
       </c>
       <c r="F797" t="n">
-        <v>206598</v>
+        <v>215337</v>
       </c>
     </row>
     <row r="798">
@@ -16372,7 +16372,7 @@
         <v>44645</v>
       </c>
       <c r="B798" t="n">
-        <v>114.52</v>
+        <v>115.3</v>
       </c>
       <c r="C798" t="n">
         <v>117.69</v>
@@ -16384,7 +16384,7 @@
         <v>115.94</v>
       </c>
       <c r="F798" t="n">
-        <v>189095</v>
+        <v>195807</v>
       </c>
     </row>
     <row r="799">
@@ -16461,10 +16461,10 @@
         <v>103.71</v>
       </c>
       <c r="E802" t="n">
-        <v>104.99</v>
+        <v>104.6</v>
       </c>
       <c r="F802" t="n">
-        <v>220967</v>
+        <v>217472</v>
       </c>
     </row>
     <row r="803">
@@ -16481,10 +16481,10 @@
         <v>101.94</v>
       </c>
       <c r="E803" t="n">
-        <v>103.88</v>
+        <v>104.13</v>
       </c>
       <c r="F803" t="n">
-        <v>181758</v>
+        <v>179677</v>
       </c>
     </row>
     <row r="804">
@@ -16561,10 +16561,10 @@
         <v>98.2</v>
       </c>
       <c r="E807" t="n">
-        <v>100.96</v>
+        <v>100.94</v>
       </c>
       <c r="F807" t="n">
-        <v>186163</v>
+        <v>183922</v>
       </c>
     </row>
     <row r="808">
@@ -16581,10 +16581,10 @@
         <v>99.28</v>
       </c>
       <c r="E808" t="n">
-        <v>101.81</v>
+        <v>102.16</v>
       </c>
       <c r="F808" t="n">
-        <v>162819</v>
+        <v>159821</v>
       </c>
     </row>
     <row r="809">
@@ -16661,10 +16661,10 @@
         <v>106.14</v>
       </c>
       <c r="E812" t="n">
-        <v>110.62</v>
+        <v>110.56</v>
       </c>
       <c r="F812" t="n">
-        <v>159785</v>
+        <v>156524</v>
       </c>
     </row>
     <row r="813">
@@ -16741,10 +16741,10 @@
         <v>106.38</v>
       </c>
       <c r="E816" t="n">
-        <v>108</v>
+        <v>107.93</v>
       </c>
       <c r="F816" t="n">
-        <v>188001</v>
+        <v>184241</v>
       </c>
     </row>
     <row r="817">
@@ -16758,13 +16758,13 @@
         <v>108.41</v>
       </c>
       <c r="D817" t="n">
-        <v>105.05</v>
+        <v>105.44</v>
       </c>
       <c r="E817" t="n">
-        <v>105.7</v>
+        <v>105.6</v>
       </c>
       <c r="F817" t="n">
-        <v>165632</v>
+        <v>162032</v>
       </c>
     </row>
     <row r="818">
@@ -16841,10 +16841,10 @@
         <v>102.74</v>
       </c>
       <c r="E821" t="n">
-        <v>106.8</v>
+        <v>107.25</v>
       </c>
       <c r="F821" t="n">
-        <v>170514</v>
+        <v>167676</v>
       </c>
     </row>
     <row r="822">
@@ -16861,10 +16861,10 @@
         <v>105.92</v>
       </c>
       <c r="E822" t="n">
-        <v>106.06</v>
+        <v>106.38</v>
       </c>
       <c r="F822" t="n">
-        <v>186051</v>
+        <v>182972</v>
       </c>
     </row>
     <row r="823">
@@ -16941,10 +16941,10 @@
         <v>108.66</v>
       </c>
       <c r="E826" t="n">
-        <v>110.4</v>
+        <v>110.3</v>
       </c>
       <c r="F826" t="n">
-        <v>201234</v>
+        <v>197687</v>
       </c>
     </row>
     <row r="827">
@@ -16961,10 +16961,10 @@
         <v>109.21</v>
       </c>
       <c r="E827" t="n">
-        <v>112.22</v>
+        <v>112.44</v>
       </c>
       <c r="F827" t="n">
-        <v>207851</v>
+        <v>203469</v>
       </c>
     </row>
     <row r="828">
@@ -17041,10 +17041,10 @@
         <v>103.97</v>
       </c>
       <c r="E831" t="n">
-        <v>106.86</v>
+        <v>107.38</v>
       </c>
       <c r="F831" t="n">
-        <v>243371</v>
+        <v>240901</v>
       </c>
     </row>
     <row r="832">
@@ -17061,10 +17061,10 @@
         <v>106.88</v>
       </c>
       <c r="E832" t="n">
-        <v>109.76</v>
+        <v>110.4</v>
       </c>
       <c r="F832" t="n">
-        <v>193013</v>
+        <v>190398</v>
       </c>
     </row>
     <row r="833">
@@ -17141,10 +17141,10 @@
         <v>104.22</v>
       </c>
       <c r="E836" t="n">
-        <v>109.5</v>
+        <v>109.59</v>
       </c>
       <c r="F836" t="n">
-        <v>250583</v>
+        <v>247278</v>
       </c>
     </row>
     <row r="837">
@@ -17161,10 +17161,10 @@
         <v>108.65</v>
       </c>
       <c r="E837" t="n">
-        <v>110.3</v>
+        <v>110.87</v>
       </c>
       <c r="F837" t="n">
-        <v>202895</v>
+        <v>198948</v>
       </c>
     </row>
     <row r="838">
@@ -17241,10 +17241,10 @@
         <v>110.83</v>
       </c>
       <c r="E841" t="n">
-        <v>114.15</v>
+        <v>114</v>
       </c>
       <c r="F841" t="n">
-        <v>175003</v>
+        <v>171535</v>
       </c>
     </row>
     <row r="842">
@@ -17261,10 +17261,10 @@
         <v>113.01</v>
       </c>
       <c r="E842" t="n">
-        <v>115.01</v>
+        <v>115.42</v>
       </c>
       <c r="F842" t="n">
-        <v>213418</v>
+        <v>210750</v>
       </c>
     </row>
     <row r="843">
@@ -17335,16 +17335,16 @@
         <v>113.88</v>
       </c>
       <c r="C846" t="n">
-        <v>117.74</v>
+        <v>117.57</v>
       </c>
       <c r="D846" t="n">
         <v>111.85</v>
       </c>
       <c r="E846" t="n">
-        <v>117.31</v>
+        <v>117.26</v>
       </c>
       <c r="F846" t="n">
-        <v>138282</v>
+        <v>137013</v>
       </c>
     </row>
     <row r="847">
@@ -17355,16 +17355,16 @@
         <v>117.37</v>
       </c>
       <c r="C847" t="n">
-        <v>120.6</v>
+        <v>120.57</v>
       </c>
       <c r="D847" t="n">
         <v>115.28</v>
       </c>
       <c r="E847" t="n">
-        <v>120.23</v>
+        <v>120.41</v>
       </c>
       <c r="F847" t="n">
-        <v>91626</v>
+        <v>90339</v>
       </c>
     </row>
     <row r="848">
@@ -17441,10 +17441,10 @@
         <v>121.23</v>
       </c>
       <c r="E851" t="n">
-        <v>121.41</v>
+        <v>121.71</v>
       </c>
       <c r="F851" t="n">
-        <v>176648</v>
+        <v>174232</v>
       </c>
     </row>
     <row r="852">
@@ -17461,10 +17461,10 @@
         <v>118.31</v>
       </c>
       <c r="E852" t="n">
-        <v>120.02</v>
+        <v>120.29</v>
       </c>
       <c r="F852" t="n">
-        <v>192334</v>
+        <v>190410</v>
       </c>
     </row>
     <row r="853">
@@ -17541,10 +17541,10 @@
         <v>113.72</v>
       </c>
       <c r="E856" t="n">
-        <v>116.92</v>
+        <v>117.15</v>
       </c>
       <c r="F856" t="n">
-        <v>231324</v>
+        <v>228931</v>
       </c>
     </row>
     <row r="857">
@@ -17561,10 +17561,10 @@
         <v>109.77</v>
       </c>
       <c r="E857" t="n">
-        <v>111.27</v>
+        <v>111.29</v>
       </c>
       <c r="F857" t="n">
-        <v>236868</v>
+        <v>233588</v>
       </c>
     </row>
     <row r="858">
@@ -17641,10 +17641,10 @@
         <v>105.25</v>
       </c>
       <c r="E861" t="n">
-        <v>106.13</v>
+        <v>106.29</v>
       </c>
       <c r="F861" t="n">
-        <v>234952</v>
+        <v>233040</v>
       </c>
     </row>
     <row r="862">
@@ -17661,10 +17661,10 @@
         <v>105.78</v>
       </c>
       <c r="E862" t="n">
-        <v>108.33</v>
+        <v>109.13</v>
       </c>
       <c r="F862" t="n">
-        <v>205227</v>
+        <v>202836</v>
       </c>
     </row>
     <row r="863">
@@ -17741,10 +17741,10 @@
         <v>107.7</v>
       </c>
       <c r="E866" t="n">
-        <v>108.43</v>
+        <v>108.69</v>
       </c>
       <c r="F866" t="n">
-        <v>212070</v>
+        <v>208599</v>
       </c>
     </row>
     <row r="867">
@@ -17761,10 +17761,10 @@
         <v>107.32</v>
       </c>
       <c r="E867" t="n">
-        <v>110.43</v>
+        <v>110.56</v>
       </c>
       <c r="F867" t="n">
-        <v>210630</v>
+        <v>209195</v>
       </c>
     </row>
     <row r="868">
@@ -17841,10 +17841,10 @@
         <v>97.11</v>
       </c>
       <c r="E871" t="n">
-        <v>102.32</v>
+        <v>102.75</v>
       </c>
       <c r="F871" t="n">
-        <v>224620</v>
+        <v>221862</v>
       </c>
     </row>
     <row r="872">
@@ -17861,10 +17861,10 @@
         <v>102.16</v>
       </c>
       <c r="E872" t="n">
-        <v>105.2</v>
+        <v>105.32</v>
       </c>
       <c r="F872" t="n">
-        <v>237030</v>
+        <v>235167</v>
       </c>
     </row>
     <row r="873">
@@ -17941,10 +17941,10 @@
         <v>92.42</v>
       </c>
       <c r="E876" t="n">
-        <v>97.12</v>
+        <v>97.17</v>
       </c>
       <c r="F876" t="n">
-        <v>217836</v>
+        <v>215919</v>
       </c>
     </row>
     <row r="877">
@@ -17961,10 +17961,10 @@
         <v>95.59</v>
       </c>
       <c r="E877" t="n">
-        <v>97.98</v>
+        <v>98.34999999999999</v>
       </c>
       <c r="F877" t="n">
-        <v>203134</v>
+        <v>200270</v>
       </c>
     </row>
     <row r="878">
@@ -18041,10 +18041,10 @@
         <v>97.86</v>
       </c>
       <c r="E881" t="n">
-        <v>99.93000000000001</v>
+        <v>100.04</v>
       </c>
       <c r="F881" t="n">
-        <v>229298</v>
+        <v>227231</v>
       </c>
     </row>
     <row r="882">
@@ -18061,10 +18061,10 @@
         <v>97.90000000000001</v>
       </c>
       <c r="E882" t="n">
-        <v>98.98999999999999</v>
+        <v>98.67</v>
       </c>
       <c r="F882" t="n">
-        <v>226135</v>
+        <v>222921</v>
       </c>
     </row>
     <row r="883">
@@ -18141,10 +18141,10 @@
         <v>100.74</v>
       </c>
       <c r="E886" t="n">
-        <v>101.99</v>
+        <v>101.93</v>
       </c>
       <c r="F886" t="n">
-        <v>132446</v>
+        <v>130398</v>
       </c>
     </row>
     <row r="887">
@@ -18161,10 +18161,10 @@
         <v>101.27</v>
       </c>
       <c r="E887" t="n">
-        <v>103.1</v>
+        <v>103.21</v>
       </c>
       <c r="F887" t="n">
-        <v>113461</v>
+        <v>112179</v>
       </c>
     </row>
     <row r="888">
@@ -18238,13 +18238,13 @@
         <v>97.17</v>
       </c>
       <c r="D891" t="n">
-        <v>92.5</v>
+        <v>92.73</v>
       </c>
       <c r="E891" t="n">
-        <v>92.52</v>
+        <v>93.38</v>
       </c>
       <c r="F891" t="n">
-        <v>162676</v>
+        <v>160629</v>
       </c>
     </row>
     <row r="892">
@@ -18261,10 +18261,10 @@
         <v>92.15000000000001</v>
       </c>
       <c r="E892" t="n">
-        <v>93.51000000000001</v>
+        <v>93.69</v>
       </c>
       <c r="F892" t="n">
-        <v>157322</v>
+        <v>155701</v>
       </c>
     </row>
     <row r="893">
@@ -18341,10 +18341,10 @@
         <v>96.08</v>
       </c>
       <c r="E896" t="n">
-        <v>98.31</v>
+        <v>98.66</v>
       </c>
       <c r="F896" t="n">
-        <v>140818</v>
+        <v>139272</v>
       </c>
     </row>
     <row r="897">
@@ -18361,10 +18361,10 @@
         <v>96.26000000000001</v>
       </c>
       <c r="E897" t="n">
-        <v>96.89</v>
+        <v>97.3</v>
       </c>
       <c r="F897" t="n">
-        <v>145858</v>
+        <v>144235</v>
       </c>
     </row>
     <row r="898">
@@ -18441,10 +18441,10 @@
         <v>92.55</v>
       </c>
       <c r="E901" t="n">
-        <v>95.56</v>
+        <v>95.93000000000001</v>
       </c>
       <c r="F901" t="n">
-        <v>123861</v>
+        <v>122235</v>
       </c>
     </row>
     <row r="902">
@@ -18461,10 +18461,10 @@
         <v>93.7</v>
       </c>
       <c r="E902" t="n">
-        <v>95.08</v>
+        <v>95.52</v>
       </c>
       <c r="F902" t="n">
-        <v>126696</v>
+        <v>125387</v>
       </c>
     </row>
     <row r="903">
@@ -18541,10 +18541,10 @@
         <v>98.23</v>
       </c>
       <c r="E906" t="n">
-        <v>98.68000000000001</v>
+        <v>99.05</v>
       </c>
       <c r="F906" t="n">
-        <v>115830</v>
+        <v>114289</v>
       </c>
     </row>
     <row r="907">
@@ -18561,10 +18561,10 @@
         <v>96.92</v>
       </c>
       <c r="E907" t="n">
-        <v>98.56999999999999</v>
+        <v>98.70999999999999</v>
       </c>
       <c r="F907" t="n">
-        <v>128357</v>
+        <v>127109</v>
       </c>
     </row>
     <row r="908">
@@ -18641,10 +18641,10 @@
         <v>91.58</v>
       </c>
       <c r="E911" t="n">
-        <v>91.59</v>
+        <v>91.75</v>
       </c>
       <c r="F911" t="n">
-        <v>172611</v>
+        <v>171383</v>
       </c>
     </row>
     <row r="912">
@@ -18661,10 +18661,10 @@
         <v>92.41</v>
       </c>
       <c r="E912" t="n">
-        <v>92.83</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="F912" t="n">
-        <v>164349</v>
+        <v>162523</v>
       </c>
     </row>
     <row r="913">
@@ -18741,10 +18741,10 @@
         <v>86.86</v>
       </c>
       <c r="E916" t="n">
-        <v>87.73999999999999</v>
+        <v>88.03</v>
       </c>
       <c r="F916" t="n">
-        <v>175783</v>
+        <v>174104</v>
       </c>
     </row>
     <row r="917">
@@ -18761,10 +18761,10 @@
         <v>88.09</v>
       </c>
       <c r="E917" t="n">
-        <v>91.42</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="F917" t="n">
-        <v>139210</v>
+        <v>137562</v>
       </c>
     </row>
     <row r="918">
@@ -18841,10 +18841,10 @@
         <v>89.39</v>
       </c>
       <c r="E921" t="n">
-        <v>89.78</v>
+        <v>90.08</v>
       </c>
       <c r="F921" t="n">
-        <v>179533</v>
+        <v>177670</v>
       </c>
     </row>
     <row r="922">
@@ -18861,10 +18861,10 @@
         <v>89.37</v>
       </c>
       <c r="E922" t="n">
-        <v>90.36</v>
+        <v>90.58</v>
       </c>
       <c r="F922" t="n">
-        <v>177056</v>
+        <v>175462</v>
       </c>
     </row>
     <row r="923">
@@ -18941,10 +18941,10 @@
         <v>88.38</v>
       </c>
       <c r="E926" t="n">
-        <v>89.48999999999999</v>
+        <v>89.53</v>
       </c>
       <c r="F926" t="n">
-        <v>169282</v>
+        <v>167346</v>
       </c>
     </row>
     <row r="927">
@@ -18961,10 +18961,10 @@
         <v>84.61</v>
       </c>
       <c r="E927" t="n">
-        <v>85.65000000000001</v>
+        <v>85.41</v>
       </c>
       <c r="F927" t="n">
-        <v>159709</v>
+        <v>157358</v>
       </c>
     </row>
     <row r="928">
@@ -19041,10 +19041,10 @@
         <v>85.98</v>
       </c>
       <c r="E931" t="n">
-        <v>87.22</v>
+        <v>87.20999999999999</v>
       </c>
       <c r="F931" t="n">
-        <v>184095</v>
+        <v>182346</v>
       </c>
     </row>
     <row r="932">
@@ -19061,10 +19061,10 @@
         <v>84.73999999999999</v>
       </c>
       <c r="E932" t="n">
-        <v>85.04000000000001</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="F932" t="n">
-        <v>174184</v>
+        <v>172540</v>
       </c>
     </row>
     <row r="933">
@@ -19141,10 +19141,10 @@
         <v>92.09</v>
       </c>
       <c r="E936" t="n">
-        <v>94.16</v>
+        <v>94.31999999999999</v>
       </c>
       <c r="F936" t="n">
-        <v>136157</v>
+        <v>134269</v>
       </c>
     </row>
     <row r="937">
@@ -19161,10 +19161,10 @@
         <v>93.25</v>
       </c>
       <c r="E937" t="n">
-        <v>97.59</v>
+        <v>96.95</v>
       </c>
       <c r="F937" t="n">
-        <v>161145</v>
+        <v>158303</v>
       </c>
     </row>
     <row r="938">
@@ -19241,10 +19241,10 @@
         <v>90.18000000000001</v>
       </c>
       <c r="E941" t="n">
-        <v>93.67</v>
+        <v>93.61</v>
       </c>
       <c r="F941" t="n">
-        <v>189909</v>
+        <v>187899</v>
       </c>
     </row>
     <row r="942">
@@ -19261,10 +19261,10 @@
         <v>90.34</v>
       </c>
       <c r="E942" t="n">
-        <v>90.66</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="F942" t="n">
-        <v>186342</v>
+        <v>184164</v>
       </c>
     </row>
     <row r="943">
@@ -19341,10 +19341,10 @@
         <v>90.34</v>
       </c>
       <c r="E946" t="n">
-        <v>91.11</v>
+        <v>91</v>
       </c>
       <c r="F946" t="n">
-        <v>172151</v>
+        <v>169394</v>
       </c>
     </row>
     <row r="947">
@@ -19361,10 +19361,10 @@
         <v>89.40000000000001</v>
       </c>
       <c r="E947" t="n">
-        <v>91.58</v>
+        <v>91.7</v>
       </c>
       <c r="F947" t="n">
-        <v>170499</v>
+        <v>168937</v>
       </c>
     </row>
     <row r="948">
@@ -19441,10 +19441,10 @@
         <v>93.06999999999999</v>
       </c>
       <c r="E951" t="n">
-        <v>94.45999999999999</v>
+        <v>94.91</v>
       </c>
       <c r="F951" t="n">
-        <v>135151</v>
+        <v>130846</v>
       </c>
     </row>
     <row r="952">
@@ -19461,10 +19461,10 @@
         <v>92.81999999999999</v>
       </c>
       <c r="E952" t="n">
-        <v>93.95</v>
+        <v>93.81</v>
       </c>
       <c r="F952" t="n">
-        <v>135363</v>
+        <v>133960</v>
       </c>
     </row>
     <row r="953">
@@ -19532,7 +19532,7 @@
         <v>44868</v>
       </c>
       <c r="B956" t="n">
-        <v>94.84</v>
+        <v>94.81</v>
       </c>
       <c r="C956" t="n">
         <v>95.45</v>
@@ -19544,7 +19544,7 @@
         <v>93.92</v>
       </c>
       <c r="F956" t="n">
-        <v>141621</v>
+        <v>143503</v>
       </c>
     </row>
     <row r="957">
@@ -19552,19 +19552,19 @@
         <v>44869</v>
       </c>
       <c r="B957" t="n">
-        <v>93.94</v>
+        <v>93.98</v>
       </c>
       <c r="C957" t="n">
         <v>98.23999999999999</v>
       </c>
       <c r="D957" t="n">
-        <v>93.94</v>
+        <v>93.76000000000001</v>
       </c>
       <c r="E957" t="n">
         <v>98.01000000000001</v>
       </c>
       <c r="F957" t="n">
-        <v>179958</v>
+        <v>182009</v>
       </c>
     </row>
     <row r="958">
@@ -19641,10 +19641,10 @@
         <v>90.97</v>
       </c>
       <c r="E961" t="n">
-        <v>92.47</v>
+        <v>92.69</v>
       </c>
       <c r="F961" t="n">
-        <v>170823</v>
+        <v>168690</v>
       </c>
     </row>
     <row r="962">
@@ -19661,10 +19661,10 @@
         <v>92.79000000000001</v>
       </c>
       <c r="E962" t="n">
-        <v>94.95999999999999</v>
+        <v>95.04000000000001</v>
       </c>
       <c r="F962" t="n">
-        <v>165782</v>
+        <v>163940</v>
       </c>
     </row>
     <row r="963">
@@ -19741,10 +19741,10 @@
         <v>88.72</v>
       </c>
       <c r="E966" t="n">
-        <v>89.34999999999999</v>
+        <v>89.28</v>
       </c>
       <c r="F966" t="n">
-        <v>159560</v>
+        <v>157265</v>
       </c>
     </row>
     <row r="967">
@@ -19761,10 +19761,10 @@
         <v>85.41</v>
       </c>
       <c r="E967" t="n">
-        <v>87.5</v>
+        <v>87.45</v>
       </c>
       <c r="F967" t="n">
-        <v>162655</v>
+        <v>160818</v>
       </c>
     </row>
     <row r="968">
@@ -19941,10 +19941,10 @@
         <v>86.26000000000001</v>
       </c>
       <c r="E976" t="n">
-        <v>86.98</v>
+        <v>86.84</v>
       </c>
       <c r="F976" t="n">
-        <v>136930</v>
+        <v>135345</v>
       </c>
     </row>
     <row r="977">
@@ -19961,10 +19961,10 @@
         <v>85.17</v>
       </c>
       <c r="E977" t="n">
-        <v>85.90000000000001</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="F977" t="n">
-        <v>137359</v>
+        <v>135815</v>
       </c>
     </row>
     <row r="978">
@@ -20041,10 +20041,10 @@
         <v>75.92</v>
       </c>
       <c r="E981" t="n">
-        <v>76.61</v>
+        <v>76.27</v>
       </c>
       <c r="F981" t="n">
-        <v>167594</v>
+        <v>165742</v>
       </c>
     </row>
     <row r="982">
@@ -20061,10 +20061,10 @@
         <v>75.34999999999999</v>
       </c>
       <c r="E982" t="n">
-        <v>76.79000000000001</v>
+        <v>76.76000000000001</v>
       </c>
       <c r="F982" t="n">
-        <v>153224</v>
+        <v>151706</v>
       </c>
     </row>
     <row r="983">
@@ -20141,10 +20141,10 @@
         <v>80.86</v>
       </c>
       <c r="E986" t="n">
-        <v>81.54000000000001</v>
+        <v>81.39</v>
       </c>
       <c r="F986" t="n">
-        <v>151489</v>
+        <v>149384</v>
       </c>
     </row>
     <row r="987">
@@ -20161,10 +20161,10 @@
         <v>78.61</v>
       </c>
       <c r="E987" t="n">
-        <v>79.44</v>
+        <v>79.36</v>
       </c>
       <c r="F987" t="n">
-        <v>151197</v>
+        <v>149990</v>
       </c>
     </row>
     <row r="988">
@@ -20241,10 +20241,10 @@
         <v>81.28</v>
       </c>
       <c r="E991" t="n">
-        <v>82.20999999999999</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="F991" t="n">
-        <v>95617</v>
+        <v>94348</v>
       </c>
     </row>
     <row r="992">
@@ -20321,10 +20321,10 @@
         <v>81.81999999999999</v>
       </c>
       <c r="E995" t="n">
-        <v>83.63</v>
+        <v>83.68000000000001</v>
       </c>
       <c r="F995" t="n">
-        <v>110699</v>
+        <v>109380</v>
       </c>
     </row>
     <row r="996">
@@ -20401,10 +20401,10 @@
         <v>77.63</v>
       </c>
       <c r="E999" t="n">
-        <v>78.8</v>
+        <v>78.68000000000001</v>
       </c>
       <c r="F999" t="n">
-        <v>150672</v>
+        <v>149266</v>
       </c>
     </row>
     <row r="1000">
@@ -20424,7 +20424,7 @@
         <v>78.51000000000001</v>
       </c>
       <c r="F1000" t="n">
-        <v>148389</v>
+        <v>147017</v>
       </c>
     </row>
     <row r="1001">
@@ -20501,10 +20501,10 @@
         <v>82.43000000000001</v>
       </c>
       <c r="E1004" t="n">
-        <v>83.84999999999999</v>
+        <v>83.91</v>
       </c>
       <c r="F1004" t="n">
-        <v>142735</v>
+        <v>141086</v>
       </c>
     </row>
     <row r="1005">
@@ -20515,16 +20515,16 @@
         <v>83.91</v>
       </c>
       <c r="C1005" t="n">
-        <v>85.61</v>
+        <v>85.55</v>
       </c>
       <c r="D1005" t="n">
         <v>83.55</v>
       </c>
       <c r="E1005" t="n">
-        <v>85.47</v>
+        <v>85.48</v>
       </c>
       <c r="F1005" t="n">
-        <v>131152</v>
+        <v>129757</v>
       </c>
     </row>
     <row r="1006">
@@ -20601,10 +20601,10 @@
         <v>83.95999999999999</v>
       </c>
       <c r="E1009" t="n">
-        <v>86.34</v>
+        <v>86.31999999999999</v>
       </c>
       <c r="F1009" t="n">
-        <v>144410</v>
+        <v>142583</v>
       </c>
     </row>
     <row r="1010">
@@ -20621,10 +20621,10 @@
         <v>85.69</v>
       </c>
       <c r="E1010" t="n">
-        <v>87.59</v>
+        <v>87.75</v>
       </c>
       <c r="F1010" t="n">
-        <v>125225</v>
+        <v>123973</v>
       </c>
     </row>
     <row r="1011">
@@ -20701,10 +20701,10 @@
         <v>85.75</v>
       </c>
       <c r="E1014" t="n">
-        <v>87.29000000000001</v>
+        <v>87.31</v>
       </c>
       <c r="F1014" t="n">
-        <v>96051</v>
+        <v>95077</v>
       </c>
     </row>
     <row r="1015">
@@ -20721,10 +20721,10 @@
         <v>85.48</v>
       </c>
       <c r="E1015" t="n">
-        <v>86.01000000000001</v>
+        <v>86.04000000000001</v>
       </c>
       <c r="F1015" t="n">
-        <v>110922</v>
+        <v>109841</v>
       </c>
     </row>
     <row r="1016">
@@ -20801,10 +20801,10 @@
         <v>81.2</v>
       </c>
       <c r="E1019" t="n">
-        <v>82.12</v>
+        <v>81.98</v>
       </c>
       <c r="F1019" t="n">
-        <v>150704</v>
+        <v>146732</v>
       </c>
     </row>
     <row r="1020">
@@ -20818,13 +20818,13 @@
         <v>84.11</v>
       </c>
       <c r="D1020" t="n">
-        <v>79.53</v>
+        <v>79.62</v>
       </c>
       <c r="E1020" t="n">
-        <v>79.62</v>
+        <v>79.64</v>
       </c>
       <c r="F1020" t="n">
-        <v>163093</v>
+        <v>161681</v>
       </c>
     </row>
     <row r="1021">
@@ -20901,10 +20901,10 @@
         <v>82.86</v>
       </c>
       <c r="E1024" t="n">
-        <v>83.95</v>
+        <v>83.88</v>
       </c>
       <c r="F1024" t="n">
-        <v>144061</v>
+        <v>142722</v>
       </c>
     </row>
     <row r="1025">
@@ -20921,10 +20921,10 @@
         <v>83.66</v>
       </c>
       <c r="E1025" t="n">
-        <v>86.2</v>
+        <v>86.29000000000001</v>
       </c>
       <c r="F1025" t="n">
-        <v>156718</v>
+        <v>155562</v>
       </c>
     </row>
     <row r="1026">
@@ -20998,13 +20998,13 @@
         <v>85.90000000000001</v>
       </c>
       <c r="D1029" t="n">
-        <v>84.28</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="E1029" t="n">
-        <v>84.31</v>
+        <v>84.37</v>
       </c>
       <c r="F1029" t="n">
-        <v>129946</v>
+        <v>128382</v>
       </c>
     </row>
     <row r="1030">
@@ -21021,10 +21021,10 @@
         <v>81.55</v>
       </c>
       <c r="E1030" t="n">
-        <v>82.72</v>
+        <v>82.68000000000001</v>
       </c>
       <c r="F1030" t="n">
-        <v>142763</v>
+        <v>141607</v>
       </c>
     </row>
     <row r="1031">
@@ -21101,10 +21101,10 @@
         <v>80.27</v>
       </c>
       <c r="E1034" t="n">
-        <v>82.18000000000001</v>
+        <v>82.12</v>
       </c>
       <c r="F1034" t="n">
-        <v>108091</v>
+        <v>107083</v>
       </c>
     </row>
     <row r="1035">
@@ -21121,10 +21121,10 @@
         <v>80.7</v>
       </c>
       <c r="E1035" t="n">
-        <v>82.77</v>
+        <v>82.94</v>
       </c>
       <c r="F1035" t="n">
-        <v>130526</v>
+        <v>129354</v>
       </c>
     </row>
     <row r="1036">
@@ -21201,10 +21201,10 @@
         <v>83.66</v>
       </c>
       <c r="E1039" t="n">
-        <v>84.23</v>
+        <v>84.34</v>
       </c>
       <c r="F1039" t="n">
-        <v>115434</v>
+        <v>114302</v>
       </c>
     </row>
     <row r="1040">
@@ -21215,16 +21215,16 @@
         <v>84.37</v>
       </c>
       <c r="C1040" t="n">
-        <v>85.81</v>
+        <v>85.8</v>
       </c>
       <c r="D1040" t="n">
         <v>82.2</v>
       </c>
       <c r="E1040" t="n">
-        <v>85.73999999999999</v>
+        <v>85.72</v>
       </c>
       <c r="F1040" t="n">
-        <v>120888</v>
+        <v>119970</v>
       </c>
     </row>
     <row r="1041">
@@ -21301,10 +21301,10 @@
         <v>81.16</v>
       </c>
       <c r="E1044" t="n">
-        <v>81.23</v>
+        <v>81.26000000000001</v>
       </c>
       <c r="F1044" t="n">
-        <v>121276</v>
+        <v>120126</v>
       </c>
     </row>
     <row r="1045">
@@ -21321,10 +21321,10 @@
         <v>80.47</v>
       </c>
       <c r="E1045" t="n">
-        <v>82.38</v>
+        <v>82.33</v>
       </c>
       <c r="F1045" t="n">
-        <v>172647</v>
+        <v>171433</v>
       </c>
     </row>
     <row r="1046">
@@ -21392,7 +21392,7 @@
         <v>45001</v>
       </c>
       <c r="B1049" t="n">
-        <v>74.59999999999999</v>
+        <v>74.04000000000001</v>
       </c>
       <c r="C1049" t="n">
         <v>75.23</v>
@@ -21404,7 +21404,7 @@
         <v>74.25</v>
       </c>
       <c r="F1049" t="n">
-        <v>206406</v>
+        <v>210322</v>
       </c>
     </row>
     <row r="1050">
@@ -21412,7 +21412,7 @@
         <v>45002</v>
       </c>
       <c r="B1050" t="n">
-        <v>74.41</v>
+        <v>74.45</v>
       </c>
       <c r="C1050" t="n">
         <v>75.65000000000001</v>
@@ -21424,7 +21424,7 @@
         <v>72.3</v>
       </c>
       <c r="F1050" t="n">
-        <v>194486</v>
+        <v>196053</v>
       </c>
     </row>
     <row r="1051">
@@ -21492,7 +21492,7 @@
         <v>45008</v>
       </c>
       <c r="B1054" t="n">
-        <v>75.73</v>
+        <v>75.58</v>
       </c>
       <c r="C1054" t="n">
         <v>77.09</v>
@@ -21504,7 +21504,7 @@
         <v>74.98999999999999</v>
       </c>
       <c r="F1054" t="n">
-        <v>132462</v>
+        <v>134971</v>
       </c>
     </row>
     <row r="1055">
@@ -21512,7 +21512,7 @@
         <v>45009</v>
       </c>
       <c r="B1055" t="n">
-        <v>74.92</v>
+        <v>75.08</v>
       </c>
       <c r="C1055" t="n">
         <v>75.89</v>
@@ -21524,7 +21524,7 @@
         <v>74.52</v>
       </c>
       <c r="F1055" t="n">
-        <v>158419</v>
+        <v>160608</v>
       </c>
     </row>
     <row r="1056">
@@ -21601,10 +21601,10 @@
         <v>77.13</v>
       </c>
       <c r="E1059" t="n">
-        <v>78.43000000000001</v>
+        <v>78.47</v>
       </c>
       <c r="F1059" t="n">
-        <v>102975</v>
+        <v>101875</v>
       </c>
     </row>
     <row r="1060">
@@ -21621,10 +21621,10 @@
         <v>77.79000000000001</v>
       </c>
       <c r="E1060" t="n">
-        <v>79.76000000000001</v>
+        <v>79.73</v>
       </c>
       <c r="F1060" t="n">
-        <v>103341</v>
+        <v>102278</v>
       </c>
     </row>
     <row r="1061">
@@ -21701,10 +21701,10 @@
         <v>83.89</v>
       </c>
       <c r="E1064" t="n">
-        <v>84.62</v>
+        <v>84.73</v>
       </c>
       <c r="F1064" t="n">
-        <v>128978</v>
+        <v>127887</v>
       </c>
     </row>
     <row r="1065">
@@ -21781,10 +21781,10 @@
         <v>85.78</v>
       </c>
       <c r="E1068" t="n">
-        <v>86.03</v>
+        <v>85.98</v>
       </c>
       <c r="F1068" t="n">
-        <v>107747</v>
+        <v>106530</v>
       </c>
     </row>
     <row r="1069">
@@ -21801,10 +21801,10 @@
         <v>85.27</v>
       </c>
       <c r="E1069" t="n">
-        <v>86.12</v>
+        <v>86.13</v>
       </c>
       <c r="F1069" t="n">
-        <v>119789</v>
+        <v>118921</v>
       </c>
     </row>
     <row r="1070">
@@ -21878,13 +21878,13 @@
         <v>82.59999999999999</v>
       </c>
       <c r="D1073" t="n">
-        <v>80.48999999999999</v>
+        <v>80.51000000000001</v>
       </c>
       <c r="E1073" t="n">
-        <v>80.48999999999999</v>
+        <v>80.62</v>
       </c>
       <c r="F1073" t="n">
-        <v>100157</v>
+        <v>99083</v>
       </c>
     </row>
     <row r="1074">
@@ -21901,10 +21901,10 @@
         <v>80.2</v>
       </c>
       <c r="E1074" t="n">
-        <v>81.53</v>
+        <v>81.38</v>
       </c>
       <c r="F1074" t="n">
-        <v>89589</v>
+        <v>88877</v>
       </c>
     </row>
     <row r="1075">
@@ -21981,10 +21981,10 @@
         <v>77.3</v>
       </c>
       <c r="E1078" t="n">
-        <v>78.17</v>
+        <v>78.23</v>
       </c>
       <c r="F1078" t="n">
-        <v>114226</v>
+        <v>112919</v>
       </c>
     </row>
     <row r="1079">
@@ -22001,10 +22001,10 @@
         <v>77.44</v>
       </c>
       <c r="E1079" t="n">
-        <v>80.08</v>
+        <v>80.20999999999999</v>
       </c>
       <c r="F1079" t="n">
-        <v>111593</v>
+        <v>110643</v>
       </c>
     </row>
     <row r="1080">
@@ -22081,10 +22081,10 @@
         <v>71.34</v>
       </c>
       <c r="E1083" t="n">
-        <v>72.38</v>
+        <v>72.34</v>
       </c>
       <c r="F1083" t="n">
-        <v>176458</v>
+        <v>175075</v>
       </c>
     </row>
     <row r="1084">
@@ -22101,10 +22101,10 @@
         <v>72.31999999999999</v>
       </c>
       <c r="E1084" t="n">
-        <v>75.15000000000001</v>
+        <v>75.22</v>
       </c>
       <c r="F1084" t="n">
-        <v>122688</v>
+        <v>121559</v>
       </c>
     </row>
     <row r="1085">
@@ -22181,10 +22181,10 @@
         <v>74.5</v>
       </c>
       <c r="E1088" t="n">
-        <v>75.26000000000001</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="F1088" t="n">
-        <v>142391</v>
+        <v>141443</v>
       </c>
     </row>
     <row r="1089">
@@ -22201,10 +22201,10 @@
         <v>73.84999999999999</v>
       </c>
       <c r="E1089" t="n">
-        <v>73.93000000000001</v>
+        <v>74.02</v>
       </c>
       <c r="F1089" t="n">
-        <v>144762</v>
+        <v>143925</v>
       </c>
     </row>
     <row r="1090">
@@ -22281,10 +22281,10 @@
         <v>75.42</v>
       </c>
       <c r="E1093" t="n">
-        <v>75.84</v>
+        <v>75.89</v>
       </c>
       <c r="F1093" t="n">
-        <v>98116</v>
+        <v>97144</v>
       </c>
     </row>
     <row r="1094">
@@ -22301,10 +22301,10 @@
         <v>75.01000000000001</v>
       </c>
       <c r="E1094" t="n">
-        <v>75.59999999999999</v>
+        <v>75.75</v>
       </c>
       <c r="F1094" t="n">
-        <v>108218</v>
+        <v>107224</v>
       </c>
     </row>
     <row r="1095">
@@ -22381,10 +22381,10 @@
         <v>75.08</v>
       </c>
       <c r="E1098" t="n">
-        <v>75.95999999999999</v>
+        <v>76.13</v>
       </c>
       <c r="F1098" t="n">
-        <v>95663</v>
+        <v>94656</v>
       </c>
     </row>
     <row r="1099">
@@ -22401,10 +22401,10 @@
         <v>75.62</v>
       </c>
       <c r="E1099" t="n">
-        <v>77.14</v>
+        <v>77.03</v>
       </c>
       <c r="F1099" t="n">
-        <v>86227</v>
+        <v>85632</v>
       </c>
     </row>
     <row r="1100">
@@ -22481,10 +22481,10 @@
         <v>72</v>
       </c>
       <c r="E1103" t="n">
-        <v>74.25</v>
+        <v>74.17</v>
       </c>
       <c r="F1103" t="n">
-        <v>124084</v>
+        <v>122959</v>
       </c>
     </row>
     <row r="1104">
@@ -22501,10 +22501,10 @@
         <v>74.13</v>
       </c>
       <c r="E1104" t="n">
-        <v>76.13</v>
+        <v>76.3</v>
       </c>
       <c r="F1104" t="n">
-        <v>111881</v>
+        <v>110715</v>
       </c>
     </row>
     <row r="1105">
@@ -22581,10 +22581,10 @@
         <v>73.52</v>
       </c>
       <c r="E1108" t="n">
-        <v>75.44</v>
+        <v>75.56999999999999</v>
       </c>
       <c r="F1108" t="n">
-        <v>142206</v>
+        <v>141391</v>
       </c>
     </row>
     <row r="1109">
@@ -22601,10 +22601,10 @@
         <v>74.67</v>
       </c>
       <c r="E1109" t="n">
-        <v>74.88</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="F1109" t="n">
-        <v>120995</v>
+        <v>120105</v>
       </c>
     </row>
     <row r="1110">
@@ -22681,10 +22681,10 @@
         <v>72.84999999999999</v>
       </c>
       <c r="E1113" t="n">
-        <v>75.52</v>
+        <v>75.56</v>
       </c>
       <c r="F1113" t="n">
-        <v>105947</v>
+        <v>104970</v>
       </c>
     </row>
     <row r="1114">
@@ -22701,10 +22701,10 @@
         <v>75.09999999999999</v>
       </c>
       <c r="E1114" t="n">
-        <v>76.23</v>
+        <v>76.47</v>
       </c>
       <c r="F1114" t="n">
-        <v>111184</v>
+        <v>109963</v>
       </c>
     </row>
     <row r="1115">
@@ -22781,10 +22781,10 @@
         <v>73.75</v>
       </c>
       <c r="E1118" t="n">
-        <v>74.3</v>
+        <v>74.2</v>
       </c>
       <c r="F1118" t="n">
-        <v>89974</v>
+        <v>89166</v>
       </c>
     </row>
     <row r="1119">
@@ -22795,16 +22795,16 @@
         <v>74.2</v>
       </c>
       <c r="C1119" t="n">
-        <v>74.45999999999999</v>
+        <v>74.36</v>
       </c>
       <c r="D1119" t="n">
         <v>72.25</v>
       </c>
       <c r="E1119" t="n">
-        <v>74.34</v>
+        <v>74.09</v>
       </c>
       <c r="F1119" t="n">
-        <v>101628</v>
+        <v>100773</v>
       </c>
     </row>
     <row r="1120">
@@ -22881,10 +22881,10 @@
         <v>73.56</v>
       </c>
       <c r="E1123" t="n">
-        <v>74.34999999999999</v>
+        <v>74.44</v>
       </c>
       <c r="F1123" t="n">
-        <v>118860</v>
+        <v>118096</v>
       </c>
     </row>
     <row r="1124">
@@ -22901,10 +22901,10 @@
         <v>74.23</v>
       </c>
       <c r="E1124" t="n">
-        <v>75.06999999999999</v>
+        <v>75.26000000000001</v>
       </c>
       <c r="F1124" t="n">
-        <v>108012</v>
+        <v>107062</v>
       </c>
     </row>
     <row r="1125">
@@ -22981,10 +22981,10 @@
         <v>74.94</v>
       </c>
       <c r="E1128" t="n">
-        <v>76.44</v>
+        <v>76.47</v>
       </c>
       <c r="F1128" t="n">
-        <v>121613</v>
+        <v>120498</v>
       </c>
     </row>
     <row r="1129">
@@ -23001,10 +23001,10 @@
         <v>75.91</v>
       </c>
       <c r="E1129" t="n">
-        <v>78.12</v>
+        <v>78.13</v>
       </c>
       <c r="F1129" t="n">
-        <v>101260</v>
+        <v>99946</v>
       </c>
     </row>
     <row r="1130">
@@ -23075,16 +23075,16 @@
         <v>79.95999999999999</v>
       </c>
       <c r="C1133" t="n">
-        <v>81.5</v>
+        <v>81.48999999999999</v>
       </c>
       <c r="D1133" t="n">
         <v>79.69</v>
       </c>
       <c r="E1133" t="n">
-        <v>81.37</v>
+        <v>81.48</v>
       </c>
       <c r="F1133" t="n">
-        <v>97805</v>
+        <v>96443</v>
       </c>
     </row>
     <row r="1134">
@@ -23098,13 +23098,13 @@
         <v>81.42</v>
       </c>
       <c r="D1134" t="n">
-        <v>79.34999999999999</v>
+        <v>79.44</v>
       </c>
       <c r="E1134" t="n">
-        <v>79.45</v>
+        <v>79.54000000000001</v>
       </c>
       <c r="F1134" t="n">
-        <v>99161</v>
+        <v>98000</v>
       </c>
     </row>
     <row r="1135">
@@ -23181,10 +23181,10 @@
         <v>78.56999999999999</v>
       </c>
       <c r="E1138" t="n">
-        <v>79.48</v>
+        <v>79.54000000000001</v>
       </c>
       <c r="F1138" t="n">
-        <v>77506</v>
+        <v>76777</v>
       </c>
     </row>
     <row r="1139">
@@ -23201,10 +23201,10 @@
         <v>79.51000000000001</v>
       </c>
       <c r="E1139" t="n">
-        <v>80.5</v>
+        <v>80.69</v>
       </c>
       <c r="F1139" t="n">
-        <v>70745</v>
+        <v>69907</v>
       </c>
     </row>
     <row r="1140">
@@ -23281,10 +23281,10 @@
         <v>82.54000000000001</v>
       </c>
       <c r="E1143" t="n">
-        <v>83.3</v>
+        <v>83.42</v>
       </c>
       <c r="F1143" t="n">
-        <v>101885</v>
+        <v>100960</v>
       </c>
     </row>
     <row r="1144">
@@ -23301,10 +23301,10 @@
         <v>82.78</v>
       </c>
       <c r="E1144" t="n">
-        <v>84.34999999999999</v>
+        <v>84.26000000000001</v>
       </c>
       <c r="F1144" t="n">
-        <v>96933</v>
+        <v>96080</v>
       </c>
     </row>
     <row r="1145">
@@ -23381,10 +23381,10 @@
         <v>82.23</v>
       </c>
       <c r="E1148" t="n">
-        <v>85.04000000000001</v>
+        <v>85.13</v>
       </c>
       <c r="F1148" t="n">
-        <v>124232</v>
+        <v>122532</v>
       </c>
     </row>
     <row r="1149">
@@ -23401,10 +23401,10 @@
         <v>84.89</v>
       </c>
       <c r="E1149" t="n">
-        <v>85.81</v>
+        <v>85.84</v>
       </c>
       <c r="F1149" t="n">
-        <v>104424</v>
+        <v>103319</v>
       </c>
     </row>
     <row r="1150">
@@ -23481,10 +23481,10 @@
         <v>85.89</v>
       </c>
       <c r="E1153" t="n">
-        <v>86.01000000000001</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="F1153" t="n">
-        <v>120019</v>
+        <v>119054</v>
       </c>
     </row>
     <row r="1154">
@@ -23501,10 +23501,10 @@
         <v>85.53</v>
       </c>
       <c r="E1154" t="n">
-        <v>86.16</v>
+        <v>86.26000000000001</v>
       </c>
       <c r="F1154" t="n">
-        <v>115051</v>
+        <v>114400</v>
       </c>
     </row>
     <row r="1155">
@@ -23581,10 +23581,10 @@
         <v>82.70999999999999</v>
       </c>
       <c r="E1158" t="n">
-        <v>83.42</v>
+        <v>83.45999999999999</v>
       </c>
       <c r="F1158" t="n">
-        <v>88033</v>
+        <v>87119</v>
       </c>
     </row>
     <row r="1159">
@@ -23601,10 +23601,10 @@
         <v>82.98</v>
       </c>
       <c r="E1159" t="n">
-        <v>84.42</v>
+        <v>84.37</v>
       </c>
       <c r="F1159" t="n">
-        <v>98761</v>
+        <v>98085</v>
       </c>
     </row>
     <row r="1160">
@@ -23681,10 +23681,10 @@
         <v>81.61</v>
       </c>
       <c r="E1163" t="n">
-        <v>82.67</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="F1163" t="n">
-        <v>77961</v>
+        <v>77118</v>
       </c>
     </row>
     <row r="1164">
@@ -23701,10 +23701,10 @@
         <v>82.2</v>
       </c>
       <c r="E1164" t="n">
-        <v>84.05</v>
+        <v>84.14</v>
       </c>
       <c r="F1164" t="n">
-        <v>102303</v>
+        <v>101382</v>
       </c>
     </row>
     <row r="1165">
@@ -23781,10 +23781,10 @@
         <v>84.98</v>
       </c>
       <c r="E1168" t="n">
-        <v>86.66</v>
+        <v>86.63</v>
       </c>
       <c r="F1168" t="n">
-        <v>85007</v>
+        <v>83934</v>
       </c>
     </row>
     <row r="1169">
@@ -23795,16 +23795,16 @@
         <v>86.63</v>
       </c>
       <c r="C1169" t="n">
-        <v>88.75</v>
+        <v>88.66</v>
       </c>
       <c r="D1169" t="n">
         <v>86.59</v>
       </c>
       <c r="E1169" t="n">
-        <v>88.68000000000001</v>
+        <v>88.64</v>
       </c>
       <c r="F1169" t="n">
-        <v>98645</v>
+        <v>97671</v>
       </c>
     </row>
     <row r="1170">
@@ -23881,10 +23881,10 @@
         <v>89.17</v>
       </c>
       <c r="E1173" t="n">
-        <v>89.47</v>
+        <v>89.76000000000001</v>
       </c>
       <c r="F1173" t="n">
-        <v>104343</v>
+        <v>103067</v>
       </c>
     </row>
     <row r="1174">
@@ -23901,10 +23901,10 @@
         <v>88.97</v>
       </c>
       <c r="E1174" t="n">
-        <v>90.09999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="F1174" t="n">
-        <v>101197</v>
+        <v>100164</v>
       </c>
     </row>
     <row r="1175">
@@ -23975,16 +23975,16 @@
         <v>91.56999999999999</v>
       </c>
       <c r="C1178" t="n">
-        <v>93.68000000000001</v>
+        <v>93.44</v>
       </c>
       <c r="D1178" t="n">
         <v>91.55</v>
       </c>
       <c r="E1178" t="n">
-        <v>93.56</v>
+        <v>93.36</v>
       </c>
       <c r="F1178" t="n">
-        <v>91727</v>
+        <v>89908</v>
       </c>
     </row>
     <row r="1179">
@@ -24001,10 +24001,10 @@
         <v>92.14</v>
       </c>
       <c r="E1179" t="n">
-        <v>93.56999999999999</v>
+        <v>93.52</v>
       </c>
       <c r="F1179" t="n">
-        <v>101498</v>
+        <v>100530</v>
       </c>
     </row>
     <row r="1180">
@@ -24081,10 +24081,10 @@
         <v>91.23999999999999</v>
       </c>
       <c r="E1183" t="n">
-        <v>92.20999999999999</v>
+        <v>92.27</v>
       </c>
       <c r="F1183" t="n">
-        <v>98137</v>
+        <v>97207</v>
       </c>
     </row>
     <row r="1184">
@@ -24101,10 +24101,10 @@
         <v>91.68000000000001</v>
       </c>
       <c r="E1184" t="n">
-        <v>92.28</v>
+        <v>92.31</v>
       </c>
       <c r="F1184" t="n">
-        <v>99665</v>
+        <v>98960</v>
       </c>
     </row>
     <row r="1185">
@@ -24181,10 +24181,10 @@
         <v>92.56</v>
       </c>
       <c r="E1188" t="n">
-        <v>92.89</v>
+        <v>92.94</v>
       </c>
       <c r="F1188" t="n">
-        <v>128240</v>
+        <v>127194</v>
       </c>
     </row>
     <row r="1189">
@@ -24201,10 +24201,10 @@
         <v>91.68000000000001</v>
       </c>
       <c r="E1189" t="n">
-        <v>91.8</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="F1189" t="n">
-        <v>117877</v>
+        <v>116761</v>
       </c>
     </row>
     <row r="1190">
@@ -24281,10 +24281,10 @@
         <v>83.31999999999999</v>
       </c>
       <c r="E1193" t="n">
-        <v>83.72</v>
+        <v>83.68000000000001</v>
       </c>
       <c r="F1193" t="n">
-        <v>149779</v>
+        <v>148426</v>
       </c>
     </row>
     <row r="1194">
@@ -24301,10 +24301,10 @@
         <v>82.97</v>
       </c>
       <c r="E1194" t="n">
-        <v>83.79000000000001</v>
+        <v>83.88</v>
       </c>
       <c r="F1194" t="n">
-        <v>140020</v>
+        <v>138785</v>
       </c>
     </row>
     <row r="1195">
@@ -24381,10 +24381,10 @@
         <v>84.59</v>
       </c>
       <c r="E1198" t="n">
-        <v>85.59999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="F1198" t="n">
-        <v>124560</v>
+        <v>123421</v>
       </c>
     </row>
     <row r="1199">
@@ -24404,7 +24404,7 @@
         <v>89.93000000000001</v>
       </c>
       <c r="F1199" t="n">
-        <v>120817</v>
+        <v>118765</v>
       </c>
     </row>
     <row r="1200">
@@ -24475,16 +24475,16 @@
         <v>90.26000000000001</v>
       </c>
       <c r="C1203" t="n">
-        <v>92.34999999999999</v>
+        <v>92.22</v>
       </c>
       <c r="D1203" t="n">
         <v>88.69</v>
       </c>
       <c r="E1203" t="n">
-        <v>92.04000000000001</v>
+        <v>92.16</v>
       </c>
       <c r="F1203" t="n">
-        <v>111224</v>
+        <v>109002</v>
       </c>
     </row>
     <row r="1204">
@@ -24501,10 +24501,10 @@
         <v>90.63</v>
       </c>
       <c r="E1204" t="n">
-        <v>91.26000000000001</v>
+        <v>91.13</v>
       </c>
       <c r="F1204" t="n">
-        <v>110661</v>
+        <v>109157</v>
       </c>
     </row>
     <row r="1205">
@@ -24581,10 +24581,10 @@
         <v>86.48</v>
       </c>
       <c r="E1208" t="n">
-        <v>87.23999999999999</v>
+        <v>87.25</v>
       </c>
       <c r="F1208" t="n">
-        <v>114536</v>
+        <v>113368</v>
       </c>
     </row>
     <row r="1209">
@@ -24601,10 +24601,10 @@
         <v>86.76000000000001</v>
       </c>
       <c r="E1209" t="n">
-        <v>88.70999999999999</v>
+        <v>88.76000000000001</v>
       </c>
       <c r="F1209" t="n">
-        <v>123231</v>
+        <v>121600</v>
       </c>
     </row>
     <row r="1210">
@@ -24672,7 +24672,7 @@
         <v>45232</v>
       </c>
       <c r="B1213" t="n">
-        <v>85.03</v>
+        <v>84.83</v>
       </c>
       <c r="C1213" t="n">
         <v>86.88</v>
@@ -24684,7 +24684,7 @@
         <v>86.63</v>
       </c>
       <c r="F1213" t="n">
-        <v>102261</v>
+        <v>103842</v>
       </c>
     </row>
     <row r="1214">
@@ -24692,7 +24692,7 @@
         <v>45233</v>
       </c>
       <c r="B1214" t="n">
-        <v>86.66</v>
+        <v>86.70999999999999</v>
       </c>
       <c r="C1214" t="n">
         <v>87.58</v>
@@ -24704,7 +24704,7 @@
         <v>84.95</v>
       </c>
       <c r="F1214" t="n">
-        <v>117913</v>
+        <v>119097</v>
       </c>
     </row>
     <row r="1215">
@@ -24781,10 +24781,10 @@
         <v>79.33</v>
       </c>
       <c r="E1218" t="n">
-        <v>79.76000000000001</v>
+        <v>79.75</v>
       </c>
       <c r="F1218" t="n">
-        <v>111847</v>
+        <v>110739</v>
       </c>
     </row>
     <row r="1219">
@@ -24801,10 +24801,10 @@
         <v>79.70999999999999</v>
       </c>
       <c r="E1219" t="n">
-        <v>81.43000000000001</v>
+        <v>81.36</v>
       </c>
       <c r="F1219" t="n">
-        <v>92327</v>
+        <v>91256</v>
       </c>
     </row>
     <row r="1220">
@@ -24881,10 +24881,10 @@
         <v>76.64</v>
       </c>
       <c r="E1223" t="n">
-        <v>77.45</v>
+        <v>77.43000000000001</v>
       </c>
       <c r="F1223" t="n">
-        <v>105749</v>
+        <v>104766</v>
       </c>
     </row>
     <row r="1224">
@@ -24901,10 +24901,10 @@
         <v>77.31</v>
       </c>
       <c r="E1224" t="n">
-        <v>80.43000000000001</v>
+        <v>80.37</v>
       </c>
       <c r="F1224" t="n">
-        <v>89648</v>
+        <v>88772</v>
       </c>
     </row>
     <row r="1225">
@@ -25078,13 +25078,13 @@
         <v>84.51000000000001</v>
       </c>
       <c r="D1233" t="n">
-        <v>79.94</v>
+        <v>79.95</v>
       </c>
       <c r="E1233" t="n">
-        <v>80.31</v>
+        <v>80</v>
       </c>
       <c r="F1233" t="n">
-        <v>145419</v>
+        <v>143673</v>
       </c>
     </row>
     <row r="1234">
@@ -25101,10 +25101,10 @@
         <v>78.69</v>
       </c>
       <c r="E1234" t="n">
-        <v>79.02</v>
+        <v>78.93000000000001</v>
       </c>
       <c r="F1234" t="n">
-        <v>126159</v>
+        <v>125186</v>
       </c>
     </row>
     <row r="1235">
@@ -25181,10 +25181,10 @@
         <v>73.68000000000001</v>
       </c>
       <c r="E1238" t="n">
-        <v>74.39</v>
+        <v>74.47</v>
       </c>
       <c r="F1238" t="n">
-        <v>116791</v>
+        <v>115986</v>
       </c>
     </row>
     <row r="1239">
@@ -25201,10 +25201,10 @@
         <v>74.25</v>
       </c>
       <c r="E1239" t="n">
-        <v>75.94</v>
+        <v>75.87</v>
       </c>
       <c r="F1239" t="n">
-        <v>114930</v>
+        <v>114085</v>
       </c>
     </row>
     <row r="1240">
@@ -25281,10 +25281,10 @@
         <v>74.56999999999999</v>
       </c>
       <c r="E1243" t="n">
-        <v>76.75</v>
+        <v>76.86</v>
       </c>
       <c r="F1243" t="n">
-        <v>84712</v>
+        <v>83845</v>
       </c>
     </row>
     <row r="1244">
@@ -25301,10 +25301,10 @@
         <v>75.48</v>
       </c>
       <c r="E1244" t="n">
-        <v>76.98999999999999</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="F1244" t="n">
-        <v>95068</v>
+        <v>94162</v>
       </c>
     </row>
     <row r="1245">
@@ -25381,10 +25381,10 @@
         <v>77.76000000000001</v>
       </c>
       <c r="E1248" t="n">
-        <v>79.12</v>
+        <v>79.19</v>
       </c>
       <c r="F1248" t="n">
-        <v>91755</v>
+        <v>91100</v>
       </c>
     </row>
     <row r="1249">
@@ -25461,10 +25461,10 @@
         <v>77.04000000000001</v>
       </c>
       <c r="E1252" t="n">
-        <v>77.36</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="F1252" t="n">
-        <v>95204</v>
+        <v>94380</v>
       </c>
     </row>
     <row r="1253">
@@ -25544,7 +25544,7 @@
         <v>77.53</v>
       </c>
       <c r="F1256" t="n">
-        <v>119158</v>
+        <v>118273</v>
       </c>
     </row>
     <row r="1257">
@@ -25641,10 +25641,10 @@
         <v>76.45</v>
       </c>
       <c r="E1261" t="n">
-        <v>78.01000000000001</v>
+        <v>77.61</v>
       </c>
       <c r="F1261" t="n">
-        <v>129868</v>
+        <v>128067</v>
       </c>
     </row>
     <row r="1262">
@@ -25741,10 +25741,10 @@
         <v>76.98</v>
       </c>
       <c r="E1266" t="n">
-        <v>78.56</v>
+        <v>78.63</v>
       </c>
       <c r="F1266" t="n">
-        <v>99368</v>
+        <v>98609</v>
       </c>
     </row>
     <row r="1267">
@@ -25841,10 +25841,10 @@
         <v>79.65000000000001</v>
       </c>
       <c r="E1271" t="n">
-        <v>81.69</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="F1271" t="n">
-        <v>76710</v>
+        <v>75889</v>
       </c>
     </row>
     <row r="1272">
@@ -25861,10 +25861,10 @@
         <v>80.75</v>
       </c>
       <c r="E1272" t="n">
-        <v>83.09999999999999</v>
+        <v>83.08</v>
       </c>
       <c r="F1272" t="n">
-        <v>87047</v>
+        <v>85666</v>
       </c>
     </row>
     <row r="1273">
@@ -25941,10 +25941,10 @@
         <v>78.5</v>
       </c>
       <c r="E1276" t="n">
-        <v>78.7</v>
+        <v>78.64</v>
       </c>
       <c r="F1276" t="n">
-        <v>140571</v>
+        <v>138682</v>
       </c>
     </row>
     <row r="1277">
@@ -25961,10 +25961,10 @@
         <v>76.78</v>
       </c>
       <c r="E1277" t="n">
-        <v>77.31999999999999</v>
+        <v>77.11</v>
       </c>
       <c r="F1277" t="n">
-        <v>133396</v>
+        <v>132023</v>
       </c>
     </row>
     <row r="1278">
@@ -26041,10 +26041,10 @@
         <v>78.84999999999999</v>
       </c>
       <c r="E1281" t="n">
-        <v>81.40000000000001</v>
+        <v>81.51000000000001</v>
       </c>
       <c r="F1281" t="n">
-        <v>87658</v>
+        <v>86597</v>
       </c>
     </row>
     <row r="1282">
@@ -26064,7 +26064,7 @@
         <v>81.63</v>
       </c>
       <c r="F1282" t="n">
-        <v>86235</v>
+        <v>85346</v>
       </c>
     </row>
     <row r="1283">
@@ -26141,10 +26141,10 @@
         <v>80.31999999999999</v>
       </c>
       <c r="E1286" t="n">
-        <v>82.22</v>
+        <v>82.37</v>
       </c>
       <c r="F1286" t="n">
-        <v>84560</v>
+        <v>83753</v>
       </c>
     </row>
     <row r="1287">
@@ -26161,10 +26161,10 @@
         <v>81.34</v>
       </c>
       <c r="E1287" t="n">
-        <v>82.68000000000001</v>
+        <v>82.70999999999999</v>
       </c>
       <c r="F1287" t="n">
-        <v>81459</v>
+        <v>80620</v>
       </c>
     </row>
     <row r="1288">
@@ -26241,10 +26241,10 @@
         <v>81.45</v>
       </c>
       <c r="E1291" t="n">
-        <v>82.51000000000001</v>
+        <v>82.63</v>
       </c>
       <c r="F1291" t="n">
-        <v>67848</v>
+        <v>67106</v>
       </c>
     </row>
     <row r="1292">
@@ -26261,10 +26261,10 @@
         <v>80.65000000000001</v>
       </c>
       <c r="E1292" t="n">
-        <v>80.84</v>
+        <v>80.88</v>
       </c>
       <c r="F1292" t="n">
-        <v>73168</v>
+        <v>72495</v>
       </c>
     </row>
     <row r="1293">
@@ -26341,10 +26341,10 @@
         <v>81.37</v>
       </c>
       <c r="E1296" t="n">
-        <v>81.8</v>
+        <v>81.70999999999999</v>
       </c>
       <c r="F1296" t="n">
-        <v>79642</v>
+        <v>78801</v>
       </c>
     </row>
     <row r="1297">
@@ -26361,10 +26361,10 @@
         <v>81.63</v>
       </c>
       <c r="E1297" t="n">
-        <v>83.12</v>
+        <v>83.19</v>
       </c>
       <c r="F1297" t="n">
-        <v>73275</v>
+        <v>72423</v>
       </c>
     </row>
     <row r="1298">
@@ -26441,10 +26441,10 @@
         <v>81.77</v>
       </c>
       <c r="E1301" t="n">
-        <v>82.87</v>
+        <v>82.52</v>
       </c>
       <c r="F1301" t="n">
-        <v>103853</v>
+        <v>102278</v>
       </c>
     </row>
     <row r="1302">
@@ -26461,10 +26461,10 @@
         <v>81.41</v>
       </c>
       <c r="E1302" t="n">
-        <v>81.55</v>
+        <v>81.66</v>
       </c>
       <c r="F1302" t="n">
-        <v>100115</v>
+        <v>99175</v>
       </c>
     </row>
     <row r="1303">
@@ -26532,19 +26532,19 @@
         <v>45365</v>
       </c>
       <c r="B1306" t="n">
-        <v>83.69</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="C1306" t="n">
         <v>85.18000000000001</v>
       </c>
       <c r="D1306" t="n">
-        <v>83.56999999999999</v>
+        <v>83.53</v>
       </c>
       <c r="E1306" t="n">
         <v>84.61</v>
       </c>
       <c r="F1306" t="n">
-        <v>71119</v>
+        <v>71844</v>
       </c>
     </row>
     <row r="1307">
@@ -26552,7 +26552,7 @@
         <v>45366</v>
       </c>
       <c r="B1307" t="n">
-        <v>84.68000000000001</v>
+        <v>84.65000000000001</v>
       </c>
       <c r="C1307" t="n">
         <v>85.09</v>
@@ -26564,7 +26564,7 @@
         <v>84.83</v>
       </c>
       <c r="F1307" t="n">
-        <v>74945</v>
+        <v>75864</v>
       </c>
     </row>
     <row r="1308">
@@ -26632,7 +26632,7 @@
         <v>45372</v>
       </c>
       <c r="B1311" t="n">
-        <v>85.81</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="C1311" t="n">
         <v>86.03</v>
@@ -26644,7 +26644,7 @@
         <v>84.95999999999999</v>
       </c>
       <c r="F1311" t="n">
-        <v>66113</v>
+        <v>67186</v>
       </c>
     </row>
     <row r="1312">
@@ -26652,7 +26652,7 @@
         <v>45373</v>
       </c>
       <c r="B1312" t="n">
-        <v>84.98999999999999</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="C1312" t="n">
         <v>85.58</v>
@@ -26664,7 +26664,7 @@
         <v>84.93000000000001</v>
       </c>
       <c r="F1312" t="n">
-        <v>53666</v>
+        <v>54286</v>
       </c>
     </row>
     <row r="1313">
@@ -26732,7 +26732,7 @@
         <v>45379</v>
       </c>
       <c r="B1316" t="n">
-        <v>85.65000000000001</v>
+        <v>85.56</v>
       </c>
       <c r="C1316" t="n">
         <v>86.89</v>
@@ -26744,7 +26744,7 @@
         <v>86.67</v>
       </c>
       <c r="F1316" t="n">
-        <v>56915</v>
+        <v>57372</v>
       </c>
     </row>
     <row r="1317">
@@ -26821,10 +26821,10 @@
         <v>88.43000000000001</v>
       </c>
       <c r="E1320" t="n">
-        <v>90.56</v>
+        <v>90.38</v>
       </c>
       <c r="F1320" t="n">
-        <v>75666</v>
+        <v>74470</v>
       </c>
     </row>
     <row r="1321">
@@ -26841,10 +26841,10 @@
         <v>90.18000000000001</v>
       </c>
       <c r="E1321" t="n">
-        <v>90.39</v>
+        <v>90.52</v>
       </c>
       <c r="F1321" t="n">
-        <v>80607</v>
+        <v>79937</v>
       </c>
     </row>
     <row r="1322">
@@ -26921,10 +26921,10 @@
         <v>88.87</v>
       </c>
       <c r="E1325" t="n">
-        <v>89.55</v>
+        <v>89.68000000000001</v>
       </c>
       <c r="F1325" t="n">
-        <v>107884</v>
+        <v>107040</v>
       </c>
     </row>
     <row r="1326">
@@ -26941,10 +26941,10 @@
         <v>89.45</v>
       </c>
       <c r="E1326" t="n">
-        <v>89.48999999999999</v>
+        <v>89.73</v>
       </c>
       <c r="F1326" t="n">
-        <v>109120</v>
+        <v>108331</v>
       </c>
     </row>
     <row r="1327">
@@ -27021,10 +27021,10 @@
         <v>85.63</v>
       </c>
       <c r="E1330" t="n">
-        <v>86.19</v>
+        <v>86.47</v>
       </c>
       <c r="F1330" t="n">
-        <v>108132</v>
+        <v>107464</v>
       </c>
     </row>
     <row r="1331">
@@ -27041,10 +27041,10 @@
         <v>85.61</v>
       </c>
       <c r="E1331" t="n">
-        <v>86.38</v>
+        <v>86.51000000000001</v>
       </c>
       <c r="F1331" t="n">
-        <v>144473</v>
+        <v>143518</v>
       </c>
     </row>
     <row r="1332">
@@ -27115,16 +27115,16 @@
         <v>86.88</v>
       </c>
       <c r="C1335" t="n">
-        <v>88</v>
+        <v>87.97</v>
       </c>
       <c r="D1335" t="n">
         <v>86.2</v>
       </c>
       <c r="E1335" t="n">
-        <v>87.83</v>
+        <v>87.95</v>
       </c>
       <c r="F1335" t="n">
-        <v>70059</v>
+        <v>69439</v>
       </c>
     </row>
     <row r="1336">
@@ -27141,10 +27141,10 @@
         <v>87.56999999999999</v>
       </c>
       <c r="E1336" t="n">
-        <v>87.89</v>
+        <v>87.98999999999999</v>
       </c>
       <c r="F1336" t="n">
-        <v>64445</v>
+        <v>63936</v>
       </c>
     </row>
     <row r="1337">
@@ -27221,10 +27221,10 @@
         <v>82.89</v>
       </c>
       <c r="E1340" t="n">
-        <v>83.48</v>
+        <v>83.47</v>
       </c>
       <c r="F1340" t="n">
-        <v>101847</v>
+        <v>100961</v>
       </c>
     </row>
     <row r="1341">
@@ -27238,13 +27238,13 @@
         <v>84.18000000000001</v>
       </c>
       <c r="D1341" t="n">
-        <v>82.53</v>
+        <v>82.65000000000001</v>
       </c>
       <c r="E1341" t="n">
-        <v>82.54000000000001</v>
+        <v>82.77</v>
       </c>
       <c r="F1341" t="n">
-        <v>83584</v>
+        <v>82987</v>
       </c>
     </row>
     <row r="1342">
@@ -27321,10 +27321,10 @@
         <v>83.18000000000001</v>
       </c>
       <c r="E1345" t="n">
-        <v>83.77</v>
+        <v>83.91</v>
       </c>
       <c r="F1345" t="n">
-        <v>67737</v>
+        <v>67201</v>
       </c>
     </row>
     <row r="1346">
@@ -27338,13 +27338,13 @@
         <v>84.23</v>
       </c>
       <c r="D1346" t="n">
-        <v>82.36</v>
+        <v>82.5</v>
       </c>
       <c r="E1346" t="n">
-        <v>82.36</v>
+        <v>82.61</v>
       </c>
       <c r="F1346" t="n">
-        <v>63117</v>
+        <v>62356</v>
       </c>
     </row>
     <row r="1347">
@@ -27421,10 +27421,10 @@
         <v>82.02</v>
       </c>
       <c r="E1350" t="n">
-        <v>82.98999999999999</v>
+        <v>83.04000000000001</v>
       </c>
       <c r="F1350" t="n">
-        <v>65759</v>
+        <v>65306</v>
       </c>
     </row>
     <row r="1351">
@@ -27441,10 +27441,10 @@
         <v>82.81999999999999</v>
       </c>
       <c r="E1351" t="n">
-        <v>83.56</v>
+        <v>83.68000000000001</v>
       </c>
       <c r="F1351" t="n">
-        <v>61133</v>
+        <v>60667</v>
       </c>
     </row>
     <row r="1352">
@@ -27521,10 +27521,10 @@
         <v>80.7</v>
       </c>
       <c r="E1355" t="n">
-        <v>81.06999999999999</v>
+        <v>81.09</v>
       </c>
       <c r="F1355" t="n">
-        <v>69958</v>
+        <v>68901</v>
       </c>
     </row>
     <row r="1356">
@@ -27541,10 +27541,10 @@
         <v>80.42</v>
       </c>
       <c r="E1356" t="n">
-        <v>81.79000000000001</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="F1356" t="n">
-        <v>56381</v>
+        <v>56045</v>
       </c>
     </row>
     <row r="1357">
@@ -27618,13 +27618,13 @@
         <v>83.51000000000001</v>
       </c>
       <c r="D1360" t="n">
-        <v>81.72</v>
+        <v>81.77</v>
       </c>
       <c r="E1360" t="n">
-        <v>81.73</v>
+        <v>81.88</v>
       </c>
       <c r="F1360" t="n">
-        <v>81864</v>
+        <v>81262</v>
       </c>
     </row>
     <row r="1361">
@@ -27641,10 +27641,10 @@
         <v>80.69</v>
       </c>
       <c r="E1361" t="n">
-        <v>81.09</v>
+        <v>81.22</v>
       </c>
       <c r="F1361" t="n">
-        <v>87130</v>
+        <v>86335</v>
       </c>
     </row>
     <row r="1362">
@@ -27721,10 +27721,10 @@
         <v>78.23999999999999</v>
       </c>
       <c r="E1365" t="n">
-        <v>79.69</v>
+        <v>79.73</v>
       </c>
       <c r="F1365" t="n">
-        <v>72677</v>
+        <v>72035</v>
       </c>
     </row>
     <row r="1366">
@@ -27741,10 +27741,10 @@
         <v>79.18000000000001</v>
       </c>
       <c r="E1366" t="n">
-        <v>79.23999999999999</v>
+        <v>79.27</v>
       </c>
       <c r="F1366" t="n">
-        <v>77440</v>
+        <v>76576</v>
       </c>
     </row>
     <row r="1367">
@@ -27821,10 +27821,10 @@
         <v>81.53</v>
       </c>
       <c r="E1370" t="n">
-        <v>81.68000000000001</v>
+        <v>81.98</v>
       </c>
       <c r="F1370" t="n">
-        <v>79567</v>
+        <v>78296</v>
       </c>
     </row>
     <row r="1371">
@@ -27841,10 +27841,10 @@
         <v>81.64</v>
       </c>
       <c r="E1371" t="n">
-        <v>82.06</v>
+        <v>82.2</v>
       </c>
       <c r="F1371" t="n">
-        <v>75768</v>
+        <v>75030</v>
       </c>
     </row>
     <row r="1372">
@@ -27921,10 +27921,10 @@
         <v>84.28</v>
       </c>
       <c r="E1375" t="n">
-        <v>84.7</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="F1375" t="n">
-        <v>59846</v>
+        <v>59448</v>
       </c>
     </row>
     <row r="1376">
@@ -27941,10 +27941,10 @@
         <v>84</v>
       </c>
       <c r="E1376" t="n">
-        <v>84.16</v>
+        <v>84.31</v>
       </c>
       <c r="F1376" t="n">
-        <v>60278</v>
+        <v>59797</v>
       </c>
     </row>
     <row r="1377">
@@ -28021,10 +28021,10 @@
         <v>84.01000000000001</v>
       </c>
       <c r="E1380" t="n">
-        <v>85.04000000000001</v>
+        <v>85.25</v>
       </c>
       <c r="F1380" t="n">
-        <v>64909</v>
+        <v>64362</v>
       </c>
     </row>
     <row r="1381">
@@ -28041,10 +28041,10 @@
         <v>84.39</v>
       </c>
       <c r="E1381" t="n">
-        <v>84.65000000000001</v>
+        <v>84.79000000000001</v>
       </c>
       <c r="F1381" t="n">
-        <v>69862</v>
+        <v>69177</v>
       </c>
     </row>
     <row r="1382">
@@ -28141,10 +28141,10 @@
         <v>86.17</v>
       </c>
       <c r="E1386" t="n">
-        <v>86.43000000000001</v>
+        <v>86.31999999999999</v>
       </c>
       <c r="F1386" t="n">
-        <v>68965</v>
+        <v>67919</v>
       </c>
     </row>
     <row r="1387">
@@ -28221,10 +28221,10 @@
         <v>84.16</v>
       </c>
       <c r="E1390" t="n">
-        <v>84.90000000000001</v>
+        <v>85.19</v>
       </c>
       <c r="F1390" t="n">
-        <v>78990</v>
+        <v>78243</v>
       </c>
     </row>
     <row r="1391">
@@ -28238,13 +28238,13 @@
         <v>85.67</v>
       </c>
       <c r="D1391" t="n">
-        <v>84.31999999999999</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="E1391" t="n">
-        <v>84.31999999999999</v>
+        <v>84.5</v>
       </c>
       <c r="F1391" t="n">
-        <v>74302</v>
+        <v>73607</v>
       </c>
     </row>
     <row r="1392">
@@ -28321,10 +28321,10 @@
         <v>83.41</v>
       </c>
       <c r="E1395" t="n">
-        <v>83.76000000000001</v>
+        <v>83.72</v>
       </c>
       <c r="F1395" t="n">
-        <v>69797</v>
+        <v>68620</v>
       </c>
     </row>
     <row r="1396">
@@ -28338,13 +28338,13 @@
         <v>84.41</v>
       </c>
       <c r="D1396" t="n">
-        <v>81.64</v>
+        <v>81.7</v>
       </c>
       <c r="E1396" t="n">
-        <v>81.64</v>
+        <v>81.89</v>
       </c>
       <c r="F1396" t="n">
-        <v>72736</v>
+        <v>72020</v>
       </c>
     </row>
     <row r="1397">
@@ -28421,10 +28421,10 @@
         <v>79.28</v>
       </c>
       <c r="E1400" t="n">
-        <v>81.37</v>
+        <v>81.33</v>
       </c>
       <c r="F1400" t="n">
-        <v>69789</v>
+        <v>69150</v>
       </c>
     </row>
     <row r="1401">
@@ -28441,10 +28441,10 @@
         <v>79.39</v>
       </c>
       <c r="E1401" t="n">
-        <v>79.48999999999999</v>
+        <v>79.92</v>
       </c>
       <c r="F1401" t="n">
-        <v>65748</v>
+        <v>64725</v>
       </c>
     </row>
     <row r="1402">
@@ -28521,10 +28521,10 @@
         <v>79.3</v>
       </c>
       <c r="E1405" t="n">
-        <v>79.83</v>
+        <v>80</v>
       </c>
       <c r="F1405" t="n">
-        <v>105741</v>
+        <v>104482</v>
       </c>
     </row>
     <row r="1406">
@@ -28541,10 +28541,10 @@
         <v>76.26000000000001</v>
       </c>
       <c r="E1406" t="n">
-        <v>77.14</v>
+        <v>77.08</v>
       </c>
       <c r="F1406" t="n">
-        <v>125792</v>
+        <v>124356</v>
       </c>
     </row>
     <row r="1407">
@@ -28621,10 +28621,10 @@
         <v>77.33</v>
       </c>
       <c r="E1410" t="n">
-        <v>78.59</v>
+        <v>78.73999999999999</v>
       </c>
       <c r="F1410" t="n">
-        <v>113892</v>
+        <v>113028</v>
       </c>
     </row>
     <row r="1411">
@@ -28641,10 +28641,10 @@
         <v>78.43000000000001</v>
       </c>
       <c r="E1411" t="n">
-        <v>79.27</v>
+        <v>79.34</v>
       </c>
       <c r="F1411" t="n">
-        <v>87467</v>
+        <v>86405</v>
       </c>
     </row>
     <row r="1412">
@@ -28721,10 +28721,10 @@
         <v>79.11</v>
       </c>
       <c r="E1415" t="n">
-        <v>80.26000000000001</v>
+        <v>80.31999999999999</v>
       </c>
       <c r="F1415" t="n">
-        <v>79567</v>
+        <v>78757</v>
       </c>
     </row>
     <row r="1416">
@@ -28741,10 +28741,10 @@
         <v>78.09</v>
       </c>
       <c r="E1416" t="n">
-        <v>78.94</v>
+        <v>79.22</v>
       </c>
       <c r="F1416" t="n">
-        <v>82030</v>
+        <v>81009</v>
       </c>
     </row>
     <row r="1417">
@@ -28821,10 +28821,10 @@
         <v>75.25</v>
       </c>
       <c r="E1420" t="n">
-        <v>76.42</v>
+        <v>76.47</v>
       </c>
       <c r="F1420" t="n">
-        <v>79873</v>
+        <v>79280</v>
       </c>
     </row>
     <row r="1421">
@@ -28841,10 +28841,10 @@
         <v>76.40000000000001</v>
       </c>
       <c r="E1421" t="n">
-        <v>78.13</v>
+        <v>78.17</v>
       </c>
       <c r="F1421" t="n">
-        <v>69081</v>
+        <v>68613</v>
       </c>
     </row>
     <row r="1422">
@@ -28921,10 +28921,10 @@
         <v>76.90000000000001</v>
       </c>
       <c r="E1425" t="n">
-        <v>78.72</v>
+        <v>78.81</v>
       </c>
       <c r="F1425" t="n">
-        <v>94397</v>
+        <v>93699</v>
       </c>
     </row>
     <row r="1426">
@@ -28941,10 +28941,10 @@
         <v>76.56</v>
       </c>
       <c r="E1426" t="n">
-        <v>76.77</v>
+        <v>76.81</v>
       </c>
       <c r="F1426" t="n">
-        <v>109124</v>
+        <v>108329</v>
       </c>
     </row>
     <row r="1427">
@@ -29021,10 +29021,10 @@
         <v>72.20999999999999</v>
       </c>
       <c r="E1430" t="n">
-        <v>72.53</v>
+        <v>72.54000000000001</v>
       </c>
       <c r="F1430" t="n">
-        <v>109541</v>
+        <v>108713</v>
       </c>
     </row>
     <row r="1431">
@@ -29041,10 +29041,10 @@
         <v>70.45</v>
       </c>
       <c r="E1431" t="n">
-        <v>71.2</v>
+        <v>71.37</v>
       </c>
       <c r="F1431" t="n">
-        <v>116954</v>
+        <v>115759</v>
       </c>
     </row>
     <row r="1432">
@@ -29121,10 +29121,10 @@
         <v>70.31999999999999</v>
       </c>
       <c r="E1435" t="n">
-        <v>71.67</v>
+        <v>71.89</v>
       </c>
       <c r="F1435" t="n">
-        <v>115156</v>
+        <v>114181</v>
       </c>
     </row>
     <row r="1436">
@@ -29141,10 +29141,10 @@
         <v>71.09</v>
       </c>
       <c r="E1436" t="n">
-        <v>71.59999999999999</v>
+        <v>71.73</v>
       </c>
       <c r="F1436" t="n">
-        <v>99629</v>
+        <v>98569</v>
       </c>
     </row>
     <row r="1437">
@@ -29221,10 +29221,10 @@
         <v>72.26000000000001</v>
       </c>
       <c r="E1440" t="n">
-        <v>73.97</v>
+        <v>74.05</v>
       </c>
       <c r="F1440" t="n">
-        <v>89094</v>
+        <v>88395</v>
       </c>
     </row>
     <row r="1441">
@@ -29241,10 +29241,10 @@
         <v>73.28</v>
       </c>
       <c r="E1441" t="n">
-        <v>73.87</v>
+        <v>73.98</v>
       </c>
       <c r="F1441" t="n">
-        <v>72413</v>
+        <v>71635</v>
       </c>
     </row>
     <row r="1442">
@@ -29321,10 +29321,10 @@
         <v>70.20999999999999</v>
       </c>
       <c r="E1445" t="n">
-        <v>70.68000000000001</v>
+        <v>70.66</v>
       </c>
       <c r="F1445" t="n">
-        <v>155899</v>
+        <v>154979</v>
       </c>
     </row>
     <row r="1446">
@@ -29335,16 +29335,16 @@
         <v>70.68000000000001</v>
       </c>
       <c r="C1446" t="n">
-        <v>71.90000000000001</v>
+        <v>71.89</v>
       </c>
       <c r="D1446" t="n">
         <v>70.39</v>
       </c>
       <c r="E1446" t="n">
-        <v>71.79000000000001</v>
+        <v>71.81999999999999</v>
       </c>
       <c r="F1446" t="n">
-        <v>123787</v>
+        <v>122438</v>
       </c>
     </row>
     <row r="1447">
@@ -29421,10 +29421,10 @@
         <v>74.18000000000001</v>
       </c>
       <c r="E1450" t="n">
-        <v>77.28</v>
+        <v>77.58</v>
       </c>
       <c r="F1450" t="n">
-        <v>125075</v>
+        <v>123449</v>
       </c>
     </row>
     <row r="1451">
@@ -29441,10 +29441,10 @@
         <v>77.19</v>
       </c>
       <c r="E1451" t="n">
-        <v>77.73</v>
+        <v>77.87</v>
       </c>
       <c r="F1451" t="n">
-        <v>121412</v>
+        <v>120535</v>
       </c>
     </row>
     <row r="1452">
@@ -38924,7 +38924,7 @@
         <v>81.53</v>
       </c>
       <c r="F1925" t="n">
-        <v>90754</v>
+        <v>90710</v>
       </c>
     </row>
     <row r="1926">
@@ -38944,7 +38944,27 @@
         <v>86.88</v>
       </c>
       <c r="F1926" t="n">
-        <v>101192</v>
+        <v>101145</v>
+      </c>
+    </row>
+    <row r="1927">
+      <c r="A1927" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B1927" t="n">
+        <v>86.76000000000001</v>
+      </c>
+      <c r="C1927" t="n">
+        <v>88.89</v>
+      </c>
+      <c r="D1927" t="n">
+        <v>85.63</v>
+      </c>
+      <c r="E1927" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="F1927" t="n">
+        <v>114314</v>
       </c>
     </row>
   </sheetData>

--- a/database/BRENT.xlsx
+++ b/database/BRENT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1927"/>
+  <dimension ref="A1:F1928"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38924,7 +38924,7 @@
         <v>81.53</v>
       </c>
       <c r="F1925" t="n">
-        <v>90710</v>
+        <v>90754</v>
       </c>
     </row>
     <row r="1926">
@@ -38964,7 +38964,27 @@
         <v>87.8</v>
       </c>
       <c r="F1927" t="n">
-        <v>114314</v>
+        <v>114422</v>
+      </c>
+    </row>
+    <row r="1928">
+      <c r="A1928" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B1928" t="n">
+        <v>87.90000000000001</v>
+      </c>
+      <c r="C1928" t="n">
+        <v>88.76000000000001</v>
+      </c>
+      <c r="D1928" t="n">
+        <v>86.91</v>
+      </c>
+      <c r="E1928" t="n">
+        <v>87.23999999999999</v>
+      </c>
+      <c r="F1928" t="n">
+        <v>104850</v>
       </c>
     </row>
   </sheetData>

--- a/database/BRENT.xlsx
+++ b/database/BRENT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1928"/>
+  <dimension ref="A1:F1929"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3881,10 +3881,10 @@
         <v>60.96</v>
       </c>
       <c r="E173" t="n">
-        <v>61.74</v>
+        <v>61.65</v>
       </c>
       <c r="F173" t="n">
-        <v>7439</v>
+        <v>7745</v>
       </c>
     </row>
     <row r="174">
@@ -3952,7 +3952,7 @@
         <v>43769</v>
       </c>
       <c r="B177" t="n">
-        <v>60.17</v>
+        <v>60.27</v>
       </c>
       <c r="C177" t="n">
         <v>60.79</v>
@@ -3964,7 +3964,7 @@
         <v>59.46</v>
       </c>
       <c r="F177" t="n">
-        <v>20831</v>
+        <v>20603</v>
       </c>
     </row>
     <row r="178">
@@ -3972,7 +3972,7 @@
         <v>43770</v>
       </c>
       <c r="B178" t="n">
-        <v>59.42</v>
+        <v>59.64</v>
       </c>
       <c r="C178" t="n">
         <v>61.8</v>
@@ -3984,7 +3984,7 @@
         <v>61.65</v>
       </c>
       <c r="F178" t="n">
-        <v>18539</v>
+        <v>18281</v>
       </c>
     </row>
     <row r="179">
@@ -4061,10 +4061,10 @@
         <v>61.63</v>
       </c>
       <c r="E182" t="n">
-        <v>62.14</v>
+        <v>62.29</v>
       </c>
       <c r="F182" t="n">
-        <v>19306</v>
+        <v>19680</v>
       </c>
     </row>
     <row r="183">
@@ -4081,10 +4081,10 @@
         <v>60.65</v>
       </c>
       <c r="E183" t="n">
-        <v>62.61</v>
+        <v>62.64</v>
       </c>
       <c r="F183" t="n">
-        <v>21625</v>
+        <v>21863</v>
       </c>
     </row>
     <row r="184">
@@ -4161,10 +4161,10 @@
         <v>62.14</v>
       </c>
       <c r="E187" t="n">
-        <v>62.38</v>
+        <v>62.33</v>
       </c>
       <c r="F187" t="n">
-        <v>19157</v>
+        <v>19293</v>
       </c>
     </row>
     <row r="188">
@@ -4181,10 +4181,10 @@
         <v>61.69</v>
       </c>
       <c r="E188" t="n">
-        <v>63.32</v>
+        <v>63.41</v>
       </c>
       <c r="F188" t="n">
-        <v>15801</v>
+        <v>16092</v>
       </c>
     </row>
     <row r="189">
@@ -4261,10 +4261,10 @@
         <v>61.91</v>
       </c>
       <c r="E192" t="n">
-        <v>63.74</v>
+        <v>63.64</v>
       </c>
       <c r="F192" t="n">
-        <v>21582</v>
+        <v>21823</v>
       </c>
     </row>
     <row r="193">
@@ -4281,10 +4281,10 @@
         <v>61.92</v>
       </c>
       <c r="E193" t="n">
-        <v>62.58</v>
+        <v>62.52</v>
       </c>
       <c r="F193" t="n">
-        <v>17577</v>
+        <v>17794</v>
       </c>
     </row>
     <row r="194">
@@ -4461,10 +4461,10 @@
         <v>62.73</v>
       </c>
       <c r="E202" t="n">
-        <v>63.33</v>
+        <v>63.26</v>
       </c>
       <c r="F202" t="n">
-        <v>24042</v>
+        <v>24300</v>
       </c>
     </row>
     <row r="203">
@@ -4481,10 +4481,10 @@
         <v>62.82</v>
       </c>
       <c r="E203" t="n">
-        <v>64.22</v>
+        <v>64.34</v>
       </c>
       <c r="F203" t="n">
-        <v>22359</v>
+        <v>22572</v>
       </c>
     </row>
     <row r="204">
@@ -4561,10 +4561,10 @@
         <v>63.86</v>
       </c>
       <c r="E207" t="n">
-        <v>64.31</v>
+        <v>64.28</v>
       </c>
       <c r="F207" t="n">
-        <v>18198</v>
+        <v>18454</v>
       </c>
     </row>
     <row r="208">
@@ -4581,10 +4581,10 @@
         <v>64.48</v>
       </c>
       <c r="E208" t="n">
-        <v>64.88</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="F208" t="n">
-        <v>21484</v>
+        <v>21671</v>
       </c>
     </row>
     <row r="209">
@@ -4661,10 +4661,10 @@
         <v>66.02</v>
       </c>
       <c r="E212" t="n">
-        <v>66.45</v>
+        <v>66.53</v>
       </c>
       <c r="F212" t="n">
-        <v>10932</v>
+        <v>11180</v>
       </c>
     </row>
     <row r="213">
@@ -4681,10 +4681,10 @@
         <v>65.72</v>
       </c>
       <c r="E213" t="n">
-        <v>65.98</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="F213" t="n">
-        <v>14693</v>
+        <v>14806</v>
       </c>
     </row>
     <row r="214">
@@ -4741,10 +4741,10 @@
         <v>66.09</v>
       </c>
       <c r="E216" t="n">
-        <v>66.65000000000001</v>
+        <v>66.75</v>
       </c>
       <c r="F216" t="n">
-        <v>9409</v>
+        <v>9613</v>
       </c>
     </row>
     <row r="217">
@@ -4761,10 +4761,10 @@
         <v>66.34</v>
       </c>
       <c r="E217" t="n">
-        <v>66.81</v>
+        <v>66.84</v>
       </c>
       <c r="F217" t="n">
-        <v>11272</v>
+        <v>11398</v>
       </c>
     </row>
     <row r="218">
@@ -4821,10 +4821,10 @@
         <v>65.7</v>
       </c>
       <c r="E220" t="n">
-        <v>66.19</v>
+        <v>66.23</v>
       </c>
       <c r="F220" t="n">
-        <v>15153</v>
+        <v>15351</v>
       </c>
     </row>
     <row r="221">
@@ -4841,10 +4841,10 @@
         <v>66.19</v>
       </c>
       <c r="E221" t="n">
-        <v>68.55</v>
+        <v>68.59</v>
       </c>
       <c r="F221" t="n">
-        <v>35427</v>
+        <v>35609</v>
       </c>
     </row>
     <row r="222">
@@ -4924,7 +4924,7 @@
         <v>65.38</v>
       </c>
       <c r="F225" t="n">
-        <v>25682</v>
+        <v>25951</v>
       </c>
     </row>
     <row r="226">
@@ -4944,7 +4944,7 @@
         <v>65</v>
       </c>
       <c r="F226" t="n">
-        <v>20016</v>
+        <v>20436</v>
       </c>
     </row>
     <row r="227">
@@ -5021,10 +5021,10 @@
         <v>63.89</v>
       </c>
       <c r="E230" t="n">
-        <v>64.64</v>
+        <v>64.7</v>
       </c>
       <c r="F230" t="n">
-        <v>16107</v>
+        <v>16472</v>
       </c>
     </row>
     <row r="231">
@@ -5041,10 +5041,10 @@
         <v>64.45</v>
       </c>
       <c r="E231" t="n">
-        <v>64.95</v>
+        <v>65.08</v>
       </c>
       <c r="F231" t="n">
-        <v>16060</v>
+        <v>16251</v>
       </c>
     </row>
     <row r="232">
@@ -5121,10 +5121,10 @@
         <v>61.24</v>
       </c>
       <c r="E235" t="n">
-        <v>61.97</v>
+        <v>62.11</v>
       </c>
       <c r="F235" t="n">
-        <v>22982</v>
+        <v>23208</v>
       </c>
     </row>
     <row r="236">
@@ -5141,10 +5141,10 @@
         <v>60.24</v>
       </c>
       <c r="E236" t="n">
-        <v>60.82</v>
+        <v>60.64</v>
       </c>
       <c r="F236" t="n">
-        <v>21411</v>
+        <v>21687</v>
       </c>
     </row>
     <row r="237">
@@ -5221,10 +5221,10 @@
         <v>56.73</v>
       </c>
       <c r="E240" t="n">
-        <v>58.03</v>
+        <v>58.2</v>
       </c>
       <c r="F240" t="n">
-        <v>28317</v>
+        <v>28894</v>
       </c>
     </row>
     <row r="241">
@@ -5244,7 +5244,7 @@
         <v>56.63</v>
       </c>
       <c r="F241" t="n">
-        <v>30854</v>
+        <v>31264</v>
       </c>
     </row>
     <row r="242">
@@ -5321,10 +5321,10 @@
         <v>54.24</v>
       </c>
       <c r="E245" t="n">
-        <v>55.07</v>
+        <v>55.14</v>
       </c>
       <c r="F245" t="n">
-        <v>31638</v>
+        <v>31917</v>
       </c>
     </row>
     <row r="246">
@@ -5341,10 +5341,10 @@
         <v>54.2</v>
       </c>
       <c r="E246" t="n">
-        <v>54.48</v>
+        <v>54.45</v>
       </c>
       <c r="F246" t="n">
-        <v>25828</v>
+        <v>26144</v>
       </c>
     </row>
     <row r="247">
@@ -5421,10 +5421,10 @@
         <v>54.95</v>
       </c>
       <c r="E250" t="n">
-        <v>56.51</v>
+        <v>56.4</v>
       </c>
       <c r="F250" t="n">
-        <v>24675</v>
+        <v>24914</v>
       </c>
     </row>
     <row r="251">
@@ -5441,10 +5441,10 @@
         <v>56.13</v>
       </c>
       <c r="E251" t="n">
-        <v>57.32</v>
+        <v>57.33</v>
       </c>
       <c r="F251" t="n">
-        <v>21410</v>
+        <v>21778</v>
       </c>
     </row>
     <row r="252">
@@ -5521,10 +5521,10 @@
         <v>58.89</v>
       </c>
       <c r="E255" t="n">
-        <v>59.28</v>
+        <v>59.03</v>
       </c>
       <c r="F255" t="n">
-        <v>23121</v>
+        <v>23391</v>
       </c>
     </row>
     <row r="256">
@@ -5541,10 +5541,10 @@
         <v>57.71</v>
       </c>
       <c r="E256" t="n">
-        <v>58.33</v>
+        <v>58.44</v>
       </c>
       <c r="F256" t="n">
-        <v>26663</v>
+        <v>26971</v>
       </c>
     </row>
     <row r="257">
@@ -5621,10 +5621,10 @@
         <v>50.38</v>
       </c>
       <c r="E260" t="n">
-        <v>51.35</v>
+        <v>50.95</v>
       </c>
       <c r="F260" t="n">
-        <v>51199</v>
+        <v>52807</v>
       </c>
     </row>
     <row r="261">
@@ -5641,10 +5641,10 @@
         <v>48.92</v>
       </c>
       <c r="E261" t="n">
-        <v>50.01</v>
+        <v>50.08</v>
       </c>
       <c r="F261" t="n">
-        <v>71739</v>
+        <v>72794</v>
       </c>
     </row>
     <row r="262">
@@ -5721,10 +5721,10 @@
         <v>49.67</v>
       </c>
       <c r="E265" t="n">
-        <v>49.95</v>
+        <v>50</v>
       </c>
       <c r="F265" t="n">
-        <v>42080</v>
+        <v>42678</v>
       </c>
     </row>
     <row r="266">
@@ -5741,10 +5741,10 @@
         <v>45.16</v>
       </c>
       <c r="E266" t="n">
-        <v>45.55</v>
+        <v>45.51</v>
       </c>
       <c r="F266" t="n">
-        <v>64437</v>
+        <v>65295</v>
       </c>
     </row>
     <row r="267">
@@ -5812,7 +5812,7 @@
         <v>43902</v>
       </c>
       <c r="B270" t="n">
-        <v>35.97</v>
+        <v>36.29</v>
       </c>
       <c r="C270" t="n">
         <v>36.45</v>
@@ -5824,7 +5824,7 @@
         <v>33.49</v>
       </c>
       <c r="F270" t="n">
-        <v>66181</v>
+        <v>64469</v>
       </c>
     </row>
     <row r="271">
@@ -6121,10 +6121,10 @@
         <v>26.12</v>
       </c>
       <c r="E285" t="n">
-        <v>30.29</v>
+        <v>29.96</v>
       </c>
       <c r="F285" t="n">
-        <v>210087</v>
+        <v>214756</v>
       </c>
     </row>
     <row r="286">
@@ -6135,16 +6135,16 @@
         <v>29.95</v>
       </c>
       <c r="C286" t="n">
-        <v>35.24</v>
+        <v>35.28</v>
       </c>
       <c r="D286" t="n">
         <v>28.9</v>
       </c>
       <c r="E286" t="n">
-        <v>34.72</v>
+        <v>35.16</v>
       </c>
       <c r="F286" t="n">
-        <v>275171</v>
+        <v>280402</v>
       </c>
     </row>
     <row r="287">
@@ -6221,10 +6221,10 @@
         <v>32.46</v>
       </c>
       <c r="E290" t="n">
-        <v>33.2</v>
+        <v>32.8</v>
       </c>
       <c r="F290" t="n">
-        <v>230614</v>
+        <v>236196</v>
       </c>
     </row>
     <row r="291">
@@ -6321,10 +6321,10 @@
         <v>29.42</v>
       </c>
       <c r="E295" t="n">
-        <v>30.65</v>
+        <v>30.59</v>
       </c>
       <c r="F295" t="n">
-        <v>146842</v>
+        <v>151526</v>
       </c>
     </row>
     <row r="296">
@@ -6341,10 +6341,10 @@
         <v>30.13</v>
       </c>
       <c r="E296" t="n">
-        <v>30.78</v>
+        <v>30.68</v>
       </c>
       <c r="F296" t="n">
-        <v>171223</v>
+        <v>174982</v>
       </c>
     </row>
     <row r="297">
@@ -6421,10 +6421,10 @@
         <v>23.38</v>
       </c>
       <c r="E300" t="n">
-        <v>24.74</v>
+        <v>24.73</v>
       </c>
       <c r="F300" t="n">
-        <v>213310</v>
+        <v>216653</v>
       </c>
     </row>
     <row r="301">
@@ -6441,10 +6441,10 @@
         <v>23.7</v>
       </c>
       <c r="E301" t="n">
-        <v>24.98</v>
+        <v>24.99</v>
       </c>
       <c r="F301" t="n">
-        <v>163124</v>
+        <v>166443</v>
       </c>
     </row>
     <row r="302">
@@ -6521,10 +6521,10 @@
         <v>24.33</v>
       </c>
       <c r="E305" t="n">
-        <v>26.83</v>
+        <v>26.85</v>
       </c>
       <c r="F305" t="n">
-        <v>224455</v>
+        <v>229615</v>
       </c>
     </row>
     <row r="306">
@@ -6541,10 +6541,10 @@
         <v>26.05</v>
       </c>
       <c r="E306" t="n">
-        <v>26.78</v>
+        <v>26.81</v>
       </c>
       <c r="F306" t="n">
-        <v>196748</v>
+        <v>199609</v>
       </c>
     </row>
     <row r="307">
@@ -6621,10 +6621,10 @@
         <v>29.4</v>
       </c>
       <c r="E310" t="n">
-        <v>29.48</v>
+        <v>29.65</v>
       </c>
       <c r="F310" t="n">
-        <v>225301</v>
+        <v>229585</v>
       </c>
     </row>
     <row r="311">
@@ -6641,10 +6641,10 @@
         <v>29.63</v>
       </c>
       <c r="E311" t="n">
-        <v>31.26</v>
+        <v>31.25</v>
       </c>
       <c r="F311" t="n">
-        <v>192233</v>
+        <v>195288</v>
       </c>
     </row>
     <row r="312">
@@ -6715,16 +6715,16 @@
         <v>29.73</v>
       </c>
       <c r="C315" t="n">
-        <v>31.65</v>
+        <v>31.75</v>
       </c>
       <c r="D315" t="n">
         <v>29.32</v>
       </c>
       <c r="E315" t="n">
-        <v>31.44</v>
+        <v>31.58</v>
       </c>
       <c r="F315" t="n">
-        <v>152193</v>
+        <v>156389</v>
       </c>
     </row>
     <row r="316">
@@ -6735,16 +6735,16 @@
         <v>31.58</v>
       </c>
       <c r="C316" t="n">
-        <v>32.96</v>
+        <v>33.06</v>
       </c>
       <c r="D316" t="n">
         <v>31.23</v>
       </c>
       <c r="E316" t="n">
-        <v>32.9</v>
+        <v>32.94</v>
       </c>
       <c r="F316" t="n">
-        <v>160121</v>
+        <v>163209</v>
       </c>
     </row>
     <row r="317">
@@ -6821,10 +6821,10 @@
         <v>35.92</v>
       </c>
       <c r="E320" t="n">
-        <v>36.38</v>
+        <v>36.3</v>
       </c>
       <c r="F320" t="n">
-        <v>157279</v>
+        <v>160329</v>
       </c>
     </row>
     <row r="321">
@@ -6841,10 +6841,10 @@
         <v>33.87</v>
       </c>
       <c r="E321" t="n">
-        <v>35.66</v>
+        <v>35.52</v>
       </c>
       <c r="F321" t="n">
-        <v>194062</v>
+        <v>198023</v>
       </c>
     </row>
     <row r="322">
@@ -6921,10 +6921,10 @@
         <v>34.37</v>
       </c>
       <c r="E325" t="n">
-        <v>35.89</v>
+        <v>35.98</v>
       </c>
       <c r="F325" t="n">
-        <v>208524</v>
+        <v>213086</v>
       </c>
     </row>
     <row r="326">
@@ -6941,10 +6941,10 @@
         <v>34.87</v>
       </c>
       <c r="E326" t="n">
-        <v>37.43</v>
+        <v>37.61</v>
       </c>
       <c r="F326" t="n">
-        <v>193664</v>
+        <v>198370</v>
       </c>
     </row>
     <row r="327">
@@ -7021,10 +7021,10 @@
         <v>39.05</v>
       </c>
       <c r="E330" t="n">
-        <v>39.78</v>
+        <v>39.92</v>
       </c>
       <c r="F330" t="n">
-        <v>158433</v>
+        <v>161661</v>
       </c>
     </row>
     <row r="331">
@@ -7041,10 +7041,10 @@
         <v>39.75</v>
       </c>
       <c r="E331" t="n">
-        <v>42.14</v>
+        <v>41.83</v>
       </c>
       <c r="F331" t="n">
-        <v>163467</v>
+        <v>167359</v>
       </c>
     </row>
     <row r="332">
@@ -7121,10 +7121,10 @@
         <v>37.96</v>
       </c>
       <c r="E335" t="n">
-        <v>38.36</v>
+        <v>38.41</v>
       </c>
       <c r="F335" t="n">
-        <v>221502</v>
+        <v>227925</v>
       </c>
     </row>
     <row r="336">
@@ -7141,10 +7141,10 @@
         <v>37.14</v>
       </c>
       <c r="E336" t="n">
-        <v>38.94</v>
+        <v>38.97</v>
       </c>
       <c r="F336" t="n">
-        <v>260674</v>
+        <v>263342</v>
       </c>
     </row>
     <row r="337">
@@ -7221,10 +7221,10 @@
         <v>40.05</v>
       </c>
       <c r="E340" t="n">
-        <v>41.37</v>
+        <v>41.33</v>
       </c>
       <c r="F340" t="n">
-        <v>161532</v>
+        <v>163774</v>
       </c>
     </row>
     <row r="341">
@@ -7241,10 +7241,10 @@
         <v>40.97</v>
       </c>
       <c r="E341" t="n">
-        <v>41.99</v>
+        <v>41.78</v>
       </c>
       <c r="F341" t="n">
-        <v>153177</v>
+        <v>156573</v>
       </c>
     </row>
     <row r="342">
@@ -7315,16 +7315,16 @@
         <v>40.45</v>
       </c>
       <c r="C345" t="n">
-        <v>41.51</v>
+        <v>41.59</v>
       </c>
       <c r="D345" t="n">
         <v>39.68</v>
       </c>
       <c r="E345" t="n">
-        <v>41.39</v>
+        <v>41.35</v>
       </c>
       <c r="F345" t="n">
-        <v>178413</v>
+        <v>181021</v>
       </c>
     </row>
     <row r="346">
@@ -7341,10 +7341,10 @@
         <v>40.25</v>
       </c>
       <c r="E346" t="n">
-        <v>40.58</v>
+        <v>40.57</v>
       </c>
       <c r="F346" t="n">
-        <v>157969</v>
+        <v>160433</v>
       </c>
     </row>
     <row r="347">
@@ -7421,10 +7421,10 @@
         <v>41.71</v>
       </c>
       <c r="E350" t="n">
-        <v>42.71</v>
+        <v>42.65</v>
       </c>
       <c r="F350" t="n">
-        <v>142409</v>
+        <v>144329</v>
       </c>
     </row>
     <row r="351">
@@ -7521,10 +7521,10 @@
         <v>41.99</v>
       </c>
       <c r="E355" t="n">
-        <v>42.32</v>
+        <v>42.35</v>
       </c>
       <c r="F355" t="n">
-        <v>133908</v>
+        <v>136451</v>
       </c>
     </row>
     <row r="356">
@@ -7541,10 +7541,10 @@
         <v>41.4</v>
       </c>
       <c r="E356" t="n">
-        <v>43.23</v>
+        <v>43.26</v>
       </c>
       <c r="F356" t="n">
-        <v>152491</v>
+        <v>154800</v>
       </c>
     </row>
     <row r="357">
@@ -7621,10 +7621,10 @@
         <v>43.19</v>
       </c>
       <c r="E360" t="n">
-        <v>43.36</v>
+        <v>43.28</v>
       </c>
       <c r="F360" t="n">
-        <v>99613</v>
+        <v>101544</v>
       </c>
     </row>
     <row r="361">
@@ -7641,10 +7641,10 @@
         <v>42.7</v>
       </c>
       <c r="E361" t="n">
-        <v>43.18</v>
+        <v>43.12</v>
       </c>
       <c r="F361" t="n">
-        <v>93740</v>
+        <v>95049</v>
       </c>
     </row>
     <row r="362">
@@ -7721,10 +7721,10 @@
         <v>43.42</v>
       </c>
       <c r="E365" t="n">
-        <v>43.82</v>
+        <v>43.53</v>
       </c>
       <c r="F365" t="n">
-        <v>109900</v>
+        <v>112495</v>
       </c>
     </row>
     <row r="366">
@@ -7741,10 +7741,10 @@
         <v>43.18</v>
       </c>
       <c r="E366" t="n">
-        <v>43.67</v>
+        <v>43.62</v>
       </c>
       <c r="F366" t="n">
-        <v>115737</v>
+        <v>117377</v>
       </c>
     </row>
     <row r="367">
@@ -7821,10 +7821,10 @@
         <v>41.95</v>
       </c>
       <c r="E370" t="n">
-        <v>43.43</v>
+        <v>43.56</v>
       </c>
       <c r="F370" t="n">
-        <v>113377</v>
+        <v>117072</v>
       </c>
     </row>
     <row r="371">
@@ -7841,10 +7841,10 @@
         <v>42.94</v>
       </c>
       <c r="E371" t="n">
-        <v>43.65</v>
+        <v>43.59</v>
       </c>
       <c r="F371" t="n">
-        <v>127155</v>
+        <v>128800</v>
       </c>
     </row>
     <row r="372">
@@ -7921,10 +7921,10 @@
         <v>44.96</v>
       </c>
       <c r="E375" t="n">
-        <v>45.28</v>
+        <v>45.13</v>
       </c>
       <c r="F375" t="n">
-        <v>120720</v>
+        <v>122044</v>
       </c>
     </row>
     <row r="376">
@@ -7941,10 +7941,10 @@
         <v>44.4</v>
       </c>
       <c r="E376" t="n">
-        <v>44.76</v>
+        <v>44.71</v>
       </c>
       <c r="F376" t="n">
-        <v>119541</v>
+        <v>120731</v>
       </c>
     </row>
     <row r="377">
@@ -8021,10 +8021,10 @@
         <v>45.07</v>
       </c>
       <c r="E380" t="n">
-        <v>45.3</v>
+        <v>45.24</v>
       </c>
       <c r="F380" t="n">
-        <v>90204</v>
+        <v>91702</v>
       </c>
     </row>
     <row r="381">
@@ -8041,10 +8041,10 @@
         <v>44.77</v>
       </c>
       <c r="E381" t="n">
-        <v>45.2</v>
+        <v>45.19</v>
       </c>
       <c r="F381" t="n">
-        <v>83793</v>
+        <v>85013</v>
       </c>
     </row>
     <row r="382">
@@ -8121,10 +8121,10 @@
         <v>44.46</v>
       </c>
       <c r="E385" t="n">
-        <v>45.36</v>
+        <v>45.27</v>
       </c>
       <c r="F385" t="n">
-        <v>86301</v>
+        <v>87294</v>
       </c>
     </row>
     <row r="386">
@@ -8141,10 +8141,10 @@
         <v>44.09</v>
       </c>
       <c r="E386" t="n">
-        <v>44.79</v>
+        <v>44.69</v>
       </c>
       <c r="F386" t="n">
-        <v>77659</v>
+        <v>78965</v>
       </c>
     </row>
     <row r="387">
@@ -8224,7 +8224,7 @@
         <v>45.59</v>
       </c>
       <c r="F390" t="n">
-        <v>95873</v>
+        <v>96916</v>
       </c>
     </row>
     <row r="391">
@@ -8241,10 +8241,10 @@
         <v>45.36</v>
       </c>
       <c r="E391" t="n">
-        <v>45.89</v>
+        <v>45.85</v>
       </c>
       <c r="F391" t="n">
-        <v>81058</v>
+        <v>81841</v>
       </c>
     </row>
     <row r="392">
@@ -8321,10 +8321,10 @@
         <v>43.27</v>
       </c>
       <c r="E395" t="n">
-        <v>44.09</v>
+        <v>44.07</v>
       </c>
       <c r="F395" t="n">
-        <v>157249</v>
+        <v>158723</v>
       </c>
     </row>
     <row r="396">
@@ -8338,13 +8338,13 @@
         <v>44.69</v>
       </c>
       <c r="D396" t="n">
-        <v>42.45</v>
+        <v>42.42</v>
       </c>
       <c r="E396" t="n">
-        <v>42.53</v>
+        <v>42.43</v>
       </c>
       <c r="F396" t="n">
-        <v>160902</v>
+        <v>162787</v>
       </c>
     </row>
     <row r="397">
@@ -8418,13 +8418,13 @@
         <v>41.23</v>
       </c>
       <c r="D400" t="n">
-        <v>40.02</v>
+        <v>39.96</v>
       </c>
       <c r="E400" t="n">
-        <v>40.07</v>
+        <v>39.97</v>
       </c>
       <c r="F400" t="n">
-        <v>147551</v>
+        <v>149451</v>
       </c>
     </row>
     <row r="401">
@@ -8441,10 +8441,10 @@
         <v>39.68</v>
       </c>
       <c r="E401" t="n">
-        <v>40.24</v>
+        <v>40.02</v>
       </c>
       <c r="F401" t="n">
-        <v>133943</v>
+        <v>135456</v>
       </c>
     </row>
     <row r="402">
@@ -8521,10 +8521,10 @@
         <v>41.89</v>
       </c>
       <c r="E405" t="n">
-        <v>43.67</v>
+        <v>43.58</v>
       </c>
       <c r="F405" t="n">
-        <v>141089</v>
+        <v>142611</v>
       </c>
     </row>
     <row r="406">
@@ -8541,10 +8541,10 @@
         <v>42.92</v>
       </c>
       <c r="E406" t="n">
-        <v>43.34</v>
+        <v>43.41</v>
       </c>
       <c r="F406" t="n">
-        <v>127380</v>
+        <v>129546</v>
       </c>
     </row>
     <row r="407">
@@ -8621,10 +8621,10 @@
         <v>41.68</v>
       </c>
       <c r="E410" t="n">
-        <v>42.27</v>
+        <v>42.16</v>
       </c>
       <c r="F410" t="n">
-        <v>132502</v>
+        <v>133961</v>
       </c>
     </row>
     <row r="411">
@@ -8641,10 +8641,10 @@
         <v>41.97</v>
       </c>
       <c r="E411" t="n">
-        <v>42.24</v>
+        <v>42.17</v>
       </c>
       <c r="F411" t="n">
-        <v>100264</v>
+        <v>102107</v>
       </c>
     </row>
     <row r="412">
@@ -8721,10 +8721,10 @@
         <v>39.98</v>
       </c>
       <c r="E415" t="n">
-        <v>40.93</v>
+        <v>40.75</v>
       </c>
       <c r="F415" t="n">
-        <v>155461</v>
+        <v>157712</v>
       </c>
     </row>
     <row r="416">
@@ -8741,10 +8741,10 @@
         <v>38.88</v>
       </c>
       <c r="E416" t="n">
-        <v>39.23</v>
+        <v>39.15</v>
       </c>
       <c r="F416" t="n">
-        <v>188336</v>
+        <v>190634</v>
       </c>
     </row>
     <row r="417">
@@ -8821,10 +8821,10 @@
         <v>42.02</v>
       </c>
       <c r="E420" t="n">
-        <v>43.54</v>
+        <v>43.52</v>
       </c>
       <c r="F420" t="n">
-        <v>110782</v>
+        <v>112342</v>
       </c>
     </row>
     <row r="421">
@@ -8841,10 +8841,10 @@
         <v>42.78</v>
       </c>
       <c r="E421" t="n">
-        <v>42.96</v>
+        <v>42.89</v>
       </c>
       <c r="F421" t="n">
-        <v>108274</v>
+        <v>109695</v>
       </c>
     </row>
     <row r="422">
@@ -8921,10 +8921,10 @@
         <v>41.79</v>
       </c>
       <c r="E425" t="n">
-        <v>43.38</v>
+        <v>43.26</v>
       </c>
       <c r="F425" t="n">
-        <v>146298</v>
+        <v>147757</v>
       </c>
     </row>
     <row r="426">
@@ -8941,10 +8941,10 @@
         <v>42.47</v>
       </c>
       <c r="E426" t="n">
-        <v>43.02</v>
+        <v>42.95</v>
       </c>
       <c r="F426" t="n">
-        <v>129338</v>
+        <v>130839</v>
       </c>
     </row>
     <row r="427">
@@ -9021,10 +9021,10 @@
         <v>41.72</v>
       </c>
       <c r="E430" t="n">
-        <v>42.71</v>
+        <v>42.59</v>
       </c>
       <c r="F430" t="n">
-        <v>108471</v>
+        <v>110171</v>
       </c>
     </row>
     <row r="431">
@@ -9041,10 +9041,10 @@
         <v>41.76</v>
       </c>
       <c r="E431" t="n">
-        <v>41.93</v>
+        <v>41.85</v>
       </c>
       <c r="F431" t="n">
-        <v>95688</v>
+        <v>97195</v>
       </c>
     </row>
     <row r="432">
@@ -9112,7 +9112,7 @@
         <v>44133</v>
       </c>
       <c r="B435" t="n">
-        <v>39.52</v>
+        <v>39.76</v>
       </c>
       <c r="C435" t="n">
         <v>39.97</v>
@@ -9124,7 +9124,7 @@
         <v>38.05</v>
       </c>
       <c r="F435" t="n">
-        <v>183949</v>
+        <v>179602</v>
       </c>
     </row>
     <row r="436">
@@ -9132,7 +9132,7 @@
         <v>44134</v>
       </c>
       <c r="B436" t="n">
-        <v>38.05</v>
+        <v>38.25</v>
       </c>
       <c r="C436" t="n">
         <v>38.72</v>
@@ -9144,7 +9144,7 @@
         <v>37.84</v>
       </c>
       <c r="F436" t="n">
-        <v>184633</v>
+        <v>181739</v>
       </c>
     </row>
     <row r="437">
@@ -9221,10 +9221,10 @@
         <v>40.42</v>
       </c>
       <c r="E440" t="n">
-        <v>40.82</v>
+        <v>40.68</v>
       </c>
       <c r="F440" t="n">
-        <v>155706</v>
+        <v>157779</v>
       </c>
     </row>
     <row r="441">
@@ -9241,10 +9241,10 @@
         <v>39.46</v>
       </c>
       <c r="E441" t="n">
-        <v>39.84</v>
+        <v>39.71</v>
       </c>
       <c r="F441" t="n">
-        <v>150078</v>
+        <v>151438</v>
       </c>
     </row>
     <row r="442">
@@ -9318,13 +9318,13 @@
         <v>44.59</v>
       </c>
       <c r="D445" t="n">
-        <v>43.42</v>
+        <v>43.35</v>
       </c>
       <c r="E445" t="n">
-        <v>43.49</v>
+        <v>43.38</v>
       </c>
       <c r="F445" t="n">
-        <v>144322</v>
+        <v>146964</v>
       </c>
     </row>
     <row r="446">
@@ -9338,13 +9338,13 @@
         <v>43.45</v>
       </c>
       <c r="D446" t="n">
-        <v>42.77</v>
+        <v>42.68</v>
       </c>
       <c r="E446" t="n">
-        <v>42.88</v>
+        <v>42.69</v>
       </c>
       <c r="F446" t="n">
-        <v>112789</v>
+        <v>114191</v>
       </c>
     </row>
     <row r="447">
@@ -9421,10 +9421,10 @@
         <v>43.87</v>
       </c>
       <c r="E450" t="n">
-        <v>44.44</v>
+        <v>44.21</v>
       </c>
       <c r="F450" t="n">
-        <v>111013</v>
+        <v>112468</v>
       </c>
     </row>
     <row r="451">
@@ -9441,10 +9441,10 @@
         <v>44.15</v>
       </c>
       <c r="E451" t="n">
-        <v>45.06</v>
+        <v>45.07</v>
       </c>
       <c r="F451" t="n">
-        <v>88612</v>
+        <v>90427</v>
       </c>
     </row>
     <row r="452">
@@ -9624,7 +9624,7 @@
         <v>48.65</v>
       </c>
       <c r="F460" t="n">
-        <v>119976</v>
+        <v>122403</v>
       </c>
     </row>
     <row r="461">
@@ -9641,10 +9641,10 @@
         <v>48.77</v>
       </c>
       <c r="E461" t="n">
-        <v>48.97</v>
+        <v>48.96</v>
       </c>
       <c r="F461" t="n">
-        <v>124413</v>
+        <v>125701</v>
       </c>
     </row>
     <row r="462">
@@ -9721,10 +9721,10 @@
         <v>48.79</v>
       </c>
       <c r="E465" t="n">
-        <v>50.26</v>
+        <v>50.25</v>
       </c>
       <c r="F465" t="n">
-        <v>130125</v>
+        <v>132386</v>
       </c>
     </row>
     <row r="466">
@@ -9741,10 +9741,10 @@
         <v>49.67</v>
       </c>
       <c r="E466" t="n">
-        <v>49.94</v>
+        <v>49.86</v>
       </c>
       <c r="F466" t="n">
-        <v>123293</v>
+        <v>124721</v>
       </c>
     </row>
     <row r="467">
@@ -9821,10 +9821,10 @@
         <v>51.06</v>
       </c>
       <c r="E470" t="n">
-        <v>51.55</v>
+        <v>51.46</v>
       </c>
       <c r="F470" t="n">
-        <v>100894</v>
+        <v>102867</v>
       </c>
     </row>
     <row r="471">
@@ -9841,10 +9841,10 @@
         <v>51.16</v>
       </c>
       <c r="E471" t="n">
-        <v>52.19</v>
+        <v>52.23</v>
       </c>
       <c r="F471" t="n">
-        <v>96861</v>
+        <v>98705</v>
       </c>
     </row>
     <row r="472">
@@ -10081,10 +10081,10 @@
         <v>53.88</v>
       </c>
       <c r="E483" t="n">
-        <v>54.45</v>
+        <v>54.34</v>
       </c>
       <c r="F483" t="n">
-        <v>140683</v>
+        <v>142258</v>
       </c>
     </row>
     <row r="484">
@@ -10095,16 +10095,16 @@
         <v>54.46</v>
       </c>
       <c r="C484" t="n">
-        <v>56.06</v>
+        <v>56.2</v>
       </c>
       <c r="D484" t="n">
         <v>54.3</v>
       </c>
       <c r="E484" t="n">
-        <v>56.02</v>
+        <v>56.11</v>
       </c>
       <c r="F484" t="n">
-        <v>151805</v>
+        <v>155413</v>
       </c>
     </row>
     <row r="485">
@@ -10181,10 +10181,10 @@
         <v>55.21</v>
       </c>
       <c r="E488" t="n">
-        <v>56.3</v>
+        <v>56.37</v>
       </c>
       <c r="F488" t="n">
-        <v>123090</v>
+        <v>125098</v>
       </c>
     </row>
     <row r="489">
@@ -10201,10 +10201,10 @@
         <v>54.63</v>
       </c>
       <c r="E489" t="n">
-        <v>54.94</v>
+        <v>54.75</v>
       </c>
       <c r="F489" t="n">
-        <v>133988</v>
+        <v>135898</v>
       </c>
     </row>
     <row r="490">
@@ -10281,10 +10281,10 @@
         <v>55.38</v>
       </c>
       <c r="E493" t="n">
-        <v>55.86</v>
+        <v>55.84</v>
       </c>
       <c r="F493" t="n">
-        <v>103188</v>
+        <v>104851</v>
       </c>
     </row>
     <row r="494">
@@ -10301,10 +10301,10 @@
         <v>54.38</v>
       </c>
       <c r="E494" t="n">
-        <v>55.08</v>
+        <v>54.88</v>
       </c>
       <c r="F494" t="n">
-        <v>133367</v>
+        <v>135622</v>
       </c>
     </row>
     <row r="495">
@@ -10378,13 +10378,13 @@
         <v>56.16</v>
       </c>
       <c r="D498" t="n">
-        <v>54.93</v>
+        <v>54.84</v>
       </c>
       <c r="E498" t="n">
-        <v>55</v>
+        <v>54.84</v>
       </c>
       <c r="F498" t="n">
-        <v>160473</v>
+        <v>162289</v>
       </c>
     </row>
     <row r="499">
@@ -10401,10 +10401,10 @@
         <v>54.84</v>
       </c>
       <c r="E499" t="n">
-        <v>55</v>
+        <v>54.93</v>
       </c>
       <c r="F499" t="n">
-        <v>160923</v>
+        <v>163671</v>
       </c>
     </row>
     <row r="500">
@@ -10481,10 +10481,10 @@
         <v>57.93</v>
       </c>
       <c r="E503" t="n">
-        <v>58.79</v>
+        <v>58.87</v>
       </c>
       <c r="F503" t="n">
-        <v>123567</v>
+        <v>125851</v>
       </c>
     </row>
     <row r="504">
@@ -10501,10 +10501,10 @@
         <v>58.87</v>
       </c>
       <c r="E504" t="n">
-        <v>59.31</v>
+        <v>59.41</v>
       </c>
       <c r="F504" t="n">
-        <v>118436</v>
+        <v>120954</v>
       </c>
     </row>
     <row r="505">
@@ -10578,13 +10578,13 @@
         <v>61.23</v>
       </c>
       <c r="D508" t="n">
-        <v>60.5</v>
+        <v>60.44</v>
       </c>
       <c r="E508" t="n">
-        <v>60.6</v>
+        <v>60.52</v>
       </c>
       <c r="F508" t="n">
-        <v>104511</v>
+        <v>107974</v>
       </c>
     </row>
     <row r="509">
@@ -10604,7 +10604,7 @@
         <v>62.22</v>
       </c>
       <c r="F509" t="n">
-        <v>123306</v>
+        <v>126905</v>
       </c>
     </row>
     <row r="510">
@@ -10681,10 +10681,10 @@
         <v>62.54</v>
       </c>
       <c r="E513" t="n">
-        <v>62.75</v>
+        <v>62.88</v>
       </c>
       <c r="F513" t="n">
-        <v>170306</v>
+        <v>173632</v>
       </c>
     </row>
     <row r="514">
@@ -10701,10 +10701,10 @@
         <v>61.42</v>
       </c>
       <c r="E514" t="n">
-        <v>61.95</v>
+        <v>61.97</v>
       </c>
       <c r="F514" t="n">
-        <v>181146</v>
+        <v>184306</v>
       </c>
     </row>
     <row r="515">
@@ -10781,10 +10781,10 @@
         <v>65.55</v>
       </c>
       <c r="E518" t="n">
-        <v>65.86</v>
+        <v>65.97</v>
       </c>
       <c r="F518" t="n">
-        <v>210726</v>
+        <v>215533</v>
       </c>
     </row>
     <row r="519">
@@ -10801,10 +10801,10 @@
         <v>64.13</v>
       </c>
       <c r="E519" t="n">
-        <v>64.25</v>
+        <v>64.27</v>
       </c>
       <c r="F519" t="n">
-        <v>234931</v>
+        <v>239274</v>
       </c>
     </row>
     <row r="520">
@@ -10881,10 +10881,10 @@
         <v>63.17</v>
       </c>
       <c r="E523" t="n">
-        <v>66.94</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="F523" t="n">
-        <v>225843</v>
+        <v>230530</v>
       </c>
     </row>
     <row r="524">
@@ -10895,16 +10895,16 @@
         <v>66.86</v>
       </c>
       <c r="C524" t="n">
-        <v>69.31999999999999</v>
+        <v>69.41</v>
       </c>
       <c r="D524" t="n">
         <v>66.43000000000001</v>
       </c>
       <c r="E524" t="n">
-        <v>69.28</v>
+        <v>69.25</v>
       </c>
       <c r="F524" t="n">
-        <v>249828</v>
+        <v>253026</v>
       </c>
     </row>
     <row r="525">
@@ -10981,10 +10981,10 @@
         <v>67.68000000000001</v>
       </c>
       <c r="E528" t="n">
-        <v>69.40000000000001</v>
+        <v>69.17</v>
       </c>
       <c r="F528" t="n">
-        <v>160838</v>
+        <v>163581</v>
       </c>
     </row>
     <row r="529">
@@ -11001,10 +11001,10 @@
         <v>68.66</v>
       </c>
       <c r="E529" t="n">
-        <v>68.88</v>
+        <v>68.81</v>
       </c>
       <c r="F529" t="n">
-        <v>148823</v>
+        <v>151042</v>
       </c>
     </row>
     <row r="530">
@@ -11072,7 +11072,7 @@
         <v>44273</v>
       </c>
       <c r="B533" t="n">
-        <v>67.48</v>
+        <v>67.47</v>
       </c>
       <c r="C533" t="n">
         <v>67.83</v>
@@ -11084,7 +11084,7 @@
         <v>62.5</v>
       </c>
       <c r="F533" t="n">
-        <v>212082</v>
+        <v>209835</v>
       </c>
     </row>
     <row r="534">
@@ -11092,7 +11092,7 @@
         <v>44274</v>
       </c>
       <c r="B534" t="n">
-        <v>62.78</v>
+        <v>63.02</v>
       </c>
       <c r="C534" t="n">
         <v>64.73</v>
@@ -11104,7 +11104,7 @@
         <v>64.31999999999999</v>
       </c>
       <c r="F534" t="n">
-        <v>228148</v>
+        <v>223529</v>
       </c>
     </row>
     <row r="535">
@@ -11172,10 +11172,10 @@
         <v>44280</v>
       </c>
       <c r="B538" t="n">
-        <v>63.95</v>
+        <v>63.89</v>
       </c>
       <c r="C538" t="n">
-        <v>64.01000000000001</v>
+        <v>63.9</v>
       </c>
       <c r="D538" t="n">
         <v>60.82</v>
@@ -11184,7 +11184,7 @@
         <v>61.47</v>
       </c>
       <c r="F538" t="n">
-        <v>206155</v>
+        <v>203253</v>
       </c>
     </row>
     <row r="539">
@@ -11192,19 +11192,19 @@
         <v>44281</v>
       </c>
       <c r="B539" t="n">
-        <v>61.47</v>
+        <v>62.45</v>
       </c>
       <c r="C539" t="n">
         <v>64.73</v>
       </c>
       <c r="D539" t="n">
-        <v>61.47</v>
+        <v>62.07</v>
       </c>
       <c r="E539" t="n">
         <v>64.19</v>
       </c>
       <c r="F539" t="n">
-        <v>171041</v>
+        <v>167422</v>
       </c>
     </row>
     <row r="540">
@@ -11284,7 +11284,7 @@
         <v>64.51000000000001</v>
       </c>
       <c r="F543" t="n">
-        <v>197783</v>
+        <v>201289</v>
       </c>
     </row>
     <row r="544">
@@ -11361,10 +11361,10 @@
         <v>62.18</v>
       </c>
       <c r="E547" t="n">
-        <v>63.07</v>
+        <v>63.04</v>
       </c>
       <c r="F547" t="n">
-        <v>146277</v>
+        <v>149186</v>
       </c>
     </row>
     <row r="548">
@@ -11381,10 +11381,10 @@
         <v>62.33</v>
       </c>
       <c r="E548" t="n">
-        <v>62.81</v>
+        <v>62.76</v>
       </c>
       <c r="F548" t="n">
-        <v>119219</v>
+        <v>121247</v>
       </c>
     </row>
     <row r="549">
@@ -11461,10 +11461,10 @@
         <v>65.65000000000001</v>
       </c>
       <c r="E552" t="n">
-        <v>66.5</v>
+        <v>66.45</v>
       </c>
       <c r="F552" t="n">
-        <v>133306</v>
+        <v>135521</v>
       </c>
     </row>
     <row r="553">
@@ -11481,10 +11481,10 @@
         <v>66.11</v>
       </c>
       <c r="E553" t="n">
-        <v>66.40000000000001</v>
+        <v>66.31999999999999</v>
       </c>
       <c r="F553" t="n">
-        <v>120895</v>
+        <v>122938</v>
       </c>
     </row>
     <row r="554">
@@ -11564,7 +11564,7 @@
         <v>64.95</v>
       </c>
       <c r="F557" t="n">
-        <v>140975</v>
+        <v>143350</v>
       </c>
     </row>
     <row r="558">
@@ -11581,10 +11581,10 @@
         <v>64.52</v>
       </c>
       <c r="E558" t="n">
-        <v>65.45</v>
+        <v>65.31999999999999</v>
       </c>
       <c r="F558" t="n">
-        <v>124432</v>
+        <v>126302</v>
       </c>
     </row>
     <row r="559">
@@ -11661,10 +11661,10 @@
         <v>66.56</v>
       </c>
       <c r="E562" t="n">
-        <v>67.86</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="F562" t="n">
-        <v>157092</v>
+        <v>160482</v>
       </c>
     </row>
     <row r="563">
@@ -11681,10 +11681,10 @@
         <v>66.17</v>
       </c>
       <c r="E563" t="n">
-        <v>66.56</v>
+        <v>66.53</v>
       </c>
       <c r="F563" t="n">
-        <v>145779</v>
+        <v>148372</v>
       </c>
     </row>
     <row r="564">
@@ -11761,10 +11761,10 @@
         <v>67.77</v>
       </c>
       <c r="E567" t="n">
-        <v>68.05</v>
+        <v>68.03</v>
       </c>
       <c r="F567" t="n">
-        <v>153533</v>
+        <v>155507</v>
       </c>
     </row>
     <row r="568">
@@ -11784,7 +11784,7 @@
         <v>68.03</v>
       </c>
       <c r="F568" t="n">
-        <v>136012</v>
+        <v>139157</v>
       </c>
     </row>
     <row r="569">
@@ -11861,10 +11861,10 @@
         <v>66.34</v>
       </c>
       <c r="E572" t="n">
-        <v>66.83</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="F572" t="n">
-        <v>180093</v>
+        <v>182316</v>
       </c>
     </row>
     <row r="573">
@@ -11875,16 +11875,16 @@
         <v>66.81</v>
       </c>
       <c r="C573" t="n">
-        <v>68.52</v>
+        <v>68.63</v>
       </c>
       <c r="D573" t="n">
         <v>66.36</v>
       </c>
       <c r="E573" t="n">
-        <v>68.45</v>
+        <v>68.52</v>
       </c>
       <c r="F573" t="n">
-        <v>139950</v>
+        <v>142226</v>
       </c>
     </row>
     <row r="574">
@@ -11958,13 +11958,13 @@
         <v>67.02</v>
       </c>
       <c r="D577" t="n">
-        <v>64.73</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="E577" t="n">
-        <v>64.98999999999999</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="F577" t="n">
-        <v>164782</v>
+        <v>168733</v>
       </c>
     </row>
     <row r="578">
@@ -11981,10 +11981,10 @@
         <v>64.48</v>
       </c>
       <c r="E578" t="n">
-        <v>66.58</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="F578" t="n">
-        <v>153693</v>
+        <v>156317</v>
       </c>
     </row>
     <row r="579">
@@ -12055,16 +12055,16 @@
         <v>68.58</v>
       </c>
       <c r="C582" t="n">
-        <v>69.18000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="D582" t="n">
         <v>67.89</v>
       </c>
       <c r="E582" t="n">
-        <v>69.05</v>
+        <v>69.12</v>
       </c>
       <c r="F582" t="n">
-        <v>119490</v>
+        <v>122427</v>
       </c>
     </row>
     <row r="583">
@@ -12081,10 +12081,10 @@
         <v>68.48999999999999</v>
       </c>
       <c r="E583" t="n">
-        <v>68.89</v>
+        <v>68.88</v>
       </c>
       <c r="F583" t="n">
-        <v>119218</v>
+        <v>121324</v>
       </c>
     </row>
     <row r="584">
@@ -12161,10 +12161,10 @@
         <v>70.5</v>
       </c>
       <c r="E587" t="n">
-        <v>71.20999999999999</v>
+        <v>71.22</v>
       </c>
       <c r="F587" t="n">
-        <v>126247</v>
+        <v>128649</v>
       </c>
     </row>
     <row r="588">
@@ -12181,10 +12181,10 @@
         <v>70.58</v>
       </c>
       <c r="E588" t="n">
-        <v>71.47</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="F588" t="n">
-        <v>113793</v>
+        <v>117041</v>
       </c>
     </row>
     <row r="589">
@@ -12261,10 +12261,10 @@
         <v>70.66</v>
       </c>
       <c r="E592" t="n">
-        <v>72.09</v>
+        <v>71.95</v>
       </c>
       <c r="F592" t="n">
-        <v>146487</v>
+        <v>148450</v>
       </c>
     </row>
     <row r="593">
@@ -12284,7 +12284,7 @@
         <v>72.23999999999999</v>
       </c>
       <c r="F593" t="n">
-        <v>140128</v>
+        <v>142367</v>
       </c>
     </row>
     <row r="594">
@@ -12361,10 +12361,10 @@
         <v>71.41</v>
       </c>
       <c r="E597" t="n">
-        <v>72.45</v>
+        <v>72.44</v>
       </c>
       <c r="F597" t="n">
-        <v>175025</v>
+        <v>178094</v>
       </c>
     </row>
     <row r="598">
@@ -12381,10 +12381,10 @@
         <v>71.55</v>
       </c>
       <c r="E598" t="n">
-        <v>72.76000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="F598" t="n">
-        <v>147859</v>
+        <v>151345</v>
       </c>
     </row>
     <row r="599">
@@ -12461,10 +12461,10 @@
         <v>73.83</v>
       </c>
       <c r="E602" t="n">
-        <v>74.79000000000001</v>
+        <v>74.81</v>
       </c>
       <c r="F602" t="n">
-        <v>84577</v>
+        <v>85692</v>
       </c>
     </row>
     <row r="603">
@@ -12481,10 +12481,10 @@
         <v>74.14</v>
       </c>
       <c r="E603" t="n">
-        <v>75.27</v>
+        <v>75.28</v>
       </c>
       <c r="F603" t="n">
-        <v>77990</v>
+        <v>79112</v>
       </c>
     </row>
     <row r="604">
@@ -12561,10 +12561,10 @@
         <v>74.36</v>
       </c>
       <c r="E607" t="n">
-        <v>75.33</v>
+        <v>75.34</v>
       </c>
       <c r="F607" t="n">
-        <v>134296</v>
+        <v>135699</v>
       </c>
     </row>
     <row r="608">
@@ -12581,10 +12581,10 @@
         <v>75</v>
       </c>
       <c r="E608" t="n">
-        <v>76.02</v>
+        <v>75.81999999999999</v>
       </c>
       <c r="F608" t="n">
-        <v>102316</v>
+        <v>104256</v>
       </c>
     </row>
     <row r="609">
@@ -12655,16 +12655,16 @@
         <v>72.97</v>
       </c>
       <c r="C612" t="n">
-        <v>73.97</v>
+        <v>74.02</v>
       </c>
       <c r="D612" t="n">
         <v>71.73999999999999</v>
       </c>
       <c r="E612" t="n">
-        <v>73.92</v>
+        <v>73.95999999999999</v>
       </c>
       <c r="F612" t="n">
-        <v>136419</v>
+        <v>138030</v>
       </c>
     </row>
     <row r="613">
@@ -12681,10 +12681,10 @@
         <v>73.38</v>
       </c>
       <c r="E613" t="n">
-        <v>75.15000000000001</v>
+        <v>75.14</v>
       </c>
       <c r="F613" t="n">
-        <v>95892</v>
+        <v>96988</v>
       </c>
     </row>
     <row r="614">
@@ -12761,10 +12761,10 @@
         <v>72.70999999999999</v>
       </c>
       <c r="E617" t="n">
-        <v>72.79000000000001</v>
+        <v>72.72</v>
       </c>
       <c r="F617" t="n">
-        <v>132350</v>
+        <v>134216</v>
       </c>
     </row>
     <row r="618">
@@ -12781,10 +12781,10 @@
         <v>71.88</v>
       </c>
       <c r="E618" t="n">
-        <v>72.81</v>
+        <v>72.64</v>
       </c>
       <c r="F618" t="n">
-        <v>108307</v>
+        <v>110158</v>
       </c>
     </row>
     <row r="619">
@@ -12864,7 +12864,7 @@
         <v>73.01000000000001</v>
       </c>
       <c r="F622" t="n">
-        <v>113951</v>
+        <v>115159</v>
       </c>
     </row>
     <row r="623">
@@ -12875,16 +12875,16 @@
         <v>72.98</v>
       </c>
       <c r="C623" t="n">
-        <v>73.52</v>
+        <v>73.56999999999999</v>
       </c>
       <c r="D623" t="n">
         <v>72.70999999999999</v>
       </c>
       <c r="E623" t="n">
-        <v>73.44</v>
+        <v>73.5</v>
       </c>
       <c r="F623" t="n">
-        <v>83411</v>
+        <v>84579</v>
       </c>
     </row>
     <row r="624">
@@ -12961,10 +12961,10 @@
         <v>73.59999999999999</v>
       </c>
       <c r="E627" t="n">
-        <v>74.97</v>
+        <v>74.75</v>
       </c>
       <c r="F627" t="n">
-        <v>79720</v>
+        <v>81467</v>
       </c>
     </row>
     <row r="628">
@@ -12981,10 +12981,10 @@
         <v>74.26000000000001</v>
       </c>
       <c r="E628" t="n">
-        <v>74.98999999999999</v>
+        <v>74.95999999999999</v>
       </c>
       <c r="F628" t="n">
-        <v>83101</v>
+        <v>84253</v>
       </c>
     </row>
     <row r="629">
@@ -13061,10 +13061,10 @@
         <v>69.56</v>
       </c>
       <c r="E632" t="n">
-        <v>71.16</v>
+        <v>71</v>
       </c>
       <c r="F632" t="n">
-        <v>107034</v>
+        <v>108267</v>
       </c>
     </row>
     <row r="633">
@@ -13078,13 +13078,13 @@
         <v>72.22</v>
       </c>
       <c r="D633" t="n">
-        <v>70.12</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="E633" t="n">
-        <v>70.34999999999999</v>
+        <v>70.08</v>
       </c>
       <c r="F633" t="n">
-        <v>111453</v>
+        <v>113105</v>
       </c>
     </row>
     <row r="634">
@@ -13161,10 +13161,10 @@
         <v>70.41</v>
       </c>
       <c r="E637" t="n">
-        <v>70.90000000000001</v>
+        <v>70.86</v>
       </c>
       <c r="F637" t="n">
-        <v>95219</v>
+        <v>96203</v>
       </c>
     </row>
     <row r="638">
@@ -13181,10 +13181,10 @@
         <v>69.73999999999999</v>
       </c>
       <c r="E638" t="n">
-        <v>69.92</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="F638" t="n">
-        <v>93960</v>
+        <v>95696</v>
       </c>
     </row>
     <row r="639">
@@ -13261,10 +13261,10 @@
         <v>65.2</v>
       </c>
       <c r="E642" t="n">
-        <v>66.51000000000001</v>
+        <v>66.23</v>
       </c>
       <c r="F642" t="n">
-        <v>185678</v>
+        <v>187712</v>
       </c>
     </row>
     <row r="643">
@@ -13278,13 +13278,13 @@
         <v>66.54000000000001</v>
       </c>
       <c r="D643" t="n">
-        <v>64.61</v>
+        <v>64.53</v>
       </c>
       <c r="E643" t="n">
-        <v>64.62</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="F643" t="n">
-        <v>137258</v>
+        <v>138989</v>
       </c>
     </row>
     <row r="644">
@@ -13361,10 +13361,10 @@
         <v>69.73999999999999</v>
       </c>
       <c r="E647" t="n">
-        <v>70.56</v>
+        <v>70.45999999999999</v>
       </c>
       <c r="F647" t="n">
-        <v>113839</v>
+        <v>115965</v>
       </c>
     </row>
     <row r="648">
@@ -13381,10 +13381,10 @@
         <v>70.16</v>
       </c>
       <c r="E648" t="n">
-        <v>71.59999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="F648" t="n">
-        <v>99158</v>
+        <v>100455</v>
       </c>
     </row>
     <row r="649">
@@ -13461,10 +13461,10 @@
         <v>70.75</v>
       </c>
       <c r="E652" t="n">
-        <v>72.56999999999999</v>
+        <v>72.61</v>
       </c>
       <c r="F652" t="n">
-        <v>103772</v>
+        <v>105073</v>
       </c>
     </row>
     <row r="653">
@@ -13481,10 +13481,10 @@
         <v>72.20999999999999</v>
       </c>
       <c r="E653" t="n">
-        <v>72.36</v>
+        <v>72.20999999999999</v>
       </c>
       <c r="F653" t="n">
-        <v>110684</v>
+        <v>111688</v>
       </c>
     </row>
     <row r="654">
@@ -13561,10 +13561,10 @@
         <v>70.54000000000001</v>
       </c>
       <c r="E657" t="n">
-        <v>70.95</v>
+        <v>70.84</v>
       </c>
       <c r="F657" t="n">
-        <v>136836</v>
+        <v>138553</v>
       </c>
     </row>
     <row r="658">
@@ -13581,10 +13581,10 @@
         <v>70.59</v>
       </c>
       <c r="E658" t="n">
-        <v>72.44</v>
+        <v>72.51000000000001</v>
       </c>
       <c r="F658" t="n">
-        <v>106315</v>
+        <v>107925</v>
       </c>
     </row>
     <row r="659">
@@ -13661,10 +13661,10 @@
         <v>74.02</v>
       </c>
       <c r="E662" t="n">
-        <v>75.17</v>
+        <v>75.09</v>
       </c>
       <c r="F662" t="n">
-        <v>134873</v>
+        <v>136265</v>
       </c>
     </row>
     <row r="663">
@@ -13681,10 +13681,10 @@
         <v>74.06999999999999</v>
       </c>
       <c r="E663" t="n">
-        <v>74.79000000000001</v>
+        <v>74.67</v>
       </c>
       <c r="F663" t="n">
-        <v>129577</v>
+        <v>131243</v>
       </c>
     </row>
     <row r="664">
@@ -13764,7 +13764,7 @@
         <v>76.45</v>
       </c>
       <c r="F667" t="n">
-        <v>102612</v>
+        <v>104066</v>
       </c>
     </row>
     <row r="668">
@@ -13781,10 +13781,10 @@
         <v>76.09</v>
       </c>
       <c r="E668" t="n">
-        <v>77.15000000000001</v>
+        <v>77.13</v>
       </c>
       <c r="F668" t="n">
-        <v>93448</v>
+        <v>94529</v>
       </c>
     </row>
     <row r="669">
@@ -13861,10 +13861,10 @@
         <v>76.37</v>
       </c>
       <c r="E672" t="n">
-        <v>78.13</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="F672" t="n">
-        <v>180155</v>
+        <v>181989</v>
       </c>
     </row>
     <row r="673">
@@ -13881,10 +13881,10 @@
         <v>77.38</v>
       </c>
       <c r="E673" t="n">
-        <v>78.98999999999999</v>
+        <v>78.93000000000001</v>
       </c>
       <c r="F673" t="n">
-        <v>149729</v>
+        <v>151482</v>
       </c>
     </row>
     <row r="674">
@@ -13961,10 +13961,10 @@
         <v>78.78</v>
       </c>
       <c r="E677" t="n">
-        <v>82.16</v>
+        <v>82.08</v>
       </c>
       <c r="F677" t="n">
-        <v>151677</v>
+        <v>153620</v>
       </c>
     </row>
     <row r="678">
@@ -13981,10 +13981,10 @@
         <v>81.63</v>
       </c>
       <c r="E678" t="n">
-        <v>82.17</v>
+        <v>82.22</v>
       </c>
       <c r="F678" t="n">
-        <v>147722</v>
+        <v>149526</v>
       </c>
     </row>
     <row r="679">
@@ -14061,10 +14061,10 @@
         <v>82.76000000000001</v>
       </c>
       <c r="E682" t="n">
-        <v>83.69</v>
+        <v>83.67</v>
       </c>
       <c r="F682" t="n">
-        <v>120650</v>
+        <v>122153</v>
       </c>
     </row>
     <row r="683">
@@ -14081,10 +14081,10 @@
         <v>83.68000000000001</v>
       </c>
       <c r="E683" t="n">
-        <v>84.23</v>
+        <v>84.33</v>
       </c>
       <c r="F683" t="n">
-        <v>114060</v>
+        <v>116437</v>
       </c>
     </row>
     <row r="684">
@@ -14161,10 +14161,10 @@
         <v>82.73</v>
       </c>
       <c r="E687" t="n">
-        <v>84.15000000000001</v>
+        <v>84.09</v>
       </c>
       <c r="F687" t="n">
-        <v>121250</v>
+        <v>122966</v>
       </c>
     </row>
     <row r="688">
@@ -14175,16 +14175,16 @@
         <v>83.81999999999999</v>
       </c>
       <c r="C688" t="n">
-        <v>84.97</v>
+        <v>85.08</v>
       </c>
       <c r="D688" t="n">
         <v>83.18000000000001</v>
       </c>
       <c r="E688" t="n">
-        <v>84.97</v>
+        <v>84.83</v>
       </c>
       <c r="F688" t="n">
-        <v>111475</v>
+        <v>113449</v>
       </c>
     </row>
     <row r="689">
@@ -14261,10 +14261,10 @@
         <v>81.48</v>
       </c>
       <c r="E692" t="n">
-        <v>83.83</v>
+        <v>83.78</v>
       </c>
       <c r="F692" t="n">
-        <v>164605</v>
+        <v>167007</v>
       </c>
     </row>
     <row r="693">
@@ -14281,10 +14281,10 @@
         <v>82.39</v>
       </c>
       <c r="E693" t="n">
-        <v>83.55</v>
+        <v>83.41</v>
       </c>
       <c r="F693" t="n">
-        <v>132228</v>
+        <v>133535</v>
       </c>
     </row>
     <row r="694">
@@ -14352,7 +14352,7 @@
         <v>44504</v>
       </c>
       <c r="B697" t="n">
-        <v>81.12</v>
+        <v>80.83</v>
       </c>
       <c r="C697" t="n">
         <v>84.08</v>
@@ -14364,7 +14364,7 @@
         <v>80.54000000000001</v>
       </c>
       <c r="F697" t="n">
-        <v>171378</v>
+        <v>168783</v>
       </c>
     </row>
     <row r="698">
@@ -14372,7 +14372,7 @@
         <v>44505</v>
       </c>
       <c r="B698" t="n">
-        <v>80.95</v>
+        <v>81.04000000000001</v>
       </c>
       <c r="C698" t="n">
         <v>82.72</v>
@@ -14384,7 +14384,7 @@
         <v>81.93000000000001</v>
       </c>
       <c r="F698" t="n">
-        <v>166390</v>
+        <v>163172</v>
       </c>
     </row>
     <row r="699">
@@ -14461,10 +14461,10 @@
         <v>81.06</v>
       </c>
       <c r="E702" t="n">
-        <v>81.91</v>
+        <v>81.92</v>
       </c>
       <c r="F702" t="n">
-        <v>159955</v>
+        <v>161511</v>
       </c>
     </row>
     <row r="703">
@@ -14481,10 +14481,10 @@
         <v>80.63</v>
       </c>
       <c r="E703" t="n">
-        <v>81.41</v>
+        <v>81.29000000000001</v>
       </c>
       <c r="F703" t="n">
-        <v>133196</v>
+        <v>134507</v>
       </c>
     </row>
     <row r="704">
@@ -14561,10 +14561,10 @@
         <v>78.55</v>
       </c>
       <c r="E707" t="n">
-        <v>80.42</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="F707" t="n">
-        <v>131123</v>
+        <v>132952</v>
       </c>
     </row>
     <row r="708">
@@ -14581,10 +14581,10 @@
         <v>77.41</v>
       </c>
       <c r="E708" t="n">
-        <v>77.76000000000001</v>
+        <v>77.77</v>
       </c>
       <c r="F708" t="n">
-        <v>175625</v>
+        <v>177513</v>
       </c>
     </row>
     <row r="709">
@@ -14761,10 +14761,10 @@
         <v>65.67</v>
       </c>
       <c r="E717" t="n">
-        <v>69.94</v>
+        <v>70.36</v>
       </c>
       <c r="F717" t="n">
-        <v>237353</v>
+        <v>240359</v>
       </c>
     </row>
     <row r="718">
@@ -14781,10 +14781,10 @@
         <v>69.09999999999999</v>
       </c>
       <c r="E718" t="n">
-        <v>69.73</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="F718" t="n">
-        <v>205214</v>
+        <v>208893</v>
       </c>
     </row>
     <row r="719">
@@ -14858,13 +14858,13 @@
         <v>76.55</v>
       </c>
       <c r="D722" t="n">
-        <v>73.78</v>
+        <v>73.70999999999999</v>
       </c>
       <c r="E722" t="n">
-        <v>73.79000000000001</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="F722" t="n">
-        <v>140659</v>
+        <v>142264</v>
       </c>
     </row>
     <row r="723">
@@ -14881,10 +14881,10 @@
         <v>73.67</v>
       </c>
       <c r="E723" t="n">
-        <v>75.23</v>
+        <v>75.16</v>
       </c>
       <c r="F723" t="n">
-        <v>151698</v>
+        <v>153301</v>
       </c>
     </row>
     <row r="724">
@@ -14961,10 +14961,10 @@
         <v>73.88</v>
       </c>
       <c r="E727" t="n">
-        <v>74.63</v>
+        <v>74.48999999999999</v>
       </c>
       <c r="F727" t="n">
-        <v>140474</v>
+        <v>142563</v>
       </c>
     </row>
     <row r="728">
@@ -14981,10 +14981,10 @@
         <v>72.63</v>
       </c>
       <c r="E728" t="n">
-        <v>73.15000000000001</v>
+        <v>72.88</v>
       </c>
       <c r="F728" t="n">
-        <v>152160</v>
+        <v>154875</v>
       </c>
     </row>
     <row r="729">
@@ -15061,10 +15061,10 @@
         <v>74.72</v>
       </c>
       <c r="E732" t="n">
-        <v>76.63</v>
+        <v>76.52</v>
       </c>
       <c r="F732" t="n">
-        <v>100583</v>
+        <v>102802</v>
       </c>
     </row>
     <row r="733">
@@ -15161,10 +15161,10 @@
         <v>78.33</v>
       </c>
       <c r="E737" t="n">
-        <v>78.97</v>
+        <v>78.86</v>
       </c>
       <c r="F737" t="n">
-        <v>103669</v>
+        <v>105405</v>
       </c>
     </row>
     <row r="738">
@@ -15261,10 +15261,10 @@
         <v>79.36</v>
       </c>
       <c r="E742" t="n">
-        <v>81.65000000000001</v>
+        <v>81.70999999999999</v>
       </c>
       <c r="F742" t="n">
-        <v>185800</v>
+        <v>187943</v>
       </c>
     </row>
     <row r="743">
@@ -15281,10 +15281,10 @@
         <v>81.12</v>
       </c>
       <c r="E743" t="n">
-        <v>81.59999999999999</v>
+        <v>81.48</v>
       </c>
       <c r="F743" t="n">
-        <v>158852</v>
+        <v>160491</v>
       </c>
     </row>
     <row r="744">
@@ -15361,10 +15361,10 @@
         <v>83.34999999999999</v>
       </c>
       <c r="E747" t="n">
-        <v>83.45</v>
+        <v>83.61</v>
       </c>
       <c r="F747" t="n">
-        <v>145171</v>
+        <v>147527</v>
       </c>
     </row>
     <row r="748">
@@ -15375,16 +15375,16 @@
         <v>83.68000000000001</v>
       </c>
       <c r="C748" t="n">
-        <v>85.97</v>
+        <v>85.98999999999999</v>
       </c>
       <c r="D748" t="n">
         <v>83.53</v>
       </c>
       <c r="E748" t="n">
-        <v>85.91</v>
+        <v>85.77</v>
       </c>
       <c r="F748" t="n">
-        <v>171152</v>
+        <v>173518</v>
       </c>
     </row>
     <row r="749">
@@ -15458,13 +15458,13 @@
         <v>88.8</v>
       </c>
       <c r="D752" t="n">
-        <v>86.56999999999999</v>
+        <v>86.38</v>
       </c>
       <c r="E752" t="n">
-        <v>86.7</v>
+        <v>86.58</v>
       </c>
       <c r="F752" t="n">
-        <v>162890</v>
+        <v>169439</v>
       </c>
     </row>
     <row r="753">
@@ -15481,10 +15481,10 @@
         <v>85.02</v>
       </c>
       <c r="E753" t="n">
-        <v>86.98</v>
+        <v>86.92</v>
       </c>
       <c r="F753" t="n">
-        <v>223066</v>
+        <v>225683</v>
       </c>
     </row>
     <row r="754">
@@ -15561,10 +15561,10 @@
         <v>87.7</v>
       </c>
       <c r="E757" t="n">
-        <v>88.40000000000001</v>
+        <v>88.63</v>
       </c>
       <c r="F757" t="n">
-        <v>270152</v>
+        <v>275711</v>
       </c>
     </row>
     <row r="758">
@@ -15581,10 +15581,10 @@
         <v>88</v>
       </c>
       <c r="E758" t="n">
-        <v>88.73</v>
+        <v>88.81999999999999</v>
       </c>
       <c r="F758" t="n">
-        <v>275262</v>
+        <v>278896</v>
       </c>
     </row>
     <row r="759">
@@ -15655,16 +15655,16 @@
         <v>88.63</v>
       </c>
       <c r="C762" t="n">
-        <v>90.73999999999999</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="D762" t="n">
         <v>87.59999999999999</v>
       </c>
       <c r="E762" t="n">
-        <v>90.45999999999999</v>
+        <v>90.51000000000001</v>
       </c>
       <c r="F762" t="n">
-        <v>163057</v>
+        <v>168353</v>
       </c>
     </row>
     <row r="763">
@@ -15681,10 +15681,10 @@
         <v>90.67</v>
       </c>
       <c r="E763" t="n">
-        <v>92.54000000000001</v>
+        <v>92.14</v>
       </c>
       <c r="F763" t="n">
-        <v>177219</v>
+        <v>180147</v>
       </c>
     </row>
     <row r="764">
@@ -15761,10 +15761,10 @@
         <v>90.09999999999999</v>
       </c>
       <c r="E767" t="n">
-        <v>90.66</v>
+        <v>90.54000000000001</v>
       </c>
       <c r="F767" t="n">
-        <v>183590</v>
+        <v>186180</v>
       </c>
     </row>
     <row r="768">
@@ -15781,10 +15781,10 @@
         <v>89.66</v>
       </c>
       <c r="E768" t="n">
-        <v>93.81</v>
+        <v>93.8</v>
       </c>
       <c r="F768" t="n">
-        <v>189880</v>
+        <v>194729</v>
       </c>
     </row>
     <row r="769">
@@ -15861,10 +15861,10 @@
         <v>90.34999999999999</v>
       </c>
       <c r="E772" t="n">
-        <v>91.18000000000001</v>
+        <v>91.16</v>
       </c>
       <c r="F772" t="n">
-        <v>209775</v>
+        <v>212213</v>
       </c>
     </row>
     <row r="773">
@@ -15875,7 +15875,7 @@
         <v>90.76000000000001</v>
       </c>
       <c r="C773" t="n">
-        <v>92.15000000000001</v>
+        <v>92.28</v>
       </c>
       <c r="D773" t="n">
         <v>88.64</v>
@@ -15884,7 +15884,7 @@
         <v>91.81</v>
       </c>
       <c r="F773" t="n">
-        <v>190175</v>
+        <v>194995</v>
       </c>
     </row>
     <row r="774">
@@ -15961,10 +15961,10 @@
         <v>93.94</v>
       </c>
       <c r="E777" t="n">
-        <v>95.61</v>
+        <v>95.41</v>
       </c>
       <c r="F777" t="n">
-        <v>309076</v>
+        <v>313423</v>
       </c>
     </row>
     <row r="778">
@@ -15981,10 +15981,10 @@
         <v>92.55</v>
       </c>
       <c r="E778" t="n">
-        <v>94.69</v>
+        <v>94.23</v>
       </c>
       <c r="F778" t="n">
-        <v>233541</v>
+        <v>237786</v>
       </c>
     </row>
     <row r="779">
@@ -16061,10 +16061,10 @@
         <v>108.17</v>
       </c>
       <c r="E782" t="n">
-        <v>109.72</v>
+        <v>109.27</v>
       </c>
       <c r="F782" t="n">
-        <v>231064</v>
+        <v>233799</v>
       </c>
     </row>
     <row r="783">
@@ -16081,10 +16081,10 @@
         <v>108.47</v>
       </c>
       <c r="E783" t="n">
-        <v>117.14</v>
+        <v>116.7</v>
       </c>
       <c r="F783" t="n">
-        <v>204618</v>
+        <v>210974</v>
       </c>
     </row>
     <row r="784">
@@ -16161,10 +16161,10 @@
         <v>107.05</v>
       </c>
       <c r="E787" t="n">
-        <v>107.97</v>
+        <v>107.11</v>
       </c>
       <c r="F787" t="n">
-        <v>170481</v>
+        <v>173653</v>
       </c>
     </row>
     <row r="788">
@@ -16181,10 +16181,10 @@
         <v>104.96</v>
       </c>
       <c r="E788" t="n">
-        <v>110.51</v>
+        <v>110.14</v>
       </c>
       <c r="F788" t="n">
-        <v>154891</v>
+        <v>157669</v>
       </c>
     </row>
     <row r="789">
@@ -16252,19 +16252,19 @@
         <v>44637</v>
       </c>
       <c r="B792" t="n">
-        <v>96.98</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="C792" t="n">
         <v>105.3</v>
       </c>
       <c r="D792" t="n">
-        <v>96.11</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="E792" t="n">
         <v>104.46</v>
       </c>
       <c r="F792" t="n">
-        <v>176604</v>
+        <v>172578</v>
       </c>
     </row>
     <row r="793">
@@ -16272,7 +16272,7 @@
         <v>44638</v>
       </c>
       <c r="B793" t="n">
-        <v>104.55</v>
+        <v>105.16</v>
       </c>
       <c r="C793" t="n">
         <v>107.23</v>
@@ -16284,7 +16284,7 @@
         <v>105.63</v>
       </c>
       <c r="F793" t="n">
-        <v>158531</v>
+        <v>155067</v>
       </c>
     </row>
     <row r="794">
@@ -16352,7 +16352,7 @@
         <v>44644</v>
       </c>
       <c r="B797" t="n">
-        <v>118.08</v>
+        <v>119.49</v>
       </c>
       <c r="C797" t="n">
         <v>120.04</v>
@@ -16364,7 +16364,7 @@
         <v>114.47</v>
       </c>
       <c r="F797" t="n">
-        <v>215337</v>
+        <v>206598</v>
       </c>
     </row>
     <row r="798">
@@ -16372,7 +16372,7 @@
         <v>44645</v>
       </c>
       <c r="B798" t="n">
-        <v>115.3</v>
+        <v>114.52</v>
       </c>
       <c r="C798" t="n">
         <v>117.69</v>
@@ -16384,7 +16384,7 @@
         <v>115.94</v>
       </c>
       <c r="F798" t="n">
-        <v>195807</v>
+        <v>189095</v>
       </c>
     </row>
     <row r="799">
@@ -16461,10 +16461,10 @@
         <v>103.71</v>
       </c>
       <c r="E802" t="n">
-        <v>104.6</v>
+        <v>104.99</v>
       </c>
       <c r="F802" t="n">
-        <v>217472</v>
+        <v>220967</v>
       </c>
     </row>
     <row r="803">
@@ -16481,10 +16481,10 @@
         <v>101.94</v>
       </c>
       <c r="E803" t="n">
-        <v>104.13</v>
+        <v>103.88</v>
       </c>
       <c r="F803" t="n">
-        <v>179677</v>
+        <v>181758</v>
       </c>
     </row>
     <row r="804">
@@ -16561,10 +16561,10 @@
         <v>98.2</v>
       </c>
       <c r="E807" t="n">
-        <v>100.94</v>
+        <v>100.96</v>
       </c>
       <c r="F807" t="n">
-        <v>183922</v>
+        <v>186163</v>
       </c>
     </row>
     <row r="808">
@@ -16581,10 +16581,10 @@
         <v>99.28</v>
       </c>
       <c r="E808" t="n">
-        <v>102.16</v>
+        <v>101.81</v>
       </c>
       <c r="F808" t="n">
-        <v>159821</v>
+        <v>162819</v>
       </c>
     </row>
     <row r="809">
@@ -16661,10 +16661,10 @@
         <v>106.14</v>
       </c>
       <c r="E812" t="n">
-        <v>110.56</v>
+        <v>110.62</v>
       </c>
       <c r="F812" t="n">
-        <v>156524</v>
+        <v>159785</v>
       </c>
     </row>
     <row r="813">
@@ -16741,10 +16741,10 @@
         <v>106.38</v>
       </c>
       <c r="E816" t="n">
-        <v>107.93</v>
+        <v>108</v>
       </c>
       <c r="F816" t="n">
-        <v>184241</v>
+        <v>188001</v>
       </c>
     </row>
     <row r="817">
@@ -16758,13 +16758,13 @@
         <v>108.41</v>
       </c>
       <c r="D817" t="n">
-        <v>105.44</v>
+        <v>105.05</v>
       </c>
       <c r="E817" t="n">
-        <v>105.6</v>
+        <v>105.7</v>
       </c>
       <c r="F817" t="n">
-        <v>162032</v>
+        <v>165632</v>
       </c>
     </row>
     <row r="818">
@@ -16841,10 +16841,10 @@
         <v>102.74</v>
       </c>
       <c r="E821" t="n">
-        <v>107.25</v>
+        <v>106.8</v>
       </c>
       <c r="F821" t="n">
-        <v>167676</v>
+        <v>170514</v>
       </c>
     </row>
     <row r="822">
@@ -16861,10 +16861,10 @@
         <v>105.92</v>
       </c>
       <c r="E822" t="n">
-        <v>106.38</v>
+        <v>106.06</v>
       </c>
       <c r="F822" t="n">
-        <v>182972</v>
+        <v>186051</v>
       </c>
     </row>
     <row r="823">
@@ -16941,10 +16941,10 @@
         <v>108.66</v>
       </c>
       <c r="E826" t="n">
-        <v>110.3</v>
+        <v>110.4</v>
       </c>
       <c r="F826" t="n">
-        <v>197687</v>
+        <v>201234</v>
       </c>
     </row>
     <row r="827">
@@ -16961,10 +16961,10 @@
         <v>109.21</v>
       </c>
       <c r="E827" t="n">
-        <v>112.44</v>
+        <v>112.22</v>
       </c>
       <c r="F827" t="n">
-        <v>203469</v>
+        <v>207851</v>
       </c>
     </row>
     <row r="828">
@@ -17041,10 +17041,10 @@
         <v>103.97</v>
       </c>
       <c r="E831" t="n">
-        <v>107.38</v>
+        <v>106.86</v>
       </c>
       <c r="F831" t="n">
-        <v>240901</v>
+        <v>243371</v>
       </c>
     </row>
     <row r="832">
@@ -17061,10 +17061,10 @@
         <v>106.88</v>
       </c>
       <c r="E832" t="n">
-        <v>110.4</v>
+        <v>109.76</v>
       </c>
       <c r="F832" t="n">
-        <v>190398</v>
+        <v>193013</v>
       </c>
     </row>
     <row r="833">
@@ -17141,10 +17141,10 @@
         <v>104.22</v>
       </c>
       <c r="E836" t="n">
-        <v>109.59</v>
+        <v>109.5</v>
       </c>
       <c r="F836" t="n">
-        <v>247278</v>
+        <v>250583</v>
       </c>
     </row>
     <row r="837">
@@ -17161,10 +17161,10 @@
         <v>108.65</v>
       </c>
       <c r="E837" t="n">
-        <v>110.87</v>
+        <v>110.3</v>
       </c>
       <c r="F837" t="n">
-        <v>198948</v>
+        <v>202895</v>
       </c>
     </row>
     <row r="838">
@@ -17241,10 +17241,10 @@
         <v>110.83</v>
       </c>
       <c r="E841" t="n">
-        <v>114</v>
+        <v>114.15</v>
       </c>
       <c r="F841" t="n">
-        <v>171535</v>
+        <v>175003</v>
       </c>
     </row>
     <row r="842">
@@ -17261,10 +17261,10 @@
         <v>113.01</v>
       </c>
       <c r="E842" t="n">
-        <v>115.42</v>
+        <v>115.01</v>
       </c>
       <c r="F842" t="n">
-        <v>210750</v>
+        <v>213418</v>
       </c>
     </row>
     <row r="843">
@@ -17335,16 +17335,16 @@
         <v>113.88</v>
       </c>
       <c r="C846" t="n">
-        <v>117.57</v>
+        <v>117.74</v>
       </c>
       <c r="D846" t="n">
         <v>111.85</v>
       </c>
       <c r="E846" t="n">
-        <v>117.26</v>
+        <v>117.31</v>
       </c>
       <c r="F846" t="n">
-        <v>137013</v>
+        <v>138282</v>
       </c>
     </row>
     <row r="847">
@@ -17355,16 +17355,16 @@
         <v>117.37</v>
       </c>
       <c r="C847" t="n">
-        <v>120.57</v>
+        <v>120.6</v>
       </c>
       <c r="D847" t="n">
         <v>115.28</v>
       </c>
       <c r="E847" t="n">
-        <v>120.41</v>
+        <v>120.23</v>
       </c>
       <c r="F847" t="n">
-        <v>90339</v>
+        <v>91626</v>
       </c>
     </row>
     <row r="848">
@@ -17441,10 +17441,10 @@
         <v>121.23</v>
       </c>
       <c r="E851" t="n">
-        <v>121.71</v>
+        <v>121.41</v>
       </c>
       <c r="F851" t="n">
-        <v>174232</v>
+        <v>176648</v>
       </c>
     </row>
     <row r="852">
@@ -17461,10 +17461,10 @@
         <v>118.31</v>
       </c>
       <c r="E852" t="n">
-        <v>120.29</v>
+        <v>120.02</v>
       </c>
       <c r="F852" t="n">
-        <v>190410</v>
+        <v>192334</v>
       </c>
     </row>
     <row r="853">
@@ -17541,10 +17541,10 @@
         <v>113.72</v>
       </c>
       <c r="E856" t="n">
-        <v>117.15</v>
+        <v>116.92</v>
       </c>
       <c r="F856" t="n">
-        <v>228931</v>
+        <v>231324</v>
       </c>
     </row>
     <row r="857">
@@ -17561,10 +17561,10 @@
         <v>109.77</v>
       </c>
       <c r="E857" t="n">
-        <v>111.29</v>
+        <v>111.27</v>
       </c>
       <c r="F857" t="n">
-        <v>233588</v>
+        <v>236868</v>
       </c>
     </row>
     <row r="858">
@@ -17641,10 +17641,10 @@
         <v>105.25</v>
       </c>
       <c r="E861" t="n">
-        <v>106.29</v>
+        <v>106.13</v>
       </c>
       <c r="F861" t="n">
-        <v>233040</v>
+        <v>234952</v>
       </c>
     </row>
     <row r="862">
@@ -17661,10 +17661,10 @@
         <v>105.78</v>
       </c>
       <c r="E862" t="n">
-        <v>109.13</v>
+        <v>108.33</v>
       </c>
       <c r="F862" t="n">
-        <v>202836</v>
+        <v>205227</v>
       </c>
     </row>
     <row r="863">
@@ -17741,10 +17741,10 @@
         <v>107.7</v>
       </c>
       <c r="E866" t="n">
-        <v>108.69</v>
+        <v>108.43</v>
       </c>
       <c r="F866" t="n">
-        <v>208599</v>
+        <v>212070</v>
       </c>
     </row>
     <row r="867">
@@ -17761,10 +17761,10 @@
         <v>107.32</v>
       </c>
       <c r="E867" t="n">
-        <v>110.56</v>
+        <v>110.43</v>
       </c>
       <c r="F867" t="n">
-        <v>209195</v>
+        <v>210630</v>
       </c>
     </row>
     <row r="868">
@@ -17841,10 +17841,10 @@
         <v>97.11</v>
       </c>
       <c r="E871" t="n">
-        <v>102.75</v>
+        <v>102.32</v>
       </c>
       <c r="F871" t="n">
-        <v>221862</v>
+        <v>224620</v>
       </c>
     </row>
     <row r="872">
@@ -17861,10 +17861,10 @@
         <v>102.16</v>
       </c>
       <c r="E872" t="n">
-        <v>105.32</v>
+        <v>105.2</v>
       </c>
       <c r="F872" t="n">
-        <v>235167</v>
+        <v>237030</v>
       </c>
     </row>
     <row r="873">
@@ -17941,10 +17941,10 @@
         <v>92.42</v>
       </c>
       <c r="E876" t="n">
-        <v>97.17</v>
+        <v>97.12</v>
       </c>
       <c r="F876" t="n">
-        <v>215919</v>
+        <v>217836</v>
       </c>
     </row>
     <row r="877">
@@ -17961,10 +17961,10 @@
         <v>95.59</v>
       </c>
       <c r="E877" t="n">
-        <v>98.34999999999999</v>
+        <v>97.98</v>
       </c>
       <c r="F877" t="n">
-        <v>200270</v>
+        <v>203134</v>
       </c>
     </row>
     <row r="878">
@@ -18041,10 +18041,10 @@
         <v>97.86</v>
       </c>
       <c r="E881" t="n">
-        <v>100.04</v>
+        <v>99.93000000000001</v>
       </c>
       <c r="F881" t="n">
-        <v>227231</v>
+        <v>229298</v>
       </c>
     </row>
     <row r="882">
@@ -18061,10 +18061,10 @@
         <v>97.90000000000001</v>
       </c>
       <c r="E882" t="n">
-        <v>98.67</v>
+        <v>98.98999999999999</v>
       </c>
       <c r="F882" t="n">
-        <v>222921</v>
+        <v>226135</v>
       </c>
     </row>
     <row r="883">
@@ -18141,10 +18141,10 @@
         <v>100.74</v>
       </c>
       <c r="E886" t="n">
-        <v>101.93</v>
+        <v>101.99</v>
       </c>
       <c r="F886" t="n">
-        <v>130398</v>
+        <v>132446</v>
       </c>
     </row>
     <row r="887">
@@ -18161,10 +18161,10 @@
         <v>101.27</v>
       </c>
       <c r="E887" t="n">
-        <v>103.21</v>
+        <v>103.1</v>
       </c>
       <c r="F887" t="n">
-        <v>112179</v>
+        <v>113461</v>
       </c>
     </row>
     <row r="888">
@@ -18238,13 +18238,13 @@
         <v>97.17</v>
       </c>
       <c r="D891" t="n">
-        <v>92.73</v>
+        <v>92.5</v>
       </c>
       <c r="E891" t="n">
-        <v>93.38</v>
+        <v>92.52</v>
       </c>
       <c r="F891" t="n">
-        <v>160629</v>
+        <v>162676</v>
       </c>
     </row>
     <row r="892">
@@ -18261,10 +18261,10 @@
         <v>92.15000000000001</v>
       </c>
       <c r="E892" t="n">
-        <v>93.69</v>
+        <v>93.51000000000001</v>
       </c>
       <c r="F892" t="n">
-        <v>155701</v>
+        <v>157322</v>
       </c>
     </row>
     <row r="893">
@@ -18341,10 +18341,10 @@
         <v>96.08</v>
       </c>
       <c r="E896" t="n">
-        <v>98.66</v>
+        <v>98.31</v>
       </c>
       <c r="F896" t="n">
-        <v>139272</v>
+        <v>140818</v>
       </c>
     </row>
     <row r="897">
@@ -18361,10 +18361,10 @@
         <v>96.26000000000001</v>
       </c>
       <c r="E897" t="n">
-        <v>97.3</v>
+        <v>96.89</v>
       </c>
       <c r="F897" t="n">
-        <v>144235</v>
+        <v>145858</v>
       </c>
     </row>
     <row r="898">
@@ -18441,10 +18441,10 @@
         <v>92.55</v>
       </c>
       <c r="E901" t="n">
-        <v>95.93000000000001</v>
+        <v>95.56</v>
       </c>
       <c r="F901" t="n">
-        <v>122235</v>
+        <v>123861</v>
       </c>
     </row>
     <row r="902">
@@ -18461,10 +18461,10 @@
         <v>93.7</v>
       </c>
       <c r="E902" t="n">
-        <v>95.52</v>
+        <v>95.08</v>
       </c>
       <c r="F902" t="n">
-        <v>125387</v>
+        <v>126696</v>
       </c>
     </row>
     <row r="903">
@@ -18541,10 +18541,10 @@
         <v>98.23</v>
       </c>
       <c r="E906" t="n">
-        <v>99.05</v>
+        <v>98.68000000000001</v>
       </c>
       <c r="F906" t="n">
-        <v>114289</v>
+        <v>115830</v>
       </c>
     </row>
     <row r="907">
@@ -18561,10 +18561,10 @@
         <v>96.92</v>
       </c>
       <c r="E907" t="n">
-        <v>98.70999999999999</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="F907" t="n">
-        <v>127109</v>
+        <v>128357</v>
       </c>
     </row>
     <row r="908">
@@ -18641,10 +18641,10 @@
         <v>91.58</v>
       </c>
       <c r="E911" t="n">
-        <v>91.75</v>
+        <v>91.59</v>
       </c>
       <c r="F911" t="n">
-        <v>171383</v>
+        <v>172611</v>
       </c>
     </row>
     <row r="912">
@@ -18661,10 +18661,10 @@
         <v>92.41</v>
       </c>
       <c r="E912" t="n">
-        <v>92.68000000000001</v>
+        <v>92.83</v>
       </c>
       <c r="F912" t="n">
-        <v>162523</v>
+        <v>164349</v>
       </c>
     </row>
     <row r="913">
@@ -18741,10 +18741,10 @@
         <v>86.86</v>
       </c>
       <c r="E916" t="n">
-        <v>88.03</v>
+        <v>87.73999999999999</v>
       </c>
       <c r="F916" t="n">
-        <v>174104</v>
+        <v>175783</v>
       </c>
     </row>
     <row r="917">
@@ -18761,10 +18761,10 @@
         <v>88.09</v>
       </c>
       <c r="E917" t="n">
-        <v>91.90000000000001</v>
+        <v>91.42</v>
       </c>
       <c r="F917" t="n">
-        <v>137562</v>
+        <v>139210</v>
       </c>
     </row>
     <row r="918">
@@ -18841,10 +18841,10 @@
         <v>89.39</v>
       </c>
       <c r="E921" t="n">
-        <v>90.08</v>
+        <v>89.78</v>
       </c>
       <c r="F921" t="n">
-        <v>177670</v>
+        <v>179533</v>
       </c>
     </row>
     <row r="922">
@@ -18861,10 +18861,10 @@
         <v>89.37</v>
       </c>
       <c r="E922" t="n">
-        <v>90.58</v>
+        <v>90.36</v>
       </c>
       <c r="F922" t="n">
-        <v>175462</v>
+        <v>177056</v>
       </c>
     </row>
     <row r="923">
@@ -18941,10 +18941,10 @@
         <v>88.38</v>
       </c>
       <c r="E926" t="n">
-        <v>89.53</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="F926" t="n">
-        <v>167346</v>
+        <v>169282</v>
       </c>
     </row>
     <row r="927">
@@ -18961,10 +18961,10 @@
         <v>84.61</v>
       </c>
       <c r="E927" t="n">
-        <v>85.41</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="F927" t="n">
-        <v>157358</v>
+        <v>159709</v>
       </c>
     </row>
     <row r="928">
@@ -19041,10 +19041,10 @@
         <v>85.98</v>
       </c>
       <c r="E931" t="n">
-        <v>87.20999999999999</v>
+        <v>87.22</v>
       </c>
       <c r="F931" t="n">
-        <v>182346</v>
+        <v>184095</v>
       </c>
     </row>
     <row r="932">
@@ -19061,10 +19061,10 @@
         <v>84.73999999999999</v>
       </c>
       <c r="E932" t="n">
-        <v>85.06999999999999</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="F932" t="n">
-        <v>172540</v>
+        <v>174184</v>
       </c>
     </row>
     <row r="933">
@@ -19141,10 +19141,10 @@
         <v>92.09</v>
       </c>
       <c r="E936" t="n">
-        <v>94.31999999999999</v>
+        <v>94.16</v>
       </c>
       <c r="F936" t="n">
-        <v>134269</v>
+        <v>136157</v>
       </c>
     </row>
     <row r="937">
@@ -19161,10 +19161,10 @@
         <v>93.25</v>
       </c>
       <c r="E937" t="n">
-        <v>96.95</v>
+        <v>97.59</v>
       </c>
       <c r="F937" t="n">
-        <v>158303</v>
+        <v>161145</v>
       </c>
     </row>
     <row r="938">
@@ -19241,10 +19241,10 @@
         <v>90.18000000000001</v>
       </c>
       <c r="E941" t="n">
-        <v>93.61</v>
+        <v>93.67</v>
       </c>
       <c r="F941" t="n">
-        <v>187899</v>
+        <v>189909</v>
       </c>
     </row>
     <row r="942">
@@ -19261,10 +19261,10 @@
         <v>90.34</v>
       </c>
       <c r="E942" t="n">
-        <v>90.84999999999999</v>
+        <v>90.66</v>
       </c>
       <c r="F942" t="n">
-        <v>184164</v>
+        <v>186342</v>
       </c>
     </row>
     <row r="943">
@@ -19341,10 +19341,10 @@
         <v>90.34</v>
       </c>
       <c r="E946" t="n">
-        <v>91</v>
+        <v>91.11</v>
       </c>
       <c r="F946" t="n">
-        <v>169394</v>
+        <v>172151</v>
       </c>
     </row>
     <row r="947">
@@ -19361,10 +19361,10 @@
         <v>89.40000000000001</v>
       </c>
       <c r="E947" t="n">
-        <v>91.7</v>
+        <v>91.58</v>
       </c>
       <c r="F947" t="n">
-        <v>168937</v>
+        <v>170499</v>
       </c>
     </row>
     <row r="948">
@@ -19441,10 +19441,10 @@
         <v>93.06999999999999</v>
       </c>
       <c r="E951" t="n">
-        <v>94.91</v>
+        <v>94.45999999999999</v>
       </c>
       <c r="F951" t="n">
-        <v>130846</v>
+        <v>135151</v>
       </c>
     </row>
     <row r="952">
@@ -19461,10 +19461,10 @@
         <v>92.81999999999999</v>
       </c>
       <c r="E952" t="n">
-        <v>93.81</v>
+        <v>93.95</v>
       </c>
       <c r="F952" t="n">
-        <v>133960</v>
+        <v>135363</v>
       </c>
     </row>
     <row r="953">
@@ -19532,7 +19532,7 @@
         <v>44868</v>
       </c>
       <c r="B956" t="n">
-        <v>94.81</v>
+        <v>94.84</v>
       </c>
       <c r="C956" t="n">
         <v>95.45</v>
@@ -19544,7 +19544,7 @@
         <v>93.92</v>
       </c>
       <c r="F956" t="n">
-        <v>143503</v>
+        <v>141621</v>
       </c>
     </row>
     <row r="957">
@@ -19552,19 +19552,19 @@
         <v>44869</v>
       </c>
       <c r="B957" t="n">
-        <v>93.98</v>
+        <v>93.94</v>
       </c>
       <c r="C957" t="n">
         <v>98.23999999999999</v>
       </c>
       <c r="D957" t="n">
-        <v>93.76000000000001</v>
+        <v>93.94</v>
       </c>
       <c r="E957" t="n">
         <v>98.01000000000001</v>
       </c>
       <c r="F957" t="n">
-        <v>182009</v>
+        <v>179958</v>
       </c>
     </row>
     <row r="958">
@@ -19641,10 +19641,10 @@
         <v>90.97</v>
       </c>
       <c r="E961" t="n">
-        <v>92.69</v>
+        <v>92.47</v>
       </c>
       <c r="F961" t="n">
-        <v>168690</v>
+        <v>170823</v>
       </c>
     </row>
     <row r="962">
@@ -19661,10 +19661,10 @@
         <v>92.79000000000001</v>
       </c>
       <c r="E962" t="n">
-        <v>95.04000000000001</v>
+        <v>94.95999999999999</v>
       </c>
       <c r="F962" t="n">
-        <v>163940</v>
+        <v>165782</v>
       </c>
     </row>
     <row r="963">
@@ -19741,10 +19741,10 @@
         <v>88.72</v>
       </c>
       <c r="E966" t="n">
-        <v>89.28</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="F966" t="n">
-        <v>157265</v>
+        <v>159560</v>
       </c>
     </row>
     <row r="967">
@@ -19761,10 +19761,10 @@
         <v>85.41</v>
       </c>
       <c r="E967" t="n">
-        <v>87.45</v>
+        <v>87.5</v>
       </c>
       <c r="F967" t="n">
-        <v>160818</v>
+        <v>162655</v>
       </c>
     </row>
     <row r="968">
@@ -19941,10 +19941,10 @@
         <v>86.26000000000001</v>
       </c>
       <c r="E976" t="n">
-        <v>86.84</v>
+        <v>86.98</v>
       </c>
       <c r="F976" t="n">
-        <v>135345</v>
+        <v>136930</v>
       </c>
     </row>
     <row r="977">
@@ -19961,10 +19961,10 @@
         <v>85.17</v>
       </c>
       <c r="E977" t="n">
-        <v>85.76000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="F977" t="n">
-        <v>135815</v>
+        <v>137359</v>
       </c>
     </row>
     <row r="978">
@@ -20041,10 +20041,10 @@
         <v>75.92</v>
       </c>
       <c r="E981" t="n">
-        <v>76.27</v>
+        <v>76.61</v>
       </c>
       <c r="F981" t="n">
-        <v>165742</v>
+        <v>167594</v>
       </c>
     </row>
     <row r="982">
@@ -20061,10 +20061,10 @@
         <v>75.34999999999999</v>
       </c>
       <c r="E982" t="n">
-        <v>76.76000000000001</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="F982" t="n">
-        <v>151706</v>
+        <v>153224</v>
       </c>
     </row>
     <row r="983">
@@ -20141,10 +20141,10 @@
         <v>80.86</v>
       </c>
       <c r="E986" t="n">
-        <v>81.39</v>
+        <v>81.54000000000001</v>
       </c>
       <c r="F986" t="n">
-        <v>149384</v>
+        <v>151489</v>
       </c>
     </row>
     <row r="987">
@@ -20161,10 +20161,10 @@
         <v>78.61</v>
       </c>
       <c r="E987" t="n">
-        <v>79.36</v>
+        <v>79.44</v>
       </c>
       <c r="F987" t="n">
-        <v>149990</v>
+        <v>151197</v>
       </c>
     </row>
     <row r="988">
@@ -20241,10 +20241,10 @@
         <v>81.28</v>
       </c>
       <c r="E991" t="n">
-        <v>82.18000000000001</v>
+        <v>82.20999999999999</v>
       </c>
       <c r="F991" t="n">
-        <v>94348</v>
+        <v>95617</v>
       </c>
     </row>
     <row r="992">
@@ -20321,10 +20321,10 @@
         <v>81.81999999999999</v>
       </c>
       <c r="E995" t="n">
-        <v>83.68000000000001</v>
+        <v>83.63</v>
       </c>
       <c r="F995" t="n">
-        <v>109380</v>
+        <v>110699</v>
       </c>
     </row>
     <row r="996">
@@ -20401,10 +20401,10 @@
         <v>77.63</v>
       </c>
       <c r="E999" t="n">
-        <v>78.68000000000001</v>
+        <v>78.8</v>
       </c>
       <c r="F999" t="n">
-        <v>149266</v>
+        <v>150672</v>
       </c>
     </row>
     <row r="1000">
@@ -20424,7 +20424,7 @@
         <v>78.51000000000001</v>
       </c>
       <c r="F1000" t="n">
-        <v>147017</v>
+        <v>148389</v>
       </c>
     </row>
     <row r="1001">
@@ -20501,10 +20501,10 @@
         <v>82.43000000000001</v>
       </c>
       <c r="E1004" t="n">
-        <v>83.91</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="F1004" t="n">
-        <v>141086</v>
+        <v>142735</v>
       </c>
     </row>
     <row r="1005">
@@ -20515,16 +20515,16 @@
         <v>83.91</v>
       </c>
       <c r="C1005" t="n">
-        <v>85.55</v>
+        <v>85.61</v>
       </c>
       <c r="D1005" t="n">
         <v>83.55</v>
       </c>
       <c r="E1005" t="n">
-        <v>85.48</v>
+        <v>85.47</v>
       </c>
       <c r="F1005" t="n">
-        <v>129757</v>
+        <v>131152</v>
       </c>
     </row>
     <row r="1006">
@@ -20601,10 +20601,10 @@
         <v>83.95999999999999</v>
       </c>
       <c r="E1009" t="n">
-        <v>86.31999999999999</v>
+        <v>86.34</v>
       </c>
       <c r="F1009" t="n">
-        <v>142583</v>
+        <v>144410</v>
       </c>
     </row>
     <row r="1010">
@@ -20621,10 +20621,10 @@
         <v>85.69</v>
       </c>
       <c r="E1010" t="n">
-        <v>87.75</v>
+        <v>87.59</v>
       </c>
       <c r="F1010" t="n">
-        <v>123973</v>
+        <v>125225</v>
       </c>
     </row>
     <row r="1011">
@@ -20701,10 +20701,10 @@
         <v>85.75</v>
       </c>
       <c r="E1014" t="n">
-        <v>87.31</v>
+        <v>87.29000000000001</v>
       </c>
       <c r="F1014" t="n">
-        <v>95077</v>
+        <v>96051</v>
       </c>
     </row>
     <row r="1015">
@@ -20721,10 +20721,10 @@
         <v>85.48</v>
       </c>
       <c r="E1015" t="n">
-        <v>86.04000000000001</v>
+        <v>86.01000000000001</v>
       </c>
       <c r="F1015" t="n">
-        <v>109841</v>
+        <v>110922</v>
       </c>
     </row>
     <row r="1016">
@@ -20801,10 +20801,10 @@
         <v>81.2</v>
       </c>
       <c r="E1019" t="n">
-        <v>81.98</v>
+        <v>82.12</v>
       </c>
       <c r="F1019" t="n">
-        <v>146732</v>
+        <v>150704</v>
       </c>
     </row>
     <row r="1020">
@@ -20818,13 +20818,13 @@
         <v>84.11</v>
       </c>
       <c r="D1020" t="n">
+        <v>79.53</v>
+      </c>
+      <c r="E1020" t="n">
         <v>79.62</v>
       </c>
-      <c r="E1020" t="n">
-        <v>79.64</v>
-      </c>
       <c r="F1020" t="n">
-        <v>161681</v>
+        <v>163093</v>
       </c>
     </row>
     <row r="1021">
@@ -20901,10 +20901,10 @@
         <v>82.86</v>
       </c>
       <c r="E1024" t="n">
-        <v>83.88</v>
+        <v>83.95</v>
       </c>
       <c r="F1024" t="n">
-        <v>142722</v>
+        <v>144061</v>
       </c>
     </row>
     <row r="1025">
@@ -20921,10 +20921,10 @@
         <v>83.66</v>
       </c>
       <c r="E1025" t="n">
-        <v>86.29000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="F1025" t="n">
-        <v>155562</v>
+        <v>156718</v>
       </c>
     </row>
     <row r="1026">
@@ -20998,13 +20998,13 @@
         <v>85.90000000000001</v>
       </c>
       <c r="D1029" t="n">
-        <v>84.31999999999999</v>
+        <v>84.28</v>
       </c>
       <c r="E1029" t="n">
-        <v>84.37</v>
+        <v>84.31</v>
       </c>
       <c r="F1029" t="n">
-        <v>128382</v>
+        <v>129946</v>
       </c>
     </row>
     <row r="1030">
@@ -21021,10 +21021,10 @@
         <v>81.55</v>
       </c>
       <c r="E1030" t="n">
-        <v>82.68000000000001</v>
+        <v>82.72</v>
       </c>
       <c r="F1030" t="n">
-        <v>141607</v>
+        <v>142763</v>
       </c>
     </row>
     <row r="1031">
@@ -21101,10 +21101,10 @@
         <v>80.27</v>
       </c>
       <c r="E1034" t="n">
-        <v>82.12</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="F1034" t="n">
-        <v>107083</v>
+        <v>108091</v>
       </c>
     </row>
     <row r="1035">
@@ -21121,10 +21121,10 @@
         <v>80.7</v>
       </c>
       <c r="E1035" t="n">
-        <v>82.94</v>
+        <v>82.77</v>
       </c>
       <c r="F1035" t="n">
-        <v>129354</v>
+        <v>130526</v>
       </c>
     </row>
     <row r="1036">
@@ -21201,10 +21201,10 @@
         <v>83.66</v>
       </c>
       <c r="E1039" t="n">
-        <v>84.34</v>
+        <v>84.23</v>
       </c>
       <c r="F1039" t="n">
-        <v>114302</v>
+        <v>115434</v>
       </c>
     </row>
     <row r="1040">
@@ -21215,16 +21215,16 @@
         <v>84.37</v>
       </c>
       <c r="C1040" t="n">
-        <v>85.8</v>
+        <v>85.81</v>
       </c>
       <c r="D1040" t="n">
         <v>82.2</v>
       </c>
       <c r="E1040" t="n">
-        <v>85.72</v>
+        <v>85.73999999999999</v>
       </c>
       <c r="F1040" t="n">
-        <v>119970</v>
+        <v>120888</v>
       </c>
     </row>
     <row r="1041">
@@ -21301,10 +21301,10 @@
         <v>81.16</v>
       </c>
       <c r="E1044" t="n">
-        <v>81.26000000000001</v>
+        <v>81.23</v>
       </c>
       <c r="F1044" t="n">
-        <v>120126</v>
+        <v>121276</v>
       </c>
     </row>
     <row r="1045">
@@ -21321,10 +21321,10 @@
         <v>80.47</v>
       </c>
       <c r="E1045" t="n">
-        <v>82.33</v>
+        <v>82.38</v>
       </c>
       <c r="F1045" t="n">
-        <v>171433</v>
+        <v>172647</v>
       </c>
     </row>
     <row r="1046">
@@ -21392,7 +21392,7 @@
         <v>45001</v>
       </c>
       <c r="B1049" t="n">
-        <v>74.04000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="C1049" t="n">
         <v>75.23</v>
@@ -21404,7 +21404,7 @@
         <v>74.25</v>
       </c>
       <c r="F1049" t="n">
-        <v>210322</v>
+        <v>206406</v>
       </c>
     </row>
     <row r="1050">
@@ -21412,7 +21412,7 @@
         <v>45002</v>
       </c>
       <c r="B1050" t="n">
-        <v>74.45</v>
+        <v>74.41</v>
       </c>
       <c r="C1050" t="n">
         <v>75.65000000000001</v>
@@ -21424,7 +21424,7 @@
         <v>72.3</v>
       </c>
       <c r="F1050" t="n">
-        <v>196053</v>
+        <v>194486</v>
       </c>
     </row>
     <row r="1051">
@@ -21492,7 +21492,7 @@
         <v>45008</v>
       </c>
       <c r="B1054" t="n">
-        <v>75.58</v>
+        <v>75.73</v>
       </c>
       <c r="C1054" t="n">
         <v>77.09</v>
@@ -21504,7 +21504,7 @@
         <v>74.98999999999999</v>
       </c>
       <c r="F1054" t="n">
-        <v>134971</v>
+        <v>132462</v>
       </c>
     </row>
     <row r="1055">
@@ -21512,7 +21512,7 @@
         <v>45009</v>
       </c>
       <c r="B1055" t="n">
-        <v>75.08</v>
+        <v>74.92</v>
       </c>
       <c r="C1055" t="n">
         <v>75.89</v>
@@ -21524,7 +21524,7 @@
         <v>74.52</v>
       </c>
       <c r="F1055" t="n">
-        <v>160608</v>
+        <v>158419</v>
       </c>
     </row>
     <row r="1056">
@@ -21601,10 +21601,10 @@
         <v>77.13</v>
       </c>
       <c r="E1059" t="n">
-        <v>78.47</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="F1059" t="n">
-        <v>101875</v>
+        <v>102975</v>
       </c>
     </row>
     <row r="1060">
@@ -21621,10 +21621,10 @@
         <v>77.79000000000001</v>
       </c>
       <c r="E1060" t="n">
-        <v>79.73</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="F1060" t="n">
-        <v>102278</v>
+        <v>103341</v>
       </c>
     </row>
     <row r="1061">
@@ -21701,10 +21701,10 @@
         <v>83.89</v>
       </c>
       <c r="E1064" t="n">
-        <v>84.73</v>
+        <v>84.62</v>
       </c>
       <c r="F1064" t="n">
-        <v>127887</v>
+        <v>128978</v>
       </c>
     </row>
     <row r="1065">
@@ -21781,10 +21781,10 @@
         <v>85.78</v>
       </c>
       <c r="E1068" t="n">
-        <v>85.98</v>
+        <v>86.03</v>
       </c>
       <c r="F1068" t="n">
-        <v>106530</v>
+        <v>107747</v>
       </c>
     </row>
     <row r="1069">
@@ -21801,10 +21801,10 @@
         <v>85.27</v>
       </c>
       <c r="E1069" t="n">
-        <v>86.13</v>
+        <v>86.12</v>
       </c>
       <c r="F1069" t="n">
-        <v>118921</v>
+        <v>119789</v>
       </c>
     </row>
     <row r="1070">
@@ -21878,13 +21878,13 @@
         <v>82.59999999999999</v>
       </c>
       <c r="D1073" t="n">
-        <v>80.51000000000001</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="E1073" t="n">
-        <v>80.62</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="F1073" t="n">
-        <v>99083</v>
+        <v>100157</v>
       </c>
     </row>
     <row r="1074">
@@ -21901,10 +21901,10 @@
         <v>80.2</v>
       </c>
       <c r="E1074" t="n">
-        <v>81.38</v>
+        <v>81.53</v>
       </c>
       <c r="F1074" t="n">
-        <v>88877</v>
+        <v>89589</v>
       </c>
     </row>
     <row r="1075">
@@ -21981,10 +21981,10 @@
         <v>77.3</v>
       </c>
       <c r="E1078" t="n">
-        <v>78.23</v>
+        <v>78.17</v>
       </c>
       <c r="F1078" t="n">
-        <v>112919</v>
+        <v>114226</v>
       </c>
     </row>
     <row r="1079">
@@ -22001,10 +22001,10 @@
         <v>77.44</v>
       </c>
       <c r="E1079" t="n">
-        <v>80.20999999999999</v>
+        <v>80.08</v>
       </c>
       <c r="F1079" t="n">
-        <v>110643</v>
+        <v>111593</v>
       </c>
     </row>
     <row r="1080">
@@ -22081,10 +22081,10 @@
         <v>71.34</v>
       </c>
       <c r="E1083" t="n">
-        <v>72.34</v>
+        <v>72.38</v>
       </c>
       <c r="F1083" t="n">
-        <v>175075</v>
+        <v>176458</v>
       </c>
     </row>
     <row r="1084">
@@ -22101,10 +22101,10 @@
         <v>72.31999999999999</v>
       </c>
       <c r="E1084" t="n">
-        <v>75.22</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="F1084" t="n">
-        <v>121559</v>
+        <v>122688</v>
       </c>
     </row>
     <row r="1085">
@@ -22181,10 +22181,10 @@
         <v>74.5</v>
       </c>
       <c r="E1088" t="n">
-        <v>75.34999999999999</v>
+        <v>75.26000000000001</v>
       </c>
       <c r="F1088" t="n">
-        <v>141443</v>
+        <v>142391</v>
       </c>
     </row>
     <row r="1089">
@@ -22201,10 +22201,10 @@
         <v>73.84999999999999</v>
       </c>
       <c r="E1089" t="n">
-        <v>74.02</v>
+        <v>73.93000000000001</v>
       </c>
       <c r="F1089" t="n">
-        <v>143925</v>
+        <v>144762</v>
       </c>
     </row>
     <row r="1090">
@@ -22281,10 +22281,10 @@
         <v>75.42</v>
       </c>
       <c r="E1093" t="n">
-        <v>75.89</v>
+        <v>75.84</v>
       </c>
       <c r="F1093" t="n">
-        <v>97144</v>
+        <v>98116</v>
       </c>
     </row>
     <row r="1094">
@@ -22301,10 +22301,10 @@
         <v>75.01000000000001</v>
       </c>
       <c r="E1094" t="n">
-        <v>75.75</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="F1094" t="n">
-        <v>107224</v>
+        <v>108218</v>
       </c>
     </row>
     <row r="1095">
@@ -22381,10 +22381,10 @@
         <v>75.08</v>
       </c>
       <c r="E1098" t="n">
-        <v>76.13</v>
+        <v>75.95999999999999</v>
       </c>
       <c r="F1098" t="n">
-        <v>94656</v>
+        <v>95663</v>
       </c>
     </row>
     <row r="1099">
@@ -22401,10 +22401,10 @@
         <v>75.62</v>
       </c>
       <c r="E1099" t="n">
-        <v>77.03</v>
+        <v>77.14</v>
       </c>
       <c r="F1099" t="n">
-        <v>85632</v>
+        <v>86227</v>
       </c>
     </row>
     <row r="1100">
@@ -22481,10 +22481,10 @@
         <v>72</v>
       </c>
       <c r="E1103" t="n">
-        <v>74.17</v>
+        <v>74.25</v>
       </c>
       <c r="F1103" t="n">
-        <v>122959</v>
+        <v>124084</v>
       </c>
     </row>
     <row r="1104">
@@ -22501,10 +22501,10 @@
         <v>74.13</v>
       </c>
       <c r="E1104" t="n">
-        <v>76.3</v>
+        <v>76.13</v>
       </c>
       <c r="F1104" t="n">
-        <v>110715</v>
+        <v>111881</v>
       </c>
     </row>
     <row r="1105">
@@ -22581,10 +22581,10 @@
         <v>73.52</v>
       </c>
       <c r="E1108" t="n">
-        <v>75.56999999999999</v>
+        <v>75.44</v>
       </c>
       <c r="F1108" t="n">
-        <v>141391</v>
+        <v>142206</v>
       </c>
     </row>
     <row r="1109">
@@ -22601,10 +22601,10 @@
         <v>74.67</v>
       </c>
       <c r="E1109" t="n">
-        <v>74.84999999999999</v>
+        <v>74.88</v>
       </c>
       <c r="F1109" t="n">
-        <v>120105</v>
+        <v>120995</v>
       </c>
     </row>
     <row r="1110">
@@ -22681,10 +22681,10 @@
         <v>72.84999999999999</v>
       </c>
       <c r="E1113" t="n">
-        <v>75.56</v>
+        <v>75.52</v>
       </c>
       <c r="F1113" t="n">
-        <v>104970</v>
+        <v>105947</v>
       </c>
     </row>
     <row r="1114">
@@ -22701,10 +22701,10 @@
         <v>75.09999999999999</v>
       </c>
       <c r="E1114" t="n">
-        <v>76.47</v>
+        <v>76.23</v>
       </c>
       <c r="F1114" t="n">
-        <v>109963</v>
+        <v>111184</v>
       </c>
     </row>
     <row r="1115">
@@ -22781,10 +22781,10 @@
         <v>73.75</v>
       </c>
       <c r="E1118" t="n">
-        <v>74.2</v>
+        <v>74.3</v>
       </c>
       <c r="F1118" t="n">
-        <v>89166</v>
+        <v>89974</v>
       </c>
     </row>
     <row r="1119">
@@ -22795,16 +22795,16 @@
         <v>74.2</v>
       </c>
       <c r="C1119" t="n">
-        <v>74.36</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="D1119" t="n">
         <v>72.25</v>
       </c>
       <c r="E1119" t="n">
-        <v>74.09</v>
+        <v>74.34</v>
       </c>
       <c r="F1119" t="n">
-        <v>100773</v>
+        <v>101628</v>
       </c>
     </row>
     <row r="1120">
@@ -22881,10 +22881,10 @@
         <v>73.56</v>
       </c>
       <c r="E1123" t="n">
-        <v>74.44</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="F1123" t="n">
-        <v>118096</v>
+        <v>118860</v>
       </c>
     </row>
     <row r="1124">
@@ -22901,10 +22901,10 @@
         <v>74.23</v>
       </c>
       <c r="E1124" t="n">
-        <v>75.26000000000001</v>
+        <v>75.06999999999999</v>
       </c>
       <c r="F1124" t="n">
-        <v>107062</v>
+        <v>108012</v>
       </c>
     </row>
     <row r="1125">
@@ -22981,10 +22981,10 @@
         <v>74.94</v>
       </c>
       <c r="E1128" t="n">
-        <v>76.47</v>
+        <v>76.44</v>
       </c>
       <c r="F1128" t="n">
-        <v>120498</v>
+        <v>121613</v>
       </c>
     </row>
     <row r="1129">
@@ -23001,10 +23001,10 @@
         <v>75.91</v>
       </c>
       <c r="E1129" t="n">
-        <v>78.13</v>
+        <v>78.12</v>
       </c>
       <c r="F1129" t="n">
-        <v>99946</v>
+        <v>101260</v>
       </c>
     </row>
     <row r="1130">
@@ -23075,16 +23075,16 @@
         <v>79.95999999999999</v>
       </c>
       <c r="C1133" t="n">
-        <v>81.48999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="D1133" t="n">
         <v>79.69</v>
       </c>
       <c r="E1133" t="n">
-        <v>81.48</v>
+        <v>81.37</v>
       </c>
       <c r="F1133" t="n">
-        <v>96443</v>
+        <v>97805</v>
       </c>
     </row>
     <row r="1134">
@@ -23098,13 +23098,13 @@
         <v>81.42</v>
       </c>
       <c r="D1134" t="n">
-        <v>79.44</v>
+        <v>79.34999999999999</v>
       </c>
       <c r="E1134" t="n">
-        <v>79.54000000000001</v>
+        <v>79.45</v>
       </c>
       <c r="F1134" t="n">
-        <v>98000</v>
+        <v>99161</v>
       </c>
     </row>
     <row r="1135">
@@ -23181,10 +23181,10 @@
         <v>78.56999999999999</v>
       </c>
       <c r="E1138" t="n">
-        <v>79.54000000000001</v>
+        <v>79.48</v>
       </c>
       <c r="F1138" t="n">
-        <v>76777</v>
+        <v>77506</v>
       </c>
     </row>
     <row r="1139">
@@ -23201,10 +23201,10 @@
         <v>79.51000000000001</v>
       </c>
       <c r="E1139" t="n">
-        <v>80.69</v>
+        <v>80.5</v>
       </c>
       <c r="F1139" t="n">
-        <v>69907</v>
+        <v>70745</v>
       </c>
     </row>
     <row r="1140">
@@ -23281,10 +23281,10 @@
         <v>82.54000000000001</v>
       </c>
       <c r="E1143" t="n">
-        <v>83.42</v>
+        <v>83.3</v>
       </c>
       <c r="F1143" t="n">
-        <v>100960</v>
+        <v>101885</v>
       </c>
     </row>
     <row r="1144">
@@ -23301,10 +23301,10 @@
         <v>82.78</v>
       </c>
       <c r="E1144" t="n">
-        <v>84.26000000000001</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="F1144" t="n">
-        <v>96080</v>
+        <v>96933</v>
       </c>
     </row>
     <row r="1145">
@@ -23381,10 +23381,10 @@
         <v>82.23</v>
       </c>
       <c r="E1148" t="n">
-        <v>85.13</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="F1148" t="n">
-        <v>122532</v>
+        <v>124232</v>
       </c>
     </row>
     <row r="1149">
@@ -23401,10 +23401,10 @@
         <v>84.89</v>
       </c>
       <c r="E1149" t="n">
-        <v>85.84</v>
+        <v>85.81</v>
       </c>
       <c r="F1149" t="n">
-        <v>103319</v>
+        <v>104424</v>
       </c>
     </row>
     <row r="1150">
@@ -23481,10 +23481,10 @@
         <v>85.89</v>
       </c>
       <c r="E1153" t="n">
-        <v>86.09999999999999</v>
+        <v>86.01000000000001</v>
       </c>
       <c r="F1153" t="n">
-        <v>119054</v>
+        <v>120019</v>
       </c>
     </row>
     <row r="1154">
@@ -23501,10 +23501,10 @@
         <v>85.53</v>
       </c>
       <c r="E1154" t="n">
-        <v>86.26000000000001</v>
+        <v>86.16</v>
       </c>
       <c r="F1154" t="n">
-        <v>114400</v>
+        <v>115051</v>
       </c>
     </row>
     <row r="1155">
@@ -23581,10 +23581,10 @@
         <v>82.70999999999999</v>
       </c>
       <c r="E1158" t="n">
-        <v>83.45999999999999</v>
+        <v>83.42</v>
       </c>
       <c r="F1158" t="n">
-        <v>87119</v>
+        <v>88033</v>
       </c>
     </row>
     <row r="1159">
@@ -23601,10 +23601,10 @@
         <v>82.98</v>
       </c>
       <c r="E1159" t="n">
-        <v>84.37</v>
+        <v>84.42</v>
       </c>
       <c r="F1159" t="n">
-        <v>98085</v>
+        <v>98761</v>
       </c>
     </row>
     <row r="1160">
@@ -23681,10 +23681,10 @@
         <v>81.61</v>
       </c>
       <c r="E1163" t="n">
-        <v>82.76000000000001</v>
+        <v>82.67</v>
       </c>
       <c r="F1163" t="n">
-        <v>77118</v>
+        <v>77961</v>
       </c>
     </row>
     <row r="1164">
@@ -23701,10 +23701,10 @@
         <v>82.2</v>
       </c>
       <c r="E1164" t="n">
-        <v>84.14</v>
+        <v>84.05</v>
       </c>
       <c r="F1164" t="n">
-        <v>101382</v>
+        <v>102303</v>
       </c>
     </row>
     <row r="1165">
@@ -23781,10 +23781,10 @@
         <v>84.98</v>
       </c>
       <c r="E1168" t="n">
-        <v>86.63</v>
+        <v>86.66</v>
       </c>
       <c r="F1168" t="n">
-        <v>83934</v>
+        <v>85007</v>
       </c>
     </row>
     <row r="1169">
@@ -23795,16 +23795,16 @@
         <v>86.63</v>
       </c>
       <c r="C1169" t="n">
-        <v>88.66</v>
+        <v>88.75</v>
       </c>
       <c r="D1169" t="n">
         <v>86.59</v>
       </c>
       <c r="E1169" t="n">
-        <v>88.64</v>
+        <v>88.68000000000001</v>
       </c>
       <c r="F1169" t="n">
-        <v>97671</v>
+        <v>98645</v>
       </c>
     </row>
     <row r="1170">
@@ -23881,10 +23881,10 @@
         <v>89.17</v>
       </c>
       <c r="E1173" t="n">
-        <v>89.76000000000001</v>
+        <v>89.47</v>
       </c>
       <c r="F1173" t="n">
-        <v>103067</v>
+        <v>104343</v>
       </c>
     </row>
     <row r="1174">
@@ -23901,10 +23901,10 @@
         <v>88.97</v>
       </c>
       <c r="E1174" t="n">
-        <v>90.2</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="F1174" t="n">
-        <v>100164</v>
+        <v>101197</v>
       </c>
     </row>
     <row r="1175">
@@ -23975,16 +23975,16 @@
         <v>91.56999999999999</v>
       </c>
       <c r="C1178" t="n">
-        <v>93.44</v>
+        <v>93.68000000000001</v>
       </c>
       <c r="D1178" t="n">
         <v>91.55</v>
       </c>
       <c r="E1178" t="n">
-        <v>93.36</v>
+        <v>93.56</v>
       </c>
       <c r="F1178" t="n">
-        <v>89908</v>
+        <v>91727</v>
       </c>
     </row>
     <row r="1179">
@@ -24001,10 +24001,10 @@
         <v>92.14</v>
       </c>
       <c r="E1179" t="n">
-        <v>93.52</v>
+        <v>93.56999999999999</v>
       </c>
       <c r="F1179" t="n">
-        <v>100530</v>
+        <v>101498</v>
       </c>
     </row>
     <row r="1180">
@@ -24081,10 +24081,10 @@
         <v>91.23999999999999</v>
       </c>
       <c r="E1183" t="n">
-        <v>92.27</v>
+        <v>92.20999999999999</v>
       </c>
       <c r="F1183" t="n">
-        <v>97207</v>
+        <v>98137</v>
       </c>
     </row>
     <row r="1184">
@@ -24101,10 +24101,10 @@
         <v>91.68000000000001</v>
       </c>
       <c r="E1184" t="n">
-        <v>92.31</v>
+        <v>92.28</v>
       </c>
       <c r="F1184" t="n">
-        <v>98960</v>
+        <v>99665</v>
       </c>
     </row>
     <row r="1185">
@@ -24181,10 +24181,10 @@
         <v>92.56</v>
       </c>
       <c r="E1188" t="n">
-        <v>92.94</v>
+        <v>92.89</v>
       </c>
       <c r="F1188" t="n">
-        <v>127194</v>
+        <v>128240</v>
       </c>
     </row>
     <row r="1189">
@@ -24201,10 +24201,10 @@
         <v>91.68000000000001</v>
       </c>
       <c r="E1189" t="n">
-        <v>91.95999999999999</v>
+        <v>91.8</v>
       </c>
       <c r="F1189" t="n">
-        <v>116761</v>
+        <v>117877</v>
       </c>
     </row>
     <row r="1190">
@@ -24281,10 +24281,10 @@
         <v>83.31999999999999</v>
       </c>
       <c r="E1193" t="n">
-        <v>83.68000000000001</v>
+        <v>83.72</v>
       </c>
       <c r="F1193" t="n">
-        <v>148426</v>
+        <v>149779</v>
       </c>
     </row>
     <row r="1194">
@@ -24301,10 +24301,10 @@
         <v>82.97</v>
       </c>
       <c r="E1194" t="n">
-        <v>83.88</v>
+        <v>83.79000000000001</v>
       </c>
       <c r="F1194" t="n">
-        <v>138785</v>
+        <v>140020</v>
       </c>
     </row>
     <row r="1195">
@@ -24381,10 +24381,10 @@
         <v>84.59</v>
       </c>
       <c r="E1198" t="n">
-        <v>85.7</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="F1198" t="n">
-        <v>123421</v>
+        <v>124560</v>
       </c>
     </row>
     <row r="1199">
@@ -24404,7 +24404,7 @@
         <v>89.93000000000001</v>
       </c>
       <c r="F1199" t="n">
-        <v>118765</v>
+        <v>120817</v>
       </c>
     </row>
     <row r="1200">
@@ -24475,16 +24475,16 @@
         <v>90.26000000000001</v>
       </c>
       <c r="C1203" t="n">
-        <v>92.22</v>
+        <v>92.34999999999999</v>
       </c>
       <c r="D1203" t="n">
         <v>88.69</v>
       </c>
       <c r="E1203" t="n">
-        <v>92.16</v>
+        <v>92.04000000000001</v>
       </c>
       <c r="F1203" t="n">
-        <v>109002</v>
+        <v>111224</v>
       </c>
     </row>
     <row r="1204">
@@ -24501,10 +24501,10 @@
         <v>90.63</v>
       </c>
       <c r="E1204" t="n">
-        <v>91.13</v>
+        <v>91.26000000000001</v>
       </c>
       <c r="F1204" t="n">
-        <v>109157</v>
+        <v>110661</v>
       </c>
     </row>
     <row r="1205">
@@ -24581,10 +24581,10 @@
         <v>86.48</v>
       </c>
       <c r="E1208" t="n">
-        <v>87.25</v>
+        <v>87.23999999999999</v>
       </c>
       <c r="F1208" t="n">
-        <v>113368</v>
+        <v>114536</v>
       </c>
     </row>
     <row r="1209">
@@ -24601,10 +24601,10 @@
         <v>86.76000000000001</v>
       </c>
       <c r="E1209" t="n">
-        <v>88.76000000000001</v>
+        <v>88.70999999999999</v>
       </c>
       <c r="F1209" t="n">
-        <v>121600</v>
+        <v>123231</v>
       </c>
     </row>
     <row r="1210">
@@ -24672,7 +24672,7 @@
         <v>45232</v>
       </c>
       <c r="B1213" t="n">
-        <v>84.83</v>
+        <v>85.03</v>
       </c>
       <c r="C1213" t="n">
         <v>86.88</v>
@@ -24684,7 +24684,7 @@
         <v>86.63</v>
       </c>
       <c r="F1213" t="n">
-        <v>103842</v>
+        <v>102261</v>
       </c>
     </row>
     <row r="1214">
@@ -24692,7 +24692,7 @@
         <v>45233</v>
       </c>
       <c r="B1214" t="n">
-        <v>86.70999999999999</v>
+        <v>86.66</v>
       </c>
       <c r="C1214" t="n">
         <v>87.58</v>
@@ -24704,7 +24704,7 @@
         <v>84.95</v>
       </c>
       <c r="F1214" t="n">
-        <v>119097</v>
+        <v>117913</v>
       </c>
     </row>
     <row r="1215">
@@ -24781,10 +24781,10 @@
         <v>79.33</v>
       </c>
       <c r="E1218" t="n">
-        <v>79.75</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="F1218" t="n">
-        <v>110739</v>
+        <v>111847</v>
       </c>
     </row>
     <row r="1219">
@@ -24801,10 +24801,10 @@
         <v>79.70999999999999</v>
       </c>
       <c r="E1219" t="n">
-        <v>81.36</v>
+        <v>81.43000000000001</v>
       </c>
       <c r="F1219" t="n">
-        <v>91256</v>
+        <v>92327</v>
       </c>
     </row>
     <row r="1220">
@@ -24881,10 +24881,10 @@
         <v>76.64</v>
       </c>
       <c r="E1223" t="n">
-        <v>77.43000000000001</v>
+        <v>77.45</v>
       </c>
       <c r="F1223" t="n">
-        <v>104766</v>
+        <v>105749</v>
       </c>
     </row>
     <row r="1224">
@@ -24901,10 +24901,10 @@
         <v>77.31</v>
       </c>
       <c r="E1224" t="n">
-        <v>80.37</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="F1224" t="n">
-        <v>88772</v>
+        <v>89648</v>
       </c>
     </row>
     <row r="1225">
@@ -25078,13 +25078,13 @@
         <v>84.51000000000001</v>
       </c>
       <c r="D1233" t="n">
-        <v>79.95</v>
+        <v>79.94</v>
       </c>
       <c r="E1233" t="n">
-        <v>80</v>
+        <v>80.31</v>
       </c>
       <c r="F1233" t="n">
-        <v>143673</v>
+        <v>145419</v>
       </c>
     </row>
     <row r="1234">
@@ -25101,10 +25101,10 @@
         <v>78.69</v>
       </c>
       <c r="E1234" t="n">
-        <v>78.93000000000001</v>
+        <v>79.02</v>
       </c>
       <c r="F1234" t="n">
-        <v>125186</v>
+        <v>126159</v>
       </c>
     </row>
     <row r="1235">
@@ -25181,10 +25181,10 @@
         <v>73.68000000000001</v>
       </c>
       <c r="E1238" t="n">
-        <v>74.47</v>
+        <v>74.39</v>
       </c>
       <c r="F1238" t="n">
-        <v>115986</v>
+        <v>116791</v>
       </c>
     </row>
     <row r="1239">
@@ -25201,10 +25201,10 @@
         <v>74.25</v>
       </c>
       <c r="E1239" t="n">
-        <v>75.87</v>
+        <v>75.94</v>
       </c>
       <c r="F1239" t="n">
-        <v>114085</v>
+        <v>114930</v>
       </c>
     </row>
     <row r="1240">
@@ -25281,10 +25281,10 @@
         <v>74.56999999999999</v>
       </c>
       <c r="E1243" t="n">
-        <v>76.86</v>
+        <v>76.75</v>
       </c>
       <c r="F1243" t="n">
-        <v>83845</v>
+        <v>84712</v>
       </c>
     </row>
     <row r="1244">
@@ -25301,10 +25301,10 @@
         <v>75.48</v>
       </c>
       <c r="E1244" t="n">
-        <v>76.90000000000001</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="F1244" t="n">
-        <v>94162</v>
+        <v>95068</v>
       </c>
     </row>
     <row r="1245">
@@ -25381,10 +25381,10 @@
         <v>77.76000000000001</v>
       </c>
       <c r="E1248" t="n">
-        <v>79.19</v>
+        <v>79.12</v>
       </c>
       <c r="F1248" t="n">
-        <v>91100</v>
+        <v>91755</v>
       </c>
     </row>
     <row r="1249">
@@ -25461,10 +25461,10 @@
         <v>77.04000000000001</v>
       </c>
       <c r="E1252" t="n">
-        <v>77.29000000000001</v>
+        <v>77.36</v>
       </c>
       <c r="F1252" t="n">
-        <v>94380</v>
+        <v>95204</v>
       </c>
     </row>
     <row r="1253">
@@ -25544,7 +25544,7 @@
         <v>77.53</v>
       </c>
       <c r="F1256" t="n">
-        <v>118273</v>
+        <v>119158</v>
       </c>
     </row>
     <row r="1257">
@@ -25641,10 +25641,10 @@
         <v>76.45</v>
       </c>
       <c r="E1261" t="n">
-        <v>77.61</v>
+        <v>78.01000000000001</v>
       </c>
       <c r="F1261" t="n">
-        <v>128067</v>
+        <v>129868</v>
       </c>
     </row>
     <row r="1262">
@@ -25741,10 +25741,10 @@
         <v>76.98</v>
       </c>
       <c r="E1266" t="n">
-        <v>78.63</v>
+        <v>78.56</v>
       </c>
       <c r="F1266" t="n">
-        <v>98609</v>
+        <v>99368</v>
       </c>
     </row>
     <row r="1267">
@@ -25841,10 +25841,10 @@
         <v>79.65000000000001</v>
       </c>
       <c r="E1271" t="n">
-        <v>81.84999999999999</v>
+        <v>81.69</v>
       </c>
       <c r="F1271" t="n">
-        <v>75889</v>
+        <v>76710</v>
       </c>
     </row>
     <row r="1272">
@@ -25861,10 +25861,10 @@
         <v>80.75</v>
       </c>
       <c r="E1272" t="n">
-        <v>83.08</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="F1272" t="n">
-        <v>85666</v>
+        <v>87047</v>
       </c>
     </row>
     <row r="1273">
@@ -25941,10 +25941,10 @@
         <v>78.5</v>
       </c>
       <c r="E1276" t="n">
-        <v>78.64</v>
+        <v>78.7</v>
       </c>
       <c r="F1276" t="n">
-        <v>138682</v>
+        <v>140571</v>
       </c>
     </row>
     <row r="1277">
@@ -25961,10 +25961,10 @@
         <v>76.78</v>
       </c>
       <c r="E1277" t="n">
-        <v>77.11</v>
+        <v>77.31999999999999</v>
       </c>
       <c r="F1277" t="n">
-        <v>132023</v>
+        <v>133396</v>
       </c>
     </row>
     <row r="1278">
@@ -26041,10 +26041,10 @@
         <v>78.84999999999999</v>
       </c>
       <c r="E1281" t="n">
-        <v>81.51000000000001</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="F1281" t="n">
-        <v>86597</v>
+        <v>87658</v>
       </c>
     </row>
     <row r="1282">
@@ -26064,7 +26064,7 @@
         <v>81.63</v>
       </c>
       <c r="F1282" t="n">
-        <v>85346</v>
+        <v>86235</v>
       </c>
     </row>
     <row r="1283">
@@ -26141,10 +26141,10 @@
         <v>80.31999999999999</v>
       </c>
       <c r="E1286" t="n">
-        <v>82.37</v>
+        <v>82.22</v>
       </c>
       <c r="F1286" t="n">
-        <v>83753</v>
+        <v>84560</v>
       </c>
     </row>
     <row r="1287">
@@ -26161,10 +26161,10 @@
         <v>81.34</v>
       </c>
       <c r="E1287" t="n">
-        <v>82.70999999999999</v>
+        <v>82.68000000000001</v>
       </c>
       <c r="F1287" t="n">
-        <v>80620</v>
+        <v>81459</v>
       </c>
     </row>
     <row r="1288">
@@ -26241,10 +26241,10 @@
         <v>81.45</v>
       </c>
       <c r="E1291" t="n">
-        <v>82.63</v>
+        <v>82.51000000000001</v>
       </c>
       <c r="F1291" t="n">
-        <v>67106</v>
+        <v>67848</v>
       </c>
     </row>
     <row r="1292">
@@ -26261,10 +26261,10 @@
         <v>80.65000000000001</v>
       </c>
       <c r="E1292" t="n">
-        <v>80.88</v>
+        <v>80.84</v>
       </c>
       <c r="F1292" t="n">
-        <v>72495</v>
+        <v>73168</v>
       </c>
     </row>
     <row r="1293">
@@ -26341,10 +26341,10 @@
         <v>81.37</v>
       </c>
       <c r="E1296" t="n">
-        <v>81.70999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="F1296" t="n">
-        <v>78801</v>
+        <v>79642</v>
       </c>
     </row>
     <row r="1297">
@@ -26361,10 +26361,10 @@
         <v>81.63</v>
       </c>
       <c r="E1297" t="n">
-        <v>83.19</v>
+        <v>83.12</v>
       </c>
       <c r="F1297" t="n">
-        <v>72423</v>
+        <v>73275</v>
       </c>
     </row>
     <row r="1298">
@@ -26441,10 +26441,10 @@
         <v>81.77</v>
       </c>
       <c r="E1301" t="n">
-        <v>82.52</v>
+        <v>82.87</v>
       </c>
       <c r="F1301" t="n">
-        <v>102278</v>
+        <v>103853</v>
       </c>
     </row>
     <row r="1302">
@@ -26461,10 +26461,10 @@
         <v>81.41</v>
       </c>
       <c r="E1302" t="n">
-        <v>81.66</v>
+        <v>81.55</v>
       </c>
       <c r="F1302" t="n">
-        <v>99175</v>
+        <v>100115</v>
       </c>
     </row>
     <row r="1303">
@@ -26532,19 +26532,19 @@
         <v>45365</v>
       </c>
       <c r="B1306" t="n">
-        <v>83.59999999999999</v>
+        <v>83.69</v>
       </c>
       <c r="C1306" t="n">
         <v>85.18000000000001</v>
       </c>
       <c r="D1306" t="n">
-        <v>83.53</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="E1306" t="n">
         <v>84.61</v>
       </c>
       <c r="F1306" t="n">
-        <v>71844</v>
+        <v>71119</v>
       </c>
     </row>
     <row r="1307">
@@ -26552,7 +26552,7 @@
         <v>45366</v>
       </c>
       <c r="B1307" t="n">
-        <v>84.65000000000001</v>
+        <v>84.68000000000001</v>
       </c>
       <c r="C1307" t="n">
         <v>85.09</v>
@@ -26564,7 +26564,7 @@
         <v>84.83</v>
       </c>
       <c r="F1307" t="n">
-        <v>75864</v>
+        <v>74945</v>
       </c>
     </row>
     <row r="1308">
@@ -26632,7 +26632,7 @@
         <v>45372</v>
       </c>
       <c r="B1311" t="n">
-        <v>85.70999999999999</v>
+        <v>85.81</v>
       </c>
       <c r="C1311" t="n">
         <v>86.03</v>
@@ -26644,7 +26644,7 @@
         <v>84.95999999999999</v>
       </c>
       <c r="F1311" t="n">
-        <v>67186</v>
+        <v>66113</v>
       </c>
     </row>
     <row r="1312">
@@ -26652,7 +26652,7 @@
         <v>45373</v>
       </c>
       <c r="B1312" t="n">
-        <v>85.09999999999999</v>
+        <v>84.98999999999999</v>
       </c>
       <c r="C1312" t="n">
         <v>85.58</v>
@@ -26664,7 +26664,7 @@
         <v>84.93000000000001</v>
       </c>
       <c r="F1312" t="n">
-        <v>54286</v>
+        <v>53666</v>
       </c>
     </row>
     <row r="1313">
@@ -26732,7 +26732,7 @@
         <v>45379</v>
       </c>
       <c r="B1316" t="n">
-        <v>85.56</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="C1316" t="n">
         <v>86.89</v>
@@ -26744,7 +26744,7 @@
         <v>86.67</v>
       </c>
       <c r="F1316" t="n">
-        <v>57372</v>
+        <v>56915</v>
       </c>
     </row>
     <row r="1317">
@@ -26821,10 +26821,10 @@
         <v>88.43000000000001</v>
       </c>
       <c r="E1320" t="n">
-        <v>90.38</v>
+        <v>90.56</v>
       </c>
       <c r="F1320" t="n">
-        <v>74470</v>
+        <v>75666</v>
       </c>
     </row>
     <row r="1321">
@@ -26841,10 +26841,10 @@
         <v>90.18000000000001</v>
       </c>
       <c r="E1321" t="n">
-        <v>90.52</v>
+        <v>90.39</v>
       </c>
       <c r="F1321" t="n">
-        <v>79937</v>
+        <v>80607</v>
       </c>
     </row>
     <row r="1322">
@@ -26921,10 +26921,10 @@
         <v>88.87</v>
       </c>
       <c r="E1325" t="n">
-        <v>89.68000000000001</v>
+        <v>89.55</v>
       </c>
       <c r="F1325" t="n">
-        <v>107040</v>
+        <v>107884</v>
       </c>
     </row>
     <row r="1326">
@@ -26941,10 +26941,10 @@
         <v>89.45</v>
       </c>
       <c r="E1326" t="n">
-        <v>89.73</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="F1326" t="n">
-        <v>108331</v>
+        <v>109120</v>
       </c>
     </row>
     <row r="1327">
@@ -27021,10 +27021,10 @@
         <v>85.63</v>
       </c>
       <c r="E1330" t="n">
-        <v>86.47</v>
+        <v>86.19</v>
       </c>
       <c r="F1330" t="n">
-        <v>107464</v>
+        <v>108132</v>
       </c>
     </row>
     <row r="1331">
@@ -27041,10 +27041,10 @@
         <v>85.61</v>
       </c>
       <c r="E1331" t="n">
-        <v>86.51000000000001</v>
+        <v>86.38</v>
       </c>
       <c r="F1331" t="n">
-        <v>143518</v>
+        <v>144473</v>
       </c>
     </row>
     <row r="1332">
@@ -27115,16 +27115,16 @@
         <v>86.88</v>
       </c>
       <c r="C1335" t="n">
-        <v>87.97</v>
+        <v>88</v>
       </c>
       <c r="D1335" t="n">
         <v>86.2</v>
       </c>
       <c r="E1335" t="n">
-        <v>87.95</v>
+        <v>87.83</v>
       </c>
       <c r="F1335" t="n">
-        <v>69439</v>
+        <v>70059</v>
       </c>
     </row>
     <row r="1336">
@@ -27141,10 +27141,10 @@
         <v>87.56999999999999</v>
       </c>
       <c r="E1336" t="n">
-        <v>87.98999999999999</v>
+        <v>87.89</v>
       </c>
       <c r="F1336" t="n">
-        <v>63936</v>
+        <v>64445</v>
       </c>
     </row>
     <row r="1337">
@@ -27221,10 +27221,10 @@
         <v>82.89</v>
       </c>
       <c r="E1340" t="n">
-        <v>83.47</v>
+        <v>83.48</v>
       </c>
       <c r="F1340" t="n">
-        <v>100961</v>
+        <v>101847</v>
       </c>
     </row>
     <row r="1341">
@@ -27238,13 +27238,13 @@
         <v>84.18000000000001</v>
       </c>
       <c r="D1341" t="n">
-        <v>82.65000000000001</v>
+        <v>82.53</v>
       </c>
       <c r="E1341" t="n">
-        <v>82.77</v>
+        <v>82.54000000000001</v>
       </c>
       <c r="F1341" t="n">
-        <v>82987</v>
+        <v>83584</v>
       </c>
     </row>
     <row r="1342">
@@ -27321,10 +27321,10 @@
         <v>83.18000000000001</v>
       </c>
       <c r="E1345" t="n">
-        <v>83.91</v>
+        <v>83.77</v>
       </c>
       <c r="F1345" t="n">
-        <v>67201</v>
+        <v>67737</v>
       </c>
     </row>
     <row r="1346">
@@ -27338,13 +27338,13 @@
         <v>84.23</v>
       </c>
       <c r="D1346" t="n">
-        <v>82.5</v>
+        <v>82.36</v>
       </c>
       <c r="E1346" t="n">
-        <v>82.61</v>
+        <v>82.36</v>
       </c>
       <c r="F1346" t="n">
-        <v>62356</v>
+        <v>63117</v>
       </c>
     </row>
     <row r="1347">
@@ -27421,10 +27421,10 @@
         <v>82.02</v>
       </c>
       <c r="E1350" t="n">
-        <v>83.04000000000001</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="F1350" t="n">
-        <v>65306</v>
+        <v>65759</v>
       </c>
     </row>
     <row r="1351">
@@ -27441,10 +27441,10 @@
         <v>82.81999999999999</v>
       </c>
       <c r="E1351" t="n">
-        <v>83.68000000000001</v>
+        <v>83.56</v>
       </c>
       <c r="F1351" t="n">
-        <v>60667</v>
+        <v>61133</v>
       </c>
     </row>
     <row r="1352">
@@ -27521,10 +27521,10 @@
         <v>80.7</v>
       </c>
       <c r="E1355" t="n">
-        <v>81.09</v>
+        <v>81.06999999999999</v>
       </c>
       <c r="F1355" t="n">
-        <v>68901</v>
+        <v>69958</v>
       </c>
     </row>
     <row r="1356">
@@ -27541,10 +27541,10 @@
         <v>80.42</v>
       </c>
       <c r="E1356" t="n">
-        <v>81.84999999999999</v>
+        <v>81.79000000000001</v>
       </c>
       <c r="F1356" t="n">
-        <v>56045</v>
+        <v>56381</v>
       </c>
     </row>
     <row r="1357">
@@ -27618,13 +27618,13 @@
         <v>83.51000000000001</v>
       </c>
       <c r="D1360" t="n">
-        <v>81.77</v>
+        <v>81.72</v>
       </c>
       <c r="E1360" t="n">
-        <v>81.88</v>
+        <v>81.73</v>
       </c>
       <c r="F1360" t="n">
-        <v>81262</v>
+        <v>81864</v>
       </c>
     </row>
     <row r="1361">
@@ -27641,10 +27641,10 @@
         <v>80.69</v>
       </c>
       <c r="E1361" t="n">
-        <v>81.22</v>
+        <v>81.09</v>
       </c>
       <c r="F1361" t="n">
-        <v>86335</v>
+        <v>87130</v>
       </c>
     </row>
     <row r="1362">
@@ -27721,10 +27721,10 @@
         <v>78.23999999999999</v>
       </c>
       <c r="E1365" t="n">
-        <v>79.73</v>
+        <v>79.69</v>
       </c>
       <c r="F1365" t="n">
-        <v>72035</v>
+        <v>72677</v>
       </c>
     </row>
     <row r="1366">
@@ -27741,10 +27741,10 @@
         <v>79.18000000000001</v>
       </c>
       <c r="E1366" t="n">
-        <v>79.27</v>
+        <v>79.23999999999999</v>
       </c>
       <c r="F1366" t="n">
-        <v>76576</v>
+        <v>77440</v>
       </c>
     </row>
     <row r="1367">
@@ -27821,10 +27821,10 @@
         <v>81.53</v>
       </c>
       <c r="E1370" t="n">
-        <v>81.98</v>
+        <v>81.68000000000001</v>
       </c>
       <c r="F1370" t="n">
-        <v>78296</v>
+        <v>79567</v>
       </c>
     </row>
     <row r="1371">
@@ -27841,10 +27841,10 @@
         <v>81.64</v>
       </c>
       <c r="E1371" t="n">
-        <v>82.2</v>
+        <v>82.06</v>
       </c>
       <c r="F1371" t="n">
-        <v>75030</v>
+        <v>75768</v>
       </c>
     </row>
     <row r="1372">
@@ -27921,10 +27921,10 @@
         <v>84.28</v>
       </c>
       <c r="E1375" t="n">
-        <v>85.01000000000001</v>
+        <v>84.7</v>
       </c>
       <c r="F1375" t="n">
-        <v>59448</v>
+        <v>59846</v>
       </c>
     </row>
     <row r="1376">
@@ -27941,10 +27941,10 @@
         <v>84</v>
       </c>
       <c r="E1376" t="n">
-        <v>84.31</v>
+        <v>84.16</v>
       </c>
       <c r="F1376" t="n">
-        <v>59797</v>
+        <v>60278</v>
       </c>
     </row>
     <row r="1377">
@@ -28021,10 +28021,10 @@
         <v>84.01000000000001</v>
       </c>
       <c r="E1380" t="n">
-        <v>85.25</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="F1380" t="n">
-        <v>64362</v>
+        <v>64909</v>
       </c>
     </row>
     <row r="1381">
@@ -28041,10 +28041,10 @@
         <v>84.39</v>
       </c>
       <c r="E1381" t="n">
-        <v>84.79000000000001</v>
+        <v>84.65000000000001</v>
       </c>
       <c r="F1381" t="n">
-        <v>69177</v>
+        <v>69862</v>
       </c>
     </row>
     <row r="1382">
@@ -28141,10 +28141,10 @@
         <v>86.17</v>
       </c>
       <c r="E1386" t="n">
-        <v>86.31999999999999</v>
+        <v>86.43000000000001</v>
       </c>
       <c r="F1386" t="n">
-        <v>67919</v>
+        <v>68965</v>
       </c>
     </row>
     <row r="1387">
@@ -28221,10 +28221,10 @@
         <v>84.16</v>
       </c>
       <c r="E1390" t="n">
-        <v>85.19</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="F1390" t="n">
-        <v>78243</v>
+        <v>78990</v>
       </c>
     </row>
     <row r="1391">
@@ -28238,13 +28238,13 @@
         <v>85.67</v>
       </c>
       <c r="D1391" t="n">
-        <v>84.40000000000001</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="E1391" t="n">
-        <v>84.5</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="F1391" t="n">
-        <v>73607</v>
+        <v>74302</v>
       </c>
     </row>
     <row r="1392">
@@ -28321,10 +28321,10 @@
         <v>83.41</v>
       </c>
       <c r="E1395" t="n">
-        <v>83.72</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="F1395" t="n">
-        <v>68620</v>
+        <v>69797</v>
       </c>
     </row>
     <row r="1396">
@@ -28338,13 +28338,13 @@
         <v>84.41</v>
       </c>
       <c r="D1396" t="n">
-        <v>81.7</v>
+        <v>81.64</v>
       </c>
       <c r="E1396" t="n">
-        <v>81.89</v>
+        <v>81.64</v>
       </c>
       <c r="F1396" t="n">
-        <v>72020</v>
+        <v>72736</v>
       </c>
     </row>
     <row r="1397">
@@ -28421,10 +28421,10 @@
         <v>79.28</v>
       </c>
       <c r="E1400" t="n">
-        <v>81.33</v>
+        <v>81.37</v>
       </c>
       <c r="F1400" t="n">
-        <v>69150</v>
+        <v>69789</v>
       </c>
     </row>
     <row r="1401">
@@ -28441,10 +28441,10 @@
         <v>79.39</v>
       </c>
       <c r="E1401" t="n">
-        <v>79.92</v>
+        <v>79.48999999999999</v>
       </c>
       <c r="F1401" t="n">
-        <v>64725</v>
+        <v>65748</v>
       </c>
     </row>
     <row r="1402">
@@ -28521,10 +28521,10 @@
         <v>79.3</v>
       </c>
       <c r="E1405" t="n">
-        <v>80</v>
+        <v>79.83</v>
       </c>
       <c r="F1405" t="n">
-        <v>104482</v>
+        <v>105741</v>
       </c>
     </row>
     <row r="1406">
@@ -28541,10 +28541,10 @@
         <v>76.26000000000001</v>
       </c>
       <c r="E1406" t="n">
-        <v>77.08</v>
+        <v>77.14</v>
       </c>
       <c r="F1406" t="n">
-        <v>124356</v>
+        <v>125792</v>
       </c>
     </row>
     <row r="1407">
@@ -28621,10 +28621,10 @@
         <v>77.33</v>
       </c>
       <c r="E1410" t="n">
-        <v>78.73999999999999</v>
+        <v>78.59</v>
       </c>
       <c r="F1410" t="n">
-        <v>113028</v>
+        <v>113892</v>
       </c>
     </row>
     <row r="1411">
@@ -28641,10 +28641,10 @@
         <v>78.43000000000001</v>
       </c>
       <c r="E1411" t="n">
-        <v>79.34</v>
+        <v>79.27</v>
       </c>
       <c r="F1411" t="n">
-        <v>86405</v>
+        <v>87467</v>
       </c>
     </row>
     <row r="1412">
@@ -28721,10 +28721,10 @@
         <v>79.11</v>
       </c>
       <c r="E1415" t="n">
-        <v>80.31999999999999</v>
+        <v>80.26000000000001</v>
       </c>
       <c r="F1415" t="n">
-        <v>78757</v>
+        <v>79567</v>
       </c>
     </row>
     <row r="1416">
@@ -28741,10 +28741,10 @@
         <v>78.09</v>
       </c>
       <c r="E1416" t="n">
-        <v>79.22</v>
+        <v>78.94</v>
       </c>
       <c r="F1416" t="n">
-        <v>81009</v>
+        <v>82030</v>
       </c>
     </row>
     <row r="1417">
@@ -28821,10 +28821,10 @@
         <v>75.25</v>
       </c>
       <c r="E1420" t="n">
-        <v>76.47</v>
+        <v>76.42</v>
       </c>
       <c r="F1420" t="n">
-        <v>79280</v>
+        <v>79873</v>
       </c>
     </row>
     <row r="1421">
@@ -28841,10 +28841,10 @@
         <v>76.40000000000001</v>
       </c>
       <c r="E1421" t="n">
-        <v>78.17</v>
+        <v>78.13</v>
       </c>
       <c r="F1421" t="n">
-        <v>68613</v>
+        <v>69081</v>
       </c>
     </row>
     <row r="1422">
@@ -28921,10 +28921,10 @@
         <v>76.90000000000001</v>
       </c>
       <c r="E1425" t="n">
-        <v>78.81</v>
+        <v>78.72</v>
       </c>
       <c r="F1425" t="n">
-        <v>93699</v>
+        <v>94397</v>
       </c>
     </row>
     <row r="1426">
@@ -28941,10 +28941,10 @@
         <v>76.56</v>
       </c>
       <c r="E1426" t="n">
-        <v>76.81</v>
+        <v>76.77</v>
       </c>
       <c r="F1426" t="n">
-        <v>108329</v>
+        <v>109124</v>
       </c>
     </row>
     <row r="1427">
@@ -29021,10 +29021,10 @@
         <v>72.20999999999999</v>
       </c>
       <c r="E1430" t="n">
-        <v>72.54000000000001</v>
+        <v>72.53</v>
       </c>
       <c r="F1430" t="n">
-        <v>108713</v>
+        <v>109541</v>
       </c>
     </row>
     <row r="1431">
@@ -29041,10 +29041,10 @@
         <v>70.45</v>
       </c>
       <c r="E1431" t="n">
-        <v>71.37</v>
+        <v>71.2</v>
       </c>
       <c r="F1431" t="n">
-        <v>115759</v>
+        <v>116954</v>
       </c>
     </row>
     <row r="1432">
@@ -29121,10 +29121,10 @@
         <v>70.31999999999999</v>
       </c>
       <c r="E1435" t="n">
-        <v>71.89</v>
+        <v>71.67</v>
       </c>
       <c r="F1435" t="n">
-        <v>114181</v>
+        <v>115156</v>
       </c>
     </row>
     <row r="1436">
@@ -29141,10 +29141,10 @@
         <v>71.09</v>
       </c>
       <c r="E1436" t="n">
-        <v>71.73</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="F1436" t="n">
-        <v>98569</v>
+        <v>99629</v>
       </c>
     </row>
     <row r="1437">
@@ -29221,10 +29221,10 @@
         <v>72.26000000000001</v>
       </c>
       <c r="E1440" t="n">
-        <v>74.05</v>
+        <v>73.97</v>
       </c>
       <c r="F1440" t="n">
-        <v>88395</v>
+        <v>89094</v>
       </c>
     </row>
     <row r="1441">
@@ -29241,10 +29241,10 @@
         <v>73.28</v>
       </c>
       <c r="E1441" t="n">
-        <v>73.98</v>
+        <v>73.87</v>
       </c>
       <c r="F1441" t="n">
-        <v>71635</v>
+        <v>72413</v>
       </c>
     </row>
     <row r="1442">
@@ -29321,10 +29321,10 @@
         <v>70.20999999999999</v>
       </c>
       <c r="E1445" t="n">
-        <v>70.66</v>
+        <v>70.68000000000001</v>
       </c>
       <c r="F1445" t="n">
-        <v>154979</v>
+        <v>155899</v>
       </c>
     </row>
     <row r="1446">
@@ -29335,16 +29335,16 @@
         <v>70.68000000000001</v>
       </c>
       <c r="C1446" t="n">
-        <v>71.89</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="D1446" t="n">
         <v>70.39</v>
       </c>
       <c r="E1446" t="n">
-        <v>71.81999999999999</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="F1446" t="n">
-        <v>122438</v>
+        <v>123787</v>
       </c>
     </row>
     <row r="1447">
@@ -29421,10 +29421,10 @@
         <v>74.18000000000001</v>
       </c>
       <c r="E1450" t="n">
-        <v>77.58</v>
+        <v>77.28</v>
       </c>
       <c r="F1450" t="n">
-        <v>123449</v>
+        <v>125075</v>
       </c>
     </row>
     <row r="1451">
@@ -29441,10 +29441,10 @@
         <v>77.19</v>
       </c>
       <c r="E1451" t="n">
-        <v>77.87</v>
+        <v>77.73</v>
       </c>
       <c r="F1451" t="n">
-        <v>120535</v>
+        <v>121412</v>
       </c>
     </row>
     <row r="1452">
@@ -38924,7 +38924,7 @@
         <v>81.53</v>
       </c>
       <c r="F1925" t="n">
-        <v>90754</v>
+        <v>90710</v>
       </c>
     </row>
     <row r="1926">
@@ -38984,7 +38984,27 @@
         <v>87.23999999999999</v>
       </c>
       <c r="F1928" t="n">
-        <v>104850</v>
+        <v>104954</v>
+      </c>
+    </row>
+    <row r="1929">
+      <c r="A1929" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B1929" t="n">
+        <v>87.22</v>
+      </c>
+      <c r="C1929" t="n">
+        <v>87.81999999999999</v>
+      </c>
+      <c r="D1929" t="n">
+        <v>84.86</v>
+      </c>
+      <c r="E1929" t="n">
+        <v>85.86</v>
+      </c>
+      <c r="F1929" t="n">
+        <v>102608</v>
       </c>
     </row>
   </sheetData>

--- a/database/BRENT.xlsx
+++ b/database/BRENT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1929"/>
+  <dimension ref="A1:F1930"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3881,10 +3881,10 @@
         <v>60.96</v>
       </c>
       <c r="E173" t="n">
-        <v>61.65</v>
+        <v>61.74</v>
       </c>
       <c r="F173" t="n">
-        <v>7745</v>
+        <v>7439</v>
       </c>
     </row>
     <row r="174">
@@ -3952,7 +3952,7 @@
         <v>43769</v>
       </c>
       <c r="B177" t="n">
-        <v>60.27</v>
+        <v>60.17</v>
       </c>
       <c r="C177" t="n">
         <v>60.79</v>
@@ -3964,7 +3964,7 @@
         <v>59.46</v>
       </c>
       <c r="F177" t="n">
-        <v>20603</v>
+        <v>20831</v>
       </c>
     </row>
     <row r="178">
@@ -3972,7 +3972,7 @@
         <v>43770</v>
       </c>
       <c r="B178" t="n">
-        <v>59.64</v>
+        <v>59.42</v>
       </c>
       <c r="C178" t="n">
         <v>61.8</v>
@@ -3984,7 +3984,7 @@
         <v>61.65</v>
       </c>
       <c r="F178" t="n">
-        <v>18281</v>
+        <v>18539</v>
       </c>
     </row>
     <row r="179">
@@ -4061,10 +4061,10 @@
         <v>61.63</v>
       </c>
       <c r="E182" t="n">
-        <v>62.29</v>
+        <v>62.14</v>
       </c>
       <c r="F182" t="n">
-        <v>19680</v>
+        <v>19306</v>
       </c>
     </row>
     <row r="183">
@@ -4081,10 +4081,10 @@
         <v>60.65</v>
       </c>
       <c r="E183" t="n">
-        <v>62.64</v>
+        <v>62.61</v>
       </c>
       <c r="F183" t="n">
-        <v>21863</v>
+        <v>21625</v>
       </c>
     </row>
     <row r="184">
@@ -4161,10 +4161,10 @@
         <v>62.14</v>
       </c>
       <c r="E187" t="n">
-        <v>62.33</v>
+        <v>62.38</v>
       </c>
       <c r="F187" t="n">
-        <v>19293</v>
+        <v>19157</v>
       </c>
     </row>
     <row r="188">
@@ -4181,10 +4181,10 @@
         <v>61.69</v>
       </c>
       <c r="E188" t="n">
-        <v>63.41</v>
+        <v>63.32</v>
       </c>
       <c r="F188" t="n">
-        <v>16092</v>
+        <v>15801</v>
       </c>
     </row>
     <row r="189">
@@ -4261,10 +4261,10 @@
         <v>61.91</v>
       </c>
       <c r="E192" t="n">
-        <v>63.64</v>
+        <v>63.74</v>
       </c>
       <c r="F192" t="n">
-        <v>21823</v>
+        <v>21582</v>
       </c>
     </row>
     <row r="193">
@@ -4281,10 +4281,10 @@
         <v>61.92</v>
       </c>
       <c r="E193" t="n">
-        <v>62.52</v>
+        <v>62.58</v>
       </c>
       <c r="F193" t="n">
-        <v>17794</v>
+        <v>17577</v>
       </c>
     </row>
     <row r="194">
@@ -4461,10 +4461,10 @@
         <v>62.73</v>
       </c>
       <c r="E202" t="n">
-        <v>63.26</v>
+        <v>63.33</v>
       </c>
       <c r="F202" t="n">
-        <v>24300</v>
+        <v>24042</v>
       </c>
     </row>
     <row r="203">
@@ -4481,10 +4481,10 @@
         <v>62.82</v>
       </c>
       <c r="E203" t="n">
-        <v>64.34</v>
+        <v>64.22</v>
       </c>
       <c r="F203" t="n">
-        <v>22572</v>
+        <v>22359</v>
       </c>
     </row>
     <row r="204">
@@ -4561,10 +4561,10 @@
         <v>63.86</v>
       </c>
       <c r="E207" t="n">
-        <v>64.28</v>
+        <v>64.31</v>
       </c>
       <c r="F207" t="n">
-        <v>18454</v>
+        <v>18198</v>
       </c>
     </row>
     <row r="208">
@@ -4581,10 +4581,10 @@
         <v>64.48</v>
       </c>
       <c r="E208" t="n">
-        <v>64.90000000000001</v>
+        <v>64.88</v>
       </c>
       <c r="F208" t="n">
-        <v>21671</v>
+        <v>21484</v>
       </c>
     </row>
     <row r="209">
@@ -4661,10 +4661,10 @@
         <v>66.02</v>
       </c>
       <c r="E212" t="n">
-        <v>66.53</v>
+        <v>66.45</v>
       </c>
       <c r="F212" t="n">
-        <v>11180</v>
+        <v>10932</v>
       </c>
     </row>
     <row r="213">
@@ -4681,10 +4681,10 @@
         <v>65.72</v>
       </c>
       <c r="E213" t="n">
-        <v>66.01000000000001</v>
+        <v>65.98</v>
       </c>
       <c r="F213" t="n">
-        <v>14806</v>
+        <v>14693</v>
       </c>
     </row>
     <row r="214">
@@ -4741,10 +4741,10 @@
         <v>66.09</v>
       </c>
       <c r="E216" t="n">
-        <v>66.75</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="F216" t="n">
-        <v>9613</v>
+        <v>9409</v>
       </c>
     </row>
     <row r="217">
@@ -4761,10 +4761,10 @@
         <v>66.34</v>
       </c>
       <c r="E217" t="n">
-        <v>66.84</v>
+        <v>66.81</v>
       </c>
       <c r="F217" t="n">
-        <v>11398</v>
+        <v>11272</v>
       </c>
     </row>
     <row r="218">
@@ -4821,10 +4821,10 @@
         <v>65.7</v>
       </c>
       <c r="E220" t="n">
-        <v>66.23</v>
+        <v>66.19</v>
       </c>
       <c r="F220" t="n">
-        <v>15351</v>
+        <v>15153</v>
       </c>
     </row>
     <row r="221">
@@ -4841,10 +4841,10 @@
         <v>66.19</v>
       </c>
       <c r="E221" t="n">
-        <v>68.59</v>
+        <v>68.55</v>
       </c>
       <c r="F221" t="n">
-        <v>35609</v>
+        <v>35427</v>
       </c>
     </row>
     <row r="222">
@@ -4924,7 +4924,7 @@
         <v>65.38</v>
       </c>
       <c r="F225" t="n">
-        <v>25951</v>
+        <v>25682</v>
       </c>
     </row>
     <row r="226">
@@ -4944,7 +4944,7 @@
         <v>65</v>
       </c>
       <c r="F226" t="n">
-        <v>20436</v>
+        <v>20016</v>
       </c>
     </row>
     <row r="227">
@@ -5021,10 +5021,10 @@
         <v>63.89</v>
       </c>
       <c r="E230" t="n">
-        <v>64.7</v>
+        <v>64.64</v>
       </c>
       <c r="F230" t="n">
-        <v>16472</v>
+        <v>16107</v>
       </c>
     </row>
     <row r="231">
@@ -5041,10 +5041,10 @@
         <v>64.45</v>
       </c>
       <c r="E231" t="n">
-        <v>65.08</v>
+        <v>64.95</v>
       </c>
       <c r="F231" t="n">
-        <v>16251</v>
+        <v>16060</v>
       </c>
     </row>
     <row r="232">
@@ -5121,10 +5121,10 @@
         <v>61.24</v>
       </c>
       <c r="E235" t="n">
-        <v>62.11</v>
+        <v>61.97</v>
       </c>
       <c r="F235" t="n">
-        <v>23208</v>
+        <v>22982</v>
       </c>
     </row>
     <row r="236">
@@ -5141,10 +5141,10 @@
         <v>60.24</v>
       </c>
       <c r="E236" t="n">
-        <v>60.64</v>
+        <v>60.82</v>
       </c>
       <c r="F236" t="n">
-        <v>21687</v>
+        <v>21411</v>
       </c>
     </row>
     <row r="237">
@@ -5221,10 +5221,10 @@
         <v>56.73</v>
       </c>
       <c r="E240" t="n">
-        <v>58.2</v>
+        <v>58.03</v>
       </c>
       <c r="F240" t="n">
-        <v>28894</v>
+        <v>28317</v>
       </c>
     </row>
     <row r="241">
@@ -5244,7 +5244,7 @@
         <v>56.63</v>
       </c>
       <c r="F241" t="n">
-        <v>31264</v>
+        <v>30854</v>
       </c>
     </row>
     <row r="242">
@@ -5321,10 +5321,10 @@
         <v>54.24</v>
       </c>
       <c r="E245" t="n">
-        <v>55.14</v>
+        <v>55.07</v>
       </c>
       <c r="F245" t="n">
-        <v>31917</v>
+        <v>31638</v>
       </c>
     </row>
     <row r="246">
@@ -5341,10 +5341,10 @@
         <v>54.2</v>
       </c>
       <c r="E246" t="n">
-        <v>54.45</v>
+        <v>54.48</v>
       </c>
       <c r="F246" t="n">
-        <v>26144</v>
+        <v>25828</v>
       </c>
     </row>
     <row r="247">
@@ -5421,10 +5421,10 @@
         <v>54.95</v>
       </c>
       <c r="E250" t="n">
-        <v>56.4</v>
+        <v>56.51</v>
       </c>
       <c r="F250" t="n">
-        <v>24914</v>
+        <v>24675</v>
       </c>
     </row>
     <row r="251">
@@ -5441,10 +5441,10 @@
         <v>56.13</v>
       </c>
       <c r="E251" t="n">
-        <v>57.33</v>
+        <v>57.32</v>
       </c>
       <c r="F251" t="n">
-        <v>21778</v>
+        <v>21410</v>
       </c>
     </row>
     <row r="252">
@@ -5521,10 +5521,10 @@
         <v>58.89</v>
       </c>
       <c r="E255" t="n">
-        <v>59.03</v>
+        <v>59.28</v>
       </c>
       <c r="F255" t="n">
-        <v>23391</v>
+        <v>23121</v>
       </c>
     </row>
     <row r="256">
@@ -5541,10 +5541,10 @@
         <v>57.71</v>
       </c>
       <c r="E256" t="n">
-        <v>58.44</v>
+        <v>58.33</v>
       </c>
       <c r="F256" t="n">
-        <v>26971</v>
+        <v>26663</v>
       </c>
     </row>
     <row r="257">
@@ -5621,10 +5621,10 @@
         <v>50.38</v>
       </c>
       <c r="E260" t="n">
-        <v>50.95</v>
+        <v>51.35</v>
       </c>
       <c r="F260" t="n">
-        <v>52807</v>
+        <v>51199</v>
       </c>
     </row>
     <row r="261">
@@ -5641,10 +5641,10 @@
         <v>48.92</v>
       </c>
       <c r="E261" t="n">
-        <v>50.08</v>
+        <v>50.01</v>
       </c>
       <c r="F261" t="n">
-        <v>72794</v>
+        <v>71739</v>
       </c>
     </row>
     <row r="262">
@@ -5721,10 +5721,10 @@
         <v>49.67</v>
       </c>
       <c r="E265" t="n">
-        <v>50</v>
+        <v>49.95</v>
       </c>
       <c r="F265" t="n">
-        <v>42678</v>
+        <v>42080</v>
       </c>
     </row>
     <row r="266">
@@ -5741,10 +5741,10 @@
         <v>45.16</v>
       </c>
       <c r="E266" t="n">
-        <v>45.51</v>
+        <v>45.55</v>
       </c>
       <c r="F266" t="n">
-        <v>65295</v>
+        <v>64437</v>
       </c>
     </row>
     <row r="267">
@@ -5812,7 +5812,7 @@
         <v>43902</v>
       </c>
       <c r="B270" t="n">
-        <v>36.29</v>
+        <v>35.97</v>
       </c>
       <c r="C270" t="n">
         <v>36.45</v>
@@ -5824,7 +5824,7 @@
         <v>33.49</v>
       </c>
       <c r="F270" t="n">
-        <v>64469</v>
+        <v>66181</v>
       </c>
     </row>
     <row r="271">
@@ -6121,10 +6121,10 @@
         <v>26.12</v>
       </c>
       <c r="E285" t="n">
-        <v>29.96</v>
+        <v>30.29</v>
       </c>
       <c r="F285" t="n">
-        <v>214756</v>
+        <v>210087</v>
       </c>
     </row>
     <row r="286">
@@ -6135,16 +6135,16 @@
         <v>29.95</v>
       </c>
       <c r="C286" t="n">
-        <v>35.28</v>
+        <v>35.24</v>
       </c>
       <c r="D286" t="n">
         <v>28.9</v>
       </c>
       <c r="E286" t="n">
-        <v>35.16</v>
+        <v>34.72</v>
       </c>
       <c r="F286" t="n">
-        <v>280402</v>
+        <v>275171</v>
       </c>
     </row>
     <row r="287">
@@ -6221,10 +6221,10 @@
         <v>32.46</v>
       </c>
       <c r="E290" t="n">
-        <v>32.8</v>
+        <v>33.2</v>
       </c>
       <c r="F290" t="n">
-        <v>236196</v>
+        <v>230614</v>
       </c>
     </row>
     <row r="291">
@@ -6321,10 +6321,10 @@
         <v>29.42</v>
       </c>
       <c r="E295" t="n">
-        <v>30.59</v>
+        <v>30.65</v>
       </c>
       <c r="F295" t="n">
-        <v>151526</v>
+        <v>146842</v>
       </c>
     </row>
     <row r="296">
@@ -6341,10 +6341,10 @@
         <v>30.13</v>
       </c>
       <c r="E296" t="n">
-        <v>30.68</v>
+        <v>30.78</v>
       </c>
       <c r="F296" t="n">
-        <v>174982</v>
+        <v>171223</v>
       </c>
     </row>
     <row r="297">
@@ -6421,10 +6421,10 @@
         <v>23.38</v>
       </c>
       <c r="E300" t="n">
-        <v>24.73</v>
+        <v>24.74</v>
       </c>
       <c r="F300" t="n">
-        <v>216653</v>
+        <v>213310</v>
       </c>
     </row>
     <row r="301">
@@ -6441,10 +6441,10 @@
         <v>23.7</v>
       </c>
       <c r="E301" t="n">
-        <v>24.99</v>
+        <v>24.98</v>
       </c>
       <c r="F301" t="n">
-        <v>166443</v>
+        <v>163124</v>
       </c>
     </row>
     <row r="302">
@@ -6521,10 +6521,10 @@
         <v>24.33</v>
       </c>
       <c r="E305" t="n">
-        <v>26.85</v>
+        <v>26.83</v>
       </c>
       <c r="F305" t="n">
-        <v>229615</v>
+        <v>224455</v>
       </c>
     </row>
     <row r="306">
@@ -6541,10 +6541,10 @@
         <v>26.05</v>
       </c>
       <c r="E306" t="n">
-        <v>26.81</v>
+        <v>26.78</v>
       </c>
       <c r="F306" t="n">
-        <v>199609</v>
+        <v>196748</v>
       </c>
     </row>
     <row r="307">
@@ -6621,10 +6621,10 @@
         <v>29.4</v>
       </c>
       <c r="E310" t="n">
-        <v>29.65</v>
+        <v>29.48</v>
       </c>
       <c r="F310" t="n">
-        <v>229585</v>
+        <v>225301</v>
       </c>
     </row>
     <row r="311">
@@ -6641,10 +6641,10 @@
         <v>29.63</v>
       </c>
       <c r="E311" t="n">
-        <v>31.25</v>
+        <v>31.26</v>
       </c>
       <c r="F311" t="n">
-        <v>195288</v>
+        <v>192233</v>
       </c>
     </row>
     <row r="312">
@@ -6715,16 +6715,16 @@
         <v>29.73</v>
       </c>
       <c r="C315" t="n">
-        <v>31.75</v>
+        <v>31.65</v>
       </c>
       <c r="D315" t="n">
         <v>29.32</v>
       </c>
       <c r="E315" t="n">
-        <v>31.58</v>
+        <v>31.44</v>
       </c>
       <c r="F315" t="n">
-        <v>156389</v>
+        <v>152193</v>
       </c>
     </row>
     <row r="316">
@@ -6735,16 +6735,16 @@
         <v>31.58</v>
       </c>
       <c r="C316" t="n">
-        <v>33.06</v>
+        <v>32.96</v>
       </c>
       <c r="D316" t="n">
         <v>31.23</v>
       </c>
       <c r="E316" t="n">
-        <v>32.94</v>
+        <v>32.9</v>
       </c>
       <c r="F316" t="n">
-        <v>163209</v>
+        <v>160121</v>
       </c>
     </row>
     <row r="317">
@@ -6821,10 +6821,10 @@
         <v>35.92</v>
       </c>
       <c r="E320" t="n">
-        <v>36.3</v>
+        <v>36.38</v>
       </c>
       <c r="F320" t="n">
-        <v>160329</v>
+        <v>157279</v>
       </c>
     </row>
     <row r="321">
@@ -6841,10 +6841,10 @@
         <v>33.87</v>
       </c>
       <c r="E321" t="n">
-        <v>35.52</v>
+        <v>35.66</v>
       </c>
       <c r="F321" t="n">
-        <v>198023</v>
+        <v>194062</v>
       </c>
     </row>
     <row r="322">
@@ -6921,10 +6921,10 @@
         <v>34.37</v>
       </c>
       <c r="E325" t="n">
-        <v>35.98</v>
+        <v>35.89</v>
       </c>
       <c r="F325" t="n">
-        <v>213086</v>
+        <v>208524</v>
       </c>
     </row>
     <row r="326">
@@ -6941,10 +6941,10 @@
         <v>34.87</v>
       </c>
       <c r="E326" t="n">
-        <v>37.61</v>
+        <v>37.43</v>
       </c>
       <c r="F326" t="n">
-        <v>198370</v>
+        <v>193664</v>
       </c>
     </row>
     <row r="327">
@@ -7021,10 +7021,10 @@
         <v>39.05</v>
       </c>
       <c r="E330" t="n">
-        <v>39.92</v>
+        <v>39.78</v>
       </c>
       <c r="F330" t="n">
-        <v>161661</v>
+        <v>158433</v>
       </c>
     </row>
     <row r="331">
@@ -7041,10 +7041,10 @@
         <v>39.75</v>
       </c>
       <c r="E331" t="n">
-        <v>41.83</v>
+        <v>42.14</v>
       </c>
       <c r="F331" t="n">
-        <v>167359</v>
+        <v>163467</v>
       </c>
     </row>
     <row r="332">
@@ -7121,10 +7121,10 @@
         <v>37.96</v>
       </c>
       <c r="E335" t="n">
-        <v>38.41</v>
+        <v>38.36</v>
       </c>
       <c r="F335" t="n">
-        <v>227925</v>
+        <v>221502</v>
       </c>
     </row>
     <row r="336">
@@ -7141,10 +7141,10 @@
         <v>37.14</v>
       </c>
       <c r="E336" t="n">
-        <v>38.97</v>
+        <v>38.94</v>
       </c>
       <c r="F336" t="n">
-        <v>263342</v>
+        <v>260674</v>
       </c>
     </row>
     <row r="337">
@@ -7221,10 +7221,10 @@
         <v>40.05</v>
       </c>
       <c r="E340" t="n">
-        <v>41.33</v>
+        <v>41.37</v>
       </c>
       <c r="F340" t="n">
-        <v>163774</v>
+        <v>161532</v>
       </c>
     </row>
     <row r="341">
@@ -7241,10 +7241,10 @@
         <v>40.97</v>
       </c>
       <c r="E341" t="n">
-        <v>41.78</v>
+        <v>41.99</v>
       </c>
       <c r="F341" t="n">
-        <v>156573</v>
+        <v>153177</v>
       </c>
     </row>
     <row r="342">
@@ -7315,16 +7315,16 @@
         <v>40.45</v>
       </c>
       <c r="C345" t="n">
-        <v>41.59</v>
+        <v>41.51</v>
       </c>
       <c r="D345" t="n">
         <v>39.68</v>
       </c>
       <c r="E345" t="n">
-        <v>41.35</v>
+        <v>41.39</v>
       </c>
       <c r="F345" t="n">
-        <v>181021</v>
+        <v>178413</v>
       </c>
     </row>
     <row r="346">
@@ -7341,10 +7341,10 @@
         <v>40.25</v>
       </c>
       <c r="E346" t="n">
-        <v>40.57</v>
+        <v>40.58</v>
       </c>
       <c r="F346" t="n">
-        <v>160433</v>
+        <v>157969</v>
       </c>
     </row>
     <row r="347">
@@ -7421,10 +7421,10 @@
         <v>41.71</v>
       </c>
       <c r="E350" t="n">
-        <v>42.65</v>
+        <v>42.71</v>
       </c>
       <c r="F350" t="n">
-        <v>144329</v>
+        <v>142409</v>
       </c>
     </row>
     <row r="351">
@@ -7521,10 +7521,10 @@
         <v>41.99</v>
       </c>
       <c r="E355" t="n">
-        <v>42.35</v>
+        <v>42.32</v>
       </c>
       <c r="F355" t="n">
-        <v>136451</v>
+        <v>133908</v>
       </c>
     </row>
     <row r="356">
@@ -7541,10 +7541,10 @@
         <v>41.4</v>
       </c>
       <c r="E356" t="n">
-        <v>43.26</v>
+        <v>43.23</v>
       </c>
       <c r="F356" t="n">
-        <v>154800</v>
+        <v>152491</v>
       </c>
     </row>
     <row r="357">
@@ -7621,10 +7621,10 @@
         <v>43.19</v>
       </c>
       <c r="E360" t="n">
-        <v>43.28</v>
+        <v>43.36</v>
       </c>
       <c r="F360" t="n">
-        <v>101544</v>
+        <v>99613</v>
       </c>
     </row>
     <row r="361">
@@ -7641,10 +7641,10 @@
         <v>42.7</v>
       </c>
       <c r="E361" t="n">
-        <v>43.12</v>
+        <v>43.18</v>
       </c>
       <c r="F361" t="n">
-        <v>95049</v>
+        <v>93740</v>
       </c>
     </row>
     <row r="362">
@@ -7721,10 +7721,10 @@
         <v>43.42</v>
       </c>
       <c r="E365" t="n">
-        <v>43.53</v>
+        <v>43.82</v>
       </c>
       <c r="F365" t="n">
-        <v>112495</v>
+        <v>109900</v>
       </c>
     </row>
     <row r="366">
@@ -7741,10 +7741,10 @@
         <v>43.18</v>
       </c>
       <c r="E366" t="n">
-        <v>43.62</v>
+        <v>43.67</v>
       </c>
       <c r="F366" t="n">
-        <v>117377</v>
+        <v>115737</v>
       </c>
     </row>
     <row r="367">
@@ -7821,10 +7821,10 @@
         <v>41.95</v>
       </c>
       <c r="E370" t="n">
-        <v>43.56</v>
+        <v>43.43</v>
       </c>
       <c r="F370" t="n">
-        <v>117072</v>
+        <v>113377</v>
       </c>
     </row>
     <row r="371">
@@ -7841,10 +7841,10 @@
         <v>42.94</v>
       </c>
       <c r="E371" t="n">
-        <v>43.59</v>
+        <v>43.65</v>
       </c>
       <c r="F371" t="n">
-        <v>128800</v>
+        <v>127155</v>
       </c>
     </row>
     <row r="372">
@@ -7921,10 +7921,10 @@
         <v>44.96</v>
       </c>
       <c r="E375" t="n">
-        <v>45.13</v>
+        <v>45.28</v>
       </c>
       <c r="F375" t="n">
-        <v>122044</v>
+        <v>120720</v>
       </c>
     </row>
     <row r="376">
@@ -7941,10 +7941,10 @@
         <v>44.4</v>
       </c>
       <c r="E376" t="n">
-        <v>44.71</v>
+        <v>44.76</v>
       </c>
       <c r="F376" t="n">
-        <v>120731</v>
+        <v>119541</v>
       </c>
     </row>
     <row r="377">
@@ -8021,10 +8021,10 @@
         <v>45.07</v>
       </c>
       <c r="E380" t="n">
-        <v>45.24</v>
+        <v>45.3</v>
       </c>
       <c r="F380" t="n">
-        <v>91702</v>
+        <v>90204</v>
       </c>
     </row>
     <row r="381">
@@ -8041,10 +8041,10 @@
         <v>44.77</v>
       </c>
       <c r="E381" t="n">
-        <v>45.19</v>
+        <v>45.2</v>
       </c>
       <c r="F381" t="n">
-        <v>85013</v>
+        <v>83793</v>
       </c>
     </row>
     <row r="382">
@@ -8121,10 +8121,10 @@
         <v>44.46</v>
       </c>
       <c r="E385" t="n">
-        <v>45.27</v>
+        <v>45.36</v>
       </c>
       <c r="F385" t="n">
-        <v>87294</v>
+        <v>86301</v>
       </c>
     </row>
     <row r="386">
@@ -8141,10 +8141,10 @@
         <v>44.09</v>
       </c>
       <c r="E386" t="n">
-        <v>44.69</v>
+        <v>44.79</v>
       </c>
       <c r="F386" t="n">
-        <v>78965</v>
+        <v>77659</v>
       </c>
     </row>
     <row r="387">
@@ -8224,7 +8224,7 @@
         <v>45.59</v>
       </c>
       <c r="F390" t="n">
-        <v>96916</v>
+        <v>95873</v>
       </c>
     </row>
     <row r="391">
@@ -8241,10 +8241,10 @@
         <v>45.36</v>
       </c>
       <c r="E391" t="n">
-        <v>45.85</v>
+        <v>45.89</v>
       </c>
       <c r="F391" t="n">
-        <v>81841</v>
+        <v>81058</v>
       </c>
     </row>
     <row r="392">
@@ -8321,10 +8321,10 @@
         <v>43.27</v>
       </c>
       <c r="E395" t="n">
-        <v>44.07</v>
+        <v>44.09</v>
       </c>
       <c r="F395" t="n">
-        <v>158723</v>
+        <v>157249</v>
       </c>
     </row>
     <row r="396">
@@ -8338,13 +8338,13 @@
         <v>44.69</v>
       </c>
       <c r="D396" t="n">
-        <v>42.42</v>
+        <v>42.45</v>
       </c>
       <c r="E396" t="n">
-        <v>42.43</v>
+        <v>42.53</v>
       </c>
       <c r="F396" t="n">
-        <v>162787</v>
+        <v>160902</v>
       </c>
     </row>
     <row r="397">
@@ -8418,13 +8418,13 @@
         <v>41.23</v>
       </c>
       <c r="D400" t="n">
-        <v>39.96</v>
+        <v>40.02</v>
       </c>
       <c r="E400" t="n">
-        <v>39.97</v>
+        <v>40.07</v>
       </c>
       <c r="F400" t="n">
-        <v>149451</v>
+        <v>147551</v>
       </c>
     </row>
     <row r="401">
@@ -8441,10 +8441,10 @@
         <v>39.68</v>
       </c>
       <c r="E401" t="n">
-        <v>40.02</v>
+        <v>40.24</v>
       </c>
       <c r="F401" t="n">
-        <v>135456</v>
+        <v>133943</v>
       </c>
     </row>
     <row r="402">
@@ -8521,10 +8521,10 @@
         <v>41.89</v>
       </c>
       <c r="E405" t="n">
-        <v>43.58</v>
+        <v>43.67</v>
       </c>
       <c r="F405" t="n">
-        <v>142611</v>
+        <v>141089</v>
       </c>
     </row>
     <row r="406">
@@ -8541,10 +8541,10 @@
         <v>42.92</v>
       </c>
       <c r="E406" t="n">
-        <v>43.41</v>
+        <v>43.34</v>
       </c>
       <c r="F406" t="n">
-        <v>129546</v>
+        <v>127380</v>
       </c>
     </row>
     <row r="407">
@@ -8621,10 +8621,10 @@
         <v>41.68</v>
       </c>
       <c r="E410" t="n">
-        <v>42.16</v>
+        <v>42.27</v>
       </c>
       <c r="F410" t="n">
-        <v>133961</v>
+        <v>132502</v>
       </c>
     </row>
     <row r="411">
@@ -8641,10 +8641,10 @@
         <v>41.97</v>
       </c>
       <c r="E411" t="n">
-        <v>42.17</v>
+        <v>42.24</v>
       </c>
       <c r="F411" t="n">
-        <v>102107</v>
+        <v>100264</v>
       </c>
     </row>
     <row r="412">
@@ -8721,10 +8721,10 @@
         <v>39.98</v>
       </c>
       <c r="E415" t="n">
-        <v>40.75</v>
+        <v>40.93</v>
       </c>
       <c r="F415" t="n">
-        <v>157712</v>
+        <v>155461</v>
       </c>
     </row>
     <row r="416">
@@ -8741,10 +8741,10 @@
         <v>38.88</v>
       </c>
       <c r="E416" t="n">
-        <v>39.15</v>
+        <v>39.23</v>
       </c>
       <c r="F416" t="n">
-        <v>190634</v>
+        <v>188336</v>
       </c>
     </row>
     <row r="417">
@@ -8821,10 +8821,10 @@
         <v>42.02</v>
       </c>
       <c r="E420" t="n">
-        <v>43.52</v>
+        <v>43.54</v>
       </c>
       <c r="F420" t="n">
-        <v>112342</v>
+        <v>110782</v>
       </c>
     </row>
     <row r="421">
@@ -8841,10 +8841,10 @@
         <v>42.78</v>
       </c>
       <c r="E421" t="n">
-        <v>42.89</v>
+        <v>42.96</v>
       </c>
       <c r="F421" t="n">
-        <v>109695</v>
+        <v>108274</v>
       </c>
     </row>
     <row r="422">
@@ -8921,10 +8921,10 @@
         <v>41.79</v>
       </c>
       <c r="E425" t="n">
-        <v>43.26</v>
+        <v>43.38</v>
       </c>
       <c r="F425" t="n">
-        <v>147757</v>
+        <v>146298</v>
       </c>
     </row>
     <row r="426">
@@ -8941,10 +8941,10 @@
         <v>42.47</v>
       </c>
       <c r="E426" t="n">
-        <v>42.95</v>
+        <v>43.02</v>
       </c>
       <c r="F426" t="n">
-        <v>130839</v>
+        <v>129338</v>
       </c>
     </row>
     <row r="427">
@@ -9021,10 +9021,10 @@
         <v>41.72</v>
       </c>
       <c r="E430" t="n">
-        <v>42.59</v>
+        <v>42.71</v>
       </c>
       <c r="F430" t="n">
-        <v>110171</v>
+        <v>108471</v>
       </c>
     </row>
     <row r="431">
@@ -9041,10 +9041,10 @@
         <v>41.76</v>
       </c>
       <c r="E431" t="n">
-        <v>41.85</v>
+        <v>41.93</v>
       </c>
       <c r="F431" t="n">
-        <v>97195</v>
+        <v>95688</v>
       </c>
     </row>
     <row r="432">
@@ -9112,7 +9112,7 @@
         <v>44133</v>
       </c>
       <c r="B435" t="n">
-        <v>39.76</v>
+        <v>39.52</v>
       </c>
       <c r="C435" t="n">
         <v>39.97</v>
@@ -9124,7 +9124,7 @@
         <v>38.05</v>
       </c>
       <c r="F435" t="n">
-        <v>179602</v>
+        <v>183949</v>
       </c>
     </row>
     <row r="436">
@@ -9132,7 +9132,7 @@
         <v>44134</v>
       </c>
       <c r="B436" t="n">
-        <v>38.25</v>
+        <v>38.05</v>
       </c>
       <c r="C436" t="n">
         <v>38.72</v>
@@ -9144,7 +9144,7 @@
         <v>37.84</v>
       </c>
       <c r="F436" t="n">
-        <v>181739</v>
+        <v>184633</v>
       </c>
     </row>
     <row r="437">
@@ -9221,10 +9221,10 @@
         <v>40.42</v>
       </c>
       <c r="E440" t="n">
-        <v>40.68</v>
+        <v>40.82</v>
       </c>
       <c r="F440" t="n">
-        <v>157779</v>
+        <v>155706</v>
       </c>
     </row>
     <row r="441">
@@ -9241,10 +9241,10 @@
         <v>39.46</v>
       </c>
       <c r="E441" t="n">
-        <v>39.71</v>
+        <v>39.84</v>
       </c>
       <c r="F441" t="n">
-        <v>151438</v>
+        <v>150078</v>
       </c>
     </row>
     <row r="442">
@@ -9318,13 +9318,13 @@
         <v>44.59</v>
       </c>
       <c r="D445" t="n">
-        <v>43.35</v>
+        <v>43.42</v>
       </c>
       <c r="E445" t="n">
-        <v>43.38</v>
+        <v>43.49</v>
       </c>
       <c r="F445" t="n">
-        <v>146964</v>
+        <v>144322</v>
       </c>
     </row>
     <row r="446">
@@ -9338,13 +9338,13 @@
         <v>43.45</v>
       </c>
       <c r="D446" t="n">
-        <v>42.68</v>
+        <v>42.77</v>
       </c>
       <c r="E446" t="n">
-        <v>42.69</v>
+        <v>42.88</v>
       </c>
       <c r="F446" t="n">
-        <v>114191</v>
+        <v>112789</v>
       </c>
     </row>
     <row r="447">
@@ -9421,10 +9421,10 @@
         <v>43.87</v>
       </c>
       <c r="E450" t="n">
-        <v>44.21</v>
+        <v>44.44</v>
       </c>
       <c r="F450" t="n">
-        <v>112468</v>
+        <v>111013</v>
       </c>
     </row>
     <row r="451">
@@ -9441,10 +9441,10 @@
         <v>44.15</v>
       </c>
       <c r="E451" t="n">
-        <v>45.07</v>
+        <v>45.06</v>
       </c>
       <c r="F451" t="n">
-        <v>90427</v>
+        <v>88612</v>
       </c>
     </row>
     <row r="452">
@@ -9624,7 +9624,7 @@
         <v>48.65</v>
       </c>
       <c r="F460" t="n">
-        <v>122403</v>
+        <v>119976</v>
       </c>
     </row>
     <row r="461">
@@ -9641,10 +9641,10 @@
         <v>48.77</v>
       </c>
       <c r="E461" t="n">
-        <v>48.96</v>
+        <v>48.97</v>
       </c>
       <c r="F461" t="n">
-        <v>125701</v>
+        <v>124413</v>
       </c>
     </row>
     <row r="462">
@@ -9721,10 +9721,10 @@
         <v>48.79</v>
       </c>
       <c r="E465" t="n">
-        <v>50.25</v>
+        <v>50.26</v>
       </c>
       <c r="F465" t="n">
-        <v>132386</v>
+        <v>130125</v>
       </c>
     </row>
     <row r="466">
@@ -9741,10 +9741,10 @@
         <v>49.67</v>
       </c>
       <c r="E466" t="n">
-        <v>49.86</v>
+        <v>49.94</v>
       </c>
       <c r="F466" t="n">
-        <v>124721</v>
+        <v>123293</v>
       </c>
     </row>
     <row r="467">
@@ -9821,10 +9821,10 @@
         <v>51.06</v>
       </c>
       <c r="E470" t="n">
-        <v>51.46</v>
+        <v>51.55</v>
       </c>
       <c r="F470" t="n">
-        <v>102867</v>
+        <v>100894</v>
       </c>
     </row>
     <row r="471">
@@ -9841,10 +9841,10 @@
         <v>51.16</v>
       </c>
       <c r="E471" t="n">
-        <v>52.23</v>
+        <v>52.19</v>
       </c>
       <c r="F471" t="n">
-        <v>98705</v>
+        <v>96861</v>
       </c>
     </row>
     <row r="472">
@@ -10081,10 +10081,10 @@
         <v>53.88</v>
       </c>
       <c r="E483" t="n">
-        <v>54.34</v>
+        <v>54.45</v>
       </c>
       <c r="F483" t="n">
-        <v>142258</v>
+        <v>140683</v>
       </c>
     </row>
     <row r="484">
@@ -10095,16 +10095,16 @@
         <v>54.46</v>
       </c>
       <c r="C484" t="n">
-        <v>56.2</v>
+        <v>56.06</v>
       </c>
       <c r="D484" t="n">
         <v>54.3</v>
       </c>
       <c r="E484" t="n">
-        <v>56.11</v>
+        <v>56.02</v>
       </c>
       <c r="F484" t="n">
-        <v>155413</v>
+        <v>151805</v>
       </c>
     </row>
     <row r="485">
@@ -10181,10 +10181,10 @@
         <v>55.21</v>
       </c>
       <c r="E488" t="n">
-        <v>56.37</v>
+        <v>56.3</v>
       </c>
       <c r="F488" t="n">
-        <v>125098</v>
+        <v>123090</v>
       </c>
     </row>
     <row r="489">
@@ -10201,10 +10201,10 @@
         <v>54.63</v>
       </c>
       <c r="E489" t="n">
-        <v>54.75</v>
+        <v>54.94</v>
       </c>
       <c r="F489" t="n">
-        <v>135898</v>
+        <v>133988</v>
       </c>
     </row>
     <row r="490">
@@ -10281,10 +10281,10 @@
         <v>55.38</v>
       </c>
       <c r="E493" t="n">
-        <v>55.84</v>
+        <v>55.86</v>
       </c>
       <c r="F493" t="n">
-        <v>104851</v>
+        <v>103188</v>
       </c>
     </row>
     <row r="494">
@@ -10301,10 +10301,10 @@
         <v>54.38</v>
       </c>
       <c r="E494" t="n">
-        <v>54.88</v>
+        <v>55.08</v>
       </c>
       <c r="F494" t="n">
-        <v>135622</v>
+        <v>133367</v>
       </c>
     </row>
     <row r="495">
@@ -10378,13 +10378,13 @@
         <v>56.16</v>
       </c>
       <c r="D498" t="n">
-        <v>54.84</v>
+        <v>54.93</v>
       </c>
       <c r="E498" t="n">
-        <v>54.84</v>
+        <v>55</v>
       </c>
       <c r="F498" t="n">
-        <v>162289</v>
+        <v>160473</v>
       </c>
     </row>
     <row r="499">
@@ -10401,10 +10401,10 @@
         <v>54.84</v>
       </c>
       <c r="E499" t="n">
-        <v>54.93</v>
+        <v>55</v>
       </c>
       <c r="F499" t="n">
-        <v>163671</v>
+        <v>160923</v>
       </c>
     </row>
     <row r="500">
@@ -10481,10 +10481,10 @@
         <v>57.93</v>
       </c>
       <c r="E503" t="n">
-        <v>58.87</v>
+        <v>58.79</v>
       </c>
       <c r="F503" t="n">
-        <v>125851</v>
+        <v>123567</v>
       </c>
     </row>
     <row r="504">
@@ -10501,10 +10501,10 @@
         <v>58.87</v>
       </c>
       <c r="E504" t="n">
-        <v>59.41</v>
+        <v>59.31</v>
       </c>
       <c r="F504" t="n">
-        <v>120954</v>
+        <v>118436</v>
       </c>
     </row>
     <row r="505">
@@ -10578,13 +10578,13 @@
         <v>61.23</v>
       </c>
       <c r="D508" t="n">
-        <v>60.44</v>
+        <v>60.5</v>
       </c>
       <c r="E508" t="n">
-        <v>60.52</v>
+        <v>60.6</v>
       </c>
       <c r="F508" t="n">
-        <v>107974</v>
+        <v>104511</v>
       </c>
     </row>
     <row r="509">
@@ -10604,7 +10604,7 @@
         <v>62.22</v>
       </c>
       <c r="F509" t="n">
-        <v>126905</v>
+        <v>123306</v>
       </c>
     </row>
     <row r="510">
@@ -10681,10 +10681,10 @@
         <v>62.54</v>
       </c>
       <c r="E513" t="n">
-        <v>62.88</v>
+        <v>62.75</v>
       </c>
       <c r="F513" t="n">
-        <v>173632</v>
+        <v>170306</v>
       </c>
     </row>
     <row r="514">
@@ -10701,10 +10701,10 @@
         <v>61.42</v>
       </c>
       <c r="E514" t="n">
-        <v>61.97</v>
+        <v>61.95</v>
       </c>
       <c r="F514" t="n">
-        <v>184306</v>
+        <v>181146</v>
       </c>
     </row>
     <row r="515">
@@ -10781,10 +10781,10 @@
         <v>65.55</v>
       </c>
       <c r="E518" t="n">
-        <v>65.97</v>
+        <v>65.86</v>
       </c>
       <c r="F518" t="n">
-        <v>215533</v>
+        <v>210726</v>
       </c>
     </row>
     <row r="519">
@@ -10801,10 +10801,10 @@
         <v>64.13</v>
       </c>
       <c r="E519" t="n">
-        <v>64.27</v>
+        <v>64.25</v>
       </c>
       <c r="F519" t="n">
-        <v>239274</v>
+        <v>234931</v>
       </c>
     </row>
     <row r="520">
@@ -10881,10 +10881,10 @@
         <v>63.17</v>
       </c>
       <c r="E523" t="n">
-        <v>66.73999999999999</v>
+        <v>66.94</v>
       </c>
       <c r="F523" t="n">
-        <v>230530</v>
+        <v>225843</v>
       </c>
     </row>
     <row r="524">
@@ -10895,16 +10895,16 @@
         <v>66.86</v>
       </c>
       <c r="C524" t="n">
-        <v>69.41</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="D524" t="n">
         <v>66.43000000000001</v>
       </c>
       <c r="E524" t="n">
-        <v>69.25</v>
+        <v>69.28</v>
       </c>
       <c r="F524" t="n">
-        <v>253026</v>
+        <v>249828</v>
       </c>
     </row>
     <row r="525">
@@ -10981,10 +10981,10 @@
         <v>67.68000000000001</v>
       </c>
       <c r="E528" t="n">
-        <v>69.17</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="F528" t="n">
-        <v>163581</v>
+        <v>160838</v>
       </c>
     </row>
     <row r="529">
@@ -11001,10 +11001,10 @@
         <v>68.66</v>
       </c>
       <c r="E529" t="n">
-        <v>68.81</v>
+        <v>68.88</v>
       </c>
       <c r="F529" t="n">
-        <v>151042</v>
+        <v>148823</v>
       </c>
     </row>
     <row r="530">
@@ -11072,7 +11072,7 @@
         <v>44273</v>
       </c>
       <c r="B533" t="n">
-        <v>67.47</v>
+        <v>67.48</v>
       </c>
       <c r="C533" t="n">
         <v>67.83</v>
@@ -11084,7 +11084,7 @@
         <v>62.5</v>
       </c>
       <c r="F533" t="n">
-        <v>209835</v>
+        <v>212082</v>
       </c>
     </row>
     <row r="534">
@@ -11092,7 +11092,7 @@
         <v>44274</v>
       </c>
       <c r="B534" t="n">
-        <v>63.02</v>
+        <v>62.78</v>
       </c>
       <c r="C534" t="n">
         <v>64.73</v>
@@ -11104,7 +11104,7 @@
         <v>64.31999999999999</v>
       </c>
       <c r="F534" t="n">
-        <v>223529</v>
+        <v>228148</v>
       </c>
     </row>
     <row r="535">
@@ -11172,10 +11172,10 @@
         <v>44280</v>
       </c>
       <c r="B538" t="n">
-        <v>63.89</v>
+        <v>63.95</v>
       </c>
       <c r="C538" t="n">
-        <v>63.9</v>
+        <v>64.01000000000001</v>
       </c>
       <c r="D538" t="n">
         <v>60.82</v>
@@ -11184,7 +11184,7 @@
         <v>61.47</v>
       </c>
       <c r="F538" t="n">
-        <v>203253</v>
+        <v>206155</v>
       </c>
     </row>
     <row r="539">
@@ -11192,19 +11192,19 @@
         <v>44281</v>
       </c>
       <c r="B539" t="n">
-        <v>62.45</v>
+        <v>61.47</v>
       </c>
       <c r="C539" t="n">
         <v>64.73</v>
       </c>
       <c r="D539" t="n">
-        <v>62.07</v>
+        <v>61.47</v>
       </c>
       <c r="E539" t="n">
         <v>64.19</v>
       </c>
       <c r="F539" t="n">
-        <v>167422</v>
+        <v>171041</v>
       </c>
     </row>
     <row r="540">
@@ -11284,7 +11284,7 @@
         <v>64.51000000000001</v>
       </c>
       <c r="F543" t="n">
-        <v>201289</v>
+        <v>197783</v>
       </c>
     </row>
     <row r="544">
@@ -11361,10 +11361,10 @@
         <v>62.18</v>
       </c>
       <c r="E547" t="n">
-        <v>63.04</v>
+        <v>63.07</v>
       </c>
       <c r="F547" t="n">
-        <v>149186</v>
+        <v>146277</v>
       </c>
     </row>
     <row r="548">
@@ -11381,10 +11381,10 @@
         <v>62.33</v>
       </c>
       <c r="E548" t="n">
-        <v>62.76</v>
+        <v>62.81</v>
       </c>
       <c r="F548" t="n">
-        <v>121247</v>
+        <v>119219</v>
       </c>
     </row>
     <row r="549">
@@ -11461,10 +11461,10 @@
         <v>65.65000000000001</v>
       </c>
       <c r="E552" t="n">
-        <v>66.45</v>
+        <v>66.5</v>
       </c>
       <c r="F552" t="n">
-        <v>135521</v>
+        <v>133306</v>
       </c>
     </row>
     <row r="553">
@@ -11481,10 +11481,10 @@
         <v>66.11</v>
       </c>
       <c r="E553" t="n">
-        <v>66.31999999999999</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="F553" t="n">
-        <v>122938</v>
+        <v>120895</v>
       </c>
     </row>
     <row r="554">
@@ -11564,7 +11564,7 @@
         <v>64.95</v>
       </c>
       <c r="F557" t="n">
-        <v>143350</v>
+        <v>140975</v>
       </c>
     </row>
     <row r="558">
@@ -11581,10 +11581,10 @@
         <v>64.52</v>
       </c>
       <c r="E558" t="n">
-        <v>65.31999999999999</v>
+        <v>65.45</v>
       </c>
       <c r="F558" t="n">
-        <v>126302</v>
+        <v>124432</v>
       </c>
     </row>
     <row r="559">
@@ -11661,10 +11661,10 @@
         <v>66.56</v>
       </c>
       <c r="E562" t="n">
-        <v>67.84999999999999</v>
+        <v>67.86</v>
       </c>
       <c r="F562" t="n">
-        <v>160482</v>
+        <v>157092</v>
       </c>
     </row>
     <row r="563">
@@ -11681,10 +11681,10 @@
         <v>66.17</v>
       </c>
       <c r="E563" t="n">
-        <v>66.53</v>
+        <v>66.56</v>
       </c>
       <c r="F563" t="n">
-        <v>148372</v>
+        <v>145779</v>
       </c>
     </row>
     <row r="564">
@@ -11761,10 +11761,10 @@
         <v>67.77</v>
       </c>
       <c r="E567" t="n">
-        <v>68.03</v>
+        <v>68.05</v>
       </c>
       <c r="F567" t="n">
-        <v>155507</v>
+        <v>153533</v>
       </c>
     </row>
     <row r="568">
@@ -11784,7 +11784,7 @@
         <v>68.03</v>
       </c>
       <c r="F568" t="n">
-        <v>139157</v>
+        <v>136012</v>
       </c>
     </row>
     <row r="569">
@@ -11861,10 +11861,10 @@
         <v>66.34</v>
       </c>
       <c r="E572" t="n">
-        <v>66.81999999999999</v>
+        <v>66.83</v>
       </c>
       <c r="F572" t="n">
-        <v>182316</v>
+        <v>180093</v>
       </c>
     </row>
     <row r="573">
@@ -11875,16 +11875,16 @@
         <v>66.81</v>
       </c>
       <c r="C573" t="n">
-        <v>68.63</v>
+        <v>68.52</v>
       </c>
       <c r="D573" t="n">
         <v>66.36</v>
       </c>
       <c r="E573" t="n">
-        <v>68.52</v>
+        <v>68.45</v>
       </c>
       <c r="F573" t="n">
-        <v>142226</v>
+        <v>139950</v>
       </c>
     </row>
     <row r="574">
@@ -11958,13 +11958,13 @@
         <v>67.02</v>
       </c>
       <c r="D577" t="n">
-        <v>64.70999999999999</v>
+        <v>64.73</v>
       </c>
       <c r="E577" t="n">
-        <v>64.73999999999999</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="F577" t="n">
-        <v>168733</v>
+        <v>164782</v>
       </c>
     </row>
     <row r="578">
@@ -11981,10 +11981,10 @@
         <v>64.48</v>
       </c>
       <c r="E578" t="n">
-        <v>66.51000000000001</v>
+        <v>66.58</v>
       </c>
       <c r="F578" t="n">
-        <v>156317</v>
+        <v>153693</v>
       </c>
     </row>
     <row r="579">
@@ -12055,16 +12055,16 @@
         <v>68.58</v>
       </c>
       <c r="C582" t="n">
-        <v>69.2</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="D582" t="n">
         <v>67.89</v>
       </c>
       <c r="E582" t="n">
-        <v>69.12</v>
+        <v>69.05</v>
       </c>
       <c r="F582" t="n">
-        <v>122427</v>
+        <v>119490</v>
       </c>
     </row>
     <row r="583">
@@ -12081,10 +12081,10 @@
         <v>68.48999999999999</v>
       </c>
       <c r="E583" t="n">
-        <v>68.88</v>
+        <v>68.89</v>
       </c>
       <c r="F583" t="n">
-        <v>121324</v>
+        <v>119218</v>
       </c>
     </row>
     <row r="584">
@@ -12161,10 +12161,10 @@
         <v>70.5</v>
       </c>
       <c r="E587" t="n">
-        <v>71.22</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="F587" t="n">
-        <v>128649</v>
+        <v>126247</v>
       </c>
     </row>
     <row r="588">
@@ -12181,10 +12181,10 @@
         <v>70.58</v>
       </c>
       <c r="E588" t="n">
-        <v>71.43000000000001</v>
+        <v>71.47</v>
       </c>
       <c r="F588" t="n">
-        <v>117041</v>
+        <v>113793</v>
       </c>
     </row>
     <row r="589">
@@ -12261,10 +12261,10 @@
         <v>70.66</v>
       </c>
       <c r="E592" t="n">
-        <v>71.95</v>
+        <v>72.09</v>
       </c>
       <c r="F592" t="n">
-        <v>148450</v>
+        <v>146487</v>
       </c>
     </row>
     <row r="593">
@@ -12284,7 +12284,7 @@
         <v>72.23999999999999</v>
       </c>
       <c r="F593" t="n">
-        <v>142367</v>
+        <v>140128</v>
       </c>
     </row>
     <row r="594">
@@ -12361,10 +12361,10 @@
         <v>71.41</v>
       </c>
       <c r="E597" t="n">
-        <v>72.44</v>
+        <v>72.45</v>
       </c>
       <c r="F597" t="n">
-        <v>178094</v>
+        <v>175025</v>
       </c>
     </row>
     <row r="598">
@@ -12381,10 +12381,10 @@
         <v>71.55</v>
       </c>
       <c r="E598" t="n">
-        <v>72.5</v>
+        <v>72.76000000000001</v>
       </c>
       <c r="F598" t="n">
-        <v>151345</v>
+        <v>147859</v>
       </c>
     </row>
     <row r="599">
@@ -12461,10 +12461,10 @@
         <v>73.83</v>
       </c>
       <c r="E602" t="n">
-        <v>74.81</v>
+        <v>74.79000000000001</v>
       </c>
       <c r="F602" t="n">
-        <v>85692</v>
+        <v>84577</v>
       </c>
     </row>
     <row r="603">
@@ -12481,10 +12481,10 @@
         <v>74.14</v>
       </c>
       <c r="E603" t="n">
-        <v>75.28</v>
+        <v>75.27</v>
       </c>
       <c r="F603" t="n">
-        <v>79112</v>
+        <v>77990</v>
       </c>
     </row>
     <row r="604">
@@ -12561,10 +12561,10 @@
         <v>74.36</v>
       </c>
       <c r="E607" t="n">
-        <v>75.34</v>
+        <v>75.33</v>
       </c>
       <c r="F607" t="n">
-        <v>135699</v>
+        <v>134296</v>
       </c>
     </row>
     <row r="608">
@@ -12581,10 +12581,10 @@
         <v>75</v>
       </c>
       <c r="E608" t="n">
-        <v>75.81999999999999</v>
+        <v>76.02</v>
       </c>
       <c r="F608" t="n">
-        <v>104256</v>
+        <v>102316</v>
       </c>
     </row>
     <row r="609">
@@ -12655,16 +12655,16 @@
         <v>72.97</v>
       </c>
       <c r="C612" t="n">
-        <v>74.02</v>
+        <v>73.97</v>
       </c>
       <c r="D612" t="n">
         <v>71.73999999999999</v>
       </c>
       <c r="E612" t="n">
-        <v>73.95999999999999</v>
+        <v>73.92</v>
       </c>
       <c r="F612" t="n">
-        <v>138030</v>
+        <v>136419</v>
       </c>
     </row>
     <row r="613">
@@ -12681,10 +12681,10 @@
         <v>73.38</v>
       </c>
       <c r="E613" t="n">
-        <v>75.14</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="F613" t="n">
-        <v>96988</v>
+        <v>95892</v>
       </c>
     </row>
     <row r="614">
@@ -12761,10 +12761,10 @@
         <v>72.70999999999999</v>
       </c>
       <c r="E617" t="n">
-        <v>72.72</v>
+        <v>72.79000000000001</v>
       </c>
       <c r="F617" t="n">
-        <v>134216</v>
+        <v>132350</v>
       </c>
     </row>
     <row r="618">
@@ -12781,10 +12781,10 @@
         <v>71.88</v>
       </c>
       <c r="E618" t="n">
-        <v>72.64</v>
+        <v>72.81</v>
       </c>
       <c r="F618" t="n">
-        <v>110158</v>
+        <v>108307</v>
       </c>
     </row>
     <row r="619">
@@ -12864,7 +12864,7 @@
         <v>73.01000000000001</v>
       </c>
       <c r="F622" t="n">
-        <v>115159</v>
+        <v>113951</v>
       </c>
     </row>
     <row r="623">
@@ -12875,16 +12875,16 @@
         <v>72.98</v>
       </c>
       <c r="C623" t="n">
-        <v>73.56999999999999</v>
+        <v>73.52</v>
       </c>
       <c r="D623" t="n">
         <v>72.70999999999999</v>
       </c>
       <c r="E623" t="n">
-        <v>73.5</v>
+        <v>73.44</v>
       </c>
       <c r="F623" t="n">
-        <v>84579</v>
+        <v>83411</v>
       </c>
     </row>
     <row r="624">
@@ -12961,10 +12961,10 @@
         <v>73.59999999999999</v>
       </c>
       <c r="E627" t="n">
-        <v>74.75</v>
+        <v>74.97</v>
       </c>
       <c r="F627" t="n">
-        <v>81467</v>
+        <v>79720</v>
       </c>
     </row>
     <row r="628">
@@ -12981,10 +12981,10 @@
         <v>74.26000000000001</v>
       </c>
       <c r="E628" t="n">
-        <v>74.95999999999999</v>
+        <v>74.98999999999999</v>
       </c>
       <c r="F628" t="n">
-        <v>84253</v>
+        <v>83101</v>
       </c>
     </row>
     <row r="629">
@@ -13061,10 +13061,10 @@
         <v>69.56</v>
       </c>
       <c r="E632" t="n">
-        <v>71</v>
+        <v>71.16</v>
       </c>
       <c r="F632" t="n">
-        <v>108267</v>
+        <v>107034</v>
       </c>
     </row>
     <row r="633">
@@ -13078,13 +13078,13 @@
         <v>72.22</v>
       </c>
       <c r="D633" t="n">
-        <v>70.06999999999999</v>
+        <v>70.12</v>
       </c>
       <c r="E633" t="n">
-        <v>70.08</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="F633" t="n">
-        <v>113105</v>
+        <v>111453</v>
       </c>
     </row>
     <row r="634">
@@ -13161,10 +13161,10 @@
         <v>70.41</v>
       </c>
       <c r="E637" t="n">
-        <v>70.86</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="F637" t="n">
-        <v>96203</v>
+        <v>95219</v>
       </c>
     </row>
     <row r="638">
@@ -13181,10 +13181,10 @@
         <v>69.73999999999999</v>
       </c>
       <c r="E638" t="n">
-        <v>69.90000000000001</v>
+        <v>69.92</v>
       </c>
       <c r="F638" t="n">
-        <v>95696</v>
+        <v>93960</v>
       </c>
     </row>
     <row r="639">
@@ -13261,10 +13261,10 @@
         <v>65.2</v>
       </c>
       <c r="E642" t="n">
-        <v>66.23</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="F642" t="n">
-        <v>187712</v>
+        <v>185678</v>
       </c>
     </row>
     <row r="643">
@@ -13278,13 +13278,13 @@
         <v>66.54000000000001</v>
       </c>
       <c r="D643" t="n">
-        <v>64.53</v>
+        <v>64.61</v>
       </c>
       <c r="E643" t="n">
-        <v>64.54000000000001</v>
+        <v>64.62</v>
       </c>
       <c r="F643" t="n">
-        <v>138989</v>
+        <v>137258</v>
       </c>
     </row>
     <row r="644">
@@ -13361,10 +13361,10 @@
         <v>69.73999999999999</v>
       </c>
       <c r="E647" t="n">
-        <v>70.45999999999999</v>
+        <v>70.56</v>
       </c>
       <c r="F647" t="n">
-        <v>115965</v>
+        <v>113839</v>
       </c>
     </row>
     <row r="648">
@@ -13381,10 +13381,10 @@
         <v>70.16</v>
       </c>
       <c r="E648" t="n">
-        <v>71.5</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="F648" t="n">
-        <v>100455</v>
+        <v>99158</v>
       </c>
     </row>
     <row r="649">
@@ -13461,10 +13461,10 @@
         <v>70.75</v>
       </c>
       <c r="E652" t="n">
-        <v>72.61</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="F652" t="n">
-        <v>105073</v>
+        <v>103772</v>
       </c>
     </row>
     <row r="653">
@@ -13481,10 +13481,10 @@
         <v>72.20999999999999</v>
       </c>
       <c r="E653" t="n">
-        <v>72.20999999999999</v>
+        <v>72.36</v>
       </c>
       <c r="F653" t="n">
-        <v>111688</v>
+        <v>110684</v>
       </c>
     </row>
     <row r="654">
@@ -13561,10 +13561,10 @@
         <v>70.54000000000001</v>
       </c>
       <c r="E657" t="n">
-        <v>70.84</v>
+        <v>70.95</v>
       </c>
       <c r="F657" t="n">
-        <v>138553</v>
+        <v>136836</v>
       </c>
     </row>
     <row r="658">
@@ -13581,10 +13581,10 @@
         <v>70.59</v>
       </c>
       <c r="E658" t="n">
-        <v>72.51000000000001</v>
+        <v>72.44</v>
       </c>
       <c r="F658" t="n">
-        <v>107925</v>
+        <v>106315</v>
       </c>
     </row>
     <row r="659">
@@ -13661,10 +13661,10 @@
         <v>74.02</v>
       </c>
       <c r="E662" t="n">
-        <v>75.09</v>
+        <v>75.17</v>
       </c>
       <c r="F662" t="n">
-        <v>136265</v>
+        <v>134873</v>
       </c>
     </row>
     <row r="663">
@@ -13681,10 +13681,10 @@
         <v>74.06999999999999</v>
       </c>
       <c r="E663" t="n">
-        <v>74.67</v>
+        <v>74.79000000000001</v>
       </c>
       <c r="F663" t="n">
-        <v>131243</v>
+        <v>129577</v>
       </c>
     </row>
     <row r="664">
@@ -13764,7 +13764,7 @@
         <v>76.45</v>
       </c>
       <c r="F667" t="n">
-        <v>104066</v>
+        <v>102612</v>
       </c>
     </row>
     <row r="668">
@@ -13781,10 +13781,10 @@
         <v>76.09</v>
       </c>
       <c r="E668" t="n">
-        <v>77.13</v>
+        <v>77.15000000000001</v>
       </c>
       <c r="F668" t="n">
-        <v>94529</v>
+        <v>93448</v>
       </c>
     </row>
     <row r="669">
@@ -13861,10 +13861,10 @@
         <v>76.37</v>
       </c>
       <c r="E672" t="n">
-        <v>78.23999999999999</v>
+        <v>78.13</v>
       </c>
       <c r="F672" t="n">
-        <v>181989</v>
+        <v>180155</v>
       </c>
     </row>
     <row r="673">
@@ -13881,10 +13881,10 @@
         <v>77.38</v>
       </c>
       <c r="E673" t="n">
-        <v>78.93000000000001</v>
+        <v>78.98999999999999</v>
       </c>
       <c r="F673" t="n">
-        <v>151482</v>
+        <v>149729</v>
       </c>
     </row>
     <row r="674">
@@ -13961,10 +13961,10 @@
         <v>78.78</v>
       </c>
       <c r="E677" t="n">
-        <v>82.08</v>
+        <v>82.16</v>
       </c>
       <c r="F677" t="n">
-        <v>153620</v>
+        <v>151677</v>
       </c>
     </row>
     <row r="678">
@@ -13981,10 +13981,10 @@
         <v>81.63</v>
       </c>
       <c r="E678" t="n">
-        <v>82.22</v>
+        <v>82.17</v>
       </c>
       <c r="F678" t="n">
-        <v>149526</v>
+        <v>147722</v>
       </c>
     </row>
     <row r="679">
@@ -14061,10 +14061,10 @@
         <v>82.76000000000001</v>
       </c>
       <c r="E682" t="n">
-        <v>83.67</v>
+        <v>83.69</v>
       </c>
       <c r="F682" t="n">
-        <v>122153</v>
+        <v>120650</v>
       </c>
     </row>
     <row r="683">
@@ -14081,10 +14081,10 @@
         <v>83.68000000000001</v>
       </c>
       <c r="E683" t="n">
-        <v>84.33</v>
+        <v>84.23</v>
       </c>
       <c r="F683" t="n">
-        <v>116437</v>
+        <v>114060</v>
       </c>
     </row>
     <row r="684">
@@ -14161,10 +14161,10 @@
         <v>82.73</v>
       </c>
       <c r="E687" t="n">
-        <v>84.09</v>
+        <v>84.15000000000001</v>
       </c>
       <c r="F687" t="n">
-        <v>122966</v>
+        <v>121250</v>
       </c>
     </row>
     <row r="688">
@@ -14175,16 +14175,16 @@
         <v>83.81999999999999</v>
       </c>
       <c r="C688" t="n">
-        <v>85.08</v>
+        <v>84.97</v>
       </c>
       <c r="D688" t="n">
         <v>83.18000000000001</v>
       </c>
       <c r="E688" t="n">
-        <v>84.83</v>
+        <v>84.97</v>
       </c>
       <c r="F688" t="n">
-        <v>113449</v>
+        <v>111475</v>
       </c>
     </row>
     <row r="689">
@@ -14261,10 +14261,10 @@
         <v>81.48</v>
       </c>
       <c r="E692" t="n">
-        <v>83.78</v>
+        <v>83.83</v>
       </c>
       <c r="F692" t="n">
-        <v>167007</v>
+        <v>164605</v>
       </c>
     </row>
     <row r="693">
@@ -14281,10 +14281,10 @@
         <v>82.39</v>
       </c>
       <c r="E693" t="n">
-        <v>83.41</v>
+        <v>83.55</v>
       </c>
       <c r="F693" t="n">
-        <v>133535</v>
+        <v>132228</v>
       </c>
     </row>
     <row r="694">
@@ -14352,7 +14352,7 @@
         <v>44504</v>
       </c>
       <c r="B697" t="n">
-        <v>80.83</v>
+        <v>81.12</v>
       </c>
       <c r="C697" t="n">
         <v>84.08</v>
@@ -14364,7 +14364,7 @@
         <v>80.54000000000001</v>
       </c>
       <c r="F697" t="n">
-        <v>168783</v>
+        <v>171378</v>
       </c>
     </row>
     <row r="698">
@@ -14372,7 +14372,7 @@
         <v>44505</v>
       </c>
       <c r="B698" t="n">
-        <v>81.04000000000001</v>
+        <v>80.95</v>
       </c>
       <c r="C698" t="n">
         <v>82.72</v>
@@ -14384,7 +14384,7 @@
         <v>81.93000000000001</v>
       </c>
       <c r="F698" t="n">
-        <v>163172</v>
+        <v>166390</v>
       </c>
     </row>
     <row r="699">
@@ -14461,10 +14461,10 @@
         <v>81.06</v>
       </c>
       <c r="E702" t="n">
-        <v>81.92</v>
+        <v>81.91</v>
       </c>
       <c r="F702" t="n">
-        <v>161511</v>
+        <v>159955</v>
       </c>
     </row>
     <row r="703">
@@ -14481,10 +14481,10 @@
         <v>80.63</v>
       </c>
       <c r="E703" t="n">
-        <v>81.29000000000001</v>
+        <v>81.41</v>
       </c>
       <c r="F703" t="n">
-        <v>134507</v>
+        <v>133196</v>
       </c>
     </row>
     <row r="704">
@@ -14561,10 +14561,10 @@
         <v>78.55</v>
       </c>
       <c r="E707" t="n">
-        <v>80.34999999999999</v>
+        <v>80.42</v>
       </c>
       <c r="F707" t="n">
-        <v>132952</v>
+        <v>131123</v>
       </c>
     </row>
     <row r="708">
@@ -14581,10 +14581,10 @@
         <v>77.41</v>
       </c>
       <c r="E708" t="n">
-        <v>77.77</v>
+        <v>77.76000000000001</v>
       </c>
       <c r="F708" t="n">
-        <v>177513</v>
+        <v>175625</v>
       </c>
     </row>
     <row r="709">
@@ -14761,10 +14761,10 @@
         <v>65.67</v>
       </c>
       <c r="E717" t="n">
-        <v>70.36</v>
+        <v>69.94</v>
       </c>
       <c r="F717" t="n">
-        <v>240359</v>
+        <v>237353</v>
       </c>
     </row>
     <row r="718">
@@ -14781,10 +14781,10 @@
         <v>69.09999999999999</v>
       </c>
       <c r="E718" t="n">
-        <v>69.70999999999999</v>
+        <v>69.73</v>
       </c>
       <c r="F718" t="n">
-        <v>208893</v>
+        <v>205214</v>
       </c>
     </row>
     <row r="719">
@@ -14858,13 +14858,13 @@
         <v>76.55</v>
       </c>
       <c r="D722" t="n">
-        <v>73.70999999999999</v>
+        <v>73.78</v>
       </c>
       <c r="E722" t="n">
-        <v>73.84999999999999</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="F722" t="n">
-        <v>142264</v>
+        <v>140659</v>
       </c>
     </row>
     <row r="723">
@@ -14881,10 +14881,10 @@
         <v>73.67</v>
       </c>
       <c r="E723" t="n">
-        <v>75.16</v>
+        <v>75.23</v>
       </c>
       <c r="F723" t="n">
-        <v>153301</v>
+        <v>151698</v>
       </c>
     </row>
     <row r="724">
@@ -14961,10 +14961,10 @@
         <v>73.88</v>
       </c>
       <c r="E727" t="n">
-        <v>74.48999999999999</v>
+        <v>74.63</v>
       </c>
       <c r="F727" t="n">
-        <v>142563</v>
+        <v>140474</v>
       </c>
     </row>
     <row r="728">
@@ -14981,10 +14981,10 @@
         <v>72.63</v>
       </c>
       <c r="E728" t="n">
-        <v>72.88</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="F728" t="n">
-        <v>154875</v>
+        <v>152160</v>
       </c>
     </row>
     <row r="729">
@@ -15061,10 +15061,10 @@
         <v>74.72</v>
       </c>
       <c r="E732" t="n">
-        <v>76.52</v>
+        <v>76.63</v>
       </c>
       <c r="F732" t="n">
-        <v>102802</v>
+        <v>100583</v>
       </c>
     </row>
     <row r="733">
@@ -15161,10 +15161,10 @@
         <v>78.33</v>
       </c>
       <c r="E737" t="n">
-        <v>78.86</v>
+        <v>78.97</v>
       </c>
       <c r="F737" t="n">
-        <v>105405</v>
+        <v>103669</v>
       </c>
     </row>
     <row r="738">
@@ -15261,10 +15261,10 @@
         <v>79.36</v>
       </c>
       <c r="E742" t="n">
-        <v>81.70999999999999</v>
+        <v>81.65000000000001</v>
       </c>
       <c r="F742" t="n">
-        <v>187943</v>
+        <v>185800</v>
       </c>
     </row>
     <row r="743">
@@ -15281,10 +15281,10 @@
         <v>81.12</v>
       </c>
       <c r="E743" t="n">
-        <v>81.48</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="F743" t="n">
-        <v>160491</v>
+        <v>158852</v>
       </c>
     </row>
     <row r="744">
@@ -15361,10 +15361,10 @@
         <v>83.34999999999999</v>
       </c>
       <c r="E747" t="n">
-        <v>83.61</v>
+        <v>83.45</v>
       </c>
       <c r="F747" t="n">
-        <v>147527</v>
+        <v>145171</v>
       </c>
     </row>
     <row r="748">
@@ -15375,16 +15375,16 @@
         <v>83.68000000000001</v>
       </c>
       <c r="C748" t="n">
-        <v>85.98999999999999</v>
+        <v>85.97</v>
       </c>
       <c r="D748" t="n">
         <v>83.53</v>
       </c>
       <c r="E748" t="n">
-        <v>85.77</v>
+        <v>85.91</v>
       </c>
       <c r="F748" t="n">
-        <v>173518</v>
+        <v>171152</v>
       </c>
     </row>
     <row r="749">
@@ -15458,13 +15458,13 @@
         <v>88.8</v>
       </c>
       <c r="D752" t="n">
-        <v>86.38</v>
+        <v>86.56999999999999</v>
       </c>
       <c r="E752" t="n">
-        <v>86.58</v>
+        <v>86.7</v>
       </c>
       <c r="F752" t="n">
-        <v>169439</v>
+        <v>162890</v>
       </c>
     </row>
     <row r="753">
@@ -15481,10 +15481,10 @@
         <v>85.02</v>
       </c>
       <c r="E753" t="n">
-        <v>86.92</v>
+        <v>86.98</v>
       </c>
       <c r="F753" t="n">
-        <v>225683</v>
+        <v>223066</v>
       </c>
     </row>
     <row r="754">
@@ -15561,10 +15561,10 @@
         <v>87.7</v>
       </c>
       <c r="E757" t="n">
-        <v>88.63</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="F757" t="n">
-        <v>275711</v>
+        <v>270152</v>
       </c>
     </row>
     <row r="758">
@@ -15581,10 +15581,10 @@
         <v>88</v>
       </c>
       <c r="E758" t="n">
-        <v>88.81999999999999</v>
+        <v>88.73</v>
       </c>
       <c r="F758" t="n">
-        <v>278896</v>
+        <v>275262</v>
       </c>
     </row>
     <row r="759">
@@ -15655,16 +15655,16 @@
         <v>88.63</v>
       </c>
       <c r="C762" t="n">
-        <v>90.84999999999999</v>
+        <v>90.73999999999999</v>
       </c>
       <c r="D762" t="n">
         <v>87.59999999999999</v>
       </c>
       <c r="E762" t="n">
-        <v>90.51000000000001</v>
+        <v>90.45999999999999</v>
       </c>
       <c r="F762" t="n">
-        <v>168353</v>
+        <v>163057</v>
       </c>
     </row>
     <row r="763">
@@ -15681,10 +15681,10 @@
         <v>90.67</v>
       </c>
       <c r="E763" t="n">
-        <v>92.14</v>
+        <v>92.54000000000001</v>
       </c>
       <c r="F763" t="n">
-        <v>180147</v>
+        <v>177219</v>
       </c>
     </row>
     <row r="764">
@@ -15761,10 +15761,10 @@
         <v>90.09999999999999</v>
       </c>
       <c r="E767" t="n">
-        <v>90.54000000000001</v>
+        <v>90.66</v>
       </c>
       <c r="F767" t="n">
-        <v>186180</v>
+        <v>183590</v>
       </c>
     </row>
     <row r="768">
@@ -15781,10 +15781,10 @@
         <v>89.66</v>
       </c>
       <c r="E768" t="n">
-        <v>93.8</v>
+        <v>93.81</v>
       </c>
       <c r="F768" t="n">
-        <v>194729</v>
+        <v>189880</v>
       </c>
     </row>
     <row r="769">
@@ -15861,10 +15861,10 @@
         <v>90.34999999999999</v>
       </c>
       <c r="E772" t="n">
-        <v>91.16</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="F772" t="n">
-        <v>212213</v>
+        <v>209775</v>
       </c>
     </row>
     <row r="773">
@@ -15875,7 +15875,7 @@
         <v>90.76000000000001</v>
       </c>
       <c r="C773" t="n">
-        <v>92.28</v>
+        <v>92.15000000000001</v>
       </c>
       <c r="D773" t="n">
         <v>88.64</v>
@@ -15884,7 +15884,7 @@
         <v>91.81</v>
       </c>
       <c r="F773" t="n">
-        <v>194995</v>
+        <v>190175</v>
       </c>
     </row>
     <row r="774">
@@ -15961,10 +15961,10 @@
         <v>93.94</v>
       </c>
       <c r="E777" t="n">
-        <v>95.41</v>
+        <v>95.61</v>
       </c>
       <c r="F777" t="n">
-        <v>313423</v>
+        <v>309076</v>
       </c>
     </row>
     <row r="778">
@@ -15981,10 +15981,10 @@
         <v>92.55</v>
       </c>
       <c r="E778" t="n">
-        <v>94.23</v>
+        <v>94.69</v>
       </c>
       <c r="F778" t="n">
-        <v>237786</v>
+        <v>233541</v>
       </c>
     </row>
     <row r="779">
@@ -16061,10 +16061,10 @@
         <v>108.17</v>
       </c>
       <c r="E782" t="n">
-        <v>109.27</v>
+        <v>109.72</v>
       </c>
       <c r="F782" t="n">
-        <v>233799</v>
+        <v>231064</v>
       </c>
     </row>
     <row r="783">
@@ -16081,10 +16081,10 @@
         <v>108.47</v>
       </c>
       <c r="E783" t="n">
-        <v>116.7</v>
+        <v>117.14</v>
       </c>
       <c r="F783" t="n">
-        <v>210974</v>
+        <v>204618</v>
       </c>
     </row>
     <row r="784">
@@ -16161,10 +16161,10 @@
         <v>107.05</v>
       </c>
       <c r="E787" t="n">
-        <v>107.11</v>
+        <v>107.97</v>
       </c>
       <c r="F787" t="n">
-        <v>173653</v>
+        <v>170481</v>
       </c>
     </row>
     <row r="788">
@@ -16181,10 +16181,10 @@
         <v>104.96</v>
       </c>
       <c r="E788" t="n">
-        <v>110.14</v>
+        <v>110.51</v>
       </c>
       <c r="F788" t="n">
-        <v>157669</v>
+        <v>154891</v>
       </c>
     </row>
     <row r="789">
@@ -16252,19 +16252,19 @@
         <v>44637</v>
       </c>
       <c r="B792" t="n">
-        <v>96.70999999999999</v>
+        <v>96.98</v>
       </c>
       <c r="C792" t="n">
         <v>105.3</v>
       </c>
       <c r="D792" t="n">
-        <v>96.70999999999999</v>
+        <v>96.11</v>
       </c>
       <c r="E792" t="n">
         <v>104.46</v>
       </c>
       <c r="F792" t="n">
-        <v>172578</v>
+        <v>176604</v>
       </c>
     </row>
     <row r="793">
@@ -16272,7 +16272,7 @@
         <v>44638</v>
       </c>
       <c r="B793" t="n">
-        <v>105.16</v>
+        <v>104.55</v>
       </c>
       <c r="C793" t="n">
         <v>107.23</v>
@@ -16284,7 +16284,7 @@
         <v>105.63</v>
       </c>
       <c r="F793" t="n">
-        <v>155067</v>
+        <v>158531</v>
       </c>
     </row>
     <row r="794">
@@ -16352,7 +16352,7 @@
         <v>44644</v>
       </c>
       <c r="B797" t="n">
-        <v>119.49</v>
+        <v>118.08</v>
       </c>
       <c r="C797" t="n">
         <v>120.04</v>
@@ -16364,7 +16364,7 @@
         <v>114.47</v>
       </c>
       <c r="F797" t="n">
-        <v>206598</v>
+        <v>215337</v>
       </c>
     </row>
     <row r="798">
@@ -16372,7 +16372,7 @@
         <v>44645</v>
       </c>
       <c r="B798" t="n">
-        <v>114.52</v>
+        <v>115.3</v>
       </c>
       <c r="C798" t="n">
         <v>117.69</v>
@@ -16384,7 +16384,7 @@
         <v>115.94</v>
       </c>
       <c r="F798" t="n">
-        <v>189095</v>
+        <v>195807</v>
       </c>
     </row>
     <row r="799">
@@ -16461,10 +16461,10 @@
         <v>103.71</v>
       </c>
       <c r="E802" t="n">
-        <v>104.99</v>
+        <v>104.6</v>
       </c>
       <c r="F802" t="n">
-        <v>220967</v>
+        <v>217472</v>
       </c>
     </row>
     <row r="803">
@@ -16481,10 +16481,10 @@
         <v>101.94</v>
       </c>
       <c r="E803" t="n">
-        <v>103.88</v>
+        <v>104.13</v>
       </c>
       <c r="F803" t="n">
-        <v>181758</v>
+        <v>179677</v>
       </c>
     </row>
     <row r="804">
@@ -16561,10 +16561,10 @@
         <v>98.2</v>
       </c>
       <c r="E807" t="n">
-        <v>100.96</v>
+        <v>100.94</v>
       </c>
       <c r="F807" t="n">
-        <v>186163</v>
+        <v>183922</v>
       </c>
     </row>
     <row r="808">
@@ -16581,10 +16581,10 @@
         <v>99.28</v>
       </c>
       <c r="E808" t="n">
-        <v>101.81</v>
+        <v>102.16</v>
       </c>
       <c r="F808" t="n">
-        <v>162819</v>
+        <v>159821</v>
       </c>
     </row>
     <row r="809">
@@ -16661,10 +16661,10 @@
         <v>106.14</v>
       </c>
       <c r="E812" t="n">
-        <v>110.62</v>
+        <v>110.56</v>
       </c>
       <c r="F812" t="n">
-        <v>159785</v>
+        <v>156524</v>
       </c>
     </row>
     <row r="813">
@@ -16741,10 +16741,10 @@
         <v>106.38</v>
       </c>
       <c r="E816" t="n">
-        <v>108</v>
+        <v>107.93</v>
       </c>
       <c r="F816" t="n">
-        <v>188001</v>
+        <v>184241</v>
       </c>
     </row>
     <row r="817">
@@ -16758,13 +16758,13 @@
         <v>108.41</v>
       </c>
       <c r="D817" t="n">
-        <v>105.05</v>
+        <v>105.44</v>
       </c>
       <c r="E817" t="n">
-        <v>105.7</v>
+        <v>105.6</v>
       </c>
       <c r="F817" t="n">
-        <v>165632</v>
+        <v>162032</v>
       </c>
     </row>
     <row r="818">
@@ -16841,10 +16841,10 @@
         <v>102.74</v>
       </c>
       <c r="E821" t="n">
-        <v>106.8</v>
+        <v>107.25</v>
       </c>
       <c r="F821" t="n">
-        <v>170514</v>
+        <v>167676</v>
       </c>
     </row>
     <row r="822">
@@ -16861,10 +16861,10 @@
         <v>105.92</v>
       </c>
       <c r="E822" t="n">
-        <v>106.06</v>
+        <v>106.38</v>
       </c>
       <c r="F822" t="n">
-        <v>186051</v>
+        <v>182972</v>
       </c>
     </row>
     <row r="823">
@@ -16941,10 +16941,10 @@
         <v>108.66</v>
       </c>
       <c r="E826" t="n">
-        <v>110.4</v>
+        <v>110.3</v>
       </c>
       <c r="F826" t="n">
-        <v>201234</v>
+        <v>197687</v>
       </c>
     </row>
     <row r="827">
@@ -16961,10 +16961,10 @@
         <v>109.21</v>
       </c>
       <c r="E827" t="n">
-        <v>112.22</v>
+        <v>112.44</v>
       </c>
       <c r="F827" t="n">
-        <v>207851</v>
+        <v>203469</v>
       </c>
     </row>
     <row r="828">
@@ -17041,10 +17041,10 @@
         <v>103.97</v>
       </c>
       <c r="E831" t="n">
-        <v>106.86</v>
+        <v>107.38</v>
       </c>
       <c r="F831" t="n">
-        <v>243371</v>
+        <v>240901</v>
       </c>
     </row>
     <row r="832">
@@ -17061,10 +17061,10 @@
         <v>106.88</v>
       </c>
       <c r="E832" t="n">
-        <v>109.76</v>
+        <v>110.4</v>
       </c>
       <c r="F832" t="n">
-        <v>193013</v>
+        <v>190398</v>
       </c>
     </row>
     <row r="833">
@@ -17141,10 +17141,10 @@
         <v>104.22</v>
       </c>
       <c r="E836" t="n">
-        <v>109.5</v>
+        <v>109.59</v>
       </c>
       <c r="F836" t="n">
-        <v>250583</v>
+        <v>247278</v>
       </c>
     </row>
     <row r="837">
@@ -17161,10 +17161,10 @@
         <v>108.65</v>
       </c>
       <c r="E837" t="n">
-        <v>110.3</v>
+        <v>110.87</v>
       </c>
       <c r="F837" t="n">
-        <v>202895</v>
+        <v>198948</v>
       </c>
     </row>
     <row r="838">
@@ -17241,10 +17241,10 @@
         <v>110.83</v>
       </c>
       <c r="E841" t="n">
-        <v>114.15</v>
+        <v>114</v>
       </c>
       <c r="F841" t="n">
-        <v>175003</v>
+        <v>171535</v>
       </c>
     </row>
     <row r="842">
@@ -17261,10 +17261,10 @@
         <v>113.01</v>
       </c>
       <c r="E842" t="n">
-        <v>115.01</v>
+        <v>115.42</v>
       </c>
       <c r="F842" t="n">
-        <v>213418</v>
+        <v>210750</v>
       </c>
     </row>
     <row r="843">
@@ -17335,16 +17335,16 @@
         <v>113.88</v>
       </c>
       <c r="C846" t="n">
-        <v>117.74</v>
+        <v>117.57</v>
       </c>
       <c r="D846" t="n">
         <v>111.85</v>
       </c>
       <c r="E846" t="n">
-        <v>117.31</v>
+        <v>117.26</v>
       </c>
       <c r="F846" t="n">
-        <v>138282</v>
+        <v>137013</v>
       </c>
     </row>
     <row r="847">
@@ -17355,16 +17355,16 @@
         <v>117.37</v>
       </c>
       <c r="C847" t="n">
-        <v>120.6</v>
+        <v>120.57</v>
       </c>
       <c r="D847" t="n">
         <v>115.28</v>
       </c>
       <c r="E847" t="n">
-        <v>120.23</v>
+        <v>120.41</v>
       </c>
       <c r="F847" t="n">
-        <v>91626</v>
+        <v>90339</v>
       </c>
     </row>
     <row r="848">
@@ -17441,10 +17441,10 @@
         <v>121.23</v>
       </c>
       <c r="E851" t="n">
-        <v>121.41</v>
+        <v>121.71</v>
       </c>
       <c r="F851" t="n">
-        <v>176648</v>
+        <v>174232</v>
       </c>
     </row>
     <row r="852">
@@ -17461,10 +17461,10 @@
         <v>118.31</v>
       </c>
       <c r="E852" t="n">
-        <v>120.02</v>
+        <v>120.29</v>
       </c>
       <c r="F852" t="n">
-        <v>192334</v>
+        <v>190410</v>
       </c>
     </row>
     <row r="853">
@@ -17541,10 +17541,10 @@
         <v>113.72</v>
       </c>
       <c r="E856" t="n">
-        <v>116.92</v>
+        <v>117.15</v>
       </c>
       <c r="F856" t="n">
-        <v>231324</v>
+        <v>228931</v>
       </c>
     </row>
     <row r="857">
@@ -17561,10 +17561,10 @@
         <v>109.77</v>
       </c>
       <c r="E857" t="n">
-        <v>111.27</v>
+        <v>111.29</v>
       </c>
       <c r="F857" t="n">
-        <v>236868</v>
+        <v>233588</v>
       </c>
     </row>
     <row r="858">
@@ -17641,10 +17641,10 @@
         <v>105.25</v>
       </c>
       <c r="E861" t="n">
-        <v>106.13</v>
+        <v>106.29</v>
       </c>
       <c r="F861" t="n">
-        <v>234952</v>
+        <v>233040</v>
       </c>
     </row>
     <row r="862">
@@ -17661,10 +17661,10 @@
         <v>105.78</v>
       </c>
       <c r="E862" t="n">
-        <v>108.33</v>
+        <v>109.13</v>
       </c>
       <c r="F862" t="n">
-        <v>205227</v>
+        <v>202836</v>
       </c>
     </row>
     <row r="863">
@@ -17741,10 +17741,10 @@
         <v>107.7</v>
       </c>
       <c r="E866" t="n">
-        <v>108.43</v>
+        <v>108.69</v>
       </c>
       <c r="F866" t="n">
-        <v>212070</v>
+        <v>208599</v>
       </c>
     </row>
     <row r="867">
@@ -17761,10 +17761,10 @@
         <v>107.32</v>
       </c>
       <c r="E867" t="n">
-        <v>110.43</v>
+        <v>110.56</v>
       </c>
       <c r="F867" t="n">
-        <v>210630</v>
+        <v>209195</v>
       </c>
     </row>
     <row r="868">
@@ -17841,10 +17841,10 @@
         <v>97.11</v>
       </c>
       <c r="E871" t="n">
-        <v>102.32</v>
+        <v>102.75</v>
       </c>
       <c r="F871" t="n">
-        <v>224620</v>
+        <v>221862</v>
       </c>
     </row>
     <row r="872">
@@ -17861,10 +17861,10 @@
         <v>102.16</v>
       </c>
       <c r="E872" t="n">
-        <v>105.2</v>
+        <v>105.32</v>
       </c>
       <c r="F872" t="n">
-        <v>237030</v>
+        <v>235167</v>
       </c>
     </row>
     <row r="873">
@@ -17941,10 +17941,10 @@
         <v>92.42</v>
       </c>
       <c r="E876" t="n">
-        <v>97.12</v>
+        <v>97.17</v>
       </c>
       <c r="F876" t="n">
-        <v>217836</v>
+        <v>215919</v>
       </c>
     </row>
     <row r="877">
@@ -17961,10 +17961,10 @@
         <v>95.59</v>
       </c>
       <c r="E877" t="n">
-        <v>97.98</v>
+        <v>98.34999999999999</v>
       </c>
       <c r="F877" t="n">
-        <v>203134</v>
+        <v>200270</v>
       </c>
     </row>
     <row r="878">
@@ -18041,10 +18041,10 @@
         <v>97.86</v>
       </c>
       <c r="E881" t="n">
-        <v>99.93000000000001</v>
+        <v>100.04</v>
       </c>
       <c r="F881" t="n">
-        <v>229298</v>
+        <v>227231</v>
       </c>
     </row>
     <row r="882">
@@ -18061,10 +18061,10 @@
         <v>97.90000000000001</v>
       </c>
       <c r="E882" t="n">
-        <v>98.98999999999999</v>
+        <v>98.67</v>
       </c>
       <c r="F882" t="n">
-        <v>226135</v>
+        <v>222921</v>
       </c>
     </row>
     <row r="883">
@@ -18141,10 +18141,10 @@
         <v>100.74</v>
       </c>
       <c r="E886" t="n">
-        <v>101.99</v>
+        <v>101.93</v>
       </c>
       <c r="F886" t="n">
-        <v>132446</v>
+        <v>130398</v>
       </c>
     </row>
     <row r="887">
@@ -18161,10 +18161,10 @@
         <v>101.27</v>
       </c>
       <c r="E887" t="n">
-        <v>103.1</v>
+        <v>103.21</v>
       </c>
       <c r="F887" t="n">
-        <v>113461</v>
+        <v>112179</v>
       </c>
     </row>
     <row r="888">
@@ -18238,13 +18238,13 @@
         <v>97.17</v>
       </c>
       <c r="D891" t="n">
-        <v>92.5</v>
+        <v>92.73</v>
       </c>
       <c r="E891" t="n">
-        <v>92.52</v>
+        <v>93.38</v>
       </c>
       <c r="F891" t="n">
-        <v>162676</v>
+        <v>160629</v>
       </c>
     </row>
     <row r="892">
@@ -18261,10 +18261,10 @@
         <v>92.15000000000001</v>
       </c>
       <c r="E892" t="n">
-        <v>93.51000000000001</v>
+        <v>93.69</v>
       </c>
       <c r="F892" t="n">
-        <v>157322</v>
+        <v>155701</v>
       </c>
     </row>
     <row r="893">
@@ -18341,10 +18341,10 @@
         <v>96.08</v>
       </c>
       <c r="E896" t="n">
-        <v>98.31</v>
+        <v>98.66</v>
       </c>
       <c r="F896" t="n">
-        <v>140818</v>
+        <v>139272</v>
       </c>
     </row>
     <row r="897">
@@ -18361,10 +18361,10 @@
         <v>96.26000000000001</v>
       </c>
       <c r="E897" t="n">
-        <v>96.89</v>
+        <v>97.3</v>
       </c>
       <c r="F897" t="n">
-        <v>145858</v>
+        <v>144235</v>
       </c>
     </row>
     <row r="898">
@@ -18441,10 +18441,10 @@
         <v>92.55</v>
       </c>
       <c r="E901" t="n">
-        <v>95.56</v>
+        <v>95.93000000000001</v>
       </c>
       <c r="F901" t="n">
-        <v>123861</v>
+        <v>122235</v>
       </c>
     </row>
     <row r="902">
@@ -18461,10 +18461,10 @@
         <v>93.7</v>
       </c>
       <c r="E902" t="n">
-        <v>95.08</v>
+        <v>95.52</v>
       </c>
       <c r="F902" t="n">
-        <v>126696</v>
+        <v>125387</v>
       </c>
     </row>
     <row r="903">
@@ -18541,10 +18541,10 @@
         <v>98.23</v>
       </c>
       <c r="E906" t="n">
-        <v>98.68000000000001</v>
+        <v>99.05</v>
       </c>
       <c r="F906" t="n">
-        <v>115830</v>
+        <v>114289</v>
       </c>
     </row>
     <row r="907">
@@ -18561,10 +18561,10 @@
         <v>96.92</v>
       </c>
       <c r="E907" t="n">
-        <v>98.56999999999999</v>
+        <v>98.70999999999999</v>
       </c>
       <c r="F907" t="n">
-        <v>128357</v>
+        <v>127109</v>
       </c>
     </row>
     <row r="908">
@@ -18641,10 +18641,10 @@
         <v>91.58</v>
       </c>
       <c r="E911" t="n">
-        <v>91.59</v>
+        <v>91.75</v>
       </c>
       <c r="F911" t="n">
-        <v>172611</v>
+        <v>171383</v>
       </c>
     </row>
     <row r="912">
@@ -18661,10 +18661,10 @@
         <v>92.41</v>
       </c>
       <c r="E912" t="n">
-        <v>92.83</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="F912" t="n">
-        <v>164349</v>
+        <v>162523</v>
       </c>
     </row>
     <row r="913">
@@ -18741,10 +18741,10 @@
         <v>86.86</v>
       </c>
       <c r="E916" t="n">
-        <v>87.73999999999999</v>
+        <v>88.03</v>
       </c>
       <c r="F916" t="n">
-        <v>175783</v>
+        <v>174104</v>
       </c>
     </row>
     <row r="917">
@@ -18761,10 +18761,10 @@
         <v>88.09</v>
       </c>
       <c r="E917" t="n">
-        <v>91.42</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="F917" t="n">
-        <v>139210</v>
+        <v>137562</v>
       </c>
     </row>
     <row r="918">
@@ -18841,10 +18841,10 @@
         <v>89.39</v>
       </c>
       <c r="E921" t="n">
-        <v>89.78</v>
+        <v>90.08</v>
       </c>
       <c r="F921" t="n">
-        <v>179533</v>
+        <v>177670</v>
       </c>
     </row>
     <row r="922">
@@ -18861,10 +18861,10 @@
         <v>89.37</v>
       </c>
       <c r="E922" t="n">
-        <v>90.36</v>
+        <v>90.58</v>
       </c>
       <c r="F922" t="n">
-        <v>177056</v>
+        <v>175462</v>
       </c>
     </row>
     <row r="923">
@@ -18941,10 +18941,10 @@
         <v>88.38</v>
       </c>
       <c r="E926" t="n">
-        <v>89.48999999999999</v>
+        <v>89.53</v>
       </c>
       <c r="F926" t="n">
-        <v>169282</v>
+        <v>167346</v>
       </c>
     </row>
     <row r="927">
@@ -18961,10 +18961,10 @@
         <v>84.61</v>
       </c>
       <c r="E927" t="n">
-        <v>85.65000000000001</v>
+        <v>85.41</v>
       </c>
       <c r="F927" t="n">
-        <v>159709</v>
+        <v>157358</v>
       </c>
     </row>
     <row r="928">
@@ -19041,10 +19041,10 @@
         <v>85.98</v>
       </c>
       <c r="E931" t="n">
-        <v>87.22</v>
+        <v>87.20999999999999</v>
       </c>
       <c r="F931" t="n">
-        <v>184095</v>
+        <v>182346</v>
       </c>
     </row>
     <row r="932">
@@ -19061,10 +19061,10 @@
         <v>84.73999999999999</v>
       </c>
       <c r="E932" t="n">
-        <v>85.04000000000001</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="F932" t="n">
-        <v>174184</v>
+        <v>172540</v>
       </c>
     </row>
     <row r="933">
@@ -19141,10 +19141,10 @@
         <v>92.09</v>
       </c>
       <c r="E936" t="n">
-        <v>94.16</v>
+        <v>94.31999999999999</v>
       </c>
       <c r="F936" t="n">
-        <v>136157</v>
+        <v>134269</v>
       </c>
     </row>
     <row r="937">
@@ -19161,10 +19161,10 @@
         <v>93.25</v>
       </c>
       <c r="E937" t="n">
-        <v>97.59</v>
+        <v>96.95</v>
       </c>
       <c r="F937" t="n">
-        <v>161145</v>
+        <v>158303</v>
       </c>
     </row>
     <row r="938">
@@ -19241,10 +19241,10 @@
         <v>90.18000000000001</v>
       </c>
       <c r="E941" t="n">
-        <v>93.67</v>
+        <v>93.61</v>
       </c>
       <c r="F941" t="n">
-        <v>189909</v>
+        <v>187899</v>
       </c>
     </row>
     <row r="942">
@@ -19261,10 +19261,10 @@
         <v>90.34</v>
       </c>
       <c r="E942" t="n">
-        <v>90.66</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="F942" t="n">
-        <v>186342</v>
+        <v>184164</v>
       </c>
     </row>
     <row r="943">
@@ -19341,10 +19341,10 @@
         <v>90.34</v>
       </c>
       <c r="E946" t="n">
-        <v>91.11</v>
+        <v>91</v>
       </c>
       <c r="F946" t="n">
-        <v>172151</v>
+        <v>169394</v>
       </c>
     </row>
     <row r="947">
@@ -19361,10 +19361,10 @@
         <v>89.40000000000001</v>
       </c>
       <c r="E947" t="n">
-        <v>91.58</v>
+        <v>91.7</v>
       </c>
       <c r="F947" t="n">
-        <v>170499</v>
+        <v>168937</v>
       </c>
     </row>
     <row r="948">
@@ -19441,10 +19441,10 @@
         <v>93.06999999999999</v>
       </c>
       <c r="E951" t="n">
-        <v>94.45999999999999</v>
+        <v>94.91</v>
       </c>
       <c r="F951" t="n">
-        <v>135151</v>
+        <v>130846</v>
       </c>
     </row>
     <row r="952">
@@ -19461,10 +19461,10 @@
         <v>92.81999999999999</v>
       </c>
       <c r="E952" t="n">
-        <v>93.95</v>
+        <v>93.81</v>
       </c>
       <c r="F952" t="n">
-        <v>135363</v>
+        <v>133960</v>
       </c>
     </row>
     <row r="953">
@@ -19532,7 +19532,7 @@
         <v>44868</v>
       </c>
       <c r="B956" t="n">
-        <v>94.84</v>
+        <v>94.81</v>
       </c>
       <c r="C956" t="n">
         <v>95.45</v>
@@ -19544,7 +19544,7 @@
         <v>93.92</v>
       </c>
       <c r="F956" t="n">
-        <v>141621</v>
+        <v>143503</v>
       </c>
     </row>
     <row r="957">
@@ -19552,19 +19552,19 @@
         <v>44869</v>
       </c>
       <c r="B957" t="n">
-        <v>93.94</v>
+        <v>93.98</v>
       </c>
       <c r="C957" t="n">
         <v>98.23999999999999</v>
       </c>
       <c r="D957" t="n">
-        <v>93.94</v>
+        <v>93.76000000000001</v>
       </c>
       <c r="E957" t="n">
         <v>98.01000000000001</v>
       </c>
       <c r="F957" t="n">
-        <v>179958</v>
+        <v>182009</v>
       </c>
     </row>
     <row r="958">
@@ -19641,10 +19641,10 @@
         <v>90.97</v>
       </c>
       <c r="E961" t="n">
-        <v>92.47</v>
+        <v>92.69</v>
       </c>
       <c r="F961" t="n">
-        <v>170823</v>
+        <v>168690</v>
       </c>
     </row>
     <row r="962">
@@ -19661,10 +19661,10 @@
         <v>92.79000000000001</v>
       </c>
       <c r="E962" t="n">
-        <v>94.95999999999999</v>
+        <v>95.04000000000001</v>
       </c>
       <c r="F962" t="n">
-        <v>165782</v>
+        <v>163940</v>
       </c>
     </row>
     <row r="963">
@@ -19741,10 +19741,10 @@
         <v>88.72</v>
       </c>
       <c r="E966" t="n">
-        <v>89.34999999999999</v>
+        <v>89.28</v>
       </c>
       <c r="F966" t="n">
-        <v>159560</v>
+        <v>157265</v>
       </c>
     </row>
     <row r="967">
@@ -19761,10 +19761,10 @@
         <v>85.41</v>
       </c>
       <c r="E967" t="n">
-        <v>87.5</v>
+        <v>87.45</v>
       </c>
       <c r="F967" t="n">
-        <v>162655</v>
+        <v>160818</v>
       </c>
     </row>
     <row r="968">
@@ -19941,10 +19941,10 @@
         <v>86.26000000000001</v>
       </c>
       <c r="E976" t="n">
-        <v>86.98</v>
+        <v>86.84</v>
       </c>
       <c r="F976" t="n">
-        <v>136930</v>
+        <v>135345</v>
       </c>
     </row>
     <row r="977">
@@ -19961,10 +19961,10 @@
         <v>85.17</v>
       </c>
       <c r="E977" t="n">
-        <v>85.90000000000001</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="F977" t="n">
-        <v>137359</v>
+        <v>135815</v>
       </c>
     </row>
     <row r="978">
@@ -20041,10 +20041,10 @@
         <v>75.92</v>
       </c>
       <c r="E981" t="n">
-        <v>76.61</v>
+        <v>76.27</v>
       </c>
       <c r="F981" t="n">
-        <v>167594</v>
+        <v>165742</v>
       </c>
     </row>
     <row r="982">
@@ -20061,10 +20061,10 @@
         <v>75.34999999999999</v>
       </c>
       <c r="E982" t="n">
-        <v>76.79000000000001</v>
+        <v>76.76000000000001</v>
       </c>
       <c r="F982" t="n">
-        <v>153224</v>
+        <v>151706</v>
       </c>
     </row>
     <row r="983">
@@ -20141,10 +20141,10 @@
         <v>80.86</v>
       </c>
       <c r="E986" t="n">
-        <v>81.54000000000001</v>
+        <v>81.39</v>
       </c>
       <c r="F986" t="n">
-        <v>151489</v>
+        <v>149384</v>
       </c>
     </row>
     <row r="987">
@@ -20161,10 +20161,10 @@
         <v>78.61</v>
       </c>
       <c r="E987" t="n">
-        <v>79.44</v>
+        <v>79.36</v>
       </c>
       <c r="F987" t="n">
-        <v>151197</v>
+        <v>149990</v>
       </c>
     </row>
     <row r="988">
@@ -20241,10 +20241,10 @@
         <v>81.28</v>
       </c>
       <c r="E991" t="n">
-        <v>82.20999999999999</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="F991" t="n">
-        <v>95617</v>
+        <v>94348</v>
       </c>
     </row>
     <row r="992">
@@ -20321,10 +20321,10 @@
         <v>81.81999999999999</v>
       </c>
       <c r="E995" t="n">
-        <v>83.63</v>
+        <v>83.68000000000001</v>
       </c>
       <c r="F995" t="n">
-        <v>110699</v>
+        <v>109380</v>
       </c>
     </row>
     <row r="996">
@@ -20401,10 +20401,10 @@
         <v>77.63</v>
       </c>
       <c r="E999" t="n">
-        <v>78.8</v>
+        <v>78.68000000000001</v>
       </c>
       <c r="F999" t="n">
-        <v>150672</v>
+        <v>149266</v>
       </c>
     </row>
     <row r="1000">
@@ -20424,7 +20424,7 @@
         <v>78.51000000000001</v>
       </c>
       <c r="F1000" t="n">
-        <v>148389</v>
+        <v>147017</v>
       </c>
     </row>
     <row r="1001">
@@ -20501,10 +20501,10 @@
         <v>82.43000000000001</v>
       </c>
       <c r="E1004" t="n">
-        <v>83.84999999999999</v>
+        <v>83.91</v>
       </c>
       <c r="F1004" t="n">
-        <v>142735</v>
+        <v>141086</v>
       </c>
     </row>
     <row r="1005">
@@ -20515,16 +20515,16 @@
         <v>83.91</v>
       </c>
       <c r="C1005" t="n">
-        <v>85.61</v>
+        <v>85.55</v>
       </c>
       <c r="D1005" t="n">
         <v>83.55</v>
       </c>
       <c r="E1005" t="n">
-        <v>85.47</v>
+        <v>85.48</v>
       </c>
       <c r="F1005" t="n">
-        <v>131152</v>
+        <v>129757</v>
       </c>
     </row>
     <row r="1006">
@@ -20601,10 +20601,10 @@
         <v>83.95999999999999</v>
       </c>
       <c r="E1009" t="n">
-        <v>86.34</v>
+        <v>86.31999999999999</v>
       </c>
       <c r="F1009" t="n">
-        <v>144410</v>
+        <v>142583</v>
       </c>
     </row>
     <row r="1010">
@@ -20621,10 +20621,10 @@
         <v>85.69</v>
       </c>
       <c r="E1010" t="n">
-        <v>87.59</v>
+        <v>87.75</v>
       </c>
       <c r="F1010" t="n">
-        <v>125225</v>
+        <v>123973</v>
       </c>
     </row>
     <row r="1011">
@@ -20701,10 +20701,10 @@
         <v>85.75</v>
       </c>
       <c r="E1014" t="n">
-        <v>87.29000000000001</v>
+        <v>87.31</v>
       </c>
       <c r="F1014" t="n">
-        <v>96051</v>
+        <v>95077</v>
       </c>
     </row>
     <row r="1015">
@@ -20721,10 +20721,10 @@
         <v>85.48</v>
       </c>
       <c r="E1015" t="n">
-        <v>86.01000000000001</v>
+        <v>86.04000000000001</v>
       </c>
       <c r="F1015" t="n">
-        <v>110922</v>
+        <v>109841</v>
       </c>
     </row>
     <row r="1016">
@@ -20801,10 +20801,10 @@
         <v>81.2</v>
       </c>
       <c r="E1019" t="n">
-        <v>82.12</v>
+        <v>81.98</v>
       </c>
       <c r="F1019" t="n">
-        <v>150704</v>
+        <v>146732</v>
       </c>
     </row>
     <row r="1020">
@@ -20818,13 +20818,13 @@
         <v>84.11</v>
       </c>
       <c r="D1020" t="n">
-        <v>79.53</v>
+        <v>79.62</v>
       </c>
       <c r="E1020" t="n">
-        <v>79.62</v>
+        <v>79.64</v>
       </c>
       <c r="F1020" t="n">
-        <v>163093</v>
+        <v>161681</v>
       </c>
     </row>
     <row r="1021">
@@ -20901,10 +20901,10 @@
         <v>82.86</v>
       </c>
       <c r="E1024" t="n">
-        <v>83.95</v>
+        <v>83.88</v>
       </c>
       <c r="F1024" t="n">
-        <v>144061</v>
+        <v>142722</v>
       </c>
     </row>
     <row r="1025">
@@ -20921,10 +20921,10 @@
         <v>83.66</v>
       </c>
       <c r="E1025" t="n">
-        <v>86.2</v>
+        <v>86.29000000000001</v>
       </c>
       <c r="F1025" t="n">
-        <v>156718</v>
+        <v>155562</v>
       </c>
     </row>
     <row r="1026">
@@ -20998,13 +20998,13 @@
         <v>85.90000000000001</v>
       </c>
       <c r="D1029" t="n">
-        <v>84.28</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="E1029" t="n">
-        <v>84.31</v>
+        <v>84.37</v>
       </c>
       <c r="F1029" t="n">
-        <v>129946</v>
+        <v>128382</v>
       </c>
     </row>
     <row r="1030">
@@ -21021,10 +21021,10 @@
         <v>81.55</v>
       </c>
       <c r="E1030" t="n">
-        <v>82.72</v>
+        <v>82.68000000000001</v>
       </c>
       <c r="F1030" t="n">
-        <v>142763</v>
+        <v>141607</v>
       </c>
     </row>
     <row r="1031">
@@ -21101,10 +21101,10 @@
         <v>80.27</v>
       </c>
       <c r="E1034" t="n">
-        <v>82.18000000000001</v>
+        <v>82.12</v>
       </c>
       <c r="F1034" t="n">
-        <v>108091</v>
+        <v>107083</v>
       </c>
     </row>
     <row r="1035">
@@ -21121,10 +21121,10 @@
         <v>80.7</v>
       </c>
       <c r="E1035" t="n">
-        <v>82.77</v>
+        <v>82.94</v>
       </c>
       <c r="F1035" t="n">
-        <v>130526</v>
+        <v>129354</v>
       </c>
     </row>
     <row r="1036">
@@ -21201,10 +21201,10 @@
         <v>83.66</v>
       </c>
       <c r="E1039" t="n">
-        <v>84.23</v>
+        <v>84.34</v>
       </c>
       <c r="F1039" t="n">
-        <v>115434</v>
+        <v>114302</v>
       </c>
     </row>
     <row r="1040">
@@ -21215,16 +21215,16 @@
         <v>84.37</v>
       </c>
       <c r="C1040" t="n">
-        <v>85.81</v>
+        <v>85.8</v>
       </c>
       <c r="D1040" t="n">
         <v>82.2</v>
       </c>
       <c r="E1040" t="n">
-        <v>85.73999999999999</v>
+        <v>85.72</v>
       </c>
       <c r="F1040" t="n">
-        <v>120888</v>
+        <v>119970</v>
       </c>
     </row>
     <row r="1041">
@@ -21301,10 +21301,10 @@
         <v>81.16</v>
       </c>
       <c r="E1044" t="n">
-        <v>81.23</v>
+        <v>81.26000000000001</v>
       </c>
       <c r="F1044" t="n">
-        <v>121276</v>
+        <v>120126</v>
       </c>
     </row>
     <row r="1045">
@@ -21321,10 +21321,10 @@
         <v>80.47</v>
       </c>
       <c r="E1045" t="n">
-        <v>82.38</v>
+        <v>82.33</v>
       </c>
       <c r="F1045" t="n">
-        <v>172647</v>
+        <v>171433</v>
       </c>
     </row>
     <row r="1046">
@@ -21392,7 +21392,7 @@
         <v>45001</v>
       </c>
       <c r="B1049" t="n">
-        <v>74.59999999999999</v>
+        <v>74.04000000000001</v>
       </c>
       <c r="C1049" t="n">
         <v>75.23</v>
@@ -21404,7 +21404,7 @@
         <v>74.25</v>
       </c>
       <c r="F1049" t="n">
-        <v>206406</v>
+        <v>210322</v>
       </c>
     </row>
     <row r="1050">
@@ -21412,7 +21412,7 @@
         <v>45002</v>
       </c>
       <c r="B1050" t="n">
-        <v>74.41</v>
+        <v>74.45</v>
       </c>
       <c r="C1050" t="n">
         <v>75.65000000000001</v>
@@ -21424,7 +21424,7 @@
         <v>72.3</v>
       </c>
       <c r="F1050" t="n">
-        <v>194486</v>
+        <v>196053</v>
       </c>
     </row>
     <row r="1051">
@@ -21492,7 +21492,7 @@
         <v>45008</v>
       </c>
       <c r="B1054" t="n">
-        <v>75.73</v>
+        <v>75.58</v>
       </c>
       <c r="C1054" t="n">
         <v>77.09</v>
@@ -21504,7 +21504,7 @@
         <v>74.98999999999999</v>
       </c>
       <c r="F1054" t="n">
-        <v>132462</v>
+        <v>134971</v>
       </c>
     </row>
     <row r="1055">
@@ -21512,7 +21512,7 @@
         <v>45009</v>
       </c>
       <c r="B1055" t="n">
-        <v>74.92</v>
+        <v>75.08</v>
       </c>
       <c r="C1055" t="n">
         <v>75.89</v>
@@ -21524,7 +21524,7 @@
         <v>74.52</v>
       </c>
       <c r="F1055" t="n">
-        <v>158419</v>
+        <v>160608</v>
       </c>
     </row>
     <row r="1056">
@@ -21601,10 +21601,10 @@
         <v>77.13</v>
       </c>
       <c r="E1059" t="n">
-        <v>78.43000000000001</v>
+        <v>78.47</v>
       </c>
       <c r="F1059" t="n">
-        <v>102975</v>
+        <v>101875</v>
       </c>
     </row>
     <row r="1060">
@@ -21621,10 +21621,10 @@
         <v>77.79000000000001</v>
       </c>
       <c r="E1060" t="n">
-        <v>79.76000000000001</v>
+        <v>79.73</v>
       </c>
       <c r="F1060" t="n">
-        <v>103341</v>
+        <v>102278</v>
       </c>
     </row>
     <row r="1061">
@@ -21701,10 +21701,10 @@
         <v>83.89</v>
       </c>
       <c r="E1064" t="n">
-        <v>84.62</v>
+        <v>84.73</v>
       </c>
       <c r="F1064" t="n">
-        <v>128978</v>
+        <v>127887</v>
       </c>
     </row>
     <row r="1065">
@@ -21781,10 +21781,10 @@
         <v>85.78</v>
       </c>
       <c r="E1068" t="n">
-        <v>86.03</v>
+        <v>85.98</v>
       </c>
       <c r="F1068" t="n">
-        <v>107747</v>
+        <v>106530</v>
       </c>
     </row>
     <row r="1069">
@@ -21801,10 +21801,10 @@
         <v>85.27</v>
       </c>
       <c r="E1069" t="n">
-        <v>86.12</v>
+        <v>86.13</v>
       </c>
       <c r="F1069" t="n">
-        <v>119789</v>
+        <v>118921</v>
       </c>
     </row>
     <row r="1070">
@@ -21878,13 +21878,13 @@
         <v>82.59999999999999</v>
       </c>
       <c r="D1073" t="n">
-        <v>80.48999999999999</v>
+        <v>80.51000000000001</v>
       </c>
       <c r="E1073" t="n">
-        <v>80.48999999999999</v>
+        <v>80.62</v>
       </c>
       <c r="F1073" t="n">
-        <v>100157</v>
+        <v>99083</v>
       </c>
     </row>
     <row r="1074">
@@ -21901,10 +21901,10 @@
         <v>80.2</v>
       </c>
       <c r="E1074" t="n">
-        <v>81.53</v>
+        <v>81.38</v>
       </c>
       <c r="F1074" t="n">
-        <v>89589</v>
+        <v>88877</v>
       </c>
     </row>
     <row r="1075">
@@ -21981,10 +21981,10 @@
         <v>77.3</v>
       </c>
       <c r="E1078" t="n">
-        <v>78.17</v>
+        <v>78.23</v>
       </c>
       <c r="F1078" t="n">
-        <v>114226</v>
+        <v>112919</v>
       </c>
     </row>
     <row r="1079">
@@ -22001,10 +22001,10 @@
         <v>77.44</v>
       </c>
       <c r="E1079" t="n">
-        <v>80.08</v>
+        <v>80.20999999999999</v>
       </c>
       <c r="F1079" t="n">
-        <v>111593</v>
+        <v>110643</v>
       </c>
     </row>
     <row r="1080">
@@ -22081,10 +22081,10 @@
         <v>71.34</v>
       </c>
       <c r="E1083" t="n">
-        <v>72.38</v>
+        <v>72.34</v>
       </c>
       <c r="F1083" t="n">
-        <v>176458</v>
+        <v>175075</v>
       </c>
     </row>
     <row r="1084">
@@ -22101,10 +22101,10 @@
         <v>72.31999999999999</v>
       </c>
       <c r="E1084" t="n">
-        <v>75.15000000000001</v>
+        <v>75.22</v>
       </c>
       <c r="F1084" t="n">
-        <v>122688</v>
+        <v>121559</v>
       </c>
     </row>
     <row r="1085">
@@ -22181,10 +22181,10 @@
         <v>74.5</v>
       </c>
       <c r="E1088" t="n">
-        <v>75.26000000000001</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="F1088" t="n">
-        <v>142391</v>
+        <v>141443</v>
       </c>
     </row>
     <row r="1089">
@@ -22201,10 +22201,10 @@
         <v>73.84999999999999</v>
       </c>
       <c r="E1089" t="n">
-        <v>73.93000000000001</v>
+        <v>74.02</v>
       </c>
       <c r="F1089" t="n">
-        <v>144762</v>
+        <v>143925</v>
       </c>
     </row>
     <row r="1090">
@@ -22281,10 +22281,10 @@
         <v>75.42</v>
       </c>
       <c r="E1093" t="n">
-        <v>75.84</v>
+        <v>75.89</v>
       </c>
       <c r="F1093" t="n">
-        <v>98116</v>
+        <v>97144</v>
       </c>
     </row>
     <row r="1094">
@@ -22301,10 +22301,10 @@
         <v>75.01000000000001</v>
       </c>
       <c r="E1094" t="n">
-        <v>75.59999999999999</v>
+        <v>75.75</v>
       </c>
       <c r="F1094" t="n">
-        <v>108218</v>
+        <v>107224</v>
       </c>
     </row>
     <row r="1095">
@@ -22381,10 +22381,10 @@
         <v>75.08</v>
       </c>
       <c r="E1098" t="n">
-        <v>75.95999999999999</v>
+        <v>76.13</v>
       </c>
       <c r="F1098" t="n">
-        <v>95663</v>
+        <v>94656</v>
       </c>
     </row>
     <row r="1099">
@@ -22401,10 +22401,10 @@
         <v>75.62</v>
       </c>
       <c r="E1099" t="n">
-        <v>77.14</v>
+        <v>77.03</v>
       </c>
       <c r="F1099" t="n">
-        <v>86227</v>
+        <v>85632</v>
       </c>
     </row>
     <row r="1100">
@@ -22481,10 +22481,10 @@
         <v>72</v>
       </c>
       <c r="E1103" t="n">
-        <v>74.25</v>
+        <v>74.17</v>
       </c>
       <c r="F1103" t="n">
-        <v>124084</v>
+        <v>122959</v>
       </c>
     </row>
     <row r="1104">
@@ -22501,10 +22501,10 @@
         <v>74.13</v>
       </c>
       <c r="E1104" t="n">
-        <v>76.13</v>
+        <v>76.3</v>
       </c>
       <c r="F1104" t="n">
-        <v>111881</v>
+        <v>110715</v>
       </c>
     </row>
     <row r="1105">
@@ -22581,10 +22581,10 @@
         <v>73.52</v>
       </c>
       <c r="E1108" t="n">
-        <v>75.44</v>
+        <v>75.56999999999999</v>
       </c>
       <c r="F1108" t="n">
-        <v>142206</v>
+        <v>141391</v>
       </c>
     </row>
     <row r="1109">
@@ -22601,10 +22601,10 @@
         <v>74.67</v>
       </c>
       <c r="E1109" t="n">
-        <v>74.88</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="F1109" t="n">
-        <v>120995</v>
+        <v>120105</v>
       </c>
     </row>
     <row r="1110">
@@ -22681,10 +22681,10 @@
         <v>72.84999999999999</v>
       </c>
       <c r="E1113" t="n">
-        <v>75.52</v>
+        <v>75.56</v>
       </c>
       <c r="F1113" t="n">
-        <v>105947</v>
+        <v>104970</v>
       </c>
     </row>
     <row r="1114">
@@ -22701,10 +22701,10 @@
         <v>75.09999999999999</v>
       </c>
       <c r="E1114" t="n">
-        <v>76.23</v>
+        <v>76.47</v>
       </c>
       <c r="F1114" t="n">
-        <v>111184</v>
+        <v>109963</v>
       </c>
     </row>
     <row r="1115">
@@ -22781,10 +22781,10 @@
         <v>73.75</v>
       </c>
       <c r="E1118" t="n">
-        <v>74.3</v>
+        <v>74.2</v>
       </c>
       <c r="F1118" t="n">
-        <v>89974</v>
+        <v>89166</v>
       </c>
     </row>
     <row r="1119">
@@ -22795,16 +22795,16 @@
         <v>74.2</v>
       </c>
       <c r="C1119" t="n">
-        <v>74.45999999999999</v>
+        <v>74.36</v>
       </c>
       <c r="D1119" t="n">
         <v>72.25</v>
       </c>
       <c r="E1119" t="n">
-        <v>74.34</v>
+        <v>74.09</v>
       </c>
       <c r="F1119" t="n">
-        <v>101628</v>
+        <v>100773</v>
       </c>
     </row>
     <row r="1120">
@@ -22881,10 +22881,10 @@
         <v>73.56</v>
       </c>
       <c r="E1123" t="n">
-        <v>74.34999999999999</v>
+        <v>74.44</v>
       </c>
       <c r="F1123" t="n">
-        <v>118860</v>
+        <v>118096</v>
       </c>
     </row>
     <row r="1124">
@@ -22901,10 +22901,10 @@
         <v>74.23</v>
       </c>
       <c r="E1124" t="n">
-        <v>75.06999999999999</v>
+        <v>75.26000000000001</v>
       </c>
       <c r="F1124" t="n">
-        <v>108012</v>
+        <v>107062</v>
       </c>
     </row>
     <row r="1125">
@@ -22981,10 +22981,10 @@
         <v>74.94</v>
       </c>
       <c r="E1128" t="n">
-        <v>76.44</v>
+        <v>76.47</v>
       </c>
       <c r="F1128" t="n">
-        <v>121613</v>
+        <v>120498</v>
       </c>
     </row>
     <row r="1129">
@@ -23001,10 +23001,10 @@
         <v>75.91</v>
       </c>
       <c r="E1129" t="n">
-        <v>78.12</v>
+        <v>78.13</v>
       </c>
       <c r="F1129" t="n">
-        <v>101260</v>
+        <v>99946</v>
       </c>
     </row>
     <row r="1130">
@@ -23075,16 +23075,16 @@
         <v>79.95999999999999</v>
       </c>
       <c r="C1133" t="n">
-        <v>81.5</v>
+        <v>81.48999999999999</v>
       </c>
       <c r="D1133" t="n">
         <v>79.69</v>
       </c>
       <c r="E1133" t="n">
-        <v>81.37</v>
+        <v>81.48</v>
       </c>
       <c r="F1133" t="n">
-        <v>97805</v>
+        <v>96443</v>
       </c>
     </row>
     <row r="1134">
@@ -23098,13 +23098,13 @@
         <v>81.42</v>
       </c>
       <c r="D1134" t="n">
-        <v>79.34999999999999</v>
+        <v>79.44</v>
       </c>
       <c r="E1134" t="n">
-        <v>79.45</v>
+        <v>79.54000000000001</v>
       </c>
       <c r="F1134" t="n">
-        <v>99161</v>
+        <v>98000</v>
       </c>
     </row>
     <row r="1135">
@@ -23181,10 +23181,10 @@
         <v>78.56999999999999</v>
       </c>
       <c r="E1138" t="n">
-        <v>79.48</v>
+        <v>79.54000000000001</v>
       </c>
       <c r="F1138" t="n">
-        <v>77506</v>
+        <v>76777</v>
       </c>
     </row>
     <row r="1139">
@@ -23201,10 +23201,10 @@
         <v>79.51000000000001</v>
       </c>
       <c r="E1139" t="n">
-        <v>80.5</v>
+        <v>80.69</v>
       </c>
       <c r="F1139" t="n">
-        <v>70745</v>
+        <v>69907</v>
       </c>
     </row>
     <row r="1140">
@@ -23281,10 +23281,10 @@
         <v>82.54000000000001</v>
       </c>
       <c r="E1143" t="n">
-        <v>83.3</v>
+        <v>83.42</v>
       </c>
       <c r="F1143" t="n">
-        <v>101885</v>
+        <v>100960</v>
       </c>
     </row>
     <row r="1144">
@@ -23301,10 +23301,10 @@
         <v>82.78</v>
       </c>
       <c r="E1144" t="n">
-        <v>84.34999999999999</v>
+        <v>84.26000000000001</v>
       </c>
       <c r="F1144" t="n">
-        <v>96933</v>
+        <v>96080</v>
       </c>
     </row>
     <row r="1145">
@@ -23381,10 +23381,10 @@
         <v>82.23</v>
       </c>
       <c r="E1148" t="n">
-        <v>85.04000000000001</v>
+        <v>85.13</v>
       </c>
       <c r="F1148" t="n">
-        <v>124232</v>
+        <v>122532</v>
       </c>
     </row>
     <row r="1149">
@@ -23401,10 +23401,10 @@
         <v>84.89</v>
       </c>
       <c r="E1149" t="n">
-        <v>85.81</v>
+        <v>85.84</v>
       </c>
       <c r="F1149" t="n">
-        <v>104424</v>
+        <v>103319</v>
       </c>
     </row>
     <row r="1150">
@@ -23481,10 +23481,10 @@
         <v>85.89</v>
       </c>
       <c r="E1153" t="n">
-        <v>86.01000000000001</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="F1153" t="n">
-        <v>120019</v>
+        <v>119054</v>
       </c>
     </row>
     <row r="1154">
@@ -23501,10 +23501,10 @@
         <v>85.53</v>
       </c>
       <c r="E1154" t="n">
-        <v>86.16</v>
+        <v>86.26000000000001</v>
       </c>
       <c r="F1154" t="n">
-        <v>115051</v>
+        <v>114400</v>
       </c>
     </row>
     <row r="1155">
@@ -23581,10 +23581,10 @@
         <v>82.70999999999999</v>
       </c>
       <c r="E1158" t="n">
-        <v>83.42</v>
+        <v>83.45999999999999</v>
       </c>
       <c r="F1158" t="n">
-        <v>88033</v>
+        <v>87119</v>
       </c>
     </row>
     <row r="1159">
@@ -23601,10 +23601,10 @@
         <v>82.98</v>
       </c>
       <c r="E1159" t="n">
-        <v>84.42</v>
+        <v>84.37</v>
       </c>
       <c r="F1159" t="n">
-        <v>98761</v>
+        <v>98085</v>
       </c>
     </row>
     <row r="1160">
@@ -23681,10 +23681,10 @@
         <v>81.61</v>
       </c>
       <c r="E1163" t="n">
-        <v>82.67</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="F1163" t="n">
-        <v>77961</v>
+        <v>77118</v>
       </c>
     </row>
     <row r="1164">
@@ -23701,10 +23701,10 @@
         <v>82.2</v>
       </c>
       <c r="E1164" t="n">
-        <v>84.05</v>
+        <v>84.14</v>
       </c>
       <c r="F1164" t="n">
-        <v>102303</v>
+        <v>101382</v>
       </c>
     </row>
     <row r="1165">
@@ -23781,10 +23781,10 @@
         <v>84.98</v>
       </c>
       <c r="E1168" t="n">
-        <v>86.66</v>
+        <v>86.63</v>
       </c>
       <c r="F1168" t="n">
-        <v>85007</v>
+        <v>83934</v>
       </c>
     </row>
     <row r="1169">
@@ -23795,16 +23795,16 @@
         <v>86.63</v>
       </c>
       <c r="C1169" t="n">
-        <v>88.75</v>
+        <v>88.66</v>
       </c>
       <c r="D1169" t="n">
         <v>86.59</v>
       </c>
       <c r="E1169" t="n">
-        <v>88.68000000000001</v>
+        <v>88.64</v>
       </c>
       <c r="F1169" t="n">
-        <v>98645</v>
+        <v>97671</v>
       </c>
     </row>
     <row r="1170">
@@ -23881,10 +23881,10 @@
         <v>89.17</v>
       </c>
       <c r="E1173" t="n">
-        <v>89.47</v>
+        <v>89.76000000000001</v>
       </c>
       <c r="F1173" t="n">
-        <v>104343</v>
+        <v>103067</v>
       </c>
     </row>
     <row r="1174">
@@ -23901,10 +23901,10 @@
         <v>88.97</v>
       </c>
       <c r="E1174" t="n">
-        <v>90.09999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="F1174" t="n">
-        <v>101197</v>
+        <v>100164</v>
       </c>
     </row>
     <row r="1175">
@@ -23975,16 +23975,16 @@
         <v>91.56999999999999</v>
       </c>
       <c r="C1178" t="n">
-        <v>93.68000000000001</v>
+        <v>93.44</v>
       </c>
       <c r="D1178" t="n">
         <v>91.55</v>
       </c>
       <c r="E1178" t="n">
-        <v>93.56</v>
+        <v>93.36</v>
       </c>
       <c r="F1178" t="n">
-        <v>91727</v>
+        <v>89908</v>
       </c>
     </row>
     <row r="1179">
@@ -24001,10 +24001,10 @@
         <v>92.14</v>
       </c>
       <c r="E1179" t="n">
-        <v>93.56999999999999</v>
+        <v>93.52</v>
       </c>
       <c r="F1179" t="n">
-        <v>101498</v>
+        <v>100530</v>
       </c>
     </row>
     <row r="1180">
@@ -24081,10 +24081,10 @@
         <v>91.23999999999999</v>
       </c>
       <c r="E1183" t="n">
-        <v>92.20999999999999</v>
+        <v>92.27</v>
       </c>
       <c r="F1183" t="n">
-        <v>98137</v>
+        <v>97207</v>
       </c>
     </row>
     <row r="1184">
@@ -24101,10 +24101,10 @@
         <v>91.68000000000001</v>
       </c>
       <c r="E1184" t="n">
-        <v>92.28</v>
+        <v>92.31</v>
       </c>
       <c r="F1184" t="n">
-        <v>99665</v>
+        <v>98960</v>
       </c>
     </row>
     <row r="1185">
@@ -24181,10 +24181,10 @@
         <v>92.56</v>
       </c>
       <c r="E1188" t="n">
-        <v>92.89</v>
+        <v>92.94</v>
       </c>
       <c r="F1188" t="n">
-        <v>128240</v>
+        <v>127194</v>
       </c>
     </row>
     <row r="1189">
@@ -24201,10 +24201,10 @@
         <v>91.68000000000001</v>
       </c>
       <c r="E1189" t="n">
-        <v>91.8</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="F1189" t="n">
-        <v>117877</v>
+        <v>116761</v>
       </c>
     </row>
     <row r="1190">
@@ -24281,10 +24281,10 @@
         <v>83.31999999999999</v>
       </c>
       <c r="E1193" t="n">
-        <v>83.72</v>
+        <v>83.68000000000001</v>
       </c>
       <c r="F1193" t="n">
-        <v>149779</v>
+        <v>148426</v>
       </c>
     </row>
     <row r="1194">
@@ -24301,10 +24301,10 @@
         <v>82.97</v>
       </c>
       <c r="E1194" t="n">
-        <v>83.79000000000001</v>
+        <v>83.88</v>
       </c>
       <c r="F1194" t="n">
-        <v>140020</v>
+        <v>138785</v>
       </c>
     </row>
     <row r="1195">
@@ -24381,10 +24381,10 @@
         <v>84.59</v>
       </c>
       <c r="E1198" t="n">
-        <v>85.59999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="F1198" t="n">
-        <v>124560</v>
+        <v>123421</v>
       </c>
     </row>
     <row r="1199">
@@ -24404,7 +24404,7 @@
         <v>89.93000000000001</v>
       </c>
       <c r="F1199" t="n">
-        <v>120817</v>
+        <v>118765</v>
       </c>
     </row>
     <row r="1200">
@@ -24475,16 +24475,16 @@
         <v>90.26000000000001</v>
       </c>
       <c r="C1203" t="n">
-        <v>92.34999999999999</v>
+        <v>92.22</v>
       </c>
       <c r="D1203" t="n">
         <v>88.69</v>
       </c>
       <c r="E1203" t="n">
-        <v>92.04000000000001</v>
+        <v>92.16</v>
       </c>
       <c r="F1203" t="n">
-        <v>111224</v>
+        <v>109002</v>
       </c>
     </row>
     <row r="1204">
@@ -24501,10 +24501,10 @@
         <v>90.63</v>
       </c>
       <c r="E1204" t="n">
-        <v>91.26000000000001</v>
+        <v>91.13</v>
       </c>
       <c r="F1204" t="n">
-        <v>110661</v>
+        <v>109157</v>
       </c>
     </row>
     <row r="1205">
@@ -24581,10 +24581,10 @@
         <v>86.48</v>
       </c>
       <c r="E1208" t="n">
-        <v>87.23999999999999</v>
+        <v>87.25</v>
       </c>
       <c r="F1208" t="n">
-        <v>114536</v>
+        <v>113368</v>
       </c>
     </row>
     <row r="1209">
@@ -24601,10 +24601,10 @@
         <v>86.76000000000001</v>
       </c>
       <c r="E1209" t="n">
-        <v>88.70999999999999</v>
+        <v>88.76000000000001</v>
       </c>
       <c r="F1209" t="n">
-        <v>123231</v>
+        <v>121600</v>
       </c>
     </row>
     <row r="1210">
@@ -24672,7 +24672,7 @@
         <v>45232</v>
       </c>
       <c r="B1213" t="n">
-        <v>85.03</v>
+        <v>84.83</v>
       </c>
       <c r="C1213" t="n">
         <v>86.88</v>
@@ -24684,7 +24684,7 @@
         <v>86.63</v>
       </c>
       <c r="F1213" t="n">
-        <v>102261</v>
+        <v>103842</v>
       </c>
     </row>
     <row r="1214">
@@ -24692,7 +24692,7 @@
         <v>45233</v>
       </c>
       <c r="B1214" t="n">
-        <v>86.66</v>
+        <v>86.70999999999999</v>
       </c>
       <c r="C1214" t="n">
         <v>87.58</v>
@@ -24704,7 +24704,7 @@
         <v>84.95</v>
       </c>
       <c r="F1214" t="n">
-        <v>117913</v>
+        <v>119097</v>
       </c>
     </row>
     <row r="1215">
@@ -24781,10 +24781,10 @@
         <v>79.33</v>
       </c>
       <c r="E1218" t="n">
-        <v>79.76000000000001</v>
+        <v>79.75</v>
       </c>
       <c r="F1218" t="n">
-        <v>111847</v>
+        <v>110739</v>
       </c>
     </row>
     <row r="1219">
@@ -24801,10 +24801,10 @@
         <v>79.70999999999999</v>
       </c>
       <c r="E1219" t="n">
-        <v>81.43000000000001</v>
+        <v>81.36</v>
       </c>
       <c r="F1219" t="n">
-        <v>92327</v>
+        <v>91256</v>
       </c>
     </row>
     <row r="1220">
@@ -24881,10 +24881,10 @@
         <v>76.64</v>
       </c>
       <c r="E1223" t="n">
-        <v>77.45</v>
+        <v>77.43000000000001</v>
       </c>
       <c r="F1223" t="n">
-        <v>105749</v>
+        <v>104766</v>
       </c>
     </row>
     <row r="1224">
@@ -24901,10 +24901,10 @@
         <v>77.31</v>
       </c>
       <c r="E1224" t="n">
-        <v>80.43000000000001</v>
+        <v>80.37</v>
       </c>
       <c r="F1224" t="n">
-        <v>89648</v>
+        <v>88772</v>
       </c>
     </row>
     <row r="1225">
@@ -25078,13 +25078,13 @@
         <v>84.51000000000001</v>
       </c>
       <c r="D1233" t="n">
-        <v>79.94</v>
+        <v>79.95</v>
       </c>
       <c r="E1233" t="n">
-        <v>80.31</v>
+        <v>80</v>
       </c>
       <c r="F1233" t="n">
-        <v>145419</v>
+        <v>143673</v>
       </c>
     </row>
     <row r="1234">
@@ -25101,10 +25101,10 @@
         <v>78.69</v>
       </c>
       <c r="E1234" t="n">
-        <v>79.02</v>
+        <v>78.93000000000001</v>
       </c>
       <c r="F1234" t="n">
-        <v>126159</v>
+        <v>125186</v>
       </c>
     </row>
     <row r="1235">
@@ -25181,10 +25181,10 @@
         <v>73.68000000000001</v>
       </c>
       <c r="E1238" t="n">
-        <v>74.39</v>
+        <v>74.47</v>
       </c>
       <c r="F1238" t="n">
-        <v>116791</v>
+        <v>115986</v>
       </c>
     </row>
     <row r="1239">
@@ -25201,10 +25201,10 @@
         <v>74.25</v>
       </c>
       <c r="E1239" t="n">
-        <v>75.94</v>
+        <v>75.87</v>
       </c>
       <c r="F1239" t="n">
-        <v>114930</v>
+        <v>114085</v>
       </c>
     </row>
     <row r="1240">
@@ -25281,10 +25281,10 @@
         <v>74.56999999999999</v>
       </c>
       <c r="E1243" t="n">
-        <v>76.75</v>
+        <v>76.86</v>
       </c>
       <c r="F1243" t="n">
-        <v>84712</v>
+        <v>83845</v>
       </c>
     </row>
     <row r="1244">
@@ -25301,10 +25301,10 @@
         <v>75.48</v>
       </c>
       <c r="E1244" t="n">
-        <v>76.98999999999999</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="F1244" t="n">
-        <v>95068</v>
+        <v>94162</v>
       </c>
     </row>
     <row r="1245">
@@ -25381,10 +25381,10 @@
         <v>77.76000000000001</v>
       </c>
       <c r="E1248" t="n">
-        <v>79.12</v>
+        <v>79.19</v>
       </c>
       <c r="F1248" t="n">
-        <v>91755</v>
+        <v>91100</v>
       </c>
     </row>
     <row r="1249">
@@ -25461,10 +25461,10 @@
         <v>77.04000000000001</v>
       </c>
       <c r="E1252" t="n">
-        <v>77.36</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="F1252" t="n">
-        <v>95204</v>
+        <v>94380</v>
       </c>
     </row>
     <row r="1253">
@@ -25544,7 +25544,7 @@
         <v>77.53</v>
       </c>
       <c r="F1256" t="n">
-        <v>119158</v>
+        <v>118273</v>
       </c>
     </row>
     <row r="1257">
@@ -25641,10 +25641,10 @@
         <v>76.45</v>
       </c>
       <c r="E1261" t="n">
-        <v>78.01000000000001</v>
+        <v>77.61</v>
       </c>
       <c r="F1261" t="n">
-        <v>129868</v>
+        <v>128067</v>
       </c>
     </row>
     <row r="1262">
@@ -25741,10 +25741,10 @@
         <v>76.98</v>
       </c>
       <c r="E1266" t="n">
-        <v>78.56</v>
+        <v>78.63</v>
       </c>
       <c r="F1266" t="n">
-        <v>99368</v>
+        <v>98609</v>
       </c>
     </row>
     <row r="1267">
@@ -25841,10 +25841,10 @@
         <v>79.65000000000001</v>
       </c>
       <c r="E1271" t="n">
-        <v>81.69</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="F1271" t="n">
-        <v>76710</v>
+        <v>75889</v>
       </c>
     </row>
     <row r="1272">
@@ -25861,10 +25861,10 @@
         <v>80.75</v>
       </c>
       <c r="E1272" t="n">
-        <v>83.09999999999999</v>
+        <v>83.08</v>
       </c>
       <c r="F1272" t="n">
-        <v>87047</v>
+        <v>85666</v>
       </c>
     </row>
     <row r="1273">
@@ -25941,10 +25941,10 @@
         <v>78.5</v>
       </c>
       <c r="E1276" t="n">
-        <v>78.7</v>
+        <v>78.64</v>
       </c>
       <c r="F1276" t="n">
-        <v>140571</v>
+        <v>138682</v>
       </c>
     </row>
     <row r="1277">
@@ -25961,10 +25961,10 @@
         <v>76.78</v>
       </c>
       <c r="E1277" t="n">
-        <v>77.31999999999999</v>
+        <v>77.11</v>
       </c>
       <c r="F1277" t="n">
-        <v>133396</v>
+        <v>132023</v>
       </c>
     </row>
     <row r="1278">
@@ -26041,10 +26041,10 @@
         <v>78.84999999999999</v>
       </c>
       <c r="E1281" t="n">
-        <v>81.40000000000001</v>
+        <v>81.51000000000001</v>
       </c>
       <c r="F1281" t="n">
-        <v>87658</v>
+        <v>86597</v>
       </c>
     </row>
     <row r="1282">
@@ -26064,7 +26064,7 @@
         <v>81.63</v>
       </c>
       <c r="F1282" t="n">
-        <v>86235</v>
+        <v>85346</v>
       </c>
     </row>
     <row r="1283">
@@ -26141,10 +26141,10 @@
         <v>80.31999999999999</v>
       </c>
       <c r="E1286" t="n">
-        <v>82.22</v>
+        <v>82.37</v>
       </c>
       <c r="F1286" t="n">
-        <v>84560</v>
+        <v>83753</v>
       </c>
     </row>
     <row r="1287">
@@ -26161,10 +26161,10 @@
         <v>81.34</v>
       </c>
       <c r="E1287" t="n">
-        <v>82.68000000000001</v>
+        <v>82.70999999999999</v>
       </c>
       <c r="F1287" t="n">
-        <v>81459</v>
+        <v>80620</v>
       </c>
     </row>
     <row r="1288">
@@ -26241,10 +26241,10 @@
         <v>81.45</v>
       </c>
       <c r="E1291" t="n">
-        <v>82.51000000000001</v>
+        <v>82.63</v>
       </c>
       <c r="F1291" t="n">
-        <v>67848</v>
+        <v>67106</v>
       </c>
     </row>
     <row r="1292">
@@ -26261,10 +26261,10 @@
         <v>80.65000000000001</v>
       </c>
       <c r="E1292" t="n">
-        <v>80.84</v>
+        <v>80.88</v>
       </c>
       <c r="F1292" t="n">
-        <v>73168</v>
+        <v>72495</v>
       </c>
     </row>
     <row r="1293">
@@ -26341,10 +26341,10 @@
         <v>81.37</v>
       </c>
       <c r="E1296" t="n">
-        <v>81.8</v>
+        <v>81.70999999999999</v>
       </c>
       <c r="F1296" t="n">
-        <v>79642</v>
+        <v>78801</v>
       </c>
     </row>
     <row r="1297">
@@ -26361,10 +26361,10 @@
         <v>81.63</v>
       </c>
       <c r="E1297" t="n">
-        <v>83.12</v>
+        <v>83.19</v>
       </c>
       <c r="F1297" t="n">
-        <v>73275</v>
+        <v>72423</v>
       </c>
     </row>
     <row r="1298">
@@ -26441,10 +26441,10 @@
         <v>81.77</v>
       </c>
       <c r="E1301" t="n">
-        <v>82.87</v>
+        <v>82.52</v>
       </c>
       <c r="F1301" t="n">
-        <v>103853</v>
+        <v>102278</v>
       </c>
     </row>
     <row r="1302">
@@ -26461,10 +26461,10 @@
         <v>81.41</v>
       </c>
       <c r="E1302" t="n">
-        <v>81.55</v>
+        <v>81.66</v>
       </c>
       <c r="F1302" t="n">
-        <v>100115</v>
+        <v>99175</v>
       </c>
     </row>
     <row r="1303">
@@ -26532,19 +26532,19 @@
         <v>45365</v>
       </c>
       <c r="B1306" t="n">
-        <v>83.69</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="C1306" t="n">
         <v>85.18000000000001</v>
       </c>
       <c r="D1306" t="n">
-        <v>83.56999999999999</v>
+        <v>83.53</v>
       </c>
       <c r="E1306" t="n">
         <v>84.61</v>
       </c>
       <c r="F1306" t="n">
-        <v>71119</v>
+        <v>71844</v>
       </c>
     </row>
     <row r="1307">
@@ -26552,7 +26552,7 @@
         <v>45366</v>
       </c>
       <c r="B1307" t="n">
-        <v>84.68000000000001</v>
+        <v>84.65000000000001</v>
       </c>
       <c r="C1307" t="n">
         <v>85.09</v>
@@ -26564,7 +26564,7 @@
         <v>84.83</v>
       </c>
       <c r="F1307" t="n">
-        <v>74945</v>
+        <v>75864</v>
       </c>
     </row>
     <row r="1308">
@@ -26632,7 +26632,7 @@
         <v>45372</v>
       </c>
       <c r="B1311" t="n">
-        <v>85.81</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="C1311" t="n">
         <v>86.03</v>
@@ -26644,7 +26644,7 @@
         <v>84.95999999999999</v>
       </c>
       <c r="F1311" t="n">
-        <v>66113</v>
+        <v>67186</v>
       </c>
     </row>
     <row r="1312">
@@ -26652,7 +26652,7 @@
         <v>45373</v>
       </c>
       <c r="B1312" t="n">
-        <v>84.98999999999999</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="C1312" t="n">
         <v>85.58</v>
@@ -26664,7 +26664,7 @@
         <v>84.93000000000001</v>
       </c>
       <c r="F1312" t="n">
-        <v>53666</v>
+        <v>54286</v>
       </c>
     </row>
     <row r="1313">
@@ -26732,7 +26732,7 @@
         <v>45379</v>
       </c>
       <c r="B1316" t="n">
-        <v>85.65000000000001</v>
+        <v>85.56</v>
       </c>
       <c r="C1316" t="n">
         <v>86.89</v>
@@ -26744,7 +26744,7 @@
         <v>86.67</v>
       </c>
       <c r="F1316" t="n">
-        <v>56915</v>
+        <v>57372</v>
       </c>
     </row>
     <row r="1317">
@@ -26821,10 +26821,10 @@
         <v>88.43000000000001</v>
       </c>
       <c r="E1320" t="n">
-        <v>90.56</v>
+        <v>90.38</v>
       </c>
       <c r="F1320" t="n">
-        <v>75666</v>
+        <v>74470</v>
       </c>
     </row>
     <row r="1321">
@@ -26841,10 +26841,10 @@
         <v>90.18000000000001</v>
       </c>
       <c r="E1321" t="n">
-        <v>90.39</v>
+        <v>90.52</v>
       </c>
       <c r="F1321" t="n">
-        <v>80607</v>
+        <v>79937</v>
       </c>
     </row>
     <row r="1322">
@@ -26921,10 +26921,10 @@
         <v>88.87</v>
       </c>
       <c r="E1325" t="n">
-        <v>89.55</v>
+        <v>89.68000000000001</v>
       </c>
       <c r="F1325" t="n">
-        <v>107884</v>
+        <v>107040</v>
       </c>
     </row>
     <row r="1326">
@@ -26941,10 +26941,10 @@
         <v>89.45</v>
       </c>
       <c r="E1326" t="n">
-        <v>89.48999999999999</v>
+        <v>89.73</v>
       </c>
       <c r="F1326" t="n">
-        <v>109120</v>
+        <v>108331</v>
       </c>
     </row>
     <row r="1327">
@@ -27021,10 +27021,10 @@
         <v>85.63</v>
       </c>
       <c r="E1330" t="n">
-        <v>86.19</v>
+        <v>86.47</v>
       </c>
       <c r="F1330" t="n">
-        <v>108132</v>
+        <v>107464</v>
       </c>
     </row>
     <row r="1331">
@@ -27041,10 +27041,10 @@
         <v>85.61</v>
       </c>
       <c r="E1331" t="n">
-        <v>86.38</v>
+        <v>86.51000000000001</v>
       </c>
       <c r="F1331" t="n">
-        <v>144473</v>
+        <v>143518</v>
       </c>
     </row>
     <row r="1332">
@@ -27115,16 +27115,16 @@
         <v>86.88</v>
       </c>
       <c r="C1335" t="n">
-        <v>88</v>
+        <v>87.97</v>
       </c>
       <c r="D1335" t="n">
         <v>86.2</v>
       </c>
       <c r="E1335" t="n">
-        <v>87.83</v>
+        <v>87.95</v>
       </c>
       <c r="F1335" t="n">
-        <v>70059</v>
+        <v>69439</v>
       </c>
     </row>
     <row r="1336">
@@ -27141,10 +27141,10 @@
         <v>87.56999999999999</v>
       </c>
       <c r="E1336" t="n">
-        <v>87.89</v>
+        <v>87.98999999999999</v>
       </c>
       <c r="F1336" t="n">
-        <v>64445</v>
+        <v>63936</v>
       </c>
     </row>
     <row r="1337">
@@ -27221,10 +27221,10 @@
         <v>82.89</v>
       </c>
       <c r="E1340" t="n">
-        <v>83.48</v>
+        <v>83.47</v>
       </c>
       <c r="F1340" t="n">
-        <v>101847</v>
+        <v>100961</v>
       </c>
     </row>
     <row r="1341">
@@ -27238,13 +27238,13 @@
         <v>84.18000000000001</v>
       </c>
       <c r="D1341" t="n">
-        <v>82.53</v>
+        <v>82.65000000000001</v>
       </c>
       <c r="E1341" t="n">
-        <v>82.54000000000001</v>
+        <v>82.77</v>
       </c>
       <c r="F1341" t="n">
-        <v>83584</v>
+        <v>82987</v>
       </c>
     </row>
     <row r="1342">
@@ -27321,10 +27321,10 @@
         <v>83.18000000000001</v>
       </c>
       <c r="E1345" t="n">
-        <v>83.77</v>
+        <v>83.91</v>
       </c>
       <c r="F1345" t="n">
-        <v>67737</v>
+        <v>67201</v>
       </c>
     </row>
     <row r="1346">
@@ -27338,13 +27338,13 @@
         <v>84.23</v>
       </c>
       <c r="D1346" t="n">
-        <v>82.36</v>
+        <v>82.5</v>
       </c>
       <c r="E1346" t="n">
-        <v>82.36</v>
+        <v>82.61</v>
       </c>
       <c r="F1346" t="n">
-        <v>63117</v>
+        <v>62356</v>
       </c>
     </row>
     <row r="1347">
@@ -27421,10 +27421,10 @@
         <v>82.02</v>
       </c>
       <c r="E1350" t="n">
-        <v>82.98999999999999</v>
+        <v>83.04000000000001</v>
       </c>
       <c r="F1350" t="n">
-        <v>65759</v>
+        <v>65306</v>
       </c>
     </row>
     <row r="1351">
@@ -27441,10 +27441,10 @@
         <v>82.81999999999999</v>
       </c>
       <c r="E1351" t="n">
-        <v>83.56</v>
+        <v>83.68000000000001</v>
       </c>
       <c r="F1351" t="n">
-        <v>61133</v>
+        <v>60667</v>
       </c>
     </row>
     <row r="1352">
@@ -27521,10 +27521,10 @@
         <v>80.7</v>
       </c>
       <c r="E1355" t="n">
-        <v>81.06999999999999</v>
+        <v>81.09</v>
       </c>
       <c r="F1355" t="n">
-        <v>69958</v>
+        <v>68901</v>
       </c>
     </row>
     <row r="1356">
@@ -27541,10 +27541,10 @@
         <v>80.42</v>
       </c>
       <c r="E1356" t="n">
-        <v>81.79000000000001</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="F1356" t="n">
-        <v>56381</v>
+        <v>56045</v>
       </c>
     </row>
     <row r="1357">
@@ -27618,13 +27618,13 @@
         <v>83.51000000000001</v>
       </c>
       <c r="D1360" t="n">
-        <v>81.72</v>
+        <v>81.77</v>
       </c>
       <c r="E1360" t="n">
-        <v>81.73</v>
+        <v>81.88</v>
       </c>
       <c r="F1360" t="n">
-        <v>81864</v>
+        <v>81262</v>
       </c>
     </row>
     <row r="1361">
@@ -27641,10 +27641,10 @@
         <v>80.69</v>
       </c>
       <c r="E1361" t="n">
-        <v>81.09</v>
+        <v>81.22</v>
       </c>
       <c r="F1361" t="n">
-        <v>87130</v>
+        <v>86335</v>
       </c>
     </row>
     <row r="1362">
@@ -27721,10 +27721,10 @@
         <v>78.23999999999999</v>
       </c>
       <c r="E1365" t="n">
-        <v>79.69</v>
+        <v>79.73</v>
       </c>
       <c r="F1365" t="n">
-        <v>72677</v>
+        <v>72035</v>
       </c>
     </row>
     <row r="1366">
@@ -27741,10 +27741,10 @@
         <v>79.18000000000001</v>
       </c>
       <c r="E1366" t="n">
-        <v>79.23999999999999</v>
+        <v>79.27</v>
       </c>
       <c r="F1366" t="n">
-        <v>77440</v>
+        <v>76576</v>
       </c>
     </row>
     <row r="1367">
@@ -27821,10 +27821,10 @@
         <v>81.53</v>
       </c>
       <c r="E1370" t="n">
-        <v>81.68000000000001</v>
+        <v>81.98</v>
       </c>
       <c r="F1370" t="n">
-        <v>79567</v>
+        <v>78296</v>
       </c>
     </row>
     <row r="1371">
@@ -27841,10 +27841,10 @@
         <v>81.64</v>
       </c>
       <c r="E1371" t="n">
-        <v>82.06</v>
+        <v>82.2</v>
       </c>
       <c r="F1371" t="n">
-        <v>75768</v>
+        <v>75030</v>
       </c>
     </row>
     <row r="1372">
@@ -27921,10 +27921,10 @@
         <v>84.28</v>
       </c>
       <c r="E1375" t="n">
-        <v>84.7</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="F1375" t="n">
-        <v>59846</v>
+        <v>59448</v>
       </c>
     </row>
     <row r="1376">
@@ -27941,10 +27941,10 @@
         <v>84</v>
       </c>
       <c r="E1376" t="n">
-        <v>84.16</v>
+        <v>84.31</v>
       </c>
       <c r="F1376" t="n">
-        <v>60278</v>
+        <v>59797</v>
       </c>
     </row>
     <row r="1377">
@@ -28021,10 +28021,10 @@
         <v>84.01000000000001</v>
       </c>
       <c r="E1380" t="n">
-        <v>85.04000000000001</v>
+        <v>85.25</v>
       </c>
       <c r="F1380" t="n">
-        <v>64909</v>
+        <v>64362</v>
       </c>
     </row>
     <row r="1381">
@@ -28041,10 +28041,10 @@
         <v>84.39</v>
       </c>
       <c r="E1381" t="n">
-        <v>84.65000000000001</v>
+        <v>84.79000000000001</v>
       </c>
       <c r="F1381" t="n">
-        <v>69862</v>
+        <v>69177</v>
       </c>
     </row>
     <row r="1382">
@@ -28141,10 +28141,10 @@
         <v>86.17</v>
       </c>
       <c r="E1386" t="n">
-        <v>86.43000000000001</v>
+        <v>86.31999999999999</v>
       </c>
       <c r="F1386" t="n">
-        <v>68965</v>
+        <v>67919</v>
       </c>
     </row>
     <row r="1387">
@@ -28221,10 +28221,10 @@
         <v>84.16</v>
       </c>
       <c r="E1390" t="n">
-        <v>84.90000000000001</v>
+        <v>85.19</v>
       </c>
       <c r="F1390" t="n">
-        <v>78990</v>
+        <v>78243</v>
       </c>
     </row>
     <row r="1391">
@@ -28238,13 +28238,13 @@
         <v>85.67</v>
       </c>
       <c r="D1391" t="n">
-        <v>84.31999999999999</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="E1391" t="n">
-        <v>84.31999999999999</v>
+        <v>84.5</v>
       </c>
       <c r="F1391" t="n">
-        <v>74302</v>
+        <v>73607</v>
       </c>
     </row>
     <row r="1392">
@@ -28321,10 +28321,10 @@
         <v>83.41</v>
       </c>
       <c r="E1395" t="n">
-        <v>83.76000000000001</v>
+        <v>83.72</v>
       </c>
       <c r="F1395" t="n">
-        <v>69797</v>
+        <v>68620</v>
       </c>
     </row>
     <row r="1396">
@@ -28338,13 +28338,13 @@
         <v>84.41</v>
       </c>
       <c r="D1396" t="n">
-        <v>81.64</v>
+        <v>81.7</v>
       </c>
       <c r="E1396" t="n">
-        <v>81.64</v>
+        <v>81.89</v>
       </c>
       <c r="F1396" t="n">
-        <v>72736</v>
+        <v>72020</v>
       </c>
     </row>
     <row r="1397">
@@ -28421,10 +28421,10 @@
         <v>79.28</v>
       </c>
       <c r="E1400" t="n">
-        <v>81.37</v>
+        <v>81.33</v>
       </c>
       <c r="F1400" t="n">
-        <v>69789</v>
+        <v>69150</v>
       </c>
     </row>
     <row r="1401">
@@ -28441,10 +28441,10 @@
         <v>79.39</v>
       </c>
       <c r="E1401" t="n">
-        <v>79.48999999999999</v>
+        <v>79.92</v>
       </c>
       <c r="F1401" t="n">
-        <v>65748</v>
+        <v>64725</v>
       </c>
     </row>
     <row r="1402">
@@ -28521,10 +28521,10 @@
         <v>79.3</v>
       </c>
       <c r="E1405" t="n">
-        <v>79.83</v>
+        <v>80</v>
       </c>
       <c r="F1405" t="n">
-        <v>105741</v>
+        <v>104482</v>
       </c>
     </row>
     <row r="1406">
@@ -28541,10 +28541,10 @@
         <v>76.26000000000001</v>
       </c>
       <c r="E1406" t="n">
-        <v>77.14</v>
+        <v>77.08</v>
       </c>
       <c r="F1406" t="n">
-        <v>125792</v>
+        <v>124356</v>
       </c>
     </row>
     <row r="1407">
@@ -28621,10 +28621,10 @@
         <v>77.33</v>
       </c>
       <c r="E1410" t="n">
-        <v>78.59</v>
+        <v>78.73999999999999</v>
       </c>
       <c r="F1410" t="n">
-        <v>113892</v>
+        <v>113028</v>
       </c>
     </row>
     <row r="1411">
@@ -28641,10 +28641,10 @@
         <v>78.43000000000001</v>
       </c>
       <c r="E1411" t="n">
-        <v>79.27</v>
+        <v>79.34</v>
       </c>
       <c r="F1411" t="n">
-        <v>87467</v>
+        <v>86405</v>
       </c>
     </row>
     <row r="1412">
@@ -28721,10 +28721,10 @@
         <v>79.11</v>
       </c>
       <c r="E1415" t="n">
-        <v>80.26000000000001</v>
+        <v>80.31999999999999</v>
       </c>
       <c r="F1415" t="n">
-        <v>79567</v>
+        <v>78757</v>
       </c>
     </row>
     <row r="1416">
@@ -28741,10 +28741,10 @@
         <v>78.09</v>
       </c>
       <c r="E1416" t="n">
-        <v>78.94</v>
+        <v>79.22</v>
       </c>
       <c r="F1416" t="n">
-        <v>82030</v>
+        <v>81009</v>
       </c>
     </row>
     <row r="1417">
@@ -28821,10 +28821,10 @@
         <v>75.25</v>
       </c>
       <c r="E1420" t="n">
-        <v>76.42</v>
+        <v>76.47</v>
       </c>
       <c r="F1420" t="n">
-        <v>79873</v>
+        <v>79280</v>
       </c>
     </row>
     <row r="1421">
@@ -28841,10 +28841,10 @@
         <v>76.40000000000001</v>
       </c>
       <c r="E1421" t="n">
-        <v>78.13</v>
+        <v>78.17</v>
       </c>
       <c r="F1421" t="n">
-        <v>69081</v>
+        <v>68613</v>
       </c>
     </row>
     <row r="1422">
@@ -28921,10 +28921,10 @@
         <v>76.90000000000001</v>
       </c>
       <c r="E1425" t="n">
-        <v>78.72</v>
+        <v>78.81</v>
       </c>
       <c r="F1425" t="n">
-        <v>94397</v>
+        <v>93699</v>
       </c>
     </row>
     <row r="1426">
@@ -28941,10 +28941,10 @@
         <v>76.56</v>
       </c>
       <c r="E1426" t="n">
-        <v>76.77</v>
+        <v>76.81</v>
       </c>
       <c r="F1426" t="n">
-        <v>109124</v>
+        <v>108329</v>
       </c>
     </row>
     <row r="1427">
@@ -29021,10 +29021,10 @@
         <v>72.20999999999999</v>
       </c>
       <c r="E1430" t="n">
-        <v>72.53</v>
+        <v>72.54000000000001</v>
       </c>
       <c r="F1430" t="n">
-        <v>109541</v>
+        <v>108713</v>
       </c>
     </row>
     <row r="1431">
@@ -29041,10 +29041,10 @@
         <v>70.45</v>
       </c>
       <c r="E1431" t="n">
-        <v>71.2</v>
+        <v>71.37</v>
       </c>
       <c r="F1431" t="n">
-        <v>116954</v>
+        <v>115759</v>
       </c>
     </row>
     <row r="1432">
@@ -29121,10 +29121,10 @@
         <v>70.31999999999999</v>
       </c>
       <c r="E1435" t="n">
-        <v>71.67</v>
+        <v>71.89</v>
       </c>
       <c r="F1435" t="n">
-        <v>115156</v>
+        <v>114181</v>
       </c>
     </row>
     <row r="1436">
@@ -29141,10 +29141,10 @@
         <v>71.09</v>
       </c>
       <c r="E1436" t="n">
-        <v>71.59999999999999</v>
+        <v>71.73</v>
       </c>
       <c r="F1436" t="n">
-        <v>99629</v>
+        <v>98569</v>
       </c>
     </row>
     <row r="1437">
@@ -29221,10 +29221,10 @@
         <v>72.26000000000001</v>
       </c>
       <c r="E1440" t="n">
-        <v>73.97</v>
+        <v>74.05</v>
       </c>
       <c r="F1440" t="n">
-        <v>89094</v>
+        <v>88395</v>
       </c>
     </row>
     <row r="1441">
@@ -29241,10 +29241,10 @@
         <v>73.28</v>
       </c>
       <c r="E1441" t="n">
-        <v>73.87</v>
+        <v>73.98</v>
       </c>
       <c r="F1441" t="n">
-        <v>72413</v>
+        <v>71635</v>
       </c>
     </row>
     <row r="1442">
@@ -29321,10 +29321,10 @@
         <v>70.20999999999999</v>
       </c>
       <c r="E1445" t="n">
-        <v>70.68000000000001</v>
+        <v>70.66</v>
       </c>
       <c r="F1445" t="n">
-        <v>155899</v>
+        <v>154979</v>
       </c>
     </row>
     <row r="1446">
@@ -29335,16 +29335,16 @@
         <v>70.68000000000001</v>
       </c>
       <c r="C1446" t="n">
-        <v>71.90000000000001</v>
+        <v>71.89</v>
       </c>
       <c r="D1446" t="n">
         <v>70.39</v>
       </c>
       <c r="E1446" t="n">
-        <v>71.79000000000001</v>
+        <v>71.81999999999999</v>
       </c>
       <c r="F1446" t="n">
-        <v>123787</v>
+        <v>122438</v>
       </c>
     </row>
     <row r="1447">
@@ -29421,10 +29421,10 @@
         <v>74.18000000000001</v>
       </c>
       <c r="E1450" t="n">
-        <v>77.28</v>
+        <v>77.58</v>
       </c>
       <c r="F1450" t="n">
-        <v>125075</v>
+        <v>123449</v>
       </c>
     </row>
     <row r="1451">
@@ -29441,10 +29441,10 @@
         <v>77.19</v>
       </c>
       <c r="E1451" t="n">
-        <v>77.73</v>
+        <v>77.87</v>
       </c>
       <c r="F1451" t="n">
-        <v>121412</v>
+        <v>120535</v>
       </c>
     </row>
     <row r="1452">
@@ -39004,7 +39004,27 @@
         <v>85.86</v>
       </c>
       <c r="F1929" t="n">
-        <v>102608</v>
+        <v>102607</v>
+      </c>
+    </row>
+    <row r="1930">
+      <c r="A1930" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B1930" t="n">
+        <v>85.95999999999999</v>
+      </c>
+      <c r="C1930" t="n">
+        <v>87.53</v>
+      </c>
+      <c r="D1930" t="n">
+        <v>85.44</v>
+      </c>
+      <c r="E1930" t="n">
+        <v>87.33</v>
+      </c>
+      <c r="F1930" t="n">
+        <v>83628</v>
       </c>
     </row>
   </sheetData>

--- a/database/BRENT.xlsx
+++ b/database/BRENT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1930"/>
+  <dimension ref="A1:F1931"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3881,10 +3881,10 @@
         <v>60.96</v>
       </c>
       <c r="E173" t="n">
-        <v>61.74</v>
+        <v>61.65</v>
       </c>
       <c r="F173" t="n">
-        <v>7439</v>
+        <v>7745</v>
       </c>
     </row>
     <row r="174">
@@ -3952,7 +3952,7 @@
         <v>43769</v>
       </c>
       <c r="B177" t="n">
-        <v>60.17</v>
+        <v>60.27</v>
       </c>
       <c r="C177" t="n">
         <v>60.79</v>
@@ -3964,7 +3964,7 @@
         <v>59.46</v>
       </c>
       <c r="F177" t="n">
-        <v>20831</v>
+        <v>20603</v>
       </c>
     </row>
     <row r="178">
@@ -3972,7 +3972,7 @@
         <v>43770</v>
       </c>
       <c r="B178" t="n">
-        <v>59.42</v>
+        <v>59.64</v>
       </c>
       <c r="C178" t="n">
         <v>61.8</v>
@@ -3984,7 +3984,7 @@
         <v>61.65</v>
       </c>
       <c r="F178" t="n">
-        <v>18539</v>
+        <v>18281</v>
       </c>
     </row>
     <row r="179">
@@ -4061,10 +4061,10 @@
         <v>61.63</v>
       </c>
       <c r="E182" t="n">
-        <v>62.14</v>
+        <v>62.29</v>
       </c>
       <c r="F182" t="n">
-        <v>19306</v>
+        <v>19680</v>
       </c>
     </row>
     <row r="183">
@@ -4081,10 +4081,10 @@
         <v>60.65</v>
       </c>
       <c r="E183" t="n">
-        <v>62.61</v>
+        <v>62.64</v>
       </c>
       <c r="F183" t="n">
-        <v>21625</v>
+        <v>21863</v>
       </c>
     </row>
     <row r="184">
@@ -4161,10 +4161,10 @@
         <v>62.14</v>
       </c>
       <c r="E187" t="n">
-        <v>62.38</v>
+        <v>62.33</v>
       </c>
       <c r="F187" t="n">
-        <v>19157</v>
+        <v>19293</v>
       </c>
     </row>
     <row r="188">
@@ -4181,10 +4181,10 @@
         <v>61.69</v>
       </c>
       <c r="E188" t="n">
-        <v>63.32</v>
+        <v>63.41</v>
       </c>
       <c r="F188" t="n">
-        <v>15801</v>
+        <v>16092</v>
       </c>
     </row>
     <row r="189">
@@ -4261,10 +4261,10 @@
         <v>61.91</v>
       </c>
       <c r="E192" t="n">
-        <v>63.74</v>
+        <v>63.64</v>
       </c>
       <c r="F192" t="n">
-        <v>21582</v>
+        <v>21823</v>
       </c>
     </row>
     <row r="193">
@@ -4281,10 +4281,10 @@
         <v>61.92</v>
       </c>
       <c r="E193" t="n">
-        <v>62.58</v>
+        <v>62.52</v>
       </c>
       <c r="F193" t="n">
-        <v>17577</v>
+        <v>17794</v>
       </c>
     </row>
     <row r="194">
@@ -4461,10 +4461,10 @@
         <v>62.73</v>
       </c>
       <c r="E202" t="n">
-        <v>63.33</v>
+        <v>63.26</v>
       </c>
       <c r="F202" t="n">
-        <v>24042</v>
+        <v>24300</v>
       </c>
     </row>
     <row r="203">
@@ -4481,10 +4481,10 @@
         <v>62.82</v>
       </c>
       <c r="E203" t="n">
-        <v>64.22</v>
+        <v>64.34</v>
       </c>
       <c r="F203" t="n">
-        <v>22359</v>
+        <v>22572</v>
       </c>
     </row>
     <row r="204">
@@ -4561,10 +4561,10 @@
         <v>63.86</v>
       </c>
       <c r="E207" t="n">
-        <v>64.31</v>
+        <v>64.28</v>
       </c>
       <c r="F207" t="n">
-        <v>18198</v>
+        <v>18454</v>
       </c>
     </row>
     <row r="208">
@@ -4581,10 +4581,10 @@
         <v>64.48</v>
       </c>
       <c r="E208" t="n">
-        <v>64.88</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="F208" t="n">
-        <v>21484</v>
+        <v>21671</v>
       </c>
     </row>
     <row r="209">
@@ -4661,10 +4661,10 @@
         <v>66.02</v>
       </c>
       <c r="E212" t="n">
-        <v>66.45</v>
+        <v>66.53</v>
       </c>
       <c r="F212" t="n">
-        <v>10932</v>
+        <v>11180</v>
       </c>
     </row>
     <row r="213">
@@ -4681,10 +4681,10 @@
         <v>65.72</v>
       </c>
       <c r="E213" t="n">
-        <v>65.98</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="F213" t="n">
-        <v>14693</v>
+        <v>14806</v>
       </c>
     </row>
     <row r="214">
@@ -4741,10 +4741,10 @@
         <v>66.09</v>
       </c>
       <c r="E216" t="n">
-        <v>66.65000000000001</v>
+        <v>66.75</v>
       </c>
       <c r="F216" t="n">
-        <v>9409</v>
+        <v>9613</v>
       </c>
     </row>
     <row r="217">
@@ -4761,10 +4761,10 @@
         <v>66.34</v>
       </c>
       <c r="E217" t="n">
-        <v>66.81</v>
+        <v>66.84</v>
       </c>
       <c r="F217" t="n">
-        <v>11272</v>
+        <v>11398</v>
       </c>
     </row>
     <row r="218">
@@ -4821,10 +4821,10 @@
         <v>65.7</v>
       </c>
       <c r="E220" t="n">
-        <v>66.19</v>
+        <v>66.23</v>
       </c>
       <c r="F220" t="n">
-        <v>15153</v>
+        <v>15351</v>
       </c>
     </row>
     <row r="221">
@@ -4841,10 +4841,10 @@
         <v>66.19</v>
       </c>
       <c r="E221" t="n">
-        <v>68.55</v>
+        <v>68.59</v>
       </c>
       <c r="F221" t="n">
-        <v>35427</v>
+        <v>35609</v>
       </c>
     </row>
     <row r="222">
@@ -4924,7 +4924,7 @@
         <v>65.38</v>
       </c>
       <c r="F225" t="n">
-        <v>25682</v>
+        <v>25951</v>
       </c>
     </row>
     <row r="226">
@@ -4944,7 +4944,7 @@
         <v>65</v>
       </c>
       <c r="F226" t="n">
-        <v>20016</v>
+        <v>20436</v>
       </c>
     </row>
     <row r="227">
@@ -5021,10 +5021,10 @@
         <v>63.89</v>
       </c>
       <c r="E230" t="n">
-        <v>64.64</v>
+        <v>64.7</v>
       </c>
       <c r="F230" t="n">
-        <v>16107</v>
+        <v>16472</v>
       </c>
     </row>
     <row r="231">
@@ -5041,10 +5041,10 @@
         <v>64.45</v>
       </c>
       <c r="E231" t="n">
-        <v>64.95</v>
+        <v>65.08</v>
       </c>
       <c r="F231" t="n">
-        <v>16060</v>
+        <v>16251</v>
       </c>
     </row>
     <row r="232">
@@ -5121,10 +5121,10 @@
         <v>61.24</v>
       </c>
       <c r="E235" t="n">
-        <v>61.97</v>
+        <v>62.11</v>
       </c>
       <c r="F235" t="n">
-        <v>22982</v>
+        <v>23208</v>
       </c>
     </row>
     <row r="236">
@@ -5141,10 +5141,10 @@
         <v>60.24</v>
       </c>
       <c r="E236" t="n">
-        <v>60.82</v>
+        <v>60.64</v>
       </c>
       <c r="F236" t="n">
-        <v>21411</v>
+        <v>21687</v>
       </c>
     </row>
     <row r="237">
@@ -5221,10 +5221,10 @@
         <v>56.73</v>
       </c>
       <c r="E240" t="n">
-        <v>58.03</v>
+        <v>58.2</v>
       </c>
       <c r="F240" t="n">
-        <v>28317</v>
+        <v>28894</v>
       </c>
     </row>
     <row r="241">
@@ -5244,7 +5244,7 @@
         <v>56.63</v>
       </c>
       <c r="F241" t="n">
-        <v>30854</v>
+        <v>31264</v>
       </c>
     </row>
     <row r="242">
@@ -5321,10 +5321,10 @@
         <v>54.24</v>
       </c>
       <c r="E245" t="n">
-        <v>55.07</v>
+        <v>55.14</v>
       </c>
       <c r="F245" t="n">
-        <v>31638</v>
+        <v>31917</v>
       </c>
     </row>
     <row r="246">
@@ -5341,10 +5341,10 @@
         <v>54.2</v>
       </c>
       <c r="E246" t="n">
-        <v>54.48</v>
+        <v>54.45</v>
       </c>
       <c r="F246" t="n">
-        <v>25828</v>
+        <v>26144</v>
       </c>
     </row>
     <row r="247">
@@ -5421,10 +5421,10 @@
         <v>54.95</v>
       </c>
       <c r="E250" t="n">
-        <v>56.51</v>
+        <v>56.4</v>
       </c>
       <c r="F250" t="n">
-        <v>24675</v>
+        <v>24914</v>
       </c>
     </row>
     <row r="251">
@@ -5441,10 +5441,10 @@
         <v>56.13</v>
       </c>
       <c r="E251" t="n">
-        <v>57.32</v>
+        <v>57.33</v>
       </c>
       <c r="F251" t="n">
-        <v>21410</v>
+        <v>21778</v>
       </c>
     </row>
     <row r="252">
@@ -5521,10 +5521,10 @@
         <v>58.89</v>
       </c>
       <c r="E255" t="n">
-        <v>59.28</v>
+        <v>59.03</v>
       </c>
       <c r="F255" t="n">
-        <v>23121</v>
+        <v>23391</v>
       </c>
     </row>
     <row r="256">
@@ -5541,10 +5541,10 @@
         <v>57.71</v>
       </c>
       <c r="E256" t="n">
-        <v>58.33</v>
+        <v>58.44</v>
       </c>
       <c r="F256" t="n">
-        <v>26663</v>
+        <v>26971</v>
       </c>
     </row>
     <row r="257">
@@ -5621,10 +5621,10 @@
         <v>50.38</v>
       </c>
       <c r="E260" t="n">
-        <v>51.35</v>
+        <v>50.95</v>
       </c>
       <c r="F260" t="n">
-        <v>51199</v>
+        <v>52807</v>
       </c>
     </row>
     <row r="261">
@@ -5641,10 +5641,10 @@
         <v>48.92</v>
       </c>
       <c r="E261" t="n">
-        <v>50.01</v>
+        <v>50.08</v>
       </c>
       <c r="F261" t="n">
-        <v>71739</v>
+        <v>72794</v>
       </c>
     </row>
     <row r="262">
@@ -5721,10 +5721,10 @@
         <v>49.67</v>
       </c>
       <c r="E265" t="n">
-        <v>49.95</v>
+        <v>50</v>
       </c>
       <c r="F265" t="n">
-        <v>42080</v>
+        <v>42678</v>
       </c>
     </row>
     <row r="266">
@@ -5741,10 +5741,10 @@
         <v>45.16</v>
       </c>
       <c r="E266" t="n">
-        <v>45.55</v>
+        <v>45.51</v>
       </c>
       <c r="F266" t="n">
-        <v>64437</v>
+        <v>65295</v>
       </c>
     </row>
     <row r="267">
@@ -5812,7 +5812,7 @@
         <v>43902</v>
       </c>
       <c r="B270" t="n">
-        <v>35.97</v>
+        <v>36.29</v>
       </c>
       <c r="C270" t="n">
         <v>36.45</v>
@@ -5824,7 +5824,7 @@
         <v>33.49</v>
       </c>
       <c r="F270" t="n">
-        <v>66181</v>
+        <v>64469</v>
       </c>
     </row>
     <row r="271">
@@ -6121,10 +6121,10 @@
         <v>26.12</v>
       </c>
       <c r="E285" t="n">
-        <v>30.29</v>
+        <v>29.96</v>
       </c>
       <c r="F285" t="n">
-        <v>210087</v>
+        <v>214756</v>
       </c>
     </row>
     <row r="286">
@@ -6135,16 +6135,16 @@
         <v>29.95</v>
       </c>
       <c r="C286" t="n">
-        <v>35.24</v>
+        <v>35.28</v>
       </c>
       <c r="D286" t="n">
         <v>28.9</v>
       </c>
       <c r="E286" t="n">
-        <v>34.72</v>
+        <v>35.16</v>
       </c>
       <c r="F286" t="n">
-        <v>275171</v>
+        <v>280402</v>
       </c>
     </row>
     <row r="287">
@@ -6221,10 +6221,10 @@
         <v>32.46</v>
       </c>
       <c r="E290" t="n">
-        <v>33.2</v>
+        <v>32.8</v>
       </c>
       <c r="F290" t="n">
-        <v>230614</v>
+        <v>236196</v>
       </c>
     </row>
     <row r="291">
@@ -6321,10 +6321,10 @@
         <v>29.42</v>
       </c>
       <c r="E295" t="n">
-        <v>30.65</v>
+        <v>30.59</v>
       </c>
       <c r="F295" t="n">
-        <v>146842</v>
+        <v>151526</v>
       </c>
     </row>
     <row r="296">
@@ -6341,10 +6341,10 @@
         <v>30.13</v>
       </c>
       <c r="E296" t="n">
-        <v>30.78</v>
+        <v>30.68</v>
       </c>
       <c r="F296" t="n">
-        <v>171223</v>
+        <v>174982</v>
       </c>
     </row>
     <row r="297">
@@ -6421,10 +6421,10 @@
         <v>23.38</v>
       </c>
       <c r="E300" t="n">
-        <v>24.74</v>
+        <v>24.73</v>
       </c>
       <c r="F300" t="n">
-        <v>213310</v>
+        <v>216653</v>
       </c>
     </row>
     <row r="301">
@@ -6441,10 +6441,10 @@
         <v>23.7</v>
       </c>
       <c r="E301" t="n">
-        <v>24.98</v>
+        <v>24.99</v>
       </c>
       <c r="F301" t="n">
-        <v>163124</v>
+        <v>166443</v>
       </c>
     </row>
     <row r="302">
@@ -6521,10 +6521,10 @@
         <v>24.33</v>
       </c>
       <c r="E305" t="n">
-        <v>26.83</v>
+        <v>26.85</v>
       </c>
       <c r="F305" t="n">
-        <v>224455</v>
+        <v>229615</v>
       </c>
     </row>
     <row r="306">
@@ -6541,10 +6541,10 @@
         <v>26.05</v>
       </c>
       <c r="E306" t="n">
-        <v>26.78</v>
+        <v>26.81</v>
       </c>
       <c r="F306" t="n">
-        <v>196748</v>
+        <v>199609</v>
       </c>
     </row>
     <row r="307">
@@ -6621,10 +6621,10 @@
         <v>29.4</v>
       </c>
       <c r="E310" t="n">
-        <v>29.48</v>
+        <v>29.65</v>
       </c>
       <c r="F310" t="n">
-        <v>225301</v>
+        <v>229585</v>
       </c>
     </row>
     <row r="311">
@@ -6641,10 +6641,10 @@
         <v>29.63</v>
       </c>
       <c r="E311" t="n">
-        <v>31.26</v>
+        <v>31.25</v>
       </c>
       <c r="F311" t="n">
-        <v>192233</v>
+        <v>195288</v>
       </c>
     </row>
     <row r="312">
@@ -6715,16 +6715,16 @@
         <v>29.73</v>
       </c>
       <c r="C315" t="n">
-        <v>31.65</v>
+        <v>31.75</v>
       </c>
       <c r="D315" t="n">
         <v>29.32</v>
       </c>
       <c r="E315" t="n">
-        <v>31.44</v>
+        <v>31.58</v>
       </c>
       <c r="F315" t="n">
-        <v>152193</v>
+        <v>156389</v>
       </c>
     </row>
     <row r="316">
@@ -6735,16 +6735,16 @@
         <v>31.58</v>
       </c>
       <c r="C316" t="n">
-        <v>32.96</v>
+        <v>33.06</v>
       </c>
       <c r="D316" t="n">
         <v>31.23</v>
       </c>
       <c r="E316" t="n">
-        <v>32.9</v>
+        <v>32.94</v>
       </c>
       <c r="F316" t="n">
-        <v>160121</v>
+        <v>163209</v>
       </c>
     </row>
     <row r="317">
@@ -6821,10 +6821,10 @@
         <v>35.92</v>
       </c>
       <c r="E320" t="n">
-        <v>36.38</v>
+        <v>36.3</v>
       </c>
       <c r="F320" t="n">
-        <v>157279</v>
+        <v>160329</v>
       </c>
     </row>
     <row r="321">
@@ -6841,10 +6841,10 @@
         <v>33.87</v>
       </c>
       <c r="E321" t="n">
-        <v>35.66</v>
+        <v>35.52</v>
       </c>
       <c r="F321" t="n">
-        <v>194062</v>
+        <v>198023</v>
       </c>
     </row>
     <row r="322">
@@ -6921,10 +6921,10 @@
         <v>34.37</v>
       </c>
       <c r="E325" t="n">
-        <v>35.89</v>
+        <v>35.98</v>
       </c>
       <c r="F325" t="n">
-        <v>208524</v>
+        <v>213086</v>
       </c>
     </row>
     <row r="326">
@@ -6941,10 +6941,10 @@
         <v>34.87</v>
       </c>
       <c r="E326" t="n">
-        <v>37.43</v>
+        <v>37.61</v>
       </c>
       <c r="F326" t="n">
-        <v>193664</v>
+        <v>198370</v>
       </c>
     </row>
     <row r="327">
@@ -7021,10 +7021,10 @@
         <v>39.05</v>
       </c>
       <c r="E330" t="n">
-        <v>39.78</v>
+        <v>39.92</v>
       </c>
       <c r="F330" t="n">
-        <v>158433</v>
+        <v>161661</v>
       </c>
     </row>
     <row r="331">
@@ -7041,10 +7041,10 @@
         <v>39.75</v>
       </c>
       <c r="E331" t="n">
-        <v>42.14</v>
+        <v>41.83</v>
       </c>
       <c r="F331" t="n">
-        <v>163467</v>
+        <v>167359</v>
       </c>
     </row>
     <row r="332">
@@ -7121,10 +7121,10 @@
         <v>37.96</v>
       </c>
       <c r="E335" t="n">
-        <v>38.36</v>
+        <v>38.41</v>
       </c>
       <c r="F335" t="n">
-        <v>221502</v>
+        <v>227925</v>
       </c>
     </row>
     <row r="336">
@@ -7141,10 +7141,10 @@
         <v>37.14</v>
       </c>
       <c r="E336" t="n">
-        <v>38.94</v>
+        <v>38.97</v>
       </c>
       <c r="F336" t="n">
-        <v>260674</v>
+        <v>263342</v>
       </c>
     </row>
     <row r="337">
@@ -7221,10 +7221,10 @@
         <v>40.05</v>
       </c>
       <c r="E340" t="n">
-        <v>41.37</v>
+        <v>41.33</v>
       </c>
       <c r="F340" t="n">
-        <v>161532</v>
+        <v>163774</v>
       </c>
     </row>
     <row r="341">
@@ -7241,10 +7241,10 @@
         <v>40.97</v>
       </c>
       <c r="E341" t="n">
-        <v>41.99</v>
+        <v>41.78</v>
       </c>
       <c r="F341" t="n">
-        <v>153177</v>
+        <v>156573</v>
       </c>
     </row>
     <row r="342">
@@ -7315,16 +7315,16 @@
         <v>40.45</v>
       </c>
       <c r="C345" t="n">
-        <v>41.51</v>
+        <v>41.59</v>
       </c>
       <c r="D345" t="n">
         <v>39.68</v>
       </c>
       <c r="E345" t="n">
-        <v>41.39</v>
+        <v>41.35</v>
       </c>
       <c r="F345" t="n">
-        <v>178413</v>
+        <v>181021</v>
       </c>
     </row>
     <row r="346">
@@ -7341,10 +7341,10 @@
         <v>40.25</v>
       </c>
       <c r="E346" t="n">
-        <v>40.58</v>
+        <v>40.57</v>
       </c>
       <c r="F346" t="n">
-        <v>157969</v>
+        <v>160433</v>
       </c>
     </row>
     <row r="347">
@@ -7421,10 +7421,10 @@
         <v>41.71</v>
       </c>
       <c r="E350" t="n">
-        <v>42.71</v>
+        <v>42.65</v>
       </c>
       <c r="F350" t="n">
-        <v>142409</v>
+        <v>144329</v>
       </c>
     </row>
     <row r="351">
@@ -7521,10 +7521,10 @@
         <v>41.99</v>
       </c>
       <c r="E355" t="n">
-        <v>42.32</v>
+        <v>42.35</v>
       </c>
       <c r="F355" t="n">
-        <v>133908</v>
+        <v>136451</v>
       </c>
     </row>
     <row r="356">
@@ -7541,10 +7541,10 @@
         <v>41.4</v>
       </c>
       <c r="E356" t="n">
-        <v>43.23</v>
+        <v>43.26</v>
       </c>
       <c r="F356" t="n">
-        <v>152491</v>
+        <v>154800</v>
       </c>
     </row>
     <row r="357">
@@ -7621,10 +7621,10 @@
         <v>43.19</v>
       </c>
       <c r="E360" t="n">
-        <v>43.36</v>
+        <v>43.28</v>
       </c>
       <c r="F360" t="n">
-        <v>99613</v>
+        <v>101544</v>
       </c>
     </row>
     <row r="361">
@@ -7641,10 +7641,10 @@
         <v>42.7</v>
       </c>
       <c r="E361" t="n">
-        <v>43.18</v>
+        <v>43.12</v>
       </c>
       <c r="F361" t="n">
-        <v>93740</v>
+        <v>95049</v>
       </c>
     </row>
     <row r="362">
@@ -7721,10 +7721,10 @@
         <v>43.42</v>
       </c>
       <c r="E365" t="n">
-        <v>43.82</v>
+        <v>43.53</v>
       </c>
       <c r="F365" t="n">
-        <v>109900</v>
+        <v>112495</v>
       </c>
     </row>
     <row r="366">
@@ -7741,10 +7741,10 @@
         <v>43.18</v>
       </c>
       <c r="E366" t="n">
-        <v>43.67</v>
+        <v>43.62</v>
       </c>
       <c r="F366" t="n">
-        <v>115737</v>
+        <v>117377</v>
       </c>
     </row>
     <row r="367">
@@ -7821,10 +7821,10 @@
         <v>41.95</v>
       </c>
       <c r="E370" t="n">
-        <v>43.43</v>
+        <v>43.56</v>
       </c>
       <c r="F370" t="n">
-        <v>113377</v>
+        <v>117072</v>
       </c>
     </row>
     <row r="371">
@@ -7841,10 +7841,10 @@
         <v>42.94</v>
       </c>
       <c r="E371" t="n">
-        <v>43.65</v>
+        <v>43.59</v>
       </c>
       <c r="F371" t="n">
-        <v>127155</v>
+        <v>128800</v>
       </c>
     </row>
     <row r="372">
@@ -7921,10 +7921,10 @@
         <v>44.96</v>
       </c>
       <c r="E375" t="n">
-        <v>45.28</v>
+        <v>45.13</v>
       </c>
       <c r="F375" t="n">
-        <v>120720</v>
+        <v>122044</v>
       </c>
     </row>
     <row r="376">
@@ -7941,10 +7941,10 @@
         <v>44.4</v>
       </c>
       <c r="E376" t="n">
-        <v>44.76</v>
+        <v>44.71</v>
       </c>
       <c r="F376" t="n">
-        <v>119541</v>
+        <v>120731</v>
       </c>
     </row>
     <row r="377">
@@ -8021,10 +8021,10 @@
         <v>45.07</v>
       </c>
       <c r="E380" t="n">
-        <v>45.3</v>
+        <v>45.24</v>
       </c>
       <c r="F380" t="n">
-        <v>90204</v>
+        <v>91702</v>
       </c>
     </row>
     <row r="381">
@@ -8041,10 +8041,10 @@
         <v>44.77</v>
       </c>
       <c r="E381" t="n">
-        <v>45.2</v>
+        <v>45.19</v>
       </c>
       <c r="F381" t="n">
-        <v>83793</v>
+        <v>85013</v>
       </c>
     </row>
     <row r="382">
@@ -8121,10 +8121,10 @@
         <v>44.46</v>
       </c>
       <c r="E385" t="n">
-        <v>45.36</v>
+        <v>45.27</v>
       </c>
       <c r="F385" t="n">
-        <v>86301</v>
+        <v>87294</v>
       </c>
     </row>
     <row r="386">
@@ -8141,10 +8141,10 @@
         <v>44.09</v>
       </c>
       <c r="E386" t="n">
-        <v>44.79</v>
+        <v>44.69</v>
       </c>
       <c r="F386" t="n">
-        <v>77659</v>
+        <v>78965</v>
       </c>
     </row>
     <row r="387">
@@ -8224,7 +8224,7 @@
         <v>45.59</v>
       </c>
       <c r="F390" t="n">
-        <v>95873</v>
+        <v>96916</v>
       </c>
     </row>
     <row r="391">
@@ -8241,10 +8241,10 @@
         <v>45.36</v>
       </c>
       <c r="E391" t="n">
-        <v>45.89</v>
+        <v>45.85</v>
       </c>
       <c r="F391" t="n">
-        <v>81058</v>
+        <v>81841</v>
       </c>
     </row>
     <row r="392">
@@ -8321,10 +8321,10 @@
         <v>43.27</v>
       </c>
       <c r="E395" t="n">
-        <v>44.09</v>
+        <v>44.07</v>
       </c>
       <c r="F395" t="n">
-        <v>157249</v>
+        <v>158723</v>
       </c>
     </row>
     <row r="396">
@@ -8338,13 +8338,13 @@
         <v>44.69</v>
       </c>
       <c r="D396" t="n">
-        <v>42.45</v>
+        <v>42.42</v>
       </c>
       <c r="E396" t="n">
-        <v>42.53</v>
+        <v>42.43</v>
       </c>
       <c r="F396" t="n">
-        <v>160902</v>
+        <v>162787</v>
       </c>
     </row>
     <row r="397">
@@ -8418,13 +8418,13 @@
         <v>41.23</v>
       </c>
       <c r="D400" t="n">
-        <v>40.02</v>
+        <v>39.96</v>
       </c>
       <c r="E400" t="n">
-        <v>40.07</v>
+        <v>39.97</v>
       </c>
       <c r="F400" t="n">
-        <v>147551</v>
+        <v>149451</v>
       </c>
     </row>
     <row r="401">
@@ -8441,10 +8441,10 @@
         <v>39.68</v>
       </c>
       <c r="E401" t="n">
-        <v>40.24</v>
+        <v>40.02</v>
       </c>
       <c r="F401" t="n">
-        <v>133943</v>
+        <v>135456</v>
       </c>
     </row>
     <row r="402">
@@ -8521,10 +8521,10 @@
         <v>41.89</v>
       </c>
       <c r="E405" t="n">
-        <v>43.67</v>
+        <v>43.58</v>
       </c>
       <c r="F405" t="n">
-        <v>141089</v>
+        <v>142611</v>
       </c>
     </row>
     <row r="406">
@@ -8541,10 +8541,10 @@
         <v>42.92</v>
       </c>
       <c r="E406" t="n">
-        <v>43.34</v>
+        <v>43.41</v>
       </c>
       <c r="F406" t="n">
-        <v>127380</v>
+        <v>129546</v>
       </c>
     </row>
     <row r="407">
@@ -8621,10 +8621,10 @@
         <v>41.68</v>
       </c>
       <c r="E410" t="n">
-        <v>42.27</v>
+        <v>42.16</v>
       </c>
       <c r="F410" t="n">
-        <v>132502</v>
+        <v>133961</v>
       </c>
     </row>
     <row r="411">
@@ -8641,10 +8641,10 @@
         <v>41.97</v>
       </c>
       <c r="E411" t="n">
-        <v>42.24</v>
+        <v>42.17</v>
       </c>
       <c r="F411" t="n">
-        <v>100264</v>
+        <v>102107</v>
       </c>
     </row>
     <row r="412">
@@ -8721,10 +8721,10 @@
         <v>39.98</v>
       </c>
       <c r="E415" t="n">
-        <v>40.93</v>
+        <v>40.75</v>
       </c>
       <c r="F415" t="n">
-        <v>155461</v>
+        <v>157712</v>
       </c>
     </row>
     <row r="416">
@@ -8741,10 +8741,10 @@
         <v>38.88</v>
       </c>
       <c r="E416" t="n">
-        <v>39.23</v>
+        <v>39.15</v>
       </c>
       <c r="F416" t="n">
-        <v>188336</v>
+        <v>190634</v>
       </c>
     </row>
     <row r="417">
@@ -8821,10 +8821,10 @@
         <v>42.02</v>
       </c>
       <c r="E420" t="n">
-        <v>43.54</v>
+        <v>43.52</v>
       </c>
       <c r="F420" t="n">
-        <v>110782</v>
+        <v>112342</v>
       </c>
     </row>
     <row r="421">
@@ -8841,10 +8841,10 @@
         <v>42.78</v>
       </c>
       <c r="E421" t="n">
-        <v>42.96</v>
+        <v>42.89</v>
       </c>
       <c r="F421" t="n">
-        <v>108274</v>
+        <v>109695</v>
       </c>
     </row>
     <row r="422">
@@ -8921,10 +8921,10 @@
         <v>41.79</v>
       </c>
       <c r="E425" t="n">
-        <v>43.38</v>
+        <v>43.26</v>
       </c>
       <c r="F425" t="n">
-        <v>146298</v>
+        <v>147757</v>
       </c>
     </row>
     <row r="426">
@@ -8941,10 +8941,10 @@
         <v>42.47</v>
       </c>
       <c r="E426" t="n">
-        <v>43.02</v>
+        <v>42.95</v>
       </c>
       <c r="F426" t="n">
-        <v>129338</v>
+        <v>130839</v>
       </c>
     </row>
     <row r="427">
@@ -9021,10 +9021,10 @@
         <v>41.72</v>
       </c>
       <c r="E430" t="n">
-        <v>42.71</v>
+        <v>42.59</v>
       </c>
       <c r="F430" t="n">
-        <v>108471</v>
+        <v>110171</v>
       </c>
     </row>
     <row r="431">
@@ -9041,10 +9041,10 @@
         <v>41.76</v>
       </c>
       <c r="E431" t="n">
-        <v>41.93</v>
+        <v>41.85</v>
       </c>
       <c r="F431" t="n">
-        <v>95688</v>
+        <v>97195</v>
       </c>
     </row>
     <row r="432">
@@ -9112,7 +9112,7 @@
         <v>44133</v>
       </c>
       <c r="B435" t="n">
-        <v>39.52</v>
+        <v>39.76</v>
       </c>
       <c r="C435" t="n">
         <v>39.97</v>
@@ -9124,7 +9124,7 @@
         <v>38.05</v>
       </c>
       <c r="F435" t="n">
-        <v>183949</v>
+        <v>179602</v>
       </c>
     </row>
     <row r="436">
@@ -9132,7 +9132,7 @@
         <v>44134</v>
       </c>
       <c r="B436" t="n">
-        <v>38.05</v>
+        <v>38.25</v>
       </c>
       <c r="C436" t="n">
         <v>38.72</v>
@@ -9144,7 +9144,7 @@
         <v>37.84</v>
       </c>
       <c r="F436" t="n">
-        <v>184633</v>
+        <v>181739</v>
       </c>
     </row>
     <row r="437">
@@ -9221,10 +9221,10 @@
         <v>40.42</v>
       </c>
       <c r="E440" t="n">
-        <v>40.82</v>
+        <v>40.68</v>
       </c>
       <c r="F440" t="n">
-        <v>155706</v>
+        <v>157779</v>
       </c>
     </row>
     <row r="441">
@@ -9241,10 +9241,10 @@
         <v>39.46</v>
       </c>
       <c r="E441" t="n">
-        <v>39.84</v>
+        <v>39.71</v>
       </c>
       <c r="F441" t="n">
-        <v>150078</v>
+        <v>151438</v>
       </c>
     </row>
     <row r="442">
@@ -9318,13 +9318,13 @@
         <v>44.59</v>
       </c>
       <c r="D445" t="n">
-        <v>43.42</v>
+        <v>43.35</v>
       </c>
       <c r="E445" t="n">
-        <v>43.49</v>
+        <v>43.38</v>
       </c>
       <c r="F445" t="n">
-        <v>144322</v>
+        <v>146964</v>
       </c>
     </row>
     <row r="446">
@@ -9338,13 +9338,13 @@
         <v>43.45</v>
       </c>
       <c r="D446" t="n">
-        <v>42.77</v>
+        <v>42.68</v>
       </c>
       <c r="E446" t="n">
-        <v>42.88</v>
+        <v>42.69</v>
       </c>
       <c r="F446" t="n">
-        <v>112789</v>
+        <v>114191</v>
       </c>
     </row>
     <row r="447">
@@ -9421,10 +9421,10 @@
         <v>43.87</v>
       </c>
       <c r="E450" t="n">
-        <v>44.44</v>
+        <v>44.21</v>
       </c>
       <c r="F450" t="n">
-        <v>111013</v>
+        <v>112468</v>
       </c>
     </row>
     <row r="451">
@@ -9441,10 +9441,10 @@
         <v>44.15</v>
       </c>
       <c r="E451" t="n">
-        <v>45.06</v>
+        <v>45.07</v>
       </c>
       <c r="F451" t="n">
-        <v>88612</v>
+        <v>90427</v>
       </c>
     </row>
     <row r="452">
@@ -9624,7 +9624,7 @@
         <v>48.65</v>
       </c>
       <c r="F460" t="n">
-        <v>119976</v>
+        <v>122403</v>
       </c>
     </row>
     <row r="461">
@@ -9641,10 +9641,10 @@
         <v>48.77</v>
       </c>
       <c r="E461" t="n">
-        <v>48.97</v>
+        <v>48.96</v>
       </c>
       <c r="F461" t="n">
-        <v>124413</v>
+        <v>125701</v>
       </c>
     </row>
     <row r="462">
@@ -9721,10 +9721,10 @@
         <v>48.79</v>
       </c>
       <c r="E465" t="n">
-        <v>50.26</v>
+        <v>50.25</v>
       </c>
       <c r="F465" t="n">
-        <v>130125</v>
+        <v>132386</v>
       </c>
     </row>
     <row r="466">
@@ -9741,10 +9741,10 @@
         <v>49.67</v>
       </c>
       <c r="E466" t="n">
-        <v>49.94</v>
+        <v>49.86</v>
       </c>
       <c r="F466" t="n">
-        <v>123293</v>
+        <v>124721</v>
       </c>
     </row>
     <row r="467">
@@ -9821,10 +9821,10 @@
         <v>51.06</v>
       </c>
       <c r="E470" t="n">
-        <v>51.55</v>
+        <v>51.46</v>
       </c>
       <c r="F470" t="n">
-        <v>100894</v>
+        <v>102867</v>
       </c>
     </row>
     <row r="471">
@@ -9841,10 +9841,10 @@
         <v>51.16</v>
       </c>
       <c r="E471" t="n">
-        <v>52.19</v>
+        <v>52.23</v>
       </c>
       <c r="F471" t="n">
-        <v>96861</v>
+        <v>98705</v>
       </c>
     </row>
     <row r="472">
@@ -10081,10 +10081,10 @@
         <v>53.88</v>
       </c>
       <c r="E483" t="n">
-        <v>54.45</v>
+        <v>54.34</v>
       </c>
       <c r="F483" t="n">
-        <v>140683</v>
+        <v>142258</v>
       </c>
     </row>
     <row r="484">
@@ -10095,16 +10095,16 @@
         <v>54.46</v>
       </c>
       <c r="C484" t="n">
-        <v>56.06</v>
+        <v>56.2</v>
       </c>
       <c r="D484" t="n">
         <v>54.3</v>
       </c>
       <c r="E484" t="n">
-        <v>56.02</v>
+        <v>56.11</v>
       </c>
       <c r="F484" t="n">
-        <v>151805</v>
+        <v>155413</v>
       </c>
     </row>
     <row r="485">
@@ -10181,10 +10181,10 @@
         <v>55.21</v>
       </c>
       <c r="E488" t="n">
-        <v>56.3</v>
+        <v>56.37</v>
       </c>
       <c r="F488" t="n">
-        <v>123090</v>
+        <v>125098</v>
       </c>
     </row>
     <row r="489">
@@ -10201,10 +10201,10 @@
         <v>54.63</v>
       </c>
       <c r="E489" t="n">
-        <v>54.94</v>
+        <v>54.75</v>
       </c>
       <c r="F489" t="n">
-        <v>133988</v>
+        <v>135898</v>
       </c>
     </row>
     <row r="490">
@@ -10281,10 +10281,10 @@
         <v>55.38</v>
       </c>
       <c r="E493" t="n">
-        <v>55.86</v>
+        <v>55.84</v>
       </c>
       <c r="F493" t="n">
-        <v>103188</v>
+        <v>104851</v>
       </c>
     </row>
     <row r="494">
@@ -10301,10 +10301,10 @@
         <v>54.38</v>
       </c>
       <c r="E494" t="n">
-        <v>55.08</v>
+        <v>54.88</v>
       </c>
       <c r="F494" t="n">
-        <v>133367</v>
+        <v>135622</v>
       </c>
     </row>
     <row r="495">
@@ -10378,13 +10378,13 @@
         <v>56.16</v>
       </c>
       <c r="D498" t="n">
-        <v>54.93</v>
+        <v>54.84</v>
       </c>
       <c r="E498" t="n">
-        <v>55</v>
+        <v>54.84</v>
       </c>
       <c r="F498" t="n">
-        <v>160473</v>
+        <v>162289</v>
       </c>
     </row>
     <row r="499">
@@ -10401,10 +10401,10 @@
         <v>54.84</v>
       </c>
       <c r="E499" t="n">
-        <v>55</v>
+        <v>54.93</v>
       </c>
       <c r="F499" t="n">
-        <v>160923</v>
+        <v>163671</v>
       </c>
     </row>
     <row r="500">
@@ -10481,10 +10481,10 @@
         <v>57.93</v>
       </c>
       <c r="E503" t="n">
-        <v>58.79</v>
+        <v>58.87</v>
       </c>
       <c r="F503" t="n">
-        <v>123567</v>
+        <v>125851</v>
       </c>
     </row>
     <row r="504">
@@ -10501,10 +10501,10 @@
         <v>58.87</v>
       </c>
       <c r="E504" t="n">
-        <v>59.31</v>
+        <v>59.41</v>
       </c>
       <c r="F504" t="n">
-        <v>118436</v>
+        <v>120954</v>
       </c>
     </row>
     <row r="505">
@@ -10578,13 +10578,13 @@
         <v>61.23</v>
       </c>
       <c r="D508" t="n">
-        <v>60.5</v>
+        <v>60.44</v>
       </c>
       <c r="E508" t="n">
-        <v>60.6</v>
+        <v>60.52</v>
       </c>
       <c r="F508" t="n">
-        <v>104511</v>
+        <v>107974</v>
       </c>
     </row>
     <row r="509">
@@ -10604,7 +10604,7 @@
         <v>62.22</v>
       </c>
       <c r="F509" t="n">
-        <v>123306</v>
+        <v>126905</v>
       </c>
     </row>
     <row r="510">
@@ -10681,10 +10681,10 @@
         <v>62.54</v>
       </c>
       <c r="E513" t="n">
-        <v>62.75</v>
+        <v>62.88</v>
       </c>
       <c r="F513" t="n">
-        <v>170306</v>
+        <v>173632</v>
       </c>
     </row>
     <row r="514">
@@ -10701,10 +10701,10 @@
         <v>61.42</v>
       </c>
       <c r="E514" t="n">
-        <v>61.95</v>
+        <v>61.97</v>
       </c>
       <c r="F514" t="n">
-        <v>181146</v>
+        <v>184306</v>
       </c>
     </row>
     <row r="515">
@@ -10781,10 +10781,10 @@
         <v>65.55</v>
       </c>
       <c r="E518" t="n">
-        <v>65.86</v>
+        <v>65.97</v>
       </c>
       <c r="F518" t="n">
-        <v>210726</v>
+        <v>215533</v>
       </c>
     </row>
     <row r="519">
@@ -10801,10 +10801,10 @@
         <v>64.13</v>
       </c>
       <c r="E519" t="n">
-        <v>64.25</v>
+        <v>64.27</v>
       </c>
       <c r="F519" t="n">
-        <v>234931</v>
+        <v>239274</v>
       </c>
     </row>
     <row r="520">
@@ -10881,10 +10881,10 @@
         <v>63.17</v>
       </c>
       <c r="E523" t="n">
-        <v>66.94</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="F523" t="n">
-        <v>225843</v>
+        <v>230530</v>
       </c>
     </row>
     <row r="524">
@@ -10895,16 +10895,16 @@
         <v>66.86</v>
       </c>
       <c r="C524" t="n">
-        <v>69.31999999999999</v>
+        <v>69.41</v>
       </c>
       <c r="D524" t="n">
         <v>66.43000000000001</v>
       </c>
       <c r="E524" t="n">
-        <v>69.28</v>
+        <v>69.25</v>
       </c>
       <c r="F524" t="n">
-        <v>249828</v>
+        <v>253026</v>
       </c>
     </row>
     <row r="525">
@@ -10981,10 +10981,10 @@
         <v>67.68000000000001</v>
       </c>
       <c r="E528" t="n">
-        <v>69.40000000000001</v>
+        <v>69.17</v>
       </c>
       <c r="F528" t="n">
-        <v>160838</v>
+        <v>163581</v>
       </c>
     </row>
     <row r="529">
@@ -11001,10 +11001,10 @@
         <v>68.66</v>
       </c>
       <c r="E529" t="n">
-        <v>68.88</v>
+        <v>68.81</v>
       </c>
       <c r="F529" t="n">
-        <v>148823</v>
+        <v>151042</v>
       </c>
     </row>
     <row r="530">
@@ -11072,7 +11072,7 @@
         <v>44273</v>
       </c>
       <c r="B533" t="n">
-        <v>67.48</v>
+        <v>67.47</v>
       </c>
       <c r="C533" t="n">
         <v>67.83</v>
@@ -11084,7 +11084,7 @@
         <v>62.5</v>
       </c>
       <c r="F533" t="n">
-        <v>212082</v>
+        <v>209835</v>
       </c>
     </row>
     <row r="534">
@@ -11092,7 +11092,7 @@
         <v>44274</v>
       </c>
       <c r="B534" t="n">
-        <v>62.78</v>
+        <v>63.02</v>
       </c>
       <c r="C534" t="n">
         <v>64.73</v>
@@ -11104,7 +11104,7 @@
         <v>64.31999999999999</v>
       </c>
       <c r="F534" t="n">
-        <v>228148</v>
+        <v>223529</v>
       </c>
     </row>
     <row r="535">
@@ -11172,10 +11172,10 @@
         <v>44280</v>
       </c>
       <c r="B538" t="n">
-        <v>63.95</v>
+        <v>63.89</v>
       </c>
       <c r="C538" t="n">
-        <v>64.01000000000001</v>
+        <v>63.9</v>
       </c>
       <c r="D538" t="n">
         <v>60.82</v>
@@ -11184,7 +11184,7 @@
         <v>61.47</v>
       </c>
       <c r="F538" t="n">
-        <v>206155</v>
+        <v>203253</v>
       </c>
     </row>
     <row r="539">
@@ -11192,19 +11192,19 @@
         <v>44281</v>
       </c>
       <c r="B539" t="n">
-        <v>61.47</v>
+        <v>62.45</v>
       </c>
       <c r="C539" t="n">
         <v>64.73</v>
       </c>
       <c r="D539" t="n">
-        <v>61.47</v>
+        <v>62.07</v>
       </c>
       <c r="E539" t="n">
         <v>64.19</v>
       </c>
       <c r="F539" t="n">
-        <v>171041</v>
+        <v>167422</v>
       </c>
     </row>
     <row r="540">
@@ -11284,7 +11284,7 @@
         <v>64.51000000000001</v>
       </c>
       <c r="F543" t="n">
-        <v>197783</v>
+        <v>201289</v>
       </c>
     </row>
     <row r="544">
@@ -11361,10 +11361,10 @@
         <v>62.18</v>
       </c>
       <c r="E547" t="n">
-        <v>63.07</v>
+        <v>63.04</v>
       </c>
       <c r="F547" t="n">
-        <v>146277</v>
+        <v>149186</v>
       </c>
     </row>
     <row r="548">
@@ -11381,10 +11381,10 @@
         <v>62.33</v>
       </c>
       <c r="E548" t="n">
-        <v>62.81</v>
+        <v>62.76</v>
       </c>
       <c r="F548" t="n">
-        <v>119219</v>
+        <v>121247</v>
       </c>
     </row>
     <row r="549">
@@ -11461,10 +11461,10 @@
         <v>65.65000000000001</v>
       </c>
       <c r="E552" t="n">
-        <v>66.5</v>
+        <v>66.45</v>
       </c>
       <c r="F552" t="n">
-        <v>133306</v>
+        <v>135521</v>
       </c>
     </row>
     <row r="553">
@@ -11481,10 +11481,10 @@
         <v>66.11</v>
       </c>
       <c r="E553" t="n">
-        <v>66.40000000000001</v>
+        <v>66.31999999999999</v>
       </c>
       <c r="F553" t="n">
-        <v>120895</v>
+        <v>122938</v>
       </c>
     </row>
     <row r="554">
@@ -11564,7 +11564,7 @@
         <v>64.95</v>
       </c>
       <c r="F557" t="n">
-        <v>140975</v>
+        <v>143350</v>
       </c>
     </row>
     <row r="558">
@@ -11581,10 +11581,10 @@
         <v>64.52</v>
       </c>
       <c r="E558" t="n">
-        <v>65.45</v>
+        <v>65.31999999999999</v>
       </c>
       <c r="F558" t="n">
-        <v>124432</v>
+        <v>126302</v>
       </c>
     </row>
     <row r="559">
@@ -11661,10 +11661,10 @@
         <v>66.56</v>
       </c>
       <c r="E562" t="n">
-        <v>67.86</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="F562" t="n">
-        <v>157092</v>
+        <v>160482</v>
       </c>
     </row>
     <row r="563">
@@ -11681,10 +11681,10 @@
         <v>66.17</v>
       </c>
       <c r="E563" t="n">
-        <v>66.56</v>
+        <v>66.53</v>
       </c>
       <c r="F563" t="n">
-        <v>145779</v>
+        <v>148372</v>
       </c>
     </row>
     <row r="564">
@@ -11761,10 +11761,10 @@
         <v>67.77</v>
       </c>
       <c r="E567" t="n">
-        <v>68.05</v>
+        <v>68.03</v>
       </c>
       <c r="F567" t="n">
-        <v>153533</v>
+        <v>155507</v>
       </c>
     </row>
     <row r="568">
@@ -11784,7 +11784,7 @@
         <v>68.03</v>
       </c>
       <c r="F568" t="n">
-        <v>136012</v>
+        <v>139157</v>
       </c>
     </row>
     <row r="569">
@@ -11861,10 +11861,10 @@
         <v>66.34</v>
       </c>
       <c r="E572" t="n">
-        <v>66.83</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="F572" t="n">
-        <v>180093</v>
+        <v>182316</v>
       </c>
     </row>
     <row r="573">
@@ -11875,16 +11875,16 @@
         <v>66.81</v>
       </c>
       <c r="C573" t="n">
-        <v>68.52</v>
+        <v>68.63</v>
       </c>
       <c r="D573" t="n">
         <v>66.36</v>
       </c>
       <c r="E573" t="n">
-        <v>68.45</v>
+        <v>68.52</v>
       </c>
       <c r="F573" t="n">
-        <v>139950</v>
+        <v>142226</v>
       </c>
     </row>
     <row r="574">
@@ -11958,13 +11958,13 @@
         <v>67.02</v>
       </c>
       <c r="D577" t="n">
-        <v>64.73</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="E577" t="n">
-        <v>64.98999999999999</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="F577" t="n">
-        <v>164782</v>
+        <v>168733</v>
       </c>
     </row>
     <row r="578">
@@ -11981,10 +11981,10 @@
         <v>64.48</v>
       </c>
       <c r="E578" t="n">
-        <v>66.58</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="F578" t="n">
-        <v>153693</v>
+        <v>156317</v>
       </c>
     </row>
     <row r="579">
@@ -12055,16 +12055,16 @@
         <v>68.58</v>
       </c>
       <c r="C582" t="n">
-        <v>69.18000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="D582" t="n">
         <v>67.89</v>
       </c>
       <c r="E582" t="n">
-        <v>69.05</v>
+        <v>69.12</v>
       </c>
       <c r="F582" t="n">
-        <v>119490</v>
+        <v>122427</v>
       </c>
     </row>
     <row r="583">
@@ -12081,10 +12081,10 @@
         <v>68.48999999999999</v>
       </c>
       <c r="E583" t="n">
-        <v>68.89</v>
+        <v>68.88</v>
       </c>
       <c r="F583" t="n">
-        <v>119218</v>
+        <v>121324</v>
       </c>
     </row>
     <row r="584">
@@ -12161,10 +12161,10 @@
         <v>70.5</v>
       </c>
       <c r="E587" t="n">
-        <v>71.20999999999999</v>
+        <v>71.22</v>
       </c>
       <c r="F587" t="n">
-        <v>126247</v>
+        <v>128649</v>
       </c>
     </row>
     <row r="588">
@@ -12181,10 +12181,10 @@
         <v>70.58</v>
       </c>
       <c r="E588" t="n">
-        <v>71.47</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="F588" t="n">
-        <v>113793</v>
+        <v>117041</v>
       </c>
     </row>
     <row r="589">
@@ -12261,10 +12261,10 @@
         <v>70.66</v>
       </c>
       <c r="E592" t="n">
-        <v>72.09</v>
+        <v>71.95</v>
       </c>
       <c r="F592" t="n">
-        <v>146487</v>
+        <v>148450</v>
       </c>
     </row>
     <row r="593">
@@ -12284,7 +12284,7 @@
         <v>72.23999999999999</v>
       </c>
       <c r="F593" t="n">
-        <v>140128</v>
+        <v>142367</v>
       </c>
     </row>
     <row r="594">
@@ -12361,10 +12361,10 @@
         <v>71.41</v>
       </c>
       <c r="E597" t="n">
-        <v>72.45</v>
+        <v>72.44</v>
       </c>
       <c r="F597" t="n">
-        <v>175025</v>
+        <v>178094</v>
       </c>
     </row>
     <row r="598">
@@ -12381,10 +12381,10 @@
         <v>71.55</v>
       </c>
       <c r="E598" t="n">
-        <v>72.76000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="F598" t="n">
-        <v>147859</v>
+        <v>151345</v>
       </c>
     </row>
     <row r="599">
@@ -12461,10 +12461,10 @@
         <v>73.83</v>
       </c>
       <c r="E602" t="n">
-        <v>74.79000000000001</v>
+        <v>74.81</v>
       </c>
       <c r="F602" t="n">
-        <v>84577</v>
+        <v>85692</v>
       </c>
     </row>
     <row r="603">
@@ -12481,10 +12481,10 @@
         <v>74.14</v>
       </c>
       <c r="E603" t="n">
-        <v>75.27</v>
+        <v>75.28</v>
       </c>
       <c r="F603" t="n">
-        <v>77990</v>
+        <v>79112</v>
       </c>
     </row>
     <row r="604">
@@ -12561,10 +12561,10 @@
         <v>74.36</v>
       </c>
       <c r="E607" t="n">
-        <v>75.33</v>
+        <v>75.34</v>
       </c>
       <c r="F607" t="n">
-        <v>134296</v>
+        <v>135699</v>
       </c>
     </row>
     <row r="608">
@@ -12581,10 +12581,10 @@
         <v>75</v>
       </c>
       <c r="E608" t="n">
-        <v>76.02</v>
+        <v>75.81999999999999</v>
       </c>
       <c r="F608" t="n">
-        <v>102316</v>
+        <v>104256</v>
       </c>
     </row>
     <row r="609">
@@ -12655,16 +12655,16 @@
         <v>72.97</v>
       </c>
       <c r="C612" t="n">
-        <v>73.97</v>
+        <v>74.02</v>
       </c>
       <c r="D612" t="n">
         <v>71.73999999999999</v>
       </c>
       <c r="E612" t="n">
-        <v>73.92</v>
+        <v>73.95999999999999</v>
       </c>
       <c r="F612" t="n">
-        <v>136419</v>
+        <v>138030</v>
       </c>
     </row>
     <row r="613">
@@ -12681,10 +12681,10 @@
         <v>73.38</v>
       </c>
       <c r="E613" t="n">
-        <v>75.15000000000001</v>
+        <v>75.14</v>
       </c>
       <c r="F613" t="n">
-        <v>95892</v>
+        <v>96988</v>
       </c>
     </row>
     <row r="614">
@@ -12761,10 +12761,10 @@
         <v>72.70999999999999</v>
       </c>
       <c r="E617" t="n">
-        <v>72.79000000000001</v>
+        <v>72.72</v>
       </c>
       <c r="F617" t="n">
-        <v>132350</v>
+        <v>134216</v>
       </c>
     </row>
     <row r="618">
@@ -12781,10 +12781,10 @@
         <v>71.88</v>
       </c>
       <c r="E618" t="n">
-        <v>72.81</v>
+        <v>72.64</v>
       </c>
       <c r="F618" t="n">
-        <v>108307</v>
+        <v>110158</v>
       </c>
     </row>
     <row r="619">
@@ -12864,7 +12864,7 @@
         <v>73.01000000000001</v>
       </c>
       <c r="F622" t="n">
-        <v>113951</v>
+        <v>115159</v>
       </c>
     </row>
     <row r="623">
@@ -12875,16 +12875,16 @@
         <v>72.98</v>
       </c>
       <c r="C623" t="n">
-        <v>73.52</v>
+        <v>73.56999999999999</v>
       </c>
       <c r="D623" t="n">
         <v>72.70999999999999</v>
       </c>
       <c r="E623" t="n">
-        <v>73.44</v>
+        <v>73.5</v>
       </c>
       <c r="F623" t="n">
-        <v>83411</v>
+        <v>84579</v>
       </c>
     </row>
     <row r="624">
@@ -12961,10 +12961,10 @@
         <v>73.59999999999999</v>
       </c>
       <c r="E627" t="n">
-        <v>74.97</v>
+        <v>74.75</v>
       </c>
       <c r="F627" t="n">
-        <v>79720</v>
+        <v>81467</v>
       </c>
     </row>
     <row r="628">
@@ -12981,10 +12981,10 @@
         <v>74.26000000000001</v>
       </c>
       <c r="E628" t="n">
-        <v>74.98999999999999</v>
+        <v>74.95999999999999</v>
       </c>
       <c r="F628" t="n">
-        <v>83101</v>
+        <v>84253</v>
       </c>
     </row>
     <row r="629">
@@ -13061,10 +13061,10 @@
         <v>69.56</v>
       </c>
       <c r="E632" t="n">
-        <v>71.16</v>
+        <v>71</v>
       </c>
       <c r="F632" t="n">
-        <v>107034</v>
+        <v>108267</v>
       </c>
     </row>
     <row r="633">
@@ -13078,13 +13078,13 @@
         <v>72.22</v>
       </c>
       <c r="D633" t="n">
-        <v>70.12</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="E633" t="n">
-        <v>70.34999999999999</v>
+        <v>70.08</v>
       </c>
       <c r="F633" t="n">
-        <v>111453</v>
+        <v>113105</v>
       </c>
     </row>
     <row r="634">
@@ -13161,10 +13161,10 @@
         <v>70.41</v>
       </c>
       <c r="E637" t="n">
-        <v>70.90000000000001</v>
+        <v>70.86</v>
       </c>
       <c r="F637" t="n">
-        <v>95219</v>
+        <v>96203</v>
       </c>
     </row>
     <row r="638">
@@ -13181,10 +13181,10 @@
         <v>69.73999999999999</v>
       </c>
       <c r="E638" t="n">
-        <v>69.92</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="F638" t="n">
-        <v>93960</v>
+        <v>95696</v>
       </c>
     </row>
     <row r="639">
@@ -13261,10 +13261,10 @@
         <v>65.2</v>
       </c>
       <c r="E642" t="n">
-        <v>66.51000000000001</v>
+        <v>66.23</v>
       </c>
       <c r="F642" t="n">
-        <v>185678</v>
+        <v>187712</v>
       </c>
     </row>
     <row r="643">
@@ -13278,13 +13278,13 @@
         <v>66.54000000000001</v>
       </c>
       <c r="D643" t="n">
-        <v>64.61</v>
+        <v>64.53</v>
       </c>
       <c r="E643" t="n">
-        <v>64.62</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="F643" t="n">
-        <v>137258</v>
+        <v>138989</v>
       </c>
     </row>
     <row r="644">
@@ -13361,10 +13361,10 @@
         <v>69.73999999999999</v>
       </c>
       <c r="E647" t="n">
-        <v>70.56</v>
+        <v>70.45999999999999</v>
       </c>
       <c r="F647" t="n">
-        <v>113839</v>
+        <v>115965</v>
       </c>
     </row>
     <row r="648">
@@ -13381,10 +13381,10 @@
         <v>70.16</v>
       </c>
       <c r="E648" t="n">
-        <v>71.59999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="F648" t="n">
-        <v>99158</v>
+        <v>100455</v>
       </c>
     </row>
     <row r="649">
@@ -13461,10 +13461,10 @@
         <v>70.75</v>
       </c>
       <c r="E652" t="n">
-        <v>72.56999999999999</v>
+        <v>72.61</v>
       </c>
       <c r="F652" t="n">
-        <v>103772</v>
+        <v>105073</v>
       </c>
     </row>
     <row r="653">
@@ -13481,10 +13481,10 @@
         <v>72.20999999999999</v>
       </c>
       <c r="E653" t="n">
-        <v>72.36</v>
+        <v>72.20999999999999</v>
       </c>
       <c r="F653" t="n">
-        <v>110684</v>
+        <v>111688</v>
       </c>
     </row>
     <row r="654">
@@ -13561,10 +13561,10 @@
         <v>70.54000000000001</v>
       </c>
       <c r="E657" t="n">
-        <v>70.95</v>
+        <v>70.84</v>
       </c>
       <c r="F657" t="n">
-        <v>136836</v>
+        <v>138553</v>
       </c>
     </row>
     <row r="658">
@@ -13581,10 +13581,10 @@
         <v>70.59</v>
       </c>
       <c r="E658" t="n">
-        <v>72.44</v>
+        <v>72.51000000000001</v>
       </c>
       <c r="F658" t="n">
-        <v>106315</v>
+        <v>107925</v>
       </c>
     </row>
     <row r="659">
@@ -13661,10 +13661,10 @@
         <v>74.02</v>
       </c>
       <c r="E662" t="n">
-        <v>75.17</v>
+        <v>75.09</v>
       </c>
       <c r="F662" t="n">
-        <v>134873</v>
+        <v>136265</v>
       </c>
     </row>
     <row r="663">
@@ -13681,10 +13681,10 @@
         <v>74.06999999999999</v>
       </c>
       <c r="E663" t="n">
-        <v>74.79000000000001</v>
+        <v>74.67</v>
       </c>
       <c r="F663" t="n">
-        <v>129577</v>
+        <v>131243</v>
       </c>
     </row>
     <row r="664">
@@ -13764,7 +13764,7 @@
         <v>76.45</v>
       </c>
       <c r="F667" t="n">
-        <v>102612</v>
+        <v>104066</v>
       </c>
     </row>
     <row r="668">
@@ -13781,10 +13781,10 @@
         <v>76.09</v>
       </c>
       <c r="E668" t="n">
-        <v>77.15000000000001</v>
+        <v>77.13</v>
       </c>
       <c r="F668" t="n">
-        <v>93448</v>
+        <v>94529</v>
       </c>
     </row>
     <row r="669">
@@ -13861,10 +13861,10 @@
         <v>76.37</v>
       </c>
       <c r="E672" t="n">
-        <v>78.13</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="F672" t="n">
-        <v>180155</v>
+        <v>181989</v>
       </c>
     </row>
     <row r="673">
@@ -13881,10 +13881,10 @@
         <v>77.38</v>
       </c>
       <c r="E673" t="n">
-        <v>78.98999999999999</v>
+        <v>78.93000000000001</v>
       </c>
       <c r="F673" t="n">
-        <v>149729</v>
+        <v>151482</v>
       </c>
     </row>
     <row r="674">
@@ -13961,10 +13961,10 @@
         <v>78.78</v>
       </c>
       <c r="E677" t="n">
-        <v>82.16</v>
+        <v>82.08</v>
       </c>
       <c r="F677" t="n">
-        <v>151677</v>
+        <v>153620</v>
       </c>
     </row>
     <row r="678">
@@ -13981,10 +13981,10 @@
         <v>81.63</v>
       </c>
       <c r="E678" t="n">
-        <v>82.17</v>
+        <v>82.22</v>
       </c>
       <c r="F678" t="n">
-        <v>147722</v>
+        <v>149526</v>
       </c>
     </row>
     <row r="679">
@@ -14061,10 +14061,10 @@
         <v>82.76000000000001</v>
       </c>
       <c r="E682" t="n">
-        <v>83.69</v>
+        <v>83.67</v>
       </c>
       <c r="F682" t="n">
-        <v>120650</v>
+        <v>122153</v>
       </c>
     </row>
     <row r="683">
@@ -14081,10 +14081,10 @@
         <v>83.68000000000001</v>
       </c>
       <c r="E683" t="n">
-        <v>84.23</v>
+        <v>84.33</v>
       </c>
       <c r="F683" t="n">
-        <v>114060</v>
+        <v>116437</v>
       </c>
     </row>
     <row r="684">
@@ -14161,10 +14161,10 @@
         <v>82.73</v>
       </c>
       <c r="E687" t="n">
-        <v>84.15000000000001</v>
+        <v>84.09</v>
       </c>
       <c r="F687" t="n">
-        <v>121250</v>
+        <v>122966</v>
       </c>
     </row>
     <row r="688">
@@ -14175,16 +14175,16 @@
         <v>83.81999999999999</v>
       </c>
       <c r="C688" t="n">
-        <v>84.97</v>
+        <v>85.08</v>
       </c>
       <c r="D688" t="n">
         <v>83.18000000000001</v>
       </c>
       <c r="E688" t="n">
-        <v>84.97</v>
+        <v>84.83</v>
       </c>
       <c r="F688" t="n">
-        <v>111475</v>
+        <v>113449</v>
       </c>
     </row>
     <row r="689">
@@ -14261,10 +14261,10 @@
         <v>81.48</v>
       </c>
       <c r="E692" t="n">
-        <v>83.83</v>
+        <v>83.78</v>
       </c>
       <c r="F692" t="n">
-        <v>164605</v>
+        <v>167007</v>
       </c>
     </row>
     <row r="693">
@@ -14281,10 +14281,10 @@
         <v>82.39</v>
       </c>
       <c r="E693" t="n">
-        <v>83.55</v>
+        <v>83.41</v>
       </c>
       <c r="F693" t="n">
-        <v>132228</v>
+        <v>133535</v>
       </c>
     </row>
     <row r="694">
@@ -14352,7 +14352,7 @@
         <v>44504</v>
       </c>
       <c r="B697" t="n">
-        <v>81.12</v>
+        <v>80.83</v>
       </c>
       <c r="C697" t="n">
         <v>84.08</v>
@@ -14364,7 +14364,7 @@
         <v>80.54000000000001</v>
       </c>
       <c r="F697" t="n">
-        <v>171378</v>
+        <v>168783</v>
       </c>
     </row>
     <row r="698">
@@ -14372,7 +14372,7 @@
         <v>44505</v>
       </c>
       <c r="B698" t="n">
-        <v>80.95</v>
+        <v>81.04000000000001</v>
       </c>
       <c r="C698" t="n">
         <v>82.72</v>
@@ -14384,7 +14384,7 @@
         <v>81.93000000000001</v>
       </c>
       <c r="F698" t="n">
-        <v>166390</v>
+        <v>163172</v>
       </c>
     </row>
     <row r="699">
@@ -14461,10 +14461,10 @@
         <v>81.06</v>
       </c>
       <c r="E702" t="n">
-        <v>81.91</v>
+        <v>81.92</v>
       </c>
       <c r="F702" t="n">
-        <v>159955</v>
+        <v>161511</v>
       </c>
     </row>
     <row r="703">
@@ -14481,10 +14481,10 @@
         <v>80.63</v>
       </c>
       <c r="E703" t="n">
-        <v>81.41</v>
+        <v>81.29000000000001</v>
       </c>
       <c r="F703" t="n">
-        <v>133196</v>
+        <v>134507</v>
       </c>
     </row>
     <row r="704">
@@ -14561,10 +14561,10 @@
         <v>78.55</v>
       </c>
       <c r="E707" t="n">
-        <v>80.42</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="F707" t="n">
-        <v>131123</v>
+        <v>132952</v>
       </c>
     </row>
     <row r="708">
@@ -14581,10 +14581,10 @@
         <v>77.41</v>
       </c>
       <c r="E708" t="n">
-        <v>77.76000000000001</v>
+        <v>77.77</v>
       </c>
       <c r="F708" t="n">
-        <v>175625</v>
+        <v>177513</v>
       </c>
     </row>
     <row r="709">
@@ -14761,10 +14761,10 @@
         <v>65.67</v>
       </c>
       <c r="E717" t="n">
-        <v>69.94</v>
+        <v>70.36</v>
       </c>
       <c r="F717" t="n">
-        <v>237353</v>
+        <v>240359</v>
       </c>
     </row>
     <row r="718">
@@ -14781,10 +14781,10 @@
         <v>69.09999999999999</v>
       </c>
       <c r="E718" t="n">
-        <v>69.73</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="F718" t="n">
-        <v>205214</v>
+        <v>208893</v>
       </c>
     </row>
     <row r="719">
@@ -14858,13 +14858,13 @@
         <v>76.55</v>
       </c>
       <c r="D722" t="n">
-        <v>73.78</v>
+        <v>73.70999999999999</v>
       </c>
       <c r="E722" t="n">
-        <v>73.79000000000001</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="F722" t="n">
-        <v>140659</v>
+        <v>142264</v>
       </c>
     </row>
     <row r="723">
@@ -14881,10 +14881,10 @@
         <v>73.67</v>
       </c>
       <c r="E723" t="n">
-        <v>75.23</v>
+        <v>75.16</v>
       </c>
       <c r="F723" t="n">
-        <v>151698</v>
+        <v>153301</v>
       </c>
     </row>
     <row r="724">
@@ -14961,10 +14961,10 @@
         <v>73.88</v>
       </c>
       <c r="E727" t="n">
-        <v>74.63</v>
+        <v>74.48999999999999</v>
       </c>
       <c r="F727" t="n">
-        <v>140474</v>
+        <v>142563</v>
       </c>
     </row>
     <row r="728">
@@ -14981,10 +14981,10 @@
         <v>72.63</v>
       </c>
       <c r="E728" t="n">
-        <v>73.15000000000001</v>
+        <v>72.88</v>
       </c>
       <c r="F728" t="n">
-        <v>152160</v>
+        <v>154875</v>
       </c>
     </row>
     <row r="729">
@@ -15061,10 +15061,10 @@
         <v>74.72</v>
       </c>
       <c r="E732" t="n">
-        <v>76.63</v>
+        <v>76.52</v>
       </c>
       <c r="F732" t="n">
-        <v>100583</v>
+        <v>102802</v>
       </c>
     </row>
     <row r="733">
@@ -15161,10 +15161,10 @@
         <v>78.33</v>
       </c>
       <c r="E737" t="n">
-        <v>78.97</v>
+        <v>78.86</v>
       </c>
       <c r="F737" t="n">
-        <v>103669</v>
+        <v>105405</v>
       </c>
     </row>
     <row r="738">
@@ -15261,10 +15261,10 @@
         <v>79.36</v>
       </c>
       <c r="E742" t="n">
-        <v>81.65000000000001</v>
+        <v>81.70999999999999</v>
       </c>
       <c r="F742" t="n">
-        <v>185800</v>
+        <v>187943</v>
       </c>
     </row>
     <row r="743">
@@ -15281,10 +15281,10 @@
         <v>81.12</v>
       </c>
       <c r="E743" t="n">
-        <v>81.59999999999999</v>
+        <v>81.48</v>
       </c>
       <c r="F743" t="n">
-        <v>158852</v>
+        <v>160491</v>
       </c>
     </row>
     <row r="744">
@@ -15361,10 +15361,10 @@
         <v>83.34999999999999</v>
       </c>
       <c r="E747" t="n">
-        <v>83.45</v>
+        <v>83.61</v>
       </c>
       <c r="F747" t="n">
-        <v>145171</v>
+        <v>147527</v>
       </c>
     </row>
     <row r="748">
@@ -15375,16 +15375,16 @@
         <v>83.68000000000001</v>
       </c>
       <c r="C748" t="n">
-        <v>85.97</v>
+        <v>85.98999999999999</v>
       </c>
       <c r="D748" t="n">
         <v>83.53</v>
       </c>
       <c r="E748" t="n">
-        <v>85.91</v>
+        <v>85.77</v>
       </c>
       <c r="F748" t="n">
-        <v>171152</v>
+        <v>173518</v>
       </c>
     </row>
     <row r="749">
@@ -15458,13 +15458,13 @@
         <v>88.8</v>
       </c>
       <c r="D752" t="n">
-        <v>86.56999999999999</v>
+        <v>86.38</v>
       </c>
       <c r="E752" t="n">
-        <v>86.7</v>
+        <v>86.58</v>
       </c>
       <c r="F752" t="n">
-        <v>162890</v>
+        <v>169439</v>
       </c>
     </row>
     <row r="753">
@@ -15481,10 +15481,10 @@
         <v>85.02</v>
       </c>
       <c r="E753" t="n">
-        <v>86.98</v>
+        <v>86.92</v>
       </c>
       <c r="F753" t="n">
-        <v>223066</v>
+        <v>225683</v>
       </c>
     </row>
     <row r="754">
@@ -15561,10 +15561,10 @@
         <v>87.7</v>
       </c>
       <c r="E757" t="n">
-        <v>88.40000000000001</v>
+        <v>88.63</v>
       </c>
       <c r="F757" t="n">
-        <v>270152</v>
+        <v>275711</v>
       </c>
     </row>
     <row r="758">
@@ -15581,10 +15581,10 @@
         <v>88</v>
       </c>
       <c r="E758" t="n">
-        <v>88.73</v>
+        <v>88.81999999999999</v>
       </c>
       <c r="F758" t="n">
-        <v>275262</v>
+        <v>278896</v>
       </c>
     </row>
     <row r="759">
@@ -15655,16 +15655,16 @@
         <v>88.63</v>
       </c>
       <c r="C762" t="n">
-        <v>90.73999999999999</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="D762" t="n">
         <v>87.59999999999999</v>
       </c>
       <c r="E762" t="n">
-        <v>90.45999999999999</v>
+        <v>90.51000000000001</v>
       </c>
       <c r="F762" t="n">
-        <v>163057</v>
+        <v>168353</v>
       </c>
     </row>
     <row r="763">
@@ -15681,10 +15681,10 @@
         <v>90.67</v>
       </c>
       <c r="E763" t="n">
-        <v>92.54000000000001</v>
+        <v>92.14</v>
       </c>
       <c r="F763" t="n">
-        <v>177219</v>
+        <v>180147</v>
       </c>
     </row>
     <row r="764">
@@ -15761,10 +15761,10 @@
         <v>90.09999999999999</v>
       </c>
       <c r="E767" t="n">
-        <v>90.66</v>
+        <v>90.54000000000001</v>
       </c>
       <c r="F767" t="n">
-        <v>183590</v>
+        <v>186180</v>
       </c>
     </row>
     <row r="768">
@@ -15781,10 +15781,10 @@
         <v>89.66</v>
       </c>
       <c r="E768" t="n">
-        <v>93.81</v>
+        <v>93.8</v>
       </c>
       <c r="F768" t="n">
-        <v>189880</v>
+        <v>194729</v>
       </c>
     </row>
     <row r="769">
@@ -15861,10 +15861,10 @@
         <v>90.34999999999999</v>
       </c>
       <c r="E772" t="n">
-        <v>91.18000000000001</v>
+        <v>91.16</v>
       </c>
       <c r="F772" t="n">
-        <v>209775</v>
+        <v>212213</v>
       </c>
     </row>
     <row r="773">
@@ -15875,7 +15875,7 @@
         <v>90.76000000000001</v>
       </c>
       <c r="C773" t="n">
-        <v>92.15000000000001</v>
+        <v>92.28</v>
       </c>
       <c r="D773" t="n">
         <v>88.64</v>
@@ -15884,7 +15884,7 @@
         <v>91.81</v>
       </c>
       <c r="F773" t="n">
-        <v>190175</v>
+        <v>194995</v>
       </c>
     </row>
     <row r="774">
@@ -15961,10 +15961,10 @@
         <v>93.94</v>
       </c>
       <c r="E777" t="n">
-        <v>95.61</v>
+        <v>95.41</v>
       </c>
       <c r="F777" t="n">
-        <v>309076</v>
+        <v>313423</v>
       </c>
     </row>
     <row r="778">
@@ -15981,10 +15981,10 @@
         <v>92.55</v>
       </c>
       <c r="E778" t="n">
-        <v>94.69</v>
+        <v>94.23</v>
       </c>
       <c r="F778" t="n">
-        <v>233541</v>
+        <v>237786</v>
       </c>
     </row>
     <row r="779">
@@ -16061,10 +16061,10 @@
         <v>108.17</v>
       </c>
       <c r="E782" t="n">
-        <v>109.72</v>
+        <v>109.27</v>
       </c>
       <c r="F782" t="n">
-        <v>231064</v>
+        <v>233799</v>
       </c>
     </row>
     <row r="783">
@@ -16081,10 +16081,10 @@
         <v>108.47</v>
       </c>
       <c r="E783" t="n">
-        <v>117.14</v>
+        <v>116.7</v>
       </c>
       <c r="F783" t="n">
-        <v>204618</v>
+        <v>210974</v>
       </c>
     </row>
     <row r="784">
@@ -16161,10 +16161,10 @@
         <v>107.05</v>
       </c>
       <c r="E787" t="n">
-        <v>107.97</v>
+        <v>107.11</v>
       </c>
       <c r="F787" t="n">
-        <v>170481</v>
+        <v>173653</v>
       </c>
     </row>
     <row r="788">
@@ -16181,10 +16181,10 @@
         <v>104.96</v>
       </c>
       <c r="E788" t="n">
-        <v>110.51</v>
+        <v>110.14</v>
       </c>
       <c r="F788" t="n">
-        <v>154891</v>
+        <v>157669</v>
       </c>
     </row>
     <row r="789">
@@ -16252,19 +16252,19 @@
         <v>44637</v>
       </c>
       <c r="B792" t="n">
-        <v>96.98</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="C792" t="n">
         <v>105.3</v>
       </c>
       <c r="D792" t="n">
-        <v>96.11</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="E792" t="n">
         <v>104.46</v>
       </c>
       <c r="F792" t="n">
-        <v>176604</v>
+        <v>172578</v>
       </c>
     </row>
     <row r="793">
@@ -16272,7 +16272,7 @@
         <v>44638</v>
       </c>
       <c r="B793" t="n">
-        <v>104.55</v>
+        <v>105.16</v>
       </c>
       <c r="C793" t="n">
         <v>107.23</v>
@@ -16284,7 +16284,7 @@
         <v>105.63</v>
       </c>
       <c r="F793" t="n">
-        <v>158531</v>
+        <v>155067</v>
       </c>
     </row>
     <row r="794">
@@ -16352,7 +16352,7 @@
         <v>44644</v>
       </c>
       <c r="B797" t="n">
-        <v>118.08</v>
+        <v>119.49</v>
       </c>
       <c r="C797" t="n">
         <v>120.04</v>
@@ -16364,7 +16364,7 @@
         <v>114.47</v>
       </c>
       <c r="F797" t="n">
-        <v>215337</v>
+        <v>206598</v>
       </c>
     </row>
     <row r="798">
@@ -16372,7 +16372,7 @@
         <v>44645</v>
       </c>
       <c r="B798" t="n">
-        <v>115.3</v>
+        <v>114.52</v>
       </c>
       <c r="C798" t="n">
         <v>117.69</v>
@@ -16384,7 +16384,7 @@
         <v>115.94</v>
       </c>
       <c r="F798" t="n">
-        <v>195807</v>
+        <v>189095</v>
       </c>
     </row>
     <row r="799">
@@ -16461,10 +16461,10 @@
         <v>103.71</v>
       </c>
       <c r="E802" t="n">
-        <v>104.6</v>
+        <v>104.99</v>
       </c>
       <c r="F802" t="n">
-        <v>217472</v>
+        <v>220967</v>
       </c>
     </row>
     <row r="803">
@@ -16481,10 +16481,10 @@
         <v>101.94</v>
       </c>
       <c r="E803" t="n">
-        <v>104.13</v>
+        <v>103.88</v>
       </c>
       <c r="F803" t="n">
-        <v>179677</v>
+        <v>181758</v>
       </c>
     </row>
     <row r="804">
@@ -16561,10 +16561,10 @@
         <v>98.2</v>
       </c>
       <c r="E807" t="n">
-        <v>100.94</v>
+        <v>100.96</v>
       </c>
       <c r="F807" t="n">
-        <v>183922</v>
+        <v>186163</v>
       </c>
     </row>
     <row r="808">
@@ -16581,10 +16581,10 @@
         <v>99.28</v>
       </c>
       <c r="E808" t="n">
-        <v>102.16</v>
+        <v>101.81</v>
       </c>
       <c r="F808" t="n">
-        <v>159821</v>
+        <v>162819</v>
       </c>
     </row>
     <row r="809">
@@ -16661,10 +16661,10 @@
         <v>106.14</v>
       </c>
       <c r="E812" t="n">
-        <v>110.56</v>
+        <v>110.62</v>
       </c>
       <c r="F812" t="n">
-        <v>156524</v>
+        <v>159785</v>
       </c>
     </row>
     <row r="813">
@@ -16741,10 +16741,10 @@
         <v>106.38</v>
       </c>
       <c r="E816" t="n">
-        <v>107.93</v>
+        <v>108</v>
       </c>
       <c r="F816" t="n">
-        <v>184241</v>
+        <v>188001</v>
       </c>
     </row>
     <row r="817">
@@ -16758,13 +16758,13 @@
         <v>108.41</v>
       </c>
       <c r="D817" t="n">
-        <v>105.44</v>
+        <v>105.05</v>
       </c>
       <c r="E817" t="n">
-        <v>105.6</v>
+        <v>105.7</v>
       </c>
       <c r="F817" t="n">
-        <v>162032</v>
+        <v>165632</v>
       </c>
     </row>
     <row r="818">
@@ -16841,10 +16841,10 @@
         <v>102.74</v>
       </c>
       <c r="E821" t="n">
-        <v>107.25</v>
+        <v>106.8</v>
       </c>
       <c r="F821" t="n">
-        <v>167676</v>
+        <v>170514</v>
       </c>
     </row>
     <row r="822">
@@ -16861,10 +16861,10 @@
         <v>105.92</v>
       </c>
       <c r="E822" t="n">
-        <v>106.38</v>
+        <v>106.06</v>
       </c>
       <c r="F822" t="n">
-        <v>182972</v>
+        <v>186051</v>
       </c>
     </row>
     <row r="823">
@@ -16941,10 +16941,10 @@
         <v>108.66</v>
       </c>
       <c r="E826" t="n">
-        <v>110.3</v>
+        <v>110.4</v>
       </c>
       <c r="F826" t="n">
-        <v>197687</v>
+        <v>201234</v>
       </c>
     </row>
     <row r="827">
@@ -16961,10 +16961,10 @@
         <v>109.21</v>
       </c>
       <c r="E827" t="n">
-        <v>112.44</v>
+        <v>112.22</v>
       </c>
       <c r="F827" t="n">
-        <v>203469</v>
+        <v>207851</v>
       </c>
     </row>
     <row r="828">
@@ -17041,10 +17041,10 @@
         <v>103.97</v>
       </c>
       <c r="E831" t="n">
-        <v>107.38</v>
+        <v>106.86</v>
       </c>
       <c r="F831" t="n">
-        <v>240901</v>
+        <v>243371</v>
       </c>
     </row>
     <row r="832">
@@ -17061,10 +17061,10 @@
         <v>106.88</v>
       </c>
       <c r="E832" t="n">
-        <v>110.4</v>
+        <v>109.76</v>
       </c>
       <c r="F832" t="n">
-        <v>190398</v>
+        <v>193013</v>
       </c>
     </row>
     <row r="833">
@@ -17141,10 +17141,10 @@
         <v>104.22</v>
       </c>
       <c r="E836" t="n">
-        <v>109.59</v>
+        <v>109.5</v>
       </c>
       <c r="F836" t="n">
-        <v>247278</v>
+        <v>250583</v>
       </c>
     </row>
     <row r="837">
@@ -17161,10 +17161,10 @@
         <v>108.65</v>
       </c>
       <c r="E837" t="n">
-        <v>110.87</v>
+        <v>110.3</v>
       </c>
       <c r="F837" t="n">
-        <v>198948</v>
+        <v>202895</v>
       </c>
     </row>
     <row r="838">
@@ -17241,10 +17241,10 @@
         <v>110.83</v>
       </c>
       <c r="E841" t="n">
-        <v>114</v>
+        <v>114.15</v>
       </c>
       <c r="F841" t="n">
-        <v>171535</v>
+        <v>175003</v>
       </c>
     </row>
     <row r="842">
@@ -17261,10 +17261,10 @@
         <v>113.01</v>
       </c>
       <c r="E842" t="n">
-        <v>115.42</v>
+        <v>115.01</v>
       </c>
       <c r="F842" t="n">
-        <v>210750</v>
+        <v>213418</v>
       </c>
     </row>
     <row r="843">
@@ -17335,16 +17335,16 @@
         <v>113.88</v>
       </c>
       <c r="C846" t="n">
-        <v>117.57</v>
+        <v>117.74</v>
       </c>
       <c r="D846" t="n">
         <v>111.85</v>
       </c>
       <c r="E846" t="n">
-        <v>117.26</v>
+        <v>117.31</v>
       </c>
       <c r="F846" t="n">
-        <v>137013</v>
+        <v>138282</v>
       </c>
     </row>
     <row r="847">
@@ -17355,16 +17355,16 @@
         <v>117.37</v>
       </c>
       <c r="C847" t="n">
-        <v>120.57</v>
+        <v>120.6</v>
       </c>
       <c r="D847" t="n">
         <v>115.28</v>
       </c>
       <c r="E847" t="n">
-        <v>120.41</v>
+        <v>120.23</v>
       </c>
       <c r="F847" t="n">
-        <v>90339</v>
+        <v>91626</v>
       </c>
     </row>
     <row r="848">
@@ -17441,10 +17441,10 @@
         <v>121.23</v>
       </c>
       <c r="E851" t="n">
-        <v>121.71</v>
+        <v>121.41</v>
       </c>
       <c r="F851" t="n">
-        <v>174232</v>
+        <v>176648</v>
       </c>
     </row>
     <row r="852">
@@ -17461,10 +17461,10 @@
         <v>118.31</v>
       </c>
       <c r="E852" t="n">
-        <v>120.29</v>
+        <v>120.02</v>
       </c>
       <c r="F852" t="n">
-        <v>190410</v>
+        <v>192334</v>
       </c>
     </row>
     <row r="853">
@@ -17541,10 +17541,10 @@
         <v>113.72</v>
       </c>
       <c r="E856" t="n">
-        <v>117.15</v>
+        <v>116.92</v>
       </c>
       <c r="F856" t="n">
-        <v>228931</v>
+        <v>231324</v>
       </c>
     </row>
     <row r="857">
@@ -17561,10 +17561,10 @@
         <v>109.77</v>
       </c>
       <c r="E857" t="n">
-        <v>111.29</v>
+        <v>111.27</v>
       </c>
       <c r="F857" t="n">
-        <v>233588</v>
+        <v>236868</v>
       </c>
     </row>
     <row r="858">
@@ -17641,10 +17641,10 @@
         <v>105.25</v>
       </c>
       <c r="E861" t="n">
-        <v>106.29</v>
+        <v>106.13</v>
       </c>
       <c r="F861" t="n">
-        <v>233040</v>
+        <v>234952</v>
       </c>
     </row>
     <row r="862">
@@ -17661,10 +17661,10 @@
         <v>105.78</v>
       </c>
       <c r="E862" t="n">
-        <v>109.13</v>
+        <v>108.33</v>
       </c>
       <c r="F862" t="n">
-        <v>202836</v>
+        <v>205227</v>
       </c>
     </row>
     <row r="863">
@@ -17741,10 +17741,10 @@
         <v>107.7</v>
       </c>
       <c r="E866" t="n">
-        <v>108.69</v>
+        <v>108.43</v>
       </c>
       <c r="F866" t="n">
-        <v>208599</v>
+        <v>212070</v>
       </c>
     </row>
     <row r="867">
@@ -17761,10 +17761,10 @@
         <v>107.32</v>
       </c>
       <c r="E867" t="n">
-        <v>110.56</v>
+        <v>110.43</v>
       </c>
       <c r="F867" t="n">
-        <v>209195</v>
+        <v>210630</v>
       </c>
     </row>
     <row r="868">
@@ -17841,10 +17841,10 @@
         <v>97.11</v>
       </c>
       <c r="E871" t="n">
-        <v>102.75</v>
+        <v>102.32</v>
       </c>
       <c r="F871" t="n">
-        <v>221862</v>
+        <v>224620</v>
       </c>
     </row>
     <row r="872">
@@ -17861,10 +17861,10 @@
         <v>102.16</v>
       </c>
       <c r="E872" t="n">
-        <v>105.32</v>
+        <v>105.2</v>
       </c>
       <c r="F872" t="n">
-        <v>235167</v>
+        <v>237030</v>
       </c>
     </row>
     <row r="873">
@@ -17941,10 +17941,10 @@
         <v>92.42</v>
       </c>
       <c r="E876" t="n">
-        <v>97.17</v>
+        <v>97.12</v>
       </c>
       <c r="F876" t="n">
-        <v>215919</v>
+        <v>217836</v>
       </c>
     </row>
     <row r="877">
@@ -17961,10 +17961,10 @@
         <v>95.59</v>
       </c>
       <c r="E877" t="n">
-        <v>98.34999999999999</v>
+        <v>97.98</v>
       </c>
       <c r="F877" t="n">
-        <v>200270</v>
+        <v>203134</v>
       </c>
     </row>
     <row r="878">
@@ -18041,10 +18041,10 @@
         <v>97.86</v>
       </c>
       <c r="E881" t="n">
-        <v>100.04</v>
+        <v>99.93000000000001</v>
       </c>
       <c r="F881" t="n">
-        <v>227231</v>
+        <v>229298</v>
       </c>
     </row>
     <row r="882">
@@ -18061,10 +18061,10 @@
         <v>97.90000000000001</v>
       </c>
       <c r="E882" t="n">
-        <v>98.67</v>
+        <v>98.98999999999999</v>
       </c>
       <c r="F882" t="n">
-        <v>222921</v>
+        <v>226135</v>
       </c>
     </row>
     <row r="883">
@@ -18141,10 +18141,10 @@
         <v>100.74</v>
       </c>
       <c r="E886" t="n">
-        <v>101.93</v>
+        <v>101.99</v>
       </c>
       <c r="F886" t="n">
-        <v>130398</v>
+        <v>132446</v>
       </c>
     </row>
     <row r="887">
@@ -18161,10 +18161,10 @@
         <v>101.27</v>
       </c>
       <c r="E887" t="n">
-        <v>103.21</v>
+        <v>103.1</v>
       </c>
       <c r="F887" t="n">
-        <v>112179</v>
+        <v>113461</v>
       </c>
     </row>
     <row r="888">
@@ -18238,13 +18238,13 @@
         <v>97.17</v>
       </c>
       <c r="D891" t="n">
-        <v>92.73</v>
+        <v>92.5</v>
       </c>
       <c r="E891" t="n">
-        <v>93.38</v>
+        <v>92.52</v>
       </c>
       <c r="F891" t="n">
-        <v>160629</v>
+        <v>162676</v>
       </c>
     </row>
     <row r="892">
@@ -18261,10 +18261,10 @@
         <v>92.15000000000001</v>
       </c>
       <c r="E892" t="n">
-        <v>93.69</v>
+        <v>93.51000000000001</v>
       </c>
       <c r="F892" t="n">
-        <v>155701</v>
+        <v>157322</v>
       </c>
     </row>
     <row r="893">
@@ -18341,10 +18341,10 @@
         <v>96.08</v>
       </c>
       <c r="E896" t="n">
-        <v>98.66</v>
+        <v>98.31</v>
       </c>
       <c r="F896" t="n">
-        <v>139272</v>
+        <v>140818</v>
       </c>
     </row>
     <row r="897">
@@ -18361,10 +18361,10 @@
         <v>96.26000000000001</v>
       </c>
       <c r="E897" t="n">
-        <v>97.3</v>
+        <v>96.89</v>
       </c>
       <c r="F897" t="n">
-        <v>144235</v>
+        <v>145858</v>
       </c>
     </row>
     <row r="898">
@@ -18441,10 +18441,10 @@
         <v>92.55</v>
       </c>
       <c r="E901" t="n">
-        <v>95.93000000000001</v>
+        <v>95.56</v>
       </c>
       <c r="F901" t="n">
-        <v>122235</v>
+        <v>123861</v>
       </c>
     </row>
     <row r="902">
@@ -18461,10 +18461,10 @@
         <v>93.7</v>
       </c>
       <c r="E902" t="n">
-        <v>95.52</v>
+        <v>95.08</v>
       </c>
       <c r="F902" t="n">
-        <v>125387</v>
+        <v>126696</v>
       </c>
     </row>
     <row r="903">
@@ -18541,10 +18541,10 @@
         <v>98.23</v>
       </c>
       <c r="E906" t="n">
-        <v>99.05</v>
+        <v>98.68000000000001</v>
       </c>
       <c r="F906" t="n">
-        <v>114289</v>
+        <v>115830</v>
       </c>
     </row>
     <row r="907">
@@ -18561,10 +18561,10 @@
         <v>96.92</v>
       </c>
       <c r="E907" t="n">
-        <v>98.70999999999999</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="F907" t="n">
-        <v>127109</v>
+        <v>128357</v>
       </c>
     </row>
     <row r="908">
@@ -18641,10 +18641,10 @@
         <v>91.58</v>
       </c>
       <c r="E911" t="n">
-        <v>91.75</v>
+        <v>91.59</v>
       </c>
       <c r="F911" t="n">
-        <v>171383</v>
+        <v>172611</v>
       </c>
     </row>
     <row r="912">
@@ -18661,10 +18661,10 @@
         <v>92.41</v>
       </c>
       <c r="E912" t="n">
-        <v>92.68000000000001</v>
+        <v>92.83</v>
       </c>
       <c r="F912" t="n">
-        <v>162523</v>
+        <v>164349</v>
       </c>
     </row>
     <row r="913">
@@ -18741,10 +18741,10 @@
         <v>86.86</v>
       </c>
       <c r="E916" t="n">
-        <v>88.03</v>
+        <v>87.73999999999999</v>
       </c>
       <c r="F916" t="n">
-        <v>174104</v>
+        <v>175783</v>
       </c>
     </row>
     <row r="917">
@@ -18761,10 +18761,10 @@
         <v>88.09</v>
       </c>
       <c r="E917" t="n">
-        <v>91.90000000000001</v>
+        <v>91.42</v>
       </c>
       <c r="F917" t="n">
-        <v>137562</v>
+        <v>139210</v>
       </c>
     </row>
     <row r="918">
@@ -18841,10 +18841,10 @@
         <v>89.39</v>
       </c>
       <c r="E921" t="n">
-        <v>90.08</v>
+        <v>89.78</v>
       </c>
       <c r="F921" t="n">
-        <v>177670</v>
+        <v>179533</v>
       </c>
     </row>
     <row r="922">
@@ -18861,10 +18861,10 @@
         <v>89.37</v>
       </c>
       <c r="E922" t="n">
-        <v>90.58</v>
+        <v>90.36</v>
       </c>
       <c r="F922" t="n">
-        <v>175462</v>
+        <v>177056</v>
       </c>
     </row>
     <row r="923">
@@ -18941,10 +18941,10 @@
         <v>88.38</v>
       </c>
       <c r="E926" t="n">
-        <v>89.53</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="F926" t="n">
-        <v>167346</v>
+        <v>169282</v>
       </c>
     </row>
     <row r="927">
@@ -18961,10 +18961,10 @@
         <v>84.61</v>
       </c>
       <c r="E927" t="n">
-        <v>85.41</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="F927" t="n">
-        <v>157358</v>
+        <v>159709</v>
       </c>
     </row>
     <row r="928">
@@ -19041,10 +19041,10 @@
         <v>85.98</v>
       </c>
       <c r="E931" t="n">
-        <v>87.20999999999999</v>
+        <v>87.22</v>
       </c>
       <c r="F931" t="n">
-        <v>182346</v>
+        <v>184095</v>
       </c>
     </row>
     <row r="932">
@@ -19061,10 +19061,10 @@
         <v>84.73999999999999</v>
       </c>
       <c r="E932" t="n">
-        <v>85.06999999999999</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="F932" t="n">
-        <v>172540</v>
+        <v>174184</v>
       </c>
     </row>
     <row r="933">
@@ -19141,10 +19141,10 @@
         <v>92.09</v>
       </c>
       <c r="E936" t="n">
-        <v>94.31999999999999</v>
+        <v>94.16</v>
       </c>
       <c r="F936" t="n">
-        <v>134269</v>
+        <v>136157</v>
       </c>
     </row>
     <row r="937">
@@ -19161,10 +19161,10 @@
         <v>93.25</v>
       </c>
       <c r="E937" t="n">
-        <v>96.95</v>
+        <v>97.59</v>
       </c>
       <c r="F937" t="n">
-        <v>158303</v>
+        <v>161145</v>
       </c>
     </row>
     <row r="938">
@@ -19241,10 +19241,10 @@
         <v>90.18000000000001</v>
       </c>
       <c r="E941" t="n">
-        <v>93.61</v>
+        <v>93.67</v>
       </c>
       <c r="F941" t="n">
-        <v>187899</v>
+        <v>189909</v>
       </c>
     </row>
     <row r="942">
@@ -19261,10 +19261,10 @@
         <v>90.34</v>
       </c>
       <c r="E942" t="n">
-        <v>90.84999999999999</v>
+        <v>90.66</v>
       </c>
       <c r="F942" t="n">
-        <v>184164</v>
+        <v>186342</v>
       </c>
     </row>
     <row r="943">
@@ -19341,10 +19341,10 @@
         <v>90.34</v>
       </c>
       <c r="E946" t="n">
-        <v>91</v>
+        <v>91.11</v>
       </c>
       <c r="F946" t="n">
-        <v>169394</v>
+        <v>172151</v>
       </c>
     </row>
     <row r="947">
@@ -19361,10 +19361,10 @@
         <v>89.40000000000001</v>
       </c>
       <c r="E947" t="n">
-        <v>91.7</v>
+        <v>91.58</v>
       </c>
       <c r="F947" t="n">
-        <v>168937</v>
+        <v>170499</v>
       </c>
     </row>
     <row r="948">
@@ -19441,10 +19441,10 @@
         <v>93.06999999999999</v>
       </c>
       <c r="E951" t="n">
-        <v>94.91</v>
+        <v>94.45999999999999</v>
       </c>
       <c r="F951" t="n">
-        <v>130846</v>
+        <v>135151</v>
       </c>
     </row>
     <row r="952">
@@ -19461,10 +19461,10 @@
         <v>92.81999999999999</v>
       </c>
       <c r="E952" t="n">
-        <v>93.81</v>
+        <v>93.95</v>
       </c>
       <c r="F952" t="n">
-        <v>133960</v>
+        <v>135363</v>
       </c>
     </row>
     <row r="953">
@@ -19532,7 +19532,7 @@
         <v>44868</v>
       </c>
       <c r="B956" t="n">
-        <v>94.81</v>
+        <v>94.84</v>
       </c>
       <c r="C956" t="n">
         <v>95.45</v>
@@ -19544,7 +19544,7 @@
         <v>93.92</v>
       </c>
       <c r="F956" t="n">
-        <v>143503</v>
+        <v>141621</v>
       </c>
     </row>
     <row r="957">
@@ -19552,19 +19552,19 @@
         <v>44869</v>
       </c>
       <c r="B957" t="n">
-        <v>93.98</v>
+        <v>93.94</v>
       </c>
       <c r="C957" t="n">
         <v>98.23999999999999</v>
       </c>
       <c r="D957" t="n">
-        <v>93.76000000000001</v>
+        <v>93.94</v>
       </c>
       <c r="E957" t="n">
         <v>98.01000000000001</v>
       </c>
       <c r="F957" t="n">
-        <v>182009</v>
+        <v>179958</v>
       </c>
     </row>
     <row r="958">
@@ -19641,10 +19641,10 @@
         <v>90.97</v>
       </c>
       <c r="E961" t="n">
-        <v>92.69</v>
+        <v>92.47</v>
       </c>
       <c r="F961" t="n">
-        <v>168690</v>
+        <v>170823</v>
       </c>
     </row>
     <row r="962">
@@ -19661,10 +19661,10 @@
         <v>92.79000000000001</v>
       </c>
       <c r="E962" t="n">
-        <v>95.04000000000001</v>
+        <v>94.95999999999999</v>
       </c>
       <c r="F962" t="n">
-        <v>163940</v>
+        <v>165782</v>
       </c>
     </row>
     <row r="963">
@@ -19741,10 +19741,10 @@
         <v>88.72</v>
       </c>
       <c r="E966" t="n">
-        <v>89.28</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="F966" t="n">
-        <v>157265</v>
+        <v>159560</v>
       </c>
     </row>
     <row r="967">
@@ -19761,10 +19761,10 @@
         <v>85.41</v>
       </c>
       <c r="E967" t="n">
-        <v>87.45</v>
+        <v>87.5</v>
       </c>
       <c r="F967" t="n">
-        <v>160818</v>
+        <v>162655</v>
       </c>
     </row>
     <row r="968">
@@ -19941,10 +19941,10 @@
         <v>86.26000000000001</v>
       </c>
       <c r="E976" t="n">
-        <v>86.84</v>
+        <v>86.98</v>
       </c>
       <c r="F976" t="n">
-        <v>135345</v>
+        <v>136930</v>
       </c>
     </row>
     <row r="977">
@@ -19961,10 +19961,10 @@
         <v>85.17</v>
       </c>
       <c r="E977" t="n">
-        <v>85.76000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="F977" t="n">
-        <v>135815</v>
+        <v>137359</v>
       </c>
     </row>
     <row r="978">
@@ -20041,10 +20041,10 @@
         <v>75.92</v>
       </c>
       <c r="E981" t="n">
-        <v>76.27</v>
+        <v>76.61</v>
       </c>
       <c r="F981" t="n">
-        <v>165742</v>
+        <v>167594</v>
       </c>
     </row>
     <row r="982">
@@ -20061,10 +20061,10 @@
         <v>75.34999999999999</v>
       </c>
       <c r="E982" t="n">
-        <v>76.76000000000001</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="F982" t="n">
-        <v>151706</v>
+        <v>153224</v>
       </c>
     </row>
     <row r="983">
@@ -20141,10 +20141,10 @@
         <v>80.86</v>
       </c>
       <c r="E986" t="n">
-        <v>81.39</v>
+        <v>81.54000000000001</v>
       </c>
       <c r="F986" t="n">
-        <v>149384</v>
+        <v>151489</v>
       </c>
     </row>
     <row r="987">
@@ -20161,10 +20161,10 @@
         <v>78.61</v>
       </c>
       <c r="E987" t="n">
-        <v>79.36</v>
+        <v>79.44</v>
       </c>
       <c r="F987" t="n">
-        <v>149990</v>
+        <v>151197</v>
       </c>
     </row>
     <row r="988">
@@ -20241,10 +20241,10 @@
         <v>81.28</v>
       </c>
       <c r="E991" t="n">
-        <v>82.18000000000001</v>
+        <v>82.20999999999999</v>
       </c>
       <c r="F991" t="n">
-        <v>94348</v>
+        <v>95617</v>
       </c>
     </row>
     <row r="992">
@@ -20321,10 +20321,10 @@
         <v>81.81999999999999</v>
       </c>
       <c r="E995" t="n">
-        <v>83.68000000000001</v>
+        <v>83.63</v>
       </c>
       <c r="F995" t="n">
-        <v>109380</v>
+        <v>110699</v>
       </c>
     </row>
     <row r="996">
@@ -20401,10 +20401,10 @@
         <v>77.63</v>
       </c>
       <c r="E999" t="n">
-        <v>78.68000000000001</v>
+        <v>78.8</v>
       </c>
       <c r="F999" t="n">
-        <v>149266</v>
+        <v>150672</v>
       </c>
     </row>
     <row r="1000">
@@ -20424,7 +20424,7 @@
         <v>78.51000000000001</v>
       </c>
       <c r="F1000" t="n">
-        <v>147017</v>
+        <v>148389</v>
       </c>
     </row>
     <row r="1001">
@@ -20501,10 +20501,10 @@
         <v>82.43000000000001</v>
       </c>
       <c r="E1004" t="n">
-        <v>83.91</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="F1004" t="n">
-        <v>141086</v>
+        <v>142735</v>
       </c>
     </row>
     <row r="1005">
@@ -20515,16 +20515,16 @@
         <v>83.91</v>
       </c>
       <c r="C1005" t="n">
-        <v>85.55</v>
+        <v>85.61</v>
       </c>
       <c r="D1005" t="n">
         <v>83.55</v>
       </c>
       <c r="E1005" t="n">
-        <v>85.48</v>
+        <v>85.47</v>
       </c>
       <c r="F1005" t="n">
-        <v>129757</v>
+        <v>131152</v>
       </c>
     </row>
     <row r="1006">
@@ -20601,10 +20601,10 @@
         <v>83.95999999999999</v>
       </c>
       <c r="E1009" t="n">
-        <v>86.31999999999999</v>
+        <v>86.34</v>
       </c>
       <c r="F1009" t="n">
-        <v>142583</v>
+        <v>144410</v>
       </c>
     </row>
     <row r="1010">
@@ -20621,10 +20621,10 @@
         <v>85.69</v>
       </c>
       <c r="E1010" t="n">
-        <v>87.75</v>
+        <v>87.59</v>
       </c>
       <c r="F1010" t="n">
-        <v>123973</v>
+        <v>125225</v>
       </c>
     </row>
     <row r="1011">
@@ -20701,10 +20701,10 @@
         <v>85.75</v>
       </c>
       <c r="E1014" t="n">
-        <v>87.31</v>
+        <v>87.29000000000001</v>
       </c>
       <c r="F1014" t="n">
-        <v>95077</v>
+        <v>96051</v>
       </c>
     </row>
     <row r="1015">
@@ -20721,10 +20721,10 @@
         <v>85.48</v>
       </c>
       <c r="E1015" t="n">
-        <v>86.04000000000001</v>
+        <v>86.01000000000001</v>
       </c>
       <c r="F1015" t="n">
-        <v>109841</v>
+        <v>110922</v>
       </c>
     </row>
     <row r="1016">
@@ -20801,10 +20801,10 @@
         <v>81.2</v>
       </c>
       <c r="E1019" t="n">
-        <v>81.98</v>
+        <v>82.12</v>
       </c>
       <c r="F1019" t="n">
-        <v>146732</v>
+        <v>150704</v>
       </c>
     </row>
     <row r="1020">
@@ -20818,13 +20818,13 @@
         <v>84.11</v>
       </c>
       <c r="D1020" t="n">
+        <v>79.53</v>
+      </c>
+      <c r="E1020" t="n">
         <v>79.62</v>
       </c>
-      <c r="E1020" t="n">
-        <v>79.64</v>
-      </c>
       <c r="F1020" t="n">
-        <v>161681</v>
+        <v>163093</v>
       </c>
     </row>
     <row r="1021">
@@ -20901,10 +20901,10 @@
         <v>82.86</v>
       </c>
       <c r="E1024" t="n">
-        <v>83.88</v>
+        <v>83.95</v>
       </c>
       <c r="F1024" t="n">
-        <v>142722</v>
+        <v>144061</v>
       </c>
     </row>
     <row r="1025">
@@ -20921,10 +20921,10 @@
         <v>83.66</v>
       </c>
       <c r="E1025" t="n">
-        <v>86.29000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="F1025" t="n">
-        <v>155562</v>
+        <v>156718</v>
       </c>
     </row>
     <row r="1026">
@@ -20998,13 +20998,13 @@
         <v>85.90000000000001</v>
       </c>
       <c r="D1029" t="n">
-        <v>84.31999999999999</v>
+        <v>84.28</v>
       </c>
       <c r="E1029" t="n">
-        <v>84.37</v>
+        <v>84.31</v>
       </c>
       <c r="F1029" t="n">
-        <v>128382</v>
+        <v>129946</v>
       </c>
     </row>
     <row r="1030">
@@ -21021,10 +21021,10 @@
         <v>81.55</v>
       </c>
       <c r="E1030" t="n">
-        <v>82.68000000000001</v>
+        <v>82.72</v>
       </c>
       <c r="F1030" t="n">
-        <v>141607</v>
+        <v>142763</v>
       </c>
     </row>
     <row r="1031">
@@ -21101,10 +21101,10 @@
         <v>80.27</v>
       </c>
       <c r="E1034" t="n">
-        <v>82.12</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="F1034" t="n">
-        <v>107083</v>
+        <v>108091</v>
       </c>
     </row>
     <row r="1035">
@@ -21121,10 +21121,10 @@
         <v>80.7</v>
       </c>
       <c r="E1035" t="n">
-        <v>82.94</v>
+        <v>82.77</v>
       </c>
       <c r="F1035" t="n">
-        <v>129354</v>
+        <v>130526</v>
       </c>
     </row>
     <row r="1036">
@@ -21201,10 +21201,10 @@
         <v>83.66</v>
       </c>
       <c r="E1039" t="n">
-        <v>84.34</v>
+        <v>84.23</v>
       </c>
       <c r="F1039" t="n">
-        <v>114302</v>
+        <v>115434</v>
       </c>
     </row>
     <row r="1040">
@@ -21215,16 +21215,16 @@
         <v>84.37</v>
       </c>
       <c r="C1040" t="n">
-        <v>85.8</v>
+        <v>85.81</v>
       </c>
       <c r="D1040" t="n">
         <v>82.2</v>
       </c>
       <c r="E1040" t="n">
-        <v>85.72</v>
+        <v>85.73999999999999</v>
       </c>
       <c r="F1040" t="n">
-        <v>119970</v>
+        <v>120888</v>
       </c>
     </row>
     <row r="1041">
@@ -21301,10 +21301,10 @@
         <v>81.16</v>
       </c>
       <c r="E1044" t="n">
-        <v>81.26000000000001</v>
+        <v>81.23</v>
       </c>
       <c r="F1044" t="n">
-        <v>120126</v>
+        <v>121276</v>
       </c>
     </row>
     <row r="1045">
@@ -21321,10 +21321,10 @@
         <v>80.47</v>
       </c>
       <c r="E1045" t="n">
-        <v>82.33</v>
+        <v>82.38</v>
       </c>
       <c r="F1045" t="n">
-        <v>171433</v>
+        <v>172647</v>
       </c>
     </row>
     <row r="1046">
@@ -21392,7 +21392,7 @@
         <v>45001</v>
       </c>
       <c r="B1049" t="n">
-        <v>74.04000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="C1049" t="n">
         <v>75.23</v>
@@ -21404,7 +21404,7 @@
         <v>74.25</v>
       </c>
       <c r="F1049" t="n">
-        <v>210322</v>
+        <v>206406</v>
       </c>
     </row>
     <row r="1050">
@@ -21412,7 +21412,7 @@
         <v>45002</v>
       </c>
       <c r="B1050" t="n">
-        <v>74.45</v>
+        <v>74.41</v>
       </c>
       <c r="C1050" t="n">
         <v>75.65000000000001</v>
@@ -21424,7 +21424,7 @@
         <v>72.3</v>
       </c>
       <c r="F1050" t="n">
-        <v>196053</v>
+        <v>194486</v>
       </c>
     </row>
     <row r="1051">
@@ -21492,7 +21492,7 @@
         <v>45008</v>
       </c>
       <c r="B1054" t="n">
-        <v>75.58</v>
+        <v>75.73</v>
       </c>
       <c r="C1054" t="n">
         <v>77.09</v>
@@ -21504,7 +21504,7 @@
         <v>74.98999999999999</v>
       </c>
       <c r="F1054" t="n">
-        <v>134971</v>
+        <v>132462</v>
       </c>
     </row>
     <row r="1055">
@@ -21512,7 +21512,7 @@
         <v>45009</v>
       </c>
       <c r="B1055" t="n">
-        <v>75.08</v>
+        <v>74.92</v>
       </c>
       <c r="C1055" t="n">
         <v>75.89</v>
@@ -21524,7 +21524,7 @@
         <v>74.52</v>
       </c>
       <c r="F1055" t="n">
-        <v>160608</v>
+        <v>158419</v>
       </c>
     </row>
     <row r="1056">
@@ -21601,10 +21601,10 @@
         <v>77.13</v>
       </c>
       <c r="E1059" t="n">
-        <v>78.47</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="F1059" t="n">
-        <v>101875</v>
+        <v>102975</v>
       </c>
     </row>
     <row r="1060">
@@ -21621,10 +21621,10 @@
         <v>77.79000000000001</v>
       </c>
       <c r="E1060" t="n">
-        <v>79.73</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="F1060" t="n">
-        <v>102278</v>
+        <v>103341</v>
       </c>
     </row>
     <row r="1061">
@@ -21701,10 +21701,10 @@
         <v>83.89</v>
       </c>
       <c r="E1064" t="n">
-        <v>84.73</v>
+        <v>84.62</v>
       </c>
       <c r="F1064" t="n">
-        <v>127887</v>
+        <v>128978</v>
       </c>
     </row>
     <row r="1065">
@@ -21781,10 +21781,10 @@
         <v>85.78</v>
       </c>
       <c r="E1068" t="n">
-        <v>85.98</v>
+        <v>86.03</v>
       </c>
       <c r="F1068" t="n">
-        <v>106530</v>
+        <v>107747</v>
       </c>
     </row>
     <row r="1069">
@@ -21801,10 +21801,10 @@
         <v>85.27</v>
       </c>
       <c r="E1069" t="n">
-        <v>86.13</v>
+        <v>86.12</v>
       </c>
       <c r="F1069" t="n">
-        <v>118921</v>
+        <v>119789</v>
       </c>
     </row>
     <row r="1070">
@@ -21878,13 +21878,13 @@
         <v>82.59999999999999</v>
       </c>
       <c r="D1073" t="n">
-        <v>80.51000000000001</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="E1073" t="n">
-        <v>80.62</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="F1073" t="n">
-        <v>99083</v>
+        <v>100157</v>
       </c>
     </row>
     <row r="1074">
@@ -21901,10 +21901,10 @@
         <v>80.2</v>
       </c>
       <c r="E1074" t="n">
-        <v>81.38</v>
+        <v>81.53</v>
       </c>
       <c r="F1074" t="n">
-        <v>88877</v>
+        <v>89589</v>
       </c>
     </row>
     <row r="1075">
@@ -21981,10 +21981,10 @@
         <v>77.3</v>
       </c>
       <c r="E1078" t="n">
-        <v>78.23</v>
+        <v>78.17</v>
       </c>
       <c r="F1078" t="n">
-        <v>112919</v>
+        <v>114226</v>
       </c>
     </row>
     <row r="1079">
@@ -22001,10 +22001,10 @@
         <v>77.44</v>
       </c>
       <c r="E1079" t="n">
-        <v>80.20999999999999</v>
+        <v>80.08</v>
       </c>
       <c r="F1079" t="n">
-        <v>110643</v>
+        <v>111593</v>
       </c>
     </row>
     <row r="1080">
@@ -22081,10 +22081,10 @@
         <v>71.34</v>
       </c>
       <c r="E1083" t="n">
-        <v>72.34</v>
+        <v>72.38</v>
       </c>
       <c r="F1083" t="n">
-        <v>175075</v>
+        <v>176458</v>
       </c>
     </row>
     <row r="1084">
@@ -22101,10 +22101,10 @@
         <v>72.31999999999999</v>
       </c>
       <c r="E1084" t="n">
-        <v>75.22</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="F1084" t="n">
-        <v>121559</v>
+        <v>122688</v>
       </c>
     </row>
     <row r="1085">
@@ -22181,10 +22181,10 @@
         <v>74.5</v>
       </c>
       <c r="E1088" t="n">
-        <v>75.34999999999999</v>
+        <v>75.26000000000001</v>
       </c>
       <c r="F1088" t="n">
-        <v>141443</v>
+        <v>142391</v>
       </c>
     </row>
     <row r="1089">
@@ -22201,10 +22201,10 @@
         <v>73.84999999999999</v>
       </c>
       <c r="E1089" t="n">
-        <v>74.02</v>
+        <v>73.93000000000001</v>
       </c>
       <c r="F1089" t="n">
-        <v>143925</v>
+        <v>144762</v>
       </c>
     </row>
     <row r="1090">
@@ -22281,10 +22281,10 @@
         <v>75.42</v>
       </c>
       <c r="E1093" t="n">
-        <v>75.89</v>
+        <v>75.84</v>
       </c>
       <c r="F1093" t="n">
-        <v>97144</v>
+        <v>98116</v>
       </c>
     </row>
     <row r="1094">
@@ -22301,10 +22301,10 @@
         <v>75.01000000000001</v>
       </c>
       <c r="E1094" t="n">
-        <v>75.75</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="F1094" t="n">
-        <v>107224</v>
+        <v>108218</v>
       </c>
     </row>
     <row r="1095">
@@ -22381,10 +22381,10 @@
         <v>75.08</v>
       </c>
       <c r="E1098" t="n">
-        <v>76.13</v>
+        <v>75.95999999999999</v>
       </c>
       <c r="F1098" t="n">
-        <v>94656</v>
+        <v>95663</v>
       </c>
     </row>
     <row r="1099">
@@ -22401,10 +22401,10 @@
         <v>75.62</v>
       </c>
       <c r="E1099" t="n">
-        <v>77.03</v>
+        <v>77.14</v>
       </c>
       <c r="F1099" t="n">
-        <v>85632</v>
+        <v>86227</v>
       </c>
     </row>
     <row r="1100">
@@ -22481,10 +22481,10 @@
         <v>72</v>
       </c>
       <c r="E1103" t="n">
-        <v>74.17</v>
+        <v>74.25</v>
       </c>
       <c r="F1103" t="n">
-        <v>122959</v>
+        <v>124084</v>
       </c>
     </row>
     <row r="1104">
@@ -22501,10 +22501,10 @@
         <v>74.13</v>
       </c>
       <c r="E1104" t="n">
-        <v>76.3</v>
+        <v>76.13</v>
       </c>
       <c r="F1104" t="n">
-        <v>110715</v>
+        <v>111881</v>
       </c>
     </row>
     <row r="1105">
@@ -22581,10 +22581,10 @@
         <v>73.52</v>
       </c>
       <c r="E1108" t="n">
-        <v>75.56999999999999</v>
+        <v>75.44</v>
       </c>
       <c r="F1108" t="n">
-        <v>141391</v>
+        <v>142206</v>
       </c>
     </row>
     <row r="1109">
@@ -22601,10 +22601,10 @@
         <v>74.67</v>
       </c>
       <c r="E1109" t="n">
-        <v>74.84999999999999</v>
+        <v>74.88</v>
       </c>
       <c r="F1109" t="n">
-        <v>120105</v>
+        <v>120995</v>
       </c>
     </row>
     <row r="1110">
@@ -22681,10 +22681,10 @@
         <v>72.84999999999999</v>
       </c>
       <c r="E1113" t="n">
-        <v>75.56</v>
+        <v>75.52</v>
       </c>
       <c r="F1113" t="n">
-        <v>104970</v>
+        <v>105947</v>
       </c>
     </row>
     <row r="1114">
@@ -22701,10 +22701,10 @@
         <v>75.09999999999999</v>
       </c>
       <c r="E1114" t="n">
-        <v>76.47</v>
+        <v>76.23</v>
       </c>
       <c r="F1114" t="n">
-        <v>109963</v>
+        <v>111184</v>
       </c>
     </row>
     <row r="1115">
@@ -22781,10 +22781,10 @@
         <v>73.75</v>
       </c>
       <c r="E1118" t="n">
-        <v>74.2</v>
+        <v>74.3</v>
       </c>
       <c r="F1118" t="n">
-        <v>89166</v>
+        <v>89974</v>
       </c>
     </row>
     <row r="1119">
@@ -22795,16 +22795,16 @@
         <v>74.2</v>
       </c>
       <c r="C1119" t="n">
-        <v>74.36</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="D1119" t="n">
         <v>72.25</v>
       </c>
       <c r="E1119" t="n">
-        <v>74.09</v>
+        <v>74.34</v>
       </c>
       <c r="F1119" t="n">
-        <v>100773</v>
+        <v>101628</v>
       </c>
     </row>
     <row r="1120">
@@ -22881,10 +22881,10 @@
         <v>73.56</v>
       </c>
       <c r="E1123" t="n">
-        <v>74.44</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="F1123" t="n">
-        <v>118096</v>
+        <v>118860</v>
       </c>
     </row>
     <row r="1124">
@@ -22901,10 +22901,10 @@
         <v>74.23</v>
       </c>
       <c r="E1124" t="n">
-        <v>75.26000000000001</v>
+        <v>75.06999999999999</v>
       </c>
       <c r="F1124" t="n">
-        <v>107062</v>
+        <v>108012</v>
       </c>
     </row>
     <row r="1125">
@@ -22981,10 +22981,10 @@
         <v>74.94</v>
       </c>
       <c r="E1128" t="n">
-        <v>76.47</v>
+        <v>76.44</v>
       </c>
       <c r="F1128" t="n">
-        <v>120498</v>
+        <v>121613</v>
       </c>
     </row>
     <row r="1129">
@@ -23001,10 +23001,10 @@
         <v>75.91</v>
       </c>
       <c r="E1129" t="n">
-        <v>78.13</v>
+        <v>78.12</v>
       </c>
       <c r="F1129" t="n">
-        <v>99946</v>
+        <v>101260</v>
       </c>
     </row>
     <row r="1130">
@@ -23075,16 +23075,16 @@
         <v>79.95999999999999</v>
       </c>
       <c r="C1133" t="n">
-        <v>81.48999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="D1133" t="n">
         <v>79.69</v>
       </c>
       <c r="E1133" t="n">
-        <v>81.48</v>
+        <v>81.37</v>
       </c>
       <c r="F1133" t="n">
-        <v>96443</v>
+        <v>97805</v>
       </c>
     </row>
     <row r="1134">
@@ -23098,13 +23098,13 @@
         <v>81.42</v>
       </c>
       <c r="D1134" t="n">
-        <v>79.44</v>
+        <v>79.34999999999999</v>
       </c>
       <c r="E1134" t="n">
-        <v>79.54000000000001</v>
+        <v>79.45</v>
       </c>
       <c r="F1134" t="n">
-        <v>98000</v>
+        <v>99161</v>
       </c>
     </row>
     <row r="1135">
@@ -23181,10 +23181,10 @@
         <v>78.56999999999999</v>
       </c>
       <c r="E1138" t="n">
-        <v>79.54000000000001</v>
+        <v>79.48</v>
       </c>
       <c r="F1138" t="n">
-        <v>76777</v>
+        <v>77506</v>
       </c>
     </row>
     <row r="1139">
@@ -23201,10 +23201,10 @@
         <v>79.51000000000001</v>
       </c>
       <c r="E1139" t="n">
-        <v>80.69</v>
+        <v>80.5</v>
       </c>
       <c r="F1139" t="n">
-        <v>69907</v>
+        <v>70745</v>
       </c>
     </row>
     <row r="1140">
@@ -23281,10 +23281,10 @@
         <v>82.54000000000001</v>
       </c>
       <c r="E1143" t="n">
-        <v>83.42</v>
+        <v>83.3</v>
       </c>
       <c r="F1143" t="n">
-        <v>100960</v>
+        <v>101885</v>
       </c>
     </row>
     <row r="1144">
@@ -23301,10 +23301,10 @@
         <v>82.78</v>
       </c>
       <c r="E1144" t="n">
-        <v>84.26000000000001</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="F1144" t="n">
-        <v>96080</v>
+        <v>96933</v>
       </c>
     </row>
     <row r="1145">
@@ -23381,10 +23381,10 @@
         <v>82.23</v>
       </c>
       <c r="E1148" t="n">
-        <v>85.13</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="F1148" t="n">
-        <v>122532</v>
+        <v>124232</v>
       </c>
     </row>
     <row r="1149">
@@ -23401,10 +23401,10 @@
         <v>84.89</v>
       </c>
       <c r="E1149" t="n">
-        <v>85.84</v>
+        <v>85.81</v>
       </c>
       <c r="F1149" t="n">
-        <v>103319</v>
+        <v>104424</v>
       </c>
     </row>
     <row r="1150">
@@ -23481,10 +23481,10 @@
         <v>85.89</v>
       </c>
       <c r="E1153" t="n">
-        <v>86.09999999999999</v>
+        <v>86.01000000000001</v>
       </c>
       <c r="F1153" t="n">
-        <v>119054</v>
+        <v>120019</v>
       </c>
     </row>
     <row r="1154">
@@ -23501,10 +23501,10 @@
         <v>85.53</v>
       </c>
       <c r="E1154" t="n">
-        <v>86.26000000000001</v>
+        <v>86.16</v>
       </c>
       <c r="F1154" t="n">
-        <v>114400</v>
+        <v>115051</v>
       </c>
     </row>
     <row r="1155">
@@ -23581,10 +23581,10 @@
         <v>82.70999999999999</v>
       </c>
       <c r="E1158" t="n">
-        <v>83.45999999999999</v>
+        <v>83.42</v>
       </c>
       <c r="F1158" t="n">
-        <v>87119</v>
+        <v>88033</v>
       </c>
     </row>
     <row r="1159">
@@ -23601,10 +23601,10 @@
         <v>82.98</v>
       </c>
       <c r="E1159" t="n">
-        <v>84.37</v>
+        <v>84.42</v>
       </c>
       <c r="F1159" t="n">
-        <v>98085</v>
+        <v>98761</v>
       </c>
     </row>
     <row r="1160">
@@ -23681,10 +23681,10 @@
         <v>81.61</v>
       </c>
       <c r="E1163" t="n">
-        <v>82.76000000000001</v>
+        <v>82.67</v>
       </c>
       <c r="F1163" t="n">
-        <v>77118</v>
+        <v>77961</v>
       </c>
     </row>
     <row r="1164">
@@ -23701,10 +23701,10 @@
         <v>82.2</v>
       </c>
       <c r="E1164" t="n">
-        <v>84.14</v>
+        <v>84.05</v>
       </c>
       <c r="F1164" t="n">
-        <v>101382</v>
+        <v>102303</v>
       </c>
     </row>
     <row r="1165">
@@ -23781,10 +23781,10 @@
         <v>84.98</v>
       </c>
       <c r="E1168" t="n">
-        <v>86.63</v>
+        <v>86.66</v>
       </c>
       <c r="F1168" t="n">
-        <v>83934</v>
+        <v>85007</v>
       </c>
     </row>
     <row r="1169">
@@ -23795,16 +23795,16 @@
         <v>86.63</v>
       </c>
       <c r="C1169" t="n">
-        <v>88.66</v>
+        <v>88.75</v>
       </c>
       <c r="D1169" t="n">
         <v>86.59</v>
       </c>
       <c r="E1169" t="n">
-        <v>88.64</v>
+        <v>88.68000000000001</v>
       </c>
       <c r="F1169" t="n">
-        <v>97671</v>
+        <v>98645</v>
       </c>
     </row>
     <row r="1170">
@@ -23881,10 +23881,10 @@
         <v>89.17</v>
       </c>
       <c r="E1173" t="n">
-        <v>89.76000000000001</v>
+        <v>89.47</v>
       </c>
       <c r="F1173" t="n">
-        <v>103067</v>
+        <v>104343</v>
       </c>
     </row>
     <row r="1174">
@@ -23901,10 +23901,10 @@
         <v>88.97</v>
       </c>
       <c r="E1174" t="n">
-        <v>90.2</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="F1174" t="n">
-        <v>100164</v>
+        <v>101197</v>
       </c>
     </row>
     <row r="1175">
@@ -23975,16 +23975,16 @@
         <v>91.56999999999999</v>
       </c>
       <c r="C1178" t="n">
-        <v>93.44</v>
+        <v>93.68000000000001</v>
       </c>
       <c r="D1178" t="n">
         <v>91.55</v>
       </c>
       <c r="E1178" t="n">
-        <v>93.36</v>
+        <v>93.56</v>
       </c>
       <c r="F1178" t="n">
-        <v>89908</v>
+        <v>91727</v>
       </c>
     </row>
     <row r="1179">
@@ -24001,10 +24001,10 @@
         <v>92.14</v>
       </c>
       <c r="E1179" t="n">
-        <v>93.52</v>
+        <v>93.56999999999999</v>
       </c>
       <c r="F1179" t="n">
-        <v>100530</v>
+        <v>101498</v>
       </c>
     </row>
     <row r="1180">
@@ -24081,10 +24081,10 @@
         <v>91.23999999999999</v>
       </c>
       <c r="E1183" t="n">
-        <v>92.27</v>
+        <v>92.20999999999999</v>
       </c>
       <c r="F1183" t="n">
-        <v>97207</v>
+        <v>98137</v>
       </c>
     </row>
     <row r="1184">
@@ -24101,10 +24101,10 @@
         <v>91.68000000000001</v>
       </c>
       <c r="E1184" t="n">
-        <v>92.31</v>
+        <v>92.28</v>
       </c>
       <c r="F1184" t="n">
-        <v>98960</v>
+        <v>99665</v>
       </c>
     </row>
     <row r="1185">
@@ -24181,10 +24181,10 @@
         <v>92.56</v>
       </c>
       <c r="E1188" t="n">
-        <v>92.94</v>
+        <v>92.89</v>
       </c>
       <c r="F1188" t="n">
-        <v>127194</v>
+        <v>128240</v>
       </c>
     </row>
     <row r="1189">
@@ -24201,10 +24201,10 @@
         <v>91.68000000000001</v>
       </c>
       <c r="E1189" t="n">
-        <v>91.95999999999999</v>
+        <v>91.8</v>
       </c>
       <c r="F1189" t="n">
-        <v>116761</v>
+        <v>117877</v>
       </c>
     </row>
     <row r="1190">
@@ -24281,10 +24281,10 @@
         <v>83.31999999999999</v>
       </c>
       <c r="E1193" t="n">
-        <v>83.68000000000001</v>
+        <v>83.72</v>
       </c>
       <c r="F1193" t="n">
-        <v>148426</v>
+        <v>149779</v>
       </c>
     </row>
     <row r="1194">
@@ -24301,10 +24301,10 @@
         <v>82.97</v>
       </c>
       <c r="E1194" t="n">
-        <v>83.88</v>
+        <v>83.79000000000001</v>
       </c>
       <c r="F1194" t="n">
-        <v>138785</v>
+        <v>140020</v>
       </c>
     </row>
     <row r="1195">
@@ -24381,10 +24381,10 @@
         <v>84.59</v>
       </c>
       <c r="E1198" t="n">
-        <v>85.7</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="F1198" t="n">
-        <v>123421</v>
+        <v>124560</v>
       </c>
     </row>
     <row r="1199">
@@ -24404,7 +24404,7 @@
         <v>89.93000000000001</v>
       </c>
       <c r="F1199" t="n">
-        <v>118765</v>
+        <v>120817</v>
       </c>
     </row>
     <row r="1200">
@@ -24475,16 +24475,16 @@
         <v>90.26000000000001</v>
       </c>
       <c r="C1203" t="n">
-        <v>92.22</v>
+        <v>92.34999999999999</v>
       </c>
       <c r="D1203" t="n">
         <v>88.69</v>
       </c>
       <c r="E1203" t="n">
-        <v>92.16</v>
+        <v>92.04000000000001</v>
       </c>
       <c r="F1203" t="n">
-        <v>109002</v>
+        <v>111224</v>
       </c>
     </row>
     <row r="1204">
@@ -24501,10 +24501,10 @@
         <v>90.63</v>
       </c>
       <c r="E1204" t="n">
-        <v>91.13</v>
+        <v>91.26000000000001</v>
       </c>
       <c r="F1204" t="n">
-        <v>109157</v>
+        <v>110661</v>
       </c>
     </row>
     <row r="1205">
@@ -24581,10 +24581,10 @@
         <v>86.48</v>
       </c>
       <c r="E1208" t="n">
-        <v>87.25</v>
+        <v>87.23999999999999</v>
       </c>
       <c r="F1208" t="n">
-        <v>113368</v>
+        <v>114536</v>
       </c>
     </row>
     <row r="1209">
@@ -24601,10 +24601,10 @@
         <v>86.76000000000001</v>
       </c>
       <c r="E1209" t="n">
-        <v>88.76000000000001</v>
+        <v>88.70999999999999</v>
       </c>
       <c r="F1209" t="n">
-        <v>121600</v>
+        <v>123231</v>
       </c>
     </row>
     <row r="1210">
@@ -24672,7 +24672,7 @@
         <v>45232</v>
       </c>
       <c r="B1213" t="n">
-        <v>84.83</v>
+        <v>85.03</v>
       </c>
       <c r="C1213" t="n">
         <v>86.88</v>
@@ -24684,7 +24684,7 @@
         <v>86.63</v>
       </c>
       <c r="F1213" t="n">
-        <v>103842</v>
+        <v>102261</v>
       </c>
     </row>
     <row r="1214">
@@ -24692,7 +24692,7 @@
         <v>45233</v>
       </c>
       <c r="B1214" t="n">
-        <v>86.70999999999999</v>
+        <v>86.66</v>
       </c>
       <c r="C1214" t="n">
         <v>87.58</v>
@@ -24704,7 +24704,7 @@
         <v>84.95</v>
       </c>
       <c r="F1214" t="n">
-        <v>119097</v>
+        <v>117913</v>
       </c>
     </row>
     <row r="1215">
@@ -24781,10 +24781,10 @@
         <v>79.33</v>
       </c>
       <c r="E1218" t="n">
-        <v>79.75</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="F1218" t="n">
-        <v>110739</v>
+        <v>111847</v>
       </c>
     </row>
     <row r="1219">
@@ -24801,10 +24801,10 @@
         <v>79.70999999999999</v>
       </c>
       <c r="E1219" t="n">
-        <v>81.36</v>
+        <v>81.43000000000001</v>
       </c>
       <c r="F1219" t="n">
-        <v>91256</v>
+        <v>92327</v>
       </c>
     </row>
     <row r="1220">
@@ -24881,10 +24881,10 @@
         <v>76.64</v>
       </c>
       <c r="E1223" t="n">
-        <v>77.43000000000001</v>
+        <v>77.45</v>
       </c>
       <c r="F1223" t="n">
-        <v>104766</v>
+        <v>105749</v>
       </c>
     </row>
     <row r="1224">
@@ -24901,10 +24901,10 @@
         <v>77.31</v>
       </c>
       <c r="E1224" t="n">
-        <v>80.37</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="F1224" t="n">
-        <v>88772</v>
+        <v>89648</v>
       </c>
     </row>
     <row r="1225">
@@ -25078,13 +25078,13 @@
         <v>84.51000000000001</v>
       </c>
       <c r="D1233" t="n">
-        <v>79.95</v>
+        <v>79.94</v>
       </c>
       <c r="E1233" t="n">
-        <v>80</v>
+        <v>80.31</v>
       </c>
       <c r="F1233" t="n">
-        <v>143673</v>
+        <v>145419</v>
       </c>
     </row>
     <row r="1234">
@@ -25101,10 +25101,10 @@
         <v>78.69</v>
       </c>
       <c r="E1234" t="n">
-        <v>78.93000000000001</v>
+        <v>79.02</v>
       </c>
       <c r="F1234" t="n">
-        <v>125186</v>
+        <v>126159</v>
       </c>
     </row>
     <row r="1235">
@@ -25181,10 +25181,10 @@
         <v>73.68000000000001</v>
       </c>
       <c r="E1238" t="n">
-        <v>74.47</v>
+        <v>74.39</v>
       </c>
       <c r="F1238" t="n">
-        <v>115986</v>
+        <v>116791</v>
       </c>
     </row>
     <row r="1239">
@@ -25201,10 +25201,10 @@
         <v>74.25</v>
       </c>
       <c r="E1239" t="n">
-        <v>75.87</v>
+        <v>75.94</v>
       </c>
       <c r="F1239" t="n">
-        <v>114085</v>
+        <v>114930</v>
       </c>
     </row>
     <row r="1240">
@@ -25281,10 +25281,10 @@
         <v>74.56999999999999</v>
       </c>
       <c r="E1243" t="n">
-        <v>76.86</v>
+        <v>76.75</v>
       </c>
       <c r="F1243" t="n">
-        <v>83845</v>
+        <v>84712</v>
       </c>
     </row>
     <row r="1244">
@@ -25301,10 +25301,10 @@
         <v>75.48</v>
       </c>
       <c r="E1244" t="n">
-        <v>76.90000000000001</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="F1244" t="n">
-        <v>94162</v>
+        <v>95068</v>
       </c>
     </row>
     <row r="1245">
@@ -25381,10 +25381,10 @@
         <v>77.76000000000001</v>
       </c>
       <c r="E1248" t="n">
-        <v>79.19</v>
+        <v>79.12</v>
       </c>
       <c r="F1248" t="n">
-        <v>91100</v>
+        <v>91755</v>
       </c>
     </row>
     <row r="1249">
@@ -25461,10 +25461,10 @@
         <v>77.04000000000001</v>
       </c>
       <c r="E1252" t="n">
-        <v>77.29000000000001</v>
+        <v>77.36</v>
       </c>
       <c r="F1252" t="n">
-        <v>94380</v>
+        <v>95204</v>
       </c>
     </row>
     <row r="1253">
@@ -25544,7 +25544,7 @@
         <v>77.53</v>
       </c>
       <c r="F1256" t="n">
-        <v>118273</v>
+        <v>119158</v>
       </c>
     </row>
     <row r="1257">
@@ -25641,10 +25641,10 @@
         <v>76.45</v>
       </c>
       <c r="E1261" t="n">
-        <v>77.61</v>
+        <v>78.01000000000001</v>
       </c>
       <c r="F1261" t="n">
-        <v>128067</v>
+        <v>129868</v>
       </c>
     </row>
     <row r="1262">
@@ -25741,10 +25741,10 @@
         <v>76.98</v>
       </c>
       <c r="E1266" t="n">
-        <v>78.63</v>
+        <v>78.56</v>
       </c>
       <c r="F1266" t="n">
-        <v>98609</v>
+        <v>99368</v>
       </c>
     </row>
     <row r="1267">
@@ -25841,10 +25841,10 @@
         <v>79.65000000000001</v>
       </c>
       <c r="E1271" t="n">
-        <v>81.84999999999999</v>
+        <v>81.69</v>
       </c>
       <c r="F1271" t="n">
-        <v>75889</v>
+        <v>76710</v>
       </c>
     </row>
     <row r="1272">
@@ -25861,10 +25861,10 @@
         <v>80.75</v>
       </c>
       <c r="E1272" t="n">
-        <v>83.08</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="F1272" t="n">
-        <v>85666</v>
+        <v>87047</v>
       </c>
     </row>
     <row r="1273">
@@ -25941,10 +25941,10 @@
         <v>78.5</v>
       </c>
       <c r="E1276" t="n">
-        <v>78.64</v>
+        <v>78.7</v>
       </c>
       <c r="F1276" t="n">
-        <v>138682</v>
+        <v>140571</v>
       </c>
     </row>
     <row r="1277">
@@ -25961,10 +25961,10 @@
         <v>76.78</v>
       </c>
       <c r="E1277" t="n">
-        <v>77.11</v>
+        <v>77.31999999999999</v>
       </c>
       <c r="F1277" t="n">
-        <v>132023</v>
+        <v>133396</v>
       </c>
     </row>
     <row r="1278">
@@ -26041,10 +26041,10 @@
         <v>78.84999999999999</v>
       </c>
       <c r="E1281" t="n">
-        <v>81.51000000000001</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="F1281" t="n">
-        <v>86597</v>
+        <v>87658</v>
       </c>
     </row>
     <row r="1282">
@@ -26064,7 +26064,7 @@
         <v>81.63</v>
       </c>
       <c r="F1282" t="n">
-        <v>85346</v>
+        <v>86235</v>
       </c>
     </row>
     <row r="1283">
@@ -26141,10 +26141,10 @@
         <v>80.31999999999999</v>
       </c>
       <c r="E1286" t="n">
-        <v>82.37</v>
+        <v>82.22</v>
       </c>
       <c r="F1286" t="n">
-        <v>83753</v>
+        <v>84560</v>
       </c>
     </row>
     <row r="1287">
@@ -26161,10 +26161,10 @@
         <v>81.34</v>
       </c>
       <c r="E1287" t="n">
-        <v>82.70999999999999</v>
+        <v>82.68000000000001</v>
       </c>
       <c r="F1287" t="n">
-        <v>80620</v>
+        <v>81459</v>
       </c>
     </row>
     <row r="1288">
@@ -26241,10 +26241,10 @@
         <v>81.45</v>
       </c>
       <c r="E1291" t="n">
-        <v>82.63</v>
+        <v>82.51000000000001</v>
       </c>
       <c r="F1291" t="n">
-        <v>67106</v>
+        <v>67848</v>
       </c>
     </row>
     <row r="1292">
@@ -26261,10 +26261,10 @@
         <v>80.65000000000001</v>
       </c>
       <c r="E1292" t="n">
-        <v>80.88</v>
+        <v>80.84</v>
       </c>
       <c r="F1292" t="n">
-        <v>72495</v>
+        <v>73168</v>
       </c>
     </row>
     <row r="1293">
@@ -26341,10 +26341,10 @@
         <v>81.37</v>
       </c>
       <c r="E1296" t="n">
-        <v>81.70999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="F1296" t="n">
-        <v>78801</v>
+        <v>79642</v>
       </c>
     </row>
     <row r="1297">
@@ -26361,10 +26361,10 @@
         <v>81.63</v>
       </c>
       <c r="E1297" t="n">
-        <v>83.19</v>
+        <v>83.12</v>
       </c>
       <c r="F1297" t="n">
-        <v>72423</v>
+        <v>73275</v>
       </c>
     </row>
     <row r="1298">
@@ -26441,10 +26441,10 @@
         <v>81.77</v>
       </c>
       <c r="E1301" t="n">
-        <v>82.52</v>
+        <v>82.87</v>
       </c>
       <c r="F1301" t="n">
-        <v>102278</v>
+        <v>103853</v>
       </c>
     </row>
     <row r="1302">
@@ -26461,10 +26461,10 @@
         <v>81.41</v>
       </c>
       <c r="E1302" t="n">
-        <v>81.66</v>
+        <v>81.55</v>
       </c>
       <c r="F1302" t="n">
-        <v>99175</v>
+        <v>100115</v>
       </c>
     </row>
     <row r="1303">
@@ -26532,19 +26532,19 @@
         <v>45365</v>
       </c>
       <c r="B1306" t="n">
-        <v>83.59999999999999</v>
+        <v>83.69</v>
       </c>
       <c r="C1306" t="n">
         <v>85.18000000000001</v>
       </c>
       <c r="D1306" t="n">
-        <v>83.53</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="E1306" t="n">
         <v>84.61</v>
       </c>
       <c r="F1306" t="n">
-        <v>71844</v>
+        <v>71119</v>
       </c>
     </row>
     <row r="1307">
@@ -26552,7 +26552,7 @@
         <v>45366</v>
       </c>
       <c r="B1307" t="n">
-        <v>84.65000000000001</v>
+        <v>84.68000000000001</v>
       </c>
       <c r="C1307" t="n">
         <v>85.09</v>
@@ -26564,7 +26564,7 @@
         <v>84.83</v>
       </c>
       <c r="F1307" t="n">
-        <v>75864</v>
+        <v>74945</v>
       </c>
     </row>
     <row r="1308">
@@ -26632,7 +26632,7 @@
         <v>45372</v>
       </c>
       <c r="B1311" t="n">
-        <v>85.70999999999999</v>
+        <v>85.81</v>
       </c>
       <c r="C1311" t="n">
         <v>86.03</v>
@@ -26644,7 +26644,7 @@
         <v>84.95999999999999</v>
       </c>
       <c r="F1311" t="n">
-        <v>67186</v>
+        <v>66113</v>
       </c>
     </row>
     <row r="1312">
@@ -26652,7 +26652,7 @@
         <v>45373</v>
       </c>
       <c r="B1312" t="n">
-        <v>85.09999999999999</v>
+        <v>84.98999999999999</v>
       </c>
       <c r="C1312" t="n">
         <v>85.58</v>
@@ -26664,7 +26664,7 @@
         <v>84.93000000000001</v>
       </c>
       <c r="F1312" t="n">
-        <v>54286</v>
+        <v>53666</v>
       </c>
     </row>
     <row r="1313">
@@ -26732,7 +26732,7 @@
         <v>45379</v>
       </c>
       <c r="B1316" t="n">
-        <v>85.56</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="C1316" t="n">
         <v>86.89</v>
@@ -26744,7 +26744,7 @@
         <v>86.67</v>
       </c>
       <c r="F1316" t="n">
-        <v>57372</v>
+        <v>56915</v>
       </c>
     </row>
     <row r="1317">
@@ -26821,10 +26821,10 @@
         <v>88.43000000000001</v>
       </c>
       <c r="E1320" t="n">
-        <v>90.38</v>
+        <v>90.56</v>
       </c>
       <c r="F1320" t="n">
-        <v>74470</v>
+        <v>75666</v>
       </c>
     </row>
     <row r="1321">
@@ -26841,10 +26841,10 @@
         <v>90.18000000000001</v>
       </c>
       <c r="E1321" t="n">
-        <v>90.52</v>
+        <v>90.39</v>
       </c>
       <c r="F1321" t="n">
-        <v>79937</v>
+        <v>80607</v>
       </c>
     </row>
     <row r="1322">
@@ -26921,10 +26921,10 @@
         <v>88.87</v>
       </c>
       <c r="E1325" t="n">
-        <v>89.68000000000001</v>
+        <v>89.55</v>
       </c>
       <c r="F1325" t="n">
-        <v>107040</v>
+        <v>107884</v>
       </c>
     </row>
     <row r="1326">
@@ -26941,10 +26941,10 @@
         <v>89.45</v>
       </c>
       <c r="E1326" t="n">
-        <v>89.73</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="F1326" t="n">
-        <v>108331</v>
+        <v>109120</v>
       </c>
     </row>
     <row r="1327">
@@ -27021,10 +27021,10 @@
         <v>85.63</v>
       </c>
       <c r="E1330" t="n">
-        <v>86.47</v>
+        <v>86.19</v>
       </c>
       <c r="F1330" t="n">
-        <v>107464</v>
+        <v>108132</v>
       </c>
     </row>
     <row r="1331">
@@ -27041,10 +27041,10 @@
         <v>85.61</v>
       </c>
       <c r="E1331" t="n">
-        <v>86.51000000000001</v>
+        <v>86.38</v>
       </c>
       <c r="F1331" t="n">
-        <v>143518</v>
+        <v>144473</v>
       </c>
     </row>
     <row r="1332">
@@ -27115,16 +27115,16 @@
         <v>86.88</v>
       </c>
       <c r="C1335" t="n">
-        <v>87.97</v>
+        <v>88</v>
       </c>
       <c r="D1335" t="n">
         <v>86.2</v>
       </c>
       <c r="E1335" t="n">
-        <v>87.95</v>
+        <v>87.83</v>
       </c>
       <c r="F1335" t="n">
-        <v>69439</v>
+        <v>70059</v>
       </c>
     </row>
     <row r="1336">
@@ -27141,10 +27141,10 @@
         <v>87.56999999999999</v>
       </c>
       <c r="E1336" t="n">
-        <v>87.98999999999999</v>
+        <v>87.89</v>
       </c>
       <c r="F1336" t="n">
-        <v>63936</v>
+        <v>64445</v>
       </c>
     </row>
     <row r="1337">
@@ -27221,10 +27221,10 @@
         <v>82.89</v>
       </c>
       <c r="E1340" t="n">
-        <v>83.47</v>
+        <v>83.48</v>
       </c>
       <c r="F1340" t="n">
-        <v>100961</v>
+        <v>101847</v>
       </c>
     </row>
     <row r="1341">
@@ -27238,13 +27238,13 @@
         <v>84.18000000000001</v>
       </c>
       <c r="D1341" t="n">
-        <v>82.65000000000001</v>
+        <v>82.53</v>
       </c>
       <c r="E1341" t="n">
-        <v>82.77</v>
+        <v>82.54000000000001</v>
       </c>
       <c r="F1341" t="n">
-        <v>82987</v>
+        <v>83584</v>
       </c>
     </row>
     <row r="1342">
@@ -27321,10 +27321,10 @@
         <v>83.18000000000001</v>
       </c>
       <c r="E1345" t="n">
-        <v>83.91</v>
+        <v>83.77</v>
       </c>
       <c r="F1345" t="n">
-        <v>67201</v>
+        <v>67737</v>
       </c>
     </row>
     <row r="1346">
@@ -27338,13 +27338,13 @@
         <v>84.23</v>
       </c>
       <c r="D1346" t="n">
-        <v>82.5</v>
+        <v>82.36</v>
       </c>
       <c r="E1346" t="n">
-        <v>82.61</v>
+        <v>82.36</v>
       </c>
       <c r="F1346" t="n">
-        <v>62356</v>
+        <v>63117</v>
       </c>
     </row>
     <row r="1347">
@@ -27421,10 +27421,10 @@
         <v>82.02</v>
       </c>
       <c r="E1350" t="n">
-        <v>83.04000000000001</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="F1350" t="n">
-        <v>65306</v>
+        <v>65759</v>
       </c>
     </row>
     <row r="1351">
@@ -27441,10 +27441,10 @@
         <v>82.81999999999999</v>
       </c>
       <c r="E1351" t="n">
-        <v>83.68000000000001</v>
+        <v>83.56</v>
       </c>
       <c r="F1351" t="n">
-        <v>60667</v>
+        <v>61133</v>
       </c>
     </row>
     <row r="1352">
@@ -27521,10 +27521,10 @@
         <v>80.7</v>
       </c>
       <c r="E1355" t="n">
-        <v>81.09</v>
+        <v>81.06999999999999</v>
       </c>
       <c r="F1355" t="n">
-        <v>68901</v>
+        <v>69958</v>
       </c>
     </row>
     <row r="1356">
@@ -27541,10 +27541,10 @@
         <v>80.42</v>
       </c>
       <c r="E1356" t="n">
-        <v>81.84999999999999</v>
+        <v>81.79000000000001</v>
       </c>
       <c r="F1356" t="n">
-        <v>56045</v>
+        <v>56381</v>
       </c>
     </row>
     <row r="1357">
@@ -27618,13 +27618,13 @@
         <v>83.51000000000001</v>
       </c>
       <c r="D1360" t="n">
-        <v>81.77</v>
+        <v>81.72</v>
       </c>
       <c r="E1360" t="n">
-        <v>81.88</v>
+        <v>81.73</v>
       </c>
       <c r="F1360" t="n">
-        <v>81262</v>
+        <v>81864</v>
       </c>
     </row>
     <row r="1361">
@@ -27641,10 +27641,10 @@
         <v>80.69</v>
       </c>
       <c r="E1361" t="n">
-        <v>81.22</v>
+        <v>81.09</v>
       </c>
       <c r="F1361" t="n">
-        <v>86335</v>
+        <v>87130</v>
       </c>
     </row>
     <row r="1362">
@@ -27721,10 +27721,10 @@
         <v>78.23999999999999</v>
       </c>
       <c r="E1365" t="n">
-        <v>79.73</v>
+        <v>79.69</v>
       </c>
       <c r="F1365" t="n">
-        <v>72035</v>
+        <v>72677</v>
       </c>
     </row>
     <row r="1366">
@@ -27741,10 +27741,10 @@
         <v>79.18000000000001</v>
       </c>
       <c r="E1366" t="n">
-        <v>79.27</v>
+        <v>79.23999999999999</v>
       </c>
       <c r="F1366" t="n">
-        <v>76576</v>
+        <v>77440</v>
       </c>
     </row>
     <row r="1367">
@@ -27821,10 +27821,10 @@
         <v>81.53</v>
       </c>
       <c r="E1370" t="n">
-        <v>81.98</v>
+        <v>81.68000000000001</v>
       </c>
       <c r="F1370" t="n">
-        <v>78296</v>
+        <v>79567</v>
       </c>
     </row>
     <row r="1371">
@@ -27841,10 +27841,10 @@
         <v>81.64</v>
       </c>
       <c r="E1371" t="n">
-        <v>82.2</v>
+        <v>82.06</v>
       </c>
       <c r="F1371" t="n">
-        <v>75030</v>
+        <v>75768</v>
       </c>
     </row>
     <row r="1372">
@@ -27921,10 +27921,10 @@
         <v>84.28</v>
       </c>
       <c r="E1375" t="n">
-        <v>85.01000000000001</v>
+        <v>84.7</v>
       </c>
       <c r="F1375" t="n">
-        <v>59448</v>
+        <v>59846</v>
       </c>
     </row>
     <row r="1376">
@@ -27941,10 +27941,10 @@
         <v>84</v>
       </c>
       <c r="E1376" t="n">
-        <v>84.31</v>
+        <v>84.16</v>
       </c>
       <c r="F1376" t="n">
-        <v>59797</v>
+        <v>60278</v>
       </c>
     </row>
     <row r="1377">
@@ -28021,10 +28021,10 @@
         <v>84.01000000000001</v>
       </c>
       <c r="E1380" t="n">
-        <v>85.25</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="F1380" t="n">
-        <v>64362</v>
+        <v>64909</v>
       </c>
     </row>
     <row r="1381">
@@ -28041,10 +28041,10 @@
         <v>84.39</v>
       </c>
       <c r="E1381" t="n">
-        <v>84.79000000000001</v>
+        <v>84.65000000000001</v>
       </c>
       <c r="F1381" t="n">
-        <v>69177</v>
+        <v>69862</v>
       </c>
     </row>
     <row r="1382">
@@ -28141,10 +28141,10 @@
         <v>86.17</v>
       </c>
       <c r="E1386" t="n">
-        <v>86.31999999999999</v>
+        <v>86.43000000000001</v>
       </c>
       <c r="F1386" t="n">
-        <v>67919</v>
+        <v>68965</v>
       </c>
     </row>
     <row r="1387">
@@ -28221,10 +28221,10 @@
         <v>84.16</v>
       </c>
       <c r="E1390" t="n">
-        <v>85.19</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="F1390" t="n">
-        <v>78243</v>
+        <v>78990</v>
       </c>
     </row>
     <row r="1391">
@@ -28238,13 +28238,13 @@
         <v>85.67</v>
       </c>
       <c r="D1391" t="n">
-        <v>84.40000000000001</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="E1391" t="n">
-        <v>84.5</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="F1391" t="n">
-        <v>73607</v>
+        <v>74302</v>
       </c>
     </row>
     <row r="1392">
@@ -28321,10 +28321,10 @@
         <v>83.41</v>
       </c>
       <c r="E1395" t="n">
-        <v>83.72</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="F1395" t="n">
-        <v>68620</v>
+        <v>69797</v>
       </c>
     </row>
     <row r="1396">
@@ -28338,13 +28338,13 @@
         <v>84.41</v>
       </c>
       <c r="D1396" t="n">
-        <v>81.7</v>
+        <v>81.64</v>
       </c>
       <c r="E1396" t="n">
-        <v>81.89</v>
+        <v>81.64</v>
       </c>
       <c r="F1396" t="n">
-        <v>72020</v>
+        <v>72736</v>
       </c>
     </row>
     <row r="1397">
@@ -28421,10 +28421,10 @@
         <v>79.28</v>
       </c>
       <c r="E1400" t="n">
-        <v>81.33</v>
+        <v>81.37</v>
       </c>
       <c r="F1400" t="n">
-        <v>69150</v>
+        <v>69789</v>
       </c>
     </row>
     <row r="1401">
@@ -28441,10 +28441,10 @@
         <v>79.39</v>
       </c>
       <c r="E1401" t="n">
-        <v>79.92</v>
+        <v>79.48999999999999</v>
       </c>
       <c r="F1401" t="n">
-        <v>64725</v>
+        <v>65748</v>
       </c>
     </row>
     <row r="1402">
@@ -28521,10 +28521,10 @@
         <v>79.3</v>
       </c>
       <c r="E1405" t="n">
-        <v>80</v>
+        <v>79.83</v>
       </c>
       <c r="F1405" t="n">
-        <v>104482</v>
+        <v>105741</v>
       </c>
     </row>
     <row r="1406">
@@ -28541,10 +28541,10 @@
         <v>76.26000000000001</v>
       </c>
       <c r="E1406" t="n">
-        <v>77.08</v>
+        <v>77.14</v>
       </c>
       <c r="F1406" t="n">
-        <v>124356</v>
+        <v>125792</v>
       </c>
     </row>
     <row r="1407">
@@ -28621,10 +28621,10 @@
         <v>77.33</v>
       </c>
       <c r="E1410" t="n">
-        <v>78.73999999999999</v>
+        <v>78.59</v>
       </c>
       <c r="F1410" t="n">
-        <v>113028</v>
+        <v>113892</v>
       </c>
     </row>
     <row r="1411">
@@ -28641,10 +28641,10 @@
         <v>78.43000000000001</v>
       </c>
       <c r="E1411" t="n">
-        <v>79.34</v>
+        <v>79.27</v>
       </c>
       <c r="F1411" t="n">
-        <v>86405</v>
+        <v>87467</v>
       </c>
     </row>
     <row r="1412">
@@ -28721,10 +28721,10 @@
         <v>79.11</v>
       </c>
       <c r="E1415" t="n">
-        <v>80.31999999999999</v>
+        <v>80.26000000000001</v>
       </c>
       <c r="F1415" t="n">
-        <v>78757</v>
+        <v>79567</v>
       </c>
     </row>
     <row r="1416">
@@ -28741,10 +28741,10 @@
         <v>78.09</v>
       </c>
       <c r="E1416" t="n">
-        <v>79.22</v>
+        <v>78.94</v>
       </c>
       <c r="F1416" t="n">
-        <v>81009</v>
+        <v>82030</v>
       </c>
     </row>
     <row r="1417">
@@ -28821,10 +28821,10 @@
         <v>75.25</v>
       </c>
       <c r="E1420" t="n">
-        <v>76.47</v>
+        <v>76.42</v>
       </c>
       <c r="F1420" t="n">
-        <v>79280</v>
+        <v>79873</v>
       </c>
     </row>
     <row r="1421">
@@ -28841,10 +28841,10 @@
         <v>76.40000000000001</v>
       </c>
       <c r="E1421" t="n">
-        <v>78.17</v>
+        <v>78.13</v>
       </c>
       <c r="F1421" t="n">
-        <v>68613</v>
+        <v>69081</v>
       </c>
     </row>
     <row r="1422">
@@ -28921,10 +28921,10 @@
         <v>76.90000000000001</v>
       </c>
       <c r="E1425" t="n">
-        <v>78.81</v>
+        <v>78.72</v>
       </c>
       <c r="F1425" t="n">
-        <v>93699</v>
+        <v>94397</v>
       </c>
     </row>
     <row r="1426">
@@ -28941,10 +28941,10 @@
         <v>76.56</v>
       </c>
       <c r="E1426" t="n">
-        <v>76.81</v>
+        <v>76.77</v>
       </c>
       <c r="F1426" t="n">
-        <v>108329</v>
+        <v>109124</v>
       </c>
     </row>
     <row r="1427">
@@ -29021,10 +29021,10 @@
         <v>72.20999999999999</v>
       </c>
       <c r="E1430" t="n">
-        <v>72.54000000000001</v>
+        <v>72.53</v>
       </c>
       <c r="F1430" t="n">
-        <v>108713</v>
+        <v>109541</v>
       </c>
     </row>
     <row r="1431">
@@ -29041,10 +29041,10 @@
         <v>70.45</v>
       </c>
       <c r="E1431" t="n">
-        <v>71.37</v>
+        <v>71.2</v>
       </c>
       <c r="F1431" t="n">
-        <v>115759</v>
+        <v>116954</v>
       </c>
     </row>
     <row r="1432">
@@ -29121,10 +29121,10 @@
         <v>70.31999999999999</v>
       </c>
       <c r="E1435" t="n">
-        <v>71.89</v>
+        <v>71.67</v>
       </c>
       <c r="F1435" t="n">
-        <v>114181</v>
+        <v>115156</v>
       </c>
     </row>
     <row r="1436">
@@ -29141,10 +29141,10 @@
         <v>71.09</v>
       </c>
       <c r="E1436" t="n">
-        <v>71.73</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="F1436" t="n">
-        <v>98569</v>
+        <v>99629</v>
       </c>
     </row>
     <row r="1437">
@@ -29221,10 +29221,10 @@
         <v>72.26000000000001</v>
       </c>
       <c r="E1440" t="n">
-        <v>74.05</v>
+        <v>73.97</v>
       </c>
       <c r="F1440" t="n">
-        <v>88395</v>
+        <v>89094</v>
       </c>
     </row>
     <row r="1441">
@@ -29241,10 +29241,10 @@
         <v>73.28</v>
       </c>
       <c r="E1441" t="n">
-        <v>73.98</v>
+        <v>73.87</v>
       </c>
       <c r="F1441" t="n">
-        <v>71635</v>
+        <v>72413</v>
       </c>
     </row>
     <row r="1442">
@@ -29321,10 +29321,10 @@
         <v>70.20999999999999</v>
       </c>
       <c r="E1445" t="n">
-        <v>70.66</v>
+        <v>70.68000000000001</v>
       </c>
       <c r="F1445" t="n">
-        <v>154979</v>
+        <v>155899</v>
       </c>
     </row>
     <row r="1446">
@@ -29335,16 +29335,16 @@
         <v>70.68000000000001</v>
       </c>
       <c r="C1446" t="n">
-        <v>71.89</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="D1446" t="n">
         <v>70.39</v>
       </c>
       <c r="E1446" t="n">
-        <v>71.81999999999999</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="F1446" t="n">
-        <v>122438</v>
+        <v>123787</v>
       </c>
     </row>
     <row r="1447">
@@ -29421,10 +29421,10 @@
         <v>74.18000000000001</v>
       </c>
       <c r="E1450" t="n">
-        <v>77.58</v>
+        <v>77.28</v>
       </c>
       <c r="F1450" t="n">
-        <v>123449</v>
+        <v>125075</v>
       </c>
     </row>
     <row r="1451">
@@ -29441,10 +29441,10 @@
         <v>77.19</v>
       </c>
       <c r="E1451" t="n">
-        <v>77.87</v>
+        <v>77.73</v>
       </c>
       <c r="F1451" t="n">
-        <v>120535</v>
+        <v>121412</v>
       </c>
     </row>
     <row r="1452">
@@ -38944,7 +38944,7 @@
         <v>86.88</v>
       </c>
       <c r="F1926" t="n">
-        <v>101145</v>
+        <v>101136</v>
       </c>
     </row>
     <row r="1927">
@@ -38964,7 +38964,7 @@
         <v>87.8</v>
       </c>
       <c r="F1927" t="n">
-        <v>114422</v>
+        <v>114314</v>
       </c>
     </row>
     <row r="1928">
@@ -38984,7 +38984,7 @@
         <v>87.23999999999999</v>
       </c>
       <c r="F1928" t="n">
-        <v>104954</v>
+        <v>104847</v>
       </c>
     </row>
     <row r="1929">
@@ -39012,7 +39012,7 @@
         <v>46248</v>
       </c>
       <c r="B1930" t="n">
-        <v>85.95999999999999</v>
+        <v>86.08</v>
       </c>
       <c r="C1930" t="n">
         <v>87.53</v>
@@ -39024,7 +39024,27 @@
         <v>87.33</v>
       </c>
       <c r="F1930" t="n">
-        <v>83628</v>
+        <v>83643</v>
+      </c>
+    </row>
+    <row r="1931">
+      <c r="A1931" s="1" t="n">
+        <v>46250</v>
+      </c>
+      <c r="B1931" t="n">
+        <v>87.31</v>
+      </c>
+      <c r="C1931" t="n">
+        <v>89.86</v>
+      </c>
+      <c r="D1931" t="n">
+        <v>86.58</v>
+      </c>
+      <c r="E1931" t="n">
+        <v>89.75</v>
+      </c>
+      <c r="F1931" t="n">
+        <v>111655</v>
       </c>
     </row>
   </sheetData>

--- a/database/BRENT.xlsx
+++ b/database/BRENT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1931"/>
+  <dimension ref="A1:F1932"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3881,10 +3881,10 @@
         <v>60.96</v>
       </c>
       <c r="E173" t="n">
-        <v>61.65</v>
+        <v>61.74</v>
       </c>
       <c r="F173" t="n">
-        <v>7745</v>
+        <v>7439</v>
       </c>
     </row>
     <row r="174">
@@ -3952,7 +3952,7 @@
         <v>43769</v>
       </c>
       <c r="B177" t="n">
-        <v>60.27</v>
+        <v>60.17</v>
       </c>
       <c r="C177" t="n">
         <v>60.79</v>
@@ -3964,7 +3964,7 @@
         <v>59.46</v>
       </c>
       <c r="F177" t="n">
-        <v>20603</v>
+        <v>20831</v>
       </c>
     </row>
     <row r="178">
@@ -3972,7 +3972,7 @@
         <v>43770</v>
       </c>
       <c r="B178" t="n">
-        <v>59.64</v>
+        <v>59.42</v>
       </c>
       <c r="C178" t="n">
         <v>61.8</v>
@@ -3984,7 +3984,7 @@
         <v>61.65</v>
       </c>
       <c r="F178" t="n">
-        <v>18281</v>
+        <v>18539</v>
       </c>
     </row>
     <row r="179">
@@ -4061,10 +4061,10 @@
         <v>61.63</v>
       </c>
       <c r="E182" t="n">
-        <v>62.29</v>
+        <v>62.14</v>
       </c>
       <c r="F182" t="n">
-        <v>19680</v>
+        <v>19306</v>
       </c>
     </row>
     <row r="183">
@@ -4081,10 +4081,10 @@
         <v>60.65</v>
       </c>
       <c r="E183" t="n">
-        <v>62.64</v>
+        <v>62.61</v>
       </c>
       <c r="F183" t="n">
-        <v>21863</v>
+        <v>21625</v>
       </c>
     </row>
     <row r="184">
@@ -4161,10 +4161,10 @@
         <v>62.14</v>
       </c>
       <c r="E187" t="n">
-        <v>62.33</v>
+        <v>62.38</v>
       </c>
       <c r="F187" t="n">
-        <v>19293</v>
+        <v>19157</v>
       </c>
     </row>
     <row r="188">
@@ -4181,10 +4181,10 @@
         <v>61.69</v>
       </c>
       <c r="E188" t="n">
-        <v>63.41</v>
+        <v>63.32</v>
       </c>
       <c r="F188" t="n">
-        <v>16092</v>
+        <v>15801</v>
       </c>
     </row>
     <row r="189">
@@ -4261,10 +4261,10 @@
         <v>61.91</v>
       </c>
       <c r="E192" t="n">
-        <v>63.64</v>
+        <v>63.74</v>
       </c>
       <c r="F192" t="n">
-        <v>21823</v>
+        <v>21582</v>
       </c>
     </row>
     <row r="193">
@@ -4281,10 +4281,10 @@
         <v>61.92</v>
       </c>
       <c r="E193" t="n">
-        <v>62.52</v>
+        <v>62.58</v>
       </c>
       <c r="F193" t="n">
-        <v>17794</v>
+        <v>17577</v>
       </c>
     </row>
     <row r="194">
@@ -4461,10 +4461,10 @@
         <v>62.73</v>
       </c>
       <c r="E202" t="n">
-        <v>63.26</v>
+        <v>63.33</v>
       </c>
       <c r="F202" t="n">
-        <v>24300</v>
+        <v>24042</v>
       </c>
     </row>
     <row r="203">
@@ -4481,10 +4481,10 @@
         <v>62.82</v>
       </c>
       <c r="E203" t="n">
-        <v>64.34</v>
+        <v>64.22</v>
       </c>
       <c r="F203" t="n">
-        <v>22572</v>
+        <v>22359</v>
       </c>
     </row>
     <row r="204">
@@ -4561,10 +4561,10 @@
         <v>63.86</v>
       </c>
       <c r="E207" t="n">
-        <v>64.28</v>
+        <v>64.31</v>
       </c>
       <c r="F207" t="n">
-        <v>18454</v>
+        <v>18198</v>
       </c>
     </row>
     <row r="208">
@@ -4581,10 +4581,10 @@
         <v>64.48</v>
       </c>
       <c r="E208" t="n">
-        <v>64.90000000000001</v>
+        <v>64.88</v>
       </c>
       <c r="F208" t="n">
-        <v>21671</v>
+        <v>21484</v>
       </c>
     </row>
     <row r="209">
@@ -4661,10 +4661,10 @@
         <v>66.02</v>
       </c>
       <c r="E212" t="n">
-        <v>66.53</v>
+        <v>66.45</v>
       </c>
       <c r="F212" t="n">
-        <v>11180</v>
+        <v>10932</v>
       </c>
     </row>
     <row r="213">
@@ -4681,10 +4681,10 @@
         <v>65.72</v>
       </c>
       <c r="E213" t="n">
-        <v>66.01000000000001</v>
+        <v>65.98</v>
       </c>
       <c r="F213" t="n">
-        <v>14806</v>
+        <v>14693</v>
       </c>
     </row>
     <row r="214">
@@ -4741,10 +4741,10 @@
         <v>66.09</v>
       </c>
       <c r="E216" t="n">
-        <v>66.75</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="F216" t="n">
-        <v>9613</v>
+        <v>9409</v>
       </c>
     </row>
     <row r="217">
@@ -4761,10 +4761,10 @@
         <v>66.34</v>
       </c>
       <c r="E217" t="n">
-        <v>66.84</v>
+        <v>66.81</v>
       </c>
       <c r="F217" t="n">
-        <v>11398</v>
+        <v>11272</v>
       </c>
     </row>
     <row r="218">
@@ -4821,10 +4821,10 @@
         <v>65.7</v>
       </c>
       <c r="E220" t="n">
-        <v>66.23</v>
+        <v>66.19</v>
       </c>
       <c r="F220" t="n">
-        <v>15351</v>
+        <v>15153</v>
       </c>
     </row>
     <row r="221">
@@ -4841,10 +4841,10 @@
         <v>66.19</v>
       </c>
       <c r="E221" t="n">
-        <v>68.59</v>
+        <v>68.55</v>
       </c>
       <c r="F221" t="n">
-        <v>35609</v>
+        <v>35427</v>
       </c>
     </row>
     <row r="222">
@@ -4924,7 +4924,7 @@
         <v>65.38</v>
       </c>
       <c r="F225" t="n">
-        <v>25951</v>
+        <v>25682</v>
       </c>
     </row>
     <row r="226">
@@ -4944,7 +4944,7 @@
         <v>65</v>
       </c>
       <c r="F226" t="n">
-        <v>20436</v>
+        <v>20016</v>
       </c>
     </row>
     <row r="227">
@@ -5021,10 +5021,10 @@
         <v>63.89</v>
       </c>
       <c r="E230" t="n">
-        <v>64.7</v>
+        <v>64.64</v>
       </c>
       <c r="F230" t="n">
-        <v>16472</v>
+        <v>16107</v>
       </c>
     </row>
     <row r="231">
@@ -5041,10 +5041,10 @@
         <v>64.45</v>
       </c>
       <c r="E231" t="n">
-        <v>65.08</v>
+        <v>64.95</v>
       </c>
       <c r="F231" t="n">
-        <v>16251</v>
+        <v>16060</v>
       </c>
     </row>
     <row r="232">
@@ -5121,10 +5121,10 @@
         <v>61.24</v>
       </c>
       <c r="E235" t="n">
-        <v>62.11</v>
+        <v>61.97</v>
       </c>
       <c r="F235" t="n">
-        <v>23208</v>
+        <v>22982</v>
       </c>
     </row>
     <row r="236">
@@ -5141,10 +5141,10 @@
         <v>60.24</v>
       </c>
       <c r="E236" t="n">
-        <v>60.64</v>
+        <v>60.82</v>
       </c>
       <c r="F236" t="n">
-        <v>21687</v>
+        <v>21411</v>
       </c>
     </row>
     <row r="237">
@@ -5221,10 +5221,10 @@
         <v>56.73</v>
       </c>
       <c r="E240" t="n">
-        <v>58.2</v>
+        <v>58.03</v>
       </c>
       <c r="F240" t="n">
-        <v>28894</v>
+        <v>28317</v>
       </c>
     </row>
     <row r="241">
@@ -5244,7 +5244,7 @@
         <v>56.63</v>
       </c>
       <c r="F241" t="n">
-        <v>31264</v>
+        <v>30854</v>
       </c>
     </row>
     <row r="242">
@@ -5321,10 +5321,10 @@
         <v>54.24</v>
       </c>
       <c r="E245" t="n">
-        <v>55.14</v>
+        <v>55.07</v>
       </c>
       <c r="F245" t="n">
-        <v>31917</v>
+        <v>31638</v>
       </c>
     </row>
     <row r="246">
@@ -5341,10 +5341,10 @@
         <v>54.2</v>
       </c>
       <c r="E246" t="n">
-        <v>54.45</v>
+        <v>54.48</v>
       </c>
       <c r="F246" t="n">
-        <v>26144</v>
+        <v>25828</v>
       </c>
     </row>
     <row r="247">
@@ -5421,10 +5421,10 @@
         <v>54.95</v>
       </c>
       <c r="E250" t="n">
-        <v>56.4</v>
+        <v>56.51</v>
       </c>
       <c r="F250" t="n">
-        <v>24914</v>
+        <v>24675</v>
       </c>
     </row>
     <row r="251">
@@ -5441,10 +5441,10 @@
         <v>56.13</v>
       </c>
       <c r="E251" t="n">
-        <v>57.33</v>
+        <v>57.32</v>
       </c>
       <c r="F251" t="n">
-        <v>21778</v>
+        <v>21410</v>
       </c>
     </row>
     <row r="252">
@@ -5521,10 +5521,10 @@
         <v>58.89</v>
       </c>
       <c r="E255" t="n">
-        <v>59.03</v>
+        <v>59.28</v>
       </c>
       <c r="F255" t="n">
-        <v>23391</v>
+        <v>23121</v>
       </c>
     </row>
     <row r="256">
@@ -5541,10 +5541,10 @@
         <v>57.71</v>
       </c>
       <c r="E256" t="n">
-        <v>58.44</v>
+        <v>58.33</v>
       </c>
       <c r="F256" t="n">
-        <v>26971</v>
+        <v>26663</v>
       </c>
     </row>
     <row r="257">
@@ -5621,10 +5621,10 @@
         <v>50.38</v>
       </c>
       <c r="E260" t="n">
-        <v>50.95</v>
+        <v>51.35</v>
       </c>
       <c r="F260" t="n">
-        <v>52807</v>
+        <v>51199</v>
       </c>
     </row>
     <row r="261">
@@ -5641,10 +5641,10 @@
         <v>48.92</v>
       </c>
       <c r="E261" t="n">
-        <v>50.08</v>
+        <v>50.01</v>
       </c>
       <c r="F261" t="n">
-        <v>72794</v>
+        <v>71739</v>
       </c>
     </row>
     <row r="262">
@@ -5721,10 +5721,10 @@
         <v>49.67</v>
       </c>
       <c r="E265" t="n">
-        <v>50</v>
+        <v>49.95</v>
       </c>
       <c r="F265" t="n">
-        <v>42678</v>
+        <v>42080</v>
       </c>
     </row>
     <row r="266">
@@ -5741,10 +5741,10 @@
         <v>45.16</v>
       </c>
       <c r="E266" t="n">
-        <v>45.51</v>
+        <v>45.55</v>
       </c>
       <c r="F266" t="n">
-        <v>65295</v>
+        <v>64437</v>
       </c>
     </row>
     <row r="267">
@@ -5812,7 +5812,7 @@
         <v>43902</v>
       </c>
       <c r="B270" t="n">
-        <v>36.29</v>
+        <v>35.97</v>
       </c>
       <c r="C270" t="n">
         <v>36.45</v>
@@ -5824,7 +5824,7 @@
         <v>33.49</v>
       </c>
       <c r="F270" t="n">
-        <v>64469</v>
+        <v>66181</v>
       </c>
     </row>
     <row r="271">
@@ -6121,10 +6121,10 @@
         <v>26.12</v>
       </c>
       <c r="E285" t="n">
-        <v>29.96</v>
+        <v>30.29</v>
       </c>
       <c r="F285" t="n">
-        <v>214756</v>
+        <v>210087</v>
       </c>
     </row>
     <row r="286">
@@ -6135,16 +6135,16 @@
         <v>29.95</v>
       </c>
       <c r="C286" t="n">
-        <v>35.28</v>
+        <v>35.24</v>
       </c>
       <c r="D286" t="n">
         <v>28.9</v>
       </c>
       <c r="E286" t="n">
-        <v>35.16</v>
+        <v>34.72</v>
       </c>
       <c r="F286" t="n">
-        <v>280402</v>
+        <v>275171</v>
       </c>
     </row>
     <row r="287">
@@ -6221,10 +6221,10 @@
         <v>32.46</v>
       </c>
       <c r="E290" t="n">
-        <v>32.8</v>
+        <v>33.2</v>
       </c>
       <c r="F290" t="n">
-        <v>236196</v>
+        <v>230614</v>
       </c>
     </row>
     <row r="291">
@@ -6321,10 +6321,10 @@
         <v>29.42</v>
       </c>
       <c r="E295" t="n">
-        <v>30.59</v>
+        <v>30.65</v>
       </c>
       <c r="F295" t="n">
-        <v>151526</v>
+        <v>146842</v>
       </c>
     </row>
     <row r="296">
@@ -6341,10 +6341,10 @@
         <v>30.13</v>
       </c>
       <c r="E296" t="n">
-        <v>30.68</v>
+        <v>30.78</v>
       </c>
       <c r="F296" t="n">
-        <v>174982</v>
+        <v>171223</v>
       </c>
     </row>
     <row r="297">
@@ -6421,10 +6421,10 @@
         <v>23.38</v>
       </c>
       <c r="E300" t="n">
-        <v>24.73</v>
+        <v>24.74</v>
       </c>
       <c r="F300" t="n">
-        <v>216653</v>
+        <v>213310</v>
       </c>
     </row>
     <row r="301">
@@ -6441,10 +6441,10 @@
         <v>23.7</v>
       </c>
       <c r="E301" t="n">
-        <v>24.99</v>
+        <v>24.98</v>
       </c>
       <c r="F301" t="n">
-        <v>166443</v>
+        <v>163124</v>
       </c>
     </row>
     <row r="302">
@@ -6521,10 +6521,10 @@
         <v>24.33</v>
       </c>
       <c r="E305" t="n">
-        <v>26.85</v>
+        <v>26.83</v>
       </c>
       <c r="F305" t="n">
-        <v>229615</v>
+        <v>224455</v>
       </c>
     </row>
     <row r="306">
@@ -6541,10 +6541,10 @@
         <v>26.05</v>
       </c>
       <c r="E306" t="n">
-        <v>26.81</v>
+        <v>26.78</v>
       </c>
       <c r="F306" t="n">
-        <v>199609</v>
+        <v>196748</v>
       </c>
     </row>
     <row r="307">
@@ -6621,10 +6621,10 @@
         <v>29.4</v>
       </c>
       <c r="E310" t="n">
-        <v>29.65</v>
+        <v>29.48</v>
       </c>
       <c r="F310" t="n">
-        <v>229585</v>
+        <v>225301</v>
       </c>
     </row>
     <row r="311">
@@ -6641,10 +6641,10 @@
         <v>29.63</v>
       </c>
       <c r="E311" t="n">
-        <v>31.25</v>
+        <v>31.26</v>
       </c>
       <c r="F311" t="n">
-        <v>195288</v>
+        <v>192233</v>
       </c>
     </row>
     <row r="312">
@@ -6715,16 +6715,16 @@
         <v>29.73</v>
       </c>
       <c r="C315" t="n">
-        <v>31.75</v>
+        <v>31.65</v>
       </c>
       <c r="D315" t="n">
         <v>29.32</v>
       </c>
       <c r="E315" t="n">
-        <v>31.58</v>
+        <v>31.44</v>
       </c>
       <c r="F315" t="n">
-        <v>156389</v>
+        <v>152193</v>
       </c>
     </row>
     <row r="316">
@@ -6735,16 +6735,16 @@
         <v>31.58</v>
       </c>
       <c r="C316" t="n">
-        <v>33.06</v>
+        <v>32.96</v>
       </c>
       <c r="D316" t="n">
         <v>31.23</v>
       </c>
       <c r="E316" t="n">
-        <v>32.94</v>
+        <v>32.9</v>
       </c>
       <c r="F316" t="n">
-        <v>163209</v>
+        <v>160121</v>
       </c>
     </row>
     <row r="317">
@@ -6821,10 +6821,10 @@
         <v>35.92</v>
       </c>
       <c r="E320" t="n">
-        <v>36.3</v>
+        <v>36.38</v>
       </c>
       <c r="F320" t="n">
-        <v>160329</v>
+        <v>157279</v>
       </c>
     </row>
     <row r="321">
@@ -6841,10 +6841,10 @@
         <v>33.87</v>
       </c>
       <c r="E321" t="n">
-        <v>35.52</v>
+        <v>35.66</v>
       </c>
       <c r="F321" t="n">
-        <v>198023</v>
+        <v>194062</v>
       </c>
     </row>
     <row r="322">
@@ -6921,10 +6921,10 @@
         <v>34.37</v>
       </c>
       <c r="E325" t="n">
-        <v>35.98</v>
+        <v>35.89</v>
       </c>
       <c r="F325" t="n">
-        <v>213086</v>
+        <v>208524</v>
       </c>
     </row>
     <row r="326">
@@ -6941,10 +6941,10 @@
         <v>34.87</v>
       </c>
       <c r="E326" t="n">
-        <v>37.61</v>
+        <v>37.43</v>
       </c>
       <c r="F326" t="n">
-        <v>198370</v>
+        <v>193664</v>
       </c>
     </row>
     <row r="327">
@@ -7021,10 +7021,10 @@
         <v>39.05</v>
       </c>
       <c r="E330" t="n">
-        <v>39.92</v>
+        <v>39.78</v>
       </c>
       <c r="F330" t="n">
-        <v>161661</v>
+        <v>158433</v>
       </c>
     </row>
     <row r="331">
@@ -7041,10 +7041,10 @@
         <v>39.75</v>
       </c>
       <c r="E331" t="n">
-        <v>41.83</v>
+        <v>42.14</v>
       </c>
       <c r="F331" t="n">
-        <v>167359</v>
+        <v>163467</v>
       </c>
     </row>
     <row r="332">
@@ -7121,10 +7121,10 @@
         <v>37.96</v>
       </c>
       <c r="E335" t="n">
-        <v>38.41</v>
+        <v>38.36</v>
       </c>
       <c r="F335" t="n">
-        <v>227925</v>
+        <v>221502</v>
       </c>
     </row>
     <row r="336">
@@ -7141,10 +7141,10 @@
         <v>37.14</v>
       </c>
       <c r="E336" t="n">
-        <v>38.97</v>
+        <v>38.94</v>
       </c>
       <c r="F336" t="n">
-        <v>263342</v>
+        <v>260674</v>
       </c>
     </row>
     <row r="337">
@@ -7221,10 +7221,10 @@
         <v>40.05</v>
       </c>
       <c r="E340" t="n">
-        <v>41.33</v>
+        <v>41.37</v>
       </c>
       <c r="F340" t="n">
-        <v>163774</v>
+        <v>161532</v>
       </c>
     </row>
     <row r="341">
@@ -7241,10 +7241,10 @@
         <v>40.97</v>
       </c>
       <c r="E341" t="n">
-        <v>41.78</v>
+        <v>41.99</v>
       </c>
       <c r="F341" t="n">
-        <v>156573</v>
+        <v>153177</v>
       </c>
     </row>
     <row r="342">
@@ -7315,16 +7315,16 @@
         <v>40.45</v>
       </c>
       <c r="C345" t="n">
-        <v>41.59</v>
+        <v>41.51</v>
       </c>
       <c r="D345" t="n">
         <v>39.68</v>
       </c>
       <c r="E345" t="n">
-        <v>41.35</v>
+        <v>41.39</v>
       </c>
       <c r="F345" t="n">
-        <v>181021</v>
+        <v>178413</v>
       </c>
     </row>
     <row r="346">
@@ -7341,10 +7341,10 @@
         <v>40.25</v>
       </c>
       <c r="E346" t="n">
-        <v>40.57</v>
+        <v>40.58</v>
       </c>
       <c r="F346" t="n">
-        <v>160433</v>
+        <v>157969</v>
       </c>
     </row>
     <row r="347">
@@ -7421,10 +7421,10 @@
         <v>41.71</v>
       </c>
       <c r="E350" t="n">
-        <v>42.65</v>
+        <v>42.71</v>
       </c>
       <c r="F350" t="n">
-        <v>144329</v>
+        <v>142409</v>
       </c>
     </row>
     <row r="351">
@@ -7521,10 +7521,10 @@
         <v>41.99</v>
       </c>
       <c r="E355" t="n">
-        <v>42.35</v>
+        <v>42.32</v>
       </c>
       <c r="F355" t="n">
-        <v>136451</v>
+        <v>133908</v>
       </c>
     </row>
     <row r="356">
@@ -7541,10 +7541,10 @@
         <v>41.4</v>
       </c>
       <c r="E356" t="n">
-        <v>43.26</v>
+        <v>43.23</v>
       </c>
       <c r="F356" t="n">
-        <v>154800</v>
+        <v>152491</v>
       </c>
     </row>
     <row r="357">
@@ -7621,10 +7621,10 @@
         <v>43.19</v>
       </c>
       <c r="E360" t="n">
-        <v>43.28</v>
+        <v>43.36</v>
       </c>
       <c r="F360" t="n">
-        <v>101544</v>
+        <v>99613</v>
       </c>
     </row>
     <row r="361">
@@ -7641,10 +7641,10 @@
         <v>42.7</v>
       </c>
       <c r="E361" t="n">
-        <v>43.12</v>
+        <v>43.18</v>
       </c>
       <c r="F361" t="n">
-        <v>95049</v>
+        <v>93740</v>
       </c>
     </row>
     <row r="362">
@@ -7721,10 +7721,10 @@
         <v>43.42</v>
       </c>
       <c r="E365" t="n">
-        <v>43.53</v>
+        <v>43.82</v>
       </c>
       <c r="F365" t="n">
-        <v>112495</v>
+        <v>109900</v>
       </c>
     </row>
     <row r="366">
@@ -7741,10 +7741,10 @@
         <v>43.18</v>
       </c>
       <c r="E366" t="n">
-        <v>43.62</v>
+        <v>43.67</v>
       </c>
       <c r="F366" t="n">
-        <v>117377</v>
+        <v>115737</v>
       </c>
     </row>
     <row r="367">
@@ -7821,10 +7821,10 @@
         <v>41.95</v>
       </c>
       <c r="E370" t="n">
-        <v>43.56</v>
+        <v>43.43</v>
       </c>
       <c r="F370" t="n">
-        <v>117072</v>
+        <v>113377</v>
       </c>
     </row>
     <row r="371">
@@ -7841,10 +7841,10 @@
         <v>42.94</v>
       </c>
       <c r="E371" t="n">
-        <v>43.59</v>
+        <v>43.65</v>
       </c>
       <c r="F371" t="n">
-        <v>128800</v>
+        <v>127155</v>
       </c>
     </row>
     <row r="372">
@@ -7921,10 +7921,10 @@
         <v>44.96</v>
       </c>
       <c r="E375" t="n">
-        <v>45.13</v>
+        <v>45.28</v>
       </c>
       <c r="F375" t="n">
-        <v>122044</v>
+        <v>120720</v>
       </c>
     </row>
     <row r="376">
@@ -7941,10 +7941,10 @@
         <v>44.4</v>
       </c>
       <c r="E376" t="n">
-        <v>44.71</v>
+        <v>44.76</v>
       </c>
       <c r="F376" t="n">
-        <v>120731</v>
+        <v>119541</v>
       </c>
     </row>
     <row r="377">
@@ -8021,10 +8021,10 @@
         <v>45.07</v>
       </c>
       <c r="E380" t="n">
-        <v>45.24</v>
+        <v>45.3</v>
       </c>
       <c r="F380" t="n">
-        <v>91702</v>
+        <v>90204</v>
       </c>
     </row>
     <row r="381">
@@ -8041,10 +8041,10 @@
         <v>44.77</v>
       </c>
       <c r="E381" t="n">
-        <v>45.19</v>
+        <v>45.2</v>
       </c>
       <c r="F381" t="n">
-        <v>85013</v>
+        <v>83793</v>
       </c>
     </row>
     <row r="382">
@@ -8121,10 +8121,10 @@
         <v>44.46</v>
       </c>
       <c r="E385" t="n">
-        <v>45.27</v>
+        <v>45.36</v>
       </c>
       <c r="F385" t="n">
-        <v>87294</v>
+        <v>86301</v>
       </c>
     </row>
     <row r="386">
@@ -8141,10 +8141,10 @@
         <v>44.09</v>
       </c>
       <c r="E386" t="n">
-        <v>44.69</v>
+        <v>44.79</v>
       </c>
       <c r="F386" t="n">
-        <v>78965</v>
+        <v>77659</v>
       </c>
     </row>
     <row r="387">
@@ -8224,7 +8224,7 @@
         <v>45.59</v>
       </c>
       <c r="F390" t="n">
-        <v>96916</v>
+        <v>95873</v>
       </c>
     </row>
     <row r="391">
@@ -8241,10 +8241,10 @@
         <v>45.36</v>
       </c>
       <c r="E391" t="n">
-        <v>45.85</v>
+        <v>45.89</v>
       </c>
       <c r="F391" t="n">
-        <v>81841</v>
+        <v>81058</v>
       </c>
     </row>
     <row r="392">
@@ -8321,10 +8321,10 @@
         <v>43.27</v>
       </c>
       <c r="E395" t="n">
-        <v>44.07</v>
+        <v>44.09</v>
       </c>
       <c r="F395" t="n">
-        <v>158723</v>
+        <v>157249</v>
       </c>
     </row>
     <row r="396">
@@ -8338,13 +8338,13 @@
         <v>44.69</v>
       </c>
       <c r="D396" t="n">
-        <v>42.42</v>
+        <v>42.45</v>
       </c>
       <c r="E396" t="n">
-        <v>42.43</v>
+        <v>42.53</v>
       </c>
       <c r="F396" t="n">
-        <v>162787</v>
+        <v>160902</v>
       </c>
     </row>
     <row r="397">
@@ -8418,13 +8418,13 @@
         <v>41.23</v>
       </c>
       <c r="D400" t="n">
-        <v>39.96</v>
+        <v>40.02</v>
       </c>
       <c r="E400" t="n">
-        <v>39.97</v>
+        <v>40.07</v>
       </c>
       <c r="F400" t="n">
-        <v>149451</v>
+        <v>147551</v>
       </c>
     </row>
     <row r="401">
@@ -8441,10 +8441,10 @@
         <v>39.68</v>
       </c>
       <c r="E401" t="n">
-        <v>40.02</v>
+        <v>40.24</v>
       </c>
       <c r="F401" t="n">
-        <v>135456</v>
+        <v>133943</v>
       </c>
     </row>
     <row r="402">
@@ -8521,10 +8521,10 @@
         <v>41.89</v>
       </c>
       <c r="E405" t="n">
-        <v>43.58</v>
+        <v>43.67</v>
       </c>
       <c r="F405" t="n">
-        <v>142611</v>
+        <v>141089</v>
       </c>
     </row>
     <row r="406">
@@ -8541,10 +8541,10 @@
         <v>42.92</v>
       </c>
       <c r="E406" t="n">
-        <v>43.41</v>
+        <v>43.34</v>
       </c>
       <c r="F406" t="n">
-        <v>129546</v>
+        <v>127380</v>
       </c>
     </row>
     <row r="407">
@@ -8621,10 +8621,10 @@
         <v>41.68</v>
       </c>
       <c r="E410" t="n">
-        <v>42.16</v>
+        <v>42.27</v>
       </c>
       <c r="F410" t="n">
-        <v>133961</v>
+        <v>132502</v>
       </c>
     </row>
     <row r="411">
@@ -8641,10 +8641,10 @@
         <v>41.97</v>
       </c>
       <c r="E411" t="n">
-        <v>42.17</v>
+        <v>42.24</v>
       </c>
       <c r="F411" t="n">
-        <v>102107</v>
+        <v>100264</v>
       </c>
     </row>
     <row r="412">
@@ -8721,10 +8721,10 @@
         <v>39.98</v>
       </c>
       <c r="E415" t="n">
-        <v>40.75</v>
+        <v>40.93</v>
       </c>
       <c r="F415" t="n">
-        <v>157712</v>
+        <v>155461</v>
       </c>
     </row>
     <row r="416">
@@ -8741,10 +8741,10 @@
         <v>38.88</v>
       </c>
       <c r="E416" t="n">
-        <v>39.15</v>
+        <v>39.23</v>
       </c>
       <c r="F416" t="n">
-        <v>190634</v>
+        <v>188336</v>
       </c>
     </row>
     <row r="417">
@@ -8821,10 +8821,10 @@
         <v>42.02</v>
       </c>
       <c r="E420" t="n">
-        <v>43.52</v>
+        <v>43.54</v>
       </c>
       <c r="F420" t="n">
-        <v>112342</v>
+        <v>110782</v>
       </c>
     </row>
     <row r="421">
@@ -8841,10 +8841,10 @@
         <v>42.78</v>
       </c>
       <c r="E421" t="n">
-        <v>42.89</v>
+        <v>42.96</v>
       </c>
       <c r="F421" t="n">
-        <v>109695</v>
+        <v>108274</v>
       </c>
     </row>
     <row r="422">
@@ -8921,10 +8921,10 @@
         <v>41.79</v>
       </c>
       <c r="E425" t="n">
-        <v>43.26</v>
+        <v>43.38</v>
       </c>
       <c r="F425" t="n">
-        <v>147757</v>
+        <v>146298</v>
       </c>
     </row>
     <row r="426">
@@ -8941,10 +8941,10 @@
         <v>42.47</v>
       </c>
       <c r="E426" t="n">
-        <v>42.95</v>
+        <v>43.02</v>
       </c>
       <c r="F426" t="n">
-        <v>130839</v>
+        <v>129338</v>
       </c>
     </row>
     <row r="427">
@@ -9021,10 +9021,10 @@
         <v>41.72</v>
       </c>
       <c r="E430" t="n">
-        <v>42.59</v>
+        <v>42.71</v>
       </c>
       <c r="F430" t="n">
-        <v>110171</v>
+        <v>108471</v>
       </c>
     </row>
     <row r="431">
@@ -9041,10 +9041,10 @@
         <v>41.76</v>
       </c>
       <c r="E431" t="n">
-        <v>41.85</v>
+        <v>41.93</v>
       </c>
       <c r="F431" t="n">
-        <v>97195</v>
+        <v>95688</v>
       </c>
     </row>
     <row r="432">
@@ -9112,7 +9112,7 @@
         <v>44133</v>
       </c>
       <c r="B435" t="n">
-        <v>39.76</v>
+        <v>39.52</v>
       </c>
       <c r="C435" t="n">
         <v>39.97</v>
@@ -9124,7 +9124,7 @@
         <v>38.05</v>
       </c>
       <c r="F435" t="n">
-        <v>179602</v>
+        <v>183949</v>
       </c>
     </row>
     <row r="436">
@@ -9132,7 +9132,7 @@
         <v>44134</v>
       </c>
       <c r="B436" t="n">
-        <v>38.25</v>
+        <v>38.05</v>
       </c>
       <c r="C436" t="n">
         <v>38.72</v>
@@ -9144,7 +9144,7 @@
         <v>37.84</v>
       </c>
       <c r="F436" t="n">
-        <v>181739</v>
+        <v>184633</v>
       </c>
     </row>
     <row r="437">
@@ -9221,10 +9221,10 @@
         <v>40.42</v>
       </c>
       <c r="E440" t="n">
-        <v>40.68</v>
+        <v>40.82</v>
       </c>
       <c r="F440" t="n">
-        <v>157779</v>
+        <v>155706</v>
       </c>
     </row>
     <row r="441">
@@ -9241,10 +9241,10 @@
         <v>39.46</v>
       </c>
       <c r="E441" t="n">
-        <v>39.71</v>
+        <v>39.84</v>
       </c>
       <c r="F441" t="n">
-        <v>151438</v>
+        <v>150078</v>
       </c>
     </row>
     <row r="442">
@@ -9318,13 +9318,13 @@
         <v>44.59</v>
       </c>
       <c r="D445" t="n">
-        <v>43.35</v>
+        <v>43.42</v>
       </c>
       <c r="E445" t="n">
-        <v>43.38</v>
+        <v>43.49</v>
       </c>
       <c r="F445" t="n">
-        <v>146964</v>
+        <v>144322</v>
       </c>
     </row>
     <row r="446">
@@ -9338,13 +9338,13 @@
         <v>43.45</v>
       </c>
       <c r="D446" t="n">
-        <v>42.68</v>
+        <v>42.77</v>
       </c>
       <c r="E446" t="n">
-        <v>42.69</v>
+        <v>42.88</v>
       </c>
       <c r="F446" t="n">
-        <v>114191</v>
+        <v>112789</v>
       </c>
     </row>
     <row r="447">
@@ -9421,10 +9421,10 @@
         <v>43.87</v>
       </c>
       <c r="E450" t="n">
-        <v>44.21</v>
+        <v>44.44</v>
       </c>
       <c r="F450" t="n">
-        <v>112468</v>
+        <v>111013</v>
       </c>
     </row>
     <row r="451">
@@ -9441,10 +9441,10 @@
         <v>44.15</v>
       </c>
       <c r="E451" t="n">
-        <v>45.07</v>
+        <v>45.06</v>
       </c>
       <c r="F451" t="n">
-        <v>90427</v>
+        <v>88612</v>
       </c>
     </row>
     <row r="452">
@@ -9624,7 +9624,7 @@
         <v>48.65</v>
       </c>
       <c r="F460" t="n">
-        <v>122403</v>
+        <v>119976</v>
       </c>
     </row>
     <row r="461">
@@ -9641,10 +9641,10 @@
         <v>48.77</v>
       </c>
       <c r="E461" t="n">
-        <v>48.96</v>
+        <v>48.97</v>
       </c>
       <c r="F461" t="n">
-        <v>125701</v>
+        <v>124413</v>
       </c>
     </row>
     <row r="462">
@@ -9721,10 +9721,10 @@
         <v>48.79</v>
       </c>
       <c r="E465" t="n">
-        <v>50.25</v>
+        <v>50.26</v>
       </c>
       <c r="F465" t="n">
-        <v>132386</v>
+        <v>130125</v>
       </c>
     </row>
     <row r="466">
@@ -9741,10 +9741,10 @@
         <v>49.67</v>
       </c>
       <c r="E466" t="n">
-        <v>49.86</v>
+        <v>49.94</v>
       </c>
       <c r="F466" t="n">
-        <v>124721</v>
+        <v>123293</v>
       </c>
     </row>
     <row r="467">
@@ -9821,10 +9821,10 @@
         <v>51.06</v>
       </c>
       <c r="E470" t="n">
-        <v>51.46</v>
+        <v>51.55</v>
       </c>
       <c r="F470" t="n">
-        <v>102867</v>
+        <v>100894</v>
       </c>
     </row>
     <row r="471">
@@ -9841,10 +9841,10 @@
         <v>51.16</v>
       </c>
       <c r="E471" t="n">
-        <v>52.23</v>
+        <v>52.19</v>
       </c>
       <c r="F471" t="n">
-        <v>98705</v>
+        <v>96861</v>
       </c>
     </row>
     <row r="472">
@@ -10081,10 +10081,10 @@
         <v>53.88</v>
       </c>
       <c r="E483" t="n">
-        <v>54.34</v>
+        <v>54.45</v>
       </c>
       <c r="F483" t="n">
-        <v>142258</v>
+        <v>140683</v>
       </c>
     </row>
     <row r="484">
@@ -10095,16 +10095,16 @@
         <v>54.46</v>
       </c>
       <c r="C484" t="n">
-        <v>56.2</v>
+        <v>56.06</v>
       </c>
       <c r="D484" t="n">
         <v>54.3</v>
       </c>
       <c r="E484" t="n">
-        <v>56.11</v>
+        <v>56.02</v>
       </c>
       <c r="F484" t="n">
-        <v>155413</v>
+        <v>151805</v>
       </c>
     </row>
     <row r="485">
@@ -10181,10 +10181,10 @@
         <v>55.21</v>
       </c>
       <c r="E488" t="n">
-        <v>56.37</v>
+        <v>56.3</v>
       </c>
       <c r="F488" t="n">
-        <v>125098</v>
+        <v>123090</v>
       </c>
     </row>
     <row r="489">
@@ -10201,10 +10201,10 @@
         <v>54.63</v>
       </c>
       <c r="E489" t="n">
-        <v>54.75</v>
+        <v>54.94</v>
       </c>
       <c r="F489" t="n">
-        <v>135898</v>
+        <v>133988</v>
       </c>
     </row>
     <row r="490">
@@ -10281,10 +10281,10 @@
         <v>55.38</v>
       </c>
       <c r="E493" t="n">
-        <v>55.84</v>
+        <v>55.86</v>
       </c>
       <c r="F493" t="n">
-        <v>104851</v>
+        <v>103188</v>
       </c>
     </row>
     <row r="494">
@@ -10301,10 +10301,10 @@
         <v>54.38</v>
       </c>
       <c r="E494" t="n">
-        <v>54.88</v>
+        <v>55.08</v>
       </c>
       <c r="F494" t="n">
-        <v>135622</v>
+        <v>133367</v>
       </c>
     </row>
     <row r="495">
@@ -10378,13 +10378,13 @@
         <v>56.16</v>
       </c>
       <c r="D498" t="n">
-        <v>54.84</v>
+        <v>54.93</v>
       </c>
       <c r="E498" t="n">
-        <v>54.84</v>
+        <v>55</v>
       </c>
       <c r="F498" t="n">
-        <v>162289</v>
+        <v>160473</v>
       </c>
     </row>
     <row r="499">
@@ -10401,10 +10401,10 @@
         <v>54.84</v>
       </c>
       <c r="E499" t="n">
-        <v>54.93</v>
+        <v>55</v>
       </c>
       <c r="F499" t="n">
-        <v>163671</v>
+        <v>160923</v>
       </c>
     </row>
     <row r="500">
@@ -10481,10 +10481,10 @@
         <v>57.93</v>
       </c>
       <c r="E503" t="n">
-        <v>58.87</v>
+        <v>58.79</v>
       </c>
       <c r="F503" t="n">
-        <v>125851</v>
+        <v>123567</v>
       </c>
     </row>
     <row r="504">
@@ -10501,10 +10501,10 @@
         <v>58.87</v>
       </c>
       <c r="E504" t="n">
-        <v>59.41</v>
+        <v>59.31</v>
       </c>
       <c r="F504" t="n">
-        <v>120954</v>
+        <v>118436</v>
       </c>
     </row>
     <row r="505">
@@ -10578,13 +10578,13 @@
         <v>61.23</v>
       </c>
       <c r="D508" t="n">
-        <v>60.44</v>
+        <v>60.5</v>
       </c>
       <c r="E508" t="n">
-        <v>60.52</v>
+        <v>60.6</v>
       </c>
       <c r="F508" t="n">
-        <v>107974</v>
+        <v>104511</v>
       </c>
     </row>
     <row r="509">
@@ -10604,7 +10604,7 @@
         <v>62.22</v>
       </c>
       <c r="F509" t="n">
-        <v>126905</v>
+        <v>123306</v>
       </c>
     </row>
     <row r="510">
@@ -10681,10 +10681,10 @@
         <v>62.54</v>
       </c>
       <c r="E513" t="n">
-        <v>62.88</v>
+        <v>62.75</v>
       </c>
       <c r="F513" t="n">
-        <v>173632</v>
+        <v>170306</v>
       </c>
     </row>
     <row r="514">
@@ -10701,10 +10701,10 @@
         <v>61.42</v>
       </c>
       <c r="E514" t="n">
-        <v>61.97</v>
+        <v>61.95</v>
       </c>
       <c r="F514" t="n">
-        <v>184306</v>
+        <v>181146</v>
       </c>
     </row>
     <row r="515">
@@ -10781,10 +10781,10 @@
         <v>65.55</v>
       </c>
       <c r="E518" t="n">
-        <v>65.97</v>
+        <v>65.86</v>
       </c>
       <c r="F518" t="n">
-        <v>215533</v>
+        <v>210726</v>
       </c>
     </row>
     <row r="519">
@@ -10801,10 +10801,10 @@
         <v>64.13</v>
       </c>
       <c r="E519" t="n">
-        <v>64.27</v>
+        <v>64.25</v>
       </c>
       <c r="F519" t="n">
-        <v>239274</v>
+        <v>234931</v>
       </c>
     </row>
     <row r="520">
@@ -10881,10 +10881,10 @@
         <v>63.17</v>
       </c>
       <c r="E523" t="n">
-        <v>66.73999999999999</v>
+        <v>66.94</v>
       </c>
       <c r="F523" t="n">
-        <v>230530</v>
+        <v>225843</v>
       </c>
     </row>
     <row r="524">
@@ -10895,16 +10895,16 @@
         <v>66.86</v>
       </c>
       <c r="C524" t="n">
-        <v>69.41</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="D524" t="n">
         <v>66.43000000000001</v>
       </c>
       <c r="E524" t="n">
-        <v>69.25</v>
+        <v>69.28</v>
       </c>
       <c r="F524" t="n">
-        <v>253026</v>
+        <v>249828</v>
       </c>
     </row>
     <row r="525">
@@ -10981,10 +10981,10 @@
         <v>67.68000000000001</v>
       </c>
       <c r="E528" t="n">
-        <v>69.17</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="F528" t="n">
-        <v>163581</v>
+        <v>160838</v>
       </c>
     </row>
     <row r="529">
@@ -11001,10 +11001,10 @@
         <v>68.66</v>
       </c>
       <c r="E529" t="n">
-        <v>68.81</v>
+        <v>68.88</v>
       </c>
       <c r="F529" t="n">
-        <v>151042</v>
+        <v>148823</v>
       </c>
     </row>
     <row r="530">
@@ -11072,7 +11072,7 @@
         <v>44273</v>
       </c>
       <c r="B533" t="n">
-        <v>67.47</v>
+        <v>67.48</v>
       </c>
       <c r="C533" t="n">
         <v>67.83</v>
@@ -11084,7 +11084,7 @@
         <v>62.5</v>
       </c>
       <c r="F533" t="n">
-        <v>209835</v>
+        <v>212082</v>
       </c>
     </row>
     <row r="534">
@@ -11092,7 +11092,7 @@
         <v>44274</v>
       </c>
       <c r="B534" t="n">
-        <v>63.02</v>
+        <v>62.78</v>
       </c>
       <c r="C534" t="n">
         <v>64.73</v>
@@ -11104,7 +11104,7 @@
         <v>64.31999999999999</v>
       </c>
       <c r="F534" t="n">
-        <v>223529</v>
+        <v>228148</v>
       </c>
     </row>
     <row r="535">
@@ -11172,10 +11172,10 @@
         <v>44280</v>
       </c>
       <c r="B538" t="n">
-        <v>63.89</v>
+        <v>63.95</v>
       </c>
       <c r="C538" t="n">
-        <v>63.9</v>
+        <v>64.01000000000001</v>
       </c>
       <c r="D538" t="n">
         <v>60.82</v>
@@ -11184,7 +11184,7 @@
         <v>61.47</v>
       </c>
       <c r="F538" t="n">
-        <v>203253</v>
+        <v>206155</v>
       </c>
     </row>
     <row r="539">
@@ -11192,19 +11192,19 @@
         <v>44281</v>
       </c>
       <c r="B539" t="n">
-        <v>62.45</v>
+        <v>61.47</v>
       </c>
       <c r="C539" t="n">
         <v>64.73</v>
       </c>
       <c r="D539" t="n">
-        <v>62.07</v>
+        <v>61.47</v>
       </c>
       <c r="E539" t="n">
         <v>64.19</v>
       </c>
       <c r="F539" t="n">
-        <v>167422</v>
+        <v>171041</v>
       </c>
     </row>
     <row r="540">
@@ -11284,7 +11284,7 @@
         <v>64.51000000000001</v>
       </c>
       <c r="F543" t="n">
-        <v>201289</v>
+        <v>197783</v>
       </c>
     </row>
     <row r="544">
@@ -11361,10 +11361,10 @@
         <v>62.18</v>
       </c>
       <c r="E547" t="n">
-        <v>63.04</v>
+        <v>63.07</v>
       </c>
       <c r="F547" t="n">
-        <v>149186</v>
+        <v>146277</v>
       </c>
     </row>
     <row r="548">
@@ -11381,10 +11381,10 @@
         <v>62.33</v>
       </c>
       <c r="E548" t="n">
-        <v>62.76</v>
+        <v>62.81</v>
       </c>
       <c r="F548" t="n">
-        <v>121247</v>
+        <v>119219</v>
       </c>
     </row>
     <row r="549">
@@ -11461,10 +11461,10 @@
         <v>65.65000000000001</v>
       </c>
       <c r="E552" t="n">
-        <v>66.45</v>
+        <v>66.5</v>
       </c>
       <c r="F552" t="n">
-        <v>135521</v>
+        <v>133306</v>
       </c>
     </row>
     <row r="553">
@@ -11481,10 +11481,10 @@
         <v>66.11</v>
       </c>
       <c r="E553" t="n">
-        <v>66.31999999999999</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="F553" t="n">
-        <v>122938</v>
+        <v>120895</v>
       </c>
     </row>
     <row r="554">
@@ -11564,7 +11564,7 @@
         <v>64.95</v>
       </c>
       <c r="F557" t="n">
-        <v>143350</v>
+        <v>140975</v>
       </c>
     </row>
     <row r="558">
@@ -11581,10 +11581,10 @@
         <v>64.52</v>
       </c>
       <c r="E558" t="n">
-        <v>65.31999999999999</v>
+        <v>65.45</v>
       </c>
       <c r="F558" t="n">
-        <v>126302</v>
+        <v>124432</v>
       </c>
     </row>
     <row r="559">
@@ -11661,10 +11661,10 @@
         <v>66.56</v>
       </c>
       <c r="E562" t="n">
-        <v>67.84999999999999</v>
+        <v>67.86</v>
       </c>
       <c r="F562" t="n">
-        <v>160482</v>
+        <v>157092</v>
       </c>
     </row>
     <row r="563">
@@ -11681,10 +11681,10 @@
         <v>66.17</v>
       </c>
       <c r="E563" t="n">
-        <v>66.53</v>
+        <v>66.56</v>
       </c>
       <c r="F563" t="n">
-        <v>148372</v>
+        <v>145779</v>
       </c>
     </row>
     <row r="564">
@@ -11761,10 +11761,10 @@
         <v>67.77</v>
       </c>
       <c r="E567" t="n">
-        <v>68.03</v>
+        <v>68.05</v>
       </c>
       <c r="F567" t="n">
-        <v>155507</v>
+        <v>153533</v>
       </c>
     </row>
     <row r="568">
@@ -11784,7 +11784,7 @@
         <v>68.03</v>
       </c>
       <c r="F568" t="n">
-        <v>139157</v>
+        <v>136012</v>
       </c>
     </row>
     <row r="569">
@@ -11861,10 +11861,10 @@
         <v>66.34</v>
       </c>
       <c r="E572" t="n">
-        <v>66.81999999999999</v>
+        <v>66.83</v>
       </c>
       <c r="F572" t="n">
-        <v>182316</v>
+        <v>180093</v>
       </c>
     </row>
     <row r="573">
@@ -11875,16 +11875,16 @@
         <v>66.81</v>
       </c>
       <c r="C573" t="n">
-        <v>68.63</v>
+        <v>68.52</v>
       </c>
       <c r="D573" t="n">
         <v>66.36</v>
       </c>
       <c r="E573" t="n">
-        <v>68.52</v>
+        <v>68.45</v>
       </c>
       <c r="F573" t="n">
-        <v>142226</v>
+        <v>139950</v>
       </c>
     </row>
     <row r="574">
@@ -11958,13 +11958,13 @@
         <v>67.02</v>
       </c>
       <c r="D577" t="n">
-        <v>64.70999999999999</v>
+        <v>64.73</v>
       </c>
       <c r="E577" t="n">
-        <v>64.73999999999999</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="F577" t="n">
-        <v>168733</v>
+        <v>164782</v>
       </c>
     </row>
     <row r="578">
@@ -11981,10 +11981,10 @@
         <v>64.48</v>
       </c>
       <c r="E578" t="n">
-        <v>66.51000000000001</v>
+        <v>66.58</v>
       </c>
       <c r="F578" t="n">
-        <v>156317</v>
+        <v>153693</v>
       </c>
     </row>
     <row r="579">
@@ -12055,16 +12055,16 @@
         <v>68.58</v>
       </c>
       <c r="C582" t="n">
-        <v>69.2</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="D582" t="n">
         <v>67.89</v>
       </c>
       <c r="E582" t="n">
-        <v>69.12</v>
+        <v>69.05</v>
       </c>
       <c r="F582" t="n">
-        <v>122427</v>
+        <v>119490</v>
       </c>
     </row>
     <row r="583">
@@ -12081,10 +12081,10 @@
         <v>68.48999999999999</v>
       </c>
       <c r="E583" t="n">
-        <v>68.88</v>
+        <v>68.89</v>
       </c>
       <c r="F583" t="n">
-        <v>121324</v>
+        <v>119218</v>
       </c>
     </row>
     <row r="584">
@@ -12161,10 +12161,10 @@
         <v>70.5</v>
       </c>
       <c r="E587" t="n">
-        <v>71.22</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="F587" t="n">
-        <v>128649</v>
+        <v>126247</v>
       </c>
     </row>
     <row r="588">
@@ -12181,10 +12181,10 @@
         <v>70.58</v>
       </c>
       <c r="E588" t="n">
-        <v>71.43000000000001</v>
+        <v>71.47</v>
       </c>
       <c r="F588" t="n">
-        <v>117041</v>
+        <v>113793</v>
       </c>
     </row>
     <row r="589">
@@ -12261,10 +12261,10 @@
         <v>70.66</v>
       </c>
       <c r="E592" t="n">
-        <v>71.95</v>
+        <v>72.09</v>
       </c>
       <c r="F592" t="n">
-        <v>148450</v>
+        <v>146487</v>
       </c>
     </row>
     <row r="593">
@@ -12284,7 +12284,7 @@
         <v>72.23999999999999</v>
       </c>
       <c r="F593" t="n">
-        <v>142367</v>
+        <v>140128</v>
       </c>
     </row>
     <row r="594">
@@ -12361,10 +12361,10 @@
         <v>71.41</v>
       </c>
       <c r="E597" t="n">
-        <v>72.44</v>
+        <v>72.45</v>
       </c>
       <c r="F597" t="n">
-        <v>178094</v>
+        <v>175025</v>
       </c>
     </row>
     <row r="598">
@@ -12381,10 +12381,10 @@
         <v>71.55</v>
       </c>
       <c r="E598" t="n">
-        <v>72.5</v>
+        <v>72.76000000000001</v>
       </c>
       <c r="F598" t="n">
-        <v>151345</v>
+        <v>147859</v>
       </c>
     </row>
     <row r="599">
@@ -12461,10 +12461,10 @@
         <v>73.83</v>
       </c>
       <c r="E602" t="n">
-        <v>74.81</v>
+        <v>74.79000000000001</v>
       </c>
       <c r="F602" t="n">
-        <v>85692</v>
+        <v>84577</v>
       </c>
     </row>
     <row r="603">
@@ -12481,10 +12481,10 @@
         <v>74.14</v>
       </c>
       <c r="E603" t="n">
-        <v>75.28</v>
+        <v>75.27</v>
       </c>
       <c r="F603" t="n">
-        <v>79112</v>
+        <v>77990</v>
       </c>
     </row>
     <row r="604">
@@ -12561,10 +12561,10 @@
         <v>74.36</v>
       </c>
       <c r="E607" t="n">
-        <v>75.34</v>
+        <v>75.33</v>
       </c>
       <c r="F607" t="n">
-        <v>135699</v>
+        <v>134296</v>
       </c>
     </row>
     <row r="608">
@@ -12581,10 +12581,10 @@
         <v>75</v>
       </c>
       <c r="E608" t="n">
-        <v>75.81999999999999</v>
+        <v>76.02</v>
       </c>
       <c r="F608" t="n">
-        <v>104256</v>
+        <v>102316</v>
       </c>
     </row>
     <row r="609">
@@ -12655,16 +12655,16 @@
         <v>72.97</v>
       </c>
       <c r="C612" t="n">
-        <v>74.02</v>
+        <v>73.97</v>
       </c>
       <c r="D612" t="n">
         <v>71.73999999999999</v>
       </c>
       <c r="E612" t="n">
-        <v>73.95999999999999</v>
+        <v>73.92</v>
       </c>
       <c r="F612" t="n">
-        <v>138030</v>
+        <v>136419</v>
       </c>
     </row>
     <row r="613">
@@ -12681,10 +12681,10 @@
         <v>73.38</v>
       </c>
       <c r="E613" t="n">
-        <v>75.14</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="F613" t="n">
-        <v>96988</v>
+        <v>95892</v>
       </c>
     </row>
     <row r="614">
@@ -12761,10 +12761,10 @@
         <v>72.70999999999999</v>
       </c>
       <c r="E617" t="n">
-        <v>72.72</v>
+        <v>72.79000000000001</v>
       </c>
       <c r="F617" t="n">
-        <v>134216</v>
+        <v>132350</v>
       </c>
     </row>
     <row r="618">
@@ -12781,10 +12781,10 @@
         <v>71.88</v>
       </c>
       <c r="E618" t="n">
-        <v>72.64</v>
+        <v>72.81</v>
       </c>
       <c r="F618" t="n">
-        <v>110158</v>
+        <v>108307</v>
       </c>
     </row>
     <row r="619">
@@ -12864,7 +12864,7 @@
         <v>73.01000000000001</v>
       </c>
       <c r="F622" t="n">
-        <v>115159</v>
+        <v>113951</v>
       </c>
     </row>
     <row r="623">
@@ -12875,16 +12875,16 @@
         <v>72.98</v>
       </c>
       <c r="C623" t="n">
-        <v>73.56999999999999</v>
+        <v>73.52</v>
       </c>
       <c r="D623" t="n">
         <v>72.70999999999999</v>
       </c>
       <c r="E623" t="n">
-        <v>73.5</v>
+        <v>73.44</v>
       </c>
       <c r="F623" t="n">
-        <v>84579</v>
+        <v>83411</v>
       </c>
     </row>
     <row r="624">
@@ -12961,10 +12961,10 @@
         <v>73.59999999999999</v>
       </c>
       <c r="E627" t="n">
-        <v>74.75</v>
+        <v>74.97</v>
       </c>
       <c r="F627" t="n">
-        <v>81467</v>
+        <v>79720</v>
       </c>
     </row>
     <row r="628">
@@ -12981,10 +12981,10 @@
         <v>74.26000000000001</v>
       </c>
       <c r="E628" t="n">
-        <v>74.95999999999999</v>
+        <v>74.98999999999999</v>
       </c>
       <c r="F628" t="n">
-        <v>84253</v>
+        <v>83101</v>
       </c>
     </row>
     <row r="629">
@@ -13061,10 +13061,10 @@
         <v>69.56</v>
       </c>
       <c r="E632" t="n">
-        <v>71</v>
+        <v>71.16</v>
       </c>
       <c r="F632" t="n">
-        <v>108267</v>
+        <v>107034</v>
       </c>
     </row>
     <row r="633">
@@ -13078,13 +13078,13 @@
         <v>72.22</v>
       </c>
       <c r="D633" t="n">
-        <v>70.06999999999999</v>
+        <v>70.12</v>
       </c>
       <c r="E633" t="n">
-        <v>70.08</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="F633" t="n">
-        <v>113105</v>
+        <v>111453</v>
       </c>
     </row>
     <row r="634">
@@ -13161,10 +13161,10 @@
         <v>70.41</v>
       </c>
       <c r="E637" t="n">
-        <v>70.86</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="F637" t="n">
-        <v>96203</v>
+        <v>95219</v>
       </c>
     </row>
     <row r="638">
@@ -13181,10 +13181,10 @@
         <v>69.73999999999999</v>
       </c>
       <c r="E638" t="n">
-        <v>69.90000000000001</v>
+        <v>69.92</v>
       </c>
       <c r="F638" t="n">
-        <v>95696</v>
+        <v>93960</v>
       </c>
     </row>
     <row r="639">
@@ -13261,10 +13261,10 @@
         <v>65.2</v>
       </c>
       <c r="E642" t="n">
-        <v>66.23</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="F642" t="n">
-        <v>187712</v>
+        <v>185678</v>
       </c>
     </row>
     <row r="643">
@@ -13278,13 +13278,13 @@
         <v>66.54000000000001</v>
       </c>
       <c r="D643" t="n">
-        <v>64.53</v>
+        <v>64.61</v>
       </c>
       <c r="E643" t="n">
-        <v>64.54000000000001</v>
+        <v>64.62</v>
       </c>
       <c r="F643" t="n">
-        <v>138989</v>
+        <v>137258</v>
       </c>
     </row>
     <row r="644">
@@ -13361,10 +13361,10 @@
         <v>69.73999999999999</v>
       </c>
       <c r="E647" t="n">
-        <v>70.45999999999999</v>
+        <v>70.56</v>
       </c>
       <c r="F647" t="n">
-        <v>115965</v>
+        <v>113839</v>
       </c>
     </row>
     <row r="648">
@@ -13381,10 +13381,10 @@
         <v>70.16</v>
       </c>
       <c r="E648" t="n">
-        <v>71.5</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="F648" t="n">
-        <v>100455</v>
+        <v>99158</v>
       </c>
     </row>
     <row r="649">
@@ -13461,10 +13461,10 @@
         <v>70.75</v>
       </c>
       <c r="E652" t="n">
-        <v>72.61</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="F652" t="n">
-        <v>105073</v>
+        <v>103772</v>
       </c>
     </row>
     <row r="653">
@@ -13481,10 +13481,10 @@
         <v>72.20999999999999</v>
       </c>
       <c r="E653" t="n">
-        <v>72.20999999999999</v>
+        <v>72.36</v>
       </c>
       <c r="F653" t="n">
-        <v>111688</v>
+        <v>110684</v>
       </c>
     </row>
     <row r="654">
@@ -13561,10 +13561,10 @@
         <v>70.54000000000001</v>
       </c>
       <c r="E657" t="n">
-        <v>70.84</v>
+        <v>70.95</v>
       </c>
       <c r="F657" t="n">
-        <v>138553</v>
+        <v>136836</v>
       </c>
     </row>
     <row r="658">
@@ -13581,10 +13581,10 @@
         <v>70.59</v>
       </c>
       <c r="E658" t="n">
-        <v>72.51000000000001</v>
+        <v>72.44</v>
       </c>
       <c r="F658" t="n">
-        <v>107925</v>
+        <v>106315</v>
       </c>
     </row>
     <row r="659">
@@ -13661,10 +13661,10 @@
         <v>74.02</v>
       </c>
       <c r="E662" t="n">
-        <v>75.09</v>
+        <v>75.17</v>
       </c>
       <c r="F662" t="n">
-        <v>136265</v>
+        <v>134873</v>
       </c>
     </row>
     <row r="663">
@@ -13681,10 +13681,10 @@
         <v>74.06999999999999</v>
       </c>
       <c r="E663" t="n">
-        <v>74.67</v>
+        <v>74.79000000000001</v>
       </c>
       <c r="F663" t="n">
-        <v>131243</v>
+        <v>129577</v>
       </c>
     </row>
     <row r="664">
@@ -13764,7 +13764,7 @@
         <v>76.45</v>
       </c>
       <c r="F667" t="n">
-        <v>104066</v>
+        <v>102612</v>
       </c>
     </row>
     <row r="668">
@@ -13781,10 +13781,10 @@
         <v>76.09</v>
       </c>
       <c r="E668" t="n">
-        <v>77.13</v>
+        <v>77.15000000000001</v>
       </c>
       <c r="F668" t="n">
-        <v>94529</v>
+        <v>93448</v>
       </c>
     </row>
     <row r="669">
@@ -13861,10 +13861,10 @@
         <v>76.37</v>
       </c>
       <c r="E672" t="n">
-        <v>78.23999999999999</v>
+        <v>78.13</v>
       </c>
       <c r="F672" t="n">
-        <v>181989</v>
+        <v>180155</v>
       </c>
     </row>
     <row r="673">
@@ -13881,10 +13881,10 @@
         <v>77.38</v>
       </c>
       <c r="E673" t="n">
-        <v>78.93000000000001</v>
+        <v>78.98999999999999</v>
       </c>
       <c r="F673" t="n">
-        <v>151482</v>
+        <v>149729</v>
       </c>
     </row>
     <row r="674">
@@ -13961,10 +13961,10 @@
         <v>78.78</v>
       </c>
       <c r="E677" t="n">
-        <v>82.08</v>
+        <v>82.16</v>
       </c>
       <c r="F677" t="n">
-        <v>153620</v>
+        <v>151677</v>
       </c>
     </row>
     <row r="678">
@@ -13981,10 +13981,10 @@
         <v>81.63</v>
       </c>
       <c r="E678" t="n">
-        <v>82.22</v>
+        <v>82.17</v>
       </c>
       <c r="F678" t="n">
-        <v>149526</v>
+        <v>147722</v>
       </c>
     </row>
     <row r="679">
@@ -14061,10 +14061,10 @@
         <v>82.76000000000001</v>
       </c>
       <c r="E682" t="n">
-        <v>83.67</v>
+        <v>83.69</v>
       </c>
       <c r="F682" t="n">
-        <v>122153</v>
+        <v>120650</v>
       </c>
     </row>
     <row r="683">
@@ -14081,10 +14081,10 @@
         <v>83.68000000000001</v>
       </c>
       <c r="E683" t="n">
-        <v>84.33</v>
+        <v>84.23</v>
       </c>
       <c r="F683" t="n">
-        <v>116437</v>
+        <v>114060</v>
       </c>
     </row>
     <row r="684">
@@ -14161,10 +14161,10 @@
         <v>82.73</v>
       </c>
       <c r="E687" t="n">
-        <v>84.09</v>
+        <v>84.15000000000001</v>
       </c>
       <c r="F687" t="n">
-        <v>122966</v>
+        <v>121250</v>
       </c>
     </row>
     <row r="688">
@@ -14175,16 +14175,16 @@
         <v>83.81999999999999</v>
       </c>
       <c r="C688" t="n">
-        <v>85.08</v>
+        <v>84.97</v>
       </c>
       <c r="D688" t="n">
         <v>83.18000000000001</v>
       </c>
       <c r="E688" t="n">
-        <v>84.83</v>
+        <v>84.97</v>
       </c>
       <c r="F688" t="n">
-        <v>113449</v>
+        <v>111475</v>
       </c>
     </row>
     <row r="689">
@@ -14261,10 +14261,10 @@
         <v>81.48</v>
       </c>
       <c r="E692" t="n">
-        <v>83.78</v>
+        <v>83.83</v>
       </c>
       <c r="F692" t="n">
-        <v>167007</v>
+        <v>164605</v>
       </c>
     </row>
     <row r="693">
@@ -14281,10 +14281,10 @@
         <v>82.39</v>
       </c>
       <c r="E693" t="n">
-        <v>83.41</v>
+        <v>83.55</v>
       </c>
       <c r="F693" t="n">
-        <v>133535</v>
+        <v>132228</v>
       </c>
     </row>
     <row r="694">
@@ -14352,7 +14352,7 @@
         <v>44504</v>
       </c>
       <c r="B697" t="n">
-        <v>80.83</v>
+        <v>81.12</v>
       </c>
       <c r="C697" t="n">
         <v>84.08</v>
@@ -14364,7 +14364,7 @@
         <v>80.54000000000001</v>
       </c>
       <c r="F697" t="n">
-        <v>168783</v>
+        <v>171378</v>
       </c>
     </row>
     <row r="698">
@@ -14372,7 +14372,7 @@
         <v>44505</v>
       </c>
       <c r="B698" t="n">
-        <v>81.04000000000001</v>
+        <v>80.95</v>
       </c>
       <c r="C698" t="n">
         <v>82.72</v>
@@ -14384,7 +14384,7 @@
         <v>81.93000000000001</v>
       </c>
       <c r="F698" t="n">
-        <v>163172</v>
+        <v>166390</v>
       </c>
     </row>
     <row r="699">
@@ -14461,10 +14461,10 @@
         <v>81.06</v>
       </c>
       <c r="E702" t="n">
-        <v>81.92</v>
+        <v>81.91</v>
       </c>
       <c r="F702" t="n">
-        <v>161511</v>
+        <v>159955</v>
       </c>
     </row>
     <row r="703">
@@ -14481,10 +14481,10 @@
         <v>80.63</v>
       </c>
       <c r="E703" t="n">
-        <v>81.29000000000001</v>
+        <v>81.41</v>
       </c>
       <c r="F703" t="n">
-        <v>134507</v>
+        <v>133196</v>
       </c>
     </row>
     <row r="704">
@@ -14561,10 +14561,10 @@
         <v>78.55</v>
       </c>
       <c r="E707" t="n">
-        <v>80.34999999999999</v>
+        <v>80.42</v>
       </c>
       <c r="F707" t="n">
-        <v>132952</v>
+        <v>131123</v>
       </c>
     </row>
     <row r="708">
@@ -14581,10 +14581,10 @@
         <v>77.41</v>
       </c>
       <c r="E708" t="n">
-        <v>77.77</v>
+        <v>77.76000000000001</v>
       </c>
       <c r="F708" t="n">
-        <v>177513</v>
+        <v>175625</v>
       </c>
     </row>
     <row r="709">
@@ -14761,10 +14761,10 @@
         <v>65.67</v>
       </c>
       <c r="E717" t="n">
-        <v>70.36</v>
+        <v>69.94</v>
       </c>
       <c r="F717" t="n">
-        <v>240359</v>
+        <v>237353</v>
       </c>
     </row>
     <row r="718">
@@ -14781,10 +14781,10 @@
         <v>69.09999999999999</v>
       </c>
       <c r="E718" t="n">
-        <v>69.70999999999999</v>
+        <v>69.73</v>
       </c>
       <c r="F718" t="n">
-        <v>208893</v>
+        <v>205214</v>
       </c>
     </row>
     <row r="719">
@@ -14858,13 +14858,13 @@
         <v>76.55</v>
       </c>
       <c r="D722" t="n">
-        <v>73.70999999999999</v>
+        <v>73.78</v>
       </c>
       <c r="E722" t="n">
-        <v>73.84999999999999</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="F722" t="n">
-        <v>142264</v>
+        <v>140659</v>
       </c>
     </row>
     <row r="723">
@@ -14881,10 +14881,10 @@
         <v>73.67</v>
       </c>
       <c r="E723" t="n">
-        <v>75.16</v>
+        <v>75.23</v>
       </c>
       <c r="F723" t="n">
-        <v>153301</v>
+        <v>151698</v>
       </c>
     </row>
     <row r="724">
@@ -14961,10 +14961,10 @@
         <v>73.88</v>
       </c>
       <c r="E727" t="n">
-        <v>74.48999999999999</v>
+        <v>74.63</v>
       </c>
       <c r="F727" t="n">
-        <v>142563</v>
+        <v>140474</v>
       </c>
     </row>
     <row r="728">
@@ -14981,10 +14981,10 @@
         <v>72.63</v>
       </c>
       <c r="E728" t="n">
-        <v>72.88</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="F728" t="n">
-        <v>154875</v>
+        <v>152160</v>
       </c>
     </row>
     <row r="729">
@@ -15061,10 +15061,10 @@
         <v>74.72</v>
       </c>
       <c r="E732" t="n">
-        <v>76.52</v>
+        <v>76.63</v>
       </c>
       <c r="F732" t="n">
-        <v>102802</v>
+        <v>100583</v>
       </c>
     </row>
     <row r="733">
@@ -15161,10 +15161,10 @@
         <v>78.33</v>
       </c>
       <c r="E737" t="n">
-        <v>78.86</v>
+        <v>78.97</v>
       </c>
       <c r="F737" t="n">
-        <v>105405</v>
+        <v>103669</v>
       </c>
     </row>
     <row r="738">
@@ -15261,10 +15261,10 @@
         <v>79.36</v>
       </c>
       <c r="E742" t="n">
-        <v>81.70999999999999</v>
+        <v>81.65000000000001</v>
       </c>
       <c r="F742" t="n">
-        <v>187943</v>
+        <v>185800</v>
       </c>
     </row>
     <row r="743">
@@ -15281,10 +15281,10 @@
         <v>81.12</v>
       </c>
       <c r="E743" t="n">
-        <v>81.48</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="F743" t="n">
-        <v>160491</v>
+        <v>158852</v>
       </c>
     </row>
     <row r="744">
@@ -15361,10 +15361,10 @@
         <v>83.34999999999999</v>
       </c>
       <c r="E747" t="n">
-        <v>83.61</v>
+        <v>83.45</v>
       </c>
       <c r="F747" t="n">
-        <v>147527</v>
+        <v>145171</v>
       </c>
     </row>
     <row r="748">
@@ -15375,16 +15375,16 @@
         <v>83.68000000000001</v>
       </c>
       <c r="C748" t="n">
-        <v>85.98999999999999</v>
+        <v>85.97</v>
       </c>
       <c r="D748" t="n">
         <v>83.53</v>
       </c>
       <c r="E748" t="n">
-        <v>85.77</v>
+        <v>85.91</v>
       </c>
       <c r="F748" t="n">
-        <v>173518</v>
+        <v>171152</v>
       </c>
     </row>
     <row r="749">
@@ -15458,13 +15458,13 @@
         <v>88.8</v>
       </c>
       <c r="D752" t="n">
-        <v>86.38</v>
+        <v>86.56999999999999</v>
       </c>
       <c r="E752" t="n">
-        <v>86.58</v>
+        <v>86.7</v>
       </c>
       <c r="F752" t="n">
-        <v>169439</v>
+        <v>162890</v>
       </c>
     </row>
     <row r="753">
@@ -15481,10 +15481,10 @@
         <v>85.02</v>
       </c>
       <c r="E753" t="n">
-        <v>86.92</v>
+        <v>86.98</v>
       </c>
       <c r="F753" t="n">
-        <v>225683</v>
+        <v>223066</v>
       </c>
     </row>
     <row r="754">
@@ -15561,10 +15561,10 @@
         <v>87.7</v>
       </c>
       <c r="E757" t="n">
-        <v>88.63</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="F757" t="n">
-        <v>275711</v>
+        <v>270152</v>
       </c>
     </row>
     <row r="758">
@@ -15581,10 +15581,10 @@
         <v>88</v>
       </c>
       <c r="E758" t="n">
-        <v>88.81999999999999</v>
+        <v>88.73</v>
       </c>
       <c r="F758" t="n">
-        <v>278896</v>
+        <v>275262</v>
       </c>
     </row>
     <row r="759">
@@ -15655,16 +15655,16 @@
         <v>88.63</v>
       </c>
       <c r="C762" t="n">
-        <v>90.84999999999999</v>
+        <v>90.73999999999999</v>
       </c>
       <c r="D762" t="n">
         <v>87.59999999999999</v>
       </c>
       <c r="E762" t="n">
-        <v>90.51000000000001</v>
+        <v>90.45999999999999</v>
       </c>
       <c r="F762" t="n">
-        <v>168353</v>
+        <v>163057</v>
       </c>
     </row>
     <row r="763">
@@ -15681,10 +15681,10 @@
         <v>90.67</v>
       </c>
       <c r="E763" t="n">
-        <v>92.14</v>
+        <v>92.54000000000001</v>
       </c>
       <c r="F763" t="n">
-        <v>180147</v>
+        <v>177219</v>
       </c>
     </row>
     <row r="764">
@@ -15761,10 +15761,10 @@
         <v>90.09999999999999</v>
       </c>
       <c r="E767" t="n">
-        <v>90.54000000000001</v>
+        <v>90.66</v>
       </c>
       <c r="F767" t="n">
-        <v>186180</v>
+        <v>183590</v>
       </c>
     </row>
     <row r="768">
@@ -15781,10 +15781,10 @@
         <v>89.66</v>
       </c>
       <c r="E768" t="n">
-        <v>93.8</v>
+        <v>93.81</v>
       </c>
       <c r="F768" t="n">
-        <v>194729</v>
+        <v>189880</v>
       </c>
     </row>
     <row r="769">
@@ -15861,10 +15861,10 @@
         <v>90.34999999999999</v>
       </c>
       <c r="E772" t="n">
-        <v>91.16</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="F772" t="n">
-        <v>212213</v>
+        <v>209775</v>
       </c>
     </row>
     <row r="773">
@@ -15875,7 +15875,7 @@
         <v>90.76000000000001</v>
       </c>
       <c r="C773" t="n">
-        <v>92.28</v>
+        <v>92.15000000000001</v>
       </c>
       <c r="D773" t="n">
         <v>88.64</v>
@@ -15884,7 +15884,7 @@
         <v>91.81</v>
       </c>
       <c r="F773" t="n">
-        <v>194995</v>
+        <v>190175</v>
       </c>
     </row>
     <row r="774">
@@ -15961,10 +15961,10 @@
         <v>93.94</v>
       </c>
       <c r="E777" t="n">
-        <v>95.41</v>
+        <v>95.61</v>
       </c>
       <c r="F777" t="n">
-        <v>313423</v>
+        <v>309076</v>
       </c>
     </row>
     <row r="778">
@@ -15981,10 +15981,10 @@
         <v>92.55</v>
       </c>
       <c r="E778" t="n">
-        <v>94.23</v>
+        <v>94.69</v>
       </c>
       <c r="F778" t="n">
-        <v>237786</v>
+        <v>233541</v>
       </c>
     </row>
     <row r="779">
@@ -16061,10 +16061,10 @@
         <v>108.17</v>
       </c>
       <c r="E782" t="n">
-        <v>109.27</v>
+        <v>109.72</v>
       </c>
       <c r="F782" t="n">
-        <v>233799</v>
+        <v>231064</v>
       </c>
     </row>
     <row r="783">
@@ -16081,10 +16081,10 @@
         <v>108.47</v>
       </c>
       <c r="E783" t="n">
-        <v>116.7</v>
+        <v>117.14</v>
       </c>
       <c r="F783" t="n">
-        <v>210974</v>
+        <v>204618</v>
       </c>
     </row>
     <row r="784">
@@ -16161,10 +16161,10 @@
         <v>107.05</v>
       </c>
       <c r="E787" t="n">
-        <v>107.11</v>
+        <v>107.97</v>
       </c>
       <c r="F787" t="n">
-        <v>173653</v>
+        <v>170481</v>
       </c>
     </row>
     <row r="788">
@@ -16181,10 +16181,10 @@
         <v>104.96</v>
       </c>
       <c r="E788" t="n">
-        <v>110.14</v>
+        <v>110.51</v>
       </c>
       <c r="F788" t="n">
-        <v>157669</v>
+        <v>154891</v>
       </c>
     </row>
     <row r="789">
@@ -16252,19 +16252,19 @@
         <v>44637</v>
       </c>
       <c r="B792" t="n">
-        <v>96.70999999999999</v>
+        <v>96.98</v>
       </c>
       <c r="C792" t="n">
         <v>105.3</v>
       </c>
       <c r="D792" t="n">
-        <v>96.70999999999999</v>
+        <v>96.11</v>
       </c>
       <c r="E792" t="n">
         <v>104.46</v>
       </c>
       <c r="F792" t="n">
-        <v>172578</v>
+        <v>176604</v>
       </c>
     </row>
     <row r="793">
@@ -16272,7 +16272,7 @@
         <v>44638</v>
       </c>
       <c r="B793" t="n">
-        <v>105.16</v>
+        <v>104.55</v>
       </c>
       <c r="C793" t="n">
         <v>107.23</v>
@@ -16284,7 +16284,7 @@
         <v>105.63</v>
       </c>
       <c r="F793" t="n">
-        <v>155067</v>
+        <v>158531</v>
       </c>
     </row>
     <row r="794">
@@ -16352,7 +16352,7 @@
         <v>44644</v>
       </c>
       <c r="B797" t="n">
-        <v>119.49</v>
+        <v>118.08</v>
       </c>
       <c r="C797" t="n">
         <v>120.04</v>
@@ -16364,7 +16364,7 @@
         <v>114.47</v>
       </c>
       <c r="F797" t="n">
-        <v>206598</v>
+        <v>215337</v>
       </c>
     </row>
     <row r="798">
@@ -16372,7 +16372,7 @@
         <v>44645</v>
       </c>
       <c r="B798" t="n">
-        <v>114.52</v>
+        <v>115.3</v>
       </c>
       <c r="C798" t="n">
         <v>117.69</v>
@@ -16384,7 +16384,7 @@
         <v>115.94</v>
       </c>
       <c r="F798" t="n">
-        <v>189095</v>
+        <v>195807</v>
       </c>
     </row>
     <row r="799">
@@ -16461,10 +16461,10 @@
         <v>103.71</v>
       </c>
       <c r="E802" t="n">
-        <v>104.99</v>
+        <v>104.6</v>
       </c>
       <c r="F802" t="n">
-        <v>220967</v>
+        <v>217472</v>
       </c>
     </row>
     <row r="803">
@@ -16481,10 +16481,10 @@
         <v>101.94</v>
       </c>
       <c r="E803" t="n">
-        <v>103.88</v>
+        <v>104.13</v>
       </c>
       <c r="F803" t="n">
-        <v>181758</v>
+        <v>179677</v>
       </c>
     </row>
     <row r="804">
@@ -16561,10 +16561,10 @@
         <v>98.2</v>
       </c>
       <c r="E807" t="n">
-        <v>100.96</v>
+        <v>100.94</v>
       </c>
       <c r="F807" t="n">
-        <v>186163</v>
+        <v>183922</v>
       </c>
     </row>
     <row r="808">
@@ -16581,10 +16581,10 @@
         <v>99.28</v>
       </c>
       <c r="E808" t="n">
-        <v>101.81</v>
+        <v>102.16</v>
       </c>
       <c r="F808" t="n">
-        <v>162819</v>
+        <v>159821</v>
       </c>
     </row>
     <row r="809">
@@ -16661,10 +16661,10 @@
         <v>106.14</v>
       </c>
       <c r="E812" t="n">
-        <v>110.62</v>
+        <v>110.56</v>
       </c>
       <c r="F812" t="n">
-        <v>159785</v>
+        <v>156524</v>
       </c>
     </row>
     <row r="813">
@@ -16741,10 +16741,10 @@
         <v>106.38</v>
       </c>
       <c r="E816" t="n">
-        <v>108</v>
+        <v>107.93</v>
       </c>
       <c r="F816" t="n">
-        <v>188001</v>
+        <v>184241</v>
       </c>
     </row>
     <row r="817">
@@ -16758,13 +16758,13 @@
         <v>108.41</v>
       </c>
       <c r="D817" t="n">
-        <v>105.05</v>
+        <v>105.44</v>
       </c>
       <c r="E817" t="n">
-        <v>105.7</v>
+        <v>105.6</v>
       </c>
       <c r="F817" t="n">
-        <v>165632</v>
+        <v>162032</v>
       </c>
     </row>
     <row r="818">
@@ -16841,10 +16841,10 @@
         <v>102.74</v>
       </c>
       <c r="E821" t="n">
-        <v>106.8</v>
+        <v>107.25</v>
       </c>
       <c r="F821" t="n">
-        <v>170514</v>
+        <v>167676</v>
       </c>
     </row>
     <row r="822">
@@ -16861,10 +16861,10 @@
         <v>105.92</v>
       </c>
       <c r="E822" t="n">
-        <v>106.06</v>
+        <v>106.38</v>
       </c>
       <c r="F822" t="n">
-        <v>186051</v>
+        <v>182972</v>
       </c>
     </row>
     <row r="823">
@@ -16941,10 +16941,10 @@
         <v>108.66</v>
       </c>
       <c r="E826" t="n">
-        <v>110.4</v>
+        <v>110.3</v>
       </c>
       <c r="F826" t="n">
-        <v>201234</v>
+        <v>197687</v>
       </c>
     </row>
     <row r="827">
@@ -16961,10 +16961,10 @@
         <v>109.21</v>
       </c>
       <c r="E827" t="n">
-        <v>112.22</v>
+        <v>112.44</v>
       </c>
       <c r="F827" t="n">
-        <v>207851</v>
+        <v>203469</v>
       </c>
     </row>
     <row r="828">
@@ -17041,10 +17041,10 @@
         <v>103.97</v>
       </c>
       <c r="E831" t="n">
-        <v>106.86</v>
+        <v>107.38</v>
       </c>
       <c r="F831" t="n">
-        <v>243371</v>
+        <v>240901</v>
       </c>
     </row>
     <row r="832">
@@ -17061,10 +17061,10 @@
         <v>106.88</v>
       </c>
       <c r="E832" t="n">
-        <v>109.76</v>
+        <v>110.4</v>
       </c>
       <c r="F832" t="n">
-        <v>193013</v>
+        <v>190398</v>
       </c>
     </row>
     <row r="833">
@@ -17141,10 +17141,10 @@
         <v>104.22</v>
       </c>
       <c r="E836" t="n">
-        <v>109.5</v>
+        <v>109.59</v>
       </c>
       <c r="F836" t="n">
-        <v>250583</v>
+        <v>247278</v>
       </c>
     </row>
     <row r="837">
@@ -17161,10 +17161,10 @@
         <v>108.65</v>
       </c>
       <c r="E837" t="n">
-        <v>110.3</v>
+        <v>110.87</v>
       </c>
       <c r="F837" t="n">
-        <v>202895</v>
+        <v>198948</v>
       </c>
     </row>
     <row r="838">
@@ -17241,10 +17241,10 @@
         <v>110.83</v>
       </c>
       <c r="E841" t="n">
-        <v>114.15</v>
+        <v>114</v>
       </c>
       <c r="F841" t="n">
-        <v>175003</v>
+        <v>171535</v>
       </c>
     </row>
     <row r="842">
@@ -17261,10 +17261,10 @@
         <v>113.01</v>
       </c>
       <c r="E842" t="n">
-        <v>115.01</v>
+        <v>115.42</v>
       </c>
       <c r="F842" t="n">
-        <v>213418</v>
+        <v>210750</v>
       </c>
     </row>
     <row r="843">
@@ -17335,16 +17335,16 @@
         <v>113.88</v>
       </c>
       <c r="C846" t="n">
-        <v>117.74</v>
+        <v>117.57</v>
       </c>
       <c r="D846" t="n">
         <v>111.85</v>
       </c>
       <c r="E846" t="n">
-        <v>117.31</v>
+        <v>117.26</v>
       </c>
       <c r="F846" t="n">
-        <v>138282</v>
+        <v>137013</v>
       </c>
     </row>
     <row r="847">
@@ -17355,16 +17355,16 @@
         <v>117.37</v>
       </c>
       <c r="C847" t="n">
-        <v>120.6</v>
+        <v>120.57</v>
       </c>
       <c r="D847" t="n">
         <v>115.28</v>
       </c>
       <c r="E847" t="n">
-        <v>120.23</v>
+        <v>120.41</v>
       </c>
       <c r="F847" t="n">
-        <v>91626</v>
+        <v>90339</v>
       </c>
     </row>
     <row r="848">
@@ -17441,10 +17441,10 @@
         <v>121.23</v>
       </c>
       <c r="E851" t="n">
-        <v>121.41</v>
+        <v>121.71</v>
       </c>
       <c r="F851" t="n">
-        <v>176648</v>
+        <v>174232</v>
       </c>
     </row>
     <row r="852">
@@ -17461,10 +17461,10 @@
         <v>118.31</v>
       </c>
       <c r="E852" t="n">
-        <v>120.02</v>
+        <v>120.29</v>
       </c>
       <c r="F852" t="n">
-        <v>192334</v>
+        <v>190410</v>
       </c>
     </row>
     <row r="853">
@@ -17541,10 +17541,10 @@
         <v>113.72</v>
       </c>
       <c r="E856" t="n">
-        <v>116.92</v>
+        <v>117.15</v>
       </c>
       <c r="F856" t="n">
-        <v>231324</v>
+        <v>228931</v>
       </c>
     </row>
     <row r="857">
@@ -17561,10 +17561,10 @@
         <v>109.77</v>
       </c>
       <c r="E857" t="n">
-        <v>111.27</v>
+        <v>111.29</v>
       </c>
       <c r="F857" t="n">
-        <v>236868</v>
+        <v>233588</v>
       </c>
     </row>
     <row r="858">
@@ -17641,10 +17641,10 @@
         <v>105.25</v>
       </c>
       <c r="E861" t="n">
-        <v>106.13</v>
+        <v>106.29</v>
       </c>
       <c r="F861" t="n">
-        <v>234952</v>
+        <v>233040</v>
       </c>
     </row>
     <row r="862">
@@ -17661,10 +17661,10 @@
         <v>105.78</v>
       </c>
       <c r="E862" t="n">
-        <v>108.33</v>
+        <v>109.13</v>
       </c>
       <c r="F862" t="n">
-        <v>205227</v>
+        <v>202836</v>
       </c>
     </row>
     <row r="863">
@@ -17741,10 +17741,10 @@
         <v>107.7</v>
       </c>
       <c r="E866" t="n">
-        <v>108.43</v>
+        <v>108.69</v>
       </c>
       <c r="F866" t="n">
-        <v>212070</v>
+        <v>208599</v>
       </c>
     </row>
     <row r="867">
@@ -17761,10 +17761,10 @@
         <v>107.32</v>
       </c>
       <c r="E867" t="n">
-        <v>110.43</v>
+        <v>110.56</v>
       </c>
       <c r="F867" t="n">
-        <v>210630</v>
+        <v>209195</v>
       </c>
     </row>
     <row r="868">
@@ -17841,10 +17841,10 @@
         <v>97.11</v>
       </c>
       <c r="E871" t="n">
-        <v>102.32</v>
+        <v>102.75</v>
       </c>
       <c r="F871" t="n">
-        <v>224620</v>
+        <v>221862</v>
       </c>
     </row>
     <row r="872">
@@ -17861,10 +17861,10 @@
         <v>102.16</v>
       </c>
       <c r="E872" t="n">
-        <v>105.2</v>
+        <v>105.32</v>
       </c>
       <c r="F872" t="n">
-        <v>237030</v>
+        <v>235167</v>
       </c>
     </row>
     <row r="873">
@@ -17941,10 +17941,10 @@
         <v>92.42</v>
       </c>
       <c r="E876" t="n">
-        <v>97.12</v>
+        <v>97.17</v>
       </c>
       <c r="F876" t="n">
-        <v>217836</v>
+        <v>215919</v>
       </c>
     </row>
     <row r="877">
@@ -17961,10 +17961,10 @@
         <v>95.59</v>
       </c>
       <c r="E877" t="n">
-        <v>97.98</v>
+        <v>98.34999999999999</v>
       </c>
       <c r="F877" t="n">
-        <v>203134</v>
+        <v>200270</v>
       </c>
     </row>
     <row r="878">
@@ -18041,10 +18041,10 @@
         <v>97.86</v>
       </c>
       <c r="E881" t="n">
-        <v>99.93000000000001</v>
+        <v>100.04</v>
       </c>
       <c r="F881" t="n">
-        <v>229298</v>
+        <v>227231</v>
       </c>
     </row>
     <row r="882">
@@ -18061,10 +18061,10 @@
         <v>97.90000000000001</v>
       </c>
       <c r="E882" t="n">
-        <v>98.98999999999999</v>
+        <v>98.67</v>
       </c>
       <c r="F882" t="n">
-        <v>226135</v>
+        <v>222921</v>
       </c>
     </row>
     <row r="883">
@@ -18141,10 +18141,10 @@
         <v>100.74</v>
       </c>
       <c r="E886" t="n">
-        <v>101.99</v>
+        <v>101.93</v>
       </c>
       <c r="F886" t="n">
-        <v>132446</v>
+        <v>130398</v>
       </c>
     </row>
     <row r="887">
@@ -18161,10 +18161,10 @@
         <v>101.27</v>
       </c>
       <c r="E887" t="n">
-        <v>103.1</v>
+        <v>103.21</v>
       </c>
       <c r="F887" t="n">
-        <v>113461</v>
+        <v>112179</v>
       </c>
     </row>
     <row r="888">
@@ -18238,13 +18238,13 @@
         <v>97.17</v>
       </c>
       <c r="D891" t="n">
-        <v>92.5</v>
+        <v>92.73</v>
       </c>
       <c r="E891" t="n">
-        <v>92.52</v>
+        <v>93.38</v>
       </c>
       <c r="F891" t="n">
-        <v>162676</v>
+        <v>160629</v>
       </c>
     </row>
     <row r="892">
@@ -18261,10 +18261,10 @@
         <v>92.15000000000001</v>
       </c>
       <c r="E892" t="n">
-        <v>93.51000000000001</v>
+        <v>93.69</v>
       </c>
       <c r="F892" t="n">
-        <v>157322</v>
+        <v>155701</v>
       </c>
     </row>
     <row r="893">
@@ -18341,10 +18341,10 @@
         <v>96.08</v>
       </c>
       <c r="E896" t="n">
-        <v>98.31</v>
+        <v>98.66</v>
       </c>
       <c r="F896" t="n">
-        <v>140818</v>
+        <v>139272</v>
       </c>
     </row>
     <row r="897">
@@ -18361,10 +18361,10 @@
         <v>96.26000000000001</v>
       </c>
       <c r="E897" t="n">
-        <v>96.89</v>
+        <v>97.3</v>
       </c>
       <c r="F897" t="n">
-        <v>145858</v>
+        <v>144235</v>
       </c>
     </row>
     <row r="898">
@@ -18441,10 +18441,10 @@
         <v>92.55</v>
       </c>
       <c r="E901" t="n">
-        <v>95.56</v>
+        <v>95.93000000000001</v>
       </c>
       <c r="F901" t="n">
-        <v>123861</v>
+        <v>122235</v>
       </c>
     </row>
     <row r="902">
@@ -18461,10 +18461,10 @@
         <v>93.7</v>
       </c>
       <c r="E902" t="n">
-        <v>95.08</v>
+        <v>95.52</v>
       </c>
       <c r="F902" t="n">
-        <v>126696</v>
+        <v>125387</v>
       </c>
     </row>
     <row r="903">
@@ -18541,10 +18541,10 @@
         <v>98.23</v>
       </c>
       <c r="E906" t="n">
-        <v>98.68000000000001</v>
+        <v>99.05</v>
       </c>
       <c r="F906" t="n">
-        <v>115830</v>
+        <v>114289</v>
       </c>
     </row>
     <row r="907">
@@ -18561,10 +18561,10 @@
         <v>96.92</v>
       </c>
       <c r="E907" t="n">
-        <v>98.56999999999999</v>
+        <v>98.70999999999999</v>
       </c>
       <c r="F907" t="n">
-        <v>128357</v>
+        <v>127109</v>
       </c>
     </row>
     <row r="908">
@@ -18641,10 +18641,10 @@
         <v>91.58</v>
       </c>
       <c r="E911" t="n">
-        <v>91.59</v>
+        <v>91.75</v>
       </c>
       <c r="F911" t="n">
-        <v>172611</v>
+        <v>171383</v>
       </c>
     </row>
     <row r="912">
@@ -18661,10 +18661,10 @@
         <v>92.41</v>
       </c>
       <c r="E912" t="n">
-        <v>92.83</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="F912" t="n">
-        <v>164349</v>
+        <v>162523</v>
       </c>
     </row>
     <row r="913">
@@ -18741,10 +18741,10 @@
         <v>86.86</v>
       </c>
       <c r="E916" t="n">
-        <v>87.73999999999999</v>
+        <v>88.03</v>
       </c>
       <c r="F916" t="n">
-        <v>175783</v>
+        <v>174104</v>
       </c>
     </row>
     <row r="917">
@@ -18761,10 +18761,10 @@
         <v>88.09</v>
       </c>
       <c r="E917" t="n">
-        <v>91.42</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="F917" t="n">
-        <v>139210</v>
+        <v>137562</v>
       </c>
     </row>
     <row r="918">
@@ -18841,10 +18841,10 @@
         <v>89.39</v>
       </c>
       <c r="E921" t="n">
-        <v>89.78</v>
+        <v>90.08</v>
       </c>
       <c r="F921" t="n">
-        <v>179533</v>
+        <v>177670</v>
       </c>
     </row>
     <row r="922">
@@ -18861,10 +18861,10 @@
         <v>89.37</v>
       </c>
       <c r="E922" t="n">
-        <v>90.36</v>
+        <v>90.58</v>
       </c>
       <c r="F922" t="n">
-        <v>177056</v>
+        <v>175462</v>
       </c>
     </row>
     <row r="923">
@@ -18941,10 +18941,10 @@
         <v>88.38</v>
       </c>
       <c r="E926" t="n">
-        <v>89.48999999999999</v>
+        <v>89.53</v>
       </c>
       <c r="F926" t="n">
-        <v>169282</v>
+        <v>167346</v>
       </c>
     </row>
     <row r="927">
@@ -18961,10 +18961,10 @@
         <v>84.61</v>
       </c>
       <c r="E927" t="n">
-        <v>85.65000000000001</v>
+        <v>85.41</v>
       </c>
       <c r="F927" t="n">
-        <v>159709</v>
+        <v>157358</v>
       </c>
     </row>
     <row r="928">
@@ -19041,10 +19041,10 @@
         <v>85.98</v>
       </c>
       <c r="E931" t="n">
-        <v>87.22</v>
+        <v>87.20999999999999</v>
       </c>
       <c r="F931" t="n">
-        <v>184095</v>
+        <v>182346</v>
       </c>
     </row>
     <row r="932">
@@ -19061,10 +19061,10 @@
         <v>84.73999999999999</v>
       </c>
       <c r="E932" t="n">
-        <v>85.04000000000001</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="F932" t="n">
-        <v>174184</v>
+        <v>172540</v>
       </c>
     </row>
     <row r="933">
@@ -19141,10 +19141,10 @@
         <v>92.09</v>
       </c>
       <c r="E936" t="n">
-        <v>94.16</v>
+        <v>94.31999999999999</v>
       </c>
       <c r="F936" t="n">
-        <v>136157</v>
+        <v>134269</v>
       </c>
     </row>
     <row r="937">
@@ -19161,10 +19161,10 @@
         <v>93.25</v>
       </c>
       <c r="E937" t="n">
-        <v>97.59</v>
+        <v>96.95</v>
       </c>
       <c r="F937" t="n">
-        <v>161145</v>
+        <v>158303</v>
       </c>
     </row>
     <row r="938">
@@ -19241,10 +19241,10 @@
         <v>90.18000000000001</v>
       </c>
       <c r="E941" t="n">
-        <v>93.67</v>
+        <v>93.61</v>
       </c>
       <c r="F941" t="n">
-        <v>189909</v>
+        <v>187899</v>
       </c>
     </row>
     <row r="942">
@@ -19261,10 +19261,10 @@
         <v>90.34</v>
       </c>
       <c r="E942" t="n">
-        <v>90.66</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="F942" t="n">
-        <v>186342</v>
+        <v>184164</v>
       </c>
     </row>
     <row r="943">
@@ -19341,10 +19341,10 @@
         <v>90.34</v>
       </c>
       <c r="E946" t="n">
-        <v>91.11</v>
+        <v>91</v>
       </c>
       <c r="F946" t="n">
-        <v>172151</v>
+        <v>169394</v>
       </c>
     </row>
     <row r="947">
@@ -19361,10 +19361,10 @@
         <v>89.40000000000001</v>
       </c>
       <c r="E947" t="n">
-        <v>91.58</v>
+        <v>91.7</v>
       </c>
       <c r="F947" t="n">
-        <v>170499</v>
+        <v>168937</v>
       </c>
     </row>
     <row r="948">
@@ -19441,10 +19441,10 @@
         <v>93.06999999999999</v>
       </c>
       <c r="E951" t="n">
-        <v>94.45999999999999</v>
+        <v>94.91</v>
       </c>
       <c r="F951" t="n">
-        <v>135151</v>
+        <v>130846</v>
       </c>
     </row>
     <row r="952">
@@ -19461,10 +19461,10 @@
         <v>92.81999999999999</v>
       </c>
       <c r="E952" t="n">
-        <v>93.95</v>
+        <v>93.81</v>
       </c>
       <c r="F952" t="n">
-        <v>135363</v>
+        <v>133960</v>
       </c>
     </row>
     <row r="953">
@@ -19532,7 +19532,7 @@
         <v>44868</v>
       </c>
       <c r="B956" t="n">
-        <v>94.84</v>
+        <v>94.81</v>
       </c>
       <c r="C956" t="n">
         <v>95.45</v>
@@ -19544,7 +19544,7 @@
         <v>93.92</v>
       </c>
       <c r="F956" t="n">
-        <v>141621</v>
+        <v>143503</v>
       </c>
     </row>
     <row r="957">
@@ -19552,19 +19552,19 @@
         <v>44869</v>
       </c>
       <c r="B957" t="n">
-        <v>93.94</v>
+        <v>93.98</v>
       </c>
       <c r="C957" t="n">
         <v>98.23999999999999</v>
       </c>
       <c r="D957" t="n">
-        <v>93.94</v>
+        <v>93.76000000000001</v>
       </c>
       <c r="E957" t="n">
         <v>98.01000000000001</v>
       </c>
       <c r="F957" t="n">
-        <v>179958</v>
+        <v>182009</v>
       </c>
     </row>
     <row r="958">
@@ -19641,10 +19641,10 @@
         <v>90.97</v>
       </c>
       <c r="E961" t="n">
-        <v>92.47</v>
+        <v>92.69</v>
       </c>
       <c r="F961" t="n">
-        <v>170823</v>
+        <v>168690</v>
       </c>
     </row>
     <row r="962">
@@ -19661,10 +19661,10 @@
         <v>92.79000000000001</v>
       </c>
       <c r="E962" t="n">
-        <v>94.95999999999999</v>
+        <v>95.04000000000001</v>
       </c>
       <c r="F962" t="n">
-        <v>165782</v>
+        <v>163940</v>
       </c>
     </row>
     <row r="963">
@@ -19741,10 +19741,10 @@
         <v>88.72</v>
       </c>
       <c r="E966" t="n">
-        <v>89.34999999999999</v>
+        <v>89.28</v>
       </c>
       <c r="F966" t="n">
-        <v>159560</v>
+        <v>157265</v>
       </c>
     </row>
     <row r="967">
@@ -19761,10 +19761,10 @@
         <v>85.41</v>
       </c>
       <c r="E967" t="n">
-        <v>87.5</v>
+        <v>87.45</v>
       </c>
       <c r="F967" t="n">
-        <v>162655</v>
+        <v>160818</v>
       </c>
     </row>
     <row r="968">
@@ -19941,10 +19941,10 @@
         <v>86.26000000000001</v>
       </c>
       <c r="E976" t="n">
-        <v>86.98</v>
+        <v>86.84</v>
       </c>
       <c r="F976" t="n">
-        <v>136930</v>
+        <v>135345</v>
       </c>
     </row>
     <row r="977">
@@ -19961,10 +19961,10 @@
         <v>85.17</v>
       </c>
       <c r="E977" t="n">
-        <v>85.90000000000001</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="F977" t="n">
-        <v>137359</v>
+        <v>135815</v>
       </c>
     </row>
     <row r="978">
@@ -20041,10 +20041,10 @@
         <v>75.92</v>
       </c>
       <c r="E981" t="n">
-        <v>76.61</v>
+        <v>76.27</v>
       </c>
       <c r="F981" t="n">
-        <v>167594</v>
+        <v>165742</v>
       </c>
     </row>
     <row r="982">
@@ -20061,10 +20061,10 @@
         <v>75.34999999999999</v>
       </c>
       <c r="E982" t="n">
-        <v>76.79000000000001</v>
+        <v>76.76000000000001</v>
       </c>
       <c r="F982" t="n">
-        <v>153224</v>
+        <v>151706</v>
       </c>
     </row>
     <row r="983">
@@ -20141,10 +20141,10 @@
         <v>80.86</v>
       </c>
       <c r="E986" t="n">
-        <v>81.54000000000001</v>
+        <v>81.39</v>
       </c>
       <c r="F986" t="n">
-        <v>151489</v>
+        <v>149384</v>
       </c>
     </row>
     <row r="987">
@@ -20161,10 +20161,10 @@
         <v>78.61</v>
       </c>
       <c r="E987" t="n">
-        <v>79.44</v>
+        <v>79.36</v>
       </c>
       <c r="F987" t="n">
-        <v>151197</v>
+        <v>149990</v>
       </c>
     </row>
     <row r="988">
@@ -20241,10 +20241,10 @@
         <v>81.28</v>
       </c>
       <c r="E991" t="n">
-        <v>82.20999999999999</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="F991" t="n">
-        <v>95617</v>
+        <v>94348</v>
       </c>
     </row>
     <row r="992">
@@ -20321,10 +20321,10 @@
         <v>81.81999999999999</v>
       </c>
       <c r="E995" t="n">
-        <v>83.63</v>
+        <v>83.68000000000001</v>
       </c>
       <c r="F995" t="n">
-        <v>110699</v>
+        <v>109380</v>
       </c>
     </row>
     <row r="996">
@@ -20401,10 +20401,10 @@
         <v>77.63</v>
       </c>
       <c r="E999" t="n">
-        <v>78.8</v>
+        <v>78.68000000000001</v>
       </c>
       <c r="F999" t="n">
-        <v>150672</v>
+        <v>149266</v>
       </c>
     </row>
     <row r="1000">
@@ -20424,7 +20424,7 @@
         <v>78.51000000000001</v>
       </c>
       <c r="F1000" t="n">
-        <v>148389</v>
+        <v>147017</v>
       </c>
     </row>
     <row r="1001">
@@ -20501,10 +20501,10 @@
         <v>82.43000000000001</v>
       </c>
       <c r="E1004" t="n">
-        <v>83.84999999999999</v>
+        <v>83.91</v>
       </c>
       <c r="F1004" t="n">
-        <v>142735</v>
+        <v>141086</v>
       </c>
     </row>
     <row r="1005">
@@ -20515,16 +20515,16 @@
         <v>83.91</v>
       </c>
       <c r="C1005" t="n">
-        <v>85.61</v>
+        <v>85.55</v>
       </c>
       <c r="D1005" t="n">
         <v>83.55</v>
       </c>
       <c r="E1005" t="n">
-        <v>85.47</v>
+        <v>85.48</v>
       </c>
       <c r="F1005" t="n">
-        <v>131152</v>
+        <v>129757</v>
       </c>
     </row>
     <row r="1006">
@@ -20601,10 +20601,10 @@
         <v>83.95999999999999</v>
       </c>
       <c r="E1009" t="n">
-        <v>86.34</v>
+        <v>86.31999999999999</v>
       </c>
       <c r="F1009" t="n">
-        <v>144410</v>
+        <v>142583</v>
       </c>
     </row>
     <row r="1010">
@@ -20621,10 +20621,10 @@
         <v>85.69</v>
       </c>
       <c r="E1010" t="n">
-        <v>87.59</v>
+        <v>87.75</v>
       </c>
       <c r="F1010" t="n">
-        <v>125225</v>
+        <v>123973</v>
       </c>
     </row>
     <row r="1011">
@@ -20701,10 +20701,10 @@
         <v>85.75</v>
       </c>
       <c r="E1014" t="n">
-        <v>87.29000000000001</v>
+        <v>87.31</v>
       </c>
       <c r="F1014" t="n">
-        <v>96051</v>
+        <v>95077</v>
       </c>
     </row>
     <row r="1015">
@@ -20721,10 +20721,10 @@
         <v>85.48</v>
       </c>
       <c r="E1015" t="n">
-        <v>86.01000000000001</v>
+        <v>86.04000000000001</v>
       </c>
       <c r="F1015" t="n">
-        <v>110922</v>
+        <v>109841</v>
       </c>
     </row>
     <row r="1016">
@@ -20801,10 +20801,10 @@
         <v>81.2</v>
       </c>
       <c r="E1019" t="n">
-        <v>82.12</v>
+        <v>81.98</v>
       </c>
       <c r="F1019" t="n">
-        <v>150704</v>
+        <v>146732</v>
       </c>
     </row>
     <row r="1020">
@@ -20818,13 +20818,13 @@
         <v>84.11</v>
       </c>
       <c r="D1020" t="n">
-        <v>79.53</v>
+        <v>79.62</v>
       </c>
       <c r="E1020" t="n">
-        <v>79.62</v>
+        <v>79.64</v>
       </c>
       <c r="F1020" t="n">
-        <v>163093</v>
+        <v>161681</v>
       </c>
     </row>
     <row r="1021">
@@ -20901,10 +20901,10 @@
         <v>82.86</v>
       </c>
       <c r="E1024" t="n">
-        <v>83.95</v>
+        <v>83.88</v>
       </c>
       <c r="F1024" t="n">
-        <v>144061</v>
+        <v>142722</v>
       </c>
     </row>
     <row r="1025">
@@ -20921,10 +20921,10 @@
         <v>83.66</v>
       </c>
       <c r="E1025" t="n">
-        <v>86.2</v>
+        <v>86.29000000000001</v>
       </c>
       <c r="F1025" t="n">
-        <v>156718</v>
+        <v>155562</v>
       </c>
     </row>
     <row r="1026">
@@ -20998,13 +20998,13 @@
         <v>85.90000000000001</v>
       </c>
       <c r="D1029" t="n">
-        <v>84.28</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="E1029" t="n">
-        <v>84.31</v>
+        <v>84.37</v>
       </c>
       <c r="F1029" t="n">
-        <v>129946</v>
+        <v>128382</v>
       </c>
     </row>
     <row r="1030">
@@ -21021,10 +21021,10 @@
         <v>81.55</v>
       </c>
       <c r="E1030" t="n">
-        <v>82.72</v>
+        <v>82.68000000000001</v>
       </c>
       <c r="F1030" t="n">
-        <v>142763</v>
+        <v>141607</v>
       </c>
     </row>
     <row r="1031">
@@ -21101,10 +21101,10 @@
         <v>80.27</v>
       </c>
       <c r="E1034" t="n">
-        <v>82.18000000000001</v>
+        <v>82.12</v>
       </c>
       <c r="F1034" t="n">
-        <v>108091</v>
+        <v>107083</v>
       </c>
     </row>
     <row r="1035">
@@ -21121,10 +21121,10 @@
         <v>80.7</v>
       </c>
       <c r="E1035" t="n">
-        <v>82.77</v>
+        <v>82.94</v>
       </c>
       <c r="F1035" t="n">
-        <v>130526</v>
+        <v>129354</v>
       </c>
     </row>
     <row r="1036">
@@ -21201,10 +21201,10 @@
         <v>83.66</v>
       </c>
       <c r="E1039" t="n">
-        <v>84.23</v>
+        <v>84.34</v>
       </c>
       <c r="F1039" t="n">
-        <v>115434</v>
+        <v>114302</v>
       </c>
     </row>
     <row r="1040">
@@ -21215,16 +21215,16 @@
         <v>84.37</v>
       </c>
       <c r="C1040" t="n">
-        <v>85.81</v>
+        <v>85.8</v>
       </c>
       <c r="D1040" t="n">
         <v>82.2</v>
       </c>
       <c r="E1040" t="n">
-        <v>85.73999999999999</v>
+        <v>85.72</v>
       </c>
       <c r="F1040" t="n">
-        <v>120888</v>
+        <v>119970</v>
       </c>
     </row>
     <row r="1041">
@@ -21301,10 +21301,10 @@
         <v>81.16</v>
       </c>
       <c r="E1044" t="n">
-        <v>81.23</v>
+        <v>81.26000000000001</v>
       </c>
       <c r="F1044" t="n">
-        <v>121276</v>
+        <v>120126</v>
       </c>
     </row>
     <row r="1045">
@@ -21321,10 +21321,10 @@
         <v>80.47</v>
       </c>
       <c r="E1045" t="n">
-        <v>82.38</v>
+        <v>82.33</v>
       </c>
       <c r="F1045" t="n">
-        <v>172647</v>
+        <v>171433</v>
       </c>
     </row>
     <row r="1046">
@@ -21392,7 +21392,7 @@
         <v>45001</v>
       </c>
       <c r="B1049" t="n">
-        <v>74.59999999999999</v>
+        <v>74.04000000000001</v>
       </c>
       <c r="C1049" t="n">
         <v>75.23</v>
@@ -21404,7 +21404,7 @@
         <v>74.25</v>
       </c>
       <c r="F1049" t="n">
-        <v>206406</v>
+        <v>210322</v>
       </c>
     </row>
     <row r="1050">
@@ -21412,7 +21412,7 @@
         <v>45002</v>
       </c>
       <c r="B1050" t="n">
-        <v>74.41</v>
+        <v>74.45</v>
       </c>
       <c r="C1050" t="n">
         <v>75.65000000000001</v>
@@ -21424,7 +21424,7 @@
         <v>72.3</v>
       </c>
       <c r="F1050" t="n">
-        <v>194486</v>
+        <v>196053</v>
       </c>
     </row>
     <row r="1051">
@@ -21492,7 +21492,7 @@
         <v>45008</v>
       </c>
       <c r="B1054" t="n">
-        <v>75.73</v>
+        <v>75.58</v>
       </c>
       <c r="C1054" t="n">
         <v>77.09</v>
@@ -21504,7 +21504,7 @@
         <v>74.98999999999999</v>
       </c>
       <c r="F1054" t="n">
-        <v>132462</v>
+        <v>134971</v>
       </c>
     </row>
     <row r="1055">
@@ -21512,7 +21512,7 @@
         <v>45009</v>
       </c>
       <c r="B1055" t="n">
-        <v>74.92</v>
+        <v>75.08</v>
       </c>
       <c r="C1055" t="n">
         <v>75.89</v>
@@ -21524,7 +21524,7 @@
         <v>74.52</v>
       </c>
       <c r="F1055" t="n">
-        <v>158419</v>
+        <v>160608</v>
       </c>
     </row>
     <row r="1056">
@@ -21601,10 +21601,10 @@
         <v>77.13</v>
       </c>
       <c r="E1059" t="n">
-        <v>78.43000000000001</v>
+        <v>78.47</v>
       </c>
       <c r="F1059" t="n">
-        <v>102975</v>
+        <v>101875</v>
       </c>
     </row>
     <row r="1060">
@@ -21621,10 +21621,10 @@
         <v>77.79000000000001</v>
       </c>
       <c r="E1060" t="n">
-        <v>79.76000000000001</v>
+        <v>79.73</v>
       </c>
       <c r="F1060" t="n">
-        <v>103341</v>
+        <v>102278</v>
       </c>
     </row>
     <row r="1061">
@@ -21701,10 +21701,10 @@
         <v>83.89</v>
       </c>
       <c r="E1064" t="n">
-        <v>84.62</v>
+        <v>84.73</v>
       </c>
       <c r="F1064" t="n">
-        <v>128978</v>
+        <v>127887</v>
       </c>
     </row>
     <row r="1065">
@@ -21781,10 +21781,10 @@
         <v>85.78</v>
       </c>
       <c r="E1068" t="n">
-        <v>86.03</v>
+        <v>85.98</v>
       </c>
       <c r="F1068" t="n">
-        <v>107747</v>
+        <v>106530</v>
       </c>
     </row>
     <row r="1069">
@@ -21801,10 +21801,10 @@
         <v>85.27</v>
       </c>
       <c r="E1069" t="n">
-        <v>86.12</v>
+        <v>86.13</v>
       </c>
       <c r="F1069" t="n">
-        <v>119789</v>
+        <v>118921</v>
       </c>
     </row>
     <row r="1070">
@@ -21878,13 +21878,13 @@
         <v>82.59999999999999</v>
       </c>
       <c r="D1073" t="n">
-        <v>80.48999999999999</v>
+        <v>80.51000000000001</v>
       </c>
       <c r="E1073" t="n">
-        <v>80.48999999999999</v>
+        <v>80.62</v>
       </c>
       <c r="F1073" t="n">
-        <v>100157</v>
+        <v>99083</v>
       </c>
     </row>
     <row r="1074">
@@ -21901,10 +21901,10 @@
         <v>80.2</v>
       </c>
       <c r="E1074" t="n">
-        <v>81.53</v>
+        <v>81.38</v>
       </c>
       <c r="F1074" t="n">
-        <v>89589</v>
+        <v>88877</v>
       </c>
     </row>
     <row r="1075">
@@ -21981,10 +21981,10 @@
         <v>77.3</v>
       </c>
       <c r="E1078" t="n">
-        <v>78.17</v>
+        <v>78.23</v>
       </c>
       <c r="F1078" t="n">
-        <v>114226</v>
+        <v>112919</v>
       </c>
     </row>
     <row r="1079">
@@ -22001,10 +22001,10 @@
         <v>77.44</v>
       </c>
       <c r="E1079" t="n">
-        <v>80.08</v>
+        <v>80.20999999999999</v>
       </c>
       <c r="F1079" t="n">
-        <v>111593</v>
+        <v>110643</v>
       </c>
     </row>
     <row r="1080">
@@ -22081,10 +22081,10 @@
         <v>71.34</v>
       </c>
       <c r="E1083" t="n">
-        <v>72.38</v>
+        <v>72.34</v>
       </c>
       <c r="F1083" t="n">
-        <v>176458</v>
+        <v>175075</v>
       </c>
     </row>
     <row r="1084">
@@ -22101,10 +22101,10 @@
         <v>72.31999999999999</v>
       </c>
       <c r="E1084" t="n">
-        <v>75.15000000000001</v>
+        <v>75.22</v>
       </c>
       <c r="F1084" t="n">
-        <v>122688</v>
+        <v>121559</v>
       </c>
     </row>
     <row r="1085">
@@ -22181,10 +22181,10 @@
         <v>74.5</v>
       </c>
       <c r="E1088" t="n">
-        <v>75.26000000000001</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="F1088" t="n">
-        <v>142391</v>
+        <v>141443</v>
       </c>
     </row>
     <row r="1089">
@@ -22201,10 +22201,10 @@
         <v>73.84999999999999</v>
       </c>
       <c r="E1089" t="n">
-        <v>73.93000000000001</v>
+        <v>74.02</v>
       </c>
       <c r="F1089" t="n">
-        <v>144762</v>
+        <v>143925</v>
       </c>
     </row>
     <row r="1090">
@@ -22281,10 +22281,10 @@
         <v>75.42</v>
       </c>
       <c r="E1093" t="n">
-        <v>75.84</v>
+        <v>75.89</v>
       </c>
       <c r="F1093" t="n">
-        <v>98116</v>
+        <v>97144</v>
       </c>
     </row>
     <row r="1094">
@@ -22301,10 +22301,10 @@
         <v>75.01000000000001</v>
       </c>
       <c r="E1094" t="n">
-        <v>75.59999999999999</v>
+        <v>75.75</v>
       </c>
       <c r="F1094" t="n">
-        <v>108218</v>
+        <v>107224</v>
       </c>
     </row>
     <row r="1095">
@@ -22381,10 +22381,10 @@
         <v>75.08</v>
       </c>
       <c r="E1098" t="n">
-        <v>75.95999999999999</v>
+        <v>76.13</v>
       </c>
       <c r="F1098" t="n">
-        <v>95663</v>
+        <v>94656</v>
       </c>
     </row>
     <row r="1099">
@@ -22401,10 +22401,10 @@
         <v>75.62</v>
       </c>
       <c r="E1099" t="n">
-        <v>77.14</v>
+        <v>77.03</v>
       </c>
       <c r="F1099" t="n">
-        <v>86227</v>
+        <v>85632</v>
       </c>
     </row>
     <row r="1100">
@@ -22481,10 +22481,10 @@
         <v>72</v>
       </c>
       <c r="E1103" t="n">
-        <v>74.25</v>
+        <v>74.17</v>
       </c>
       <c r="F1103" t="n">
-        <v>124084</v>
+        <v>122959</v>
       </c>
     </row>
     <row r="1104">
@@ -22501,10 +22501,10 @@
         <v>74.13</v>
       </c>
       <c r="E1104" t="n">
-        <v>76.13</v>
+        <v>76.3</v>
       </c>
       <c r="F1104" t="n">
-        <v>111881</v>
+        <v>110715</v>
       </c>
     </row>
     <row r="1105">
@@ -22581,10 +22581,10 @@
         <v>73.52</v>
       </c>
       <c r="E1108" t="n">
-        <v>75.44</v>
+        <v>75.56999999999999</v>
       </c>
       <c r="F1108" t="n">
-        <v>142206</v>
+        <v>141391</v>
       </c>
     </row>
     <row r="1109">
@@ -22601,10 +22601,10 @@
         <v>74.67</v>
       </c>
       <c r="E1109" t="n">
-        <v>74.88</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="F1109" t="n">
-        <v>120995</v>
+        <v>120105</v>
       </c>
     </row>
     <row r="1110">
@@ -22681,10 +22681,10 @@
         <v>72.84999999999999</v>
       </c>
       <c r="E1113" t="n">
-        <v>75.52</v>
+        <v>75.56</v>
       </c>
       <c r="F1113" t="n">
-        <v>105947</v>
+        <v>104970</v>
       </c>
     </row>
     <row r="1114">
@@ -22701,10 +22701,10 @@
         <v>75.09999999999999</v>
       </c>
       <c r="E1114" t="n">
-        <v>76.23</v>
+        <v>76.47</v>
       </c>
       <c r="F1114" t="n">
-        <v>111184</v>
+        <v>109963</v>
       </c>
     </row>
     <row r="1115">
@@ -22781,10 +22781,10 @@
         <v>73.75</v>
       </c>
       <c r="E1118" t="n">
-        <v>74.3</v>
+        <v>74.2</v>
       </c>
       <c r="F1118" t="n">
-        <v>89974</v>
+        <v>89166</v>
       </c>
     </row>
     <row r="1119">
@@ -22795,16 +22795,16 @@
         <v>74.2</v>
       </c>
       <c r="C1119" t="n">
-        <v>74.45999999999999</v>
+        <v>74.36</v>
       </c>
       <c r="D1119" t="n">
         <v>72.25</v>
       </c>
       <c r="E1119" t="n">
-        <v>74.34</v>
+        <v>74.09</v>
       </c>
       <c r="F1119" t="n">
-        <v>101628</v>
+        <v>100773</v>
       </c>
     </row>
     <row r="1120">
@@ -22881,10 +22881,10 @@
         <v>73.56</v>
       </c>
       <c r="E1123" t="n">
-        <v>74.34999999999999</v>
+        <v>74.44</v>
       </c>
       <c r="F1123" t="n">
-        <v>118860</v>
+        <v>118096</v>
       </c>
     </row>
     <row r="1124">
@@ -22901,10 +22901,10 @@
         <v>74.23</v>
       </c>
       <c r="E1124" t="n">
-        <v>75.06999999999999</v>
+        <v>75.26000000000001</v>
       </c>
       <c r="F1124" t="n">
-        <v>108012</v>
+        <v>107062</v>
       </c>
     </row>
     <row r="1125">
@@ -22981,10 +22981,10 @@
         <v>74.94</v>
       </c>
       <c r="E1128" t="n">
-        <v>76.44</v>
+        <v>76.47</v>
       </c>
       <c r="F1128" t="n">
-        <v>121613</v>
+        <v>120498</v>
       </c>
     </row>
     <row r="1129">
@@ -23001,10 +23001,10 @@
         <v>75.91</v>
       </c>
       <c r="E1129" t="n">
-        <v>78.12</v>
+        <v>78.13</v>
       </c>
       <c r="F1129" t="n">
-        <v>101260</v>
+        <v>99946</v>
       </c>
     </row>
     <row r="1130">
@@ -23075,16 +23075,16 @@
         <v>79.95999999999999</v>
       </c>
       <c r="C1133" t="n">
-        <v>81.5</v>
+        <v>81.48999999999999</v>
       </c>
       <c r="D1133" t="n">
         <v>79.69</v>
       </c>
       <c r="E1133" t="n">
-        <v>81.37</v>
+        <v>81.48</v>
       </c>
       <c r="F1133" t="n">
-        <v>97805</v>
+        <v>96443</v>
       </c>
     </row>
     <row r="1134">
@@ -23098,13 +23098,13 @@
         <v>81.42</v>
       </c>
       <c r="D1134" t="n">
-        <v>79.34999999999999</v>
+        <v>79.44</v>
       </c>
       <c r="E1134" t="n">
-        <v>79.45</v>
+        <v>79.54000000000001</v>
       </c>
       <c r="F1134" t="n">
-        <v>99161</v>
+        <v>98000</v>
       </c>
     </row>
     <row r="1135">
@@ -23181,10 +23181,10 @@
         <v>78.56999999999999</v>
       </c>
       <c r="E1138" t="n">
-        <v>79.48</v>
+        <v>79.54000000000001</v>
       </c>
       <c r="F1138" t="n">
-        <v>77506</v>
+        <v>76777</v>
       </c>
     </row>
     <row r="1139">
@@ -23201,10 +23201,10 @@
         <v>79.51000000000001</v>
       </c>
       <c r="E1139" t="n">
-        <v>80.5</v>
+        <v>80.69</v>
       </c>
       <c r="F1139" t="n">
-        <v>70745</v>
+        <v>69907</v>
       </c>
     </row>
     <row r="1140">
@@ -23281,10 +23281,10 @@
         <v>82.54000000000001</v>
       </c>
       <c r="E1143" t="n">
-        <v>83.3</v>
+        <v>83.42</v>
       </c>
       <c r="F1143" t="n">
-        <v>101885</v>
+        <v>100960</v>
       </c>
     </row>
     <row r="1144">
@@ -23301,10 +23301,10 @@
         <v>82.78</v>
       </c>
       <c r="E1144" t="n">
-        <v>84.34999999999999</v>
+        <v>84.26000000000001</v>
       </c>
       <c r="F1144" t="n">
-        <v>96933</v>
+        <v>96080</v>
       </c>
     </row>
     <row r="1145">
@@ -23381,10 +23381,10 @@
         <v>82.23</v>
       </c>
       <c r="E1148" t="n">
-        <v>85.04000000000001</v>
+        <v>85.13</v>
       </c>
       <c r="F1148" t="n">
-        <v>124232</v>
+        <v>122532</v>
       </c>
     </row>
     <row r="1149">
@@ -23401,10 +23401,10 @@
         <v>84.89</v>
       </c>
       <c r="E1149" t="n">
-        <v>85.81</v>
+        <v>85.84</v>
       </c>
       <c r="F1149" t="n">
-        <v>104424</v>
+        <v>103319</v>
       </c>
     </row>
     <row r="1150">
@@ -23481,10 +23481,10 @@
         <v>85.89</v>
       </c>
       <c r="E1153" t="n">
-        <v>86.01000000000001</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="F1153" t="n">
-        <v>120019</v>
+        <v>119054</v>
       </c>
     </row>
     <row r="1154">
@@ -23501,10 +23501,10 @@
         <v>85.53</v>
       </c>
       <c r="E1154" t="n">
-        <v>86.16</v>
+        <v>86.26000000000001</v>
       </c>
       <c r="F1154" t="n">
-        <v>115051</v>
+        <v>114400</v>
       </c>
     </row>
     <row r="1155">
@@ -23581,10 +23581,10 @@
         <v>82.70999999999999</v>
       </c>
       <c r="E1158" t="n">
-        <v>83.42</v>
+        <v>83.45999999999999</v>
       </c>
       <c r="F1158" t="n">
-        <v>88033</v>
+        <v>87119</v>
       </c>
     </row>
     <row r="1159">
@@ -23601,10 +23601,10 @@
         <v>82.98</v>
       </c>
       <c r="E1159" t="n">
-        <v>84.42</v>
+        <v>84.37</v>
       </c>
       <c r="F1159" t="n">
-        <v>98761</v>
+        <v>98085</v>
       </c>
     </row>
     <row r="1160">
@@ -23681,10 +23681,10 @@
         <v>81.61</v>
       </c>
       <c r="E1163" t="n">
-        <v>82.67</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="F1163" t="n">
-        <v>77961</v>
+        <v>77118</v>
       </c>
     </row>
     <row r="1164">
@@ -23701,10 +23701,10 @@
         <v>82.2</v>
       </c>
       <c r="E1164" t="n">
-        <v>84.05</v>
+        <v>84.14</v>
       </c>
       <c r="F1164" t="n">
-        <v>102303</v>
+        <v>101382</v>
       </c>
     </row>
     <row r="1165">
@@ -23781,10 +23781,10 @@
         <v>84.98</v>
       </c>
       <c r="E1168" t="n">
-        <v>86.66</v>
+        <v>86.63</v>
       </c>
       <c r="F1168" t="n">
-        <v>85007</v>
+        <v>83934</v>
       </c>
     </row>
     <row r="1169">
@@ -23795,16 +23795,16 @@
         <v>86.63</v>
       </c>
       <c r="C1169" t="n">
-        <v>88.75</v>
+        <v>88.66</v>
       </c>
       <c r="D1169" t="n">
         <v>86.59</v>
       </c>
       <c r="E1169" t="n">
-        <v>88.68000000000001</v>
+        <v>88.64</v>
       </c>
       <c r="F1169" t="n">
-        <v>98645</v>
+        <v>97671</v>
       </c>
     </row>
     <row r="1170">
@@ -23881,10 +23881,10 @@
         <v>89.17</v>
       </c>
       <c r="E1173" t="n">
-        <v>89.47</v>
+        <v>89.76000000000001</v>
       </c>
       <c r="F1173" t="n">
-        <v>104343</v>
+        <v>103067</v>
       </c>
     </row>
     <row r="1174">
@@ -23901,10 +23901,10 @@
         <v>88.97</v>
       </c>
       <c r="E1174" t="n">
-        <v>90.09999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="F1174" t="n">
-        <v>101197</v>
+        <v>100164</v>
       </c>
     </row>
     <row r="1175">
@@ -23975,16 +23975,16 @@
         <v>91.56999999999999</v>
       </c>
       <c r="C1178" t="n">
-        <v>93.68000000000001</v>
+        <v>93.44</v>
       </c>
       <c r="D1178" t="n">
         <v>91.55</v>
       </c>
       <c r="E1178" t="n">
-        <v>93.56</v>
+        <v>93.36</v>
       </c>
       <c r="F1178" t="n">
-        <v>91727</v>
+        <v>89908</v>
       </c>
     </row>
     <row r="1179">
@@ -24001,10 +24001,10 @@
         <v>92.14</v>
       </c>
       <c r="E1179" t="n">
-        <v>93.56999999999999</v>
+        <v>93.52</v>
       </c>
       <c r="F1179" t="n">
-        <v>101498</v>
+        <v>100530</v>
       </c>
     </row>
     <row r="1180">
@@ -24081,10 +24081,10 @@
         <v>91.23999999999999</v>
       </c>
       <c r="E1183" t="n">
-        <v>92.20999999999999</v>
+        <v>92.27</v>
       </c>
       <c r="F1183" t="n">
-        <v>98137</v>
+        <v>97207</v>
       </c>
     </row>
     <row r="1184">
@@ -24101,10 +24101,10 @@
         <v>91.68000000000001</v>
       </c>
       <c r="E1184" t="n">
-        <v>92.28</v>
+        <v>92.31</v>
       </c>
       <c r="F1184" t="n">
-        <v>99665</v>
+        <v>98960</v>
       </c>
     </row>
     <row r="1185">
@@ -24181,10 +24181,10 @@
         <v>92.56</v>
       </c>
       <c r="E1188" t="n">
-        <v>92.89</v>
+        <v>92.94</v>
       </c>
       <c r="F1188" t="n">
-        <v>128240</v>
+        <v>127194</v>
       </c>
     </row>
     <row r="1189">
@@ -24201,10 +24201,10 @@
         <v>91.68000000000001</v>
       </c>
       <c r="E1189" t="n">
-        <v>91.8</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="F1189" t="n">
-        <v>117877</v>
+        <v>116761</v>
       </c>
     </row>
     <row r="1190">
@@ -24281,10 +24281,10 @@
         <v>83.31999999999999</v>
       </c>
       <c r="E1193" t="n">
-        <v>83.72</v>
+        <v>83.68000000000001</v>
       </c>
       <c r="F1193" t="n">
-        <v>149779</v>
+        <v>148426</v>
       </c>
     </row>
     <row r="1194">
@@ -24301,10 +24301,10 @@
         <v>82.97</v>
       </c>
       <c r="E1194" t="n">
-        <v>83.79000000000001</v>
+        <v>83.88</v>
       </c>
       <c r="F1194" t="n">
-        <v>140020</v>
+        <v>138785</v>
       </c>
     </row>
     <row r="1195">
@@ -24381,10 +24381,10 @@
         <v>84.59</v>
       </c>
       <c r="E1198" t="n">
-        <v>85.59999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="F1198" t="n">
-        <v>124560</v>
+        <v>123421</v>
       </c>
     </row>
     <row r="1199">
@@ -24404,7 +24404,7 @@
         <v>89.93000000000001</v>
       </c>
       <c r="F1199" t="n">
-        <v>120817</v>
+        <v>118765</v>
       </c>
     </row>
     <row r="1200">
@@ -24475,16 +24475,16 @@
         <v>90.26000000000001</v>
       </c>
       <c r="C1203" t="n">
-        <v>92.34999999999999</v>
+        <v>92.22</v>
       </c>
       <c r="D1203" t="n">
         <v>88.69</v>
       </c>
       <c r="E1203" t="n">
-        <v>92.04000000000001</v>
+        <v>92.16</v>
       </c>
       <c r="F1203" t="n">
-        <v>111224</v>
+        <v>109002</v>
       </c>
     </row>
     <row r="1204">
@@ -24501,10 +24501,10 @@
         <v>90.63</v>
       </c>
       <c r="E1204" t="n">
-        <v>91.26000000000001</v>
+        <v>91.13</v>
       </c>
       <c r="F1204" t="n">
-        <v>110661</v>
+        <v>109157</v>
       </c>
     </row>
     <row r="1205">
@@ -24581,10 +24581,10 @@
         <v>86.48</v>
       </c>
       <c r="E1208" t="n">
-        <v>87.23999999999999</v>
+        <v>87.25</v>
       </c>
       <c r="F1208" t="n">
-        <v>114536</v>
+        <v>113368</v>
       </c>
     </row>
     <row r="1209">
@@ -24601,10 +24601,10 @@
         <v>86.76000000000001</v>
       </c>
       <c r="E1209" t="n">
-        <v>88.70999999999999</v>
+        <v>88.76000000000001</v>
       </c>
       <c r="F1209" t="n">
-        <v>123231</v>
+        <v>121600</v>
       </c>
     </row>
     <row r="1210">
@@ -24672,7 +24672,7 @@
         <v>45232</v>
       </c>
       <c r="B1213" t="n">
-        <v>85.03</v>
+        <v>84.83</v>
       </c>
       <c r="C1213" t="n">
         <v>86.88</v>
@@ -24684,7 +24684,7 @@
         <v>86.63</v>
       </c>
       <c r="F1213" t="n">
-        <v>102261</v>
+        <v>103842</v>
       </c>
     </row>
     <row r="1214">
@@ -24692,7 +24692,7 @@
         <v>45233</v>
       </c>
       <c r="B1214" t="n">
-        <v>86.66</v>
+        <v>86.70999999999999</v>
       </c>
       <c r="C1214" t="n">
         <v>87.58</v>
@@ -24704,7 +24704,7 @@
         <v>84.95</v>
       </c>
       <c r="F1214" t="n">
-        <v>117913</v>
+        <v>119097</v>
       </c>
     </row>
     <row r="1215">
@@ -24781,10 +24781,10 @@
         <v>79.33</v>
       </c>
       <c r="E1218" t="n">
-        <v>79.76000000000001</v>
+        <v>79.75</v>
       </c>
       <c r="F1218" t="n">
-        <v>111847</v>
+        <v>110739</v>
       </c>
     </row>
     <row r="1219">
@@ -24801,10 +24801,10 @@
         <v>79.70999999999999</v>
       </c>
       <c r="E1219" t="n">
-        <v>81.43000000000001</v>
+        <v>81.36</v>
       </c>
       <c r="F1219" t="n">
-        <v>92327</v>
+        <v>91256</v>
       </c>
     </row>
     <row r="1220">
@@ -24881,10 +24881,10 @@
         <v>76.64</v>
       </c>
       <c r="E1223" t="n">
-        <v>77.45</v>
+        <v>77.43000000000001</v>
       </c>
       <c r="F1223" t="n">
-        <v>105749</v>
+        <v>104766</v>
       </c>
     </row>
     <row r="1224">
@@ -24901,10 +24901,10 @@
         <v>77.31</v>
       </c>
       <c r="E1224" t="n">
-        <v>80.43000000000001</v>
+        <v>80.37</v>
       </c>
       <c r="F1224" t="n">
-        <v>89648</v>
+        <v>88772</v>
       </c>
     </row>
     <row r="1225">
@@ -25078,13 +25078,13 @@
         <v>84.51000000000001</v>
       </c>
       <c r="D1233" t="n">
-        <v>79.94</v>
+        <v>79.95</v>
       </c>
       <c r="E1233" t="n">
-        <v>80.31</v>
+        <v>80</v>
       </c>
       <c r="F1233" t="n">
-        <v>145419</v>
+        <v>143673</v>
       </c>
     </row>
     <row r="1234">
@@ -25101,10 +25101,10 @@
         <v>78.69</v>
       </c>
       <c r="E1234" t="n">
-        <v>79.02</v>
+        <v>78.93000000000001</v>
       </c>
       <c r="F1234" t="n">
-        <v>126159</v>
+        <v>125186</v>
       </c>
     </row>
     <row r="1235">
@@ -25181,10 +25181,10 @@
         <v>73.68000000000001</v>
       </c>
       <c r="E1238" t="n">
-        <v>74.39</v>
+        <v>74.47</v>
       </c>
       <c r="F1238" t="n">
-        <v>116791</v>
+        <v>115986</v>
       </c>
     </row>
     <row r="1239">
@@ -25201,10 +25201,10 @@
         <v>74.25</v>
       </c>
       <c r="E1239" t="n">
-        <v>75.94</v>
+        <v>75.87</v>
       </c>
       <c r="F1239" t="n">
-        <v>114930</v>
+        <v>114085</v>
       </c>
     </row>
     <row r="1240">
@@ -25281,10 +25281,10 @@
         <v>74.56999999999999</v>
       </c>
       <c r="E1243" t="n">
-        <v>76.75</v>
+        <v>76.86</v>
       </c>
       <c r="F1243" t="n">
-        <v>84712</v>
+        <v>83845</v>
       </c>
     </row>
     <row r="1244">
@@ -25301,10 +25301,10 @@
         <v>75.48</v>
       </c>
       <c r="E1244" t="n">
-        <v>76.98999999999999</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="F1244" t="n">
-        <v>95068</v>
+        <v>94162</v>
       </c>
     </row>
     <row r="1245">
@@ -25381,10 +25381,10 @@
         <v>77.76000000000001</v>
       </c>
       <c r="E1248" t="n">
-        <v>79.12</v>
+        <v>79.19</v>
       </c>
       <c r="F1248" t="n">
-        <v>91755</v>
+        <v>91100</v>
       </c>
     </row>
     <row r="1249">
@@ -25461,10 +25461,10 @@
         <v>77.04000000000001</v>
       </c>
       <c r="E1252" t="n">
-        <v>77.36</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="F1252" t="n">
-        <v>95204</v>
+        <v>94380</v>
       </c>
     </row>
     <row r="1253">
@@ -25544,7 +25544,7 @@
         <v>77.53</v>
       </c>
       <c r="F1256" t="n">
-        <v>119158</v>
+        <v>118273</v>
       </c>
     </row>
     <row r="1257">
@@ -25641,10 +25641,10 @@
         <v>76.45</v>
       </c>
       <c r="E1261" t="n">
-        <v>78.01000000000001</v>
+        <v>77.61</v>
       </c>
       <c r="F1261" t="n">
-        <v>129868</v>
+        <v>128067</v>
       </c>
     </row>
     <row r="1262">
@@ -25741,10 +25741,10 @@
         <v>76.98</v>
       </c>
       <c r="E1266" t="n">
-        <v>78.56</v>
+        <v>78.63</v>
       </c>
       <c r="F1266" t="n">
-        <v>99368</v>
+        <v>98609</v>
       </c>
     </row>
     <row r="1267">
@@ -25841,10 +25841,10 @@
         <v>79.65000000000001</v>
       </c>
       <c r="E1271" t="n">
-        <v>81.69</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="F1271" t="n">
-        <v>76710</v>
+        <v>75889</v>
       </c>
     </row>
     <row r="1272">
@@ -25861,10 +25861,10 @@
         <v>80.75</v>
       </c>
       <c r="E1272" t="n">
-        <v>83.09999999999999</v>
+        <v>83.08</v>
       </c>
       <c r="F1272" t="n">
-        <v>87047</v>
+        <v>85666</v>
       </c>
     </row>
     <row r="1273">
@@ -25941,10 +25941,10 @@
         <v>78.5</v>
       </c>
       <c r="E1276" t="n">
-        <v>78.7</v>
+        <v>78.64</v>
       </c>
       <c r="F1276" t="n">
-        <v>140571</v>
+        <v>138682</v>
       </c>
     </row>
     <row r="1277">
@@ -25961,10 +25961,10 @@
         <v>76.78</v>
       </c>
       <c r="E1277" t="n">
-        <v>77.31999999999999</v>
+        <v>77.11</v>
       </c>
       <c r="F1277" t="n">
-        <v>133396</v>
+        <v>132023</v>
       </c>
     </row>
     <row r="1278">
@@ -26041,10 +26041,10 @@
         <v>78.84999999999999</v>
       </c>
       <c r="E1281" t="n">
-        <v>81.40000000000001</v>
+        <v>81.51000000000001</v>
       </c>
       <c r="F1281" t="n">
-        <v>87658</v>
+        <v>86597</v>
       </c>
     </row>
     <row r="1282">
@@ -26064,7 +26064,7 @@
         <v>81.63</v>
       </c>
       <c r="F1282" t="n">
-        <v>86235</v>
+        <v>85346</v>
       </c>
     </row>
     <row r="1283">
@@ -26141,10 +26141,10 @@
         <v>80.31999999999999</v>
       </c>
       <c r="E1286" t="n">
-        <v>82.22</v>
+        <v>82.37</v>
       </c>
       <c r="F1286" t="n">
-        <v>84560</v>
+        <v>83753</v>
       </c>
     </row>
     <row r="1287">
@@ -26161,10 +26161,10 @@
         <v>81.34</v>
       </c>
       <c r="E1287" t="n">
-        <v>82.68000000000001</v>
+        <v>82.70999999999999</v>
       </c>
       <c r="F1287" t="n">
-        <v>81459</v>
+        <v>80620</v>
       </c>
     </row>
     <row r="1288">
@@ -26241,10 +26241,10 @@
         <v>81.45</v>
       </c>
       <c r="E1291" t="n">
-        <v>82.51000000000001</v>
+        <v>82.63</v>
       </c>
       <c r="F1291" t="n">
-        <v>67848</v>
+        <v>67106</v>
       </c>
     </row>
     <row r="1292">
@@ -26261,10 +26261,10 @@
         <v>80.65000000000001</v>
       </c>
       <c r="E1292" t="n">
-        <v>80.84</v>
+        <v>80.88</v>
       </c>
       <c r="F1292" t="n">
-        <v>73168</v>
+        <v>72495</v>
       </c>
     </row>
     <row r="1293">
@@ -26341,10 +26341,10 @@
         <v>81.37</v>
       </c>
       <c r="E1296" t="n">
-        <v>81.8</v>
+        <v>81.70999999999999</v>
       </c>
       <c r="F1296" t="n">
-        <v>79642</v>
+        <v>78801</v>
       </c>
     </row>
     <row r="1297">
@@ -26361,10 +26361,10 @@
         <v>81.63</v>
       </c>
       <c r="E1297" t="n">
-        <v>83.12</v>
+        <v>83.19</v>
       </c>
       <c r="F1297" t="n">
-        <v>73275</v>
+        <v>72423</v>
       </c>
     </row>
     <row r="1298">
@@ -26441,10 +26441,10 @@
         <v>81.77</v>
       </c>
       <c r="E1301" t="n">
-        <v>82.87</v>
+        <v>82.52</v>
       </c>
       <c r="F1301" t="n">
-        <v>103853</v>
+        <v>102278</v>
       </c>
     </row>
     <row r="1302">
@@ -26461,10 +26461,10 @@
         <v>81.41</v>
       </c>
       <c r="E1302" t="n">
-        <v>81.55</v>
+        <v>81.66</v>
       </c>
       <c r="F1302" t="n">
-        <v>100115</v>
+        <v>99175</v>
       </c>
     </row>
     <row r="1303">
@@ -26532,19 +26532,19 @@
         <v>45365</v>
       </c>
       <c r="B1306" t="n">
-        <v>83.69</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="C1306" t="n">
         <v>85.18000000000001</v>
       </c>
       <c r="D1306" t="n">
-        <v>83.56999999999999</v>
+        <v>83.53</v>
       </c>
       <c r="E1306" t="n">
         <v>84.61</v>
       </c>
       <c r="F1306" t="n">
-        <v>71119</v>
+        <v>71844</v>
       </c>
     </row>
     <row r="1307">
@@ -26552,7 +26552,7 @@
         <v>45366</v>
       </c>
       <c r="B1307" t="n">
-        <v>84.68000000000001</v>
+        <v>84.65000000000001</v>
       </c>
       <c r="C1307" t="n">
         <v>85.09</v>
@@ -26564,7 +26564,7 @@
         <v>84.83</v>
       </c>
       <c r="F1307" t="n">
-        <v>74945</v>
+        <v>75864</v>
       </c>
     </row>
     <row r="1308">
@@ -26632,7 +26632,7 @@
         <v>45372</v>
       </c>
       <c r="B1311" t="n">
-        <v>85.81</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="C1311" t="n">
         <v>86.03</v>
@@ -26644,7 +26644,7 @@
         <v>84.95999999999999</v>
       </c>
       <c r="F1311" t="n">
-        <v>66113</v>
+        <v>67186</v>
       </c>
     </row>
     <row r="1312">
@@ -26652,7 +26652,7 @@
         <v>45373</v>
       </c>
       <c r="B1312" t="n">
-        <v>84.98999999999999</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="C1312" t="n">
         <v>85.58</v>
@@ -26664,7 +26664,7 @@
         <v>84.93000000000001</v>
       </c>
       <c r="F1312" t="n">
-        <v>53666</v>
+        <v>54286</v>
       </c>
     </row>
     <row r="1313">
@@ -26732,7 +26732,7 @@
         <v>45379</v>
       </c>
       <c r="B1316" t="n">
-        <v>85.65000000000001</v>
+        <v>85.56</v>
       </c>
       <c r="C1316" t="n">
         <v>86.89</v>
@@ -26744,7 +26744,7 @@
         <v>86.67</v>
       </c>
       <c r="F1316" t="n">
-        <v>56915</v>
+        <v>57372</v>
       </c>
     </row>
     <row r="1317">
@@ -26821,10 +26821,10 @@
         <v>88.43000000000001</v>
       </c>
       <c r="E1320" t="n">
-        <v>90.56</v>
+        <v>90.38</v>
       </c>
       <c r="F1320" t="n">
-        <v>75666</v>
+        <v>74470</v>
       </c>
     </row>
     <row r="1321">
@@ -26841,10 +26841,10 @@
         <v>90.18000000000001</v>
       </c>
       <c r="E1321" t="n">
-        <v>90.39</v>
+        <v>90.52</v>
       </c>
       <c r="F1321" t="n">
-        <v>80607</v>
+        <v>79937</v>
       </c>
     </row>
     <row r="1322">
@@ -26921,10 +26921,10 @@
         <v>88.87</v>
       </c>
       <c r="E1325" t="n">
-        <v>89.55</v>
+        <v>89.68000000000001</v>
       </c>
       <c r="F1325" t="n">
-        <v>107884</v>
+        <v>107040</v>
       </c>
     </row>
     <row r="1326">
@@ -26941,10 +26941,10 @@
         <v>89.45</v>
       </c>
       <c r="E1326" t="n">
-        <v>89.48999999999999</v>
+        <v>89.73</v>
       </c>
       <c r="F1326" t="n">
-        <v>109120</v>
+        <v>108331</v>
       </c>
     </row>
     <row r="1327">
@@ -27021,10 +27021,10 @@
         <v>85.63</v>
       </c>
       <c r="E1330" t="n">
-        <v>86.19</v>
+        <v>86.47</v>
       </c>
       <c r="F1330" t="n">
-        <v>108132</v>
+        <v>107464</v>
       </c>
     </row>
     <row r="1331">
@@ -27041,10 +27041,10 @@
         <v>85.61</v>
       </c>
       <c r="E1331" t="n">
-        <v>86.38</v>
+        <v>86.51000000000001</v>
       </c>
       <c r="F1331" t="n">
-        <v>144473</v>
+        <v>143518</v>
       </c>
     </row>
     <row r="1332">
@@ -27115,16 +27115,16 @@
         <v>86.88</v>
       </c>
       <c r="C1335" t="n">
-        <v>88</v>
+        <v>87.97</v>
       </c>
       <c r="D1335" t="n">
         <v>86.2</v>
       </c>
       <c r="E1335" t="n">
-        <v>87.83</v>
+        <v>87.95</v>
       </c>
       <c r="F1335" t="n">
-        <v>70059</v>
+        <v>69439</v>
       </c>
     </row>
     <row r="1336">
@@ -27141,10 +27141,10 @@
         <v>87.56999999999999</v>
       </c>
       <c r="E1336" t="n">
-        <v>87.89</v>
+        <v>87.98999999999999</v>
       </c>
       <c r="F1336" t="n">
-        <v>64445</v>
+        <v>63936</v>
       </c>
     </row>
     <row r="1337">
@@ -27221,10 +27221,10 @@
         <v>82.89</v>
       </c>
       <c r="E1340" t="n">
-        <v>83.48</v>
+        <v>83.47</v>
       </c>
       <c r="F1340" t="n">
-        <v>101847</v>
+        <v>100961</v>
       </c>
     </row>
     <row r="1341">
@@ -27238,13 +27238,13 @@
         <v>84.18000000000001</v>
       </c>
       <c r="D1341" t="n">
-        <v>82.53</v>
+        <v>82.65000000000001</v>
       </c>
       <c r="E1341" t="n">
-        <v>82.54000000000001</v>
+        <v>82.77</v>
       </c>
       <c r="F1341" t="n">
-        <v>83584</v>
+        <v>82987</v>
       </c>
     </row>
     <row r="1342">
@@ -27321,10 +27321,10 @@
         <v>83.18000000000001</v>
       </c>
       <c r="E1345" t="n">
-        <v>83.77</v>
+        <v>83.91</v>
       </c>
       <c r="F1345" t="n">
-        <v>67737</v>
+        <v>67201</v>
       </c>
     </row>
     <row r="1346">
@@ -27338,13 +27338,13 @@
         <v>84.23</v>
       </c>
       <c r="D1346" t="n">
-        <v>82.36</v>
+        <v>82.5</v>
       </c>
       <c r="E1346" t="n">
-        <v>82.36</v>
+        <v>82.61</v>
       </c>
       <c r="F1346" t="n">
-        <v>63117</v>
+        <v>62356</v>
       </c>
     </row>
     <row r="1347">
@@ -27421,10 +27421,10 @@
         <v>82.02</v>
       </c>
       <c r="E1350" t="n">
-        <v>82.98999999999999</v>
+        <v>83.04000000000001</v>
       </c>
       <c r="F1350" t="n">
-        <v>65759</v>
+        <v>65306</v>
       </c>
     </row>
     <row r="1351">
@@ -27441,10 +27441,10 @@
         <v>82.81999999999999</v>
       </c>
       <c r="E1351" t="n">
-        <v>83.56</v>
+        <v>83.68000000000001</v>
       </c>
       <c r="F1351" t="n">
-        <v>61133</v>
+        <v>60667</v>
       </c>
     </row>
     <row r="1352">
@@ -27521,10 +27521,10 @@
         <v>80.7</v>
       </c>
       <c r="E1355" t="n">
-        <v>81.06999999999999</v>
+        <v>81.09</v>
       </c>
       <c r="F1355" t="n">
-        <v>69958</v>
+        <v>68901</v>
       </c>
     </row>
     <row r="1356">
@@ -27541,10 +27541,10 @@
         <v>80.42</v>
       </c>
       <c r="E1356" t="n">
-        <v>81.79000000000001</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="F1356" t="n">
-        <v>56381</v>
+        <v>56045</v>
       </c>
     </row>
     <row r="1357">
@@ -27618,13 +27618,13 @@
         <v>83.51000000000001</v>
       </c>
       <c r="D1360" t="n">
-        <v>81.72</v>
+        <v>81.77</v>
       </c>
       <c r="E1360" t="n">
-        <v>81.73</v>
+        <v>81.88</v>
       </c>
       <c r="F1360" t="n">
-        <v>81864</v>
+        <v>81262</v>
       </c>
     </row>
     <row r="1361">
@@ -27641,10 +27641,10 @@
         <v>80.69</v>
       </c>
       <c r="E1361" t="n">
-        <v>81.09</v>
+        <v>81.22</v>
       </c>
       <c r="F1361" t="n">
-        <v>87130</v>
+        <v>86335</v>
       </c>
     </row>
     <row r="1362">
@@ -27721,10 +27721,10 @@
         <v>78.23999999999999</v>
       </c>
       <c r="E1365" t="n">
-        <v>79.69</v>
+        <v>79.73</v>
       </c>
       <c r="F1365" t="n">
-        <v>72677</v>
+        <v>72035</v>
       </c>
     </row>
     <row r="1366">
@@ -27741,10 +27741,10 @@
         <v>79.18000000000001</v>
       </c>
       <c r="E1366" t="n">
-        <v>79.23999999999999</v>
+        <v>79.27</v>
       </c>
       <c r="F1366" t="n">
-        <v>77440</v>
+        <v>76576</v>
       </c>
     </row>
     <row r="1367">
@@ -27821,10 +27821,10 @@
         <v>81.53</v>
       </c>
       <c r="E1370" t="n">
-        <v>81.68000000000001</v>
+        <v>81.98</v>
       </c>
       <c r="F1370" t="n">
-        <v>79567</v>
+        <v>78296</v>
       </c>
     </row>
     <row r="1371">
@@ -27841,10 +27841,10 @@
         <v>81.64</v>
       </c>
       <c r="E1371" t="n">
-        <v>82.06</v>
+        <v>82.2</v>
       </c>
       <c r="F1371" t="n">
-        <v>75768</v>
+        <v>75030</v>
       </c>
     </row>
     <row r="1372">
@@ -27921,10 +27921,10 @@
         <v>84.28</v>
       </c>
       <c r="E1375" t="n">
-        <v>84.7</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="F1375" t="n">
-        <v>59846</v>
+        <v>59448</v>
       </c>
     </row>
     <row r="1376">
@@ -27941,10 +27941,10 @@
         <v>84</v>
       </c>
       <c r="E1376" t="n">
-        <v>84.16</v>
+        <v>84.31</v>
       </c>
       <c r="F1376" t="n">
-        <v>60278</v>
+        <v>59797</v>
       </c>
     </row>
     <row r="1377">
@@ -28021,10 +28021,10 @@
         <v>84.01000000000001</v>
       </c>
       <c r="E1380" t="n">
-        <v>85.04000000000001</v>
+        <v>85.25</v>
       </c>
       <c r="F1380" t="n">
-        <v>64909</v>
+        <v>64362</v>
       </c>
     </row>
     <row r="1381">
@@ -28041,10 +28041,10 @@
         <v>84.39</v>
       </c>
       <c r="E1381" t="n">
-        <v>84.65000000000001</v>
+        <v>84.79000000000001</v>
       </c>
       <c r="F1381" t="n">
-        <v>69862</v>
+        <v>69177</v>
       </c>
     </row>
     <row r="1382">
@@ -28141,10 +28141,10 @@
         <v>86.17</v>
       </c>
       <c r="E1386" t="n">
-        <v>86.43000000000001</v>
+        <v>86.31999999999999</v>
       </c>
       <c r="F1386" t="n">
-        <v>68965</v>
+        <v>67919</v>
       </c>
     </row>
     <row r="1387">
@@ -28221,10 +28221,10 @@
         <v>84.16</v>
       </c>
       <c r="E1390" t="n">
-        <v>84.90000000000001</v>
+        <v>85.19</v>
       </c>
       <c r="F1390" t="n">
-        <v>78990</v>
+        <v>78243</v>
       </c>
     </row>
     <row r="1391">
@@ -28238,13 +28238,13 @@
         <v>85.67</v>
       </c>
       <c r="D1391" t="n">
-        <v>84.31999999999999</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="E1391" t="n">
-        <v>84.31999999999999</v>
+        <v>84.5</v>
       </c>
       <c r="F1391" t="n">
-        <v>74302</v>
+        <v>73607</v>
       </c>
     </row>
     <row r="1392">
@@ -28321,10 +28321,10 @@
         <v>83.41</v>
       </c>
       <c r="E1395" t="n">
-        <v>83.76000000000001</v>
+        <v>83.72</v>
       </c>
       <c r="F1395" t="n">
-        <v>69797</v>
+        <v>68620</v>
       </c>
     </row>
     <row r="1396">
@@ -28338,13 +28338,13 @@
         <v>84.41</v>
       </c>
       <c r="D1396" t="n">
-        <v>81.64</v>
+        <v>81.7</v>
       </c>
       <c r="E1396" t="n">
-        <v>81.64</v>
+        <v>81.89</v>
       </c>
       <c r="F1396" t="n">
-        <v>72736</v>
+        <v>72020</v>
       </c>
     </row>
     <row r="1397">
@@ -28421,10 +28421,10 @@
         <v>79.28</v>
       </c>
       <c r="E1400" t="n">
-        <v>81.37</v>
+        <v>81.33</v>
       </c>
       <c r="F1400" t="n">
-        <v>69789</v>
+        <v>69150</v>
       </c>
     </row>
     <row r="1401">
@@ -28441,10 +28441,10 @@
         <v>79.39</v>
       </c>
       <c r="E1401" t="n">
-        <v>79.48999999999999</v>
+        <v>79.92</v>
       </c>
       <c r="F1401" t="n">
-        <v>65748</v>
+        <v>64725</v>
       </c>
     </row>
     <row r="1402">
@@ -28521,10 +28521,10 @@
         <v>79.3</v>
       </c>
       <c r="E1405" t="n">
-        <v>79.83</v>
+        <v>80</v>
       </c>
       <c r="F1405" t="n">
-        <v>105741</v>
+        <v>104482</v>
       </c>
     </row>
     <row r="1406">
@@ -28541,10 +28541,10 @@
         <v>76.26000000000001</v>
       </c>
       <c r="E1406" t="n">
-        <v>77.14</v>
+        <v>77.08</v>
       </c>
       <c r="F1406" t="n">
-        <v>125792</v>
+        <v>124356</v>
       </c>
     </row>
     <row r="1407">
@@ -28621,10 +28621,10 @@
         <v>77.33</v>
       </c>
       <c r="E1410" t="n">
-        <v>78.59</v>
+        <v>78.73999999999999</v>
       </c>
       <c r="F1410" t="n">
-        <v>113892</v>
+        <v>113028</v>
       </c>
     </row>
     <row r="1411">
@@ -28641,10 +28641,10 @@
         <v>78.43000000000001</v>
       </c>
       <c r="E1411" t="n">
-        <v>79.27</v>
+        <v>79.34</v>
       </c>
       <c r="F1411" t="n">
-        <v>87467</v>
+        <v>86405</v>
       </c>
     </row>
     <row r="1412">
@@ -28721,10 +28721,10 @@
         <v>79.11</v>
       </c>
       <c r="E1415" t="n">
-        <v>80.26000000000001</v>
+        <v>80.31999999999999</v>
       </c>
       <c r="F1415" t="n">
-        <v>79567</v>
+        <v>78757</v>
       </c>
     </row>
     <row r="1416">
@@ -28741,10 +28741,10 @@
         <v>78.09</v>
       </c>
       <c r="E1416" t="n">
-        <v>78.94</v>
+        <v>79.22</v>
       </c>
       <c r="F1416" t="n">
-        <v>82030</v>
+        <v>81009</v>
       </c>
     </row>
     <row r="1417">
@@ -28821,10 +28821,10 @@
         <v>75.25</v>
       </c>
       <c r="E1420" t="n">
-        <v>76.42</v>
+        <v>76.47</v>
       </c>
       <c r="F1420" t="n">
-        <v>79873</v>
+        <v>79280</v>
       </c>
     </row>
     <row r="1421">
@@ -28841,10 +28841,10 @@
         <v>76.40000000000001</v>
       </c>
       <c r="E1421" t="n">
-        <v>78.13</v>
+        <v>78.17</v>
       </c>
       <c r="F1421" t="n">
-        <v>69081</v>
+        <v>68613</v>
       </c>
     </row>
     <row r="1422">
@@ -28921,10 +28921,10 @@
         <v>76.90000000000001</v>
       </c>
       <c r="E1425" t="n">
-        <v>78.72</v>
+        <v>78.81</v>
       </c>
       <c r="F1425" t="n">
-        <v>94397</v>
+        <v>93699</v>
       </c>
     </row>
     <row r="1426">
@@ -28941,10 +28941,10 @@
         <v>76.56</v>
       </c>
       <c r="E1426" t="n">
-        <v>76.77</v>
+        <v>76.81</v>
       </c>
       <c r="F1426" t="n">
-        <v>109124</v>
+        <v>108329</v>
       </c>
     </row>
     <row r="1427">
@@ -29021,10 +29021,10 @@
         <v>72.20999999999999</v>
       </c>
       <c r="E1430" t="n">
-        <v>72.53</v>
+        <v>72.54000000000001</v>
       </c>
       <c r="F1430" t="n">
-        <v>109541</v>
+        <v>108713</v>
       </c>
     </row>
     <row r="1431">
@@ -29041,10 +29041,10 @@
         <v>70.45</v>
       </c>
       <c r="E1431" t="n">
-        <v>71.2</v>
+        <v>71.37</v>
       </c>
       <c r="F1431" t="n">
-        <v>116954</v>
+        <v>115759</v>
       </c>
     </row>
     <row r="1432">
@@ -29121,10 +29121,10 @@
         <v>70.31999999999999</v>
       </c>
       <c r="E1435" t="n">
-        <v>71.67</v>
+        <v>71.89</v>
       </c>
       <c r="F1435" t="n">
-        <v>115156</v>
+        <v>114181</v>
       </c>
     </row>
     <row r="1436">
@@ -29141,10 +29141,10 @@
         <v>71.09</v>
       </c>
       <c r="E1436" t="n">
-        <v>71.59999999999999</v>
+        <v>71.73</v>
       </c>
       <c r="F1436" t="n">
-        <v>99629</v>
+        <v>98569</v>
       </c>
     </row>
     <row r="1437">
@@ -29221,10 +29221,10 @@
         <v>72.26000000000001</v>
       </c>
       <c r="E1440" t="n">
-        <v>73.97</v>
+        <v>74.05</v>
       </c>
       <c r="F1440" t="n">
-        <v>89094</v>
+        <v>88395</v>
       </c>
     </row>
     <row r="1441">
@@ -29241,10 +29241,10 @@
         <v>73.28</v>
       </c>
       <c r="E1441" t="n">
-        <v>73.87</v>
+        <v>73.98</v>
       </c>
       <c r="F1441" t="n">
-        <v>72413</v>
+        <v>71635</v>
       </c>
     </row>
     <row r="1442">
@@ -29321,10 +29321,10 @@
         <v>70.20999999999999</v>
       </c>
       <c r="E1445" t="n">
-        <v>70.68000000000001</v>
+        <v>70.66</v>
       </c>
       <c r="F1445" t="n">
-        <v>155899</v>
+        <v>154979</v>
       </c>
     </row>
     <row r="1446">
@@ -29335,16 +29335,16 @@
         <v>70.68000000000001</v>
       </c>
       <c r="C1446" t="n">
-        <v>71.90000000000001</v>
+        <v>71.89</v>
       </c>
       <c r="D1446" t="n">
         <v>70.39</v>
       </c>
       <c r="E1446" t="n">
-        <v>71.79000000000001</v>
+        <v>71.81999999999999</v>
       </c>
       <c r="F1446" t="n">
-        <v>123787</v>
+        <v>122438</v>
       </c>
     </row>
     <row r="1447">
@@ -29421,10 +29421,10 @@
         <v>74.18000000000001</v>
       </c>
       <c r="E1450" t="n">
-        <v>77.28</v>
+        <v>77.58</v>
       </c>
       <c r="F1450" t="n">
-        <v>125075</v>
+        <v>123449</v>
       </c>
     </row>
     <row r="1451">
@@ -29441,10 +29441,10 @@
         <v>77.19</v>
       </c>
       <c r="E1451" t="n">
-        <v>77.73</v>
+        <v>77.87</v>
       </c>
       <c r="F1451" t="n">
-        <v>121412</v>
+        <v>120535</v>
       </c>
     </row>
     <row r="1452">
@@ -39044,7 +39044,27 @@
         <v>89.75</v>
       </c>
       <c r="F1931" t="n">
-        <v>111655</v>
+        <v>111654</v>
+      </c>
+    </row>
+    <row r="1932">
+      <c r="A1932" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B1932" t="n">
+        <v>89.76000000000001</v>
+      </c>
+      <c r="C1932" t="n">
+        <v>90.79000000000001</v>
+      </c>
+      <c r="D1932" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="E1932" t="n">
+        <v>90.13</v>
+      </c>
+      <c r="F1932" t="n">
+        <v>87714</v>
       </c>
     </row>
   </sheetData>

--- a/database/BRENT.xlsx
+++ b/database/BRENT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1932"/>
+  <dimension ref="A1:F1933"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39064,7 +39064,27 @@
         <v>90.13</v>
       </c>
       <c r="F1932" t="n">
-        <v>87714</v>
+        <v>87766</v>
+      </c>
+    </row>
+    <row r="1933">
+      <c r="A1933" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B1933" t="n">
+        <v>90.15000000000001</v>
+      </c>
+      <c r="C1933" t="n">
+        <v>91.34</v>
+      </c>
+      <c r="D1933" t="n">
+        <v>89.22</v>
+      </c>
+      <c r="E1933" t="n">
+        <v>90.13</v>
+      </c>
+      <c r="F1933" t="n">
+        <v>101698</v>
       </c>
     </row>
   </sheetData>

--- a/database/BRENT.xlsx
+++ b/database/BRENT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1933"/>
+  <dimension ref="A1:F1934"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3881,10 +3881,10 @@
         <v>60.96</v>
       </c>
       <c r="E173" t="n">
-        <v>61.74</v>
+        <v>61.65</v>
       </c>
       <c r="F173" t="n">
-        <v>7439</v>
+        <v>7745</v>
       </c>
     </row>
     <row r="174">
@@ -3952,7 +3952,7 @@
         <v>43769</v>
       </c>
       <c r="B177" t="n">
-        <v>60.17</v>
+        <v>60.27</v>
       </c>
       <c r="C177" t="n">
         <v>60.79</v>
@@ -3964,7 +3964,7 @@
         <v>59.46</v>
       </c>
       <c r="F177" t="n">
-        <v>20831</v>
+        <v>20603</v>
       </c>
     </row>
     <row r="178">
@@ -3972,7 +3972,7 @@
         <v>43770</v>
       </c>
       <c r="B178" t="n">
-        <v>59.42</v>
+        <v>59.64</v>
       </c>
       <c r="C178" t="n">
         <v>61.8</v>
@@ -3984,7 +3984,7 @@
         <v>61.65</v>
       </c>
       <c r="F178" t="n">
-        <v>18539</v>
+        <v>18281</v>
       </c>
     </row>
     <row r="179">
@@ -4061,10 +4061,10 @@
         <v>61.63</v>
       </c>
       <c r="E182" t="n">
-        <v>62.14</v>
+        <v>62.29</v>
       </c>
       <c r="F182" t="n">
-        <v>19306</v>
+        <v>19680</v>
       </c>
     </row>
     <row r="183">
@@ -4081,10 +4081,10 @@
         <v>60.65</v>
       </c>
       <c r="E183" t="n">
-        <v>62.61</v>
+        <v>62.64</v>
       </c>
       <c r="F183" t="n">
-        <v>21625</v>
+        <v>21863</v>
       </c>
     </row>
     <row r="184">
@@ -4161,10 +4161,10 @@
         <v>62.14</v>
       </c>
       <c r="E187" t="n">
-        <v>62.38</v>
+        <v>62.33</v>
       </c>
       <c r="F187" t="n">
-        <v>19157</v>
+        <v>19293</v>
       </c>
     </row>
     <row r="188">
@@ -4181,10 +4181,10 @@
         <v>61.69</v>
       </c>
       <c r="E188" t="n">
-        <v>63.32</v>
+        <v>63.41</v>
       </c>
       <c r="F188" t="n">
-        <v>15801</v>
+        <v>16092</v>
       </c>
     </row>
     <row r="189">
@@ -4261,10 +4261,10 @@
         <v>61.91</v>
       </c>
       <c r="E192" t="n">
-        <v>63.74</v>
+        <v>63.64</v>
       </c>
       <c r="F192" t="n">
-        <v>21582</v>
+        <v>21823</v>
       </c>
     </row>
     <row r="193">
@@ -4281,10 +4281,10 @@
         <v>61.92</v>
       </c>
       <c r="E193" t="n">
-        <v>62.58</v>
+        <v>62.52</v>
       </c>
       <c r="F193" t="n">
-        <v>17577</v>
+        <v>17794</v>
       </c>
     </row>
     <row r="194">
@@ -4461,10 +4461,10 @@
         <v>62.73</v>
       </c>
       <c r="E202" t="n">
-        <v>63.33</v>
+        <v>63.26</v>
       </c>
       <c r="F202" t="n">
-        <v>24042</v>
+        <v>24300</v>
       </c>
     </row>
     <row r="203">
@@ -4481,10 +4481,10 @@
         <v>62.82</v>
       </c>
       <c r="E203" t="n">
-        <v>64.22</v>
+        <v>64.34</v>
       </c>
       <c r="F203" t="n">
-        <v>22359</v>
+        <v>22572</v>
       </c>
     </row>
     <row r="204">
@@ -4561,10 +4561,10 @@
         <v>63.86</v>
       </c>
       <c r="E207" t="n">
-        <v>64.31</v>
+        <v>64.28</v>
       </c>
       <c r="F207" t="n">
-        <v>18198</v>
+        <v>18454</v>
       </c>
     </row>
     <row r="208">
@@ -4581,10 +4581,10 @@
         <v>64.48</v>
       </c>
       <c r="E208" t="n">
-        <v>64.88</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="F208" t="n">
-        <v>21484</v>
+        <v>21671</v>
       </c>
     </row>
     <row r="209">
@@ -4661,10 +4661,10 @@
         <v>66.02</v>
       </c>
       <c r="E212" t="n">
-        <v>66.45</v>
+        <v>66.53</v>
       </c>
       <c r="F212" t="n">
-        <v>10932</v>
+        <v>11180</v>
       </c>
     </row>
     <row r="213">
@@ -4681,10 +4681,10 @@
         <v>65.72</v>
       </c>
       <c r="E213" t="n">
-        <v>65.98</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="F213" t="n">
-        <v>14693</v>
+        <v>14806</v>
       </c>
     </row>
     <row r="214">
@@ -4741,10 +4741,10 @@
         <v>66.09</v>
       </c>
       <c r="E216" t="n">
-        <v>66.65000000000001</v>
+        <v>66.75</v>
       </c>
       <c r="F216" t="n">
-        <v>9409</v>
+        <v>9613</v>
       </c>
     </row>
     <row r="217">
@@ -4761,10 +4761,10 @@
         <v>66.34</v>
       </c>
       <c r="E217" t="n">
-        <v>66.81</v>
+        <v>66.84</v>
       </c>
       <c r="F217" t="n">
-        <v>11272</v>
+        <v>11398</v>
       </c>
     </row>
     <row r="218">
@@ -4821,10 +4821,10 @@
         <v>65.7</v>
       </c>
       <c r="E220" t="n">
-        <v>66.19</v>
+        <v>66.23</v>
       </c>
       <c r="F220" t="n">
-        <v>15153</v>
+        <v>15351</v>
       </c>
     </row>
     <row r="221">
@@ -4841,10 +4841,10 @@
         <v>66.19</v>
       </c>
       <c r="E221" t="n">
-        <v>68.55</v>
+        <v>68.59</v>
       </c>
       <c r="F221" t="n">
-        <v>35427</v>
+        <v>35609</v>
       </c>
     </row>
     <row r="222">
@@ -4924,7 +4924,7 @@
         <v>65.38</v>
       </c>
       <c r="F225" t="n">
-        <v>25682</v>
+        <v>25951</v>
       </c>
     </row>
     <row r="226">
@@ -4944,7 +4944,7 @@
         <v>65</v>
       </c>
       <c r="F226" t="n">
-        <v>20016</v>
+        <v>20436</v>
       </c>
     </row>
     <row r="227">
@@ -5021,10 +5021,10 @@
         <v>63.89</v>
       </c>
       <c r="E230" t="n">
-        <v>64.64</v>
+        <v>64.7</v>
       </c>
       <c r="F230" t="n">
-        <v>16107</v>
+        <v>16472</v>
       </c>
     </row>
     <row r="231">
@@ -5041,10 +5041,10 @@
         <v>64.45</v>
       </c>
       <c r="E231" t="n">
-        <v>64.95</v>
+        <v>65.08</v>
       </c>
       <c r="F231" t="n">
-        <v>16060</v>
+        <v>16251</v>
       </c>
     </row>
     <row r="232">
@@ -5121,10 +5121,10 @@
         <v>61.24</v>
       </c>
       <c r="E235" t="n">
-        <v>61.97</v>
+        <v>62.11</v>
       </c>
       <c r="F235" t="n">
-        <v>22982</v>
+        <v>23208</v>
       </c>
     </row>
     <row r="236">
@@ -5141,10 +5141,10 @@
         <v>60.24</v>
       </c>
       <c r="E236" t="n">
-        <v>60.82</v>
+        <v>60.64</v>
       </c>
       <c r="F236" t="n">
-        <v>21411</v>
+        <v>21687</v>
       </c>
     </row>
     <row r="237">
@@ -5221,10 +5221,10 @@
         <v>56.73</v>
       </c>
       <c r="E240" t="n">
-        <v>58.03</v>
+        <v>58.2</v>
       </c>
       <c r="F240" t="n">
-        <v>28317</v>
+        <v>28894</v>
       </c>
     </row>
     <row r="241">
@@ -5244,7 +5244,7 @@
         <v>56.63</v>
       </c>
       <c r="F241" t="n">
-        <v>30854</v>
+        <v>31264</v>
       </c>
     </row>
     <row r="242">
@@ -5321,10 +5321,10 @@
         <v>54.24</v>
       </c>
       <c r="E245" t="n">
-        <v>55.07</v>
+        <v>55.14</v>
       </c>
       <c r="F245" t="n">
-        <v>31638</v>
+        <v>31917</v>
       </c>
     </row>
     <row r="246">
@@ -5341,10 +5341,10 @@
         <v>54.2</v>
       </c>
       <c r="E246" t="n">
-        <v>54.48</v>
+        <v>54.45</v>
       </c>
       <c r="F246" t="n">
-        <v>25828</v>
+        <v>26144</v>
       </c>
     </row>
     <row r="247">
@@ -5421,10 +5421,10 @@
         <v>54.95</v>
       </c>
       <c r="E250" t="n">
-        <v>56.51</v>
+        <v>56.4</v>
       </c>
       <c r="F250" t="n">
-        <v>24675</v>
+        <v>24914</v>
       </c>
     </row>
     <row r="251">
@@ -5441,10 +5441,10 @@
         <v>56.13</v>
       </c>
       <c r="E251" t="n">
-        <v>57.32</v>
+        <v>57.33</v>
       </c>
       <c r="F251" t="n">
-        <v>21410</v>
+        <v>21778</v>
       </c>
     </row>
     <row r="252">
@@ -5521,10 +5521,10 @@
         <v>58.89</v>
       </c>
       <c r="E255" t="n">
-        <v>59.28</v>
+        <v>59.03</v>
       </c>
       <c r="F255" t="n">
-        <v>23121</v>
+        <v>23391</v>
       </c>
     </row>
     <row r="256">
@@ -5541,10 +5541,10 @@
         <v>57.71</v>
       </c>
       <c r="E256" t="n">
-        <v>58.33</v>
+        <v>58.44</v>
       </c>
       <c r="F256" t="n">
-        <v>26663</v>
+        <v>26971</v>
       </c>
     </row>
     <row r="257">
@@ -5621,10 +5621,10 @@
         <v>50.38</v>
       </c>
       <c r="E260" t="n">
-        <v>51.35</v>
+        <v>50.95</v>
       </c>
       <c r="F260" t="n">
-        <v>51199</v>
+        <v>52807</v>
       </c>
     </row>
     <row r="261">
@@ -5641,10 +5641,10 @@
         <v>48.92</v>
       </c>
       <c r="E261" t="n">
-        <v>50.01</v>
+        <v>50.08</v>
       </c>
       <c r="F261" t="n">
-        <v>71739</v>
+        <v>72794</v>
       </c>
     </row>
     <row r="262">
@@ -5721,10 +5721,10 @@
         <v>49.67</v>
       </c>
       <c r="E265" t="n">
-        <v>49.95</v>
+        <v>50</v>
       </c>
       <c r="F265" t="n">
-        <v>42080</v>
+        <v>42678</v>
       </c>
     </row>
     <row r="266">
@@ -5741,10 +5741,10 @@
         <v>45.16</v>
       </c>
       <c r="E266" t="n">
-        <v>45.55</v>
+        <v>45.51</v>
       </c>
       <c r="F266" t="n">
-        <v>64437</v>
+        <v>65295</v>
       </c>
     </row>
     <row r="267">
@@ -5812,7 +5812,7 @@
         <v>43902</v>
       </c>
       <c r="B270" t="n">
-        <v>35.97</v>
+        <v>36.29</v>
       </c>
       <c r="C270" t="n">
         <v>36.45</v>
@@ -5824,7 +5824,7 @@
         <v>33.49</v>
       </c>
       <c r="F270" t="n">
-        <v>66181</v>
+        <v>64469</v>
       </c>
     </row>
     <row r="271">
@@ -6121,10 +6121,10 @@
         <v>26.12</v>
       </c>
       <c r="E285" t="n">
-        <v>30.29</v>
+        <v>29.96</v>
       </c>
       <c r="F285" t="n">
-        <v>210087</v>
+        <v>214756</v>
       </c>
     </row>
     <row r="286">
@@ -6135,16 +6135,16 @@
         <v>29.95</v>
       </c>
       <c r="C286" t="n">
-        <v>35.24</v>
+        <v>35.28</v>
       </c>
       <c r="D286" t="n">
         <v>28.9</v>
       </c>
       <c r="E286" t="n">
-        <v>34.72</v>
+        <v>35.16</v>
       </c>
       <c r="F286" t="n">
-        <v>275171</v>
+        <v>280402</v>
       </c>
     </row>
     <row r="287">
@@ -6221,10 +6221,10 @@
         <v>32.46</v>
       </c>
       <c r="E290" t="n">
-        <v>33.2</v>
+        <v>32.8</v>
       </c>
       <c r="F290" t="n">
-        <v>230614</v>
+        <v>236196</v>
       </c>
     </row>
     <row r="291">
@@ -6321,10 +6321,10 @@
         <v>29.42</v>
       </c>
       <c r="E295" t="n">
-        <v>30.65</v>
+        <v>30.59</v>
       </c>
       <c r="F295" t="n">
-        <v>146842</v>
+        <v>151526</v>
       </c>
     </row>
     <row r="296">
@@ -6341,10 +6341,10 @@
         <v>30.13</v>
       </c>
       <c r="E296" t="n">
-        <v>30.78</v>
+        <v>30.68</v>
       </c>
       <c r="F296" t="n">
-        <v>171223</v>
+        <v>174982</v>
       </c>
     </row>
     <row r="297">
@@ -6421,10 +6421,10 @@
         <v>23.38</v>
       </c>
       <c r="E300" t="n">
-        <v>24.74</v>
+        <v>24.73</v>
       </c>
       <c r="F300" t="n">
-        <v>213310</v>
+        <v>216653</v>
       </c>
     </row>
     <row r="301">
@@ -6441,10 +6441,10 @@
         <v>23.7</v>
       </c>
       <c r="E301" t="n">
-        <v>24.98</v>
+        <v>24.99</v>
       </c>
       <c r="F301" t="n">
-        <v>163124</v>
+        <v>166443</v>
       </c>
     </row>
     <row r="302">
@@ -6521,10 +6521,10 @@
         <v>24.33</v>
       </c>
       <c r="E305" t="n">
-        <v>26.83</v>
+        <v>26.85</v>
       </c>
       <c r="F305" t="n">
-        <v>224455</v>
+        <v>229615</v>
       </c>
     </row>
     <row r="306">
@@ -6541,10 +6541,10 @@
         <v>26.05</v>
       </c>
       <c r="E306" t="n">
-        <v>26.78</v>
+        <v>26.81</v>
       </c>
       <c r="F306" t="n">
-        <v>196748</v>
+        <v>199609</v>
       </c>
     </row>
     <row r="307">
@@ -6621,10 +6621,10 @@
         <v>29.4</v>
       </c>
       <c r="E310" t="n">
-        <v>29.48</v>
+        <v>29.65</v>
       </c>
       <c r="F310" t="n">
-        <v>225301</v>
+        <v>229585</v>
       </c>
     </row>
     <row r="311">
@@ -6641,10 +6641,10 @@
         <v>29.63</v>
       </c>
       <c r="E311" t="n">
-        <v>31.26</v>
+        <v>31.25</v>
       </c>
       <c r="F311" t="n">
-        <v>192233</v>
+        <v>195288</v>
       </c>
     </row>
     <row r="312">
@@ -6715,16 +6715,16 @@
         <v>29.73</v>
       </c>
       <c r="C315" t="n">
-        <v>31.65</v>
+        <v>31.75</v>
       </c>
       <c r="D315" t="n">
         <v>29.32</v>
       </c>
       <c r="E315" t="n">
-        <v>31.44</v>
+        <v>31.58</v>
       </c>
       <c r="F315" t="n">
-        <v>152193</v>
+        <v>156389</v>
       </c>
     </row>
     <row r="316">
@@ -6735,16 +6735,16 @@
         <v>31.58</v>
       </c>
       <c r="C316" t="n">
-        <v>32.96</v>
+        <v>33.06</v>
       </c>
       <c r="D316" t="n">
         <v>31.23</v>
       </c>
       <c r="E316" t="n">
-        <v>32.9</v>
+        <v>32.94</v>
       </c>
       <c r="F316" t="n">
-        <v>160121</v>
+        <v>163209</v>
       </c>
     </row>
     <row r="317">
@@ -6821,10 +6821,10 @@
         <v>35.92</v>
       </c>
       <c r="E320" t="n">
-        <v>36.38</v>
+        <v>36.3</v>
       </c>
       <c r="F320" t="n">
-        <v>157279</v>
+        <v>160329</v>
       </c>
     </row>
     <row r="321">
@@ -6841,10 +6841,10 @@
         <v>33.87</v>
       </c>
       <c r="E321" t="n">
-        <v>35.66</v>
+        <v>35.52</v>
       </c>
       <c r="F321" t="n">
-        <v>194062</v>
+        <v>198023</v>
       </c>
     </row>
     <row r="322">
@@ -6921,10 +6921,10 @@
         <v>34.37</v>
       </c>
       <c r="E325" t="n">
-        <v>35.89</v>
+        <v>35.98</v>
       </c>
       <c r="F325" t="n">
-        <v>208524</v>
+        <v>213086</v>
       </c>
     </row>
     <row r="326">
@@ -6941,10 +6941,10 @@
         <v>34.87</v>
       </c>
       <c r="E326" t="n">
-        <v>37.43</v>
+        <v>37.61</v>
       </c>
       <c r="F326" t="n">
-        <v>193664</v>
+        <v>198370</v>
       </c>
     </row>
     <row r="327">
@@ -7021,10 +7021,10 @@
         <v>39.05</v>
       </c>
       <c r="E330" t="n">
-        <v>39.78</v>
+        <v>39.92</v>
       </c>
       <c r="F330" t="n">
-        <v>158433</v>
+        <v>161661</v>
       </c>
     </row>
     <row r="331">
@@ -7041,10 +7041,10 @@
         <v>39.75</v>
       </c>
       <c r="E331" t="n">
-        <v>42.14</v>
+        <v>41.83</v>
       </c>
       <c r="F331" t="n">
-        <v>163467</v>
+        <v>167359</v>
       </c>
     </row>
     <row r="332">
@@ -7121,10 +7121,10 @@
         <v>37.96</v>
       </c>
       <c r="E335" t="n">
-        <v>38.36</v>
+        <v>38.41</v>
       </c>
       <c r="F335" t="n">
-        <v>221502</v>
+        <v>227925</v>
       </c>
     </row>
     <row r="336">
@@ -7141,10 +7141,10 @@
         <v>37.14</v>
       </c>
       <c r="E336" t="n">
-        <v>38.94</v>
+        <v>38.97</v>
       </c>
       <c r="F336" t="n">
-        <v>260674</v>
+        <v>263342</v>
       </c>
     </row>
     <row r="337">
@@ -7221,10 +7221,10 @@
         <v>40.05</v>
       </c>
       <c r="E340" t="n">
-        <v>41.37</v>
+        <v>41.33</v>
       </c>
       <c r="F340" t="n">
-        <v>161532</v>
+        <v>163774</v>
       </c>
     </row>
     <row r="341">
@@ -7241,10 +7241,10 @@
         <v>40.97</v>
       </c>
       <c r="E341" t="n">
-        <v>41.99</v>
+        <v>41.78</v>
       </c>
       <c r="F341" t="n">
-        <v>153177</v>
+        <v>156573</v>
       </c>
     </row>
     <row r="342">
@@ -7315,16 +7315,16 @@
         <v>40.45</v>
       </c>
       <c r="C345" t="n">
-        <v>41.51</v>
+        <v>41.59</v>
       </c>
       <c r="D345" t="n">
         <v>39.68</v>
       </c>
       <c r="E345" t="n">
-        <v>41.39</v>
+        <v>41.35</v>
       </c>
       <c r="F345" t="n">
-        <v>178413</v>
+        <v>181021</v>
       </c>
     </row>
     <row r="346">
@@ -7341,10 +7341,10 @@
         <v>40.25</v>
       </c>
       <c r="E346" t="n">
-        <v>40.58</v>
+        <v>40.57</v>
       </c>
       <c r="F346" t="n">
-        <v>157969</v>
+        <v>160433</v>
       </c>
     </row>
     <row r="347">
@@ -7421,10 +7421,10 @@
         <v>41.71</v>
       </c>
       <c r="E350" t="n">
-        <v>42.71</v>
+        <v>42.65</v>
       </c>
       <c r="F350" t="n">
-        <v>142409</v>
+        <v>144329</v>
       </c>
     </row>
     <row r="351">
@@ -7521,10 +7521,10 @@
         <v>41.99</v>
       </c>
       <c r="E355" t="n">
-        <v>42.32</v>
+        <v>42.35</v>
       </c>
       <c r="F355" t="n">
-        <v>133908</v>
+        <v>136451</v>
       </c>
     </row>
     <row r="356">
@@ -7541,10 +7541,10 @@
         <v>41.4</v>
       </c>
       <c r="E356" t="n">
-        <v>43.23</v>
+        <v>43.26</v>
       </c>
       <c r="F356" t="n">
-        <v>152491</v>
+        <v>154800</v>
       </c>
     </row>
     <row r="357">
@@ -7621,10 +7621,10 @@
         <v>43.19</v>
       </c>
       <c r="E360" t="n">
-        <v>43.36</v>
+        <v>43.28</v>
       </c>
       <c r="F360" t="n">
-        <v>99613</v>
+        <v>101544</v>
       </c>
     </row>
     <row r="361">
@@ -7641,10 +7641,10 @@
         <v>42.7</v>
       </c>
       <c r="E361" t="n">
-        <v>43.18</v>
+        <v>43.12</v>
       </c>
       <c r="F361" t="n">
-        <v>93740</v>
+        <v>95049</v>
       </c>
     </row>
     <row r="362">
@@ -7721,10 +7721,10 @@
         <v>43.42</v>
       </c>
       <c r="E365" t="n">
-        <v>43.82</v>
+        <v>43.53</v>
       </c>
       <c r="F365" t="n">
-        <v>109900</v>
+        <v>112495</v>
       </c>
     </row>
     <row r="366">
@@ -7741,10 +7741,10 @@
         <v>43.18</v>
       </c>
       <c r="E366" t="n">
-        <v>43.67</v>
+        <v>43.62</v>
       </c>
       <c r="F366" t="n">
-        <v>115737</v>
+        <v>117377</v>
       </c>
     </row>
     <row r="367">
@@ -7821,10 +7821,10 @@
         <v>41.95</v>
       </c>
       <c r="E370" t="n">
-        <v>43.43</v>
+        <v>43.56</v>
       </c>
       <c r="F370" t="n">
-        <v>113377</v>
+        <v>117072</v>
       </c>
     </row>
     <row r="371">
@@ -7841,10 +7841,10 @@
         <v>42.94</v>
       </c>
       <c r="E371" t="n">
-        <v>43.65</v>
+        <v>43.59</v>
       </c>
       <c r="F371" t="n">
-        <v>127155</v>
+        <v>128800</v>
       </c>
     </row>
     <row r="372">
@@ -7921,10 +7921,10 @@
         <v>44.96</v>
       </c>
       <c r="E375" t="n">
-        <v>45.28</v>
+        <v>45.13</v>
       </c>
       <c r="F375" t="n">
-        <v>120720</v>
+        <v>122044</v>
       </c>
     </row>
     <row r="376">
@@ -7941,10 +7941,10 @@
         <v>44.4</v>
       </c>
       <c r="E376" t="n">
-        <v>44.76</v>
+        <v>44.71</v>
       </c>
       <c r="F376" t="n">
-        <v>119541</v>
+        <v>120731</v>
       </c>
     </row>
     <row r="377">
@@ -8021,10 +8021,10 @@
         <v>45.07</v>
       </c>
       <c r="E380" t="n">
-        <v>45.3</v>
+        <v>45.24</v>
       </c>
       <c r="F380" t="n">
-        <v>90204</v>
+        <v>91702</v>
       </c>
     </row>
     <row r="381">
@@ -8041,10 +8041,10 @@
         <v>44.77</v>
       </c>
       <c r="E381" t="n">
-        <v>45.2</v>
+        <v>45.19</v>
       </c>
       <c r="F381" t="n">
-        <v>83793</v>
+        <v>85013</v>
       </c>
     </row>
     <row r="382">
@@ -8121,10 +8121,10 @@
         <v>44.46</v>
       </c>
       <c r="E385" t="n">
-        <v>45.36</v>
+        <v>45.27</v>
       </c>
       <c r="F385" t="n">
-        <v>86301</v>
+        <v>87294</v>
       </c>
     </row>
     <row r="386">
@@ -8141,10 +8141,10 @@
         <v>44.09</v>
       </c>
       <c r="E386" t="n">
-        <v>44.79</v>
+        <v>44.69</v>
       </c>
       <c r="F386" t="n">
-        <v>77659</v>
+        <v>78965</v>
       </c>
     </row>
     <row r="387">
@@ -8224,7 +8224,7 @@
         <v>45.59</v>
       </c>
       <c r="F390" t="n">
-        <v>95873</v>
+        <v>96916</v>
       </c>
     </row>
     <row r="391">
@@ -8241,10 +8241,10 @@
         <v>45.36</v>
       </c>
       <c r="E391" t="n">
-        <v>45.89</v>
+        <v>45.85</v>
       </c>
       <c r="F391" t="n">
-        <v>81058</v>
+        <v>81841</v>
       </c>
     </row>
     <row r="392">
@@ -8321,10 +8321,10 @@
         <v>43.27</v>
       </c>
       <c r="E395" t="n">
-        <v>44.09</v>
+        <v>44.07</v>
       </c>
       <c r="F395" t="n">
-        <v>157249</v>
+        <v>158723</v>
       </c>
     </row>
     <row r="396">
@@ -8338,13 +8338,13 @@
         <v>44.69</v>
       </c>
       <c r="D396" t="n">
-        <v>42.45</v>
+        <v>42.42</v>
       </c>
       <c r="E396" t="n">
-        <v>42.53</v>
+        <v>42.43</v>
       </c>
       <c r="F396" t="n">
-        <v>160902</v>
+        <v>162787</v>
       </c>
     </row>
     <row r="397">
@@ -8418,13 +8418,13 @@
         <v>41.23</v>
       </c>
       <c r="D400" t="n">
-        <v>40.02</v>
+        <v>39.96</v>
       </c>
       <c r="E400" t="n">
-        <v>40.07</v>
+        <v>39.97</v>
       </c>
       <c r="F400" t="n">
-        <v>147551</v>
+        <v>149451</v>
       </c>
     </row>
     <row r="401">
@@ -8441,10 +8441,10 @@
         <v>39.68</v>
       </c>
       <c r="E401" t="n">
-        <v>40.24</v>
+        <v>40.02</v>
       </c>
       <c r="F401" t="n">
-        <v>133943</v>
+        <v>135456</v>
       </c>
     </row>
     <row r="402">
@@ -8521,10 +8521,10 @@
         <v>41.89</v>
       </c>
       <c r="E405" t="n">
-        <v>43.67</v>
+        <v>43.58</v>
       </c>
       <c r="F405" t="n">
-        <v>141089</v>
+        <v>142611</v>
       </c>
     </row>
     <row r="406">
@@ -8541,10 +8541,10 @@
         <v>42.92</v>
       </c>
       <c r="E406" t="n">
-        <v>43.34</v>
+        <v>43.41</v>
       </c>
       <c r="F406" t="n">
-        <v>127380</v>
+        <v>129546</v>
       </c>
     </row>
     <row r="407">
@@ -8621,10 +8621,10 @@
         <v>41.68</v>
       </c>
       <c r="E410" t="n">
-        <v>42.27</v>
+        <v>42.16</v>
       </c>
       <c r="F410" t="n">
-        <v>132502</v>
+        <v>133961</v>
       </c>
     </row>
     <row r="411">
@@ -8641,10 +8641,10 @@
         <v>41.97</v>
       </c>
       <c r="E411" t="n">
-        <v>42.24</v>
+        <v>42.17</v>
       </c>
       <c r="F411" t="n">
-        <v>100264</v>
+        <v>102107</v>
       </c>
     </row>
     <row r="412">
@@ -8721,10 +8721,10 @@
         <v>39.98</v>
       </c>
       <c r="E415" t="n">
-        <v>40.93</v>
+        <v>40.75</v>
       </c>
       <c r="F415" t="n">
-        <v>155461</v>
+        <v>157712</v>
       </c>
     </row>
     <row r="416">
@@ -8741,10 +8741,10 @@
         <v>38.88</v>
       </c>
       <c r="E416" t="n">
-        <v>39.23</v>
+        <v>39.15</v>
       </c>
       <c r="F416" t="n">
-        <v>188336</v>
+        <v>190634</v>
       </c>
     </row>
     <row r="417">
@@ -8821,10 +8821,10 @@
         <v>42.02</v>
       </c>
       <c r="E420" t="n">
-        <v>43.54</v>
+        <v>43.52</v>
       </c>
       <c r="F420" t="n">
-        <v>110782</v>
+        <v>112342</v>
       </c>
     </row>
     <row r="421">
@@ -8841,10 +8841,10 @@
         <v>42.78</v>
       </c>
       <c r="E421" t="n">
-        <v>42.96</v>
+        <v>42.89</v>
       </c>
       <c r="F421" t="n">
-        <v>108274</v>
+        <v>109695</v>
       </c>
     </row>
     <row r="422">
@@ -8921,10 +8921,10 @@
         <v>41.79</v>
       </c>
       <c r="E425" t="n">
-        <v>43.38</v>
+        <v>43.26</v>
       </c>
       <c r="F425" t="n">
-        <v>146298</v>
+        <v>147757</v>
       </c>
     </row>
     <row r="426">
@@ -8941,10 +8941,10 @@
         <v>42.47</v>
       </c>
       <c r="E426" t="n">
-        <v>43.02</v>
+        <v>42.95</v>
       </c>
       <c r="F426" t="n">
-        <v>129338</v>
+        <v>130839</v>
       </c>
     </row>
     <row r="427">
@@ -9021,10 +9021,10 @@
         <v>41.72</v>
       </c>
       <c r="E430" t="n">
-        <v>42.71</v>
+        <v>42.59</v>
       </c>
       <c r="F430" t="n">
-        <v>108471</v>
+        <v>110171</v>
       </c>
     </row>
     <row r="431">
@@ -9041,10 +9041,10 @@
         <v>41.76</v>
       </c>
       <c r="E431" t="n">
-        <v>41.93</v>
+        <v>41.85</v>
       </c>
       <c r="F431" t="n">
-        <v>95688</v>
+        <v>97195</v>
       </c>
     </row>
     <row r="432">
@@ -9112,7 +9112,7 @@
         <v>44133</v>
       </c>
       <c r="B435" t="n">
-        <v>39.52</v>
+        <v>39.76</v>
       </c>
       <c r="C435" t="n">
         <v>39.97</v>
@@ -9124,7 +9124,7 @@
         <v>38.05</v>
       </c>
       <c r="F435" t="n">
-        <v>183949</v>
+        <v>179602</v>
       </c>
     </row>
     <row r="436">
@@ -9132,7 +9132,7 @@
         <v>44134</v>
       </c>
       <c r="B436" t="n">
-        <v>38.05</v>
+        <v>38.25</v>
       </c>
       <c r="C436" t="n">
         <v>38.72</v>
@@ -9144,7 +9144,7 @@
         <v>37.84</v>
       </c>
       <c r="F436" t="n">
-        <v>184633</v>
+        <v>181739</v>
       </c>
     </row>
     <row r="437">
@@ -9221,10 +9221,10 @@
         <v>40.42</v>
       </c>
       <c r="E440" t="n">
-        <v>40.82</v>
+        <v>40.68</v>
       </c>
       <c r="F440" t="n">
-        <v>155706</v>
+        <v>157779</v>
       </c>
     </row>
     <row r="441">
@@ -9241,10 +9241,10 @@
         <v>39.46</v>
       </c>
       <c r="E441" t="n">
-        <v>39.84</v>
+        <v>39.71</v>
       </c>
       <c r="F441" t="n">
-        <v>150078</v>
+        <v>151438</v>
       </c>
     </row>
     <row r="442">
@@ -9318,13 +9318,13 @@
         <v>44.59</v>
       </c>
       <c r="D445" t="n">
-        <v>43.42</v>
+        <v>43.35</v>
       </c>
       <c r="E445" t="n">
-        <v>43.49</v>
+        <v>43.38</v>
       </c>
       <c r="F445" t="n">
-        <v>144322</v>
+        <v>146964</v>
       </c>
     </row>
     <row r="446">
@@ -9338,13 +9338,13 @@
         <v>43.45</v>
       </c>
       <c r="D446" t="n">
-        <v>42.77</v>
+        <v>42.68</v>
       </c>
       <c r="E446" t="n">
-        <v>42.88</v>
+        <v>42.69</v>
       </c>
       <c r="F446" t="n">
-        <v>112789</v>
+        <v>114191</v>
       </c>
     </row>
     <row r="447">
@@ -9421,10 +9421,10 @@
         <v>43.87</v>
       </c>
       <c r="E450" t="n">
-        <v>44.44</v>
+        <v>44.21</v>
       </c>
       <c r="F450" t="n">
-        <v>111013</v>
+        <v>112468</v>
       </c>
     </row>
     <row r="451">
@@ -9441,10 +9441,10 @@
         <v>44.15</v>
       </c>
       <c r="E451" t="n">
-        <v>45.06</v>
+        <v>45.07</v>
       </c>
       <c r="F451" t="n">
-        <v>88612</v>
+        <v>90427</v>
       </c>
     </row>
     <row r="452">
@@ -9624,7 +9624,7 @@
         <v>48.65</v>
       </c>
       <c r="F460" t="n">
-        <v>119976</v>
+        <v>122403</v>
       </c>
     </row>
     <row r="461">
@@ -9641,10 +9641,10 @@
         <v>48.77</v>
       </c>
       <c r="E461" t="n">
-        <v>48.97</v>
+        <v>48.96</v>
       </c>
       <c r="F461" t="n">
-        <v>124413</v>
+        <v>125701</v>
       </c>
     </row>
     <row r="462">
@@ -9721,10 +9721,10 @@
         <v>48.79</v>
       </c>
       <c r="E465" t="n">
-        <v>50.26</v>
+        <v>50.25</v>
       </c>
       <c r="F465" t="n">
-        <v>130125</v>
+        <v>132386</v>
       </c>
     </row>
     <row r="466">
@@ -9741,10 +9741,10 @@
         <v>49.67</v>
       </c>
       <c r="E466" t="n">
-        <v>49.94</v>
+        <v>49.86</v>
       </c>
       <c r="F466" t="n">
-        <v>123293</v>
+        <v>124721</v>
       </c>
     </row>
     <row r="467">
@@ -9821,10 +9821,10 @@
         <v>51.06</v>
       </c>
       <c r="E470" t="n">
-        <v>51.55</v>
+        <v>51.46</v>
       </c>
       <c r="F470" t="n">
-        <v>100894</v>
+        <v>102867</v>
       </c>
     </row>
     <row r="471">
@@ -9841,10 +9841,10 @@
         <v>51.16</v>
       </c>
       <c r="E471" t="n">
-        <v>52.19</v>
+        <v>52.23</v>
       </c>
       <c r="F471" t="n">
-        <v>96861</v>
+        <v>98705</v>
       </c>
     </row>
     <row r="472">
@@ -10081,10 +10081,10 @@
         <v>53.88</v>
       </c>
       <c r="E483" t="n">
-        <v>54.45</v>
+        <v>54.34</v>
       </c>
       <c r="F483" t="n">
-        <v>140683</v>
+        <v>142258</v>
       </c>
     </row>
     <row r="484">
@@ -10095,16 +10095,16 @@
         <v>54.46</v>
       </c>
       <c r="C484" t="n">
-        <v>56.06</v>
+        <v>56.2</v>
       </c>
       <c r="D484" t="n">
         <v>54.3</v>
       </c>
       <c r="E484" t="n">
-        <v>56.02</v>
+        <v>56.11</v>
       </c>
       <c r="F484" t="n">
-        <v>151805</v>
+        <v>155413</v>
       </c>
     </row>
     <row r="485">
@@ -10181,10 +10181,10 @@
         <v>55.21</v>
       </c>
       <c r="E488" t="n">
-        <v>56.3</v>
+        <v>56.37</v>
       </c>
       <c r="F488" t="n">
-        <v>123090</v>
+        <v>125098</v>
       </c>
     </row>
     <row r="489">
@@ -10201,10 +10201,10 @@
         <v>54.63</v>
       </c>
       <c r="E489" t="n">
-        <v>54.94</v>
+        <v>54.75</v>
       </c>
       <c r="F489" t="n">
-        <v>133988</v>
+        <v>135898</v>
       </c>
     </row>
     <row r="490">
@@ -10281,10 +10281,10 @@
         <v>55.38</v>
       </c>
       <c r="E493" t="n">
-        <v>55.86</v>
+        <v>55.84</v>
       </c>
       <c r="F493" t="n">
-        <v>103188</v>
+        <v>104851</v>
       </c>
     </row>
     <row r="494">
@@ -10301,10 +10301,10 @@
         <v>54.38</v>
       </c>
       <c r="E494" t="n">
-        <v>55.08</v>
+        <v>54.88</v>
       </c>
       <c r="F494" t="n">
-        <v>133367</v>
+        <v>135622</v>
       </c>
     </row>
     <row r="495">
@@ -10378,13 +10378,13 @@
         <v>56.16</v>
       </c>
       <c r="D498" t="n">
-        <v>54.93</v>
+        <v>54.84</v>
       </c>
       <c r="E498" t="n">
-        <v>55</v>
+        <v>54.84</v>
       </c>
       <c r="F498" t="n">
-        <v>160473</v>
+        <v>162289</v>
       </c>
     </row>
     <row r="499">
@@ -10401,10 +10401,10 @@
         <v>54.84</v>
       </c>
       <c r="E499" t="n">
-        <v>55</v>
+        <v>54.93</v>
       </c>
       <c r="F499" t="n">
-        <v>160923</v>
+        <v>163671</v>
       </c>
     </row>
     <row r="500">
@@ -10481,10 +10481,10 @@
         <v>57.93</v>
       </c>
       <c r="E503" t="n">
-        <v>58.79</v>
+        <v>58.87</v>
       </c>
       <c r="F503" t="n">
-        <v>123567</v>
+        <v>125851</v>
       </c>
     </row>
     <row r="504">
@@ -10501,10 +10501,10 @@
         <v>58.87</v>
       </c>
       <c r="E504" t="n">
-        <v>59.31</v>
+        <v>59.41</v>
       </c>
       <c r="F504" t="n">
-        <v>118436</v>
+        <v>120954</v>
       </c>
     </row>
     <row r="505">
@@ -10578,13 +10578,13 @@
         <v>61.23</v>
       </c>
       <c r="D508" t="n">
-        <v>60.5</v>
+        <v>60.44</v>
       </c>
       <c r="E508" t="n">
-        <v>60.6</v>
+        <v>60.52</v>
       </c>
       <c r="F508" t="n">
-        <v>104511</v>
+        <v>107974</v>
       </c>
     </row>
     <row r="509">
@@ -10604,7 +10604,7 @@
         <v>62.22</v>
       </c>
       <c r="F509" t="n">
-        <v>123306</v>
+        <v>126905</v>
       </c>
     </row>
     <row r="510">
@@ -10681,10 +10681,10 @@
         <v>62.54</v>
       </c>
       <c r="E513" t="n">
-        <v>62.75</v>
+        <v>62.88</v>
       </c>
       <c r="F513" t="n">
-        <v>170306</v>
+        <v>173632</v>
       </c>
     </row>
     <row r="514">
@@ -10701,10 +10701,10 @@
         <v>61.42</v>
       </c>
       <c r="E514" t="n">
-        <v>61.95</v>
+        <v>61.97</v>
       </c>
       <c r="F514" t="n">
-        <v>181146</v>
+        <v>184306</v>
       </c>
     </row>
     <row r="515">
@@ -10781,10 +10781,10 @@
         <v>65.55</v>
       </c>
       <c r="E518" t="n">
-        <v>65.86</v>
+        <v>65.97</v>
       </c>
       <c r="F518" t="n">
-        <v>210726</v>
+        <v>215533</v>
       </c>
     </row>
     <row r="519">
@@ -10801,10 +10801,10 @@
         <v>64.13</v>
       </c>
       <c r="E519" t="n">
-        <v>64.25</v>
+        <v>64.27</v>
       </c>
       <c r="F519" t="n">
-        <v>234931</v>
+        <v>239274</v>
       </c>
     </row>
     <row r="520">
@@ -10881,10 +10881,10 @@
         <v>63.17</v>
       </c>
       <c r="E523" t="n">
-        <v>66.94</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="F523" t="n">
-        <v>225843</v>
+        <v>230530</v>
       </c>
     </row>
     <row r="524">
@@ -10895,16 +10895,16 @@
         <v>66.86</v>
       </c>
       <c r="C524" t="n">
-        <v>69.31999999999999</v>
+        <v>69.41</v>
       </c>
       <c r="D524" t="n">
         <v>66.43000000000001</v>
       </c>
       <c r="E524" t="n">
-        <v>69.28</v>
+        <v>69.25</v>
       </c>
       <c r="F524" t="n">
-        <v>249828</v>
+        <v>253026</v>
       </c>
     </row>
     <row r="525">
@@ -10981,10 +10981,10 @@
         <v>67.68000000000001</v>
       </c>
       <c r="E528" t="n">
-        <v>69.40000000000001</v>
+        <v>69.17</v>
       </c>
       <c r="F528" t="n">
-        <v>160838</v>
+        <v>163581</v>
       </c>
     </row>
     <row r="529">
@@ -11001,10 +11001,10 @@
         <v>68.66</v>
       </c>
       <c r="E529" t="n">
-        <v>68.88</v>
+        <v>68.81</v>
       </c>
       <c r="F529" t="n">
-        <v>148823</v>
+        <v>151042</v>
       </c>
     </row>
     <row r="530">
@@ -11072,7 +11072,7 @@
         <v>44273</v>
       </c>
       <c r="B533" t="n">
-        <v>67.48</v>
+        <v>67.47</v>
       </c>
       <c r="C533" t="n">
         <v>67.83</v>
@@ -11084,7 +11084,7 @@
         <v>62.5</v>
       </c>
       <c r="F533" t="n">
-        <v>212082</v>
+        <v>209835</v>
       </c>
     </row>
     <row r="534">
@@ -11092,7 +11092,7 @@
         <v>44274</v>
       </c>
       <c r="B534" t="n">
-        <v>62.78</v>
+        <v>63.02</v>
       </c>
       <c r="C534" t="n">
         <v>64.73</v>
@@ -11104,7 +11104,7 @@
         <v>64.31999999999999</v>
       </c>
       <c r="F534" t="n">
-        <v>228148</v>
+        <v>223529</v>
       </c>
     </row>
     <row r="535">
@@ -11172,10 +11172,10 @@
         <v>44280</v>
       </c>
       <c r="B538" t="n">
-        <v>63.95</v>
+        <v>63.89</v>
       </c>
       <c r="C538" t="n">
-        <v>64.01000000000001</v>
+        <v>63.9</v>
       </c>
       <c r="D538" t="n">
         <v>60.82</v>
@@ -11184,7 +11184,7 @@
         <v>61.47</v>
       </c>
       <c r="F538" t="n">
-        <v>206155</v>
+        <v>203253</v>
       </c>
     </row>
     <row r="539">
@@ -11192,19 +11192,19 @@
         <v>44281</v>
       </c>
       <c r="B539" t="n">
-        <v>61.47</v>
+        <v>62.45</v>
       </c>
       <c r="C539" t="n">
         <v>64.73</v>
       </c>
       <c r="D539" t="n">
-        <v>61.47</v>
+        <v>62.07</v>
       </c>
       <c r="E539" t="n">
         <v>64.19</v>
       </c>
       <c r="F539" t="n">
-        <v>171041</v>
+        <v>167422</v>
       </c>
     </row>
     <row r="540">
@@ -11284,7 +11284,7 @@
         <v>64.51000000000001</v>
       </c>
       <c r="F543" t="n">
-        <v>197783</v>
+        <v>201289</v>
       </c>
     </row>
     <row r="544">
@@ -11361,10 +11361,10 @@
         <v>62.18</v>
       </c>
       <c r="E547" t="n">
-        <v>63.07</v>
+        <v>63.04</v>
       </c>
       <c r="F547" t="n">
-        <v>146277</v>
+        <v>149186</v>
       </c>
     </row>
     <row r="548">
@@ -11381,10 +11381,10 @@
         <v>62.33</v>
       </c>
       <c r="E548" t="n">
-        <v>62.81</v>
+        <v>62.76</v>
       </c>
       <c r="F548" t="n">
-        <v>119219</v>
+        <v>121247</v>
       </c>
     </row>
     <row r="549">
@@ -11461,10 +11461,10 @@
         <v>65.65000000000001</v>
       </c>
       <c r="E552" t="n">
-        <v>66.5</v>
+        <v>66.45</v>
       </c>
       <c r="F552" t="n">
-        <v>133306</v>
+        <v>135521</v>
       </c>
     </row>
     <row r="553">
@@ -11481,10 +11481,10 @@
         <v>66.11</v>
       </c>
       <c r="E553" t="n">
-        <v>66.40000000000001</v>
+        <v>66.31999999999999</v>
       </c>
       <c r="F553" t="n">
-        <v>120895</v>
+        <v>122938</v>
       </c>
     </row>
     <row r="554">
@@ -11564,7 +11564,7 @@
         <v>64.95</v>
       </c>
       <c r="F557" t="n">
-        <v>140975</v>
+        <v>143350</v>
       </c>
     </row>
     <row r="558">
@@ -11581,10 +11581,10 @@
         <v>64.52</v>
       </c>
       <c r="E558" t="n">
-        <v>65.45</v>
+        <v>65.31999999999999</v>
       </c>
       <c r="F558" t="n">
-        <v>124432</v>
+        <v>126302</v>
       </c>
     </row>
     <row r="559">
@@ -11661,10 +11661,10 @@
         <v>66.56</v>
       </c>
       <c r="E562" t="n">
-        <v>67.86</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="F562" t="n">
-        <v>157092</v>
+        <v>160482</v>
       </c>
     </row>
     <row r="563">
@@ -11681,10 +11681,10 @@
         <v>66.17</v>
       </c>
       <c r="E563" t="n">
-        <v>66.56</v>
+        <v>66.53</v>
       </c>
       <c r="F563" t="n">
-        <v>145779</v>
+        <v>148372</v>
       </c>
     </row>
     <row r="564">
@@ -11761,10 +11761,10 @@
         <v>67.77</v>
       </c>
       <c r="E567" t="n">
-        <v>68.05</v>
+        <v>68.03</v>
       </c>
       <c r="F567" t="n">
-        <v>153533</v>
+        <v>155507</v>
       </c>
     </row>
     <row r="568">
@@ -11784,7 +11784,7 @@
         <v>68.03</v>
       </c>
       <c r="F568" t="n">
-        <v>136012</v>
+        <v>139157</v>
       </c>
     </row>
     <row r="569">
@@ -11861,10 +11861,10 @@
         <v>66.34</v>
       </c>
       <c r="E572" t="n">
-        <v>66.83</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="F572" t="n">
-        <v>180093</v>
+        <v>182316</v>
       </c>
     </row>
     <row r="573">
@@ -11875,16 +11875,16 @@
         <v>66.81</v>
       </c>
       <c r="C573" t="n">
-        <v>68.52</v>
+        <v>68.63</v>
       </c>
       <c r="D573" t="n">
         <v>66.36</v>
       </c>
       <c r="E573" t="n">
-        <v>68.45</v>
+        <v>68.52</v>
       </c>
       <c r="F573" t="n">
-        <v>139950</v>
+        <v>142226</v>
       </c>
     </row>
     <row r="574">
@@ -11958,13 +11958,13 @@
         <v>67.02</v>
       </c>
       <c r="D577" t="n">
-        <v>64.73</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="E577" t="n">
-        <v>64.98999999999999</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="F577" t="n">
-        <v>164782</v>
+        <v>168733</v>
       </c>
     </row>
     <row r="578">
@@ -11981,10 +11981,10 @@
         <v>64.48</v>
       </c>
       <c r="E578" t="n">
-        <v>66.58</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="F578" t="n">
-        <v>153693</v>
+        <v>156317</v>
       </c>
     </row>
     <row r="579">
@@ -12055,16 +12055,16 @@
         <v>68.58</v>
       </c>
       <c r="C582" t="n">
-        <v>69.18000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="D582" t="n">
         <v>67.89</v>
       </c>
       <c r="E582" t="n">
-        <v>69.05</v>
+        <v>69.12</v>
       </c>
       <c r="F582" t="n">
-        <v>119490</v>
+        <v>122427</v>
       </c>
     </row>
     <row r="583">
@@ -12081,10 +12081,10 @@
         <v>68.48999999999999</v>
       </c>
       <c r="E583" t="n">
-        <v>68.89</v>
+        <v>68.88</v>
       </c>
       <c r="F583" t="n">
-        <v>119218</v>
+        <v>121324</v>
       </c>
     </row>
     <row r="584">
@@ -12161,10 +12161,10 @@
         <v>70.5</v>
       </c>
       <c r="E587" t="n">
-        <v>71.20999999999999</v>
+        <v>71.22</v>
       </c>
       <c r="F587" t="n">
-        <v>126247</v>
+        <v>128649</v>
       </c>
     </row>
     <row r="588">
@@ -12181,10 +12181,10 @@
         <v>70.58</v>
       </c>
       <c r="E588" t="n">
-        <v>71.47</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="F588" t="n">
-        <v>113793</v>
+        <v>117041</v>
       </c>
     </row>
     <row r="589">
@@ -12261,10 +12261,10 @@
         <v>70.66</v>
       </c>
       <c r="E592" t="n">
-        <v>72.09</v>
+        <v>71.95</v>
       </c>
       <c r="F592" t="n">
-        <v>146487</v>
+        <v>148450</v>
       </c>
     </row>
     <row r="593">
@@ -12284,7 +12284,7 @@
         <v>72.23999999999999</v>
       </c>
       <c r="F593" t="n">
-        <v>140128</v>
+        <v>142367</v>
       </c>
     </row>
     <row r="594">
@@ -12361,10 +12361,10 @@
         <v>71.41</v>
       </c>
       <c r="E597" t="n">
-        <v>72.45</v>
+        <v>72.44</v>
       </c>
       <c r="F597" t="n">
-        <v>175025</v>
+        <v>178094</v>
       </c>
     </row>
     <row r="598">
@@ -12381,10 +12381,10 @@
         <v>71.55</v>
       </c>
       <c r="E598" t="n">
-        <v>72.76000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="F598" t="n">
-        <v>147859</v>
+        <v>151345</v>
       </c>
     </row>
     <row r="599">
@@ -12461,10 +12461,10 @@
         <v>73.83</v>
       </c>
       <c r="E602" t="n">
-        <v>74.79000000000001</v>
+        <v>74.81</v>
       </c>
       <c r="F602" t="n">
-        <v>84577</v>
+        <v>85692</v>
       </c>
     </row>
     <row r="603">
@@ -12481,10 +12481,10 @@
         <v>74.14</v>
       </c>
       <c r="E603" t="n">
-        <v>75.27</v>
+        <v>75.28</v>
       </c>
       <c r="F603" t="n">
-        <v>77990</v>
+        <v>79112</v>
       </c>
     </row>
     <row r="604">
@@ -12561,10 +12561,10 @@
         <v>74.36</v>
       </c>
       <c r="E607" t="n">
-        <v>75.33</v>
+        <v>75.34</v>
       </c>
       <c r="F607" t="n">
-        <v>134296</v>
+        <v>135699</v>
       </c>
     </row>
     <row r="608">
@@ -12581,10 +12581,10 @@
         <v>75</v>
       </c>
       <c r="E608" t="n">
-        <v>76.02</v>
+        <v>75.81999999999999</v>
       </c>
       <c r="F608" t="n">
-        <v>102316</v>
+        <v>104256</v>
       </c>
     </row>
     <row r="609">
@@ -12655,16 +12655,16 @@
         <v>72.97</v>
       </c>
       <c r="C612" t="n">
-        <v>73.97</v>
+        <v>74.02</v>
       </c>
       <c r="D612" t="n">
         <v>71.73999999999999</v>
       </c>
       <c r="E612" t="n">
-        <v>73.92</v>
+        <v>73.95999999999999</v>
       </c>
       <c r="F612" t="n">
-        <v>136419</v>
+        <v>138030</v>
       </c>
     </row>
     <row r="613">
@@ -12681,10 +12681,10 @@
         <v>73.38</v>
       </c>
       <c r="E613" t="n">
-        <v>75.15000000000001</v>
+        <v>75.14</v>
       </c>
       <c r="F613" t="n">
-        <v>95892</v>
+        <v>96988</v>
       </c>
     </row>
     <row r="614">
@@ -12761,10 +12761,10 @@
         <v>72.70999999999999</v>
       </c>
       <c r="E617" t="n">
-        <v>72.79000000000001</v>
+        <v>72.72</v>
       </c>
       <c r="F617" t="n">
-        <v>132350</v>
+        <v>134216</v>
       </c>
     </row>
     <row r="618">
@@ -12781,10 +12781,10 @@
         <v>71.88</v>
       </c>
       <c r="E618" t="n">
-        <v>72.81</v>
+        <v>72.64</v>
       </c>
       <c r="F618" t="n">
-        <v>108307</v>
+        <v>110158</v>
       </c>
     </row>
     <row r="619">
@@ -12864,7 +12864,7 @@
         <v>73.01000000000001</v>
       </c>
       <c r="F622" t="n">
-        <v>113951</v>
+        <v>115159</v>
       </c>
     </row>
     <row r="623">
@@ -12875,16 +12875,16 @@
         <v>72.98</v>
       </c>
       <c r="C623" t="n">
-        <v>73.52</v>
+        <v>73.56999999999999</v>
       </c>
       <c r="D623" t="n">
         <v>72.70999999999999</v>
       </c>
       <c r="E623" t="n">
-        <v>73.44</v>
+        <v>73.5</v>
       </c>
       <c r="F623" t="n">
-        <v>83411</v>
+        <v>84579</v>
       </c>
     </row>
     <row r="624">
@@ -12961,10 +12961,10 @@
         <v>73.59999999999999</v>
       </c>
       <c r="E627" t="n">
-        <v>74.97</v>
+        <v>74.75</v>
       </c>
       <c r="F627" t="n">
-        <v>79720</v>
+        <v>81467</v>
       </c>
     </row>
     <row r="628">
@@ -12981,10 +12981,10 @@
         <v>74.26000000000001</v>
       </c>
       <c r="E628" t="n">
-        <v>74.98999999999999</v>
+        <v>74.95999999999999</v>
       </c>
       <c r="F628" t="n">
-        <v>83101</v>
+        <v>84253</v>
       </c>
     </row>
     <row r="629">
@@ -13061,10 +13061,10 @@
         <v>69.56</v>
       </c>
       <c r="E632" t="n">
-        <v>71.16</v>
+        <v>71</v>
       </c>
       <c r="F632" t="n">
-        <v>107034</v>
+        <v>108267</v>
       </c>
     </row>
     <row r="633">
@@ -13078,13 +13078,13 @@
         <v>72.22</v>
       </c>
       <c r="D633" t="n">
-        <v>70.12</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="E633" t="n">
-        <v>70.34999999999999</v>
+        <v>70.08</v>
       </c>
       <c r="F633" t="n">
-        <v>111453</v>
+        <v>113105</v>
       </c>
     </row>
     <row r="634">
@@ -13161,10 +13161,10 @@
         <v>70.41</v>
       </c>
       <c r="E637" t="n">
-        <v>70.90000000000001</v>
+        <v>70.86</v>
       </c>
       <c r="F637" t="n">
-        <v>95219</v>
+        <v>96203</v>
       </c>
     </row>
     <row r="638">
@@ -13181,10 +13181,10 @@
         <v>69.73999999999999</v>
       </c>
       <c r="E638" t="n">
-        <v>69.92</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="F638" t="n">
-        <v>93960</v>
+        <v>95696</v>
       </c>
     </row>
     <row r="639">
@@ -13261,10 +13261,10 @@
         <v>65.2</v>
       </c>
       <c r="E642" t="n">
-        <v>66.51000000000001</v>
+        <v>66.23</v>
       </c>
       <c r="F642" t="n">
-        <v>185678</v>
+        <v>187712</v>
       </c>
     </row>
     <row r="643">
@@ -13278,13 +13278,13 @@
         <v>66.54000000000001</v>
       </c>
       <c r="D643" t="n">
-        <v>64.61</v>
+        <v>64.53</v>
       </c>
       <c r="E643" t="n">
-        <v>64.62</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="F643" t="n">
-        <v>137258</v>
+        <v>138989</v>
       </c>
     </row>
     <row r="644">
@@ -13361,10 +13361,10 @@
         <v>69.73999999999999</v>
       </c>
       <c r="E647" t="n">
-        <v>70.56</v>
+        <v>70.45999999999999</v>
       </c>
       <c r="F647" t="n">
-        <v>113839</v>
+        <v>115965</v>
       </c>
     </row>
     <row r="648">
@@ -13381,10 +13381,10 @@
         <v>70.16</v>
       </c>
       <c r="E648" t="n">
-        <v>71.59999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="F648" t="n">
-        <v>99158</v>
+        <v>100455</v>
       </c>
     </row>
     <row r="649">
@@ -13461,10 +13461,10 @@
         <v>70.75</v>
       </c>
       <c r="E652" t="n">
-        <v>72.56999999999999</v>
+        <v>72.61</v>
       </c>
       <c r="F652" t="n">
-        <v>103772</v>
+        <v>105073</v>
       </c>
     </row>
     <row r="653">
@@ -13481,10 +13481,10 @@
         <v>72.20999999999999</v>
       </c>
       <c r="E653" t="n">
-        <v>72.36</v>
+        <v>72.20999999999999</v>
       </c>
       <c r="F653" t="n">
-        <v>110684</v>
+        <v>111688</v>
       </c>
     </row>
     <row r="654">
@@ -13561,10 +13561,10 @@
         <v>70.54000000000001</v>
       </c>
       <c r="E657" t="n">
-        <v>70.95</v>
+        <v>70.84</v>
       </c>
       <c r="F657" t="n">
-        <v>136836</v>
+        <v>138553</v>
       </c>
     </row>
     <row r="658">
@@ -13581,10 +13581,10 @@
         <v>70.59</v>
       </c>
       <c r="E658" t="n">
-        <v>72.44</v>
+        <v>72.51000000000001</v>
       </c>
       <c r="F658" t="n">
-        <v>106315</v>
+        <v>107925</v>
       </c>
     </row>
     <row r="659">
@@ -13661,10 +13661,10 @@
         <v>74.02</v>
       </c>
       <c r="E662" t="n">
-        <v>75.17</v>
+        <v>75.09</v>
       </c>
       <c r="F662" t="n">
-        <v>134873</v>
+        <v>136265</v>
       </c>
     </row>
     <row r="663">
@@ -13681,10 +13681,10 @@
         <v>74.06999999999999</v>
       </c>
       <c r="E663" t="n">
-        <v>74.79000000000001</v>
+        <v>74.67</v>
       </c>
       <c r="F663" t="n">
-        <v>129577</v>
+        <v>131243</v>
       </c>
     </row>
     <row r="664">
@@ -13764,7 +13764,7 @@
         <v>76.45</v>
       </c>
       <c r="F667" t="n">
-        <v>102612</v>
+        <v>104066</v>
       </c>
     </row>
     <row r="668">
@@ -13781,10 +13781,10 @@
         <v>76.09</v>
       </c>
       <c r="E668" t="n">
-        <v>77.15000000000001</v>
+        <v>77.13</v>
       </c>
       <c r="F668" t="n">
-        <v>93448</v>
+        <v>94529</v>
       </c>
     </row>
     <row r="669">
@@ -13861,10 +13861,10 @@
         <v>76.37</v>
       </c>
       <c r="E672" t="n">
-        <v>78.13</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="F672" t="n">
-        <v>180155</v>
+        <v>181989</v>
       </c>
     </row>
     <row r="673">
@@ -13881,10 +13881,10 @@
         <v>77.38</v>
       </c>
       <c r="E673" t="n">
-        <v>78.98999999999999</v>
+        <v>78.93000000000001</v>
       </c>
       <c r="F673" t="n">
-        <v>149729</v>
+        <v>151482</v>
       </c>
     </row>
     <row r="674">
@@ -13961,10 +13961,10 @@
         <v>78.78</v>
       </c>
       <c r="E677" t="n">
-        <v>82.16</v>
+        <v>82.08</v>
       </c>
       <c r="F677" t="n">
-        <v>151677</v>
+        <v>153620</v>
       </c>
     </row>
     <row r="678">
@@ -13981,10 +13981,10 @@
         <v>81.63</v>
       </c>
       <c r="E678" t="n">
-        <v>82.17</v>
+        <v>82.22</v>
       </c>
       <c r="F678" t="n">
-        <v>147722</v>
+        <v>149526</v>
       </c>
     </row>
     <row r="679">
@@ -14061,10 +14061,10 @@
         <v>82.76000000000001</v>
       </c>
       <c r="E682" t="n">
-        <v>83.69</v>
+        <v>83.67</v>
       </c>
       <c r="F682" t="n">
-        <v>120650</v>
+        <v>122153</v>
       </c>
     </row>
     <row r="683">
@@ -14081,10 +14081,10 @@
         <v>83.68000000000001</v>
       </c>
       <c r="E683" t="n">
-        <v>84.23</v>
+        <v>84.33</v>
       </c>
       <c r="F683" t="n">
-        <v>114060</v>
+        <v>116437</v>
       </c>
     </row>
     <row r="684">
@@ -14161,10 +14161,10 @@
         <v>82.73</v>
       </c>
       <c r="E687" t="n">
-        <v>84.15000000000001</v>
+        <v>84.09</v>
       </c>
       <c r="F687" t="n">
-        <v>121250</v>
+        <v>122966</v>
       </c>
     </row>
     <row r="688">
@@ -14175,16 +14175,16 @@
         <v>83.81999999999999</v>
       </c>
       <c r="C688" t="n">
-        <v>84.97</v>
+        <v>85.08</v>
       </c>
       <c r="D688" t="n">
         <v>83.18000000000001</v>
       </c>
       <c r="E688" t="n">
-        <v>84.97</v>
+        <v>84.83</v>
       </c>
       <c r="F688" t="n">
-        <v>111475</v>
+        <v>113449</v>
       </c>
     </row>
     <row r="689">
@@ -14261,10 +14261,10 @@
         <v>81.48</v>
       </c>
       <c r="E692" t="n">
-        <v>83.83</v>
+        <v>83.78</v>
       </c>
       <c r="F692" t="n">
-        <v>164605</v>
+        <v>167007</v>
       </c>
     </row>
     <row r="693">
@@ -14281,10 +14281,10 @@
         <v>82.39</v>
       </c>
       <c r="E693" t="n">
-        <v>83.55</v>
+        <v>83.41</v>
       </c>
       <c r="F693" t="n">
-        <v>132228</v>
+        <v>133535</v>
       </c>
     </row>
     <row r="694">
@@ -14352,7 +14352,7 @@
         <v>44504</v>
       </c>
       <c r="B697" t="n">
-        <v>81.12</v>
+        <v>80.83</v>
       </c>
       <c r="C697" t="n">
         <v>84.08</v>
@@ -14364,7 +14364,7 @@
         <v>80.54000000000001</v>
       </c>
       <c r="F697" t="n">
-        <v>171378</v>
+        <v>168783</v>
       </c>
     </row>
     <row r="698">
@@ -14372,7 +14372,7 @@
         <v>44505</v>
       </c>
       <c r="B698" t="n">
-        <v>80.95</v>
+        <v>81.04000000000001</v>
       </c>
       <c r="C698" t="n">
         <v>82.72</v>
@@ -14384,7 +14384,7 @@
         <v>81.93000000000001</v>
       </c>
       <c r="F698" t="n">
-        <v>166390</v>
+        <v>163172</v>
       </c>
     </row>
     <row r="699">
@@ -14461,10 +14461,10 @@
         <v>81.06</v>
       </c>
       <c r="E702" t="n">
-        <v>81.91</v>
+        <v>81.92</v>
       </c>
       <c r="F702" t="n">
-        <v>159955</v>
+        <v>161511</v>
       </c>
     </row>
     <row r="703">
@@ -14481,10 +14481,10 @@
         <v>80.63</v>
       </c>
       <c r="E703" t="n">
-        <v>81.41</v>
+        <v>81.29000000000001</v>
       </c>
       <c r="F703" t="n">
-        <v>133196</v>
+        <v>134507</v>
       </c>
     </row>
     <row r="704">
@@ -14561,10 +14561,10 @@
         <v>78.55</v>
       </c>
       <c r="E707" t="n">
-        <v>80.42</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="F707" t="n">
-        <v>131123</v>
+        <v>132952</v>
       </c>
     </row>
     <row r="708">
@@ -14581,10 +14581,10 @@
         <v>77.41</v>
       </c>
       <c r="E708" t="n">
-        <v>77.76000000000001</v>
+        <v>77.77</v>
       </c>
       <c r="F708" t="n">
-        <v>175625</v>
+        <v>177513</v>
       </c>
     </row>
     <row r="709">
@@ -14761,10 +14761,10 @@
         <v>65.67</v>
       </c>
       <c r="E717" t="n">
-        <v>69.94</v>
+        <v>70.36</v>
       </c>
       <c r="F717" t="n">
-        <v>237353</v>
+        <v>240359</v>
       </c>
     </row>
     <row r="718">
@@ -14781,10 +14781,10 @@
         <v>69.09999999999999</v>
       </c>
       <c r="E718" t="n">
-        <v>69.73</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="F718" t="n">
-        <v>205214</v>
+        <v>208893</v>
       </c>
     </row>
     <row r="719">
@@ -14858,13 +14858,13 @@
         <v>76.55</v>
       </c>
       <c r="D722" t="n">
-        <v>73.78</v>
+        <v>73.70999999999999</v>
       </c>
       <c r="E722" t="n">
-        <v>73.79000000000001</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="F722" t="n">
-        <v>140659</v>
+        <v>142264</v>
       </c>
     </row>
     <row r="723">
@@ -14881,10 +14881,10 @@
         <v>73.67</v>
       </c>
       <c r="E723" t="n">
-        <v>75.23</v>
+        <v>75.16</v>
       </c>
       <c r="F723" t="n">
-        <v>151698</v>
+        <v>153301</v>
       </c>
     </row>
     <row r="724">
@@ -14961,10 +14961,10 @@
         <v>73.88</v>
       </c>
       <c r="E727" t="n">
-        <v>74.63</v>
+        <v>74.48999999999999</v>
       </c>
       <c r="F727" t="n">
-        <v>140474</v>
+        <v>142563</v>
       </c>
     </row>
     <row r="728">
@@ -14981,10 +14981,10 @@
         <v>72.63</v>
       </c>
       <c r="E728" t="n">
-        <v>73.15000000000001</v>
+        <v>72.88</v>
       </c>
       <c r="F728" t="n">
-        <v>152160</v>
+        <v>154875</v>
       </c>
     </row>
     <row r="729">
@@ -15061,10 +15061,10 @@
         <v>74.72</v>
       </c>
       <c r="E732" t="n">
-        <v>76.63</v>
+        <v>76.52</v>
       </c>
       <c r="F732" t="n">
-        <v>100583</v>
+        <v>102802</v>
       </c>
     </row>
     <row r="733">
@@ -15161,10 +15161,10 @@
         <v>78.33</v>
       </c>
       <c r="E737" t="n">
-        <v>78.97</v>
+        <v>78.86</v>
       </c>
       <c r="F737" t="n">
-        <v>103669</v>
+        <v>105405</v>
       </c>
     </row>
     <row r="738">
@@ -15261,10 +15261,10 @@
         <v>79.36</v>
       </c>
       <c r="E742" t="n">
-        <v>81.65000000000001</v>
+        <v>81.70999999999999</v>
       </c>
       <c r="F742" t="n">
-        <v>185800</v>
+        <v>187943</v>
       </c>
     </row>
     <row r="743">
@@ -15281,10 +15281,10 @@
         <v>81.12</v>
       </c>
       <c r="E743" t="n">
-        <v>81.59999999999999</v>
+        <v>81.48</v>
       </c>
       <c r="F743" t="n">
-        <v>158852</v>
+        <v>160491</v>
       </c>
     </row>
     <row r="744">
@@ -15361,10 +15361,10 @@
         <v>83.34999999999999</v>
       </c>
       <c r="E747" t="n">
-        <v>83.45</v>
+        <v>83.61</v>
       </c>
       <c r="F747" t="n">
-        <v>145171</v>
+        <v>147527</v>
       </c>
     </row>
     <row r="748">
@@ -15375,16 +15375,16 @@
         <v>83.68000000000001</v>
       </c>
       <c r="C748" t="n">
-        <v>85.97</v>
+        <v>85.98999999999999</v>
       </c>
       <c r="D748" t="n">
         <v>83.53</v>
       </c>
       <c r="E748" t="n">
-        <v>85.91</v>
+        <v>85.77</v>
       </c>
       <c r="F748" t="n">
-        <v>171152</v>
+        <v>173518</v>
       </c>
     </row>
     <row r="749">
@@ -15458,13 +15458,13 @@
         <v>88.8</v>
       </c>
       <c r="D752" t="n">
-        <v>86.56999999999999</v>
+        <v>86.38</v>
       </c>
       <c r="E752" t="n">
-        <v>86.7</v>
+        <v>86.58</v>
       </c>
       <c r="F752" t="n">
-        <v>162890</v>
+        <v>169439</v>
       </c>
     </row>
     <row r="753">
@@ -15481,10 +15481,10 @@
         <v>85.02</v>
       </c>
       <c r="E753" t="n">
-        <v>86.98</v>
+        <v>86.92</v>
       </c>
       <c r="F753" t="n">
-        <v>223066</v>
+        <v>225683</v>
       </c>
     </row>
     <row r="754">
@@ -15561,10 +15561,10 @@
         <v>87.7</v>
       </c>
       <c r="E757" t="n">
-        <v>88.40000000000001</v>
+        <v>88.63</v>
       </c>
       <c r="F757" t="n">
-        <v>270152</v>
+        <v>275711</v>
       </c>
     </row>
     <row r="758">
@@ -15581,10 +15581,10 @@
         <v>88</v>
       </c>
       <c r="E758" t="n">
-        <v>88.73</v>
+        <v>88.81999999999999</v>
       </c>
       <c r="F758" t="n">
-        <v>275262</v>
+        <v>278896</v>
       </c>
     </row>
     <row r="759">
@@ -15655,16 +15655,16 @@
         <v>88.63</v>
       </c>
       <c r="C762" t="n">
-        <v>90.73999999999999</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="D762" t="n">
         <v>87.59999999999999</v>
       </c>
       <c r="E762" t="n">
-        <v>90.45999999999999</v>
+        <v>90.51000000000001</v>
       </c>
       <c r="F762" t="n">
-        <v>163057</v>
+        <v>168353</v>
       </c>
     </row>
     <row r="763">
@@ -15681,10 +15681,10 @@
         <v>90.67</v>
       </c>
       <c r="E763" t="n">
-        <v>92.54000000000001</v>
+        <v>92.14</v>
       </c>
       <c r="F763" t="n">
-        <v>177219</v>
+        <v>180147</v>
       </c>
     </row>
     <row r="764">
@@ -15761,10 +15761,10 @@
         <v>90.09999999999999</v>
       </c>
       <c r="E767" t="n">
-        <v>90.66</v>
+        <v>90.54000000000001</v>
       </c>
       <c r="F767" t="n">
-        <v>183590</v>
+        <v>186180</v>
       </c>
     </row>
     <row r="768">
@@ -15781,10 +15781,10 @@
         <v>89.66</v>
       </c>
       <c r="E768" t="n">
-        <v>93.81</v>
+        <v>93.8</v>
       </c>
       <c r="F768" t="n">
-        <v>189880</v>
+        <v>194729</v>
       </c>
     </row>
     <row r="769">
@@ -15861,10 +15861,10 @@
         <v>90.34999999999999</v>
       </c>
       <c r="E772" t="n">
-        <v>91.18000000000001</v>
+        <v>91.16</v>
       </c>
       <c r="F772" t="n">
-        <v>209775</v>
+        <v>212213</v>
       </c>
     </row>
     <row r="773">
@@ -15875,7 +15875,7 @@
         <v>90.76000000000001</v>
       </c>
       <c r="C773" t="n">
-        <v>92.15000000000001</v>
+        <v>92.28</v>
       </c>
       <c r="D773" t="n">
         <v>88.64</v>
@@ -15884,7 +15884,7 @@
         <v>91.81</v>
       </c>
       <c r="F773" t="n">
-        <v>190175</v>
+        <v>194995</v>
       </c>
     </row>
     <row r="774">
@@ -15961,10 +15961,10 @@
         <v>93.94</v>
       </c>
       <c r="E777" t="n">
-        <v>95.61</v>
+        <v>95.41</v>
       </c>
       <c r="F777" t="n">
-        <v>309076</v>
+        <v>313423</v>
       </c>
     </row>
     <row r="778">
@@ -15981,10 +15981,10 @@
         <v>92.55</v>
       </c>
       <c r="E778" t="n">
-        <v>94.69</v>
+        <v>94.23</v>
       </c>
       <c r="F778" t="n">
-        <v>233541</v>
+        <v>237786</v>
       </c>
     </row>
     <row r="779">
@@ -16061,10 +16061,10 @@
         <v>108.17</v>
       </c>
       <c r="E782" t="n">
-        <v>109.72</v>
+        <v>109.27</v>
       </c>
       <c r="F782" t="n">
-        <v>231064</v>
+        <v>233799</v>
       </c>
     </row>
     <row r="783">
@@ -16081,10 +16081,10 @@
         <v>108.47</v>
       </c>
       <c r="E783" t="n">
-        <v>117.14</v>
+        <v>116.7</v>
       </c>
       <c r="F783" t="n">
-        <v>204618</v>
+        <v>210974</v>
       </c>
     </row>
     <row r="784">
@@ -16161,10 +16161,10 @@
         <v>107.05</v>
       </c>
       <c r="E787" t="n">
-        <v>107.97</v>
+        <v>107.11</v>
       </c>
       <c r="F787" t="n">
-        <v>170481</v>
+        <v>173653</v>
       </c>
     </row>
     <row r="788">
@@ -16181,10 +16181,10 @@
         <v>104.96</v>
       </c>
       <c r="E788" t="n">
-        <v>110.51</v>
+        <v>110.14</v>
       </c>
       <c r="F788" t="n">
-        <v>154891</v>
+        <v>157669</v>
       </c>
     </row>
     <row r="789">
@@ -16252,19 +16252,19 @@
         <v>44637</v>
       </c>
       <c r="B792" t="n">
-        <v>96.98</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="C792" t="n">
         <v>105.3</v>
       </c>
       <c r="D792" t="n">
-        <v>96.11</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="E792" t="n">
         <v>104.46</v>
       </c>
       <c r="F792" t="n">
-        <v>176604</v>
+        <v>172578</v>
       </c>
     </row>
     <row r="793">
@@ -16272,7 +16272,7 @@
         <v>44638</v>
       </c>
       <c r="B793" t="n">
-        <v>104.55</v>
+        <v>105.16</v>
       </c>
       <c r="C793" t="n">
         <v>107.23</v>
@@ -16284,7 +16284,7 @@
         <v>105.63</v>
       </c>
       <c r="F793" t="n">
-        <v>158531</v>
+        <v>155067</v>
       </c>
     </row>
     <row r="794">
@@ -16352,7 +16352,7 @@
         <v>44644</v>
       </c>
       <c r="B797" t="n">
-        <v>118.08</v>
+        <v>119.49</v>
       </c>
       <c r="C797" t="n">
         <v>120.04</v>
@@ -16364,7 +16364,7 @@
         <v>114.47</v>
       </c>
       <c r="F797" t="n">
-        <v>215337</v>
+        <v>206598</v>
       </c>
     </row>
     <row r="798">
@@ -16372,7 +16372,7 @@
         <v>44645</v>
       </c>
       <c r="B798" t="n">
-        <v>115.3</v>
+        <v>114.52</v>
       </c>
       <c r="C798" t="n">
         <v>117.69</v>
@@ -16384,7 +16384,7 @@
         <v>115.94</v>
       </c>
       <c r="F798" t="n">
-        <v>195807</v>
+        <v>189095</v>
       </c>
     </row>
     <row r="799">
@@ -16461,10 +16461,10 @@
         <v>103.71</v>
       </c>
       <c r="E802" t="n">
-        <v>104.6</v>
+        <v>104.99</v>
       </c>
       <c r="F802" t="n">
-        <v>217472</v>
+        <v>220967</v>
       </c>
     </row>
     <row r="803">
@@ -16481,10 +16481,10 @@
         <v>101.94</v>
       </c>
       <c r="E803" t="n">
-        <v>104.13</v>
+        <v>103.88</v>
       </c>
       <c r="F803" t="n">
-        <v>179677</v>
+        <v>181758</v>
       </c>
     </row>
     <row r="804">
@@ -16561,10 +16561,10 @@
         <v>98.2</v>
       </c>
       <c r="E807" t="n">
-        <v>100.94</v>
+        <v>100.96</v>
       </c>
       <c r="F807" t="n">
-        <v>183922</v>
+        <v>186163</v>
       </c>
     </row>
     <row r="808">
@@ -16581,10 +16581,10 @@
         <v>99.28</v>
       </c>
       <c r="E808" t="n">
-        <v>102.16</v>
+        <v>101.81</v>
       </c>
       <c r="F808" t="n">
-        <v>159821</v>
+        <v>162819</v>
       </c>
     </row>
     <row r="809">
@@ -16661,10 +16661,10 @@
         <v>106.14</v>
       </c>
       <c r="E812" t="n">
-        <v>110.56</v>
+        <v>110.62</v>
       </c>
       <c r="F812" t="n">
-        <v>156524</v>
+        <v>159785</v>
       </c>
     </row>
     <row r="813">
@@ -16741,10 +16741,10 @@
         <v>106.38</v>
       </c>
       <c r="E816" t="n">
-        <v>107.93</v>
+        <v>108</v>
       </c>
       <c r="F816" t="n">
-        <v>184241</v>
+        <v>188001</v>
       </c>
     </row>
     <row r="817">
@@ -16758,13 +16758,13 @@
         <v>108.41</v>
       </c>
       <c r="D817" t="n">
-        <v>105.44</v>
+        <v>105.05</v>
       </c>
       <c r="E817" t="n">
-        <v>105.6</v>
+        <v>105.7</v>
       </c>
       <c r="F817" t="n">
-        <v>162032</v>
+        <v>165632</v>
       </c>
     </row>
     <row r="818">
@@ -16841,10 +16841,10 @@
         <v>102.74</v>
       </c>
       <c r="E821" t="n">
-        <v>107.25</v>
+        <v>106.8</v>
       </c>
       <c r="F821" t="n">
-        <v>167676</v>
+        <v>170514</v>
       </c>
     </row>
     <row r="822">
@@ -16861,10 +16861,10 @@
         <v>105.92</v>
       </c>
       <c r="E822" t="n">
-        <v>106.38</v>
+        <v>106.06</v>
       </c>
       <c r="F822" t="n">
-        <v>182972</v>
+        <v>186051</v>
       </c>
     </row>
     <row r="823">
@@ -16941,10 +16941,10 @@
         <v>108.66</v>
       </c>
       <c r="E826" t="n">
-        <v>110.3</v>
+        <v>110.4</v>
       </c>
       <c r="F826" t="n">
-        <v>197687</v>
+        <v>201234</v>
       </c>
     </row>
     <row r="827">
@@ -16961,10 +16961,10 @@
         <v>109.21</v>
       </c>
       <c r="E827" t="n">
-        <v>112.44</v>
+        <v>112.22</v>
       </c>
       <c r="F827" t="n">
-        <v>203469</v>
+        <v>207851</v>
       </c>
     </row>
     <row r="828">
@@ -17041,10 +17041,10 @@
         <v>103.97</v>
       </c>
       <c r="E831" t="n">
-        <v>107.38</v>
+        <v>106.86</v>
       </c>
       <c r="F831" t="n">
-        <v>240901</v>
+        <v>243371</v>
       </c>
     </row>
     <row r="832">
@@ -17061,10 +17061,10 @@
         <v>106.88</v>
       </c>
       <c r="E832" t="n">
-        <v>110.4</v>
+        <v>109.76</v>
       </c>
       <c r="F832" t="n">
-        <v>190398</v>
+        <v>193013</v>
       </c>
     </row>
     <row r="833">
@@ -17141,10 +17141,10 @@
         <v>104.22</v>
       </c>
       <c r="E836" t="n">
-        <v>109.59</v>
+        <v>109.5</v>
       </c>
       <c r="F836" t="n">
-        <v>247278</v>
+        <v>250583</v>
       </c>
     </row>
     <row r="837">
@@ -17161,10 +17161,10 @@
         <v>108.65</v>
       </c>
       <c r="E837" t="n">
-        <v>110.87</v>
+        <v>110.3</v>
       </c>
       <c r="F837" t="n">
-        <v>198948</v>
+        <v>202895</v>
       </c>
     </row>
     <row r="838">
@@ -17241,10 +17241,10 @@
         <v>110.83</v>
       </c>
       <c r="E841" t="n">
-        <v>114</v>
+        <v>114.15</v>
       </c>
       <c r="F841" t="n">
-        <v>171535</v>
+        <v>175003</v>
       </c>
     </row>
     <row r="842">
@@ -17261,10 +17261,10 @@
         <v>113.01</v>
       </c>
       <c r="E842" t="n">
-        <v>115.42</v>
+        <v>115.01</v>
       </c>
       <c r="F842" t="n">
-        <v>210750</v>
+        <v>213418</v>
       </c>
     </row>
     <row r="843">
@@ -17335,16 +17335,16 @@
         <v>113.88</v>
       </c>
       <c r="C846" t="n">
-        <v>117.57</v>
+        <v>117.74</v>
       </c>
       <c r="D846" t="n">
         <v>111.85</v>
       </c>
       <c r="E846" t="n">
-        <v>117.26</v>
+        <v>117.31</v>
       </c>
       <c r="F846" t="n">
-        <v>137013</v>
+        <v>138282</v>
       </c>
     </row>
     <row r="847">
@@ -17355,16 +17355,16 @@
         <v>117.37</v>
       </c>
       <c r="C847" t="n">
-        <v>120.57</v>
+        <v>120.6</v>
       </c>
       <c r="D847" t="n">
         <v>115.28</v>
       </c>
       <c r="E847" t="n">
-        <v>120.41</v>
+        <v>120.23</v>
       </c>
       <c r="F847" t="n">
-        <v>90339</v>
+        <v>91626</v>
       </c>
     </row>
     <row r="848">
@@ -17441,10 +17441,10 @@
         <v>121.23</v>
       </c>
       <c r="E851" t="n">
-        <v>121.71</v>
+        <v>121.41</v>
       </c>
       <c r="F851" t="n">
-        <v>174232</v>
+        <v>176648</v>
       </c>
     </row>
     <row r="852">
@@ -17461,10 +17461,10 @@
         <v>118.31</v>
       </c>
       <c r="E852" t="n">
-        <v>120.29</v>
+        <v>120.02</v>
       </c>
       <c r="F852" t="n">
-        <v>190410</v>
+        <v>192334</v>
       </c>
     </row>
     <row r="853">
@@ -17541,10 +17541,10 @@
         <v>113.72</v>
       </c>
       <c r="E856" t="n">
-        <v>117.15</v>
+        <v>116.92</v>
       </c>
       <c r="F856" t="n">
-        <v>228931</v>
+        <v>231324</v>
       </c>
     </row>
     <row r="857">
@@ -17561,10 +17561,10 @@
         <v>109.77</v>
       </c>
       <c r="E857" t="n">
-        <v>111.29</v>
+        <v>111.27</v>
       </c>
       <c r="F857" t="n">
-        <v>233588</v>
+        <v>236868</v>
       </c>
     </row>
     <row r="858">
@@ -17641,10 +17641,10 @@
         <v>105.25</v>
       </c>
       <c r="E861" t="n">
-        <v>106.29</v>
+        <v>106.13</v>
       </c>
       <c r="F861" t="n">
-        <v>233040</v>
+        <v>234952</v>
       </c>
     </row>
     <row r="862">
@@ -17661,10 +17661,10 @@
         <v>105.78</v>
       </c>
       <c r="E862" t="n">
-        <v>109.13</v>
+        <v>108.33</v>
       </c>
       <c r="F862" t="n">
-        <v>202836</v>
+        <v>205227</v>
       </c>
     </row>
     <row r="863">
@@ -17741,10 +17741,10 @@
         <v>107.7</v>
       </c>
       <c r="E866" t="n">
-        <v>108.69</v>
+        <v>108.43</v>
       </c>
       <c r="F866" t="n">
-        <v>208599</v>
+        <v>212070</v>
       </c>
     </row>
     <row r="867">
@@ -17761,10 +17761,10 @@
         <v>107.32</v>
       </c>
       <c r="E867" t="n">
-        <v>110.56</v>
+        <v>110.43</v>
       </c>
       <c r="F867" t="n">
-        <v>209195</v>
+        <v>210630</v>
       </c>
     </row>
     <row r="868">
@@ -17841,10 +17841,10 @@
         <v>97.11</v>
       </c>
       <c r="E871" t="n">
-        <v>102.75</v>
+        <v>102.32</v>
       </c>
       <c r="F871" t="n">
-        <v>221862</v>
+        <v>224620</v>
       </c>
     </row>
     <row r="872">
@@ -17861,10 +17861,10 @@
         <v>102.16</v>
       </c>
       <c r="E872" t="n">
-        <v>105.32</v>
+        <v>105.2</v>
       </c>
       <c r="F872" t="n">
-        <v>235167</v>
+        <v>237030</v>
       </c>
     </row>
     <row r="873">
@@ -17941,10 +17941,10 @@
         <v>92.42</v>
       </c>
       <c r="E876" t="n">
-        <v>97.17</v>
+        <v>97.12</v>
       </c>
       <c r="F876" t="n">
-        <v>215919</v>
+        <v>217836</v>
       </c>
     </row>
     <row r="877">
@@ -17961,10 +17961,10 @@
         <v>95.59</v>
       </c>
       <c r="E877" t="n">
-        <v>98.34999999999999</v>
+        <v>97.98</v>
       </c>
       <c r="F877" t="n">
-        <v>200270</v>
+        <v>203134</v>
       </c>
     </row>
     <row r="878">
@@ -18041,10 +18041,10 @@
         <v>97.86</v>
       </c>
       <c r="E881" t="n">
-        <v>100.04</v>
+        <v>99.93000000000001</v>
       </c>
       <c r="F881" t="n">
-        <v>227231</v>
+        <v>229298</v>
       </c>
     </row>
     <row r="882">
@@ -18061,10 +18061,10 @@
         <v>97.90000000000001</v>
       </c>
       <c r="E882" t="n">
-        <v>98.67</v>
+        <v>98.98999999999999</v>
       </c>
       <c r="F882" t="n">
-        <v>222921</v>
+        <v>226135</v>
       </c>
     </row>
     <row r="883">
@@ -18141,10 +18141,10 @@
         <v>100.74</v>
       </c>
       <c r="E886" t="n">
-        <v>101.93</v>
+        <v>101.99</v>
       </c>
       <c r="F886" t="n">
-        <v>130398</v>
+        <v>132446</v>
       </c>
     </row>
     <row r="887">
@@ -18161,10 +18161,10 @@
         <v>101.27</v>
       </c>
       <c r="E887" t="n">
-        <v>103.21</v>
+        <v>103.1</v>
       </c>
       <c r="F887" t="n">
-        <v>112179</v>
+        <v>113461</v>
       </c>
     </row>
     <row r="888">
@@ -18238,13 +18238,13 @@
         <v>97.17</v>
       </c>
       <c r="D891" t="n">
-        <v>92.73</v>
+        <v>92.5</v>
       </c>
       <c r="E891" t="n">
-        <v>93.38</v>
+        <v>92.52</v>
       </c>
       <c r="F891" t="n">
-        <v>160629</v>
+        <v>162676</v>
       </c>
     </row>
     <row r="892">
@@ -18261,10 +18261,10 @@
         <v>92.15000000000001</v>
       </c>
       <c r="E892" t="n">
-        <v>93.69</v>
+        <v>93.51000000000001</v>
       </c>
       <c r="F892" t="n">
-        <v>155701</v>
+        <v>157322</v>
       </c>
     </row>
     <row r="893">
@@ -18341,10 +18341,10 @@
         <v>96.08</v>
       </c>
       <c r="E896" t="n">
-        <v>98.66</v>
+        <v>98.31</v>
       </c>
       <c r="F896" t="n">
-        <v>139272</v>
+        <v>140818</v>
       </c>
     </row>
     <row r="897">
@@ -18361,10 +18361,10 @@
         <v>96.26000000000001</v>
       </c>
       <c r="E897" t="n">
-        <v>97.3</v>
+        <v>96.89</v>
       </c>
       <c r="F897" t="n">
-        <v>144235</v>
+        <v>145858</v>
       </c>
     </row>
     <row r="898">
@@ -18441,10 +18441,10 @@
         <v>92.55</v>
       </c>
       <c r="E901" t="n">
-        <v>95.93000000000001</v>
+        <v>95.56</v>
       </c>
       <c r="F901" t="n">
-        <v>122235</v>
+        <v>123861</v>
       </c>
     </row>
     <row r="902">
@@ -18461,10 +18461,10 @@
         <v>93.7</v>
       </c>
       <c r="E902" t="n">
-        <v>95.52</v>
+        <v>95.08</v>
       </c>
       <c r="F902" t="n">
-        <v>125387</v>
+        <v>126696</v>
       </c>
     </row>
     <row r="903">
@@ -18541,10 +18541,10 @@
         <v>98.23</v>
       </c>
       <c r="E906" t="n">
-        <v>99.05</v>
+        <v>98.68000000000001</v>
       </c>
       <c r="F906" t="n">
-        <v>114289</v>
+        <v>115830</v>
       </c>
     </row>
     <row r="907">
@@ -18561,10 +18561,10 @@
         <v>96.92</v>
       </c>
       <c r="E907" t="n">
-        <v>98.70999999999999</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="F907" t="n">
-        <v>127109</v>
+        <v>128357</v>
       </c>
     </row>
     <row r="908">
@@ -18641,10 +18641,10 @@
         <v>91.58</v>
       </c>
       <c r="E911" t="n">
-        <v>91.75</v>
+        <v>91.59</v>
       </c>
       <c r="F911" t="n">
-        <v>171383</v>
+        <v>172611</v>
       </c>
     </row>
     <row r="912">
@@ -18661,10 +18661,10 @@
         <v>92.41</v>
       </c>
       <c r="E912" t="n">
-        <v>92.68000000000001</v>
+        <v>92.83</v>
       </c>
       <c r="F912" t="n">
-        <v>162523</v>
+        <v>164349</v>
       </c>
     </row>
     <row r="913">
@@ -18741,10 +18741,10 @@
         <v>86.86</v>
       </c>
       <c r="E916" t="n">
-        <v>88.03</v>
+        <v>87.73999999999999</v>
       </c>
       <c r="F916" t="n">
-        <v>174104</v>
+        <v>175783</v>
       </c>
     </row>
     <row r="917">
@@ -18761,10 +18761,10 @@
         <v>88.09</v>
       </c>
       <c r="E917" t="n">
-        <v>91.90000000000001</v>
+        <v>91.42</v>
       </c>
       <c r="F917" t="n">
-        <v>137562</v>
+        <v>139210</v>
       </c>
     </row>
     <row r="918">
@@ -18841,10 +18841,10 @@
         <v>89.39</v>
       </c>
       <c r="E921" t="n">
-        <v>90.08</v>
+        <v>89.78</v>
       </c>
       <c r="F921" t="n">
-        <v>177670</v>
+        <v>179533</v>
       </c>
     </row>
     <row r="922">
@@ -18861,10 +18861,10 @@
         <v>89.37</v>
       </c>
       <c r="E922" t="n">
-        <v>90.58</v>
+        <v>90.36</v>
       </c>
       <c r="F922" t="n">
-        <v>175462</v>
+        <v>177056</v>
       </c>
     </row>
     <row r="923">
@@ -18941,10 +18941,10 @@
         <v>88.38</v>
       </c>
       <c r="E926" t="n">
-        <v>89.53</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="F926" t="n">
-        <v>167346</v>
+        <v>169282</v>
       </c>
     </row>
     <row r="927">
@@ -18961,10 +18961,10 @@
         <v>84.61</v>
       </c>
       <c r="E927" t="n">
-        <v>85.41</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="F927" t="n">
-        <v>157358</v>
+        <v>159709</v>
       </c>
     </row>
     <row r="928">
@@ -19041,10 +19041,10 @@
         <v>85.98</v>
       </c>
       <c r="E931" t="n">
-        <v>87.20999999999999</v>
+        <v>87.22</v>
       </c>
       <c r="F931" t="n">
-        <v>182346</v>
+        <v>184095</v>
       </c>
     </row>
     <row r="932">
@@ -19061,10 +19061,10 @@
         <v>84.73999999999999</v>
       </c>
       <c r="E932" t="n">
-        <v>85.06999999999999</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="F932" t="n">
-        <v>172540</v>
+        <v>174184</v>
       </c>
     </row>
     <row r="933">
@@ -19141,10 +19141,10 @@
         <v>92.09</v>
       </c>
       <c r="E936" t="n">
-        <v>94.31999999999999</v>
+        <v>94.16</v>
       </c>
       <c r="F936" t="n">
-        <v>134269</v>
+        <v>136157</v>
       </c>
     </row>
     <row r="937">
@@ -19161,10 +19161,10 @@
         <v>93.25</v>
       </c>
       <c r="E937" t="n">
-        <v>96.95</v>
+        <v>97.59</v>
       </c>
       <c r="F937" t="n">
-        <v>158303</v>
+        <v>161145</v>
       </c>
     </row>
     <row r="938">
@@ -19241,10 +19241,10 @@
         <v>90.18000000000001</v>
       </c>
       <c r="E941" t="n">
-        <v>93.61</v>
+        <v>93.67</v>
       </c>
       <c r="F941" t="n">
-        <v>187899</v>
+        <v>189909</v>
       </c>
     </row>
     <row r="942">
@@ -19261,10 +19261,10 @@
         <v>90.34</v>
       </c>
       <c r="E942" t="n">
-        <v>90.84999999999999</v>
+        <v>90.66</v>
       </c>
       <c r="F942" t="n">
-        <v>184164</v>
+        <v>186342</v>
       </c>
     </row>
     <row r="943">
@@ -19341,10 +19341,10 @@
         <v>90.34</v>
       </c>
       <c r="E946" t="n">
-        <v>91</v>
+        <v>91.11</v>
       </c>
       <c r="F946" t="n">
-        <v>169394</v>
+        <v>172151</v>
       </c>
     </row>
     <row r="947">
@@ -19361,10 +19361,10 @@
         <v>89.40000000000001</v>
       </c>
       <c r="E947" t="n">
-        <v>91.7</v>
+        <v>91.58</v>
       </c>
       <c r="F947" t="n">
-        <v>168937</v>
+        <v>170499</v>
       </c>
     </row>
     <row r="948">
@@ -19441,10 +19441,10 @@
         <v>93.06999999999999</v>
       </c>
       <c r="E951" t="n">
-        <v>94.91</v>
+        <v>94.45999999999999</v>
       </c>
       <c r="F951" t="n">
-        <v>130846</v>
+        <v>135151</v>
       </c>
     </row>
     <row r="952">
@@ -19461,10 +19461,10 @@
         <v>92.81999999999999</v>
       </c>
       <c r="E952" t="n">
-        <v>93.81</v>
+        <v>93.95</v>
       </c>
       <c r="F952" t="n">
-        <v>133960</v>
+        <v>135363</v>
       </c>
     </row>
     <row r="953">
@@ -19532,7 +19532,7 @@
         <v>44868</v>
       </c>
       <c r="B956" t="n">
-        <v>94.81</v>
+        <v>94.84</v>
       </c>
       <c r="C956" t="n">
         <v>95.45</v>
@@ -19544,7 +19544,7 @@
         <v>93.92</v>
       </c>
       <c r="F956" t="n">
-        <v>143503</v>
+        <v>141621</v>
       </c>
     </row>
     <row r="957">
@@ -19552,19 +19552,19 @@
         <v>44869</v>
       </c>
       <c r="B957" t="n">
-        <v>93.98</v>
+        <v>93.94</v>
       </c>
       <c r="C957" t="n">
         <v>98.23999999999999</v>
       </c>
       <c r="D957" t="n">
-        <v>93.76000000000001</v>
+        <v>93.94</v>
       </c>
       <c r="E957" t="n">
         <v>98.01000000000001</v>
       </c>
       <c r="F957" t="n">
-        <v>182009</v>
+        <v>179958</v>
       </c>
     </row>
     <row r="958">
@@ -19641,10 +19641,10 @@
         <v>90.97</v>
       </c>
       <c r="E961" t="n">
-        <v>92.69</v>
+        <v>92.47</v>
       </c>
       <c r="F961" t="n">
-        <v>168690</v>
+        <v>170823</v>
       </c>
     </row>
     <row r="962">
@@ -19661,10 +19661,10 @@
         <v>92.79000000000001</v>
       </c>
       <c r="E962" t="n">
-        <v>95.04000000000001</v>
+        <v>94.95999999999999</v>
       </c>
       <c r="F962" t="n">
-        <v>163940</v>
+        <v>165782</v>
       </c>
     </row>
     <row r="963">
@@ -19741,10 +19741,10 @@
         <v>88.72</v>
       </c>
       <c r="E966" t="n">
-        <v>89.28</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="F966" t="n">
-        <v>157265</v>
+        <v>159560</v>
       </c>
     </row>
     <row r="967">
@@ -19761,10 +19761,10 @@
         <v>85.41</v>
       </c>
       <c r="E967" t="n">
-        <v>87.45</v>
+        <v>87.5</v>
       </c>
       <c r="F967" t="n">
-        <v>160818</v>
+        <v>162655</v>
       </c>
     </row>
     <row r="968">
@@ -19941,10 +19941,10 @@
         <v>86.26000000000001</v>
       </c>
       <c r="E976" t="n">
-        <v>86.84</v>
+        <v>86.98</v>
       </c>
       <c r="F976" t="n">
-        <v>135345</v>
+        <v>136930</v>
       </c>
     </row>
     <row r="977">
@@ -19961,10 +19961,10 @@
         <v>85.17</v>
       </c>
       <c r="E977" t="n">
-        <v>85.76000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="F977" t="n">
-        <v>135815</v>
+        <v>137359</v>
       </c>
     </row>
     <row r="978">
@@ -20041,10 +20041,10 @@
         <v>75.92</v>
       </c>
       <c r="E981" t="n">
-        <v>76.27</v>
+        <v>76.61</v>
       </c>
       <c r="F981" t="n">
-        <v>165742</v>
+        <v>167594</v>
       </c>
     </row>
     <row r="982">
@@ -20061,10 +20061,10 @@
         <v>75.34999999999999</v>
       </c>
       <c r="E982" t="n">
-        <v>76.76000000000001</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="F982" t="n">
-        <v>151706</v>
+        <v>153224</v>
       </c>
     </row>
     <row r="983">
@@ -20141,10 +20141,10 @@
         <v>80.86</v>
       </c>
       <c r="E986" t="n">
-        <v>81.39</v>
+        <v>81.54000000000001</v>
       </c>
       <c r="F986" t="n">
-        <v>149384</v>
+        <v>151489</v>
       </c>
     </row>
     <row r="987">
@@ -20161,10 +20161,10 @@
         <v>78.61</v>
       </c>
       <c r="E987" t="n">
-        <v>79.36</v>
+        <v>79.44</v>
       </c>
       <c r="F987" t="n">
-        <v>149990</v>
+        <v>151197</v>
       </c>
     </row>
     <row r="988">
@@ -20241,10 +20241,10 @@
         <v>81.28</v>
       </c>
       <c r="E991" t="n">
-        <v>82.18000000000001</v>
+        <v>82.20999999999999</v>
       </c>
       <c r="F991" t="n">
-        <v>94348</v>
+        <v>95617</v>
       </c>
     </row>
     <row r="992">
@@ -20321,10 +20321,10 @@
         <v>81.81999999999999</v>
       </c>
       <c r="E995" t="n">
-        <v>83.68000000000001</v>
+        <v>83.63</v>
       </c>
       <c r="F995" t="n">
-        <v>109380</v>
+        <v>110699</v>
       </c>
     </row>
     <row r="996">
@@ -20401,10 +20401,10 @@
         <v>77.63</v>
       </c>
       <c r="E999" t="n">
-        <v>78.68000000000001</v>
+        <v>78.8</v>
       </c>
       <c r="F999" t="n">
-        <v>149266</v>
+        <v>150672</v>
       </c>
     </row>
     <row r="1000">
@@ -20424,7 +20424,7 @@
         <v>78.51000000000001</v>
       </c>
       <c r="F1000" t="n">
-        <v>147017</v>
+        <v>148389</v>
       </c>
     </row>
     <row r="1001">
@@ -20501,10 +20501,10 @@
         <v>82.43000000000001</v>
       </c>
       <c r="E1004" t="n">
-        <v>83.91</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="F1004" t="n">
-        <v>141086</v>
+        <v>142735</v>
       </c>
     </row>
     <row r="1005">
@@ -20515,16 +20515,16 @@
         <v>83.91</v>
       </c>
       <c r="C1005" t="n">
-        <v>85.55</v>
+        <v>85.61</v>
       </c>
       <c r="D1005" t="n">
         <v>83.55</v>
       </c>
       <c r="E1005" t="n">
-        <v>85.48</v>
+        <v>85.47</v>
       </c>
       <c r="F1005" t="n">
-        <v>129757</v>
+        <v>131152</v>
       </c>
     </row>
     <row r="1006">
@@ -20601,10 +20601,10 @@
         <v>83.95999999999999</v>
       </c>
       <c r="E1009" t="n">
-        <v>86.31999999999999</v>
+        <v>86.34</v>
       </c>
       <c r="F1009" t="n">
-        <v>142583</v>
+        <v>144410</v>
       </c>
     </row>
     <row r="1010">
@@ -20621,10 +20621,10 @@
         <v>85.69</v>
       </c>
       <c r="E1010" t="n">
-        <v>87.75</v>
+        <v>87.59</v>
       </c>
       <c r="F1010" t="n">
-        <v>123973</v>
+        <v>125225</v>
       </c>
     </row>
     <row r="1011">
@@ -20701,10 +20701,10 @@
         <v>85.75</v>
       </c>
       <c r="E1014" t="n">
-        <v>87.31</v>
+        <v>87.29000000000001</v>
       </c>
       <c r="F1014" t="n">
-        <v>95077</v>
+        <v>96051</v>
       </c>
     </row>
     <row r="1015">
@@ -20721,10 +20721,10 @@
         <v>85.48</v>
       </c>
       <c r="E1015" t="n">
-        <v>86.04000000000001</v>
+        <v>86.01000000000001</v>
       </c>
       <c r="F1015" t="n">
-        <v>109841</v>
+        <v>110922</v>
       </c>
     </row>
     <row r="1016">
@@ -20801,10 +20801,10 @@
         <v>81.2</v>
       </c>
       <c r="E1019" t="n">
-        <v>81.98</v>
+        <v>82.12</v>
       </c>
       <c r="F1019" t="n">
-        <v>146732</v>
+        <v>150704</v>
       </c>
     </row>
     <row r="1020">
@@ -20818,13 +20818,13 @@
         <v>84.11</v>
       </c>
       <c r="D1020" t="n">
+        <v>79.53</v>
+      </c>
+      <c r="E1020" t="n">
         <v>79.62</v>
       </c>
-      <c r="E1020" t="n">
-        <v>79.64</v>
-      </c>
       <c r="F1020" t="n">
-        <v>161681</v>
+        <v>163093</v>
       </c>
     </row>
     <row r="1021">
@@ -20901,10 +20901,10 @@
         <v>82.86</v>
       </c>
       <c r="E1024" t="n">
-        <v>83.88</v>
+        <v>83.95</v>
       </c>
       <c r="F1024" t="n">
-        <v>142722</v>
+        <v>144061</v>
       </c>
     </row>
     <row r="1025">
@@ -20921,10 +20921,10 @@
         <v>83.66</v>
       </c>
       <c r="E1025" t="n">
-        <v>86.29000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="F1025" t="n">
-        <v>155562</v>
+        <v>156718</v>
       </c>
     </row>
     <row r="1026">
@@ -20998,13 +20998,13 @@
         <v>85.90000000000001</v>
       </c>
       <c r="D1029" t="n">
-        <v>84.31999999999999</v>
+        <v>84.28</v>
       </c>
       <c r="E1029" t="n">
-        <v>84.37</v>
+        <v>84.31</v>
       </c>
       <c r="F1029" t="n">
-        <v>128382</v>
+        <v>129946</v>
       </c>
     </row>
     <row r="1030">
@@ -21021,10 +21021,10 @@
         <v>81.55</v>
       </c>
       <c r="E1030" t="n">
-        <v>82.68000000000001</v>
+        <v>82.72</v>
       </c>
       <c r="F1030" t="n">
-        <v>141607</v>
+        <v>142763</v>
       </c>
     </row>
     <row r="1031">
@@ -21101,10 +21101,10 @@
         <v>80.27</v>
       </c>
       <c r="E1034" t="n">
-        <v>82.12</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="F1034" t="n">
-        <v>107083</v>
+        <v>108091</v>
       </c>
     </row>
     <row r="1035">
@@ -21121,10 +21121,10 @@
         <v>80.7</v>
       </c>
       <c r="E1035" t="n">
-        <v>82.94</v>
+        <v>82.77</v>
       </c>
       <c r="F1035" t="n">
-        <v>129354</v>
+        <v>130526</v>
       </c>
     </row>
     <row r="1036">
@@ -21201,10 +21201,10 @@
         <v>83.66</v>
       </c>
       <c r="E1039" t="n">
-        <v>84.34</v>
+        <v>84.23</v>
       </c>
       <c r="F1039" t="n">
-        <v>114302</v>
+        <v>115434</v>
       </c>
     </row>
     <row r="1040">
@@ -21215,16 +21215,16 @@
         <v>84.37</v>
       </c>
       <c r="C1040" t="n">
-        <v>85.8</v>
+        <v>85.81</v>
       </c>
       <c r="D1040" t="n">
         <v>82.2</v>
       </c>
       <c r="E1040" t="n">
-        <v>85.72</v>
+        <v>85.73999999999999</v>
       </c>
       <c r="F1040" t="n">
-        <v>119970</v>
+        <v>120888</v>
       </c>
     </row>
     <row r="1041">
@@ -21301,10 +21301,10 @@
         <v>81.16</v>
       </c>
       <c r="E1044" t="n">
-        <v>81.26000000000001</v>
+        <v>81.23</v>
       </c>
       <c r="F1044" t="n">
-        <v>120126</v>
+        <v>121276</v>
       </c>
     </row>
     <row r="1045">
@@ -21321,10 +21321,10 @@
         <v>80.47</v>
       </c>
       <c r="E1045" t="n">
-        <v>82.33</v>
+        <v>82.38</v>
       </c>
       <c r="F1045" t="n">
-        <v>171433</v>
+        <v>172647</v>
       </c>
     </row>
     <row r="1046">
@@ -21392,7 +21392,7 @@
         <v>45001</v>
       </c>
       <c r="B1049" t="n">
-        <v>74.04000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="C1049" t="n">
         <v>75.23</v>
@@ -21404,7 +21404,7 @@
         <v>74.25</v>
       </c>
       <c r="F1049" t="n">
-        <v>210322</v>
+        <v>206406</v>
       </c>
     </row>
     <row r="1050">
@@ -21412,7 +21412,7 @@
         <v>45002</v>
       </c>
       <c r="B1050" t="n">
-        <v>74.45</v>
+        <v>74.41</v>
       </c>
       <c r="C1050" t="n">
         <v>75.65000000000001</v>
@@ -21424,7 +21424,7 @@
         <v>72.3</v>
       </c>
       <c r="F1050" t="n">
-        <v>196053</v>
+        <v>194486</v>
       </c>
     </row>
     <row r="1051">
@@ -21492,7 +21492,7 @@
         <v>45008</v>
       </c>
       <c r="B1054" t="n">
-        <v>75.58</v>
+        <v>75.73</v>
       </c>
       <c r="C1054" t="n">
         <v>77.09</v>
@@ -21504,7 +21504,7 @@
         <v>74.98999999999999</v>
       </c>
       <c r="F1054" t="n">
-        <v>134971</v>
+        <v>132462</v>
       </c>
     </row>
     <row r="1055">
@@ -21512,7 +21512,7 @@
         <v>45009</v>
       </c>
       <c r="B1055" t="n">
-        <v>75.08</v>
+        <v>74.92</v>
       </c>
       <c r="C1055" t="n">
         <v>75.89</v>
@@ -21524,7 +21524,7 @@
         <v>74.52</v>
       </c>
       <c r="F1055" t="n">
-        <v>160608</v>
+        <v>158419</v>
       </c>
     </row>
     <row r="1056">
@@ -21601,10 +21601,10 @@
         <v>77.13</v>
       </c>
       <c r="E1059" t="n">
-        <v>78.47</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="F1059" t="n">
-        <v>101875</v>
+        <v>102975</v>
       </c>
     </row>
     <row r="1060">
@@ -21621,10 +21621,10 @@
         <v>77.79000000000001</v>
       </c>
       <c r="E1060" t="n">
-        <v>79.73</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="F1060" t="n">
-        <v>102278</v>
+        <v>103341</v>
       </c>
     </row>
     <row r="1061">
@@ -21701,10 +21701,10 @@
         <v>83.89</v>
       </c>
       <c r="E1064" t="n">
-        <v>84.73</v>
+        <v>84.62</v>
       </c>
       <c r="F1064" t="n">
-        <v>127887</v>
+        <v>128978</v>
       </c>
     </row>
     <row r="1065">
@@ -21781,10 +21781,10 @@
         <v>85.78</v>
       </c>
       <c r="E1068" t="n">
-        <v>85.98</v>
+        <v>86.03</v>
       </c>
       <c r="F1068" t="n">
-        <v>106530</v>
+        <v>107747</v>
       </c>
     </row>
     <row r="1069">
@@ -21801,10 +21801,10 @@
         <v>85.27</v>
       </c>
       <c r="E1069" t="n">
-        <v>86.13</v>
+        <v>86.12</v>
       </c>
       <c r="F1069" t="n">
-        <v>118921</v>
+        <v>119789</v>
       </c>
     </row>
     <row r="1070">
@@ -21878,13 +21878,13 @@
         <v>82.59999999999999</v>
       </c>
       <c r="D1073" t="n">
-        <v>80.51000000000001</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="E1073" t="n">
-        <v>80.62</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="F1073" t="n">
-        <v>99083</v>
+        <v>100157</v>
       </c>
     </row>
     <row r="1074">
@@ -21901,10 +21901,10 @@
         <v>80.2</v>
       </c>
       <c r="E1074" t="n">
-        <v>81.38</v>
+        <v>81.53</v>
       </c>
       <c r="F1074" t="n">
-        <v>88877</v>
+        <v>89589</v>
       </c>
     </row>
     <row r="1075">
@@ -21981,10 +21981,10 @@
         <v>77.3</v>
       </c>
       <c r="E1078" t="n">
-        <v>78.23</v>
+        <v>78.17</v>
       </c>
       <c r="F1078" t="n">
-        <v>112919</v>
+        <v>114226</v>
       </c>
     </row>
     <row r="1079">
@@ -22001,10 +22001,10 @@
         <v>77.44</v>
       </c>
       <c r="E1079" t="n">
-        <v>80.20999999999999</v>
+        <v>80.08</v>
       </c>
       <c r="F1079" t="n">
-        <v>110643</v>
+        <v>111593</v>
       </c>
     </row>
     <row r="1080">
@@ -22081,10 +22081,10 @@
         <v>71.34</v>
       </c>
       <c r="E1083" t="n">
-        <v>72.34</v>
+        <v>72.38</v>
       </c>
       <c r="F1083" t="n">
-        <v>175075</v>
+        <v>176458</v>
       </c>
     </row>
     <row r="1084">
@@ -22101,10 +22101,10 @@
         <v>72.31999999999999</v>
       </c>
       <c r="E1084" t="n">
-        <v>75.22</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="F1084" t="n">
-        <v>121559</v>
+        <v>122688</v>
       </c>
     </row>
     <row r="1085">
@@ -22181,10 +22181,10 @@
         <v>74.5</v>
       </c>
       <c r="E1088" t="n">
-        <v>75.34999999999999</v>
+        <v>75.26000000000001</v>
       </c>
       <c r="F1088" t="n">
-        <v>141443</v>
+        <v>142391</v>
       </c>
     </row>
     <row r="1089">
@@ -22201,10 +22201,10 @@
         <v>73.84999999999999</v>
       </c>
       <c r="E1089" t="n">
-        <v>74.02</v>
+        <v>73.93000000000001</v>
       </c>
       <c r="F1089" t="n">
-        <v>143925</v>
+        <v>144762</v>
       </c>
     </row>
     <row r="1090">
@@ -22281,10 +22281,10 @@
         <v>75.42</v>
       </c>
       <c r="E1093" t="n">
-        <v>75.89</v>
+        <v>75.84</v>
       </c>
       <c r="F1093" t="n">
-        <v>97144</v>
+        <v>98116</v>
       </c>
     </row>
     <row r="1094">
@@ -22301,10 +22301,10 @@
         <v>75.01000000000001</v>
       </c>
       <c r="E1094" t="n">
-        <v>75.75</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="F1094" t="n">
-        <v>107224</v>
+        <v>108218</v>
       </c>
     </row>
     <row r="1095">
@@ -22381,10 +22381,10 @@
         <v>75.08</v>
       </c>
       <c r="E1098" t="n">
-        <v>76.13</v>
+        <v>75.95999999999999</v>
       </c>
       <c r="F1098" t="n">
-        <v>94656</v>
+        <v>95663</v>
       </c>
     </row>
     <row r="1099">
@@ -22401,10 +22401,10 @@
         <v>75.62</v>
       </c>
       <c r="E1099" t="n">
-        <v>77.03</v>
+        <v>77.14</v>
       </c>
       <c r="F1099" t="n">
-        <v>85632</v>
+        <v>86227</v>
       </c>
     </row>
     <row r="1100">
@@ -22481,10 +22481,10 @@
         <v>72</v>
       </c>
       <c r="E1103" t="n">
-        <v>74.17</v>
+        <v>74.25</v>
       </c>
       <c r="F1103" t="n">
-        <v>122959</v>
+        <v>124084</v>
       </c>
     </row>
     <row r="1104">
@@ -22501,10 +22501,10 @@
         <v>74.13</v>
       </c>
       <c r="E1104" t="n">
-        <v>76.3</v>
+        <v>76.13</v>
       </c>
       <c r="F1104" t="n">
-        <v>110715</v>
+        <v>111881</v>
       </c>
     </row>
     <row r="1105">
@@ -22581,10 +22581,10 @@
         <v>73.52</v>
       </c>
       <c r="E1108" t="n">
-        <v>75.56999999999999</v>
+        <v>75.44</v>
       </c>
       <c r="F1108" t="n">
-        <v>141391</v>
+        <v>142206</v>
       </c>
     </row>
     <row r="1109">
@@ -22601,10 +22601,10 @@
         <v>74.67</v>
       </c>
       <c r="E1109" t="n">
-        <v>74.84999999999999</v>
+        <v>74.88</v>
       </c>
       <c r="F1109" t="n">
-        <v>120105</v>
+        <v>120995</v>
       </c>
     </row>
     <row r="1110">
@@ -22681,10 +22681,10 @@
         <v>72.84999999999999</v>
       </c>
       <c r="E1113" t="n">
-        <v>75.56</v>
+        <v>75.52</v>
       </c>
       <c r="F1113" t="n">
-        <v>104970</v>
+        <v>105947</v>
       </c>
     </row>
     <row r="1114">
@@ -22701,10 +22701,10 @@
         <v>75.09999999999999</v>
       </c>
       <c r="E1114" t="n">
-        <v>76.47</v>
+        <v>76.23</v>
       </c>
       <c r="F1114" t="n">
-        <v>109963</v>
+        <v>111184</v>
       </c>
     </row>
     <row r="1115">
@@ -22781,10 +22781,10 @@
         <v>73.75</v>
       </c>
       <c r="E1118" t="n">
-        <v>74.2</v>
+        <v>74.3</v>
       </c>
       <c r="F1118" t="n">
-        <v>89166</v>
+        <v>89974</v>
       </c>
     </row>
     <row r="1119">
@@ -22795,16 +22795,16 @@
         <v>74.2</v>
       </c>
       <c r="C1119" t="n">
-        <v>74.36</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="D1119" t="n">
         <v>72.25</v>
       </c>
       <c r="E1119" t="n">
-        <v>74.09</v>
+        <v>74.34</v>
       </c>
       <c r="F1119" t="n">
-        <v>100773</v>
+        <v>101628</v>
       </c>
     </row>
     <row r="1120">
@@ -22881,10 +22881,10 @@
         <v>73.56</v>
       </c>
       <c r="E1123" t="n">
-        <v>74.44</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="F1123" t="n">
-        <v>118096</v>
+        <v>118860</v>
       </c>
     </row>
     <row r="1124">
@@ -22901,10 +22901,10 @@
         <v>74.23</v>
       </c>
       <c r="E1124" t="n">
-        <v>75.26000000000001</v>
+        <v>75.06999999999999</v>
       </c>
       <c r="F1124" t="n">
-        <v>107062</v>
+        <v>108012</v>
       </c>
     </row>
     <row r="1125">
@@ -22981,10 +22981,10 @@
         <v>74.94</v>
       </c>
       <c r="E1128" t="n">
-        <v>76.47</v>
+        <v>76.44</v>
       </c>
       <c r="F1128" t="n">
-        <v>120498</v>
+        <v>121613</v>
       </c>
     </row>
     <row r="1129">
@@ -23001,10 +23001,10 @@
         <v>75.91</v>
       </c>
       <c r="E1129" t="n">
-        <v>78.13</v>
+        <v>78.12</v>
       </c>
       <c r="F1129" t="n">
-        <v>99946</v>
+        <v>101260</v>
       </c>
     </row>
     <row r="1130">
@@ -23075,16 +23075,16 @@
         <v>79.95999999999999</v>
       </c>
       <c r="C1133" t="n">
-        <v>81.48999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="D1133" t="n">
         <v>79.69</v>
       </c>
       <c r="E1133" t="n">
-        <v>81.48</v>
+        <v>81.37</v>
       </c>
       <c r="F1133" t="n">
-        <v>96443</v>
+        <v>97805</v>
       </c>
     </row>
     <row r="1134">
@@ -23098,13 +23098,13 @@
         <v>81.42</v>
       </c>
       <c r="D1134" t="n">
-        <v>79.44</v>
+        <v>79.34999999999999</v>
       </c>
       <c r="E1134" t="n">
-        <v>79.54000000000001</v>
+        <v>79.45</v>
       </c>
       <c r="F1134" t="n">
-        <v>98000</v>
+        <v>99161</v>
       </c>
     </row>
     <row r="1135">
@@ -23181,10 +23181,10 @@
         <v>78.56999999999999</v>
       </c>
       <c r="E1138" t="n">
-        <v>79.54000000000001</v>
+        <v>79.48</v>
       </c>
       <c r="F1138" t="n">
-        <v>76777</v>
+        <v>77506</v>
       </c>
     </row>
     <row r="1139">
@@ -23201,10 +23201,10 @@
         <v>79.51000000000001</v>
       </c>
       <c r="E1139" t="n">
-        <v>80.69</v>
+        <v>80.5</v>
       </c>
       <c r="F1139" t="n">
-        <v>69907</v>
+        <v>70745</v>
       </c>
     </row>
     <row r="1140">
@@ -23281,10 +23281,10 @@
         <v>82.54000000000001</v>
       </c>
       <c r="E1143" t="n">
-        <v>83.42</v>
+        <v>83.3</v>
       </c>
       <c r="F1143" t="n">
-        <v>100960</v>
+        <v>101885</v>
       </c>
     </row>
     <row r="1144">
@@ -23301,10 +23301,10 @@
         <v>82.78</v>
       </c>
       <c r="E1144" t="n">
-        <v>84.26000000000001</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="F1144" t="n">
-        <v>96080</v>
+        <v>96933</v>
       </c>
     </row>
     <row r="1145">
@@ -23381,10 +23381,10 @@
         <v>82.23</v>
       </c>
       <c r="E1148" t="n">
-        <v>85.13</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="F1148" t="n">
-        <v>122532</v>
+        <v>124232</v>
       </c>
     </row>
     <row r="1149">
@@ -23401,10 +23401,10 @@
         <v>84.89</v>
       </c>
       <c r="E1149" t="n">
-        <v>85.84</v>
+        <v>85.81</v>
       </c>
       <c r="F1149" t="n">
-        <v>103319</v>
+        <v>104424</v>
       </c>
     </row>
     <row r="1150">
@@ -23481,10 +23481,10 @@
         <v>85.89</v>
       </c>
       <c r="E1153" t="n">
-        <v>86.09999999999999</v>
+        <v>86.01000000000001</v>
       </c>
       <c r="F1153" t="n">
-        <v>119054</v>
+        <v>120019</v>
       </c>
     </row>
     <row r="1154">
@@ -23501,10 +23501,10 @@
         <v>85.53</v>
       </c>
       <c r="E1154" t="n">
-        <v>86.26000000000001</v>
+        <v>86.16</v>
       </c>
       <c r="F1154" t="n">
-        <v>114400</v>
+        <v>115051</v>
       </c>
     </row>
     <row r="1155">
@@ -23581,10 +23581,10 @@
         <v>82.70999999999999</v>
       </c>
       <c r="E1158" t="n">
-        <v>83.45999999999999</v>
+        <v>83.42</v>
       </c>
       <c r="F1158" t="n">
-        <v>87119</v>
+        <v>88033</v>
       </c>
     </row>
     <row r="1159">
@@ -23601,10 +23601,10 @@
         <v>82.98</v>
       </c>
       <c r="E1159" t="n">
-        <v>84.37</v>
+        <v>84.42</v>
       </c>
       <c r="F1159" t="n">
-        <v>98085</v>
+        <v>98761</v>
       </c>
     </row>
     <row r="1160">
@@ -23681,10 +23681,10 @@
         <v>81.61</v>
       </c>
       <c r="E1163" t="n">
-        <v>82.76000000000001</v>
+        <v>82.67</v>
       </c>
       <c r="F1163" t="n">
-        <v>77118</v>
+        <v>77961</v>
       </c>
     </row>
     <row r="1164">
@@ -23701,10 +23701,10 @@
         <v>82.2</v>
       </c>
       <c r="E1164" t="n">
-        <v>84.14</v>
+        <v>84.05</v>
       </c>
       <c r="F1164" t="n">
-        <v>101382</v>
+        <v>102303</v>
       </c>
     </row>
     <row r="1165">
@@ -23781,10 +23781,10 @@
         <v>84.98</v>
       </c>
       <c r="E1168" t="n">
-        <v>86.63</v>
+        <v>86.66</v>
       </c>
       <c r="F1168" t="n">
-        <v>83934</v>
+        <v>85007</v>
       </c>
     </row>
     <row r="1169">
@@ -23795,16 +23795,16 @@
         <v>86.63</v>
       </c>
       <c r="C1169" t="n">
-        <v>88.66</v>
+        <v>88.75</v>
       </c>
       <c r="D1169" t="n">
         <v>86.59</v>
       </c>
       <c r="E1169" t="n">
-        <v>88.64</v>
+        <v>88.68000000000001</v>
       </c>
       <c r="F1169" t="n">
-        <v>97671</v>
+        <v>98645</v>
       </c>
     </row>
     <row r="1170">
@@ -23881,10 +23881,10 @@
         <v>89.17</v>
       </c>
       <c r="E1173" t="n">
-        <v>89.76000000000001</v>
+        <v>89.47</v>
       </c>
       <c r="F1173" t="n">
-        <v>103067</v>
+        <v>104343</v>
       </c>
     </row>
     <row r="1174">
@@ -23901,10 +23901,10 @@
         <v>88.97</v>
       </c>
       <c r="E1174" t="n">
-        <v>90.2</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="F1174" t="n">
-        <v>100164</v>
+        <v>101197</v>
       </c>
     </row>
     <row r="1175">
@@ -23975,16 +23975,16 @@
         <v>91.56999999999999</v>
       </c>
       <c r="C1178" t="n">
-        <v>93.44</v>
+        <v>93.68000000000001</v>
       </c>
       <c r="D1178" t="n">
         <v>91.55</v>
       </c>
       <c r="E1178" t="n">
-        <v>93.36</v>
+        <v>93.56</v>
       </c>
       <c r="F1178" t="n">
-        <v>89908</v>
+        <v>91727</v>
       </c>
     </row>
     <row r="1179">
@@ -24001,10 +24001,10 @@
         <v>92.14</v>
       </c>
       <c r="E1179" t="n">
-        <v>93.52</v>
+        <v>93.56999999999999</v>
       </c>
       <c r="F1179" t="n">
-        <v>100530</v>
+        <v>101498</v>
       </c>
     </row>
     <row r="1180">
@@ -24081,10 +24081,10 @@
         <v>91.23999999999999</v>
       </c>
       <c r="E1183" t="n">
-        <v>92.27</v>
+        <v>92.20999999999999</v>
       </c>
       <c r="F1183" t="n">
-        <v>97207</v>
+        <v>98137</v>
       </c>
     </row>
     <row r="1184">
@@ -24101,10 +24101,10 @@
         <v>91.68000000000001</v>
       </c>
       <c r="E1184" t="n">
-        <v>92.31</v>
+        <v>92.28</v>
       </c>
       <c r="F1184" t="n">
-        <v>98960</v>
+        <v>99665</v>
       </c>
     </row>
     <row r="1185">
@@ -24181,10 +24181,10 @@
         <v>92.56</v>
       </c>
       <c r="E1188" t="n">
-        <v>92.94</v>
+        <v>92.89</v>
       </c>
       <c r="F1188" t="n">
-        <v>127194</v>
+        <v>128240</v>
       </c>
     </row>
     <row r="1189">
@@ -24201,10 +24201,10 @@
         <v>91.68000000000001</v>
       </c>
       <c r="E1189" t="n">
-        <v>91.95999999999999</v>
+        <v>91.8</v>
       </c>
       <c r="F1189" t="n">
-        <v>116761</v>
+        <v>117877</v>
       </c>
     </row>
     <row r="1190">
@@ -24281,10 +24281,10 @@
         <v>83.31999999999999</v>
       </c>
       <c r="E1193" t="n">
-        <v>83.68000000000001</v>
+        <v>83.72</v>
       </c>
       <c r="F1193" t="n">
-        <v>148426</v>
+        <v>149779</v>
       </c>
     </row>
     <row r="1194">
@@ -24301,10 +24301,10 @@
         <v>82.97</v>
       </c>
       <c r="E1194" t="n">
-        <v>83.88</v>
+        <v>83.79000000000001</v>
       </c>
       <c r="F1194" t="n">
-        <v>138785</v>
+        <v>140020</v>
       </c>
     </row>
     <row r="1195">
@@ -24381,10 +24381,10 @@
         <v>84.59</v>
       </c>
       <c r="E1198" t="n">
-        <v>85.7</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="F1198" t="n">
-        <v>123421</v>
+        <v>124560</v>
       </c>
     </row>
     <row r="1199">
@@ -24404,7 +24404,7 @@
         <v>89.93000000000001</v>
       </c>
       <c r="F1199" t="n">
-        <v>118765</v>
+        <v>120817</v>
       </c>
     </row>
     <row r="1200">
@@ -24475,16 +24475,16 @@
         <v>90.26000000000001</v>
       </c>
       <c r="C1203" t="n">
-        <v>92.22</v>
+        <v>92.34999999999999</v>
       </c>
       <c r="D1203" t="n">
         <v>88.69</v>
       </c>
       <c r="E1203" t="n">
-        <v>92.16</v>
+        <v>92.04000000000001</v>
       </c>
       <c r="F1203" t="n">
-        <v>109002</v>
+        <v>111224</v>
       </c>
     </row>
     <row r="1204">
@@ -24501,10 +24501,10 @@
         <v>90.63</v>
       </c>
       <c r="E1204" t="n">
-        <v>91.13</v>
+        <v>91.26000000000001</v>
       </c>
       <c r="F1204" t="n">
-        <v>109157</v>
+        <v>110661</v>
       </c>
     </row>
     <row r="1205">
@@ -24581,10 +24581,10 @@
         <v>86.48</v>
       </c>
       <c r="E1208" t="n">
-        <v>87.25</v>
+        <v>87.23999999999999</v>
       </c>
       <c r="F1208" t="n">
-        <v>113368</v>
+        <v>114536</v>
       </c>
     </row>
     <row r="1209">
@@ -24601,10 +24601,10 @@
         <v>86.76000000000001</v>
       </c>
       <c r="E1209" t="n">
-        <v>88.76000000000001</v>
+        <v>88.70999999999999</v>
       </c>
       <c r="F1209" t="n">
-        <v>121600</v>
+        <v>123231</v>
       </c>
     </row>
     <row r="1210">
@@ -24672,7 +24672,7 @@
         <v>45232</v>
       </c>
       <c r="B1213" t="n">
-        <v>84.83</v>
+        <v>85.03</v>
       </c>
       <c r="C1213" t="n">
         <v>86.88</v>
@@ -24684,7 +24684,7 @@
         <v>86.63</v>
       </c>
       <c r="F1213" t="n">
-        <v>103842</v>
+        <v>102261</v>
       </c>
     </row>
     <row r="1214">
@@ -24692,7 +24692,7 @@
         <v>45233</v>
       </c>
       <c r="B1214" t="n">
-        <v>86.70999999999999</v>
+        <v>86.66</v>
       </c>
       <c r="C1214" t="n">
         <v>87.58</v>
@@ -24704,7 +24704,7 @@
         <v>84.95</v>
       </c>
       <c r="F1214" t="n">
-        <v>119097</v>
+        <v>117913</v>
       </c>
     </row>
     <row r="1215">
@@ -24781,10 +24781,10 @@
         <v>79.33</v>
       </c>
       <c r="E1218" t="n">
-        <v>79.75</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="F1218" t="n">
-        <v>110739</v>
+        <v>111847</v>
       </c>
     </row>
     <row r="1219">
@@ -24801,10 +24801,10 @@
         <v>79.70999999999999</v>
       </c>
       <c r="E1219" t="n">
-        <v>81.36</v>
+        <v>81.43000000000001</v>
       </c>
       <c r="F1219" t="n">
-        <v>91256</v>
+        <v>92327</v>
       </c>
     </row>
     <row r="1220">
@@ -24881,10 +24881,10 @@
         <v>76.64</v>
       </c>
       <c r="E1223" t="n">
-        <v>77.43000000000001</v>
+        <v>77.45</v>
       </c>
       <c r="F1223" t="n">
-        <v>104766</v>
+        <v>105749</v>
       </c>
     </row>
     <row r="1224">
@@ -24901,10 +24901,10 @@
         <v>77.31</v>
       </c>
       <c r="E1224" t="n">
-        <v>80.37</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="F1224" t="n">
-        <v>88772</v>
+        <v>89648</v>
       </c>
     </row>
     <row r="1225">
@@ -25078,13 +25078,13 @@
         <v>84.51000000000001</v>
       </c>
       <c r="D1233" t="n">
-        <v>79.95</v>
+        <v>79.94</v>
       </c>
       <c r="E1233" t="n">
-        <v>80</v>
+        <v>80.31</v>
       </c>
       <c r="F1233" t="n">
-        <v>143673</v>
+        <v>145419</v>
       </c>
     </row>
     <row r="1234">
@@ -25101,10 +25101,10 @@
         <v>78.69</v>
       </c>
       <c r="E1234" t="n">
-        <v>78.93000000000001</v>
+        <v>79.02</v>
       </c>
       <c r="F1234" t="n">
-        <v>125186</v>
+        <v>126159</v>
       </c>
     </row>
     <row r="1235">
@@ -25181,10 +25181,10 @@
         <v>73.68000000000001</v>
       </c>
       <c r="E1238" t="n">
-        <v>74.47</v>
+        <v>74.39</v>
       </c>
       <c r="F1238" t="n">
-        <v>115986</v>
+        <v>116791</v>
       </c>
     </row>
     <row r="1239">
@@ -25201,10 +25201,10 @@
         <v>74.25</v>
       </c>
       <c r="E1239" t="n">
-        <v>75.87</v>
+        <v>75.94</v>
       </c>
       <c r="F1239" t="n">
-        <v>114085</v>
+        <v>114930</v>
       </c>
     </row>
     <row r="1240">
@@ -25281,10 +25281,10 @@
         <v>74.56999999999999</v>
       </c>
       <c r="E1243" t="n">
-        <v>76.86</v>
+        <v>76.75</v>
       </c>
       <c r="F1243" t="n">
-        <v>83845</v>
+        <v>84712</v>
       </c>
     </row>
     <row r="1244">
@@ -25301,10 +25301,10 @@
         <v>75.48</v>
       </c>
       <c r="E1244" t="n">
-        <v>76.90000000000001</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="F1244" t="n">
-        <v>94162</v>
+        <v>95068</v>
       </c>
     </row>
     <row r="1245">
@@ -25381,10 +25381,10 @@
         <v>77.76000000000001</v>
       </c>
       <c r="E1248" t="n">
-        <v>79.19</v>
+        <v>79.12</v>
       </c>
       <c r="F1248" t="n">
-        <v>91100</v>
+        <v>91755</v>
       </c>
     </row>
     <row r="1249">
@@ -25461,10 +25461,10 @@
         <v>77.04000000000001</v>
       </c>
       <c r="E1252" t="n">
-        <v>77.29000000000001</v>
+        <v>77.36</v>
       </c>
       <c r="F1252" t="n">
-        <v>94380</v>
+        <v>95204</v>
       </c>
     </row>
     <row r="1253">
@@ -25544,7 +25544,7 @@
         <v>77.53</v>
       </c>
       <c r="F1256" t="n">
-        <v>118273</v>
+        <v>119158</v>
       </c>
     </row>
     <row r="1257">
@@ -25641,10 +25641,10 @@
         <v>76.45</v>
       </c>
       <c r="E1261" t="n">
-        <v>77.61</v>
+        <v>78.01000000000001</v>
       </c>
       <c r="F1261" t="n">
-        <v>128067</v>
+        <v>129868</v>
       </c>
     </row>
     <row r="1262">
@@ -25741,10 +25741,10 @@
         <v>76.98</v>
       </c>
       <c r="E1266" t="n">
-        <v>78.63</v>
+        <v>78.56</v>
       </c>
       <c r="F1266" t="n">
-        <v>98609</v>
+        <v>99368</v>
       </c>
     </row>
     <row r="1267">
@@ -25841,10 +25841,10 @@
         <v>79.65000000000001</v>
       </c>
       <c r="E1271" t="n">
-        <v>81.84999999999999</v>
+        <v>81.69</v>
       </c>
       <c r="F1271" t="n">
-        <v>75889</v>
+        <v>76710</v>
       </c>
     </row>
     <row r="1272">
@@ -25861,10 +25861,10 @@
         <v>80.75</v>
       </c>
       <c r="E1272" t="n">
-        <v>83.08</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="F1272" t="n">
-        <v>85666</v>
+        <v>87047</v>
       </c>
     </row>
     <row r="1273">
@@ -25941,10 +25941,10 @@
         <v>78.5</v>
       </c>
       <c r="E1276" t="n">
-        <v>78.64</v>
+        <v>78.7</v>
       </c>
       <c r="F1276" t="n">
-        <v>138682</v>
+        <v>140571</v>
       </c>
     </row>
     <row r="1277">
@@ -25961,10 +25961,10 @@
         <v>76.78</v>
       </c>
       <c r="E1277" t="n">
-        <v>77.11</v>
+        <v>77.31999999999999</v>
       </c>
       <c r="F1277" t="n">
-        <v>132023</v>
+        <v>133396</v>
       </c>
     </row>
     <row r="1278">
@@ -26041,10 +26041,10 @@
         <v>78.84999999999999</v>
       </c>
       <c r="E1281" t="n">
-        <v>81.51000000000001</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="F1281" t="n">
-        <v>86597</v>
+        <v>87658</v>
       </c>
     </row>
     <row r="1282">
@@ -26064,7 +26064,7 @@
         <v>81.63</v>
       </c>
       <c r="F1282" t="n">
-        <v>85346</v>
+        <v>86235</v>
       </c>
     </row>
     <row r="1283">
@@ -26141,10 +26141,10 @@
         <v>80.31999999999999</v>
       </c>
       <c r="E1286" t="n">
-        <v>82.37</v>
+        <v>82.22</v>
       </c>
       <c r="F1286" t="n">
-        <v>83753</v>
+        <v>84560</v>
       </c>
     </row>
     <row r="1287">
@@ -26161,10 +26161,10 @@
         <v>81.34</v>
       </c>
       <c r="E1287" t="n">
-        <v>82.70999999999999</v>
+        <v>82.68000000000001</v>
       </c>
       <c r="F1287" t="n">
-        <v>80620</v>
+        <v>81459</v>
       </c>
     </row>
     <row r="1288">
@@ -26241,10 +26241,10 @@
         <v>81.45</v>
       </c>
       <c r="E1291" t="n">
-        <v>82.63</v>
+        <v>82.51000000000001</v>
       </c>
       <c r="F1291" t="n">
-        <v>67106</v>
+        <v>67848</v>
       </c>
     </row>
     <row r="1292">
@@ -26261,10 +26261,10 @@
         <v>80.65000000000001</v>
       </c>
       <c r="E1292" t="n">
-        <v>80.88</v>
+        <v>80.84</v>
       </c>
       <c r="F1292" t="n">
-        <v>72495</v>
+        <v>73168</v>
       </c>
     </row>
     <row r="1293">
@@ -26341,10 +26341,10 @@
         <v>81.37</v>
       </c>
       <c r="E1296" t="n">
-        <v>81.70999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="F1296" t="n">
-        <v>78801</v>
+        <v>79642</v>
       </c>
     </row>
     <row r="1297">
@@ -26361,10 +26361,10 @@
         <v>81.63</v>
       </c>
       <c r="E1297" t="n">
-        <v>83.19</v>
+        <v>83.12</v>
       </c>
       <c r="F1297" t="n">
-        <v>72423</v>
+        <v>73275</v>
       </c>
     </row>
     <row r="1298">
@@ -26441,10 +26441,10 @@
         <v>81.77</v>
       </c>
       <c r="E1301" t="n">
-        <v>82.52</v>
+        <v>82.87</v>
       </c>
       <c r="F1301" t="n">
-        <v>102278</v>
+        <v>103853</v>
       </c>
     </row>
     <row r="1302">
@@ -26461,10 +26461,10 @@
         <v>81.41</v>
       </c>
       <c r="E1302" t="n">
-        <v>81.66</v>
+        <v>81.55</v>
       </c>
       <c r="F1302" t="n">
-        <v>99175</v>
+        <v>100115</v>
       </c>
     </row>
     <row r="1303">
@@ -26532,19 +26532,19 @@
         <v>45365</v>
       </c>
       <c r="B1306" t="n">
-        <v>83.59999999999999</v>
+        <v>83.69</v>
       </c>
       <c r="C1306" t="n">
         <v>85.18000000000001</v>
       </c>
       <c r="D1306" t="n">
-        <v>83.53</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="E1306" t="n">
         <v>84.61</v>
       </c>
       <c r="F1306" t="n">
-        <v>71844</v>
+        <v>71119</v>
       </c>
     </row>
     <row r="1307">
@@ -26552,7 +26552,7 @@
         <v>45366</v>
       </c>
       <c r="B1307" t="n">
-        <v>84.65000000000001</v>
+        <v>84.68000000000001</v>
       </c>
       <c r="C1307" t="n">
         <v>85.09</v>
@@ -26564,7 +26564,7 @@
         <v>84.83</v>
       </c>
       <c r="F1307" t="n">
-        <v>75864</v>
+        <v>74945</v>
       </c>
     </row>
     <row r="1308">
@@ -26632,7 +26632,7 @@
         <v>45372</v>
       </c>
       <c r="B1311" t="n">
-        <v>85.70999999999999</v>
+        <v>85.81</v>
       </c>
       <c r="C1311" t="n">
         <v>86.03</v>
@@ -26644,7 +26644,7 @@
         <v>84.95999999999999</v>
       </c>
       <c r="F1311" t="n">
-        <v>67186</v>
+        <v>66113</v>
       </c>
     </row>
     <row r="1312">
@@ -26652,7 +26652,7 @@
         <v>45373</v>
       </c>
       <c r="B1312" t="n">
-        <v>85.09999999999999</v>
+        <v>84.98999999999999</v>
       </c>
       <c r="C1312" t="n">
         <v>85.58</v>
@@ -26664,7 +26664,7 @@
         <v>84.93000000000001</v>
       </c>
       <c r="F1312" t="n">
-        <v>54286</v>
+        <v>53666</v>
       </c>
     </row>
     <row r="1313">
@@ -26732,7 +26732,7 @@
         <v>45379</v>
       </c>
       <c r="B1316" t="n">
-        <v>85.56</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="C1316" t="n">
         <v>86.89</v>
@@ -26744,7 +26744,7 @@
         <v>86.67</v>
       </c>
       <c r="F1316" t="n">
-        <v>57372</v>
+        <v>56915</v>
       </c>
     </row>
     <row r="1317">
@@ -26821,10 +26821,10 @@
         <v>88.43000000000001</v>
       </c>
       <c r="E1320" t="n">
-        <v>90.38</v>
+        <v>90.56</v>
       </c>
       <c r="F1320" t="n">
-        <v>74470</v>
+        <v>75666</v>
       </c>
     </row>
     <row r="1321">
@@ -26841,10 +26841,10 @@
         <v>90.18000000000001</v>
       </c>
       <c r="E1321" t="n">
-        <v>90.52</v>
+        <v>90.39</v>
       </c>
       <c r="F1321" t="n">
-        <v>79937</v>
+        <v>80607</v>
       </c>
     </row>
     <row r="1322">
@@ -26921,10 +26921,10 @@
         <v>88.87</v>
       </c>
       <c r="E1325" t="n">
-        <v>89.68000000000001</v>
+        <v>89.55</v>
       </c>
       <c r="F1325" t="n">
-        <v>107040</v>
+        <v>107884</v>
       </c>
     </row>
     <row r="1326">
@@ -26941,10 +26941,10 @@
         <v>89.45</v>
       </c>
       <c r="E1326" t="n">
-        <v>89.73</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="F1326" t="n">
-        <v>108331</v>
+        <v>109120</v>
       </c>
     </row>
     <row r="1327">
@@ -27021,10 +27021,10 @@
         <v>85.63</v>
       </c>
       <c r="E1330" t="n">
-        <v>86.47</v>
+        <v>86.19</v>
       </c>
       <c r="F1330" t="n">
-        <v>107464</v>
+        <v>108132</v>
       </c>
     </row>
     <row r="1331">
@@ -27041,10 +27041,10 @@
         <v>85.61</v>
       </c>
       <c r="E1331" t="n">
-        <v>86.51000000000001</v>
+        <v>86.38</v>
       </c>
       <c r="F1331" t="n">
-        <v>143518</v>
+        <v>144473</v>
       </c>
     </row>
     <row r="1332">
@@ -27115,16 +27115,16 @@
         <v>86.88</v>
       </c>
       <c r="C1335" t="n">
-        <v>87.97</v>
+        <v>88</v>
       </c>
       <c r="D1335" t="n">
         <v>86.2</v>
       </c>
       <c r="E1335" t="n">
-        <v>87.95</v>
+        <v>87.83</v>
       </c>
       <c r="F1335" t="n">
-        <v>69439</v>
+        <v>70059</v>
       </c>
     </row>
     <row r="1336">
@@ -27141,10 +27141,10 @@
         <v>87.56999999999999</v>
       </c>
       <c r="E1336" t="n">
-        <v>87.98999999999999</v>
+        <v>87.89</v>
       </c>
       <c r="F1336" t="n">
-        <v>63936</v>
+        <v>64445</v>
       </c>
     </row>
     <row r="1337">
@@ -27221,10 +27221,10 @@
         <v>82.89</v>
       </c>
       <c r="E1340" t="n">
-        <v>83.47</v>
+        <v>83.48</v>
       </c>
       <c r="F1340" t="n">
-        <v>100961</v>
+        <v>101847</v>
       </c>
     </row>
     <row r="1341">
@@ -27238,13 +27238,13 @@
         <v>84.18000000000001</v>
       </c>
       <c r="D1341" t="n">
-        <v>82.65000000000001</v>
+        <v>82.53</v>
       </c>
       <c r="E1341" t="n">
-        <v>82.77</v>
+        <v>82.54000000000001</v>
       </c>
       <c r="F1341" t="n">
-        <v>82987</v>
+        <v>83584</v>
       </c>
     </row>
     <row r="1342">
@@ -27321,10 +27321,10 @@
         <v>83.18000000000001</v>
       </c>
       <c r="E1345" t="n">
-        <v>83.91</v>
+        <v>83.77</v>
       </c>
       <c r="F1345" t="n">
-        <v>67201</v>
+        <v>67737</v>
       </c>
     </row>
     <row r="1346">
@@ -27338,13 +27338,13 @@
         <v>84.23</v>
       </c>
       <c r="D1346" t="n">
-        <v>82.5</v>
+        <v>82.36</v>
       </c>
       <c r="E1346" t="n">
-        <v>82.61</v>
+        <v>82.36</v>
       </c>
       <c r="F1346" t="n">
-        <v>62356</v>
+        <v>63117</v>
       </c>
     </row>
     <row r="1347">
@@ -27421,10 +27421,10 @@
         <v>82.02</v>
       </c>
       <c r="E1350" t="n">
-        <v>83.04000000000001</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="F1350" t="n">
-        <v>65306</v>
+        <v>65759</v>
       </c>
     </row>
     <row r="1351">
@@ -27441,10 +27441,10 @@
         <v>82.81999999999999</v>
       </c>
       <c r="E1351" t="n">
-        <v>83.68000000000001</v>
+        <v>83.56</v>
       </c>
       <c r="F1351" t="n">
-        <v>60667</v>
+        <v>61133</v>
       </c>
     </row>
     <row r="1352">
@@ -27521,10 +27521,10 @@
         <v>80.7</v>
       </c>
       <c r="E1355" t="n">
-        <v>81.09</v>
+        <v>81.06999999999999</v>
       </c>
       <c r="F1355" t="n">
-        <v>68901</v>
+        <v>69958</v>
       </c>
     </row>
     <row r="1356">
@@ -27541,10 +27541,10 @@
         <v>80.42</v>
       </c>
       <c r="E1356" t="n">
-        <v>81.84999999999999</v>
+        <v>81.79000000000001</v>
       </c>
       <c r="F1356" t="n">
-        <v>56045</v>
+        <v>56381</v>
       </c>
     </row>
     <row r="1357">
@@ -27618,13 +27618,13 @@
         <v>83.51000000000001</v>
       </c>
       <c r="D1360" t="n">
-        <v>81.77</v>
+        <v>81.72</v>
       </c>
       <c r="E1360" t="n">
-        <v>81.88</v>
+        <v>81.73</v>
       </c>
       <c r="F1360" t="n">
-        <v>81262</v>
+        <v>81864</v>
       </c>
     </row>
     <row r="1361">
@@ -27641,10 +27641,10 @@
         <v>80.69</v>
       </c>
       <c r="E1361" t="n">
-        <v>81.22</v>
+        <v>81.09</v>
       </c>
       <c r="F1361" t="n">
-        <v>86335</v>
+        <v>87130</v>
       </c>
     </row>
     <row r="1362">
@@ -27721,10 +27721,10 @@
         <v>78.23999999999999</v>
       </c>
       <c r="E1365" t="n">
-        <v>79.73</v>
+        <v>79.69</v>
       </c>
       <c r="F1365" t="n">
-        <v>72035</v>
+        <v>72677</v>
       </c>
     </row>
     <row r="1366">
@@ -27741,10 +27741,10 @@
         <v>79.18000000000001</v>
       </c>
       <c r="E1366" t="n">
-        <v>79.27</v>
+        <v>79.23999999999999</v>
       </c>
       <c r="F1366" t="n">
-        <v>76576</v>
+        <v>77440</v>
       </c>
     </row>
     <row r="1367">
@@ -27821,10 +27821,10 @@
         <v>81.53</v>
       </c>
       <c r="E1370" t="n">
-        <v>81.98</v>
+        <v>81.68000000000001</v>
       </c>
       <c r="F1370" t="n">
-        <v>78296</v>
+        <v>79567</v>
       </c>
     </row>
     <row r="1371">
@@ -27841,10 +27841,10 @@
         <v>81.64</v>
       </c>
       <c r="E1371" t="n">
-        <v>82.2</v>
+        <v>82.06</v>
       </c>
       <c r="F1371" t="n">
-        <v>75030</v>
+        <v>75768</v>
       </c>
     </row>
     <row r="1372">
@@ -27921,10 +27921,10 @@
         <v>84.28</v>
       </c>
       <c r="E1375" t="n">
-        <v>85.01000000000001</v>
+        <v>84.7</v>
       </c>
       <c r="F1375" t="n">
-        <v>59448</v>
+        <v>59846</v>
       </c>
     </row>
     <row r="1376">
@@ -27941,10 +27941,10 @@
         <v>84</v>
       </c>
       <c r="E1376" t="n">
-        <v>84.31</v>
+        <v>84.16</v>
       </c>
       <c r="F1376" t="n">
-        <v>59797</v>
+        <v>60278</v>
       </c>
     </row>
     <row r="1377">
@@ -28021,10 +28021,10 @@
         <v>84.01000000000001</v>
       </c>
       <c r="E1380" t="n">
-        <v>85.25</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="F1380" t="n">
-        <v>64362</v>
+        <v>64909</v>
       </c>
     </row>
     <row r="1381">
@@ -28041,10 +28041,10 @@
         <v>84.39</v>
       </c>
       <c r="E1381" t="n">
-        <v>84.79000000000001</v>
+        <v>84.65000000000001</v>
       </c>
       <c r="F1381" t="n">
-        <v>69177</v>
+        <v>69862</v>
       </c>
     </row>
     <row r="1382">
@@ -28141,10 +28141,10 @@
         <v>86.17</v>
       </c>
       <c r="E1386" t="n">
-        <v>86.31999999999999</v>
+        <v>86.43000000000001</v>
       </c>
       <c r="F1386" t="n">
-        <v>67919</v>
+        <v>68965</v>
       </c>
     </row>
     <row r="1387">
@@ -28221,10 +28221,10 @@
         <v>84.16</v>
       </c>
       <c r="E1390" t="n">
-        <v>85.19</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="F1390" t="n">
-        <v>78243</v>
+        <v>78990</v>
       </c>
     </row>
     <row r="1391">
@@ -28238,13 +28238,13 @@
         <v>85.67</v>
       </c>
       <c r="D1391" t="n">
-        <v>84.40000000000001</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="E1391" t="n">
-        <v>84.5</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="F1391" t="n">
-        <v>73607</v>
+        <v>74302</v>
       </c>
     </row>
     <row r="1392">
@@ -28321,10 +28321,10 @@
         <v>83.41</v>
       </c>
       <c r="E1395" t="n">
-        <v>83.72</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="F1395" t="n">
-        <v>68620</v>
+        <v>69797</v>
       </c>
     </row>
     <row r="1396">
@@ -28338,13 +28338,13 @@
         <v>84.41</v>
       </c>
       <c r="D1396" t="n">
-        <v>81.7</v>
+        <v>81.64</v>
       </c>
       <c r="E1396" t="n">
-        <v>81.89</v>
+        <v>81.64</v>
       </c>
       <c r="F1396" t="n">
-        <v>72020</v>
+        <v>72736</v>
       </c>
     </row>
     <row r="1397">
@@ -28421,10 +28421,10 @@
         <v>79.28</v>
       </c>
       <c r="E1400" t="n">
-        <v>81.33</v>
+        <v>81.37</v>
       </c>
       <c r="F1400" t="n">
-        <v>69150</v>
+        <v>69789</v>
       </c>
     </row>
     <row r="1401">
@@ -28441,10 +28441,10 @@
         <v>79.39</v>
       </c>
       <c r="E1401" t="n">
-        <v>79.92</v>
+        <v>79.48999999999999</v>
       </c>
       <c r="F1401" t="n">
-        <v>64725</v>
+        <v>65748</v>
       </c>
     </row>
     <row r="1402">
@@ -28521,10 +28521,10 @@
         <v>79.3</v>
       </c>
       <c r="E1405" t="n">
-        <v>80</v>
+        <v>79.83</v>
       </c>
       <c r="F1405" t="n">
-        <v>104482</v>
+        <v>105741</v>
       </c>
     </row>
     <row r="1406">
@@ -28541,10 +28541,10 @@
         <v>76.26000000000001</v>
       </c>
       <c r="E1406" t="n">
-        <v>77.08</v>
+        <v>77.14</v>
       </c>
       <c r="F1406" t="n">
-        <v>124356</v>
+        <v>125792</v>
       </c>
     </row>
     <row r="1407">
@@ -28621,10 +28621,10 @@
         <v>77.33</v>
       </c>
       <c r="E1410" t="n">
-        <v>78.73999999999999</v>
+        <v>78.59</v>
       </c>
       <c r="F1410" t="n">
-        <v>113028</v>
+        <v>113892</v>
       </c>
     </row>
     <row r="1411">
@@ -28641,10 +28641,10 @@
         <v>78.43000000000001</v>
       </c>
       <c r="E1411" t="n">
-        <v>79.34</v>
+        <v>79.27</v>
       </c>
       <c r="F1411" t="n">
-        <v>86405</v>
+        <v>87467</v>
       </c>
     </row>
     <row r="1412">
@@ -28721,10 +28721,10 @@
         <v>79.11</v>
       </c>
       <c r="E1415" t="n">
-        <v>80.31999999999999</v>
+        <v>80.26000000000001</v>
       </c>
       <c r="F1415" t="n">
-        <v>78757</v>
+        <v>79567</v>
       </c>
     </row>
     <row r="1416">
@@ -28741,10 +28741,10 @@
         <v>78.09</v>
       </c>
       <c r="E1416" t="n">
-        <v>79.22</v>
+        <v>78.94</v>
       </c>
       <c r="F1416" t="n">
-        <v>81009</v>
+        <v>82030</v>
       </c>
     </row>
     <row r="1417">
@@ -28821,10 +28821,10 @@
         <v>75.25</v>
       </c>
       <c r="E1420" t="n">
-        <v>76.47</v>
+        <v>76.42</v>
       </c>
       <c r="F1420" t="n">
-        <v>79280</v>
+        <v>79873</v>
       </c>
     </row>
     <row r="1421">
@@ -28841,10 +28841,10 @@
         <v>76.40000000000001</v>
       </c>
       <c r="E1421" t="n">
-        <v>78.17</v>
+        <v>78.13</v>
       </c>
       <c r="F1421" t="n">
-        <v>68613</v>
+        <v>69081</v>
       </c>
     </row>
     <row r="1422">
@@ -28921,10 +28921,10 @@
         <v>76.90000000000001</v>
       </c>
       <c r="E1425" t="n">
-        <v>78.81</v>
+        <v>78.72</v>
       </c>
       <c r="F1425" t="n">
-        <v>93699</v>
+        <v>94397</v>
       </c>
     </row>
     <row r="1426">
@@ -28941,10 +28941,10 @@
         <v>76.56</v>
       </c>
       <c r="E1426" t="n">
-        <v>76.81</v>
+        <v>76.77</v>
       </c>
       <c r="F1426" t="n">
-        <v>108329</v>
+        <v>109124</v>
       </c>
     </row>
     <row r="1427">
@@ -29021,10 +29021,10 @@
         <v>72.20999999999999</v>
       </c>
       <c r="E1430" t="n">
-        <v>72.54000000000001</v>
+        <v>72.53</v>
       </c>
       <c r="F1430" t="n">
-        <v>108713</v>
+        <v>109541</v>
       </c>
     </row>
     <row r="1431">
@@ -29041,10 +29041,10 @@
         <v>70.45</v>
       </c>
       <c r="E1431" t="n">
-        <v>71.37</v>
+        <v>71.2</v>
       </c>
       <c r="F1431" t="n">
-        <v>115759</v>
+        <v>116954</v>
       </c>
     </row>
     <row r="1432">
@@ -29121,10 +29121,10 @@
         <v>70.31999999999999</v>
       </c>
       <c r="E1435" t="n">
-        <v>71.89</v>
+        <v>71.67</v>
       </c>
       <c r="F1435" t="n">
-        <v>114181</v>
+        <v>115156</v>
       </c>
     </row>
     <row r="1436">
@@ -29141,10 +29141,10 @@
         <v>71.09</v>
       </c>
       <c r="E1436" t="n">
-        <v>71.73</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="F1436" t="n">
-        <v>98569</v>
+        <v>99629</v>
       </c>
     </row>
     <row r="1437">
@@ -29221,10 +29221,10 @@
         <v>72.26000000000001</v>
       </c>
       <c r="E1440" t="n">
-        <v>74.05</v>
+        <v>73.97</v>
       </c>
       <c r="F1440" t="n">
-        <v>88395</v>
+        <v>89094</v>
       </c>
     </row>
     <row r="1441">
@@ -29241,10 +29241,10 @@
         <v>73.28</v>
       </c>
       <c r="E1441" t="n">
-        <v>73.98</v>
+        <v>73.87</v>
       </c>
       <c r="F1441" t="n">
-        <v>71635</v>
+        <v>72413</v>
       </c>
     </row>
     <row r="1442">
@@ -29321,10 +29321,10 @@
         <v>70.20999999999999</v>
       </c>
       <c r="E1445" t="n">
-        <v>70.66</v>
+        <v>70.68000000000001</v>
       </c>
       <c r="F1445" t="n">
-        <v>154979</v>
+        <v>155899</v>
       </c>
     </row>
     <row r="1446">
@@ -29335,16 +29335,16 @@
         <v>70.68000000000001</v>
       </c>
       <c r="C1446" t="n">
-        <v>71.89</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="D1446" t="n">
         <v>70.39</v>
       </c>
       <c r="E1446" t="n">
-        <v>71.81999999999999</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="F1446" t="n">
-        <v>122438</v>
+        <v>123787</v>
       </c>
     </row>
     <row r="1447">
@@ -29421,10 +29421,10 @@
         <v>74.18000000000001</v>
       </c>
       <c r="E1450" t="n">
-        <v>77.58</v>
+        <v>77.28</v>
       </c>
       <c r="F1450" t="n">
-        <v>123449</v>
+        <v>125075</v>
       </c>
     </row>
     <row r="1451">
@@ -29441,10 +29441,10 @@
         <v>77.19</v>
       </c>
       <c r="E1451" t="n">
-        <v>77.87</v>
+        <v>77.73</v>
       </c>
       <c r="F1451" t="n">
-        <v>120535</v>
+        <v>121412</v>
       </c>
     </row>
     <row r="1452">
@@ -39084,7 +39084,27 @@
         <v>90.13</v>
       </c>
       <c r="F1933" t="n">
-        <v>101698</v>
+        <v>101485</v>
+      </c>
+    </row>
+    <row r="1934">
+      <c r="A1934" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B1934" t="n">
+        <v>90.18000000000001</v>
+      </c>
+      <c r="C1934" t="n">
+        <v>92.98999999999999</v>
+      </c>
+      <c r="D1934" t="n">
+        <v>90</v>
+      </c>
+      <c r="E1934" t="n">
+        <v>91.72</v>
+      </c>
+      <c r="F1934" t="n">
+        <v>103131</v>
       </c>
     </row>
   </sheetData>

--- a/database/BRENT.xlsx
+++ b/database/BRENT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1934"/>
+  <dimension ref="A1:F1935"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3881,10 +3881,10 @@
         <v>60.96</v>
       </c>
       <c r="E173" t="n">
-        <v>61.65</v>
+        <v>61.74</v>
       </c>
       <c r="F173" t="n">
-        <v>7745</v>
+        <v>7439</v>
       </c>
     </row>
     <row r="174">
@@ -3952,7 +3952,7 @@
         <v>43769</v>
       </c>
       <c r="B177" t="n">
-        <v>60.27</v>
+        <v>60.17</v>
       </c>
       <c r="C177" t="n">
         <v>60.79</v>
@@ -3964,7 +3964,7 @@
         <v>59.46</v>
       </c>
       <c r="F177" t="n">
-        <v>20603</v>
+        <v>20831</v>
       </c>
     </row>
     <row r="178">
@@ -3972,7 +3972,7 @@
         <v>43770</v>
       </c>
       <c r="B178" t="n">
-        <v>59.64</v>
+        <v>59.42</v>
       </c>
       <c r="C178" t="n">
         <v>61.8</v>
@@ -3984,7 +3984,7 @@
         <v>61.65</v>
       </c>
       <c r="F178" t="n">
-        <v>18281</v>
+        <v>18539</v>
       </c>
     </row>
     <row r="179">
@@ -4061,10 +4061,10 @@
         <v>61.63</v>
       </c>
       <c r="E182" t="n">
-        <v>62.29</v>
+        <v>62.14</v>
       </c>
       <c r="F182" t="n">
-        <v>19680</v>
+        <v>19306</v>
       </c>
     </row>
     <row r="183">
@@ -4081,10 +4081,10 @@
         <v>60.65</v>
       </c>
       <c r="E183" t="n">
-        <v>62.64</v>
+        <v>62.61</v>
       </c>
       <c r="F183" t="n">
-        <v>21863</v>
+        <v>21625</v>
       </c>
     </row>
     <row r="184">
@@ -4161,10 +4161,10 @@
         <v>62.14</v>
       </c>
       <c r="E187" t="n">
-        <v>62.33</v>
+        <v>62.38</v>
       </c>
       <c r="F187" t="n">
-        <v>19293</v>
+        <v>19157</v>
       </c>
     </row>
     <row r="188">
@@ -4181,10 +4181,10 @@
         <v>61.69</v>
       </c>
       <c r="E188" t="n">
-        <v>63.41</v>
+        <v>63.32</v>
       </c>
       <c r="F188" t="n">
-        <v>16092</v>
+        <v>15801</v>
       </c>
     </row>
     <row r="189">
@@ -4261,10 +4261,10 @@
         <v>61.91</v>
       </c>
       <c r="E192" t="n">
-        <v>63.64</v>
+        <v>63.74</v>
       </c>
       <c r="F192" t="n">
-        <v>21823</v>
+        <v>21582</v>
       </c>
     </row>
     <row r="193">
@@ -4281,10 +4281,10 @@
         <v>61.92</v>
       </c>
       <c r="E193" t="n">
-        <v>62.52</v>
+        <v>62.58</v>
       </c>
       <c r="F193" t="n">
-        <v>17794</v>
+        <v>17577</v>
       </c>
     </row>
     <row r="194">
@@ -4461,10 +4461,10 @@
         <v>62.73</v>
       </c>
       <c r="E202" t="n">
-        <v>63.26</v>
+        <v>63.33</v>
       </c>
       <c r="F202" t="n">
-        <v>24300</v>
+        <v>24042</v>
       </c>
     </row>
     <row r="203">
@@ -4481,10 +4481,10 @@
         <v>62.82</v>
       </c>
       <c r="E203" t="n">
-        <v>64.34</v>
+        <v>64.22</v>
       </c>
       <c r="F203" t="n">
-        <v>22572</v>
+        <v>22359</v>
       </c>
     </row>
     <row r="204">
@@ -4561,10 +4561,10 @@
         <v>63.86</v>
       </c>
       <c r="E207" t="n">
-        <v>64.28</v>
+        <v>64.31</v>
       </c>
       <c r="F207" t="n">
-        <v>18454</v>
+        <v>18198</v>
       </c>
     </row>
     <row r="208">
@@ -4581,10 +4581,10 @@
         <v>64.48</v>
       </c>
       <c r="E208" t="n">
-        <v>64.90000000000001</v>
+        <v>64.88</v>
       </c>
       <c r="F208" t="n">
-        <v>21671</v>
+        <v>21484</v>
       </c>
     </row>
     <row r="209">
@@ -4661,10 +4661,10 @@
         <v>66.02</v>
       </c>
       <c r="E212" t="n">
-        <v>66.53</v>
+        <v>66.45</v>
       </c>
       <c r="F212" t="n">
-        <v>11180</v>
+        <v>10932</v>
       </c>
     </row>
     <row r="213">
@@ -4681,10 +4681,10 @@
         <v>65.72</v>
       </c>
       <c r="E213" t="n">
-        <v>66.01000000000001</v>
+        <v>65.98</v>
       </c>
       <c r="F213" t="n">
-        <v>14806</v>
+        <v>14693</v>
       </c>
     </row>
     <row r="214">
@@ -4741,10 +4741,10 @@
         <v>66.09</v>
       </c>
       <c r="E216" t="n">
-        <v>66.75</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="F216" t="n">
-        <v>9613</v>
+        <v>9409</v>
       </c>
     </row>
     <row r="217">
@@ -4761,10 +4761,10 @@
         <v>66.34</v>
       </c>
       <c r="E217" t="n">
-        <v>66.84</v>
+        <v>66.81</v>
       </c>
       <c r="F217" t="n">
-        <v>11398</v>
+        <v>11272</v>
       </c>
     </row>
     <row r="218">
@@ -4821,10 +4821,10 @@
         <v>65.7</v>
       </c>
       <c r="E220" t="n">
-        <v>66.23</v>
+        <v>66.19</v>
       </c>
       <c r="F220" t="n">
-        <v>15351</v>
+        <v>15153</v>
       </c>
     </row>
     <row r="221">
@@ -4841,10 +4841,10 @@
         <v>66.19</v>
       </c>
       <c r="E221" t="n">
-        <v>68.59</v>
+        <v>68.55</v>
       </c>
       <c r="F221" t="n">
-        <v>35609</v>
+        <v>35427</v>
       </c>
     </row>
     <row r="222">
@@ -4924,7 +4924,7 @@
         <v>65.38</v>
       </c>
       <c r="F225" t="n">
-        <v>25951</v>
+        <v>25682</v>
       </c>
     </row>
     <row r="226">
@@ -4944,7 +4944,7 @@
         <v>65</v>
       </c>
       <c r="F226" t="n">
-        <v>20436</v>
+        <v>20016</v>
       </c>
     </row>
     <row r="227">
@@ -5021,10 +5021,10 @@
         <v>63.89</v>
       </c>
       <c r="E230" t="n">
-        <v>64.7</v>
+        <v>64.64</v>
       </c>
       <c r="F230" t="n">
-        <v>16472</v>
+        <v>16107</v>
       </c>
     </row>
     <row r="231">
@@ -5041,10 +5041,10 @@
         <v>64.45</v>
       </c>
       <c r="E231" t="n">
-        <v>65.08</v>
+        <v>64.95</v>
       </c>
       <c r="F231" t="n">
-        <v>16251</v>
+        <v>16060</v>
       </c>
     </row>
     <row r="232">
@@ -5121,10 +5121,10 @@
         <v>61.24</v>
       </c>
       <c r="E235" t="n">
-        <v>62.11</v>
+        <v>61.97</v>
       </c>
       <c r="F235" t="n">
-        <v>23208</v>
+        <v>22982</v>
       </c>
     </row>
     <row r="236">
@@ -5141,10 +5141,10 @@
         <v>60.24</v>
       </c>
       <c r="E236" t="n">
-        <v>60.64</v>
+        <v>60.82</v>
       </c>
       <c r="F236" t="n">
-        <v>21687</v>
+        <v>21411</v>
       </c>
     </row>
     <row r="237">
@@ -5221,10 +5221,10 @@
         <v>56.73</v>
       </c>
       <c r="E240" t="n">
-        <v>58.2</v>
+        <v>58.03</v>
       </c>
       <c r="F240" t="n">
-        <v>28894</v>
+        <v>28317</v>
       </c>
     </row>
     <row r="241">
@@ -5244,7 +5244,7 @@
         <v>56.63</v>
       </c>
       <c r="F241" t="n">
-        <v>31264</v>
+        <v>30854</v>
       </c>
     </row>
     <row r="242">
@@ -5321,10 +5321,10 @@
         <v>54.24</v>
       </c>
       <c r="E245" t="n">
-        <v>55.14</v>
+        <v>55.07</v>
       </c>
       <c r="F245" t="n">
-        <v>31917</v>
+        <v>31638</v>
       </c>
     </row>
     <row r="246">
@@ -5341,10 +5341,10 @@
         <v>54.2</v>
       </c>
       <c r="E246" t="n">
-        <v>54.45</v>
+        <v>54.48</v>
       </c>
       <c r="F246" t="n">
-        <v>26144</v>
+        <v>25828</v>
       </c>
     </row>
     <row r="247">
@@ -5421,10 +5421,10 @@
         <v>54.95</v>
       </c>
       <c r="E250" t="n">
-        <v>56.4</v>
+        <v>56.51</v>
       </c>
       <c r="F250" t="n">
-        <v>24914</v>
+        <v>24675</v>
       </c>
     </row>
     <row r="251">
@@ -5441,10 +5441,10 @@
         <v>56.13</v>
       </c>
       <c r="E251" t="n">
-        <v>57.33</v>
+        <v>57.32</v>
       </c>
       <c r="F251" t="n">
-        <v>21778</v>
+        <v>21410</v>
       </c>
     </row>
     <row r="252">
@@ -5521,10 +5521,10 @@
         <v>58.89</v>
       </c>
       <c r="E255" t="n">
-        <v>59.03</v>
+        <v>59.28</v>
       </c>
       <c r="F255" t="n">
-        <v>23391</v>
+        <v>23121</v>
       </c>
     </row>
     <row r="256">
@@ -5541,10 +5541,10 @@
         <v>57.71</v>
       </c>
       <c r="E256" t="n">
-        <v>58.44</v>
+        <v>58.33</v>
       </c>
       <c r="F256" t="n">
-        <v>26971</v>
+        <v>26663</v>
       </c>
     </row>
     <row r="257">
@@ -5621,10 +5621,10 @@
         <v>50.38</v>
       </c>
       <c r="E260" t="n">
-        <v>50.95</v>
+        <v>51.35</v>
       </c>
       <c r="F260" t="n">
-        <v>52807</v>
+        <v>51199</v>
       </c>
     </row>
     <row r="261">
@@ -5641,10 +5641,10 @@
         <v>48.92</v>
       </c>
       <c r="E261" t="n">
-        <v>50.08</v>
+        <v>50.01</v>
       </c>
       <c r="F261" t="n">
-        <v>72794</v>
+        <v>71739</v>
       </c>
     </row>
     <row r="262">
@@ -5721,10 +5721,10 @@
         <v>49.67</v>
       </c>
       <c r="E265" t="n">
-        <v>50</v>
+        <v>49.95</v>
       </c>
       <c r="F265" t="n">
-        <v>42678</v>
+        <v>42080</v>
       </c>
     </row>
     <row r="266">
@@ -5741,10 +5741,10 @@
         <v>45.16</v>
       </c>
       <c r="E266" t="n">
-        <v>45.51</v>
+        <v>45.55</v>
       </c>
       <c r="F266" t="n">
-        <v>65295</v>
+        <v>64437</v>
       </c>
     </row>
     <row r="267">
@@ -5812,7 +5812,7 @@
         <v>43902</v>
       </c>
       <c r="B270" t="n">
-        <v>36.29</v>
+        <v>35.97</v>
       </c>
       <c r="C270" t="n">
         <v>36.45</v>
@@ -5824,7 +5824,7 @@
         <v>33.49</v>
       </c>
       <c r="F270" t="n">
-        <v>64469</v>
+        <v>66181</v>
       </c>
     </row>
     <row r="271">
@@ -6121,10 +6121,10 @@
         <v>26.12</v>
       </c>
       <c r="E285" t="n">
-        <v>29.96</v>
+        <v>30.29</v>
       </c>
       <c r="F285" t="n">
-        <v>214756</v>
+        <v>210087</v>
       </c>
     </row>
     <row r="286">
@@ -6135,16 +6135,16 @@
         <v>29.95</v>
       </c>
       <c r="C286" t="n">
-        <v>35.28</v>
+        <v>35.24</v>
       </c>
       <c r="D286" t="n">
         <v>28.9</v>
       </c>
       <c r="E286" t="n">
-        <v>35.16</v>
+        <v>34.72</v>
       </c>
       <c r="F286" t="n">
-        <v>280402</v>
+        <v>275171</v>
       </c>
     </row>
     <row r="287">
@@ -6221,10 +6221,10 @@
         <v>32.46</v>
       </c>
       <c r="E290" t="n">
-        <v>32.8</v>
+        <v>33.2</v>
       </c>
       <c r="F290" t="n">
-        <v>236196</v>
+        <v>230614</v>
       </c>
     </row>
     <row r="291">
@@ -6321,10 +6321,10 @@
         <v>29.42</v>
       </c>
       <c r="E295" t="n">
-        <v>30.59</v>
+        <v>30.65</v>
       </c>
       <c r="F295" t="n">
-        <v>151526</v>
+        <v>146842</v>
       </c>
     </row>
     <row r="296">
@@ -6341,10 +6341,10 @@
         <v>30.13</v>
       </c>
       <c r="E296" t="n">
-        <v>30.68</v>
+        <v>30.78</v>
       </c>
       <c r="F296" t="n">
-        <v>174982</v>
+        <v>171223</v>
       </c>
     </row>
     <row r="297">
@@ -6421,10 +6421,10 @@
         <v>23.38</v>
       </c>
       <c r="E300" t="n">
-        <v>24.73</v>
+        <v>24.74</v>
       </c>
       <c r="F300" t="n">
-        <v>216653</v>
+        <v>213310</v>
       </c>
     </row>
     <row r="301">
@@ -6441,10 +6441,10 @@
         <v>23.7</v>
       </c>
       <c r="E301" t="n">
-        <v>24.99</v>
+        <v>24.98</v>
       </c>
       <c r="F301" t="n">
-        <v>166443</v>
+        <v>163124</v>
       </c>
     </row>
     <row r="302">
@@ -6521,10 +6521,10 @@
         <v>24.33</v>
       </c>
       <c r="E305" t="n">
-        <v>26.85</v>
+        <v>26.83</v>
       </c>
       <c r="F305" t="n">
-        <v>229615</v>
+        <v>224455</v>
       </c>
     </row>
     <row r="306">
@@ -6541,10 +6541,10 @@
         <v>26.05</v>
       </c>
       <c r="E306" t="n">
-        <v>26.81</v>
+        <v>26.78</v>
       </c>
       <c r="F306" t="n">
-        <v>199609</v>
+        <v>196748</v>
       </c>
     </row>
     <row r="307">
@@ -6621,10 +6621,10 @@
         <v>29.4</v>
       </c>
       <c r="E310" t="n">
-        <v>29.65</v>
+        <v>29.48</v>
       </c>
       <c r="F310" t="n">
-        <v>229585</v>
+        <v>225301</v>
       </c>
     </row>
     <row r="311">
@@ -6641,10 +6641,10 @@
         <v>29.63</v>
       </c>
       <c r="E311" t="n">
-        <v>31.25</v>
+        <v>31.26</v>
       </c>
       <c r="F311" t="n">
-        <v>195288</v>
+        <v>192233</v>
       </c>
     </row>
     <row r="312">
@@ -6715,16 +6715,16 @@
         <v>29.73</v>
       </c>
       <c r="C315" t="n">
-        <v>31.75</v>
+        <v>31.65</v>
       </c>
       <c r="D315" t="n">
         <v>29.32</v>
       </c>
       <c r="E315" t="n">
-        <v>31.58</v>
+        <v>31.44</v>
       </c>
       <c r="F315" t="n">
-        <v>156389</v>
+        <v>152193</v>
       </c>
     </row>
     <row r="316">
@@ -6735,16 +6735,16 @@
         <v>31.58</v>
       </c>
       <c r="C316" t="n">
-        <v>33.06</v>
+        <v>32.96</v>
       </c>
       <c r="D316" t="n">
         <v>31.23</v>
       </c>
       <c r="E316" t="n">
-        <v>32.94</v>
+        <v>32.9</v>
       </c>
       <c r="F316" t="n">
-        <v>163209</v>
+        <v>160121</v>
       </c>
     </row>
     <row r="317">
@@ -6821,10 +6821,10 @@
         <v>35.92</v>
       </c>
       <c r="E320" t="n">
-        <v>36.3</v>
+        <v>36.38</v>
       </c>
       <c r="F320" t="n">
-        <v>160329</v>
+        <v>157279</v>
       </c>
     </row>
     <row r="321">
@@ -6841,10 +6841,10 @@
         <v>33.87</v>
       </c>
       <c r="E321" t="n">
-        <v>35.52</v>
+        <v>35.66</v>
       </c>
       <c r="F321" t="n">
-        <v>198023</v>
+        <v>194062</v>
       </c>
     </row>
     <row r="322">
@@ -6921,10 +6921,10 @@
         <v>34.37</v>
       </c>
       <c r="E325" t="n">
-        <v>35.98</v>
+        <v>35.89</v>
       </c>
       <c r="F325" t="n">
-        <v>213086</v>
+        <v>208524</v>
       </c>
     </row>
     <row r="326">
@@ -6941,10 +6941,10 @@
         <v>34.87</v>
       </c>
       <c r="E326" t="n">
-        <v>37.61</v>
+        <v>37.43</v>
       </c>
       <c r="F326" t="n">
-        <v>198370</v>
+        <v>193664</v>
       </c>
     </row>
     <row r="327">
@@ -7021,10 +7021,10 @@
         <v>39.05</v>
       </c>
       <c r="E330" t="n">
-        <v>39.92</v>
+        <v>39.78</v>
       </c>
       <c r="F330" t="n">
-        <v>161661</v>
+        <v>158433</v>
       </c>
     </row>
     <row r="331">
@@ -7041,10 +7041,10 @@
         <v>39.75</v>
       </c>
       <c r="E331" t="n">
-        <v>41.83</v>
+        <v>42.14</v>
       </c>
       <c r="F331" t="n">
-        <v>167359</v>
+        <v>163467</v>
       </c>
     </row>
     <row r="332">
@@ -7121,10 +7121,10 @@
         <v>37.96</v>
       </c>
       <c r="E335" t="n">
-        <v>38.41</v>
+        <v>38.36</v>
       </c>
       <c r="F335" t="n">
-        <v>227925</v>
+        <v>221502</v>
       </c>
     </row>
     <row r="336">
@@ -7141,10 +7141,10 @@
         <v>37.14</v>
       </c>
       <c r="E336" t="n">
-        <v>38.97</v>
+        <v>38.94</v>
       </c>
       <c r="F336" t="n">
-        <v>263342</v>
+        <v>260674</v>
       </c>
     </row>
     <row r="337">
@@ -7221,10 +7221,10 @@
         <v>40.05</v>
       </c>
       <c r="E340" t="n">
-        <v>41.33</v>
+        <v>41.37</v>
       </c>
       <c r="F340" t="n">
-        <v>163774</v>
+        <v>161532</v>
       </c>
     </row>
     <row r="341">
@@ -7241,10 +7241,10 @@
         <v>40.97</v>
       </c>
       <c r="E341" t="n">
-        <v>41.78</v>
+        <v>41.99</v>
       </c>
       <c r="F341" t="n">
-        <v>156573</v>
+        <v>153177</v>
       </c>
     </row>
     <row r="342">
@@ -7315,16 +7315,16 @@
         <v>40.45</v>
       </c>
       <c r="C345" t="n">
-        <v>41.59</v>
+        <v>41.51</v>
       </c>
       <c r="D345" t="n">
         <v>39.68</v>
       </c>
       <c r="E345" t="n">
-        <v>41.35</v>
+        <v>41.39</v>
       </c>
       <c r="F345" t="n">
-        <v>181021</v>
+        <v>178413</v>
       </c>
     </row>
     <row r="346">
@@ -7341,10 +7341,10 @@
         <v>40.25</v>
       </c>
       <c r="E346" t="n">
-        <v>40.57</v>
+        <v>40.58</v>
       </c>
       <c r="F346" t="n">
-        <v>160433</v>
+        <v>157969</v>
       </c>
     </row>
     <row r="347">
@@ -7421,10 +7421,10 @@
         <v>41.71</v>
       </c>
       <c r="E350" t="n">
-        <v>42.65</v>
+        <v>42.71</v>
       </c>
       <c r="F350" t="n">
-        <v>144329</v>
+        <v>142409</v>
       </c>
     </row>
     <row r="351">
@@ -7521,10 +7521,10 @@
         <v>41.99</v>
       </c>
       <c r="E355" t="n">
-        <v>42.35</v>
+        <v>42.32</v>
       </c>
       <c r="F355" t="n">
-        <v>136451</v>
+        <v>133908</v>
       </c>
     </row>
     <row r="356">
@@ -7541,10 +7541,10 @@
         <v>41.4</v>
       </c>
       <c r="E356" t="n">
-        <v>43.26</v>
+        <v>43.23</v>
       </c>
       <c r="F356" t="n">
-        <v>154800</v>
+        <v>152491</v>
       </c>
     </row>
     <row r="357">
@@ -7621,10 +7621,10 @@
         <v>43.19</v>
       </c>
       <c r="E360" t="n">
-        <v>43.28</v>
+        <v>43.36</v>
       </c>
       <c r="F360" t="n">
-        <v>101544</v>
+        <v>99613</v>
       </c>
     </row>
     <row r="361">
@@ -7641,10 +7641,10 @@
         <v>42.7</v>
       </c>
       <c r="E361" t="n">
-        <v>43.12</v>
+        <v>43.18</v>
       </c>
       <c r="F361" t="n">
-        <v>95049</v>
+        <v>93740</v>
       </c>
     </row>
     <row r="362">
@@ -7721,10 +7721,10 @@
         <v>43.42</v>
       </c>
       <c r="E365" t="n">
-        <v>43.53</v>
+        <v>43.82</v>
       </c>
       <c r="F365" t="n">
-        <v>112495</v>
+        <v>109900</v>
       </c>
     </row>
     <row r="366">
@@ -7741,10 +7741,10 @@
         <v>43.18</v>
       </c>
       <c r="E366" t="n">
-        <v>43.62</v>
+        <v>43.67</v>
       </c>
       <c r="F366" t="n">
-        <v>117377</v>
+        <v>115737</v>
       </c>
     </row>
     <row r="367">
@@ -7821,10 +7821,10 @@
         <v>41.95</v>
       </c>
       <c r="E370" t="n">
-        <v>43.56</v>
+        <v>43.43</v>
       </c>
       <c r="F370" t="n">
-        <v>117072</v>
+        <v>113377</v>
       </c>
     </row>
     <row r="371">
@@ -7841,10 +7841,10 @@
         <v>42.94</v>
       </c>
       <c r="E371" t="n">
-        <v>43.59</v>
+        <v>43.65</v>
       </c>
       <c r="F371" t="n">
-        <v>128800</v>
+        <v>127155</v>
       </c>
     </row>
     <row r="372">
@@ -7921,10 +7921,10 @@
         <v>44.96</v>
       </c>
       <c r="E375" t="n">
-        <v>45.13</v>
+        <v>45.28</v>
       </c>
       <c r="F375" t="n">
-        <v>122044</v>
+        <v>120720</v>
       </c>
     </row>
     <row r="376">
@@ -7941,10 +7941,10 @@
         <v>44.4</v>
       </c>
       <c r="E376" t="n">
-        <v>44.71</v>
+        <v>44.76</v>
       </c>
       <c r="F376" t="n">
-        <v>120731</v>
+        <v>119541</v>
       </c>
     </row>
     <row r="377">
@@ -8021,10 +8021,10 @@
         <v>45.07</v>
       </c>
       <c r="E380" t="n">
-        <v>45.24</v>
+        <v>45.3</v>
       </c>
       <c r="F380" t="n">
-        <v>91702</v>
+        <v>90204</v>
       </c>
     </row>
     <row r="381">
@@ -8041,10 +8041,10 @@
         <v>44.77</v>
       </c>
       <c r="E381" t="n">
-        <v>45.19</v>
+        <v>45.2</v>
       </c>
       <c r="F381" t="n">
-        <v>85013</v>
+        <v>83793</v>
       </c>
     </row>
     <row r="382">
@@ -8121,10 +8121,10 @@
         <v>44.46</v>
       </c>
       <c r="E385" t="n">
-        <v>45.27</v>
+        <v>45.36</v>
       </c>
       <c r="F385" t="n">
-        <v>87294</v>
+        <v>86301</v>
       </c>
     </row>
     <row r="386">
@@ -8141,10 +8141,10 @@
         <v>44.09</v>
       </c>
       <c r="E386" t="n">
-        <v>44.69</v>
+        <v>44.79</v>
       </c>
       <c r="F386" t="n">
-        <v>78965</v>
+        <v>77659</v>
       </c>
     </row>
     <row r="387">
@@ -8224,7 +8224,7 @@
         <v>45.59</v>
       </c>
       <c r="F390" t="n">
-        <v>96916</v>
+        <v>95873</v>
       </c>
     </row>
     <row r="391">
@@ -8241,10 +8241,10 @@
         <v>45.36</v>
       </c>
       <c r="E391" t="n">
-        <v>45.85</v>
+        <v>45.89</v>
       </c>
       <c r="F391" t="n">
-        <v>81841</v>
+        <v>81058</v>
       </c>
     </row>
     <row r="392">
@@ -8321,10 +8321,10 @@
         <v>43.27</v>
       </c>
       <c r="E395" t="n">
-        <v>44.07</v>
+        <v>44.09</v>
       </c>
       <c r="F395" t="n">
-        <v>158723</v>
+        <v>157249</v>
       </c>
     </row>
     <row r="396">
@@ -8338,13 +8338,13 @@
         <v>44.69</v>
       </c>
       <c r="D396" t="n">
-        <v>42.42</v>
+        <v>42.45</v>
       </c>
       <c r="E396" t="n">
-        <v>42.43</v>
+        <v>42.53</v>
       </c>
       <c r="F396" t="n">
-        <v>162787</v>
+        <v>160902</v>
       </c>
     </row>
     <row r="397">
@@ -8418,13 +8418,13 @@
         <v>41.23</v>
       </c>
       <c r="D400" t="n">
-        <v>39.96</v>
+        <v>40.02</v>
       </c>
       <c r="E400" t="n">
-        <v>39.97</v>
+        <v>40.07</v>
       </c>
       <c r="F400" t="n">
-        <v>149451</v>
+        <v>147551</v>
       </c>
     </row>
     <row r="401">
@@ -8441,10 +8441,10 @@
         <v>39.68</v>
       </c>
       <c r="E401" t="n">
-        <v>40.02</v>
+        <v>40.24</v>
       </c>
       <c r="F401" t="n">
-        <v>135456</v>
+        <v>133943</v>
       </c>
     </row>
     <row r="402">
@@ -8521,10 +8521,10 @@
         <v>41.89</v>
       </c>
       <c r="E405" t="n">
-        <v>43.58</v>
+        <v>43.67</v>
       </c>
       <c r="F405" t="n">
-        <v>142611</v>
+        <v>141089</v>
       </c>
     </row>
     <row r="406">
@@ -8541,10 +8541,10 @@
         <v>42.92</v>
       </c>
       <c r="E406" t="n">
-        <v>43.41</v>
+        <v>43.34</v>
       </c>
       <c r="F406" t="n">
-        <v>129546</v>
+        <v>127380</v>
       </c>
     </row>
     <row r="407">
@@ -8621,10 +8621,10 @@
         <v>41.68</v>
       </c>
       <c r="E410" t="n">
-        <v>42.16</v>
+        <v>42.27</v>
       </c>
       <c r="F410" t="n">
-        <v>133961</v>
+        <v>132502</v>
       </c>
     </row>
     <row r="411">
@@ -8641,10 +8641,10 @@
         <v>41.97</v>
       </c>
       <c r="E411" t="n">
-        <v>42.17</v>
+        <v>42.24</v>
       </c>
       <c r="F411" t="n">
-        <v>102107</v>
+        <v>100264</v>
       </c>
     </row>
     <row r="412">
@@ -8721,10 +8721,10 @@
         <v>39.98</v>
       </c>
       <c r="E415" t="n">
-        <v>40.75</v>
+        <v>40.93</v>
       </c>
       <c r="F415" t="n">
-        <v>157712</v>
+        <v>155461</v>
       </c>
     </row>
     <row r="416">
@@ -8741,10 +8741,10 @@
         <v>38.88</v>
       </c>
       <c r="E416" t="n">
-        <v>39.15</v>
+        <v>39.23</v>
       </c>
       <c r="F416" t="n">
-        <v>190634</v>
+        <v>188336</v>
       </c>
     </row>
     <row r="417">
@@ -8821,10 +8821,10 @@
         <v>42.02</v>
       </c>
       <c r="E420" t="n">
-        <v>43.52</v>
+        <v>43.54</v>
       </c>
       <c r="F420" t="n">
-        <v>112342</v>
+        <v>110782</v>
       </c>
     </row>
     <row r="421">
@@ -8841,10 +8841,10 @@
         <v>42.78</v>
       </c>
       <c r="E421" t="n">
-        <v>42.89</v>
+        <v>42.96</v>
       </c>
       <c r="F421" t="n">
-        <v>109695</v>
+        <v>108274</v>
       </c>
     </row>
     <row r="422">
@@ -8921,10 +8921,10 @@
         <v>41.79</v>
       </c>
       <c r="E425" t="n">
-        <v>43.26</v>
+        <v>43.38</v>
       </c>
       <c r="F425" t="n">
-        <v>147757</v>
+        <v>146298</v>
       </c>
     </row>
     <row r="426">
@@ -8941,10 +8941,10 @@
         <v>42.47</v>
       </c>
       <c r="E426" t="n">
-        <v>42.95</v>
+        <v>43.02</v>
       </c>
       <c r="F426" t="n">
-        <v>130839</v>
+        <v>129338</v>
       </c>
     </row>
     <row r="427">
@@ -9021,10 +9021,10 @@
         <v>41.72</v>
       </c>
       <c r="E430" t="n">
-        <v>42.59</v>
+        <v>42.71</v>
       </c>
       <c r="F430" t="n">
-        <v>110171</v>
+        <v>108471</v>
       </c>
     </row>
     <row r="431">
@@ -9041,10 +9041,10 @@
         <v>41.76</v>
       </c>
       <c r="E431" t="n">
-        <v>41.85</v>
+        <v>41.93</v>
       </c>
       <c r="F431" t="n">
-        <v>97195</v>
+        <v>95688</v>
       </c>
     </row>
     <row r="432">
@@ -9112,7 +9112,7 @@
         <v>44133</v>
       </c>
       <c r="B435" t="n">
-        <v>39.76</v>
+        <v>39.52</v>
       </c>
       <c r="C435" t="n">
         <v>39.97</v>
@@ -9124,7 +9124,7 @@
         <v>38.05</v>
       </c>
       <c r="F435" t="n">
-        <v>179602</v>
+        <v>183949</v>
       </c>
     </row>
     <row r="436">
@@ -9132,7 +9132,7 @@
         <v>44134</v>
       </c>
       <c r="B436" t="n">
-        <v>38.25</v>
+        <v>38.05</v>
       </c>
       <c r="C436" t="n">
         <v>38.72</v>
@@ -9144,7 +9144,7 @@
         <v>37.84</v>
       </c>
       <c r="F436" t="n">
-        <v>181739</v>
+        <v>184633</v>
       </c>
     </row>
     <row r="437">
@@ -9221,10 +9221,10 @@
         <v>40.42</v>
       </c>
       <c r="E440" t="n">
-        <v>40.68</v>
+        <v>40.82</v>
       </c>
       <c r="F440" t="n">
-        <v>157779</v>
+        <v>155706</v>
       </c>
     </row>
     <row r="441">
@@ -9241,10 +9241,10 @@
         <v>39.46</v>
       </c>
       <c r="E441" t="n">
-        <v>39.71</v>
+        <v>39.84</v>
       </c>
       <c r="F441" t="n">
-        <v>151438</v>
+        <v>150078</v>
       </c>
     </row>
     <row r="442">
@@ -9318,13 +9318,13 @@
         <v>44.59</v>
       </c>
       <c r="D445" t="n">
-        <v>43.35</v>
+        <v>43.42</v>
       </c>
       <c r="E445" t="n">
-        <v>43.38</v>
+        <v>43.49</v>
       </c>
       <c r="F445" t="n">
-        <v>146964</v>
+        <v>144322</v>
       </c>
     </row>
     <row r="446">
@@ -9338,13 +9338,13 @@
         <v>43.45</v>
       </c>
       <c r="D446" t="n">
-        <v>42.68</v>
+        <v>42.77</v>
       </c>
       <c r="E446" t="n">
-        <v>42.69</v>
+        <v>42.88</v>
       </c>
       <c r="F446" t="n">
-        <v>114191</v>
+        <v>112789</v>
       </c>
     </row>
     <row r="447">
@@ -9421,10 +9421,10 @@
         <v>43.87</v>
       </c>
       <c r="E450" t="n">
-        <v>44.21</v>
+        <v>44.44</v>
       </c>
       <c r="F450" t="n">
-        <v>112468</v>
+        <v>111013</v>
       </c>
     </row>
     <row r="451">
@@ -9441,10 +9441,10 @@
         <v>44.15</v>
       </c>
       <c r="E451" t="n">
-        <v>45.07</v>
+        <v>45.06</v>
       </c>
       <c r="F451" t="n">
-        <v>90427</v>
+        <v>88612</v>
       </c>
     </row>
     <row r="452">
@@ -9624,7 +9624,7 @@
         <v>48.65</v>
       </c>
       <c r="F460" t="n">
-        <v>122403</v>
+        <v>119976</v>
       </c>
     </row>
     <row r="461">
@@ -9641,10 +9641,10 @@
         <v>48.77</v>
       </c>
       <c r="E461" t="n">
-        <v>48.96</v>
+        <v>48.97</v>
       </c>
       <c r="F461" t="n">
-        <v>125701</v>
+        <v>124413</v>
       </c>
     </row>
     <row r="462">
@@ -9721,10 +9721,10 @@
         <v>48.79</v>
       </c>
       <c r="E465" t="n">
-        <v>50.25</v>
+        <v>50.26</v>
       </c>
       <c r="F465" t="n">
-        <v>132386</v>
+        <v>130125</v>
       </c>
     </row>
     <row r="466">
@@ -9741,10 +9741,10 @@
         <v>49.67</v>
       </c>
       <c r="E466" t="n">
-        <v>49.86</v>
+        <v>49.94</v>
       </c>
       <c r="F466" t="n">
-        <v>124721</v>
+        <v>123293</v>
       </c>
     </row>
     <row r="467">
@@ -9821,10 +9821,10 @@
         <v>51.06</v>
       </c>
       <c r="E470" t="n">
-        <v>51.46</v>
+        <v>51.55</v>
       </c>
       <c r="F470" t="n">
-        <v>102867</v>
+        <v>100894</v>
       </c>
     </row>
     <row r="471">
@@ -9841,10 +9841,10 @@
         <v>51.16</v>
       </c>
       <c r="E471" t="n">
-        <v>52.23</v>
+        <v>52.19</v>
       </c>
       <c r="F471" t="n">
-        <v>98705</v>
+        <v>96861</v>
       </c>
     </row>
     <row r="472">
@@ -10081,10 +10081,10 @@
         <v>53.88</v>
       </c>
       <c r="E483" t="n">
-        <v>54.34</v>
+        <v>54.45</v>
       </c>
       <c r="F483" t="n">
-        <v>142258</v>
+        <v>140683</v>
       </c>
     </row>
     <row r="484">
@@ -10095,16 +10095,16 @@
         <v>54.46</v>
       </c>
       <c r="C484" t="n">
-        <v>56.2</v>
+        <v>56.06</v>
       </c>
       <c r="D484" t="n">
         <v>54.3</v>
       </c>
       <c r="E484" t="n">
-        <v>56.11</v>
+        <v>56.02</v>
       </c>
       <c r="F484" t="n">
-        <v>155413</v>
+        <v>151805</v>
       </c>
     </row>
     <row r="485">
@@ -10181,10 +10181,10 @@
         <v>55.21</v>
       </c>
       <c r="E488" t="n">
-        <v>56.37</v>
+        <v>56.3</v>
       </c>
       <c r="F488" t="n">
-        <v>125098</v>
+        <v>123090</v>
       </c>
     </row>
     <row r="489">
@@ -10201,10 +10201,10 @@
         <v>54.63</v>
       </c>
       <c r="E489" t="n">
-        <v>54.75</v>
+        <v>54.94</v>
       </c>
       <c r="F489" t="n">
-        <v>135898</v>
+        <v>133988</v>
       </c>
     </row>
     <row r="490">
@@ -10281,10 +10281,10 @@
         <v>55.38</v>
       </c>
       <c r="E493" t="n">
-        <v>55.84</v>
+        <v>55.86</v>
       </c>
       <c r="F493" t="n">
-        <v>104851</v>
+        <v>103188</v>
       </c>
     </row>
     <row r="494">
@@ -10301,10 +10301,10 @@
         <v>54.38</v>
       </c>
       <c r="E494" t="n">
-        <v>54.88</v>
+        <v>55.08</v>
       </c>
       <c r="F494" t="n">
-        <v>135622</v>
+        <v>133367</v>
       </c>
     </row>
     <row r="495">
@@ -10378,13 +10378,13 @@
         <v>56.16</v>
       </c>
       <c r="D498" t="n">
-        <v>54.84</v>
+        <v>54.93</v>
       </c>
       <c r="E498" t="n">
-        <v>54.84</v>
+        <v>55</v>
       </c>
       <c r="F498" t="n">
-        <v>162289</v>
+        <v>160473</v>
       </c>
     </row>
     <row r="499">
@@ -10401,10 +10401,10 @@
         <v>54.84</v>
       </c>
       <c r="E499" t="n">
-        <v>54.93</v>
+        <v>55</v>
       </c>
       <c r="F499" t="n">
-        <v>163671</v>
+        <v>160923</v>
       </c>
     </row>
     <row r="500">
@@ -10481,10 +10481,10 @@
         <v>57.93</v>
       </c>
       <c r="E503" t="n">
-        <v>58.87</v>
+        <v>58.79</v>
       </c>
       <c r="F503" t="n">
-        <v>125851</v>
+        <v>123567</v>
       </c>
     </row>
     <row r="504">
@@ -10501,10 +10501,10 @@
         <v>58.87</v>
       </c>
       <c r="E504" t="n">
-        <v>59.41</v>
+        <v>59.31</v>
       </c>
       <c r="F504" t="n">
-        <v>120954</v>
+        <v>118436</v>
       </c>
     </row>
     <row r="505">
@@ -10578,13 +10578,13 @@
         <v>61.23</v>
       </c>
       <c r="D508" t="n">
-        <v>60.44</v>
+        <v>60.5</v>
       </c>
       <c r="E508" t="n">
-        <v>60.52</v>
+        <v>60.6</v>
       </c>
       <c r="F508" t="n">
-        <v>107974</v>
+        <v>104511</v>
       </c>
     </row>
     <row r="509">
@@ -10604,7 +10604,7 @@
         <v>62.22</v>
       </c>
       <c r="F509" t="n">
-        <v>126905</v>
+        <v>123306</v>
       </c>
     </row>
     <row r="510">
@@ -10681,10 +10681,10 @@
         <v>62.54</v>
       </c>
       <c r="E513" t="n">
-        <v>62.88</v>
+        <v>62.75</v>
       </c>
       <c r="F513" t="n">
-        <v>173632</v>
+        <v>170306</v>
       </c>
     </row>
     <row r="514">
@@ -10701,10 +10701,10 @@
         <v>61.42</v>
       </c>
       <c r="E514" t="n">
-        <v>61.97</v>
+        <v>61.95</v>
       </c>
       <c r="F514" t="n">
-        <v>184306</v>
+        <v>181146</v>
       </c>
     </row>
     <row r="515">
@@ -10781,10 +10781,10 @@
         <v>65.55</v>
       </c>
       <c r="E518" t="n">
-        <v>65.97</v>
+        <v>65.86</v>
       </c>
       <c r="F518" t="n">
-        <v>215533</v>
+        <v>210726</v>
       </c>
     </row>
     <row r="519">
@@ -10801,10 +10801,10 @@
         <v>64.13</v>
       </c>
       <c r="E519" t="n">
-        <v>64.27</v>
+        <v>64.25</v>
       </c>
       <c r="F519" t="n">
-        <v>239274</v>
+        <v>234931</v>
       </c>
     </row>
     <row r="520">
@@ -10881,10 +10881,10 @@
         <v>63.17</v>
       </c>
       <c r="E523" t="n">
-        <v>66.73999999999999</v>
+        <v>66.94</v>
       </c>
       <c r="F523" t="n">
-        <v>230530</v>
+        <v>225843</v>
       </c>
     </row>
     <row r="524">
@@ -10895,16 +10895,16 @@
         <v>66.86</v>
       </c>
       <c r="C524" t="n">
-        <v>69.41</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="D524" t="n">
         <v>66.43000000000001</v>
       </c>
       <c r="E524" t="n">
-        <v>69.25</v>
+        <v>69.28</v>
       </c>
       <c r="F524" t="n">
-        <v>253026</v>
+        <v>249828</v>
       </c>
     </row>
     <row r="525">
@@ -10981,10 +10981,10 @@
         <v>67.68000000000001</v>
       </c>
       <c r="E528" t="n">
-        <v>69.17</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="F528" t="n">
-        <v>163581</v>
+        <v>160838</v>
       </c>
     </row>
     <row r="529">
@@ -11001,10 +11001,10 @@
         <v>68.66</v>
       </c>
       <c r="E529" t="n">
-        <v>68.81</v>
+        <v>68.88</v>
       </c>
       <c r="F529" t="n">
-        <v>151042</v>
+        <v>148823</v>
       </c>
     </row>
     <row r="530">
@@ -11072,7 +11072,7 @@
         <v>44273</v>
       </c>
       <c r="B533" t="n">
-        <v>67.47</v>
+        <v>67.48</v>
       </c>
       <c r="C533" t="n">
         <v>67.83</v>
@@ -11084,7 +11084,7 @@
         <v>62.5</v>
       </c>
       <c r="F533" t="n">
-        <v>209835</v>
+        <v>212082</v>
       </c>
     </row>
     <row r="534">
@@ -11092,7 +11092,7 @@
         <v>44274</v>
       </c>
       <c r="B534" t="n">
-        <v>63.02</v>
+        <v>62.78</v>
       </c>
       <c r="C534" t="n">
         <v>64.73</v>
@@ -11104,7 +11104,7 @@
         <v>64.31999999999999</v>
       </c>
       <c r="F534" t="n">
-        <v>223529</v>
+        <v>228148</v>
       </c>
     </row>
     <row r="535">
@@ -11172,10 +11172,10 @@
         <v>44280</v>
       </c>
       <c r="B538" t="n">
-        <v>63.89</v>
+        <v>63.95</v>
       </c>
       <c r="C538" t="n">
-        <v>63.9</v>
+        <v>64.01000000000001</v>
       </c>
       <c r="D538" t="n">
         <v>60.82</v>
@@ -11184,7 +11184,7 @@
         <v>61.47</v>
       </c>
       <c r="F538" t="n">
-        <v>203253</v>
+        <v>206155</v>
       </c>
     </row>
     <row r="539">
@@ -11192,19 +11192,19 @@
         <v>44281</v>
       </c>
       <c r="B539" t="n">
-        <v>62.45</v>
+        <v>61.47</v>
       </c>
       <c r="C539" t="n">
         <v>64.73</v>
       </c>
       <c r="D539" t="n">
-        <v>62.07</v>
+        <v>61.47</v>
       </c>
       <c r="E539" t="n">
         <v>64.19</v>
       </c>
       <c r="F539" t="n">
-        <v>167422</v>
+        <v>171041</v>
       </c>
     </row>
     <row r="540">
@@ -11284,7 +11284,7 @@
         <v>64.51000000000001</v>
       </c>
       <c r="F543" t="n">
-        <v>201289</v>
+        <v>197783</v>
       </c>
     </row>
     <row r="544">
@@ -11361,10 +11361,10 @@
         <v>62.18</v>
       </c>
       <c r="E547" t="n">
-        <v>63.04</v>
+        <v>63.07</v>
       </c>
       <c r="F547" t="n">
-        <v>149186</v>
+        <v>146277</v>
       </c>
     </row>
     <row r="548">
@@ -11381,10 +11381,10 @@
         <v>62.33</v>
       </c>
       <c r="E548" t="n">
-        <v>62.76</v>
+        <v>62.81</v>
       </c>
       <c r="F548" t="n">
-        <v>121247</v>
+        <v>119219</v>
       </c>
     </row>
     <row r="549">
@@ -11461,10 +11461,10 @@
         <v>65.65000000000001</v>
       </c>
       <c r="E552" t="n">
-        <v>66.45</v>
+        <v>66.5</v>
       </c>
       <c r="F552" t="n">
-        <v>135521</v>
+        <v>133306</v>
       </c>
     </row>
     <row r="553">
@@ -11481,10 +11481,10 @@
         <v>66.11</v>
       </c>
       <c r="E553" t="n">
-        <v>66.31999999999999</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="F553" t="n">
-        <v>122938</v>
+        <v>120895</v>
       </c>
     </row>
     <row r="554">
@@ -11564,7 +11564,7 @@
         <v>64.95</v>
       </c>
       <c r="F557" t="n">
-        <v>143350</v>
+        <v>140975</v>
       </c>
     </row>
     <row r="558">
@@ -11581,10 +11581,10 @@
         <v>64.52</v>
       </c>
       <c r="E558" t="n">
-        <v>65.31999999999999</v>
+        <v>65.45</v>
       </c>
       <c r="F558" t="n">
-        <v>126302</v>
+        <v>124432</v>
       </c>
     </row>
     <row r="559">
@@ -11661,10 +11661,10 @@
         <v>66.56</v>
       </c>
       <c r="E562" t="n">
-        <v>67.84999999999999</v>
+        <v>67.86</v>
       </c>
       <c r="F562" t="n">
-        <v>160482</v>
+        <v>157092</v>
       </c>
     </row>
     <row r="563">
@@ -11681,10 +11681,10 @@
         <v>66.17</v>
       </c>
       <c r="E563" t="n">
-        <v>66.53</v>
+        <v>66.56</v>
       </c>
       <c r="F563" t="n">
-        <v>148372</v>
+        <v>145779</v>
       </c>
     </row>
     <row r="564">
@@ -11761,10 +11761,10 @@
         <v>67.77</v>
       </c>
       <c r="E567" t="n">
-        <v>68.03</v>
+        <v>68.05</v>
       </c>
       <c r="F567" t="n">
-        <v>155507</v>
+        <v>153533</v>
       </c>
     </row>
     <row r="568">
@@ -11784,7 +11784,7 @@
         <v>68.03</v>
       </c>
       <c r="F568" t="n">
-        <v>139157</v>
+        <v>136012</v>
       </c>
     </row>
     <row r="569">
@@ -11861,10 +11861,10 @@
         <v>66.34</v>
       </c>
       <c r="E572" t="n">
-        <v>66.81999999999999</v>
+        <v>66.83</v>
       </c>
       <c r="F572" t="n">
-        <v>182316</v>
+        <v>180093</v>
       </c>
     </row>
     <row r="573">
@@ -11875,16 +11875,16 @@
         <v>66.81</v>
       </c>
       <c r="C573" t="n">
-        <v>68.63</v>
+        <v>68.52</v>
       </c>
       <c r="D573" t="n">
         <v>66.36</v>
       </c>
       <c r="E573" t="n">
-        <v>68.52</v>
+        <v>68.45</v>
       </c>
       <c r="F573" t="n">
-        <v>142226</v>
+        <v>139950</v>
       </c>
     </row>
     <row r="574">
@@ -11958,13 +11958,13 @@
         <v>67.02</v>
       </c>
       <c r="D577" t="n">
-        <v>64.70999999999999</v>
+        <v>64.73</v>
       </c>
       <c r="E577" t="n">
-        <v>64.73999999999999</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="F577" t="n">
-        <v>168733</v>
+        <v>164782</v>
       </c>
     </row>
     <row r="578">
@@ -11981,10 +11981,10 @@
         <v>64.48</v>
       </c>
       <c r="E578" t="n">
-        <v>66.51000000000001</v>
+        <v>66.58</v>
       </c>
       <c r="F578" t="n">
-        <v>156317</v>
+        <v>153693</v>
       </c>
     </row>
     <row r="579">
@@ -12055,16 +12055,16 @@
         <v>68.58</v>
       </c>
       <c r="C582" t="n">
-        <v>69.2</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="D582" t="n">
         <v>67.89</v>
       </c>
       <c r="E582" t="n">
-        <v>69.12</v>
+        <v>69.05</v>
       </c>
       <c r="F582" t="n">
-        <v>122427</v>
+        <v>119490</v>
       </c>
     </row>
     <row r="583">
@@ -12081,10 +12081,10 @@
         <v>68.48999999999999</v>
       </c>
       <c r="E583" t="n">
-        <v>68.88</v>
+        <v>68.89</v>
       </c>
       <c r="F583" t="n">
-        <v>121324</v>
+        <v>119218</v>
       </c>
     </row>
     <row r="584">
@@ -12161,10 +12161,10 @@
         <v>70.5</v>
       </c>
       <c r="E587" t="n">
-        <v>71.22</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="F587" t="n">
-        <v>128649</v>
+        <v>126247</v>
       </c>
     </row>
     <row r="588">
@@ -12181,10 +12181,10 @@
         <v>70.58</v>
       </c>
       <c r="E588" t="n">
-        <v>71.43000000000001</v>
+        <v>71.47</v>
       </c>
       <c r="F588" t="n">
-        <v>117041</v>
+        <v>113793</v>
       </c>
     </row>
     <row r="589">
@@ -12261,10 +12261,10 @@
         <v>70.66</v>
       </c>
       <c r="E592" t="n">
-        <v>71.95</v>
+        <v>72.09</v>
       </c>
       <c r="F592" t="n">
-        <v>148450</v>
+        <v>146487</v>
       </c>
     </row>
     <row r="593">
@@ -12284,7 +12284,7 @@
         <v>72.23999999999999</v>
       </c>
       <c r="F593" t="n">
-        <v>142367</v>
+        <v>140128</v>
       </c>
     </row>
     <row r="594">
@@ -12361,10 +12361,10 @@
         <v>71.41</v>
       </c>
       <c r="E597" t="n">
-        <v>72.44</v>
+        <v>72.45</v>
       </c>
       <c r="F597" t="n">
-        <v>178094</v>
+        <v>175025</v>
       </c>
     </row>
     <row r="598">
@@ -12381,10 +12381,10 @@
         <v>71.55</v>
       </c>
       <c r="E598" t="n">
-        <v>72.5</v>
+        <v>72.76000000000001</v>
       </c>
       <c r="F598" t="n">
-        <v>151345</v>
+        <v>147859</v>
       </c>
     </row>
     <row r="599">
@@ -12461,10 +12461,10 @@
         <v>73.83</v>
       </c>
       <c r="E602" t="n">
-        <v>74.81</v>
+        <v>74.79000000000001</v>
       </c>
       <c r="F602" t="n">
-        <v>85692</v>
+        <v>84577</v>
       </c>
     </row>
     <row r="603">
@@ -12481,10 +12481,10 @@
         <v>74.14</v>
       </c>
       <c r="E603" t="n">
-        <v>75.28</v>
+        <v>75.27</v>
       </c>
       <c r="F603" t="n">
-        <v>79112</v>
+        <v>77990</v>
       </c>
     </row>
     <row r="604">
@@ -12561,10 +12561,10 @@
         <v>74.36</v>
       </c>
       <c r="E607" t="n">
-        <v>75.34</v>
+        <v>75.33</v>
       </c>
       <c r="F607" t="n">
-        <v>135699</v>
+        <v>134296</v>
       </c>
     </row>
     <row r="608">
@@ -12581,10 +12581,10 @@
         <v>75</v>
       </c>
       <c r="E608" t="n">
-        <v>75.81999999999999</v>
+        <v>76.02</v>
       </c>
       <c r="F608" t="n">
-        <v>104256</v>
+        <v>102316</v>
       </c>
     </row>
     <row r="609">
@@ -12655,16 +12655,16 @@
         <v>72.97</v>
       </c>
       <c r="C612" t="n">
-        <v>74.02</v>
+        <v>73.97</v>
       </c>
       <c r="D612" t="n">
         <v>71.73999999999999</v>
       </c>
       <c r="E612" t="n">
-        <v>73.95999999999999</v>
+        <v>73.92</v>
       </c>
       <c r="F612" t="n">
-        <v>138030</v>
+        <v>136419</v>
       </c>
     </row>
     <row r="613">
@@ -12681,10 +12681,10 @@
         <v>73.38</v>
       </c>
       <c r="E613" t="n">
-        <v>75.14</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="F613" t="n">
-        <v>96988</v>
+        <v>95892</v>
       </c>
     </row>
     <row r="614">
@@ -12761,10 +12761,10 @@
         <v>72.70999999999999</v>
       </c>
       <c r="E617" t="n">
-        <v>72.72</v>
+        <v>72.79000000000001</v>
       </c>
       <c r="F617" t="n">
-        <v>134216</v>
+        <v>132350</v>
       </c>
     </row>
     <row r="618">
@@ -12781,10 +12781,10 @@
         <v>71.88</v>
       </c>
       <c r="E618" t="n">
-        <v>72.64</v>
+        <v>72.81</v>
       </c>
       <c r="F618" t="n">
-        <v>110158</v>
+        <v>108307</v>
       </c>
     </row>
     <row r="619">
@@ -12864,7 +12864,7 @@
         <v>73.01000000000001</v>
       </c>
       <c r="F622" t="n">
-        <v>115159</v>
+        <v>113951</v>
       </c>
     </row>
     <row r="623">
@@ -12875,16 +12875,16 @@
         <v>72.98</v>
       </c>
       <c r="C623" t="n">
-        <v>73.56999999999999</v>
+        <v>73.52</v>
       </c>
       <c r="D623" t="n">
         <v>72.70999999999999</v>
       </c>
       <c r="E623" t="n">
-        <v>73.5</v>
+        <v>73.44</v>
       </c>
       <c r="F623" t="n">
-        <v>84579</v>
+        <v>83411</v>
       </c>
     </row>
     <row r="624">
@@ -12961,10 +12961,10 @@
         <v>73.59999999999999</v>
       </c>
       <c r="E627" t="n">
-        <v>74.75</v>
+        <v>74.97</v>
       </c>
       <c r="F627" t="n">
-        <v>81467</v>
+        <v>79720</v>
       </c>
     </row>
     <row r="628">
@@ -12981,10 +12981,10 @@
         <v>74.26000000000001</v>
       </c>
       <c r="E628" t="n">
-        <v>74.95999999999999</v>
+        <v>74.98999999999999</v>
       </c>
       <c r="F628" t="n">
-        <v>84253</v>
+        <v>83101</v>
       </c>
     </row>
     <row r="629">
@@ -13061,10 +13061,10 @@
         <v>69.56</v>
       </c>
       <c r="E632" t="n">
-        <v>71</v>
+        <v>71.16</v>
       </c>
       <c r="F632" t="n">
-        <v>108267</v>
+        <v>107034</v>
       </c>
     </row>
     <row r="633">
@@ -13078,13 +13078,13 @@
         <v>72.22</v>
       </c>
       <c r="D633" t="n">
-        <v>70.06999999999999</v>
+        <v>70.12</v>
       </c>
       <c r="E633" t="n">
-        <v>70.08</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="F633" t="n">
-        <v>113105</v>
+        <v>111453</v>
       </c>
     </row>
     <row r="634">
@@ -13161,10 +13161,10 @@
         <v>70.41</v>
       </c>
       <c r="E637" t="n">
-        <v>70.86</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="F637" t="n">
-        <v>96203</v>
+        <v>95219</v>
       </c>
     </row>
     <row r="638">
@@ -13181,10 +13181,10 @@
         <v>69.73999999999999</v>
       </c>
       <c r="E638" t="n">
-        <v>69.90000000000001</v>
+        <v>69.92</v>
       </c>
       <c r="F638" t="n">
-        <v>95696</v>
+        <v>93960</v>
       </c>
     </row>
     <row r="639">
@@ -13261,10 +13261,10 @@
         <v>65.2</v>
       </c>
       <c r="E642" t="n">
-        <v>66.23</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="F642" t="n">
-        <v>187712</v>
+        <v>185678</v>
       </c>
     </row>
     <row r="643">
@@ -13278,13 +13278,13 @@
         <v>66.54000000000001</v>
       </c>
       <c r="D643" t="n">
-        <v>64.53</v>
+        <v>64.61</v>
       </c>
       <c r="E643" t="n">
-        <v>64.54000000000001</v>
+        <v>64.62</v>
       </c>
       <c r="F643" t="n">
-        <v>138989</v>
+        <v>137258</v>
       </c>
     </row>
     <row r="644">
@@ -13361,10 +13361,10 @@
         <v>69.73999999999999</v>
       </c>
       <c r="E647" t="n">
-        <v>70.45999999999999</v>
+        <v>70.56</v>
       </c>
       <c r="F647" t="n">
-        <v>115965</v>
+        <v>113839</v>
       </c>
     </row>
     <row r="648">
@@ -13381,10 +13381,10 @@
         <v>70.16</v>
       </c>
       <c r="E648" t="n">
-        <v>71.5</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="F648" t="n">
-        <v>100455</v>
+        <v>99158</v>
       </c>
     </row>
     <row r="649">
@@ -13461,10 +13461,10 @@
         <v>70.75</v>
       </c>
       <c r="E652" t="n">
-        <v>72.61</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="F652" t="n">
-        <v>105073</v>
+        <v>103772</v>
       </c>
     </row>
     <row r="653">
@@ -13481,10 +13481,10 @@
         <v>72.20999999999999</v>
       </c>
       <c r="E653" t="n">
-        <v>72.20999999999999</v>
+        <v>72.36</v>
       </c>
       <c r="F653" t="n">
-        <v>111688</v>
+        <v>110684</v>
       </c>
     </row>
     <row r="654">
@@ -13561,10 +13561,10 @@
         <v>70.54000000000001</v>
       </c>
       <c r="E657" t="n">
-        <v>70.84</v>
+        <v>70.95</v>
       </c>
       <c r="F657" t="n">
-        <v>138553</v>
+        <v>136836</v>
       </c>
     </row>
     <row r="658">
@@ -13581,10 +13581,10 @@
         <v>70.59</v>
       </c>
       <c r="E658" t="n">
-        <v>72.51000000000001</v>
+        <v>72.44</v>
       </c>
       <c r="F658" t="n">
-        <v>107925</v>
+        <v>106315</v>
       </c>
     </row>
     <row r="659">
@@ -13661,10 +13661,10 @@
         <v>74.02</v>
       </c>
       <c r="E662" t="n">
-        <v>75.09</v>
+        <v>75.17</v>
       </c>
       <c r="F662" t="n">
-        <v>136265</v>
+        <v>134873</v>
       </c>
     </row>
     <row r="663">
@@ -13681,10 +13681,10 @@
         <v>74.06999999999999</v>
       </c>
       <c r="E663" t="n">
-        <v>74.67</v>
+        <v>74.79000000000001</v>
       </c>
       <c r="F663" t="n">
-        <v>131243</v>
+        <v>129577</v>
       </c>
     </row>
     <row r="664">
@@ -13764,7 +13764,7 @@
         <v>76.45</v>
       </c>
       <c r="F667" t="n">
-        <v>104066</v>
+        <v>102612</v>
       </c>
     </row>
     <row r="668">
@@ -13781,10 +13781,10 @@
         <v>76.09</v>
       </c>
       <c r="E668" t="n">
-        <v>77.13</v>
+        <v>77.15000000000001</v>
       </c>
       <c r="F668" t="n">
-        <v>94529</v>
+        <v>93448</v>
       </c>
     </row>
     <row r="669">
@@ -13861,10 +13861,10 @@
         <v>76.37</v>
       </c>
       <c r="E672" t="n">
-        <v>78.23999999999999</v>
+        <v>78.13</v>
       </c>
       <c r="F672" t="n">
-        <v>181989</v>
+        <v>180155</v>
       </c>
     </row>
     <row r="673">
@@ -13881,10 +13881,10 @@
         <v>77.38</v>
       </c>
       <c r="E673" t="n">
-        <v>78.93000000000001</v>
+        <v>78.98999999999999</v>
       </c>
       <c r="F673" t="n">
-        <v>151482</v>
+        <v>149729</v>
       </c>
     </row>
     <row r="674">
@@ -13961,10 +13961,10 @@
         <v>78.78</v>
       </c>
       <c r="E677" t="n">
-        <v>82.08</v>
+        <v>82.16</v>
       </c>
       <c r="F677" t="n">
-        <v>153620</v>
+        <v>151677</v>
       </c>
     </row>
     <row r="678">
@@ -13981,10 +13981,10 @@
         <v>81.63</v>
       </c>
       <c r="E678" t="n">
-        <v>82.22</v>
+        <v>82.17</v>
       </c>
       <c r="F678" t="n">
-        <v>149526</v>
+        <v>147722</v>
       </c>
     </row>
     <row r="679">
@@ -14061,10 +14061,10 @@
         <v>82.76000000000001</v>
       </c>
       <c r="E682" t="n">
-        <v>83.67</v>
+        <v>83.69</v>
       </c>
       <c r="F682" t="n">
-        <v>122153</v>
+        <v>120650</v>
       </c>
     </row>
     <row r="683">
@@ -14081,10 +14081,10 @@
         <v>83.68000000000001</v>
       </c>
       <c r="E683" t="n">
-        <v>84.33</v>
+        <v>84.23</v>
       </c>
       <c r="F683" t="n">
-        <v>116437</v>
+        <v>114060</v>
       </c>
     </row>
     <row r="684">
@@ -14161,10 +14161,10 @@
         <v>82.73</v>
       </c>
       <c r="E687" t="n">
-        <v>84.09</v>
+        <v>84.15000000000001</v>
       </c>
       <c r="F687" t="n">
-        <v>122966</v>
+        <v>121250</v>
       </c>
     </row>
     <row r="688">
@@ -14175,16 +14175,16 @@
         <v>83.81999999999999</v>
       </c>
       <c r="C688" t="n">
-        <v>85.08</v>
+        <v>84.97</v>
       </c>
       <c r="D688" t="n">
         <v>83.18000000000001</v>
       </c>
       <c r="E688" t="n">
-        <v>84.83</v>
+        <v>84.97</v>
       </c>
       <c r="F688" t="n">
-        <v>113449</v>
+        <v>111475</v>
       </c>
     </row>
     <row r="689">
@@ -14261,10 +14261,10 @@
         <v>81.48</v>
       </c>
       <c r="E692" t="n">
-        <v>83.78</v>
+        <v>83.83</v>
       </c>
       <c r="F692" t="n">
-        <v>167007</v>
+        <v>164605</v>
       </c>
     </row>
     <row r="693">
@@ -14281,10 +14281,10 @@
         <v>82.39</v>
       </c>
       <c r="E693" t="n">
-        <v>83.41</v>
+        <v>83.55</v>
       </c>
       <c r="F693" t="n">
-        <v>133535</v>
+        <v>132228</v>
       </c>
     </row>
     <row r="694">
@@ -14352,7 +14352,7 @@
         <v>44504</v>
       </c>
       <c r="B697" t="n">
-        <v>80.83</v>
+        <v>81.12</v>
       </c>
       <c r="C697" t="n">
         <v>84.08</v>
@@ -14364,7 +14364,7 @@
         <v>80.54000000000001</v>
       </c>
       <c r="F697" t="n">
-        <v>168783</v>
+        <v>171378</v>
       </c>
     </row>
     <row r="698">
@@ -14372,7 +14372,7 @@
         <v>44505</v>
       </c>
       <c r="B698" t="n">
-        <v>81.04000000000001</v>
+        <v>80.95</v>
       </c>
       <c r="C698" t="n">
         <v>82.72</v>
@@ -14384,7 +14384,7 @@
         <v>81.93000000000001</v>
       </c>
       <c r="F698" t="n">
-        <v>163172</v>
+        <v>166390</v>
       </c>
     </row>
     <row r="699">
@@ -14461,10 +14461,10 @@
         <v>81.06</v>
       </c>
       <c r="E702" t="n">
-        <v>81.92</v>
+        <v>81.91</v>
       </c>
       <c r="F702" t="n">
-        <v>161511</v>
+        <v>159955</v>
       </c>
     </row>
     <row r="703">
@@ -14481,10 +14481,10 @@
         <v>80.63</v>
       </c>
       <c r="E703" t="n">
-        <v>81.29000000000001</v>
+        <v>81.41</v>
       </c>
       <c r="F703" t="n">
-        <v>134507</v>
+        <v>133196</v>
       </c>
     </row>
     <row r="704">
@@ -14561,10 +14561,10 @@
         <v>78.55</v>
       </c>
       <c r="E707" t="n">
-        <v>80.34999999999999</v>
+        <v>80.42</v>
       </c>
       <c r="F707" t="n">
-        <v>132952</v>
+        <v>131123</v>
       </c>
     </row>
     <row r="708">
@@ -14581,10 +14581,10 @@
         <v>77.41</v>
       </c>
       <c r="E708" t="n">
-        <v>77.77</v>
+        <v>77.76000000000001</v>
       </c>
       <c r="F708" t="n">
-        <v>177513</v>
+        <v>175625</v>
       </c>
     </row>
     <row r="709">
@@ -14761,10 +14761,10 @@
         <v>65.67</v>
       </c>
       <c r="E717" t="n">
-        <v>70.36</v>
+        <v>69.94</v>
       </c>
       <c r="F717" t="n">
-        <v>240359</v>
+        <v>237353</v>
       </c>
     </row>
     <row r="718">
@@ -14781,10 +14781,10 @@
         <v>69.09999999999999</v>
       </c>
       <c r="E718" t="n">
-        <v>69.70999999999999</v>
+        <v>69.73</v>
       </c>
       <c r="F718" t="n">
-        <v>208893</v>
+        <v>205214</v>
       </c>
     </row>
     <row r="719">
@@ -14858,13 +14858,13 @@
         <v>76.55</v>
       </c>
       <c r="D722" t="n">
-        <v>73.70999999999999</v>
+        <v>73.78</v>
       </c>
       <c r="E722" t="n">
-        <v>73.84999999999999</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="F722" t="n">
-        <v>142264</v>
+        <v>140659</v>
       </c>
     </row>
     <row r="723">
@@ -14881,10 +14881,10 @@
         <v>73.67</v>
       </c>
       <c r="E723" t="n">
-        <v>75.16</v>
+        <v>75.23</v>
       </c>
       <c r="F723" t="n">
-        <v>153301</v>
+        <v>151698</v>
       </c>
     </row>
     <row r="724">
@@ -14961,10 +14961,10 @@
         <v>73.88</v>
       </c>
       <c r="E727" t="n">
-        <v>74.48999999999999</v>
+        <v>74.63</v>
       </c>
       <c r="F727" t="n">
-        <v>142563</v>
+        <v>140474</v>
       </c>
     </row>
     <row r="728">
@@ -14981,10 +14981,10 @@
         <v>72.63</v>
       </c>
       <c r="E728" t="n">
-        <v>72.88</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="F728" t="n">
-        <v>154875</v>
+        <v>152160</v>
       </c>
     </row>
     <row r="729">
@@ -15061,10 +15061,10 @@
         <v>74.72</v>
       </c>
       <c r="E732" t="n">
-        <v>76.52</v>
+        <v>76.63</v>
       </c>
       <c r="F732" t="n">
-        <v>102802</v>
+        <v>100583</v>
       </c>
     </row>
     <row r="733">
@@ -15161,10 +15161,10 @@
         <v>78.33</v>
       </c>
       <c r="E737" t="n">
-        <v>78.86</v>
+        <v>78.97</v>
       </c>
       <c r="F737" t="n">
-        <v>105405</v>
+        <v>103669</v>
       </c>
     </row>
     <row r="738">
@@ -15261,10 +15261,10 @@
         <v>79.36</v>
       </c>
       <c r="E742" t="n">
-        <v>81.70999999999999</v>
+        <v>81.65000000000001</v>
       </c>
       <c r="F742" t="n">
-        <v>187943</v>
+        <v>185800</v>
       </c>
     </row>
     <row r="743">
@@ -15281,10 +15281,10 @@
         <v>81.12</v>
       </c>
       <c r="E743" t="n">
-        <v>81.48</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="F743" t="n">
-        <v>160491</v>
+        <v>158852</v>
       </c>
     </row>
     <row r="744">
@@ -15361,10 +15361,10 @@
         <v>83.34999999999999</v>
       </c>
       <c r="E747" t="n">
-        <v>83.61</v>
+        <v>83.45</v>
       </c>
       <c r="F747" t="n">
-        <v>147527</v>
+        <v>145171</v>
       </c>
     </row>
     <row r="748">
@@ -15375,16 +15375,16 @@
         <v>83.68000000000001</v>
       </c>
       <c r="C748" t="n">
-        <v>85.98999999999999</v>
+        <v>85.97</v>
       </c>
       <c r="D748" t="n">
         <v>83.53</v>
       </c>
       <c r="E748" t="n">
-        <v>85.77</v>
+        <v>85.91</v>
       </c>
       <c r="F748" t="n">
-        <v>173518</v>
+        <v>171152</v>
       </c>
     </row>
     <row r="749">
@@ -15458,13 +15458,13 @@
         <v>88.8</v>
       </c>
       <c r="D752" t="n">
-        <v>86.38</v>
+        <v>86.56999999999999</v>
       </c>
       <c r="E752" t="n">
-        <v>86.58</v>
+        <v>86.7</v>
       </c>
       <c r="F752" t="n">
-        <v>169439</v>
+        <v>162890</v>
       </c>
     </row>
     <row r="753">
@@ -15481,10 +15481,10 @@
         <v>85.02</v>
       </c>
       <c r="E753" t="n">
-        <v>86.92</v>
+        <v>86.98</v>
       </c>
       <c r="F753" t="n">
-        <v>225683</v>
+        <v>223066</v>
       </c>
     </row>
     <row r="754">
@@ -15561,10 +15561,10 @@
         <v>87.7</v>
       </c>
       <c r="E757" t="n">
-        <v>88.63</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="F757" t="n">
-        <v>275711</v>
+        <v>270152</v>
       </c>
     </row>
     <row r="758">
@@ -15581,10 +15581,10 @@
         <v>88</v>
       </c>
       <c r="E758" t="n">
-        <v>88.81999999999999</v>
+        <v>88.73</v>
       </c>
       <c r="F758" t="n">
-        <v>278896</v>
+        <v>275262</v>
       </c>
     </row>
     <row r="759">
@@ -15655,16 +15655,16 @@
         <v>88.63</v>
       </c>
       <c r="C762" t="n">
-        <v>90.84999999999999</v>
+        <v>90.73999999999999</v>
       </c>
       <c r="D762" t="n">
         <v>87.59999999999999</v>
       </c>
       <c r="E762" t="n">
-        <v>90.51000000000001</v>
+        <v>90.45999999999999</v>
       </c>
       <c r="F762" t="n">
-        <v>168353</v>
+        <v>163057</v>
       </c>
     </row>
     <row r="763">
@@ -15681,10 +15681,10 @@
         <v>90.67</v>
       </c>
       <c r="E763" t="n">
-        <v>92.14</v>
+        <v>92.54000000000001</v>
       </c>
       <c r="F763" t="n">
-        <v>180147</v>
+        <v>177219</v>
       </c>
     </row>
     <row r="764">
@@ -15761,10 +15761,10 @@
         <v>90.09999999999999</v>
       </c>
       <c r="E767" t="n">
-        <v>90.54000000000001</v>
+        <v>90.66</v>
       </c>
       <c r="F767" t="n">
-        <v>186180</v>
+        <v>183590</v>
       </c>
     </row>
     <row r="768">
@@ -15781,10 +15781,10 @@
         <v>89.66</v>
       </c>
       <c r="E768" t="n">
-        <v>93.8</v>
+        <v>93.81</v>
       </c>
       <c r="F768" t="n">
-        <v>194729</v>
+        <v>189880</v>
       </c>
     </row>
     <row r="769">
@@ -15861,10 +15861,10 @@
         <v>90.34999999999999</v>
       </c>
       <c r="E772" t="n">
-        <v>91.16</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="F772" t="n">
-        <v>212213</v>
+        <v>209775</v>
       </c>
     </row>
     <row r="773">
@@ -15875,7 +15875,7 @@
         <v>90.76000000000001</v>
       </c>
       <c r="C773" t="n">
-        <v>92.28</v>
+        <v>92.15000000000001</v>
       </c>
       <c r="D773" t="n">
         <v>88.64</v>
@@ -15884,7 +15884,7 @@
         <v>91.81</v>
       </c>
       <c r="F773" t="n">
-        <v>194995</v>
+        <v>190175</v>
       </c>
     </row>
     <row r="774">
@@ -15961,10 +15961,10 @@
         <v>93.94</v>
       </c>
       <c r="E777" t="n">
-        <v>95.41</v>
+        <v>95.61</v>
       </c>
       <c r="F777" t="n">
-        <v>313423</v>
+        <v>309076</v>
       </c>
     </row>
     <row r="778">
@@ -15981,10 +15981,10 @@
         <v>92.55</v>
       </c>
       <c r="E778" t="n">
-        <v>94.23</v>
+        <v>94.69</v>
       </c>
       <c r="F778" t="n">
-        <v>237786</v>
+        <v>233541</v>
       </c>
     </row>
     <row r="779">
@@ -16061,10 +16061,10 @@
         <v>108.17</v>
       </c>
       <c r="E782" t="n">
-        <v>109.27</v>
+        <v>109.72</v>
       </c>
       <c r="F782" t="n">
-        <v>233799</v>
+        <v>231064</v>
       </c>
     </row>
     <row r="783">
@@ -16081,10 +16081,10 @@
         <v>108.47</v>
       </c>
       <c r="E783" t="n">
-        <v>116.7</v>
+        <v>117.14</v>
       </c>
       <c r="F783" t="n">
-        <v>210974</v>
+        <v>204618</v>
       </c>
     </row>
     <row r="784">
@@ -16161,10 +16161,10 @@
         <v>107.05</v>
       </c>
       <c r="E787" t="n">
-        <v>107.11</v>
+        <v>107.97</v>
       </c>
       <c r="F787" t="n">
-        <v>173653</v>
+        <v>170481</v>
       </c>
     </row>
     <row r="788">
@@ -16181,10 +16181,10 @@
         <v>104.96</v>
       </c>
       <c r="E788" t="n">
-        <v>110.14</v>
+        <v>110.51</v>
       </c>
       <c r="F788" t="n">
-        <v>157669</v>
+        <v>154891</v>
       </c>
     </row>
     <row r="789">
@@ -16252,19 +16252,19 @@
         <v>44637</v>
       </c>
       <c r="B792" t="n">
-        <v>96.70999999999999</v>
+        <v>96.98</v>
       </c>
       <c r="C792" t="n">
         <v>105.3</v>
       </c>
       <c r="D792" t="n">
-        <v>96.70999999999999</v>
+        <v>96.11</v>
       </c>
       <c r="E792" t="n">
         <v>104.46</v>
       </c>
       <c r="F792" t="n">
-        <v>172578</v>
+        <v>176604</v>
       </c>
     </row>
     <row r="793">
@@ -16272,7 +16272,7 @@
         <v>44638</v>
       </c>
       <c r="B793" t="n">
-        <v>105.16</v>
+        <v>104.55</v>
       </c>
       <c r="C793" t="n">
         <v>107.23</v>
@@ -16284,7 +16284,7 @@
         <v>105.63</v>
       </c>
       <c r="F793" t="n">
-        <v>155067</v>
+        <v>158531</v>
       </c>
     </row>
     <row r="794">
@@ -16352,7 +16352,7 @@
         <v>44644</v>
       </c>
       <c r="B797" t="n">
-        <v>119.49</v>
+        <v>118.08</v>
       </c>
       <c r="C797" t="n">
         <v>120.04</v>
@@ -16364,7 +16364,7 @@
         <v>114.47</v>
       </c>
       <c r="F797" t="n">
-        <v>206598</v>
+        <v>215337</v>
       </c>
     </row>
     <row r="798">
@@ -16372,7 +16372,7 @@
         <v>44645</v>
       </c>
       <c r="B798" t="n">
-        <v>114.52</v>
+        <v>115.3</v>
       </c>
       <c r="C798" t="n">
         <v>117.69</v>
@@ -16384,7 +16384,7 @@
         <v>115.94</v>
       </c>
       <c r="F798" t="n">
-        <v>189095</v>
+        <v>195807</v>
       </c>
     </row>
     <row r="799">
@@ -16461,10 +16461,10 @@
         <v>103.71</v>
       </c>
       <c r="E802" t="n">
-        <v>104.99</v>
+        <v>104.6</v>
       </c>
       <c r="F802" t="n">
-        <v>220967</v>
+        <v>217472</v>
       </c>
     </row>
     <row r="803">
@@ -16481,10 +16481,10 @@
         <v>101.94</v>
       </c>
       <c r="E803" t="n">
-        <v>103.88</v>
+        <v>104.13</v>
       </c>
       <c r="F803" t="n">
-        <v>181758</v>
+        <v>179677</v>
       </c>
     </row>
     <row r="804">
@@ -16561,10 +16561,10 @@
         <v>98.2</v>
       </c>
       <c r="E807" t="n">
-        <v>100.96</v>
+        <v>100.94</v>
       </c>
       <c r="F807" t="n">
-        <v>186163</v>
+        <v>183922</v>
       </c>
     </row>
     <row r="808">
@@ -16581,10 +16581,10 @@
         <v>99.28</v>
       </c>
       <c r="E808" t="n">
-        <v>101.81</v>
+        <v>102.16</v>
       </c>
       <c r="F808" t="n">
-        <v>162819</v>
+        <v>159821</v>
       </c>
     </row>
     <row r="809">
@@ -16661,10 +16661,10 @@
         <v>106.14</v>
       </c>
       <c r="E812" t="n">
-        <v>110.62</v>
+        <v>110.56</v>
       </c>
       <c r="F812" t="n">
-        <v>159785</v>
+        <v>156524</v>
       </c>
     </row>
     <row r="813">
@@ -16741,10 +16741,10 @@
         <v>106.38</v>
       </c>
       <c r="E816" t="n">
-        <v>108</v>
+        <v>107.93</v>
       </c>
       <c r="F816" t="n">
-        <v>188001</v>
+        <v>184241</v>
       </c>
     </row>
     <row r="817">
@@ -16758,13 +16758,13 @@
         <v>108.41</v>
       </c>
       <c r="D817" t="n">
-        <v>105.05</v>
+        <v>105.44</v>
       </c>
       <c r="E817" t="n">
-        <v>105.7</v>
+        <v>105.6</v>
       </c>
       <c r="F817" t="n">
-        <v>165632</v>
+        <v>162032</v>
       </c>
     </row>
     <row r="818">
@@ -16841,10 +16841,10 @@
         <v>102.74</v>
       </c>
       <c r="E821" t="n">
-        <v>106.8</v>
+        <v>107.25</v>
       </c>
       <c r="F821" t="n">
-        <v>170514</v>
+        <v>167676</v>
       </c>
     </row>
     <row r="822">
@@ -16861,10 +16861,10 @@
         <v>105.92</v>
       </c>
       <c r="E822" t="n">
-        <v>106.06</v>
+        <v>106.38</v>
       </c>
       <c r="F822" t="n">
-        <v>186051</v>
+        <v>182972</v>
       </c>
     </row>
     <row r="823">
@@ -16941,10 +16941,10 @@
         <v>108.66</v>
       </c>
       <c r="E826" t="n">
-        <v>110.4</v>
+        <v>110.3</v>
       </c>
       <c r="F826" t="n">
-        <v>201234</v>
+        <v>197687</v>
       </c>
     </row>
     <row r="827">
@@ -16961,10 +16961,10 @@
         <v>109.21</v>
       </c>
       <c r="E827" t="n">
-        <v>112.22</v>
+        <v>112.44</v>
       </c>
       <c r="F827" t="n">
-        <v>207851</v>
+        <v>203469</v>
       </c>
     </row>
     <row r="828">
@@ -17041,10 +17041,10 @@
         <v>103.97</v>
       </c>
       <c r="E831" t="n">
-        <v>106.86</v>
+        <v>107.38</v>
       </c>
       <c r="F831" t="n">
-        <v>243371</v>
+        <v>240901</v>
       </c>
     </row>
     <row r="832">
@@ -17061,10 +17061,10 @@
         <v>106.88</v>
       </c>
       <c r="E832" t="n">
-        <v>109.76</v>
+        <v>110.4</v>
       </c>
       <c r="F832" t="n">
-        <v>193013</v>
+        <v>190398</v>
       </c>
     </row>
     <row r="833">
@@ -17141,10 +17141,10 @@
         <v>104.22</v>
       </c>
       <c r="E836" t="n">
-        <v>109.5</v>
+        <v>109.59</v>
       </c>
       <c r="F836" t="n">
-        <v>250583</v>
+        <v>247278</v>
       </c>
     </row>
     <row r="837">
@@ -17161,10 +17161,10 @@
         <v>108.65</v>
       </c>
       <c r="E837" t="n">
-        <v>110.3</v>
+        <v>110.87</v>
       </c>
       <c r="F837" t="n">
-        <v>202895</v>
+        <v>198948</v>
       </c>
     </row>
     <row r="838">
@@ -17241,10 +17241,10 @@
         <v>110.83</v>
       </c>
       <c r="E841" t="n">
-        <v>114.15</v>
+        <v>114</v>
       </c>
       <c r="F841" t="n">
-        <v>175003</v>
+        <v>171535</v>
       </c>
     </row>
     <row r="842">
@@ -17261,10 +17261,10 @@
         <v>113.01</v>
       </c>
       <c r="E842" t="n">
-        <v>115.01</v>
+        <v>115.42</v>
       </c>
       <c r="F842" t="n">
-        <v>213418</v>
+        <v>210750</v>
       </c>
     </row>
     <row r="843">
@@ -17335,16 +17335,16 @@
         <v>113.88</v>
       </c>
       <c r="C846" t="n">
-        <v>117.74</v>
+        <v>117.57</v>
       </c>
       <c r="D846" t="n">
         <v>111.85</v>
       </c>
       <c r="E846" t="n">
-        <v>117.31</v>
+        <v>117.26</v>
       </c>
       <c r="F846" t="n">
-        <v>138282</v>
+        <v>137013</v>
       </c>
     </row>
     <row r="847">
@@ -17355,16 +17355,16 @@
         <v>117.37</v>
       </c>
       <c r="C847" t="n">
-        <v>120.6</v>
+        <v>120.57</v>
       </c>
       <c r="D847" t="n">
         <v>115.28</v>
       </c>
       <c r="E847" t="n">
-        <v>120.23</v>
+        <v>120.41</v>
       </c>
       <c r="F847" t="n">
-        <v>91626</v>
+        <v>90339</v>
       </c>
     </row>
     <row r="848">
@@ -17441,10 +17441,10 @@
         <v>121.23</v>
       </c>
       <c r="E851" t="n">
-        <v>121.41</v>
+        <v>121.71</v>
       </c>
       <c r="F851" t="n">
-        <v>176648</v>
+        <v>174232</v>
       </c>
     </row>
     <row r="852">
@@ -17461,10 +17461,10 @@
         <v>118.31</v>
       </c>
       <c r="E852" t="n">
-        <v>120.02</v>
+        <v>120.29</v>
       </c>
       <c r="F852" t="n">
-        <v>192334</v>
+        <v>190410</v>
       </c>
     </row>
     <row r="853">
@@ -17541,10 +17541,10 @@
         <v>113.72</v>
       </c>
       <c r="E856" t="n">
-        <v>116.92</v>
+        <v>117.15</v>
       </c>
       <c r="F856" t="n">
-        <v>231324</v>
+        <v>228931</v>
       </c>
     </row>
     <row r="857">
@@ -17561,10 +17561,10 @@
         <v>109.77</v>
       </c>
       <c r="E857" t="n">
-        <v>111.27</v>
+        <v>111.29</v>
       </c>
       <c r="F857" t="n">
-        <v>236868</v>
+        <v>233588</v>
       </c>
     </row>
     <row r="858">
@@ -17641,10 +17641,10 @@
         <v>105.25</v>
       </c>
       <c r="E861" t="n">
-        <v>106.13</v>
+        <v>106.29</v>
       </c>
       <c r="F861" t="n">
-        <v>234952</v>
+        <v>233040</v>
       </c>
     </row>
     <row r="862">
@@ -17661,10 +17661,10 @@
         <v>105.78</v>
       </c>
       <c r="E862" t="n">
-        <v>108.33</v>
+        <v>109.13</v>
       </c>
       <c r="F862" t="n">
-        <v>205227</v>
+        <v>202836</v>
       </c>
     </row>
     <row r="863">
@@ -17741,10 +17741,10 @@
         <v>107.7</v>
       </c>
       <c r="E866" t="n">
-        <v>108.43</v>
+        <v>108.69</v>
       </c>
       <c r="F866" t="n">
-        <v>212070</v>
+        <v>208599</v>
       </c>
     </row>
     <row r="867">
@@ -17761,10 +17761,10 @@
         <v>107.32</v>
       </c>
       <c r="E867" t="n">
-        <v>110.43</v>
+        <v>110.56</v>
       </c>
       <c r="F867" t="n">
-        <v>210630</v>
+        <v>209195</v>
       </c>
     </row>
     <row r="868">
@@ -17841,10 +17841,10 @@
         <v>97.11</v>
       </c>
       <c r="E871" t="n">
-        <v>102.32</v>
+        <v>102.75</v>
       </c>
       <c r="F871" t="n">
-        <v>224620</v>
+        <v>221862</v>
       </c>
     </row>
     <row r="872">
@@ -17861,10 +17861,10 @@
         <v>102.16</v>
       </c>
       <c r="E872" t="n">
-        <v>105.2</v>
+        <v>105.32</v>
       </c>
       <c r="F872" t="n">
-        <v>237030</v>
+        <v>235167</v>
       </c>
     </row>
     <row r="873">
@@ -17941,10 +17941,10 @@
         <v>92.42</v>
       </c>
       <c r="E876" t="n">
-        <v>97.12</v>
+        <v>97.17</v>
       </c>
       <c r="F876" t="n">
-        <v>217836</v>
+        <v>215919</v>
       </c>
     </row>
     <row r="877">
@@ -17961,10 +17961,10 @@
         <v>95.59</v>
       </c>
       <c r="E877" t="n">
-        <v>97.98</v>
+        <v>98.34999999999999</v>
       </c>
       <c r="F877" t="n">
-        <v>203134</v>
+        <v>200270</v>
       </c>
     </row>
     <row r="878">
@@ -18041,10 +18041,10 @@
         <v>97.86</v>
       </c>
       <c r="E881" t="n">
-        <v>99.93000000000001</v>
+        <v>100.04</v>
       </c>
       <c r="F881" t="n">
-        <v>229298</v>
+        <v>227231</v>
       </c>
     </row>
     <row r="882">
@@ -18061,10 +18061,10 @@
         <v>97.90000000000001</v>
       </c>
       <c r="E882" t="n">
-        <v>98.98999999999999</v>
+        <v>98.67</v>
       </c>
       <c r="F882" t="n">
-        <v>226135</v>
+        <v>222921</v>
       </c>
     </row>
     <row r="883">
@@ -18141,10 +18141,10 @@
         <v>100.74</v>
       </c>
       <c r="E886" t="n">
-        <v>101.99</v>
+        <v>101.93</v>
       </c>
       <c r="F886" t="n">
-        <v>132446</v>
+        <v>130398</v>
       </c>
     </row>
     <row r="887">
@@ -18161,10 +18161,10 @@
         <v>101.27</v>
       </c>
       <c r="E887" t="n">
-        <v>103.1</v>
+        <v>103.21</v>
       </c>
       <c r="F887" t="n">
-        <v>113461</v>
+        <v>112179</v>
       </c>
     </row>
     <row r="888">
@@ -18238,13 +18238,13 @@
         <v>97.17</v>
       </c>
       <c r="D891" t="n">
-        <v>92.5</v>
+        <v>92.73</v>
       </c>
       <c r="E891" t="n">
-        <v>92.52</v>
+        <v>93.38</v>
       </c>
       <c r="F891" t="n">
-        <v>162676</v>
+        <v>160629</v>
       </c>
     </row>
     <row r="892">
@@ -18261,10 +18261,10 @@
         <v>92.15000000000001</v>
       </c>
       <c r="E892" t="n">
-        <v>93.51000000000001</v>
+        <v>93.69</v>
       </c>
       <c r="F892" t="n">
-        <v>157322</v>
+        <v>155701</v>
       </c>
     </row>
     <row r="893">
@@ -18341,10 +18341,10 @@
         <v>96.08</v>
       </c>
       <c r="E896" t="n">
-        <v>98.31</v>
+        <v>98.66</v>
       </c>
       <c r="F896" t="n">
-        <v>140818</v>
+        <v>139272</v>
       </c>
     </row>
     <row r="897">
@@ -18361,10 +18361,10 @@
         <v>96.26000000000001</v>
       </c>
       <c r="E897" t="n">
-        <v>96.89</v>
+        <v>97.3</v>
       </c>
       <c r="F897" t="n">
-        <v>145858</v>
+        <v>144235</v>
       </c>
     </row>
     <row r="898">
@@ -18441,10 +18441,10 @@
         <v>92.55</v>
       </c>
       <c r="E901" t="n">
-        <v>95.56</v>
+        <v>95.93000000000001</v>
       </c>
       <c r="F901" t="n">
-        <v>123861</v>
+        <v>122235</v>
       </c>
     </row>
     <row r="902">
@@ -18461,10 +18461,10 @@
         <v>93.7</v>
       </c>
       <c r="E902" t="n">
-        <v>95.08</v>
+        <v>95.52</v>
       </c>
       <c r="F902" t="n">
-        <v>126696</v>
+        <v>125387</v>
       </c>
     </row>
     <row r="903">
@@ -18541,10 +18541,10 @@
         <v>98.23</v>
       </c>
       <c r="E906" t="n">
-        <v>98.68000000000001</v>
+        <v>99.05</v>
       </c>
       <c r="F906" t="n">
-        <v>115830</v>
+        <v>114289</v>
       </c>
     </row>
     <row r="907">
@@ -18561,10 +18561,10 @@
         <v>96.92</v>
       </c>
       <c r="E907" t="n">
-        <v>98.56999999999999</v>
+        <v>98.70999999999999</v>
       </c>
       <c r="F907" t="n">
-        <v>128357</v>
+        <v>127109</v>
       </c>
     </row>
     <row r="908">
@@ -18641,10 +18641,10 @@
         <v>91.58</v>
       </c>
       <c r="E911" t="n">
-        <v>91.59</v>
+        <v>91.75</v>
       </c>
       <c r="F911" t="n">
-        <v>172611</v>
+        <v>171383</v>
       </c>
     </row>
     <row r="912">
@@ -18661,10 +18661,10 @@
         <v>92.41</v>
       </c>
       <c r="E912" t="n">
-        <v>92.83</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="F912" t="n">
-        <v>164349</v>
+        <v>162523</v>
       </c>
     </row>
     <row r="913">
@@ -18741,10 +18741,10 @@
         <v>86.86</v>
       </c>
       <c r="E916" t="n">
-        <v>87.73999999999999</v>
+        <v>88.03</v>
       </c>
       <c r="F916" t="n">
-        <v>175783</v>
+        <v>174104</v>
       </c>
     </row>
     <row r="917">
@@ -18761,10 +18761,10 @@
         <v>88.09</v>
       </c>
       <c r="E917" t="n">
-        <v>91.42</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="F917" t="n">
-        <v>139210</v>
+        <v>137562</v>
       </c>
     </row>
     <row r="918">
@@ -18841,10 +18841,10 @@
         <v>89.39</v>
       </c>
       <c r="E921" t="n">
-        <v>89.78</v>
+        <v>90.08</v>
       </c>
       <c r="F921" t="n">
-        <v>179533</v>
+        <v>177670</v>
       </c>
     </row>
     <row r="922">
@@ -18861,10 +18861,10 @@
         <v>89.37</v>
       </c>
       <c r="E922" t="n">
-        <v>90.36</v>
+        <v>90.58</v>
       </c>
       <c r="F922" t="n">
-        <v>177056</v>
+        <v>175462</v>
       </c>
     </row>
     <row r="923">
@@ -18941,10 +18941,10 @@
         <v>88.38</v>
       </c>
       <c r="E926" t="n">
-        <v>89.48999999999999</v>
+        <v>89.53</v>
       </c>
       <c r="F926" t="n">
-        <v>169282</v>
+        <v>167346</v>
       </c>
     </row>
     <row r="927">
@@ -18961,10 +18961,10 @@
         <v>84.61</v>
       </c>
       <c r="E927" t="n">
-        <v>85.65000000000001</v>
+        <v>85.41</v>
       </c>
       <c r="F927" t="n">
-        <v>159709</v>
+        <v>157358</v>
       </c>
     </row>
     <row r="928">
@@ -19041,10 +19041,10 @@
         <v>85.98</v>
       </c>
       <c r="E931" t="n">
-        <v>87.22</v>
+        <v>87.20999999999999</v>
       </c>
       <c r="F931" t="n">
-        <v>184095</v>
+        <v>182346</v>
       </c>
     </row>
     <row r="932">
@@ -19061,10 +19061,10 @@
         <v>84.73999999999999</v>
       </c>
       <c r="E932" t="n">
-        <v>85.04000000000001</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="F932" t="n">
-        <v>174184</v>
+        <v>172540</v>
       </c>
     </row>
     <row r="933">
@@ -19141,10 +19141,10 @@
         <v>92.09</v>
       </c>
       <c r="E936" t="n">
-        <v>94.16</v>
+        <v>94.31999999999999</v>
       </c>
       <c r="F936" t="n">
-        <v>136157</v>
+        <v>134269</v>
       </c>
     </row>
     <row r="937">
@@ -19161,10 +19161,10 @@
         <v>93.25</v>
       </c>
       <c r="E937" t="n">
-        <v>97.59</v>
+        <v>96.95</v>
       </c>
       <c r="F937" t="n">
-        <v>161145</v>
+        <v>158303</v>
       </c>
     </row>
     <row r="938">
@@ -19241,10 +19241,10 @@
         <v>90.18000000000001</v>
       </c>
       <c r="E941" t="n">
-        <v>93.67</v>
+        <v>93.61</v>
       </c>
       <c r="F941" t="n">
-        <v>189909</v>
+        <v>187899</v>
       </c>
     </row>
     <row r="942">
@@ -19261,10 +19261,10 @@
         <v>90.34</v>
       </c>
       <c r="E942" t="n">
-        <v>90.66</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="F942" t="n">
-        <v>186342</v>
+        <v>184164</v>
       </c>
     </row>
     <row r="943">
@@ -19341,10 +19341,10 @@
         <v>90.34</v>
       </c>
       <c r="E946" t="n">
-        <v>91.11</v>
+        <v>91</v>
       </c>
       <c r="F946" t="n">
-        <v>172151</v>
+        <v>169394</v>
       </c>
     </row>
     <row r="947">
@@ -19361,10 +19361,10 @@
         <v>89.40000000000001</v>
       </c>
       <c r="E947" t="n">
-        <v>91.58</v>
+        <v>91.7</v>
       </c>
       <c r="F947" t="n">
-        <v>170499</v>
+        <v>168937</v>
       </c>
     </row>
     <row r="948">
@@ -19441,10 +19441,10 @@
         <v>93.06999999999999</v>
       </c>
       <c r="E951" t="n">
-        <v>94.45999999999999</v>
+        <v>94.91</v>
       </c>
       <c r="F951" t="n">
-        <v>135151</v>
+        <v>130846</v>
       </c>
     </row>
     <row r="952">
@@ -19461,10 +19461,10 @@
         <v>92.81999999999999</v>
       </c>
       <c r="E952" t="n">
-        <v>93.95</v>
+        <v>93.81</v>
       </c>
       <c r="F952" t="n">
-        <v>135363</v>
+        <v>133960</v>
       </c>
     </row>
     <row r="953">
@@ -19532,7 +19532,7 @@
         <v>44868</v>
       </c>
       <c r="B956" t="n">
-        <v>94.84</v>
+        <v>94.81</v>
       </c>
 